--- a/data/picks.xlsx
+++ b/data/picks.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CA6" headerRowCount="1">
-  <autoFilter ref="A1:CA6"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CA10" headerRowCount="1">
+  <autoFilter ref="A1:CA10"/>
   <tableColumns count="79">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -738,19 +738,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$6)</f>
+        <f>COUNTA('Picks'!$A$2:$A$10)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$6,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$10,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$6,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$10,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$6,"settled",'Picks'!$V$2:$V$6,"win")+COUNTIFS('Picks'!$U$2:$U$6,"settled",'Picks'!$V$2:$V$6,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"win")+COUNTIFS('Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -778,19 +778,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$6,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$10,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$6,"&gt;0",'Picks'!$V$2:$V$6,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$6,"&gt;0",'Picks'!$V$2:$V$6,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$10,"&gt;0",'Picks'!$V$2:$V$10,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$10,"&gt;0",'Picks'!$V$2:$V$10,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$6,"&gt;0",'Picks'!$V$2:$V$6,"win")/(COUNTIFS('Picks'!$BX$2:$BX$6,"&gt;0",'Picks'!$V$2:$V$6,"win")+COUNTIFS('Picks'!$BX$2:$BX$6,"&gt;0",'Picks'!$V$2:$V$6,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$10,"&gt;0",'Picks'!$V$2:$V$10,"win")/(COUNTIFS('Picks'!$BX$2:$BX$10,"&gt;0",'Picks'!$V$2:$V$10,"win")+COUNTIFS('Picks'!$BX$2:$BX$10,"&gt;0",'Picks'!$V$2:$V$10,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$6)/SUM('Picks'!$BX$2:$BX$6),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$10)/SUM('Picks'!$BX$2:$BX$10),0)</f>
         <v/>
       </c>
     </row>
@@ -818,19 +818,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$6)</f>
+        <f>SUM('Picks'!$BY$2:$BY$10)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$6,"&lt;&gt;",'Picks'!$AB$2:$AB$6),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$10,"&lt;&gt;",'Picks'!$AB$2:$AB$10),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$6,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$6,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$10,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$10,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$6,'Picks'!$AM$2:$AM$6,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$10,'Picks'!$AM$2:$AM$10,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -885,15 +885,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$6,$A14,'Picks'!$U$2:$U$6,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$10,$A14,'Picks'!$U$2:$U$10,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$6,$A14,'Picks'!$U$2:$U$6,"settled",'Picks'!$V$2:$V$6,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$10,$A14,'Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$6,$A14,'Picks'!$U$2:$U$6,"settled",'Picks'!$V$2:$V$6,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$10,$A14,'Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -901,11 +901,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$6,'Picks'!$H$2:$H$6,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$10,'Picks'!$H$2:$H$10,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$6,'Picks'!$H$2:$H$6,$A14,'Picks'!$U$2:$U$6,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$10,'Picks'!$H$2:$H$10,$A14,'Picks'!$U$2:$U$10,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -916,15 +916,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$6,$A15,'Picks'!$U$2:$U$6,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$10,$A15,'Picks'!$U$2:$U$10,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$6,$A15,'Picks'!$U$2:$U$6,"settled",'Picks'!$V$2:$V$6,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$10,$A15,'Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$6,$A15,'Picks'!$U$2:$U$6,"settled",'Picks'!$V$2:$V$6,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$10,$A15,'Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -932,11 +932,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$6,'Picks'!$H$2:$H$6,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$10,'Picks'!$H$2:$H$10,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$6,'Picks'!$H$2:$H$6,$A15,'Picks'!$U$2:$U$6,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$10,'Picks'!$H$2:$H$10,$A15,'Picks'!$U$2:$U$10,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -947,15 +947,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$6,$A16,'Picks'!$U$2:$U$6,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$10,$A16,'Picks'!$U$2:$U$10,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$6,$A16,'Picks'!$U$2:$U$6,"settled",'Picks'!$V$2:$V$6,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$10,$A16,'Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$6,$A16,'Picks'!$U$2:$U$6,"settled",'Picks'!$V$2:$V$6,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$10,$A16,'Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -963,11 +963,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$6,'Picks'!$H$2:$H$6,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$10,'Picks'!$H$2:$H$10,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$6,'Picks'!$H$2:$H$6,$A16,'Picks'!$U$2:$U$6,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$10,'Picks'!$H$2:$H$10,$A16,'Picks'!$U$2:$U$10,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -996,7 +996,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CA6"/>
+  <dimension ref="A1:CA10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2722,6 +2722,1002 @@
       <c r="BZ6" s="24" t="n"/>
       <c r="CA6" s="31" t="n"/>
     </row>
+    <row r="7" ht="36" customHeight="1">
+      <c r="A7" s="24" t="inlineStr">
+        <is>
+          <t>d0e98df55d684f7a</t>
+        </is>
+      </c>
+      <c r="B7" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-17T14:02:14.862720Z</t>
+        </is>
+      </c>
+      <c r="C7" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-17T23:40Z</t>
+        </is>
+      </c>
+      <c r="D7" s="24" t="inlineStr">
+        <is>
+          <t>401816148</t>
+        </is>
+      </c>
+      <c r="E7" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F7" s="24" t="inlineStr">
+        <is>
+          <t>Miami Marlins</t>
+        </is>
+      </c>
+      <c r="G7" s="24" t="inlineStr">
+        <is>
+          <t>Milwaukee Brewers</t>
+        </is>
+      </c>
+      <c r="H7" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I7" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J7" s="25" t="n"/>
+      <c r="K7" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L7" s="26" t="n">
+        <v>-141</v>
+      </c>
+      <c r="M7" s="27" t="n">
+        <v>1.70922</v>
+      </c>
+      <c r="N7" s="28" t="n">
+        <v>0.585062</v>
+      </c>
+      <c r="O7" s="28" t="n">
+        <v>0.605633</v>
+      </c>
+      <c r="P7" s="28" t="n"/>
+      <c r="Q7" s="28" t="n">
+        <v>0.020571</v>
+      </c>
+      <c r="R7" s="26" t="n">
+        <v>60</v>
+      </c>
+      <c r="S7" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="U7" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V7" s="24" t="n"/>
+      <c r="W7" s="26" t="n"/>
+      <c r="X7" s="26" t="n"/>
+      <c r="Y7" s="25" t="n"/>
+      <c r="Z7" s="26" t="n"/>
+      <c r="AA7" s="28" t="n"/>
+      <c r="AB7" s="28" t="n"/>
+      <c r="AC7" s="30" t="n"/>
+      <c r="AD7" s="24" t="n"/>
+      <c r="AE7" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.6018; executable ask 0.5850 (aec-mlb-mia-mil-2026-07-17).</t>
+        </is>
+      </c>
+      <c r="AF7" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
+        </is>
+      </c>
+      <c r="AG7" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH7" s="24" t="n"/>
+      <c r="AI7" s="31" t="n"/>
+      <c r="AJ7" s="31" t="n"/>
+      <c r="AK7" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL7" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM7" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN7" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO7" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MISSING_UNCERTAINTY</t>
+        </is>
+      </c>
+      <c r="AP7" s="24" t="inlineStr">
+        <is>
+          <t>mlb-mia</t>
+        </is>
+      </c>
+      <c r="AQ7" s="24" t="inlineStr">
+        <is>
+          <t>Miami Marlins</t>
+        </is>
+      </c>
+      <c r="AR7" s="24" t="inlineStr">
+        <is>
+          <t>Miami Marlins</t>
+        </is>
+      </c>
+      <c r="AS7" s="24" t="inlineStr">
+        <is>
+          <t>mlb-mil</t>
+        </is>
+      </c>
+      <c r="AT7" s="24" t="inlineStr">
+        <is>
+          <t>Milwaukee Brewers</t>
+        </is>
+      </c>
+      <c r="AU7" s="24" t="inlineStr">
+        <is>
+          <t>Milwaukee Brewers</t>
+        </is>
+      </c>
+      <c r="AV7" s="24" t="n"/>
+      <c r="AW7" s="24" t="n"/>
+      <c r="AX7" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY7" s="24" t="n"/>
+      <c r="AZ7" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA7" s="24" t="inlineStr">
+        <is>
+          <t>a454281ab207d2924d585d6b967363fb8e88af45132e3e9d354e4351fb5c237f</t>
+        </is>
+      </c>
+      <c r="BB7" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC7" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BD7" s="24" t="inlineStr">
+        <is>
+          <t>a454281ab207d2924d585d6b967363fb8e88af45132e3e9d354e4351fb5c237f</t>
+        </is>
+      </c>
+      <c r="BE7" s="24" t="inlineStr">
+        <is>
+          <t>27ad4a1da893e4b8</t>
+        </is>
+      </c>
+      <c r="BF7" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG7" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BH7" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-17T14:01:56.626918Z</t>
+        </is>
+      </c>
+      <c r="BI7" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ7" s="25" t="n"/>
+      <c r="BK7" s="26" t="n">
+        <v>-141</v>
+      </c>
+      <c r="BL7" s="27" t="n">
+        <v>1.70922</v>
+      </c>
+      <c r="BM7" s="28" t="n">
+        <v>0.585062</v>
+      </c>
+      <c r="BN7" s="28" t="n">
+        <v>0.58209</v>
+      </c>
+      <c r="BO7" s="28" t="n"/>
+      <c r="BP7" s="25" t="n"/>
+      <c r="BQ7" s="27" t="n"/>
+      <c r="BR7" s="28" t="n"/>
+      <c r="BS7" s="28" t="n"/>
+      <c r="BT7" s="28" t="n"/>
+      <c r="BU7" s="25" t="n"/>
+      <c r="BV7" s="29" t="n"/>
+      <c r="BW7" s="24" t="n"/>
+      <c r="BX7" s="30" t="n"/>
+      <c r="BY7" s="27" t="n"/>
+      <c r="BZ7" s="24" t="n"/>
+      <c r="CA7" s="31" t="n"/>
+    </row>
+    <row r="8" ht="36" customHeight="1">
+      <c r="A8" s="24" t="inlineStr">
+        <is>
+          <t>3b98081a1ff04c62</t>
+        </is>
+      </c>
+      <c r="B8" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-17T14:02:14.862720Z</t>
+        </is>
+      </c>
+      <c r="C8" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-18T00:05Z</t>
+        </is>
+      </c>
+      <c r="D8" s="24" t="inlineStr">
+        <is>
+          <t>401816149</t>
+        </is>
+      </c>
+      <c r="E8" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F8" s="24" t="inlineStr">
+        <is>
+          <t>Minnesota Twins</t>
+        </is>
+      </c>
+      <c r="G8" s="24" t="inlineStr">
+        <is>
+          <t>Chicago Cubs</t>
+        </is>
+      </c>
+      <c r="H8" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I8" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J8" s="25" t="n"/>
+      <c r="K8" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L8" s="26" t="n">
+        <v>-130</v>
+      </c>
+      <c r="M8" s="27" t="n">
+        <v>1.769231</v>
+      </c>
+      <c r="N8" s="28" t="n">
+        <v>0.565217</v>
+      </c>
+      <c r="O8" s="28" t="n">
+        <v>0.606876</v>
+      </c>
+      <c r="P8" s="28" t="n"/>
+      <c r="Q8" s="28" t="n">
+        <v>0.041659</v>
+      </c>
+      <c r="R8" s="26" t="n">
+        <v>71</v>
+      </c>
+      <c r="S8" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="U8" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V8" s="24" t="n"/>
+      <c r="W8" s="26" t="n"/>
+      <c r="X8" s="26" t="n"/>
+      <c r="Y8" s="25" t="n"/>
+      <c r="Z8" s="26" t="n"/>
+      <c r="AA8" s="28" t="n"/>
+      <c r="AB8" s="28" t="n"/>
+      <c r="AC8" s="30" t="n"/>
+      <c r="AD8" s="24" t="n"/>
+      <c r="AE8" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.6018; executable ask 0.5650 (aec-mlb-min-chc-2026-07-17).</t>
+        </is>
+      </c>
+      <c r="AF8" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
+        </is>
+      </c>
+      <c r="AG8" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH8" s="24" t="n"/>
+      <c r="AI8" s="31" t="n"/>
+      <c r="AJ8" s="31" t="n"/>
+      <c r="AK8" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL8" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM8" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN8" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO8" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MISSING_UNCERTAINTY</t>
+        </is>
+      </c>
+      <c r="AP8" s="24" t="inlineStr">
+        <is>
+          <t>mlb-min</t>
+        </is>
+      </c>
+      <c r="AQ8" s="24" t="inlineStr">
+        <is>
+          <t>Minnesota Twins</t>
+        </is>
+      </c>
+      <c r="AR8" s="24" t="inlineStr">
+        <is>
+          <t>Minnesota Twins</t>
+        </is>
+      </c>
+      <c r="AS8" s="24" t="inlineStr">
+        <is>
+          <t>mlb-chc</t>
+        </is>
+      </c>
+      <c r="AT8" s="24" t="inlineStr">
+        <is>
+          <t>Chicago Cubs</t>
+        </is>
+      </c>
+      <c r="AU8" s="24" t="inlineStr">
+        <is>
+          <t>Chicago Cubs</t>
+        </is>
+      </c>
+      <c r="AV8" s="24" t="n"/>
+      <c r="AW8" s="24" t="n"/>
+      <c r="AX8" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY8" s="24" t="n"/>
+      <c r="AZ8" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA8" s="24" t="inlineStr">
+        <is>
+          <t>a454281ab207d2924d585d6b967363fb8e88af45132e3e9d354e4351fb5c237f</t>
+        </is>
+      </c>
+      <c r="BB8" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC8" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BD8" s="24" t="inlineStr">
+        <is>
+          <t>a454281ab207d2924d585d6b967363fb8e88af45132e3e9d354e4351fb5c237f</t>
+        </is>
+      </c>
+      <c r="BE8" s="24" t="inlineStr">
+        <is>
+          <t>8438bc3f26be5eae</t>
+        </is>
+      </c>
+      <c r="BF8" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG8" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BH8" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-17T14:01:57.663980Z</t>
+        </is>
+      </c>
+      <c r="BI8" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ8" s="25" t="n"/>
+      <c r="BK8" s="26" t="n">
+        <v>-130</v>
+      </c>
+      <c r="BL8" s="27" t="n">
+        <v>1.769231</v>
+      </c>
+      <c r="BM8" s="28" t="n">
+        <v>0.565217</v>
+      </c>
+      <c r="BN8" s="28" t="n">
+        <v>0.562189</v>
+      </c>
+      <c r="BO8" s="28" t="n"/>
+      <c r="BP8" s="25" t="n"/>
+      <c r="BQ8" s="27" t="n"/>
+      <c r="BR8" s="28" t="n"/>
+      <c r="BS8" s="28" t="n"/>
+      <c r="BT8" s="28" t="n"/>
+      <c r="BU8" s="25" t="n"/>
+      <c r="BV8" s="29" t="n"/>
+      <c r="BW8" s="24" t="n"/>
+      <c r="BX8" s="30" t="n"/>
+      <c r="BY8" s="27" t="n"/>
+      <c r="BZ8" s="24" t="n"/>
+      <c r="CA8" s="31" t="n"/>
+    </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="24" t="inlineStr">
+        <is>
+          <t>f592ac231a074ea9</t>
+        </is>
+      </c>
+      <c r="B9" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-17T14:02:17.091788Z</t>
+        </is>
+      </c>
+      <c r="C9" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-17T23:30Z</t>
+        </is>
+      </c>
+      <c r="D9" s="24" t="inlineStr">
+        <is>
+          <t>401857075</t>
+        </is>
+      </c>
+      <c r="E9" s="24" t="inlineStr">
+        <is>
+          <t>WNBA</t>
+        </is>
+      </c>
+      <c r="F9" s="24" t="inlineStr">
+        <is>
+          <t>Los Angeles Sparks</t>
+        </is>
+      </c>
+      <c r="G9" s="24" t="inlineStr">
+        <is>
+          <t>Chicago Sky</t>
+        </is>
+      </c>
+      <c r="H9" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I9" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J9" s="25" t="n"/>
+      <c r="K9" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L9" s="26" t="n">
+        <v>108</v>
+      </c>
+      <c r="M9" s="27" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="N9" s="28" t="n">
+        <v>0.480769</v>
+      </c>
+      <c r="O9" s="28" t="n">
+        <v>0.580113</v>
+      </c>
+      <c r="P9" s="28" t="n"/>
+      <c r="Q9" s="28" t="n">
+        <v>0.099344</v>
+      </c>
+      <c r="R9" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S9" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="U9" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V9" s="24" t="n"/>
+      <c r="W9" s="26" t="n"/>
+      <c r="X9" s="26" t="n"/>
+      <c r="Y9" s="25" t="n"/>
+      <c r="Z9" s="26" t="n"/>
+      <c r="AA9" s="28" t="n"/>
+      <c r="AB9" s="28" t="n"/>
+      <c r="AC9" s="30" t="n"/>
+      <c r="AD9" s="24" t="n"/>
+      <c r="AE9" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5018; executable ask 0.4800 (aec-wnba-la-chi-2026-07-17).</t>
+        </is>
+      </c>
+      <c r="AF9" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
+        </is>
+      </c>
+      <c r="AG9" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH9" s="24" t="n"/>
+      <c r="AI9" s="31" t="n"/>
+      <c r="AJ9" s="31" t="n"/>
+      <c r="AK9" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL9" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM9" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN9" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO9" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MISSING_UNCERTAINTY</t>
+        </is>
+      </c>
+      <c r="AP9" s="24" t="inlineStr">
+        <is>
+          <t>wnba-las</t>
+        </is>
+      </c>
+      <c r="AQ9" s="24" t="inlineStr">
+        <is>
+          <t>Los Angeles Sparks</t>
+        </is>
+      </c>
+      <c r="AR9" s="24" t="inlineStr">
+        <is>
+          <t>Los Angeles Sparks</t>
+        </is>
+      </c>
+      <c r="AS9" s="24" t="inlineStr">
+        <is>
+          <t>wnba-chi</t>
+        </is>
+      </c>
+      <c r="AT9" s="24" t="inlineStr">
+        <is>
+          <t>Chicago Sky</t>
+        </is>
+      </c>
+      <c r="AU9" s="24" t="inlineStr">
+        <is>
+          <t>Chicago Sky</t>
+        </is>
+      </c>
+      <c r="AV9" s="24" t="n"/>
+      <c r="AW9" s="24" t="n"/>
+      <c r="AX9" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY9" s="24" t="n"/>
+      <c r="AZ9" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA9" s="24" t="inlineStr">
+        <is>
+          <t>286653236675a65e58674d10837572801218599b31772016e9d8575bfefa53b4</t>
+        </is>
+      </c>
+      <c r="BB9" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC9" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BD9" s="24" t="inlineStr">
+        <is>
+          <t>286653236675a65e58674d10837572801218599b31772016e9d8575bfefa53b4</t>
+        </is>
+      </c>
+      <c r="BE9" s="24" t="inlineStr">
+        <is>
+          <t>8c7d8b8b613f1c27</t>
+        </is>
+      </c>
+      <c r="BF9" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG9" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BH9" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-17T14:02:10.568774Z</t>
+        </is>
+      </c>
+      <c r="BI9" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ9" s="25" t="n"/>
+      <c r="BK9" s="26" t="n">
+        <v>108</v>
+      </c>
+      <c r="BL9" s="27" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BM9" s="28" t="n">
+        <v>0.480769</v>
+      </c>
+      <c r="BN9" s="28" t="n">
+        <v>0.475248</v>
+      </c>
+      <c r="BO9" s="28" t="n"/>
+      <c r="BP9" s="25" t="n"/>
+      <c r="BQ9" s="27" t="n"/>
+      <c r="BR9" s="28" t="n"/>
+      <c r="BS9" s="28" t="n"/>
+      <c r="BT9" s="28" t="n"/>
+      <c r="BU9" s="25" t="n"/>
+      <c r="BV9" s="29" t="n"/>
+      <c r="BW9" s="24" t="n"/>
+      <c r="BX9" s="30" t="n"/>
+      <c r="BY9" s="27" t="n"/>
+      <c r="BZ9" s="24" t="n"/>
+      <c r="CA9" s="31" t="n"/>
+    </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="24" t="inlineStr">
+        <is>
+          <t>3405fe6d522c42ec</t>
+        </is>
+      </c>
+      <c r="B10" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-17T14:02:17.091788Z</t>
+        </is>
+      </c>
+      <c r="C10" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-18T02:00Z</t>
+        </is>
+      </c>
+      <c r="D10" s="24" t="inlineStr">
+        <is>
+          <t>401857076</t>
+        </is>
+      </c>
+      <c r="E10" s="24" t="inlineStr">
+        <is>
+          <t>WNBA</t>
+        </is>
+      </c>
+      <c r="F10" s="24" t="inlineStr">
+        <is>
+          <t>Connecticut Sun</t>
+        </is>
+      </c>
+      <c r="G10" s="24" t="inlineStr">
+        <is>
+          <t>Phoenix Mercury</t>
+        </is>
+      </c>
+      <c r="H10" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I10" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J10" s="25" t="n"/>
+      <c r="K10" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L10" s="26" t="n">
+        <v>-178</v>
+      </c>
+      <c r="M10" s="27" t="n">
+        <v>1.561798</v>
+      </c>
+      <c r="N10" s="28" t="n">
+        <v>0.640288</v>
+      </c>
+      <c r="O10" s="28" t="n">
+        <v>0.672243</v>
+      </c>
+      <c r="P10" s="28" t="n"/>
+      <c r="Q10" s="28" t="n">
+        <v>0.031955</v>
+      </c>
+      <c r="R10" s="26" t="n">
+        <v>66</v>
+      </c>
+      <c r="S10" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="U10" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V10" s="24" t="n"/>
+      <c r="W10" s="26" t="n"/>
+      <c r="X10" s="26" t="n"/>
+      <c r="Y10" s="25" t="n"/>
+      <c r="Z10" s="26" t="n"/>
+      <c r="AA10" s="28" t="n"/>
+      <c r="AB10" s="28" t="n"/>
+      <c r="AC10" s="30" t="n"/>
+      <c r="AD10" s="24" t="n"/>
+      <c r="AE10" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5018; executable ask 0.6400 (aec-wnba-conn-phx-2026-07-17).</t>
+        </is>
+      </c>
+      <c r="AF10" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
+        </is>
+      </c>
+      <c r="AG10" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH10" s="24" t="n"/>
+      <c r="AI10" s="31" t="n"/>
+      <c r="AJ10" s="31" t="n"/>
+      <c r="AK10" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL10" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM10" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN10" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO10" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MISSING_UNCERTAINTY</t>
+        </is>
+      </c>
+      <c r="AP10" s="24" t="inlineStr">
+        <is>
+          <t>wnba-con</t>
+        </is>
+      </c>
+      <c r="AQ10" s="24" t="inlineStr">
+        <is>
+          <t>Connecticut Sun</t>
+        </is>
+      </c>
+      <c r="AR10" s="24" t="inlineStr">
+        <is>
+          <t>Connecticut Sun</t>
+        </is>
+      </c>
+      <c r="AS10" s="24" t="inlineStr">
+        <is>
+          <t>wnba-phx</t>
+        </is>
+      </c>
+      <c r="AT10" s="24" t="inlineStr">
+        <is>
+          <t>Phoenix Mercury</t>
+        </is>
+      </c>
+      <c r="AU10" s="24" t="inlineStr">
+        <is>
+          <t>Phoenix Mercury</t>
+        </is>
+      </c>
+      <c r="AV10" s="24" t="n"/>
+      <c r="AW10" s="24" t="n"/>
+      <c r="AX10" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY10" s="24" t="n"/>
+      <c r="AZ10" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA10" s="24" t="inlineStr">
+        <is>
+          <t>286653236675a65e58674d10837572801218599b31772016e9d8575bfefa53b4</t>
+        </is>
+      </c>
+      <c r="BB10" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC10" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BD10" s="24" t="inlineStr">
+        <is>
+          <t>286653236675a65e58674d10837572801218599b31772016e9d8575bfefa53b4</t>
+        </is>
+      </c>
+      <c r="BE10" s="24" t="inlineStr">
+        <is>
+          <t>5b26e70fb7a6c509</t>
+        </is>
+      </c>
+      <c r="BF10" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG10" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BH10" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-17T14:02:11.780961Z</t>
+        </is>
+      </c>
+      <c r="BI10" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ10" s="25" t="n"/>
+      <c r="BK10" s="26" t="n">
+        <v>-178</v>
+      </c>
+      <c r="BL10" s="27" t="n">
+        <v>1.561798</v>
+      </c>
+      <c r="BM10" s="28" t="n">
+        <v>0.640288</v>
+      </c>
+      <c r="BN10" s="28" t="n">
+        <v>0.633663</v>
+      </c>
+      <c r="BO10" s="28" t="n"/>
+      <c r="BP10" s="25" t="n"/>
+      <c r="BQ10" s="27" t="n"/>
+      <c r="BR10" s="28" t="n"/>
+      <c r="BS10" s="28" t="n"/>
+      <c r="BT10" s="28" t="n"/>
+      <c r="BU10" s="25" t="n"/>
+      <c r="BV10" s="29" t="n"/>
+      <c r="BW10" s="24" t="n"/>
+      <c r="BX10" s="30" t="n"/>
+      <c r="BY10" s="27" t="n"/>
+      <c r="BZ10" s="24" t="n"/>
+      <c r="CA10" s="31" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/picks.xlsx
+++ b/data/picks.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CA10" headerRowCount="1">
-  <autoFilter ref="A1:CA10"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CA12" headerRowCount="1">
+  <autoFilter ref="A1:CA12"/>
   <tableColumns count="79">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -738,19 +738,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$10)</f>
+        <f>COUNTA('Picks'!$A$2:$A$12)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$10,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$12,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$10,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$12,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"win")+COUNTIFS('Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$12,"settled",'Picks'!$V$2:$V$12,"win")+COUNTIFS('Picks'!$U$2:$U$12,"settled",'Picks'!$V$2:$V$12,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -778,19 +778,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$10,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$12,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$10,"&gt;0",'Picks'!$V$2:$V$10,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$10,"&gt;0",'Picks'!$V$2:$V$10,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$12,"&gt;0",'Picks'!$V$2:$V$12,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$12,"&gt;0",'Picks'!$V$2:$V$12,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$10,"&gt;0",'Picks'!$V$2:$V$10,"win")/(COUNTIFS('Picks'!$BX$2:$BX$10,"&gt;0",'Picks'!$V$2:$V$10,"win")+COUNTIFS('Picks'!$BX$2:$BX$10,"&gt;0",'Picks'!$V$2:$V$10,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$12,"&gt;0",'Picks'!$V$2:$V$12,"win")/(COUNTIFS('Picks'!$BX$2:$BX$12,"&gt;0",'Picks'!$V$2:$V$12,"win")+COUNTIFS('Picks'!$BX$2:$BX$12,"&gt;0",'Picks'!$V$2:$V$12,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$10)/SUM('Picks'!$BX$2:$BX$10),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$12)/SUM('Picks'!$BX$2:$BX$12),0)</f>
         <v/>
       </c>
     </row>
@@ -818,19 +818,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$10)</f>
+        <f>SUM('Picks'!$BY$2:$BY$12)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$10,"&lt;&gt;",'Picks'!$AB$2:$AB$10),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$12,"&lt;&gt;",'Picks'!$AB$2:$AB$12),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$10,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$10,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$12,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$12,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$10,'Picks'!$AM$2:$AM$10,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$12,'Picks'!$AM$2:$AM$12,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -885,15 +885,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$10,$A14,'Picks'!$U$2:$U$10,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$12,$A14,'Picks'!$U$2:$U$12,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$10,$A14,'Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$12,$A14,'Picks'!$U$2:$U$12,"settled",'Picks'!$V$2:$V$12,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$10,$A14,'Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$12,$A14,'Picks'!$U$2:$U$12,"settled",'Picks'!$V$2:$V$12,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -901,11 +901,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$10,'Picks'!$H$2:$H$10,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$12,'Picks'!$H$2:$H$12,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$10,'Picks'!$H$2:$H$10,$A14,'Picks'!$U$2:$U$10,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$12,'Picks'!$H$2:$H$12,$A14,'Picks'!$U$2:$U$12,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -916,15 +916,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$10,$A15,'Picks'!$U$2:$U$10,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$12,$A15,'Picks'!$U$2:$U$12,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$10,$A15,'Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$12,$A15,'Picks'!$U$2:$U$12,"settled",'Picks'!$V$2:$V$12,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$10,$A15,'Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$12,$A15,'Picks'!$U$2:$U$12,"settled",'Picks'!$V$2:$V$12,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -932,11 +932,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$10,'Picks'!$H$2:$H$10,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$12,'Picks'!$H$2:$H$12,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$10,'Picks'!$H$2:$H$10,$A15,'Picks'!$U$2:$U$10,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$12,'Picks'!$H$2:$H$12,$A15,'Picks'!$U$2:$U$12,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -947,15 +947,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$10,$A16,'Picks'!$U$2:$U$10,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$12,$A16,'Picks'!$U$2:$U$12,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$10,$A16,'Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$12,$A16,'Picks'!$U$2:$U$12,"settled",'Picks'!$V$2:$V$12,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$10,$A16,'Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$12,$A16,'Picks'!$U$2:$U$12,"settled",'Picks'!$V$2:$V$12,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -963,11 +963,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$10,'Picks'!$H$2:$H$10,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$12,'Picks'!$H$2:$H$12,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$10,'Picks'!$H$2:$H$10,$A16,'Picks'!$U$2:$U$10,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$12,'Picks'!$H$2:$H$12,$A16,'Picks'!$U$2:$U$12,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -996,7 +996,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CA10"/>
+  <dimension ref="A1:CA12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3718,6 +3718,504 @@
       <c r="BZ10" s="24" t="n"/>
       <c r="CA10" s="31" t="n"/>
     </row>
+    <row r="11" ht="36" customHeight="1">
+      <c r="A11" s="24" t="inlineStr">
+        <is>
+          <t>93a3540bf0dd49bb</t>
+        </is>
+      </c>
+      <c r="B11" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-17T16:21:24.725309Z</t>
+        </is>
+      </c>
+      <c r="C11" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-18T20:10Z</t>
+        </is>
+      </c>
+      <c r="D11" s="24" t="inlineStr">
+        <is>
+          <t>401816163</t>
+        </is>
+      </c>
+      <c r="E11" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F11" s="24" t="inlineStr">
+        <is>
+          <t>Miami Marlins</t>
+        </is>
+      </c>
+      <c r="G11" s="24" t="inlineStr">
+        <is>
+          <t>Milwaukee Brewers</t>
+        </is>
+      </c>
+      <c r="H11" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I11" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J11" s="25" t="n"/>
+      <c r="K11" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L11" s="26" t="n">
+        <v>-130</v>
+      </c>
+      <c r="M11" s="27" t="n">
+        <v>1.769231</v>
+      </c>
+      <c r="N11" s="28" t="n">
+        <v>0.565217</v>
+      </c>
+      <c r="O11" s="28" t="n">
+        <v>0.605633</v>
+      </c>
+      <c r="P11" s="28" t="n"/>
+      <c r="Q11" s="28" t="n">
+        <v>0.040416</v>
+      </c>
+      <c r="R11" s="26" t="n">
+        <v>70</v>
+      </c>
+      <c r="S11" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="U11" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V11" s="24" t="n"/>
+      <c r="W11" s="26" t="n"/>
+      <c r="X11" s="26" t="n"/>
+      <c r="Y11" s="25" t="n"/>
+      <c r="Z11" s="26" t="n"/>
+      <c r="AA11" s="28" t="n"/>
+      <c r="AB11" s="28" t="n"/>
+      <c r="AC11" s="30" t="n"/>
+      <c r="AD11" s="24" t="n"/>
+      <c r="AE11" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.6018; executable ask 0.5650 (aec-mlb-mia-mil-2026-07-18).</t>
+        </is>
+      </c>
+      <c r="AF11" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
+        </is>
+      </c>
+      <c r="AG11" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH11" s="24" t="n"/>
+      <c r="AI11" s="31" t="n"/>
+      <c r="AJ11" s="31" t="n"/>
+      <c r="AK11" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL11" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM11" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN11" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO11" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MISSING_UNCERTAINTY</t>
+        </is>
+      </c>
+      <c r="AP11" s="24" t="inlineStr">
+        <is>
+          <t>mlb-mia</t>
+        </is>
+      </c>
+      <c r="AQ11" s="24" t="inlineStr">
+        <is>
+          <t>Miami Marlins</t>
+        </is>
+      </c>
+      <c r="AR11" s="24" t="inlineStr">
+        <is>
+          <t>Miami Marlins</t>
+        </is>
+      </c>
+      <c r="AS11" s="24" t="inlineStr">
+        <is>
+          <t>mlb-mil</t>
+        </is>
+      </c>
+      <c r="AT11" s="24" t="inlineStr">
+        <is>
+          <t>Milwaukee Brewers</t>
+        </is>
+      </c>
+      <c r="AU11" s="24" t="inlineStr">
+        <is>
+          <t>Milwaukee Brewers</t>
+        </is>
+      </c>
+      <c r="AV11" s="24" t="n"/>
+      <c r="AW11" s="24" t="n"/>
+      <c r="AX11" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY11" s="24" t="n"/>
+      <c r="AZ11" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA11" s="24" t="inlineStr">
+        <is>
+          <t>a454281ab207d2924d585d6b967363fb8e88af45132e3e9d354e4351fb5c237f</t>
+        </is>
+      </c>
+      <c r="BB11" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC11" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BD11" s="24" t="inlineStr">
+        <is>
+          <t>a454281ab207d2924d585d6b967363fb8e88af45132e3e9d354e4351fb5c237f</t>
+        </is>
+      </c>
+      <c r="BE11" s="24" t="inlineStr">
+        <is>
+          <t>c7348ce29d666909</t>
+        </is>
+      </c>
+      <c r="BF11" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG11" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BH11" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-17T16:21:07.161405Z</t>
+        </is>
+      </c>
+      <c r="BI11" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ11" s="25" t="n"/>
+      <c r="BK11" s="26" t="n">
+        <v>-130</v>
+      </c>
+      <c r="BL11" s="27" t="n">
+        <v>1.769231</v>
+      </c>
+      <c r="BM11" s="28" t="n">
+        <v>0.565217</v>
+      </c>
+      <c r="BN11" s="28" t="n">
+        <v>0.562189</v>
+      </c>
+      <c r="BO11" s="28" t="n"/>
+      <c r="BP11" s="25" t="n"/>
+      <c r="BQ11" s="27" t="n"/>
+      <c r="BR11" s="28" t="n"/>
+      <c r="BS11" s="28" t="n"/>
+      <c r="BT11" s="28" t="n"/>
+      <c r="BU11" s="25" t="n"/>
+      <c r="BV11" s="29" t="n"/>
+      <c r="BW11" s="24" t="n"/>
+      <c r="BX11" s="30" t="n"/>
+      <c r="BY11" s="27" t="n"/>
+      <c r="BZ11" s="24" t="n"/>
+      <c r="CA11" s="31" t="n"/>
+    </row>
+    <row r="12" ht="36" customHeight="1">
+      <c r="A12" s="24" t="inlineStr">
+        <is>
+          <t>c884dc7cf1104640</t>
+        </is>
+      </c>
+      <c r="B12" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-17T16:21:30.375686Z</t>
+        </is>
+      </c>
+      <c r="C12" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-19T00:00Z</t>
+        </is>
+      </c>
+      <c r="D12" s="24" t="inlineStr">
+        <is>
+          <t>401857077</t>
+        </is>
+      </c>
+      <c r="E12" s="24" t="inlineStr">
+        <is>
+          <t>WNBA</t>
+        </is>
+      </c>
+      <c r="F12" s="24" t="inlineStr">
+        <is>
+          <t>New York Liberty</t>
+        </is>
+      </c>
+      <c r="G12" s="24" t="inlineStr">
+        <is>
+          <t>Indiana Fever</t>
+        </is>
+      </c>
+      <c r="H12" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I12" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J12" s="25" t="n"/>
+      <c r="K12" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L12" s="26" t="n">
+        <v>117</v>
+      </c>
+      <c r="M12" s="27" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="N12" s="28" t="n">
+        <v>0.460829</v>
+      </c>
+      <c r="O12" s="28" t="n">
+        <v>0.632778</v>
+      </c>
+      <c r="P12" s="28" t="n"/>
+      <c r="Q12" s="28" t="n">
+        <v>0.171949</v>
+      </c>
+      <c r="R12" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S12" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="U12" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V12" s="24" t="n"/>
+      <c r="W12" s="26" t="n"/>
+      <c r="X12" s="26" t="n"/>
+      <c r="Y12" s="25" t="n"/>
+      <c r="Z12" s="26" t="n"/>
+      <c r="AA12" s="28" t="n"/>
+      <c r="AB12" s="28" t="n"/>
+      <c r="AC12" s="30" t="n"/>
+      <c r="AD12" s="24" t="n"/>
+      <c r="AE12" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5018; executable ask 0.4600 (aec-wnba-ny-ind-2026-07-18).</t>
+        </is>
+      </c>
+      <c r="AF12" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
+        </is>
+      </c>
+      <c r="AG12" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH12" s="24" t="n"/>
+      <c r="AI12" s="31" t="n"/>
+      <c r="AJ12" s="31" t="n"/>
+      <c r="AK12" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL12" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM12" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN12" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO12" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MISSING_UNCERTAINTY</t>
+        </is>
+      </c>
+      <c r="AP12" s="24" t="inlineStr">
+        <is>
+          <t>wnba-nyl</t>
+        </is>
+      </c>
+      <c r="AQ12" s="24" t="inlineStr">
+        <is>
+          <t>New York Liberty</t>
+        </is>
+      </c>
+      <c r="AR12" s="24" t="inlineStr">
+        <is>
+          <t>New York Liberty</t>
+        </is>
+      </c>
+      <c r="AS12" s="24" t="inlineStr">
+        <is>
+          <t>wnba-ind</t>
+        </is>
+      </c>
+      <c r="AT12" s="24" t="inlineStr">
+        <is>
+          <t>Indiana Fever</t>
+        </is>
+      </c>
+      <c r="AU12" s="24" t="inlineStr">
+        <is>
+          <t>Indiana Fever</t>
+        </is>
+      </c>
+      <c r="AV12" s="24" t="n"/>
+      <c r="AW12" s="24" t="n"/>
+      <c r="AX12" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY12" s="24" t="n"/>
+      <c r="AZ12" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA12" s="24" t="inlineStr">
+        <is>
+          <t>286653236675a65e58674d10837572801218599b31772016e9d8575bfefa53b4</t>
+        </is>
+      </c>
+      <c r="BB12" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC12" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BD12" s="24" t="inlineStr">
+        <is>
+          <t>286653236675a65e58674d10837572801218599b31772016e9d8575bfefa53b4</t>
+        </is>
+      </c>
+      <c r="BE12" s="24" t="inlineStr">
+        <is>
+          <t>e4f3f616d306cafe</t>
+        </is>
+      </c>
+      <c r="BF12" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG12" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BH12" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-17T16:21:13.188564Z</t>
+        </is>
+      </c>
+      <c r="BI12" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ12" s="25" t="n"/>
+      <c r="BK12" s="26" t="n">
+        <v>117</v>
+      </c>
+      <c r="BL12" s="27" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BM12" s="28" t="n">
+        <v>0.460829</v>
+      </c>
+      <c r="BN12" s="28" t="n">
+        <v>0.455446</v>
+      </c>
+      <c r="BO12" s="28" t="n"/>
+      <c r="BP12" s="25" t="n"/>
+      <c r="BQ12" s="27" t="n"/>
+      <c r="BR12" s="28" t="n"/>
+      <c r="BS12" s="28" t="n"/>
+      <c r="BT12" s="28" t="n"/>
+      <c r="BU12" s="25" t="n"/>
+      <c r="BV12" s="29" t="n"/>
+      <c r="BW12" s="24" t="n"/>
+      <c r="BX12" s="30" t="n"/>
+      <c r="BY12" s="27" t="n"/>
+      <c r="BZ12" s="24" t="n"/>
+      <c r="CA12" s="31" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/picks.xlsx
+++ b/data/picks.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CA12" headerRowCount="1">
-  <autoFilter ref="A1:CA12"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CA13" headerRowCount="1">
+  <autoFilter ref="A1:CA13"/>
   <tableColumns count="79">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -738,19 +738,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$12)</f>
+        <f>COUNTA('Picks'!$A$2:$A$13)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$12,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$13,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$12,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$13,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$12,"settled",'Picks'!$V$2:$V$12,"win")+COUNTIFS('Picks'!$U$2:$U$12,"settled",'Picks'!$V$2:$V$12,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$13,"settled",'Picks'!$V$2:$V$13,"win")+COUNTIFS('Picks'!$U$2:$U$13,"settled",'Picks'!$V$2:$V$13,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -778,19 +778,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$12,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$13,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$12,"&gt;0",'Picks'!$V$2:$V$12,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$12,"&gt;0",'Picks'!$V$2:$V$12,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$13,"&gt;0",'Picks'!$V$2:$V$13,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$13,"&gt;0",'Picks'!$V$2:$V$13,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$12,"&gt;0",'Picks'!$V$2:$V$12,"win")/(COUNTIFS('Picks'!$BX$2:$BX$12,"&gt;0",'Picks'!$V$2:$V$12,"win")+COUNTIFS('Picks'!$BX$2:$BX$12,"&gt;0",'Picks'!$V$2:$V$12,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$13,"&gt;0",'Picks'!$V$2:$V$13,"win")/(COUNTIFS('Picks'!$BX$2:$BX$13,"&gt;0",'Picks'!$V$2:$V$13,"win")+COUNTIFS('Picks'!$BX$2:$BX$13,"&gt;0",'Picks'!$V$2:$V$13,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$12)/SUM('Picks'!$BX$2:$BX$12),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$13)/SUM('Picks'!$BX$2:$BX$13),0)</f>
         <v/>
       </c>
     </row>
@@ -818,19 +818,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$12)</f>
+        <f>SUM('Picks'!$BY$2:$BY$13)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$12,"&lt;&gt;",'Picks'!$AB$2:$AB$12),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$13,"&lt;&gt;",'Picks'!$AB$2:$AB$13),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$12,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$12,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$13,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$13,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$12,'Picks'!$AM$2:$AM$12,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$13,'Picks'!$AM$2:$AM$13,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -885,15 +885,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$12,$A14,'Picks'!$U$2:$U$12,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$13,$A14,'Picks'!$U$2:$U$13,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$12,$A14,'Picks'!$U$2:$U$12,"settled",'Picks'!$V$2:$V$12,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$13,$A14,'Picks'!$U$2:$U$13,"settled",'Picks'!$V$2:$V$13,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$12,$A14,'Picks'!$U$2:$U$12,"settled",'Picks'!$V$2:$V$12,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$13,$A14,'Picks'!$U$2:$U$13,"settled",'Picks'!$V$2:$V$13,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -901,11 +901,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$12,'Picks'!$H$2:$H$12,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$13,'Picks'!$H$2:$H$13,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$12,'Picks'!$H$2:$H$12,$A14,'Picks'!$U$2:$U$12,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$13,'Picks'!$H$2:$H$13,$A14,'Picks'!$U$2:$U$13,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -916,15 +916,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$12,$A15,'Picks'!$U$2:$U$12,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$13,$A15,'Picks'!$U$2:$U$13,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$12,$A15,'Picks'!$U$2:$U$12,"settled",'Picks'!$V$2:$V$12,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$13,$A15,'Picks'!$U$2:$U$13,"settled",'Picks'!$V$2:$V$13,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$12,$A15,'Picks'!$U$2:$U$12,"settled",'Picks'!$V$2:$V$12,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$13,$A15,'Picks'!$U$2:$U$13,"settled",'Picks'!$V$2:$V$13,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -932,11 +932,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$12,'Picks'!$H$2:$H$12,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$13,'Picks'!$H$2:$H$13,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$12,'Picks'!$H$2:$H$12,$A15,'Picks'!$U$2:$U$12,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$13,'Picks'!$H$2:$H$13,$A15,'Picks'!$U$2:$U$13,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -947,15 +947,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$12,$A16,'Picks'!$U$2:$U$12,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$13,$A16,'Picks'!$U$2:$U$13,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$12,$A16,'Picks'!$U$2:$U$12,"settled",'Picks'!$V$2:$V$12,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$13,$A16,'Picks'!$U$2:$U$13,"settled",'Picks'!$V$2:$V$13,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$12,$A16,'Picks'!$U$2:$U$12,"settled",'Picks'!$V$2:$V$12,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$13,$A16,'Picks'!$U$2:$U$13,"settled",'Picks'!$V$2:$V$13,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -963,11 +963,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$12,'Picks'!$H$2:$H$12,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$13,'Picks'!$H$2:$H$13,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$12,'Picks'!$H$2:$H$12,$A16,'Picks'!$U$2:$U$12,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$13,'Picks'!$H$2:$H$13,$A16,'Picks'!$U$2:$U$13,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -996,7 +996,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CA12"/>
+  <dimension ref="A1:CA13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1558,18 +1558,38 @@
       </c>
       <c r="U2" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V2" s="24" t="n"/>
-      <c r="W2" s="26" t="n"/>
-      <c r="X2" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V2" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W2" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" s="26" t="n">
+        <v>2</v>
+      </c>
       <c r="Y2" s="25" t="n"/>
-      <c r="Z2" s="26" t="n"/>
-      <c r="AA2" s="28" t="n"/>
-      <c r="AB2" s="28" t="n"/>
-      <c r="AC2" s="30" t="n"/>
-      <c r="AD2" s="24" t="n"/>
+      <c r="Z2" s="26" t="n">
+        <v>-147</v>
+      </c>
+      <c r="AA2" s="28" t="n">
+        <v>0.595</v>
+      </c>
+      <c r="AB2" s="28" t="n">
+        <v>0.009938000000000001</v>
+      </c>
+      <c r="AC2" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-18T05:45:53.690448Z</t>
+        </is>
+      </c>
       <c r="AE2" s="31" t="inlineStr">
         <is>
           <t>Learned LR call at threshold 0.6018; executable ask 0.5850 (aec-mlb-mia-mil-2026-07-17).</t>
@@ -1714,17 +1734,33 @@
       </c>
       <c r="BO2" s="28" t="n"/>
       <c r="BP2" s="25" t="n"/>
-      <c r="BQ2" s="27" t="n"/>
-      <c r="BR2" s="28" t="n"/>
+      <c r="BQ2" s="27" t="n">
+        <v>1.680272</v>
+      </c>
+      <c r="BR2" s="28" t="n">
+        <v>0.595</v>
+      </c>
       <c r="BS2" s="28" t="n"/>
       <c r="BT2" s="28" t="n"/>
       <c r="BU2" s="25" t="n"/>
       <c r="BV2" s="29" t="n"/>
       <c r="BW2" s="24" t="n"/>
-      <c r="BX2" s="30" t="n"/>
-      <c r="BY2" s="27" t="n"/>
-      <c r="BZ2" s="24" t="n"/>
-      <c r="CA2" s="31" t="n"/>
+      <c r="BX2" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY2" s="27" t="n">
+        <v>0.70922</v>
+      </c>
+      <c r="BZ2" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-18T05:45:53.690448Z</t>
+        </is>
+      </c>
+      <c r="CA2" s="31" t="inlineStr">
+        <is>
+          <t>fixed one-unit hypothetical scoring; no real exposure or execution</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="36" customHeight="1">
       <c r="A3" s="24" t="inlineStr">
@@ -1807,18 +1843,38 @@
       </c>
       <c r="U3" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V3" s="24" t="n"/>
-      <c r="W3" s="26" t="n"/>
-      <c r="X3" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V3" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W3" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="X3" s="26" t="n">
+        <v>2</v>
+      </c>
       <c r="Y3" s="25" t="n"/>
-      <c r="Z3" s="26" t="n"/>
-      <c r="AA3" s="28" t="n"/>
-      <c r="AB3" s="28" t="n"/>
-      <c r="AC3" s="30" t="n"/>
-      <c r="AD3" s="24" t="n"/>
+      <c r="Z3" s="26" t="n">
+        <v>-133</v>
+      </c>
+      <c r="AA3" s="28" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AB3" s="28" t="n">
+        <v>0.004783</v>
+      </c>
+      <c r="AC3" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-18T05:45:53.777767Z</t>
+        </is>
+      </c>
       <c r="AE3" s="31" t="inlineStr">
         <is>
           <t>Learned LR call at threshold 0.6018; executable ask 0.5650 (aec-mlb-min-chc-2026-07-17).</t>
@@ -1831,7 +1887,7 @@
       </c>
       <c r="AG3" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH3" s="24" t="n"/>
@@ -1963,17 +2019,33 @@
       </c>
       <c r="BO3" s="28" t="n"/>
       <c r="BP3" s="25" t="n"/>
-      <c r="BQ3" s="27" t="n"/>
-      <c r="BR3" s="28" t="n"/>
+      <c r="BQ3" s="27" t="n">
+        <v>1.75188</v>
+      </c>
+      <c r="BR3" s="28" t="n">
+        <v>0.57</v>
+      </c>
       <c r="BS3" s="28" t="n"/>
       <c r="BT3" s="28" t="n"/>
       <c r="BU3" s="25" t="n"/>
       <c r="BV3" s="29" t="n"/>
       <c r="BW3" s="24" t="n"/>
-      <c r="BX3" s="30" t="n"/>
-      <c r="BY3" s="27" t="n"/>
-      <c r="BZ3" s="24" t="n"/>
-      <c r="CA3" s="31" t="n"/>
+      <c r="BX3" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY3" s="27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BZ3" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-18T05:45:53.777767Z</t>
+        </is>
+      </c>
+      <c r="CA3" s="31" t="inlineStr">
+        <is>
+          <t>fixed one-unit hypothetical scoring; no real exposure or execution</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="24" t="inlineStr">
@@ -2056,18 +2128,32 @@
       </c>
       <c r="U4" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V4" s="24" t="n"/>
-      <c r="W4" s="26" t="n"/>
-      <c r="X4" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V4" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W4" s="26" t="n">
+        <v>107</v>
+      </c>
+      <c r="X4" s="26" t="n">
+        <v>110</v>
+      </c>
       <c r="Y4" s="25" t="n"/>
       <c r="Z4" s="26" t="n"/>
       <c r="AA4" s="28" t="n"/>
       <c r="AB4" s="28" t="n"/>
-      <c r="AC4" s="30" t="n"/>
-      <c r="AD4" s="24" t="n"/>
+      <c r="AC4" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-18T05:45:54.458400Z</t>
+        </is>
+      </c>
       <c r="AE4" s="31" t="inlineStr">
         <is>
           <t>Learned LR call at threshold 0.5018; executable ask 0.7800 (aec-wnba-sea-ind-2026-07-17).</t>
@@ -2219,10 +2305,22 @@
       <c r="BU4" s="25" t="n"/>
       <c r="BV4" s="29" t="n"/>
       <c r="BW4" s="24" t="n"/>
-      <c r="BX4" s="30" t="n"/>
-      <c r="BY4" s="27" t="n"/>
-      <c r="BZ4" s="24" t="n"/>
-      <c r="CA4" s="31" t="n"/>
+      <c r="BX4" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY4" s="27" t="n">
+        <v>0.28169</v>
+      </c>
+      <c r="BZ4" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-18T05:45:54.458400Z</t>
+        </is>
+      </c>
+      <c r="CA4" s="31" t="inlineStr">
+        <is>
+          <t>fixed one-unit hypothetical scoring; no real exposure or execution</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="36" customHeight="1">
       <c r="A5" s="24" t="inlineStr">
@@ -2305,18 +2403,32 @@
       </c>
       <c r="U5" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V5" s="24" t="n"/>
-      <c r="W5" s="26" t="n"/>
-      <c r="X5" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V5" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W5" s="26" t="n">
+        <v>82</v>
+      </c>
+      <c r="X5" s="26" t="n">
+        <v>96</v>
+      </c>
       <c r="Y5" s="25" t="n"/>
       <c r="Z5" s="26" t="n"/>
       <c r="AA5" s="28" t="n"/>
       <c r="AB5" s="28" t="n"/>
-      <c r="AC5" s="30" t="n"/>
-      <c r="AD5" s="24" t="n"/>
+      <c r="AC5" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-18T05:45:54.545671Z</t>
+        </is>
+      </c>
       <c r="AE5" s="31" t="inlineStr">
         <is>
           <t>Learned LR call at threshold 0.5018; executable ask 0.4900 (aec-wnba-la-chi-2026-07-17).</t>
@@ -2329,7 +2441,7 @@
       </c>
       <c r="AG5" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH5" s="24" t="n"/>
@@ -2468,10 +2580,22 @@
       <c r="BU5" s="25" t="n"/>
       <c r="BV5" s="29" t="n"/>
       <c r="BW5" s="24" t="n"/>
-      <c r="BX5" s="30" t="n"/>
-      <c r="BY5" s="27" t="n"/>
-      <c r="BZ5" s="24" t="n"/>
-      <c r="CA5" s="31" t="n"/>
+      <c r="BX5" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY5" s="27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BZ5" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-18T05:45:54.545671Z</t>
+        </is>
+      </c>
+      <c r="CA5" s="31" t="inlineStr">
+        <is>
+          <t>fixed one-unit hypothetical scoring; no real exposure or execution</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="36" customHeight="1">
       <c r="A6" s="24" t="inlineStr">
@@ -2554,18 +2678,32 @@
       </c>
       <c r="U6" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V6" s="24" t="n"/>
-      <c r="W6" s="26" t="n"/>
-      <c r="X6" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V6" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W6" s="26" t="n">
+        <v>96</v>
+      </c>
+      <c r="X6" s="26" t="n">
+        <v>83</v>
+      </c>
       <c r="Y6" s="25" t="n"/>
       <c r="Z6" s="26" t="n"/>
       <c r="AA6" s="28" t="n"/>
       <c r="AB6" s="28" t="n"/>
-      <c r="AC6" s="30" t="n"/>
-      <c r="AD6" s="24" t="n"/>
+      <c r="AC6" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-18T05:45:54.629639Z</t>
+        </is>
+      </c>
       <c r="AE6" s="31" t="inlineStr">
         <is>
           <t>Learned LR call at threshold 0.5018; executable ask 0.6400 (aec-wnba-conn-phx-2026-07-17).</t>
@@ -2578,7 +2716,7 @@
       </c>
       <c r="AG6" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH6" s="24" t="n"/>
@@ -2717,10 +2855,22 @@
       <c r="BU6" s="25" t="n"/>
       <c r="BV6" s="29" t="n"/>
       <c r="BW6" s="24" t="n"/>
-      <c r="BX6" s="30" t="n"/>
-      <c r="BY6" s="27" t="n"/>
-      <c r="BZ6" s="24" t="n"/>
-      <c r="CA6" s="31" t="n"/>
+      <c r="BX6" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY6" s="27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BZ6" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-18T05:45:54.629639Z</t>
+        </is>
+      </c>
+      <c r="CA6" s="31" t="inlineStr">
+        <is>
+          <t>fixed one-unit hypothetical scoring; no real exposure or execution</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="36" customHeight="1">
       <c r="A7" s="24" t="inlineStr">
@@ -2803,18 +2953,38 @@
       </c>
       <c r="U7" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V7" s="24" t="n"/>
-      <c r="W7" s="26" t="n"/>
-      <c r="X7" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V7" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W7" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X7" s="26" t="n">
+        <v>2</v>
+      </c>
       <c r="Y7" s="25" t="n"/>
-      <c r="Z7" s="26" t="n"/>
-      <c r="AA7" s="28" t="n"/>
-      <c r="AB7" s="28" t="n"/>
-      <c r="AC7" s="30" t="n"/>
-      <c r="AD7" s="24" t="n"/>
+      <c r="Z7" s="26" t="n">
+        <v>-147</v>
+      </c>
+      <c r="AA7" s="28" t="n">
+        <v>0.595</v>
+      </c>
+      <c r="AB7" s="28" t="n">
+        <v>0.009938000000000001</v>
+      </c>
+      <c r="AC7" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-18T05:45:54.715857Z</t>
+        </is>
+      </c>
       <c r="AE7" s="31" t="inlineStr">
         <is>
           <t>Learned LR call at threshold 0.6018; executable ask 0.5850 (aec-mlb-mia-mil-2026-07-17).</t>
@@ -2959,17 +3129,33 @@
       </c>
       <c r="BO7" s="28" t="n"/>
       <c r="BP7" s="25" t="n"/>
-      <c r="BQ7" s="27" t="n"/>
-      <c r="BR7" s="28" t="n"/>
+      <c r="BQ7" s="27" t="n">
+        <v>1.680272</v>
+      </c>
+      <c r="BR7" s="28" t="n">
+        <v>0.595</v>
+      </c>
       <c r="BS7" s="28" t="n"/>
       <c r="BT7" s="28" t="n"/>
       <c r="BU7" s="25" t="n"/>
       <c r="BV7" s="29" t="n"/>
       <c r="BW7" s="24" t="n"/>
-      <c r="BX7" s="30" t="n"/>
-      <c r="BY7" s="27" t="n"/>
-      <c r="BZ7" s="24" t="n"/>
-      <c r="CA7" s="31" t="n"/>
+      <c r="BX7" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY7" s="27" t="n">
+        <v>0.70922</v>
+      </c>
+      <c r="BZ7" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-18T05:45:54.715857Z</t>
+        </is>
+      </c>
+      <c r="CA7" s="31" t="inlineStr">
+        <is>
+          <t>fixed one-unit hypothetical scoring; no real exposure or execution</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="36" customHeight="1">
       <c r="A8" s="24" t="inlineStr">
@@ -3052,18 +3238,38 @@
       </c>
       <c r="U8" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V8" s="24" t="n"/>
-      <c r="W8" s="26" t="n"/>
-      <c r="X8" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V8" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W8" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="X8" s="26" t="n">
+        <v>2</v>
+      </c>
       <c r="Y8" s="25" t="n"/>
-      <c r="Z8" s="26" t="n"/>
-      <c r="AA8" s="28" t="n"/>
-      <c r="AB8" s="28" t="n"/>
-      <c r="AC8" s="30" t="n"/>
-      <c r="AD8" s="24" t="n"/>
+      <c r="Z8" s="26" t="n">
+        <v>-133</v>
+      </c>
+      <c r="AA8" s="28" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AB8" s="28" t="n">
+        <v>0.004783</v>
+      </c>
+      <c r="AC8" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-18T05:45:54.800172Z</t>
+        </is>
+      </c>
       <c r="AE8" s="31" t="inlineStr">
         <is>
           <t>Learned LR call at threshold 0.6018; executable ask 0.5650 (aec-mlb-min-chc-2026-07-17).</t>
@@ -3076,7 +3282,7 @@
       </c>
       <c r="AG8" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH8" s="24" t="n"/>
@@ -3208,17 +3414,33 @@
       </c>
       <c r="BO8" s="28" t="n"/>
       <c r="BP8" s="25" t="n"/>
-      <c r="BQ8" s="27" t="n"/>
-      <c r="BR8" s="28" t="n"/>
+      <c r="BQ8" s="27" t="n">
+        <v>1.75188</v>
+      </c>
+      <c r="BR8" s="28" t="n">
+        <v>0.57</v>
+      </c>
       <c r="BS8" s="28" t="n"/>
       <c r="BT8" s="28" t="n"/>
       <c r="BU8" s="25" t="n"/>
       <c r="BV8" s="29" t="n"/>
       <c r="BW8" s="24" t="n"/>
-      <c r="BX8" s="30" t="n"/>
-      <c r="BY8" s="27" t="n"/>
-      <c r="BZ8" s="24" t="n"/>
-      <c r="CA8" s="31" t="n"/>
+      <c r="BX8" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY8" s="27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BZ8" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-18T05:45:54.800172Z</t>
+        </is>
+      </c>
+      <c r="CA8" s="31" t="inlineStr">
+        <is>
+          <t>fixed one-unit hypothetical scoring; no real exposure or execution</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="36" customHeight="1">
       <c r="A9" s="24" t="inlineStr">
@@ -3301,18 +3523,32 @@
       </c>
       <c r="U9" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V9" s="24" t="n"/>
-      <c r="W9" s="26" t="n"/>
-      <c r="X9" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V9" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W9" s="26" t="n">
+        <v>82</v>
+      </c>
+      <c r="X9" s="26" t="n">
+        <v>96</v>
+      </c>
       <c r="Y9" s="25" t="n"/>
       <c r="Z9" s="26" t="n"/>
       <c r="AA9" s="28" t="n"/>
       <c r="AB9" s="28" t="n"/>
-      <c r="AC9" s="30" t="n"/>
-      <c r="AD9" s="24" t="n"/>
+      <c r="AC9" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-18T05:45:54.886428Z</t>
+        </is>
+      </c>
       <c r="AE9" s="31" t="inlineStr">
         <is>
           <t>Learned LR call at threshold 0.5018; executable ask 0.4800 (aec-wnba-la-chi-2026-07-17).</t>
@@ -3325,7 +3561,7 @@
       </c>
       <c r="AG9" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH9" s="24" t="n"/>
@@ -3464,10 +3700,22 @@
       <c r="BU9" s="25" t="n"/>
       <c r="BV9" s="29" t="n"/>
       <c r="BW9" s="24" t="n"/>
-      <c r="BX9" s="30" t="n"/>
-      <c r="BY9" s="27" t="n"/>
-      <c r="BZ9" s="24" t="n"/>
-      <c r="CA9" s="31" t="n"/>
+      <c r="BX9" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY9" s="27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BZ9" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-18T05:45:54.886428Z</t>
+        </is>
+      </c>
+      <c r="CA9" s="31" t="inlineStr">
+        <is>
+          <t>fixed one-unit hypothetical scoring; no real exposure or execution</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="36" customHeight="1">
       <c r="A10" s="24" t="inlineStr">
@@ -3550,18 +3798,32 @@
       </c>
       <c r="U10" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V10" s="24" t="n"/>
-      <c r="W10" s="26" t="n"/>
-      <c r="X10" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V10" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W10" s="26" t="n">
+        <v>96</v>
+      </c>
+      <c r="X10" s="26" t="n">
+        <v>83</v>
+      </c>
       <c r="Y10" s="25" t="n"/>
       <c r="Z10" s="26" t="n"/>
       <c r="AA10" s="28" t="n"/>
       <c r="AB10" s="28" t="n"/>
-      <c r="AC10" s="30" t="n"/>
-      <c r="AD10" s="24" t="n"/>
+      <c r="AC10" s="30" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AD10" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-18T05:45:54.971822Z</t>
+        </is>
+      </c>
       <c r="AE10" s="31" t="inlineStr">
         <is>
           <t>Learned LR call at threshold 0.5018; executable ask 0.6400 (aec-wnba-conn-phx-2026-07-17).</t>
@@ -3574,7 +3836,7 @@
       </c>
       <c r="AG10" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH10" s="24" t="n"/>
@@ -3713,10 +3975,22 @@
       <c r="BU10" s="25" t="n"/>
       <c r="BV10" s="29" t="n"/>
       <c r="BW10" s="24" t="n"/>
-      <c r="BX10" s="30" t="n"/>
-      <c r="BY10" s="27" t="n"/>
-      <c r="BZ10" s="24" t="n"/>
-      <c r="CA10" s="31" t="n"/>
+      <c r="BX10" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY10" s="27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BZ10" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-18T05:45:54.971822Z</t>
+        </is>
+      </c>
+      <c r="CA10" s="31" t="inlineStr">
+        <is>
+          <t>fixed one-unit hypothetical scoring; no real exposure or execution</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="24" t="inlineStr">
@@ -4216,6 +4490,255 @@
       <c r="BZ12" s="24" t="n"/>
       <c r="CA12" s="31" t="n"/>
     </row>
+    <row r="13" ht="36" customHeight="1">
+      <c r="A13" s="24" t="inlineStr">
+        <is>
+          <t>4c2ec934da05478b</t>
+        </is>
+      </c>
+      <c r="B13" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-18T05:45:47.429402Z</t>
+        </is>
+      </c>
+      <c r="C13" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-18T18:20Z</t>
+        </is>
+      </c>
+      <c r="D13" s="24" t="inlineStr">
+        <is>
+          <t>401816164</t>
+        </is>
+      </c>
+      <c r="E13" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F13" s="24" t="inlineStr">
+        <is>
+          <t>Minnesota Twins</t>
+        </is>
+      </c>
+      <c r="G13" s="24" t="inlineStr">
+        <is>
+          <t>Chicago Cubs</t>
+        </is>
+      </c>
+      <c r="H13" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I13" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J13" s="25" t="n"/>
+      <c r="K13" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L13" s="26" t="n">
+        <v>-133</v>
+      </c>
+      <c r="M13" s="27" t="n">
+        <v>1.75188</v>
+      </c>
+      <c r="N13" s="28" t="n">
+        <v>0.570815</v>
+      </c>
+      <c r="O13" s="28" t="n">
+        <v>0.606876</v>
+      </c>
+      <c r="P13" s="28" t="n"/>
+      <c r="Q13" s="28" t="n">
+        <v>0.036061</v>
+      </c>
+      <c r="R13" s="26" t="n">
+        <v>68</v>
+      </c>
+      <c r="S13" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="U13" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V13" s="24" t="n"/>
+      <c r="W13" s="26" t="n"/>
+      <c r="X13" s="26" t="n"/>
+      <c r="Y13" s="25" t="n"/>
+      <c r="Z13" s="26" t="n"/>
+      <c r="AA13" s="28" t="n"/>
+      <c r="AB13" s="28" t="n"/>
+      <c r="AC13" s="30" t="n"/>
+      <c r="AD13" s="24" t="n"/>
+      <c r="AE13" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.6018; executable ask 0.5700 (aec-mlb-min-chc-2026-07-18).</t>
+        </is>
+      </c>
+      <c r="AF13" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
+        </is>
+      </c>
+      <c r="AG13" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH13" s="24" t="n"/>
+      <c r="AI13" s="31" t="n"/>
+      <c r="AJ13" s="31" t="n"/>
+      <c r="AK13" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL13" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM13" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN13" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO13" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MISSING_UNCERTAINTY</t>
+        </is>
+      </c>
+      <c r="AP13" s="24" t="inlineStr">
+        <is>
+          <t>mlb-min</t>
+        </is>
+      </c>
+      <c r="AQ13" s="24" t="inlineStr">
+        <is>
+          <t>Minnesota Twins</t>
+        </is>
+      </c>
+      <c r="AR13" s="24" t="inlineStr">
+        <is>
+          <t>Minnesota Twins</t>
+        </is>
+      </c>
+      <c r="AS13" s="24" t="inlineStr">
+        <is>
+          <t>mlb-chc</t>
+        </is>
+      </c>
+      <c r="AT13" s="24" t="inlineStr">
+        <is>
+          <t>Chicago Cubs</t>
+        </is>
+      </c>
+      <c r="AU13" s="24" t="inlineStr">
+        <is>
+          <t>Chicago Cubs</t>
+        </is>
+      </c>
+      <c r="AV13" s="24" t="n"/>
+      <c r="AW13" s="24" t="n"/>
+      <c r="AX13" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY13" s="24" t="n"/>
+      <c r="AZ13" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA13" s="24" t="inlineStr">
+        <is>
+          <t>a454281ab207d2924d585d6b967363fb8e88af45132e3e9d354e4351fb5c237f</t>
+        </is>
+      </c>
+      <c r="BB13" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC13" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BD13" s="24" t="inlineStr">
+        <is>
+          <t>a454281ab207d2924d585d6b967363fb8e88af45132e3e9d354e4351fb5c237f</t>
+        </is>
+      </c>
+      <c r="BE13" s="24" t="inlineStr">
+        <is>
+          <t>3acab0aa8ac04a91</t>
+        </is>
+      </c>
+      <c r="BF13" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG13" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BH13" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-18T05:44:27.731285Z</t>
+        </is>
+      </c>
+      <c r="BI13" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ13" s="25" t="n"/>
+      <c r="BK13" s="26" t="n">
+        <v>-133</v>
+      </c>
+      <c r="BL13" s="27" t="n">
+        <v>1.75188</v>
+      </c>
+      <c r="BM13" s="28" t="n">
+        <v>0.570815</v>
+      </c>
+      <c r="BN13" s="28" t="n">
+        <v>0.567164</v>
+      </c>
+      <c r="BO13" s="28" t="n"/>
+      <c r="BP13" s="25" t="n"/>
+      <c r="BQ13" s="27" t="n"/>
+      <c r="BR13" s="28" t="n"/>
+      <c r="BS13" s="28" t="n"/>
+      <c r="BT13" s="28" t="n"/>
+      <c r="BU13" s="25" t="n"/>
+      <c r="BV13" s="29" t="n"/>
+      <c r="BW13" s="24" t="n"/>
+      <c r="BX13" s="30" t="n"/>
+      <c r="BY13" s="27" t="n"/>
+      <c r="BZ13" s="24" t="n"/>
+      <c r="CA13" s="31" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/picks.xlsx
+++ b/data/picks.xlsx
@@ -21,10 +21,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="0.0###"/>
-    <numFmt numFmtId="165" formatCode="0.000000"/>
-    <numFmt numFmtId="166" formatCode="0.0000"/>
-    <numFmt numFmtId="167" formatCode="0.0%"/>
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
+    <numFmt numFmtId="166" formatCode="0.0###"/>
+    <numFmt numFmtId="167" formatCode="0.000000"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -136,7 +136,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -150,10 +150,10 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -169,10 +169,10 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -184,10 +184,10 @@
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -202,26 +202,53 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="top"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -785,11 +812,11 @@
         <f>COUNTIFS('Picks'!$BX$2:$BX$13,"&gt;0",'Picks'!$V$2:$V$13,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$13,"&gt;0",'Picks'!$V$2:$V$13,"loss")</f>
         <v/>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="32">
         <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$13,"&gt;0",'Picks'!$V$2:$V$13,"win")/(COUNTIFS('Picks'!$BX$2:$BX$13,"&gt;0",'Picks'!$V$2:$V$13,"win")+COUNTIFS('Picks'!$BX$2:$BX$13,"&gt;0",'Picks'!$V$2:$V$13,"loss")),0)</f>
         <v/>
       </c>
-      <c r="G7" s="7">
+      <c r="G7" s="32">
         <f>IFERROR(SUM('Picks'!$BY$2:$BY$13)/SUM('Picks'!$BX$2:$BX$13),0)</f>
         <v/>
       </c>
@@ -817,7 +844,7 @@
       </c>
     </row>
     <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="8">
+      <c r="A10" s="33">
         <f>SUM('Picks'!$BY$2:$BY$13)</f>
         <v/>
       </c>
@@ -829,7 +856,7 @@
         <f>COUNTIFS('Picks'!$AM$2:$AM$13,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$13,"settled")</f>
         <v/>
       </c>
-      <c r="G10" s="8">
+      <c r="G10" s="33">
         <f>SUMIFS('Picks'!$AC$2:$AC$13,'Picks'!$AM$2:$AM$13,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
@@ -896,11 +923,11 @@
         <f>COUNTIFS('Picks'!$H$2:$H$13,$A14,'Picks'!$U$2:$U$13,"settled",'Picks'!$V$2:$V$13,"loss")</f>
         <v/>
       </c>
-      <c r="E14" s="14">
+      <c r="E14" s="34">
         <f>IFERROR(C14/(C14+D14),0)</f>
         <v/>
       </c>
-      <c r="F14" s="15">
+      <c r="F14" s="35">
         <f>SUMIFS('Picks'!$BY$2:$BY$13,'Picks'!$H$2:$H$13,$A14)</f>
         <v/>
       </c>
@@ -927,11 +954,11 @@
         <f>COUNTIFS('Picks'!$H$2:$H$13,$A15,'Picks'!$U$2:$U$13,"settled",'Picks'!$V$2:$V$13,"loss")</f>
         <v/>
       </c>
-      <c r="E15" s="19">
+      <c r="E15" s="36">
         <f>IFERROR(C15/(C15+D15),0)</f>
         <v/>
       </c>
-      <c r="F15" s="20">
+      <c r="F15" s="37">
         <f>SUMIFS('Picks'!$BY$2:$BY$13,'Picks'!$H$2:$H$13,$A15)</f>
         <v/>
       </c>
@@ -958,11 +985,11 @@
         <f>COUNTIFS('Picks'!$H$2:$H$13,$A16,'Picks'!$U$2:$U$13,"settled",'Picks'!$V$2:$V$13,"loss")</f>
         <v/>
       </c>
-      <c r="E16" s="14">
+      <c r="E16" s="34">
         <f>IFERROR(C16/(C16+D16),0)</f>
         <v/>
       </c>
-      <c r="F16" s="15">
+      <c r="F16" s="35">
         <f>SUMIFS('Picks'!$BY$2:$BY$13,'Picks'!$H$2:$H$13,$A16)</f>
         <v/>
       </c>
@@ -996,7 +1023,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CA13"/>
+  <dimension ref="A1:CA7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1523,7 +1550,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J2" s="25" t="n"/>
+      <c r="J2" s="38" t="n"/>
       <c r="K2" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -1532,7 +1559,7 @@
       <c r="L2" s="26" t="n">
         <v>-141</v>
       </c>
-      <c r="M2" s="27" t="n">
+      <c r="M2" s="39" t="n">
         <v>1.70922</v>
       </c>
       <c r="N2" s="28" t="n">
@@ -1572,7 +1599,7 @@
       <c r="X2" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y2" s="25" t="n"/>
+      <c r="Y2" s="38" t="n"/>
       <c r="Z2" s="26" t="n">
         <v>-147</v>
       </c>
@@ -1582,7 +1609,7 @@
       <c r="AB2" s="28" t="n">
         <v>0.009938000000000001</v>
       </c>
-      <c r="AC2" s="30" t="n">
+      <c r="AC2" s="40" t="n">
         <v>0</v>
       </c>
       <c r="AD2" s="24" t="inlineStr">
@@ -1719,11 +1746,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ2" s="25" t="n"/>
+      <c r="BJ2" s="38" t="n"/>
       <c r="BK2" s="26" t="n">
         <v>-141</v>
       </c>
-      <c r="BL2" s="27" t="n">
+      <c r="BL2" s="39" t="n">
         <v>1.70922</v>
       </c>
       <c r="BM2" s="28" t="n">
@@ -1733,8 +1760,8 @@
         <v>0.58209</v>
       </c>
       <c r="BO2" s="28" t="n"/>
-      <c r="BP2" s="25" t="n"/>
-      <c r="BQ2" s="27" t="n">
+      <c r="BP2" s="38" t="n"/>
+      <c r="BQ2" s="39" t="n">
         <v>1.680272</v>
       </c>
       <c r="BR2" s="28" t="n">
@@ -1742,13 +1769,13 @@
       </c>
       <c r="BS2" s="28" t="n"/>
       <c r="BT2" s="28" t="n"/>
-      <c r="BU2" s="25" t="n"/>
+      <c r="BU2" s="38" t="n"/>
       <c r="BV2" s="29" t="n"/>
       <c r="BW2" s="24" t="n"/>
-      <c r="BX2" s="30" t="n">
+      <c r="BX2" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY2" s="27" t="n">
+      <c r="BY2" s="39" t="n">
         <v>0.70922</v>
       </c>
       <c r="BZ2" s="24" t="inlineStr">
@@ -1808,7 +1835,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J3" s="25" t="n"/>
+      <c r="J3" s="38" t="n"/>
       <c r="K3" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -1817,7 +1844,7 @@
       <c r="L3" s="26" t="n">
         <v>-130</v>
       </c>
-      <c r="M3" s="27" t="n">
+      <c r="M3" s="39" t="n">
         <v>1.769231</v>
       </c>
       <c r="N3" s="28" t="n">
@@ -1857,7 +1884,7 @@
       <c r="X3" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y3" s="25" t="n"/>
+      <c r="Y3" s="38" t="n"/>
       <c r="Z3" s="26" t="n">
         <v>-133</v>
       </c>
@@ -1867,7 +1894,7 @@
       <c r="AB3" s="28" t="n">
         <v>0.004783</v>
       </c>
-      <c r="AC3" s="30" t="n">
+      <c r="AC3" s="40" t="n">
         <v>0</v>
       </c>
       <c r="AD3" s="24" t="inlineStr">
@@ -2004,11 +2031,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ3" s="25" t="n"/>
+      <c r="BJ3" s="38" t="n"/>
       <c r="BK3" s="26" t="n">
         <v>-130</v>
       </c>
-      <c r="BL3" s="27" t="n">
+      <c r="BL3" s="39" t="n">
         <v>1.769231</v>
       </c>
       <c r="BM3" s="28" t="n">
@@ -2018,8 +2045,8 @@
         <v>0.562189</v>
       </c>
       <c r="BO3" s="28" t="n"/>
-      <c r="BP3" s="25" t="n"/>
-      <c r="BQ3" s="27" t="n">
+      <c r="BP3" s="38" t="n"/>
+      <c r="BQ3" s="39" t="n">
         <v>1.75188</v>
       </c>
       <c r="BR3" s="28" t="n">
@@ -2027,13 +2054,13 @@
       </c>
       <c r="BS3" s="28" t="n"/>
       <c r="BT3" s="28" t="n"/>
-      <c r="BU3" s="25" t="n"/>
+      <c r="BU3" s="38" t="n"/>
       <c r="BV3" s="29" t="n"/>
       <c r="BW3" s="24" t="n"/>
-      <c r="BX3" s="30" t="n">
+      <c r="BX3" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY3" s="27" t="n">
+      <c r="BY3" s="39" t="n">
         <v>-1</v>
       </c>
       <c r="BZ3" s="24" t="inlineStr">
@@ -2050,37 +2077,37 @@
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="24" t="inlineStr">
         <is>
-          <t>1784b306a2764ca0</t>
+          <t>d0e98df55d684f7a</t>
         </is>
       </c>
       <c r="B4" s="24" t="inlineStr">
         <is>
-          <t>2026-07-17T10:47:01.653330Z</t>
+          <t>2026-07-17T14:02:14.862720Z</t>
         </is>
       </c>
       <c r="C4" s="24" t="inlineStr">
         <is>
-          <t>2026-07-17T23:30Z</t>
+          <t>2026-07-17T23:40Z</t>
         </is>
       </c>
       <c r="D4" s="24" t="inlineStr">
         <is>
-          <t>401857073</t>
+          <t>401816148</t>
         </is>
       </c>
       <c r="E4" s="24" t="inlineStr">
         <is>
-          <t>WNBA</t>
+          <t>MLB</t>
         </is>
       </c>
       <c r="F4" s="24" t="inlineStr">
         <is>
-          <t>Seattle Storm</t>
+          <t>Miami Marlins</t>
         </is>
       </c>
       <c r="G4" s="24" t="inlineStr">
         <is>
-          <t>Indiana Fever</t>
+          <t>Milwaukee Brewers</t>
         </is>
       </c>
       <c r="H4" s="24" t="inlineStr">
@@ -2093,37 +2120,37 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J4" s="25" t="n"/>
+      <c r="J4" s="38" t="n"/>
       <c r="K4" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
         </is>
       </c>
       <c r="L4" s="26" t="n">
-        <v>-355</v>
-      </c>
-      <c r="M4" s="27" t="n">
-        <v>1.28169</v>
+        <v>-141</v>
+      </c>
+      <c r="M4" s="39" t="n">
+        <v>1.70922</v>
       </c>
       <c r="N4" s="28" t="n">
-        <v>0.78022</v>
+        <v>0.585062</v>
       </c>
       <c r="O4" s="28" t="n">
-        <v>0.6531090000000001</v>
+        <v>0.605633</v>
       </c>
       <c r="P4" s="28" t="n"/>
       <c r="Q4" s="28" t="n">
-        <v>-0.127111</v>
+        <v>0.020571</v>
       </c>
       <c r="R4" s="26" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="S4" s="29" t="n">
         <v>0</v>
       </c>
       <c r="T4" s="24" t="inlineStr">
         <is>
-          <t>wnba-elo-trend-lr-v2</t>
+          <t>mlb-elo-trend-lr-v3</t>
         </is>
       </c>
       <c r="U4" s="24" t="inlineStr">
@@ -2137,26 +2164,32 @@
         </is>
       </c>
       <c r="W4" s="26" t="n">
-        <v>107</v>
+        <v>1</v>
       </c>
       <c r="X4" s="26" t="n">
-        <v>110</v>
-      </c>
-      <c r="Y4" s="25" t="n"/>
-      <c r="Z4" s="26" t="n"/>
-      <c r="AA4" s="28" t="n"/>
-      <c r="AB4" s="28" t="n"/>
-      <c r="AC4" s="30" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y4" s="38" t="n"/>
+      <c r="Z4" s="26" t="n">
+        <v>-147</v>
+      </c>
+      <c r="AA4" s="28" t="n">
+        <v>0.595</v>
+      </c>
+      <c r="AB4" s="28" t="n">
+        <v>0.009938000000000001</v>
+      </c>
+      <c r="AC4" s="40" t="n">
         <v>0</v>
       </c>
       <c r="AD4" s="24" t="inlineStr">
         <is>
-          <t>2026-07-18T05:45:54.458400Z</t>
+          <t>2026-07-18T05:45:54.715857Z</t>
         </is>
       </c>
       <c r="AE4" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5018; executable ask 0.7800 (aec-wnba-sea-ind-2026-07-17).</t>
+          <t>Learned LR call at threshold 0.6018; executable ask 0.5850 (aec-mlb-mia-mil-2026-07-17).</t>
         </is>
       </c>
       <c r="AF4" s="31" t="inlineStr">
@@ -2197,32 +2230,32 @@
       </c>
       <c r="AP4" s="24" t="inlineStr">
         <is>
-          <t>wnba-sea</t>
+          <t>mlb-mia</t>
         </is>
       </c>
       <c r="AQ4" s="24" t="inlineStr">
         <is>
-          <t>Seattle Storm</t>
+          <t>Miami Marlins</t>
         </is>
       </c>
       <c r="AR4" s="24" t="inlineStr">
         <is>
-          <t>Seattle Storm</t>
+          <t>Miami Marlins</t>
         </is>
       </c>
       <c r="AS4" s="24" t="inlineStr">
         <is>
-          <t>wnba-ind</t>
+          <t>mlb-mil</t>
         </is>
       </c>
       <c r="AT4" s="24" t="inlineStr">
         <is>
-          <t>Indiana Fever</t>
+          <t>Milwaukee Brewers</t>
         </is>
       </c>
       <c r="AU4" s="24" t="inlineStr">
         <is>
-          <t>Indiana Fever</t>
+          <t>Milwaukee Brewers</t>
         </is>
       </c>
       <c r="AV4" s="24" t="n"/>
@@ -2240,7 +2273,7 @@
       </c>
       <c r="BA4" s="24" t="inlineStr">
         <is>
-          <t>593925b19cd0d6a88880d7d2e868f8b3cffef14f1697019de3a8a7e28e173bc7</t>
+          <t>a454281ab207d2924d585d6b967363fb8e88af45132e3e9d354e4351fb5c237f</t>
         </is>
       </c>
       <c r="BB4" s="24" t="inlineStr">
@@ -2250,17 +2283,17 @@
       </c>
       <c r="BC4" s="24" t="inlineStr">
         <is>
-          <t>wnba-elo-trend-lr-v2</t>
+          <t>mlb-elo-trend-lr-v3</t>
         </is>
       </c>
       <c r="BD4" s="24" t="inlineStr">
         <is>
-          <t>593925b19cd0d6a88880d7d2e868f8b3cffef14f1697019de3a8a7e28e173bc7</t>
+          <t>a454281ab207d2924d585d6b967363fb8e88af45132e3e9d354e4351fb5c237f</t>
         </is>
       </c>
       <c r="BE4" s="24" t="inlineStr">
         <is>
-          <t>15f518082bd1133e</t>
+          <t>27ad4a1da893e4b8</t>
         </is>
       </c>
       <c r="BF4" s="24" t="inlineStr">
@@ -2270,12 +2303,12 @@
       </c>
       <c r="BG4" s="24" t="inlineStr">
         <is>
-          <t>wnba-elo-trend-lr-v2</t>
+          <t>mlb-elo-trend-lr-v3</t>
         </is>
       </c>
       <c r="BH4" s="24" t="inlineStr">
         <is>
-          <t>2026-07-17T10:46:53.056520Z</t>
+          <t>2026-07-17T14:01:56.626918Z</t>
         </is>
       </c>
       <c r="BI4" s="24" t="inlineStr">
@@ -2283,79 +2316,83 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ4" s="25" t="n"/>
+      <c r="BJ4" s="38" t="n"/>
       <c r="BK4" s="26" t="n">
-        <v>-355</v>
-      </c>
-      <c r="BL4" s="27" t="n">
-        <v>1.28169</v>
+        <v>-141</v>
+      </c>
+      <c r="BL4" s="39" t="n">
+        <v>1.70922</v>
       </c>
       <c r="BM4" s="28" t="n">
-        <v>0.78022</v>
+        <v>0.585062</v>
       </c>
       <c r="BN4" s="28" t="n">
-        <v>0.772277</v>
+        <v>0.58209</v>
       </c>
       <c r="BO4" s="28" t="n"/>
-      <c r="BP4" s="25" t="n"/>
-      <c r="BQ4" s="27" t="n"/>
-      <c r="BR4" s="28" t="n"/>
+      <c r="BP4" s="38" t="n"/>
+      <c r="BQ4" s="39" t="n">
+        <v>1.680272</v>
+      </c>
+      <c r="BR4" s="28" t="n">
+        <v>0.595</v>
+      </c>
       <c r="BS4" s="28" t="n"/>
       <c r="BT4" s="28" t="n"/>
-      <c r="BU4" s="25" t="n"/>
+      <c r="BU4" s="38" t="n"/>
       <c r="BV4" s="29" t="n"/>
       <c r="BW4" s="24" t="n"/>
-      <c r="BX4" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="BY4" s="27" t="n">
-        <v>0.28169</v>
+      <c r="BX4" s="40" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BY4" s="39" t="n">
+        <v>1.06383</v>
       </c>
       <c r="BZ4" s="24" t="inlineStr">
         <is>
-          <t>2026-07-18T05:45:54.458400Z</t>
+          <t>2026-07-18T06:03:40.307635Z</t>
         </is>
       </c>
       <c r="CA4" s="31" t="inlineStr">
         <is>
-          <t>fixed one-unit hypothetical scoring; no real exposure or execution</t>
+          <t>decision-time model-sized hypothetical scoring; migrated 2026-07-18; no real exposure</t>
         </is>
       </c>
     </row>
     <row r="5" ht="36" customHeight="1">
       <c r="A5" s="24" t="inlineStr">
         <is>
-          <t>c6927110c2754085</t>
+          <t>3b98081a1ff04c62</t>
         </is>
       </c>
       <c r="B5" s="24" t="inlineStr">
         <is>
-          <t>2026-07-17T10:47:01.653330Z</t>
+          <t>2026-07-17T14:02:14.862720Z</t>
         </is>
       </c>
       <c r="C5" s="24" t="inlineStr">
         <is>
-          <t>2026-07-17T23:30Z</t>
+          <t>2026-07-18T00:05Z</t>
         </is>
       </c>
       <c r="D5" s="24" t="inlineStr">
         <is>
-          <t>401857075</t>
+          <t>401816149</t>
         </is>
       </c>
       <c r="E5" s="24" t="inlineStr">
         <is>
-          <t>WNBA</t>
+          <t>MLB</t>
         </is>
       </c>
       <c r="F5" s="24" t="inlineStr">
         <is>
-          <t>Los Angeles Sparks</t>
+          <t>Minnesota Twins</t>
         </is>
       </c>
       <c r="G5" s="24" t="inlineStr">
         <is>
-          <t>Chicago Sky</t>
+          <t>Chicago Cubs</t>
         </is>
       </c>
       <c r="H5" s="24" t="inlineStr">
@@ -2365,40 +2402,40 @@
       </c>
       <c r="I5" s="24" t="inlineStr">
         <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J5" s="25" t="n"/>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J5" s="38" t="n"/>
       <c r="K5" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
         </is>
       </c>
       <c r="L5" s="26" t="n">
-        <v>104</v>
-      </c>
-      <c r="M5" s="27" t="n">
-        <v>2.04</v>
+        <v>-130</v>
+      </c>
+      <c r="M5" s="39" t="n">
+        <v>1.769231</v>
       </c>
       <c r="N5" s="28" t="n">
-        <v>0.490196</v>
+        <v>0.565217</v>
       </c>
       <c r="O5" s="28" t="n">
-        <v>0.580113</v>
+        <v>0.606876</v>
       </c>
       <c r="P5" s="28" t="n"/>
       <c r="Q5" s="28" t="n">
-        <v>0.089917</v>
+        <v>0.041659</v>
       </c>
       <c r="R5" s="26" t="n">
-        <v>95</v>
+        <v>71</v>
       </c>
       <c r="S5" s="29" t="n">
         <v>0</v>
       </c>
       <c r="T5" s="24" t="inlineStr">
         <is>
-          <t>wnba-elo-trend-lr-v2</t>
+          <t>mlb-elo-trend-lr-v3</t>
         </is>
       </c>
       <c r="U5" s="24" t="inlineStr">
@@ -2412,26 +2449,32 @@
         </is>
       </c>
       <c r="W5" s="26" t="n">
-        <v>82</v>
+        <v>5</v>
       </c>
       <c r="X5" s="26" t="n">
-        <v>96</v>
-      </c>
-      <c r="Y5" s="25" t="n"/>
-      <c r="Z5" s="26" t="n"/>
-      <c r="AA5" s="28" t="n"/>
-      <c r="AB5" s="28" t="n"/>
-      <c r="AC5" s="30" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y5" s="38" t="n"/>
+      <c r="Z5" s="26" t="n">
+        <v>-133</v>
+      </c>
+      <c r="AA5" s="28" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AB5" s="28" t="n">
+        <v>0.004783</v>
+      </c>
+      <c r="AC5" s="40" t="n">
         <v>0</v>
       </c>
       <c r="AD5" s="24" t="inlineStr">
         <is>
-          <t>2026-07-18T05:45:54.545671Z</t>
+          <t>2026-07-18T05:45:54.800172Z</t>
         </is>
       </c>
       <c r="AE5" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5018; executable ask 0.4900 (aec-wnba-la-chi-2026-07-17).</t>
+          <t>Learned LR call at threshold 0.6018; executable ask 0.5650 (aec-mlb-min-chc-2026-07-17).</t>
         </is>
       </c>
       <c r="AF5" s="31" t="inlineStr">
@@ -2472,32 +2515,32 @@
       </c>
       <c r="AP5" s="24" t="inlineStr">
         <is>
-          <t>wnba-las</t>
+          <t>mlb-min</t>
         </is>
       </c>
       <c r="AQ5" s="24" t="inlineStr">
         <is>
-          <t>Los Angeles Sparks</t>
+          <t>Minnesota Twins</t>
         </is>
       </c>
       <c r="AR5" s="24" t="inlineStr">
         <is>
-          <t>Los Angeles Sparks</t>
+          <t>Minnesota Twins</t>
         </is>
       </c>
       <c r="AS5" s="24" t="inlineStr">
         <is>
-          <t>wnba-chi</t>
+          <t>mlb-chc</t>
         </is>
       </c>
       <c r="AT5" s="24" t="inlineStr">
         <is>
-          <t>Chicago Sky</t>
+          <t>Chicago Cubs</t>
         </is>
       </c>
       <c r="AU5" s="24" t="inlineStr">
         <is>
-          <t>Chicago Sky</t>
+          <t>Chicago Cubs</t>
         </is>
       </c>
       <c r="AV5" s="24" t="n"/>
@@ -2515,7 +2558,7 @@
       </c>
       <c r="BA5" s="24" t="inlineStr">
         <is>
-          <t>593925b19cd0d6a88880d7d2e868f8b3cffef14f1697019de3a8a7e28e173bc7</t>
+          <t>a454281ab207d2924d585d6b967363fb8e88af45132e3e9d354e4351fb5c237f</t>
         </is>
       </c>
       <c r="BB5" s="24" t="inlineStr">
@@ -2525,17 +2568,17 @@
       </c>
       <c r="BC5" s="24" t="inlineStr">
         <is>
-          <t>wnba-elo-trend-lr-v2</t>
+          <t>mlb-elo-trend-lr-v3</t>
         </is>
       </c>
       <c r="BD5" s="24" t="inlineStr">
         <is>
-          <t>593925b19cd0d6a88880d7d2e868f8b3cffef14f1697019de3a8a7e28e173bc7</t>
+          <t>a454281ab207d2924d585d6b967363fb8e88af45132e3e9d354e4351fb5c237f</t>
         </is>
       </c>
       <c r="BE5" s="24" t="inlineStr">
         <is>
-          <t>8c7d8b8b613f1c27</t>
+          <t>8438bc3f26be5eae</t>
         </is>
       </c>
       <c r="BF5" s="24" t="inlineStr">
@@ -2545,12 +2588,12 @@
       </c>
       <c r="BG5" s="24" t="inlineStr">
         <is>
-          <t>wnba-elo-trend-lr-v2</t>
+          <t>mlb-elo-trend-lr-v3</t>
         </is>
       </c>
       <c r="BH5" s="24" t="inlineStr">
         <is>
-          <t>2026-07-17T10:46:55.117340Z</t>
+          <t>2026-07-17T14:01:57.663980Z</t>
         </is>
       </c>
       <c r="BI5" s="24" t="inlineStr">
@@ -2558,79 +2601,83 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ5" s="25" t="n"/>
+      <c r="BJ5" s="38" t="n"/>
       <c r="BK5" s="26" t="n">
-        <v>104</v>
-      </c>
-      <c r="BL5" s="27" t="n">
-        <v>2.04</v>
+        <v>-130</v>
+      </c>
+      <c r="BL5" s="39" t="n">
+        <v>1.769231</v>
       </c>
       <c r="BM5" s="28" t="n">
-        <v>0.490196</v>
+        <v>0.565217</v>
       </c>
       <c r="BN5" s="28" t="n">
-        <v>0.485149</v>
+        <v>0.562189</v>
       </c>
       <c r="BO5" s="28" t="n"/>
-      <c r="BP5" s="25" t="n"/>
-      <c r="BQ5" s="27" t="n"/>
-      <c r="BR5" s="28" t="n"/>
+      <c r="BP5" s="38" t="n"/>
+      <c r="BQ5" s="39" t="n">
+        <v>1.75188</v>
+      </c>
+      <c r="BR5" s="28" t="n">
+        <v>0.57</v>
+      </c>
       <c r="BS5" s="28" t="n"/>
       <c r="BT5" s="28" t="n"/>
-      <c r="BU5" s="25" t="n"/>
+      <c r="BU5" s="38" t="n"/>
       <c r="BV5" s="29" t="n"/>
       <c r="BW5" s="24" t="n"/>
-      <c r="BX5" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="BY5" s="27" t="n">
-        <v>-1</v>
+      <c r="BX5" s="40" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BY5" s="39" t="n">
+        <v>-1.5</v>
       </c>
       <c r="BZ5" s="24" t="inlineStr">
         <is>
-          <t>2026-07-18T05:45:54.545671Z</t>
+          <t>2026-07-18T06:03:40.307635Z</t>
         </is>
       </c>
       <c r="CA5" s="31" t="inlineStr">
         <is>
-          <t>fixed one-unit hypothetical scoring; no real exposure or execution</t>
+          <t>decision-time model-sized hypothetical scoring; migrated 2026-07-18; no real exposure</t>
         </is>
       </c>
     </row>
     <row r="6" ht="36" customHeight="1">
       <c r="A6" s="24" t="inlineStr">
         <is>
-          <t>ec5e7cc40c1a4c2b</t>
+          <t>93a3540bf0dd49bb</t>
         </is>
       </c>
       <c r="B6" s="24" t="inlineStr">
         <is>
-          <t>2026-07-17T10:47:01.653330Z</t>
+          <t>2026-07-17T16:21:24.725309Z</t>
         </is>
       </c>
       <c r="C6" s="24" t="inlineStr">
         <is>
-          <t>2026-07-18T02:00Z</t>
+          <t>2026-07-18T20:10Z</t>
         </is>
       </c>
       <c r="D6" s="24" t="inlineStr">
         <is>
-          <t>401857076</t>
+          <t>401816163</t>
         </is>
       </c>
       <c r="E6" s="24" t="inlineStr">
         <is>
-          <t>WNBA</t>
+          <t>MLB</t>
         </is>
       </c>
       <c r="F6" s="24" t="inlineStr">
         <is>
-          <t>Connecticut Sun</t>
+          <t>Miami Marlins</t>
         </is>
       </c>
       <c r="G6" s="24" t="inlineStr">
         <is>
-          <t>Phoenix Mercury</t>
+          <t>Milwaukee Brewers</t>
         </is>
       </c>
       <c r="H6" s="24" t="inlineStr">
@@ -2643,70 +2690,56 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J6" s="25" t="n"/>
+      <c r="J6" s="38" t="n"/>
       <c r="K6" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
         </is>
       </c>
       <c r="L6" s="26" t="n">
-        <v>-178</v>
-      </c>
-      <c r="M6" s="27" t="n">
-        <v>1.561798</v>
+        <v>-130</v>
+      </c>
+      <c r="M6" s="39" t="n">
+        <v>1.769231</v>
       </c>
       <c r="N6" s="28" t="n">
-        <v>0.640288</v>
+        <v>0.565217</v>
       </c>
       <c r="O6" s="28" t="n">
-        <v>0.672243</v>
+        <v>0.605633</v>
       </c>
       <c r="P6" s="28" t="n"/>
       <c r="Q6" s="28" t="n">
-        <v>0.031955</v>
+        <v>0.040416</v>
       </c>
       <c r="R6" s="26" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="S6" s="29" t="n">
         <v>0</v>
       </c>
       <c r="T6" s="24" t="inlineStr">
         <is>
-          <t>wnba-elo-trend-lr-v2</t>
+          <t>mlb-elo-trend-lr-v3</t>
         </is>
       </c>
       <c r="U6" s="24" t="inlineStr">
         <is>
-          <t>settled</t>
-        </is>
-      </c>
-      <c r="V6" s="24" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="W6" s="26" t="n">
-        <v>96</v>
-      </c>
-      <c r="X6" s="26" t="n">
-        <v>83</v>
-      </c>
-      <c r="Y6" s="25" t="n"/>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V6" s="24" t="n"/>
+      <c r="W6" s="26" t="n"/>
+      <c r="X6" s="26" t="n"/>
+      <c r="Y6" s="38" t="n"/>
       <c r="Z6" s="26" t="n"/>
       <c r="AA6" s="28" t="n"/>
       <c r="AB6" s="28" t="n"/>
-      <c r="AC6" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-18T05:45:54.629639Z</t>
-        </is>
-      </c>
+      <c r="AC6" s="40" t="n"/>
+      <c r="AD6" s="24" t="n"/>
       <c r="AE6" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5018; executable ask 0.6400 (aec-wnba-conn-phx-2026-07-17).</t>
+          <t>Learned LR call at threshold 0.6018; executable ask 0.5650 (aec-mlb-mia-mil-2026-07-18).</t>
         </is>
       </c>
       <c r="AF6" s="31" t="inlineStr">
@@ -2716,7 +2749,7 @@
       </c>
       <c r="AG6" s="24" t="inlineStr">
         <is>
-          <t>review_required</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="AH6" s="24" t="n"/>
@@ -2747,32 +2780,32 @@
       </c>
       <c r="AP6" s="24" t="inlineStr">
         <is>
-          <t>wnba-con</t>
+          <t>mlb-mia</t>
         </is>
       </c>
       <c r="AQ6" s="24" t="inlineStr">
         <is>
-          <t>Connecticut Sun</t>
+          <t>Miami Marlins</t>
         </is>
       </c>
       <c r="AR6" s="24" t="inlineStr">
         <is>
-          <t>Connecticut Sun</t>
+          <t>Miami Marlins</t>
         </is>
       </c>
       <c r="AS6" s="24" t="inlineStr">
         <is>
-          <t>wnba-phx</t>
+          <t>mlb-mil</t>
         </is>
       </c>
       <c r="AT6" s="24" t="inlineStr">
         <is>
-          <t>Phoenix Mercury</t>
+          <t>Milwaukee Brewers</t>
         </is>
       </c>
       <c r="AU6" s="24" t="inlineStr">
         <is>
-          <t>Phoenix Mercury</t>
+          <t>Milwaukee Brewers</t>
         </is>
       </c>
       <c r="AV6" s="24" t="n"/>
@@ -2790,7 +2823,7 @@
       </c>
       <c r="BA6" s="24" t="inlineStr">
         <is>
-          <t>593925b19cd0d6a88880d7d2e868f8b3cffef14f1697019de3a8a7e28e173bc7</t>
+          <t>a454281ab207d2924d585d6b967363fb8e88af45132e3e9d354e4351fb5c237f</t>
         </is>
       </c>
       <c r="BB6" s="24" t="inlineStr">
@@ -2800,17 +2833,17 @@
       </c>
       <c r="BC6" s="24" t="inlineStr">
         <is>
-          <t>wnba-elo-trend-lr-v2</t>
+          <t>mlb-elo-trend-lr-v3</t>
         </is>
       </c>
       <c r="BD6" s="24" t="inlineStr">
         <is>
-          <t>593925b19cd0d6a88880d7d2e868f8b3cffef14f1697019de3a8a7e28e173bc7</t>
+          <t>a454281ab207d2924d585d6b967363fb8e88af45132e3e9d354e4351fb5c237f</t>
         </is>
       </c>
       <c r="BE6" s="24" t="inlineStr">
         <is>
-          <t>5b26e70fb7a6c509</t>
+          <t>c7348ce29d666909</t>
         </is>
       </c>
       <c r="BF6" s="24" t="inlineStr">
@@ -2820,12 +2853,12 @@
       </c>
       <c r="BG6" s="24" t="inlineStr">
         <is>
-          <t>wnba-elo-trend-lr-v2</t>
+          <t>mlb-elo-trend-lr-v3</t>
         </is>
       </c>
       <c r="BH6" s="24" t="inlineStr">
         <is>
-          <t>2026-07-17T10:46:56.693440Z</t>
+          <t>2026-07-17T16:21:07.161405Z</t>
         </is>
       </c>
       <c r="BI6" s="24" t="inlineStr">
@@ -2833,64 +2866,52 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ6" s="25" t="n"/>
+      <c r="BJ6" s="38" t="n"/>
       <c r="BK6" s="26" t="n">
-        <v>-178</v>
-      </c>
-      <c r="BL6" s="27" t="n">
-        <v>1.561798</v>
+        <v>-130</v>
+      </c>
+      <c r="BL6" s="39" t="n">
+        <v>1.769231</v>
       </c>
       <c r="BM6" s="28" t="n">
-        <v>0.640288</v>
+        <v>0.565217</v>
       </c>
       <c r="BN6" s="28" t="n">
-        <v>0.633663</v>
+        <v>0.562189</v>
       </c>
       <c r="BO6" s="28" t="n"/>
-      <c r="BP6" s="25" t="n"/>
-      <c r="BQ6" s="27" t="n"/>
+      <c r="BP6" s="38" t="n"/>
+      <c r="BQ6" s="39" t="n"/>
       <c r="BR6" s="28" t="n"/>
       <c r="BS6" s="28" t="n"/>
       <c r="BT6" s="28" t="n"/>
-      <c r="BU6" s="25" t="n"/>
+      <c r="BU6" s="38" t="n"/>
       <c r="BV6" s="29" t="n"/>
       <c r="BW6" s="24" t="n"/>
-      <c r="BX6" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="BY6" s="27" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BZ6" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-18T05:45:54.629639Z</t>
-        </is>
-      </c>
-      <c r="CA6" s="31" t="inlineStr">
-        <is>
-          <t>fixed one-unit hypothetical scoring; no real exposure or execution</t>
-        </is>
-      </c>
+      <c r="BX6" s="40" t="n"/>
+      <c r="BY6" s="39" t="n"/>
+      <c r="BZ6" s="24" t="n"/>
+      <c r="CA6" s="31" t="n"/>
     </row>
     <row r="7" ht="36" customHeight="1">
       <c r="A7" s="24" t="inlineStr">
         <is>
-          <t>d0e98df55d684f7a</t>
+          <t>4c2ec934da05478b</t>
         </is>
       </c>
       <c r="B7" s="24" t="inlineStr">
         <is>
-          <t>2026-07-17T14:02:14.862720Z</t>
+          <t>2026-07-18T05:45:47.429402Z</t>
         </is>
       </c>
       <c r="C7" s="24" t="inlineStr">
         <is>
-          <t>2026-07-17T23:40Z</t>
+          <t>2026-07-18T18:20Z</t>
         </is>
       </c>
       <c r="D7" s="24" t="inlineStr">
         <is>
-          <t>401816148</t>
+          <t>401816164</t>
         </is>
       </c>
       <c r="E7" s="24" t="inlineStr">
@@ -2900,12 +2921,12 @@
       </c>
       <c r="F7" s="24" t="inlineStr">
         <is>
-          <t>Miami Marlins</t>
+          <t>Minnesota Twins</t>
         </is>
       </c>
       <c r="G7" s="24" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers</t>
+          <t>Chicago Cubs</t>
         </is>
       </c>
       <c r="H7" s="24" t="inlineStr">
@@ -2918,30 +2939,30 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J7" s="25" t="n"/>
+      <c r="J7" s="38" t="n"/>
       <c r="K7" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
         </is>
       </c>
       <c r="L7" s="26" t="n">
-        <v>-141</v>
-      </c>
-      <c r="M7" s="27" t="n">
-        <v>1.70922</v>
+        <v>-133</v>
+      </c>
+      <c r="M7" s="39" t="n">
+        <v>1.75188</v>
       </c>
       <c r="N7" s="28" t="n">
-        <v>0.585062</v>
+        <v>0.570815</v>
       </c>
       <c r="O7" s="28" t="n">
-        <v>0.605633</v>
+        <v>0.606876</v>
       </c>
       <c r="P7" s="28" t="n"/>
       <c r="Q7" s="28" t="n">
-        <v>0.020571</v>
+        <v>0.036061</v>
       </c>
       <c r="R7" s="26" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="S7" s="29" t="n">
         <v>0</v>
@@ -2953,41 +2974,21 @@
       </c>
       <c r="U7" s="24" t="inlineStr">
         <is>
-          <t>settled</t>
-        </is>
-      </c>
-      <c r="V7" s="24" t="inlineStr">
-        <is>
-          <t>win</t>
-        </is>
-      </c>
-      <c r="W7" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="X7" s="26" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y7" s="25" t="n"/>
-      <c r="Z7" s="26" t="n">
-        <v>-147</v>
-      </c>
-      <c r="AA7" s="28" t="n">
-        <v>0.595</v>
-      </c>
-      <c r="AB7" s="28" t="n">
-        <v>0.009938000000000001</v>
-      </c>
-      <c r="AC7" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD7" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-18T05:45:54.715857Z</t>
-        </is>
-      </c>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V7" s="24" t="n"/>
+      <c r="W7" s="26" t="n"/>
+      <c r="X7" s="26" t="n"/>
+      <c r="Y7" s="38" t="n"/>
+      <c r="Z7" s="26" t="n"/>
+      <c r="AA7" s="28" t="n"/>
+      <c r="AB7" s="28" t="n"/>
+      <c r="AC7" s="40" t="n"/>
+      <c r="AD7" s="24" t="n"/>
       <c r="AE7" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.6018; executable ask 0.5850 (aec-mlb-mia-mil-2026-07-17).</t>
+          <t>Learned LR call at threshold 0.6018; executable ask 0.5700 (aec-mlb-min-chc-2026-07-18).</t>
         </is>
       </c>
       <c r="AF7" s="31" t="inlineStr">
@@ -3028,32 +3029,32 @@
       </c>
       <c r="AP7" s="24" t="inlineStr">
         <is>
-          <t>mlb-mia</t>
+          <t>mlb-min</t>
         </is>
       </c>
       <c r="AQ7" s="24" t="inlineStr">
         <is>
-          <t>Miami Marlins</t>
+          <t>Minnesota Twins</t>
         </is>
       </c>
       <c r="AR7" s="24" t="inlineStr">
         <is>
-          <t>Miami Marlins</t>
+          <t>Minnesota Twins</t>
         </is>
       </c>
       <c r="AS7" s="24" t="inlineStr">
         <is>
-          <t>mlb-mil</t>
+          <t>mlb-chc</t>
         </is>
       </c>
       <c r="AT7" s="24" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers</t>
+          <t>Chicago Cubs</t>
         </is>
       </c>
       <c r="AU7" s="24" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers</t>
+          <t>Chicago Cubs</t>
         </is>
       </c>
       <c r="AV7" s="24" t="n"/>
@@ -3091,7 +3092,7 @@
       </c>
       <c r="BE7" s="24" t="inlineStr">
         <is>
-          <t>27ad4a1da893e4b8</t>
+          <t>3acab0aa8ac04a91</t>
         </is>
       </c>
       <c r="BF7" s="24" t="inlineStr">
@@ -3106,7 +3107,7 @@
       </c>
       <c r="BH7" s="24" t="inlineStr">
         <is>
-          <t>2026-07-17T14:01:56.626918Z</t>
+          <t>2026-07-18T05:44:27.731285Z</t>
         </is>
       </c>
       <c r="BI7" s="24" t="inlineStr">
@@ -3114,1631 +3115,39 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ7" s="25" t="n"/>
+      <c r="BJ7" s="38" t="n"/>
       <c r="BK7" s="26" t="n">
-        <v>-141</v>
-      </c>
-      <c r="BL7" s="27" t="n">
-        <v>1.70922</v>
+        <v>-133</v>
+      </c>
+      <c r="BL7" s="39" t="n">
+        <v>1.75188</v>
       </c>
       <c r="BM7" s="28" t="n">
-        <v>0.585062</v>
+        <v>0.570815</v>
       </c>
       <c r="BN7" s="28" t="n">
-        <v>0.58209</v>
+        <v>0.567164</v>
       </c>
       <c r="BO7" s="28" t="n"/>
-      <c r="BP7" s="25" t="n"/>
-      <c r="BQ7" s="27" t="n">
-        <v>1.680272</v>
-      </c>
-      <c r="BR7" s="28" t="n">
-        <v>0.595</v>
-      </c>
+      <c r="BP7" s="38" t="n"/>
+      <c r="BQ7" s="39" t="n"/>
+      <c r="BR7" s="28" t="n"/>
       <c r="BS7" s="28" t="n"/>
       <c r="BT7" s="28" t="n"/>
-      <c r="BU7" s="25" t="n"/>
+      <c r="BU7" s="38" t="n"/>
       <c r="BV7" s="29" t="n"/>
       <c r="BW7" s="24" t="n"/>
-      <c r="BX7" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="BY7" s="27" t="n">
-        <v>0.70922</v>
-      </c>
-      <c r="BZ7" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-18T05:45:54.715857Z</t>
-        </is>
-      </c>
-      <c r="CA7" s="31" t="inlineStr">
-        <is>
-          <t>fixed one-unit hypothetical scoring; no real exposure or execution</t>
-        </is>
-      </c>
+      <c r="BX7" s="40" t="n"/>
+      <c r="BY7" s="39" t="n"/>
+      <c r="BZ7" s="24" t="n"/>
+      <c r="CA7" s="31" t="n"/>
     </row>
-    <row r="8" ht="36" customHeight="1">
-      <c r="A8" s="24" t="inlineStr">
-        <is>
-          <t>3b98081a1ff04c62</t>
-        </is>
-      </c>
-      <c r="B8" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-17T14:02:14.862720Z</t>
-        </is>
-      </c>
-      <c r="C8" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-18T00:05Z</t>
-        </is>
-      </c>
-      <c r="D8" s="24" t="inlineStr">
-        <is>
-          <t>401816149</t>
-        </is>
-      </c>
-      <c r="E8" s="24" t="inlineStr">
-        <is>
-          <t>MLB</t>
-        </is>
-      </c>
-      <c r="F8" s="24" t="inlineStr">
-        <is>
-          <t>Minnesota Twins</t>
-        </is>
-      </c>
-      <c r="G8" s="24" t="inlineStr">
-        <is>
-          <t>Chicago Cubs</t>
-        </is>
-      </c>
-      <c r="H8" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I8" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J8" s="25" t="n"/>
-      <c r="K8" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L8" s="26" t="n">
-        <v>-130</v>
-      </c>
-      <c r="M8" s="27" t="n">
-        <v>1.769231</v>
-      </c>
-      <c r="N8" s="28" t="n">
-        <v>0.565217</v>
-      </c>
-      <c r="O8" s="28" t="n">
-        <v>0.606876</v>
-      </c>
-      <c r="P8" s="28" t="n"/>
-      <c r="Q8" s="28" t="n">
-        <v>0.041659</v>
-      </c>
-      <c r="R8" s="26" t="n">
-        <v>71</v>
-      </c>
-      <c r="S8" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v3</t>
-        </is>
-      </c>
-      <c r="U8" s="24" t="inlineStr">
-        <is>
-          <t>settled</t>
-        </is>
-      </c>
-      <c r="V8" s="24" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="W8" s="26" t="n">
-        <v>5</v>
-      </c>
-      <c r="X8" s="26" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y8" s="25" t="n"/>
-      <c r="Z8" s="26" t="n">
-        <v>-133</v>
-      </c>
-      <c r="AA8" s="28" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="AB8" s="28" t="n">
-        <v>0.004783</v>
-      </c>
-      <c r="AC8" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-18T05:45:54.800172Z</t>
-        </is>
-      </c>
-      <c r="AE8" s="31" t="inlineStr">
-        <is>
-          <t>Learned LR call at threshold 0.6018; executable ask 0.5650 (aec-mlb-min-chc-2026-07-17).</t>
-        </is>
-      </c>
-      <c r="AF8" s="31" t="inlineStr">
-        <is>
-          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
-        </is>
-      </c>
-      <c r="AG8" s="24" t="inlineStr">
-        <is>
-          <t>review_required</t>
-        </is>
-      </c>
-      <c r="AH8" s="24" t="n"/>
-      <c r="AI8" s="31" t="n"/>
-      <c r="AJ8" s="31" t="n"/>
-      <c r="AK8" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL8" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM8" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN8" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO8" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_MISSING_UNCERTAINTY</t>
-        </is>
-      </c>
-      <c r="AP8" s="24" t="inlineStr">
-        <is>
-          <t>mlb-min</t>
-        </is>
-      </c>
-      <c r="AQ8" s="24" t="inlineStr">
-        <is>
-          <t>Minnesota Twins</t>
-        </is>
-      </c>
-      <c r="AR8" s="24" t="inlineStr">
-        <is>
-          <t>Minnesota Twins</t>
-        </is>
-      </c>
-      <c r="AS8" s="24" t="inlineStr">
-        <is>
-          <t>mlb-chc</t>
-        </is>
-      </c>
-      <c r="AT8" s="24" t="inlineStr">
-        <is>
-          <t>Chicago Cubs</t>
-        </is>
-      </c>
-      <c r="AU8" s="24" t="inlineStr">
-        <is>
-          <t>Chicago Cubs</t>
-        </is>
-      </c>
-      <c r="AV8" s="24" t="n"/>
-      <c r="AW8" s="24" t="n"/>
-      <c r="AX8" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY8" s="24" t="n"/>
-      <c r="AZ8" s="24" t="inlineStr">
-        <is>
-          <t>research</t>
-        </is>
-      </c>
-      <c r="BA8" s="24" t="inlineStr">
-        <is>
-          <t>a454281ab207d2924d585d6b967363fb8e88af45132e3e9d354e4351fb5c237f</t>
-        </is>
-      </c>
-      <c r="BB8" s="24" t="inlineStr">
-        <is>
-          <t>learned_lr</t>
-        </is>
-      </c>
-      <c r="BC8" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v3</t>
-        </is>
-      </c>
-      <c r="BD8" s="24" t="inlineStr">
-        <is>
-          <t>a454281ab207d2924d585d6b967363fb8e88af45132e3e9d354e4351fb5c237f</t>
-        </is>
-      </c>
-      <c r="BE8" s="24" t="inlineStr">
-        <is>
-          <t>8438bc3f26be5eae</t>
-        </is>
-      </c>
-      <c r="BF8" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG8" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v3</t>
-        </is>
-      </c>
-      <c r="BH8" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-17T14:01:57.663980Z</t>
-        </is>
-      </c>
-      <c r="BI8" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ8" s="25" t="n"/>
-      <c r="BK8" s="26" t="n">
-        <v>-130</v>
-      </c>
-      <c r="BL8" s="27" t="n">
-        <v>1.769231</v>
-      </c>
-      <c r="BM8" s="28" t="n">
-        <v>0.565217</v>
-      </c>
-      <c r="BN8" s="28" t="n">
-        <v>0.562189</v>
-      </c>
-      <c r="BO8" s="28" t="n"/>
-      <c r="BP8" s="25" t="n"/>
-      <c r="BQ8" s="27" t="n">
-        <v>1.75188</v>
-      </c>
-      <c r="BR8" s="28" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="BS8" s="28" t="n"/>
-      <c r="BT8" s="28" t="n"/>
-      <c r="BU8" s="25" t="n"/>
-      <c r="BV8" s="29" t="n"/>
-      <c r="BW8" s="24" t="n"/>
-      <c r="BX8" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="BY8" s="27" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BZ8" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-18T05:45:54.800172Z</t>
-        </is>
-      </c>
-      <c r="CA8" s="31" t="inlineStr">
-        <is>
-          <t>fixed one-unit hypothetical scoring; no real exposure or execution</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="36" customHeight="1">
-      <c r="A9" s="24" t="inlineStr">
-        <is>
-          <t>f592ac231a074ea9</t>
-        </is>
-      </c>
-      <c r="B9" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-17T14:02:17.091788Z</t>
-        </is>
-      </c>
-      <c r="C9" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-17T23:30Z</t>
-        </is>
-      </c>
-      <c r="D9" s="24" t="inlineStr">
-        <is>
-          <t>401857075</t>
-        </is>
-      </c>
-      <c r="E9" s="24" t="inlineStr">
-        <is>
-          <t>WNBA</t>
-        </is>
-      </c>
-      <c r="F9" s="24" t="inlineStr">
-        <is>
-          <t>Los Angeles Sparks</t>
-        </is>
-      </c>
-      <c r="G9" s="24" t="inlineStr">
-        <is>
-          <t>Chicago Sky</t>
-        </is>
-      </c>
-      <c r="H9" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I9" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J9" s="25" t="n"/>
-      <c r="K9" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L9" s="26" t="n">
-        <v>108</v>
-      </c>
-      <c r="M9" s="27" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="N9" s="28" t="n">
-        <v>0.480769</v>
-      </c>
-      <c r="O9" s="28" t="n">
-        <v>0.580113</v>
-      </c>
-      <c r="P9" s="28" t="n"/>
-      <c r="Q9" s="28" t="n">
-        <v>0.099344</v>
-      </c>
-      <c r="R9" s="26" t="n">
-        <v>100</v>
-      </c>
-      <c r="S9" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" s="24" t="inlineStr">
-        <is>
-          <t>wnba-elo-trend-lr-v3</t>
-        </is>
-      </c>
-      <c r="U9" s="24" t="inlineStr">
-        <is>
-          <t>settled</t>
-        </is>
-      </c>
-      <c r="V9" s="24" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="W9" s="26" t="n">
-        <v>82</v>
-      </c>
-      <c r="X9" s="26" t="n">
-        <v>96</v>
-      </c>
-      <c r="Y9" s="25" t="n"/>
-      <c r="Z9" s="26" t="n"/>
-      <c r="AA9" s="28" t="n"/>
-      <c r="AB9" s="28" t="n"/>
-      <c r="AC9" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD9" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-18T05:45:54.886428Z</t>
-        </is>
-      </c>
-      <c r="AE9" s="31" t="inlineStr">
-        <is>
-          <t>Learned LR call at threshold 0.5018; executable ask 0.4800 (aec-wnba-la-chi-2026-07-17).</t>
-        </is>
-      </c>
-      <c r="AF9" s="31" t="inlineStr">
-        <is>
-          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
-        </is>
-      </c>
-      <c r="AG9" s="24" t="inlineStr">
-        <is>
-          <t>review_required</t>
-        </is>
-      </c>
-      <c r="AH9" s="24" t="n"/>
-      <c r="AI9" s="31" t="n"/>
-      <c r="AJ9" s="31" t="n"/>
-      <c r="AK9" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL9" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM9" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN9" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO9" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_MISSING_UNCERTAINTY</t>
-        </is>
-      </c>
-      <c r="AP9" s="24" t="inlineStr">
-        <is>
-          <t>wnba-las</t>
-        </is>
-      </c>
-      <c r="AQ9" s="24" t="inlineStr">
-        <is>
-          <t>Los Angeles Sparks</t>
-        </is>
-      </c>
-      <c r="AR9" s="24" t="inlineStr">
-        <is>
-          <t>Los Angeles Sparks</t>
-        </is>
-      </c>
-      <c r="AS9" s="24" t="inlineStr">
-        <is>
-          <t>wnba-chi</t>
-        </is>
-      </c>
-      <c r="AT9" s="24" t="inlineStr">
-        <is>
-          <t>Chicago Sky</t>
-        </is>
-      </c>
-      <c r="AU9" s="24" t="inlineStr">
-        <is>
-          <t>Chicago Sky</t>
-        </is>
-      </c>
-      <c r="AV9" s="24" t="n"/>
-      <c r="AW9" s="24" t="n"/>
-      <c r="AX9" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY9" s="24" t="n"/>
-      <c r="AZ9" s="24" t="inlineStr">
-        <is>
-          <t>research</t>
-        </is>
-      </c>
-      <c r="BA9" s="24" t="inlineStr">
-        <is>
-          <t>286653236675a65e58674d10837572801218599b31772016e9d8575bfefa53b4</t>
-        </is>
-      </c>
-      <c r="BB9" s="24" t="inlineStr">
-        <is>
-          <t>learned_lr</t>
-        </is>
-      </c>
-      <c r="BC9" s="24" t="inlineStr">
-        <is>
-          <t>wnba-elo-trend-lr-v3</t>
-        </is>
-      </c>
-      <c r="BD9" s="24" t="inlineStr">
-        <is>
-          <t>286653236675a65e58674d10837572801218599b31772016e9d8575bfefa53b4</t>
-        </is>
-      </c>
-      <c r="BE9" s="24" t="inlineStr">
-        <is>
-          <t>8c7d8b8b613f1c27</t>
-        </is>
-      </c>
-      <c r="BF9" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG9" s="24" t="inlineStr">
-        <is>
-          <t>wnba-elo-trend-lr-v3</t>
-        </is>
-      </c>
-      <c r="BH9" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-17T14:02:10.568774Z</t>
-        </is>
-      </c>
-      <c r="BI9" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ9" s="25" t="n"/>
-      <c r="BK9" s="26" t="n">
-        <v>108</v>
-      </c>
-      <c r="BL9" s="27" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="BM9" s="28" t="n">
-        <v>0.480769</v>
-      </c>
-      <c r="BN9" s="28" t="n">
-        <v>0.475248</v>
-      </c>
-      <c r="BO9" s="28" t="n"/>
-      <c r="BP9" s="25" t="n"/>
-      <c r="BQ9" s="27" t="n"/>
-      <c r="BR9" s="28" t="n"/>
-      <c r="BS9" s="28" t="n"/>
-      <c r="BT9" s="28" t="n"/>
-      <c r="BU9" s="25" t="n"/>
-      <c r="BV9" s="29" t="n"/>
-      <c r="BW9" s="24" t="n"/>
-      <c r="BX9" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="BY9" s="27" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BZ9" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-18T05:45:54.886428Z</t>
-        </is>
-      </c>
-      <c r="CA9" s="31" t="inlineStr">
-        <is>
-          <t>fixed one-unit hypothetical scoring; no real exposure or execution</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="36" customHeight="1">
-      <c r="A10" s="24" t="inlineStr">
-        <is>
-          <t>3405fe6d522c42ec</t>
-        </is>
-      </c>
-      <c r="B10" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-17T14:02:17.091788Z</t>
-        </is>
-      </c>
-      <c r="C10" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-18T02:00Z</t>
-        </is>
-      </c>
-      <c r="D10" s="24" t="inlineStr">
-        <is>
-          <t>401857076</t>
-        </is>
-      </c>
-      <c r="E10" s="24" t="inlineStr">
-        <is>
-          <t>WNBA</t>
-        </is>
-      </c>
-      <c r="F10" s="24" t="inlineStr">
-        <is>
-          <t>Connecticut Sun</t>
-        </is>
-      </c>
-      <c r="G10" s="24" t="inlineStr">
-        <is>
-          <t>Phoenix Mercury</t>
-        </is>
-      </c>
-      <c r="H10" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I10" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J10" s="25" t="n"/>
-      <c r="K10" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L10" s="26" t="n">
-        <v>-178</v>
-      </c>
-      <c r="M10" s="27" t="n">
-        <v>1.561798</v>
-      </c>
-      <c r="N10" s="28" t="n">
-        <v>0.640288</v>
-      </c>
-      <c r="O10" s="28" t="n">
-        <v>0.672243</v>
-      </c>
-      <c r="P10" s="28" t="n"/>
-      <c r="Q10" s="28" t="n">
-        <v>0.031955</v>
-      </c>
-      <c r="R10" s="26" t="n">
-        <v>66</v>
-      </c>
-      <c r="S10" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" s="24" t="inlineStr">
-        <is>
-          <t>wnba-elo-trend-lr-v3</t>
-        </is>
-      </c>
-      <c r="U10" s="24" t="inlineStr">
-        <is>
-          <t>settled</t>
-        </is>
-      </c>
-      <c r="V10" s="24" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="W10" s="26" t="n">
-        <v>96</v>
-      </c>
-      <c r="X10" s="26" t="n">
-        <v>83</v>
-      </c>
-      <c r="Y10" s="25" t="n"/>
-      <c r="Z10" s="26" t="n"/>
-      <c r="AA10" s="28" t="n"/>
-      <c r="AB10" s="28" t="n"/>
-      <c r="AC10" s="30" t="n">
-        <v>-0</v>
-      </c>
-      <c r="AD10" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-18T05:45:54.971822Z</t>
-        </is>
-      </c>
-      <c r="AE10" s="31" t="inlineStr">
-        <is>
-          <t>Learned LR call at threshold 0.5018; executable ask 0.6400 (aec-wnba-conn-phx-2026-07-17).</t>
-        </is>
-      </c>
-      <c r="AF10" s="31" t="inlineStr">
-        <is>
-          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
-        </is>
-      </c>
-      <c r="AG10" s="24" t="inlineStr">
-        <is>
-          <t>review_required</t>
-        </is>
-      </c>
-      <c r="AH10" s="24" t="n"/>
-      <c r="AI10" s="31" t="n"/>
-      <c r="AJ10" s="31" t="n"/>
-      <c r="AK10" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL10" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM10" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN10" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO10" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_MISSING_UNCERTAINTY</t>
-        </is>
-      </c>
-      <c r="AP10" s="24" t="inlineStr">
-        <is>
-          <t>wnba-con</t>
-        </is>
-      </c>
-      <c r="AQ10" s="24" t="inlineStr">
-        <is>
-          <t>Connecticut Sun</t>
-        </is>
-      </c>
-      <c r="AR10" s="24" t="inlineStr">
-        <is>
-          <t>Connecticut Sun</t>
-        </is>
-      </c>
-      <c r="AS10" s="24" t="inlineStr">
-        <is>
-          <t>wnba-phx</t>
-        </is>
-      </c>
-      <c r="AT10" s="24" t="inlineStr">
-        <is>
-          <t>Phoenix Mercury</t>
-        </is>
-      </c>
-      <c r="AU10" s="24" t="inlineStr">
-        <is>
-          <t>Phoenix Mercury</t>
-        </is>
-      </c>
-      <c r="AV10" s="24" t="n"/>
-      <c r="AW10" s="24" t="n"/>
-      <c r="AX10" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY10" s="24" t="n"/>
-      <c r="AZ10" s="24" t="inlineStr">
-        <is>
-          <t>research</t>
-        </is>
-      </c>
-      <c r="BA10" s="24" t="inlineStr">
-        <is>
-          <t>286653236675a65e58674d10837572801218599b31772016e9d8575bfefa53b4</t>
-        </is>
-      </c>
-      <c r="BB10" s="24" t="inlineStr">
-        <is>
-          <t>learned_lr</t>
-        </is>
-      </c>
-      <c r="BC10" s="24" t="inlineStr">
-        <is>
-          <t>wnba-elo-trend-lr-v3</t>
-        </is>
-      </c>
-      <c r="BD10" s="24" t="inlineStr">
-        <is>
-          <t>286653236675a65e58674d10837572801218599b31772016e9d8575bfefa53b4</t>
-        </is>
-      </c>
-      <c r="BE10" s="24" t="inlineStr">
-        <is>
-          <t>5b26e70fb7a6c509</t>
-        </is>
-      </c>
-      <c r="BF10" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG10" s="24" t="inlineStr">
-        <is>
-          <t>wnba-elo-trend-lr-v3</t>
-        </is>
-      </c>
-      <c r="BH10" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-17T14:02:11.780961Z</t>
-        </is>
-      </c>
-      <c r="BI10" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ10" s="25" t="n"/>
-      <c r="BK10" s="26" t="n">
-        <v>-178</v>
-      </c>
-      <c r="BL10" s="27" t="n">
-        <v>1.561798</v>
-      </c>
-      <c r="BM10" s="28" t="n">
-        <v>0.640288</v>
-      </c>
-      <c r="BN10" s="28" t="n">
-        <v>0.633663</v>
-      </c>
-      <c r="BO10" s="28" t="n"/>
-      <c r="BP10" s="25" t="n"/>
-      <c r="BQ10" s="27" t="n"/>
-      <c r="BR10" s="28" t="n"/>
-      <c r="BS10" s="28" t="n"/>
-      <c r="BT10" s="28" t="n"/>
-      <c r="BU10" s="25" t="n"/>
-      <c r="BV10" s="29" t="n"/>
-      <c r="BW10" s="24" t="n"/>
-      <c r="BX10" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="BY10" s="27" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BZ10" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-18T05:45:54.971822Z</t>
-        </is>
-      </c>
-      <c r="CA10" s="31" t="inlineStr">
-        <is>
-          <t>fixed one-unit hypothetical scoring; no real exposure or execution</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="36" customHeight="1">
-      <c r="A11" s="24" t="inlineStr">
-        <is>
-          <t>93a3540bf0dd49bb</t>
-        </is>
-      </c>
-      <c r="B11" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-17T16:21:24.725309Z</t>
-        </is>
-      </c>
-      <c r="C11" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-18T20:10Z</t>
-        </is>
-      </c>
-      <c r="D11" s="24" t="inlineStr">
-        <is>
-          <t>401816163</t>
-        </is>
-      </c>
-      <c r="E11" s="24" t="inlineStr">
-        <is>
-          <t>MLB</t>
-        </is>
-      </c>
-      <c r="F11" s="24" t="inlineStr">
-        <is>
-          <t>Miami Marlins</t>
-        </is>
-      </c>
-      <c r="G11" s="24" t="inlineStr">
-        <is>
-          <t>Milwaukee Brewers</t>
-        </is>
-      </c>
-      <c r="H11" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I11" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J11" s="25" t="n"/>
-      <c r="K11" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L11" s="26" t="n">
-        <v>-130</v>
-      </c>
-      <c r="M11" s="27" t="n">
-        <v>1.769231</v>
-      </c>
-      <c r="N11" s="28" t="n">
-        <v>0.565217</v>
-      </c>
-      <c r="O11" s="28" t="n">
-        <v>0.605633</v>
-      </c>
-      <c r="P11" s="28" t="n"/>
-      <c r="Q11" s="28" t="n">
-        <v>0.040416</v>
-      </c>
-      <c r="R11" s="26" t="n">
-        <v>70</v>
-      </c>
-      <c r="S11" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v3</t>
-        </is>
-      </c>
-      <c r="U11" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V11" s="24" t="n"/>
-      <c r="W11" s="26" t="n"/>
-      <c r="X11" s="26" t="n"/>
-      <c r="Y11" s="25" t="n"/>
-      <c r="Z11" s="26" t="n"/>
-      <c r="AA11" s="28" t="n"/>
-      <c r="AB11" s="28" t="n"/>
-      <c r="AC11" s="30" t="n"/>
-      <c r="AD11" s="24" t="n"/>
-      <c r="AE11" s="31" t="inlineStr">
-        <is>
-          <t>Learned LR call at threshold 0.6018; executable ask 0.5650 (aec-mlb-mia-mil-2026-07-18).</t>
-        </is>
-      </c>
-      <c r="AF11" s="31" t="inlineStr">
-        <is>
-          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
-        </is>
-      </c>
-      <c r="AG11" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH11" s="24" t="n"/>
-      <c r="AI11" s="31" t="n"/>
-      <c r="AJ11" s="31" t="n"/>
-      <c r="AK11" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL11" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM11" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN11" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO11" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_MISSING_UNCERTAINTY</t>
-        </is>
-      </c>
-      <c r="AP11" s="24" t="inlineStr">
-        <is>
-          <t>mlb-mia</t>
-        </is>
-      </c>
-      <c r="AQ11" s="24" t="inlineStr">
-        <is>
-          <t>Miami Marlins</t>
-        </is>
-      </c>
-      <c r="AR11" s="24" t="inlineStr">
-        <is>
-          <t>Miami Marlins</t>
-        </is>
-      </c>
-      <c r="AS11" s="24" t="inlineStr">
-        <is>
-          <t>mlb-mil</t>
-        </is>
-      </c>
-      <c r="AT11" s="24" t="inlineStr">
-        <is>
-          <t>Milwaukee Brewers</t>
-        </is>
-      </c>
-      <c r="AU11" s="24" t="inlineStr">
-        <is>
-          <t>Milwaukee Brewers</t>
-        </is>
-      </c>
-      <c r="AV11" s="24" t="n"/>
-      <c r="AW11" s="24" t="n"/>
-      <c r="AX11" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY11" s="24" t="n"/>
-      <c r="AZ11" s="24" t="inlineStr">
-        <is>
-          <t>research</t>
-        </is>
-      </c>
-      <c r="BA11" s="24" t="inlineStr">
-        <is>
-          <t>a454281ab207d2924d585d6b967363fb8e88af45132e3e9d354e4351fb5c237f</t>
-        </is>
-      </c>
-      <c r="BB11" s="24" t="inlineStr">
-        <is>
-          <t>learned_lr</t>
-        </is>
-      </c>
-      <c r="BC11" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v3</t>
-        </is>
-      </c>
-      <c r="BD11" s="24" t="inlineStr">
-        <is>
-          <t>a454281ab207d2924d585d6b967363fb8e88af45132e3e9d354e4351fb5c237f</t>
-        </is>
-      </c>
-      <c r="BE11" s="24" t="inlineStr">
-        <is>
-          <t>c7348ce29d666909</t>
-        </is>
-      </c>
-      <c r="BF11" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG11" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v3</t>
-        </is>
-      </c>
-      <c r="BH11" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-17T16:21:07.161405Z</t>
-        </is>
-      </c>
-      <c r="BI11" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ11" s="25" t="n"/>
-      <c r="BK11" s="26" t="n">
-        <v>-130</v>
-      </c>
-      <c r="BL11" s="27" t="n">
-        <v>1.769231</v>
-      </c>
-      <c r="BM11" s="28" t="n">
-        <v>0.565217</v>
-      </c>
-      <c r="BN11" s="28" t="n">
-        <v>0.562189</v>
-      </c>
-      <c r="BO11" s="28" t="n"/>
-      <c r="BP11" s="25" t="n"/>
-      <c r="BQ11" s="27" t="n"/>
-      <c r="BR11" s="28" t="n"/>
-      <c r="BS11" s="28" t="n"/>
-      <c r="BT11" s="28" t="n"/>
-      <c r="BU11" s="25" t="n"/>
-      <c r="BV11" s="29" t="n"/>
-      <c r="BW11" s="24" t="n"/>
-      <c r="BX11" s="30" t="n"/>
-      <c r="BY11" s="27" t="n"/>
-      <c r="BZ11" s="24" t="n"/>
-      <c r="CA11" s="31" t="n"/>
-    </row>
-    <row r="12" ht="36" customHeight="1">
-      <c r="A12" s="24" t="inlineStr">
-        <is>
-          <t>c884dc7cf1104640</t>
-        </is>
-      </c>
-      <c r="B12" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-17T16:21:30.375686Z</t>
-        </is>
-      </c>
-      <c r="C12" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-19T00:00Z</t>
-        </is>
-      </c>
-      <c r="D12" s="24" t="inlineStr">
-        <is>
-          <t>401857077</t>
-        </is>
-      </c>
-      <c r="E12" s="24" t="inlineStr">
-        <is>
-          <t>WNBA</t>
-        </is>
-      </c>
-      <c r="F12" s="24" t="inlineStr">
-        <is>
-          <t>New York Liberty</t>
-        </is>
-      </c>
-      <c r="G12" s="24" t="inlineStr">
-        <is>
-          <t>Indiana Fever</t>
-        </is>
-      </c>
-      <c r="H12" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I12" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J12" s="25" t="n"/>
-      <c r="K12" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L12" s="26" t="n">
-        <v>117</v>
-      </c>
-      <c r="M12" s="27" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="N12" s="28" t="n">
-        <v>0.460829</v>
-      </c>
-      <c r="O12" s="28" t="n">
-        <v>0.632778</v>
-      </c>
-      <c r="P12" s="28" t="n"/>
-      <c r="Q12" s="28" t="n">
-        <v>0.171949</v>
-      </c>
-      <c r="R12" s="26" t="n">
-        <v>100</v>
-      </c>
-      <c r="S12" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" s="24" t="inlineStr">
-        <is>
-          <t>wnba-elo-trend-lr-v3</t>
-        </is>
-      </c>
-      <c r="U12" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V12" s="24" t="n"/>
-      <c r="W12" s="26" t="n"/>
-      <c r="X12" s="26" t="n"/>
-      <c r="Y12" s="25" t="n"/>
-      <c r="Z12" s="26" t="n"/>
-      <c r="AA12" s="28" t="n"/>
-      <c r="AB12" s="28" t="n"/>
-      <c r="AC12" s="30" t="n"/>
-      <c r="AD12" s="24" t="n"/>
-      <c r="AE12" s="31" t="inlineStr">
-        <is>
-          <t>Learned LR call at threshold 0.5018; executable ask 0.4600 (aec-wnba-ny-ind-2026-07-18).</t>
-        </is>
-      </c>
-      <c r="AF12" s="31" t="inlineStr">
-        <is>
-          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
-        </is>
-      </c>
-      <c r="AG12" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH12" s="24" t="n"/>
-      <c r="AI12" s="31" t="n"/>
-      <c r="AJ12" s="31" t="n"/>
-      <c r="AK12" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL12" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM12" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN12" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO12" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_MISSING_UNCERTAINTY</t>
-        </is>
-      </c>
-      <c r="AP12" s="24" t="inlineStr">
-        <is>
-          <t>wnba-nyl</t>
-        </is>
-      </c>
-      <c r="AQ12" s="24" t="inlineStr">
-        <is>
-          <t>New York Liberty</t>
-        </is>
-      </c>
-      <c r="AR12" s="24" t="inlineStr">
-        <is>
-          <t>New York Liberty</t>
-        </is>
-      </c>
-      <c r="AS12" s="24" t="inlineStr">
-        <is>
-          <t>wnba-ind</t>
-        </is>
-      </c>
-      <c r="AT12" s="24" t="inlineStr">
-        <is>
-          <t>Indiana Fever</t>
-        </is>
-      </c>
-      <c r="AU12" s="24" t="inlineStr">
-        <is>
-          <t>Indiana Fever</t>
-        </is>
-      </c>
-      <c r="AV12" s="24" t="n"/>
-      <c r="AW12" s="24" t="n"/>
-      <c r="AX12" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY12" s="24" t="n"/>
-      <c r="AZ12" s="24" t="inlineStr">
-        <is>
-          <t>research</t>
-        </is>
-      </c>
-      <c r="BA12" s="24" t="inlineStr">
-        <is>
-          <t>286653236675a65e58674d10837572801218599b31772016e9d8575bfefa53b4</t>
-        </is>
-      </c>
-      <c r="BB12" s="24" t="inlineStr">
-        <is>
-          <t>learned_lr</t>
-        </is>
-      </c>
-      <c r="BC12" s="24" t="inlineStr">
-        <is>
-          <t>wnba-elo-trend-lr-v3</t>
-        </is>
-      </c>
-      <c r="BD12" s="24" t="inlineStr">
-        <is>
-          <t>286653236675a65e58674d10837572801218599b31772016e9d8575bfefa53b4</t>
-        </is>
-      </c>
-      <c r="BE12" s="24" t="inlineStr">
-        <is>
-          <t>e4f3f616d306cafe</t>
-        </is>
-      </c>
-      <c r="BF12" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG12" s="24" t="inlineStr">
-        <is>
-          <t>wnba-elo-trend-lr-v3</t>
-        </is>
-      </c>
-      <c r="BH12" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-17T16:21:13.188564Z</t>
-        </is>
-      </c>
-      <c r="BI12" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ12" s="25" t="n"/>
-      <c r="BK12" s="26" t="n">
-        <v>117</v>
-      </c>
-      <c r="BL12" s="27" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="BM12" s="28" t="n">
-        <v>0.460829</v>
-      </c>
-      <c r="BN12" s="28" t="n">
-        <v>0.455446</v>
-      </c>
-      <c r="BO12" s="28" t="n"/>
-      <c r="BP12" s="25" t="n"/>
-      <c r="BQ12" s="27" t="n"/>
-      <c r="BR12" s="28" t="n"/>
-      <c r="BS12" s="28" t="n"/>
-      <c r="BT12" s="28" t="n"/>
-      <c r="BU12" s="25" t="n"/>
-      <c r="BV12" s="29" t="n"/>
-      <c r="BW12" s="24" t="n"/>
-      <c r="BX12" s="30" t="n"/>
-      <c r="BY12" s="27" t="n"/>
-      <c r="BZ12" s="24" t="n"/>
-      <c r="CA12" s="31" t="n"/>
-    </row>
-    <row r="13" ht="36" customHeight="1">
-      <c r="A13" s="24" t="inlineStr">
-        <is>
-          <t>4c2ec934da05478b</t>
-        </is>
-      </c>
-      <c r="B13" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-18T05:45:47.429402Z</t>
-        </is>
-      </c>
-      <c r="C13" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-18T18:20Z</t>
-        </is>
-      </c>
-      <c r="D13" s="24" t="inlineStr">
-        <is>
-          <t>401816164</t>
-        </is>
-      </c>
-      <c r="E13" s="24" t="inlineStr">
-        <is>
-          <t>MLB</t>
-        </is>
-      </c>
-      <c r="F13" s="24" t="inlineStr">
-        <is>
-          <t>Minnesota Twins</t>
-        </is>
-      </c>
-      <c r="G13" s="24" t="inlineStr">
-        <is>
-          <t>Chicago Cubs</t>
-        </is>
-      </c>
-      <c r="H13" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I13" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J13" s="25" t="n"/>
-      <c r="K13" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L13" s="26" t="n">
-        <v>-133</v>
-      </c>
-      <c r="M13" s="27" t="n">
-        <v>1.75188</v>
-      </c>
-      <c r="N13" s="28" t="n">
-        <v>0.570815</v>
-      </c>
-      <c r="O13" s="28" t="n">
-        <v>0.606876</v>
-      </c>
-      <c r="P13" s="28" t="n"/>
-      <c r="Q13" s="28" t="n">
-        <v>0.036061</v>
-      </c>
-      <c r="R13" s="26" t="n">
-        <v>68</v>
-      </c>
-      <c r="S13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v3</t>
-        </is>
-      </c>
-      <c r="U13" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V13" s="24" t="n"/>
-      <c r="W13" s="26" t="n"/>
-      <c r="X13" s="26" t="n"/>
-      <c r="Y13" s="25" t="n"/>
-      <c r="Z13" s="26" t="n"/>
-      <c r="AA13" s="28" t="n"/>
-      <c r="AB13" s="28" t="n"/>
-      <c r="AC13" s="30" t="n"/>
-      <c r="AD13" s="24" t="n"/>
-      <c r="AE13" s="31" t="inlineStr">
-        <is>
-          <t>Learned LR call at threshold 0.6018; executable ask 0.5700 (aec-mlb-min-chc-2026-07-18).</t>
-        </is>
-      </c>
-      <c r="AF13" s="31" t="inlineStr">
-        <is>
-          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
-        </is>
-      </c>
-      <c r="AG13" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH13" s="24" t="n"/>
-      <c r="AI13" s="31" t="n"/>
-      <c r="AJ13" s="31" t="n"/>
-      <c r="AK13" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL13" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM13" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN13" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO13" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_MISSING_UNCERTAINTY</t>
-        </is>
-      </c>
-      <c r="AP13" s="24" t="inlineStr">
-        <is>
-          <t>mlb-min</t>
-        </is>
-      </c>
-      <c r="AQ13" s="24" t="inlineStr">
-        <is>
-          <t>Minnesota Twins</t>
-        </is>
-      </c>
-      <c r="AR13" s="24" t="inlineStr">
-        <is>
-          <t>Minnesota Twins</t>
-        </is>
-      </c>
-      <c r="AS13" s="24" t="inlineStr">
-        <is>
-          <t>mlb-chc</t>
-        </is>
-      </c>
-      <c r="AT13" s="24" t="inlineStr">
-        <is>
-          <t>Chicago Cubs</t>
-        </is>
-      </c>
-      <c r="AU13" s="24" t="inlineStr">
-        <is>
-          <t>Chicago Cubs</t>
-        </is>
-      </c>
-      <c r="AV13" s="24" t="n"/>
-      <c r="AW13" s="24" t="n"/>
-      <c r="AX13" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY13" s="24" t="n"/>
-      <c r="AZ13" s="24" t="inlineStr">
-        <is>
-          <t>research</t>
-        </is>
-      </c>
-      <c r="BA13" s="24" t="inlineStr">
-        <is>
-          <t>a454281ab207d2924d585d6b967363fb8e88af45132e3e9d354e4351fb5c237f</t>
-        </is>
-      </c>
-      <c r="BB13" s="24" t="inlineStr">
-        <is>
-          <t>learned_lr</t>
-        </is>
-      </c>
-      <c r="BC13" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v3</t>
-        </is>
-      </c>
-      <c r="BD13" s="24" t="inlineStr">
-        <is>
-          <t>a454281ab207d2924d585d6b967363fb8e88af45132e3e9d354e4351fb5c237f</t>
-        </is>
-      </c>
-      <c r="BE13" s="24" t="inlineStr">
-        <is>
-          <t>3acab0aa8ac04a91</t>
-        </is>
-      </c>
-      <c r="BF13" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG13" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v3</t>
-        </is>
-      </c>
-      <c r="BH13" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-18T05:44:27.731285Z</t>
-        </is>
-      </c>
-      <c r="BI13" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ13" s="25" t="n"/>
-      <c r="BK13" s="26" t="n">
-        <v>-133</v>
-      </c>
-      <c r="BL13" s="27" t="n">
-        <v>1.75188</v>
-      </c>
-      <c r="BM13" s="28" t="n">
-        <v>0.570815</v>
-      </c>
-      <c r="BN13" s="28" t="n">
-        <v>0.567164</v>
-      </c>
-      <c r="BO13" s="28" t="n"/>
-      <c r="BP13" s="25" t="n"/>
-      <c r="BQ13" s="27" t="n"/>
-      <c r="BR13" s="28" t="n"/>
-      <c r="BS13" s="28" t="n"/>
-      <c r="BT13" s="28" t="n"/>
-      <c r="BU13" s="25" t="n"/>
-      <c r="BV13" s="29" t="n"/>
-      <c r="BW13" s="24" t="n"/>
-      <c r="BX13" s="30" t="n"/>
-      <c r="BY13" s="27" t="n"/>
-      <c r="BZ13" s="24" t="n"/>
-      <c r="CA13" s="31" t="n"/>
-    </row>
+    <row r="8" ht="36" customHeight="1"/>
+    <row r="9" ht="36" customHeight="1"/>
+    <row r="10" ht="36" customHeight="1"/>
+    <row r="11" ht="36" customHeight="1"/>
+    <row r="12" ht="36" customHeight="1"/>
+    <row r="13" ht="36" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/picks.xlsx
+++ b/data/picks.xlsx
@@ -21,10 +21,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="0.0%"/>
-    <numFmt numFmtId="165" formatCode="0.0000"/>
-    <numFmt numFmtId="166" formatCode="0.0###"/>
-    <numFmt numFmtId="167" formatCode="0.000000"/>
+    <numFmt numFmtId="164" formatCode="0.0###"/>
+    <numFmt numFmtId="165" formatCode="0.000000"/>
+    <numFmt numFmtId="166" formatCode="0.0000"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -136,7 +136,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -150,10 +150,10 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -169,10 +169,10 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -184,10 +184,10 @@
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -202,13 +202,13 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="10" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -217,38 +217,11 @@
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -327,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CA13" headerRowCount="1">
-  <autoFilter ref="A1:CA13"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CA9" headerRowCount="1">
+  <autoFilter ref="A1:CA9"/>
   <tableColumns count="79">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -765,19 +738,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$13)</f>
+        <f>COUNTA('Picks'!$A$2:$A$9)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$13,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$9,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$13,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$9,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$13,"settled",'Picks'!$V$2:$V$13,"win")+COUNTIFS('Picks'!$U$2:$U$13,"settled",'Picks'!$V$2:$V$13,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$9,"settled",'Picks'!$V$2:$V$9,"win")+COUNTIFS('Picks'!$U$2:$U$9,"settled",'Picks'!$V$2:$V$9,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -805,19 +778,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$13,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$9,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$13,"&gt;0",'Picks'!$V$2:$V$13,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$13,"&gt;0",'Picks'!$V$2:$V$13,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$9,"&gt;0",'Picks'!$V$2:$V$9,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$9,"&gt;0",'Picks'!$V$2:$V$9,"loss")</f>
         <v/>
       </c>
-      <c r="E7" s="32">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$13,"&gt;0",'Picks'!$V$2:$V$13,"win")/(COUNTIFS('Picks'!$BX$2:$BX$13,"&gt;0",'Picks'!$V$2:$V$13,"win")+COUNTIFS('Picks'!$BX$2:$BX$13,"&gt;0",'Picks'!$V$2:$V$13,"loss")),0)</f>
+      <c r="E7" s="7">
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$9,"&gt;0",'Picks'!$V$2:$V$9,"win")/(COUNTIFS('Picks'!$BX$2:$BX$9,"&gt;0",'Picks'!$V$2:$V$9,"win")+COUNTIFS('Picks'!$BX$2:$BX$9,"&gt;0",'Picks'!$V$2:$V$9,"loss")),0)</f>
         <v/>
       </c>
-      <c r="G7" s="32">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$13)/SUM('Picks'!$BX$2:$BX$13),0)</f>
+      <c r="G7" s="7">
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$9)/SUM('Picks'!$BX$2:$BX$9),0)</f>
         <v/>
       </c>
     </row>
@@ -844,20 +817,20 @@
       </c>
     </row>
     <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="33">
-        <f>SUM('Picks'!$BY$2:$BY$13)</f>
+      <c r="A10" s="8">
+        <f>SUM('Picks'!$BY$2:$BY$9)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$13,"&lt;&gt;",'Picks'!$AB$2:$AB$13),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$9,"&lt;&gt;",'Picks'!$AB$2:$AB$9),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$13,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$13,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$9,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$9,"settled")</f>
         <v/>
       </c>
-      <c r="G10" s="33">
-        <f>SUMIFS('Picks'!$AC$2:$AC$13,'Picks'!$AM$2:$AM$13,"QUALIFIED_SHADOW_CALL")</f>
+      <c r="G10" s="8">
+        <f>SUMIFS('Picks'!$AC$2:$AC$9,'Picks'!$AM$2:$AM$9,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -912,27 +885,27 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$13,$A14,'Picks'!$U$2:$U$13,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$9,$A14,'Picks'!$U$2:$U$9,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$13,$A14,'Picks'!$U$2:$U$13,"settled",'Picks'!$V$2:$V$13,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$9,$A14,'Picks'!$U$2:$U$9,"settled",'Picks'!$V$2:$V$9,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$13,$A14,'Picks'!$U$2:$U$13,"settled",'Picks'!$V$2:$V$13,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$9,$A14,'Picks'!$U$2:$U$9,"settled",'Picks'!$V$2:$V$9,"loss")</f>
         <v/>
       </c>
-      <c r="E14" s="34">
+      <c r="E14" s="14">
         <f>IFERROR(C14/(C14+D14),0)</f>
         <v/>
       </c>
-      <c r="F14" s="35">
-        <f>SUMIFS('Picks'!$BY$2:$BY$13,'Picks'!$H$2:$H$13,$A14)</f>
+      <c r="F14" s="15">
+        <f>SUMIFS('Picks'!$BY$2:$BY$9,'Picks'!$H$2:$H$9,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$13,'Picks'!$H$2:$H$13,$A14,'Picks'!$U$2:$U$13,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$9,'Picks'!$H$2:$H$9,$A14,'Picks'!$U$2:$U$9,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -943,27 +916,27 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$13,$A15,'Picks'!$U$2:$U$13,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$9,$A15,'Picks'!$U$2:$U$9,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$13,$A15,'Picks'!$U$2:$U$13,"settled",'Picks'!$V$2:$V$13,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$9,$A15,'Picks'!$U$2:$U$9,"settled",'Picks'!$V$2:$V$9,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$13,$A15,'Picks'!$U$2:$U$13,"settled",'Picks'!$V$2:$V$13,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$9,$A15,'Picks'!$U$2:$U$9,"settled",'Picks'!$V$2:$V$9,"loss")</f>
         <v/>
       </c>
-      <c r="E15" s="36">
+      <c r="E15" s="19">
         <f>IFERROR(C15/(C15+D15),0)</f>
         <v/>
       </c>
-      <c r="F15" s="37">
-        <f>SUMIFS('Picks'!$BY$2:$BY$13,'Picks'!$H$2:$H$13,$A15)</f>
+      <c r="F15" s="20">
+        <f>SUMIFS('Picks'!$BY$2:$BY$9,'Picks'!$H$2:$H$9,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$13,'Picks'!$H$2:$H$13,$A15,'Picks'!$U$2:$U$13,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$9,'Picks'!$H$2:$H$9,$A15,'Picks'!$U$2:$U$9,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -974,27 +947,27 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$13,$A16,'Picks'!$U$2:$U$13,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$9,$A16,'Picks'!$U$2:$U$9,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$13,$A16,'Picks'!$U$2:$U$13,"settled",'Picks'!$V$2:$V$13,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$9,$A16,'Picks'!$U$2:$U$9,"settled",'Picks'!$V$2:$V$9,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$13,$A16,'Picks'!$U$2:$U$13,"settled",'Picks'!$V$2:$V$13,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$9,$A16,'Picks'!$U$2:$U$9,"settled",'Picks'!$V$2:$V$9,"loss")</f>
         <v/>
       </c>
-      <c r="E16" s="34">
+      <c r="E16" s="14">
         <f>IFERROR(C16/(C16+D16),0)</f>
         <v/>
       </c>
-      <c r="F16" s="35">
-        <f>SUMIFS('Picks'!$BY$2:$BY$13,'Picks'!$H$2:$H$13,$A16)</f>
+      <c r="F16" s="15">
+        <f>SUMIFS('Picks'!$BY$2:$BY$9,'Picks'!$H$2:$H$9,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$13,'Picks'!$H$2:$H$13,$A16,'Picks'!$U$2:$U$13,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$9,'Picks'!$H$2:$H$9,$A16,'Picks'!$U$2:$U$9,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1023,7 +996,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CA7"/>
+  <dimension ref="A1:CA9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1550,7 +1523,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J2" s="38" t="n"/>
+      <c r="J2" s="25" t="n"/>
       <c r="K2" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -1559,7 +1532,7 @@
       <c r="L2" s="26" t="n">
         <v>-141</v>
       </c>
-      <c r="M2" s="39" t="n">
+      <c r="M2" s="27" t="n">
         <v>1.70922</v>
       </c>
       <c r="N2" s="28" t="n">
@@ -1599,7 +1572,7 @@
       <c r="X2" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y2" s="38" t="n"/>
+      <c r="Y2" s="25" t="n"/>
       <c r="Z2" s="26" t="n">
         <v>-147</v>
       </c>
@@ -1609,7 +1582,7 @@
       <c r="AB2" s="28" t="n">
         <v>0.009938000000000001</v>
       </c>
-      <c r="AC2" s="40" t="n">
+      <c r="AC2" s="30" t="n">
         <v>0</v>
       </c>
       <c r="AD2" s="24" t="inlineStr">
@@ -1746,11 +1719,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ2" s="38" t="n"/>
+      <c r="BJ2" s="25" t="n"/>
       <c r="BK2" s="26" t="n">
         <v>-141</v>
       </c>
-      <c r="BL2" s="39" t="n">
+      <c r="BL2" s="27" t="n">
         <v>1.70922</v>
       </c>
       <c r="BM2" s="28" t="n">
@@ -1760,8 +1733,8 @@
         <v>0.58209</v>
       </c>
       <c r="BO2" s="28" t="n"/>
-      <c r="BP2" s="38" t="n"/>
-      <c r="BQ2" s="39" t="n">
+      <c r="BP2" s="25" t="n"/>
+      <c r="BQ2" s="27" t="n">
         <v>1.680272</v>
       </c>
       <c r="BR2" s="28" t="n">
@@ -1769,13 +1742,13 @@
       </c>
       <c r="BS2" s="28" t="n"/>
       <c r="BT2" s="28" t="n"/>
-      <c r="BU2" s="38" t="n"/>
+      <c r="BU2" s="25" t="n"/>
       <c r="BV2" s="29" t="n"/>
       <c r="BW2" s="24" t="n"/>
-      <c r="BX2" s="40" t="n">
+      <c r="BX2" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY2" s="39" t="n">
+      <c r="BY2" s="27" t="n">
         <v>0.70922</v>
       </c>
       <c r="BZ2" s="24" t="inlineStr">
@@ -1835,7 +1808,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J3" s="38" t="n"/>
+      <c r="J3" s="25" t="n"/>
       <c r="K3" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -1844,7 +1817,7 @@
       <c r="L3" s="26" t="n">
         <v>-130</v>
       </c>
-      <c r="M3" s="39" t="n">
+      <c r="M3" s="27" t="n">
         <v>1.769231</v>
       </c>
       <c r="N3" s="28" t="n">
@@ -1884,7 +1857,7 @@
       <c r="X3" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y3" s="38" t="n"/>
+      <c r="Y3" s="25" t="n"/>
       <c r="Z3" s="26" t="n">
         <v>-133</v>
       </c>
@@ -1894,7 +1867,7 @@
       <c r="AB3" s="28" t="n">
         <v>0.004783</v>
       </c>
-      <c r="AC3" s="40" t="n">
+      <c r="AC3" s="30" t="n">
         <v>0</v>
       </c>
       <c r="AD3" s="24" t="inlineStr">
@@ -2031,11 +2004,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ3" s="38" t="n"/>
+      <c r="BJ3" s="25" t="n"/>
       <c r="BK3" s="26" t="n">
         <v>-130</v>
       </c>
-      <c r="BL3" s="39" t="n">
+      <c r="BL3" s="27" t="n">
         <v>1.769231</v>
       </c>
       <c r="BM3" s="28" t="n">
@@ -2045,8 +2018,8 @@
         <v>0.562189</v>
       </c>
       <c r="BO3" s="28" t="n"/>
-      <c r="BP3" s="38" t="n"/>
-      <c r="BQ3" s="39" t="n">
+      <c r="BP3" s="25" t="n"/>
+      <c r="BQ3" s="27" t="n">
         <v>1.75188</v>
       </c>
       <c r="BR3" s="28" t="n">
@@ -2054,13 +2027,13 @@
       </c>
       <c r="BS3" s="28" t="n"/>
       <c r="BT3" s="28" t="n"/>
-      <c r="BU3" s="38" t="n"/>
+      <c r="BU3" s="25" t="n"/>
       <c r="BV3" s="29" t="n"/>
       <c r="BW3" s="24" t="n"/>
-      <c r="BX3" s="40" t="n">
+      <c r="BX3" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY3" s="39" t="n">
+      <c r="BY3" s="27" t="n">
         <v>-1</v>
       </c>
       <c r="BZ3" s="24" t="inlineStr">
@@ -2120,7 +2093,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J4" s="38" t="n"/>
+      <c r="J4" s="25" t="n"/>
       <c r="K4" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -2129,7 +2102,7 @@
       <c r="L4" s="26" t="n">
         <v>-141</v>
       </c>
-      <c r="M4" s="39" t="n">
+      <c r="M4" s="27" t="n">
         <v>1.70922</v>
       </c>
       <c r="N4" s="28" t="n">
@@ -2169,7 +2142,7 @@
       <c r="X4" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y4" s="38" t="n"/>
+      <c r="Y4" s="25" t="n"/>
       <c r="Z4" s="26" t="n">
         <v>-147</v>
       </c>
@@ -2179,7 +2152,7 @@
       <c r="AB4" s="28" t="n">
         <v>0.009938000000000001</v>
       </c>
-      <c r="AC4" s="40" t="n">
+      <c r="AC4" s="30" t="n">
         <v>0</v>
       </c>
       <c r="AD4" s="24" t="inlineStr">
@@ -2316,11 +2289,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ4" s="38" t="n"/>
+      <c r="BJ4" s="25" t="n"/>
       <c r="BK4" s="26" t="n">
         <v>-141</v>
       </c>
-      <c r="BL4" s="39" t="n">
+      <c r="BL4" s="27" t="n">
         <v>1.70922</v>
       </c>
       <c r="BM4" s="28" t="n">
@@ -2330,8 +2303,8 @@
         <v>0.58209</v>
       </c>
       <c r="BO4" s="28" t="n"/>
-      <c r="BP4" s="38" t="n"/>
-      <c r="BQ4" s="39" t="n">
+      <c r="BP4" s="25" t="n"/>
+      <c r="BQ4" s="27" t="n">
         <v>1.680272</v>
       </c>
       <c r="BR4" s="28" t="n">
@@ -2339,13 +2312,13 @@
       </c>
       <c r="BS4" s="28" t="n"/>
       <c r="BT4" s="28" t="n"/>
-      <c r="BU4" s="38" t="n"/>
+      <c r="BU4" s="25" t="n"/>
       <c r="BV4" s="29" t="n"/>
       <c r="BW4" s="24" t="n"/>
-      <c r="BX4" s="40" t="n">
+      <c r="BX4" s="30" t="n">
         <v>1.5</v>
       </c>
-      <c r="BY4" s="39" t="n">
+      <c r="BY4" s="27" t="n">
         <v>1.06383</v>
       </c>
       <c r="BZ4" s="24" t="inlineStr">
@@ -2405,7 +2378,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J5" s="38" t="n"/>
+      <c r="J5" s="25" t="n"/>
       <c r="K5" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -2414,7 +2387,7 @@
       <c r="L5" s="26" t="n">
         <v>-130</v>
       </c>
-      <c r="M5" s="39" t="n">
+      <c r="M5" s="27" t="n">
         <v>1.769231</v>
       </c>
       <c r="N5" s="28" t="n">
@@ -2454,7 +2427,7 @@
       <c r="X5" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y5" s="38" t="n"/>
+      <c r="Y5" s="25" t="n"/>
       <c r="Z5" s="26" t="n">
         <v>-133</v>
       </c>
@@ -2464,7 +2437,7 @@
       <c r="AB5" s="28" t="n">
         <v>0.004783</v>
       </c>
-      <c r="AC5" s="40" t="n">
+      <c r="AC5" s="30" t="n">
         <v>0</v>
       </c>
       <c r="AD5" s="24" t="inlineStr">
@@ -2601,11 +2574,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ5" s="38" t="n"/>
+      <c r="BJ5" s="25" t="n"/>
       <c r="BK5" s="26" t="n">
         <v>-130</v>
       </c>
-      <c r="BL5" s="39" t="n">
+      <c r="BL5" s="27" t="n">
         <v>1.769231</v>
       </c>
       <c r="BM5" s="28" t="n">
@@ -2615,8 +2588,8 @@
         <v>0.562189</v>
       </c>
       <c r="BO5" s="28" t="n"/>
-      <c r="BP5" s="38" t="n"/>
-      <c r="BQ5" s="39" t="n">
+      <c r="BP5" s="25" t="n"/>
+      <c r="BQ5" s="27" t="n">
         <v>1.75188</v>
       </c>
       <c r="BR5" s="28" t="n">
@@ -2624,13 +2597,13 @@
       </c>
       <c r="BS5" s="28" t="n"/>
       <c r="BT5" s="28" t="n"/>
-      <c r="BU5" s="38" t="n"/>
+      <c r="BU5" s="25" t="n"/>
       <c r="BV5" s="29" t="n"/>
       <c r="BW5" s="24" t="n"/>
-      <c r="BX5" s="40" t="n">
+      <c r="BX5" s="30" t="n">
         <v>1.5</v>
       </c>
-      <c r="BY5" s="39" t="n">
+      <c r="BY5" s="27" t="n">
         <v>-1.5</v>
       </c>
       <c r="BZ5" s="24" t="inlineStr">
@@ -2690,7 +2663,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J6" s="38" t="n"/>
+      <c r="J6" s="25" t="n"/>
       <c r="K6" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -2699,7 +2672,7 @@
       <c r="L6" s="26" t="n">
         <v>-130</v>
       </c>
-      <c r="M6" s="39" t="n">
+      <c r="M6" s="27" t="n">
         <v>1.769231</v>
       </c>
       <c r="N6" s="28" t="n">
@@ -2731,11 +2704,11 @@
       <c r="V6" s="24" t="n"/>
       <c r="W6" s="26" t="n"/>
       <c r="X6" s="26" t="n"/>
-      <c r="Y6" s="38" t="n"/>
+      <c r="Y6" s="25" t="n"/>
       <c r="Z6" s="26" t="n"/>
       <c r="AA6" s="28" t="n"/>
       <c r="AB6" s="28" t="n"/>
-      <c r="AC6" s="40" t="n"/>
+      <c r="AC6" s="30" t="n"/>
       <c r="AD6" s="24" t="n"/>
       <c r="AE6" s="31" t="inlineStr">
         <is>
@@ -2866,11 +2839,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ6" s="38" t="n"/>
+      <c r="BJ6" s="25" t="n"/>
       <c r="BK6" s="26" t="n">
         <v>-130</v>
       </c>
-      <c r="BL6" s="39" t="n">
+      <c r="BL6" s="27" t="n">
         <v>1.769231</v>
       </c>
       <c r="BM6" s="28" t="n">
@@ -2880,16 +2853,16 @@
         <v>0.562189</v>
       </c>
       <c r="BO6" s="28" t="n"/>
-      <c r="BP6" s="38" t="n"/>
-      <c r="BQ6" s="39" t="n"/>
+      <c r="BP6" s="25" t="n"/>
+      <c r="BQ6" s="27" t="n"/>
       <c r="BR6" s="28" t="n"/>
       <c r="BS6" s="28" t="n"/>
       <c r="BT6" s="28" t="n"/>
-      <c r="BU6" s="38" t="n"/>
+      <c r="BU6" s="25" t="n"/>
       <c r="BV6" s="29" t="n"/>
       <c r="BW6" s="24" t="n"/>
-      <c r="BX6" s="40" t="n"/>
-      <c r="BY6" s="39" t="n"/>
+      <c r="BX6" s="30" t="n"/>
+      <c r="BY6" s="27" t="n"/>
       <c r="BZ6" s="24" t="n"/>
       <c r="CA6" s="31" t="n"/>
     </row>
@@ -2939,7 +2912,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J7" s="38" t="n"/>
+      <c r="J7" s="25" t="n"/>
       <c r="K7" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -2948,7 +2921,7 @@
       <c r="L7" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="M7" s="39" t="n">
+      <c r="M7" s="27" t="n">
         <v>1.75188</v>
       </c>
       <c r="N7" s="28" t="n">
@@ -2980,11 +2953,11 @@
       <c r="V7" s="24" t="n"/>
       <c r="W7" s="26" t="n"/>
       <c r="X7" s="26" t="n"/>
-      <c r="Y7" s="38" t="n"/>
+      <c r="Y7" s="25" t="n"/>
       <c r="Z7" s="26" t="n"/>
       <c r="AA7" s="28" t="n"/>
       <c r="AB7" s="28" t="n"/>
-      <c r="AC7" s="40" t="n"/>
+      <c r="AC7" s="30" t="n"/>
       <c r="AD7" s="24" t="n"/>
       <c r="AE7" s="31" t="inlineStr">
         <is>
@@ -3115,11 +3088,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ7" s="38" t="n"/>
+      <c r="BJ7" s="25" t="n"/>
       <c r="BK7" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="BL7" s="39" t="n">
+      <c r="BL7" s="27" t="n">
         <v>1.75188</v>
       </c>
       <c r="BM7" s="28" t="n">
@@ -3129,25 +3102,517 @@
         <v>0.567164</v>
       </c>
       <c r="BO7" s="28" t="n"/>
-      <c r="BP7" s="38" t="n"/>
-      <c r="BQ7" s="39" t="n"/>
+      <c r="BP7" s="25" t="n"/>
+      <c r="BQ7" s="27" t="n"/>
       <c r="BR7" s="28" t="n"/>
       <c r="BS7" s="28" t="n"/>
       <c r="BT7" s="28" t="n"/>
-      <c r="BU7" s="38" t="n"/>
+      <c r="BU7" s="25" t="n"/>
       <c r="BV7" s="29" t="n"/>
       <c r="BW7" s="24" t="n"/>
-      <c r="BX7" s="40" t="n"/>
-      <c r="BY7" s="39" t="n"/>
+      <c r="BX7" s="30" t="n"/>
+      <c r="BY7" s="27" t="n"/>
       <c r="BZ7" s="24" t="n"/>
       <c r="CA7" s="31" t="n"/>
     </row>
-    <row r="8" ht="36" customHeight="1"/>
-    <row r="9" ht="36" customHeight="1"/>
-    <row r="10" ht="36" customHeight="1"/>
-    <row r="11" ht="36" customHeight="1"/>
-    <row r="12" ht="36" customHeight="1"/>
-    <row r="13" ht="36" customHeight="1"/>
+    <row r="8" ht="36" customHeight="1">
+      <c r="A8" s="24" t="inlineStr">
+        <is>
+          <t>ef7830f025d54963</t>
+        </is>
+      </c>
+      <c r="B8" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-18T07:12:56.298602Z</t>
+        </is>
+      </c>
+      <c r="C8" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-19T00:00Z</t>
+        </is>
+      </c>
+      <c r="D8" s="24" t="inlineStr">
+        <is>
+          <t>401857077</t>
+        </is>
+      </c>
+      <c r="E8" s="24" t="inlineStr">
+        <is>
+          <t>WNBA</t>
+        </is>
+      </c>
+      <c r="F8" s="24" t="inlineStr">
+        <is>
+          <t>New York Liberty</t>
+        </is>
+      </c>
+      <c r="G8" s="24" t="inlineStr">
+        <is>
+          <t>Indiana Fever</t>
+        </is>
+      </c>
+      <c r="H8" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I8" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J8" s="25" t="n"/>
+      <c r="K8" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L8" s="26" t="n">
+        <v>117</v>
+      </c>
+      <c r="M8" s="27" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="N8" s="28" t="n">
+        <v>0.460829</v>
+      </c>
+      <c r="O8" s="28" t="n">
+        <v>0.593309</v>
+      </c>
+      <c r="P8" s="28" t="n"/>
+      <c r="Q8" s="28" t="n">
+        <v>0.13248</v>
+      </c>
+      <c r="R8" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S8" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="U8" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V8" s="24" t="n"/>
+      <c r="W8" s="26" t="n"/>
+      <c r="X8" s="26" t="n"/>
+      <c r="Y8" s="25" t="n"/>
+      <c r="Z8" s="26" t="n"/>
+      <c r="AA8" s="28" t="n"/>
+      <c r="AB8" s="28" t="n"/>
+      <c r="AC8" s="30" t="n"/>
+      <c r="AD8" s="24" t="n"/>
+      <c r="AE8" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5413; executable ask 0.4600 (aec-wnba-ny-ind-2026-07-18).</t>
+        </is>
+      </c>
+      <c r="AF8" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
+        </is>
+      </c>
+      <c r="AG8" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH8" s="24" t="n"/>
+      <c r="AI8" s="31" t="n"/>
+      <c r="AJ8" s="31" t="n"/>
+      <c r="AK8" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL8" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM8" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN8" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO8" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP8" s="24" t="inlineStr">
+        <is>
+          <t>wnba-nyl</t>
+        </is>
+      </c>
+      <c r="AQ8" s="24" t="inlineStr">
+        <is>
+          <t>New York Liberty</t>
+        </is>
+      </c>
+      <c r="AR8" s="24" t="inlineStr">
+        <is>
+          <t>New York Liberty</t>
+        </is>
+      </c>
+      <c r="AS8" s="24" t="inlineStr">
+        <is>
+          <t>wnba-ind</t>
+        </is>
+      </c>
+      <c r="AT8" s="24" t="inlineStr">
+        <is>
+          <t>Indiana Fever</t>
+        </is>
+      </c>
+      <c r="AU8" s="24" t="inlineStr">
+        <is>
+          <t>Indiana Fever</t>
+        </is>
+      </c>
+      <c r="AV8" s="24" t="n"/>
+      <c r="AW8" s="24" t="n"/>
+      <c r="AX8" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY8" s="24" t="n"/>
+      <c r="AZ8" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA8" s="24" t="inlineStr">
+        <is>
+          <t>6b38a269117f4c6c1ae1e324273c2f9b9d11b2c15d99242f39aa89882d15db32</t>
+        </is>
+      </c>
+      <c r="BB8" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC8" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BD8" s="24" t="inlineStr">
+        <is>
+          <t>6b38a269117f4c6c1ae1e324273c2f9b9d11b2c15d99242f39aa89882d15db32</t>
+        </is>
+      </c>
+      <c r="BE8" s="24" t="inlineStr">
+        <is>
+          <t>3a7dae2b4e6e8f88</t>
+        </is>
+      </c>
+      <c r="BF8" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG8" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BH8" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-18T07:12:40.468242Z</t>
+        </is>
+      </c>
+      <c r="BI8" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ8" s="25" t="n"/>
+      <c r="BK8" s="26" t="n">
+        <v>117</v>
+      </c>
+      <c r="BL8" s="27" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BM8" s="28" t="n">
+        <v>0.460829</v>
+      </c>
+      <c r="BN8" s="28" t="n">
+        <v>0.455446</v>
+      </c>
+      <c r="BO8" s="28" t="n"/>
+      <c r="BP8" s="25" t="n"/>
+      <c r="BQ8" s="27" t="n"/>
+      <c r="BR8" s="28" t="n"/>
+      <c r="BS8" s="28" t="n"/>
+      <c r="BT8" s="28" t="n"/>
+      <c r="BU8" s="25" t="n"/>
+      <c r="BV8" s="29" t="n"/>
+      <c r="BW8" s="24" t="n"/>
+      <c r="BX8" s="30" t="n"/>
+      <c r="BY8" s="27" t="n"/>
+      <c r="BZ8" s="24" t="n"/>
+      <c r="CA8" s="31" t="n"/>
+    </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="24" t="inlineStr">
+        <is>
+          <t>56bb9605ed754d48</t>
+        </is>
+      </c>
+      <c r="B9" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-18T07:32:01.818646Z</t>
+        </is>
+      </c>
+      <c r="C9" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-19T00:08Z</t>
+        </is>
+      </c>
+      <c r="D9" s="24" t="inlineStr">
+        <is>
+          <t>401816168</t>
+        </is>
+      </c>
+      <c r="E9" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F9" s="24" t="inlineStr">
+        <is>
+          <t>San Francisco Giants</t>
+        </is>
+      </c>
+      <c r="G9" s="24" t="inlineStr">
+        <is>
+          <t>Seattle Mariners</t>
+        </is>
+      </c>
+      <c r="H9" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I9" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J9" s="25" t="n"/>
+      <c r="K9" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L9" s="26" t="n">
+        <v>-125</v>
+      </c>
+      <c r="M9" s="27" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="N9" s="28" t="n">
+        <v>0.555556</v>
+      </c>
+      <c r="O9" s="28" t="n">
+        <v>0.608716</v>
+      </c>
+      <c r="P9" s="28" t="n"/>
+      <c r="Q9" s="28" t="n">
+        <v>0.05316</v>
+      </c>
+      <c r="R9" s="26" t="n">
+        <v>77</v>
+      </c>
+      <c r="S9" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="U9" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V9" s="24" t="n"/>
+      <c r="W9" s="26" t="n"/>
+      <c r="X9" s="26" t="n"/>
+      <c r="Y9" s="25" t="n"/>
+      <c r="Z9" s="26" t="n"/>
+      <c r="AA9" s="28" t="n"/>
+      <c r="AB9" s="28" t="n"/>
+      <c r="AC9" s="30" t="n"/>
+      <c r="AD9" s="24" t="n"/>
+      <c r="AE9" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5928; executable ask 0.5550 (aec-mlb-sf-sea-2026-07-18).</t>
+        </is>
+      </c>
+      <c r="AF9" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
+        </is>
+      </c>
+      <c r="AG9" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH9" s="24" t="n"/>
+      <c r="AI9" s="31" t="n"/>
+      <c r="AJ9" s="31" t="n"/>
+      <c r="AK9" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL9" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM9" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN9" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO9" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP9" s="24" t="inlineStr">
+        <is>
+          <t>mlb-sf</t>
+        </is>
+      </c>
+      <c r="AQ9" s="24" t="inlineStr">
+        <is>
+          <t>San Francisco Giants</t>
+        </is>
+      </c>
+      <c r="AR9" s="24" t="inlineStr">
+        <is>
+          <t>San Francisco Giants</t>
+        </is>
+      </c>
+      <c r="AS9" s="24" t="inlineStr">
+        <is>
+          <t>mlb-sea</t>
+        </is>
+      </c>
+      <c r="AT9" s="24" t="inlineStr">
+        <is>
+          <t>Seattle Mariners</t>
+        </is>
+      </c>
+      <c r="AU9" s="24" t="inlineStr">
+        <is>
+          <t>Seattle Mariners</t>
+        </is>
+      </c>
+      <c r="AV9" s="24" t="n"/>
+      <c r="AW9" s="24" t="n"/>
+      <c r="AX9" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY9" s="24" t="n"/>
+      <c r="AZ9" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA9" s="24" t="inlineStr">
+        <is>
+          <t>8c639973a346cd55f4b616c1c107da2fded0fffcef60638bed21345e7ccc3bee</t>
+        </is>
+      </c>
+      <c r="BB9" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC9" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BD9" s="24" t="inlineStr">
+        <is>
+          <t>8c639973a346cd55f4b616c1c107da2fded0fffcef60638bed21345e7ccc3bee</t>
+        </is>
+      </c>
+      <c r="BE9" s="24" t="inlineStr">
+        <is>
+          <t>2a653312c42c783b</t>
+        </is>
+      </c>
+      <c r="BF9" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG9" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BH9" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-18T07:31:14.759261Z</t>
+        </is>
+      </c>
+      <c r="BI9" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ9" s="25" t="n"/>
+      <c r="BK9" s="26" t="n">
+        <v>-125</v>
+      </c>
+      <c r="BL9" s="27" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BM9" s="28" t="n">
+        <v>0.555556</v>
+      </c>
+      <c r="BN9" s="28" t="n">
+        <v>0.552239</v>
+      </c>
+      <c r="BO9" s="28" t="n"/>
+      <c r="BP9" s="25" t="n"/>
+      <c r="BQ9" s="27" t="n"/>
+      <c r="BR9" s="28" t="n"/>
+      <c r="BS9" s="28" t="n"/>
+      <c r="BT9" s="28" t="n"/>
+      <c r="BU9" s="25" t="n"/>
+      <c r="BV9" s="29" t="n"/>
+      <c r="BW9" s="24" t="n"/>
+      <c r="BX9" s="30" t="n"/>
+      <c r="BY9" s="27" t="n"/>
+      <c r="BZ9" s="24" t="n"/>
+      <c r="CA9" s="31" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/picks.xlsx
+++ b/data/picks.xlsx
@@ -21,10 +21,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="0.0%"/>
-    <numFmt numFmtId="165" formatCode="0.0000"/>
-    <numFmt numFmtId="166" formatCode="0.0###"/>
-    <numFmt numFmtId="167" formatCode="0.000000"/>
+    <numFmt numFmtId="164" formatCode="0.0###"/>
+    <numFmt numFmtId="165" formatCode="0.000000"/>
+    <numFmt numFmtId="166" formatCode="0.0000"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -136,7 +136,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -150,10 +150,10 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -169,10 +169,10 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -184,10 +184,10 @@
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -202,13 +202,13 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="10" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -217,38 +217,11 @@
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -327,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CA9" headerRowCount="1">
-  <autoFilter ref="A1:CA9"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CA14" headerRowCount="1">
+  <autoFilter ref="A1:CA14"/>
   <tableColumns count="79">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -765,19 +738,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$9)</f>
+        <f>COUNTA('Picks'!$A$2:$A$14)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$9,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$14,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$9,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$14,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$9,"settled",'Picks'!$V$2:$V$9,"win")+COUNTIFS('Picks'!$U$2:$U$9,"settled",'Picks'!$V$2:$V$9,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"win")+COUNTIFS('Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -805,19 +778,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$9,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$14,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$9,"&gt;0",'Picks'!$V$2:$V$9,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$9,"&gt;0",'Picks'!$V$2:$V$9,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$14,"&gt;0",'Picks'!$V$2:$V$14,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$14,"&gt;0",'Picks'!$V$2:$V$14,"loss")</f>
         <v/>
       </c>
-      <c r="E7" s="32">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$9,"&gt;0",'Picks'!$V$2:$V$9,"win")/(COUNTIFS('Picks'!$BX$2:$BX$9,"&gt;0",'Picks'!$V$2:$V$9,"win")+COUNTIFS('Picks'!$BX$2:$BX$9,"&gt;0",'Picks'!$V$2:$V$9,"loss")),0)</f>
+      <c r="E7" s="7">
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$14,"&gt;0",'Picks'!$V$2:$V$14,"win")/(COUNTIFS('Picks'!$BX$2:$BX$14,"&gt;0",'Picks'!$V$2:$V$14,"win")+COUNTIFS('Picks'!$BX$2:$BX$14,"&gt;0",'Picks'!$V$2:$V$14,"loss")),0)</f>
         <v/>
       </c>
-      <c r="G7" s="32">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$9)/SUM('Picks'!$BX$2:$BX$9),0)</f>
+      <c r="G7" s="7">
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$14)/SUM('Picks'!$BX$2:$BX$14),0)</f>
         <v/>
       </c>
     </row>
@@ -844,20 +817,20 @@
       </c>
     </row>
     <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="33">
-        <f>SUM('Picks'!$BY$2:$BY$9)</f>
+      <c r="A10" s="8">
+        <f>SUM('Picks'!$BY$2:$BY$14)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$9,"&lt;&gt;",'Picks'!$AB$2:$AB$9),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$14,"&lt;&gt;",'Picks'!$AB$2:$AB$14),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$9,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$9,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$14,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$14,"settled")</f>
         <v/>
       </c>
-      <c r="G10" s="33">
-        <f>SUMIFS('Picks'!$AC$2:$AC$9,'Picks'!$AM$2:$AM$9,"QUALIFIED_SHADOW_CALL")</f>
+      <c r="G10" s="8">
+        <f>SUMIFS('Picks'!$AC$2:$AC$14,'Picks'!$AM$2:$AM$14,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -912,27 +885,27 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$9,$A14,'Picks'!$U$2:$U$9,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$14,$A14,'Picks'!$U$2:$U$14,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$9,$A14,'Picks'!$U$2:$U$9,"settled",'Picks'!$V$2:$V$9,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$14,$A14,'Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$9,$A14,'Picks'!$U$2:$U$9,"settled",'Picks'!$V$2:$V$9,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$14,$A14,'Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"loss")</f>
         <v/>
       </c>
-      <c r="E14" s="34">
+      <c r="E14" s="14">
         <f>IFERROR(C14/(C14+D14),0)</f>
         <v/>
       </c>
-      <c r="F14" s="35">
-        <f>SUMIFS('Picks'!$BY$2:$BY$9,'Picks'!$H$2:$H$9,$A14)</f>
+      <c r="F14" s="15">
+        <f>SUMIFS('Picks'!$BY$2:$BY$14,'Picks'!$H$2:$H$14,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$9,'Picks'!$H$2:$H$9,$A14,'Picks'!$U$2:$U$9,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$14,'Picks'!$H$2:$H$14,$A14,'Picks'!$U$2:$U$14,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -943,27 +916,27 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$9,$A15,'Picks'!$U$2:$U$9,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$14,$A15,'Picks'!$U$2:$U$14,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$9,$A15,'Picks'!$U$2:$U$9,"settled",'Picks'!$V$2:$V$9,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$14,$A15,'Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$9,$A15,'Picks'!$U$2:$U$9,"settled",'Picks'!$V$2:$V$9,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$14,$A15,'Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"loss")</f>
         <v/>
       </c>
-      <c r="E15" s="36">
+      <c r="E15" s="19">
         <f>IFERROR(C15/(C15+D15),0)</f>
         <v/>
       </c>
-      <c r="F15" s="37">
-        <f>SUMIFS('Picks'!$BY$2:$BY$9,'Picks'!$H$2:$H$9,$A15)</f>
+      <c r="F15" s="20">
+        <f>SUMIFS('Picks'!$BY$2:$BY$14,'Picks'!$H$2:$H$14,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$9,'Picks'!$H$2:$H$9,$A15,'Picks'!$U$2:$U$9,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$14,'Picks'!$H$2:$H$14,$A15,'Picks'!$U$2:$U$14,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -974,27 +947,27 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$9,$A16,'Picks'!$U$2:$U$9,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$14,$A16,'Picks'!$U$2:$U$14,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$9,$A16,'Picks'!$U$2:$U$9,"settled",'Picks'!$V$2:$V$9,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$14,$A16,'Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$9,$A16,'Picks'!$U$2:$U$9,"settled",'Picks'!$V$2:$V$9,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$14,$A16,'Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"loss")</f>
         <v/>
       </c>
-      <c r="E16" s="34">
+      <c r="E16" s="14">
         <f>IFERROR(C16/(C16+D16),0)</f>
         <v/>
       </c>
-      <c r="F16" s="35">
-        <f>SUMIFS('Picks'!$BY$2:$BY$9,'Picks'!$H$2:$H$9,$A16)</f>
+      <c r="F16" s="15">
+        <f>SUMIFS('Picks'!$BY$2:$BY$14,'Picks'!$H$2:$H$14,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$9,'Picks'!$H$2:$H$9,$A16,'Picks'!$U$2:$U$9,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$14,'Picks'!$H$2:$H$14,$A16,'Picks'!$U$2:$U$14,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1023,7 +996,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CA3"/>
+  <dimension ref="A1:CA14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1550,7 +1523,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J2" s="38" t="n"/>
+      <c r="J2" s="25" t="n"/>
       <c r="K2" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -1559,7 +1532,7 @@
       <c r="L2" s="26" t="n">
         <v>117</v>
       </c>
-      <c r="M2" s="39" t="n">
+      <c r="M2" s="27" t="n">
         <v>2.17</v>
       </c>
       <c r="N2" s="28" t="n">
@@ -1591,11 +1564,11 @@
       <c r="V2" s="24" t="n"/>
       <c r="W2" s="26" t="n"/>
       <c r="X2" s="26" t="n"/>
-      <c r="Y2" s="38" t="n"/>
+      <c r="Y2" s="25" t="n"/>
       <c r="Z2" s="26" t="n"/>
       <c r="AA2" s="28" t="n"/>
       <c r="AB2" s="28" t="n"/>
-      <c r="AC2" s="40" t="n"/>
+      <c r="AC2" s="30" t="n"/>
       <c r="AD2" s="24" t="n"/>
       <c r="AE2" s="31" t="inlineStr">
         <is>
@@ -1726,11 +1699,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ2" s="38" t="n"/>
+      <c r="BJ2" s="25" t="n"/>
       <c r="BK2" s="26" t="n">
         <v>117</v>
       </c>
-      <c r="BL2" s="39" t="n">
+      <c r="BL2" s="27" t="n">
         <v>2.17</v>
       </c>
       <c r="BM2" s="28" t="n">
@@ -1740,174 +1713,2943 @@
         <v>0.455446</v>
       </c>
       <c r="BO2" s="28" t="n"/>
-      <c r="BP2" s="38" t="n"/>
-      <c r="BQ2" s="39" t="n"/>
+      <c r="BP2" s="25" t="n"/>
+      <c r="BQ2" s="27" t="n"/>
       <c r="BR2" s="28" t="n"/>
       <c r="BS2" s="28" t="n"/>
       <c r="BT2" s="28" t="n"/>
-      <c r="BU2" s="38" t="n"/>
+      <c r="BU2" s="25" t="n"/>
       <c r="BV2" s="29" t="n"/>
       <c r="BW2" s="24" t="n"/>
-      <c r="BX2" s="40" t="n"/>
-      <c r="BY2" s="39" t="n"/>
+      <c r="BX2" s="30" t="n"/>
+      <c r="BY2" s="27" t="n"/>
       <c r="BZ2" s="24" t="n"/>
       <c r="CA2" s="31" t="n"/>
     </row>
-    <row r="3" ht="36" customHeight="1">
-      <c r="A3" t="inlineStr">
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="24" t="inlineStr">
         <is>
           <t>607e61329ed3424c</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="24" t="inlineStr">
         <is>
           <t>2026-07-17T14:02:17Z</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="24" t="inlineStr">
         <is>
           <t>2026-07-17T23:30Z</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="24" t="inlineStr">
         <is>
           <t>401857073</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="24" t="inlineStr">
         <is>
           <t>WNBA</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="24" t="inlineStr">
         <is>
           <t>Seattle Storm</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="24" t="inlineStr">
         <is>
           <t>Indiana Fever</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="24" t="inlineStr">
         <is>
           <t>moneyline</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="24" t="inlineStr">
         <is>
           <t>home</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="J3" s="25" t="n"/>
+      <c r="K3" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>-354</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>1.282</t>
-        </is>
-      </c>
-      <c r="N3" t="n">
+      <c r="L3" s="26" t="n">
+        <v>-354</v>
+      </c>
+      <c r="M3" s="27" t="n">
+        <v>1.282</v>
+      </c>
+      <c r="N3" s="28" t="n">
         <v>0.78</v>
       </c>
-      <c r="O3" t="n">
+      <c r="O3" s="28" t="n">
         <v>0.6207</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="P3" s="28" t="n"/>
+      <c r="Q3" s="28" t="n">
         <v>-0.1593</v>
       </c>
-      <c r="S3" t="n">
+      <c r="R3" s="26" t="n"/>
+      <c r="S3" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="T3" s="24" t="inlineStr">
         <is>
           <t>wnba-elo-trend-lr-v3</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="U3" s="24" t="inlineStr">
         <is>
           <t>settled</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="V3" s="24" t="inlineStr">
         <is>
           <t>win</t>
         </is>
       </c>
-      <c r="W3" t="n">
+      <c r="W3" s="26" t="n">
         <v>107</v>
       </c>
-      <c r="X3" t="n">
+      <c r="X3" s="26" t="n">
         <v>110</v>
       </c>
-      <c r="AC3" t="n">
+      <c r="Y3" s="25" t="n"/>
+      <c r="Z3" s="26" t="n"/>
+      <c r="AA3" s="28" t="n"/>
+      <c r="AB3" s="28" t="n"/>
+      <c r="AC3" s="30" t="n">
         <v>0.282</v>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AD3" s="24" t="inlineStr">
         <is>
           <t>2026-07-18T14:36:00Z</t>
         </is>
       </c>
-      <c r="AK3" t="inlineStr">
+      <c r="AE3" s="31" t="n"/>
+      <c r="AF3" s="31" t="n"/>
+      <c r="AG3" s="24" t="n"/>
+      <c r="AH3" s="24" t="n"/>
+      <c r="AI3" s="31" t="n"/>
+      <c r="AJ3" s="31" t="n"/>
+      <c r="AK3" s="24" t="inlineStr">
         <is>
           <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
-      <c r="AL3" t="inlineStr">
+      <c r="AL3" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM3" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN3" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO3" s="24" t="inlineStr">
+        <is>
+          <t>CALL_LEARNED_CONFIDENCE</t>
+        </is>
+      </c>
+      <c r="AP3" s="24" t="n"/>
+      <c r="AQ3" s="24" t="n"/>
+      <c r="AR3" s="24" t="n"/>
+      <c r="AS3" s="24" t="n"/>
+      <c r="AT3" s="24" t="n"/>
+      <c r="AU3" s="24" t="n"/>
+      <c r="AV3" s="24" t="n"/>
+      <c r="AW3" s="24" t="n"/>
+      <c r="AX3" s="24" t="inlineStr">
+        <is>
+          <t>learned</t>
+        </is>
+      </c>
+      <c r="AY3" s="24" t="n"/>
+      <c r="AZ3" s="24" t="n"/>
+      <c r="BA3" s="24" t="n"/>
+      <c r="BB3" s="24" t="n"/>
+      <c r="BC3" s="24" t="n"/>
+      <c r="BD3" s="24" t="n"/>
+      <c r="BE3" s="24" t="n"/>
+      <c r="BF3" s="24" t="n"/>
+      <c r="BG3" s="24" t="n"/>
+      <c r="BH3" s="24" t="n"/>
+      <c r="BI3" s="24" t="n"/>
+      <c r="BJ3" s="25" t="n"/>
+      <c r="BK3" s="26" t="n">
+        <v>-354</v>
+      </c>
+      <c r="BL3" s="27" t="n">
+        <v>1.282</v>
+      </c>
+      <c r="BM3" s="28" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="BN3" s="28" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="BO3" s="28" t="n"/>
+      <c r="BP3" s="25" t="n"/>
+      <c r="BQ3" s="27" t="n"/>
+      <c r="BR3" s="28" t="n"/>
+      <c r="BS3" s="28" t="n"/>
+      <c r="BT3" s="28" t="n"/>
+      <c r="BU3" s="25" t="n"/>
+      <c r="BV3" s="29" t="n"/>
+      <c r="BW3" s="24" t="n"/>
+      <c r="BX3" s="30" t="n"/>
+      <c r="BY3" s="27" t="n"/>
+      <c r="BZ3" s="24" t="n"/>
+      <c r="CA3" s="31" t="n"/>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="24" t="inlineStr">
+        <is>
+          <t>931feaf381a247bc</t>
+        </is>
+      </c>
+      <c r="B4" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-18T16:16:11.093520Z</t>
+        </is>
+      </c>
+      <c r="C4" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-18T20:10Z</t>
+        </is>
+      </c>
+      <c r="D4" s="24" t="inlineStr">
+        <is>
+          <t>401816163</t>
+        </is>
+      </c>
+      <c r="E4" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F4" s="24" t="inlineStr">
+        <is>
+          <t>Miami Marlins</t>
+        </is>
+      </c>
+      <c r="G4" s="24" t="inlineStr">
+        <is>
+          <t>Milwaukee Brewers</t>
+        </is>
+      </c>
+      <c r="H4" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I4" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J4" s="25" t="n"/>
+      <c r="K4" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L4" s="26" t="n">
+        <v>-133</v>
+      </c>
+      <c r="M4" s="27" t="n">
+        <v>1.75188</v>
+      </c>
+      <c r="N4" s="28" t="n">
+        <v>0.570815</v>
+      </c>
+      <c r="O4" s="28" t="n">
+        <v>0.608753</v>
+      </c>
+      <c r="P4" s="28" t="n"/>
+      <c r="Q4" s="28" t="n">
+        <v>0.037938</v>
+      </c>
+      <c r="R4" s="26" t="n">
+        <v>69</v>
+      </c>
+      <c r="S4" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="U4" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V4" s="24" t="n"/>
+      <c r="W4" s="26" t="n"/>
+      <c r="X4" s="26" t="n"/>
+      <c r="Y4" s="25" t="n"/>
+      <c r="Z4" s="26" t="n"/>
+      <c r="AA4" s="28" t="n"/>
+      <c r="AB4" s="28" t="n"/>
+      <c r="AC4" s="30" t="n"/>
+      <c r="AD4" s="24" t="n"/>
+      <c r="AE4" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.6000; executable ask 0.5700 (aec-mlb-mia-mil-2026-07-18).</t>
+        </is>
+      </c>
+      <c r="AF4" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
+        </is>
+      </c>
+      <c r="AG4" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH4" s="24" t="n"/>
+      <c r="AI4" s="31" t="n"/>
+      <c r="AJ4" s="31" t="n"/>
+      <c r="AK4" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL4" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM4" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN4" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO4" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP4" s="24" t="inlineStr">
+        <is>
+          <t>mlb-mia</t>
+        </is>
+      </c>
+      <c r="AQ4" s="24" t="inlineStr">
+        <is>
+          <t>Miami Marlins</t>
+        </is>
+      </c>
+      <c r="AR4" s="24" t="inlineStr">
+        <is>
+          <t>Miami Marlins</t>
+        </is>
+      </c>
+      <c r="AS4" s="24" t="inlineStr">
+        <is>
+          <t>mlb-mil</t>
+        </is>
+      </c>
+      <c r="AT4" s="24" t="inlineStr">
+        <is>
+          <t>Milwaukee Brewers</t>
+        </is>
+      </c>
+      <c r="AU4" s="24" t="inlineStr">
+        <is>
+          <t>Milwaukee Brewers</t>
+        </is>
+      </c>
+      <c r="AV4" s="24" t="n"/>
+      <c r="AW4" s="24" t="n"/>
+      <c r="AX4" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY4" s="24" t="n"/>
+      <c r="AZ4" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA4" s="24" t="inlineStr">
+        <is>
+          <t>117c03794b1d1031deec3bd4cce88c9158bebd0622c621defd0aab3eb37c0a6e</t>
+        </is>
+      </c>
+      <c r="BB4" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC4" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BD4" s="24" t="inlineStr">
+        <is>
+          <t>117c03794b1d1031deec3bd4cce88c9158bebd0622c621defd0aab3eb37c0a6e</t>
+        </is>
+      </c>
+      <c r="BE4" s="24" t="inlineStr">
+        <is>
+          <t>0f54459b91a18ff1</t>
+        </is>
+      </c>
+      <c r="BF4" s="24" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>CALL_LEARNED_CONFIDENCE</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>learned</t>
-        </is>
-      </c>
-      <c r="BK3" t="inlineStr">
-        <is>
-          <t>-354</t>
-        </is>
-      </c>
-      <c r="BL3" t="inlineStr">
-        <is>
-          <t>1.282</t>
-        </is>
-      </c>
-      <c r="BM3" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>0.78</v>
-      </c>
+      <c r="BG4" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BH4" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-18T16:15:15.200995Z</t>
+        </is>
+      </c>
+      <c r="BI4" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ4" s="25" t="n"/>
+      <c r="BK4" s="26" t="n">
+        <v>-133</v>
+      </c>
+      <c r="BL4" s="27" t="n">
+        <v>1.75188</v>
+      </c>
+      <c r="BM4" s="28" t="n">
+        <v>0.570815</v>
+      </c>
+      <c r="BN4" s="28" t="n">
+        <v>0.567164</v>
+      </c>
+      <c r="BO4" s="28" t="n"/>
+      <c r="BP4" s="25" t="n"/>
+      <c r="BQ4" s="27" t="n"/>
+      <c r="BR4" s="28" t="n"/>
+      <c r="BS4" s="28" t="n"/>
+      <c r="BT4" s="28" t="n"/>
+      <c r="BU4" s="25" t="n"/>
+      <c r="BV4" s="29" t="n"/>
+      <c r="BW4" s="24" t="n"/>
+      <c r="BX4" s="30" t="n"/>
+      <c r="BY4" s="27" t="n"/>
+      <c r="BZ4" s="24" t="n"/>
+      <c r="CA4" s="31" t="n"/>
     </row>
-    <row r="4" ht="36" customHeight="1"/>
-    <row r="5" ht="36" customHeight="1"/>
-    <row r="6" ht="36" customHeight="1"/>
-    <row r="7" ht="36" customHeight="1"/>
-    <row r="8" ht="36" customHeight="1"/>
-    <row r="9" ht="36" customHeight="1"/>
+    <row r="5" ht="36" customHeight="1">
+      <c r="A5" s="24" t="inlineStr">
+        <is>
+          <t>8789a71883f94701</t>
+        </is>
+      </c>
+      <c r="B5" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-18T16:44:20.099051Z</t>
+        </is>
+      </c>
+      <c r="C5" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-18T17:10Z</t>
+        </is>
+      </c>
+      <c r="D5" s="24" t="inlineStr">
+        <is>
+          <t>401896568</t>
+        </is>
+      </c>
+      <c r="E5" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F5" s="24" t="inlineStr">
+        <is>
+          <t>Pittsburgh Pirates</t>
+        </is>
+      </c>
+      <c r="G5" s="24" t="inlineStr">
+        <is>
+          <t>Cleveland Guardians</t>
+        </is>
+      </c>
+      <c r="H5" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I5" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J5" s="25" t="n"/>
+      <c r="K5" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L5" s="26" t="n">
+        <v>-102</v>
+      </c>
+      <c r="M5" s="27" t="n">
+        <v>1.980392</v>
+      </c>
+      <c r="N5" s="28" t="n">
+        <v>0.50495</v>
+      </c>
+      <c r="O5" s="28" t="n">
+        <v>0.554084</v>
+      </c>
+      <c r="P5" s="28" t="n"/>
+      <c r="Q5" s="28" t="n">
+        <v>0.049134</v>
+      </c>
+      <c r="R5" s="26" t="n">
+        <v>75</v>
+      </c>
+      <c r="S5" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="U5" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V5" s="24" t="n"/>
+      <c r="W5" s="26" t="n"/>
+      <c r="X5" s="26" t="n"/>
+      <c r="Y5" s="25" t="n"/>
+      <c r="Z5" s="26" t="n"/>
+      <c r="AA5" s="28" t="n"/>
+      <c r="AB5" s="28" t="n"/>
+      <c r="AC5" s="30" t="n"/>
+      <c r="AD5" s="24" t="n"/>
+      <c r="AE5" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5500; executable ask 0.5050 (aec-mlb-pit-cle-2026-07-18).</t>
+        </is>
+      </c>
+      <c r="AF5" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
+        </is>
+      </c>
+      <c r="AG5" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH5" s="24" t="n"/>
+      <c r="AI5" s="31" t="n"/>
+      <c r="AJ5" s="31" t="n"/>
+      <c r="AK5" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL5" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM5" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN5" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO5" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP5" s="24" t="inlineStr">
+        <is>
+          <t>mlb-pit</t>
+        </is>
+      </c>
+      <c r="AQ5" s="24" t="inlineStr">
+        <is>
+          <t>Pittsburgh Pirates</t>
+        </is>
+      </c>
+      <c r="AR5" s="24" t="inlineStr">
+        <is>
+          <t>Pittsburgh Pirates</t>
+        </is>
+      </c>
+      <c r="AS5" s="24" t="inlineStr">
+        <is>
+          <t>mlb-cle</t>
+        </is>
+      </c>
+      <c r="AT5" s="24" t="inlineStr">
+        <is>
+          <t>Cleveland Guardians</t>
+        </is>
+      </c>
+      <c r="AU5" s="24" t="inlineStr">
+        <is>
+          <t>Cleveland Guardians</t>
+        </is>
+      </c>
+      <c r="AV5" s="24" t="n"/>
+      <c r="AW5" s="24" t="n"/>
+      <c r="AX5" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY5" s="24" t="n"/>
+      <c r="AZ5" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA5" s="24" t="inlineStr">
+        <is>
+          <t>c97732889cfca1912f8d78791ff63f04ee3fe987951aced9e4fab541932597cd</t>
+        </is>
+      </c>
+      <c r="BB5" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC5" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BD5" s="24" t="inlineStr">
+        <is>
+          <t>c97732889cfca1912f8d78791ff63f04ee3fe987951aced9e4fab541932597cd</t>
+        </is>
+      </c>
+      <c r="BE5" s="24" t="inlineStr">
+        <is>
+          <t>6df496ff8b2da9c6</t>
+        </is>
+      </c>
+      <c r="BF5" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG5" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BH5" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-18T16:42:59.880808Z</t>
+        </is>
+      </c>
+      <c r="BI5" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ5" s="25" t="n"/>
+      <c r="BK5" s="26" t="n">
+        <v>-102</v>
+      </c>
+      <c r="BL5" s="27" t="n">
+        <v>1.980392</v>
+      </c>
+      <c r="BM5" s="28" t="n">
+        <v>0.50495</v>
+      </c>
+      <c r="BN5" s="28" t="n">
+        <v>0.502488</v>
+      </c>
+      <c r="BO5" s="28" t="n"/>
+      <c r="BP5" s="25" t="n"/>
+      <c r="BQ5" s="27" t="n"/>
+      <c r="BR5" s="28" t="n"/>
+      <c r="BS5" s="28" t="n"/>
+      <c r="BT5" s="28" t="n"/>
+      <c r="BU5" s="25" t="n"/>
+      <c r="BV5" s="29" t="n"/>
+      <c r="BW5" s="24" t="n"/>
+      <c r="BX5" s="30" t="n"/>
+      <c r="BY5" s="27" t="n"/>
+      <c r="BZ5" s="24" t="n"/>
+      <c r="CA5" s="31" t="n"/>
+    </row>
+    <row r="6" ht="36" customHeight="1">
+      <c r="A6" s="24" t="inlineStr">
+        <is>
+          <t>512e4ebfdf1a456e</t>
+        </is>
+      </c>
+      <c r="B6" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-18T16:44:20.099051Z</t>
+        </is>
+      </c>
+      <c r="C6" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-18T18:20Z</t>
+        </is>
+      </c>
+      <c r="D6" s="24" t="inlineStr">
+        <is>
+          <t>401816164</t>
+        </is>
+      </c>
+      <c r="E6" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F6" s="24" t="inlineStr">
+        <is>
+          <t>Minnesota Twins</t>
+        </is>
+      </c>
+      <c r="G6" s="24" t="inlineStr">
+        <is>
+          <t>Chicago Cubs</t>
+        </is>
+      </c>
+      <c r="H6" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I6" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J6" s="25" t="n"/>
+      <c r="K6" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L6" s="26" t="n">
+        <v>-133</v>
+      </c>
+      <c r="M6" s="27" t="n">
+        <v>1.75188</v>
+      </c>
+      <c r="N6" s="28" t="n">
+        <v>0.570815</v>
+      </c>
+      <c r="O6" s="28" t="n">
+        <v>0.608363</v>
+      </c>
+      <c r="P6" s="28" t="n"/>
+      <c r="Q6" s="28" t="n">
+        <v>0.037548</v>
+      </c>
+      <c r="R6" s="26" t="n">
+        <v>69</v>
+      </c>
+      <c r="S6" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="U6" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V6" s="24" t="n"/>
+      <c r="W6" s="26" t="n"/>
+      <c r="X6" s="26" t="n"/>
+      <c r="Y6" s="25" t="n"/>
+      <c r="Z6" s="26" t="n"/>
+      <c r="AA6" s="28" t="n"/>
+      <c r="AB6" s="28" t="n"/>
+      <c r="AC6" s="30" t="n"/>
+      <c r="AD6" s="24" t="n"/>
+      <c r="AE6" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5500; executable ask 0.5700 (aec-mlb-min-chc-2026-07-18).</t>
+        </is>
+      </c>
+      <c r="AF6" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
+        </is>
+      </c>
+      <c r="AG6" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH6" s="24" t="n"/>
+      <c r="AI6" s="31" t="n"/>
+      <c r="AJ6" s="31" t="n"/>
+      <c r="AK6" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL6" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM6" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN6" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO6" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP6" s="24" t="inlineStr">
+        <is>
+          <t>mlb-min</t>
+        </is>
+      </c>
+      <c r="AQ6" s="24" t="inlineStr">
+        <is>
+          <t>Minnesota Twins</t>
+        </is>
+      </c>
+      <c r="AR6" s="24" t="inlineStr">
+        <is>
+          <t>Minnesota Twins</t>
+        </is>
+      </c>
+      <c r="AS6" s="24" t="inlineStr">
+        <is>
+          <t>mlb-chc</t>
+        </is>
+      </c>
+      <c r="AT6" s="24" t="inlineStr">
+        <is>
+          <t>Chicago Cubs</t>
+        </is>
+      </c>
+      <c r="AU6" s="24" t="inlineStr">
+        <is>
+          <t>Chicago Cubs</t>
+        </is>
+      </c>
+      <c r="AV6" s="24" t="n"/>
+      <c r="AW6" s="24" t="n"/>
+      <c r="AX6" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY6" s="24" t="n"/>
+      <c r="AZ6" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA6" s="24" t="inlineStr">
+        <is>
+          <t>c97732889cfca1912f8d78791ff63f04ee3fe987951aced9e4fab541932597cd</t>
+        </is>
+      </c>
+      <c r="BB6" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC6" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BD6" s="24" t="inlineStr">
+        <is>
+          <t>c97732889cfca1912f8d78791ff63f04ee3fe987951aced9e4fab541932597cd</t>
+        </is>
+      </c>
+      <c r="BE6" s="24" t="inlineStr">
+        <is>
+          <t>7166685f6e68e237</t>
+        </is>
+      </c>
+      <c r="BF6" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG6" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BH6" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-18T16:42:49.506840Z</t>
+        </is>
+      </c>
+      <c r="BI6" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ6" s="25" t="n"/>
+      <c r="BK6" s="26" t="n">
+        <v>-133</v>
+      </c>
+      <c r="BL6" s="27" t="n">
+        <v>1.75188</v>
+      </c>
+      <c r="BM6" s="28" t="n">
+        <v>0.570815</v>
+      </c>
+      <c r="BN6" s="28" t="n">
+        <v>0.567164</v>
+      </c>
+      <c r="BO6" s="28" t="n"/>
+      <c r="BP6" s="25" t="n"/>
+      <c r="BQ6" s="27" t="n"/>
+      <c r="BR6" s="28" t="n"/>
+      <c r="BS6" s="28" t="n"/>
+      <c r="BT6" s="28" t="n"/>
+      <c r="BU6" s="25" t="n"/>
+      <c r="BV6" s="29" t="n"/>
+      <c r="BW6" s="24" t="n"/>
+      <c r="BX6" s="30" t="n"/>
+      <c r="BY6" s="27" t="n"/>
+      <c r="BZ6" s="24" t="n"/>
+      <c r="CA6" s="31" t="n"/>
+    </row>
+    <row r="7" ht="36" customHeight="1">
+      <c r="A7" s="24" t="inlineStr">
+        <is>
+          <t>80b7c78aaffb4905</t>
+        </is>
+      </c>
+      <c r="B7" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-18T16:44:20.099051Z</t>
+        </is>
+      </c>
+      <c r="C7" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-18T19:07Z</t>
+        </is>
+      </c>
+      <c r="D7" s="24" t="inlineStr">
+        <is>
+          <t>401816156</t>
+        </is>
+      </c>
+      <c r="E7" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F7" s="24" t="inlineStr">
+        <is>
+          <t>Chicago White Sox</t>
+        </is>
+      </c>
+      <c r="G7" s="24" t="inlineStr">
+        <is>
+          <t>Toronto Blue Jays</t>
+        </is>
+      </c>
+      <c r="H7" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I7" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J7" s="25" t="n"/>
+      <c r="K7" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L7" s="26" t="n">
+        <v>-104</v>
+      </c>
+      <c r="M7" s="27" t="n">
+        <v>1.961538</v>
+      </c>
+      <c r="N7" s="28" t="n">
+        <v>0.509804</v>
+      </c>
+      <c r="O7" s="28" t="n">
+        <v>0.5767679999999999</v>
+      </c>
+      <c r="P7" s="28" t="n"/>
+      <c r="Q7" s="28" t="n">
+        <v>0.066964</v>
+      </c>
+      <c r="R7" s="26" t="n">
+        <v>83</v>
+      </c>
+      <c r="S7" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="U7" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V7" s="24" t="n"/>
+      <c r="W7" s="26" t="n"/>
+      <c r="X7" s="26" t="n"/>
+      <c r="Y7" s="25" t="n"/>
+      <c r="Z7" s="26" t="n"/>
+      <c r="AA7" s="28" t="n"/>
+      <c r="AB7" s="28" t="n"/>
+      <c r="AC7" s="30" t="n"/>
+      <c r="AD7" s="24" t="n"/>
+      <c r="AE7" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5500; executable ask 0.5100 (aec-mlb-cws-tor-2026-07-18).</t>
+        </is>
+      </c>
+      <c r="AF7" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
+        </is>
+      </c>
+      <c r="AG7" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH7" s="24" t="n"/>
+      <c r="AI7" s="31" t="n"/>
+      <c r="AJ7" s="31" t="n"/>
+      <c r="AK7" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL7" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM7" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN7" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO7" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP7" s="24" t="inlineStr">
+        <is>
+          <t>mlb-cws</t>
+        </is>
+      </c>
+      <c r="AQ7" s="24" t="inlineStr">
+        <is>
+          <t>Chicago White Sox</t>
+        </is>
+      </c>
+      <c r="AR7" s="24" t="inlineStr">
+        <is>
+          <t>Chicago White Sox</t>
+        </is>
+      </c>
+      <c r="AS7" s="24" t="inlineStr">
+        <is>
+          <t>mlb-tor</t>
+        </is>
+      </c>
+      <c r="AT7" s="24" t="inlineStr">
+        <is>
+          <t>Toronto Blue Jays</t>
+        </is>
+      </c>
+      <c r="AU7" s="24" t="inlineStr">
+        <is>
+          <t>Toronto Blue Jays</t>
+        </is>
+      </c>
+      <c r="AV7" s="24" t="n"/>
+      <c r="AW7" s="24" t="n"/>
+      <c r="AX7" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY7" s="24" t="n"/>
+      <c r="AZ7" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA7" s="24" t="inlineStr">
+        <is>
+          <t>c97732889cfca1912f8d78791ff63f04ee3fe987951aced9e4fab541932597cd</t>
+        </is>
+      </c>
+      <c r="BB7" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC7" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BD7" s="24" t="inlineStr">
+        <is>
+          <t>c97732889cfca1912f8d78791ff63f04ee3fe987951aced9e4fab541932597cd</t>
+        </is>
+      </c>
+      <c r="BE7" s="24" t="inlineStr">
+        <is>
+          <t>990421d336b67011</t>
+        </is>
+      </c>
+      <c r="BF7" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG7" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BH7" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-18T16:42:50.404282Z</t>
+        </is>
+      </c>
+      <c r="BI7" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ7" s="25" t="n"/>
+      <c r="BK7" s="26" t="n">
+        <v>-104</v>
+      </c>
+      <c r="BL7" s="27" t="n">
+        <v>1.961538</v>
+      </c>
+      <c r="BM7" s="28" t="n">
+        <v>0.509804</v>
+      </c>
+      <c r="BN7" s="28" t="n">
+        <v>0.507463</v>
+      </c>
+      <c r="BO7" s="28" t="n"/>
+      <c r="BP7" s="25" t="n"/>
+      <c r="BQ7" s="27" t="n"/>
+      <c r="BR7" s="28" t="n"/>
+      <c r="BS7" s="28" t="n"/>
+      <c r="BT7" s="28" t="n"/>
+      <c r="BU7" s="25" t="n"/>
+      <c r="BV7" s="29" t="n"/>
+      <c r="BW7" s="24" t="n"/>
+      <c r="BX7" s="30" t="n"/>
+      <c r="BY7" s="27" t="n"/>
+      <c r="BZ7" s="24" t="n"/>
+      <c r="CA7" s="31" t="n"/>
+    </row>
+    <row r="8" ht="36" customHeight="1">
+      <c r="A8" s="24" t="inlineStr">
+        <is>
+          <t>c7e4de168a8f4e3d</t>
+        </is>
+      </c>
+      <c r="B8" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-18T16:44:20.099051Z</t>
+        </is>
+      </c>
+      <c r="C8" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-18T19:10Z</t>
+        </is>
+      </c>
+      <c r="D8" s="24" t="inlineStr">
+        <is>
+          <t>401816166</t>
+        </is>
+      </c>
+      <c r="E8" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F8" s="24" t="inlineStr">
+        <is>
+          <t>Cincinnati Reds</t>
+        </is>
+      </c>
+      <c r="G8" s="24" t="inlineStr">
+        <is>
+          <t>Colorado Rockies</t>
+        </is>
+      </c>
+      <c r="H8" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I8" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J8" s="25" t="n"/>
+      <c r="K8" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L8" s="26" t="n">
+        <v>-104</v>
+      </c>
+      <c r="M8" s="27" t="n">
+        <v>1.961538</v>
+      </c>
+      <c r="N8" s="28" t="n">
+        <v>0.509804</v>
+      </c>
+      <c r="O8" s="28" t="n">
+        <v>0.582367</v>
+      </c>
+      <c r="P8" s="28" t="n"/>
+      <c r="Q8" s="28" t="n">
+        <v>0.072563</v>
+      </c>
+      <c r="R8" s="26" t="n">
+        <v>86</v>
+      </c>
+      <c r="S8" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="U8" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V8" s="24" t="n"/>
+      <c r="W8" s="26" t="n"/>
+      <c r="X8" s="26" t="n"/>
+      <c r="Y8" s="25" t="n"/>
+      <c r="Z8" s="26" t="n"/>
+      <c r="AA8" s="28" t="n"/>
+      <c r="AB8" s="28" t="n"/>
+      <c r="AC8" s="30" t="n"/>
+      <c r="AD8" s="24" t="n"/>
+      <c r="AE8" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5500; executable ask 0.5100 (aec-mlb-cin-col-2026-07-18).</t>
+        </is>
+      </c>
+      <c r="AF8" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
+        </is>
+      </c>
+      <c r="AG8" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH8" s="24" t="n"/>
+      <c r="AI8" s="31" t="n"/>
+      <c r="AJ8" s="31" t="n"/>
+      <c r="AK8" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL8" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM8" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN8" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO8" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP8" s="24" t="inlineStr">
+        <is>
+          <t>mlb-cin</t>
+        </is>
+      </c>
+      <c r="AQ8" s="24" t="inlineStr">
+        <is>
+          <t>Cincinnati Reds</t>
+        </is>
+      </c>
+      <c r="AR8" s="24" t="inlineStr">
+        <is>
+          <t>Cincinnati Reds</t>
+        </is>
+      </c>
+      <c r="AS8" s="24" t="inlineStr">
+        <is>
+          <t>mlb-col</t>
+        </is>
+      </c>
+      <c r="AT8" s="24" t="inlineStr">
+        <is>
+          <t>Colorado Rockies</t>
+        </is>
+      </c>
+      <c r="AU8" s="24" t="inlineStr">
+        <is>
+          <t>Colorado Rockies</t>
+        </is>
+      </c>
+      <c r="AV8" s="24" t="n"/>
+      <c r="AW8" s="24" t="n"/>
+      <c r="AX8" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY8" s="24" t="n"/>
+      <c r="AZ8" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA8" s="24" t="inlineStr">
+        <is>
+          <t>c97732889cfca1912f8d78791ff63f04ee3fe987951aced9e4fab541932597cd</t>
+        </is>
+      </c>
+      <c r="BB8" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC8" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BD8" s="24" t="inlineStr">
+        <is>
+          <t>c97732889cfca1912f8d78791ff63f04ee3fe987951aced9e4fab541932597cd</t>
+        </is>
+      </c>
+      <c r="BE8" s="24" t="inlineStr">
+        <is>
+          <t>4215d10b9bfb4b91</t>
+        </is>
+      </c>
+      <c r="BF8" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG8" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BH8" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-18T16:42:52.313468Z</t>
+        </is>
+      </c>
+      <c r="BI8" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ8" s="25" t="n"/>
+      <c r="BK8" s="26" t="n">
+        <v>-104</v>
+      </c>
+      <c r="BL8" s="27" t="n">
+        <v>1.961538</v>
+      </c>
+      <c r="BM8" s="28" t="n">
+        <v>0.509804</v>
+      </c>
+      <c r="BN8" s="28" t="n">
+        <v>0.507463</v>
+      </c>
+      <c r="BO8" s="28" t="n"/>
+      <c r="BP8" s="25" t="n"/>
+      <c r="BQ8" s="27" t="n"/>
+      <c r="BR8" s="28" t="n"/>
+      <c r="BS8" s="28" t="n"/>
+      <c r="BT8" s="28" t="n"/>
+      <c r="BU8" s="25" t="n"/>
+      <c r="BV8" s="29" t="n"/>
+      <c r="BW8" s="24" t="n"/>
+      <c r="BX8" s="30" t="n"/>
+      <c r="BY8" s="27" t="n"/>
+      <c r="BZ8" s="24" t="n"/>
+      <c r="CA8" s="31" t="n"/>
+    </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="24" t="inlineStr">
+        <is>
+          <t>2ec6744dbfd84ecf</t>
+        </is>
+      </c>
+      <c r="B9" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-18T16:44:20.099051Z</t>
+        </is>
+      </c>
+      <c r="C9" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-18T20:10Z</t>
+        </is>
+      </c>
+      <c r="D9" s="24" t="inlineStr">
+        <is>
+          <t>401816161</t>
+        </is>
+      </c>
+      <c r="E9" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F9" s="24" t="inlineStr">
+        <is>
+          <t>Texas Rangers</t>
+        </is>
+      </c>
+      <c r="G9" s="24" t="inlineStr">
+        <is>
+          <t>Atlanta Braves</t>
+        </is>
+      </c>
+      <c r="H9" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I9" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J9" s="25" t="n"/>
+      <c r="K9" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L9" s="26" t="n">
+        <v>-106</v>
+      </c>
+      <c r="M9" s="27" t="n">
+        <v>1.943396</v>
+      </c>
+      <c r="N9" s="28" t="n">
+        <v>0.514563</v>
+      </c>
+      <c r="O9" s="28" t="n">
+        <v>0.550297</v>
+      </c>
+      <c r="P9" s="28" t="n"/>
+      <c r="Q9" s="28" t="n">
+        <v>0.035734</v>
+      </c>
+      <c r="R9" s="26" t="n">
+        <v>68</v>
+      </c>
+      <c r="S9" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="U9" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V9" s="24" t="n"/>
+      <c r="W9" s="26" t="n"/>
+      <c r="X9" s="26" t="n"/>
+      <c r="Y9" s="25" t="n"/>
+      <c r="Z9" s="26" t="n"/>
+      <c r="AA9" s="28" t="n"/>
+      <c r="AB9" s="28" t="n"/>
+      <c r="AC9" s="30" t="n"/>
+      <c r="AD9" s="24" t="n"/>
+      <c r="AE9" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5500; executable ask 0.5150 (aec-mlb-tex-atl-2026-07-18).</t>
+        </is>
+      </c>
+      <c r="AF9" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
+        </is>
+      </c>
+      <c r="AG9" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH9" s="24" t="n"/>
+      <c r="AI9" s="31" t="n"/>
+      <c r="AJ9" s="31" t="n"/>
+      <c r="AK9" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL9" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM9" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN9" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO9" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP9" s="24" t="inlineStr">
+        <is>
+          <t>mlb-tex</t>
+        </is>
+      </c>
+      <c r="AQ9" s="24" t="inlineStr">
+        <is>
+          <t>Texas Rangers</t>
+        </is>
+      </c>
+      <c r="AR9" s="24" t="inlineStr">
+        <is>
+          <t>Texas Rangers</t>
+        </is>
+      </c>
+      <c r="AS9" s="24" t="inlineStr">
+        <is>
+          <t>mlb-atl</t>
+        </is>
+      </c>
+      <c r="AT9" s="24" t="inlineStr">
+        <is>
+          <t>Atlanta Braves</t>
+        </is>
+      </c>
+      <c r="AU9" s="24" t="inlineStr">
+        <is>
+          <t>Atlanta Braves</t>
+        </is>
+      </c>
+      <c r="AV9" s="24" t="n"/>
+      <c r="AW9" s="24" t="n"/>
+      <c r="AX9" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY9" s="24" t="n"/>
+      <c r="AZ9" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA9" s="24" t="inlineStr">
+        <is>
+          <t>c97732889cfca1912f8d78791ff63f04ee3fe987951aced9e4fab541932597cd</t>
+        </is>
+      </c>
+      <c r="BB9" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC9" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BD9" s="24" t="inlineStr">
+        <is>
+          <t>c97732889cfca1912f8d78791ff63f04ee3fe987951aced9e4fab541932597cd</t>
+        </is>
+      </c>
+      <c r="BE9" s="24" t="inlineStr">
+        <is>
+          <t>a999da31a6f5af28</t>
+        </is>
+      </c>
+      <c r="BF9" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG9" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BH9" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-18T16:42:57.199270Z</t>
+        </is>
+      </c>
+      <c r="BI9" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ9" s="25" t="n"/>
+      <c r="BK9" s="26" t="n">
+        <v>-106</v>
+      </c>
+      <c r="BL9" s="27" t="n">
+        <v>1.943396</v>
+      </c>
+      <c r="BM9" s="28" t="n">
+        <v>0.514563</v>
+      </c>
+      <c r="BN9" s="28" t="n">
+        <v>0.5124379999999999</v>
+      </c>
+      <c r="BO9" s="28" t="n"/>
+      <c r="BP9" s="25" t="n"/>
+      <c r="BQ9" s="27" t="n"/>
+      <c r="BR9" s="28" t="n"/>
+      <c r="BS9" s="28" t="n"/>
+      <c r="BT9" s="28" t="n"/>
+      <c r="BU9" s="25" t="n"/>
+      <c r="BV9" s="29" t="n"/>
+      <c r="BW9" s="24" t="n"/>
+      <c r="BX9" s="30" t="n"/>
+      <c r="BY9" s="27" t="n"/>
+      <c r="BZ9" s="24" t="n"/>
+      <c r="CA9" s="31" t="n"/>
+    </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="24" t="inlineStr">
+        <is>
+          <t>634e9b9c56164f59</t>
+        </is>
+      </c>
+      <c r="B10" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-18T16:44:20.099051Z</t>
+        </is>
+      </c>
+      <c r="C10" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-18T23:10Z</t>
+        </is>
+      </c>
+      <c r="D10" s="24" t="inlineStr">
+        <is>
+          <t>401816159</t>
+        </is>
+      </c>
+      <c r="E10" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F10" s="24" t="inlineStr">
+        <is>
+          <t>Pittsburgh Pirates</t>
+        </is>
+      </c>
+      <c r="G10" s="24" t="inlineStr">
+        <is>
+          <t>Cleveland Guardians</t>
+        </is>
+      </c>
+      <c r="H10" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I10" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J10" s="25" t="n"/>
+      <c r="K10" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L10" s="26" t="n">
+        <v>-102</v>
+      </c>
+      <c r="M10" s="27" t="n">
+        <v>1.980392</v>
+      </c>
+      <c r="N10" s="28" t="n">
+        <v>0.50495</v>
+      </c>
+      <c r="O10" s="28" t="n">
+        <v>0.554084</v>
+      </c>
+      <c r="P10" s="28" t="n"/>
+      <c r="Q10" s="28" t="n">
+        <v>0.049134</v>
+      </c>
+      <c r="R10" s="26" t="n">
+        <v>75</v>
+      </c>
+      <c r="S10" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="U10" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V10" s="24" t="n"/>
+      <c r="W10" s="26" t="n"/>
+      <c r="X10" s="26" t="n"/>
+      <c r="Y10" s="25" t="n"/>
+      <c r="Z10" s="26" t="n"/>
+      <c r="AA10" s="28" t="n"/>
+      <c r="AB10" s="28" t="n"/>
+      <c r="AC10" s="30" t="n"/>
+      <c r="AD10" s="24" t="n"/>
+      <c r="AE10" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5500; executable ask 0.5050 (aec-mlb-pit-cle-2026-07-18).</t>
+        </is>
+      </c>
+      <c r="AF10" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
+        </is>
+      </c>
+      <c r="AG10" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH10" s="24" t="n"/>
+      <c r="AI10" s="31" t="n"/>
+      <c r="AJ10" s="31" t="n"/>
+      <c r="AK10" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL10" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM10" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN10" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO10" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP10" s="24" t="inlineStr">
+        <is>
+          <t>mlb-pit</t>
+        </is>
+      </c>
+      <c r="AQ10" s="24" t="inlineStr">
+        <is>
+          <t>Pittsburgh Pirates</t>
+        </is>
+      </c>
+      <c r="AR10" s="24" t="inlineStr">
+        <is>
+          <t>Pittsburgh Pirates</t>
+        </is>
+      </c>
+      <c r="AS10" s="24" t="inlineStr">
+        <is>
+          <t>mlb-cle</t>
+        </is>
+      </c>
+      <c r="AT10" s="24" t="inlineStr">
+        <is>
+          <t>Cleveland Guardians</t>
+        </is>
+      </c>
+      <c r="AU10" s="24" t="inlineStr">
+        <is>
+          <t>Cleveland Guardians</t>
+        </is>
+      </c>
+      <c r="AV10" s="24" t="n"/>
+      <c r="AW10" s="24" t="n"/>
+      <c r="AX10" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY10" s="24" t="n"/>
+      <c r="AZ10" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA10" s="24" t="inlineStr">
+        <is>
+          <t>c97732889cfca1912f8d78791ff63f04ee3fe987951aced9e4fab541932597cd</t>
+        </is>
+      </c>
+      <c r="BB10" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC10" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BD10" s="24" t="inlineStr">
+        <is>
+          <t>c97732889cfca1912f8d78791ff63f04ee3fe987951aced9e4fab541932597cd</t>
+        </is>
+      </c>
+      <c r="BE10" s="24" t="inlineStr">
+        <is>
+          <t>3c0f9e9f1d0333c4</t>
+        </is>
+      </c>
+      <c r="BF10" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG10" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BH10" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-18T16:42:59.880808Z</t>
+        </is>
+      </c>
+      <c r="BI10" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ10" s="25" t="n"/>
+      <c r="BK10" s="26" t="n">
+        <v>-102</v>
+      </c>
+      <c r="BL10" s="27" t="n">
+        <v>1.980392</v>
+      </c>
+      <c r="BM10" s="28" t="n">
+        <v>0.50495</v>
+      </c>
+      <c r="BN10" s="28" t="n">
+        <v>0.502488</v>
+      </c>
+      <c r="BO10" s="28" t="n"/>
+      <c r="BP10" s="25" t="n"/>
+      <c r="BQ10" s="27" t="n"/>
+      <c r="BR10" s="28" t="n"/>
+      <c r="BS10" s="28" t="n"/>
+      <c r="BT10" s="28" t="n"/>
+      <c r="BU10" s="25" t="n"/>
+      <c r="BV10" s="29" t="n"/>
+      <c r="BW10" s="24" t="n"/>
+      <c r="BX10" s="30" t="n"/>
+      <c r="BY10" s="27" t="n"/>
+      <c r="BZ10" s="24" t="n"/>
+      <c r="CA10" s="31" t="n"/>
+    </row>
+    <row r="11" ht="36" customHeight="1">
+      <c r="A11" s="24" t="inlineStr">
+        <is>
+          <t>0a1abd6e59a84720</t>
+        </is>
+      </c>
+      <c r="B11" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-18T16:44:20.099051Z</t>
+        </is>
+      </c>
+      <c r="C11" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-19T00:08Z</t>
+        </is>
+      </c>
+      <c r="D11" s="24" t="inlineStr">
+        <is>
+          <t>401816168</t>
+        </is>
+      </c>
+      <c r="E11" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F11" s="24" t="inlineStr">
+        <is>
+          <t>San Francisco Giants</t>
+        </is>
+      </c>
+      <c r="G11" s="24" t="inlineStr">
+        <is>
+          <t>Seattle Mariners</t>
+        </is>
+      </c>
+      <c r="H11" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I11" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J11" s="25" t="n"/>
+      <c r="K11" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L11" s="26" t="n">
+        <v>-138</v>
+      </c>
+      <c r="M11" s="27" t="n">
+        <v>1.724638</v>
+      </c>
+      <c r="N11" s="28" t="n">
+        <v>0.579832</v>
+      </c>
+      <c r="O11" s="28" t="n">
+        <v>0.627758</v>
+      </c>
+      <c r="P11" s="28" t="n"/>
+      <c r="Q11" s="28" t="n">
+        <v>0.047926</v>
+      </c>
+      <c r="R11" s="26" t="n">
+        <v>74</v>
+      </c>
+      <c r="S11" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="U11" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V11" s="24" t="n"/>
+      <c r="W11" s="26" t="n"/>
+      <c r="X11" s="26" t="n"/>
+      <c r="Y11" s="25" t="n"/>
+      <c r="Z11" s="26" t="n"/>
+      <c r="AA11" s="28" t="n"/>
+      <c r="AB11" s="28" t="n"/>
+      <c r="AC11" s="30" t="n"/>
+      <c r="AD11" s="24" t="n"/>
+      <c r="AE11" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5500; executable ask 0.5800 (aec-mlb-sf-sea-2026-07-18).</t>
+        </is>
+      </c>
+      <c r="AF11" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
+        </is>
+      </c>
+      <c r="AG11" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH11" s="24" t="n"/>
+      <c r="AI11" s="31" t="n"/>
+      <c r="AJ11" s="31" t="n"/>
+      <c r="AK11" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL11" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM11" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN11" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO11" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP11" s="24" t="inlineStr">
+        <is>
+          <t>mlb-sf</t>
+        </is>
+      </c>
+      <c r="AQ11" s="24" t="inlineStr">
+        <is>
+          <t>San Francisco Giants</t>
+        </is>
+      </c>
+      <c r="AR11" s="24" t="inlineStr">
+        <is>
+          <t>San Francisco Giants</t>
+        </is>
+      </c>
+      <c r="AS11" s="24" t="inlineStr">
+        <is>
+          <t>mlb-sea</t>
+        </is>
+      </c>
+      <c r="AT11" s="24" t="inlineStr">
+        <is>
+          <t>Seattle Mariners</t>
+        </is>
+      </c>
+      <c r="AU11" s="24" t="inlineStr">
+        <is>
+          <t>Seattle Mariners</t>
+        </is>
+      </c>
+      <c r="AV11" s="24" t="n"/>
+      <c r="AW11" s="24" t="n"/>
+      <c r="AX11" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY11" s="24" t="n"/>
+      <c r="AZ11" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA11" s="24" t="inlineStr">
+        <is>
+          <t>c97732889cfca1912f8d78791ff63f04ee3fe987951aced9e4fab541932597cd</t>
+        </is>
+      </c>
+      <c r="BB11" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC11" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BD11" s="24" t="inlineStr">
+        <is>
+          <t>c97732889cfca1912f8d78791ff63f04ee3fe987951aced9e4fab541932597cd</t>
+        </is>
+      </c>
+      <c r="BE11" s="24" t="inlineStr">
+        <is>
+          <t>29d502a7704e228f</t>
+        </is>
+      </c>
+      <c r="BF11" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG11" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BH11" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-18T16:43:04.779295Z</t>
+        </is>
+      </c>
+      <c r="BI11" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ11" s="25" t="n"/>
+      <c r="BK11" s="26" t="n">
+        <v>-138</v>
+      </c>
+      <c r="BL11" s="27" t="n">
+        <v>1.724638</v>
+      </c>
+      <c r="BM11" s="28" t="n">
+        <v>0.579832</v>
+      </c>
+      <c r="BN11" s="28" t="n">
+        <v>0.577114</v>
+      </c>
+      <c r="BO11" s="28" t="n"/>
+      <c r="BP11" s="25" t="n"/>
+      <c r="BQ11" s="27" t="n"/>
+      <c r="BR11" s="28" t="n"/>
+      <c r="BS11" s="28" t="n"/>
+      <c r="BT11" s="28" t="n"/>
+      <c r="BU11" s="25" t="n"/>
+      <c r="BV11" s="29" t="n"/>
+      <c r="BW11" s="24" t="n"/>
+      <c r="BX11" s="30" t="n"/>
+      <c r="BY11" s="27" t="n"/>
+      <c r="BZ11" s="24" t="n"/>
+      <c r="CA11" s="31" t="n"/>
+    </row>
+    <row r="12" ht="36" customHeight="1">
+      <c r="A12" s="24" t="inlineStr">
+        <is>
+          <t>534daa3057c4428f</t>
+        </is>
+      </c>
+      <c r="B12" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-18T16:44:20.099051Z</t>
+        </is>
+      </c>
+      <c r="C12" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-19T02:05Z</t>
+        </is>
+      </c>
+      <c r="D12" s="24" t="inlineStr">
+        <is>
+          <t>401816170</t>
+        </is>
+      </c>
+      <c r="E12" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F12" s="24" t="inlineStr">
+        <is>
+          <t>Washington Nationals</t>
+        </is>
+      </c>
+      <c r="G12" s="24" t="inlineStr">
+        <is>
+          <t>Athletics</t>
+        </is>
+      </c>
+      <c r="H12" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I12" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J12" s="25" t="n"/>
+      <c r="K12" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L12" s="26" t="n">
+        <v>102</v>
+      </c>
+      <c r="M12" s="27" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="N12" s="28" t="n">
+        <v>0.49505</v>
+      </c>
+      <c r="O12" s="28" t="n">
+        <v>0.569735</v>
+      </c>
+      <c r="P12" s="28" t="n"/>
+      <c r="Q12" s="28" t="n">
+        <v>0.074685</v>
+      </c>
+      <c r="R12" s="26" t="n">
+        <v>87</v>
+      </c>
+      <c r="S12" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="U12" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V12" s="24" t="n"/>
+      <c r="W12" s="26" t="n"/>
+      <c r="X12" s="26" t="n"/>
+      <c r="Y12" s="25" t="n"/>
+      <c r="Z12" s="26" t="n"/>
+      <c r="AA12" s="28" t="n"/>
+      <c r="AB12" s="28" t="n"/>
+      <c r="AC12" s="30" t="n"/>
+      <c r="AD12" s="24" t="n"/>
+      <c r="AE12" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5500; executable ask 0.4950 (aec-mlb-wsh-ath-2026-07-18).</t>
+        </is>
+      </c>
+      <c r="AF12" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
+        </is>
+      </c>
+      <c r="AG12" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH12" s="24" t="n"/>
+      <c r="AI12" s="31" t="n"/>
+      <c r="AJ12" s="31" t="n"/>
+      <c r="AK12" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL12" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM12" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN12" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO12" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP12" s="24" t="inlineStr">
+        <is>
+          <t>mlb-wsh</t>
+        </is>
+      </c>
+      <c r="AQ12" s="24" t="inlineStr">
+        <is>
+          <t>Washington Nationals</t>
+        </is>
+      </c>
+      <c r="AR12" s="24" t="inlineStr">
+        <is>
+          <t>Washington Nationals</t>
+        </is>
+      </c>
+      <c r="AS12" s="24" t="inlineStr">
+        <is>
+          <t>mlb-ath</t>
+        </is>
+      </c>
+      <c r="AT12" s="24" t="inlineStr">
+        <is>
+          <t>Athletics</t>
+        </is>
+      </c>
+      <c r="AU12" s="24" t="inlineStr">
+        <is>
+          <t>Athletics</t>
+        </is>
+      </c>
+      <c r="AV12" s="24" t="n"/>
+      <c r="AW12" s="24" t="n"/>
+      <c r="AX12" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY12" s="24" t="n"/>
+      <c r="AZ12" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA12" s="24" t="inlineStr">
+        <is>
+          <t>c97732889cfca1912f8d78791ff63f04ee3fe987951aced9e4fab541932597cd</t>
+        </is>
+      </c>
+      <c r="BB12" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC12" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BD12" s="24" t="inlineStr">
+        <is>
+          <t>c97732889cfca1912f8d78791ff63f04ee3fe987951aced9e4fab541932597cd</t>
+        </is>
+      </c>
+      <c r="BE12" s="24" t="inlineStr">
+        <is>
+          <t>d2faed7be6c04691</t>
+        </is>
+      </c>
+      <c r="BF12" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG12" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BH12" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-18T16:43:06.321641Z</t>
+        </is>
+      </c>
+      <c r="BI12" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ12" s="25" t="n"/>
+      <c r="BK12" s="26" t="n">
+        <v>102</v>
+      </c>
+      <c r="BL12" s="27" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BM12" s="28" t="n">
+        <v>0.49505</v>
+      </c>
+      <c r="BN12" s="28" t="n">
+        <v>0.492537</v>
+      </c>
+      <c r="BO12" s="28" t="n"/>
+      <c r="BP12" s="25" t="n"/>
+      <c r="BQ12" s="27" t="n"/>
+      <c r="BR12" s="28" t="n"/>
+      <c r="BS12" s="28" t="n"/>
+      <c r="BT12" s="28" t="n"/>
+      <c r="BU12" s="25" t="n"/>
+      <c r="BV12" s="29" t="n"/>
+      <c r="BW12" s="24" t="n"/>
+      <c r="BX12" s="30" t="n"/>
+      <c r="BY12" s="27" t="n"/>
+      <c r="BZ12" s="24" t="n"/>
+      <c r="CA12" s="31" t="n"/>
+    </row>
+    <row r="13" ht="36" customHeight="1">
+      <c r="A13" s="24" t="inlineStr">
+        <is>
+          <t>5ab4cdd6444d4f9b</t>
+        </is>
+      </c>
+      <c r="B13" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-18T16:50:38.270483Z</t>
+        </is>
+      </c>
+      <c r="C13" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-18T20:10Z</t>
+        </is>
+      </c>
+      <c r="D13" s="24" t="inlineStr">
+        <is>
+          <t>401816162</t>
+        </is>
+      </c>
+      <c r="E13" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F13" s="24" t="inlineStr">
+        <is>
+          <t>Baltimore Orioles</t>
+        </is>
+      </c>
+      <c r="G13" s="24" t="inlineStr">
+        <is>
+          <t>Houston Astros</t>
+        </is>
+      </c>
+      <c r="H13" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I13" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J13" s="25" t="n"/>
+      <c r="K13" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L13" s="26" t="n">
+        <v>-102</v>
+      </c>
+      <c r="M13" s="27" t="n">
+        <v>1.980392</v>
+      </c>
+      <c r="N13" s="28" t="n">
+        <v>0.50495</v>
+      </c>
+      <c r="O13" s="28" t="n">
+        <v>0.545167</v>
+      </c>
+      <c r="P13" s="28" t="n"/>
+      <c r="Q13" s="28" t="n">
+        <v>0.040217</v>
+      </c>
+      <c r="R13" s="26" t="n">
+        <v>70</v>
+      </c>
+      <c r="S13" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="U13" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V13" s="24" t="n"/>
+      <c r="W13" s="26" t="n"/>
+      <c r="X13" s="26" t="n"/>
+      <c r="Y13" s="25" t="n"/>
+      <c r="Z13" s="26" t="n"/>
+      <c r="AA13" s="28" t="n"/>
+      <c r="AB13" s="28" t="n"/>
+      <c r="AC13" s="30" t="n"/>
+      <c r="AD13" s="24" t="n"/>
+      <c r="AE13" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5100; executable ask 0.5050 (aec-mlb-bal-hou-2026-07-18).</t>
+        </is>
+      </c>
+      <c r="AF13" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
+        </is>
+      </c>
+      <c r="AG13" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH13" s="24" t="n"/>
+      <c r="AI13" s="31" t="n"/>
+      <c r="AJ13" s="31" t="n"/>
+      <c r="AK13" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL13" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM13" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN13" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO13" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP13" s="24" t="inlineStr">
+        <is>
+          <t>mlb-bal</t>
+        </is>
+      </c>
+      <c r="AQ13" s="24" t="inlineStr">
+        <is>
+          <t>Baltimore Orioles</t>
+        </is>
+      </c>
+      <c r="AR13" s="24" t="inlineStr">
+        <is>
+          <t>Baltimore Orioles</t>
+        </is>
+      </c>
+      <c r="AS13" s="24" t="inlineStr">
+        <is>
+          <t>mlb-hou</t>
+        </is>
+      </c>
+      <c r="AT13" s="24" t="inlineStr">
+        <is>
+          <t>Houston Astros</t>
+        </is>
+      </c>
+      <c r="AU13" s="24" t="inlineStr">
+        <is>
+          <t>Houston Astros</t>
+        </is>
+      </c>
+      <c r="AV13" s="24" t="n"/>
+      <c r="AW13" s="24" t="n"/>
+      <c r="AX13" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY13" s="24" t="n"/>
+      <c r="AZ13" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA13" s="24" t="inlineStr">
+        <is>
+          <t>40e5d70a6fae1347ad85569354088d9df4f2d6970f7d7c2f9d4924d65efd0c19</t>
+        </is>
+      </c>
+      <c r="BB13" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC13" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BD13" s="24" t="inlineStr">
+        <is>
+          <t>40e5d70a6fae1347ad85569354088d9df4f2d6970f7d7c2f9d4924d65efd0c19</t>
+        </is>
+      </c>
+      <c r="BE13" s="24" t="inlineStr">
+        <is>
+          <t>f6cae9c590f4ed48</t>
+        </is>
+      </c>
+      <c r="BF13" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG13" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BH13" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-18T16:49:31.642864Z</t>
+        </is>
+      </c>
+      <c r="BI13" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ13" s="25" t="n"/>
+      <c r="BK13" s="26" t="n">
+        <v>-102</v>
+      </c>
+      <c r="BL13" s="27" t="n">
+        <v>1.980392</v>
+      </c>
+      <c r="BM13" s="28" t="n">
+        <v>0.50495</v>
+      </c>
+      <c r="BN13" s="28" t="n">
+        <v>0.502488</v>
+      </c>
+      <c r="BO13" s="28" t="n"/>
+      <c r="BP13" s="25" t="n"/>
+      <c r="BQ13" s="27" t="n"/>
+      <c r="BR13" s="28" t="n"/>
+      <c r="BS13" s="28" t="n"/>
+      <c r="BT13" s="28" t="n"/>
+      <c r="BU13" s="25" t="n"/>
+      <c r="BV13" s="29" t="n"/>
+      <c r="BW13" s="24" t="n"/>
+      <c r="BX13" s="30" t="n"/>
+      <c r="BY13" s="27" t="n"/>
+      <c r="BZ13" s="24" t="n"/>
+      <c r="CA13" s="31" t="n"/>
+    </row>
+    <row r="14" ht="36" customHeight="1">
+      <c r="A14" s="24" t="inlineStr">
+        <is>
+          <t>87feefaaee354c43</t>
+        </is>
+      </c>
+      <c r="B14" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-18T16:50:38.270483Z</t>
+        </is>
+      </c>
+      <c r="C14" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-19T00:08Z</t>
+        </is>
+      </c>
+      <c r="D14" s="24" t="inlineStr">
+        <is>
+          <t>401816157</t>
+        </is>
+      </c>
+      <c r="E14" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F14" s="24" t="inlineStr">
+        <is>
+          <t>Los Angeles Dodgers</t>
+        </is>
+      </c>
+      <c r="G14" s="24" t="inlineStr">
+        <is>
+          <t>New York Yankees</t>
+        </is>
+      </c>
+      <c r="H14" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I14" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J14" s="25" t="n"/>
+      <c r="K14" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L14" s="26" t="n">
+        <v>102</v>
+      </c>
+      <c r="M14" s="27" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="N14" s="28" t="n">
+        <v>0.49505</v>
+      </c>
+      <c r="O14" s="28" t="n">
+        <v>0.532568</v>
+      </c>
+      <c r="P14" s="28" t="n"/>
+      <c r="Q14" s="28" t="n">
+        <v>0.037518</v>
+      </c>
+      <c r="R14" s="26" t="n">
+        <v>69</v>
+      </c>
+      <c r="S14" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="U14" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V14" s="24" t="n"/>
+      <c r="W14" s="26" t="n"/>
+      <c r="X14" s="26" t="n"/>
+      <c r="Y14" s="25" t="n"/>
+      <c r="Z14" s="26" t="n"/>
+      <c r="AA14" s="28" t="n"/>
+      <c r="AB14" s="28" t="n"/>
+      <c r="AC14" s="30" t="n"/>
+      <c r="AD14" s="24" t="n"/>
+      <c r="AE14" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5100; executable ask 0.4950 (aec-mlb-lad-nyy-2026-07-18).</t>
+        </is>
+      </c>
+      <c r="AF14" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
+        </is>
+      </c>
+      <c r="AG14" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH14" s="24" t="n"/>
+      <c r="AI14" s="31" t="n"/>
+      <c r="AJ14" s="31" t="n"/>
+      <c r="AK14" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL14" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM14" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN14" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO14" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP14" s="24" t="inlineStr">
+        <is>
+          <t>mlb-lad</t>
+        </is>
+      </c>
+      <c r="AQ14" s="24" t="inlineStr">
+        <is>
+          <t>Los Angeles Dodgers</t>
+        </is>
+      </c>
+      <c r="AR14" s="24" t="inlineStr">
+        <is>
+          <t>Los Angeles Dodgers</t>
+        </is>
+      </c>
+      <c r="AS14" s="24" t="inlineStr">
+        <is>
+          <t>mlb-nyy</t>
+        </is>
+      </c>
+      <c r="AT14" s="24" t="inlineStr">
+        <is>
+          <t>New York Yankees</t>
+        </is>
+      </c>
+      <c r="AU14" s="24" t="inlineStr">
+        <is>
+          <t>New York Yankees</t>
+        </is>
+      </c>
+      <c r="AV14" s="24" t="n"/>
+      <c r="AW14" s="24" t="n"/>
+      <c r="AX14" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY14" s="24" t="n"/>
+      <c r="AZ14" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA14" s="24" t="inlineStr">
+        <is>
+          <t>40e5d70a6fae1347ad85569354088d9df4f2d6970f7d7c2f9d4924d65efd0c19</t>
+        </is>
+      </c>
+      <c r="BB14" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC14" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BD14" s="24" t="inlineStr">
+        <is>
+          <t>40e5d70a6fae1347ad85569354088d9df4f2d6970f7d7c2f9d4924d65efd0c19</t>
+        </is>
+      </c>
+      <c r="BE14" s="24" t="inlineStr">
+        <is>
+          <t>3492e72a2faca7c7</t>
+        </is>
+      </c>
+      <c r="BF14" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG14" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BH14" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-18T16:49:36.781770Z</t>
+        </is>
+      </c>
+      <c r="BI14" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ14" s="25" t="n"/>
+      <c r="BK14" s="26" t="n">
+        <v>102</v>
+      </c>
+      <c r="BL14" s="27" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BM14" s="28" t="n">
+        <v>0.49505</v>
+      </c>
+      <c r="BN14" s="28" t="n">
+        <v>0.492537</v>
+      </c>
+      <c r="BO14" s="28" t="n"/>
+      <c r="BP14" s="25" t="n"/>
+      <c r="BQ14" s="27" t="n"/>
+      <c r="BR14" s="28" t="n"/>
+      <c r="BS14" s="28" t="n"/>
+      <c r="BT14" s="28" t="n"/>
+      <c r="BU14" s="25" t="n"/>
+      <c r="BV14" s="29" t="n"/>
+      <c r="BW14" s="24" t="n"/>
+      <c r="BX14" s="30" t="n"/>
+      <c r="BY14" s="27" t="n"/>
+      <c r="BZ14" s="24" t="n"/>
+      <c r="CA14" s="31" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/picks.xlsx
+++ b/data/picks.xlsx
@@ -781,7 +781,6 @@
         <v/>
       </c>
     </row>
-    <row r="5"/>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
@@ -822,7 +821,6 @@
         <v/>
       </c>
     </row>
-    <row r="8"/>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
@@ -863,7 +861,6 @@
         <v/>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
@@ -1001,7 +998,6 @@
         <v/>
       </c>
     </row>
-    <row r="17"/>
     <row r="18">
       <c r="A18" s="22" t="inlineStr">
         <is>
@@ -1010,55 +1006,11 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2026-07-16T18:00:00Z</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>mlb</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>New York Mets</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Philadelphia Phillies</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Philadelphia Phillies</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>polymarket</t>
-        </is>
-      </c>
-      <c r="J19" t="n">
-        <v>-110</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0.6118</v>
-      </c>
       <c r="M19" t="inlineStr">
         <is>
           <t>mlb-elo-trend-lr-v3</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>analyst_estimate</t>
@@ -1069,7 +1021,6 @@
           <t>research</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr">
         <is>
           <t>identity</t>
@@ -1080,7 +1031,6 @@
           <t>identity-v1</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr">
         <is>
           <t>1</t>
@@ -1096,7 +1046,6 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="AA19" t="inlineStr"/>
       <c r="AE19" t="inlineStr">
         <is>
           <t>settled</t>
@@ -1117,7 +1066,6 @@
           <t>2026-07-16T18:00:00Z</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
           <t>wnba</t>
@@ -1159,8 +1107,6 @@
           <t>wnba-elo-trend-lr-v3</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>analyst_estimate</t>
@@ -1171,7 +1117,6 @@
           <t>research</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr">
         <is>
           <t>identity</t>
@@ -1182,7 +1127,6 @@
           <t>identity-v1</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr"/>
       <c r="X20" t="inlineStr">
         <is>
           <t>1</t>
@@ -1198,7 +1142,6 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="AA20" t="inlineStr"/>
       <c r="AE20" t="inlineStr">
         <is>
           <t>settled</t>
@@ -1219,7 +1162,6 @@
           <t>2026-07-17T18:00:00Z</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
           <t>mlb</t>
@@ -1261,8 +1203,6 @@
           <t>mlb-elo-trend-lr-v3</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>analyst_estimate</t>
@@ -1273,7 +1213,6 @@
           <t>research</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr">
         <is>
           <t>identity</t>
@@ -1284,7 +1223,6 @@
           <t>identity-v1</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr"/>
       <c r="X21" t="inlineStr">
         <is>
           <t>1</t>
@@ -1300,7 +1238,6 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="AA21" t="inlineStr"/>
       <c r="AE21" t="inlineStr">
         <is>
           <t>settled</t>
@@ -1321,7 +1258,6 @@
           <t>2026-07-17T18:00:00Z</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
           <t>mlb</t>
@@ -1363,8 +1299,6 @@
           <t>mlb-elo-trend-lr-v3</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>analyst_estimate</t>
@@ -1375,7 +1309,6 @@
           <t>research</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr">
         <is>
           <t>identity</t>
@@ -1386,7 +1319,6 @@
           <t>identity-v1</t>
         </is>
       </c>
-      <c r="W22" t="inlineStr"/>
       <c r="X22" t="inlineStr">
         <is>
           <t>1</t>
@@ -1402,7 +1334,6 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="AA22" t="inlineStr"/>
       <c r="AE22" t="inlineStr">
         <is>
           <t>settled</t>
@@ -1423,7 +1354,6 @@
           <t>2026-07-17T18:00:00Z</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
           <t>mlb</t>
@@ -1465,8 +1395,6 @@
           <t>mlb-elo-trend-lr-v3</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>analyst_estimate</t>
@@ -1477,7 +1405,6 @@
           <t>research</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr">
         <is>
           <t>identity</t>
@@ -1488,7 +1415,6 @@
           <t>identity-v1</t>
         </is>
       </c>
-      <c r="W23" t="inlineStr"/>
       <c r="X23" t="inlineStr">
         <is>
           <t>1</t>
@@ -1504,7 +1430,6 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="AA23" t="inlineStr"/>
       <c r="AE23" t="inlineStr">
         <is>
           <t>settled</t>
@@ -1525,7 +1450,6 @@
           <t>2026-07-17T18:00:00Z</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
           <t>mlb</t>
@@ -1567,8 +1491,6 @@
           <t>mlb-elo-trend-lr-v3</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>analyst_estimate</t>
@@ -1579,7 +1501,6 @@
           <t>research</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr">
         <is>
           <t>identity</t>
@@ -1590,7 +1511,6 @@
           <t>identity-v1</t>
         </is>
       </c>
-      <c r="W24" t="inlineStr"/>
       <c r="X24" t="inlineStr">
         <is>
           <t>1</t>
@@ -1606,7 +1526,6 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="AA24" t="inlineStr"/>
       <c r="AE24" t="inlineStr">
         <is>
           <t>settled</t>
@@ -1627,7 +1546,6 @@
           <t>2026-07-17T18:00:00Z</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
           <t>mlb</t>
@@ -1669,8 +1587,6 @@
           <t>mlb-elo-trend-lr-v3</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>analyst_estimate</t>
@@ -1681,7 +1597,6 @@
           <t>research</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr">
         <is>
           <t>identity</t>
@@ -1692,7 +1607,6 @@
           <t>identity-v1</t>
         </is>
       </c>
-      <c r="W25" t="inlineStr"/>
       <c r="X25" t="inlineStr">
         <is>
           <t>1</t>
@@ -1708,7 +1622,6 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="AA25" t="inlineStr"/>
       <c r="AE25" t="inlineStr">
         <is>
           <t>settled</t>
@@ -1729,7 +1642,6 @@
           <t>2026-07-17T18:00:00Z</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
           <t>mlb</t>
@@ -1771,8 +1683,6 @@
           <t>mlb-elo-trend-lr-v3</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>analyst_estimate</t>
@@ -1783,7 +1693,6 @@
           <t>research</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr">
         <is>
           <t>identity</t>
@@ -1794,7 +1703,6 @@
           <t>identity-v1</t>
         </is>
       </c>
-      <c r="W26" t="inlineStr"/>
       <c r="X26" t="inlineStr">
         <is>
           <t>1</t>
@@ -1810,7 +1718,6 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="AA26" t="inlineStr"/>
       <c r="AE26" t="inlineStr">
         <is>
           <t>settled</t>
@@ -1831,7 +1738,6 @@
           <t>2026-07-17T18:00:00Z</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
           <t>mlb</t>
@@ -1873,8 +1779,6 @@
           <t>mlb-elo-trend-lr-v3</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>analyst_estimate</t>
@@ -1885,7 +1789,6 @@
           <t>research</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr">
         <is>
           <t>identity</t>
@@ -1896,7 +1799,6 @@
           <t>identity-v1</t>
         </is>
       </c>
-      <c r="W27" t="inlineStr"/>
       <c r="X27" t="inlineStr">
         <is>
           <t>1</t>
@@ -1912,7 +1814,6 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="AA27" t="inlineStr"/>
       <c r="AE27" t="inlineStr">
         <is>
           <t>settled</t>
@@ -1933,7 +1834,6 @@
           <t>2026-07-17T18:00:00Z</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr">
         <is>
           <t>mlb</t>
@@ -1975,8 +1875,6 @@
           <t>mlb-elo-trend-lr-v3</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>analyst_estimate</t>
@@ -1987,7 +1885,6 @@
           <t>research</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr">
         <is>
           <t>identity</t>
@@ -1998,7 +1895,6 @@
           <t>identity-v1</t>
         </is>
       </c>
-      <c r="W28" t="inlineStr"/>
       <c r="X28" t="inlineStr">
         <is>
           <t>1</t>
@@ -2014,7 +1910,6 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="AA28" t="inlineStr"/>
       <c r="AE28" t="inlineStr">
         <is>
           <t>settled</t>
@@ -2035,7 +1930,6 @@
           <t>2026-07-17T18:00:00Z</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
           <t>mlb</t>
@@ -2077,8 +1971,6 @@
           <t>mlb-elo-trend-lr-v3</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>analyst_estimate</t>
@@ -2089,7 +1981,6 @@
           <t>research</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr">
         <is>
           <t>identity</t>
@@ -2100,7 +1991,6 @@
           <t>identity-v1</t>
         </is>
       </c>
-      <c r="W29" t="inlineStr"/>
       <c r="X29" t="inlineStr">
         <is>
           <t>1</t>
@@ -2116,7 +2006,6 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="AA29" t="inlineStr"/>
       <c r="AE29" t="inlineStr">
         <is>
           <t>settled</t>
@@ -2137,7 +2026,6 @@
           <t>2026-07-17T18:00:00Z</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
           <t>mlb</t>
@@ -2179,8 +2067,6 @@
           <t>mlb-elo-trend-lr-v3</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>analyst_estimate</t>
@@ -2191,7 +2077,6 @@
           <t>research</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr">
         <is>
           <t>identity</t>
@@ -2202,7 +2087,6 @@
           <t>identity-v1</t>
         </is>
       </c>
-      <c r="W30" t="inlineStr"/>
       <c r="X30" t="inlineStr">
         <is>
           <t>1</t>
@@ -2218,7 +2102,6 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="AA30" t="inlineStr"/>
       <c r="AE30" t="inlineStr">
         <is>
           <t>settled</t>
@@ -2239,7 +2122,6 @@
           <t>2026-07-17T18:00:00Z</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
           <t>mlb</t>
@@ -2281,8 +2163,6 @@
           <t>mlb-elo-trend-lr-v3</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>analyst_estimate</t>
@@ -2293,7 +2173,6 @@
           <t>research</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr">
         <is>
           <t>identity</t>
@@ -2304,7 +2183,6 @@
           <t>identity-v1</t>
         </is>
       </c>
-      <c r="W31" t="inlineStr"/>
       <c r="X31" t="inlineStr">
         <is>
           <t>1</t>
@@ -2320,7 +2198,6 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="AA31" t="inlineStr"/>
       <c r="AE31" t="inlineStr">
         <is>
           <t>settled</t>
@@ -2341,7 +2218,6 @@
           <t>2026-07-17T18:00:00Z</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
           <t>mlb</t>
@@ -2383,8 +2259,6 @@
           <t>mlb-elo-trend-lr-v3</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>analyst_estimate</t>
@@ -2395,7 +2269,6 @@
           <t>research</t>
         </is>
       </c>
-      <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr">
         <is>
           <t>identity</t>
@@ -2406,7 +2279,6 @@
           <t>identity-v1</t>
         </is>
       </c>
-      <c r="W32" t="inlineStr"/>
       <c r="X32" t="inlineStr">
         <is>
           <t>1</t>
@@ -2422,7 +2294,6 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="AA32" t="inlineStr"/>
       <c r="AE32" t="inlineStr">
         <is>
           <t>settled</t>
@@ -2443,7 +2314,6 @@
           <t>2026-07-17T18:00:00Z</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr">
         <is>
           <t>mlb</t>
@@ -2485,8 +2355,6 @@
           <t>mlb-elo-trend-lr-v3</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>analyst_estimate</t>
@@ -2497,7 +2365,6 @@
           <t>research</t>
         </is>
       </c>
-      <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr">
         <is>
           <t>identity</t>
@@ -2508,7 +2375,6 @@
           <t>identity-v1</t>
         </is>
       </c>
-      <c r="W33" t="inlineStr"/>
       <c r="X33" t="inlineStr">
         <is>
           <t>1</t>
@@ -2524,7 +2390,6 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="AA33" t="inlineStr"/>
       <c r="AE33" t="inlineStr">
         <is>
           <t>settled</t>
@@ -2545,7 +2410,6 @@
           <t>2026-07-17T18:00:00Z</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
         <is>
           <t>wnba</t>
@@ -2587,8 +2451,6 @@
           <t>wnba-elo-trend-lr-v3</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>analyst_estimate</t>
@@ -2599,7 +2461,6 @@
           <t>research</t>
         </is>
       </c>
-      <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr">
         <is>
           <t>identity</t>
@@ -2610,7 +2471,6 @@
           <t>identity-v1</t>
         </is>
       </c>
-      <c r="W34" t="inlineStr"/>
       <c r="X34" t="inlineStr">
         <is>
           <t>1</t>
@@ -2626,7 +2486,6 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="AA34" t="inlineStr"/>
       <c r="AE34" t="inlineStr">
         <is>
           <t>settled</t>
@@ -2647,7 +2506,6 @@
           <t>2026-07-17T18:00:00Z</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
           <t>wnba</t>
@@ -2689,8 +2547,6 @@
           <t>wnba-elo-trend-lr-v3</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>analyst_estimate</t>
@@ -2701,7 +2557,6 @@
           <t>research</t>
         </is>
       </c>
-      <c r="T35" t="inlineStr"/>
       <c r="U35" t="inlineStr">
         <is>
           <t>identity</t>
@@ -2712,7 +2567,6 @@
           <t>identity-v1</t>
         </is>
       </c>
-      <c r="W35" t="inlineStr"/>
       <c r="X35" t="inlineStr">
         <is>
           <t>1</t>
@@ -2728,7 +2582,6 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="AA35" t="inlineStr"/>
       <c r="AE35" t="inlineStr">
         <is>
           <t>settled</t>
@@ -2749,7 +2602,6 @@
           <t>2026-07-17T18:00:00Z</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
           <t>wnba</t>
@@ -2791,8 +2643,6 @@
           <t>wnba-elo-trend-lr-v3</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>analyst_estimate</t>
@@ -2803,7 +2653,6 @@
           <t>research</t>
         </is>
       </c>
-      <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr">
         <is>
           <t>identity</t>
@@ -2814,7 +2663,6 @@
           <t>identity-v1</t>
         </is>
       </c>
-      <c r="W36" t="inlineStr"/>
       <c r="X36" t="inlineStr">
         <is>
           <t>1</t>
@@ -2830,7 +2678,6 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="AA36" t="inlineStr"/>
       <c r="AE36" t="inlineStr">
         <is>
           <t>settled</t>
@@ -2851,7 +2698,6 @@
           <t>2026-07-17T18:00:00Z</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
           <t>wnba</t>
@@ -2893,8 +2739,6 @@
           <t>wnba-elo-trend-lr-v3</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>analyst_estimate</t>
@@ -2905,7 +2749,6 @@
           <t>research</t>
         </is>
       </c>
-      <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr">
         <is>
           <t>identity</t>
@@ -2916,7 +2759,6 @@
           <t>identity-v1</t>
         </is>
       </c>
-      <c r="W37" t="inlineStr"/>
       <c r="X37" t="inlineStr">
         <is>
           <t>1</t>
@@ -2932,7 +2774,6 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="AA37" t="inlineStr"/>
       <c r="AE37" t="inlineStr">
         <is>
           <t>settled</t>
@@ -2953,7 +2794,6 @@
           <t>2026-07-18T18:00:00Z</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
           <t>mlb</t>
@@ -2995,8 +2835,6 @@
           <t>mlb-elo-trend-lr-v3</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>analyst_estimate</t>
@@ -3007,7 +2845,6 @@
           <t>research</t>
         </is>
       </c>
-      <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr">
         <is>
           <t>identity</t>
@@ -3018,7 +2855,6 @@
           <t>identity-v1</t>
         </is>
       </c>
-      <c r="W38" t="inlineStr"/>
       <c r="X38" t="inlineStr">
         <is>
           <t>1</t>
@@ -3034,7 +2870,6 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="AA38" t="inlineStr"/>
       <c r="AE38" t="inlineStr">
         <is>
           <t>settled</t>
@@ -3055,7 +2890,6 @@
           <t>2026-07-18T18:00:00Z</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr">
         <is>
           <t>mlb</t>
@@ -3097,8 +2931,6 @@
           <t>mlb-elo-trend-lr-v3</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>analyst_estimate</t>
@@ -3109,7 +2941,6 @@
           <t>research</t>
         </is>
       </c>
-      <c r="T39" t="inlineStr"/>
       <c r="U39" t="inlineStr">
         <is>
           <t>identity</t>
@@ -3120,7 +2951,6 @@
           <t>identity-v1</t>
         </is>
       </c>
-      <c r="W39" t="inlineStr"/>
       <c r="X39" t="inlineStr">
         <is>
           <t>1</t>
@@ -3136,7 +2966,6 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="AA39" t="inlineStr"/>
       <c r="AE39" t="inlineStr">
         <is>
           <t>settled</t>
@@ -3157,7 +2986,6 @@
           <t>2026-07-18T18:00:00Z</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr">
         <is>
           <t>mlb</t>
@@ -3199,8 +3027,6 @@
           <t>mlb-elo-trend-lr-v3</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>analyst_estimate</t>
@@ -3211,7 +3037,6 @@
           <t>research</t>
         </is>
       </c>
-      <c r="T40" t="inlineStr"/>
       <c r="U40" t="inlineStr">
         <is>
           <t>identity</t>
@@ -3222,7 +3047,6 @@
           <t>identity-v1</t>
         </is>
       </c>
-      <c r="W40" t="inlineStr"/>
       <c r="X40" t="inlineStr">
         <is>
           <t>1</t>
@@ -3238,7 +3062,6 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="AA40" t="inlineStr"/>
       <c r="AE40" t="inlineStr">
         <is>
           <t>settled</t>
@@ -3259,7 +3082,6 @@
           <t>2026-07-18T18:00:00Z</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
           <t>mlb</t>
@@ -3301,8 +3123,6 @@
           <t>mlb-elo-trend-lr-v3</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>analyst_estimate</t>
@@ -3313,7 +3133,6 @@
           <t>research</t>
         </is>
       </c>
-      <c r="T41" t="inlineStr"/>
       <c r="U41" t="inlineStr">
         <is>
           <t>identity</t>
@@ -3324,7 +3143,6 @@
           <t>identity-v1</t>
         </is>
       </c>
-      <c r="W41" t="inlineStr"/>
       <c r="X41" t="inlineStr">
         <is>
           <t>1</t>
@@ -3340,7 +3158,6 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="AA41" t="inlineStr"/>
       <c r="AE41" t="inlineStr">
         <is>
           <t>settled</t>
@@ -3361,7 +3178,6 @@
           <t>2026-07-18T18:00:00Z</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr">
         <is>
           <t>mlb</t>
@@ -3403,8 +3219,6 @@
           <t>mlb-elo-trend-lr-v3</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>analyst_estimate</t>
@@ -3415,7 +3229,6 @@
           <t>research</t>
         </is>
       </c>
-      <c r="T42" t="inlineStr"/>
       <c r="U42" t="inlineStr">
         <is>
           <t>identity</t>
@@ -3426,7 +3239,6 @@
           <t>identity-v1</t>
         </is>
       </c>
-      <c r="W42" t="inlineStr"/>
       <c r="X42" t="inlineStr">
         <is>
           <t>1</t>
@@ -3442,7 +3254,6 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="AA42" t="inlineStr"/>
       <c r="AE42" t="inlineStr">
         <is>
           <t>settled</t>
@@ -3463,7 +3274,6 @@
           <t>2026-07-18T18:00:00Z</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr">
         <is>
           <t>mlb</t>
@@ -3505,8 +3315,6 @@
           <t>mlb-elo-trend-lr-v3</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>analyst_estimate</t>
@@ -3517,7 +3325,6 @@
           <t>research</t>
         </is>
       </c>
-      <c r="T43" t="inlineStr"/>
       <c r="U43" t="inlineStr">
         <is>
           <t>identity</t>
@@ -3528,7 +3335,6 @@
           <t>identity-v1</t>
         </is>
       </c>
-      <c r="W43" t="inlineStr"/>
       <c r="X43" t="inlineStr">
         <is>
           <t>1</t>
@@ -3544,7 +3350,6 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="AA43" t="inlineStr"/>
       <c r="AE43" t="inlineStr">
         <is>
           <t>settled</t>
@@ -3565,7 +3370,6 @@
           <t>2026-07-18T18:00:00Z</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
           <t>mlb</t>
@@ -3607,8 +3411,6 @@
           <t>mlb-elo-trend-lr-v3</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>analyst_estimate</t>
@@ -3619,7 +3421,6 @@
           <t>research</t>
         </is>
       </c>
-      <c r="T44" t="inlineStr"/>
       <c r="U44" t="inlineStr">
         <is>
           <t>identity</t>
@@ -3630,7 +3431,6 @@
           <t>identity-v1</t>
         </is>
       </c>
-      <c r="W44" t="inlineStr"/>
       <c r="X44" t="inlineStr">
         <is>
           <t>1</t>
@@ -3646,7 +3446,6 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="AA44" t="inlineStr"/>
       <c r="AE44" t="inlineStr">
         <is>
           <t>settled</t>
@@ -3667,7 +3466,6 @@
           <t>2026-07-18T18:00:00Z</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
           <t>mlb</t>
@@ -3709,8 +3507,6 @@
           <t>mlb-elo-trend-lr-v3</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>analyst_estimate</t>
@@ -3721,7 +3517,6 @@
           <t>research</t>
         </is>
       </c>
-      <c r="T45" t="inlineStr"/>
       <c r="U45" t="inlineStr">
         <is>
           <t>identity</t>
@@ -3732,7 +3527,6 @@
           <t>identity-v1</t>
         </is>
       </c>
-      <c r="W45" t="inlineStr"/>
       <c r="X45" t="inlineStr">
         <is>
           <t>1</t>
@@ -3748,7 +3542,6 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="AA45" t="inlineStr"/>
       <c r="AE45" t="inlineStr">
         <is>
           <t>settled</t>
@@ -3769,7 +3562,6 @@
           <t>2026-07-18T18:00:00Z</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
           <t>mlb</t>
@@ -3811,8 +3603,6 @@
           <t>mlb-elo-trend-lr-v3</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>analyst_estimate</t>
@@ -3823,7 +3613,6 @@
           <t>research</t>
         </is>
       </c>
-      <c r="T46" t="inlineStr"/>
       <c r="U46" t="inlineStr">
         <is>
           <t>identity</t>
@@ -3834,7 +3623,6 @@
           <t>identity-v1</t>
         </is>
       </c>
-      <c r="W46" t="inlineStr"/>
       <c r="X46" t="inlineStr">
         <is>
           <t>1</t>
@@ -3850,7 +3638,6 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="AA46" t="inlineStr"/>
       <c r="AE46" t="inlineStr">
         <is>
           <t>settled</t>
@@ -3871,7 +3658,6 @@
           <t>2026-07-18T18:00:00Z</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
           <t>mlb</t>
@@ -3913,8 +3699,6 @@
           <t>mlb-elo-trend-lr-v3</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>analyst_estimate</t>
@@ -3925,7 +3709,6 @@
           <t>research</t>
         </is>
       </c>
-      <c r="T47" t="inlineStr"/>
       <c r="U47" t="inlineStr">
         <is>
           <t>identity</t>
@@ -3936,7 +3719,6 @@
           <t>identity-v1</t>
         </is>
       </c>
-      <c r="W47" t="inlineStr"/>
       <c r="X47" t="inlineStr">
         <is>
           <t>1</t>
@@ -3952,7 +3734,6 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="AA47" t="inlineStr"/>
       <c r="AE47" t="inlineStr">
         <is>
           <t>settled</t>
@@ -3973,7 +3754,6 @@
           <t>2026-07-18T18:00:00Z</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
           <t>mlb</t>
@@ -4015,8 +3795,6 @@
           <t>mlb-elo-trend-lr-v3</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>analyst_estimate</t>
@@ -4027,7 +3805,6 @@
           <t>research</t>
         </is>
       </c>
-      <c r="T48" t="inlineStr"/>
       <c r="U48" t="inlineStr">
         <is>
           <t>identity</t>
@@ -4038,7 +3815,6 @@
           <t>identity-v1</t>
         </is>
       </c>
-      <c r="W48" t="inlineStr"/>
       <c r="X48" t="inlineStr">
         <is>
           <t>1</t>
@@ -4054,7 +3830,6 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="AA48" t="inlineStr"/>
       <c r="AE48" t="inlineStr">
         <is>
           <t>settled</t>
@@ -4075,7 +3850,6 @@
           <t>2026-07-18T18:00:00Z</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr">
         <is>
           <t>mlb</t>
@@ -4117,8 +3891,6 @@
           <t>mlb-elo-trend-lr-v3</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>analyst_estimate</t>
@@ -4129,7 +3901,6 @@
           <t>research</t>
         </is>
       </c>
-      <c r="T49" t="inlineStr"/>
       <c r="U49" t="inlineStr">
         <is>
           <t>identity</t>
@@ -4140,7 +3911,6 @@
           <t>identity-v1</t>
         </is>
       </c>
-      <c r="W49" t="inlineStr"/>
       <c r="X49" t="inlineStr">
         <is>
           <t>1</t>
@@ -4156,7 +3926,6 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="AA49" t="inlineStr"/>
       <c r="AE49" t="inlineStr">
         <is>
           <t>settled</t>
@@ -4177,7 +3946,6 @@
           <t>2026-07-18T18:00:00Z</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr">
         <is>
           <t>mlb</t>
@@ -4219,8 +3987,6 @@
           <t>mlb-elo-trend-lr-v3</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>analyst_estimate</t>
@@ -4231,7 +3997,6 @@
           <t>research</t>
         </is>
       </c>
-      <c r="T50" t="inlineStr"/>
       <c r="U50" t="inlineStr">
         <is>
           <t>identity</t>
@@ -4242,7 +4007,6 @@
           <t>identity-v1</t>
         </is>
       </c>
-      <c r="W50" t="inlineStr"/>
       <c r="X50" t="inlineStr">
         <is>
           <t>1</t>
@@ -4258,7 +4022,6 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="AA50" t="inlineStr"/>
       <c r="AE50" t="inlineStr">
         <is>
           <t>settled</t>
@@ -4279,7 +4042,6 @@
           <t>2026-07-18T18:00:00Z</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr">
         <is>
           <t>mlb</t>
@@ -4321,8 +4083,6 @@
           <t>mlb-elo-trend-lr-v3</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>analyst_estimate</t>
@@ -4333,7 +4093,6 @@
           <t>research</t>
         </is>
       </c>
-      <c r="T51" t="inlineStr"/>
       <c r="U51" t="inlineStr">
         <is>
           <t>identity</t>
@@ -4344,7 +4103,6 @@
           <t>identity-v1</t>
         </is>
       </c>
-      <c r="W51" t="inlineStr"/>
       <c r="X51" t="inlineStr">
         <is>
           <t>1</t>
@@ -4360,7 +4118,6 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="AA51" t="inlineStr"/>
       <c r="AE51" t="inlineStr">
         <is>
           <t>settled</t>
@@ -4381,7 +4138,6 @@
           <t>2026-07-18T18:00:00Z</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr">
         <is>
           <t>mlb</t>
@@ -4423,8 +4179,6 @@
           <t>mlb-elo-trend-lr-v3</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>analyst_estimate</t>
@@ -4435,7 +4189,6 @@
           <t>research</t>
         </is>
       </c>
-      <c r="T52" t="inlineStr"/>
       <c r="U52" t="inlineStr">
         <is>
           <t>identity</t>
@@ -4446,7 +4199,6 @@
           <t>identity-v1</t>
         </is>
       </c>
-      <c r="W52" t="inlineStr"/>
       <c r="X52" t="inlineStr">
         <is>
           <t>1</t>
@@ -4462,7 +4214,6 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="AA52" t="inlineStr"/>
       <c r="AE52" t="inlineStr">
         <is>
           <t>settled</t>
@@ -4483,7 +4234,6 @@
           <t>2026-07-18T18:00:00Z</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr">
         <is>
           <t>wnba</t>
@@ -4525,8 +4275,6 @@
           <t>wnba-elo-trend-lr-v3</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>analyst_estimate</t>
@@ -4537,7 +4285,6 @@
           <t>research</t>
         </is>
       </c>
-      <c r="T53" t="inlineStr"/>
       <c r="U53" t="inlineStr">
         <is>
           <t>identity</t>
@@ -4548,7 +4295,6 @@
           <t>identity-v1</t>
         </is>
       </c>
-      <c r="W53" t="inlineStr"/>
       <c r="X53" t="inlineStr">
         <is>
           <t>1</t>
@@ -4564,7 +4310,6 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="AA53" t="inlineStr"/>
       <c r="AE53" t="inlineStr">
         <is>
           <t>settled</t>
@@ -4585,7 +4330,6 @@
           <t>2026-07-18T18:00:00Z</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr">
         <is>
           <t>wnba</t>
@@ -4627,8 +4371,6 @@
           <t>wnba-elo-trend-lr-v3</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>analyst_estimate</t>
@@ -4639,7 +4381,6 @@
           <t>research</t>
         </is>
       </c>
-      <c r="T54" t="inlineStr"/>
       <c r="U54" t="inlineStr">
         <is>
           <t>identity</t>
@@ -4650,7 +4391,6 @@
           <t>identity-v1</t>
         </is>
       </c>
-      <c r="W54" t="inlineStr"/>
       <c r="X54" t="inlineStr">
         <is>
           <t>1</t>
@@ -4666,7 +4406,6 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="AA54" t="inlineStr"/>
       <c r="AE54" t="inlineStr">
         <is>
           <t>settled</t>
@@ -4687,7 +4426,6 @@
           <t>2026-07-18T18:00:00Z</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr">
         <is>
           <t>wnba</t>
@@ -4729,8 +4467,6 @@
           <t>wnba-elo-trend-lr-v3</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>analyst_estimate</t>
@@ -4741,7 +4477,6 @@
           <t>research</t>
         </is>
       </c>
-      <c r="T55" t="inlineStr"/>
       <c r="U55" t="inlineStr">
         <is>
           <t>identity</t>
@@ -4752,7 +4487,6 @@
           <t>identity-v1</t>
         </is>
       </c>
-      <c r="W55" t="inlineStr"/>
       <c r="X55" t="inlineStr">
         <is>
           <t>1</t>
@@ -4768,7 +4502,6 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="AA55" t="inlineStr"/>
       <c r="AE55" t="inlineStr">
         <is>
           <t>settled</t>
@@ -4800,7 +4533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CA32"/>
+  <dimension ref="A1:CA56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -13274,6 +13007,3486 @@
       <c r="BZ32" s="24" t="n"/>
       <c r="CA32" s="31" t="n"/>
     </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2fe604a809ed46d5</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-07-19T10:49:38.448695+00:00</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2026-07-17T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Tamp-Bost-2026-07-17</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Boston Red Sox</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Boston Red Sox</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>0.550333</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>0.909091</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr"/>
+      <c r="X33" t="inlineStr"/>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr"/>
+      <c r="AB33" t="inlineStr"/>
+      <c r="AC33" t="inlineStr"/>
+      <c r="AD33" t="inlineStr"/>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>backtest</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="inlineStr"/>
+      <c r="AH33" t="inlineStr"/>
+      <c r="AI33" t="inlineStr"/>
+      <c r="AJ33" t="inlineStr"/>
+      <c r="AK33" t="inlineStr"/>
+      <c r="AL33" t="inlineStr"/>
+      <c r="AM33" t="inlineStr"/>
+      <c r="AN33" t="inlineStr"/>
+      <c r="AO33" t="inlineStr"/>
+      <c r="AP33" t="inlineStr"/>
+      <c r="AQ33" t="inlineStr"/>
+      <c r="AR33" t="inlineStr"/>
+      <c r="AS33" t="inlineStr"/>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AU33" t="inlineStr"/>
+      <c r="AV33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr"/>
+      <c r="AX33" t="inlineStr"/>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr"/>
+      <c r="BA33" t="inlineStr"/>
+      <c r="BB33" t="inlineStr"/>
+      <c r="BC33" t="inlineStr"/>
+      <c r="BD33" t="inlineStr"/>
+      <c r="BE33" t="inlineStr"/>
+      <c r="BF33" t="inlineStr"/>
+      <c r="BG33" t="inlineStr"/>
+      <c r="BH33" t="inlineStr"/>
+      <c r="BI33" t="inlineStr"/>
+      <c r="BJ33" t="inlineStr"/>
+      <c r="BK33" t="inlineStr"/>
+      <c r="BL33" t="inlineStr"/>
+      <c r="BM33" t="inlineStr"/>
+      <c r="BN33" t="inlineStr"/>
+      <c r="BO33" t="inlineStr"/>
+      <c r="BP33" t="inlineStr"/>
+      <c r="BQ33" t="inlineStr"/>
+      <c r="BR33" t="inlineStr"/>
+      <c r="BS33" t="inlineStr"/>
+      <c r="BT33" t="inlineStr"/>
+      <c r="BU33" t="inlineStr"/>
+      <c r="BV33" t="inlineStr"/>
+      <c r="BW33" t="inlineStr"/>
+      <c r="BX33" t="inlineStr"/>
+      <c r="BY33" t="inlineStr"/>
+      <c r="BZ33" t="inlineStr"/>
+      <c r="CA33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>47dbb1641a0a4833</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-07-19T10:49:38.448695+00:00</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2026-07-17T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Tamp-Bost-2026-07-17</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Boston Red Sox</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Boston Red Sox</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>0.550333</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>0.909091</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr"/>
+      <c r="X34" t="inlineStr"/>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr"/>
+      <c r="AB34" t="inlineStr"/>
+      <c r="AC34" t="inlineStr"/>
+      <c r="AD34" t="inlineStr"/>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>backtest</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="inlineStr"/>
+      <c r="AH34" t="inlineStr"/>
+      <c r="AI34" t="inlineStr"/>
+      <c r="AJ34" t="inlineStr"/>
+      <c r="AK34" t="inlineStr"/>
+      <c r="AL34" t="inlineStr"/>
+      <c r="AM34" t="inlineStr"/>
+      <c r="AN34" t="inlineStr"/>
+      <c r="AO34" t="inlineStr"/>
+      <c r="AP34" t="inlineStr"/>
+      <c r="AQ34" t="inlineStr"/>
+      <c r="AR34" t="inlineStr"/>
+      <c r="AS34" t="inlineStr"/>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AU34" t="inlineStr"/>
+      <c r="AV34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr"/>
+      <c r="AX34" t="inlineStr"/>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr"/>
+      <c r="BA34" t="inlineStr"/>
+      <c r="BB34" t="inlineStr"/>
+      <c r="BC34" t="inlineStr"/>
+      <c r="BD34" t="inlineStr"/>
+      <c r="BE34" t="inlineStr"/>
+      <c r="BF34" t="inlineStr"/>
+      <c r="BG34" t="inlineStr"/>
+      <c r="BH34" t="inlineStr"/>
+      <c r="BI34" t="inlineStr"/>
+      <c r="BJ34" t="inlineStr"/>
+      <c r="BK34" t="inlineStr"/>
+      <c r="BL34" t="inlineStr"/>
+      <c r="BM34" t="inlineStr"/>
+      <c r="BN34" t="inlineStr"/>
+      <c r="BO34" t="inlineStr"/>
+      <c r="BP34" t="inlineStr"/>
+      <c r="BQ34" t="inlineStr"/>
+      <c r="BR34" t="inlineStr"/>
+      <c r="BS34" t="inlineStr"/>
+      <c r="BT34" t="inlineStr"/>
+      <c r="BU34" t="inlineStr"/>
+      <c r="BV34" t="inlineStr"/>
+      <c r="BW34" t="inlineStr"/>
+      <c r="BX34" t="inlineStr"/>
+      <c r="BY34" t="inlineStr"/>
+      <c r="BZ34" t="inlineStr"/>
+      <c r="CA34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>ba6d8918b5e04b6c</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-07-19T10:49:38.448695+00:00</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2026-07-17T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Texa-Atla-2026-07-17</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Texas Rangers</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Atlanta Braves</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Atlanta Braves</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>0.577396</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>0.909091</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr"/>
+      <c r="X35" t="inlineStr"/>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
+      <c r="AA35" t="inlineStr"/>
+      <c r="AB35" t="inlineStr"/>
+      <c r="AC35" t="inlineStr"/>
+      <c r="AD35" t="inlineStr"/>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>backtest</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="inlineStr"/>
+      <c r="AH35" t="inlineStr"/>
+      <c r="AI35" t="inlineStr"/>
+      <c r="AJ35" t="inlineStr"/>
+      <c r="AK35" t="inlineStr"/>
+      <c r="AL35" t="inlineStr"/>
+      <c r="AM35" t="inlineStr"/>
+      <c r="AN35" t="inlineStr"/>
+      <c r="AO35" t="inlineStr"/>
+      <c r="AP35" t="inlineStr"/>
+      <c r="AQ35" t="inlineStr"/>
+      <c r="AR35" t="inlineStr"/>
+      <c r="AS35" t="inlineStr"/>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AU35" t="inlineStr"/>
+      <c r="AV35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr"/>
+      <c r="AX35" t="inlineStr"/>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr"/>
+      <c r="BA35" t="inlineStr"/>
+      <c r="BB35" t="inlineStr"/>
+      <c r="BC35" t="inlineStr"/>
+      <c r="BD35" t="inlineStr"/>
+      <c r="BE35" t="inlineStr"/>
+      <c r="BF35" t="inlineStr"/>
+      <c r="BG35" t="inlineStr"/>
+      <c r="BH35" t="inlineStr"/>
+      <c r="BI35" t="inlineStr"/>
+      <c r="BJ35" t="inlineStr"/>
+      <c r="BK35" t="inlineStr"/>
+      <c r="BL35" t="inlineStr"/>
+      <c r="BM35" t="inlineStr"/>
+      <c r="BN35" t="inlineStr"/>
+      <c r="BO35" t="inlineStr"/>
+      <c r="BP35" t="inlineStr"/>
+      <c r="BQ35" t="inlineStr"/>
+      <c r="BR35" t="inlineStr"/>
+      <c r="BS35" t="inlineStr"/>
+      <c r="BT35" t="inlineStr"/>
+      <c r="BU35" t="inlineStr"/>
+      <c r="BV35" t="inlineStr"/>
+      <c r="BW35" t="inlineStr"/>
+      <c r="BX35" t="inlineStr"/>
+      <c r="BY35" t="inlineStr"/>
+      <c r="BZ35" t="inlineStr"/>
+      <c r="CA35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>713f57aaeede4418</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-07-19T10:49:38.448695+00:00</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2026-07-17T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Chic-Toro-2026-07-17</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Chicago White Sox</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Toronto Blue Jays</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Toronto Blue Jays</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>0.551581</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr"/>
+      <c r="X36" t="inlineStr"/>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
+      <c r="AA36" t="inlineStr"/>
+      <c r="AB36" t="inlineStr"/>
+      <c r="AC36" t="inlineStr"/>
+      <c r="AD36" t="inlineStr"/>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>backtest</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="inlineStr"/>
+      <c r="AH36" t="inlineStr"/>
+      <c r="AI36" t="inlineStr"/>
+      <c r="AJ36" t="inlineStr"/>
+      <c r="AK36" t="inlineStr"/>
+      <c r="AL36" t="inlineStr"/>
+      <c r="AM36" t="inlineStr"/>
+      <c r="AN36" t="inlineStr"/>
+      <c r="AO36" t="inlineStr"/>
+      <c r="AP36" t="inlineStr"/>
+      <c r="AQ36" t="inlineStr"/>
+      <c r="AR36" t="inlineStr"/>
+      <c r="AS36" t="inlineStr"/>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AU36" t="inlineStr"/>
+      <c r="AV36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr"/>
+      <c r="AX36" t="inlineStr"/>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr"/>
+      <c r="BA36" t="inlineStr"/>
+      <c r="BB36" t="inlineStr"/>
+      <c r="BC36" t="inlineStr"/>
+      <c r="BD36" t="inlineStr"/>
+      <c r="BE36" t="inlineStr"/>
+      <c r="BF36" t="inlineStr"/>
+      <c r="BG36" t="inlineStr"/>
+      <c r="BH36" t="inlineStr"/>
+      <c r="BI36" t="inlineStr"/>
+      <c r="BJ36" t="inlineStr"/>
+      <c r="BK36" t="inlineStr"/>
+      <c r="BL36" t="inlineStr"/>
+      <c r="BM36" t="inlineStr"/>
+      <c r="BN36" t="inlineStr"/>
+      <c r="BO36" t="inlineStr"/>
+      <c r="BP36" t="inlineStr"/>
+      <c r="BQ36" t="inlineStr"/>
+      <c r="BR36" t="inlineStr"/>
+      <c r="BS36" t="inlineStr"/>
+      <c r="BT36" t="inlineStr"/>
+      <c r="BU36" t="inlineStr"/>
+      <c r="BV36" t="inlineStr"/>
+      <c r="BW36" t="inlineStr"/>
+      <c r="BX36" t="inlineStr"/>
+      <c r="BY36" t="inlineStr"/>
+      <c r="BZ36" t="inlineStr"/>
+      <c r="CA36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>baee116aa2834b53</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-07-19T10:49:38.448695+00:00</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2026-07-17T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Miam-Milw-2026-07-17</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Miami Marlins</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Milwaukee Brewers</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Milwaukee Brewers</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>0.616198</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>0.909091</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr"/>
+      <c r="X37" t="inlineStr"/>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr"/>
+      <c r="AA37" t="inlineStr"/>
+      <c r="AB37" t="inlineStr"/>
+      <c r="AC37" t="inlineStr"/>
+      <c r="AD37" t="inlineStr"/>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>backtest</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="inlineStr"/>
+      <c r="AH37" t="inlineStr"/>
+      <c r="AI37" t="inlineStr"/>
+      <c r="AJ37" t="inlineStr"/>
+      <c r="AK37" t="inlineStr"/>
+      <c r="AL37" t="inlineStr"/>
+      <c r="AM37" t="inlineStr"/>
+      <c r="AN37" t="inlineStr"/>
+      <c r="AO37" t="inlineStr"/>
+      <c r="AP37" t="inlineStr"/>
+      <c r="AQ37" t="inlineStr"/>
+      <c r="AR37" t="inlineStr"/>
+      <c r="AS37" t="inlineStr"/>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AU37" t="inlineStr"/>
+      <c r="AV37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr"/>
+      <c r="AX37" t="inlineStr"/>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr"/>
+      <c r="BA37" t="inlineStr"/>
+      <c r="BB37" t="inlineStr"/>
+      <c r="BC37" t="inlineStr"/>
+      <c r="BD37" t="inlineStr"/>
+      <c r="BE37" t="inlineStr"/>
+      <c r="BF37" t="inlineStr"/>
+      <c r="BG37" t="inlineStr"/>
+      <c r="BH37" t="inlineStr"/>
+      <c r="BI37" t="inlineStr"/>
+      <c r="BJ37" t="inlineStr"/>
+      <c r="BK37" t="inlineStr"/>
+      <c r="BL37" t="inlineStr"/>
+      <c r="BM37" t="inlineStr"/>
+      <c r="BN37" t="inlineStr"/>
+      <c r="BO37" t="inlineStr"/>
+      <c r="BP37" t="inlineStr"/>
+      <c r="BQ37" t="inlineStr"/>
+      <c r="BR37" t="inlineStr"/>
+      <c r="BS37" t="inlineStr"/>
+      <c r="BT37" t="inlineStr"/>
+      <c r="BU37" t="inlineStr"/>
+      <c r="BV37" t="inlineStr"/>
+      <c r="BW37" t="inlineStr"/>
+      <c r="BX37" t="inlineStr"/>
+      <c r="BY37" t="inlineStr"/>
+      <c r="BZ37" t="inlineStr"/>
+      <c r="CA37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>509252032f1947b8</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-07-19T10:49:38.448695+00:00</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2026-07-17T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Minn-Chic-2026-07-17</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Minnesota Twins</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Chicago Cubs</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Chicago Cubs</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>0.60271</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr"/>
+      <c r="X38" t="inlineStr"/>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr"/>
+      <c r="AA38" t="inlineStr"/>
+      <c r="AB38" t="inlineStr"/>
+      <c r="AC38" t="inlineStr"/>
+      <c r="AD38" t="inlineStr"/>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>backtest</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="inlineStr"/>
+      <c r="AH38" t="inlineStr"/>
+      <c r="AI38" t="inlineStr"/>
+      <c r="AJ38" t="inlineStr"/>
+      <c r="AK38" t="inlineStr"/>
+      <c r="AL38" t="inlineStr"/>
+      <c r="AM38" t="inlineStr"/>
+      <c r="AN38" t="inlineStr"/>
+      <c r="AO38" t="inlineStr"/>
+      <c r="AP38" t="inlineStr"/>
+      <c r="AQ38" t="inlineStr"/>
+      <c r="AR38" t="inlineStr"/>
+      <c r="AS38" t="inlineStr"/>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AU38" t="inlineStr"/>
+      <c r="AV38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr"/>
+      <c r="AX38" t="inlineStr"/>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr"/>
+      <c r="BA38" t="inlineStr"/>
+      <c r="BB38" t="inlineStr"/>
+      <c r="BC38" t="inlineStr"/>
+      <c r="BD38" t="inlineStr"/>
+      <c r="BE38" t="inlineStr"/>
+      <c r="BF38" t="inlineStr"/>
+      <c r="BG38" t="inlineStr"/>
+      <c r="BH38" t="inlineStr"/>
+      <c r="BI38" t="inlineStr"/>
+      <c r="BJ38" t="inlineStr"/>
+      <c r="BK38" t="inlineStr"/>
+      <c r="BL38" t="inlineStr"/>
+      <c r="BM38" t="inlineStr"/>
+      <c r="BN38" t="inlineStr"/>
+      <c r="BO38" t="inlineStr"/>
+      <c r="BP38" t="inlineStr"/>
+      <c r="BQ38" t="inlineStr"/>
+      <c r="BR38" t="inlineStr"/>
+      <c r="BS38" t="inlineStr"/>
+      <c r="BT38" t="inlineStr"/>
+      <c r="BU38" t="inlineStr"/>
+      <c r="BV38" t="inlineStr"/>
+      <c r="BW38" t="inlineStr"/>
+      <c r="BX38" t="inlineStr"/>
+      <c r="BY38" t="inlineStr"/>
+      <c r="BZ38" t="inlineStr"/>
+      <c r="CA38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>4224d3689d5b44ed</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-07-19T10:49:38.448695+00:00</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2026-07-17T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>SanD-Kans-2026-07-17</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>San Diego Padres</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Kansas City Royals</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>San Diego Padres</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>0.521172</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr"/>
+      <c r="X39" t="inlineStr"/>
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr"/>
+      <c r="AA39" t="inlineStr"/>
+      <c r="AB39" t="inlineStr"/>
+      <c r="AC39" t="inlineStr"/>
+      <c r="AD39" t="inlineStr"/>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>backtest</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="inlineStr"/>
+      <c r="AH39" t="inlineStr"/>
+      <c r="AI39" t="inlineStr"/>
+      <c r="AJ39" t="inlineStr"/>
+      <c r="AK39" t="inlineStr"/>
+      <c r="AL39" t="inlineStr"/>
+      <c r="AM39" t="inlineStr"/>
+      <c r="AN39" t="inlineStr"/>
+      <c r="AO39" t="inlineStr"/>
+      <c r="AP39" t="inlineStr"/>
+      <c r="AQ39" t="inlineStr"/>
+      <c r="AR39" t="inlineStr"/>
+      <c r="AS39" t="inlineStr"/>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AU39" t="inlineStr"/>
+      <c r="AV39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr"/>
+      <c r="AX39" t="inlineStr"/>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr"/>
+      <c r="BA39" t="inlineStr"/>
+      <c r="BB39" t="inlineStr"/>
+      <c r="BC39" t="inlineStr"/>
+      <c r="BD39" t="inlineStr"/>
+      <c r="BE39" t="inlineStr"/>
+      <c r="BF39" t="inlineStr"/>
+      <c r="BG39" t="inlineStr"/>
+      <c r="BH39" t="inlineStr"/>
+      <c r="BI39" t="inlineStr"/>
+      <c r="BJ39" t="inlineStr"/>
+      <c r="BK39" t="inlineStr"/>
+      <c r="BL39" t="inlineStr"/>
+      <c r="BM39" t="inlineStr"/>
+      <c r="BN39" t="inlineStr"/>
+      <c r="BO39" t="inlineStr"/>
+      <c r="BP39" t="inlineStr"/>
+      <c r="BQ39" t="inlineStr"/>
+      <c r="BR39" t="inlineStr"/>
+      <c r="BS39" t="inlineStr"/>
+      <c r="BT39" t="inlineStr"/>
+      <c r="BU39" t="inlineStr"/>
+      <c r="BV39" t="inlineStr"/>
+      <c r="BW39" t="inlineStr"/>
+      <c r="BX39" t="inlineStr"/>
+      <c r="BY39" t="inlineStr"/>
+      <c r="BZ39" t="inlineStr"/>
+      <c r="CA39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>caa582b839304286</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-07-19T10:49:38.448695+00:00</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2026-07-17T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Balt-Hous-2026-07-17</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Baltimore Orioles</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Houston Astros</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Houston Astros</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>0.524624</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr"/>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr"/>
+      <c r="X40" t="inlineStr"/>
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="inlineStr"/>
+      <c r="AA40" t="inlineStr"/>
+      <c r="AB40" t="inlineStr"/>
+      <c r="AC40" t="inlineStr"/>
+      <c r="AD40" t="inlineStr"/>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>backtest</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="inlineStr"/>
+      <c r="AH40" t="inlineStr"/>
+      <c r="AI40" t="inlineStr"/>
+      <c r="AJ40" t="inlineStr"/>
+      <c r="AK40" t="inlineStr"/>
+      <c r="AL40" t="inlineStr"/>
+      <c r="AM40" t="inlineStr"/>
+      <c r="AN40" t="inlineStr"/>
+      <c r="AO40" t="inlineStr"/>
+      <c r="AP40" t="inlineStr"/>
+      <c r="AQ40" t="inlineStr"/>
+      <c r="AR40" t="inlineStr"/>
+      <c r="AS40" t="inlineStr"/>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AU40" t="inlineStr"/>
+      <c r="AV40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr"/>
+      <c r="AX40" t="inlineStr"/>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr"/>
+      <c r="BA40" t="inlineStr"/>
+      <c r="BB40" t="inlineStr"/>
+      <c r="BC40" t="inlineStr"/>
+      <c r="BD40" t="inlineStr"/>
+      <c r="BE40" t="inlineStr"/>
+      <c r="BF40" t="inlineStr"/>
+      <c r="BG40" t="inlineStr"/>
+      <c r="BH40" t="inlineStr"/>
+      <c r="BI40" t="inlineStr"/>
+      <c r="BJ40" t="inlineStr"/>
+      <c r="BK40" t="inlineStr"/>
+      <c r="BL40" t="inlineStr"/>
+      <c r="BM40" t="inlineStr"/>
+      <c r="BN40" t="inlineStr"/>
+      <c r="BO40" t="inlineStr"/>
+      <c r="BP40" t="inlineStr"/>
+      <c r="BQ40" t="inlineStr"/>
+      <c r="BR40" t="inlineStr"/>
+      <c r="BS40" t="inlineStr"/>
+      <c r="BT40" t="inlineStr"/>
+      <c r="BU40" t="inlineStr"/>
+      <c r="BV40" t="inlineStr"/>
+      <c r="BW40" t="inlineStr"/>
+      <c r="BX40" t="inlineStr"/>
+      <c r="BY40" t="inlineStr"/>
+      <c r="BZ40" t="inlineStr"/>
+      <c r="CA40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>19647b771ec94081</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-07-19T10:49:38.448695+00:00</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2026-07-17T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Cinc-Colo-2026-07-17</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Cincinnati Reds</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Colorado Rockies</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Cincinnati Reds</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>0.582862</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>0.909091</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr"/>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr"/>
+      <c r="X41" t="inlineStr"/>
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="inlineStr"/>
+      <c r="AA41" t="inlineStr"/>
+      <c r="AB41" t="inlineStr"/>
+      <c r="AC41" t="inlineStr"/>
+      <c r="AD41" t="inlineStr"/>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>backtest</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="inlineStr"/>
+      <c r="AH41" t="inlineStr"/>
+      <c r="AI41" t="inlineStr"/>
+      <c r="AJ41" t="inlineStr"/>
+      <c r="AK41" t="inlineStr"/>
+      <c r="AL41" t="inlineStr"/>
+      <c r="AM41" t="inlineStr"/>
+      <c r="AN41" t="inlineStr"/>
+      <c r="AO41" t="inlineStr"/>
+      <c r="AP41" t="inlineStr"/>
+      <c r="AQ41" t="inlineStr"/>
+      <c r="AR41" t="inlineStr"/>
+      <c r="AS41" t="inlineStr"/>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AU41" t="inlineStr"/>
+      <c r="AV41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr"/>
+      <c r="AX41" t="inlineStr"/>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr"/>
+      <c r="BA41" t="inlineStr"/>
+      <c r="BB41" t="inlineStr"/>
+      <c r="BC41" t="inlineStr"/>
+      <c r="BD41" t="inlineStr"/>
+      <c r="BE41" t="inlineStr"/>
+      <c r="BF41" t="inlineStr"/>
+      <c r="BG41" t="inlineStr"/>
+      <c r="BH41" t="inlineStr"/>
+      <c r="BI41" t="inlineStr"/>
+      <c r="BJ41" t="inlineStr"/>
+      <c r="BK41" t="inlineStr"/>
+      <c r="BL41" t="inlineStr"/>
+      <c r="BM41" t="inlineStr"/>
+      <c r="BN41" t="inlineStr"/>
+      <c r="BO41" t="inlineStr"/>
+      <c r="BP41" t="inlineStr"/>
+      <c r="BQ41" t="inlineStr"/>
+      <c r="BR41" t="inlineStr"/>
+      <c r="BS41" t="inlineStr"/>
+      <c r="BT41" t="inlineStr"/>
+      <c r="BU41" t="inlineStr"/>
+      <c r="BV41" t="inlineStr"/>
+      <c r="BW41" t="inlineStr"/>
+      <c r="BX41" t="inlineStr"/>
+      <c r="BY41" t="inlineStr"/>
+      <c r="BZ41" t="inlineStr"/>
+      <c r="CA41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>632575e6d24b409b</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-07-19T10:49:38.448695+00:00</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2026-07-17T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Detr-LosA-2026-07-17</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Detroit Tigers</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Los Angeles Angels</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Detroit Tigers</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>0.550233</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>0.909091</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr"/>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr"/>
+      <c r="X42" t="inlineStr"/>
+      <c r="Y42" t="inlineStr"/>
+      <c r="Z42" t="inlineStr"/>
+      <c r="AA42" t="inlineStr"/>
+      <c r="AB42" t="inlineStr"/>
+      <c r="AC42" t="inlineStr"/>
+      <c r="AD42" t="inlineStr"/>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>backtest</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="inlineStr"/>
+      <c r="AH42" t="inlineStr"/>
+      <c r="AI42" t="inlineStr"/>
+      <c r="AJ42" t="inlineStr"/>
+      <c r="AK42" t="inlineStr"/>
+      <c r="AL42" t="inlineStr"/>
+      <c r="AM42" t="inlineStr"/>
+      <c r="AN42" t="inlineStr"/>
+      <c r="AO42" t="inlineStr"/>
+      <c r="AP42" t="inlineStr"/>
+      <c r="AQ42" t="inlineStr"/>
+      <c r="AR42" t="inlineStr"/>
+      <c r="AS42" t="inlineStr"/>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AU42" t="inlineStr"/>
+      <c r="AV42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr"/>
+      <c r="AX42" t="inlineStr"/>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr"/>
+      <c r="BA42" t="inlineStr"/>
+      <c r="BB42" t="inlineStr"/>
+      <c r="BC42" t="inlineStr"/>
+      <c r="BD42" t="inlineStr"/>
+      <c r="BE42" t="inlineStr"/>
+      <c r="BF42" t="inlineStr"/>
+      <c r="BG42" t="inlineStr"/>
+      <c r="BH42" t="inlineStr"/>
+      <c r="BI42" t="inlineStr"/>
+      <c r="BJ42" t="inlineStr"/>
+      <c r="BK42" t="inlineStr"/>
+      <c r="BL42" t="inlineStr"/>
+      <c r="BM42" t="inlineStr"/>
+      <c r="BN42" t="inlineStr"/>
+      <c r="BO42" t="inlineStr"/>
+      <c r="BP42" t="inlineStr"/>
+      <c r="BQ42" t="inlineStr"/>
+      <c r="BR42" t="inlineStr"/>
+      <c r="BS42" t="inlineStr"/>
+      <c r="BT42" t="inlineStr"/>
+      <c r="BU42" t="inlineStr"/>
+      <c r="BV42" t="inlineStr"/>
+      <c r="BW42" t="inlineStr"/>
+      <c r="BX42" t="inlineStr"/>
+      <c r="BY42" t="inlineStr"/>
+      <c r="BZ42" t="inlineStr"/>
+      <c r="CA42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>673ea47c54654f7f</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-07-19T10:49:38.448695+00:00</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2026-07-17T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Wash-Athl-2026-07-17</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Washington Nationals</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Athletics</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Athletics</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>0.530299</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr"/>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr"/>
+      <c r="X43" t="inlineStr"/>
+      <c r="Y43" t="inlineStr"/>
+      <c r="Z43" t="inlineStr"/>
+      <c r="AA43" t="inlineStr"/>
+      <c r="AB43" t="inlineStr"/>
+      <c r="AC43" t="inlineStr"/>
+      <c r="AD43" t="inlineStr"/>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>backtest</t>
+        </is>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="inlineStr"/>
+      <c r="AH43" t="inlineStr"/>
+      <c r="AI43" t="inlineStr"/>
+      <c r="AJ43" t="inlineStr"/>
+      <c r="AK43" t="inlineStr"/>
+      <c r="AL43" t="inlineStr"/>
+      <c r="AM43" t="inlineStr"/>
+      <c r="AN43" t="inlineStr"/>
+      <c r="AO43" t="inlineStr"/>
+      <c r="AP43" t="inlineStr"/>
+      <c r="AQ43" t="inlineStr"/>
+      <c r="AR43" t="inlineStr"/>
+      <c r="AS43" t="inlineStr"/>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AU43" t="inlineStr"/>
+      <c r="AV43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr"/>
+      <c r="AX43" t="inlineStr"/>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr"/>
+      <c r="BA43" t="inlineStr"/>
+      <c r="BB43" t="inlineStr"/>
+      <c r="BC43" t="inlineStr"/>
+      <c r="BD43" t="inlineStr"/>
+      <c r="BE43" t="inlineStr"/>
+      <c r="BF43" t="inlineStr"/>
+      <c r="BG43" t="inlineStr"/>
+      <c r="BH43" t="inlineStr"/>
+      <c r="BI43" t="inlineStr"/>
+      <c r="BJ43" t="inlineStr"/>
+      <c r="BK43" t="inlineStr"/>
+      <c r="BL43" t="inlineStr"/>
+      <c r="BM43" t="inlineStr"/>
+      <c r="BN43" t="inlineStr"/>
+      <c r="BO43" t="inlineStr"/>
+      <c r="BP43" t="inlineStr"/>
+      <c r="BQ43" t="inlineStr"/>
+      <c r="BR43" t="inlineStr"/>
+      <c r="BS43" t="inlineStr"/>
+      <c r="BT43" t="inlineStr"/>
+      <c r="BU43" t="inlineStr"/>
+      <c r="BV43" t="inlineStr"/>
+      <c r="BW43" t="inlineStr"/>
+      <c r="BX43" t="inlineStr"/>
+      <c r="BY43" t="inlineStr"/>
+      <c r="BZ43" t="inlineStr"/>
+      <c r="CA43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>f7bfb70dfae84f8f</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-07-19T10:49:38.448695+00:00</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2026-07-17T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>St.L-Ariz-2026-07-17</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>St. Louis Cardinals</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Arizona Diamondbacks</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Arizona Diamondbacks</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>0.525388</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr"/>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr"/>
+      <c r="X44" t="inlineStr"/>
+      <c r="Y44" t="inlineStr"/>
+      <c r="Z44" t="inlineStr"/>
+      <c r="AA44" t="inlineStr"/>
+      <c r="AB44" t="inlineStr"/>
+      <c r="AC44" t="inlineStr"/>
+      <c r="AD44" t="inlineStr"/>
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t>backtest</t>
+        </is>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="inlineStr"/>
+      <c r="AH44" t="inlineStr"/>
+      <c r="AI44" t="inlineStr"/>
+      <c r="AJ44" t="inlineStr"/>
+      <c r="AK44" t="inlineStr"/>
+      <c r="AL44" t="inlineStr"/>
+      <c r="AM44" t="inlineStr"/>
+      <c r="AN44" t="inlineStr"/>
+      <c r="AO44" t="inlineStr"/>
+      <c r="AP44" t="inlineStr"/>
+      <c r="AQ44" t="inlineStr"/>
+      <c r="AR44" t="inlineStr"/>
+      <c r="AS44" t="inlineStr"/>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AU44" t="inlineStr"/>
+      <c r="AV44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr"/>
+      <c r="AX44" t="inlineStr"/>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr"/>
+      <c r="BA44" t="inlineStr"/>
+      <c r="BB44" t="inlineStr"/>
+      <c r="BC44" t="inlineStr"/>
+      <c r="BD44" t="inlineStr"/>
+      <c r="BE44" t="inlineStr"/>
+      <c r="BF44" t="inlineStr"/>
+      <c r="BG44" t="inlineStr"/>
+      <c r="BH44" t="inlineStr"/>
+      <c r="BI44" t="inlineStr"/>
+      <c r="BJ44" t="inlineStr"/>
+      <c r="BK44" t="inlineStr"/>
+      <c r="BL44" t="inlineStr"/>
+      <c r="BM44" t="inlineStr"/>
+      <c r="BN44" t="inlineStr"/>
+      <c r="BO44" t="inlineStr"/>
+      <c r="BP44" t="inlineStr"/>
+      <c r="BQ44" t="inlineStr"/>
+      <c r="BR44" t="inlineStr"/>
+      <c r="BS44" t="inlineStr"/>
+      <c r="BT44" t="inlineStr"/>
+      <c r="BU44" t="inlineStr"/>
+      <c r="BV44" t="inlineStr"/>
+      <c r="BW44" t="inlineStr"/>
+      <c r="BX44" t="inlineStr"/>
+      <c r="BY44" t="inlineStr"/>
+      <c r="BZ44" t="inlineStr"/>
+      <c r="CA44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>cebdc679239c4a7e</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-07-19T10:49:38.448695+00:00</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2026-07-17T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>SanF-Seat-2026-07-17</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>San Francisco Giants</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Seattle Mariners</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Seattle Mariners</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>0.597575</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr"/>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr"/>
+      <c r="X45" t="inlineStr"/>
+      <c r="Y45" t="inlineStr"/>
+      <c r="Z45" t="inlineStr"/>
+      <c r="AA45" t="inlineStr"/>
+      <c r="AB45" t="inlineStr"/>
+      <c r="AC45" t="inlineStr"/>
+      <c r="AD45" t="inlineStr"/>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>backtest</t>
+        </is>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="inlineStr"/>
+      <c r="AH45" t="inlineStr"/>
+      <c r="AI45" t="inlineStr"/>
+      <c r="AJ45" t="inlineStr"/>
+      <c r="AK45" t="inlineStr"/>
+      <c r="AL45" t="inlineStr"/>
+      <c r="AM45" t="inlineStr"/>
+      <c r="AN45" t="inlineStr"/>
+      <c r="AO45" t="inlineStr"/>
+      <c r="AP45" t="inlineStr"/>
+      <c r="AQ45" t="inlineStr"/>
+      <c r="AR45" t="inlineStr"/>
+      <c r="AS45" t="inlineStr"/>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AU45" t="inlineStr"/>
+      <c r="AV45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr"/>
+      <c r="AX45" t="inlineStr"/>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr"/>
+      <c r="BA45" t="inlineStr"/>
+      <c r="BB45" t="inlineStr"/>
+      <c r="BC45" t="inlineStr"/>
+      <c r="BD45" t="inlineStr"/>
+      <c r="BE45" t="inlineStr"/>
+      <c r="BF45" t="inlineStr"/>
+      <c r="BG45" t="inlineStr"/>
+      <c r="BH45" t="inlineStr"/>
+      <c r="BI45" t="inlineStr"/>
+      <c r="BJ45" t="inlineStr"/>
+      <c r="BK45" t="inlineStr"/>
+      <c r="BL45" t="inlineStr"/>
+      <c r="BM45" t="inlineStr"/>
+      <c r="BN45" t="inlineStr"/>
+      <c r="BO45" t="inlineStr"/>
+      <c r="BP45" t="inlineStr"/>
+      <c r="BQ45" t="inlineStr"/>
+      <c r="BR45" t="inlineStr"/>
+      <c r="BS45" t="inlineStr"/>
+      <c r="BT45" t="inlineStr"/>
+      <c r="BU45" t="inlineStr"/>
+      <c r="BV45" t="inlineStr"/>
+      <c r="BW45" t="inlineStr"/>
+      <c r="BX45" t="inlineStr"/>
+      <c r="BY45" t="inlineStr"/>
+      <c r="BZ45" t="inlineStr"/>
+      <c r="CA45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>deb68aa7d25042de</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-07-19T10:49:38.448695+00:00</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2026-07-17T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Atla-Toro-2026-07-17</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>WNBA</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Atlanta Dream</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Toronto Tempo</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Atlanta Dream</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>0.534506</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>0.909091</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr"/>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr"/>
+      <c r="X46" t="inlineStr"/>
+      <c r="Y46" t="inlineStr"/>
+      <c r="Z46" t="inlineStr"/>
+      <c r="AA46" t="inlineStr"/>
+      <c r="AB46" t="inlineStr"/>
+      <c r="AC46" t="inlineStr"/>
+      <c r="AD46" t="inlineStr"/>
+      <c r="AE46" t="inlineStr">
+        <is>
+          <t>backtest</t>
+        </is>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="inlineStr"/>
+      <c r="AH46" t="inlineStr"/>
+      <c r="AI46" t="inlineStr"/>
+      <c r="AJ46" t="inlineStr"/>
+      <c r="AK46" t="inlineStr"/>
+      <c r="AL46" t="inlineStr"/>
+      <c r="AM46" t="inlineStr"/>
+      <c r="AN46" t="inlineStr"/>
+      <c r="AO46" t="inlineStr"/>
+      <c r="AP46" t="inlineStr"/>
+      <c r="AQ46" t="inlineStr"/>
+      <c r="AR46" t="inlineStr"/>
+      <c r="AS46" t="inlineStr"/>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AU46" t="inlineStr"/>
+      <c r="AV46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr"/>
+      <c r="AX46" t="inlineStr"/>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr"/>
+      <c r="BA46" t="inlineStr"/>
+      <c r="BB46" t="inlineStr"/>
+      <c r="BC46" t="inlineStr"/>
+      <c r="BD46" t="inlineStr"/>
+      <c r="BE46" t="inlineStr"/>
+      <c r="BF46" t="inlineStr"/>
+      <c r="BG46" t="inlineStr"/>
+      <c r="BH46" t="inlineStr"/>
+      <c r="BI46" t="inlineStr"/>
+      <c r="BJ46" t="inlineStr"/>
+      <c r="BK46" t="inlineStr"/>
+      <c r="BL46" t="inlineStr"/>
+      <c r="BM46" t="inlineStr"/>
+      <c r="BN46" t="inlineStr"/>
+      <c r="BO46" t="inlineStr"/>
+      <c r="BP46" t="inlineStr"/>
+      <c r="BQ46" t="inlineStr"/>
+      <c r="BR46" t="inlineStr"/>
+      <c r="BS46" t="inlineStr"/>
+      <c r="BT46" t="inlineStr"/>
+      <c r="BU46" t="inlineStr"/>
+      <c r="BV46" t="inlineStr"/>
+      <c r="BW46" t="inlineStr"/>
+      <c r="BX46" t="inlineStr"/>
+      <c r="BY46" t="inlineStr"/>
+      <c r="BZ46" t="inlineStr"/>
+      <c r="CA46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>9d42b77cda3d44a7</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-07-19T10:49:38.448695+00:00</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2026-07-17T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LosA-Chic-2026-07-17</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>WNBA</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Los Angeles Sparks</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Chicago Sky</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Chicago Sky</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.505358</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr"/>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>0.909091</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr"/>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr"/>
+      <c r="X47" t="inlineStr"/>
+      <c r="Y47" t="inlineStr"/>
+      <c r="Z47" t="inlineStr"/>
+      <c r="AA47" t="inlineStr"/>
+      <c r="AB47" t="inlineStr"/>
+      <c r="AC47" t="inlineStr"/>
+      <c r="AD47" t="inlineStr"/>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>backtest</t>
+        </is>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="inlineStr"/>
+      <c r="AH47" t="inlineStr"/>
+      <c r="AI47" t="inlineStr"/>
+      <c r="AJ47" t="inlineStr"/>
+      <c r="AK47" t="inlineStr"/>
+      <c r="AL47" t="inlineStr"/>
+      <c r="AM47" t="inlineStr"/>
+      <c r="AN47" t="inlineStr"/>
+      <c r="AO47" t="inlineStr"/>
+      <c r="AP47" t="inlineStr"/>
+      <c r="AQ47" t="inlineStr"/>
+      <c r="AR47" t="inlineStr"/>
+      <c r="AS47" t="inlineStr"/>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AU47" t="inlineStr"/>
+      <c r="AV47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr"/>
+      <c r="AX47" t="inlineStr"/>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr"/>
+      <c r="BA47" t="inlineStr"/>
+      <c r="BB47" t="inlineStr"/>
+      <c r="BC47" t="inlineStr"/>
+      <c r="BD47" t="inlineStr"/>
+      <c r="BE47" t="inlineStr"/>
+      <c r="BF47" t="inlineStr"/>
+      <c r="BG47" t="inlineStr"/>
+      <c r="BH47" t="inlineStr"/>
+      <c r="BI47" t="inlineStr"/>
+      <c r="BJ47" t="inlineStr"/>
+      <c r="BK47" t="inlineStr"/>
+      <c r="BL47" t="inlineStr"/>
+      <c r="BM47" t="inlineStr"/>
+      <c r="BN47" t="inlineStr"/>
+      <c r="BO47" t="inlineStr"/>
+      <c r="BP47" t="inlineStr"/>
+      <c r="BQ47" t="inlineStr"/>
+      <c r="BR47" t="inlineStr"/>
+      <c r="BS47" t="inlineStr"/>
+      <c r="BT47" t="inlineStr"/>
+      <c r="BU47" t="inlineStr"/>
+      <c r="BV47" t="inlineStr"/>
+      <c r="BW47" t="inlineStr"/>
+      <c r="BX47" t="inlineStr"/>
+      <c r="BY47" t="inlineStr"/>
+      <c r="BZ47" t="inlineStr"/>
+      <c r="CA47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>33934bb67697420b</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-07-19T10:49:38.448695+00:00</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2026-07-17T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Conn-Phoe-2026-07-17</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>WNBA</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Connecticut Sun</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Phoenix Mercury</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Phoenix Mercury</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.637935</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr"/>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr"/>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr"/>
+      <c r="X48" t="inlineStr"/>
+      <c r="Y48" t="inlineStr"/>
+      <c r="Z48" t="inlineStr"/>
+      <c r="AA48" t="inlineStr"/>
+      <c r="AB48" t="inlineStr"/>
+      <c r="AC48" t="inlineStr"/>
+      <c r="AD48" t="inlineStr"/>
+      <c r="AE48" t="inlineStr">
+        <is>
+          <t>backtest</t>
+        </is>
+      </c>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="inlineStr"/>
+      <c r="AH48" t="inlineStr"/>
+      <c r="AI48" t="inlineStr"/>
+      <c r="AJ48" t="inlineStr"/>
+      <c r="AK48" t="inlineStr"/>
+      <c r="AL48" t="inlineStr"/>
+      <c r="AM48" t="inlineStr"/>
+      <c r="AN48" t="inlineStr"/>
+      <c r="AO48" t="inlineStr"/>
+      <c r="AP48" t="inlineStr"/>
+      <c r="AQ48" t="inlineStr"/>
+      <c r="AR48" t="inlineStr"/>
+      <c r="AS48" t="inlineStr"/>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AU48" t="inlineStr"/>
+      <c r="AV48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr"/>
+      <c r="AX48" t="inlineStr"/>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr"/>
+      <c r="BA48" t="inlineStr"/>
+      <c r="BB48" t="inlineStr"/>
+      <c r="BC48" t="inlineStr"/>
+      <c r="BD48" t="inlineStr"/>
+      <c r="BE48" t="inlineStr"/>
+      <c r="BF48" t="inlineStr"/>
+      <c r="BG48" t="inlineStr"/>
+      <c r="BH48" t="inlineStr"/>
+      <c r="BI48" t="inlineStr"/>
+      <c r="BJ48" t="inlineStr"/>
+      <c r="BK48" t="inlineStr"/>
+      <c r="BL48" t="inlineStr"/>
+      <c r="BM48" t="inlineStr"/>
+      <c r="BN48" t="inlineStr"/>
+      <c r="BO48" t="inlineStr"/>
+      <c r="BP48" t="inlineStr"/>
+      <c r="BQ48" t="inlineStr"/>
+      <c r="BR48" t="inlineStr"/>
+      <c r="BS48" t="inlineStr"/>
+      <c r="BT48" t="inlineStr"/>
+      <c r="BU48" t="inlineStr"/>
+      <c r="BV48" t="inlineStr"/>
+      <c r="BW48" t="inlineStr"/>
+      <c r="BX48" t="inlineStr"/>
+      <c r="BY48" t="inlineStr"/>
+      <c r="BZ48" t="inlineStr"/>
+      <c r="CA48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>9e5a3c9d33b2497b</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-07-19T10:49:38.448695+00:00</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>2026-07-18T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NewY-Phil-2026-07-18</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>New York Mets</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Philadelphia Phillies</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Philadelphia Phillies</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.611768</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr"/>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>0.909091</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr"/>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr"/>
+      <c r="X49" t="inlineStr"/>
+      <c r="Y49" t="inlineStr"/>
+      <c r="Z49" t="inlineStr"/>
+      <c r="AA49" t="inlineStr"/>
+      <c r="AB49" t="inlineStr"/>
+      <c r="AC49" t="inlineStr"/>
+      <c r="AD49" t="inlineStr"/>
+      <c r="AE49" t="inlineStr">
+        <is>
+          <t>backtest</t>
+        </is>
+      </c>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="inlineStr"/>
+      <c r="AH49" t="inlineStr"/>
+      <c r="AI49" t="inlineStr"/>
+      <c r="AJ49" t="inlineStr"/>
+      <c r="AK49" t="inlineStr"/>
+      <c r="AL49" t="inlineStr"/>
+      <c r="AM49" t="inlineStr"/>
+      <c r="AN49" t="inlineStr"/>
+      <c r="AO49" t="inlineStr"/>
+      <c r="AP49" t="inlineStr"/>
+      <c r="AQ49" t="inlineStr"/>
+      <c r="AR49" t="inlineStr"/>
+      <c r="AS49" t="inlineStr"/>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AU49" t="inlineStr"/>
+      <c r="AV49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr"/>
+      <c r="AX49" t="inlineStr"/>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr"/>
+      <c r="BA49" t="inlineStr"/>
+      <c r="BB49" t="inlineStr"/>
+      <c r="BC49" t="inlineStr"/>
+      <c r="BD49" t="inlineStr"/>
+      <c r="BE49" t="inlineStr"/>
+      <c r="BF49" t="inlineStr"/>
+      <c r="BG49" t="inlineStr"/>
+      <c r="BH49" t="inlineStr"/>
+      <c r="BI49" t="inlineStr"/>
+      <c r="BJ49" t="inlineStr"/>
+      <c r="BK49" t="inlineStr"/>
+      <c r="BL49" t="inlineStr"/>
+      <c r="BM49" t="inlineStr"/>
+      <c r="BN49" t="inlineStr"/>
+      <c r="BO49" t="inlineStr"/>
+      <c r="BP49" t="inlineStr"/>
+      <c r="BQ49" t="inlineStr"/>
+      <c r="BR49" t="inlineStr"/>
+      <c r="BS49" t="inlineStr"/>
+      <c r="BT49" t="inlineStr"/>
+      <c r="BU49" t="inlineStr"/>
+      <c r="BV49" t="inlineStr"/>
+      <c r="BW49" t="inlineStr"/>
+      <c r="BX49" t="inlineStr"/>
+      <c r="BY49" t="inlineStr"/>
+      <c r="BZ49" t="inlineStr"/>
+      <c r="CA49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>f8293c8d16d748f5</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-07-19T10:49:38.448695+00:00</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2026-07-18T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>St.L-Ariz-2026-07-18</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>St. Louis Cardinals</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Arizona Diamondbacks</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Arizona Diamondbacks</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.525388</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr"/>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>0.909091</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr"/>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr"/>
+      <c r="X50" t="inlineStr"/>
+      <c r="Y50" t="inlineStr"/>
+      <c r="Z50" t="inlineStr"/>
+      <c r="AA50" t="inlineStr"/>
+      <c r="AB50" t="inlineStr"/>
+      <c r="AC50" t="inlineStr"/>
+      <c r="AD50" t="inlineStr"/>
+      <c r="AE50" t="inlineStr">
+        <is>
+          <t>backtest</t>
+        </is>
+      </c>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="inlineStr"/>
+      <c r="AH50" t="inlineStr"/>
+      <c r="AI50" t="inlineStr"/>
+      <c r="AJ50" t="inlineStr"/>
+      <c r="AK50" t="inlineStr"/>
+      <c r="AL50" t="inlineStr"/>
+      <c r="AM50" t="inlineStr"/>
+      <c r="AN50" t="inlineStr"/>
+      <c r="AO50" t="inlineStr"/>
+      <c r="AP50" t="inlineStr"/>
+      <c r="AQ50" t="inlineStr"/>
+      <c r="AR50" t="inlineStr"/>
+      <c r="AS50" t="inlineStr"/>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AU50" t="inlineStr"/>
+      <c r="AV50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr"/>
+      <c r="AX50" t="inlineStr"/>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr"/>
+      <c r="BA50" t="inlineStr"/>
+      <c r="BB50" t="inlineStr"/>
+      <c r="BC50" t="inlineStr"/>
+      <c r="BD50" t="inlineStr"/>
+      <c r="BE50" t="inlineStr"/>
+      <c r="BF50" t="inlineStr"/>
+      <c r="BG50" t="inlineStr"/>
+      <c r="BH50" t="inlineStr"/>
+      <c r="BI50" t="inlineStr"/>
+      <c r="BJ50" t="inlineStr"/>
+      <c r="BK50" t="inlineStr"/>
+      <c r="BL50" t="inlineStr"/>
+      <c r="BM50" t="inlineStr"/>
+      <c r="BN50" t="inlineStr"/>
+      <c r="BO50" t="inlineStr"/>
+      <c r="BP50" t="inlineStr"/>
+      <c r="BQ50" t="inlineStr"/>
+      <c r="BR50" t="inlineStr"/>
+      <c r="BS50" t="inlineStr"/>
+      <c r="BT50" t="inlineStr"/>
+      <c r="BU50" t="inlineStr"/>
+      <c r="BV50" t="inlineStr"/>
+      <c r="BW50" t="inlineStr"/>
+      <c r="BX50" t="inlineStr"/>
+      <c r="BY50" t="inlineStr"/>
+      <c r="BZ50" t="inlineStr"/>
+      <c r="CA50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>f1019aa0671049ee</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-07-19T10:49:38.448695+00:00</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2026-07-18T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>SanF-Seat-2026-07-18</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>San Francisco Giants</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Seattle Mariners</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Seattle Mariners</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.597575</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr"/>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>0.909091</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr"/>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr"/>
+      <c r="X51" t="inlineStr"/>
+      <c r="Y51" t="inlineStr"/>
+      <c r="Z51" t="inlineStr"/>
+      <c r="AA51" t="inlineStr"/>
+      <c r="AB51" t="inlineStr"/>
+      <c r="AC51" t="inlineStr"/>
+      <c r="AD51" t="inlineStr"/>
+      <c r="AE51" t="inlineStr">
+        <is>
+          <t>backtest</t>
+        </is>
+      </c>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="inlineStr"/>
+      <c r="AH51" t="inlineStr"/>
+      <c r="AI51" t="inlineStr"/>
+      <c r="AJ51" t="inlineStr"/>
+      <c r="AK51" t="inlineStr"/>
+      <c r="AL51" t="inlineStr"/>
+      <c r="AM51" t="inlineStr"/>
+      <c r="AN51" t="inlineStr"/>
+      <c r="AO51" t="inlineStr"/>
+      <c r="AP51" t="inlineStr"/>
+      <c r="AQ51" t="inlineStr"/>
+      <c r="AR51" t="inlineStr"/>
+      <c r="AS51" t="inlineStr"/>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AU51" t="inlineStr"/>
+      <c r="AV51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr"/>
+      <c r="AX51" t="inlineStr"/>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr"/>
+      <c r="BA51" t="inlineStr"/>
+      <c r="BB51" t="inlineStr"/>
+      <c r="BC51" t="inlineStr"/>
+      <c r="BD51" t="inlineStr"/>
+      <c r="BE51" t="inlineStr"/>
+      <c r="BF51" t="inlineStr"/>
+      <c r="BG51" t="inlineStr"/>
+      <c r="BH51" t="inlineStr"/>
+      <c r="BI51" t="inlineStr"/>
+      <c r="BJ51" t="inlineStr"/>
+      <c r="BK51" t="inlineStr"/>
+      <c r="BL51" t="inlineStr"/>
+      <c r="BM51" t="inlineStr"/>
+      <c r="BN51" t="inlineStr"/>
+      <c r="BO51" t="inlineStr"/>
+      <c r="BP51" t="inlineStr"/>
+      <c r="BQ51" t="inlineStr"/>
+      <c r="BR51" t="inlineStr"/>
+      <c r="BS51" t="inlineStr"/>
+      <c r="BT51" t="inlineStr"/>
+      <c r="BU51" t="inlineStr"/>
+      <c r="BV51" t="inlineStr"/>
+      <c r="BW51" t="inlineStr"/>
+      <c r="BX51" t="inlineStr"/>
+      <c r="BY51" t="inlineStr"/>
+      <c r="BZ51" t="inlineStr"/>
+      <c r="CA51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>ef9102ddf70441de</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-07-19T10:49:38.448695+00:00</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2026-07-18T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Wash-Athl-2026-07-18</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Washington Nationals</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Athletics</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Athletics</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.530299</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr"/>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr"/>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr"/>
+      <c r="X52" t="inlineStr"/>
+      <c r="Y52" t="inlineStr"/>
+      <c r="Z52" t="inlineStr"/>
+      <c r="AA52" t="inlineStr"/>
+      <c r="AB52" t="inlineStr"/>
+      <c r="AC52" t="inlineStr"/>
+      <c r="AD52" t="inlineStr"/>
+      <c r="AE52" t="inlineStr">
+        <is>
+          <t>backtest</t>
+        </is>
+      </c>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="inlineStr"/>
+      <c r="AH52" t="inlineStr"/>
+      <c r="AI52" t="inlineStr"/>
+      <c r="AJ52" t="inlineStr"/>
+      <c r="AK52" t="inlineStr"/>
+      <c r="AL52" t="inlineStr"/>
+      <c r="AM52" t="inlineStr"/>
+      <c r="AN52" t="inlineStr"/>
+      <c r="AO52" t="inlineStr"/>
+      <c r="AP52" t="inlineStr"/>
+      <c r="AQ52" t="inlineStr"/>
+      <c r="AR52" t="inlineStr"/>
+      <c r="AS52" t="inlineStr"/>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AU52" t="inlineStr"/>
+      <c r="AV52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr"/>
+      <c r="AX52" t="inlineStr"/>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr"/>
+      <c r="BA52" t="inlineStr"/>
+      <c r="BB52" t="inlineStr"/>
+      <c r="BC52" t="inlineStr"/>
+      <c r="BD52" t="inlineStr"/>
+      <c r="BE52" t="inlineStr"/>
+      <c r="BF52" t="inlineStr"/>
+      <c r="BG52" t="inlineStr"/>
+      <c r="BH52" t="inlineStr"/>
+      <c r="BI52" t="inlineStr"/>
+      <c r="BJ52" t="inlineStr"/>
+      <c r="BK52" t="inlineStr"/>
+      <c r="BL52" t="inlineStr"/>
+      <c r="BM52" t="inlineStr"/>
+      <c r="BN52" t="inlineStr"/>
+      <c r="BO52" t="inlineStr"/>
+      <c r="BP52" t="inlineStr"/>
+      <c r="BQ52" t="inlineStr"/>
+      <c r="BR52" t="inlineStr"/>
+      <c r="BS52" t="inlineStr"/>
+      <c r="BT52" t="inlineStr"/>
+      <c r="BU52" t="inlineStr"/>
+      <c r="BV52" t="inlineStr"/>
+      <c r="BW52" t="inlineStr"/>
+      <c r="BX52" t="inlineStr"/>
+      <c r="BY52" t="inlineStr"/>
+      <c r="BZ52" t="inlineStr"/>
+      <c r="CA52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>7e8754f391d2475e</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-07-19T10:49:38.448695+00:00</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2026-07-18T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Detr-LosA-2026-07-18</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Detroit Tigers</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Los Angeles Angels</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Detroit Tigers</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>0.550233</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr"/>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>0.909091</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr"/>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr"/>
+      <c r="X53" t="inlineStr"/>
+      <c r="Y53" t="inlineStr"/>
+      <c r="Z53" t="inlineStr"/>
+      <c r="AA53" t="inlineStr"/>
+      <c r="AB53" t="inlineStr"/>
+      <c r="AC53" t="inlineStr"/>
+      <c r="AD53" t="inlineStr"/>
+      <c r="AE53" t="inlineStr">
+        <is>
+          <t>backtest</t>
+        </is>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="inlineStr"/>
+      <c r="AH53" t="inlineStr"/>
+      <c r="AI53" t="inlineStr"/>
+      <c r="AJ53" t="inlineStr"/>
+      <c r="AK53" t="inlineStr"/>
+      <c r="AL53" t="inlineStr"/>
+      <c r="AM53" t="inlineStr"/>
+      <c r="AN53" t="inlineStr"/>
+      <c r="AO53" t="inlineStr"/>
+      <c r="AP53" t="inlineStr"/>
+      <c r="AQ53" t="inlineStr"/>
+      <c r="AR53" t="inlineStr"/>
+      <c r="AS53" t="inlineStr"/>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AU53" t="inlineStr"/>
+      <c r="AV53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr"/>
+      <c r="AX53" t="inlineStr"/>
+      <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr"/>
+      <c r="BA53" t="inlineStr"/>
+      <c r="BB53" t="inlineStr"/>
+      <c r="BC53" t="inlineStr"/>
+      <c r="BD53" t="inlineStr"/>
+      <c r="BE53" t="inlineStr"/>
+      <c r="BF53" t="inlineStr"/>
+      <c r="BG53" t="inlineStr"/>
+      <c r="BH53" t="inlineStr"/>
+      <c r="BI53" t="inlineStr"/>
+      <c r="BJ53" t="inlineStr"/>
+      <c r="BK53" t="inlineStr"/>
+      <c r="BL53" t="inlineStr"/>
+      <c r="BM53" t="inlineStr"/>
+      <c r="BN53" t="inlineStr"/>
+      <c r="BO53" t="inlineStr"/>
+      <c r="BP53" t="inlineStr"/>
+      <c r="BQ53" t="inlineStr"/>
+      <c r="BR53" t="inlineStr"/>
+      <c r="BS53" t="inlineStr"/>
+      <c r="BT53" t="inlineStr"/>
+      <c r="BU53" t="inlineStr"/>
+      <c r="BV53" t="inlineStr"/>
+      <c r="BW53" t="inlineStr"/>
+      <c r="BX53" t="inlineStr"/>
+      <c r="BY53" t="inlineStr"/>
+      <c r="BZ53" t="inlineStr"/>
+      <c r="CA53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>5c32fca0897f4465</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-07-19T10:49:38.448695+00:00</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2026-07-18T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Port-Minn-2026-07-18</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>WNBA</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Portland Fire</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Minnesota Lynx</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Minnesota Lynx</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>0.741703</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr"/>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>0.909091</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr"/>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr"/>
+      <c r="X54" t="inlineStr"/>
+      <c r="Y54" t="inlineStr"/>
+      <c r="Z54" t="inlineStr"/>
+      <c r="AA54" t="inlineStr"/>
+      <c r="AB54" t="inlineStr"/>
+      <c r="AC54" t="inlineStr"/>
+      <c r="AD54" t="inlineStr"/>
+      <c r="AE54" t="inlineStr">
+        <is>
+          <t>backtest</t>
+        </is>
+      </c>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="inlineStr"/>
+      <c r="AH54" t="inlineStr"/>
+      <c r="AI54" t="inlineStr"/>
+      <c r="AJ54" t="inlineStr"/>
+      <c r="AK54" t="inlineStr"/>
+      <c r="AL54" t="inlineStr"/>
+      <c r="AM54" t="inlineStr"/>
+      <c r="AN54" t="inlineStr"/>
+      <c r="AO54" t="inlineStr"/>
+      <c r="AP54" t="inlineStr"/>
+      <c r="AQ54" t="inlineStr"/>
+      <c r="AR54" t="inlineStr"/>
+      <c r="AS54" t="inlineStr"/>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AU54" t="inlineStr"/>
+      <c r="AV54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr"/>
+      <c r="AX54" t="inlineStr"/>
+      <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr"/>
+      <c r="BA54" t="inlineStr"/>
+      <c r="BB54" t="inlineStr"/>
+      <c r="BC54" t="inlineStr"/>
+      <c r="BD54" t="inlineStr"/>
+      <c r="BE54" t="inlineStr"/>
+      <c r="BF54" t="inlineStr"/>
+      <c r="BG54" t="inlineStr"/>
+      <c r="BH54" t="inlineStr"/>
+      <c r="BI54" t="inlineStr"/>
+      <c r="BJ54" t="inlineStr"/>
+      <c r="BK54" t="inlineStr"/>
+      <c r="BL54" t="inlineStr"/>
+      <c r="BM54" t="inlineStr"/>
+      <c r="BN54" t="inlineStr"/>
+      <c r="BO54" t="inlineStr"/>
+      <c r="BP54" t="inlineStr"/>
+      <c r="BQ54" t="inlineStr"/>
+      <c r="BR54" t="inlineStr"/>
+      <c r="BS54" t="inlineStr"/>
+      <c r="BT54" t="inlineStr"/>
+      <c r="BU54" t="inlineStr"/>
+      <c r="BV54" t="inlineStr"/>
+      <c r="BW54" t="inlineStr"/>
+      <c r="BX54" t="inlineStr"/>
+      <c r="BY54" t="inlineStr"/>
+      <c r="BZ54" t="inlineStr"/>
+      <c r="CA54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>90b65fc52d124bc1</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-07-19T10:49:38.448695+00:00</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2026-07-18T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NewY-Indi-2026-07-18</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>WNBA</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>New York Liberty</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Indiana Fever</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Indiana Fever</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>0.59624</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr"/>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>0.909091</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr"/>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr"/>
+      <c r="X55" t="inlineStr"/>
+      <c r="Y55" t="inlineStr"/>
+      <c r="Z55" t="inlineStr"/>
+      <c r="AA55" t="inlineStr"/>
+      <c r="AB55" t="inlineStr"/>
+      <c r="AC55" t="inlineStr"/>
+      <c r="AD55" t="inlineStr"/>
+      <c r="AE55" t="inlineStr">
+        <is>
+          <t>backtest</t>
+        </is>
+      </c>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="inlineStr"/>
+      <c r="AH55" t="inlineStr"/>
+      <c r="AI55" t="inlineStr"/>
+      <c r="AJ55" t="inlineStr"/>
+      <c r="AK55" t="inlineStr"/>
+      <c r="AL55" t="inlineStr"/>
+      <c r="AM55" t="inlineStr"/>
+      <c r="AN55" t="inlineStr"/>
+      <c r="AO55" t="inlineStr"/>
+      <c r="AP55" t="inlineStr"/>
+      <c r="AQ55" t="inlineStr"/>
+      <c r="AR55" t="inlineStr"/>
+      <c r="AS55" t="inlineStr"/>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AU55" t="inlineStr"/>
+      <c r="AV55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr"/>
+      <c r="AX55" t="inlineStr"/>
+      <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr"/>
+      <c r="BA55" t="inlineStr"/>
+      <c r="BB55" t="inlineStr"/>
+      <c r="BC55" t="inlineStr"/>
+      <c r="BD55" t="inlineStr"/>
+      <c r="BE55" t="inlineStr"/>
+      <c r="BF55" t="inlineStr"/>
+      <c r="BG55" t="inlineStr"/>
+      <c r="BH55" t="inlineStr"/>
+      <c r="BI55" t="inlineStr"/>
+      <c r="BJ55" t="inlineStr"/>
+      <c r="BK55" t="inlineStr"/>
+      <c r="BL55" t="inlineStr"/>
+      <c r="BM55" t="inlineStr"/>
+      <c r="BN55" t="inlineStr"/>
+      <c r="BO55" t="inlineStr"/>
+      <c r="BP55" t="inlineStr"/>
+      <c r="BQ55" t="inlineStr"/>
+      <c r="BR55" t="inlineStr"/>
+      <c r="BS55" t="inlineStr"/>
+      <c r="BT55" t="inlineStr"/>
+      <c r="BU55" t="inlineStr"/>
+      <c r="BV55" t="inlineStr"/>
+      <c r="BW55" t="inlineStr"/>
+      <c r="BX55" t="inlineStr"/>
+      <c r="BY55" t="inlineStr"/>
+      <c r="BZ55" t="inlineStr"/>
+      <c r="CA55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>413a2bc86aab48de</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-07-19T10:49:38.448695+00:00</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2026-07-18T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Wash-Gold-2026-07-18</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>WNBA</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Washington Mystics</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Golden State Valkyries</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Golden State Valkyries</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>polymarket</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>0.743891</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr"/>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>0.909091</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr"/>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr"/>
+      <c r="X56" t="inlineStr"/>
+      <c r="Y56" t="inlineStr"/>
+      <c r="Z56" t="inlineStr"/>
+      <c r="AA56" t="inlineStr"/>
+      <c r="AB56" t="inlineStr"/>
+      <c r="AC56" t="inlineStr"/>
+      <c r="AD56" t="inlineStr"/>
+      <c r="AE56" t="inlineStr">
+        <is>
+          <t>backtest</t>
+        </is>
+      </c>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="inlineStr"/>
+      <c r="AH56" t="inlineStr"/>
+      <c r="AI56" t="inlineStr"/>
+      <c r="AJ56" t="inlineStr"/>
+      <c r="AK56" t="inlineStr"/>
+      <c r="AL56" t="inlineStr"/>
+      <c r="AM56" t="inlineStr"/>
+      <c r="AN56" t="inlineStr"/>
+      <c r="AO56" t="inlineStr"/>
+      <c r="AP56" t="inlineStr"/>
+      <c r="AQ56" t="inlineStr"/>
+      <c r="AR56" t="inlineStr"/>
+      <c r="AS56" t="inlineStr"/>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AU56" t="inlineStr"/>
+      <c r="AV56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr"/>
+      <c r="AX56" t="inlineStr"/>
+      <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr"/>
+      <c r="BA56" t="inlineStr"/>
+      <c r="BB56" t="inlineStr"/>
+      <c r="BC56" t="inlineStr"/>
+      <c r="BD56" t="inlineStr"/>
+      <c r="BE56" t="inlineStr"/>
+      <c r="BF56" t="inlineStr"/>
+      <c r="BG56" t="inlineStr"/>
+      <c r="BH56" t="inlineStr"/>
+      <c r="BI56" t="inlineStr"/>
+      <c r="BJ56" t="inlineStr"/>
+      <c r="BK56" t="inlineStr"/>
+      <c r="BL56" t="inlineStr"/>
+      <c r="BM56" t="inlineStr"/>
+      <c r="BN56" t="inlineStr"/>
+      <c r="BO56" t="inlineStr"/>
+      <c r="BP56" t="inlineStr"/>
+      <c r="BQ56" t="inlineStr"/>
+      <c r="BR56" t="inlineStr"/>
+      <c r="BS56" t="inlineStr"/>
+      <c r="BT56" t="inlineStr"/>
+      <c r="BU56" t="inlineStr"/>
+      <c r="BV56" t="inlineStr"/>
+      <c r="BW56" t="inlineStr"/>
+      <c r="BX56" t="inlineStr"/>
+      <c r="BY56" t="inlineStr"/>
+      <c r="BZ56" t="inlineStr"/>
+      <c r="CA56" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/picks.xlsx
+++ b/data/picks.xlsx
@@ -21,10 +21,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="0.0%"/>
-    <numFmt numFmtId="165" formatCode="0.0000"/>
-    <numFmt numFmtId="166" formatCode="0.0###"/>
-    <numFmt numFmtId="167" formatCode="0.000000"/>
+    <numFmt numFmtId="164" formatCode="0.0###"/>
+    <numFmt numFmtId="165" formatCode="0.000000"/>
+    <numFmt numFmtId="166" formatCode="0.0000"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -136,7 +136,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -150,10 +150,10 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -169,10 +169,10 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -184,10 +184,10 @@
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -202,13 +202,13 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="10" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -217,38 +217,11 @@
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -327,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CA31" headerRowCount="1">
-  <autoFilter ref="A1:CA31"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CA39" headerRowCount="1">
+  <autoFilter ref="A1:CA39"/>
   <tableColumns count="79">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -765,23 +738,22 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$31)</f>
+        <f>COUNTA('Picks'!$A$2:$A$39)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$31,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$39,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$31,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$39,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$31,"settled",'Picks'!$V$2:$V$31,"win")+COUNTIFS('Picks'!$U$2:$U$31,"settled",'Picks'!$V$2:$V$31,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$39,"settled",'Picks'!$V$2:$V$39,"win")+COUNTIFS('Picks'!$U$2:$U$39,"settled",'Picks'!$V$2:$V$39,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
-    <row r="5"/>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
@@ -806,23 +778,22 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$31,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$39,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$31,"&gt;0",'Picks'!$V$2:$V$31,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$31,"&gt;0",'Picks'!$V$2:$V$31,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$39,"&gt;0",'Picks'!$V$2:$V$39,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$39,"&gt;0",'Picks'!$V$2:$V$39,"loss")</f>
         <v/>
       </c>
-      <c r="E7" s="32">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$31,"&gt;0",'Picks'!$V$2:$V$31,"win")/(COUNTIFS('Picks'!$BX$2:$BX$31,"&gt;0",'Picks'!$V$2:$V$31,"win")+COUNTIFS('Picks'!$BX$2:$BX$31,"&gt;0",'Picks'!$V$2:$V$31,"loss")),0)</f>
+      <c r="E7" s="7">
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$39,"&gt;0",'Picks'!$V$2:$V$39,"win")/(COUNTIFS('Picks'!$BX$2:$BX$39,"&gt;0",'Picks'!$V$2:$V$39,"win")+COUNTIFS('Picks'!$BX$2:$BX$39,"&gt;0",'Picks'!$V$2:$V$39,"loss")),0)</f>
         <v/>
       </c>
-      <c r="G7" s="32">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$31)/SUM('Picks'!$BX$2:$BX$31),0)</f>
+      <c r="G7" s="7">
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$39)/SUM('Picks'!$BX$2:$BX$39),0)</f>
         <v/>
       </c>
     </row>
-    <row r="8"/>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
@@ -846,24 +817,23 @@
       </c>
     </row>
     <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="33">
-        <f>SUM('Picks'!$BY$2:$BY$31)</f>
+      <c r="A10" s="8">
+        <f>SUM('Picks'!$BY$2:$BY$39)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$31,"&lt;&gt;",'Picks'!$AB$2:$AB$31),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$39,"&lt;&gt;",'Picks'!$AB$2:$AB$39),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$31,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$31,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$39,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$39,"settled")</f>
         <v/>
       </c>
-      <c r="G10" s="33">
-        <f>SUMIFS('Picks'!$AC$2:$AC$31,'Picks'!$AM$2:$AM$31,"QUALIFIED_SHADOW_CALL")</f>
+      <c r="G10" s="8">
+        <f>SUMIFS('Picks'!$AC$2:$AC$39,'Picks'!$AM$2:$AM$39,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
@@ -915,27 +885,27 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$31,$A14,'Picks'!$U$2:$U$31,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$39,$A14,'Picks'!$U$2:$U$39,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$31,$A14,'Picks'!$U$2:$U$31,"settled",'Picks'!$V$2:$V$31,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$39,$A14,'Picks'!$U$2:$U$39,"settled",'Picks'!$V$2:$V$39,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$31,$A14,'Picks'!$U$2:$U$31,"settled",'Picks'!$V$2:$V$31,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$39,$A14,'Picks'!$U$2:$U$39,"settled",'Picks'!$V$2:$V$39,"loss")</f>
         <v/>
       </c>
-      <c r="E14" s="34">
+      <c r="E14" s="14">
         <f>IFERROR(C14/(C14+D14),0)</f>
         <v/>
       </c>
-      <c r="F14" s="35">
-        <f>SUMIFS('Picks'!$BY$2:$BY$31,'Picks'!$H$2:$H$31,$A14)</f>
+      <c r="F14" s="15">
+        <f>SUMIFS('Picks'!$BY$2:$BY$39,'Picks'!$H$2:$H$39,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$31,'Picks'!$H$2:$H$31,$A14,'Picks'!$U$2:$U$31,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$39,'Picks'!$H$2:$H$39,$A14,'Picks'!$U$2:$U$39,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -946,27 +916,27 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$31,$A15,'Picks'!$U$2:$U$31,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$39,$A15,'Picks'!$U$2:$U$39,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$31,$A15,'Picks'!$U$2:$U$31,"settled",'Picks'!$V$2:$V$31,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$39,$A15,'Picks'!$U$2:$U$39,"settled",'Picks'!$V$2:$V$39,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$31,$A15,'Picks'!$U$2:$U$31,"settled",'Picks'!$V$2:$V$31,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$39,$A15,'Picks'!$U$2:$U$39,"settled",'Picks'!$V$2:$V$39,"loss")</f>
         <v/>
       </c>
-      <c r="E15" s="36">
+      <c r="E15" s="19">
         <f>IFERROR(C15/(C15+D15),0)</f>
         <v/>
       </c>
-      <c r="F15" s="37">
-        <f>SUMIFS('Picks'!$BY$2:$BY$31,'Picks'!$H$2:$H$31,$A15)</f>
+      <c r="F15" s="20">
+        <f>SUMIFS('Picks'!$BY$2:$BY$39,'Picks'!$H$2:$H$39,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$31,'Picks'!$H$2:$H$31,$A15,'Picks'!$U$2:$U$31,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$39,'Picks'!$H$2:$H$39,$A15,'Picks'!$U$2:$U$39,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -977,31 +947,30 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$31,$A16,'Picks'!$U$2:$U$31,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$39,$A16,'Picks'!$U$2:$U$39,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$31,$A16,'Picks'!$U$2:$U$31,"settled",'Picks'!$V$2:$V$31,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$39,$A16,'Picks'!$U$2:$U$39,"settled",'Picks'!$V$2:$V$39,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$31,$A16,'Picks'!$U$2:$U$31,"settled",'Picks'!$V$2:$V$31,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$39,$A16,'Picks'!$U$2:$U$39,"settled",'Picks'!$V$2:$V$39,"loss")</f>
         <v/>
       </c>
-      <c r="E16" s="34">
+      <c r="E16" s="14">
         <f>IFERROR(C16/(C16+D16),0)</f>
         <v/>
       </c>
-      <c r="F16" s="35">
-        <f>SUMIFS('Picks'!$BY$2:$BY$31,'Picks'!$H$2:$H$31,$A16)</f>
+      <c r="F16" s="15">
+        <f>SUMIFS('Picks'!$BY$2:$BY$39,'Picks'!$H$2:$H$39,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$31,'Picks'!$H$2:$H$31,$A16,'Picks'!$U$2:$U$31,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$39,'Picks'!$H$2:$H$39,$A16,'Picks'!$U$2:$U$39,"settled"),0)</f>
         <v/>
       </c>
     </row>
-    <row r="17"/>
     <row r="18">
       <c r="A18" s="22" t="inlineStr">
         <is>
@@ -1027,7 +996,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CA31"/>
+  <dimension ref="A1:CA39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1554,7 +1523,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J2" s="38" t="n"/>
+      <c r="J2" s="25" t="n"/>
       <c r="K2" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -1563,7 +1532,7 @@
       <c r="L2" s="26" t="n">
         <v>117</v>
       </c>
-      <c r="M2" s="39" t="n">
+      <c r="M2" s="27" t="n">
         <v>2.17</v>
       </c>
       <c r="N2" s="28" t="n">
@@ -1603,11 +1572,11 @@
       <c r="X2" s="26" t="n">
         <v>108</v>
       </c>
-      <c r="Y2" s="38" t="n"/>
+      <c r="Y2" s="25" t="n"/>
       <c r="Z2" s="26" t="n"/>
       <c r="AA2" s="28" t="n"/>
       <c r="AB2" s="28" t="n"/>
-      <c r="AC2" s="40" t="n">
+      <c r="AC2" s="30" t="n">
         <v>1.755</v>
       </c>
       <c r="AD2" s="24" t="inlineStr">
@@ -1744,11 +1713,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ2" s="38" t="n"/>
+      <c r="BJ2" s="25" t="n"/>
       <c r="BK2" s="26" t="n">
         <v>117</v>
       </c>
-      <c r="BL2" s="39" t="n">
+      <c r="BL2" s="27" t="n">
         <v>2.17</v>
       </c>
       <c r="BM2" s="28" t="n">
@@ -1758,18 +1727,18 @@
         <v>0.455446</v>
       </c>
       <c r="BO2" s="28" t="n"/>
-      <c r="BP2" s="38" t="n"/>
-      <c r="BQ2" s="39" t="n"/>
+      <c r="BP2" s="25" t="n"/>
+      <c r="BQ2" s="27" t="n"/>
       <c r="BR2" s="28" t="n"/>
       <c r="BS2" s="28" t="n"/>
       <c r="BT2" s="28" t="n"/>
-      <c r="BU2" s="38" t="n"/>
+      <c r="BU2" s="25" t="n"/>
       <c r="BV2" s="29" t="n"/>
       <c r="BW2" s="24" t="n"/>
-      <c r="BX2" s="40" t="n">
+      <c r="BX2" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY2" s="39" t="n">
+      <c r="BY2" s="27" t="n">
         <v>1.17</v>
       </c>
       <c r="BZ2" s="24" t="inlineStr">
@@ -1829,7 +1798,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J3" s="38" t="n"/>
+      <c r="J3" s="25" t="n"/>
       <c r="K3" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -1838,7 +1807,7 @@
       <c r="L3" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="M3" s="39" t="n">
+      <c r="M3" s="27" t="n">
         <v>1.75188</v>
       </c>
       <c r="N3" s="28" t="n">
@@ -1878,11 +1847,11 @@
       <c r="X3" s="26" t="n">
         <v>8</v>
       </c>
-      <c r="Y3" s="38" t="n"/>
+      <c r="Y3" s="25" t="n"/>
       <c r="Z3" s="26" t="n"/>
       <c r="AA3" s="28" t="n"/>
       <c r="AB3" s="28" t="n"/>
-      <c r="AC3" s="40" t="n">
+      <c r="AC3" s="30" t="n">
         <v>1.1278</v>
       </c>
       <c r="AD3" s="24" t="inlineStr">
@@ -2019,11 +1988,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ3" s="38" t="n"/>
+      <c r="BJ3" s="25" t="n"/>
       <c r="BK3" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="BL3" s="39" t="n">
+      <c r="BL3" s="27" t="n">
         <v>1.75188</v>
       </c>
       <c r="BM3" s="28" t="n">
@@ -2033,18 +2002,18 @@
         <v>0.567164</v>
       </c>
       <c r="BO3" s="28" t="n"/>
-      <c r="BP3" s="38" t="n"/>
-      <c r="BQ3" s="39" t="n"/>
+      <c r="BP3" s="25" t="n"/>
+      <c r="BQ3" s="27" t="n"/>
       <c r="BR3" s="28" t="n"/>
       <c r="BS3" s="28" t="n"/>
       <c r="BT3" s="28" t="n"/>
-      <c r="BU3" s="38" t="n"/>
+      <c r="BU3" s="25" t="n"/>
       <c r="BV3" s="29" t="n"/>
       <c r="BW3" s="24" t="n"/>
-      <c r="BX3" s="40" t="n">
+      <c r="BX3" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY3" s="39" t="n">
+      <c r="BY3" s="27" t="n">
         <v>0.75188</v>
       </c>
       <c r="BZ3" s="24" t="inlineStr">
@@ -2104,7 +2073,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J4" s="38" t="n"/>
+      <c r="J4" s="25" t="n"/>
       <c r="K4" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -2113,7 +2082,7 @@
       <c r="L4" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="M4" s="39" t="n">
+      <c r="M4" s="27" t="n">
         <v>1.980392</v>
       </c>
       <c r="N4" s="28" t="n">
@@ -2153,11 +2122,11 @@
       <c r="X4" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="Y4" s="38" t="n"/>
+      <c r="Y4" s="25" t="n"/>
       <c r="Z4" s="26" t="n"/>
       <c r="AA4" s="28" t="n"/>
       <c r="AB4" s="28" t="n"/>
-      <c r="AC4" s="40" t="n">
+      <c r="AC4" s="30" t="n">
         <v>-1</v>
       </c>
       <c r="AD4" s="24" t="inlineStr">
@@ -2294,11 +2263,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ4" s="38" t="n"/>
+      <c r="BJ4" s="25" t="n"/>
       <c r="BK4" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="BL4" s="39" t="n">
+      <c r="BL4" s="27" t="n">
         <v>1.980392</v>
       </c>
       <c r="BM4" s="28" t="n">
@@ -2308,18 +2277,18 @@
         <v>0.502488</v>
       </c>
       <c r="BO4" s="28" t="n"/>
-      <c r="BP4" s="38" t="n"/>
-      <c r="BQ4" s="39" t="n"/>
+      <c r="BP4" s="25" t="n"/>
+      <c r="BQ4" s="27" t="n"/>
       <c r="BR4" s="28" t="n"/>
       <c r="BS4" s="28" t="n"/>
       <c r="BT4" s="28" t="n"/>
-      <c r="BU4" s="38" t="n"/>
+      <c r="BU4" s="25" t="n"/>
       <c r="BV4" s="29" t="n"/>
       <c r="BW4" s="24" t="n"/>
-      <c r="BX4" s="40" t="n">
+      <c r="BX4" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY4" s="39" t="n">
+      <c r="BY4" s="27" t="n">
         <v>-1</v>
       </c>
       <c r="BZ4" s="24" t="inlineStr">
@@ -2379,7 +2348,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J5" s="38" t="n"/>
+      <c r="J5" s="25" t="n"/>
       <c r="K5" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -2388,7 +2357,7 @@
       <c r="L5" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="M5" s="39" t="n">
+      <c r="M5" s="27" t="n">
         <v>1.75188</v>
       </c>
       <c r="N5" s="28" t="n">
@@ -2428,11 +2397,11 @@
       <c r="X5" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="Y5" s="38" t="n"/>
+      <c r="Y5" s="25" t="n"/>
       <c r="Z5" s="26" t="n"/>
       <c r="AA5" s="28" t="n"/>
       <c r="AB5" s="28" t="n"/>
-      <c r="AC5" s="40" t="n">
+      <c r="AC5" s="30" t="n">
         <v>1.1278</v>
       </c>
       <c r="AD5" s="24" t="inlineStr">
@@ -2569,11 +2538,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ5" s="38" t="n"/>
+      <c r="BJ5" s="25" t="n"/>
       <c r="BK5" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="BL5" s="39" t="n">
+      <c r="BL5" s="27" t="n">
         <v>1.75188</v>
       </c>
       <c r="BM5" s="28" t="n">
@@ -2583,18 +2552,18 @@
         <v>0.567164</v>
       </c>
       <c r="BO5" s="28" t="n"/>
-      <c r="BP5" s="38" t="n"/>
-      <c r="BQ5" s="39" t="n"/>
+      <c r="BP5" s="25" t="n"/>
+      <c r="BQ5" s="27" t="n"/>
       <c r="BR5" s="28" t="n"/>
       <c r="BS5" s="28" t="n"/>
       <c r="BT5" s="28" t="n"/>
-      <c r="BU5" s="38" t="n"/>
+      <c r="BU5" s="25" t="n"/>
       <c r="BV5" s="29" t="n"/>
       <c r="BW5" s="24" t="n"/>
-      <c r="BX5" s="40" t="n">
+      <c r="BX5" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY5" s="39" t="n">
+      <c r="BY5" s="27" t="n">
         <v>0.75188</v>
       </c>
       <c r="BZ5" s="24" t="inlineStr">
@@ -2654,7 +2623,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J6" s="38" t="n"/>
+      <c r="J6" s="25" t="n"/>
       <c r="K6" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -2663,7 +2632,7 @@
       <c r="L6" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="M6" s="39" t="n">
+      <c r="M6" s="27" t="n">
         <v>1.961538</v>
       </c>
       <c r="N6" s="28" t="n">
@@ -2703,11 +2672,11 @@
       <c r="X6" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="Y6" s="38" t="n"/>
+      <c r="Y6" s="25" t="n"/>
       <c r="Z6" s="26" t="n"/>
       <c r="AA6" s="28" t="n"/>
       <c r="AB6" s="28" t="n"/>
-      <c r="AC6" s="40" t="n">
+      <c r="AC6" s="30" t="n">
         <v>1.2019</v>
       </c>
       <c r="AD6" s="24" t="inlineStr">
@@ -2844,11 +2813,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ6" s="38" t="n"/>
+      <c r="BJ6" s="25" t="n"/>
       <c r="BK6" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="BL6" s="39" t="n">
+      <c r="BL6" s="27" t="n">
         <v>1.961538</v>
       </c>
       <c r="BM6" s="28" t="n">
@@ -2858,18 +2827,18 @@
         <v>0.507463</v>
       </c>
       <c r="BO6" s="28" t="n"/>
-      <c r="BP6" s="38" t="n"/>
-      <c r="BQ6" s="39" t="n"/>
+      <c r="BP6" s="25" t="n"/>
+      <c r="BQ6" s="27" t="n"/>
       <c r="BR6" s="28" t="n"/>
       <c r="BS6" s="28" t="n"/>
       <c r="BT6" s="28" t="n"/>
-      <c r="BU6" s="38" t="n"/>
+      <c r="BU6" s="25" t="n"/>
       <c r="BV6" s="29" t="n"/>
       <c r="BW6" s="24" t="n"/>
-      <c r="BX6" s="40" t="n">
+      <c r="BX6" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY6" s="39" t="n">
+      <c r="BY6" s="27" t="n">
         <v>0.961538</v>
       </c>
       <c r="BZ6" s="24" t="inlineStr">
@@ -2929,7 +2898,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J7" s="38" t="n"/>
+      <c r="J7" s="25" t="n"/>
       <c r="K7" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -2938,7 +2907,7 @@
       <c r="L7" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="M7" s="39" t="n">
+      <c r="M7" s="27" t="n">
         <v>1.961538</v>
       </c>
       <c r="N7" s="28" t="n">
@@ -2978,11 +2947,11 @@
       <c r="X7" s="26" t="n">
         <v>10</v>
       </c>
-      <c r="Y7" s="38" t="n"/>
+      <c r="Y7" s="25" t="n"/>
       <c r="Z7" s="26" t="n"/>
       <c r="AA7" s="28" t="n"/>
       <c r="AB7" s="28" t="n"/>
-      <c r="AC7" s="40" t="n">
+      <c r="AC7" s="30" t="n">
         <v>-1.25</v>
       </c>
       <c r="AD7" s="24" t="inlineStr">
@@ -3119,11 +3088,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ7" s="38" t="n"/>
+      <c r="BJ7" s="25" t="n"/>
       <c r="BK7" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="BL7" s="39" t="n">
+      <c r="BL7" s="27" t="n">
         <v>1.961538</v>
       </c>
       <c r="BM7" s="28" t="n">
@@ -3133,18 +3102,18 @@
         <v>0.507463</v>
       </c>
       <c r="BO7" s="28" t="n"/>
-      <c r="BP7" s="38" t="n"/>
-      <c r="BQ7" s="39" t="n"/>
+      <c r="BP7" s="25" t="n"/>
+      <c r="BQ7" s="27" t="n"/>
       <c r="BR7" s="28" t="n"/>
       <c r="BS7" s="28" t="n"/>
       <c r="BT7" s="28" t="n"/>
-      <c r="BU7" s="38" t="n"/>
+      <c r="BU7" s="25" t="n"/>
       <c r="BV7" s="29" t="n"/>
       <c r="BW7" s="24" t="n"/>
-      <c r="BX7" s="40" t="n">
+      <c r="BX7" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY7" s="39" t="n">
+      <c r="BY7" s="27" t="n">
         <v>-1</v>
       </c>
       <c r="BZ7" s="24" t="inlineStr">
@@ -3204,7 +3173,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J8" s="38" t="n"/>
+      <c r="J8" s="25" t="n"/>
       <c r="K8" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -3213,7 +3182,7 @@
       <c r="L8" s="26" t="n">
         <v>-106</v>
       </c>
-      <c r="M8" s="39" t="n">
+      <c r="M8" s="27" t="n">
         <v>1.943396</v>
       </c>
       <c r="N8" s="28" t="n">
@@ -3253,11 +3222,11 @@
       <c r="X8" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="Y8" s="38" t="n"/>
+      <c r="Y8" s="25" t="n"/>
       <c r="Z8" s="26" t="n"/>
       <c r="AA8" s="28" t="n"/>
       <c r="AB8" s="28" t="n"/>
-      <c r="AC8" s="40" t="n">
+      <c r="AC8" s="30" t="n">
         <v>-1</v>
       </c>
       <c r="AD8" s="24" t="inlineStr">
@@ -3394,11 +3363,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ8" s="38" t="n"/>
+      <c r="BJ8" s="25" t="n"/>
       <c r="BK8" s="26" t="n">
         <v>-106</v>
       </c>
-      <c r="BL8" s="39" t="n">
+      <c r="BL8" s="27" t="n">
         <v>1.943396</v>
       </c>
       <c r="BM8" s="28" t="n">
@@ -3408,18 +3377,18 @@
         <v>0.5124379999999999</v>
       </c>
       <c r="BO8" s="28" t="n"/>
-      <c r="BP8" s="38" t="n"/>
-      <c r="BQ8" s="39" t="n"/>
+      <c r="BP8" s="25" t="n"/>
+      <c r="BQ8" s="27" t="n"/>
       <c r="BR8" s="28" t="n"/>
       <c r="BS8" s="28" t="n"/>
       <c r="BT8" s="28" t="n"/>
-      <c r="BU8" s="38" t="n"/>
+      <c r="BU8" s="25" t="n"/>
       <c r="BV8" s="29" t="n"/>
       <c r="BW8" s="24" t="n"/>
-      <c r="BX8" s="40" t="n">
+      <c r="BX8" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY8" s="39" t="n">
+      <c r="BY8" s="27" t="n">
         <v>-1</v>
       </c>
       <c r="BZ8" s="24" t="inlineStr">
@@ -3479,7 +3448,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J9" s="38" t="n"/>
+      <c r="J9" s="25" t="n"/>
       <c r="K9" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -3488,7 +3457,7 @@
       <c r="L9" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="M9" s="39" t="n">
+      <c r="M9" s="27" t="n">
         <v>1.980392</v>
       </c>
       <c r="N9" s="28" t="n">
@@ -3519,21 +3488,21 @@
       </c>
       <c r="V9" s="24" t="inlineStr">
         <is>
-          <t>loss</t>
+          <t>win</t>
         </is>
       </c>
       <c r="W9" s="26" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="X9" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y9" s="38" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="Y9" s="25" t="n"/>
       <c r="Z9" s="26" t="n"/>
       <c r="AA9" s="28" t="n"/>
       <c r="AB9" s="28" t="n"/>
-      <c r="AC9" s="40" t="n">
-        <v>-1</v>
+      <c r="AC9" s="30" t="n">
+        <v>0.9804</v>
       </c>
       <c r="AD9" s="24" t="inlineStr">
         <is>
@@ -3669,11 +3638,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ9" s="38" t="n"/>
+      <c r="BJ9" s="25" t="n"/>
       <c r="BK9" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="BL9" s="39" t="n">
+      <c r="BL9" s="27" t="n">
         <v>1.980392</v>
       </c>
       <c r="BM9" s="28" t="n">
@@ -3683,19 +3652,19 @@
         <v>0.502488</v>
       </c>
       <c r="BO9" s="28" t="n"/>
-      <c r="BP9" s="38" t="n"/>
-      <c r="BQ9" s="39" t="n"/>
+      <c r="BP9" s="25" t="n"/>
+      <c r="BQ9" s="27" t="n"/>
       <c r="BR9" s="28" t="n"/>
       <c r="BS9" s="28" t="n"/>
       <c r="BT9" s="28" t="n"/>
-      <c r="BU9" s="38" t="n"/>
+      <c r="BU9" s="25" t="n"/>
       <c r="BV9" s="29" t="n"/>
       <c r="BW9" s="24" t="n"/>
-      <c r="BX9" s="40" t="n">
+      <c r="BX9" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY9" s="39" t="n">
-        <v>-1</v>
+      <c r="BY9" s="27" t="n">
+        <v>0.980392</v>
       </c>
       <c r="BZ9" s="24" t="inlineStr">
         <is>
@@ -3754,7 +3723,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J10" s="38" t="n"/>
+      <c r="J10" s="25" t="n"/>
       <c r="K10" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -3763,7 +3732,7 @@
       <c r="L10" s="26" t="n">
         <v>-138</v>
       </c>
-      <c r="M10" s="39" t="n">
+      <c r="M10" s="27" t="n">
         <v>1.724638</v>
       </c>
       <c r="N10" s="28" t="n">
@@ -3803,11 +3772,11 @@
       <c r="X10" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="Y10" s="38" t="n"/>
+      <c r="Y10" s="25" t="n"/>
       <c r="Z10" s="26" t="n"/>
       <c r="AA10" s="28" t="n"/>
       <c r="AB10" s="28" t="n"/>
-      <c r="AC10" s="40" t="n">
+      <c r="AC10" s="30" t="n">
         <v>1.2681</v>
       </c>
       <c r="AD10" s="24" t="inlineStr">
@@ -3944,11 +3913,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ10" s="38" t="n"/>
+      <c r="BJ10" s="25" t="n"/>
       <c r="BK10" s="26" t="n">
         <v>-138</v>
       </c>
-      <c r="BL10" s="39" t="n">
+      <c r="BL10" s="27" t="n">
         <v>1.724638</v>
       </c>
       <c r="BM10" s="28" t="n">
@@ -3958,18 +3927,18 @@
         <v>0.577114</v>
       </c>
       <c r="BO10" s="28" t="n"/>
-      <c r="BP10" s="38" t="n"/>
-      <c r="BQ10" s="39" t="n"/>
+      <c r="BP10" s="25" t="n"/>
+      <c r="BQ10" s="27" t="n"/>
       <c r="BR10" s="28" t="n"/>
       <c r="BS10" s="28" t="n"/>
       <c r="BT10" s="28" t="n"/>
-      <c r="BU10" s="38" t="n"/>
+      <c r="BU10" s="25" t="n"/>
       <c r="BV10" s="29" t="n"/>
       <c r="BW10" s="24" t="n"/>
-      <c r="BX10" s="40" t="n">
+      <c r="BX10" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY10" s="39" t="n">
+      <c r="BY10" s="27" t="n">
         <v>0.724638</v>
       </c>
       <c r="BZ10" s="24" t="inlineStr">
@@ -4029,7 +3998,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J11" s="38" t="n"/>
+      <c r="J11" s="25" t="n"/>
       <c r="K11" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -4038,7 +4007,7 @@
       <c r="L11" s="26" t="n">
         <v>102</v>
       </c>
-      <c r="M11" s="39" t="n">
+      <c r="M11" s="27" t="n">
         <v>2.02</v>
       </c>
       <c r="N11" s="28" t="n">
@@ -4078,11 +4047,11 @@
       <c r="X11" s="26" t="n">
         <v>15</v>
       </c>
-      <c r="Y11" s="38" t="n"/>
+      <c r="Y11" s="25" t="n"/>
       <c r="Z11" s="26" t="n"/>
       <c r="AA11" s="28" t="n"/>
       <c r="AB11" s="28" t="n"/>
-      <c r="AC11" s="40" t="n">
+      <c r="AC11" s="30" t="n">
         <v>1.275</v>
       </c>
       <c r="AD11" s="24" t="inlineStr">
@@ -4219,11 +4188,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ11" s="38" t="n"/>
+      <c r="BJ11" s="25" t="n"/>
       <c r="BK11" s="26" t="n">
         <v>102</v>
       </c>
-      <c r="BL11" s="39" t="n">
+      <c r="BL11" s="27" t="n">
         <v>2.02</v>
       </c>
       <c r="BM11" s="28" t="n">
@@ -4233,18 +4202,18 @@
         <v>0.492537</v>
       </c>
       <c r="BO11" s="28" t="n"/>
-      <c r="BP11" s="38" t="n"/>
-      <c r="BQ11" s="39" t="n"/>
+      <c r="BP11" s="25" t="n"/>
+      <c r="BQ11" s="27" t="n"/>
       <c r="BR11" s="28" t="n"/>
       <c r="BS11" s="28" t="n"/>
       <c r="BT11" s="28" t="n"/>
-      <c r="BU11" s="38" t="n"/>
+      <c r="BU11" s="25" t="n"/>
       <c r="BV11" s="29" t="n"/>
       <c r="BW11" s="24" t="n"/>
-      <c r="BX11" s="40" t="n">
+      <c r="BX11" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY11" s="39" t="n">
+      <c r="BY11" s="27" t="n">
         <v>1.02</v>
       </c>
       <c r="BZ11" s="24" t="inlineStr">
@@ -4304,7 +4273,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J12" s="38" t="n"/>
+      <c r="J12" s="25" t="n"/>
       <c r="K12" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -4313,7 +4282,7 @@
       <c r="L12" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="M12" s="39" t="n">
+      <c r="M12" s="27" t="n">
         <v>1.980392</v>
       </c>
       <c r="N12" s="28" t="n">
@@ -4353,11 +4322,11 @@
       <c r="X12" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y12" s="38" t="n"/>
+      <c r="Y12" s="25" t="n"/>
       <c r="Z12" s="26" t="n"/>
       <c r="AA12" s="28" t="n"/>
       <c r="AB12" s="28" t="n"/>
-      <c r="AC12" s="40" t="n">
+      <c r="AC12" s="30" t="n">
         <v>-1</v>
       </c>
       <c r="AD12" s="24" t="inlineStr">
@@ -4494,11 +4463,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ12" s="38" t="n"/>
+      <c r="BJ12" s="25" t="n"/>
       <c r="BK12" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="BL12" s="39" t="n">
+      <c r="BL12" s="27" t="n">
         <v>1.980392</v>
       </c>
       <c r="BM12" s="28" t="n">
@@ -4508,18 +4477,18 @@
         <v>0.502488</v>
       </c>
       <c r="BO12" s="28" t="n"/>
-      <c r="BP12" s="38" t="n"/>
-      <c r="BQ12" s="39" t="n"/>
+      <c r="BP12" s="25" t="n"/>
+      <c r="BQ12" s="27" t="n"/>
       <c r="BR12" s="28" t="n"/>
       <c r="BS12" s="28" t="n"/>
       <c r="BT12" s="28" t="n"/>
-      <c r="BU12" s="38" t="n"/>
+      <c r="BU12" s="25" t="n"/>
       <c r="BV12" s="29" t="n"/>
       <c r="BW12" s="24" t="n"/>
-      <c r="BX12" s="40" t="n">
+      <c r="BX12" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY12" s="39" t="n">
+      <c r="BY12" s="27" t="n">
         <v>-1</v>
       </c>
       <c r="BZ12" s="24" t="inlineStr">
@@ -4579,7 +4548,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J13" s="38" t="n"/>
+      <c r="J13" s="25" t="n"/>
       <c r="K13" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -4588,7 +4557,7 @@
       <c r="L13" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="M13" s="39" t="n">
+      <c r="M13" s="27" t="n">
         <v>1.980392</v>
       </c>
       <c r="N13" s="28" t="n">
@@ -4628,11 +4597,11 @@
       <c r="X13" s="26" t="n">
         <v>7</v>
       </c>
-      <c r="Y13" s="38" t="n"/>
+      <c r="Y13" s="25" t="n"/>
       <c r="Z13" s="26" t="n"/>
       <c r="AA13" s="28" t="n"/>
       <c r="AB13" s="28" t="n"/>
-      <c r="AC13" s="40" t="n">
+      <c r="AC13" s="30" t="n">
         <v>1.2255</v>
       </c>
       <c r="AD13" s="24" t="inlineStr">
@@ -4769,11 +4738,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ13" s="38" t="n"/>
+      <c r="BJ13" s="25" t="n"/>
       <c r="BK13" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="BL13" s="39" t="n">
+      <c r="BL13" s="27" t="n">
         <v>1.980392</v>
       </c>
       <c r="BM13" s="28" t="n">
@@ -4783,18 +4752,18 @@
         <v>0.502488</v>
       </c>
       <c r="BO13" s="28" t="n"/>
-      <c r="BP13" s="38" t="n"/>
-      <c r="BQ13" s="39" t="n"/>
+      <c r="BP13" s="25" t="n"/>
+      <c r="BQ13" s="27" t="n"/>
       <c r="BR13" s="28" t="n"/>
       <c r="BS13" s="28" t="n"/>
       <c r="BT13" s="28" t="n"/>
-      <c r="BU13" s="38" t="n"/>
+      <c r="BU13" s="25" t="n"/>
       <c r="BV13" s="29" t="n"/>
       <c r="BW13" s="24" t="n"/>
-      <c r="BX13" s="40" t="n">
+      <c r="BX13" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY13" s="39" t="n">
+      <c r="BY13" s="27" t="n">
         <v>0.980392</v>
       </c>
       <c r="BZ13" s="24" t="inlineStr">
@@ -4854,7 +4823,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J14" s="38" t="n"/>
+      <c r="J14" s="25" t="n"/>
       <c r="K14" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -4863,7 +4832,7 @@
       <c r="L14" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="M14" s="39" t="n">
+      <c r="M14" s="27" t="n">
         <v>1.961538</v>
       </c>
       <c r="N14" s="28" t="n">
@@ -4903,11 +4872,11 @@
       <c r="X14" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="Y14" s="38" t="n"/>
+      <c r="Y14" s="25" t="n"/>
       <c r="Z14" s="26" t="n"/>
       <c r="AA14" s="28" t="n"/>
       <c r="AB14" s="28" t="n"/>
-      <c r="AC14" s="40" t="n">
+      <c r="AC14" s="30" t="n">
         <v>-0.75</v>
       </c>
       <c r="AD14" s="24" t="inlineStr">
@@ -5044,11 +5013,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ14" s="38" t="n"/>
+      <c r="BJ14" s="25" t="n"/>
       <c r="BK14" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="BL14" s="39" t="n">
+      <c r="BL14" s="27" t="n">
         <v>1.961538</v>
       </c>
       <c r="BM14" s="28" t="n">
@@ -5058,18 +5027,18 @@
         <v>0.507463</v>
       </c>
       <c r="BO14" s="28" t="n"/>
-      <c r="BP14" s="38" t="n"/>
-      <c r="BQ14" s="39" t="n"/>
+      <c r="BP14" s="25" t="n"/>
+      <c r="BQ14" s="27" t="n"/>
       <c r="BR14" s="28" t="n"/>
       <c r="BS14" s="28" t="n"/>
       <c r="BT14" s="28" t="n"/>
-      <c r="BU14" s="38" t="n"/>
+      <c r="BU14" s="25" t="n"/>
       <c r="BV14" s="29" t="n"/>
       <c r="BW14" s="24" t="n"/>
-      <c r="BX14" s="40" t="n">
+      <c r="BX14" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY14" s="39" t="n">
+      <c r="BY14" s="27" t="n">
         <v>-1</v>
       </c>
       <c r="BZ14" s="24" t="inlineStr">
@@ -5129,7 +5098,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J15" s="38" t="n"/>
+      <c r="J15" s="25" t="n"/>
       <c r="K15" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -5138,7 +5107,7 @@
       <c r="L15" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="M15" s="39" t="n">
+      <c r="M15" s="27" t="n">
         <v>1.961538</v>
       </c>
       <c r="N15" s="28" t="n">
@@ -5155,27 +5124,41 @@
         <v>70</v>
       </c>
       <c r="S15" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T15" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="U15" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V15" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W15" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="X15" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="T15" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v3</t>
-        </is>
-      </c>
-      <c r="U15" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V15" s="24" t="n"/>
-      <c r="W15" s="26" t="n"/>
-      <c r="X15" s="26" t="n"/>
-      <c r="Y15" s="38" t="n"/>
+      <c r="Y15" s="25" t="n"/>
       <c r="Z15" s="26" t="n"/>
       <c r="AA15" s="28" t="n"/>
       <c r="AB15" s="28" t="n"/>
-      <c r="AC15" s="40" t="n"/>
-      <c r="AD15" s="24" t="n"/>
+      <c r="AC15" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD15" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-19T21:31:34.426330Z</t>
+        </is>
+      </c>
       <c r="AE15" s="31" t="inlineStr">
         <is>
           <t>Learned LR call at threshold 0.5100; executable ask 0.5100 (aec-mlb-cws-tor-2026-07-19).</t>
@@ -5188,7 +5171,7 @@
       </c>
       <c r="AG15" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH15" s="24" t="n"/>
@@ -5305,11 +5288,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ15" s="38" t="n"/>
+      <c r="BJ15" s="25" t="n"/>
       <c r="BK15" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="BL15" s="39" t="n">
+      <c r="BL15" s="27" t="n">
         <v>1.961538</v>
       </c>
       <c r="BM15" s="28" t="n">
@@ -5319,18 +5302,30 @@
         <v>0.507463</v>
       </c>
       <c r="BO15" s="28" t="n"/>
-      <c r="BP15" s="38" t="n"/>
-      <c r="BQ15" s="39" t="n"/>
+      <c r="BP15" s="25" t="n"/>
+      <c r="BQ15" s="27" t="n"/>
       <c r="BR15" s="28" t="n"/>
       <c r="BS15" s="28" t="n"/>
       <c r="BT15" s="28" t="n"/>
-      <c r="BU15" s="38" t="n"/>
+      <c r="BU15" s="25" t="n"/>
       <c r="BV15" s="29" t="n"/>
       <c r="BW15" s="24" t="n"/>
-      <c r="BX15" s="40" t="n"/>
-      <c r="BY15" s="39" t="n"/>
-      <c r="BZ15" s="24" t="n"/>
-      <c r="CA15" s="31" t="n"/>
+      <c r="BX15" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY15" s="27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BZ15" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-19T21:31:34.426330Z</t>
+        </is>
+      </c>
+      <c r="CA15" s="31" t="inlineStr">
+        <is>
+          <t>fixed one-unit hypothetical scoring; no real exposure or execution</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="36" customHeight="1">
       <c r="A16" s="24" t="inlineStr">
@@ -5378,7 +5373,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J16" s="38" t="n"/>
+      <c r="J16" s="25" t="n"/>
       <c r="K16" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -5387,7 +5382,7 @@
       <c r="L16" s="26" t="n">
         <v>-111</v>
       </c>
-      <c r="M16" s="39" t="n">
+      <c r="M16" s="27" t="n">
         <v>1.900901</v>
       </c>
       <c r="N16" s="28" t="n">
@@ -5404,7 +5399,7 @@
         <v>90</v>
       </c>
       <c r="S16" s="29" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T16" s="24" t="inlineStr">
         <is>
@@ -5413,18 +5408,32 @@
       </c>
       <c r="U16" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V16" s="24" t="n"/>
-      <c r="W16" s="26" t="n"/>
-      <c r="X16" s="26" t="n"/>
-      <c r="Y16" s="38" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V16" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W16" s="26" t="n">
+        <v>6</v>
+      </c>
+      <c r="X16" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y16" s="25" t="n"/>
       <c r="Z16" s="26" t="n"/>
       <c r="AA16" s="28" t="n"/>
       <c r="AB16" s="28" t="n"/>
-      <c r="AC16" s="40" t="n"/>
-      <c r="AD16" s="24" t="n"/>
+      <c r="AC16" s="30" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AD16" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-19T21:31:34.633018Z</t>
+        </is>
+      </c>
       <c r="AE16" s="31" t="inlineStr">
         <is>
           <t>Learned LR call at threshold 0.5100; executable ask 0.5250 (aec-mlb-nym-phi-2026-07-19).</t>
@@ -5437,7 +5446,7 @@
       </c>
       <c r="AG16" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH16" s="24" t="n"/>
@@ -5554,11 +5563,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ16" s="38" t="n"/>
+      <c r="BJ16" s="25" t="n"/>
       <c r="BK16" s="26" t="n">
         <v>-111</v>
       </c>
-      <c r="BL16" s="39" t="n">
+      <c r="BL16" s="27" t="n">
         <v>1.900901</v>
       </c>
       <c r="BM16" s="28" t="n">
@@ -5568,18 +5577,30 @@
         <v>0.522388</v>
       </c>
       <c r="BO16" s="28" t="n"/>
-      <c r="BP16" s="38" t="n"/>
-      <c r="BQ16" s="39" t="n"/>
+      <c r="BP16" s="25" t="n"/>
+      <c r="BQ16" s="27" t="n"/>
       <c r="BR16" s="28" t="n"/>
       <c r="BS16" s="28" t="n"/>
       <c r="BT16" s="28" t="n"/>
-      <c r="BU16" s="38" t="n"/>
+      <c r="BU16" s="25" t="n"/>
       <c r="BV16" s="29" t="n"/>
       <c r="BW16" s="24" t="n"/>
-      <c r="BX16" s="40" t="n"/>
-      <c r="BY16" s="39" t="n"/>
-      <c r="BZ16" s="24" t="n"/>
-      <c r="CA16" s="31" t="n"/>
+      <c r="BX16" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY16" s="27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BZ16" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-19T21:31:34.633018Z</t>
+        </is>
+      </c>
+      <c r="CA16" s="31" t="inlineStr">
+        <is>
+          <t>fixed one-unit hypothetical scoring; no real exposure or execution</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="36" customHeight="1">
       <c r="A17" s="24" t="inlineStr">
@@ -5627,7 +5648,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J17" s="38" t="n"/>
+      <c r="J17" s="25" t="n"/>
       <c r="K17" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -5636,7 +5657,7 @@
       <c r="L17" s="26" t="n">
         <v>-108</v>
       </c>
-      <c r="M17" s="39" t="n">
+      <c r="M17" s="27" t="n">
         <v>1.925926</v>
       </c>
       <c r="N17" s="28" t="n">
@@ -5653,7 +5674,7 @@
         <v>66</v>
       </c>
       <c r="S17" s="29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T17" s="24" t="inlineStr">
         <is>
@@ -5662,18 +5683,32 @@
       </c>
       <c r="U17" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V17" s="24" t="n"/>
-      <c r="W17" s="26" t="n"/>
-      <c r="X17" s="26" t="n"/>
-      <c r="Y17" s="38" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V17" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W17" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X17" s="26" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y17" s="25" t="n"/>
       <c r="Z17" s="26" t="n"/>
       <c r="AA17" s="28" t="n"/>
       <c r="AB17" s="28" t="n"/>
-      <c r="AC17" s="40" t="n"/>
-      <c r="AD17" s="24" t="n"/>
+      <c r="AC17" s="30" t="n">
+        <v>0.9258999999999999</v>
+      </c>
+      <c r="AD17" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-19T21:31:34.820097Z</t>
+        </is>
+      </c>
       <c r="AE17" s="31" t="inlineStr">
         <is>
           <t>Learned LR call at threshold 0.5100; executable ask 0.5200 (aec-mlb-tb-bos-2026-07-19).</t>
@@ -5803,11 +5838,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ17" s="38" t="n"/>
+      <c r="BJ17" s="25" t="n"/>
       <c r="BK17" s="26" t="n">
         <v>-108</v>
       </c>
-      <c r="BL17" s="39" t="n">
+      <c r="BL17" s="27" t="n">
         <v>1.925926</v>
       </c>
       <c r="BM17" s="28" t="n">
@@ -5817,18 +5852,30 @@
         <v>0.5148509999999999</v>
       </c>
       <c r="BO17" s="28" t="n"/>
-      <c r="BP17" s="38" t="n"/>
-      <c r="BQ17" s="39" t="n"/>
+      <c r="BP17" s="25" t="n"/>
+      <c r="BQ17" s="27" t="n"/>
       <c r="BR17" s="28" t="n"/>
       <c r="BS17" s="28" t="n"/>
       <c r="BT17" s="28" t="n"/>
-      <c r="BU17" s="38" t="n"/>
+      <c r="BU17" s="25" t="n"/>
       <c r="BV17" s="29" t="n"/>
       <c r="BW17" s="24" t="n"/>
-      <c r="BX17" s="40" t="n"/>
-      <c r="BY17" s="39" t="n"/>
-      <c r="BZ17" s="24" t="n"/>
-      <c r="CA17" s="31" t="n"/>
+      <c r="BX17" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY17" s="27" t="n">
+        <v>0.925926</v>
+      </c>
+      <c r="BZ17" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-19T21:31:34.820097Z</t>
+        </is>
+      </c>
+      <c r="CA17" s="31" t="inlineStr">
+        <is>
+          <t>fixed one-unit hypothetical scoring; no real exposure or execution</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="36" customHeight="1">
       <c r="A18" s="24" t="inlineStr">
@@ -5876,7 +5923,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J18" s="38" t="n"/>
+      <c r="J18" s="25" t="n"/>
       <c r="K18" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -5885,7 +5932,7 @@
       <c r="L18" s="26" t="n">
         <v>111</v>
       </c>
-      <c r="M18" s="39" t="n">
+      <c r="M18" s="27" t="n">
         <v>2.11</v>
       </c>
       <c r="N18" s="28" t="n">
@@ -5902,7 +5949,7 @@
         <v>95</v>
       </c>
       <c r="S18" s="29" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T18" s="24" t="inlineStr">
         <is>
@@ -5911,18 +5958,32 @@
       </c>
       <c r="U18" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V18" s="24" t="n"/>
-      <c r="W18" s="26" t="n"/>
-      <c r="X18" s="26" t="n"/>
-      <c r="Y18" s="38" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V18" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W18" s="26" t="n">
+        <v>7</v>
+      </c>
+      <c r="X18" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y18" s="25" t="n"/>
       <c r="Z18" s="26" t="n"/>
       <c r="AA18" s="28" t="n"/>
       <c r="AB18" s="28" t="n"/>
-      <c r="AC18" s="40" t="n"/>
-      <c r="AD18" s="24" t="n"/>
+      <c r="AC18" s="30" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="AD18" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-19T21:31:35.008100Z</t>
+        </is>
+      </c>
       <c r="AE18" s="31" t="inlineStr">
         <is>
           <t>Learned LR call at threshold 0.5100; executable ask 0.4750 (aec-mlb-pit-cle-2026-07-19).</t>
@@ -5935,7 +5996,7 @@
       </c>
       <c r="AG18" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH18" s="24" t="n"/>
@@ -6052,11 +6113,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ18" s="38" t="n"/>
+      <c r="BJ18" s="25" t="n"/>
       <c r="BK18" s="26" t="n">
         <v>111</v>
       </c>
-      <c r="BL18" s="39" t="n">
+      <c r="BL18" s="27" t="n">
         <v>2.11</v>
       </c>
       <c r="BM18" s="28" t="n">
@@ -6066,18 +6127,30 @@
         <v>0.472637</v>
       </c>
       <c r="BO18" s="28" t="n"/>
-      <c r="BP18" s="38" t="n"/>
-      <c r="BQ18" s="39" t="n"/>
+      <c r="BP18" s="25" t="n"/>
+      <c r="BQ18" s="27" t="n"/>
       <c r="BR18" s="28" t="n"/>
       <c r="BS18" s="28" t="n"/>
       <c r="BT18" s="28" t="n"/>
-      <c r="BU18" s="38" t="n"/>
+      <c r="BU18" s="25" t="n"/>
       <c r="BV18" s="29" t="n"/>
       <c r="BW18" s="24" t="n"/>
-      <c r="BX18" s="40" t="n"/>
-      <c r="BY18" s="39" t="n"/>
-      <c r="BZ18" s="24" t="n"/>
-      <c r="CA18" s="31" t="n"/>
+      <c r="BX18" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY18" s="27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BZ18" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-19T21:31:35.008100Z</t>
+        </is>
+      </c>
+      <c r="CA18" s="31" t="inlineStr">
+        <is>
+          <t>fixed one-unit hypothetical scoring; no real exposure or execution</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="36" customHeight="1">
       <c r="A19" s="24" t="inlineStr">
@@ -6125,7 +6198,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J19" s="38" t="n"/>
+      <c r="J19" s="25" t="n"/>
       <c r="K19" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -6134,7 +6207,7 @@
       <c r="L19" s="26" t="n">
         <v>-125</v>
       </c>
-      <c r="M19" s="39" t="n">
+      <c r="M19" s="27" t="n">
         <v>1.8</v>
       </c>
       <c r="N19" s="28" t="n">
@@ -6151,7 +6224,7 @@
         <v>76</v>
       </c>
       <c r="S19" s="29" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T19" s="24" t="inlineStr">
         <is>
@@ -6160,18 +6233,32 @@
       </c>
       <c r="U19" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V19" s="24" t="n"/>
-      <c r="W19" s="26" t="n"/>
-      <c r="X19" s="26" t="n"/>
-      <c r="Y19" s="38" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V19" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W19" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X19" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y19" s="25" t="n"/>
       <c r="Z19" s="26" t="n"/>
       <c r="AA19" s="28" t="n"/>
       <c r="AB19" s="28" t="n"/>
-      <c r="AC19" s="40" t="n"/>
-      <c r="AD19" s="24" t="n"/>
+      <c r="AC19" s="30" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AD19" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-19T21:31:35.195059Z</t>
+        </is>
+      </c>
       <c r="AE19" s="31" t="inlineStr">
         <is>
           <t>Learned LR call at threshold 0.5100; executable ask 0.5550 (aec-mlb-mia-mil-2026-07-19).</t>
@@ -6301,11 +6388,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ19" s="38" t="n"/>
+      <c r="BJ19" s="25" t="n"/>
       <c r="BK19" s="26" t="n">
         <v>-125</v>
       </c>
-      <c r="BL19" s="39" t="n">
+      <c r="BL19" s="27" t="n">
         <v>1.8</v>
       </c>
       <c r="BM19" s="28" t="n">
@@ -6315,18 +6402,30 @@
         <v>0.552239</v>
       </c>
       <c r="BO19" s="28" t="n"/>
-      <c r="BP19" s="38" t="n"/>
-      <c r="BQ19" s="39" t="n"/>
+      <c r="BP19" s="25" t="n"/>
+      <c r="BQ19" s="27" t="n"/>
       <c r="BR19" s="28" t="n"/>
       <c r="BS19" s="28" t="n"/>
       <c r="BT19" s="28" t="n"/>
-      <c r="BU19" s="38" t="n"/>
+      <c r="BU19" s="25" t="n"/>
       <c r="BV19" s="29" t="n"/>
       <c r="BW19" s="24" t="n"/>
-      <c r="BX19" s="40" t="n"/>
-      <c r="BY19" s="39" t="n"/>
-      <c r="BZ19" s="24" t="n"/>
-      <c r="CA19" s="31" t="n"/>
+      <c r="BX19" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY19" s="27" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="BZ19" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-19T21:31:35.195059Z</t>
+        </is>
+      </c>
+      <c r="CA19" s="31" t="inlineStr">
+        <is>
+          <t>fixed one-unit hypothetical scoring; no real exposure or execution</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="36" customHeight="1">
       <c r="A20" s="24" t="inlineStr">
@@ -6374,7 +6473,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J20" s="38" t="n"/>
+      <c r="J20" s="25" t="n"/>
       <c r="K20" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -6383,7 +6482,7 @@
       <c r="L20" s="26" t="n">
         <v>106</v>
       </c>
-      <c r="M20" s="39" t="n">
+      <c r="M20" s="27" t="n">
         <v>2.06</v>
       </c>
       <c r="N20" s="28" t="n">
@@ -6400,7 +6499,7 @@
         <v>68</v>
       </c>
       <c r="S20" s="29" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="T20" s="24" t="inlineStr">
         <is>
@@ -6409,18 +6508,32 @@
       </c>
       <c r="U20" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V20" s="24" t="n"/>
-      <c r="W20" s="26" t="n"/>
-      <c r="X20" s="26" t="n"/>
-      <c r="Y20" s="38" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V20" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W20" s="26" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y20" s="25" t="n"/>
       <c r="Z20" s="26" t="n"/>
       <c r="AA20" s="28" t="n"/>
       <c r="AB20" s="28" t="n"/>
-      <c r="AC20" s="40" t="n"/>
-      <c r="AD20" s="24" t="n"/>
+      <c r="AC20" s="30" t="n">
+        <v>0.795</v>
+      </c>
+      <c r="AD20" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-19T21:31:35.380420Z</t>
+        </is>
+      </c>
       <c r="AE20" s="31" t="inlineStr">
         <is>
           <t>Learned LR call at threshold 0.5100; executable ask 0.4850 (aec-mlb-sd-kc-2026-07-19).</t>
@@ -6550,11 +6663,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ20" s="38" t="n"/>
+      <c r="BJ20" s="25" t="n"/>
       <c r="BK20" s="26" t="n">
         <v>106</v>
       </c>
-      <c r="BL20" s="39" t="n">
+      <c r="BL20" s="27" t="n">
         <v>2.06</v>
       </c>
       <c r="BM20" s="28" t="n">
@@ -6564,18 +6677,30 @@
         <v>0.482587</v>
       </c>
       <c r="BO20" s="28" t="n"/>
-      <c r="BP20" s="38" t="n"/>
-      <c r="BQ20" s="39" t="n"/>
+      <c r="BP20" s="25" t="n"/>
+      <c r="BQ20" s="27" t="n"/>
       <c r="BR20" s="28" t="n"/>
       <c r="BS20" s="28" t="n"/>
       <c r="BT20" s="28" t="n"/>
-      <c r="BU20" s="38" t="n"/>
+      <c r="BU20" s="25" t="n"/>
       <c r="BV20" s="29" t="n"/>
       <c r="BW20" s="24" t="n"/>
-      <c r="BX20" s="40" t="n"/>
-      <c r="BY20" s="39" t="n"/>
-      <c r="BZ20" s="24" t="n"/>
-      <c r="CA20" s="31" t="n"/>
+      <c r="BX20" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY20" s="27" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="BZ20" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-19T21:31:35.380420Z</t>
+        </is>
+      </c>
+      <c r="CA20" s="31" t="inlineStr">
+        <is>
+          <t>fixed one-unit hypothetical scoring; no real exposure or execution</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="36" customHeight="1">
       <c r="A21" s="24" t="inlineStr">
@@ -6623,7 +6748,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J21" s="38" t="n"/>
+      <c r="J21" s="25" t="n"/>
       <c r="K21" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -6632,11 +6757,11 @@
       <c r="L21" s="26" t="n">
         <v>-106</v>
       </c>
-      <c r="M21" s="39" t="n">
-        <v>1.941748</v>
+      <c r="M21" s="27" t="n">
+        <v>1.943396</v>
       </c>
       <c r="N21" s="28" t="n">
-        <v>0.515</v>
+        <v>0.514563</v>
       </c>
       <c r="O21" s="28" t="n">
         <v>0.550333</v>
@@ -6645,7 +6770,7 @@
         <v>0.05</v>
       </c>
       <c r="Q21" s="28" t="n">
-        <v>0.035333</v>
+        <v>0.03577</v>
       </c>
       <c r="R21" s="26" t="n"/>
       <c r="S21" s="29" t="n">
@@ -6666,14 +6791,18 @@
           <t>win</t>
         </is>
       </c>
-      <c r="W21" s="26" t="n"/>
-      <c r="X21" s="26" t="n"/>
-      <c r="Y21" s="38" t="n"/>
+      <c r="W21" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" s="26" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y21" s="25" t="n"/>
       <c r="Z21" s="26" t="n"/>
       <c r="AA21" s="28" t="n"/>
       <c r="AB21" s="28" t="n"/>
-      <c r="AC21" s="40" t="n">
-        <v>0.9417</v>
+      <c r="AC21" s="30" t="n">
+        <v>0.9434</v>
       </c>
       <c r="AD21" s="24" t="inlineStr">
         <is>
@@ -6719,30 +6848,30 @@
         </is>
       </c>
       <c r="BI21" s="24" t="n"/>
-      <c r="BJ21" s="38" t="n"/>
+      <c r="BJ21" s="25" t="n"/>
       <c r="BK21" s="26" t="n">
         <v>-106</v>
       </c>
-      <c r="BL21" s="39" t="n">
-        <v>1.941748</v>
+      <c r="BL21" s="27" t="n">
+        <v>1.943396</v>
       </c>
       <c r="BM21" s="28" t="n">
-        <v>0.515</v>
+        <v>0.514563</v>
       </c>
       <c r="BN21" s="28" t="n">
         <v>0.5124379999999999</v>
       </c>
       <c r="BO21" s="28" t="n"/>
-      <c r="BP21" s="38" t="n"/>
-      <c r="BQ21" s="39" t="n"/>
+      <c r="BP21" s="25" t="n"/>
+      <c r="BQ21" s="27" t="n"/>
       <c r="BR21" s="28" t="n"/>
       <c r="BS21" s="28" t="n"/>
       <c r="BT21" s="28" t="n"/>
-      <c r="BU21" s="38" t="n"/>
+      <c r="BU21" s="25" t="n"/>
       <c r="BV21" s="29" t="n"/>
       <c r="BW21" s="24" t="n"/>
-      <c r="BX21" s="40" t="n"/>
-      <c r="BY21" s="39" t="n"/>
+      <c r="BX21" s="30" t="n"/>
+      <c r="BY21" s="27" t="n"/>
       <c r="BZ21" s="24" t="n"/>
       <c r="CA21" s="31" t="n"/>
     </row>
@@ -6792,7 +6921,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J22" s="38" t="n"/>
+      <c r="J22" s="25" t="n"/>
       <c r="K22" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -6801,11 +6930,11 @@
       <c r="L22" s="26" t="n">
         <v>-106</v>
       </c>
-      <c r="M22" s="39" t="n">
-        <v>1.941748</v>
+      <c r="M22" s="27" t="n">
+        <v>1.943396</v>
       </c>
       <c r="N22" s="28" t="n">
-        <v>0.515</v>
+        <v>0.514563</v>
       </c>
       <c r="O22" s="28" t="n">
         <v>0.550333</v>
@@ -6814,7 +6943,7 @@
         <v>0.05</v>
       </c>
       <c r="Q22" s="28" t="n">
-        <v>0.035333</v>
+        <v>0.03577</v>
       </c>
       <c r="R22" s="26" t="n"/>
       <c r="S22" s="29" t="n">
@@ -6835,14 +6964,18 @@
           <t>win</t>
         </is>
       </c>
-      <c r="W22" s="26" t="n"/>
-      <c r="X22" s="26" t="n"/>
-      <c r="Y22" s="38" t="n"/>
+      <c r="W22" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="X22" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y22" s="25" t="n"/>
       <c r="Z22" s="26" t="n"/>
       <c r="AA22" s="28" t="n"/>
       <c r="AB22" s="28" t="n"/>
-      <c r="AC22" s="40" t="n">
-        <v>0.9417</v>
+      <c r="AC22" s="30" t="n">
+        <v>0.9434</v>
       </c>
       <c r="AD22" s="24" t="inlineStr">
         <is>
@@ -6888,30 +7021,30 @@
         </is>
       </c>
       <c r="BI22" s="24" t="n"/>
-      <c r="BJ22" s="38" t="n"/>
+      <c r="BJ22" s="25" t="n"/>
       <c r="BK22" s="26" t="n">
         <v>-106</v>
       </c>
-      <c r="BL22" s="39" t="n">
-        <v>1.941748</v>
+      <c r="BL22" s="27" t="n">
+        <v>1.943396</v>
       </c>
       <c r="BM22" s="28" t="n">
-        <v>0.515</v>
+        <v>0.514563</v>
       </c>
       <c r="BN22" s="28" t="n">
         <v>0.5124379999999999</v>
       </c>
       <c r="BO22" s="28" t="n"/>
-      <c r="BP22" s="38" t="n"/>
-      <c r="BQ22" s="39" t="n"/>
+      <c r="BP22" s="25" t="n"/>
+      <c r="BQ22" s="27" t="n"/>
       <c r="BR22" s="28" t="n"/>
       <c r="BS22" s="28" t="n"/>
       <c r="BT22" s="28" t="n"/>
-      <c r="BU22" s="38" t="n"/>
+      <c r="BU22" s="25" t="n"/>
       <c r="BV22" s="29" t="n"/>
       <c r="BW22" s="24" t="n"/>
-      <c r="BX22" s="40" t="n"/>
-      <c r="BY22" s="39" t="n"/>
+      <c r="BX22" s="30" t="n"/>
+      <c r="BY22" s="27" t="n"/>
       <c r="BZ22" s="24" t="n"/>
       <c r="CA22" s="31" t="n"/>
     </row>
@@ -6961,7 +7094,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J23" s="38" t="n"/>
+      <c r="J23" s="25" t="n"/>
       <c r="K23" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -6970,11 +7103,11 @@
       <c r="L23" s="26" t="n">
         <v>-141</v>
       </c>
-      <c r="M23" s="39" t="n">
-        <v>1.709402</v>
+      <c r="M23" s="27" t="n">
+        <v>1.70922</v>
       </c>
       <c r="N23" s="28" t="n">
-        <v>0.585</v>
+        <v>0.585062</v>
       </c>
       <c r="O23" s="28" t="n">
         <v>0.616198</v>
@@ -6983,7 +7116,7 @@
         <v>0.05</v>
       </c>
       <c r="Q23" s="28" t="n">
-        <v>0.031198</v>
+        <v>0.031136</v>
       </c>
       <c r="R23" s="26" t="n"/>
       <c r="S23" s="29" t="n">
@@ -7004,14 +7137,18 @@
           <t>win</t>
         </is>
       </c>
-      <c r="W23" s="26" t="n"/>
-      <c r="X23" s="26" t="n"/>
-      <c r="Y23" s="38" t="n"/>
+      <c r="W23" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X23" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y23" s="25" t="n"/>
       <c r="Z23" s="26" t="n"/>
       <c r="AA23" s="28" t="n"/>
       <c r="AB23" s="28" t="n"/>
-      <c r="AC23" s="40" t="n">
-        <v>1.2415</v>
+      <c r="AC23" s="30" t="n">
+        <v>1.2411</v>
       </c>
       <c r="AD23" s="24" t="inlineStr">
         <is>
@@ -7057,30 +7194,30 @@
         </is>
       </c>
       <c r="BI23" s="24" t="n"/>
-      <c r="BJ23" s="38" t="n"/>
+      <c r="BJ23" s="25" t="n"/>
       <c r="BK23" s="26" t="n">
         <v>-141</v>
       </c>
-      <c r="BL23" s="39" t="n">
-        <v>1.709402</v>
+      <c r="BL23" s="27" t="n">
+        <v>1.70922</v>
       </c>
       <c r="BM23" s="28" t="n">
-        <v>0.585</v>
+        <v>0.585062</v>
       </c>
       <c r="BN23" s="28" t="n">
         <v>0.58209</v>
       </c>
       <c r="BO23" s="28" t="n"/>
-      <c r="BP23" s="38" t="n"/>
-      <c r="BQ23" s="39" t="n"/>
+      <c r="BP23" s="25" t="n"/>
+      <c r="BQ23" s="27" t="n"/>
       <c r="BR23" s="28" t="n"/>
       <c r="BS23" s="28" t="n"/>
       <c r="BT23" s="28" t="n"/>
-      <c r="BU23" s="38" t="n"/>
+      <c r="BU23" s="25" t="n"/>
       <c r="BV23" s="29" t="n"/>
       <c r="BW23" s="24" t="n"/>
-      <c r="BX23" s="40" t="n"/>
-      <c r="BY23" s="39" t="n"/>
+      <c r="BX23" s="30" t="n"/>
+      <c r="BY23" s="27" t="n"/>
       <c r="BZ23" s="24" t="n"/>
       <c r="CA23" s="31" t="n"/>
     </row>
@@ -7130,7 +7267,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J24" s="38" t="n"/>
+      <c r="J24" s="25" t="n"/>
       <c r="K24" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -7139,11 +7276,11 @@
       <c r="L24" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="M24" s="39" t="n">
-        <v>1.754386</v>
+      <c r="M24" s="27" t="n">
+        <v>1.75188</v>
       </c>
       <c r="N24" s="28" t="n">
-        <v>0.57</v>
+        <v>0.570815</v>
       </c>
       <c r="O24" s="28" t="n">
         <v>0.60271</v>
@@ -7152,7 +7289,7 @@
         <v>0.05</v>
       </c>
       <c r="Q24" s="28" t="n">
-        <v>0.03271</v>
+        <v>0.031895</v>
       </c>
       <c r="R24" s="26" t="n"/>
       <c r="S24" s="29" t="n">
@@ -7173,13 +7310,17 @@
           <t>loss</t>
         </is>
       </c>
-      <c r="W24" s="26" t="n"/>
-      <c r="X24" s="26" t="n"/>
-      <c r="Y24" s="38" t="n"/>
+      <c r="W24" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="X24" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y24" s="25" t="n"/>
       <c r="Z24" s="26" t="n"/>
       <c r="AA24" s="28" t="n"/>
       <c r="AB24" s="28" t="n"/>
-      <c r="AC24" s="40" t="n">
+      <c r="AC24" s="30" t="n">
         <v>-1.5</v>
       </c>
       <c r="AD24" s="24" t="inlineStr">
@@ -7226,30 +7367,30 @@
         </is>
       </c>
       <c r="BI24" s="24" t="n"/>
-      <c r="BJ24" s="38" t="n"/>
+      <c r="BJ24" s="25" t="n"/>
       <c r="BK24" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="BL24" s="39" t="n">
-        <v>1.754386</v>
+      <c r="BL24" s="27" t="n">
+        <v>1.75188</v>
       </c>
       <c r="BM24" s="28" t="n">
-        <v>0.57</v>
+        <v>0.570815</v>
       </c>
       <c r="BN24" s="28" t="n">
         <v>0.567164</v>
       </c>
       <c r="BO24" s="28" t="n"/>
-      <c r="BP24" s="38" t="n"/>
-      <c r="BQ24" s="39" t="n"/>
+      <c r="BP24" s="25" t="n"/>
+      <c r="BQ24" s="27" t="n"/>
       <c r="BR24" s="28" t="n"/>
       <c r="BS24" s="28" t="n"/>
       <c r="BT24" s="28" t="n"/>
-      <c r="BU24" s="38" t="n"/>
+      <c r="BU24" s="25" t="n"/>
       <c r="BV24" s="29" t="n"/>
       <c r="BW24" s="24" t="n"/>
-      <c r="BX24" s="40" t="n"/>
-      <c r="BY24" s="39" t="n"/>
+      <c r="BX24" s="30" t="n"/>
+      <c r="BY24" s="27" t="n"/>
       <c r="BZ24" s="24" t="n"/>
       <c r="CA24" s="31" t="n"/>
     </row>
@@ -7299,7 +7440,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J25" s="38" t="n"/>
+      <c r="J25" s="25" t="n"/>
       <c r="K25" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -7308,11 +7449,11 @@
       <c r="L25" s="26" t="n">
         <v>104</v>
       </c>
-      <c r="M25" s="39" t="n">
-        <v>2.040816</v>
+      <c r="M25" s="27" t="n">
+        <v>2.04</v>
       </c>
       <c r="N25" s="28" t="n">
-        <v>0.49</v>
+        <v>0.490196</v>
       </c>
       <c r="O25" s="28" t="n">
         <v>0.582862</v>
@@ -7321,7 +7462,7 @@
         <v>0.05</v>
       </c>
       <c r="Q25" s="28" t="n">
-        <v>0.092862</v>
+        <v>0.092666</v>
       </c>
       <c r="R25" s="26" t="n"/>
       <c r="S25" s="29" t="n">
@@ -7342,14 +7483,18 @@
           <t>win</t>
         </is>
       </c>
-      <c r="W25" s="26" t="n"/>
-      <c r="X25" s="26" t="n"/>
-      <c r="Y25" s="38" t="n"/>
+      <c r="W25" s="26" t="n">
+        <v>7</v>
+      </c>
+      <c r="X25" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y25" s="25" t="n"/>
       <c r="Z25" s="26" t="n"/>
       <c r="AA25" s="28" t="n"/>
       <c r="AB25" s="28" t="n"/>
-      <c r="AC25" s="40" t="n">
-        <v>1.301</v>
+      <c r="AC25" s="30" t="n">
+        <v>1.3</v>
       </c>
       <c r="AD25" s="24" t="inlineStr">
         <is>
@@ -7395,30 +7540,30 @@
         </is>
       </c>
       <c r="BI25" s="24" t="n"/>
-      <c r="BJ25" s="38" t="n"/>
+      <c r="BJ25" s="25" t="n"/>
       <c r="BK25" s="26" t="n">
         <v>104</v>
       </c>
-      <c r="BL25" s="39" t="n">
-        <v>2.040816</v>
+      <c r="BL25" s="27" t="n">
+        <v>2.04</v>
       </c>
       <c r="BM25" s="28" t="n">
-        <v>0.49</v>
+        <v>0.490196</v>
       </c>
       <c r="BN25" s="28" t="n">
         <v>0.487562</v>
       </c>
       <c r="BO25" s="28" t="n"/>
-      <c r="BP25" s="38" t="n"/>
-      <c r="BQ25" s="39" t="n"/>
+      <c r="BP25" s="25" t="n"/>
+      <c r="BQ25" s="27" t="n"/>
       <c r="BR25" s="28" t="n"/>
       <c r="BS25" s="28" t="n"/>
       <c r="BT25" s="28" t="n"/>
-      <c r="BU25" s="38" t="n"/>
+      <c r="BU25" s="25" t="n"/>
       <c r="BV25" s="29" t="n"/>
       <c r="BW25" s="24" t="n"/>
-      <c r="BX25" s="40" t="n"/>
-      <c r="BY25" s="39" t="n"/>
+      <c r="BX25" s="30" t="n"/>
+      <c r="BY25" s="27" t="n"/>
       <c r="BZ25" s="24" t="n"/>
       <c r="CA25" s="31" t="n"/>
     </row>
@@ -7468,7 +7613,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J26" s="38" t="n"/>
+      <c r="J26" s="25" t="n"/>
       <c r="K26" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -7477,11 +7622,11 @@
       <c r="L26" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="M26" s="39" t="n">
-        <v>1.960784</v>
+      <c r="M26" s="27" t="n">
+        <v>1.961538</v>
       </c>
       <c r="N26" s="28" t="n">
-        <v>0.51</v>
+        <v>0.509804</v>
       </c>
       <c r="O26" s="28" t="n">
         <v>0.550233</v>
@@ -7490,7 +7635,7 @@
         <v>0.05</v>
       </c>
       <c r="Q26" s="28" t="n">
-        <v>0.040233</v>
+        <v>0.040429</v>
       </c>
       <c r="R26" s="26" t="n"/>
       <c r="S26" s="29" t="n">
@@ -7511,14 +7656,18 @@
           <t>win</t>
         </is>
       </c>
-      <c r="W26" s="26" t="n"/>
-      <c r="X26" s="26" t="n"/>
-      <c r="Y26" s="38" t="n"/>
+      <c r="W26" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="X26" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y26" s="25" t="n"/>
       <c r="Z26" s="26" t="n"/>
       <c r="AA26" s="28" t="n"/>
       <c r="AB26" s="28" t="n"/>
-      <c r="AC26" s="40" t="n">
-        <v>0.9608</v>
+      <c r="AC26" s="30" t="n">
+        <v>0.9615</v>
       </c>
       <c r="AD26" s="24" t="inlineStr">
         <is>
@@ -7564,30 +7713,30 @@
         </is>
       </c>
       <c r="BI26" s="24" t="n"/>
-      <c r="BJ26" s="38" t="n"/>
+      <c r="BJ26" s="25" t="n"/>
       <c r="BK26" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="BL26" s="39" t="n">
-        <v>1.960784</v>
+      <c r="BL26" s="27" t="n">
+        <v>1.961538</v>
       </c>
       <c r="BM26" s="28" t="n">
-        <v>0.51</v>
+        <v>0.509804</v>
       </c>
       <c r="BN26" s="28" t="n">
         <v>0.507463</v>
       </c>
       <c r="BO26" s="28" t="n"/>
-      <c r="BP26" s="38" t="n"/>
-      <c r="BQ26" s="39" t="n"/>
+      <c r="BP26" s="25" t="n"/>
+      <c r="BQ26" s="27" t="n"/>
       <c r="BR26" s="28" t="n"/>
       <c r="BS26" s="28" t="n"/>
       <c r="BT26" s="28" t="n"/>
-      <c r="BU26" s="38" t="n"/>
+      <c r="BU26" s="25" t="n"/>
       <c r="BV26" s="29" t="n"/>
       <c r="BW26" s="24" t="n"/>
-      <c r="BX26" s="40" t="n"/>
-      <c r="BY26" s="39" t="n"/>
+      <c r="BX26" s="30" t="n"/>
+      <c r="BY26" s="27" t="n"/>
       <c r="BZ26" s="24" t="n"/>
       <c r="CA26" s="31" t="n"/>
     </row>
@@ -7637,7 +7786,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J27" s="38" t="n"/>
+      <c r="J27" s="25" t="n"/>
       <c r="K27" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -7646,11 +7795,11 @@
       <c r="L27" s="26" t="n">
         <v>120</v>
       </c>
-      <c r="M27" s="39" t="n">
-        <v>2.197802</v>
+      <c r="M27" s="27" t="n">
+        <v>2.2</v>
       </c>
       <c r="N27" s="28" t="n">
-        <v>0.455</v>
+        <v>0.454545</v>
       </c>
       <c r="O27" s="28" t="n">
         <v>0.530299</v>
@@ -7659,7 +7808,7 @@
         <v>0.05</v>
       </c>
       <c r="Q27" s="28" t="n">
-        <v>0.075299</v>
+        <v>0.075754</v>
       </c>
       <c r="R27" s="26" t="n"/>
       <c r="S27" s="29" t="n">
@@ -7680,13 +7829,17 @@
           <t>loss</t>
         </is>
       </c>
-      <c r="W27" s="26" t="n"/>
-      <c r="X27" s="26" t="n"/>
-      <c r="Y27" s="38" t="n"/>
+      <c r="W27" s="26" t="n">
+        <v>23</v>
+      </c>
+      <c r="X27" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y27" s="25" t="n"/>
       <c r="Z27" s="26" t="n"/>
       <c r="AA27" s="28" t="n"/>
       <c r="AB27" s="28" t="n"/>
-      <c r="AC27" s="40" t="n">
+      <c r="AC27" s="30" t="n">
         <v>-0.75</v>
       </c>
       <c r="AD27" s="24" t="inlineStr">
@@ -7733,30 +7886,30 @@
         </is>
       </c>
       <c r="BI27" s="24" t="n"/>
-      <c r="BJ27" s="38" t="n"/>
+      <c r="BJ27" s="25" t="n"/>
       <c r="BK27" s="26" t="n">
         <v>120</v>
       </c>
-      <c r="BL27" s="39" t="n">
-        <v>2.197802</v>
+      <c r="BL27" s="27" t="n">
+        <v>2.2</v>
       </c>
       <c r="BM27" s="28" t="n">
-        <v>0.455</v>
+        <v>0.454545</v>
       </c>
       <c r="BN27" s="28" t="n">
         <v>0.452736</v>
       </c>
       <c r="BO27" s="28" t="n"/>
-      <c r="BP27" s="38" t="n"/>
-      <c r="BQ27" s="39" t="n"/>
+      <c r="BP27" s="25" t="n"/>
+      <c r="BQ27" s="27" t="n"/>
       <c r="BR27" s="28" t="n"/>
       <c r="BS27" s="28" t="n"/>
       <c r="BT27" s="28" t="n"/>
-      <c r="BU27" s="38" t="n"/>
+      <c r="BU27" s="25" t="n"/>
       <c r="BV27" s="29" t="n"/>
       <c r="BW27" s="24" t="n"/>
-      <c r="BX27" s="40" t="n"/>
-      <c r="BY27" s="39" t="n"/>
+      <c r="BX27" s="30" t="n"/>
+      <c r="BY27" s="27" t="n"/>
       <c r="BZ27" s="24" t="n"/>
       <c r="CA27" s="31" t="n"/>
     </row>
@@ -7806,7 +7959,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J28" s="38" t="n"/>
+      <c r="J28" s="25" t="n"/>
       <c r="K28" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -7815,7 +7968,7 @@
       <c r="L28" s="26" t="n">
         <v>100</v>
       </c>
-      <c r="M28" s="39" t="n">
+      <c r="M28" s="27" t="n">
         <v>2</v>
       </c>
       <c r="N28" s="28" t="n">
@@ -7849,13 +8002,17 @@
           <t>loss</t>
         </is>
       </c>
-      <c r="W28" s="26" t="n"/>
-      <c r="X28" s="26" t="n"/>
-      <c r="Y28" s="38" t="n"/>
+      <c r="W28" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="X28" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y28" s="25" t="n"/>
       <c r="Z28" s="26" t="n"/>
       <c r="AA28" s="28" t="n"/>
       <c r="AB28" s="28" t="n"/>
-      <c r="AC28" s="40" t="n">
+      <c r="AC28" s="30" t="n">
         <v>-0.75</v>
       </c>
       <c r="AD28" s="24" t="inlineStr">
@@ -7902,11 +8059,11 @@
         </is>
       </c>
       <c r="BI28" s="24" t="n"/>
-      <c r="BJ28" s="38" t="n"/>
+      <c r="BJ28" s="25" t="n"/>
       <c r="BK28" s="26" t="n">
         <v>100</v>
       </c>
-      <c r="BL28" s="39" t="n">
+      <c r="BL28" s="27" t="n">
         <v>2</v>
       </c>
       <c r="BM28" s="28" t="n">
@@ -7916,16 +8073,16 @@
         <v>0.497512</v>
       </c>
       <c r="BO28" s="28" t="n"/>
-      <c r="BP28" s="38" t="n"/>
-      <c r="BQ28" s="39" t="n"/>
+      <c r="BP28" s="25" t="n"/>
+      <c r="BQ28" s="27" t="n"/>
       <c r="BR28" s="28" t="n"/>
       <c r="BS28" s="28" t="n"/>
       <c r="BT28" s="28" t="n"/>
-      <c r="BU28" s="38" t="n"/>
+      <c r="BU28" s="25" t="n"/>
       <c r="BV28" s="29" t="n"/>
       <c r="BW28" s="24" t="n"/>
-      <c r="BX28" s="40" t="n"/>
-      <c r="BY28" s="39" t="n"/>
+      <c r="BX28" s="30" t="n"/>
+      <c r="BY28" s="27" t="n"/>
       <c r="BZ28" s="24" t="n"/>
       <c r="CA28" s="31" t="n"/>
     </row>
@@ -7975,7 +8132,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J29" s="38" t="n"/>
+      <c r="J29" s="25" t="n"/>
       <c r="K29" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -7984,7 +8141,7 @@
       <c r="L29" s="26" t="n">
         <v>108</v>
       </c>
-      <c r="M29" s="39" t="n">
+      <c r="M29" s="27" t="n">
         <v>2.08</v>
       </c>
       <c r="N29" s="28" t="n">
@@ -8001,7 +8158,7 @@
         <v>93</v>
       </c>
       <c r="S29" s="29" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T29" s="24" t="inlineStr">
         <is>
@@ -8010,18 +8167,32 @@
       </c>
       <c r="U29" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V29" s="24" t="n"/>
-      <c r="W29" s="26" t="n"/>
-      <c r="X29" s="26" t="n"/>
-      <c r="Y29" s="38" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V29" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W29" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="X29" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y29" s="25" t="n"/>
       <c r="Z29" s="26" t="n"/>
       <c r="AA29" s="28" t="n"/>
       <c r="AB29" s="28" t="n"/>
-      <c r="AC29" s="40" t="n"/>
-      <c r="AD29" s="24" t="n"/>
+      <c r="AC29" s="30" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AD29" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-19T21:31:35.621312Z</t>
+        </is>
+      </c>
       <c r="AE29" s="31" t="inlineStr">
         <is>
           <t>Learned LR call at threshold 0.5150; executable ask 0.4800 (aec-mlb-tex-atl-2026-07-19).</t>
@@ -8151,11 +8322,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ29" s="38" t="n"/>
+      <c r="BJ29" s="25" t="n"/>
       <c r="BK29" s="26" t="n">
         <v>108</v>
       </c>
-      <c r="BL29" s="39" t="n">
+      <c r="BL29" s="27" t="n">
         <v>2.08</v>
       </c>
       <c r="BM29" s="28" t="n">
@@ -8165,18 +8336,30 @@
         <v>0.477612</v>
       </c>
       <c r="BO29" s="28" t="n"/>
-      <c r="BP29" s="38" t="n"/>
-      <c r="BQ29" s="39" t="n"/>
+      <c r="BP29" s="25" t="n"/>
+      <c r="BQ29" s="27" t="n"/>
       <c r="BR29" s="28" t="n"/>
       <c r="BS29" s="28" t="n"/>
       <c r="BT29" s="28" t="n"/>
-      <c r="BU29" s="38" t="n"/>
+      <c r="BU29" s="25" t="n"/>
       <c r="BV29" s="29" t="n"/>
       <c r="BW29" s="24" t="n"/>
-      <c r="BX29" s="40" t="n"/>
-      <c r="BY29" s="39" t="n"/>
-      <c r="BZ29" s="24" t="n"/>
-      <c r="CA29" s="31" t="n"/>
+      <c r="BX29" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY29" s="27" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="BZ29" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-19T21:31:35.621312Z</t>
+        </is>
+      </c>
+      <c r="CA29" s="31" t="inlineStr">
+        <is>
+          <t>fixed one-unit hypothetical scoring; no real exposure or execution</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="36" customHeight="1">
       <c r="A30" s="24" t="inlineStr">
@@ -8224,7 +8407,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J30" s="38" t="n"/>
+      <c r="J30" s="25" t="n"/>
       <c r="K30" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -8233,7 +8416,7 @@
       <c r="L30" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="M30" s="39" t="n">
+      <c r="M30" s="27" t="n">
         <v>1.75188</v>
       </c>
       <c r="N30" s="28" t="n">
@@ -8250,7 +8433,7 @@
         <v>65</v>
       </c>
       <c r="S30" s="29" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T30" s="24" t="inlineStr">
         <is>
@@ -8259,18 +8442,32 @@
       </c>
       <c r="U30" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V30" s="24" t="n"/>
-      <c r="W30" s="26" t="n"/>
-      <c r="X30" s="26" t="n"/>
-      <c r="Y30" s="38" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V30" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W30" s="26" t="n">
+        <v>9</v>
+      </c>
+      <c r="X30" s="26" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y30" s="25" t="n"/>
       <c r="Z30" s="26" t="n"/>
       <c r="AA30" s="28" t="n"/>
       <c r="AB30" s="28" t="n"/>
-      <c r="AC30" s="40" t="n"/>
-      <c r="AD30" s="24" t="n"/>
+      <c r="AC30" s="30" t="n">
+        <v>1.1278</v>
+      </c>
+      <c r="AD30" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-19T22:14:31.386508Z</t>
+        </is>
+      </c>
       <c r="AE30" s="31" t="inlineStr">
         <is>
           <t>Learned LR call at threshold 0.5150; executable ask 0.5700 (aec-mlb-cin-col-2026-07-19).</t>
@@ -8400,11 +8597,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ30" s="38" t="n"/>
+      <c r="BJ30" s="25" t="n"/>
       <c r="BK30" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="BL30" s="39" t="n">
+      <c r="BL30" s="27" t="n">
         <v>1.75188</v>
       </c>
       <c r="BM30" s="28" t="n">
@@ -8414,18 +8611,30 @@
         <v>0.567164</v>
       </c>
       <c r="BO30" s="28" t="n"/>
-      <c r="BP30" s="38" t="n"/>
-      <c r="BQ30" s="39" t="n"/>
+      <c r="BP30" s="25" t="n"/>
+      <c r="BQ30" s="27" t="n"/>
       <c r="BR30" s="28" t="n"/>
       <c r="BS30" s="28" t="n"/>
       <c r="BT30" s="28" t="n"/>
-      <c r="BU30" s="38" t="n"/>
+      <c r="BU30" s="25" t="n"/>
       <c r="BV30" s="29" t="n"/>
       <c r="BW30" s="24" t="n"/>
-      <c r="BX30" s="40" t="n"/>
-      <c r="BY30" s="39" t="n"/>
-      <c r="BZ30" s="24" t="n"/>
-      <c r="CA30" s="31" t="n"/>
+      <c r="BX30" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY30" s="27" t="n">
+        <v>0.75188</v>
+      </c>
+      <c r="BZ30" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-19T22:14:31.386508Z</t>
+        </is>
+      </c>
+      <c r="CA30" s="31" t="inlineStr">
+        <is>
+          <t>fixed one-unit hypothetical scoring; no real exposure or execution</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="36" customHeight="1">
       <c r="A31" s="24" t="inlineStr">
@@ -8473,7 +8682,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J31" s="38" t="n"/>
+      <c r="J31" s="25" t="n"/>
       <c r="K31" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -8482,7 +8691,7 @@
       <c r="L31" s="26" t="n">
         <v>130</v>
       </c>
-      <c r="M31" s="39" t="n">
+      <c r="M31" s="27" t="n">
         <v>2.3</v>
       </c>
       <c r="N31" s="28" t="n">
@@ -8499,7 +8708,7 @@
         <v>100</v>
       </c>
       <c r="S31" s="29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T31" s="24" t="inlineStr">
         <is>
@@ -8508,18 +8717,32 @@
       </c>
       <c r="U31" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V31" s="24" t="n"/>
-      <c r="W31" s="26" t="n"/>
-      <c r="X31" s="26" t="n"/>
-      <c r="Y31" s="38" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V31" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W31" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="X31" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y31" s="25" t="n"/>
       <c r="Z31" s="26" t="n"/>
       <c r="AA31" s="28" t="n"/>
       <c r="AB31" s="28" t="n"/>
-      <c r="AC31" s="40" t="n"/>
-      <c r="AD31" s="24" t="n"/>
+      <c r="AC31" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD31" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-19T23:07:45.507453Z</t>
+        </is>
+      </c>
       <c r="AE31" s="31" t="inlineStr">
         <is>
           <t>Learned LR call at threshold 0.5150; executable ask 0.4350 (aec-mlb-wsh-ath-2026-07-19).</t>
@@ -8532,7 +8755,7 @@
       </c>
       <c r="AG31" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH31" s="24" t="n"/>
@@ -8649,11 +8872,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ31" s="38" t="n"/>
+      <c r="BJ31" s="25" t="n"/>
       <c r="BK31" s="26" t="n">
         <v>130</v>
       </c>
-      <c r="BL31" s="39" t="n">
+      <c r="BL31" s="27" t="n">
         <v>2.3</v>
       </c>
       <c r="BM31" s="28" t="n">
@@ -8663,18 +8886,2022 @@
         <v>0.432836</v>
       </c>
       <c r="BO31" s="28" t="n"/>
-      <c r="BP31" s="38" t="n"/>
-      <c r="BQ31" s="39" t="n"/>
+      <c r="BP31" s="25" t="n"/>
+      <c r="BQ31" s="27" t="n"/>
       <c r="BR31" s="28" t="n"/>
       <c r="BS31" s="28" t="n"/>
       <c r="BT31" s="28" t="n"/>
-      <c r="BU31" s="38" t="n"/>
+      <c r="BU31" s="25" t="n"/>
       <c r="BV31" s="29" t="n"/>
       <c r="BW31" s="24" t="n"/>
-      <c r="BX31" s="40" t="n"/>
-      <c r="BY31" s="39" t="n"/>
-      <c r="BZ31" s="24" t="n"/>
-      <c r="CA31" s="31" t="n"/>
+      <c r="BX31" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY31" s="27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BZ31" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-19T23:07:45.507453Z</t>
+        </is>
+      </c>
+      <c r="CA31" s="31" t="inlineStr">
+        <is>
+          <t>fixed one-unit hypothetical scoring; no real exposure or execution</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="36" customHeight="1">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>4ae204a92d8a47fc</t>
+        </is>
+      </c>
+      <c r="B32" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-19T17:18:24.670965Z</t>
+        </is>
+      </c>
+      <c r="C32" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T18:40:00-0400</t>
+        </is>
+      </c>
+      <c r="D32" s="24" t="inlineStr">
+        <is>
+          <t>401816188</t>
+        </is>
+      </c>
+      <c r="E32" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F32" s="24" t="inlineStr">
+        <is>
+          <t>Minnesota Twins</t>
+        </is>
+      </c>
+      <c r="G32" s="24" t="inlineStr">
+        <is>
+          <t>Cleveland Guardians</t>
+        </is>
+      </c>
+      <c r="H32" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I32" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J32" s="25" t="n"/>
+      <c r="K32" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L32" s="26" t="n">
+        <v>-108</v>
+      </c>
+      <c r="M32" s="27" t="n">
+        <v>1.925926</v>
+      </c>
+      <c r="N32" s="28" t="n">
+        <v>0.519231</v>
+      </c>
+      <c r="O32" s="28" t="n">
+        <v>0.583941</v>
+      </c>
+      <c r="P32" s="28" t="n"/>
+      <c r="Q32" s="28" t="n">
+        <v>0.06471</v>
+      </c>
+      <c r="R32" s="26" t="n">
+        <v>52</v>
+      </c>
+      <c r="S32" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T32" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="U32" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V32" s="24" t="n"/>
+      <c r="W32" s="26" t="n"/>
+      <c r="X32" s="26" t="n"/>
+      <c r="Y32" s="25" t="n"/>
+      <c r="Z32" s="26" t="n"/>
+      <c r="AA32" s="28" t="n"/>
+      <c r="AB32" s="28" t="n"/>
+      <c r="AC32" s="30" t="n"/>
+      <c r="AD32" s="24" t="n"/>
+      <c r="AE32" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5150; executable ask 0.5200 (aec-mlb-min-cle-2026-07-20).</t>
+        </is>
+      </c>
+      <c r="AF32" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
+        </is>
+      </c>
+      <c r="AG32" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH32" s="24" t="n"/>
+      <c r="AI32" s="31" t="n"/>
+      <c r="AJ32" s="31" t="n"/>
+      <c r="AK32" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL32" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM32" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN32" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO32" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP32" s="24" t="inlineStr">
+        <is>
+          <t>mlb-min</t>
+        </is>
+      </c>
+      <c r="AQ32" s="24" t="inlineStr">
+        <is>
+          <t>Minnesota Twins</t>
+        </is>
+      </c>
+      <c r="AR32" s="24" t="inlineStr">
+        <is>
+          <t>Minnesota Twins</t>
+        </is>
+      </c>
+      <c r="AS32" s="24" t="inlineStr">
+        <is>
+          <t>mlb-cle</t>
+        </is>
+      </c>
+      <c r="AT32" s="24" t="inlineStr">
+        <is>
+          <t>Cleveland Guardians</t>
+        </is>
+      </c>
+      <c r="AU32" s="24" t="inlineStr">
+        <is>
+          <t>Cleveland Guardians</t>
+        </is>
+      </c>
+      <c r="AV32" s="24" t="n"/>
+      <c r="AW32" s="24" t="n"/>
+      <c r="AX32" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY32" s="24" t="n"/>
+      <c r="AZ32" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA32" s="24" t="inlineStr">
+        <is>
+          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+        </is>
+      </c>
+      <c r="BB32" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC32" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BD32" s="24" t="inlineStr">
+        <is>
+          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+        </is>
+      </c>
+      <c r="BE32" s="24" t="inlineStr">
+        <is>
+          <t>19929f0cfbcdf2ed</t>
+        </is>
+      </c>
+      <c r="BF32" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG32" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BH32" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-19T17:17:28.488847Z</t>
+        </is>
+      </c>
+      <c r="BI32" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ32" s="25" t="n"/>
+      <c r="BK32" s="26" t="n">
+        <v>-108</v>
+      </c>
+      <c r="BL32" s="27" t="n">
+        <v>1.925926</v>
+      </c>
+      <c r="BM32" s="28" t="n">
+        <v>0.519231</v>
+      </c>
+      <c r="BN32" s="28" t="n">
+        <v>0.517413</v>
+      </c>
+      <c r="BO32" s="28" t="n"/>
+      <c r="BP32" s="25" t="n"/>
+      <c r="BQ32" s="27" t="n"/>
+      <c r="BR32" s="28" t="n"/>
+      <c r="BS32" s="28" t="n"/>
+      <c r="BT32" s="28" t="n"/>
+      <c r="BU32" s="25" t="n"/>
+      <c r="BV32" s="29" t="n"/>
+      <c r="BW32" s="24" t="n"/>
+      <c r="BX32" s="30" t="n"/>
+      <c r="BY32" s="27" t="n"/>
+      <c r="BZ32" s="24" t="n"/>
+      <c r="CA32" s="31" t="n"/>
+    </row>
+    <row r="33" ht="36" customHeight="1">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>279e8c5dd40743fe</t>
+        </is>
+      </c>
+      <c r="B33" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-19T17:18:24.670965Z</t>
+        </is>
+      </c>
+      <c r="C33" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T19:00:00-0400</t>
+        </is>
+      </c>
+      <c r="D33" s="24" t="inlineStr">
+        <is>
+          <t>401816187</t>
+        </is>
+      </c>
+      <c r="E33" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F33" s="24" t="inlineStr">
+        <is>
+          <t>Los Angeles Dodgers</t>
+        </is>
+      </c>
+      <c r="G33" s="24" t="inlineStr">
+        <is>
+          <t>Philadelphia Phillies</t>
+        </is>
+      </c>
+      <c r="H33" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I33" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J33" s="25" t="n"/>
+      <c r="K33" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L33" s="26" t="n">
+        <v>135</v>
+      </c>
+      <c r="M33" s="27" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="N33" s="28" t="n">
+        <v>0.425532</v>
+      </c>
+      <c r="O33" s="28" t="n">
+        <v>0.535498</v>
+      </c>
+      <c r="P33" s="28" t="n"/>
+      <c r="Q33" s="28" t="n">
+        <v>0.109966</v>
+      </c>
+      <c r="R33" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S33" s="29" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="T33" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="U33" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V33" s="24" t="n"/>
+      <c r="W33" s="26" t="n"/>
+      <c r="X33" s="26" t="n"/>
+      <c r="Y33" s="25" t="n"/>
+      <c r="Z33" s="26" t="n"/>
+      <c r="AA33" s="28" t="n"/>
+      <c r="AB33" s="28" t="n"/>
+      <c r="AC33" s="30" t="n"/>
+      <c r="AD33" s="24" t="n"/>
+      <c r="AE33" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5150; executable ask 0.4250 (aec-mlb-lad-phi-2026-07-20).</t>
+        </is>
+      </c>
+      <c r="AF33" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
+        </is>
+      </c>
+      <c r="AG33" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH33" s="24" t="n"/>
+      <c r="AI33" s="31" t="n"/>
+      <c r="AJ33" s="31" t="n"/>
+      <c r="AK33" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL33" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM33" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN33" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO33" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LARGE_DISAGREEMENT_REVIEW</t>
+        </is>
+      </c>
+      <c r="AP33" s="24" t="inlineStr">
+        <is>
+          <t>mlb-lad</t>
+        </is>
+      </c>
+      <c r="AQ33" s="24" t="inlineStr">
+        <is>
+          <t>Los Angeles Dodgers</t>
+        </is>
+      </c>
+      <c r="AR33" s="24" t="inlineStr">
+        <is>
+          <t>Los Angeles Dodgers</t>
+        </is>
+      </c>
+      <c r="AS33" s="24" t="inlineStr">
+        <is>
+          <t>mlb-phi</t>
+        </is>
+      </c>
+      <c r="AT33" s="24" t="inlineStr">
+        <is>
+          <t>Philadelphia Phillies</t>
+        </is>
+      </c>
+      <c r="AU33" s="24" t="inlineStr">
+        <is>
+          <t>Philadelphia Phillies</t>
+        </is>
+      </c>
+      <c r="AV33" s="24" t="n"/>
+      <c r="AW33" s="24" t="n"/>
+      <c r="AX33" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY33" s="24" t="n"/>
+      <c r="AZ33" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA33" s="24" t="inlineStr">
+        <is>
+          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+        </is>
+      </c>
+      <c r="BB33" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC33" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BD33" s="24" t="inlineStr">
+        <is>
+          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+        </is>
+      </c>
+      <c r="BE33" s="24" t="inlineStr">
+        <is>
+          <t>2e2c2111662001b9</t>
+        </is>
+      </c>
+      <c r="BF33" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG33" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BH33" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-19T17:17:33.614115Z</t>
+        </is>
+      </c>
+      <c r="BI33" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ33" s="25" t="n"/>
+      <c r="BK33" s="26" t="n">
+        <v>135</v>
+      </c>
+      <c r="BL33" s="27" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BM33" s="28" t="n">
+        <v>0.425532</v>
+      </c>
+      <c r="BN33" s="28" t="n">
+        <v>0.422886</v>
+      </c>
+      <c r="BO33" s="28" t="n"/>
+      <c r="BP33" s="25" t="n"/>
+      <c r="BQ33" s="27" t="n"/>
+      <c r="BR33" s="28" t="n"/>
+      <c r="BS33" s="28" t="n"/>
+      <c r="BT33" s="28" t="n"/>
+      <c r="BU33" s="25" t="n"/>
+      <c r="BV33" s="29" t="n"/>
+      <c r="BW33" s="24" t="n"/>
+      <c r="BX33" s="30" t="n"/>
+      <c r="BY33" s="27" t="n"/>
+      <c r="BZ33" s="24" t="n"/>
+      <c r="CA33" s="31" t="n"/>
+    </row>
+    <row r="34" ht="36" customHeight="1">
+      <c r="A34" s="24" t="inlineStr">
+        <is>
+          <t>5d2cb57b32f14866</t>
+        </is>
+      </c>
+      <c r="B34" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-19T17:18:24.670965Z</t>
+        </is>
+      </c>
+      <c r="C34" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T19:05:00-0400</t>
+        </is>
+      </c>
+      <c r="D34" s="24" t="inlineStr">
+        <is>
+          <t>401816189</t>
+        </is>
+      </c>
+      <c r="E34" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F34" s="24" t="inlineStr">
+        <is>
+          <t>Pittsburgh Pirates</t>
+        </is>
+      </c>
+      <c r="G34" s="24" t="inlineStr">
+        <is>
+          <t>New York Yankees</t>
+        </is>
+      </c>
+      <c r="H34" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I34" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J34" s="25" t="n"/>
+      <c r="K34" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L34" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="M34" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="N34" s="28" t="n">
+        <v>0.5594710000000001</v>
+      </c>
+      <c r="O34" s="28" t="n">
+        <v>0.58711</v>
+      </c>
+      <c r="P34" s="28" t="n"/>
+      <c r="Q34" s="28" t="n">
+        <v>0.027639</v>
+      </c>
+      <c r="R34" s="26" t="n">
+        <v>34</v>
+      </c>
+      <c r="S34" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T34" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="U34" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V34" s="24" t="n"/>
+      <c r="W34" s="26" t="n"/>
+      <c r="X34" s="26" t="n"/>
+      <c r="Y34" s="25" t="n"/>
+      <c r="Z34" s="26" t="n"/>
+      <c r="AA34" s="28" t="n"/>
+      <c r="AB34" s="28" t="n"/>
+      <c r="AC34" s="30" t="n"/>
+      <c r="AD34" s="24" t="n"/>
+      <c r="AE34" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5150; executable ask 0.5600 (aec-mlb-pit-nyy-2026-07-20).</t>
+        </is>
+      </c>
+      <c r="AF34" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
+        </is>
+      </c>
+      <c r="AG34" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH34" s="24" t="n"/>
+      <c r="AI34" s="31" t="n"/>
+      <c r="AJ34" s="31" t="n"/>
+      <c r="AK34" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL34" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM34" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN34" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO34" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP34" s="24" t="inlineStr">
+        <is>
+          <t>mlb-pit</t>
+        </is>
+      </c>
+      <c r="AQ34" s="24" t="inlineStr">
+        <is>
+          <t>Pittsburgh Pirates</t>
+        </is>
+      </c>
+      <c r="AR34" s="24" t="inlineStr">
+        <is>
+          <t>Pittsburgh Pirates</t>
+        </is>
+      </c>
+      <c r="AS34" s="24" t="inlineStr">
+        <is>
+          <t>mlb-nyy</t>
+        </is>
+      </c>
+      <c r="AT34" s="24" t="inlineStr">
+        <is>
+          <t>New York Yankees</t>
+        </is>
+      </c>
+      <c r="AU34" s="24" t="inlineStr">
+        <is>
+          <t>New York Yankees</t>
+        </is>
+      </c>
+      <c r="AV34" s="24" t="n"/>
+      <c r="AW34" s="24" t="n"/>
+      <c r="AX34" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY34" s="24" t="n"/>
+      <c r="AZ34" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA34" s="24" t="inlineStr">
+        <is>
+          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+        </is>
+      </c>
+      <c r="BB34" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC34" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BD34" s="24" t="inlineStr">
+        <is>
+          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+        </is>
+      </c>
+      <c r="BE34" s="24" t="inlineStr">
+        <is>
+          <t>5ace88fdb9c57ce4</t>
+        </is>
+      </c>
+      <c r="BF34" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG34" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BH34" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-19T17:17:29.263038Z</t>
+        </is>
+      </c>
+      <c r="BI34" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ34" s="25" t="n"/>
+      <c r="BK34" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="BL34" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="BM34" s="28" t="n">
+        <v>0.5594710000000001</v>
+      </c>
+      <c r="BN34" s="28" t="n">
+        <v>0.557214</v>
+      </c>
+      <c r="BO34" s="28" t="n"/>
+      <c r="BP34" s="25" t="n"/>
+      <c r="BQ34" s="27" t="n"/>
+      <c r="BR34" s="28" t="n"/>
+      <c r="BS34" s="28" t="n"/>
+      <c r="BT34" s="28" t="n"/>
+      <c r="BU34" s="25" t="n"/>
+      <c r="BV34" s="29" t="n"/>
+      <c r="BW34" s="24" t="n"/>
+      <c r="BX34" s="30" t="n"/>
+      <c r="BY34" s="27" t="n"/>
+      <c r="BZ34" s="24" t="n"/>
+      <c r="CA34" s="31" t="n"/>
+    </row>
+    <row r="35" ht="36" customHeight="1">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>a1f560f16ca8495f</t>
+        </is>
+      </c>
+      <c r="B35" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-19T17:18:24.670965Z</t>
+        </is>
+      </c>
+      <c r="C35" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T19:10:00-0400</t>
+        </is>
+      </c>
+      <c r="D35" s="24" t="inlineStr">
+        <is>
+          <t>401816186</t>
+        </is>
+      </c>
+      <c r="E35" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F35" s="24" t="inlineStr">
+        <is>
+          <t>Baltimore Orioles</t>
+        </is>
+      </c>
+      <c r="G35" s="24" t="inlineStr">
+        <is>
+          <t>Boston Red Sox</t>
+        </is>
+      </c>
+      <c r="H35" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I35" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J35" s="25" t="n"/>
+      <c r="K35" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L35" s="26" t="n">
+        <v>-117</v>
+      </c>
+      <c r="M35" s="27" t="n">
+        <v>1.854701</v>
+      </c>
+      <c r="N35" s="28" t="n">
+        <v>0.539171</v>
+      </c>
+      <c r="O35" s="28" t="n">
+        <v>0.56697</v>
+      </c>
+      <c r="P35" s="28" t="n"/>
+      <c r="Q35" s="28" t="n">
+        <v>0.027799</v>
+      </c>
+      <c r="R35" s="26" t="n">
+        <v>34</v>
+      </c>
+      <c r="S35" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T35" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="U35" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V35" s="24" t="n"/>
+      <c r="W35" s="26" t="n"/>
+      <c r="X35" s="26" t="n"/>
+      <c r="Y35" s="25" t="n"/>
+      <c r="Z35" s="26" t="n"/>
+      <c r="AA35" s="28" t="n"/>
+      <c r="AB35" s="28" t="n"/>
+      <c r="AC35" s="30" t="n"/>
+      <c r="AD35" s="24" t="n"/>
+      <c r="AE35" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5150; executable ask 0.5400 (aec-mlb-bal-bos-2026-07-20).</t>
+        </is>
+      </c>
+      <c r="AF35" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
+        </is>
+      </c>
+      <c r="AG35" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH35" s="24" t="n"/>
+      <c r="AI35" s="31" t="n"/>
+      <c r="AJ35" s="31" t="n"/>
+      <c r="AK35" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL35" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM35" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN35" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO35" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP35" s="24" t="inlineStr">
+        <is>
+          <t>mlb-bal</t>
+        </is>
+      </c>
+      <c r="AQ35" s="24" t="inlineStr">
+        <is>
+          <t>Baltimore Orioles</t>
+        </is>
+      </c>
+      <c r="AR35" s="24" t="inlineStr">
+        <is>
+          <t>Baltimore Orioles</t>
+        </is>
+      </c>
+      <c r="AS35" s="24" t="inlineStr">
+        <is>
+          <t>mlb-bos</t>
+        </is>
+      </c>
+      <c r="AT35" s="24" t="inlineStr">
+        <is>
+          <t>Boston Red Sox</t>
+        </is>
+      </c>
+      <c r="AU35" s="24" t="inlineStr">
+        <is>
+          <t>Boston Red Sox</t>
+        </is>
+      </c>
+      <c r="AV35" s="24" t="n"/>
+      <c r="AW35" s="24" t="n"/>
+      <c r="AX35" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY35" s="24" t="n"/>
+      <c r="AZ35" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA35" s="24" t="inlineStr">
+        <is>
+          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+        </is>
+      </c>
+      <c r="BB35" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC35" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BD35" s="24" t="inlineStr">
+        <is>
+          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+        </is>
+      </c>
+      <c r="BE35" s="24" t="inlineStr">
+        <is>
+          <t>a6a83b5ac90d7962</t>
+        </is>
+      </c>
+      <c r="BF35" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG35" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BH35" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-19T17:17:31.410943Z</t>
+        </is>
+      </c>
+      <c r="BI35" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ35" s="25" t="n"/>
+      <c r="BK35" s="26" t="n">
+        <v>-117</v>
+      </c>
+      <c r="BL35" s="27" t="n">
+        <v>1.854701</v>
+      </c>
+      <c r="BM35" s="28" t="n">
+        <v>0.539171</v>
+      </c>
+      <c r="BN35" s="28" t="n">
+        <v>0.537313</v>
+      </c>
+      <c r="BO35" s="28" t="n"/>
+      <c r="BP35" s="25" t="n"/>
+      <c r="BQ35" s="27" t="n"/>
+      <c r="BR35" s="28" t="n"/>
+      <c r="BS35" s="28" t="n"/>
+      <c r="BT35" s="28" t="n"/>
+      <c r="BU35" s="25" t="n"/>
+      <c r="BV35" s="29" t="n"/>
+      <c r="BW35" s="24" t="n"/>
+      <c r="BX35" s="30" t="n"/>
+      <c r="BY35" s="27" t="n"/>
+      <c r="BZ35" s="24" t="n"/>
+      <c r="CA35" s="31" t="n"/>
+    </row>
+    <row r="36" ht="36" customHeight="1">
+      <c r="A36" s="24" t="inlineStr">
+        <is>
+          <t>369b925b172f4b6a</t>
+        </is>
+      </c>
+      <c r="B36" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-19T17:18:24.670965Z</t>
+        </is>
+      </c>
+      <c r="C36" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-21T01:40Z</t>
+        </is>
+      </c>
+      <c r="D36" s="24" t="inlineStr">
+        <is>
+          <t>401816199</t>
+        </is>
+      </c>
+      <c r="E36" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F36" s="24" t="inlineStr">
+        <is>
+          <t>Cincinnati Reds</t>
+        </is>
+      </c>
+      <c r="G36" s="24" t="inlineStr">
+        <is>
+          <t>Seattle Mariners</t>
+        </is>
+      </c>
+      <c r="H36" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I36" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J36" s="25" t="n"/>
+      <c r="K36" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L36" s="26" t="n">
+        <v>-125</v>
+      </c>
+      <c r="M36" s="27" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="N36" s="28" t="n">
+        <v>0.555556</v>
+      </c>
+      <c r="O36" s="28" t="n">
+        <v>0.597509</v>
+      </c>
+      <c r="P36" s="28" t="n"/>
+      <c r="Q36" s="28" t="n">
+        <v>0.041953</v>
+      </c>
+      <c r="R36" s="26" t="n">
+        <v>41</v>
+      </c>
+      <c r="S36" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T36" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="U36" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V36" s="24" t="n"/>
+      <c r="W36" s="26" t="n"/>
+      <c r="X36" s="26" t="n"/>
+      <c r="Y36" s="25" t="n"/>
+      <c r="Z36" s="26" t="n"/>
+      <c r="AA36" s="28" t="n"/>
+      <c r="AB36" s="28" t="n"/>
+      <c r="AC36" s="30" t="n"/>
+      <c r="AD36" s="24" t="n"/>
+      <c r="AE36" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5150; executable ask 0.5550 (aec-mlb-cin-sea-2026-07-20).</t>
+        </is>
+      </c>
+      <c r="AF36" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
+        </is>
+      </c>
+      <c r="AG36" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH36" s="24" t="n"/>
+      <c r="AI36" s="31" t="n"/>
+      <c r="AJ36" s="31" t="n"/>
+      <c r="AK36" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL36" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM36" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN36" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO36" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP36" s="24" t="inlineStr">
+        <is>
+          <t>mlb-cin</t>
+        </is>
+      </c>
+      <c r="AQ36" s="24" t="inlineStr">
+        <is>
+          <t>Cincinnati Reds</t>
+        </is>
+      </c>
+      <c r="AR36" s="24" t="inlineStr">
+        <is>
+          <t>Cincinnati Reds</t>
+        </is>
+      </c>
+      <c r="AS36" s="24" t="inlineStr">
+        <is>
+          <t>mlb-sea</t>
+        </is>
+      </c>
+      <c r="AT36" s="24" t="inlineStr">
+        <is>
+          <t>Seattle Mariners</t>
+        </is>
+      </c>
+      <c r="AU36" s="24" t="inlineStr">
+        <is>
+          <t>Seattle Mariners</t>
+        </is>
+      </c>
+      <c r="AV36" s="24" t="n"/>
+      <c r="AW36" s="24" t="n"/>
+      <c r="AX36" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY36" s="24" t="n"/>
+      <c r="AZ36" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA36" s="24" t="inlineStr">
+        <is>
+          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+        </is>
+      </c>
+      <c r="BB36" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC36" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BD36" s="24" t="inlineStr">
+        <is>
+          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+        </is>
+      </c>
+      <c r="BE36" s="24" t="inlineStr">
+        <is>
+          <t>982d73638d70c45b</t>
+        </is>
+      </c>
+      <c r="BF36" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG36" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BH36" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-19T17:17:46.849555Z</t>
+        </is>
+      </c>
+      <c r="BI36" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ36" s="25" t="n"/>
+      <c r="BK36" s="26" t="n">
+        <v>-125</v>
+      </c>
+      <c r="BL36" s="27" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BM36" s="28" t="n">
+        <v>0.555556</v>
+      </c>
+      <c r="BN36" s="28" t="n">
+        <v>0.552239</v>
+      </c>
+      <c r="BO36" s="28" t="n"/>
+      <c r="BP36" s="25" t="n"/>
+      <c r="BQ36" s="27" t="n"/>
+      <c r="BR36" s="28" t="n"/>
+      <c r="BS36" s="28" t="n"/>
+      <c r="BT36" s="28" t="n"/>
+      <c r="BU36" s="25" t="n"/>
+      <c r="BV36" s="29" t="n"/>
+      <c r="BW36" s="24" t="n"/>
+      <c r="BX36" s="30" t="n"/>
+      <c r="BY36" s="27" t="n"/>
+      <c r="BZ36" s="24" t="n"/>
+      <c r="CA36" s="31" t="n"/>
+    </row>
+    <row r="37" ht="36" customHeight="1">
+      <c r="A37" s="24" t="inlineStr">
+        <is>
+          <t>c7a1577522fb4d37</t>
+        </is>
+      </c>
+      <c r="B37" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-19T17:18:24.670965Z</t>
+        </is>
+      </c>
+      <c r="C37" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-21T02:00Z</t>
+        </is>
+      </c>
+      <c r="D37" s="24" t="inlineStr">
+        <is>
+          <t>401816200</t>
+        </is>
+      </c>
+      <c r="E37" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F37" s="24" t="inlineStr">
+        <is>
+          <t>St. Louis Cardinals</t>
+        </is>
+      </c>
+      <c r="G37" s="24" t="inlineStr">
+        <is>
+          <t>Los Angeles Angels</t>
+        </is>
+      </c>
+      <c r="H37" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I37" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J37" s="25" t="n"/>
+      <c r="K37" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L37" s="26" t="n">
+        <v>-102</v>
+      </c>
+      <c r="M37" s="27" t="n">
+        <v>1.980392</v>
+      </c>
+      <c r="N37" s="28" t="n">
+        <v>0.50495</v>
+      </c>
+      <c r="O37" s="28" t="n">
+        <v>0.541942</v>
+      </c>
+      <c r="P37" s="28" t="n"/>
+      <c r="Q37" s="28" t="n">
+        <v>0.036992</v>
+      </c>
+      <c r="R37" s="26" t="n">
+        <v>38</v>
+      </c>
+      <c r="S37" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T37" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="U37" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V37" s="24" t="n"/>
+      <c r="W37" s="26" t="n"/>
+      <c r="X37" s="26" t="n"/>
+      <c r="Y37" s="25" t="n"/>
+      <c r="Z37" s="26" t="n"/>
+      <c r="AA37" s="28" t="n"/>
+      <c r="AB37" s="28" t="n"/>
+      <c r="AC37" s="30" t="n"/>
+      <c r="AD37" s="24" t="n"/>
+      <c r="AE37" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5150; executable ask 0.5050 (aec-mlb-stl-laa-2026-07-20).</t>
+        </is>
+      </c>
+      <c r="AF37" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
+        </is>
+      </c>
+      <c r="AG37" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH37" s="24" t="n"/>
+      <c r="AI37" s="31" t="n"/>
+      <c r="AJ37" s="31" t="n"/>
+      <c r="AK37" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL37" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM37" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN37" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO37" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP37" s="24" t="inlineStr">
+        <is>
+          <t>mlb-stl</t>
+        </is>
+      </c>
+      <c r="AQ37" s="24" t="inlineStr">
+        <is>
+          <t>St. Louis Cardinals</t>
+        </is>
+      </c>
+      <c r="AR37" s="24" t="inlineStr">
+        <is>
+          <t>St. Louis Cardinals</t>
+        </is>
+      </c>
+      <c r="AS37" s="24" t="inlineStr">
+        <is>
+          <t>mlb-laa</t>
+        </is>
+      </c>
+      <c r="AT37" s="24" t="inlineStr">
+        <is>
+          <t>Los Angeles Angels</t>
+        </is>
+      </c>
+      <c r="AU37" s="24" t="inlineStr">
+        <is>
+          <t>Los Angeles Angels</t>
+        </is>
+      </c>
+      <c r="AV37" s="24" t="n"/>
+      <c r="AW37" s="24" t="n"/>
+      <c r="AX37" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY37" s="24" t="n"/>
+      <c r="AZ37" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA37" s="24" t="inlineStr">
+        <is>
+          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+        </is>
+      </c>
+      <c r="BB37" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC37" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BD37" s="24" t="inlineStr">
+        <is>
+          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+        </is>
+      </c>
+      <c r="BE37" s="24" t="inlineStr">
+        <is>
+          <t>83613a19346b831e</t>
+        </is>
+      </c>
+      <c r="BF37" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG37" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BH37" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-19T17:17:47.727344Z</t>
+        </is>
+      </c>
+      <c r="BI37" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ37" s="25" t="n"/>
+      <c r="BK37" s="26" t="n">
+        <v>-102</v>
+      </c>
+      <c r="BL37" s="27" t="n">
+        <v>1.980392</v>
+      </c>
+      <c r="BM37" s="28" t="n">
+        <v>0.50495</v>
+      </c>
+      <c r="BN37" s="28" t="n">
+        <v>0.502488</v>
+      </c>
+      <c r="BO37" s="28" t="n"/>
+      <c r="BP37" s="25" t="n"/>
+      <c r="BQ37" s="27" t="n"/>
+      <c r="BR37" s="28" t="n"/>
+      <c r="BS37" s="28" t="n"/>
+      <c r="BT37" s="28" t="n"/>
+      <c r="BU37" s="25" t="n"/>
+      <c r="BV37" s="29" t="n"/>
+      <c r="BW37" s="24" t="n"/>
+      <c r="BX37" s="30" t="n"/>
+      <c r="BY37" s="27" t="n"/>
+      <c r="BZ37" s="24" t="n"/>
+      <c r="CA37" s="31" t="n"/>
+    </row>
+    <row r="38" ht="36" customHeight="1">
+      <c r="A38" s="24" t="inlineStr">
+        <is>
+          <t>5ddbae8d805944cb</t>
+        </is>
+      </c>
+      <c r="B38" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-19T17:18:29.371620Z</t>
+        </is>
+      </c>
+      <c r="C38" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-21T00:00Z</t>
+        </is>
+      </c>
+      <c r="D38" s="24" t="inlineStr">
+        <is>
+          <t>401892393</t>
+        </is>
+      </c>
+      <c r="E38" s="24" t="inlineStr">
+        <is>
+          <t>WNBA</t>
+        </is>
+      </c>
+      <c r="F38" s="24" t="inlineStr">
+        <is>
+          <t>New York Liberty</t>
+        </is>
+      </c>
+      <c r="G38" s="24" t="inlineStr">
+        <is>
+          <t>Dallas Wings</t>
+        </is>
+      </c>
+      <c r="H38" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I38" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J38" s="25" t="n"/>
+      <c r="K38" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L38" s="26" t="n">
+        <v>108</v>
+      </c>
+      <c r="M38" s="27" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="N38" s="28" t="n">
+        <v>0.480769</v>
+      </c>
+      <c r="O38" s="28" t="n">
+        <v>0.6787840000000001</v>
+      </c>
+      <c r="P38" s="28" t="n"/>
+      <c r="Q38" s="28" t="n">
+        <v>0.198015</v>
+      </c>
+      <c r="R38" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S38" s="29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T38" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="U38" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V38" s="24" t="n"/>
+      <c r="W38" s="26" t="n"/>
+      <c r="X38" s="26" t="n"/>
+      <c r="Y38" s="25" t="n"/>
+      <c r="Z38" s="26" t="n"/>
+      <c r="AA38" s="28" t="n"/>
+      <c r="AB38" s="28" t="n"/>
+      <c r="AC38" s="30" t="n"/>
+      <c r="AD38" s="24" t="n"/>
+      <c r="AE38" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5000; executable ask 0.4800 (aec-wnba-ny-dal-2026-07-20).</t>
+        </is>
+      </c>
+      <c r="AF38" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
+        </is>
+      </c>
+      <c r="AG38" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH38" s="24" t="n"/>
+      <c r="AI38" s="31" t="n"/>
+      <c r="AJ38" s="31" t="n"/>
+      <c r="AK38" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL38" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM38" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN38" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO38" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LARGE_DISAGREEMENT_REVIEW</t>
+        </is>
+      </c>
+      <c r="AP38" s="24" t="inlineStr">
+        <is>
+          <t>wnba-nyl</t>
+        </is>
+      </c>
+      <c r="AQ38" s="24" t="inlineStr">
+        <is>
+          <t>New York Liberty</t>
+        </is>
+      </c>
+      <c r="AR38" s="24" t="inlineStr">
+        <is>
+          <t>New York Liberty</t>
+        </is>
+      </c>
+      <c r="AS38" s="24" t="inlineStr">
+        <is>
+          <t>wnba-dal</t>
+        </is>
+      </c>
+      <c r="AT38" s="24" t="inlineStr">
+        <is>
+          <t>Dallas Wings</t>
+        </is>
+      </c>
+      <c r="AU38" s="24" t="inlineStr">
+        <is>
+          <t>Dallas Wings</t>
+        </is>
+      </c>
+      <c r="AV38" s="24" t="n"/>
+      <c r="AW38" s="24" t="n"/>
+      <c r="AX38" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY38" s="24" t="n"/>
+      <c r="AZ38" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA38" s="24" t="inlineStr">
+        <is>
+          <t>d339198b196cb3fcd02950ed5efbdd4cefbeb95b2cd63cd756e77f99dc483719</t>
+        </is>
+      </c>
+      <c r="BB38" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC38" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BD38" s="24" t="inlineStr">
+        <is>
+          <t>d339198b196cb3fcd02950ed5efbdd4cefbeb95b2cd63cd756e77f99dc483719</t>
+        </is>
+      </c>
+      <c r="BE38" s="24" t="inlineStr">
+        <is>
+          <t>1c6f45e72b2d1f80</t>
+        </is>
+      </c>
+      <c r="BF38" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG38" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BH38" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-19T17:17:49.472621Z</t>
+        </is>
+      </c>
+      <c r="BI38" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ38" s="25" t="n"/>
+      <c r="BK38" s="26" t="n">
+        <v>108</v>
+      </c>
+      <c r="BL38" s="27" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BM38" s="28" t="n">
+        <v>0.480769</v>
+      </c>
+      <c r="BN38" s="28" t="n">
+        <v>0.475248</v>
+      </c>
+      <c r="BO38" s="28" t="n"/>
+      <c r="BP38" s="25" t="n"/>
+      <c r="BQ38" s="27" t="n"/>
+      <c r="BR38" s="28" t="n"/>
+      <c r="BS38" s="28" t="n"/>
+      <c r="BT38" s="28" t="n"/>
+      <c r="BU38" s="25" t="n"/>
+      <c r="BV38" s="29" t="n"/>
+      <c r="BW38" s="24" t="n"/>
+      <c r="BX38" s="30" t="n"/>
+      <c r="BY38" s="27" t="n"/>
+      <c r="BZ38" s="24" t="n"/>
+      <c r="CA38" s="31" t="n"/>
+    </row>
+    <row r="39" ht="36" customHeight="1">
+      <c r="A39" s="24" t="inlineStr">
+        <is>
+          <t>742b29ba1ffd440b</t>
+        </is>
+      </c>
+      <c r="B39" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-19T22:20:13.941752Z</t>
+        </is>
+      </c>
+      <c r="C39" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T20:05:00-0400</t>
+        </is>
+      </c>
+      <c r="D39" s="24" t="inlineStr">
+        <is>
+          <t>401816193</t>
+        </is>
+      </c>
+      <c r="E39" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F39" s="24" t="inlineStr">
+        <is>
+          <t>Detroit Tigers</t>
+        </is>
+      </c>
+      <c r="G39" s="24" t="inlineStr">
+        <is>
+          <t>Chicago Cubs</t>
+        </is>
+      </c>
+      <c r="H39" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I39" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J39" s="25" t="n"/>
+      <c r="K39" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L39" s="26" t="n">
+        <v>-108</v>
+      </c>
+      <c r="M39" s="27" t="n">
+        <v>1.925926</v>
+      </c>
+      <c r="N39" s="28" t="n">
+        <v>0.519231</v>
+      </c>
+      <c r="O39" s="28" t="n">
+        <v>0.575831</v>
+      </c>
+      <c r="P39" s="28" t="n"/>
+      <c r="Q39" s="28" t="n">
+        <v>0.0566</v>
+      </c>
+      <c r="R39" s="26" t="n">
+        <v>48</v>
+      </c>
+      <c r="S39" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T39" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="U39" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V39" s="24" t="n"/>
+      <c r="W39" s="26" t="n"/>
+      <c r="X39" s="26" t="n"/>
+      <c r="Y39" s="25" t="n"/>
+      <c r="Z39" s="26" t="n"/>
+      <c r="AA39" s="28" t="n"/>
+      <c r="AB39" s="28" t="n"/>
+      <c r="AC39" s="30" t="n"/>
+      <c r="AD39" s="24" t="n"/>
+      <c r="AE39" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5150; executable ask 0.5200 (aec-mlb-det-chc-2026-07-20).</t>
+        </is>
+      </c>
+      <c r="AF39" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
+        </is>
+      </c>
+      <c r="AG39" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH39" s="24" t="n"/>
+      <c r="AI39" s="31" t="n"/>
+      <c r="AJ39" s="31" t="n"/>
+      <c r="AK39" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL39" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM39" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN39" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO39" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP39" s="24" t="inlineStr">
+        <is>
+          <t>mlb-det</t>
+        </is>
+      </c>
+      <c r="AQ39" s="24" t="inlineStr">
+        <is>
+          <t>Detroit Tigers</t>
+        </is>
+      </c>
+      <c r="AR39" s="24" t="inlineStr">
+        <is>
+          <t>Detroit Tigers</t>
+        </is>
+      </c>
+      <c r="AS39" s="24" t="inlineStr">
+        <is>
+          <t>mlb-chc</t>
+        </is>
+      </c>
+      <c r="AT39" s="24" t="inlineStr">
+        <is>
+          <t>Chicago Cubs</t>
+        </is>
+      </c>
+      <c r="AU39" s="24" t="inlineStr">
+        <is>
+          <t>Chicago Cubs</t>
+        </is>
+      </c>
+      <c r="AV39" s="24" t="n"/>
+      <c r="AW39" s="24" t="n"/>
+      <c r="AX39" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY39" s="24" t="n"/>
+      <c r="AZ39" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA39" s="24" t="inlineStr">
+        <is>
+          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+        </is>
+      </c>
+      <c r="BB39" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC39" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BD39" s="24" t="inlineStr">
+        <is>
+          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+        </is>
+      </c>
+      <c r="BE39" s="24" t="inlineStr">
+        <is>
+          <t>4f45054abf6875ac</t>
+        </is>
+      </c>
+      <c r="BF39" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG39" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v3</t>
+        </is>
+      </c>
+      <c r="BH39" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-19T17:19:26.722324Z</t>
+        </is>
+      </c>
+      <c r="BI39" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ39" s="25" t="n"/>
+      <c r="BK39" s="26" t="n">
+        <v>-108</v>
+      </c>
+      <c r="BL39" s="27" t="n">
+        <v>1.925926</v>
+      </c>
+      <c r="BM39" s="28" t="n">
+        <v>0.519231</v>
+      </c>
+      <c r="BN39" s="28" t="n">
+        <v>0.517413</v>
+      </c>
+      <c r="BO39" s="28" t="n"/>
+      <c r="BP39" s="25" t="n"/>
+      <c r="BQ39" s="27" t="n"/>
+      <c r="BR39" s="28" t="n"/>
+      <c r="BS39" s="28" t="n"/>
+      <c r="BT39" s="28" t="n"/>
+      <c r="BU39" s="25" t="n"/>
+      <c r="BV39" s="29" t="n"/>
+      <c r="BW39" s="24" t="n"/>
+      <c r="BX39" s="30" t="n"/>
+      <c r="BY39" s="27" t="n"/>
+      <c r="BZ39" s="24" t="n"/>
+      <c r="CA39" s="31" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/picks.xlsx
+++ b/data/picks.xlsx
@@ -21,10 +21,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="0.0###"/>
-    <numFmt numFmtId="165" formatCode="0.000000"/>
-    <numFmt numFmtId="166" formatCode="0.0000"/>
-    <numFmt numFmtId="167" formatCode="0.0%"/>
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
+    <numFmt numFmtId="166" formatCode="0.0###"/>
+    <numFmt numFmtId="167" formatCode="0.000000"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -136,7 +136,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -150,10 +150,10 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -169,10 +169,10 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -184,10 +184,10 @@
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -202,13 +202,13 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="10" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -217,11 +217,38 @@
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -754,6 +781,7 @@
         <v/>
       </c>
     </row>
+    <row r="5"/>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
@@ -785,15 +813,16 @@
         <f>COUNTIFS('Picks'!$BX$2:$BX$39,"&gt;0",'Picks'!$V$2:$V$39,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$39,"&gt;0",'Picks'!$V$2:$V$39,"loss")</f>
         <v/>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="32">
         <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$39,"&gt;0",'Picks'!$V$2:$V$39,"win")/(COUNTIFS('Picks'!$BX$2:$BX$39,"&gt;0",'Picks'!$V$2:$V$39,"win")+COUNTIFS('Picks'!$BX$2:$BX$39,"&gt;0",'Picks'!$V$2:$V$39,"loss")),0)</f>
         <v/>
       </c>
-      <c r="G7" s="7">
+      <c r="G7" s="32">
         <f>IFERROR(SUM('Picks'!$BY$2:$BY$39)/SUM('Picks'!$BX$2:$BX$39),0)</f>
         <v/>
       </c>
     </row>
+    <row r="8"/>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
@@ -817,7 +846,7 @@
       </c>
     </row>
     <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="8">
+      <c r="A10" s="33">
         <f>SUM('Picks'!$BY$2:$BY$39)</f>
         <v/>
       </c>
@@ -829,11 +858,12 @@
         <f>COUNTIFS('Picks'!$AM$2:$AM$39,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$39,"settled")</f>
         <v/>
       </c>
-      <c r="G10" s="8">
+      <c r="G10" s="33">
         <f>SUMIFS('Picks'!$AC$2:$AC$39,'Picks'!$AM$2:$AM$39,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
@@ -896,11 +926,11 @@
         <f>COUNTIFS('Picks'!$H$2:$H$39,$A14,'Picks'!$U$2:$U$39,"settled",'Picks'!$V$2:$V$39,"loss")</f>
         <v/>
       </c>
-      <c r="E14" s="14">
+      <c r="E14" s="34">
         <f>IFERROR(C14/(C14+D14),0)</f>
         <v/>
       </c>
-      <c r="F14" s="15">
+      <c r="F14" s="35">
         <f>SUMIFS('Picks'!$BY$2:$BY$39,'Picks'!$H$2:$H$39,$A14)</f>
         <v/>
       </c>
@@ -927,11 +957,11 @@
         <f>COUNTIFS('Picks'!$H$2:$H$39,$A15,'Picks'!$U$2:$U$39,"settled",'Picks'!$V$2:$V$39,"loss")</f>
         <v/>
       </c>
-      <c r="E15" s="19">
+      <c r="E15" s="36">
         <f>IFERROR(C15/(C15+D15),0)</f>
         <v/>
       </c>
-      <c r="F15" s="20">
+      <c r="F15" s="37">
         <f>SUMIFS('Picks'!$BY$2:$BY$39,'Picks'!$H$2:$H$39,$A15)</f>
         <v/>
       </c>
@@ -958,11 +988,11 @@
         <f>COUNTIFS('Picks'!$H$2:$H$39,$A16,'Picks'!$U$2:$U$39,"settled",'Picks'!$V$2:$V$39,"loss")</f>
         <v/>
       </c>
-      <c r="E16" s="14">
+      <c r="E16" s="34">
         <f>IFERROR(C16/(C16+D16),0)</f>
         <v/>
       </c>
-      <c r="F16" s="15">
+      <c r="F16" s="35">
         <f>SUMIFS('Picks'!$BY$2:$BY$39,'Picks'!$H$2:$H$39,$A16)</f>
         <v/>
       </c>
@@ -971,6 +1001,7 @@
         <v/>
       </c>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="22" t="inlineStr">
         <is>
@@ -1523,7 +1554,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J2" s="25" t="n"/>
+      <c r="J2" s="38" t="n"/>
       <c r="K2" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -1532,7 +1563,7 @@
       <c r="L2" s="26" t="n">
         <v>117</v>
       </c>
-      <c r="M2" s="27" t="n">
+      <c r="M2" s="39" t="n">
         <v>2.17</v>
       </c>
       <c r="N2" s="28" t="n">
@@ -1572,11 +1603,11 @@
       <c r="X2" s="26" t="n">
         <v>108</v>
       </c>
-      <c r="Y2" s="25" t="n"/>
+      <c r="Y2" s="38" t="n"/>
       <c r="Z2" s="26" t="n"/>
       <c r="AA2" s="28" t="n"/>
       <c r="AB2" s="28" t="n"/>
-      <c r="AC2" s="30" t="n">
+      <c r="AC2" s="40" t="n">
         <v>1.755</v>
       </c>
       <c r="AD2" s="24" t="inlineStr">
@@ -1713,11 +1744,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ2" s="25" t="n"/>
+      <c r="BJ2" s="38" t="n"/>
       <c r="BK2" s="26" t="n">
         <v>117</v>
       </c>
-      <c r="BL2" s="27" t="n">
+      <c r="BL2" s="39" t="n">
         <v>2.17</v>
       </c>
       <c r="BM2" s="28" t="n">
@@ -1727,18 +1758,18 @@
         <v>0.455446</v>
       </c>
       <c r="BO2" s="28" t="n"/>
-      <c r="BP2" s="25" t="n"/>
-      <c r="BQ2" s="27" t="n"/>
+      <c r="BP2" s="38" t="n"/>
+      <c r="BQ2" s="39" t="n"/>
       <c r="BR2" s="28" t="n"/>
       <c r="BS2" s="28" t="n"/>
       <c r="BT2" s="28" t="n"/>
-      <c r="BU2" s="25" t="n"/>
+      <c r="BU2" s="38" t="n"/>
       <c r="BV2" s="29" t="n"/>
       <c r="BW2" s="24" t="n"/>
-      <c r="BX2" s="30" t="n">
+      <c r="BX2" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY2" s="27" t="n">
+      <c r="BY2" s="39" t="n">
         <v>1.17</v>
       </c>
       <c r="BZ2" s="24" t="inlineStr">
@@ -1798,7 +1829,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J3" s="25" t="n"/>
+      <c r="J3" s="38" t="n"/>
       <c r="K3" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -1807,7 +1838,7 @@
       <c r="L3" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="M3" s="27" t="n">
+      <c r="M3" s="39" t="n">
         <v>1.75188</v>
       </c>
       <c r="N3" s="28" t="n">
@@ -1847,11 +1878,11 @@
       <c r="X3" s="26" t="n">
         <v>8</v>
       </c>
-      <c r="Y3" s="25" t="n"/>
+      <c r="Y3" s="38" t="n"/>
       <c r="Z3" s="26" t="n"/>
       <c r="AA3" s="28" t="n"/>
       <c r="AB3" s="28" t="n"/>
-      <c r="AC3" s="30" t="n">
+      <c r="AC3" s="40" t="n">
         <v>1.1278</v>
       </c>
       <c r="AD3" s="24" t="inlineStr">
@@ -1988,11 +2019,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ3" s="25" t="n"/>
+      <c r="BJ3" s="38" t="n"/>
       <c r="BK3" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="BL3" s="27" t="n">
+      <c r="BL3" s="39" t="n">
         <v>1.75188</v>
       </c>
       <c r="BM3" s="28" t="n">
@@ -2002,18 +2033,18 @@
         <v>0.567164</v>
       </c>
       <c r="BO3" s="28" t="n"/>
-      <c r="BP3" s="25" t="n"/>
-      <c r="BQ3" s="27" t="n"/>
+      <c r="BP3" s="38" t="n"/>
+      <c r="BQ3" s="39" t="n"/>
       <c r="BR3" s="28" t="n"/>
       <c r="BS3" s="28" t="n"/>
       <c r="BT3" s="28" t="n"/>
-      <c r="BU3" s="25" t="n"/>
+      <c r="BU3" s="38" t="n"/>
       <c r="BV3" s="29" t="n"/>
       <c r="BW3" s="24" t="n"/>
-      <c r="BX3" s="30" t="n">
+      <c r="BX3" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY3" s="27" t="n">
+      <c r="BY3" s="39" t="n">
         <v>0.75188</v>
       </c>
       <c r="BZ3" s="24" t="inlineStr">
@@ -2073,7 +2104,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J4" s="25" t="n"/>
+      <c r="J4" s="38" t="n"/>
       <c r="K4" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -2082,7 +2113,7 @@
       <c r="L4" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="M4" s="27" t="n">
+      <c r="M4" s="39" t="n">
         <v>1.980392</v>
       </c>
       <c r="N4" s="28" t="n">
@@ -2122,11 +2153,11 @@
       <c r="X4" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="Y4" s="25" t="n"/>
+      <c r="Y4" s="38" t="n"/>
       <c r="Z4" s="26" t="n"/>
       <c r="AA4" s="28" t="n"/>
       <c r="AB4" s="28" t="n"/>
-      <c r="AC4" s="30" t="n">
+      <c r="AC4" s="40" t="n">
         <v>-1</v>
       </c>
       <c r="AD4" s="24" t="inlineStr">
@@ -2263,11 +2294,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ4" s="25" t="n"/>
+      <c r="BJ4" s="38" t="n"/>
       <c r="BK4" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="BL4" s="27" t="n">
+      <c r="BL4" s="39" t="n">
         <v>1.980392</v>
       </c>
       <c r="BM4" s="28" t="n">
@@ -2277,18 +2308,18 @@
         <v>0.502488</v>
       </c>
       <c r="BO4" s="28" t="n"/>
-      <c r="BP4" s="25" t="n"/>
-      <c r="BQ4" s="27" t="n"/>
+      <c r="BP4" s="38" t="n"/>
+      <c r="BQ4" s="39" t="n"/>
       <c r="BR4" s="28" t="n"/>
       <c r="BS4" s="28" t="n"/>
       <c r="BT4" s="28" t="n"/>
-      <c r="BU4" s="25" t="n"/>
+      <c r="BU4" s="38" t="n"/>
       <c r="BV4" s="29" t="n"/>
       <c r="BW4" s="24" t="n"/>
-      <c r="BX4" s="30" t="n">
+      <c r="BX4" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY4" s="27" t="n">
+      <c r="BY4" s="39" t="n">
         <v>-1</v>
       </c>
       <c r="BZ4" s="24" t="inlineStr">
@@ -2348,7 +2379,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J5" s="25" t="n"/>
+      <c r="J5" s="38" t="n"/>
       <c r="K5" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -2357,7 +2388,7 @@
       <c r="L5" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="M5" s="27" t="n">
+      <c r="M5" s="39" t="n">
         <v>1.75188</v>
       </c>
       <c r="N5" s="28" t="n">
@@ -2397,11 +2428,11 @@
       <c r="X5" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="Y5" s="25" t="n"/>
+      <c r="Y5" s="38" t="n"/>
       <c r="Z5" s="26" t="n"/>
       <c r="AA5" s="28" t="n"/>
       <c r="AB5" s="28" t="n"/>
-      <c r="AC5" s="30" t="n">
+      <c r="AC5" s="40" t="n">
         <v>1.1278</v>
       </c>
       <c r="AD5" s="24" t="inlineStr">
@@ -2538,11 +2569,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ5" s="25" t="n"/>
+      <c r="BJ5" s="38" t="n"/>
       <c r="BK5" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="BL5" s="27" t="n">
+      <c r="BL5" s="39" t="n">
         <v>1.75188</v>
       </c>
       <c r="BM5" s="28" t="n">
@@ -2552,18 +2583,18 @@
         <v>0.567164</v>
       </c>
       <c r="BO5" s="28" t="n"/>
-      <c r="BP5" s="25" t="n"/>
-      <c r="BQ5" s="27" t="n"/>
+      <c r="BP5" s="38" t="n"/>
+      <c r="BQ5" s="39" t="n"/>
       <c r="BR5" s="28" t="n"/>
       <c r="BS5" s="28" t="n"/>
       <c r="BT5" s="28" t="n"/>
-      <c r="BU5" s="25" t="n"/>
+      <c r="BU5" s="38" t="n"/>
       <c r="BV5" s="29" t="n"/>
       <c r="BW5" s="24" t="n"/>
-      <c r="BX5" s="30" t="n">
+      <c r="BX5" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY5" s="27" t="n">
+      <c r="BY5" s="39" t="n">
         <v>0.75188</v>
       </c>
       <c r="BZ5" s="24" t="inlineStr">
@@ -2623,7 +2654,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J6" s="25" t="n"/>
+      <c r="J6" s="38" t="n"/>
       <c r="K6" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -2632,7 +2663,7 @@
       <c r="L6" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="M6" s="27" t="n">
+      <c r="M6" s="39" t="n">
         <v>1.961538</v>
       </c>
       <c r="N6" s="28" t="n">
@@ -2672,11 +2703,11 @@
       <c r="X6" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="Y6" s="25" t="n"/>
+      <c r="Y6" s="38" t="n"/>
       <c r="Z6" s="26" t="n"/>
       <c r="AA6" s="28" t="n"/>
       <c r="AB6" s="28" t="n"/>
-      <c r="AC6" s="30" t="n">
+      <c r="AC6" s="40" t="n">
         <v>1.2019</v>
       </c>
       <c r="AD6" s="24" t="inlineStr">
@@ -2813,11 +2844,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ6" s="25" t="n"/>
+      <c r="BJ6" s="38" t="n"/>
       <c r="BK6" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="BL6" s="27" t="n">
+      <c r="BL6" s="39" t="n">
         <v>1.961538</v>
       </c>
       <c r="BM6" s="28" t="n">
@@ -2827,18 +2858,18 @@
         <v>0.507463</v>
       </c>
       <c r="BO6" s="28" t="n"/>
-      <c r="BP6" s="25" t="n"/>
-      <c r="BQ6" s="27" t="n"/>
+      <c r="BP6" s="38" t="n"/>
+      <c r="BQ6" s="39" t="n"/>
       <c r="BR6" s="28" t="n"/>
       <c r="BS6" s="28" t="n"/>
       <c r="BT6" s="28" t="n"/>
-      <c r="BU6" s="25" t="n"/>
+      <c r="BU6" s="38" t="n"/>
       <c r="BV6" s="29" t="n"/>
       <c r="BW6" s="24" t="n"/>
-      <c r="BX6" s="30" t="n">
+      <c r="BX6" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY6" s="27" t="n">
+      <c r="BY6" s="39" t="n">
         <v>0.961538</v>
       </c>
       <c r="BZ6" s="24" t="inlineStr">
@@ -2898,7 +2929,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J7" s="25" t="n"/>
+      <c r="J7" s="38" t="n"/>
       <c r="K7" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -2907,7 +2938,7 @@
       <c r="L7" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="M7" s="27" t="n">
+      <c r="M7" s="39" t="n">
         <v>1.961538</v>
       </c>
       <c r="N7" s="28" t="n">
@@ -2947,11 +2978,11 @@
       <c r="X7" s="26" t="n">
         <v>10</v>
       </c>
-      <c r="Y7" s="25" t="n"/>
+      <c r="Y7" s="38" t="n"/>
       <c r="Z7" s="26" t="n"/>
       <c r="AA7" s="28" t="n"/>
       <c r="AB7" s="28" t="n"/>
-      <c r="AC7" s="30" t="n">
+      <c r="AC7" s="40" t="n">
         <v>-1.25</v>
       </c>
       <c r="AD7" s="24" t="inlineStr">
@@ -3088,11 +3119,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ7" s="25" t="n"/>
+      <c r="BJ7" s="38" t="n"/>
       <c r="BK7" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="BL7" s="27" t="n">
+      <c r="BL7" s="39" t="n">
         <v>1.961538</v>
       </c>
       <c r="BM7" s="28" t="n">
@@ -3102,18 +3133,18 @@
         <v>0.507463</v>
       </c>
       <c r="BO7" s="28" t="n"/>
-      <c r="BP7" s="25" t="n"/>
-      <c r="BQ7" s="27" t="n"/>
+      <c r="BP7" s="38" t="n"/>
+      <c r="BQ7" s="39" t="n"/>
       <c r="BR7" s="28" t="n"/>
       <c r="BS7" s="28" t="n"/>
       <c r="BT7" s="28" t="n"/>
-      <c r="BU7" s="25" t="n"/>
+      <c r="BU7" s="38" t="n"/>
       <c r="BV7" s="29" t="n"/>
       <c r="BW7" s="24" t="n"/>
-      <c r="BX7" s="30" t="n">
+      <c r="BX7" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY7" s="27" t="n">
+      <c r="BY7" s="39" t="n">
         <v>-1</v>
       </c>
       <c r="BZ7" s="24" t="inlineStr">
@@ -3173,7 +3204,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J8" s="25" t="n"/>
+      <c r="J8" s="38" t="n"/>
       <c r="K8" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -3182,7 +3213,7 @@
       <c r="L8" s="26" t="n">
         <v>-106</v>
       </c>
-      <c r="M8" s="27" t="n">
+      <c r="M8" s="39" t="n">
         <v>1.943396</v>
       </c>
       <c r="N8" s="28" t="n">
@@ -3222,11 +3253,11 @@
       <c r="X8" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="Y8" s="25" t="n"/>
+      <c r="Y8" s="38" t="n"/>
       <c r="Z8" s="26" t="n"/>
       <c r="AA8" s="28" t="n"/>
       <c r="AB8" s="28" t="n"/>
-      <c r="AC8" s="30" t="n">
+      <c r="AC8" s="40" t="n">
         <v>-1</v>
       </c>
       <c r="AD8" s="24" t="inlineStr">
@@ -3363,11 +3394,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ8" s="25" t="n"/>
+      <c r="BJ8" s="38" t="n"/>
       <c r="BK8" s="26" t="n">
         <v>-106</v>
       </c>
-      <c r="BL8" s="27" t="n">
+      <c r="BL8" s="39" t="n">
         <v>1.943396</v>
       </c>
       <c r="BM8" s="28" t="n">
@@ -3377,18 +3408,18 @@
         <v>0.5124379999999999</v>
       </c>
       <c r="BO8" s="28" t="n"/>
-      <c r="BP8" s="25" t="n"/>
-      <c r="BQ8" s="27" t="n"/>
+      <c r="BP8" s="38" t="n"/>
+      <c r="BQ8" s="39" t="n"/>
       <c r="BR8" s="28" t="n"/>
       <c r="BS8" s="28" t="n"/>
       <c r="BT8" s="28" t="n"/>
-      <c r="BU8" s="25" t="n"/>
+      <c r="BU8" s="38" t="n"/>
       <c r="BV8" s="29" t="n"/>
       <c r="BW8" s="24" t="n"/>
-      <c r="BX8" s="30" t="n">
+      <c r="BX8" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY8" s="27" t="n">
+      <c r="BY8" s="39" t="n">
         <v>-1</v>
       </c>
       <c r="BZ8" s="24" t="inlineStr">
@@ -3448,7 +3479,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J9" s="25" t="n"/>
+      <c r="J9" s="38" t="n"/>
       <c r="K9" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -3457,7 +3488,7 @@
       <c r="L9" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="M9" s="27" t="n">
+      <c r="M9" s="39" t="n">
         <v>1.980392</v>
       </c>
       <c r="N9" s="28" t="n">
@@ -3497,11 +3528,11 @@
       <c r="X9" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="Y9" s="25" t="n"/>
+      <c r="Y9" s="38" t="n"/>
       <c r="Z9" s="26" t="n"/>
       <c r="AA9" s="28" t="n"/>
       <c r="AB9" s="28" t="n"/>
-      <c r="AC9" s="30" t="n">
+      <c r="AC9" s="40" t="n">
         <v>0.9804</v>
       </c>
       <c r="AD9" s="24" t="inlineStr">
@@ -3638,11 +3669,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ9" s="25" t="n"/>
+      <c r="BJ9" s="38" t="n"/>
       <c r="BK9" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="BL9" s="27" t="n">
+      <c r="BL9" s="39" t="n">
         <v>1.980392</v>
       </c>
       <c r="BM9" s="28" t="n">
@@ -3652,18 +3683,18 @@
         <v>0.502488</v>
       </c>
       <c r="BO9" s="28" t="n"/>
-      <c r="BP9" s="25" t="n"/>
-      <c r="BQ9" s="27" t="n"/>
+      <c r="BP9" s="38" t="n"/>
+      <c r="BQ9" s="39" t="n"/>
       <c r="BR9" s="28" t="n"/>
       <c r="BS9" s="28" t="n"/>
       <c r="BT9" s="28" t="n"/>
-      <c r="BU9" s="25" t="n"/>
+      <c r="BU9" s="38" t="n"/>
       <c r="BV9" s="29" t="n"/>
       <c r="BW9" s="24" t="n"/>
-      <c r="BX9" s="30" t="n">
+      <c r="BX9" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY9" s="27" t="n">
+      <c r="BY9" s="39" t="n">
         <v>0.980392</v>
       </c>
       <c r="BZ9" s="24" t="inlineStr">
@@ -3723,7 +3754,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J10" s="25" t="n"/>
+      <c r="J10" s="38" t="n"/>
       <c r="K10" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -3732,7 +3763,7 @@
       <c r="L10" s="26" t="n">
         <v>-138</v>
       </c>
-      <c r="M10" s="27" t="n">
+      <c r="M10" s="39" t="n">
         <v>1.724638</v>
       </c>
       <c r="N10" s="28" t="n">
@@ -3772,11 +3803,11 @@
       <c r="X10" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="Y10" s="25" t="n"/>
+      <c r="Y10" s="38" t="n"/>
       <c r="Z10" s="26" t="n"/>
       <c r="AA10" s="28" t="n"/>
       <c r="AB10" s="28" t="n"/>
-      <c r="AC10" s="30" t="n">
+      <c r="AC10" s="40" t="n">
         <v>1.2681</v>
       </c>
       <c r="AD10" s="24" t="inlineStr">
@@ -3913,11 +3944,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ10" s="25" t="n"/>
+      <c r="BJ10" s="38" t="n"/>
       <c r="BK10" s="26" t="n">
         <v>-138</v>
       </c>
-      <c r="BL10" s="27" t="n">
+      <c r="BL10" s="39" t="n">
         <v>1.724638</v>
       </c>
       <c r="BM10" s="28" t="n">
@@ -3927,18 +3958,18 @@
         <v>0.577114</v>
       </c>
       <c r="BO10" s="28" t="n"/>
-      <c r="BP10" s="25" t="n"/>
-      <c r="BQ10" s="27" t="n"/>
+      <c r="BP10" s="38" t="n"/>
+      <c r="BQ10" s="39" t="n"/>
       <c r="BR10" s="28" t="n"/>
       <c r="BS10" s="28" t="n"/>
       <c r="BT10" s="28" t="n"/>
-      <c r="BU10" s="25" t="n"/>
+      <c r="BU10" s="38" t="n"/>
       <c r="BV10" s="29" t="n"/>
       <c r="BW10" s="24" t="n"/>
-      <c r="BX10" s="30" t="n">
+      <c r="BX10" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY10" s="27" t="n">
+      <c r="BY10" s="39" t="n">
         <v>0.724638</v>
       </c>
       <c r="BZ10" s="24" t="inlineStr">
@@ -3998,7 +4029,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J11" s="25" t="n"/>
+      <c r="J11" s="38" t="n"/>
       <c r="K11" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -4007,7 +4038,7 @@
       <c r="L11" s="26" t="n">
         <v>102</v>
       </c>
-      <c r="M11" s="27" t="n">
+      <c r="M11" s="39" t="n">
         <v>2.02</v>
       </c>
       <c r="N11" s="28" t="n">
@@ -4047,11 +4078,11 @@
       <c r="X11" s="26" t="n">
         <v>15</v>
       </c>
-      <c r="Y11" s="25" t="n"/>
+      <c r="Y11" s="38" t="n"/>
       <c r="Z11" s="26" t="n"/>
       <c r="AA11" s="28" t="n"/>
       <c r="AB11" s="28" t="n"/>
-      <c r="AC11" s="30" t="n">
+      <c r="AC11" s="40" t="n">
         <v>1.275</v>
       </c>
       <c r="AD11" s="24" t="inlineStr">
@@ -4188,11 +4219,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ11" s="25" t="n"/>
+      <c r="BJ11" s="38" t="n"/>
       <c r="BK11" s="26" t="n">
         <v>102</v>
       </c>
-      <c r="BL11" s="27" t="n">
+      <c r="BL11" s="39" t="n">
         <v>2.02</v>
       </c>
       <c r="BM11" s="28" t="n">
@@ -4202,18 +4233,18 @@
         <v>0.492537</v>
       </c>
       <c r="BO11" s="28" t="n"/>
-      <c r="BP11" s="25" t="n"/>
-      <c r="BQ11" s="27" t="n"/>
+      <c r="BP11" s="38" t="n"/>
+      <c r="BQ11" s="39" t="n"/>
       <c r="BR11" s="28" t="n"/>
       <c r="BS11" s="28" t="n"/>
       <c r="BT11" s="28" t="n"/>
-      <c r="BU11" s="25" t="n"/>
+      <c r="BU11" s="38" t="n"/>
       <c r="BV11" s="29" t="n"/>
       <c r="BW11" s="24" t="n"/>
-      <c r="BX11" s="30" t="n">
+      <c r="BX11" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY11" s="27" t="n">
+      <c r="BY11" s="39" t="n">
         <v>1.02</v>
       </c>
       <c r="BZ11" s="24" t="inlineStr">
@@ -4273,7 +4304,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J12" s="25" t="n"/>
+      <c r="J12" s="38" t="n"/>
       <c r="K12" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -4282,7 +4313,7 @@
       <c r="L12" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="M12" s="27" t="n">
+      <c r="M12" s="39" t="n">
         <v>1.980392</v>
       </c>
       <c r="N12" s="28" t="n">
@@ -4322,11 +4353,11 @@
       <c r="X12" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y12" s="25" t="n"/>
+      <c r="Y12" s="38" t="n"/>
       <c r="Z12" s="26" t="n"/>
       <c r="AA12" s="28" t="n"/>
       <c r="AB12" s="28" t="n"/>
-      <c r="AC12" s="30" t="n">
+      <c r="AC12" s="40" t="n">
         <v>-1</v>
       </c>
       <c r="AD12" s="24" t="inlineStr">
@@ -4463,11 +4494,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ12" s="25" t="n"/>
+      <c r="BJ12" s="38" t="n"/>
       <c r="BK12" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="BL12" s="27" t="n">
+      <c r="BL12" s="39" t="n">
         <v>1.980392</v>
       </c>
       <c r="BM12" s="28" t="n">
@@ -4477,18 +4508,18 @@
         <v>0.502488</v>
       </c>
       <c r="BO12" s="28" t="n"/>
-      <c r="BP12" s="25" t="n"/>
-      <c r="BQ12" s="27" t="n"/>
+      <c r="BP12" s="38" t="n"/>
+      <c r="BQ12" s="39" t="n"/>
       <c r="BR12" s="28" t="n"/>
       <c r="BS12" s="28" t="n"/>
       <c r="BT12" s="28" t="n"/>
-      <c r="BU12" s="25" t="n"/>
+      <c r="BU12" s="38" t="n"/>
       <c r="BV12" s="29" t="n"/>
       <c r="BW12" s="24" t="n"/>
-      <c r="BX12" s="30" t="n">
+      <c r="BX12" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY12" s="27" t="n">
+      <c r="BY12" s="39" t="n">
         <v>-1</v>
       </c>
       <c r="BZ12" s="24" t="inlineStr">
@@ -4548,7 +4579,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J13" s="25" t="n"/>
+      <c r="J13" s="38" t="n"/>
       <c r="K13" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -4557,7 +4588,7 @@
       <c r="L13" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="M13" s="27" t="n">
+      <c r="M13" s="39" t="n">
         <v>1.980392</v>
       </c>
       <c r="N13" s="28" t="n">
@@ -4597,11 +4628,11 @@
       <c r="X13" s="26" t="n">
         <v>7</v>
       </c>
-      <c r="Y13" s="25" t="n"/>
+      <c r="Y13" s="38" t="n"/>
       <c r="Z13" s="26" t="n"/>
       <c r="AA13" s="28" t="n"/>
       <c r="AB13" s="28" t="n"/>
-      <c r="AC13" s="30" t="n">
+      <c r="AC13" s="40" t="n">
         <v>1.2255</v>
       </c>
       <c r="AD13" s="24" t="inlineStr">
@@ -4738,11 +4769,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ13" s="25" t="n"/>
+      <c r="BJ13" s="38" t="n"/>
       <c r="BK13" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="BL13" s="27" t="n">
+      <c r="BL13" s="39" t="n">
         <v>1.980392</v>
       </c>
       <c r="BM13" s="28" t="n">
@@ -4752,18 +4783,18 @@
         <v>0.502488</v>
       </c>
       <c r="BO13" s="28" t="n"/>
-      <c r="BP13" s="25" t="n"/>
-      <c r="BQ13" s="27" t="n"/>
+      <c r="BP13" s="38" t="n"/>
+      <c r="BQ13" s="39" t="n"/>
       <c r="BR13" s="28" t="n"/>
       <c r="BS13" s="28" t="n"/>
       <c r="BT13" s="28" t="n"/>
-      <c r="BU13" s="25" t="n"/>
+      <c r="BU13" s="38" t="n"/>
       <c r="BV13" s="29" t="n"/>
       <c r="BW13" s="24" t="n"/>
-      <c r="BX13" s="30" t="n">
+      <c r="BX13" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY13" s="27" t="n">
+      <c r="BY13" s="39" t="n">
         <v>0.980392</v>
       </c>
       <c r="BZ13" s="24" t="inlineStr">
@@ -4823,7 +4854,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J14" s="25" t="n"/>
+      <c r="J14" s="38" t="n"/>
       <c r="K14" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -4832,7 +4863,7 @@
       <c r="L14" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="M14" s="27" t="n">
+      <c r="M14" s="39" t="n">
         <v>1.961538</v>
       </c>
       <c r="N14" s="28" t="n">
@@ -4872,11 +4903,11 @@
       <c r="X14" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="Y14" s="25" t="n"/>
+      <c r="Y14" s="38" t="n"/>
       <c r="Z14" s="26" t="n"/>
       <c r="AA14" s="28" t="n"/>
       <c r="AB14" s="28" t="n"/>
-      <c r="AC14" s="30" t="n">
+      <c r="AC14" s="40" t="n">
         <v>-0.75</v>
       </c>
       <c r="AD14" s="24" t="inlineStr">
@@ -5013,11 +5044,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ14" s="25" t="n"/>
+      <c r="BJ14" s="38" t="n"/>
       <c r="BK14" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="BL14" s="27" t="n">
+      <c r="BL14" s="39" t="n">
         <v>1.961538</v>
       </c>
       <c r="BM14" s="28" t="n">
@@ -5027,18 +5058,18 @@
         <v>0.507463</v>
       </c>
       <c r="BO14" s="28" t="n"/>
-      <c r="BP14" s="25" t="n"/>
-      <c r="BQ14" s="27" t="n"/>
+      <c r="BP14" s="38" t="n"/>
+      <c r="BQ14" s="39" t="n"/>
       <c r="BR14" s="28" t="n"/>
       <c r="BS14" s="28" t="n"/>
       <c r="BT14" s="28" t="n"/>
-      <c r="BU14" s="25" t="n"/>
+      <c r="BU14" s="38" t="n"/>
       <c r="BV14" s="29" t="n"/>
       <c r="BW14" s="24" t="n"/>
-      <c r="BX14" s="30" t="n">
+      <c r="BX14" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY14" s="27" t="n">
+      <c r="BY14" s="39" t="n">
         <v>-1</v>
       </c>
       <c r="BZ14" s="24" t="inlineStr">
@@ -5098,7 +5129,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J15" s="25" t="n"/>
+      <c r="J15" s="38" t="n"/>
       <c r="K15" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -5107,7 +5138,7 @@
       <c r="L15" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="M15" s="27" t="n">
+      <c r="M15" s="39" t="n">
         <v>1.961538</v>
       </c>
       <c r="N15" s="28" t="n">
@@ -5147,11 +5178,11 @@
       <c r="X15" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="Y15" s="25" t="n"/>
+      <c r="Y15" s="38" t="n"/>
       <c r="Z15" s="26" t="n"/>
       <c r="AA15" s="28" t="n"/>
       <c r="AB15" s="28" t="n"/>
-      <c r="AC15" s="30" t="n">
+      <c r="AC15" s="40" t="n">
         <v>-1</v>
       </c>
       <c r="AD15" s="24" t="inlineStr">
@@ -5288,11 +5319,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ15" s="25" t="n"/>
+      <c r="BJ15" s="38" t="n"/>
       <c r="BK15" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="BL15" s="27" t="n">
+      <c r="BL15" s="39" t="n">
         <v>1.961538</v>
       </c>
       <c r="BM15" s="28" t="n">
@@ -5302,18 +5333,18 @@
         <v>0.507463</v>
       </c>
       <c r="BO15" s="28" t="n"/>
-      <c r="BP15" s="25" t="n"/>
-      <c r="BQ15" s="27" t="n"/>
+      <c r="BP15" s="38" t="n"/>
+      <c r="BQ15" s="39" t="n"/>
       <c r="BR15" s="28" t="n"/>
       <c r="BS15" s="28" t="n"/>
       <c r="BT15" s="28" t="n"/>
-      <c r="BU15" s="25" t="n"/>
+      <c r="BU15" s="38" t="n"/>
       <c r="BV15" s="29" t="n"/>
       <c r="BW15" s="24" t="n"/>
-      <c r="BX15" s="30" t="n">
+      <c r="BX15" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY15" s="27" t="n">
+      <c r="BY15" s="39" t="n">
         <v>-1</v>
       </c>
       <c r="BZ15" s="24" t="inlineStr">
@@ -5373,7 +5404,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J16" s="25" t="n"/>
+      <c r="J16" s="38" t="n"/>
       <c r="K16" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -5382,7 +5413,7 @@
       <c r="L16" s="26" t="n">
         <v>-111</v>
       </c>
-      <c r="M16" s="27" t="n">
+      <c r="M16" s="39" t="n">
         <v>1.900901</v>
       </c>
       <c r="N16" s="28" t="n">
@@ -5422,11 +5453,11 @@
       <c r="X16" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="Y16" s="25" t="n"/>
+      <c r="Y16" s="38" t="n"/>
       <c r="Z16" s="26" t="n"/>
       <c r="AA16" s="28" t="n"/>
       <c r="AB16" s="28" t="n"/>
-      <c r="AC16" s="30" t="n">
+      <c r="AC16" s="40" t="n">
         <v>-1.5</v>
       </c>
       <c r="AD16" s="24" t="inlineStr">
@@ -5563,11 +5594,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ16" s="25" t="n"/>
+      <c r="BJ16" s="38" t="n"/>
       <c r="BK16" s="26" t="n">
         <v>-111</v>
       </c>
-      <c r="BL16" s="27" t="n">
+      <c r="BL16" s="39" t="n">
         <v>1.900901</v>
       </c>
       <c r="BM16" s="28" t="n">
@@ -5577,18 +5608,18 @@
         <v>0.522388</v>
       </c>
       <c r="BO16" s="28" t="n"/>
-      <c r="BP16" s="25" t="n"/>
-      <c r="BQ16" s="27" t="n"/>
+      <c r="BP16" s="38" t="n"/>
+      <c r="BQ16" s="39" t="n"/>
       <c r="BR16" s="28" t="n"/>
       <c r="BS16" s="28" t="n"/>
       <c r="BT16" s="28" t="n"/>
-      <c r="BU16" s="25" t="n"/>
+      <c r="BU16" s="38" t="n"/>
       <c r="BV16" s="29" t="n"/>
       <c r="BW16" s="24" t="n"/>
-      <c r="BX16" s="30" t="n">
+      <c r="BX16" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY16" s="27" t="n">
+      <c r="BY16" s="39" t="n">
         <v>-1</v>
       </c>
       <c r="BZ16" s="24" t="inlineStr">
@@ -5648,7 +5679,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J17" s="25" t="n"/>
+      <c r="J17" s="38" t="n"/>
       <c r="K17" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -5657,7 +5688,7 @@
       <c r="L17" s="26" t="n">
         <v>-108</v>
       </c>
-      <c r="M17" s="27" t="n">
+      <c r="M17" s="39" t="n">
         <v>1.925926</v>
       </c>
       <c r="N17" s="28" t="n">
@@ -5697,11 +5728,11 @@
       <c r="X17" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="Y17" s="25" t="n"/>
+      <c r="Y17" s="38" t="n"/>
       <c r="Z17" s="26" t="n"/>
       <c r="AA17" s="28" t="n"/>
       <c r="AB17" s="28" t="n"/>
-      <c r="AC17" s="30" t="n">
+      <c r="AC17" s="40" t="n">
         <v>0.9258999999999999</v>
       </c>
       <c r="AD17" s="24" t="inlineStr">
@@ -5838,11 +5869,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ17" s="25" t="n"/>
+      <c r="BJ17" s="38" t="n"/>
       <c r="BK17" s="26" t="n">
         <v>-108</v>
       </c>
-      <c r="BL17" s="27" t="n">
+      <c r="BL17" s="39" t="n">
         <v>1.925926</v>
       </c>
       <c r="BM17" s="28" t="n">
@@ -5852,18 +5883,18 @@
         <v>0.5148509999999999</v>
       </c>
       <c r="BO17" s="28" t="n"/>
-      <c r="BP17" s="25" t="n"/>
-      <c r="BQ17" s="27" t="n"/>
+      <c r="BP17" s="38" t="n"/>
+      <c r="BQ17" s="39" t="n"/>
       <c r="BR17" s="28" t="n"/>
       <c r="BS17" s="28" t="n"/>
       <c r="BT17" s="28" t="n"/>
-      <c r="BU17" s="25" t="n"/>
+      <c r="BU17" s="38" t="n"/>
       <c r="BV17" s="29" t="n"/>
       <c r="BW17" s="24" t="n"/>
-      <c r="BX17" s="30" t="n">
+      <c r="BX17" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY17" s="27" t="n">
+      <c r="BY17" s="39" t="n">
         <v>0.925926</v>
       </c>
       <c r="BZ17" s="24" t="inlineStr">
@@ -5923,7 +5954,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J18" s="25" t="n"/>
+      <c r="J18" s="38" t="n"/>
       <c r="K18" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -5932,7 +5963,7 @@
       <c r="L18" s="26" t="n">
         <v>111</v>
       </c>
-      <c r="M18" s="27" t="n">
+      <c r="M18" s="39" t="n">
         <v>2.11</v>
       </c>
       <c r="N18" s="28" t="n">
@@ -5972,11 +6003,11 @@
       <c r="X18" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="Y18" s="25" t="n"/>
+      <c r="Y18" s="38" t="n"/>
       <c r="Z18" s="26" t="n"/>
       <c r="AA18" s="28" t="n"/>
       <c r="AB18" s="28" t="n"/>
-      <c r="AC18" s="30" t="n">
+      <c r="AC18" s="40" t="n">
         <v>-1.25</v>
       </c>
       <c r="AD18" s="24" t="inlineStr">
@@ -6113,11 +6144,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ18" s="25" t="n"/>
+      <c r="BJ18" s="38" t="n"/>
       <c r="BK18" s="26" t="n">
         <v>111</v>
       </c>
-      <c r="BL18" s="27" t="n">
+      <c r="BL18" s="39" t="n">
         <v>2.11</v>
       </c>
       <c r="BM18" s="28" t="n">
@@ -6127,18 +6158,18 @@
         <v>0.472637</v>
       </c>
       <c r="BO18" s="28" t="n"/>
-      <c r="BP18" s="25" t="n"/>
-      <c r="BQ18" s="27" t="n"/>
+      <c r="BP18" s="38" t="n"/>
+      <c r="BQ18" s="39" t="n"/>
       <c r="BR18" s="28" t="n"/>
       <c r="BS18" s="28" t="n"/>
       <c r="BT18" s="28" t="n"/>
-      <c r="BU18" s="25" t="n"/>
+      <c r="BU18" s="38" t="n"/>
       <c r="BV18" s="29" t="n"/>
       <c r="BW18" s="24" t="n"/>
-      <c r="BX18" s="30" t="n">
+      <c r="BX18" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY18" s="27" t="n">
+      <c r="BY18" s="39" t="n">
         <v>-1</v>
       </c>
       <c r="BZ18" s="24" t="inlineStr">
@@ -6198,7 +6229,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J19" s="25" t="n"/>
+      <c r="J19" s="38" t="n"/>
       <c r="K19" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -6207,7 +6238,7 @@
       <c r="L19" s="26" t="n">
         <v>-125</v>
       </c>
-      <c r="M19" s="27" t="n">
+      <c r="M19" s="39" t="n">
         <v>1.8</v>
       </c>
       <c r="N19" s="28" t="n">
@@ -6247,11 +6278,11 @@
       <c r="X19" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="Y19" s="25" t="n"/>
+      <c r="Y19" s="38" t="n"/>
       <c r="Z19" s="26" t="n"/>
       <c r="AA19" s="28" t="n"/>
       <c r="AB19" s="28" t="n"/>
-      <c r="AC19" s="30" t="n">
+      <c r="AC19" s="40" t="n">
         <v>1.2</v>
       </c>
       <c r="AD19" s="24" t="inlineStr">
@@ -6388,11 +6419,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ19" s="25" t="n"/>
+      <c r="BJ19" s="38" t="n"/>
       <c r="BK19" s="26" t="n">
         <v>-125</v>
       </c>
-      <c r="BL19" s="27" t="n">
+      <c r="BL19" s="39" t="n">
         <v>1.8</v>
       </c>
       <c r="BM19" s="28" t="n">
@@ -6402,18 +6433,18 @@
         <v>0.552239</v>
       </c>
       <c r="BO19" s="28" t="n"/>
-      <c r="BP19" s="25" t="n"/>
-      <c r="BQ19" s="27" t="n"/>
+      <c r="BP19" s="38" t="n"/>
+      <c r="BQ19" s="39" t="n"/>
       <c r="BR19" s="28" t="n"/>
       <c r="BS19" s="28" t="n"/>
       <c r="BT19" s="28" t="n"/>
-      <c r="BU19" s="25" t="n"/>
+      <c r="BU19" s="38" t="n"/>
       <c r="BV19" s="29" t="n"/>
       <c r="BW19" s="24" t="n"/>
-      <c r="BX19" s="30" t="n">
+      <c r="BX19" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY19" s="27" t="n">
+      <c r="BY19" s="39" t="n">
         <v>0.8</v>
       </c>
       <c r="BZ19" s="24" t="inlineStr">
@@ -6473,7 +6504,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J20" s="25" t="n"/>
+      <c r="J20" s="38" t="n"/>
       <c r="K20" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -6482,7 +6513,7 @@
       <c r="L20" s="26" t="n">
         <v>106</v>
       </c>
-      <c r="M20" s="27" t="n">
+      <c r="M20" s="39" t="n">
         <v>2.06</v>
       </c>
       <c r="N20" s="28" t="n">
@@ -6522,11 +6553,11 @@
       <c r="X20" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y20" s="25" t="n"/>
+      <c r="Y20" s="38" t="n"/>
       <c r="Z20" s="26" t="n"/>
       <c r="AA20" s="28" t="n"/>
       <c r="AB20" s="28" t="n"/>
-      <c r="AC20" s="30" t="n">
+      <c r="AC20" s="40" t="n">
         <v>0.795</v>
       </c>
       <c r="AD20" s="24" t="inlineStr">
@@ -6663,11 +6694,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ20" s="25" t="n"/>
+      <c r="BJ20" s="38" t="n"/>
       <c r="BK20" s="26" t="n">
         <v>106</v>
       </c>
-      <c r="BL20" s="27" t="n">
+      <c r="BL20" s="39" t="n">
         <v>2.06</v>
       </c>
       <c r="BM20" s="28" t="n">
@@ -6677,18 +6708,18 @@
         <v>0.482587</v>
       </c>
       <c r="BO20" s="28" t="n"/>
-      <c r="BP20" s="25" t="n"/>
-      <c r="BQ20" s="27" t="n"/>
+      <c r="BP20" s="38" t="n"/>
+      <c r="BQ20" s="39" t="n"/>
       <c r="BR20" s="28" t="n"/>
       <c r="BS20" s="28" t="n"/>
       <c r="BT20" s="28" t="n"/>
-      <c r="BU20" s="25" t="n"/>
+      <c r="BU20" s="38" t="n"/>
       <c r="BV20" s="29" t="n"/>
       <c r="BW20" s="24" t="n"/>
-      <c r="BX20" s="30" t="n">
+      <c r="BX20" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY20" s="27" t="n">
+      <c r="BY20" s="39" t="n">
         <v>1.06</v>
       </c>
       <c r="BZ20" s="24" t="inlineStr">
@@ -6748,7 +6779,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J21" s="25" t="n"/>
+      <c r="J21" s="38" t="n"/>
       <c r="K21" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -6757,7 +6788,7 @@
       <c r="L21" s="26" t="n">
         <v>-106</v>
       </c>
-      <c r="M21" s="27" t="n">
+      <c r="M21" s="39" t="n">
         <v>1.943396</v>
       </c>
       <c r="N21" s="28" t="n">
@@ -6797,11 +6828,11 @@
       <c r="X21" s="26" t="n">
         <v>10</v>
       </c>
-      <c r="Y21" s="25" t="n"/>
+      <c r="Y21" s="38" t="n"/>
       <c r="Z21" s="26" t="n"/>
       <c r="AA21" s="28" t="n"/>
       <c r="AB21" s="28" t="n"/>
-      <c r="AC21" s="30" t="n">
+      <c r="AC21" s="40" t="n">
         <v>0.9434</v>
       </c>
       <c r="AD21" s="24" t="inlineStr">
@@ -6848,11 +6879,11 @@
         </is>
       </c>
       <c r="BI21" s="24" t="n"/>
-      <c r="BJ21" s="25" t="n"/>
+      <c r="BJ21" s="38" t="n"/>
       <c r="BK21" s="26" t="n">
         <v>-106</v>
       </c>
-      <c r="BL21" s="27" t="n">
+      <c r="BL21" s="39" t="n">
         <v>1.943396</v>
       </c>
       <c r="BM21" s="28" t="n">
@@ -6862,16 +6893,16 @@
         <v>0.5124379999999999</v>
       </c>
       <c r="BO21" s="28" t="n"/>
-      <c r="BP21" s="25" t="n"/>
-      <c r="BQ21" s="27" t="n"/>
+      <c r="BP21" s="38" t="n"/>
+      <c r="BQ21" s="39" t="n"/>
       <c r="BR21" s="28" t="n"/>
       <c r="BS21" s="28" t="n"/>
       <c r="BT21" s="28" t="n"/>
-      <c r="BU21" s="25" t="n"/>
+      <c r="BU21" s="38" t="n"/>
       <c r="BV21" s="29" t="n"/>
       <c r="BW21" s="24" t="n"/>
-      <c r="BX21" s="30" t="n"/>
-      <c r="BY21" s="27" t="n"/>
+      <c r="BX21" s="40" t="n"/>
+      <c r="BY21" s="39" t="n"/>
       <c r="BZ21" s="24" t="n"/>
       <c r="CA21" s="31" t="n"/>
     </row>
@@ -6921,7 +6952,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J22" s="25" t="n"/>
+      <c r="J22" s="38" t="n"/>
       <c r="K22" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -6930,7 +6961,7 @@
       <c r="L22" s="26" t="n">
         <v>-106</v>
       </c>
-      <c r="M22" s="27" t="n">
+      <c r="M22" s="39" t="n">
         <v>1.943396</v>
       </c>
       <c r="N22" s="28" t="n">
@@ -6970,11 +7001,11 @@
       <c r="X22" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="Y22" s="25" t="n"/>
+      <c r="Y22" s="38" t="n"/>
       <c r="Z22" s="26" t="n"/>
       <c r="AA22" s="28" t="n"/>
       <c r="AB22" s="28" t="n"/>
-      <c r="AC22" s="30" t="n">
+      <c r="AC22" s="40" t="n">
         <v>0.9434</v>
       </c>
       <c r="AD22" s="24" t="inlineStr">
@@ -7021,11 +7052,11 @@
         </is>
       </c>
       <c r="BI22" s="24" t="n"/>
-      <c r="BJ22" s="25" t="n"/>
+      <c r="BJ22" s="38" t="n"/>
       <c r="BK22" s="26" t="n">
         <v>-106</v>
       </c>
-      <c r="BL22" s="27" t="n">
+      <c r="BL22" s="39" t="n">
         <v>1.943396</v>
       </c>
       <c r="BM22" s="28" t="n">
@@ -7035,16 +7066,16 @@
         <v>0.5124379999999999</v>
       </c>
       <c r="BO22" s="28" t="n"/>
-      <c r="BP22" s="25" t="n"/>
-      <c r="BQ22" s="27" t="n"/>
+      <c r="BP22" s="38" t="n"/>
+      <c r="BQ22" s="39" t="n"/>
       <c r="BR22" s="28" t="n"/>
       <c r="BS22" s="28" t="n"/>
       <c r="BT22" s="28" t="n"/>
-      <c r="BU22" s="25" t="n"/>
+      <c r="BU22" s="38" t="n"/>
       <c r="BV22" s="29" t="n"/>
       <c r="BW22" s="24" t="n"/>
-      <c r="BX22" s="30" t="n"/>
-      <c r="BY22" s="27" t="n"/>
+      <c r="BX22" s="40" t="n"/>
+      <c r="BY22" s="39" t="n"/>
       <c r="BZ22" s="24" t="n"/>
       <c r="CA22" s="31" t="n"/>
     </row>
@@ -7094,7 +7125,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J23" s="25" t="n"/>
+      <c r="J23" s="38" t="n"/>
       <c r="K23" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -7103,7 +7134,7 @@
       <c r="L23" s="26" t="n">
         <v>-141</v>
       </c>
-      <c r="M23" s="27" t="n">
+      <c r="M23" s="39" t="n">
         <v>1.70922</v>
       </c>
       <c r="N23" s="28" t="n">
@@ -7143,11 +7174,11 @@
       <c r="X23" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y23" s="25" t="n"/>
+      <c r="Y23" s="38" t="n"/>
       <c r="Z23" s="26" t="n"/>
       <c r="AA23" s="28" t="n"/>
       <c r="AB23" s="28" t="n"/>
-      <c r="AC23" s="30" t="n">
+      <c r="AC23" s="40" t="n">
         <v>1.2411</v>
       </c>
       <c r="AD23" s="24" t="inlineStr">
@@ -7194,11 +7225,11 @@
         </is>
       </c>
       <c r="BI23" s="24" t="n"/>
-      <c r="BJ23" s="25" t="n"/>
+      <c r="BJ23" s="38" t="n"/>
       <c r="BK23" s="26" t="n">
         <v>-141</v>
       </c>
-      <c r="BL23" s="27" t="n">
+      <c r="BL23" s="39" t="n">
         <v>1.70922</v>
       </c>
       <c r="BM23" s="28" t="n">
@@ -7208,16 +7239,16 @@
         <v>0.58209</v>
       </c>
       <c r="BO23" s="28" t="n"/>
-      <c r="BP23" s="25" t="n"/>
-      <c r="BQ23" s="27" t="n"/>
+      <c r="BP23" s="38" t="n"/>
+      <c r="BQ23" s="39" t="n"/>
       <c r="BR23" s="28" t="n"/>
       <c r="BS23" s="28" t="n"/>
       <c r="BT23" s="28" t="n"/>
-      <c r="BU23" s="25" t="n"/>
+      <c r="BU23" s="38" t="n"/>
       <c r="BV23" s="29" t="n"/>
       <c r="BW23" s="24" t="n"/>
-      <c r="BX23" s="30" t="n"/>
-      <c r="BY23" s="27" t="n"/>
+      <c r="BX23" s="40" t="n"/>
+      <c r="BY23" s="39" t="n"/>
       <c r="BZ23" s="24" t="n"/>
       <c r="CA23" s="31" t="n"/>
     </row>
@@ -7267,7 +7298,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J24" s="25" t="n"/>
+      <c r="J24" s="38" t="n"/>
       <c r="K24" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -7276,7 +7307,7 @@
       <c r="L24" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="M24" s="27" t="n">
+      <c r="M24" s="39" t="n">
         <v>1.75188</v>
       </c>
       <c r="N24" s="28" t="n">
@@ -7316,11 +7347,11 @@
       <c r="X24" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y24" s="25" t="n"/>
+      <c r="Y24" s="38" t="n"/>
       <c r="Z24" s="26" t="n"/>
       <c r="AA24" s="28" t="n"/>
       <c r="AB24" s="28" t="n"/>
-      <c r="AC24" s="30" t="n">
+      <c r="AC24" s="40" t="n">
         <v>-1.5</v>
       </c>
       <c r="AD24" s="24" t="inlineStr">
@@ -7367,11 +7398,11 @@
         </is>
       </c>
       <c r="BI24" s="24" t="n"/>
-      <c r="BJ24" s="25" t="n"/>
+      <c r="BJ24" s="38" t="n"/>
       <c r="BK24" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="BL24" s="27" t="n">
+      <c r="BL24" s="39" t="n">
         <v>1.75188</v>
       </c>
       <c r="BM24" s="28" t="n">
@@ -7381,16 +7412,16 @@
         <v>0.567164</v>
       </c>
       <c r="BO24" s="28" t="n"/>
-      <c r="BP24" s="25" t="n"/>
-      <c r="BQ24" s="27" t="n"/>
+      <c r="BP24" s="38" t="n"/>
+      <c r="BQ24" s="39" t="n"/>
       <c r="BR24" s="28" t="n"/>
       <c r="BS24" s="28" t="n"/>
       <c r="BT24" s="28" t="n"/>
-      <c r="BU24" s="25" t="n"/>
+      <c r="BU24" s="38" t="n"/>
       <c r="BV24" s="29" t="n"/>
       <c r="BW24" s="24" t="n"/>
-      <c r="BX24" s="30" t="n"/>
-      <c r="BY24" s="27" t="n"/>
+      <c r="BX24" s="40" t="n"/>
+      <c r="BY24" s="39" t="n"/>
       <c r="BZ24" s="24" t="n"/>
       <c r="CA24" s="31" t="n"/>
     </row>
@@ -7440,7 +7471,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J25" s="25" t="n"/>
+      <c r="J25" s="38" t="n"/>
       <c r="K25" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -7449,7 +7480,7 @@
       <c r="L25" s="26" t="n">
         <v>104</v>
       </c>
-      <c r="M25" s="27" t="n">
+      <c r="M25" s="39" t="n">
         <v>2.04</v>
       </c>
       <c r="N25" s="28" t="n">
@@ -7489,11 +7520,11 @@
       <c r="X25" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y25" s="25" t="n"/>
+      <c r="Y25" s="38" t="n"/>
       <c r="Z25" s="26" t="n"/>
       <c r="AA25" s="28" t="n"/>
       <c r="AB25" s="28" t="n"/>
-      <c r="AC25" s="30" t="n">
+      <c r="AC25" s="40" t="n">
         <v>1.3</v>
       </c>
       <c r="AD25" s="24" t="inlineStr">
@@ -7540,11 +7571,11 @@
         </is>
       </c>
       <c r="BI25" s="24" t="n"/>
-      <c r="BJ25" s="25" t="n"/>
+      <c r="BJ25" s="38" t="n"/>
       <c r="BK25" s="26" t="n">
         <v>104</v>
       </c>
-      <c r="BL25" s="27" t="n">
+      <c r="BL25" s="39" t="n">
         <v>2.04</v>
       </c>
       <c r="BM25" s="28" t="n">
@@ -7554,16 +7585,16 @@
         <v>0.487562</v>
       </c>
       <c r="BO25" s="28" t="n"/>
-      <c r="BP25" s="25" t="n"/>
-      <c r="BQ25" s="27" t="n"/>
+      <c r="BP25" s="38" t="n"/>
+      <c r="BQ25" s="39" t="n"/>
       <c r="BR25" s="28" t="n"/>
       <c r="BS25" s="28" t="n"/>
       <c r="BT25" s="28" t="n"/>
-      <c r="BU25" s="25" t="n"/>
+      <c r="BU25" s="38" t="n"/>
       <c r="BV25" s="29" t="n"/>
       <c r="BW25" s="24" t="n"/>
-      <c r="BX25" s="30" t="n"/>
-      <c r="BY25" s="27" t="n"/>
+      <c r="BX25" s="40" t="n"/>
+      <c r="BY25" s="39" t="n"/>
       <c r="BZ25" s="24" t="n"/>
       <c r="CA25" s="31" t="n"/>
     </row>
@@ -7613,7 +7644,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J26" s="25" t="n"/>
+      <c r="J26" s="38" t="n"/>
       <c r="K26" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -7622,7 +7653,7 @@
       <c r="L26" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="M26" s="27" t="n">
+      <c r="M26" s="39" t="n">
         <v>1.961538</v>
       </c>
       <c r="N26" s="28" t="n">
@@ -7662,11 +7693,11 @@
       <c r="X26" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="Y26" s="25" t="n"/>
+      <c r="Y26" s="38" t="n"/>
       <c r="Z26" s="26" t="n"/>
       <c r="AA26" s="28" t="n"/>
       <c r="AB26" s="28" t="n"/>
-      <c r="AC26" s="30" t="n">
+      <c r="AC26" s="40" t="n">
         <v>0.9615</v>
       </c>
       <c r="AD26" s="24" t="inlineStr">
@@ -7713,11 +7744,11 @@
         </is>
       </c>
       <c r="BI26" s="24" t="n"/>
-      <c r="BJ26" s="25" t="n"/>
+      <c r="BJ26" s="38" t="n"/>
       <c r="BK26" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="BL26" s="27" t="n">
+      <c r="BL26" s="39" t="n">
         <v>1.961538</v>
       </c>
       <c r="BM26" s="28" t="n">
@@ -7727,16 +7758,16 @@
         <v>0.507463</v>
       </c>
       <c r="BO26" s="28" t="n"/>
-      <c r="BP26" s="25" t="n"/>
-      <c r="BQ26" s="27" t="n"/>
+      <c r="BP26" s="38" t="n"/>
+      <c r="BQ26" s="39" t="n"/>
       <c r="BR26" s="28" t="n"/>
       <c r="BS26" s="28" t="n"/>
       <c r="BT26" s="28" t="n"/>
-      <c r="BU26" s="25" t="n"/>
+      <c r="BU26" s="38" t="n"/>
       <c r="BV26" s="29" t="n"/>
       <c r="BW26" s="24" t="n"/>
-      <c r="BX26" s="30" t="n"/>
-      <c r="BY26" s="27" t="n"/>
+      <c r="BX26" s="40" t="n"/>
+      <c r="BY26" s="39" t="n"/>
       <c r="BZ26" s="24" t="n"/>
       <c r="CA26" s="31" t="n"/>
     </row>
@@ -7786,7 +7817,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J27" s="25" t="n"/>
+      <c r="J27" s="38" t="n"/>
       <c r="K27" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -7795,7 +7826,7 @@
       <c r="L27" s="26" t="n">
         <v>120</v>
       </c>
-      <c r="M27" s="27" t="n">
+      <c r="M27" s="39" t="n">
         <v>2.2</v>
       </c>
       <c r="N27" s="28" t="n">
@@ -7835,11 +7866,11 @@
       <c r="X27" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="Y27" s="25" t="n"/>
+      <c r="Y27" s="38" t="n"/>
       <c r="Z27" s="26" t="n"/>
       <c r="AA27" s="28" t="n"/>
       <c r="AB27" s="28" t="n"/>
-      <c r="AC27" s="30" t="n">
+      <c r="AC27" s="40" t="n">
         <v>-0.75</v>
       </c>
       <c r="AD27" s="24" t="inlineStr">
@@ -7886,11 +7917,11 @@
         </is>
       </c>
       <c r="BI27" s="24" t="n"/>
-      <c r="BJ27" s="25" t="n"/>
+      <c r="BJ27" s="38" t="n"/>
       <c r="BK27" s="26" t="n">
         <v>120</v>
       </c>
-      <c r="BL27" s="27" t="n">
+      <c r="BL27" s="39" t="n">
         <v>2.2</v>
       </c>
       <c r="BM27" s="28" t="n">
@@ -7900,16 +7931,16 @@
         <v>0.452736</v>
       </c>
       <c r="BO27" s="28" t="n"/>
-      <c r="BP27" s="25" t="n"/>
-      <c r="BQ27" s="27" t="n"/>
+      <c r="BP27" s="38" t="n"/>
+      <c r="BQ27" s="39" t="n"/>
       <c r="BR27" s="28" t="n"/>
       <c r="BS27" s="28" t="n"/>
       <c r="BT27" s="28" t="n"/>
-      <c r="BU27" s="25" t="n"/>
+      <c r="BU27" s="38" t="n"/>
       <c r="BV27" s="29" t="n"/>
       <c r="BW27" s="24" t="n"/>
-      <c r="BX27" s="30" t="n"/>
-      <c r="BY27" s="27" t="n"/>
+      <c r="BX27" s="40" t="n"/>
+      <c r="BY27" s="39" t="n"/>
       <c r="BZ27" s="24" t="n"/>
       <c r="CA27" s="31" t="n"/>
     </row>
@@ -7959,7 +7990,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J28" s="25" t="n"/>
+      <c r="J28" s="38" t="n"/>
       <c r="K28" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -7968,7 +7999,7 @@
       <c r="L28" s="26" t="n">
         <v>100</v>
       </c>
-      <c r="M28" s="27" t="n">
+      <c r="M28" s="39" t="n">
         <v>2</v>
       </c>
       <c r="N28" s="28" t="n">
@@ -8008,11 +8039,11 @@
       <c r="X28" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="Y28" s="25" t="n"/>
+      <c r="Y28" s="38" t="n"/>
       <c r="Z28" s="26" t="n"/>
       <c r="AA28" s="28" t="n"/>
       <c r="AB28" s="28" t="n"/>
-      <c r="AC28" s="30" t="n">
+      <c r="AC28" s="40" t="n">
         <v>-0.75</v>
       </c>
       <c r="AD28" s="24" t="inlineStr">
@@ -8059,11 +8090,11 @@
         </is>
       </c>
       <c r="BI28" s="24" t="n"/>
-      <c r="BJ28" s="25" t="n"/>
+      <c r="BJ28" s="38" t="n"/>
       <c r="BK28" s="26" t="n">
         <v>100</v>
       </c>
-      <c r="BL28" s="27" t="n">
+      <c r="BL28" s="39" t="n">
         <v>2</v>
       </c>
       <c r="BM28" s="28" t="n">
@@ -8073,16 +8104,16 @@
         <v>0.497512</v>
       </c>
       <c r="BO28" s="28" t="n"/>
-      <c r="BP28" s="25" t="n"/>
-      <c r="BQ28" s="27" t="n"/>
+      <c r="BP28" s="38" t="n"/>
+      <c r="BQ28" s="39" t="n"/>
       <c r="BR28" s="28" t="n"/>
       <c r="BS28" s="28" t="n"/>
       <c r="BT28" s="28" t="n"/>
-      <c r="BU28" s="25" t="n"/>
+      <c r="BU28" s="38" t="n"/>
       <c r="BV28" s="29" t="n"/>
       <c r="BW28" s="24" t="n"/>
-      <c r="BX28" s="30" t="n"/>
-      <c r="BY28" s="27" t="n"/>
+      <c r="BX28" s="40" t="n"/>
+      <c r="BY28" s="39" t="n"/>
       <c r="BZ28" s="24" t="n"/>
       <c r="CA28" s="31" t="n"/>
     </row>
@@ -8132,7 +8163,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J29" s="25" t="n"/>
+      <c r="J29" s="38" t="n"/>
       <c r="K29" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -8141,7 +8172,7 @@
       <c r="L29" s="26" t="n">
         <v>108</v>
       </c>
-      <c r="M29" s="27" t="n">
+      <c r="M29" s="39" t="n">
         <v>2.08</v>
       </c>
       <c r="N29" s="28" t="n">
@@ -8181,11 +8212,11 @@
       <c r="X29" s="26" t="n">
         <v>8</v>
       </c>
-      <c r="Y29" s="25" t="n"/>
+      <c r="Y29" s="38" t="n"/>
       <c r="Z29" s="26" t="n"/>
       <c r="AA29" s="28" t="n"/>
       <c r="AB29" s="28" t="n"/>
-      <c r="AC29" s="30" t="n">
+      <c r="AC29" s="40" t="n">
         <v>1.35</v>
       </c>
       <c r="AD29" s="24" t="inlineStr">
@@ -8322,11 +8353,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ29" s="25" t="n"/>
+      <c r="BJ29" s="38" t="n"/>
       <c r="BK29" s="26" t="n">
         <v>108</v>
       </c>
-      <c r="BL29" s="27" t="n">
+      <c r="BL29" s="39" t="n">
         <v>2.08</v>
       </c>
       <c r="BM29" s="28" t="n">
@@ -8336,18 +8367,18 @@
         <v>0.477612</v>
       </c>
       <c r="BO29" s="28" t="n"/>
-      <c r="BP29" s="25" t="n"/>
-      <c r="BQ29" s="27" t="n"/>
+      <c r="BP29" s="38" t="n"/>
+      <c r="BQ29" s="39" t="n"/>
       <c r="BR29" s="28" t="n"/>
       <c r="BS29" s="28" t="n"/>
       <c r="BT29" s="28" t="n"/>
-      <c r="BU29" s="25" t="n"/>
+      <c r="BU29" s="38" t="n"/>
       <c r="BV29" s="29" t="n"/>
       <c r="BW29" s="24" t="n"/>
-      <c r="BX29" s="30" t="n">
+      <c r="BX29" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY29" s="27" t="n">
+      <c r="BY29" s="39" t="n">
         <v>1.08</v>
       </c>
       <c r="BZ29" s="24" t="inlineStr">
@@ -8407,7 +8438,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J30" s="25" t="n"/>
+      <c r="J30" s="38" t="n"/>
       <c r="K30" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -8416,7 +8447,7 @@
       <c r="L30" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="M30" s="27" t="n">
+      <c r="M30" s="39" t="n">
         <v>1.75188</v>
       </c>
       <c r="N30" s="28" t="n">
@@ -8456,11 +8487,11 @@
       <c r="X30" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="Y30" s="25" t="n"/>
+      <c r="Y30" s="38" t="n"/>
       <c r="Z30" s="26" t="n"/>
       <c r="AA30" s="28" t="n"/>
       <c r="AB30" s="28" t="n"/>
-      <c r="AC30" s="30" t="n">
+      <c r="AC30" s="40" t="n">
         <v>1.1278</v>
       </c>
       <c r="AD30" s="24" t="inlineStr">
@@ -8597,11 +8628,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ30" s="25" t="n"/>
+      <c r="BJ30" s="38" t="n"/>
       <c r="BK30" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="BL30" s="27" t="n">
+      <c r="BL30" s="39" t="n">
         <v>1.75188</v>
       </c>
       <c r="BM30" s="28" t="n">
@@ -8611,18 +8642,18 @@
         <v>0.567164</v>
       </c>
       <c r="BO30" s="28" t="n"/>
-      <c r="BP30" s="25" t="n"/>
-      <c r="BQ30" s="27" t="n"/>
+      <c r="BP30" s="38" t="n"/>
+      <c r="BQ30" s="39" t="n"/>
       <c r="BR30" s="28" t="n"/>
       <c r="BS30" s="28" t="n"/>
       <c r="BT30" s="28" t="n"/>
-      <c r="BU30" s="25" t="n"/>
+      <c r="BU30" s="38" t="n"/>
       <c r="BV30" s="29" t="n"/>
       <c r="BW30" s="24" t="n"/>
-      <c r="BX30" s="30" t="n">
+      <c r="BX30" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY30" s="27" t="n">
+      <c r="BY30" s="39" t="n">
         <v>0.75188</v>
       </c>
       <c r="BZ30" s="24" t="inlineStr">
@@ -8682,7 +8713,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J31" s="25" t="n"/>
+      <c r="J31" s="38" t="n"/>
       <c r="K31" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -8691,7 +8722,7 @@
       <c r="L31" s="26" t="n">
         <v>130</v>
       </c>
-      <c r="M31" s="27" t="n">
+      <c r="M31" s="39" t="n">
         <v>2.3</v>
       </c>
       <c r="N31" s="28" t="n">
@@ -8731,11 +8762,11 @@
       <c r="X31" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y31" s="25" t="n"/>
+      <c r="Y31" s="38" t="n"/>
       <c r="Z31" s="26" t="n"/>
       <c r="AA31" s="28" t="n"/>
       <c r="AB31" s="28" t="n"/>
-      <c r="AC31" s="30" t="n">
+      <c r="AC31" s="40" t="n">
         <v>-1</v>
       </c>
       <c r="AD31" s="24" t="inlineStr">
@@ -8872,11 +8903,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ31" s="25" t="n"/>
+      <c r="BJ31" s="38" t="n"/>
       <c r="BK31" s="26" t="n">
         <v>130</v>
       </c>
-      <c r="BL31" s="27" t="n">
+      <c r="BL31" s="39" t="n">
         <v>2.3</v>
       </c>
       <c r="BM31" s="28" t="n">
@@ -8886,18 +8917,18 @@
         <v>0.432836</v>
       </c>
       <c r="BO31" s="28" t="n"/>
-      <c r="BP31" s="25" t="n"/>
-      <c r="BQ31" s="27" t="n"/>
+      <c r="BP31" s="38" t="n"/>
+      <c r="BQ31" s="39" t="n"/>
       <c r="BR31" s="28" t="n"/>
       <c r="BS31" s="28" t="n"/>
       <c r="BT31" s="28" t="n"/>
-      <c r="BU31" s="25" t="n"/>
+      <c r="BU31" s="38" t="n"/>
       <c r="BV31" s="29" t="n"/>
       <c r="BW31" s="24" t="n"/>
-      <c r="BX31" s="30" t="n">
+      <c r="BX31" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY31" s="27" t="n">
+      <c r="BY31" s="39" t="n">
         <v>-1</v>
       </c>
       <c r="BZ31" s="24" t="inlineStr">
@@ -8957,7 +8988,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J32" s="25" t="n"/>
+      <c r="J32" s="38" t="n"/>
       <c r="K32" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -8966,7 +8997,7 @@
       <c r="L32" s="26" t="n">
         <v>-108</v>
       </c>
-      <c r="M32" s="27" t="n">
+      <c r="M32" s="39" t="n">
         <v>1.925926</v>
       </c>
       <c r="N32" s="28" t="n">
@@ -8998,11 +9029,11 @@
       <c r="V32" s="24" t="n"/>
       <c r="W32" s="26" t="n"/>
       <c r="X32" s="26" t="n"/>
-      <c r="Y32" s="25" t="n"/>
+      <c r="Y32" s="38" t="n"/>
       <c r="Z32" s="26" t="n"/>
       <c r="AA32" s="28" t="n"/>
       <c r="AB32" s="28" t="n"/>
-      <c r="AC32" s="30" t="n"/>
+      <c r="AC32" s="40" t="n"/>
       <c r="AD32" s="24" t="n"/>
       <c r="AE32" s="31" t="inlineStr">
         <is>
@@ -9133,11 +9164,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ32" s="25" t="n"/>
+      <c r="BJ32" s="38" t="n"/>
       <c r="BK32" s="26" t="n">
         <v>-108</v>
       </c>
-      <c r="BL32" s="27" t="n">
+      <c r="BL32" s="39" t="n">
         <v>1.925926</v>
       </c>
       <c r="BM32" s="28" t="n">
@@ -9147,16 +9178,16 @@
         <v>0.517413</v>
       </c>
       <c r="BO32" s="28" t="n"/>
-      <c r="BP32" s="25" t="n"/>
-      <c r="BQ32" s="27" t="n"/>
+      <c r="BP32" s="38" t="n"/>
+      <c r="BQ32" s="39" t="n"/>
       <c r="BR32" s="28" t="n"/>
       <c r="BS32" s="28" t="n"/>
       <c r="BT32" s="28" t="n"/>
-      <c r="BU32" s="25" t="n"/>
+      <c r="BU32" s="38" t="n"/>
       <c r="BV32" s="29" t="n"/>
       <c r="BW32" s="24" t="n"/>
-      <c r="BX32" s="30" t="n"/>
-      <c r="BY32" s="27" t="n"/>
+      <c r="BX32" s="40" t="n"/>
+      <c r="BY32" s="39" t="n"/>
       <c r="BZ32" s="24" t="n"/>
       <c r="CA32" s="31" t="n"/>
     </row>
@@ -9206,7 +9237,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J33" s="25" t="n"/>
+      <c r="J33" s="38" t="n"/>
       <c r="K33" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -9215,7 +9246,7 @@
       <c r="L33" s="26" t="n">
         <v>135</v>
       </c>
-      <c r="M33" s="27" t="n">
+      <c r="M33" s="39" t="n">
         <v>2.35</v>
       </c>
       <c r="N33" s="28" t="n">
@@ -9247,11 +9278,11 @@
       <c r="V33" s="24" t="n"/>
       <c r="W33" s="26" t="n"/>
       <c r="X33" s="26" t="n"/>
-      <c r="Y33" s="25" t="n"/>
+      <c r="Y33" s="38" t="n"/>
       <c r="Z33" s="26" t="n"/>
       <c r="AA33" s="28" t="n"/>
       <c r="AB33" s="28" t="n"/>
-      <c r="AC33" s="30" t="n"/>
+      <c r="AC33" s="40" t="n"/>
       <c r="AD33" s="24" t="n"/>
       <c r="AE33" s="31" t="inlineStr">
         <is>
@@ -9382,11 +9413,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ33" s="25" t="n"/>
+      <c r="BJ33" s="38" t="n"/>
       <c r="BK33" s="26" t="n">
         <v>135</v>
       </c>
-      <c r="BL33" s="27" t="n">
+      <c r="BL33" s="39" t="n">
         <v>2.35</v>
       </c>
       <c r="BM33" s="28" t="n">
@@ -9396,16 +9427,16 @@
         <v>0.422886</v>
       </c>
       <c r="BO33" s="28" t="n"/>
-      <c r="BP33" s="25" t="n"/>
-      <c r="BQ33" s="27" t="n"/>
+      <c r="BP33" s="38" t="n"/>
+      <c r="BQ33" s="39" t="n"/>
       <c r="BR33" s="28" t="n"/>
       <c r="BS33" s="28" t="n"/>
       <c r="BT33" s="28" t="n"/>
-      <c r="BU33" s="25" t="n"/>
+      <c r="BU33" s="38" t="n"/>
       <c r="BV33" s="29" t="n"/>
       <c r="BW33" s="24" t="n"/>
-      <c r="BX33" s="30" t="n"/>
-      <c r="BY33" s="27" t="n"/>
+      <c r="BX33" s="40" t="n"/>
+      <c r="BY33" s="39" t="n"/>
       <c r="BZ33" s="24" t="n"/>
       <c r="CA33" s="31" t="n"/>
     </row>
@@ -9455,7 +9486,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J34" s="25" t="n"/>
+      <c r="J34" s="38" t="n"/>
       <c r="K34" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -9464,7 +9495,7 @@
       <c r="L34" s="26" t="n">
         <v>-127</v>
       </c>
-      <c r="M34" s="27" t="n">
+      <c r="M34" s="39" t="n">
         <v>1.787402</v>
       </c>
       <c r="N34" s="28" t="n">
@@ -9496,11 +9527,11 @@
       <c r="V34" s="24" t="n"/>
       <c r="W34" s="26" t="n"/>
       <c r="X34" s="26" t="n"/>
-      <c r="Y34" s="25" t="n"/>
+      <c r="Y34" s="38" t="n"/>
       <c r="Z34" s="26" t="n"/>
       <c r="AA34" s="28" t="n"/>
       <c r="AB34" s="28" t="n"/>
-      <c r="AC34" s="30" t="n"/>
+      <c r="AC34" s="40" t="n"/>
       <c r="AD34" s="24" t="n"/>
       <c r="AE34" s="31" t="inlineStr">
         <is>
@@ -9631,11 +9662,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ34" s="25" t="n"/>
+      <c r="BJ34" s="38" t="n"/>
       <c r="BK34" s="26" t="n">
         <v>-127</v>
       </c>
-      <c r="BL34" s="27" t="n">
+      <c r="BL34" s="39" t="n">
         <v>1.787402</v>
       </c>
       <c r="BM34" s="28" t="n">
@@ -9645,16 +9676,16 @@
         <v>0.557214</v>
       </c>
       <c r="BO34" s="28" t="n"/>
-      <c r="BP34" s="25" t="n"/>
-      <c r="BQ34" s="27" t="n"/>
+      <c r="BP34" s="38" t="n"/>
+      <c r="BQ34" s="39" t="n"/>
       <c r="BR34" s="28" t="n"/>
       <c r="BS34" s="28" t="n"/>
       <c r="BT34" s="28" t="n"/>
-      <c r="BU34" s="25" t="n"/>
+      <c r="BU34" s="38" t="n"/>
       <c r="BV34" s="29" t="n"/>
       <c r="BW34" s="24" t="n"/>
-      <c r="BX34" s="30" t="n"/>
-      <c r="BY34" s="27" t="n"/>
+      <c r="BX34" s="40" t="n"/>
+      <c r="BY34" s="39" t="n"/>
       <c r="BZ34" s="24" t="n"/>
       <c r="CA34" s="31" t="n"/>
     </row>
@@ -9704,7 +9735,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J35" s="25" t="n"/>
+      <c r="J35" s="38" t="n"/>
       <c r="K35" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -9713,7 +9744,7 @@
       <c r="L35" s="26" t="n">
         <v>-117</v>
       </c>
-      <c r="M35" s="27" t="n">
+      <c r="M35" s="39" t="n">
         <v>1.854701</v>
       </c>
       <c r="N35" s="28" t="n">
@@ -9745,11 +9776,11 @@
       <c r="V35" s="24" t="n"/>
       <c r="W35" s="26" t="n"/>
       <c r="X35" s="26" t="n"/>
-      <c r="Y35" s="25" t="n"/>
+      <c r="Y35" s="38" t="n"/>
       <c r="Z35" s="26" t="n"/>
       <c r="AA35" s="28" t="n"/>
       <c r="AB35" s="28" t="n"/>
-      <c r="AC35" s="30" t="n"/>
+      <c r="AC35" s="40" t="n"/>
       <c r="AD35" s="24" t="n"/>
       <c r="AE35" s="31" t="inlineStr">
         <is>
@@ -9880,11 +9911,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ35" s="25" t="n"/>
+      <c r="BJ35" s="38" t="n"/>
       <c r="BK35" s="26" t="n">
         <v>-117</v>
       </c>
-      <c r="BL35" s="27" t="n">
+      <c r="BL35" s="39" t="n">
         <v>1.854701</v>
       </c>
       <c r="BM35" s="28" t="n">
@@ -9894,16 +9925,16 @@
         <v>0.537313</v>
       </c>
       <c r="BO35" s="28" t="n"/>
-      <c r="BP35" s="25" t="n"/>
-      <c r="BQ35" s="27" t="n"/>
+      <c r="BP35" s="38" t="n"/>
+      <c r="BQ35" s="39" t="n"/>
       <c r="BR35" s="28" t="n"/>
       <c r="BS35" s="28" t="n"/>
       <c r="BT35" s="28" t="n"/>
-      <c r="BU35" s="25" t="n"/>
+      <c r="BU35" s="38" t="n"/>
       <c r="BV35" s="29" t="n"/>
       <c r="BW35" s="24" t="n"/>
-      <c r="BX35" s="30" t="n"/>
-      <c r="BY35" s="27" t="n"/>
+      <c r="BX35" s="40" t="n"/>
+      <c r="BY35" s="39" t="n"/>
       <c r="BZ35" s="24" t="n"/>
       <c r="CA35" s="31" t="n"/>
     </row>
@@ -9953,7 +9984,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J36" s="25" t="n"/>
+      <c r="J36" s="38" t="n"/>
       <c r="K36" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -9962,7 +9993,7 @@
       <c r="L36" s="26" t="n">
         <v>-125</v>
       </c>
-      <c r="M36" s="27" t="n">
+      <c r="M36" s="39" t="n">
         <v>1.8</v>
       </c>
       <c r="N36" s="28" t="n">
@@ -9994,11 +10025,11 @@
       <c r="V36" s="24" t="n"/>
       <c r="W36" s="26" t="n"/>
       <c r="X36" s="26" t="n"/>
-      <c r="Y36" s="25" t="n"/>
+      <c r="Y36" s="38" t="n"/>
       <c r="Z36" s="26" t="n"/>
       <c r="AA36" s="28" t="n"/>
       <c r="AB36" s="28" t="n"/>
-      <c r="AC36" s="30" t="n"/>
+      <c r="AC36" s="40" t="n"/>
       <c r="AD36" s="24" t="n"/>
       <c r="AE36" s="31" t="inlineStr">
         <is>
@@ -10129,11 +10160,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ36" s="25" t="n"/>
+      <c r="BJ36" s="38" t="n"/>
       <c r="BK36" s="26" t="n">
         <v>-125</v>
       </c>
-      <c r="BL36" s="27" t="n">
+      <c r="BL36" s="39" t="n">
         <v>1.8</v>
       </c>
       <c r="BM36" s="28" t="n">
@@ -10143,16 +10174,16 @@
         <v>0.552239</v>
       </c>
       <c r="BO36" s="28" t="n"/>
-      <c r="BP36" s="25" t="n"/>
-      <c r="BQ36" s="27" t="n"/>
+      <c r="BP36" s="38" t="n"/>
+      <c r="BQ36" s="39" t="n"/>
       <c r="BR36" s="28" t="n"/>
       <c r="BS36" s="28" t="n"/>
       <c r="BT36" s="28" t="n"/>
-      <c r="BU36" s="25" t="n"/>
+      <c r="BU36" s="38" t="n"/>
       <c r="BV36" s="29" t="n"/>
       <c r="BW36" s="24" t="n"/>
-      <c r="BX36" s="30" t="n"/>
-      <c r="BY36" s="27" t="n"/>
+      <c r="BX36" s="40" t="n"/>
+      <c r="BY36" s="39" t="n"/>
       <c r="BZ36" s="24" t="n"/>
       <c r="CA36" s="31" t="n"/>
     </row>
@@ -10202,7 +10233,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J37" s="25" t="n"/>
+      <c r="J37" s="38" t="n"/>
       <c r="K37" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -10211,7 +10242,7 @@
       <c r="L37" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="M37" s="27" t="n">
+      <c r="M37" s="39" t="n">
         <v>1.980392</v>
       </c>
       <c r="N37" s="28" t="n">
@@ -10243,11 +10274,11 @@
       <c r="V37" s="24" t="n"/>
       <c r="W37" s="26" t="n"/>
       <c r="X37" s="26" t="n"/>
-      <c r="Y37" s="25" t="n"/>
+      <c r="Y37" s="38" t="n"/>
       <c r="Z37" s="26" t="n"/>
       <c r="AA37" s="28" t="n"/>
       <c r="AB37" s="28" t="n"/>
-      <c r="AC37" s="30" t="n"/>
+      <c r="AC37" s="40" t="n"/>
       <c r="AD37" s="24" t="n"/>
       <c r="AE37" s="31" t="inlineStr">
         <is>
@@ -10378,11 +10409,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ37" s="25" t="n"/>
+      <c r="BJ37" s="38" t="n"/>
       <c r="BK37" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="BL37" s="27" t="n">
+      <c r="BL37" s="39" t="n">
         <v>1.980392</v>
       </c>
       <c r="BM37" s="28" t="n">
@@ -10392,16 +10423,16 @@
         <v>0.502488</v>
       </c>
       <c r="BO37" s="28" t="n"/>
-      <c r="BP37" s="25" t="n"/>
-      <c r="BQ37" s="27" t="n"/>
+      <c r="BP37" s="38" t="n"/>
+      <c r="BQ37" s="39" t="n"/>
       <c r="BR37" s="28" t="n"/>
       <c r="BS37" s="28" t="n"/>
       <c r="BT37" s="28" t="n"/>
-      <c r="BU37" s="25" t="n"/>
+      <c r="BU37" s="38" t="n"/>
       <c r="BV37" s="29" t="n"/>
       <c r="BW37" s="24" t="n"/>
-      <c r="BX37" s="30" t="n"/>
-      <c r="BY37" s="27" t="n"/>
+      <c r="BX37" s="40" t="n"/>
+      <c r="BY37" s="39" t="n"/>
       <c r="BZ37" s="24" t="n"/>
       <c r="CA37" s="31" t="n"/>
     </row>
@@ -10451,7 +10482,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J38" s="25" t="n"/>
+      <c r="J38" s="38" t="n"/>
       <c r="K38" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -10460,7 +10491,7 @@
       <c r="L38" s="26" t="n">
         <v>108</v>
       </c>
-      <c r="M38" s="27" t="n">
+      <c r="M38" s="39" t="n">
         <v>2.08</v>
       </c>
       <c r="N38" s="28" t="n">
@@ -10492,11 +10523,11 @@
       <c r="V38" s="24" t="n"/>
       <c r="W38" s="26" t="n"/>
       <c r="X38" s="26" t="n"/>
-      <c r="Y38" s="25" t="n"/>
+      <c r="Y38" s="38" t="n"/>
       <c r="Z38" s="26" t="n"/>
       <c r="AA38" s="28" t="n"/>
       <c r="AB38" s="28" t="n"/>
-      <c r="AC38" s="30" t="n"/>
+      <c r="AC38" s="40" t="n"/>
       <c r="AD38" s="24" t="n"/>
       <c r="AE38" s="31" t="inlineStr">
         <is>
@@ -10627,11 +10658,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ38" s="25" t="n"/>
+      <c r="BJ38" s="38" t="n"/>
       <c r="BK38" s="26" t="n">
         <v>108</v>
       </c>
-      <c r="BL38" s="27" t="n">
+      <c r="BL38" s="39" t="n">
         <v>2.08</v>
       </c>
       <c r="BM38" s="28" t="n">
@@ -10641,16 +10672,16 @@
         <v>0.475248</v>
       </c>
       <c r="BO38" s="28" t="n"/>
-      <c r="BP38" s="25" t="n"/>
-      <c r="BQ38" s="27" t="n"/>
+      <c r="BP38" s="38" t="n"/>
+      <c r="BQ38" s="39" t="n"/>
       <c r="BR38" s="28" t="n"/>
       <c r="BS38" s="28" t="n"/>
       <c r="BT38" s="28" t="n"/>
-      <c r="BU38" s="25" t="n"/>
+      <c r="BU38" s="38" t="n"/>
       <c r="BV38" s="29" t="n"/>
       <c r="BW38" s="24" t="n"/>
-      <c r="BX38" s="30" t="n"/>
-      <c r="BY38" s="27" t="n"/>
+      <c r="BX38" s="40" t="n"/>
+      <c r="BY38" s="39" t="n"/>
       <c r="BZ38" s="24" t="n"/>
       <c r="CA38" s="31" t="n"/>
     </row>
@@ -10700,7 +10731,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J39" s="25" t="n"/>
+      <c r="J39" s="38" t="n"/>
       <c r="K39" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -10709,7 +10740,7 @@
       <c r="L39" s="26" t="n">
         <v>-108</v>
       </c>
-      <c r="M39" s="27" t="n">
+      <c r="M39" s="39" t="n">
         <v>1.925926</v>
       </c>
       <c r="N39" s="28" t="n">
@@ -10741,11 +10772,11 @@
       <c r="V39" s="24" t="n"/>
       <c r="W39" s="26" t="n"/>
       <c r="X39" s="26" t="n"/>
-      <c r="Y39" s="25" t="n"/>
+      <c r="Y39" s="38" t="n"/>
       <c r="Z39" s="26" t="n"/>
       <c r="AA39" s="28" t="n"/>
       <c r="AB39" s="28" t="n"/>
-      <c r="AC39" s="30" t="n"/>
+      <c r="AC39" s="40" t="n"/>
       <c r="AD39" s="24" t="n"/>
       <c r="AE39" s="31" t="inlineStr">
         <is>
@@ -10876,11 +10907,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ39" s="25" t="n"/>
+      <c r="BJ39" s="38" t="n"/>
       <c r="BK39" s="26" t="n">
         <v>-108</v>
       </c>
-      <c r="BL39" s="27" t="n">
+      <c r="BL39" s="39" t="n">
         <v>1.925926</v>
       </c>
       <c r="BM39" s="28" t="n">
@@ -10890,16 +10921,16 @@
         <v>0.517413</v>
       </c>
       <c r="BO39" s="28" t="n"/>
-      <c r="BP39" s="25" t="n"/>
-      <c r="BQ39" s="27" t="n"/>
+      <c r="BP39" s="38" t="n"/>
+      <c r="BQ39" s="39" t="n"/>
       <c r="BR39" s="28" t="n"/>
       <c r="BS39" s="28" t="n"/>
       <c r="BT39" s="28" t="n"/>
-      <c r="BU39" s="25" t="n"/>
+      <c r="BU39" s="38" t="n"/>
       <c r="BV39" s="29" t="n"/>
       <c r="BW39" s="24" t="n"/>
-      <c r="BX39" s="30" t="n"/>
-      <c r="BY39" s="27" t="n"/>
+      <c r="BX39" s="40" t="n"/>
+      <c r="BY39" s="39" t="n"/>
       <c r="BZ39" s="24" t="n"/>
       <c r="CA39" s="31" t="n"/>
     </row>

--- a/data/picks.xlsx
+++ b/data/picks.xlsx
@@ -21,10 +21,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="0.0%"/>
-    <numFmt numFmtId="165" formatCode="0.0000"/>
-    <numFmt numFmtId="166" formatCode="0.0###"/>
-    <numFmt numFmtId="167" formatCode="0.000000"/>
+    <numFmt numFmtId="164" formatCode="0.0###"/>
+    <numFmt numFmtId="165" formatCode="0.000000"/>
+    <numFmt numFmtId="166" formatCode="0.0000"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -136,7 +136,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -150,10 +150,10 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -169,10 +169,10 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -184,10 +184,10 @@
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -202,13 +202,13 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="10" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -217,38 +217,11 @@
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -781,7 +754,6 @@
         <v/>
       </c>
     </row>
-    <row r="5"/>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
@@ -813,16 +785,15 @@
         <f>COUNTIFS('Picks'!$BX$2:$BX$39,"&gt;0",'Picks'!$V$2:$V$39,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$39,"&gt;0",'Picks'!$V$2:$V$39,"loss")</f>
         <v/>
       </c>
-      <c r="E7" s="32">
+      <c r="E7" s="7">
         <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$39,"&gt;0",'Picks'!$V$2:$V$39,"win")/(COUNTIFS('Picks'!$BX$2:$BX$39,"&gt;0",'Picks'!$V$2:$V$39,"win")+COUNTIFS('Picks'!$BX$2:$BX$39,"&gt;0",'Picks'!$V$2:$V$39,"loss")),0)</f>
         <v/>
       </c>
-      <c r="G7" s="32">
+      <c r="G7" s="7">
         <f>IFERROR(SUM('Picks'!$BY$2:$BY$39)/SUM('Picks'!$BX$2:$BX$39),0)</f>
         <v/>
       </c>
     </row>
-    <row r="8"/>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
@@ -846,7 +817,7 @@
       </c>
     </row>
     <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="33">
+      <c r="A10" s="8">
         <f>SUM('Picks'!$BY$2:$BY$39)</f>
         <v/>
       </c>
@@ -858,12 +829,11 @@
         <f>COUNTIFS('Picks'!$AM$2:$AM$39,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$39,"settled")</f>
         <v/>
       </c>
-      <c r="G10" s="33">
+      <c r="G10" s="8">
         <f>SUMIFS('Picks'!$AC$2:$AC$39,'Picks'!$AM$2:$AM$39,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
@@ -926,11 +896,11 @@
         <f>COUNTIFS('Picks'!$H$2:$H$39,$A14,'Picks'!$U$2:$U$39,"settled",'Picks'!$V$2:$V$39,"loss")</f>
         <v/>
       </c>
-      <c r="E14" s="34">
+      <c r="E14" s="14">
         <f>IFERROR(C14/(C14+D14),0)</f>
         <v/>
       </c>
-      <c r="F14" s="35">
+      <c r="F14" s="15">
         <f>SUMIFS('Picks'!$BY$2:$BY$39,'Picks'!$H$2:$H$39,$A14)</f>
         <v/>
       </c>
@@ -957,11 +927,11 @@
         <f>COUNTIFS('Picks'!$H$2:$H$39,$A15,'Picks'!$U$2:$U$39,"settled",'Picks'!$V$2:$V$39,"loss")</f>
         <v/>
       </c>
-      <c r="E15" s="36">
+      <c r="E15" s="19">
         <f>IFERROR(C15/(C15+D15),0)</f>
         <v/>
       </c>
-      <c r="F15" s="37">
+      <c r="F15" s="20">
         <f>SUMIFS('Picks'!$BY$2:$BY$39,'Picks'!$H$2:$H$39,$A15)</f>
         <v/>
       </c>
@@ -988,11 +958,11 @@
         <f>COUNTIFS('Picks'!$H$2:$H$39,$A16,'Picks'!$U$2:$U$39,"settled",'Picks'!$V$2:$V$39,"loss")</f>
         <v/>
       </c>
-      <c r="E16" s="34">
+      <c r="E16" s="14">
         <f>IFERROR(C16/(C16+D16),0)</f>
         <v/>
       </c>
-      <c r="F16" s="35">
+      <c r="F16" s="15">
         <f>SUMIFS('Picks'!$BY$2:$BY$39,'Picks'!$H$2:$H$39,$A16)</f>
         <v/>
       </c>
@@ -1001,7 +971,6 @@
         <v/>
       </c>
     </row>
-    <row r="17"/>
     <row r="18">
       <c r="A18" s="22" t="inlineStr">
         <is>
@@ -1554,7 +1523,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J2" s="38" t="n"/>
+      <c r="J2" s="25" t="n"/>
       <c r="K2" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -1563,7 +1532,7 @@
       <c r="L2" s="26" t="n">
         <v>117</v>
       </c>
-      <c r="M2" s="39" t="n">
+      <c r="M2" s="27" t="n">
         <v>2.17</v>
       </c>
       <c r="N2" s="28" t="n">
@@ -1603,11 +1572,11 @@
       <c r="X2" s="26" t="n">
         <v>108</v>
       </c>
-      <c r="Y2" s="38" t="n"/>
+      <c r="Y2" s="25" t="n"/>
       <c r="Z2" s="26" t="n"/>
       <c r="AA2" s="28" t="n"/>
       <c r="AB2" s="28" t="n"/>
-      <c r="AC2" s="40" t="n">
+      <c r="AC2" s="30" t="n">
         <v>1.755</v>
       </c>
       <c r="AD2" s="24" t="inlineStr">
@@ -1744,11 +1713,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ2" s="38" t="n"/>
+      <c r="BJ2" s="25" t="n"/>
       <c r="BK2" s="26" t="n">
         <v>117</v>
       </c>
-      <c r="BL2" s="39" t="n">
+      <c r="BL2" s="27" t="n">
         <v>2.17</v>
       </c>
       <c r="BM2" s="28" t="n">
@@ -1758,18 +1727,18 @@
         <v>0.455446</v>
       </c>
       <c r="BO2" s="28" t="n"/>
-      <c r="BP2" s="38" t="n"/>
-      <c r="BQ2" s="39" t="n"/>
+      <c r="BP2" s="25" t="n"/>
+      <c r="BQ2" s="27" t="n"/>
       <c r="BR2" s="28" t="n"/>
       <c r="BS2" s="28" t="n"/>
       <c r="BT2" s="28" t="n"/>
-      <c r="BU2" s="38" t="n"/>
+      <c r="BU2" s="25" t="n"/>
       <c r="BV2" s="29" t="n"/>
       <c r="BW2" s="24" t="n"/>
-      <c r="BX2" s="40" t="n">
+      <c r="BX2" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY2" s="39" t="n">
+      <c r="BY2" s="27" t="n">
         <v>1.17</v>
       </c>
       <c r="BZ2" s="24" t="inlineStr">
@@ -1829,7 +1798,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J3" s="38" t="n"/>
+      <c r="J3" s="25" t="n"/>
       <c r="K3" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -1838,7 +1807,7 @@
       <c r="L3" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="M3" s="39" t="n">
+      <c r="M3" s="27" t="n">
         <v>1.75188</v>
       </c>
       <c r="N3" s="28" t="n">
@@ -1878,11 +1847,11 @@
       <c r="X3" s="26" t="n">
         <v>8</v>
       </c>
-      <c r="Y3" s="38" t="n"/>
+      <c r="Y3" s="25" t="n"/>
       <c r="Z3" s="26" t="n"/>
       <c r="AA3" s="28" t="n"/>
       <c r="AB3" s="28" t="n"/>
-      <c r="AC3" s="40" t="n">
+      <c r="AC3" s="30" t="n">
         <v>1.1278</v>
       </c>
       <c r="AD3" s="24" t="inlineStr">
@@ -2019,11 +1988,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ3" s="38" t="n"/>
+      <c r="BJ3" s="25" t="n"/>
       <c r="BK3" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="BL3" s="39" t="n">
+      <c r="BL3" s="27" t="n">
         <v>1.75188</v>
       </c>
       <c r="BM3" s="28" t="n">
@@ -2033,18 +2002,18 @@
         <v>0.567164</v>
       </c>
       <c r="BO3" s="28" t="n"/>
-      <c r="BP3" s="38" t="n"/>
-      <c r="BQ3" s="39" t="n"/>
+      <c r="BP3" s="25" t="n"/>
+      <c r="BQ3" s="27" t="n"/>
       <c r="BR3" s="28" t="n"/>
       <c r="BS3" s="28" t="n"/>
       <c r="BT3" s="28" t="n"/>
-      <c r="BU3" s="38" t="n"/>
+      <c r="BU3" s="25" t="n"/>
       <c r="BV3" s="29" t="n"/>
       <c r="BW3" s="24" t="n"/>
-      <c r="BX3" s="40" t="n">
+      <c r="BX3" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY3" s="39" t="n">
+      <c r="BY3" s="27" t="n">
         <v>0.75188</v>
       </c>
       <c r="BZ3" s="24" t="inlineStr">
@@ -2104,7 +2073,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J4" s="38" t="n"/>
+      <c r="J4" s="25" t="n"/>
       <c r="K4" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -2113,7 +2082,7 @@
       <c r="L4" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="M4" s="39" t="n">
+      <c r="M4" s="27" t="n">
         <v>1.980392</v>
       </c>
       <c r="N4" s="28" t="n">
@@ -2153,11 +2122,11 @@
       <c r="X4" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="Y4" s="38" t="n"/>
+      <c r="Y4" s="25" t="n"/>
       <c r="Z4" s="26" t="n"/>
       <c r="AA4" s="28" t="n"/>
       <c r="AB4" s="28" t="n"/>
-      <c r="AC4" s="40" t="n">
+      <c r="AC4" s="30" t="n">
         <v>-1</v>
       </c>
       <c r="AD4" s="24" t="inlineStr">
@@ -2294,11 +2263,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ4" s="38" t="n"/>
+      <c r="BJ4" s="25" t="n"/>
       <c r="BK4" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="BL4" s="39" t="n">
+      <c r="BL4" s="27" t="n">
         <v>1.980392</v>
       </c>
       <c r="BM4" s="28" t="n">
@@ -2308,18 +2277,18 @@
         <v>0.502488</v>
       </c>
       <c r="BO4" s="28" t="n"/>
-      <c r="BP4" s="38" t="n"/>
-      <c r="BQ4" s="39" t="n"/>
+      <c r="BP4" s="25" t="n"/>
+      <c r="BQ4" s="27" t="n"/>
       <c r="BR4" s="28" t="n"/>
       <c r="BS4" s="28" t="n"/>
       <c r="BT4" s="28" t="n"/>
-      <c r="BU4" s="38" t="n"/>
+      <c r="BU4" s="25" t="n"/>
       <c r="BV4" s="29" t="n"/>
       <c r="BW4" s="24" t="n"/>
-      <c r="BX4" s="40" t="n">
+      <c r="BX4" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY4" s="39" t="n">
+      <c r="BY4" s="27" t="n">
         <v>-1</v>
       </c>
       <c r="BZ4" s="24" t="inlineStr">
@@ -2379,7 +2348,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J5" s="38" t="n"/>
+      <c r="J5" s="25" t="n"/>
       <c r="K5" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -2388,7 +2357,7 @@
       <c r="L5" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="M5" s="39" t="n">
+      <c r="M5" s="27" t="n">
         <v>1.75188</v>
       </c>
       <c r="N5" s="28" t="n">
@@ -2428,11 +2397,11 @@
       <c r="X5" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="Y5" s="38" t="n"/>
+      <c r="Y5" s="25" t="n"/>
       <c r="Z5" s="26" t="n"/>
       <c r="AA5" s="28" t="n"/>
       <c r="AB5" s="28" t="n"/>
-      <c r="AC5" s="40" t="n">
+      <c r="AC5" s="30" t="n">
         <v>1.1278</v>
       </c>
       <c r="AD5" s="24" t="inlineStr">
@@ -2569,11 +2538,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ5" s="38" t="n"/>
+      <c r="BJ5" s="25" t="n"/>
       <c r="BK5" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="BL5" s="39" t="n">
+      <c r="BL5" s="27" t="n">
         <v>1.75188</v>
       </c>
       <c r="BM5" s="28" t="n">
@@ -2583,18 +2552,18 @@
         <v>0.567164</v>
       </c>
       <c r="BO5" s="28" t="n"/>
-      <c r="BP5" s="38" t="n"/>
-      <c r="BQ5" s="39" t="n"/>
+      <c r="BP5" s="25" t="n"/>
+      <c r="BQ5" s="27" t="n"/>
       <c r="BR5" s="28" t="n"/>
       <c r="BS5" s="28" t="n"/>
       <c r="BT5" s="28" t="n"/>
-      <c r="BU5" s="38" t="n"/>
+      <c r="BU5" s="25" t="n"/>
       <c r="BV5" s="29" t="n"/>
       <c r="BW5" s="24" t="n"/>
-      <c r="BX5" s="40" t="n">
+      <c r="BX5" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY5" s="39" t="n">
+      <c r="BY5" s="27" t="n">
         <v>0.75188</v>
       </c>
       <c r="BZ5" s="24" t="inlineStr">
@@ -2654,7 +2623,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J6" s="38" t="n"/>
+      <c r="J6" s="25" t="n"/>
       <c r="K6" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -2663,7 +2632,7 @@
       <c r="L6" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="M6" s="39" t="n">
+      <c r="M6" s="27" t="n">
         <v>1.961538</v>
       </c>
       <c r="N6" s="28" t="n">
@@ -2703,11 +2672,11 @@
       <c r="X6" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="Y6" s="38" t="n"/>
+      <c r="Y6" s="25" t="n"/>
       <c r="Z6" s="26" t="n"/>
       <c r="AA6" s="28" t="n"/>
       <c r="AB6" s="28" t="n"/>
-      <c r="AC6" s="40" t="n">
+      <c r="AC6" s="30" t="n">
         <v>1.2019</v>
       </c>
       <c r="AD6" s="24" t="inlineStr">
@@ -2844,11 +2813,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ6" s="38" t="n"/>
+      <c r="BJ6" s="25" t="n"/>
       <c r="BK6" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="BL6" s="39" t="n">
+      <c r="BL6" s="27" t="n">
         <v>1.961538</v>
       </c>
       <c r="BM6" s="28" t="n">
@@ -2858,18 +2827,18 @@
         <v>0.507463</v>
       </c>
       <c r="BO6" s="28" t="n"/>
-      <c r="BP6" s="38" t="n"/>
-      <c r="BQ6" s="39" t="n"/>
+      <c r="BP6" s="25" t="n"/>
+      <c r="BQ6" s="27" t="n"/>
       <c r="BR6" s="28" t="n"/>
       <c r="BS6" s="28" t="n"/>
       <c r="BT6" s="28" t="n"/>
-      <c r="BU6" s="38" t="n"/>
+      <c r="BU6" s="25" t="n"/>
       <c r="BV6" s="29" t="n"/>
       <c r="BW6" s="24" t="n"/>
-      <c r="BX6" s="40" t="n">
+      <c r="BX6" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY6" s="39" t="n">
+      <c r="BY6" s="27" t="n">
         <v>0.961538</v>
       </c>
       <c r="BZ6" s="24" t="inlineStr">
@@ -2929,7 +2898,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J7" s="38" t="n"/>
+      <c r="J7" s="25" t="n"/>
       <c r="K7" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -2938,7 +2907,7 @@
       <c r="L7" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="M7" s="39" t="n">
+      <c r="M7" s="27" t="n">
         <v>1.961538</v>
       </c>
       <c r="N7" s="28" t="n">
@@ -2978,11 +2947,11 @@
       <c r="X7" s="26" t="n">
         <v>10</v>
       </c>
-      <c r="Y7" s="38" t="n"/>
+      <c r="Y7" s="25" t="n"/>
       <c r="Z7" s="26" t="n"/>
       <c r="AA7" s="28" t="n"/>
       <c r="AB7" s="28" t="n"/>
-      <c r="AC7" s="40" t="n">
+      <c r="AC7" s="30" t="n">
         <v>-1.25</v>
       </c>
       <c r="AD7" s="24" t="inlineStr">
@@ -3119,11 +3088,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ7" s="38" t="n"/>
+      <c r="BJ7" s="25" t="n"/>
       <c r="BK7" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="BL7" s="39" t="n">
+      <c r="BL7" s="27" t="n">
         <v>1.961538</v>
       </c>
       <c r="BM7" s="28" t="n">
@@ -3133,18 +3102,18 @@
         <v>0.507463</v>
       </c>
       <c r="BO7" s="28" t="n"/>
-      <c r="BP7" s="38" t="n"/>
-      <c r="BQ7" s="39" t="n"/>
+      <c r="BP7" s="25" t="n"/>
+      <c r="BQ7" s="27" t="n"/>
       <c r="BR7" s="28" t="n"/>
       <c r="BS7" s="28" t="n"/>
       <c r="BT7" s="28" t="n"/>
-      <c r="BU7" s="38" t="n"/>
+      <c r="BU7" s="25" t="n"/>
       <c r="BV7" s="29" t="n"/>
       <c r="BW7" s="24" t="n"/>
-      <c r="BX7" s="40" t="n">
+      <c r="BX7" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY7" s="39" t="n">
+      <c r="BY7" s="27" t="n">
         <v>-1</v>
       </c>
       <c r="BZ7" s="24" t="inlineStr">
@@ -3204,7 +3173,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J8" s="38" t="n"/>
+      <c r="J8" s="25" t="n"/>
       <c r="K8" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -3213,7 +3182,7 @@
       <c r="L8" s="26" t="n">
         <v>-106</v>
       </c>
-      <c r="M8" s="39" t="n">
+      <c r="M8" s="27" t="n">
         <v>1.943396</v>
       </c>
       <c r="N8" s="28" t="n">
@@ -3253,11 +3222,11 @@
       <c r="X8" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="Y8" s="38" t="n"/>
+      <c r="Y8" s="25" t="n"/>
       <c r="Z8" s="26" t="n"/>
       <c r="AA8" s="28" t="n"/>
       <c r="AB8" s="28" t="n"/>
-      <c r="AC8" s="40" t="n">
+      <c r="AC8" s="30" t="n">
         <v>-1</v>
       </c>
       <c r="AD8" s="24" t="inlineStr">
@@ -3394,11 +3363,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ8" s="38" t="n"/>
+      <c r="BJ8" s="25" t="n"/>
       <c r="BK8" s="26" t="n">
         <v>-106</v>
       </c>
-      <c r="BL8" s="39" t="n">
+      <c r="BL8" s="27" t="n">
         <v>1.943396</v>
       </c>
       <c r="BM8" s="28" t="n">
@@ -3408,18 +3377,18 @@
         <v>0.5124379999999999</v>
       </c>
       <c r="BO8" s="28" t="n"/>
-      <c r="BP8" s="38" t="n"/>
-      <c r="BQ8" s="39" t="n"/>
+      <c r="BP8" s="25" t="n"/>
+      <c r="BQ8" s="27" t="n"/>
       <c r="BR8" s="28" t="n"/>
       <c r="BS8" s="28" t="n"/>
       <c r="BT8" s="28" t="n"/>
-      <c r="BU8" s="38" t="n"/>
+      <c r="BU8" s="25" t="n"/>
       <c r="BV8" s="29" t="n"/>
       <c r="BW8" s="24" t="n"/>
-      <c r="BX8" s="40" t="n">
+      <c r="BX8" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY8" s="39" t="n">
+      <c r="BY8" s="27" t="n">
         <v>-1</v>
       </c>
       <c r="BZ8" s="24" t="inlineStr">
@@ -3479,7 +3448,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J9" s="38" t="n"/>
+      <c r="J9" s="25" t="n"/>
       <c r="K9" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -3488,7 +3457,7 @@
       <c r="L9" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="M9" s="39" t="n">
+      <c r="M9" s="27" t="n">
         <v>1.980392</v>
       </c>
       <c r="N9" s="28" t="n">
@@ -3528,11 +3497,11 @@
       <c r="X9" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="Y9" s="38" t="n"/>
+      <c r="Y9" s="25" t="n"/>
       <c r="Z9" s="26" t="n"/>
       <c r="AA9" s="28" t="n"/>
       <c r="AB9" s="28" t="n"/>
-      <c r="AC9" s="40" t="n">
+      <c r="AC9" s="30" t="n">
         <v>0.9804</v>
       </c>
       <c r="AD9" s="24" t="inlineStr">
@@ -3669,11 +3638,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ9" s="38" t="n"/>
+      <c r="BJ9" s="25" t="n"/>
       <c r="BK9" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="BL9" s="39" t="n">
+      <c r="BL9" s="27" t="n">
         <v>1.980392</v>
       </c>
       <c r="BM9" s="28" t="n">
@@ -3683,18 +3652,18 @@
         <v>0.502488</v>
       </c>
       <c r="BO9" s="28" t="n"/>
-      <c r="BP9" s="38" t="n"/>
-      <c r="BQ9" s="39" t="n"/>
+      <c r="BP9" s="25" t="n"/>
+      <c r="BQ9" s="27" t="n"/>
       <c r="BR9" s="28" t="n"/>
       <c r="BS9" s="28" t="n"/>
       <c r="BT9" s="28" t="n"/>
-      <c r="BU9" s="38" t="n"/>
+      <c r="BU9" s="25" t="n"/>
       <c r="BV9" s="29" t="n"/>
       <c r="BW9" s="24" t="n"/>
-      <c r="BX9" s="40" t="n">
+      <c r="BX9" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY9" s="39" t="n">
+      <c r="BY9" s="27" t="n">
         <v>0.980392</v>
       </c>
       <c r="BZ9" s="24" t="inlineStr">
@@ -3754,7 +3723,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J10" s="38" t="n"/>
+      <c r="J10" s="25" t="n"/>
       <c r="K10" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -3763,7 +3732,7 @@
       <c r="L10" s="26" t="n">
         <v>-138</v>
       </c>
-      <c r="M10" s="39" t="n">
+      <c r="M10" s="27" t="n">
         <v>1.724638</v>
       </c>
       <c r="N10" s="28" t="n">
@@ -3803,11 +3772,11 @@
       <c r="X10" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="Y10" s="38" t="n"/>
+      <c r="Y10" s="25" t="n"/>
       <c r="Z10" s="26" t="n"/>
       <c r="AA10" s="28" t="n"/>
       <c r="AB10" s="28" t="n"/>
-      <c r="AC10" s="40" t="n">
+      <c r="AC10" s="30" t="n">
         <v>1.2681</v>
       </c>
       <c r="AD10" s="24" t="inlineStr">
@@ -3944,11 +3913,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ10" s="38" t="n"/>
+      <c r="BJ10" s="25" t="n"/>
       <c r="BK10" s="26" t="n">
         <v>-138</v>
       </c>
-      <c r="BL10" s="39" t="n">
+      <c r="BL10" s="27" t="n">
         <v>1.724638</v>
       </c>
       <c r="BM10" s="28" t="n">
@@ -3958,18 +3927,18 @@
         <v>0.577114</v>
       </c>
       <c r="BO10" s="28" t="n"/>
-      <c r="BP10" s="38" t="n"/>
-      <c r="BQ10" s="39" t="n"/>
+      <c r="BP10" s="25" t="n"/>
+      <c r="BQ10" s="27" t="n"/>
       <c r="BR10" s="28" t="n"/>
       <c r="BS10" s="28" t="n"/>
       <c r="BT10" s="28" t="n"/>
-      <c r="BU10" s="38" t="n"/>
+      <c r="BU10" s="25" t="n"/>
       <c r="BV10" s="29" t="n"/>
       <c r="BW10" s="24" t="n"/>
-      <c r="BX10" s="40" t="n">
+      <c r="BX10" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY10" s="39" t="n">
+      <c r="BY10" s="27" t="n">
         <v>0.724638</v>
       </c>
       <c r="BZ10" s="24" t="inlineStr">
@@ -4029,7 +3998,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J11" s="38" t="n"/>
+      <c r="J11" s="25" t="n"/>
       <c r="K11" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -4038,7 +4007,7 @@
       <c r="L11" s="26" t="n">
         <v>102</v>
       </c>
-      <c r="M11" s="39" t="n">
+      <c r="M11" s="27" t="n">
         <v>2.02</v>
       </c>
       <c r="N11" s="28" t="n">
@@ -4078,11 +4047,11 @@
       <c r="X11" s="26" t="n">
         <v>15</v>
       </c>
-      <c r="Y11" s="38" t="n"/>
+      <c r="Y11" s="25" t="n"/>
       <c r="Z11" s="26" t="n"/>
       <c r="AA11" s="28" t="n"/>
       <c r="AB11" s="28" t="n"/>
-      <c r="AC11" s="40" t="n">
+      <c r="AC11" s="30" t="n">
         <v>1.275</v>
       </c>
       <c r="AD11" s="24" t="inlineStr">
@@ -4219,11 +4188,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ11" s="38" t="n"/>
+      <c r="BJ11" s="25" t="n"/>
       <c r="BK11" s="26" t="n">
         <v>102</v>
       </c>
-      <c r="BL11" s="39" t="n">
+      <c r="BL11" s="27" t="n">
         <v>2.02</v>
       </c>
       <c r="BM11" s="28" t="n">
@@ -4233,18 +4202,18 @@
         <v>0.492537</v>
       </c>
       <c r="BO11" s="28" t="n"/>
-      <c r="BP11" s="38" t="n"/>
-      <c r="BQ11" s="39" t="n"/>
+      <c r="BP11" s="25" t="n"/>
+      <c r="BQ11" s="27" t="n"/>
       <c r="BR11" s="28" t="n"/>
       <c r="BS11" s="28" t="n"/>
       <c r="BT11" s="28" t="n"/>
-      <c r="BU11" s="38" t="n"/>
+      <c r="BU11" s="25" t="n"/>
       <c r="BV11" s="29" t="n"/>
       <c r="BW11" s="24" t="n"/>
-      <c r="BX11" s="40" t="n">
+      <c r="BX11" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY11" s="39" t="n">
+      <c r="BY11" s="27" t="n">
         <v>1.02</v>
       </c>
       <c r="BZ11" s="24" t="inlineStr">
@@ -4304,7 +4273,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J12" s="38" t="n"/>
+      <c r="J12" s="25" t="n"/>
       <c r="K12" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -4313,7 +4282,7 @@
       <c r="L12" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="M12" s="39" t="n">
+      <c r="M12" s="27" t="n">
         <v>1.980392</v>
       </c>
       <c r="N12" s="28" t="n">
@@ -4353,11 +4322,11 @@
       <c r="X12" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y12" s="38" t="n"/>
+      <c r="Y12" s="25" t="n"/>
       <c r="Z12" s="26" t="n"/>
       <c r="AA12" s="28" t="n"/>
       <c r="AB12" s="28" t="n"/>
-      <c r="AC12" s="40" t="n">
+      <c r="AC12" s="30" t="n">
         <v>-1</v>
       </c>
       <c r="AD12" s="24" t="inlineStr">
@@ -4494,11 +4463,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ12" s="38" t="n"/>
+      <c r="BJ12" s="25" t="n"/>
       <c r="BK12" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="BL12" s="39" t="n">
+      <c r="BL12" s="27" t="n">
         <v>1.980392</v>
       </c>
       <c r="BM12" s="28" t="n">
@@ -4508,18 +4477,18 @@
         <v>0.502488</v>
       </c>
       <c r="BO12" s="28" t="n"/>
-      <c r="BP12" s="38" t="n"/>
-      <c r="BQ12" s="39" t="n"/>
+      <c r="BP12" s="25" t="n"/>
+      <c r="BQ12" s="27" t="n"/>
       <c r="BR12" s="28" t="n"/>
       <c r="BS12" s="28" t="n"/>
       <c r="BT12" s="28" t="n"/>
-      <c r="BU12" s="38" t="n"/>
+      <c r="BU12" s="25" t="n"/>
       <c r="BV12" s="29" t="n"/>
       <c r="BW12" s="24" t="n"/>
-      <c r="BX12" s="40" t="n">
+      <c r="BX12" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY12" s="39" t="n">
+      <c r="BY12" s="27" t="n">
         <v>-1</v>
       </c>
       <c r="BZ12" s="24" t="inlineStr">
@@ -4579,7 +4548,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J13" s="38" t="n"/>
+      <c r="J13" s="25" t="n"/>
       <c r="K13" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -4588,7 +4557,7 @@
       <c r="L13" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="M13" s="39" t="n">
+      <c r="M13" s="27" t="n">
         <v>1.980392</v>
       </c>
       <c r="N13" s="28" t="n">
@@ -4628,11 +4597,11 @@
       <c r="X13" s="26" t="n">
         <v>7</v>
       </c>
-      <c r="Y13" s="38" t="n"/>
+      <c r="Y13" s="25" t="n"/>
       <c r="Z13" s="26" t="n"/>
       <c r="AA13" s="28" t="n"/>
       <c r="AB13" s="28" t="n"/>
-      <c r="AC13" s="40" t="n">
+      <c r="AC13" s="30" t="n">
         <v>1.2255</v>
       </c>
       <c r="AD13" s="24" t="inlineStr">
@@ -4769,11 +4738,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ13" s="38" t="n"/>
+      <c r="BJ13" s="25" t="n"/>
       <c r="BK13" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="BL13" s="39" t="n">
+      <c r="BL13" s="27" t="n">
         <v>1.980392</v>
       </c>
       <c r="BM13" s="28" t="n">
@@ -4783,18 +4752,18 @@
         <v>0.502488</v>
       </c>
       <c r="BO13" s="28" t="n"/>
-      <c r="BP13" s="38" t="n"/>
-      <c r="BQ13" s="39" t="n"/>
+      <c r="BP13" s="25" t="n"/>
+      <c r="BQ13" s="27" t="n"/>
       <c r="BR13" s="28" t="n"/>
       <c r="BS13" s="28" t="n"/>
       <c r="BT13" s="28" t="n"/>
-      <c r="BU13" s="38" t="n"/>
+      <c r="BU13" s="25" t="n"/>
       <c r="BV13" s="29" t="n"/>
       <c r="BW13" s="24" t="n"/>
-      <c r="BX13" s="40" t="n">
+      <c r="BX13" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY13" s="39" t="n">
+      <c r="BY13" s="27" t="n">
         <v>0.980392</v>
       </c>
       <c r="BZ13" s="24" t="inlineStr">
@@ -4854,7 +4823,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J14" s="38" t="n"/>
+      <c r="J14" s="25" t="n"/>
       <c r="K14" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -4863,7 +4832,7 @@
       <c r="L14" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="M14" s="39" t="n">
+      <c r="M14" s="27" t="n">
         <v>1.961538</v>
       </c>
       <c r="N14" s="28" t="n">
@@ -4903,11 +4872,11 @@
       <c r="X14" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="Y14" s="38" t="n"/>
+      <c r="Y14" s="25" t="n"/>
       <c r="Z14" s="26" t="n"/>
       <c r="AA14" s="28" t="n"/>
       <c r="AB14" s="28" t="n"/>
-      <c r="AC14" s="40" t="n">
+      <c r="AC14" s="30" t="n">
         <v>-0.75</v>
       </c>
       <c r="AD14" s="24" t="inlineStr">
@@ -5044,11 +5013,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ14" s="38" t="n"/>
+      <c r="BJ14" s="25" t="n"/>
       <c r="BK14" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="BL14" s="39" t="n">
+      <c r="BL14" s="27" t="n">
         <v>1.961538</v>
       </c>
       <c r="BM14" s="28" t="n">
@@ -5058,18 +5027,18 @@
         <v>0.507463</v>
       </c>
       <c r="BO14" s="28" t="n"/>
-      <c r="BP14" s="38" t="n"/>
-      <c r="BQ14" s="39" t="n"/>
+      <c r="BP14" s="25" t="n"/>
+      <c r="BQ14" s="27" t="n"/>
       <c r="BR14" s="28" t="n"/>
       <c r="BS14" s="28" t="n"/>
       <c r="BT14" s="28" t="n"/>
-      <c r="BU14" s="38" t="n"/>
+      <c r="BU14" s="25" t="n"/>
       <c r="BV14" s="29" t="n"/>
       <c r="BW14" s="24" t="n"/>
-      <c r="BX14" s="40" t="n">
+      <c r="BX14" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY14" s="39" t="n">
+      <c r="BY14" s="27" t="n">
         <v>-1</v>
       </c>
       <c r="BZ14" s="24" t="inlineStr">
@@ -5129,7 +5098,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J15" s="38" t="n"/>
+      <c r="J15" s="25" t="n"/>
       <c r="K15" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -5138,7 +5107,7 @@
       <c r="L15" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="M15" s="39" t="n">
+      <c r="M15" s="27" t="n">
         <v>1.961538</v>
       </c>
       <c r="N15" s="28" t="n">
@@ -5178,11 +5147,11 @@
       <c r="X15" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="Y15" s="38" t="n"/>
+      <c r="Y15" s="25" t="n"/>
       <c r="Z15" s="26" t="n"/>
       <c r="AA15" s="28" t="n"/>
       <c r="AB15" s="28" t="n"/>
-      <c r="AC15" s="40" t="n">
+      <c r="AC15" s="30" t="n">
         <v>-1</v>
       </c>
       <c r="AD15" s="24" t="inlineStr">
@@ -5319,11 +5288,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ15" s="38" t="n"/>
+      <c r="BJ15" s="25" t="n"/>
       <c r="BK15" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="BL15" s="39" t="n">
+      <c r="BL15" s="27" t="n">
         <v>1.961538</v>
       </c>
       <c r="BM15" s="28" t="n">
@@ -5333,18 +5302,18 @@
         <v>0.507463</v>
       </c>
       <c r="BO15" s="28" t="n"/>
-      <c r="BP15" s="38" t="n"/>
-      <c r="BQ15" s="39" t="n"/>
+      <c r="BP15" s="25" t="n"/>
+      <c r="BQ15" s="27" t="n"/>
       <c r="BR15" s="28" t="n"/>
       <c r="BS15" s="28" t="n"/>
       <c r="BT15" s="28" t="n"/>
-      <c r="BU15" s="38" t="n"/>
+      <c r="BU15" s="25" t="n"/>
       <c r="BV15" s="29" t="n"/>
       <c r="BW15" s="24" t="n"/>
-      <c r="BX15" s="40" t="n">
+      <c r="BX15" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY15" s="39" t="n">
+      <c r="BY15" s="27" t="n">
         <v>-1</v>
       </c>
       <c r="BZ15" s="24" t="inlineStr">
@@ -5404,7 +5373,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J16" s="38" t="n"/>
+      <c r="J16" s="25" t="n"/>
       <c r="K16" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -5413,7 +5382,7 @@
       <c r="L16" s="26" t="n">
         <v>-111</v>
       </c>
-      <c r="M16" s="39" t="n">
+      <c r="M16" s="27" t="n">
         <v>1.900901</v>
       </c>
       <c r="N16" s="28" t="n">
@@ -5453,11 +5422,11 @@
       <c r="X16" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="Y16" s="38" t="n"/>
+      <c r="Y16" s="25" t="n"/>
       <c r="Z16" s="26" t="n"/>
       <c r="AA16" s="28" t="n"/>
       <c r="AB16" s="28" t="n"/>
-      <c r="AC16" s="40" t="n">
+      <c r="AC16" s="30" t="n">
         <v>-1.5</v>
       </c>
       <c r="AD16" s="24" t="inlineStr">
@@ -5594,11 +5563,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ16" s="38" t="n"/>
+      <c r="BJ16" s="25" t="n"/>
       <c r="BK16" s="26" t="n">
         <v>-111</v>
       </c>
-      <c r="BL16" s="39" t="n">
+      <c r="BL16" s="27" t="n">
         <v>1.900901</v>
       </c>
       <c r="BM16" s="28" t="n">
@@ -5608,18 +5577,18 @@
         <v>0.522388</v>
       </c>
       <c r="BO16" s="28" t="n"/>
-      <c r="BP16" s="38" t="n"/>
-      <c r="BQ16" s="39" t="n"/>
+      <c r="BP16" s="25" t="n"/>
+      <c r="BQ16" s="27" t="n"/>
       <c r="BR16" s="28" t="n"/>
       <c r="BS16" s="28" t="n"/>
       <c r="BT16" s="28" t="n"/>
-      <c r="BU16" s="38" t="n"/>
+      <c r="BU16" s="25" t="n"/>
       <c r="BV16" s="29" t="n"/>
       <c r="BW16" s="24" t="n"/>
-      <c r="BX16" s="40" t="n">
+      <c r="BX16" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY16" s="39" t="n">
+      <c r="BY16" s="27" t="n">
         <v>-1</v>
       </c>
       <c r="BZ16" s="24" t="inlineStr">
@@ -5679,7 +5648,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J17" s="38" t="n"/>
+      <c r="J17" s="25" t="n"/>
       <c r="K17" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -5688,7 +5657,7 @@
       <c r="L17" s="26" t="n">
         <v>-108</v>
       </c>
-      <c r="M17" s="39" t="n">
+      <c r="M17" s="27" t="n">
         <v>1.925926</v>
       </c>
       <c r="N17" s="28" t="n">
@@ -5728,11 +5697,11 @@
       <c r="X17" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="Y17" s="38" t="n"/>
+      <c r="Y17" s="25" t="n"/>
       <c r="Z17" s="26" t="n"/>
       <c r="AA17" s="28" t="n"/>
       <c r="AB17" s="28" t="n"/>
-      <c r="AC17" s="40" t="n">
+      <c r="AC17" s="30" t="n">
         <v>0.9258999999999999</v>
       </c>
       <c r="AD17" s="24" t="inlineStr">
@@ -5869,11 +5838,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ17" s="38" t="n"/>
+      <c r="BJ17" s="25" t="n"/>
       <c r="BK17" s="26" t="n">
         <v>-108</v>
       </c>
-      <c r="BL17" s="39" t="n">
+      <c r="BL17" s="27" t="n">
         <v>1.925926</v>
       </c>
       <c r="BM17" s="28" t="n">
@@ -5883,18 +5852,18 @@
         <v>0.5148509999999999</v>
       </c>
       <c r="BO17" s="28" t="n"/>
-      <c r="BP17" s="38" t="n"/>
-      <c r="BQ17" s="39" t="n"/>
+      <c r="BP17" s="25" t="n"/>
+      <c r="BQ17" s="27" t="n"/>
       <c r="BR17" s="28" t="n"/>
       <c r="BS17" s="28" t="n"/>
       <c r="BT17" s="28" t="n"/>
-      <c r="BU17" s="38" t="n"/>
+      <c r="BU17" s="25" t="n"/>
       <c r="BV17" s="29" t="n"/>
       <c r="BW17" s="24" t="n"/>
-      <c r="BX17" s="40" t="n">
+      <c r="BX17" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY17" s="39" t="n">
+      <c r="BY17" s="27" t="n">
         <v>0.925926</v>
       </c>
       <c r="BZ17" s="24" t="inlineStr">
@@ -5954,7 +5923,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J18" s="38" t="n"/>
+      <c r="J18" s="25" t="n"/>
       <c r="K18" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -5963,7 +5932,7 @@
       <c r="L18" s="26" t="n">
         <v>111</v>
       </c>
-      <c r="M18" s="39" t="n">
+      <c r="M18" s="27" t="n">
         <v>2.11</v>
       </c>
       <c r="N18" s="28" t="n">
@@ -6003,11 +5972,11 @@
       <c r="X18" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="Y18" s="38" t="n"/>
+      <c r="Y18" s="25" t="n"/>
       <c r="Z18" s="26" t="n"/>
       <c r="AA18" s="28" t="n"/>
       <c r="AB18" s="28" t="n"/>
-      <c r="AC18" s="40" t="n">
+      <c r="AC18" s="30" t="n">
         <v>-1.25</v>
       </c>
       <c r="AD18" s="24" t="inlineStr">
@@ -6144,11 +6113,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ18" s="38" t="n"/>
+      <c r="BJ18" s="25" t="n"/>
       <c r="BK18" s="26" t="n">
         <v>111</v>
       </c>
-      <c r="BL18" s="39" t="n">
+      <c r="BL18" s="27" t="n">
         <v>2.11</v>
       </c>
       <c r="BM18" s="28" t="n">
@@ -6158,18 +6127,18 @@
         <v>0.472637</v>
       </c>
       <c r="BO18" s="28" t="n"/>
-      <c r="BP18" s="38" t="n"/>
-      <c r="BQ18" s="39" t="n"/>
+      <c r="BP18" s="25" t="n"/>
+      <c r="BQ18" s="27" t="n"/>
       <c r="BR18" s="28" t="n"/>
       <c r="BS18" s="28" t="n"/>
       <c r="BT18" s="28" t="n"/>
-      <c r="BU18" s="38" t="n"/>
+      <c r="BU18" s="25" t="n"/>
       <c r="BV18" s="29" t="n"/>
       <c r="BW18" s="24" t="n"/>
-      <c r="BX18" s="40" t="n">
+      <c r="BX18" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY18" s="39" t="n">
+      <c r="BY18" s="27" t="n">
         <v>-1</v>
       </c>
       <c r="BZ18" s="24" t="inlineStr">
@@ -6229,7 +6198,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J19" s="38" t="n"/>
+      <c r="J19" s="25" t="n"/>
       <c r="K19" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -6238,7 +6207,7 @@
       <c r="L19" s="26" t="n">
         <v>-125</v>
       </c>
-      <c r="M19" s="39" t="n">
+      <c r="M19" s="27" t="n">
         <v>1.8</v>
       </c>
       <c r="N19" s="28" t="n">
@@ -6278,11 +6247,11 @@
       <c r="X19" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="Y19" s="38" t="n"/>
+      <c r="Y19" s="25" t="n"/>
       <c r="Z19" s="26" t="n"/>
       <c r="AA19" s="28" t="n"/>
       <c r="AB19" s="28" t="n"/>
-      <c r="AC19" s="40" t="n">
+      <c r="AC19" s="30" t="n">
         <v>1.2</v>
       </c>
       <c r="AD19" s="24" t="inlineStr">
@@ -6419,11 +6388,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ19" s="38" t="n"/>
+      <c r="BJ19" s="25" t="n"/>
       <c r="BK19" s="26" t="n">
         <v>-125</v>
       </c>
-      <c r="BL19" s="39" t="n">
+      <c r="BL19" s="27" t="n">
         <v>1.8</v>
       </c>
       <c r="BM19" s="28" t="n">
@@ -6433,18 +6402,18 @@
         <v>0.552239</v>
       </c>
       <c r="BO19" s="28" t="n"/>
-      <c r="BP19" s="38" t="n"/>
-      <c r="BQ19" s="39" t="n"/>
+      <c r="BP19" s="25" t="n"/>
+      <c r="BQ19" s="27" t="n"/>
       <c r="BR19" s="28" t="n"/>
       <c r="BS19" s="28" t="n"/>
       <c r="BT19" s="28" t="n"/>
-      <c r="BU19" s="38" t="n"/>
+      <c r="BU19" s="25" t="n"/>
       <c r="BV19" s="29" t="n"/>
       <c r="BW19" s="24" t="n"/>
-      <c r="BX19" s="40" t="n">
+      <c r="BX19" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY19" s="39" t="n">
+      <c r="BY19" s="27" t="n">
         <v>0.8</v>
       </c>
       <c r="BZ19" s="24" t="inlineStr">
@@ -6504,7 +6473,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J20" s="38" t="n"/>
+      <c r="J20" s="25" t="n"/>
       <c r="K20" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -6513,7 +6482,7 @@
       <c r="L20" s="26" t="n">
         <v>106</v>
       </c>
-      <c r="M20" s="39" t="n">
+      <c r="M20" s="27" t="n">
         <v>2.06</v>
       </c>
       <c r="N20" s="28" t="n">
@@ -6553,11 +6522,11 @@
       <c r="X20" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y20" s="38" t="n"/>
+      <c r="Y20" s="25" t="n"/>
       <c r="Z20" s="26" t="n"/>
       <c r="AA20" s="28" t="n"/>
       <c r="AB20" s="28" t="n"/>
-      <c r="AC20" s="40" t="n">
+      <c r="AC20" s="30" t="n">
         <v>0.795</v>
       </c>
       <c r="AD20" s="24" t="inlineStr">
@@ -6694,11 +6663,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ20" s="38" t="n"/>
+      <c r="BJ20" s="25" t="n"/>
       <c r="BK20" s="26" t="n">
         <v>106</v>
       </c>
-      <c r="BL20" s="39" t="n">
+      <c r="BL20" s="27" t="n">
         <v>2.06</v>
       </c>
       <c r="BM20" s="28" t="n">
@@ -6708,18 +6677,18 @@
         <v>0.482587</v>
       </c>
       <c r="BO20" s="28" t="n"/>
-      <c r="BP20" s="38" t="n"/>
-      <c r="BQ20" s="39" t="n"/>
+      <c r="BP20" s="25" t="n"/>
+      <c r="BQ20" s="27" t="n"/>
       <c r="BR20" s="28" t="n"/>
       <c r="BS20" s="28" t="n"/>
       <c r="BT20" s="28" t="n"/>
-      <c r="BU20" s="38" t="n"/>
+      <c r="BU20" s="25" t="n"/>
       <c r="BV20" s="29" t="n"/>
       <c r="BW20" s="24" t="n"/>
-      <c r="BX20" s="40" t="n">
+      <c r="BX20" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY20" s="39" t="n">
+      <c r="BY20" s="27" t="n">
         <v>1.06</v>
       </c>
       <c r="BZ20" s="24" t="inlineStr">
@@ -6779,7 +6748,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J21" s="38" t="n"/>
+      <c r="J21" s="25" t="n"/>
       <c r="K21" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -6788,7 +6757,7 @@
       <c r="L21" s="26" t="n">
         <v>-106</v>
       </c>
-      <c r="M21" s="39" t="n">
+      <c r="M21" s="27" t="n">
         <v>1.943396</v>
       </c>
       <c r="N21" s="28" t="n">
@@ -6828,11 +6797,11 @@
       <c r="X21" s="26" t="n">
         <v>10</v>
       </c>
-      <c r="Y21" s="38" t="n"/>
+      <c r="Y21" s="25" t="n"/>
       <c r="Z21" s="26" t="n"/>
       <c r="AA21" s="28" t="n"/>
       <c r="AB21" s="28" t="n"/>
-      <c r="AC21" s="40" t="n">
+      <c r="AC21" s="30" t="n">
         <v>0.9434</v>
       </c>
       <c r="AD21" s="24" t="inlineStr">
@@ -6879,11 +6848,11 @@
         </is>
       </c>
       <c r="BI21" s="24" t="n"/>
-      <c r="BJ21" s="38" t="n"/>
+      <c r="BJ21" s="25" t="n"/>
       <c r="BK21" s="26" t="n">
         <v>-106</v>
       </c>
-      <c r="BL21" s="39" t="n">
+      <c r="BL21" s="27" t="n">
         <v>1.943396</v>
       </c>
       <c r="BM21" s="28" t="n">
@@ -6893,16 +6862,16 @@
         <v>0.5124379999999999</v>
       </c>
       <c r="BO21" s="28" t="n"/>
-      <c r="BP21" s="38" t="n"/>
-      <c r="BQ21" s="39" t="n"/>
+      <c r="BP21" s="25" t="n"/>
+      <c r="BQ21" s="27" t="n"/>
       <c r="BR21" s="28" t="n"/>
       <c r="BS21" s="28" t="n"/>
       <c r="BT21" s="28" t="n"/>
-      <c r="BU21" s="38" t="n"/>
+      <c r="BU21" s="25" t="n"/>
       <c r="BV21" s="29" t="n"/>
       <c r="BW21" s="24" t="n"/>
-      <c r="BX21" s="40" t="n"/>
-      <c r="BY21" s="39" t="n"/>
+      <c r="BX21" s="30" t="n"/>
+      <c r="BY21" s="27" t="n"/>
       <c r="BZ21" s="24" t="n"/>
       <c r="CA21" s="31" t="n"/>
     </row>
@@ -6952,7 +6921,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J22" s="38" t="n"/>
+      <c r="J22" s="25" t="n"/>
       <c r="K22" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -6961,7 +6930,7 @@
       <c r="L22" s="26" t="n">
         <v>-106</v>
       </c>
-      <c r="M22" s="39" t="n">
+      <c r="M22" s="27" t="n">
         <v>1.943396</v>
       </c>
       <c r="N22" s="28" t="n">
@@ -7001,11 +6970,11 @@
       <c r="X22" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="Y22" s="38" t="n"/>
+      <c r="Y22" s="25" t="n"/>
       <c r="Z22" s="26" t="n"/>
       <c r="AA22" s="28" t="n"/>
       <c r="AB22" s="28" t="n"/>
-      <c r="AC22" s="40" t="n">
+      <c r="AC22" s="30" t="n">
         <v>0.9434</v>
       </c>
       <c r="AD22" s="24" t="inlineStr">
@@ -7052,11 +7021,11 @@
         </is>
       </c>
       <c r="BI22" s="24" t="n"/>
-      <c r="BJ22" s="38" t="n"/>
+      <c r="BJ22" s="25" t="n"/>
       <c r="BK22" s="26" t="n">
         <v>-106</v>
       </c>
-      <c r="BL22" s="39" t="n">
+      <c r="BL22" s="27" t="n">
         <v>1.943396</v>
       </c>
       <c r="BM22" s="28" t="n">
@@ -7066,16 +7035,16 @@
         <v>0.5124379999999999</v>
       </c>
       <c r="BO22" s="28" t="n"/>
-      <c r="BP22" s="38" t="n"/>
-      <c r="BQ22" s="39" t="n"/>
+      <c r="BP22" s="25" t="n"/>
+      <c r="BQ22" s="27" t="n"/>
       <c r="BR22" s="28" t="n"/>
       <c r="BS22" s="28" t="n"/>
       <c r="BT22" s="28" t="n"/>
-      <c r="BU22" s="38" t="n"/>
+      <c r="BU22" s="25" t="n"/>
       <c r="BV22" s="29" t="n"/>
       <c r="BW22" s="24" t="n"/>
-      <c r="BX22" s="40" t="n"/>
-      <c r="BY22" s="39" t="n"/>
+      <c r="BX22" s="30" t="n"/>
+      <c r="BY22" s="27" t="n"/>
       <c r="BZ22" s="24" t="n"/>
       <c r="CA22" s="31" t="n"/>
     </row>
@@ -7125,7 +7094,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J23" s="38" t="n"/>
+      <c r="J23" s="25" t="n"/>
       <c r="K23" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -7134,7 +7103,7 @@
       <c r="L23" s="26" t="n">
         <v>-141</v>
       </c>
-      <c r="M23" s="39" t="n">
+      <c r="M23" s="27" t="n">
         <v>1.70922</v>
       </c>
       <c r="N23" s="28" t="n">
@@ -7174,11 +7143,11 @@
       <c r="X23" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y23" s="38" t="n"/>
+      <c r="Y23" s="25" t="n"/>
       <c r="Z23" s="26" t="n"/>
       <c r="AA23" s="28" t="n"/>
       <c r="AB23" s="28" t="n"/>
-      <c r="AC23" s="40" t="n">
+      <c r="AC23" s="30" t="n">
         <v>1.2411</v>
       </c>
       <c r="AD23" s="24" t="inlineStr">
@@ -7225,11 +7194,11 @@
         </is>
       </c>
       <c r="BI23" s="24" t="n"/>
-      <c r="BJ23" s="38" t="n"/>
+      <c r="BJ23" s="25" t="n"/>
       <c r="BK23" s="26" t="n">
         <v>-141</v>
       </c>
-      <c r="BL23" s="39" t="n">
+      <c r="BL23" s="27" t="n">
         <v>1.70922</v>
       </c>
       <c r="BM23" s="28" t="n">
@@ -7239,16 +7208,16 @@
         <v>0.58209</v>
       </c>
       <c r="BO23" s="28" t="n"/>
-      <c r="BP23" s="38" t="n"/>
-      <c r="BQ23" s="39" t="n"/>
+      <c r="BP23" s="25" t="n"/>
+      <c r="BQ23" s="27" t="n"/>
       <c r="BR23" s="28" t="n"/>
       <c r="BS23" s="28" t="n"/>
       <c r="BT23" s="28" t="n"/>
-      <c r="BU23" s="38" t="n"/>
+      <c r="BU23" s="25" t="n"/>
       <c r="BV23" s="29" t="n"/>
       <c r="BW23" s="24" t="n"/>
-      <c r="BX23" s="40" t="n"/>
-      <c r="BY23" s="39" t="n"/>
+      <c r="BX23" s="30" t="n"/>
+      <c r="BY23" s="27" t="n"/>
       <c r="BZ23" s="24" t="n"/>
       <c r="CA23" s="31" t="n"/>
     </row>
@@ -7298,7 +7267,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J24" s="38" t="n"/>
+      <c r="J24" s="25" t="n"/>
       <c r="K24" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -7307,7 +7276,7 @@
       <c r="L24" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="M24" s="39" t="n">
+      <c r="M24" s="27" t="n">
         <v>1.75188</v>
       </c>
       <c r="N24" s="28" t="n">
@@ -7347,11 +7316,11 @@
       <c r="X24" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y24" s="38" t="n"/>
+      <c r="Y24" s="25" t="n"/>
       <c r="Z24" s="26" t="n"/>
       <c r="AA24" s="28" t="n"/>
       <c r="AB24" s="28" t="n"/>
-      <c r="AC24" s="40" t="n">
+      <c r="AC24" s="30" t="n">
         <v>-1.5</v>
       </c>
       <c r="AD24" s="24" t="inlineStr">
@@ -7398,11 +7367,11 @@
         </is>
       </c>
       <c r="BI24" s="24" t="n"/>
-      <c r="BJ24" s="38" t="n"/>
+      <c r="BJ24" s="25" t="n"/>
       <c r="BK24" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="BL24" s="39" t="n">
+      <c r="BL24" s="27" t="n">
         <v>1.75188</v>
       </c>
       <c r="BM24" s="28" t="n">
@@ -7412,16 +7381,16 @@
         <v>0.567164</v>
       </c>
       <c r="BO24" s="28" t="n"/>
-      <c r="BP24" s="38" t="n"/>
-      <c r="BQ24" s="39" t="n"/>
+      <c r="BP24" s="25" t="n"/>
+      <c r="BQ24" s="27" t="n"/>
       <c r="BR24" s="28" t="n"/>
       <c r="BS24" s="28" t="n"/>
       <c r="BT24" s="28" t="n"/>
-      <c r="BU24" s="38" t="n"/>
+      <c r="BU24" s="25" t="n"/>
       <c r="BV24" s="29" t="n"/>
       <c r="BW24" s="24" t="n"/>
-      <c r="BX24" s="40" t="n"/>
-      <c r="BY24" s="39" t="n"/>
+      <c r="BX24" s="30" t="n"/>
+      <c r="BY24" s="27" t="n"/>
       <c r="BZ24" s="24" t="n"/>
       <c r="CA24" s="31" t="n"/>
     </row>
@@ -7471,7 +7440,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J25" s="38" t="n"/>
+      <c r="J25" s="25" t="n"/>
       <c r="K25" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -7480,7 +7449,7 @@
       <c r="L25" s="26" t="n">
         <v>104</v>
       </c>
-      <c r="M25" s="39" t="n">
+      <c r="M25" s="27" t="n">
         <v>2.04</v>
       </c>
       <c r="N25" s="28" t="n">
@@ -7520,11 +7489,11 @@
       <c r="X25" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y25" s="38" t="n"/>
+      <c r="Y25" s="25" t="n"/>
       <c r="Z25" s="26" t="n"/>
       <c r="AA25" s="28" t="n"/>
       <c r="AB25" s="28" t="n"/>
-      <c r="AC25" s="40" t="n">
+      <c r="AC25" s="30" t="n">
         <v>1.3</v>
       </c>
       <c r="AD25" s="24" t="inlineStr">
@@ -7571,11 +7540,11 @@
         </is>
       </c>
       <c r="BI25" s="24" t="n"/>
-      <c r="BJ25" s="38" t="n"/>
+      <c r="BJ25" s="25" t="n"/>
       <c r="BK25" s="26" t="n">
         <v>104</v>
       </c>
-      <c r="BL25" s="39" t="n">
+      <c r="BL25" s="27" t="n">
         <v>2.04</v>
       </c>
       <c r="BM25" s="28" t="n">
@@ -7585,16 +7554,16 @@
         <v>0.487562</v>
       </c>
       <c r="BO25" s="28" t="n"/>
-      <c r="BP25" s="38" t="n"/>
-      <c r="BQ25" s="39" t="n"/>
+      <c r="BP25" s="25" t="n"/>
+      <c r="BQ25" s="27" t="n"/>
       <c r="BR25" s="28" t="n"/>
       <c r="BS25" s="28" t="n"/>
       <c r="BT25" s="28" t="n"/>
-      <c r="BU25" s="38" t="n"/>
+      <c r="BU25" s="25" t="n"/>
       <c r="BV25" s="29" t="n"/>
       <c r="BW25" s="24" t="n"/>
-      <c r="BX25" s="40" t="n"/>
-      <c r="BY25" s="39" t="n"/>
+      <c r="BX25" s="30" t="n"/>
+      <c r="BY25" s="27" t="n"/>
       <c r="BZ25" s="24" t="n"/>
       <c r="CA25" s="31" t="n"/>
     </row>
@@ -7644,7 +7613,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J26" s="38" t="n"/>
+      <c r="J26" s="25" t="n"/>
       <c r="K26" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -7653,7 +7622,7 @@
       <c r="L26" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="M26" s="39" t="n">
+      <c r="M26" s="27" t="n">
         <v>1.961538</v>
       </c>
       <c r="N26" s="28" t="n">
@@ -7693,11 +7662,11 @@
       <c r="X26" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="Y26" s="38" t="n"/>
+      <c r="Y26" s="25" t="n"/>
       <c r="Z26" s="26" t="n"/>
       <c r="AA26" s="28" t="n"/>
       <c r="AB26" s="28" t="n"/>
-      <c r="AC26" s="40" t="n">
+      <c r="AC26" s="30" t="n">
         <v>0.9615</v>
       </c>
       <c r="AD26" s="24" t="inlineStr">
@@ -7744,11 +7713,11 @@
         </is>
       </c>
       <c r="BI26" s="24" t="n"/>
-      <c r="BJ26" s="38" t="n"/>
+      <c r="BJ26" s="25" t="n"/>
       <c r="BK26" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="BL26" s="39" t="n">
+      <c r="BL26" s="27" t="n">
         <v>1.961538</v>
       </c>
       <c r="BM26" s="28" t="n">
@@ -7758,16 +7727,16 @@
         <v>0.507463</v>
       </c>
       <c r="BO26" s="28" t="n"/>
-      <c r="BP26" s="38" t="n"/>
-      <c r="BQ26" s="39" t="n"/>
+      <c r="BP26" s="25" t="n"/>
+      <c r="BQ26" s="27" t="n"/>
       <c r="BR26" s="28" t="n"/>
       <c r="BS26" s="28" t="n"/>
       <c r="BT26" s="28" t="n"/>
-      <c r="BU26" s="38" t="n"/>
+      <c r="BU26" s="25" t="n"/>
       <c r="BV26" s="29" t="n"/>
       <c r="BW26" s="24" t="n"/>
-      <c r="BX26" s="40" t="n"/>
-      <c r="BY26" s="39" t="n"/>
+      <c r="BX26" s="30" t="n"/>
+      <c r="BY26" s="27" t="n"/>
       <c r="BZ26" s="24" t="n"/>
       <c r="CA26" s="31" t="n"/>
     </row>
@@ -7817,7 +7786,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J27" s="38" t="n"/>
+      <c r="J27" s="25" t="n"/>
       <c r="K27" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -7826,7 +7795,7 @@
       <c r="L27" s="26" t="n">
         <v>120</v>
       </c>
-      <c r="M27" s="39" t="n">
+      <c r="M27" s="27" t="n">
         <v>2.2</v>
       </c>
       <c r="N27" s="28" t="n">
@@ -7866,11 +7835,11 @@
       <c r="X27" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="Y27" s="38" t="n"/>
+      <c r="Y27" s="25" t="n"/>
       <c r="Z27" s="26" t="n"/>
       <c r="AA27" s="28" t="n"/>
       <c r="AB27" s="28" t="n"/>
-      <c r="AC27" s="40" t="n">
+      <c r="AC27" s="30" t="n">
         <v>-0.75</v>
       </c>
       <c r="AD27" s="24" t="inlineStr">
@@ -7917,11 +7886,11 @@
         </is>
       </c>
       <c r="BI27" s="24" t="n"/>
-      <c r="BJ27" s="38" t="n"/>
+      <c r="BJ27" s="25" t="n"/>
       <c r="BK27" s="26" t="n">
         <v>120</v>
       </c>
-      <c r="BL27" s="39" t="n">
+      <c r="BL27" s="27" t="n">
         <v>2.2</v>
       </c>
       <c r="BM27" s="28" t="n">
@@ -7931,16 +7900,16 @@
         <v>0.452736</v>
       </c>
       <c r="BO27" s="28" t="n"/>
-      <c r="BP27" s="38" t="n"/>
-      <c r="BQ27" s="39" t="n"/>
+      <c r="BP27" s="25" t="n"/>
+      <c r="BQ27" s="27" t="n"/>
       <c r="BR27" s="28" t="n"/>
       <c r="BS27" s="28" t="n"/>
       <c r="BT27" s="28" t="n"/>
-      <c r="BU27" s="38" t="n"/>
+      <c r="BU27" s="25" t="n"/>
       <c r="BV27" s="29" t="n"/>
       <c r="BW27" s="24" t="n"/>
-      <c r="BX27" s="40" t="n"/>
-      <c r="BY27" s="39" t="n"/>
+      <c r="BX27" s="30" t="n"/>
+      <c r="BY27" s="27" t="n"/>
       <c r="BZ27" s="24" t="n"/>
       <c r="CA27" s="31" t="n"/>
     </row>
@@ -7990,7 +7959,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J28" s="38" t="n"/>
+      <c r="J28" s="25" t="n"/>
       <c r="K28" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -7999,7 +7968,7 @@
       <c r="L28" s="26" t="n">
         <v>100</v>
       </c>
-      <c r="M28" s="39" t="n">
+      <c r="M28" s="27" t="n">
         <v>2</v>
       </c>
       <c r="N28" s="28" t="n">
@@ -8039,11 +8008,11 @@
       <c r="X28" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="Y28" s="38" t="n"/>
+      <c r="Y28" s="25" t="n"/>
       <c r="Z28" s="26" t="n"/>
       <c r="AA28" s="28" t="n"/>
       <c r="AB28" s="28" t="n"/>
-      <c r="AC28" s="40" t="n">
+      <c r="AC28" s="30" t="n">
         <v>-0.75</v>
       </c>
       <c r="AD28" s="24" t="inlineStr">
@@ -8090,11 +8059,11 @@
         </is>
       </c>
       <c r="BI28" s="24" t="n"/>
-      <c r="BJ28" s="38" t="n"/>
+      <c r="BJ28" s="25" t="n"/>
       <c r="BK28" s="26" t="n">
         <v>100</v>
       </c>
-      <c r="BL28" s="39" t="n">
+      <c r="BL28" s="27" t="n">
         <v>2</v>
       </c>
       <c r="BM28" s="28" t="n">
@@ -8104,16 +8073,16 @@
         <v>0.497512</v>
       </c>
       <c r="BO28" s="28" t="n"/>
-      <c r="BP28" s="38" t="n"/>
-      <c r="BQ28" s="39" t="n"/>
+      <c r="BP28" s="25" t="n"/>
+      <c r="BQ28" s="27" t="n"/>
       <c r="BR28" s="28" t="n"/>
       <c r="BS28" s="28" t="n"/>
       <c r="BT28" s="28" t="n"/>
-      <c r="BU28" s="38" t="n"/>
+      <c r="BU28" s="25" t="n"/>
       <c r="BV28" s="29" t="n"/>
       <c r="BW28" s="24" t="n"/>
-      <c r="BX28" s="40" t="n"/>
-      <c r="BY28" s="39" t="n"/>
+      <c r="BX28" s="30" t="n"/>
+      <c r="BY28" s="27" t="n"/>
       <c r="BZ28" s="24" t="n"/>
       <c r="CA28" s="31" t="n"/>
     </row>
@@ -8163,7 +8132,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J29" s="38" t="n"/>
+      <c r="J29" s="25" t="n"/>
       <c r="K29" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -8172,7 +8141,7 @@
       <c r="L29" s="26" t="n">
         <v>108</v>
       </c>
-      <c r="M29" s="39" t="n">
+      <c r="M29" s="27" t="n">
         <v>2.08</v>
       </c>
       <c r="N29" s="28" t="n">
@@ -8212,11 +8181,11 @@
       <c r="X29" s="26" t="n">
         <v>8</v>
       </c>
-      <c r="Y29" s="38" t="n"/>
+      <c r="Y29" s="25" t="n"/>
       <c r="Z29" s="26" t="n"/>
       <c r="AA29" s="28" t="n"/>
       <c r="AB29" s="28" t="n"/>
-      <c r="AC29" s="40" t="n">
+      <c r="AC29" s="30" t="n">
         <v>1.35</v>
       </c>
       <c r="AD29" s="24" t="inlineStr">
@@ -8353,11 +8322,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ29" s="38" t="n"/>
+      <c r="BJ29" s="25" t="n"/>
       <c r="BK29" s="26" t="n">
         <v>108</v>
       </c>
-      <c r="BL29" s="39" t="n">
+      <c r="BL29" s="27" t="n">
         <v>2.08</v>
       </c>
       <c r="BM29" s="28" t="n">
@@ -8367,18 +8336,18 @@
         <v>0.477612</v>
       </c>
       <c r="BO29" s="28" t="n"/>
-      <c r="BP29" s="38" t="n"/>
-      <c r="BQ29" s="39" t="n"/>
+      <c r="BP29" s="25" t="n"/>
+      <c r="BQ29" s="27" t="n"/>
       <c r="BR29" s="28" t="n"/>
       <c r="BS29" s="28" t="n"/>
       <c r="BT29" s="28" t="n"/>
-      <c r="BU29" s="38" t="n"/>
+      <c r="BU29" s="25" t="n"/>
       <c r="BV29" s="29" t="n"/>
       <c r="BW29" s="24" t="n"/>
-      <c r="BX29" s="40" t="n">
+      <c r="BX29" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY29" s="39" t="n">
+      <c r="BY29" s="27" t="n">
         <v>1.08</v>
       </c>
       <c r="BZ29" s="24" t="inlineStr">
@@ -8438,7 +8407,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J30" s="38" t="n"/>
+      <c r="J30" s="25" t="n"/>
       <c r="K30" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -8447,7 +8416,7 @@
       <c r="L30" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="M30" s="39" t="n">
+      <c r="M30" s="27" t="n">
         <v>1.75188</v>
       </c>
       <c r="N30" s="28" t="n">
@@ -8487,11 +8456,11 @@
       <c r="X30" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="Y30" s="38" t="n"/>
+      <c r="Y30" s="25" t="n"/>
       <c r="Z30" s="26" t="n"/>
       <c r="AA30" s="28" t="n"/>
       <c r="AB30" s="28" t="n"/>
-      <c r="AC30" s="40" t="n">
+      <c r="AC30" s="30" t="n">
         <v>1.1278</v>
       </c>
       <c r="AD30" s="24" t="inlineStr">
@@ -8628,11 +8597,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ30" s="38" t="n"/>
+      <c r="BJ30" s="25" t="n"/>
       <c r="BK30" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="BL30" s="39" t="n">
+      <c r="BL30" s="27" t="n">
         <v>1.75188</v>
       </c>
       <c r="BM30" s="28" t="n">
@@ -8642,18 +8611,18 @@
         <v>0.567164</v>
       </c>
       <c r="BO30" s="28" t="n"/>
-      <c r="BP30" s="38" t="n"/>
-      <c r="BQ30" s="39" t="n"/>
+      <c r="BP30" s="25" t="n"/>
+      <c r="BQ30" s="27" t="n"/>
       <c r="BR30" s="28" t="n"/>
       <c r="BS30" s="28" t="n"/>
       <c r="BT30" s="28" t="n"/>
-      <c r="BU30" s="38" t="n"/>
+      <c r="BU30" s="25" t="n"/>
       <c r="BV30" s="29" t="n"/>
       <c r="BW30" s="24" t="n"/>
-      <c r="BX30" s="40" t="n">
+      <c r="BX30" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY30" s="39" t="n">
+      <c r="BY30" s="27" t="n">
         <v>0.75188</v>
       </c>
       <c r="BZ30" s="24" t="inlineStr">
@@ -8713,7 +8682,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J31" s="38" t="n"/>
+      <c r="J31" s="25" t="n"/>
       <c r="K31" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -8722,7 +8691,7 @@
       <c r="L31" s="26" t="n">
         <v>130</v>
       </c>
-      <c r="M31" s="39" t="n">
+      <c r="M31" s="27" t="n">
         <v>2.3</v>
       </c>
       <c r="N31" s="28" t="n">
@@ -8762,11 +8731,11 @@
       <c r="X31" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y31" s="38" t="n"/>
+      <c r="Y31" s="25" t="n"/>
       <c r="Z31" s="26" t="n"/>
       <c r="AA31" s="28" t="n"/>
       <c r="AB31" s="28" t="n"/>
-      <c r="AC31" s="40" t="n">
+      <c r="AC31" s="30" t="n">
         <v>-1</v>
       </c>
       <c r="AD31" s="24" t="inlineStr">
@@ -8903,11 +8872,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ31" s="38" t="n"/>
+      <c r="BJ31" s="25" t="n"/>
       <c r="BK31" s="26" t="n">
         <v>130</v>
       </c>
-      <c r="BL31" s="39" t="n">
+      <c r="BL31" s="27" t="n">
         <v>2.3</v>
       </c>
       <c r="BM31" s="28" t="n">
@@ -8917,18 +8886,18 @@
         <v>0.432836</v>
       </c>
       <c r="BO31" s="28" t="n"/>
-      <c r="BP31" s="38" t="n"/>
-      <c r="BQ31" s="39" t="n"/>
+      <c r="BP31" s="25" t="n"/>
+      <c r="BQ31" s="27" t="n"/>
       <c r="BR31" s="28" t="n"/>
       <c r="BS31" s="28" t="n"/>
       <c r="BT31" s="28" t="n"/>
-      <c r="BU31" s="38" t="n"/>
+      <c r="BU31" s="25" t="n"/>
       <c r="BV31" s="29" t="n"/>
       <c r="BW31" s="24" t="n"/>
-      <c r="BX31" s="40" t="n">
+      <c r="BX31" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY31" s="39" t="n">
+      <c r="BY31" s="27" t="n">
         <v>-1</v>
       </c>
       <c r="BZ31" s="24" t="inlineStr">
@@ -8988,7 +8957,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J32" s="38" t="n"/>
+      <c r="J32" s="25" t="n"/>
       <c r="K32" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -8997,7 +8966,7 @@
       <c r="L32" s="26" t="n">
         <v>-108</v>
       </c>
-      <c r="M32" s="39" t="n">
+      <c r="M32" s="27" t="n">
         <v>1.925926</v>
       </c>
       <c r="N32" s="28" t="n">
@@ -9029,11 +8998,11 @@
       <c r="V32" s="24" t="n"/>
       <c r="W32" s="26" t="n"/>
       <c r="X32" s="26" t="n"/>
-      <c r="Y32" s="38" t="n"/>
+      <c r="Y32" s="25" t="n"/>
       <c r="Z32" s="26" t="n"/>
       <c r="AA32" s="28" t="n"/>
       <c r="AB32" s="28" t="n"/>
-      <c r="AC32" s="40" t="n"/>
+      <c r="AC32" s="30" t="n"/>
       <c r="AD32" s="24" t="n"/>
       <c r="AE32" s="31" t="inlineStr">
         <is>
@@ -9164,11 +9133,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ32" s="38" t="n"/>
+      <c r="BJ32" s="25" t="n"/>
       <c r="BK32" s="26" t="n">
         <v>-108</v>
       </c>
-      <c r="BL32" s="39" t="n">
+      <c r="BL32" s="27" t="n">
         <v>1.925926</v>
       </c>
       <c r="BM32" s="28" t="n">
@@ -9178,16 +9147,16 @@
         <v>0.517413</v>
       </c>
       <c r="BO32" s="28" t="n"/>
-      <c r="BP32" s="38" t="n"/>
-      <c r="BQ32" s="39" t="n"/>
+      <c r="BP32" s="25" t="n"/>
+      <c r="BQ32" s="27" t="n"/>
       <c r="BR32" s="28" t="n"/>
       <c r="BS32" s="28" t="n"/>
       <c r="BT32" s="28" t="n"/>
-      <c r="BU32" s="38" t="n"/>
+      <c r="BU32" s="25" t="n"/>
       <c r="BV32" s="29" t="n"/>
       <c r="BW32" s="24" t="n"/>
-      <c r="BX32" s="40" t="n"/>
-      <c r="BY32" s="39" t="n"/>
+      <c r="BX32" s="30" t="n"/>
+      <c r="BY32" s="27" t="n"/>
       <c r="BZ32" s="24" t="n"/>
       <c r="CA32" s="31" t="n"/>
     </row>
@@ -9237,7 +9206,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J33" s="38" t="n"/>
+      <c r="J33" s="25" t="n"/>
       <c r="K33" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -9246,7 +9215,7 @@
       <c r="L33" s="26" t="n">
         <v>135</v>
       </c>
-      <c r="M33" s="39" t="n">
+      <c r="M33" s="27" t="n">
         <v>2.35</v>
       </c>
       <c r="N33" s="28" t="n">
@@ -9278,11 +9247,11 @@
       <c r="V33" s="24" t="n"/>
       <c r="W33" s="26" t="n"/>
       <c r="X33" s="26" t="n"/>
-      <c r="Y33" s="38" t="n"/>
+      <c r="Y33" s="25" t="n"/>
       <c r="Z33" s="26" t="n"/>
       <c r="AA33" s="28" t="n"/>
       <c r="AB33" s="28" t="n"/>
-      <c r="AC33" s="40" t="n"/>
+      <c r="AC33" s="30" t="n"/>
       <c r="AD33" s="24" t="n"/>
       <c r="AE33" s="31" t="inlineStr">
         <is>
@@ -9413,11 +9382,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ33" s="38" t="n"/>
+      <c r="BJ33" s="25" t="n"/>
       <c r="BK33" s="26" t="n">
         <v>135</v>
       </c>
-      <c r="BL33" s="39" t="n">
+      <c r="BL33" s="27" t="n">
         <v>2.35</v>
       </c>
       <c r="BM33" s="28" t="n">
@@ -9427,16 +9396,16 @@
         <v>0.422886</v>
       </c>
       <c r="BO33" s="28" t="n"/>
-      <c r="BP33" s="38" t="n"/>
-      <c r="BQ33" s="39" t="n"/>
+      <c r="BP33" s="25" t="n"/>
+      <c r="BQ33" s="27" t="n"/>
       <c r="BR33" s="28" t="n"/>
       <c r="BS33" s="28" t="n"/>
       <c r="BT33" s="28" t="n"/>
-      <c r="BU33" s="38" t="n"/>
+      <c r="BU33" s="25" t="n"/>
       <c r="BV33" s="29" t="n"/>
       <c r="BW33" s="24" t="n"/>
-      <c r="BX33" s="40" t="n"/>
-      <c r="BY33" s="39" t="n"/>
+      <c r="BX33" s="30" t="n"/>
+      <c r="BY33" s="27" t="n"/>
       <c r="BZ33" s="24" t="n"/>
       <c r="CA33" s="31" t="n"/>
     </row>
@@ -9486,7 +9455,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J34" s="38" t="n"/>
+      <c r="J34" s="25" t="n"/>
       <c r="K34" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -9495,7 +9464,7 @@
       <c r="L34" s="26" t="n">
         <v>-127</v>
       </c>
-      <c r="M34" s="39" t="n">
+      <c r="M34" s="27" t="n">
         <v>1.787402</v>
       </c>
       <c r="N34" s="28" t="n">
@@ -9527,11 +9496,11 @@
       <c r="V34" s="24" t="n"/>
       <c r="W34" s="26" t="n"/>
       <c r="X34" s="26" t="n"/>
-      <c r="Y34" s="38" t="n"/>
+      <c r="Y34" s="25" t="n"/>
       <c r="Z34" s="26" t="n"/>
       <c r="AA34" s="28" t="n"/>
       <c r="AB34" s="28" t="n"/>
-      <c r="AC34" s="40" t="n"/>
+      <c r="AC34" s="30" t="n"/>
       <c r="AD34" s="24" t="n"/>
       <c r="AE34" s="31" t="inlineStr">
         <is>
@@ -9662,11 +9631,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ34" s="38" t="n"/>
+      <c r="BJ34" s="25" t="n"/>
       <c r="BK34" s="26" t="n">
         <v>-127</v>
       </c>
-      <c r="BL34" s="39" t="n">
+      <c r="BL34" s="27" t="n">
         <v>1.787402</v>
       </c>
       <c r="BM34" s="28" t="n">
@@ -9676,16 +9645,16 @@
         <v>0.557214</v>
       </c>
       <c r="BO34" s="28" t="n"/>
-      <c r="BP34" s="38" t="n"/>
-      <c r="BQ34" s="39" t="n"/>
+      <c r="BP34" s="25" t="n"/>
+      <c r="BQ34" s="27" t="n"/>
       <c r="BR34" s="28" t="n"/>
       <c r="BS34" s="28" t="n"/>
       <c r="BT34" s="28" t="n"/>
-      <c r="BU34" s="38" t="n"/>
+      <c r="BU34" s="25" t="n"/>
       <c r="BV34" s="29" t="n"/>
       <c r="BW34" s="24" t="n"/>
-      <c r="BX34" s="40" t="n"/>
-      <c r="BY34" s="39" t="n"/>
+      <c r="BX34" s="30" t="n"/>
+      <c r="BY34" s="27" t="n"/>
       <c r="BZ34" s="24" t="n"/>
       <c r="CA34" s="31" t="n"/>
     </row>
@@ -9735,7 +9704,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J35" s="38" t="n"/>
+      <c r="J35" s="25" t="n"/>
       <c r="K35" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -9744,7 +9713,7 @@
       <c r="L35" s="26" t="n">
         <v>-117</v>
       </c>
-      <c r="M35" s="39" t="n">
+      <c r="M35" s="27" t="n">
         <v>1.854701</v>
       </c>
       <c r="N35" s="28" t="n">
@@ -9776,11 +9745,11 @@
       <c r="V35" s="24" t="n"/>
       <c r="W35" s="26" t="n"/>
       <c r="X35" s="26" t="n"/>
-      <c r="Y35" s="38" t="n"/>
+      <c r="Y35" s="25" t="n"/>
       <c r="Z35" s="26" t="n"/>
       <c r="AA35" s="28" t="n"/>
       <c r="AB35" s="28" t="n"/>
-      <c r="AC35" s="40" t="n"/>
+      <c r="AC35" s="30" t="n"/>
       <c r="AD35" s="24" t="n"/>
       <c r="AE35" s="31" t="inlineStr">
         <is>
@@ -9911,11 +9880,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ35" s="38" t="n"/>
+      <c r="BJ35" s="25" t="n"/>
       <c r="BK35" s="26" t="n">
         <v>-117</v>
       </c>
-      <c r="BL35" s="39" t="n">
+      <c r="BL35" s="27" t="n">
         <v>1.854701</v>
       </c>
       <c r="BM35" s="28" t="n">
@@ -9925,16 +9894,16 @@
         <v>0.537313</v>
       </c>
       <c r="BO35" s="28" t="n"/>
-      <c r="BP35" s="38" t="n"/>
-      <c r="BQ35" s="39" t="n"/>
+      <c r="BP35" s="25" t="n"/>
+      <c r="BQ35" s="27" t="n"/>
       <c r="BR35" s="28" t="n"/>
       <c r="BS35" s="28" t="n"/>
       <c r="BT35" s="28" t="n"/>
-      <c r="BU35" s="38" t="n"/>
+      <c r="BU35" s="25" t="n"/>
       <c r="BV35" s="29" t="n"/>
       <c r="BW35" s="24" t="n"/>
-      <c r="BX35" s="40" t="n"/>
-      <c r="BY35" s="39" t="n"/>
+      <c r="BX35" s="30" t="n"/>
+      <c r="BY35" s="27" t="n"/>
       <c r="BZ35" s="24" t="n"/>
       <c r="CA35" s="31" t="n"/>
     </row>
@@ -9984,7 +9953,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J36" s="38" t="n"/>
+      <c r="J36" s="25" t="n"/>
       <c r="K36" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -9993,7 +9962,7 @@
       <c r="L36" s="26" t="n">
         <v>-125</v>
       </c>
-      <c r="M36" s="39" t="n">
+      <c r="M36" s="27" t="n">
         <v>1.8</v>
       </c>
       <c r="N36" s="28" t="n">
@@ -10025,11 +9994,11 @@
       <c r="V36" s="24" t="n"/>
       <c r="W36" s="26" t="n"/>
       <c r="X36" s="26" t="n"/>
-      <c r="Y36" s="38" t="n"/>
+      <c r="Y36" s="25" t="n"/>
       <c r="Z36" s="26" t="n"/>
       <c r="AA36" s="28" t="n"/>
       <c r="AB36" s="28" t="n"/>
-      <c r="AC36" s="40" t="n"/>
+      <c r="AC36" s="30" t="n"/>
       <c r="AD36" s="24" t="n"/>
       <c r="AE36" s="31" t="inlineStr">
         <is>
@@ -10160,11 +10129,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ36" s="38" t="n"/>
+      <c r="BJ36" s="25" t="n"/>
       <c r="BK36" s="26" t="n">
         <v>-125</v>
       </c>
-      <c r="BL36" s="39" t="n">
+      <c r="BL36" s="27" t="n">
         <v>1.8</v>
       </c>
       <c r="BM36" s="28" t="n">
@@ -10174,16 +10143,16 @@
         <v>0.552239</v>
       </c>
       <c r="BO36" s="28" t="n"/>
-      <c r="BP36" s="38" t="n"/>
-      <c r="BQ36" s="39" t="n"/>
+      <c r="BP36" s="25" t="n"/>
+      <c r="BQ36" s="27" t="n"/>
       <c r="BR36" s="28" t="n"/>
       <c r="BS36" s="28" t="n"/>
       <c r="BT36" s="28" t="n"/>
-      <c r="BU36" s="38" t="n"/>
+      <c r="BU36" s="25" t="n"/>
       <c r="BV36" s="29" t="n"/>
       <c r="BW36" s="24" t="n"/>
-      <c r="BX36" s="40" t="n"/>
-      <c r="BY36" s="39" t="n"/>
+      <c r="BX36" s="30" t="n"/>
+      <c r="BY36" s="27" t="n"/>
       <c r="BZ36" s="24" t="n"/>
       <c r="CA36" s="31" t="n"/>
     </row>
@@ -10233,7 +10202,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J37" s="38" t="n"/>
+      <c r="J37" s="25" t="n"/>
       <c r="K37" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -10242,7 +10211,7 @@
       <c r="L37" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="M37" s="39" t="n">
+      <c r="M37" s="27" t="n">
         <v>1.980392</v>
       </c>
       <c r="N37" s="28" t="n">
@@ -10274,11 +10243,11 @@
       <c r="V37" s="24" t="n"/>
       <c r="W37" s="26" t="n"/>
       <c r="X37" s="26" t="n"/>
-      <c r="Y37" s="38" t="n"/>
+      <c r="Y37" s="25" t="n"/>
       <c r="Z37" s="26" t="n"/>
       <c r="AA37" s="28" t="n"/>
       <c r="AB37" s="28" t="n"/>
-      <c r="AC37" s="40" t="n"/>
+      <c r="AC37" s="30" t="n"/>
       <c r="AD37" s="24" t="n"/>
       <c r="AE37" s="31" t="inlineStr">
         <is>
@@ -10409,11 +10378,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ37" s="38" t="n"/>
+      <c r="BJ37" s="25" t="n"/>
       <c r="BK37" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="BL37" s="39" t="n">
+      <c r="BL37" s="27" t="n">
         <v>1.980392</v>
       </c>
       <c r="BM37" s="28" t="n">
@@ -10423,16 +10392,16 @@
         <v>0.502488</v>
       </c>
       <c r="BO37" s="28" t="n"/>
-      <c r="BP37" s="38" t="n"/>
-      <c r="BQ37" s="39" t="n"/>
+      <c r="BP37" s="25" t="n"/>
+      <c r="BQ37" s="27" t="n"/>
       <c r="BR37" s="28" t="n"/>
       <c r="BS37" s="28" t="n"/>
       <c r="BT37" s="28" t="n"/>
-      <c r="BU37" s="38" t="n"/>
+      <c r="BU37" s="25" t="n"/>
       <c r="BV37" s="29" t="n"/>
       <c r="BW37" s="24" t="n"/>
-      <c r="BX37" s="40" t="n"/>
-      <c r="BY37" s="39" t="n"/>
+      <c r="BX37" s="30" t="n"/>
+      <c r="BY37" s="27" t="n"/>
       <c r="BZ37" s="24" t="n"/>
       <c r="CA37" s="31" t="n"/>
     </row>
@@ -10482,7 +10451,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J38" s="38" t="n"/>
+      <c r="J38" s="25" t="n"/>
       <c r="K38" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -10491,7 +10460,7 @@
       <c r="L38" s="26" t="n">
         <v>108</v>
       </c>
-      <c r="M38" s="39" t="n">
+      <c r="M38" s="27" t="n">
         <v>2.08</v>
       </c>
       <c r="N38" s="28" t="n">
@@ -10523,11 +10492,11 @@
       <c r="V38" s="24" t="n"/>
       <c r="W38" s="26" t="n"/>
       <c r="X38" s="26" t="n"/>
-      <c r="Y38" s="38" t="n"/>
+      <c r="Y38" s="25" t="n"/>
       <c r="Z38" s="26" t="n"/>
       <c r="AA38" s="28" t="n"/>
       <c r="AB38" s="28" t="n"/>
-      <c r="AC38" s="40" t="n"/>
+      <c r="AC38" s="30" t="n"/>
       <c r="AD38" s="24" t="n"/>
       <c r="AE38" s="31" t="inlineStr">
         <is>
@@ -10658,11 +10627,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ38" s="38" t="n"/>
+      <c r="BJ38" s="25" t="n"/>
       <c r="BK38" s="26" t="n">
         <v>108</v>
       </c>
-      <c r="BL38" s="39" t="n">
+      <c r="BL38" s="27" t="n">
         <v>2.08</v>
       </c>
       <c r="BM38" s="28" t="n">
@@ -10672,16 +10641,16 @@
         <v>0.475248</v>
       </c>
       <c r="BO38" s="28" t="n"/>
-      <c r="BP38" s="38" t="n"/>
-      <c r="BQ38" s="39" t="n"/>
+      <c r="BP38" s="25" t="n"/>
+      <c r="BQ38" s="27" t="n"/>
       <c r="BR38" s="28" t="n"/>
       <c r="BS38" s="28" t="n"/>
       <c r="BT38" s="28" t="n"/>
-      <c r="BU38" s="38" t="n"/>
+      <c r="BU38" s="25" t="n"/>
       <c r="BV38" s="29" t="n"/>
       <c r="BW38" s="24" t="n"/>
-      <c r="BX38" s="40" t="n"/>
-      <c r="BY38" s="39" t="n"/>
+      <c r="BX38" s="30" t="n"/>
+      <c r="BY38" s="27" t="n"/>
       <c r="BZ38" s="24" t="n"/>
       <c r="CA38" s="31" t="n"/>
     </row>
@@ -10731,7 +10700,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J39" s="38" t="n"/>
+      <c r="J39" s="25" t="n"/>
       <c r="K39" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -10740,7 +10709,7 @@
       <c r="L39" s="26" t="n">
         <v>-108</v>
       </c>
-      <c r="M39" s="39" t="n">
+      <c r="M39" s="27" t="n">
         <v>1.925926</v>
       </c>
       <c r="N39" s="28" t="n">
@@ -10772,11 +10741,11 @@
       <c r="V39" s="24" t="n"/>
       <c r="W39" s="26" t="n"/>
       <c r="X39" s="26" t="n"/>
-      <c r="Y39" s="38" t="n"/>
+      <c r="Y39" s="25" t="n"/>
       <c r="Z39" s="26" t="n"/>
       <c r="AA39" s="28" t="n"/>
       <c r="AB39" s="28" t="n"/>
-      <c r="AC39" s="40" t="n"/>
+      <c r="AC39" s="30" t="n"/>
       <c r="AD39" s="24" t="n"/>
       <c r="AE39" s="31" t="inlineStr">
         <is>
@@ -10907,11 +10876,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ39" s="38" t="n"/>
+      <c r="BJ39" s="25" t="n"/>
       <c r="BK39" s="26" t="n">
         <v>-108</v>
       </c>
-      <c r="BL39" s="39" t="n">
+      <c r="BL39" s="27" t="n">
         <v>1.925926</v>
       </c>
       <c r="BM39" s="28" t="n">
@@ -10921,16 +10890,16 @@
         <v>0.517413</v>
       </c>
       <c r="BO39" s="28" t="n"/>
-      <c r="BP39" s="38" t="n"/>
-      <c r="BQ39" s="39" t="n"/>
+      <c r="BP39" s="25" t="n"/>
+      <c r="BQ39" s="27" t="n"/>
       <c r="BR39" s="28" t="n"/>
       <c r="BS39" s="28" t="n"/>
       <c r="BT39" s="28" t="n"/>
-      <c r="BU39" s="38" t="n"/>
+      <c r="BU39" s="25" t="n"/>
       <c r="BV39" s="29" t="n"/>
       <c r="BW39" s="24" t="n"/>
-      <c r="BX39" s="40" t="n"/>
-      <c r="BY39" s="39" t="n"/>
+      <c r="BX39" s="30" t="n"/>
+      <c r="BY39" s="27" t="n"/>
       <c r="BZ39" s="24" t="n"/>
       <c r="CA39" s="31" t="n"/>
     </row>

--- a/data/picks.xlsx
+++ b/data/picks.xlsx
@@ -8914,7 +8914,7 @@
     <row r="32" ht="36" customHeight="1">
       <c r="A32" s="24" t="inlineStr">
         <is>
-          <t>4ae204a92d8a47fc</t>
+          <t>279e8c5dd40743fe</t>
         </is>
       </c>
       <c r="B32" s="24" t="inlineStr">
@@ -8924,12 +8924,12 @@
       </c>
       <c r="C32" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T18:40:00-0400</t>
+          <t>2026-07-20T19:00:00-0400</t>
         </is>
       </c>
       <c r="D32" s="24" t="inlineStr">
         <is>
-          <t>401816188</t>
+          <t>401816187</t>
         </is>
       </c>
       <c r="E32" s="24" t="inlineStr">
@@ -8939,12 +8939,12 @@
       </c>
       <c r="F32" s="24" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="G32" s="24" t="inlineStr">
         <is>
-          <t>Cleveland Guardians</t>
+          <t>Philadelphia Phillies</t>
         </is>
       </c>
       <c r="H32" s="24" t="inlineStr">
@@ -8954,7 +8954,7 @@
       </c>
       <c r="I32" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J32" s="25" t="n"/>
@@ -8964,26 +8964,26 @@
         </is>
       </c>
       <c r="L32" s="26" t="n">
-        <v>-108</v>
+        <v>135</v>
       </c>
       <c r="M32" s="27" t="n">
-        <v>1.925926</v>
+        <v>2.35</v>
       </c>
       <c r="N32" s="28" t="n">
-        <v>0.519231</v>
+        <v>0.425532</v>
       </c>
       <c r="O32" s="28" t="n">
-        <v>0.583941</v>
+        <v>0.535498</v>
       </c>
       <c r="P32" s="28" t="n"/>
       <c r="Q32" s="28" t="n">
-        <v>0.06471</v>
+        <v>0.109966</v>
       </c>
       <c r="R32" s="26" t="n">
-        <v>52</v>
+        <v>100</v>
       </c>
       <c r="S32" s="29" t="n">
-        <v>1.25</v>
+        <v>0.75</v>
       </c>
       <c r="T32" s="24" t="inlineStr">
         <is>
@@ -9006,7 +9006,7 @@
       <c r="AD32" s="24" t="n"/>
       <c r="AE32" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5150; executable ask 0.5200 (aec-mlb-min-cle-2026-07-20).</t>
+          <t>Learned LR call at threshold 0.5150; executable ask 0.4250 (aec-mlb-lad-phi-2026-07-20).</t>
         </is>
       </c>
       <c r="AF32" s="31" t="inlineStr">
@@ -9042,37 +9042,37 @@
       </c>
       <c r="AO32" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>NO_CALL_LARGE_DISAGREEMENT_REVIEW</t>
         </is>
       </c>
       <c r="AP32" s="24" t="inlineStr">
         <is>
-          <t>mlb-min</t>
+          <t>mlb-lad</t>
         </is>
       </c>
       <c r="AQ32" s="24" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="AR32" s="24" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="AS32" s="24" t="inlineStr">
         <is>
-          <t>mlb-cle</t>
+          <t>mlb-phi</t>
         </is>
       </c>
       <c r="AT32" s="24" t="inlineStr">
         <is>
-          <t>Cleveland Guardians</t>
+          <t>Philadelphia Phillies</t>
         </is>
       </c>
       <c r="AU32" s="24" t="inlineStr">
         <is>
-          <t>Cleveland Guardians</t>
+          <t>Philadelphia Phillies</t>
         </is>
       </c>
       <c r="AV32" s="24" t="n"/>
@@ -9110,7 +9110,7 @@
       </c>
       <c r="BE32" s="24" t="inlineStr">
         <is>
-          <t>19929f0cfbcdf2ed</t>
+          <t>2e2c2111662001b9</t>
         </is>
       </c>
       <c r="BF32" s="24" t="inlineStr">
@@ -9125,7 +9125,7 @@
       </c>
       <c r="BH32" s="24" t="inlineStr">
         <is>
-          <t>2026-07-19T17:17:28.488847Z</t>
+          <t>2026-07-19T17:17:33.614115Z</t>
         </is>
       </c>
       <c r="BI32" s="24" t="inlineStr">
@@ -9135,16 +9135,16 @@
       </c>
       <c r="BJ32" s="25" t="n"/>
       <c r="BK32" s="26" t="n">
-        <v>-108</v>
+        <v>135</v>
       </c>
       <c r="BL32" s="27" t="n">
-        <v>1.925926</v>
+        <v>2.35</v>
       </c>
       <c r="BM32" s="28" t="n">
-        <v>0.519231</v>
+        <v>0.425532</v>
       </c>
       <c r="BN32" s="28" t="n">
-        <v>0.517413</v>
+        <v>0.422886</v>
       </c>
       <c r="BO32" s="28" t="n"/>
       <c r="BP32" s="25" t="n"/>
@@ -9163,7 +9163,7 @@
     <row r="33" ht="36" customHeight="1">
       <c r="A33" s="24" t="inlineStr">
         <is>
-          <t>279e8c5dd40743fe</t>
+          <t>a1f560f16ca8495f</t>
         </is>
       </c>
       <c r="B33" s="24" t="inlineStr">
@@ -9173,12 +9173,12 @@
       </c>
       <c r="C33" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T19:00:00-0400</t>
+          <t>2026-07-20T19:10:00-0400</t>
         </is>
       </c>
       <c r="D33" s="24" t="inlineStr">
         <is>
-          <t>401816187</t>
+          <t>401816186</t>
         </is>
       </c>
       <c r="E33" s="24" t="inlineStr">
@@ -9188,12 +9188,12 @@
       </c>
       <c r="F33" s="24" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers</t>
+          <t>Baltimore Orioles</t>
         </is>
       </c>
       <c r="G33" s="24" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies</t>
+          <t>Boston Red Sox</t>
         </is>
       </c>
       <c r="H33" s="24" t="inlineStr">
@@ -9203,7 +9203,7 @@
       </c>
       <c r="I33" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J33" s="25" t="n"/>
@@ -9213,26 +9213,26 @@
         </is>
       </c>
       <c r="L33" s="26" t="n">
-        <v>135</v>
+        <v>-117</v>
       </c>
       <c r="M33" s="27" t="n">
-        <v>2.35</v>
+        <v>1.854701</v>
       </c>
       <c r="N33" s="28" t="n">
-        <v>0.425532</v>
+        <v>0.539171</v>
       </c>
       <c r="O33" s="28" t="n">
-        <v>0.535498</v>
+        <v>0.56697</v>
       </c>
       <c r="P33" s="28" t="n"/>
       <c r="Q33" s="28" t="n">
-        <v>0.109966</v>
+        <v>0.027799</v>
       </c>
       <c r="R33" s="26" t="n">
-        <v>100</v>
+        <v>34</v>
       </c>
       <c r="S33" s="29" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="T33" s="24" t="inlineStr">
         <is>
@@ -9255,7 +9255,7 @@
       <c r="AD33" s="24" t="n"/>
       <c r="AE33" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5150; executable ask 0.4250 (aec-mlb-lad-phi-2026-07-20).</t>
+          <t>Learned LR call at threshold 0.5150; executable ask 0.5400 (aec-mlb-bal-bos-2026-07-20).</t>
         </is>
       </c>
       <c r="AF33" s="31" t="inlineStr">
@@ -9291,37 +9291,37 @@
       </c>
       <c r="AO33" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LARGE_DISAGREEMENT_REVIEW</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP33" s="24" t="inlineStr">
         <is>
-          <t>mlb-lad</t>
+          <t>mlb-bal</t>
         </is>
       </c>
       <c r="AQ33" s="24" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers</t>
+          <t>Baltimore Orioles</t>
         </is>
       </c>
       <c r="AR33" s="24" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers</t>
+          <t>Baltimore Orioles</t>
         </is>
       </c>
       <c r="AS33" s="24" t="inlineStr">
         <is>
-          <t>mlb-phi</t>
+          <t>mlb-bos</t>
         </is>
       </c>
       <c r="AT33" s="24" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies</t>
+          <t>Boston Red Sox</t>
         </is>
       </c>
       <c r="AU33" s="24" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies</t>
+          <t>Boston Red Sox</t>
         </is>
       </c>
       <c r="AV33" s="24" t="n"/>
@@ -9359,7 +9359,7 @@
       </c>
       <c r="BE33" s="24" t="inlineStr">
         <is>
-          <t>2e2c2111662001b9</t>
+          <t>a6a83b5ac90d7962</t>
         </is>
       </c>
       <c r="BF33" s="24" t="inlineStr">
@@ -9374,7 +9374,7 @@
       </c>
       <c r="BH33" s="24" t="inlineStr">
         <is>
-          <t>2026-07-19T17:17:33.614115Z</t>
+          <t>2026-07-19T17:17:31.410943Z</t>
         </is>
       </c>
       <c r="BI33" s="24" t="inlineStr">
@@ -9384,16 +9384,16 @@
       </c>
       <c r="BJ33" s="25" t="n"/>
       <c r="BK33" s="26" t="n">
-        <v>135</v>
+        <v>-117</v>
       </c>
       <c r="BL33" s="27" t="n">
-        <v>2.35</v>
+        <v>1.854701</v>
       </c>
       <c r="BM33" s="28" t="n">
-        <v>0.425532</v>
+        <v>0.539171</v>
       </c>
       <c r="BN33" s="28" t="n">
-        <v>0.422886</v>
+        <v>0.537313</v>
       </c>
       <c r="BO33" s="28" t="n"/>
       <c r="BP33" s="25" t="n"/>
@@ -9412,7 +9412,7 @@
     <row r="34" ht="36" customHeight="1">
       <c r="A34" s="24" t="inlineStr">
         <is>
-          <t>5d2cb57b32f14866</t>
+          <t>369b925b172f4b6a</t>
         </is>
       </c>
       <c r="B34" s="24" t="inlineStr">
@@ -9422,12 +9422,12 @@
       </c>
       <c r="C34" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T19:05:00-0400</t>
+          <t>2026-07-21T01:40Z</t>
         </is>
       </c>
       <c r="D34" s="24" t="inlineStr">
         <is>
-          <t>401816189</t>
+          <t>401816199</t>
         </is>
       </c>
       <c r="E34" s="24" t="inlineStr">
@@ -9437,12 +9437,12 @@
       </c>
       <c r="F34" s="24" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>Cincinnati Reds</t>
         </is>
       </c>
       <c r="G34" s="24" t="inlineStr">
         <is>
-          <t>New York Yankees</t>
+          <t>Seattle Mariners</t>
         </is>
       </c>
       <c r="H34" s="24" t="inlineStr">
@@ -9462,26 +9462,26 @@
         </is>
       </c>
       <c r="L34" s="26" t="n">
-        <v>-127</v>
+        <v>-125</v>
       </c>
       <c r="M34" s="27" t="n">
-        <v>1.787402</v>
+        <v>1.8</v>
       </c>
       <c r="N34" s="28" t="n">
-        <v>0.5594710000000001</v>
+        <v>0.555556</v>
       </c>
       <c r="O34" s="28" t="n">
-        <v>0.58711</v>
+        <v>0.597509</v>
       </c>
       <c r="P34" s="28" t="n"/>
       <c r="Q34" s="28" t="n">
-        <v>0.027639</v>
+        <v>0.041953</v>
       </c>
       <c r="R34" s="26" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="S34" s="29" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="T34" s="24" t="inlineStr">
         <is>
@@ -9504,7 +9504,7 @@
       <c r="AD34" s="24" t="n"/>
       <c r="AE34" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5150; executable ask 0.5600 (aec-mlb-pit-nyy-2026-07-20).</t>
+          <t>Learned LR call at threshold 0.5150; executable ask 0.5550 (aec-mlb-cin-sea-2026-07-20).</t>
         </is>
       </c>
       <c r="AF34" s="31" t="inlineStr">
@@ -9545,32 +9545,32 @@
       </c>
       <c r="AP34" s="24" t="inlineStr">
         <is>
-          <t>mlb-pit</t>
+          <t>mlb-cin</t>
         </is>
       </c>
       <c r="AQ34" s="24" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>Cincinnati Reds</t>
         </is>
       </c>
       <c r="AR34" s="24" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>Cincinnati Reds</t>
         </is>
       </c>
       <c r="AS34" s="24" t="inlineStr">
         <is>
-          <t>mlb-nyy</t>
+          <t>mlb-sea</t>
         </is>
       </c>
       <c r="AT34" s="24" t="inlineStr">
         <is>
-          <t>New York Yankees</t>
+          <t>Seattle Mariners</t>
         </is>
       </c>
       <c r="AU34" s="24" t="inlineStr">
         <is>
-          <t>New York Yankees</t>
+          <t>Seattle Mariners</t>
         </is>
       </c>
       <c r="AV34" s="24" t="n"/>
@@ -9608,7 +9608,7 @@
       </c>
       <c r="BE34" s="24" t="inlineStr">
         <is>
-          <t>5ace88fdb9c57ce4</t>
+          <t>982d73638d70c45b</t>
         </is>
       </c>
       <c r="BF34" s="24" t="inlineStr">
@@ -9623,7 +9623,7 @@
       </c>
       <c r="BH34" s="24" t="inlineStr">
         <is>
-          <t>2026-07-19T17:17:29.263038Z</t>
+          <t>2026-07-19T17:17:46.849555Z</t>
         </is>
       </c>
       <c r="BI34" s="24" t="inlineStr">
@@ -9633,16 +9633,16 @@
       </c>
       <c r="BJ34" s="25" t="n"/>
       <c r="BK34" s="26" t="n">
-        <v>-127</v>
+        <v>-125</v>
       </c>
       <c r="BL34" s="27" t="n">
-        <v>1.787402</v>
+        <v>1.8</v>
       </c>
       <c r="BM34" s="28" t="n">
-        <v>0.5594710000000001</v>
+        <v>0.555556</v>
       </c>
       <c r="BN34" s="28" t="n">
-        <v>0.557214</v>
+        <v>0.552239</v>
       </c>
       <c r="BO34" s="28" t="n"/>
       <c r="BP34" s="25" t="n"/>
@@ -9661,7 +9661,7 @@
     <row r="35" ht="36" customHeight="1">
       <c r="A35" s="24" t="inlineStr">
         <is>
-          <t>a1f560f16ca8495f</t>
+          <t>c7a1577522fb4d37</t>
         </is>
       </c>
       <c r="B35" s="24" t="inlineStr">
@@ -9671,12 +9671,12 @@
       </c>
       <c r="C35" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T19:10:00-0400</t>
+          <t>2026-07-21T02:00Z</t>
         </is>
       </c>
       <c r="D35" s="24" t="inlineStr">
         <is>
-          <t>401816186</t>
+          <t>401816200</t>
         </is>
       </c>
       <c r="E35" s="24" t="inlineStr">
@@ -9686,12 +9686,12 @@
       </c>
       <c r="F35" s="24" t="inlineStr">
         <is>
-          <t>Baltimore Orioles</t>
+          <t>St. Louis Cardinals</t>
         </is>
       </c>
       <c r="G35" s="24" t="inlineStr">
         <is>
-          <t>Boston Red Sox</t>
+          <t>Los Angeles Angels</t>
         </is>
       </c>
       <c r="H35" s="24" t="inlineStr">
@@ -9701,7 +9701,7 @@
       </c>
       <c r="I35" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J35" s="25" t="n"/>
@@ -9711,26 +9711,26 @@
         </is>
       </c>
       <c r="L35" s="26" t="n">
-        <v>-117</v>
+        <v>-102</v>
       </c>
       <c r="M35" s="27" t="n">
-        <v>1.854701</v>
+        <v>1.980392</v>
       </c>
       <c r="N35" s="28" t="n">
-        <v>0.539171</v>
+        <v>0.50495</v>
       </c>
       <c r="O35" s="28" t="n">
-        <v>0.56697</v>
+        <v>0.541942</v>
       </c>
       <c r="P35" s="28" t="n"/>
       <c r="Q35" s="28" t="n">
-        <v>0.027799</v>
+        <v>0.036992</v>
       </c>
       <c r="R35" s="26" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="S35" s="29" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="T35" s="24" t="inlineStr">
         <is>
@@ -9753,7 +9753,7 @@
       <c r="AD35" s="24" t="n"/>
       <c r="AE35" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5150; executable ask 0.5400 (aec-mlb-bal-bos-2026-07-20).</t>
+          <t>Learned LR call at threshold 0.5150; executable ask 0.5050 (aec-mlb-stl-laa-2026-07-20).</t>
         </is>
       </c>
       <c r="AF35" s="31" t="inlineStr">
@@ -9794,32 +9794,32 @@
       </c>
       <c r="AP35" s="24" t="inlineStr">
         <is>
-          <t>mlb-bal</t>
+          <t>mlb-stl</t>
         </is>
       </c>
       <c r="AQ35" s="24" t="inlineStr">
         <is>
-          <t>Baltimore Orioles</t>
+          <t>St. Louis Cardinals</t>
         </is>
       </c>
       <c r="AR35" s="24" t="inlineStr">
         <is>
-          <t>Baltimore Orioles</t>
+          <t>St. Louis Cardinals</t>
         </is>
       </c>
       <c r="AS35" s="24" t="inlineStr">
         <is>
-          <t>mlb-bos</t>
+          <t>mlb-laa</t>
         </is>
       </c>
       <c r="AT35" s="24" t="inlineStr">
         <is>
-          <t>Boston Red Sox</t>
+          <t>Los Angeles Angels</t>
         </is>
       </c>
       <c r="AU35" s="24" t="inlineStr">
         <is>
-          <t>Boston Red Sox</t>
+          <t>Los Angeles Angels</t>
         </is>
       </c>
       <c r="AV35" s="24" t="n"/>
@@ -9857,7 +9857,7 @@
       </c>
       <c r="BE35" s="24" t="inlineStr">
         <is>
-          <t>a6a83b5ac90d7962</t>
+          <t>83613a19346b831e</t>
         </is>
       </c>
       <c r="BF35" s="24" t="inlineStr">
@@ -9872,7 +9872,7 @@
       </c>
       <c r="BH35" s="24" t="inlineStr">
         <is>
-          <t>2026-07-19T17:17:31.410943Z</t>
+          <t>2026-07-19T17:17:47.727344Z</t>
         </is>
       </c>
       <c r="BI35" s="24" t="inlineStr">
@@ -9882,16 +9882,16 @@
       </c>
       <c r="BJ35" s="25" t="n"/>
       <c r="BK35" s="26" t="n">
-        <v>-117</v>
+        <v>-102</v>
       </c>
       <c r="BL35" s="27" t="n">
-        <v>1.854701</v>
+        <v>1.980392</v>
       </c>
       <c r="BM35" s="28" t="n">
-        <v>0.539171</v>
+        <v>0.50495</v>
       </c>
       <c r="BN35" s="28" t="n">
-        <v>0.537313</v>
+        <v>0.502488</v>
       </c>
       <c r="BO35" s="28" t="n"/>
       <c r="BP35" s="25" t="n"/>
@@ -9910,37 +9910,37 @@
     <row r="36" ht="36" customHeight="1">
       <c r="A36" s="24" t="inlineStr">
         <is>
-          <t>369b925b172f4b6a</t>
+          <t>5ddbae8d805944cb</t>
         </is>
       </c>
       <c r="B36" s="24" t="inlineStr">
         <is>
-          <t>2026-07-19T17:18:24.670965Z</t>
+          <t>2026-07-19T17:18:29.371620Z</t>
         </is>
       </c>
       <c r="C36" s="24" t="inlineStr">
         <is>
-          <t>2026-07-21T01:40Z</t>
+          <t>2026-07-21T00:00Z</t>
         </is>
       </c>
       <c r="D36" s="24" t="inlineStr">
         <is>
-          <t>401816199</t>
+          <t>401892393</t>
         </is>
       </c>
       <c r="E36" s="24" t="inlineStr">
         <is>
-          <t>MLB</t>
+          <t>WNBA</t>
         </is>
       </c>
       <c r="F36" s="24" t="inlineStr">
         <is>
-          <t>Cincinnati Reds</t>
+          <t>New York Liberty</t>
         </is>
       </c>
       <c r="G36" s="24" t="inlineStr">
         <is>
-          <t>Seattle Mariners</t>
+          <t>Dallas Wings</t>
         </is>
       </c>
       <c r="H36" s="24" t="inlineStr">
@@ -9960,30 +9960,30 @@
         </is>
       </c>
       <c r="L36" s="26" t="n">
-        <v>-125</v>
+        <v>108</v>
       </c>
       <c r="M36" s="27" t="n">
-        <v>1.8</v>
+        <v>2.08</v>
       </c>
       <c r="N36" s="28" t="n">
-        <v>0.555556</v>
+        <v>0.480769</v>
       </c>
       <c r="O36" s="28" t="n">
-        <v>0.597509</v>
+        <v>0.6787840000000001</v>
       </c>
       <c r="P36" s="28" t="n"/>
       <c r="Q36" s="28" t="n">
-        <v>0.041953</v>
+        <v>0.198015</v>
       </c>
       <c r="R36" s="26" t="n">
-        <v>41</v>
+        <v>100</v>
       </c>
       <c r="S36" s="29" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="T36" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>wnba-elo-trend-lr-v3</t>
         </is>
       </c>
       <c r="U36" s="24" t="inlineStr">
@@ -10002,7 +10002,7 @@
       <c r="AD36" s="24" t="n"/>
       <c r="AE36" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5150; executable ask 0.5550 (aec-mlb-cin-sea-2026-07-20).</t>
+          <t>Learned LR call at threshold 0.5000; executable ask 0.4800 (aec-wnba-ny-dal-2026-07-20).</t>
         </is>
       </c>
       <c r="AF36" s="31" t="inlineStr">
@@ -10038,37 +10038,37 @@
       </c>
       <c r="AO36" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>NO_CALL_LARGE_DISAGREEMENT_REVIEW</t>
         </is>
       </c>
       <c r="AP36" s="24" t="inlineStr">
         <is>
-          <t>mlb-cin</t>
+          <t>wnba-nyl</t>
         </is>
       </c>
       <c r="AQ36" s="24" t="inlineStr">
         <is>
-          <t>Cincinnati Reds</t>
+          <t>New York Liberty</t>
         </is>
       </c>
       <c r="AR36" s="24" t="inlineStr">
         <is>
-          <t>Cincinnati Reds</t>
+          <t>New York Liberty</t>
         </is>
       </c>
       <c r="AS36" s="24" t="inlineStr">
         <is>
-          <t>mlb-sea</t>
+          <t>wnba-dal</t>
         </is>
       </c>
       <c r="AT36" s="24" t="inlineStr">
         <is>
-          <t>Seattle Mariners</t>
+          <t>Dallas Wings</t>
         </is>
       </c>
       <c r="AU36" s="24" t="inlineStr">
         <is>
-          <t>Seattle Mariners</t>
+          <t>Dallas Wings</t>
         </is>
       </c>
       <c r="AV36" s="24" t="n"/>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="BA36" s="24" t="inlineStr">
         <is>
-          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+          <t>d339198b196cb3fcd02950ed5efbdd4cefbeb95b2cd63cd756e77f99dc483719</t>
         </is>
       </c>
       <c r="BB36" s="24" t="inlineStr">
@@ -10096,17 +10096,17 @@
       </c>
       <c r="BC36" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>wnba-elo-trend-lr-v3</t>
         </is>
       </c>
       <c r="BD36" s="24" t="inlineStr">
         <is>
-          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+          <t>d339198b196cb3fcd02950ed5efbdd4cefbeb95b2cd63cd756e77f99dc483719</t>
         </is>
       </c>
       <c r="BE36" s="24" t="inlineStr">
         <is>
-          <t>982d73638d70c45b</t>
+          <t>1c6f45e72b2d1f80</t>
         </is>
       </c>
       <c r="BF36" s="24" t="inlineStr">
@@ -10116,12 +10116,12 @@
       </c>
       <c r="BG36" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>wnba-elo-trend-lr-v3</t>
         </is>
       </c>
       <c r="BH36" s="24" t="inlineStr">
         <is>
-          <t>2026-07-19T17:17:46.849555Z</t>
+          <t>2026-07-19T17:17:49.472621Z</t>
         </is>
       </c>
       <c r="BI36" s="24" t="inlineStr">
@@ -10131,16 +10131,16 @@
       </c>
       <c r="BJ36" s="25" t="n"/>
       <c r="BK36" s="26" t="n">
-        <v>-125</v>
+        <v>108</v>
       </c>
       <c r="BL36" s="27" t="n">
-        <v>1.8</v>
+        <v>2.08</v>
       </c>
       <c r="BM36" s="28" t="n">
-        <v>0.555556</v>
+        <v>0.480769</v>
       </c>
       <c r="BN36" s="28" t="n">
-        <v>0.552239</v>
+        <v>0.475248</v>
       </c>
       <c r="BO36" s="28" t="n"/>
       <c r="BP36" s="25" t="n"/>
@@ -10159,22 +10159,22 @@
     <row r="37" ht="36" customHeight="1">
       <c r="A37" s="24" t="inlineStr">
         <is>
-          <t>c7a1577522fb4d37</t>
+          <t>ea9a359adce843bc</t>
         </is>
       </c>
       <c r="B37" s="24" t="inlineStr">
         <is>
-          <t>2026-07-19T17:18:24.670965Z</t>
+          <t>2026-07-20T14:58:17.970946Z</t>
         </is>
       </c>
       <c r="C37" s="24" t="inlineStr">
         <is>
-          <t>2026-07-21T02:00Z</t>
+          <t>2026-07-20T18:40:00-0400</t>
         </is>
       </c>
       <c r="D37" s="24" t="inlineStr">
         <is>
-          <t>401816200</t>
+          <t>401816188</t>
         </is>
       </c>
       <c r="E37" s="24" t="inlineStr">
@@ -10184,12 +10184,12 @@
       </c>
       <c r="F37" s="24" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals</t>
+          <t>Minnesota Twins</t>
         </is>
       </c>
       <c r="G37" s="24" t="inlineStr">
         <is>
-          <t>Los Angeles Angels</t>
+          <t>Cleveland Guardians</t>
         </is>
       </c>
       <c r="H37" s="24" t="inlineStr">
@@ -10199,7 +10199,7 @@
       </c>
       <c r="I37" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J37" s="25" t="n"/>
@@ -10209,30 +10209,30 @@
         </is>
       </c>
       <c r="L37" s="26" t="n">
-        <v>-102</v>
+        <v>111</v>
       </c>
       <c r="M37" s="27" t="n">
-        <v>1.980392</v>
+        <v>2.11</v>
       </c>
       <c r="N37" s="28" t="n">
-        <v>0.50495</v>
+        <v>0.473934</v>
       </c>
       <c r="O37" s="28" t="n">
-        <v>0.541942</v>
+        <v>0.5726869999999999</v>
       </c>
       <c r="P37" s="28" t="n"/>
       <c r="Q37" s="28" t="n">
-        <v>0.036992</v>
+        <v>0.09875299999999999</v>
       </c>
       <c r="R37" s="26" t="n">
-        <v>38</v>
+        <v>99</v>
       </c>
       <c r="S37" s="29" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="T37" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U37" s="24" t="inlineStr">
@@ -10251,7 +10251,7 @@
       <c r="AD37" s="24" t="n"/>
       <c r="AE37" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5150; executable ask 0.5050 (aec-mlb-stl-laa-2026-07-20).</t>
+          <t>Learned LR call at threshold 0.5500; executable ask 0.4750 (aec-mlb-min-cle-2026-07-20).</t>
         </is>
       </c>
       <c r="AF37" s="31" t="inlineStr">
@@ -10287,37 +10287,37 @@
       </c>
       <c r="AO37" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>NO_CALL_LARGE_DISAGREEMENT_REVIEW</t>
         </is>
       </c>
       <c r="AP37" s="24" t="inlineStr">
         <is>
-          <t>mlb-stl</t>
+          <t>mlb-min</t>
         </is>
       </c>
       <c r="AQ37" s="24" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals</t>
+          <t>Minnesota Twins</t>
         </is>
       </c>
       <c r="AR37" s="24" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals</t>
+          <t>Minnesota Twins</t>
         </is>
       </c>
       <c r="AS37" s="24" t="inlineStr">
         <is>
-          <t>mlb-laa</t>
+          <t>mlb-cle</t>
         </is>
       </c>
       <c r="AT37" s="24" t="inlineStr">
         <is>
-          <t>Los Angeles Angels</t>
+          <t>Cleveland Guardians</t>
         </is>
       </c>
       <c r="AU37" s="24" t="inlineStr">
         <is>
-          <t>Los Angeles Angels</t>
+          <t>Cleveland Guardians</t>
         </is>
       </c>
       <c r="AV37" s="24" t="n"/>
@@ -10335,7 +10335,7 @@
       </c>
       <c r="BA37" s="24" t="inlineStr">
         <is>
-          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BB37" s="24" t="inlineStr">
@@ -10345,17 +10345,17 @@
       </c>
       <c r="BC37" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="BD37" s="24" t="inlineStr">
         <is>
-          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BE37" s="24" t="inlineStr">
         <is>
-          <t>83613a19346b831e</t>
+          <t>2170ac399ced5417</t>
         </is>
       </c>
       <c r="BF37" s="24" t="inlineStr">
@@ -10365,12 +10365,12 @@
       </c>
       <c r="BG37" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="BH37" s="24" t="inlineStr">
         <is>
-          <t>2026-07-19T17:17:47.727344Z</t>
+          <t>2026-07-20T14:57:32.219947Z</t>
         </is>
       </c>
       <c r="BI37" s="24" t="inlineStr">
@@ -10380,16 +10380,16 @@
       </c>
       <c r="BJ37" s="25" t="n"/>
       <c r="BK37" s="26" t="n">
-        <v>-102</v>
+        <v>111</v>
       </c>
       <c r="BL37" s="27" t="n">
-        <v>1.980392</v>
+        <v>2.11</v>
       </c>
       <c r="BM37" s="28" t="n">
-        <v>0.50495</v>
+        <v>0.473934</v>
       </c>
       <c r="BN37" s="28" t="n">
-        <v>0.502488</v>
+        <v>0.472637</v>
       </c>
       <c r="BO37" s="28" t="n"/>
       <c r="BP37" s="25" t="n"/>
@@ -10408,37 +10408,37 @@
     <row r="38" ht="36" customHeight="1">
       <c r="A38" s="24" t="inlineStr">
         <is>
-          <t>5ddbae8d805944cb</t>
+          <t>9a7ddbfc3b7343bd</t>
         </is>
       </c>
       <c r="B38" s="24" t="inlineStr">
         <is>
-          <t>2026-07-19T17:18:29.371620Z</t>
+          <t>2026-07-20T14:58:17.970946Z</t>
         </is>
       </c>
       <c r="C38" s="24" t="inlineStr">
         <is>
-          <t>2026-07-21T00:00Z</t>
+          <t>2026-07-20T19:05:00-0400</t>
         </is>
       </c>
       <c r="D38" s="24" t="inlineStr">
         <is>
-          <t>401892393</t>
+          <t>401816189</t>
         </is>
       </c>
       <c r="E38" s="24" t="inlineStr">
         <is>
-          <t>WNBA</t>
+          <t>MLB</t>
         </is>
       </c>
       <c r="F38" s="24" t="inlineStr">
         <is>
-          <t>New York Liberty</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="G38" s="24" t="inlineStr">
         <is>
-          <t>Dallas Wings</t>
+          <t>New York Yankees</t>
         </is>
       </c>
       <c r="H38" s="24" t="inlineStr">
@@ -10458,30 +10458,30 @@
         </is>
       </c>
       <c r="L38" s="26" t="n">
-        <v>108</v>
+        <v>-108</v>
       </c>
       <c r="M38" s="27" t="n">
-        <v>2.08</v>
+        <v>1.925926</v>
       </c>
       <c r="N38" s="28" t="n">
-        <v>0.480769</v>
+        <v>0.519231</v>
       </c>
       <c r="O38" s="28" t="n">
-        <v>0.6787840000000001</v>
+        <v>0.578558</v>
       </c>
       <c r="P38" s="28" t="n"/>
       <c r="Q38" s="28" t="n">
-        <v>0.198015</v>
+        <v>0.059327</v>
       </c>
       <c r="R38" s="26" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="S38" s="29" t="n">
-        <v>0.5</v>
+        <v>1.25</v>
       </c>
       <c r="T38" s="24" t="inlineStr">
         <is>
-          <t>wnba-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U38" s="24" t="inlineStr">
@@ -10500,7 +10500,7 @@
       <c r="AD38" s="24" t="n"/>
       <c r="AE38" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5000; executable ask 0.4800 (aec-wnba-ny-dal-2026-07-20).</t>
+          <t>Learned LR call at threshold 0.5500; executable ask 0.5200 (aec-mlb-pit-nyy-2026-07-20).</t>
         </is>
       </c>
       <c r="AF38" s="31" t="inlineStr">
@@ -10536,37 +10536,37 @@
       </c>
       <c r="AO38" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LARGE_DISAGREEMENT_REVIEW</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP38" s="24" t="inlineStr">
         <is>
-          <t>wnba-nyl</t>
+          <t>mlb-pit</t>
         </is>
       </c>
       <c r="AQ38" s="24" t="inlineStr">
         <is>
-          <t>New York Liberty</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="AR38" s="24" t="inlineStr">
         <is>
-          <t>New York Liberty</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="AS38" s="24" t="inlineStr">
         <is>
-          <t>wnba-dal</t>
+          <t>mlb-nyy</t>
         </is>
       </c>
       <c r="AT38" s="24" t="inlineStr">
         <is>
-          <t>Dallas Wings</t>
+          <t>New York Yankees</t>
         </is>
       </c>
       <c r="AU38" s="24" t="inlineStr">
         <is>
-          <t>Dallas Wings</t>
+          <t>New York Yankees</t>
         </is>
       </c>
       <c r="AV38" s="24" t="n"/>
@@ -10584,7 +10584,7 @@
       </c>
       <c r="BA38" s="24" t="inlineStr">
         <is>
-          <t>d339198b196cb3fcd02950ed5efbdd4cefbeb95b2cd63cd756e77f99dc483719</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BB38" s="24" t="inlineStr">
@@ -10594,17 +10594,17 @@
       </c>
       <c r="BC38" s="24" t="inlineStr">
         <is>
-          <t>wnba-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="BD38" s="24" t="inlineStr">
         <is>
-          <t>d339198b196cb3fcd02950ed5efbdd4cefbeb95b2cd63cd756e77f99dc483719</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BE38" s="24" t="inlineStr">
         <is>
-          <t>1c6f45e72b2d1f80</t>
+          <t>38ab7db5a3798f0c</t>
         </is>
       </c>
       <c r="BF38" s="24" t="inlineStr">
@@ -10614,12 +10614,12 @@
       </c>
       <c r="BG38" s="24" t="inlineStr">
         <is>
-          <t>wnba-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="BH38" s="24" t="inlineStr">
         <is>
-          <t>2026-07-19T17:17:49.472621Z</t>
+          <t>2026-07-20T14:57:35.056972Z</t>
         </is>
       </c>
       <c r="BI38" s="24" t="inlineStr">
@@ -10629,16 +10629,16 @@
       </c>
       <c r="BJ38" s="25" t="n"/>
       <c r="BK38" s="26" t="n">
-        <v>108</v>
+        <v>-108</v>
       </c>
       <c r="BL38" s="27" t="n">
-        <v>2.08</v>
+        <v>1.925926</v>
       </c>
       <c r="BM38" s="28" t="n">
-        <v>0.480769</v>
+        <v>0.519231</v>
       </c>
       <c r="BN38" s="28" t="n">
-        <v>0.475248</v>
+        <v>0.517413</v>
       </c>
       <c r="BO38" s="28" t="n"/>
       <c r="BP38" s="25" t="n"/>
@@ -10657,12 +10657,12 @@
     <row r="39" ht="36" customHeight="1">
       <c r="A39" s="24" t="inlineStr">
         <is>
-          <t>742b29ba1ffd440b</t>
+          <t>33b7223ce80841b3</t>
         </is>
       </c>
       <c r="B39" s="24" t="inlineStr">
         <is>
-          <t>2026-07-19T22:20:13.941752Z</t>
+          <t>2026-07-20T14:58:17.970946Z</t>
         </is>
       </c>
       <c r="C39" s="24" t="inlineStr">
@@ -10716,21 +10716,21 @@
         <v>0.519231</v>
       </c>
       <c r="O39" s="28" t="n">
-        <v>0.575831</v>
+        <v>0.566967</v>
       </c>
       <c r="P39" s="28" t="n"/>
       <c r="Q39" s="28" t="n">
-        <v>0.0566</v>
+        <v>0.047736</v>
       </c>
       <c r="R39" s="26" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="S39" s="29" t="n">
         <v>1.25</v>
       </c>
       <c r="T39" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U39" s="24" t="inlineStr">
@@ -10749,7 +10749,7 @@
       <c r="AD39" s="24" t="n"/>
       <c r="AE39" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5150; executable ask 0.5200 (aec-mlb-det-chc-2026-07-20).</t>
+          <t>Learned LR call at threshold 0.5500; executable ask 0.5200 (aec-mlb-det-chc-2026-07-20).</t>
         </is>
       </c>
       <c r="AF39" s="31" t="inlineStr">
@@ -10833,7 +10833,7 @@
       </c>
       <c r="BA39" s="24" t="inlineStr">
         <is>
-          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BB39" s="24" t="inlineStr">
@@ -10843,17 +10843,17 @@
       </c>
       <c r="BC39" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="BD39" s="24" t="inlineStr">
         <is>
-          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BE39" s="24" t="inlineStr">
         <is>
-          <t>4f45054abf6875ac</t>
+          <t>b84afb2c70e14d93</t>
         </is>
       </c>
       <c r="BF39" s="24" t="inlineStr">
@@ -10863,12 +10863,12 @@
       </c>
       <c r="BG39" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="BH39" s="24" t="inlineStr">
         <is>
-          <t>2026-07-19T17:19:26.722324Z</t>
+          <t>2026-07-20T14:57:46.871986Z</t>
         </is>
       </c>
       <c r="BI39" s="24" t="inlineStr">

--- a/data/picks.xlsx
+++ b/data/picks.xlsx
@@ -21,10 +21,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="0.0###"/>
-    <numFmt numFmtId="165" formatCode="0.000000"/>
-    <numFmt numFmtId="166" formatCode="0.0000"/>
-    <numFmt numFmtId="167" formatCode="0.0%"/>
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
+    <numFmt numFmtId="166" formatCode="0.0###"/>
+    <numFmt numFmtId="167" formatCode="0.000000"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -136,7 +136,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -150,10 +150,10 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -169,10 +169,10 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -184,10 +184,10 @@
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -202,13 +202,13 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="10" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -217,11 +217,38 @@
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -300,8 +327,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CA39" headerRowCount="1">
-  <autoFilter ref="A1:CA39"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CA35" headerRowCount="1">
+  <autoFilter ref="A1:CA35"/>
   <tableColumns count="79">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -738,22 +765,23 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$39)</f>
+        <f>COUNTA('Picks'!$A$2:$A$35)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$39,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$35,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$39,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$35,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$39,"settled",'Picks'!$V$2:$V$39,"win")+COUNTIFS('Picks'!$U$2:$U$39,"settled",'Picks'!$V$2:$V$39,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$35,"settled",'Picks'!$V$2:$V$35,"win")+COUNTIFS('Picks'!$U$2:$U$35,"settled",'Picks'!$V$2:$V$35,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
+    <row r="5"/>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
@@ -778,22 +806,23 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$39,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$35,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$39,"&gt;0",'Picks'!$V$2:$V$39,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$39,"&gt;0",'Picks'!$V$2:$V$39,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$35,"&gt;0",'Picks'!$V$2:$V$35,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$35,"&gt;0",'Picks'!$V$2:$V$35,"loss")</f>
         <v/>
       </c>
-      <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$39,"&gt;0",'Picks'!$V$2:$V$39,"win")/(COUNTIFS('Picks'!$BX$2:$BX$39,"&gt;0",'Picks'!$V$2:$V$39,"win")+COUNTIFS('Picks'!$BX$2:$BX$39,"&gt;0",'Picks'!$V$2:$V$39,"loss")),0)</f>
+      <c r="E7" s="32">
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$35,"&gt;0",'Picks'!$V$2:$V$35,"win")/(COUNTIFS('Picks'!$BX$2:$BX$35,"&gt;0",'Picks'!$V$2:$V$35,"win")+COUNTIFS('Picks'!$BX$2:$BX$35,"&gt;0",'Picks'!$V$2:$V$35,"loss")),0)</f>
         <v/>
       </c>
-      <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$39)/SUM('Picks'!$BX$2:$BX$39),0)</f>
+      <c r="G7" s="32">
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$35)/SUM('Picks'!$BX$2:$BX$35),0)</f>
         <v/>
       </c>
     </row>
+    <row r="8"/>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
@@ -817,23 +846,24 @@
       </c>
     </row>
     <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$39)</f>
+      <c r="A10" s="33">
+        <f>SUM('Picks'!$BY$2:$BY$35)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$39,"&lt;&gt;",'Picks'!$AB$2:$AB$39),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$35,"&lt;&gt;",'Picks'!$AB$2:$AB$35),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$39,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$39,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$35,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$35,"settled")</f>
         <v/>
       </c>
-      <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$39,'Picks'!$AM$2:$AM$39,"QUALIFIED_SHADOW_CALL")</f>
+      <c r="G10" s="33">
+        <f>SUMIFS('Picks'!$AC$2:$AC$35,'Picks'!$AM$2:$AM$35,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
@@ -885,27 +915,27 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$39,$A14,'Picks'!$U$2:$U$39,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$35,$A14,'Picks'!$U$2:$U$35,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$39,$A14,'Picks'!$U$2:$U$39,"settled",'Picks'!$V$2:$V$39,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$35,$A14,'Picks'!$U$2:$U$35,"settled",'Picks'!$V$2:$V$35,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$39,$A14,'Picks'!$U$2:$U$39,"settled",'Picks'!$V$2:$V$39,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$35,$A14,'Picks'!$U$2:$U$35,"settled",'Picks'!$V$2:$V$35,"loss")</f>
         <v/>
       </c>
-      <c r="E14" s="14">
+      <c r="E14" s="34">
         <f>IFERROR(C14/(C14+D14),0)</f>
         <v/>
       </c>
-      <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$39,'Picks'!$H$2:$H$39,$A14)</f>
+      <c r="F14" s="35">
+        <f>SUMIFS('Picks'!$BY$2:$BY$35,'Picks'!$H$2:$H$35,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$39,'Picks'!$H$2:$H$39,$A14,'Picks'!$U$2:$U$39,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$35,'Picks'!$H$2:$H$35,$A14,'Picks'!$U$2:$U$35,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -916,27 +946,27 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$39,$A15,'Picks'!$U$2:$U$39,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$35,$A15,'Picks'!$U$2:$U$35,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$39,$A15,'Picks'!$U$2:$U$39,"settled",'Picks'!$V$2:$V$39,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$35,$A15,'Picks'!$U$2:$U$35,"settled",'Picks'!$V$2:$V$35,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$39,$A15,'Picks'!$U$2:$U$39,"settled",'Picks'!$V$2:$V$39,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$35,$A15,'Picks'!$U$2:$U$35,"settled",'Picks'!$V$2:$V$35,"loss")</f>
         <v/>
       </c>
-      <c r="E15" s="19">
+      <c r="E15" s="36">
         <f>IFERROR(C15/(C15+D15),0)</f>
         <v/>
       </c>
-      <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$39,'Picks'!$H$2:$H$39,$A15)</f>
+      <c r="F15" s="37">
+        <f>SUMIFS('Picks'!$BY$2:$BY$35,'Picks'!$H$2:$H$35,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$39,'Picks'!$H$2:$H$39,$A15,'Picks'!$U$2:$U$39,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$35,'Picks'!$H$2:$H$35,$A15,'Picks'!$U$2:$U$35,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -947,30 +977,31 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$39,$A16,'Picks'!$U$2:$U$39,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$35,$A16,'Picks'!$U$2:$U$35,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$39,$A16,'Picks'!$U$2:$U$39,"settled",'Picks'!$V$2:$V$39,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$35,$A16,'Picks'!$U$2:$U$35,"settled",'Picks'!$V$2:$V$35,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$39,$A16,'Picks'!$U$2:$U$39,"settled",'Picks'!$V$2:$V$39,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$35,$A16,'Picks'!$U$2:$U$35,"settled",'Picks'!$V$2:$V$35,"loss")</f>
         <v/>
       </c>
-      <c r="E16" s="14">
+      <c r="E16" s="34">
         <f>IFERROR(C16/(C16+D16),0)</f>
         <v/>
       </c>
-      <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$39,'Picks'!$H$2:$H$39,$A16)</f>
+      <c r="F16" s="35">
+        <f>SUMIFS('Picks'!$BY$2:$BY$35,'Picks'!$H$2:$H$35,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$39,'Picks'!$H$2:$H$39,$A16,'Picks'!$U$2:$U$39,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$35,'Picks'!$H$2:$H$35,$A16,'Picks'!$U$2:$U$35,"settled"),0)</f>
         <v/>
       </c>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="22" t="inlineStr">
         <is>
@@ -996,7 +1027,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CA39"/>
+  <dimension ref="A1:CA35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1523,7 +1554,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J2" s="25" t="n"/>
+      <c r="J2" s="38" t="n"/>
       <c r="K2" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -1532,7 +1563,7 @@
       <c r="L2" s="26" t="n">
         <v>117</v>
       </c>
-      <c r="M2" s="27" t="n">
+      <c r="M2" s="39" t="n">
         <v>2.17</v>
       </c>
       <c r="N2" s="28" t="n">
@@ -1572,11 +1603,11 @@
       <c r="X2" s="26" t="n">
         <v>108</v>
       </c>
-      <c r="Y2" s="25" t="n"/>
+      <c r="Y2" s="38" t="n"/>
       <c r="Z2" s="26" t="n"/>
       <c r="AA2" s="28" t="n"/>
       <c r="AB2" s="28" t="n"/>
-      <c r="AC2" s="30" t="n">
+      <c r="AC2" s="40" t="n">
         <v>1.755</v>
       </c>
       <c r="AD2" s="24" t="inlineStr">
@@ -1713,11 +1744,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ2" s="25" t="n"/>
+      <c r="BJ2" s="38" t="n"/>
       <c r="BK2" s="26" t="n">
         <v>117</v>
       </c>
-      <c r="BL2" s="27" t="n">
+      <c r="BL2" s="39" t="n">
         <v>2.17</v>
       </c>
       <c r="BM2" s="28" t="n">
@@ -1727,18 +1758,18 @@
         <v>0.455446</v>
       </c>
       <c r="BO2" s="28" t="n"/>
-      <c r="BP2" s="25" t="n"/>
-      <c r="BQ2" s="27" t="n"/>
+      <c r="BP2" s="38" t="n"/>
+      <c r="BQ2" s="39" t="n"/>
       <c r="BR2" s="28" t="n"/>
       <c r="BS2" s="28" t="n"/>
       <c r="BT2" s="28" t="n"/>
-      <c r="BU2" s="25" t="n"/>
+      <c r="BU2" s="38" t="n"/>
       <c r="BV2" s="29" t="n"/>
       <c r="BW2" s="24" t="n"/>
-      <c r="BX2" s="30" t="n">
+      <c r="BX2" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY2" s="27" t="n">
+      <c r="BY2" s="39" t="n">
         <v>1.17</v>
       </c>
       <c r="BZ2" s="24" t="inlineStr">
@@ -1798,7 +1829,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J3" s="25" t="n"/>
+      <c r="J3" s="38" t="n"/>
       <c r="K3" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -1807,7 +1838,7 @@
       <c r="L3" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="M3" s="27" t="n">
+      <c r="M3" s="39" t="n">
         <v>1.75188</v>
       </c>
       <c r="N3" s="28" t="n">
@@ -1821,14 +1852,14 @@
         <v>0.037938</v>
       </c>
       <c r="R3" s="26" t="n">
-        <v>69</v>
+        <v>37</v>
       </c>
       <c r="S3" s="29" t="n">
         <v>1.5</v>
       </c>
       <c r="T3" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U3" s="24" t="inlineStr">
@@ -1847,11 +1878,11 @@
       <c r="X3" s="26" t="n">
         <v>8</v>
       </c>
-      <c r="Y3" s="25" t="n"/>
+      <c r="Y3" s="38" t="n"/>
       <c r="Z3" s="26" t="n"/>
       <c r="AA3" s="28" t="n"/>
       <c r="AB3" s="28" t="n"/>
-      <c r="AC3" s="30" t="n">
+      <c r="AC3" s="40" t="n">
         <v>1.1278</v>
       </c>
       <c r="AD3" s="24" t="inlineStr">
@@ -1945,7 +1976,7 @@
       </c>
       <c r="BA3" s="24" t="inlineStr">
         <is>
-          <t>117c03794b1d1031deec3bd4cce88c9158bebd0622c621defd0aab3eb37c0a6e</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BB3" s="24" t="inlineStr">
@@ -1955,29 +1986,29 @@
       </c>
       <c r="BC3" s="24" t="inlineStr">
         <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD3" s="24" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
+      <c r="BE3" s="24" t="inlineStr">
+        <is>
+          <t>0f54459b91a18ff1</t>
+        </is>
+      </c>
+      <c r="BF3" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG3" s="24" t="inlineStr">
+        <is>
           <t>mlb-elo-trend-lr-v3</t>
         </is>
       </c>
-      <c r="BD3" s="24" t="inlineStr">
-        <is>
-          <t>117c03794b1d1031deec3bd4cce88c9158bebd0622c621defd0aab3eb37c0a6e</t>
-        </is>
-      </c>
-      <c r="BE3" s="24" t="inlineStr">
-        <is>
-          <t>0f54459b91a18ff1</t>
-        </is>
-      </c>
-      <c r="BF3" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG3" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v3</t>
-        </is>
-      </c>
       <c r="BH3" s="24" t="inlineStr">
         <is>
           <t>2026-07-18T16:15:15.200995Z</t>
@@ -1988,11 +2019,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ3" s="25" t="n"/>
+      <c r="BJ3" s="38" t="n"/>
       <c r="BK3" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="BL3" s="27" t="n">
+      <c r="BL3" s="39" t="n">
         <v>1.75188</v>
       </c>
       <c r="BM3" s="28" t="n">
@@ -2002,18 +2033,18 @@
         <v>0.567164</v>
       </c>
       <c r="BO3" s="28" t="n"/>
-      <c r="BP3" s="25" t="n"/>
-      <c r="BQ3" s="27" t="n"/>
+      <c r="BP3" s="38" t="n"/>
+      <c r="BQ3" s="39" t="n"/>
       <c r="BR3" s="28" t="n"/>
       <c r="BS3" s="28" t="n"/>
       <c r="BT3" s="28" t="n"/>
-      <c r="BU3" s="25" t="n"/>
+      <c r="BU3" s="38" t="n"/>
       <c r="BV3" s="29" t="n"/>
       <c r="BW3" s="24" t="n"/>
-      <c r="BX3" s="30" t="n">
+      <c r="BX3" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY3" s="27" t="n">
+      <c r="BY3" s="39" t="n">
         <v>0.75188</v>
       </c>
       <c r="BZ3" s="24" t="inlineStr">
@@ -2073,7 +2104,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J4" s="25" t="n"/>
+      <c r="J4" s="38" t="n"/>
       <c r="K4" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -2082,7 +2113,7 @@
       <c r="L4" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="M4" s="27" t="n">
+      <c r="M4" s="39" t="n">
         <v>1.980392</v>
       </c>
       <c r="N4" s="28" t="n">
@@ -2096,14 +2127,14 @@
         <v>0.049134</v>
       </c>
       <c r="R4" s="26" t="n">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="S4" s="29" t="n">
         <v>1</v>
       </c>
       <c r="T4" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U4" s="24" t="inlineStr">
@@ -2122,11 +2153,11 @@
       <c r="X4" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="Y4" s="25" t="n"/>
+      <c r="Y4" s="38" t="n"/>
       <c r="Z4" s="26" t="n"/>
       <c r="AA4" s="28" t="n"/>
       <c r="AB4" s="28" t="n"/>
-      <c r="AC4" s="30" t="n">
+      <c r="AC4" s="40" t="n">
         <v>-1</v>
       </c>
       <c r="AD4" s="24" t="inlineStr">
@@ -2220,7 +2251,7 @@
       </c>
       <c r="BA4" s="24" t="inlineStr">
         <is>
-          <t>c97732889cfca1912f8d78791ff63f04ee3fe987951aced9e4fab541932597cd</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BB4" s="24" t="inlineStr">
@@ -2230,29 +2261,29 @@
       </c>
       <c r="BC4" s="24" t="inlineStr">
         <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD4" s="24" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
+      <c r="BE4" s="24" t="inlineStr">
+        <is>
+          <t>6df496ff8b2da9c6</t>
+        </is>
+      </c>
+      <c r="BF4" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG4" s="24" t="inlineStr">
+        <is>
           <t>mlb-elo-trend-lr-v3</t>
         </is>
       </c>
-      <c r="BD4" s="24" t="inlineStr">
-        <is>
-          <t>c97732889cfca1912f8d78791ff63f04ee3fe987951aced9e4fab541932597cd</t>
-        </is>
-      </c>
-      <c r="BE4" s="24" t="inlineStr">
-        <is>
-          <t>6df496ff8b2da9c6</t>
-        </is>
-      </c>
-      <c r="BF4" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG4" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v3</t>
-        </is>
-      </c>
       <c r="BH4" s="24" t="inlineStr">
         <is>
           <t>2026-07-18T16:42:59.880808Z</t>
@@ -2263,11 +2294,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ4" s="25" t="n"/>
+      <c r="BJ4" s="38" t="n"/>
       <c r="BK4" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="BL4" s="27" t="n">
+      <c r="BL4" s="39" t="n">
         <v>1.980392</v>
       </c>
       <c r="BM4" s="28" t="n">
@@ -2277,18 +2308,18 @@
         <v>0.502488</v>
       </c>
       <c r="BO4" s="28" t="n"/>
-      <c r="BP4" s="25" t="n"/>
-      <c r="BQ4" s="27" t="n"/>
+      <c r="BP4" s="38" t="n"/>
+      <c r="BQ4" s="39" t="n"/>
       <c r="BR4" s="28" t="n"/>
       <c r="BS4" s="28" t="n"/>
       <c r="BT4" s="28" t="n"/>
-      <c r="BU4" s="25" t="n"/>
+      <c r="BU4" s="38" t="n"/>
       <c r="BV4" s="29" t="n"/>
       <c r="BW4" s="24" t="n"/>
-      <c r="BX4" s="30" t="n">
+      <c r="BX4" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY4" s="27" t="n">
+      <c r="BY4" s="39" t="n">
         <v>-1</v>
       </c>
       <c r="BZ4" s="24" t="inlineStr">
@@ -2348,7 +2379,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J5" s="25" t="n"/>
+      <c r="J5" s="38" t="n"/>
       <c r="K5" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -2357,7 +2388,7 @@
       <c r="L5" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="M5" s="27" t="n">
+      <c r="M5" s="39" t="n">
         <v>1.75188</v>
       </c>
       <c r="N5" s="28" t="n">
@@ -2371,14 +2402,14 @@
         <v>0.037548</v>
       </c>
       <c r="R5" s="26" t="n">
-        <v>69</v>
+        <v>37</v>
       </c>
       <c r="S5" s="29" t="n">
         <v>1.5</v>
       </c>
       <c r="T5" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U5" s="24" t="inlineStr">
@@ -2397,11 +2428,11 @@
       <c r="X5" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="Y5" s="25" t="n"/>
+      <c r="Y5" s="38" t="n"/>
       <c r="Z5" s="26" t="n"/>
       <c r="AA5" s="28" t="n"/>
       <c r="AB5" s="28" t="n"/>
-      <c r="AC5" s="30" t="n">
+      <c r="AC5" s="40" t="n">
         <v>1.1278</v>
       </c>
       <c r="AD5" s="24" t="inlineStr">
@@ -2495,7 +2526,7 @@
       </c>
       <c r="BA5" s="24" t="inlineStr">
         <is>
-          <t>c97732889cfca1912f8d78791ff63f04ee3fe987951aced9e4fab541932597cd</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BB5" s="24" t="inlineStr">
@@ -2505,29 +2536,29 @@
       </c>
       <c r="BC5" s="24" t="inlineStr">
         <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD5" s="24" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
+      <c r="BE5" s="24" t="inlineStr">
+        <is>
+          <t>7166685f6e68e237</t>
+        </is>
+      </c>
+      <c r="BF5" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG5" s="24" t="inlineStr">
+        <is>
           <t>mlb-elo-trend-lr-v3</t>
         </is>
       </c>
-      <c r="BD5" s="24" t="inlineStr">
-        <is>
-          <t>c97732889cfca1912f8d78791ff63f04ee3fe987951aced9e4fab541932597cd</t>
-        </is>
-      </c>
-      <c r="BE5" s="24" t="inlineStr">
-        <is>
-          <t>7166685f6e68e237</t>
-        </is>
-      </c>
-      <c r="BF5" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG5" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v3</t>
-        </is>
-      </c>
       <c r="BH5" s="24" t="inlineStr">
         <is>
           <t>2026-07-18T16:42:49.506840Z</t>
@@ -2538,11 +2569,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ5" s="25" t="n"/>
+      <c r="BJ5" s="38" t="n"/>
       <c r="BK5" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="BL5" s="27" t="n">
+      <c r="BL5" s="39" t="n">
         <v>1.75188</v>
       </c>
       <c r="BM5" s="28" t="n">
@@ -2552,18 +2583,18 @@
         <v>0.567164</v>
       </c>
       <c r="BO5" s="28" t="n"/>
-      <c r="BP5" s="25" t="n"/>
-      <c r="BQ5" s="27" t="n"/>
+      <c r="BP5" s="38" t="n"/>
+      <c r="BQ5" s="39" t="n"/>
       <c r="BR5" s="28" t="n"/>
       <c r="BS5" s="28" t="n"/>
       <c r="BT5" s="28" t="n"/>
-      <c r="BU5" s="25" t="n"/>
+      <c r="BU5" s="38" t="n"/>
       <c r="BV5" s="29" t="n"/>
       <c r="BW5" s="24" t="n"/>
-      <c r="BX5" s="30" t="n">
+      <c r="BX5" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY5" s="27" t="n">
+      <c r="BY5" s="39" t="n">
         <v>0.75188</v>
       </c>
       <c r="BZ5" s="24" t="inlineStr">
@@ -2623,7 +2654,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J6" s="25" t="n"/>
+      <c r="J6" s="38" t="n"/>
       <c r="K6" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -2632,7 +2663,7 @@
       <c r="L6" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="M6" s="27" t="n">
+      <c r="M6" s="39" t="n">
         <v>1.961538</v>
       </c>
       <c r="N6" s="28" t="n">
@@ -2646,14 +2677,14 @@
         <v>0.066964</v>
       </c>
       <c r="R6" s="26" t="n">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="S6" s="29" t="n">
         <v>1.25</v>
       </c>
       <c r="T6" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U6" s="24" t="inlineStr">
@@ -2672,11 +2703,11 @@
       <c r="X6" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="Y6" s="25" t="n"/>
+      <c r="Y6" s="38" t="n"/>
       <c r="Z6" s="26" t="n"/>
       <c r="AA6" s="28" t="n"/>
       <c r="AB6" s="28" t="n"/>
-      <c r="AC6" s="30" t="n">
+      <c r="AC6" s="40" t="n">
         <v>1.2019</v>
       </c>
       <c r="AD6" s="24" t="inlineStr">
@@ -2770,7 +2801,7 @@
       </c>
       <c r="BA6" s="24" t="inlineStr">
         <is>
-          <t>c97732889cfca1912f8d78791ff63f04ee3fe987951aced9e4fab541932597cd</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BB6" s="24" t="inlineStr">
@@ -2780,29 +2811,29 @@
       </c>
       <c r="BC6" s="24" t="inlineStr">
         <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD6" s="24" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
+      <c r="BE6" s="24" t="inlineStr">
+        <is>
+          <t>990421d336b67011</t>
+        </is>
+      </c>
+      <c r="BF6" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG6" s="24" t="inlineStr">
+        <is>
           <t>mlb-elo-trend-lr-v3</t>
         </is>
       </c>
-      <c r="BD6" s="24" t="inlineStr">
-        <is>
-          <t>c97732889cfca1912f8d78791ff63f04ee3fe987951aced9e4fab541932597cd</t>
-        </is>
-      </c>
-      <c r="BE6" s="24" t="inlineStr">
-        <is>
-          <t>990421d336b67011</t>
-        </is>
-      </c>
-      <c r="BF6" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG6" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v3</t>
-        </is>
-      </c>
       <c r="BH6" s="24" t="inlineStr">
         <is>
           <t>2026-07-18T16:42:50.404282Z</t>
@@ -2813,11 +2844,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ6" s="25" t="n"/>
+      <c r="BJ6" s="38" t="n"/>
       <c r="BK6" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="BL6" s="27" t="n">
+      <c r="BL6" s="39" t="n">
         <v>1.961538</v>
       </c>
       <c r="BM6" s="28" t="n">
@@ -2827,18 +2858,18 @@
         <v>0.507463</v>
       </c>
       <c r="BO6" s="28" t="n"/>
-      <c r="BP6" s="25" t="n"/>
-      <c r="BQ6" s="27" t="n"/>
+      <c r="BP6" s="38" t="n"/>
+      <c r="BQ6" s="39" t="n"/>
       <c r="BR6" s="28" t="n"/>
       <c r="BS6" s="28" t="n"/>
       <c r="BT6" s="28" t="n"/>
-      <c r="BU6" s="25" t="n"/>
+      <c r="BU6" s="38" t="n"/>
       <c r="BV6" s="29" t="n"/>
       <c r="BW6" s="24" t="n"/>
-      <c r="BX6" s="30" t="n">
+      <c r="BX6" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY6" s="27" t="n">
+      <c r="BY6" s="39" t="n">
         <v>0.961538</v>
       </c>
       <c r="BZ6" s="24" t="inlineStr">
@@ -2898,7 +2929,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J7" s="25" t="n"/>
+      <c r="J7" s="38" t="n"/>
       <c r="K7" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -2907,7 +2938,7 @@
       <c r="L7" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="M7" s="27" t="n">
+      <c r="M7" s="39" t="n">
         <v>1.961538</v>
       </c>
       <c r="N7" s="28" t="n">
@@ -2921,14 +2952,14 @@
         <v>0.072563</v>
       </c>
       <c r="R7" s="26" t="n">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="S7" s="29" t="n">
         <v>1.25</v>
       </c>
       <c r="T7" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U7" s="24" t="inlineStr">
@@ -2947,11 +2978,11 @@
       <c r="X7" s="26" t="n">
         <v>10</v>
       </c>
-      <c r="Y7" s="25" t="n"/>
+      <c r="Y7" s="38" t="n"/>
       <c r="Z7" s="26" t="n"/>
       <c r="AA7" s="28" t="n"/>
       <c r="AB7" s="28" t="n"/>
-      <c r="AC7" s="30" t="n">
+      <c r="AC7" s="40" t="n">
         <v>-1.25</v>
       </c>
       <c r="AD7" s="24" t="inlineStr">
@@ -3045,7 +3076,7 @@
       </c>
       <c r="BA7" s="24" t="inlineStr">
         <is>
-          <t>c97732889cfca1912f8d78791ff63f04ee3fe987951aced9e4fab541932597cd</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BB7" s="24" t="inlineStr">
@@ -3055,29 +3086,29 @@
       </c>
       <c r="BC7" s="24" t="inlineStr">
         <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD7" s="24" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
+      <c r="BE7" s="24" t="inlineStr">
+        <is>
+          <t>4215d10b9bfb4b91</t>
+        </is>
+      </c>
+      <c r="BF7" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG7" s="24" t="inlineStr">
+        <is>
           <t>mlb-elo-trend-lr-v3</t>
         </is>
       </c>
-      <c r="BD7" s="24" t="inlineStr">
-        <is>
-          <t>c97732889cfca1912f8d78791ff63f04ee3fe987951aced9e4fab541932597cd</t>
-        </is>
-      </c>
-      <c r="BE7" s="24" t="inlineStr">
-        <is>
-          <t>4215d10b9bfb4b91</t>
-        </is>
-      </c>
-      <c r="BF7" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG7" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v3</t>
-        </is>
-      </c>
       <c r="BH7" s="24" t="inlineStr">
         <is>
           <t>2026-07-18T16:42:52.313468Z</t>
@@ -3088,11 +3119,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ7" s="25" t="n"/>
+      <c r="BJ7" s="38" t="n"/>
       <c r="BK7" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="BL7" s="27" t="n">
+      <c r="BL7" s="39" t="n">
         <v>1.961538</v>
       </c>
       <c r="BM7" s="28" t="n">
@@ -3102,18 +3133,18 @@
         <v>0.507463</v>
       </c>
       <c r="BO7" s="28" t="n"/>
-      <c r="BP7" s="25" t="n"/>
-      <c r="BQ7" s="27" t="n"/>
+      <c r="BP7" s="38" t="n"/>
+      <c r="BQ7" s="39" t="n"/>
       <c r="BR7" s="28" t="n"/>
       <c r="BS7" s="28" t="n"/>
       <c r="BT7" s="28" t="n"/>
-      <c r="BU7" s="25" t="n"/>
+      <c r="BU7" s="38" t="n"/>
       <c r="BV7" s="29" t="n"/>
       <c r="BW7" s="24" t="n"/>
-      <c r="BX7" s="30" t="n">
+      <c r="BX7" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY7" s="27" t="n">
+      <c r="BY7" s="39" t="n">
         <v>-1</v>
       </c>
       <c r="BZ7" s="24" t="inlineStr">
@@ -3173,7 +3204,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J8" s="25" t="n"/>
+      <c r="J8" s="38" t="n"/>
       <c r="K8" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -3182,7 +3213,7 @@
       <c r="L8" s="26" t="n">
         <v>-106</v>
       </c>
-      <c r="M8" s="27" t="n">
+      <c r="M8" s="39" t="n">
         <v>1.943396</v>
       </c>
       <c r="N8" s="28" t="n">
@@ -3196,14 +3227,14 @@
         <v>0.035734</v>
       </c>
       <c r="R8" s="26" t="n">
-        <v>68</v>
+        <v>35</v>
       </c>
       <c r="S8" s="29" t="n">
         <v>1</v>
       </c>
       <c r="T8" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U8" s="24" t="inlineStr">
@@ -3222,11 +3253,11 @@
       <c r="X8" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="Y8" s="25" t="n"/>
+      <c r="Y8" s="38" t="n"/>
       <c r="Z8" s="26" t="n"/>
       <c r="AA8" s="28" t="n"/>
       <c r="AB8" s="28" t="n"/>
-      <c r="AC8" s="30" t="n">
+      <c r="AC8" s="40" t="n">
         <v>-1</v>
       </c>
       <c r="AD8" s="24" t="inlineStr">
@@ -3320,7 +3351,7 @@
       </c>
       <c r="BA8" s="24" t="inlineStr">
         <is>
-          <t>c97732889cfca1912f8d78791ff63f04ee3fe987951aced9e4fab541932597cd</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BB8" s="24" t="inlineStr">
@@ -3330,29 +3361,29 @@
       </c>
       <c r="BC8" s="24" t="inlineStr">
         <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD8" s="24" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
+      <c r="BE8" s="24" t="inlineStr">
+        <is>
+          <t>a999da31a6f5af28</t>
+        </is>
+      </c>
+      <c r="BF8" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG8" s="24" t="inlineStr">
+        <is>
           <t>mlb-elo-trend-lr-v3</t>
         </is>
       </c>
-      <c r="BD8" s="24" t="inlineStr">
-        <is>
-          <t>c97732889cfca1912f8d78791ff63f04ee3fe987951aced9e4fab541932597cd</t>
-        </is>
-      </c>
-      <c r="BE8" s="24" t="inlineStr">
-        <is>
-          <t>a999da31a6f5af28</t>
-        </is>
-      </c>
-      <c r="BF8" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG8" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v3</t>
-        </is>
-      </c>
       <c r="BH8" s="24" t="inlineStr">
         <is>
           <t>2026-07-18T16:42:57.199270Z</t>
@@ -3363,11 +3394,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ8" s="25" t="n"/>
+      <c r="BJ8" s="38" t="n"/>
       <c r="BK8" s="26" t="n">
         <v>-106</v>
       </c>
-      <c r="BL8" s="27" t="n">
+      <c r="BL8" s="39" t="n">
         <v>1.943396</v>
       </c>
       <c r="BM8" s="28" t="n">
@@ -3377,18 +3408,18 @@
         <v>0.5124379999999999</v>
       </c>
       <c r="BO8" s="28" t="n"/>
-      <c r="BP8" s="25" t="n"/>
-      <c r="BQ8" s="27" t="n"/>
+      <c r="BP8" s="38" t="n"/>
+      <c r="BQ8" s="39" t="n"/>
       <c r="BR8" s="28" t="n"/>
       <c r="BS8" s="28" t="n"/>
       <c r="BT8" s="28" t="n"/>
-      <c r="BU8" s="25" t="n"/>
+      <c r="BU8" s="38" t="n"/>
       <c r="BV8" s="29" t="n"/>
       <c r="BW8" s="24" t="n"/>
-      <c r="BX8" s="30" t="n">
+      <c r="BX8" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY8" s="27" t="n">
+      <c r="BY8" s="39" t="n">
         <v>-1</v>
       </c>
       <c r="BZ8" s="24" t="inlineStr">
@@ -3448,7 +3479,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J9" s="25" t="n"/>
+      <c r="J9" s="38" t="n"/>
       <c r="K9" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -3457,7 +3488,7 @@
       <c r="L9" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="M9" s="27" t="n">
+      <c r="M9" s="39" t="n">
         <v>1.980392</v>
       </c>
       <c r="N9" s="28" t="n">
@@ -3471,14 +3502,14 @@
         <v>0.049134</v>
       </c>
       <c r="R9" s="26" t="n">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="S9" s="29" t="n">
         <v>1</v>
       </c>
       <c r="T9" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U9" s="24" t="inlineStr">
@@ -3497,11 +3528,11 @@
       <c r="X9" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="Y9" s="25" t="n"/>
+      <c r="Y9" s="38" t="n"/>
       <c r="Z9" s="26" t="n"/>
       <c r="AA9" s="28" t="n"/>
       <c r="AB9" s="28" t="n"/>
-      <c r="AC9" s="30" t="n">
+      <c r="AC9" s="40" t="n">
         <v>0.9804</v>
       </c>
       <c r="AD9" s="24" t="inlineStr">
@@ -3595,7 +3626,7 @@
       </c>
       <c r="BA9" s="24" t="inlineStr">
         <is>
-          <t>c97732889cfca1912f8d78791ff63f04ee3fe987951aced9e4fab541932597cd</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BB9" s="24" t="inlineStr">
@@ -3605,29 +3636,29 @@
       </c>
       <c r="BC9" s="24" t="inlineStr">
         <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD9" s="24" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
+      <c r="BE9" s="24" t="inlineStr">
+        <is>
+          <t>3c0f9e9f1d0333c4</t>
+        </is>
+      </c>
+      <c r="BF9" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG9" s="24" t="inlineStr">
+        <is>
           <t>mlb-elo-trend-lr-v3</t>
         </is>
       </c>
-      <c r="BD9" s="24" t="inlineStr">
-        <is>
-          <t>c97732889cfca1912f8d78791ff63f04ee3fe987951aced9e4fab541932597cd</t>
-        </is>
-      </c>
-      <c r="BE9" s="24" t="inlineStr">
-        <is>
-          <t>3c0f9e9f1d0333c4</t>
-        </is>
-      </c>
-      <c r="BF9" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG9" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v3</t>
-        </is>
-      </c>
       <c r="BH9" s="24" t="inlineStr">
         <is>
           <t>2026-07-18T16:42:59.880808Z</t>
@@ -3638,11 +3669,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ9" s="25" t="n"/>
+      <c r="BJ9" s="38" t="n"/>
       <c r="BK9" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="BL9" s="27" t="n">
+      <c r="BL9" s="39" t="n">
         <v>1.980392</v>
       </c>
       <c r="BM9" s="28" t="n">
@@ -3652,18 +3683,18 @@
         <v>0.502488</v>
       </c>
       <c r="BO9" s="28" t="n"/>
-      <c r="BP9" s="25" t="n"/>
-      <c r="BQ9" s="27" t="n"/>
+      <c r="BP9" s="38" t="n"/>
+      <c r="BQ9" s="39" t="n"/>
       <c r="BR9" s="28" t="n"/>
       <c r="BS9" s="28" t="n"/>
       <c r="BT9" s="28" t="n"/>
-      <c r="BU9" s="25" t="n"/>
+      <c r="BU9" s="38" t="n"/>
       <c r="BV9" s="29" t="n"/>
       <c r="BW9" s="24" t="n"/>
-      <c r="BX9" s="30" t="n">
+      <c r="BX9" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY9" s="27" t="n">
+      <c r="BY9" s="39" t="n">
         <v>0.980392</v>
       </c>
       <c r="BZ9" s="24" t="inlineStr">
@@ -3723,7 +3754,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J10" s="25" t="n"/>
+      <c r="J10" s="38" t="n"/>
       <c r="K10" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -3732,7 +3763,7 @@
       <c r="L10" s="26" t="n">
         <v>-138</v>
       </c>
-      <c r="M10" s="27" t="n">
+      <c r="M10" s="39" t="n">
         <v>1.724638</v>
       </c>
       <c r="N10" s="28" t="n">
@@ -3746,14 +3777,14 @@
         <v>0.047926</v>
       </c>
       <c r="R10" s="26" t="n">
-        <v>74</v>
+        <v>47</v>
       </c>
       <c r="S10" s="29" t="n">
         <v>1.75</v>
       </c>
       <c r="T10" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U10" s="24" t="inlineStr">
@@ -3772,11 +3803,11 @@
       <c r="X10" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="Y10" s="25" t="n"/>
+      <c r="Y10" s="38" t="n"/>
       <c r="Z10" s="26" t="n"/>
       <c r="AA10" s="28" t="n"/>
       <c r="AB10" s="28" t="n"/>
-      <c r="AC10" s="30" t="n">
+      <c r="AC10" s="40" t="n">
         <v>1.2681</v>
       </c>
       <c r="AD10" s="24" t="inlineStr">
@@ -3870,7 +3901,7 @@
       </c>
       <c r="BA10" s="24" t="inlineStr">
         <is>
-          <t>c97732889cfca1912f8d78791ff63f04ee3fe987951aced9e4fab541932597cd</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BB10" s="24" t="inlineStr">
@@ -3880,29 +3911,29 @@
       </c>
       <c r="BC10" s="24" t="inlineStr">
         <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD10" s="24" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
+      <c r="BE10" s="24" t="inlineStr">
+        <is>
+          <t>29d502a7704e228f</t>
+        </is>
+      </c>
+      <c r="BF10" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG10" s="24" t="inlineStr">
+        <is>
           <t>mlb-elo-trend-lr-v3</t>
         </is>
       </c>
-      <c r="BD10" s="24" t="inlineStr">
-        <is>
-          <t>c97732889cfca1912f8d78791ff63f04ee3fe987951aced9e4fab541932597cd</t>
-        </is>
-      </c>
-      <c r="BE10" s="24" t="inlineStr">
-        <is>
-          <t>29d502a7704e228f</t>
-        </is>
-      </c>
-      <c r="BF10" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG10" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v3</t>
-        </is>
-      </c>
       <c r="BH10" s="24" t="inlineStr">
         <is>
           <t>2026-07-18T16:43:04.779295Z</t>
@@ -3913,11 +3944,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ10" s="25" t="n"/>
+      <c r="BJ10" s="38" t="n"/>
       <c r="BK10" s="26" t="n">
         <v>-138</v>
       </c>
-      <c r="BL10" s="27" t="n">
+      <c r="BL10" s="39" t="n">
         <v>1.724638</v>
       </c>
       <c r="BM10" s="28" t="n">
@@ -3927,18 +3958,18 @@
         <v>0.577114</v>
       </c>
       <c r="BO10" s="28" t="n"/>
-      <c r="BP10" s="25" t="n"/>
-      <c r="BQ10" s="27" t="n"/>
+      <c r="BP10" s="38" t="n"/>
+      <c r="BQ10" s="39" t="n"/>
       <c r="BR10" s="28" t="n"/>
       <c r="BS10" s="28" t="n"/>
       <c r="BT10" s="28" t="n"/>
-      <c r="BU10" s="25" t="n"/>
+      <c r="BU10" s="38" t="n"/>
       <c r="BV10" s="29" t="n"/>
       <c r="BW10" s="24" t="n"/>
-      <c r="BX10" s="30" t="n">
+      <c r="BX10" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY10" s="27" t="n">
+      <c r="BY10" s="39" t="n">
         <v>0.724638</v>
       </c>
       <c r="BZ10" s="24" t="inlineStr">
@@ -3998,7 +4029,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J11" s="25" t="n"/>
+      <c r="J11" s="38" t="n"/>
       <c r="K11" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -4007,7 +4038,7 @@
       <c r="L11" s="26" t="n">
         <v>102</v>
       </c>
-      <c r="M11" s="27" t="n">
+      <c r="M11" s="39" t="n">
         <v>2.02</v>
       </c>
       <c r="N11" s="28" t="n">
@@ -4021,14 +4052,14 @@
         <v>0.074685</v>
       </c>
       <c r="R11" s="26" t="n">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="S11" s="29" t="n">
         <v>1.25</v>
       </c>
       <c r="T11" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U11" s="24" t="inlineStr">
@@ -4047,11 +4078,11 @@
       <c r="X11" s="26" t="n">
         <v>15</v>
       </c>
-      <c r="Y11" s="25" t="n"/>
+      <c r="Y11" s="38" t="n"/>
       <c r="Z11" s="26" t="n"/>
       <c r="AA11" s="28" t="n"/>
       <c r="AB11" s="28" t="n"/>
-      <c r="AC11" s="30" t="n">
+      <c r="AC11" s="40" t="n">
         <v>1.275</v>
       </c>
       <c r="AD11" s="24" t="inlineStr">
@@ -4145,7 +4176,7 @@
       </c>
       <c r="BA11" s="24" t="inlineStr">
         <is>
-          <t>c97732889cfca1912f8d78791ff63f04ee3fe987951aced9e4fab541932597cd</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BB11" s="24" t="inlineStr">
@@ -4155,29 +4186,29 @@
       </c>
       <c r="BC11" s="24" t="inlineStr">
         <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD11" s="24" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
+      <c r="BE11" s="24" t="inlineStr">
+        <is>
+          <t>d2faed7be6c04691</t>
+        </is>
+      </c>
+      <c r="BF11" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG11" s="24" t="inlineStr">
+        <is>
           <t>mlb-elo-trend-lr-v3</t>
         </is>
       </c>
-      <c r="BD11" s="24" t="inlineStr">
-        <is>
-          <t>c97732889cfca1912f8d78791ff63f04ee3fe987951aced9e4fab541932597cd</t>
-        </is>
-      </c>
-      <c r="BE11" s="24" t="inlineStr">
-        <is>
-          <t>d2faed7be6c04691</t>
-        </is>
-      </c>
-      <c r="BF11" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG11" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v3</t>
-        </is>
-      </c>
       <c r="BH11" s="24" t="inlineStr">
         <is>
           <t>2026-07-18T16:43:06.321641Z</t>
@@ -4188,11 +4219,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ11" s="25" t="n"/>
+      <c r="BJ11" s="38" t="n"/>
       <c r="BK11" s="26" t="n">
         <v>102</v>
       </c>
-      <c r="BL11" s="27" t="n">
+      <c r="BL11" s="39" t="n">
         <v>2.02</v>
       </c>
       <c r="BM11" s="28" t="n">
@@ -4202,18 +4233,18 @@
         <v>0.492537</v>
       </c>
       <c r="BO11" s="28" t="n"/>
-      <c r="BP11" s="25" t="n"/>
-      <c r="BQ11" s="27" t="n"/>
+      <c r="BP11" s="38" t="n"/>
+      <c r="BQ11" s="39" t="n"/>
       <c r="BR11" s="28" t="n"/>
       <c r="BS11" s="28" t="n"/>
       <c r="BT11" s="28" t="n"/>
-      <c r="BU11" s="25" t="n"/>
+      <c r="BU11" s="38" t="n"/>
       <c r="BV11" s="29" t="n"/>
       <c r="BW11" s="24" t="n"/>
-      <c r="BX11" s="30" t="n">
+      <c r="BX11" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY11" s="27" t="n">
+      <c r="BY11" s="39" t="n">
         <v>1.02</v>
       </c>
       <c r="BZ11" s="24" t="inlineStr">
@@ -4273,7 +4304,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J12" s="25" t="n"/>
+      <c r="J12" s="38" t="n"/>
       <c r="K12" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -4282,7 +4313,7 @@
       <c r="L12" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="M12" s="27" t="n">
+      <c r="M12" s="39" t="n">
         <v>1.980392</v>
       </c>
       <c r="N12" s="28" t="n">
@@ -4296,14 +4327,14 @@
         <v>0.040217</v>
       </c>
       <c r="R12" s="26" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="S12" s="29" t="n">
         <v>1</v>
       </c>
       <c r="T12" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U12" s="24" t="inlineStr">
@@ -4322,11 +4353,11 @@
       <c r="X12" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y12" s="25" t="n"/>
+      <c r="Y12" s="38" t="n"/>
       <c r="Z12" s="26" t="n"/>
       <c r="AA12" s="28" t="n"/>
       <c r="AB12" s="28" t="n"/>
-      <c r="AC12" s="30" t="n">
+      <c r="AC12" s="40" t="n">
         <v>-1</v>
       </c>
       <c r="AD12" s="24" t="inlineStr">
@@ -4420,7 +4451,7 @@
       </c>
       <c r="BA12" s="24" t="inlineStr">
         <is>
-          <t>40e5d70a6fae1347ad85569354088d9df4f2d6970f7d7c2f9d4924d65efd0c19</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BB12" s="24" t="inlineStr">
@@ -4430,29 +4461,29 @@
       </c>
       <c r="BC12" s="24" t="inlineStr">
         <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD12" s="24" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
+      <c r="BE12" s="24" t="inlineStr">
+        <is>
+          <t>f6cae9c590f4ed48</t>
+        </is>
+      </c>
+      <c r="BF12" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG12" s="24" t="inlineStr">
+        <is>
           <t>mlb-elo-trend-lr-v3</t>
         </is>
       </c>
-      <c r="BD12" s="24" t="inlineStr">
-        <is>
-          <t>40e5d70a6fae1347ad85569354088d9df4f2d6970f7d7c2f9d4924d65efd0c19</t>
-        </is>
-      </c>
-      <c r="BE12" s="24" t="inlineStr">
-        <is>
-          <t>f6cae9c590f4ed48</t>
-        </is>
-      </c>
-      <c r="BF12" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG12" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v3</t>
-        </is>
-      </c>
       <c r="BH12" s="24" t="inlineStr">
         <is>
           <t>2026-07-18T16:49:31.642864Z</t>
@@ -4463,11 +4494,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ12" s="25" t="n"/>
+      <c r="BJ12" s="38" t="n"/>
       <c r="BK12" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="BL12" s="27" t="n">
+      <c r="BL12" s="39" t="n">
         <v>1.980392</v>
       </c>
       <c r="BM12" s="28" t="n">
@@ -4477,18 +4508,18 @@
         <v>0.502488</v>
       </c>
       <c r="BO12" s="28" t="n"/>
-      <c r="BP12" s="25" t="n"/>
-      <c r="BQ12" s="27" t="n"/>
+      <c r="BP12" s="38" t="n"/>
+      <c r="BQ12" s="39" t="n"/>
       <c r="BR12" s="28" t="n"/>
       <c r="BS12" s="28" t="n"/>
       <c r="BT12" s="28" t="n"/>
-      <c r="BU12" s="25" t="n"/>
+      <c r="BU12" s="38" t="n"/>
       <c r="BV12" s="29" t="n"/>
       <c r="BW12" s="24" t="n"/>
-      <c r="BX12" s="30" t="n">
+      <c r="BX12" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY12" s="27" t="n">
+      <c r="BY12" s="39" t="n">
         <v>-1</v>
       </c>
       <c r="BZ12" s="24" t="inlineStr">
@@ -4548,7 +4579,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J13" s="25" t="n"/>
+      <c r="J13" s="38" t="n"/>
       <c r="K13" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -4557,7 +4588,7 @@
       <c r="L13" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="M13" s="27" t="n">
+      <c r="M13" s="39" t="n">
         <v>1.980392</v>
       </c>
       <c r="N13" s="28" t="n">
@@ -4571,14 +4602,14 @@
         <v>0.06776799999999999</v>
       </c>
       <c r="R13" s="26" t="n">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="S13" s="29" t="n">
         <v>1.25</v>
       </c>
       <c r="T13" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U13" s="24" t="inlineStr">
@@ -4597,11 +4628,11 @@
       <c r="X13" s="26" t="n">
         <v>7</v>
       </c>
-      <c r="Y13" s="25" t="n"/>
+      <c r="Y13" s="38" t="n"/>
       <c r="Z13" s="26" t="n"/>
       <c r="AA13" s="28" t="n"/>
       <c r="AB13" s="28" t="n"/>
-      <c r="AC13" s="30" t="n">
+      <c r="AC13" s="40" t="n">
         <v>1.2255</v>
       </c>
       <c r="AD13" s="24" t="inlineStr">
@@ -4695,7 +4726,7 @@
       </c>
       <c r="BA13" s="24" t="inlineStr">
         <is>
-          <t>21de40f664c548e677d8ffc04521004b3df55963718b1d039537d56f08b84fb1</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BB13" s="24" t="inlineStr">
@@ -4705,29 +4736,29 @@
       </c>
       <c r="BC13" s="24" t="inlineStr">
         <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD13" s="24" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
+      <c r="BE13" s="24" t="inlineStr">
+        <is>
+          <t>db0a002aa4e19b4b</t>
+        </is>
+      </c>
+      <c r="BF13" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG13" s="24" t="inlineStr">
+        <is>
           <t>mlb-elo-trend-lr-v3</t>
         </is>
       </c>
-      <c r="BD13" s="24" t="inlineStr">
-        <is>
-          <t>21de40f664c548e677d8ffc04521004b3df55963718b1d039537d56f08b84fb1</t>
-        </is>
-      </c>
-      <c r="BE13" s="24" t="inlineStr">
-        <is>
-          <t>db0a002aa4e19b4b</t>
-        </is>
-      </c>
-      <c r="BF13" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG13" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v3</t>
-        </is>
-      </c>
       <c r="BH13" s="24" t="inlineStr">
         <is>
           <t>2026-07-18T17:27:47.084596Z</t>
@@ -4738,11 +4769,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ13" s="25" t="n"/>
+      <c r="BJ13" s="38" t="n"/>
       <c r="BK13" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="BL13" s="27" t="n">
+      <c r="BL13" s="39" t="n">
         <v>1.980392</v>
       </c>
       <c r="BM13" s="28" t="n">
@@ -4752,18 +4783,18 @@
         <v>0.502488</v>
       </c>
       <c r="BO13" s="28" t="n"/>
-      <c r="BP13" s="25" t="n"/>
-      <c r="BQ13" s="27" t="n"/>
+      <c r="BP13" s="38" t="n"/>
+      <c r="BQ13" s="39" t="n"/>
       <c r="BR13" s="28" t="n"/>
       <c r="BS13" s="28" t="n"/>
       <c r="BT13" s="28" t="n"/>
-      <c r="BU13" s="25" t="n"/>
+      <c r="BU13" s="38" t="n"/>
       <c r="BV13" s="29" t="n"/>
       <c r="BW13" s="24" t="n"/>
-      <c r="BX13" s="30" t="n">
+      <c r="BX13" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY13" s="27" t="n">
+      <c r="BY13" s="39" t="n">
         <v>0.980392</v>
       </c>
       <c r="BZ13" s="24" t="inlineStr">
@@ -4823,7 +4854,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J14" s="25" t="n"/>
+      <c r="J14" s="38" t="n"/>
       <c r="K14" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -4832,7 +4863,7 @@
       <c r="L14" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="M14" s="27" t="n">
+      <c r="M14" s="39" t="n">
         <v>1.961538</v>
       </c>
       <c r="N14" s="28" t="n">
@@ -4846,14 +4877,14 @@
         <v>0.020811</v>
       </c>
       <c r="R14" s="26" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="S14" s="29" t="n">
         <v>0.75</v>
       </c>
       <c r="T14" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U14" s="24" t="inlineStr">
@@ -4872,11 +4903,11 @@
       <c r="X14" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="Y14" s="25" t="n"/>
+      <c r="Y14" s="38" t="n"/>
       <c r="Z14" s="26" t="n"/>
       <c r="AA14" s="28" t="n"/>
       <c r="AB14" s="28" t="n"/>
-      <c r="AC14" s="30" t="n">
+      <c r="AC14" s="40" t="n">
         <v>-0.75</v>
       </c>
       <c r="AD14" s="24" t="inlineStr">
@@ -4970,7 +5001,7 @@
       </c>
       <c r="BA14" s="24" t="inlineStr">
         <is>
-          <t>21de40f664c548e677d8ffc04521004b3df55963718b1d039537d56f08b84fb1</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BB14" s="24" t="inlineStr">
@@ -4980,29 +5011,29 @@
       </c>
       <c r="BC14" s="24" t="inlineStr">
         <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD14" s="24" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
+      <c r="BE14" s="24" t="inlineStr">
+        <is>
+          <t>ed4675d45b8d4ffe</t>
+        </is>
+      </c>
+      <c r="BF14" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG14" s="24" t="inlineStr">
+        <is>
           <t>mlb-elo-trend-lr-v3</t>
         </is>
       </c>
-      <c r="BD14" s="24" t="inlineStr">
-        <is>
-          <t>21de40f664c548e677d8ffc04521004b3df55963718b1d039537d56f08b84fb1</t>
-        </is>
-      </c>
-      <c r="BE14" s="24" t="inlineStr">
-        <is>
-          <t>ed4675d45b8d4ffe</t>
-        </is>
-      </c>
-      <c r="BF14" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG14" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v3</t>
-        </is>
-      </c>
       <c r="BH14" s="24" t="inlineStr">
         <is>
           <t>2026-07-18T17:27:46.135351Z</t>
@@ -5013,11 +5044,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ14" s="25" t="n"/>
+      <c r="BJ14" s="38" t="n"/>
       <c r="BK14" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="BL14" s="27" t="n">
+      <c r="BL14" s="39" t="n">
         <v>1.961538</v>
       </c>
       <c r="BM14" s="28" t="n">
@@ -5027,18 +5058,18 @@
         <v>0.507463</v>
       </c>
       <c r="BO14" s="28" t="n"/>
-      <c r="BP14" s="25" t="n"/>
-      <c r="BQ14" s="27" t="n"/>
+      <c r="BP14" s="38" t="n"/>
+      <c r="BQ14" s="39" t="n"/>
       <c r="BR14" s="28" t="n"/>
       <c r="BS14" s="28" t="n"/>
       <c r="BT14" s="28" t="n"/>
-      <c r="BU14" s="25" t="n"/>
+      <c r="BU14" s="38" t="n"/>
       <c r="BV14" s="29" t="n"/>
       <c r="BW14" s="24" t="n"/>
-      <c r="BX14" s="30" t="n">
+      <c r="BX14" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY14" s="27" t="n">
+      <c r="BY14" s="39" t="n">
         <v>-1</v>
       </c>
       <c r="BZ14" s="24" t="inlineStr">
@@ -5098,7 +5129,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J15" s="25" t="n"/>
+      <c r="J15" s="38" t="n"/>
       <c r="K15" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -5107,7 +5138,7 @@
       <c r="L15" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="M15" s="27" t="n">
+      <c r="M15" s="39" t="n">
         <v>1.961538</v>
       </c>
       <c r="N15" s="28" t="n">
@@ -5121,14 +5152,14 @@
         <v>0.039772</v>
       </c>
       <c r="R15" s="26" t="n">
-        <v>70</v>
+        <v>39</v>
       </c>
       <c r="S15" s="29" t="n">
         <v>1</v>
       </c>
       <c r="T15" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U15" s="24" t="inlineStr">
@@ -5147,11 +5178,11 @@
       <c r="X15" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="Y15" s="25" t="n"/>
+      <c r="Y15" s="38" t="n"/>
       <c r="Z15" s="26" t="n"/>
       <c r="AA15" s="28" t="n"/>
       <c r="AB15" s="28" t="n"/>
-      <c r="AC15" s="30" t="n">
+      <c r="AC15" s="40" t="n">
         <v>-1</v>
       </c>
       <c r="AD15" s="24" t="inlineStr">
@@ -5245,7 +5276,7 @@
       </c>
       <c r="BA15" s="24" t="inlineStr">
         <is>
-          <t>21de40f664c548e677d8ffc04521004b3df55963718b1d039537d56f08b84fb1</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BB15" s="24" t="inlineStr">
@@ -5255,29 +5286,29 @@
       </c>
       <c r="BC15" s="24" t="inlineStr">
         <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD15" s="24" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
+      <c r="BE15" s="24" t="inlineStr">
+        <is>
+          <t>50f6dab0538e7f4a</t>
+        </is>
+      </c>
+      <c r="BF15" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG15" s="24" t="inlineStr">
+        <is>
           <t>mlb-elo-trend-lr-v3</t>
         </is>
       </c>
-      <c r="BD15" s="24" t="inlineStr">
-        <is>
-          <t>21de40f664c548e677d8ffc04521004b3df55963718b1d039537d56f08b84fb1</t>
-        </is>
-      </c>
-      <c r="BE15" s="24" t="inlineStr">
-        <is>
-          <t>50f6dab0538e7f4a</t>
-        </is>
-      </c>
-      <c r="BF15" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG15" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v3</t>
-        </is>
-      </c>
       <c r="BH15" s="24" t="inlineStr">
         <is>
           <t>2026-07-18T17:36:34.425604Z</t>
@@ -5288,11 +5319,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ15" s="25" t="n"/>
+      <c r="BJ15" s="38" t="n"/>
       <c r="BK15" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="BL15" s="27" t="n">
+      <c r="BL15" s="39" t="n">
         <v>1.961538</v>
       </c>
       <c r="BM15" s="28" t="n">
@@ -5302,18 +5333,18 @@
         <v>0.507463</v>
       </c>
       <c r="BO15" s="28" t="n"/>
-      <c r="BP15" s="25" t="n"/>
-      <c r="BQ15" s="27" t="n"/>
+      <c r="BP15" s="38" t="n"/>
+      <c r="BQ15" s="39" t="n"/>
       <c r="BR15" s="28" t="n"/>
       <c r="BS15" s="28" t="n"/>
       <c r="BT15" s="28" t="n"/>
-      <c r="BU15" s="25" t="n"/>
+      <c r="BU15" s="38" t="n"/>
       <c r="BV15" s="29" t="n"/>
       <c r="BW15" s="24" t="n"/>
-      <c r="BX15" s="30" t="n">
+      <c r="BX15" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY15" s="27" t="n">
+      <c r="BY15" s="39" t="n">
         <v>-1</v>
       </c>
       <c r="BZ15" s="24" t="inlineStr">
@@ -5373,7 +5404,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J16" s="25" t="n"/>
+      <c r="J16" s="38" t="n"/>
       <c r="K16" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -5382,7 +5413,7 @@
       <c r="L16" s="26" t="n">
         <v>-111</v>
       </c>
-      <c r="M16" s="27" t="n">
+      <c r="M16" s="39" t="n">
         <v>1.900901</v>
       </c>
       <c r="N16" s="28" t="n">
@@ -5396,14 +5427,14 @@
         <v>0.079943</v>
       </c>
       <c r="R16" s="26" t="n">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="S16" s="29" t="n">
         <v>1.5</v>
       </c>
       <c r="T16" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U16" s="24" t="inlineStr">
@@ -5422,11 +5453,11 @@
       <c r="X16" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="Y16" s="25" t="n"/>
+      <c r="Y16" s="38" t="n"/>
       <c r="Z16" s="26" t="n"/>
       <c r="AA16" s="28" t="n"/>
       <c r="AB16" s="28" t="n"/>
-      <c r="AC16" s="30" t="n">
+      <c r="AC16" s="40" t="n">
         <v>-1.5</v>
       </c>
       <c r="AD16" s="24" t="inlineStr">
@@ -5520,7 +5551,7 @@
       </c>
       <c r="BA16" s="24" t="inlineStr">
         <is>
-          <t>21de40f664c548e677d8ffc04521004b3df55963718b1d039537d56f08b84fb1</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BB16" s="24" t="inlineStr">
@@ -5530,29 +5561,29 @@
       </c>
       <c r="BC16" s="24" t="inlineStr">
         <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD16" s="24" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
+      <c r="BE16" s="24" t="inlineStr">
+        <is>
+          <t>ce93768fc5c8be02</t>
+        </is>
+      </c>
+      <c r="BF16" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG16" s="24" t="inlineStr">
+        <is>
           <t>mlb-elo-trend-lr-v3</t>
         </is>
       </c>
-      <c r="BD16" s="24" t="inlineStr">
-        <is>
-          <t>21de40f664c548e677d8ffc04521004b3df55963718b1d039537d56f08b84fb1</t>
-        </is>
-      </c>
-      <c r="BE16" s="24" t="inlineStr">
-        <is>
-          <t>ce93768fc5c8be02</t>
-        </is>
-      </c>
-      <c r="BF16" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG16" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v3</t>
-        </is>
-      </c>
       <c r="BH16" s="24" t="inlineStr">
         <is>
           <t>2026-07-18T17:36:34.787099Z</t>
@@ -5563,11 +5594,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ16" s="25" t="n"/>
+      <c r="BJ16" s="38" t="n"/>
       <c r="BK16" s="26" t="n">
         <v>-111</v>
       </c>
-      <c r="BL16" s="27" t="n">
+      <c r="BL16" s="39" t="n">
         <v>1.900901</v>
       </c>
       <c r="BM16" s="28" t="n">
@@ -5577,18 +5608,18 @@
         <v>0.522388</v>
       </c>
       <c r="BO16" s="28" t="n"/>
-      <c r="BP16" s="25" t="n"/>
-      <c r="BQ16" s="27" t="n"/>
+      <c r="BP16" s="38" t="n"/>
+      <c r="BQ16" s="39" t="n"/>
       <c r="BR16" s="28" t="n"/>
       <c r="BS16" s="28" t="n"/>
       <c r="BT16" s="28" t="n"/>
-      <c r="BU16" s="25" t="n"/>
+      <c r="BU16" s="38" t="n"/>
       <c r="BV16" s="29" t="n"/>
       <c r="BW16" s="24" t="n"/>
-      <c r="BX16" s="30" t="n">
+      <c r="BX16" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY16" s="27" t="n">
+      <c r="BY16" s="39" t="n">
         <v>-1</v>
       </c>
       <c r="BZ16" s="24" t="inlineStr">
@@ -5648,7 +5679,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J17" s="25" t="n"/>
+      <c r="J17" s="38" t="n"/>
       <c r="K17" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -5657,7 +5688,7 @@
       <c r="L17" s="26" t="n">
         <v>-108</v>
       </c>
-      <c r="M17" s="27" t="n">
+      <c r="M17" s="39" t="n">
         <v>1.925926</v>
       </c>
       <c r="N17" s="28" t="n">
@@ -5671,14 +5702,14 @@
         <v>0.031345</v>
       </c>
       <c r="R17" s="26" t="n">
-        <v>66</v>
+        <v>31</v>
       </c>
       <c r="S17" s="29" t="n">
         <v>1</v>
       </c>
       <c r="T17" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U17" s="24" t="inlineStr">
@@ -5697,11 +5728,11 @@
       <c r="X17" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="Y17" s="25" t="n"/>
+      <c r="Y17" s="38" t="n"/>
       <c r="Z17" s="26" t="n"/>
       <c r="AA17" s="28" t="n"/>
       <c r="AB17" s="28" t="n"/>
-      <c r="AC17" s="30" t="n">
+      <c r="AC17" s="40" t="n">
         <v>0.9258999999999999</v>
       </c>
       <c r="AD17" s="24" t="inlineStr">
@@ -5795,7 +5826,7 @@
       </c>
       <c r="BA17" s="24" t="inlineStr">
         <is>
-          <t>21de40f664c548e677d8ffc04521004b3df55963718b1d039537d56f08b84fb1</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BB17" s="24" t="inlineStr">
@@ -5805,29 +5836,29 @@
       </c>
       <c r="BC17" s="24" t="inlineStr">
         <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD17" s="24" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
+      <c r="BE17" s="24" t="inlineStr">
+        <is>
+          <t>1e50d689e0ba0748</t>
+        </is>
+      </c>
+      <c r="BF17" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG17" s="24" t="inlineStr">
+        <is>
           <t>mlb-elo-trend-lr-v3</t>
         </is>
       </c>
-      <c r="BD17" s="24" t="inlineStr">
-        <is>
-          <t>21de40f664c548e677d8ffc04521004b3df55963718b1d039537d56f08b84fb1</t>
-        </is>
-      </c>
-      <c r="BE17" s="24" t="inlineStr">
-        <is>
-          <t>1e50d689e0ba0748</t>
-        </is>
-      </c>
-      <c r="BF17" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG17" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v3</t>
-        </is>
-      </c>
       <c r="BH17" s="24" t="inlineStr">
         <is>
           <t>2026-07-18T17:36:36.879504Z</t>
@@ -5838,11 +5869,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ17" s="25" t="n"/>
+      <c r="BJ17" s="38" t="n"/>
       <c r="BK17" s="26" t="n">
         <v>-108</v>
       </c>
-      <c r="BL17" s="27" t="n">
+      <c r="BL17" s="39" t="n">
         <v>1.925926</v>
       </c>
       <c r="BM17" s="28" t="n">
@@ -5852,18 +5883,18 @@
         <v>0.5148509999999999</v>
       </c>
       <c r="BO17" s="28" t="n"/>
-      <c r="BP17" s="25" t="n"/>
-      <c r="BQ17" s="27" t="n"/>
+      <c r="BP17" s="38" t="n"/>
+      <c r="BQ17" s="39" t="n"/>
       <c r="BR17" s="28" t="n"/>
       <c r="BS17" s="28" t="n"/>
       <c r="BT17" s="28" t="n"/>
-      <c r="BU17" s="25" t="n"/>
+      <c r="BU17" s="38" t="n"/>
       <c r="BV17" s="29" t="n"/>
       <c r="BW17" s="24" t="n"/>
-      <c r="BX17" s="30" t="n">
+      <c r="BX17" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY17" s="27" t="n">
+      <c r="BY17" s="39" t="n">
         <v>0.925926</v>
       </c>
       <c r="BZ17" s="24" t="inlineStr">
@@ -5923,7 +5954,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J18" s="25" t="n"/>
+      <c r="J18" s="38" t="n"/>
       <c r="K18" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -5932,7 +5963,7 @@
       <c r="L18" s="26" t="n">
         <v>111</v>
       </c>
-      <c r="M18" s="27" t="n">
+      <c r="M18" s="39" t="n">
         <v>2.11</v>
       </c>
       <c r="N18" s="28" t="n">
@@ -5946,14 +5977,14 @@
         <v>0.090138</v>
       </c>
       <c r="R18" s="26" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="S18" s="29" t="n">
         <v>1.25</v>
       </c>
       <c r="T18" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U18" s="24" t="inlineStr">
@@ -5972,11 +6003,11 @@
       <c r="X18" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="Y18" s="25" t="n"/>
+      <c r="Y18" s="38" t="n"/>
       <c r="Z18" s="26" t="n"/>
       <c r="AA18" s="28" t="n"/>
       <c r="AB18" s="28" t="n"/>
-      <c r="AC18" s="30" t="n">
+      <c r="AC18" s="40" t="n">
         <v>-1.25</v>
       </c>
       <c r="AD18" s="24" t="inlineStr">
@@ -6070,7 +6101,7 @@
       </c>
       <c r="BA18" s="24" t="inlineStr">
         <is>
-          <t>21de40f664c548e677d8ffc04521004b3df55963718b1d039537d56f08b84fb1</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BB18" s="24" t="inlineStr">
@@ -6080,29 +6111,29 @@
       </c>
       <c r="BC18" s="24" t="inlineStr">
         <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD18" s="24" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
+      <c r="BE18" s="24" t="inlineStr">
+        <is>
+          <t>5e36475e8b7bf75d</t>
+        </is>
+      </c>
+      <c r="BF18" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG18" s="24" t="inlineStr">
+        <is>
           <t>mlb-elo-trend-lr-v3</t>
         </is>
       </c>
-      <c r="BD18" s="24" t="inlineStr">
-        <is>
-          <t>21de40f664c548e677d8ffc04521004b3df55963718b1d039537d56f08b84fb1</t>
-        </is>
-      </c>
-      <c r="BE18" s="24" t="inlineStr">
-        <is>
-          <t>5e36475e8b7bf75d</t>
-        </is>
-      </c>
-      <c r="BF18" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG18" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v3</t>
-        </is>
-      </c>
       <c r="BH18" s="24" t="inlineStr">
         <is>
           <t>2026-07-18T17:36:37.946655Z</t>
@@ -6113,11 +6144,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ18" s="25" t="n"/>
+      <c r="BJ18" s="38" t="n"/>
       <c r="BK18" s="26" t="n">
         <v>111</v>
       </c>
-      <c r="BL18" s="27" t="n">
+      <c r="BL18" s="39" t="n">
         <v>2.11</v>
       </c>
       <c r="BM18" s="28" t="n">
@@ -6127,18 +6158,18 @@
         <v>0.472637</v>
       </c>
       <c r="BO18" s="28" t="n"/>
-      <c r="BP18" s="25" t="n"/>
-      <c r="BQ18" s="27" t="n"/>
+      <c r="BP18" s="38" t="n"/>
+      <c r="BQ18" s="39" t="n"/>
       <c r="BR18" s="28" t="n"/>
       <c r="BS18" s="28" t="n"/>
       <c r="BT18" s="28" t="n"/>
-      <c r="BU18" s="25" t="n"/>
+      <c r="BU18" s="38" t="n"/>
       <c r="BV18" s="29" t="n"/>
       <c r="BW18" s="24" t="n"/>
-      <c r="BX18" s="30" t="n">
+      <c r="BX18" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY18" s="27" t="n">
+      <c r="BY18" s="39" t="n">
         <v>-1</v>
       </c>
       <c r="BZ18" s="24" t="inlineStr">
@@ -6198,7 +6229,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J19" s="25" t="n"/>
+      <c r="J19" s="38" t="n"/>
       <c r="K19" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -6207,7 +6238,7 @@
       <c r="L19" s="26" t="n">
         <v>-125</v>
       </c>
-      <c r="M19" s="27" t="n">
+      <c r="M19" s="39" t="n">
         <v>1.8</v>
       </c>
       <c r="N19" s="28" t="n">
@@ -6221,14 +6252,14 @@
         <v>0.051613</v>
       </c>
       <c r="R19" s="26" t="n">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="S19" s="29" t="n">
         <v>1.5</v>
       </c>
       <c r="T19" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U19" s="24" t="inlineStr">
@@ -6247,11 +6278,11 @@
       <c r="X19" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="Y19" s="25" t="n"/>
+      <c r="Y19" s="38" t="n"/>
       <c r="Z19" s="26" t="n"/>
       <c r="AA19" s="28" t="n"/>
       <c r="AB19" s="28" t="n"/>
-      <c r="AC19" s="30" t="n">
+      <c r="AC19" s="40" t="n">
         <v>1.2</v>
       </c>
       <c r="AD19" s="24" t="inlineStr">
@@ -6345,7 +6376,7 @@
       </c>
       <c r="BA19" s="24" t="inlineStr">
         <is>
-          <t>21de40f664c548e677d8ffc04521004b3df55963718b1d039537d56f08b84fb1</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BB19" s="24" t="inlineStr">
@@ -6355,29 +6386,29 @@
       </c>
       <c r="BC19" s="24" t="inlineStr">
         <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD19" s="24" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
+      <c r="BE19" s="24" t="inlineStr">
+        <is>
+          <t>a0d9b1134dce1744</t>
+        </is>
+      </c>
+      <c r="BF19" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG19" s="24" t="inlineStr">
+        <is>
           <t>mlb-elo-trend-lr-v3</t>
         </is>
       </c>
-      <c r="BD19" s="24" t="inlineStr">
-        <is>
-          <t>21de40f664c548e677d8ffc04521004b3df55963718b1d039537d56f08b84fb1</t>
-        </is>
-      </c>
-      <c r="BE19" s="24" t="inlineStr">
-        <is>
-          <t>a0d9b1134dce1744</t>
-        </is>
-      </c>
-      <c r="BF19" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG19" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v3</t>
-        </is>
-      </c>
       <c r="BH19" s="24" t="inlineStr">
         <is>
           <t>2026-07-18T17:36:41.204729Z</t>
@@ -6388,11 +6419,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ19" s="25" t="n"/>
+      <c r="BJ19" s="38" t="n"/>
       <c r="BK19" s="26" t="n">
         <v>-125</v>
       </c>
-      <c r="BL19" s="27" t="n">
+      <c r="BL19" s="39" t="n">
         <v>1.8</v>
       </c>
       <c r="BM19" s="28" t="n">
@@ -6402,18 +6433,18 @@
         <v>0.552239</v>
       </c>
       <c r="BO19" s="28" t="n"/>
-      <c r="BP19" s="25" t="n"/>
-      <c r="BQ19" s="27" t="n"/>
+      <c r="BP19" s="38" t="n"/>
+      <c r="BQ19" s="39" t="n"/>
       <c r="BR19" s="28" t="n"/>
       <c r="BS19" s="28" t="n"/>
       <c r="BT19" s="28" t="n"/>
-      <c r="BU19" s="25" t="n"/>
+      <c r="BU19" s="38" t="n"/>
       <c r="BV19" s="29" t="n"/>
       <c r="BW19" s="24" t="n"/>
-      <c r="BX19" s="30" t="n">
+      <c r="BX19" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY19" s="27" t="n">
+      <c r="BY19" s="39" t="n">
         <v>0.8</v>
       </c>
       <c r="BZ19" s="24" t="inlineStr">
@@ -6473,7 +6504,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J20" s="25" t="n"/>
+      <c r="J20" s="38" t="n"/>
       <c r="K20" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -6482,7 +6513,7 @@
       <c r="L20" s="26" t="n">
         <v>106</v>
       </c>
-      <c r="M20" s="27" t="n">
+      <c r="M20" s="39" t="n">
         <v>2.06</v>
       </c>
       <c r="N20" s="28" t="n">
@@ -6496,14 +6527,14 @@
         <v>0.035428</v>
       </c>
       <c r="R20" s="26" t="n">
-        <v>68</v>
+        <v>35</v>
       </c>
       <c r="S20" s="29" t="n">
         <v>0.75</v>
       </c>
       <c r="T20" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U20" s="24" t="inlineStr">
@@ -6522,11 +6553,11 @@
       <c r="X20" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y20" s="25" t="n"/>
+      <c r="Y20" s="38" t="n"/>
       <c r="Z20" s="26" t="n"/>
       <c r="AA20" s="28" t="n"/>
       <c r="AB20" s="28" t="n"/>
-      <c r="AC20" s="30" t="n">
+      <c r="AC20" s="40" t="n">
         <v>0.795</v>
       </c>
       <c r="AD20" s="24" t="inlineStr">
@@ -6620,7 +6651,7 @@
       </c>
       <c r="BA20" s="24" t="inlineStr">
         <is>
-          <t>21de40f664c548e677d8ffc04521004b3df55963718b1d039537d56f08b84fb1</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BB20" s="24" t="inlineStr">
@@ -6630,29 +6661,29 @@
       </c>
       <c r="BC20" s="24" t="inlineStr">
         <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD20" s="24" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
+      <c r="BE20" s="24" t="inlineStr">
+        <is>
+          <t>b9e5139f50e614b7</t>
+        </is>
+      </c>
+      <c r="BF20" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG20" s="24" t="inlineStr">
+        <is>
           <t>mlb-elo-trend-lr-v3</t>
         </is>
       </c>
-      <c r="BD20" s="24" t="inlineStr">
-        <is>
-          <t>21de40f664c548e677d8ffc04521004b3df55963718b1d039537d56f08b84fb1</t>
-        </is>
-      </c>
-      <c r="BE20" s="24" t="inlineStr">
-        <is>
-          <t>b9e5139f50e614b7</t>
-        </is>
-      </c>
-      <c r="BF20" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG20" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v3</t>
-        </is>
-      </c>
       <c r="BH20" s="24" t="inlineStr">
         <is>
           <t>2026-07-18T17:36:40.632965Z</t>
@@ -6663,11 +6694,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ20" s="25" t="n"/>
+      <c r="BJ20" s="38" t="n"/>
       <c r="BK20" s="26" t="n">
         <v>106</v>
       </c>
-      <c r="BL20" s="27" t="n">
+      <c r="BL20" s="39" t="n">
         <v>2.06</v>
       </c>
       <c r="BM20" s="28" t="n">
@@ -6677,18 +6708,18 @@
         <v>0.482587</v>
       </c>
       <c r="BO20" s="28" t="n"/>
-      <c r="BP20" s="25" t="n"/>
-      <c r="BQ20" s="27" t="n"/>
+      <c r="BP20" s="38" t="n"/>
+      <c r="BQ20" s="39" t="n"/>
       <c r="BR20" s="28" t="n"/>
       <c r="BS20" s="28" t="n"/>
       <c r="BT20" s="28" t="n"/>
-      <c r="BU20" s="25" t="n"/>
+      <c r="BU20" s="38" t="n"/>
       <c r="BV20" s="29" t="n"/>
       <c r="BW20" s="24" t="n"/>
-      <c r="BX20" s="30" t="n">
+      <c r="BX20" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY20" s="27" t="n">
+      <c r="BY20" s="39" t="n">
         <v>1.06</v>
       </c>
       <c r="BZ20" s="24" t="inlineStr">
@@ -6748,7 +6779,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J21" s="25" t="n"/>
+      <c r="J21" s="38" t="n"/>
       <c r="K21" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -6757,7 +6788,7 @@
       <c r="L21" s="26" t="n">
         <v>-106</v>
       </c>
-      <c r="M21" s="27" t="n">
+      <c r="M21" s="39" t="n">
         <v>1.943396</v>
       </c>
       <c r="N21" s="28" t="n">
@@ -6772,13 +6803,15 @@
       <c r="Q21" s="28" t="n">
         <v>0.03577</v>
       </c>
-      <c r="R21" s="26" t="n"/>
+      <c r="R21" s="26" t="n">
+        <v>35</v>
+      </c>
       <c r="S21" s="29" t="n">
         <v>1</v>
       </c>
       <c r="T21" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U21" s="24" t="inlineStr">
@@ -6797,11 +6830,11 @@
       <c r="X21" s="26" t="n">
         <v>10</v>
       </c>
-      <c r="Y21" s="25" t="n"/>
+      <c r="Y21" s="38" t="n"/>
       <c r="Z21" s="26" t="n"/>
       <c r="AA21" s="28" t="n"/>
       <c r="AB21" s="28" t="n"/>
-      <c r="AC21" s="30" t="n">
+      <c r="AC21" s="40" t="n">
         <v>0.9434</v>
       </c>
       <c r="AD21" s="24" t="inlineStr">
@@ -6835,10 +6868,22 @@
       <c r="AX21" s="24" t="n"/>
       <c r="AY21" s="24" t="n"/>
       <c r="AZ21" s="24" t="n"/>
-      <c r="BA21" s="24" t="n"/>
+      <c r="BA21" s="24" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
       <c r="BB21" s="24" t="n"/>
-      <c r="BC21" s="24" t="n"/>
-      <c r="BD21" s="24" t="n"/>
+      <c r="BC21" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD21" s="24" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
       <c r="BE21" s="24" t="n"/>
       <c r="BF21" s="24" t="n"/>
       <c r="BG21" s="24" t="n"/>
@@ -6848,11 +6893,11 @@
         </is>
       </c>
       <c r="BI21" s="24" t="n"/>
-      <c r="BJ21" s="25" t="n"/>
+      <c r="BJ21" s="38" t="n"/>
       <c r="BK21" s="26" t="n">
         <v>-106</v>
       </c>
-      <c r="BL21" s="27" t="n">
+      <c r="BL21" s="39" t="n">
         <v>1.943396</v>
       </c>
       <c r="BM21" s="28" t="n">
@@ -6862,16 +6907,16 @@
         <v>0.5124379999999999</v>
       </c>
       <c r="BO21" s="28" t="n"/>
-      <c r="BP21" s="25" t="n"/>
-      <c r="BQ21" s="27" t="n"/>
+      <c r="BP21" s="38" t="n"/>
+      <c r="BQ21" s="39" t="n"/>
       <c r="BR21" s="28" t="n"/>
       <c r="BS21" s="28" t="n"/>
       <c r="BT21" s="28" t="n"/>
-      <c r="BU21" s="25" t="n"/>
+      <c r="BU21" s="38" t="n"/>
       <c r="BV21" s="29" t="n"/>
       <c r="BW21" s="24" t="n"/>
-      <c r="BX21" s="30" t="n"/>
-      <c r="BY21" s="27" t="n"/>
+      <c r="BX21" s="40" t="n"/>
+      <c r="BY21" s="39" t="n"/>
       <c r="BZ21" s="24" t="n"/>
       <c r="CA21" s="31" t="n"/>
     </row>
@@ -6921,7 +6966,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J22" s="25" t="n"/>
+      <c r="J22" s="38" t="n"/>
       <c r="K22" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -6930,7 +6975,7 @@
       <c r="L22" s="26" t="n">
         <v>-106</v>
       </c>
-      <c r="M22" s="27" t="n">
+      <c r="M22" s="39" t="n">
         <v>1.943396</v>
       </c>
       <c r="N22" s="28" t="n">
@@ -6945,13 +6990,15 @@
       <c r="Q22" s="28" t="n">
         <v>0.03577</v>
       </c>
-      <c r="R22" s="26" t="n"/>
+      <c r="R22" s="26" t="n">
+        <v>35</v>
+      </c>
       <c r="S22" s="29" t="n">
         <v>1</v>
       </c>
       <c r="T22" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U22" s="24" t="inlineStr">
@@ -6970,11 +7017,11 @@
       <c r="X22" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="Y22" s="25" t="n"/>
+      <c r="Y22" s="38" t="n"/>
       <c r="Z22" s="26" t="n"/>
       <c r="AA22" s="28" t="n"/>
       <c r="AB22" s="28" t="n"/>
-      <c r="AC22" s="30" t="n">
+      <c r="AC22" s="40" t="n">
         <v>0.9434</v>
       </c>
       <c r="AD22" s="24" t="inlineStr">
@@ -7008,10 +7055,22 @@
       <c r="AX22" s="24" t="n"/>
       <c r="AY22" s="24" t="n"/>
       <c r="AZ22" s="24" t="n"/>
-      <c r="BA22" s="24" t="n"/>
+      <c r="BA22" s="24" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
       <c r="BB22" s="24" t="n"/>
-      <c r="BC22" s="24" t="n"/>
-      <c r="BD22" s="24" t="n"/>
+      <c r="BC22" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD22" s="24" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
       <c r="BE22" s="24" t="n"/>
       <c r="BF22" s="24" t="n"/>
       <c r="BG22" s="24" t="n"/>
@@ -7021,11 +7080,11 @@
         </is>
       </c>
       <c r="BI22" s="24" t="n"/>
-      <c r="BJ22" s="25" t="n"/>
+      <c r="BJ22" s="38" t="n"/>
       <c r="BK22" s="26" t="n">
         <v>-106</v>
       </c>
-      <c r="BL22" s="27" t="n">
+      <c r="BL22" s="39" t="n">
         <v>1.943396</v>
       </c>
       <c r="BM22" s="28" t="n">
@@ -7035,16 +7094,16 @@
         <v>0.5124379999999999</v>
       </c>
       <c r="BO22" s="28" t="n"/>
-      <c r="BP22" s="25" t="n"/>
-      <c r="BQ22" s="27" t="n"/>
+      <c r="BP22" s="38" t="n"/>
+      <c r="BQ22" s="39" t="n"/>
       <c r="BR22" s="28" t="n"/>
       <c r="BS22" s="28" t="n"/>
       <c r="BT22" s="28" t="n"/>
-      <c r="BU22" s="25" t="n"/>
+      <c r="BU22" s="38" t="n"/>
       <c r="BV22" s="29" t="n"/>
       <c r="BW22" s="24" t="n"/>
-      <c r="BX22" s="30" t="n"/>
-      <c r="BY22" s="27" t="n"/>
+      <c r="BX22" s="40" t="n"/>
+      <c r="BY22" s="39" t="n"/>
       <c r="BZ22" s="24" t="n"/>
       <c r="CA22" s="31" t="n"/>
     </row>
@@ -7094,7 +7153,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J23" s="25" t="n"/>
+      <c r="J23" s="38" t="n"/>
       <c r="K23" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -7103,7 +7162,7 @@
       <c r="L23" s="26" t="n">
         <v>-141</v>
       </c>
-      <c r="M23" s="27" t="n">
+      <c r="M23" s="39" t="n">
         <v>1.70922</v>
       </c>
       <c r="N23" s="28" t="n">
@@ -7118,13 +7177,15 @@
       <c r="Q23" s="28" t="n">
         <v>0.031136</v>
       </c>
-      <c r="R23" s="26" t="n"/>
+      <c r="R23" s="26" t="n">
+        <v>31</v>
+      </c>
       <c r="S23" s="29" t="n">
         <v>1.75</v>
       </c>
       <c r="T23" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U23" s="24" t="inlineStr">
@@ -7143,11 +7204,11 @@
       <c r="X23" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y23" s="25" t="n"/>
+      <c r="Y23" s="38" t="n"/>
       <c r="Z23" s="26" t="n"/>
       <c r="AA23" s="28" t="n"/>
       <c r="AB23" s="28" t="n"/>
-      <c r="AC23" s="30" t="n">
+      <c r="AC23" s="40" t="n">
         <v>1.2411</v>
       </c>
       <c r="AD23" s="24" t="inlineStr">
@@ -7181,10 +7242,22 @@
       <c r="AX23" s="24" t="n"/>
       <c r="AY23" s="24" t="n"/>
       <c r="AZ23" s="24" t="n"/>
-      <c r="BA23" s="24" t="n"/>
+      <c r="BA23" s="24" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
       <c r="BB23" s="24" t="n"/>
-      <c r="BC23" s="24" t="n"/>
-      <c r="BD23" s="24" t="n"/>
+      <c r="BC23" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD23" s="24" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
       <c r="BE23" s="24" t="n"/>
       <c r="BF23" s="24" t="n"/>
       <c r="BG23" s="24" t="n"/>
@@ -7194,11 +7267,11 @@
         </is>
       </c>
       <c r="BI23" s="24" t="n"/>
-      <c r="BJ23" s="25" t="n"/>
+      <c r="BJ23" s="38" t="n"/>
       <c r="BK23" s="26" t="n">
         <v>-141</v>
       </c>
-      <c r="BL23" s="27" t="n">
+      <c r="BL23" s="39" t="n">
         <v>1.70922</v>
       </c>
       <c r="BM23" s="28" t="n">
@@ -7208,16 +7281,16 @@
         <v>0.58209</v>
       </c>
       <c r="BO23" s="28" t="n"/>
-      <c r="BP23" s="25" t="n"/>
-      <c r="BQ23" s="27" t="n"/>
+      <c r="BP23" s="38" t="n"/>
+      <c r="BQ23" s="39" t="n"/>
       <c r="BR23" s="28" t="n"/>
       <c r="BS23" s="28" t="n"/>
       <c r="BT23" s="28" t="n"/>
-      <c r="BU23" s="25" t="n"/>
+      <c r="BU23" s="38" t="n"/>
       <c r="BV23" s="29" t="n"/>
       <c r="BW23" s="24" t="n"/>
-      <c r="BX23" s="30" t="n"/>
-      <c r="BY23" s="27" t="n"/>
+      <c r="BX23" s="40" t="n"/>
+      <c r="BY23" s="39" t="n"/>
       <c r="BZ23" s="24" t="n"/>
       <c r="CA23" s="31" t="n"/>
     </row>
@@ -7267,7 +7340,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J24" s="25" t="n"/>
+      <c r="J24" s="38" t="n"/>
       <c r="K24" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -7276,7 +7349,7 @@
       <c r="L24" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="M24" s="27" t="n">
+      <c r="M24" s="39" t="n">
         <v>1.75188</v>
       </c>
       <c r="N24" s="28" t="n">
@@ -7291,13 +7364,15 @@
       <c r="Q24" s="28" t="n">
         <v>0.031895</v>
       </c>
-      <c r="R24" s="26" t="n"/>
+      <c r="R24" s="26" t="n">
+        <v>31</v>
+      </c>
       <c r="S24" s="29" t="n">
         <v>1.5</v>
       </c>
       <c r="T24" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U24" s="24" t="inlineStr">
@@ -7316,11 +7391,11 @@
       <c r="X24" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y24" s="25" t="n"/>
+      <c r="Y24" s="38" t="n"/>
       <c r="Z24" s="26" t="n"/>
       <c r="AA24" s="28" t="n"/>
       <c r="AB24" s="28" t="n"/>
-      <c r="AC24" s="30" t="n">
+      <c r="AC24" s="40" t="n">
         <v>-1.5</v>
       </c>
       <c r="AD24" s="24" t="inlineStr">
@@ -7354,10 +7429,22 @@
       <c r="AX24" s="24" t="n"/>
       <c r="AY24" s="24" t="n"/>
       <c r="AZ24" s="24" t="n"/>
-      <c r="BA24" s="24" t="n"/>
+      <c r="BA24" s="24" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
       <c r="BB24" s="24" t="n"/>
-      <c r="BC24" s="24" t="n"/>
-      <c r="BD24" s="24" t="n"/>
+      <c r="BC24" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD24" s="24" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
       <c r="BE24" s="24" t="n"/>
       <c r="BF24" s="24" t="n"/>
       <c r="BG24" s="24" t="n"/>
@@ -7367,11 +7454,11 @@
         </is>
       </c>
       <c r="BI24" s="24" t="n"/>
-      <c r="BJ24" s="25" t="n"/>
+      <c r="BJ24" s="38" t="n"/>
       <c r="BK24" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="BL24" s="27" t="n">
+      <c r="BL24" s="39" t="n">
         <v>1.75188</v>
       </c>
       <c r="BM24" s="28" t="n">
@@ -7381,16 +7468,16 @@
         <v>0.567164</v>
       </c>
       <c r="BO24" s="28" t="n"/>
-      <c r="BP24" s="25" t="n"/>
-      <c r="BQ24" s="27" t="n"/>
+      <c r="BP24" s="38" t="n"/>
+      <c r="BQ24" s="39" t="n"/>
       <c r="BR24" s="28" t="n"/>
       <c r="BS24" s="28" t="n"/>
       <c r="BT24" s="28" t="n"/>
-      <c r="BU24" s="25" t="n"/>
+      <c r="BU24" s="38" t="n"/>
       <c r="BV24" s="29" t="n"/>
       <c r="BW24" s="24" t="n"/>
-      <c r="BX24" s="30" t="n"/>
-      <c r="BY24" s="27" t="n"/>
+      <c r="BX24" s="40" t="n"/>
+      <c r="BY24" s="39" t="n"/>
       <c r="BZ24" s="24" t="n"/>
       <c r="CA24" s="31" t="n"/>
     </row>
@@ -7440,7 +7527,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J25" s="25" t="n"/>
+      <c r="J25" s="38" t="n"/>
       <c r="K25" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -7449,7 +7536,7 @@
       <c r="L25" s="26" t="n">
         <v>104</v>
       </c>
-      <c r="M25" s="27" t="n">
+      <c r="M25" s="39" t="n">
         <v>2.04</v>
       </c>
       <c r="N25" s="28" t="n">
@@ -7464,13 +7551,15 @@
       <c r="Q25" s="28" t="n">
         <v>0.092666</v>
       </c>
-      <c r="R25" s="26" t="n"/>
+      <c r="R25" s="26" t="n">
+        <v>92</v>
+      </c>
       <c r="S25" s="29" t="n">
         <v>1.25</v>
       </c>
       <c r="T25" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U25" s="24" t="inlineStr">
@@ -7489,11 +7578,11 @@
       <c r="X25" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y25" s="25" t="n"/>
+      <c r="Y25" s="38" t="n"/>
       <c r="Z25" s="26" t="n"/>
       <c r="AA25" s="28" t="n"/>
       <c r="AB25" s="28" t="n"/>
-      <c r="AC25" s="30" t="n">
+      <c r="AC25" s="40" t="n">
         <v>1.3</v>
       </c>
       <c r="AD25" s="24" t="inlineStr">
@@ -7527,10 +7616,22 @@
       <c r="AX25" s="24" t="n"/>
       <c r="AY25" s="24" t="n"/>
       <c r="AZ25" s="24" t="n"/>
-      <c r="BA25" s="24" t="n"/>
+      <c r="BA25" s="24" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
       <c r="BB25" s="24" t="n"/>
-      <c r="BC25" s="24" t="n"/>
-      <c r="BD25" s="24" t="n"/>
+      <c r="BC25" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD25" s="24" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
       <c r="BE25" s="24" t="n"/>
       <c r="BF25" s="24" t="n"/>
       <c r="BG25" s="24" t="n"/>
@@ -7540,11 +7641,11 @@
         </is>
       </c>
       <c r="BI25" s="24" t="n"/>
-      <c r="BJ25" s="25" t="n"/>
+      <c r="BJ25" s="38" t="n"/>
       <c r="BK25" s="26" t="n">
         <v>104</v>
       </c>
-      <c r="BL25" s="27" t="n">
+      <c r="BL25" s="39" t="n">
         <v>2.04</v>
       </c>
       <c r="BM25" s="28" t="n">
@@ -7554,16 +7655,16 @@
         <v>0.487562</v>
       </c>
       <c r="BO25" s="28" t="n"/>
-      <c r="BP25" s="25" t="n"/>
-      <c r="BQ25" s="27" t="n"/>
+      <c r="BP25" s="38" t="n"/>
+      <c r="BQ25" s="39" t="n"/>
       <c r="BR25" s="28" t="n"/>
       <c r="BS25" s="28" t="n"/>
       <c r="BT25" s="28" t="n"/>
-      <c r="BU25" s="25" t="n"/>
+      <c r="BU25" s="38" t="n"/>
       <c r="BV25" s="29" t="n"/>
       <c r="BW25" s="24" t="n"/>
-      <c r="BX25" s="30" t="n"/>
-      <c r="BY25" s="27" t="n"/>
+      <c r="BX25" s="40" t="n"/>
+      <c r="BY25" s="39" t="n"/>
       <c r="BZ25" s="24" t="n"/>
       <c r="CA25" s="31" t="n"/>
     </row>
@@ -7613,7 +7714,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J26" s="25" t="n"/>
+      <c r="J26" s="38" t="n"/>
       <c r="K26" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -7622,7 +7723,7 @@
       <c r="L26" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="M26" s="27" t="n">
+      <c r="M26" s="39" t="n">
         <v>1.961538</v>
       </c>
       <c r="N26" s="28" t="n">
@@ -7637,13 +7738,15 @@
       <c r="Q26" s="28" t="n">
         <v>0.040429</v>
       </c>
-      <c r="R26" s="26" t="n"/>
+      <c r="R26" s="26" t="n">
+        <v>40</v>
+      </c>
       <c r="S26" s="29" t="n">
         <v>1</v>
       </c>
       <c r="T26" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U26" s="24" t="inlineStr">
@@ -7662,11 +7765,11 @@
       <c r="X26" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="Y26" s="25" t="n"/>
+      <c r="Y26" s="38" t="n"/>
       <c r="Z26" s="26" t="n"/>
       <c r="AA26" s="28" t="n"/>
       <c r="AB26" s="28" t="n"/>
-      <c r="AC26" s="30" t="n">
+      <c r="AC26" s="40" t="n">
         <v>0.9615</v>
       </c>
       <c r="AD26" s="24" t="inlineStr">
@@ -7700,10 +7803,22 @@
       <c r="AX26" s="24" t="n"/>
       <c r="AY26" s="24" t="n"/>
       <c r="AZ26" s="24" t="n"/>
-      <c r="BA26" s="24" t="n"/>
+      <c r="BA26" s="24" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
       <c r="BB26" s="24" t="n"/>
-      <c r="BC26" s="24" t="n"/>
-      <c r="BD26" s="24" t="n"/>
+      <c r="BC26" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD26" s="24" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
       <c r="BE26" s="24" t="n"/>
       <c r="BF26" s="24" t="n"/>
       <c r="BG26" s="24" t="n"/>
@@ -7713,11 +7828,11 @@
         </is>
       </c>
       <c r="BI26" s="24" t="n"/>
-      <c r="BJ26" s="25" t="n"/>
+      <c r="BJ26" s="38" t="n"/>
       <c r="BK26" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="BL26" s="27" t="n">
+      <c r="BL26" s="39" t="n">
         <v>1.961538</v>
       </c>
       <c r="BM26" s="28" t="n">
@@ -7727,16 +7842,16 @@
         <v>0.507463</v>
       </c>
       <c r="BO26" s="28" t="n"/>
-      <c r="BP26" s="25" t="n"/>
-      <c r="BQ26" s="27" t="n"/>
+      <c r="BP26" s="38" t="n"/>
+      <c r="BQ26" s="39" t="n"/>
       <c r="BR26" s="28" t="n"/>
       <c r="BS26" s="28" t="n"/>
       <c r="BT26" s="28" t="n"/>
-      <c r="BU26" s="25" t="n"/>
+      <c r="BU26" s="38" t="n"/>
       <c r="BV26" s="29" t="n"/>
       <c r="BW26" s="24" t="n"/>
-      <c r="BX26" s="30" t="n"/>
-      <c r="BY26" s="27" t="n"/>
+      <c r="BX26" s="40" t="n"/>
+      <c r="BY26" s="39" t="n"/>
       <c r="BZ26" s="24" t="n"/>
       <c r="CA26" s="31" t="n"/>
     </row>
@@ -7786,7 +7901,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J27" s="25" t="n"/>
+      <c r="J27" s="38" t="n"/>
       <c r="K27" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -7795,7 +7910,7 @@
       <c r="L27" s="26" t="n">
         <v>120</v>
       </c>
-      <c r="M27" s="27" t="n">
+      <c r="M27" s="39" t="n">
         <v>2.2</v>
       </c>
       <c r="N27" s="28" t="n">
@@ -7810,13 +7925,15 @@
       <c r="Q27" s="28" t="n">
         <v>0.075754</v>
       </c>
-      <c r="R27" s="26" t="n"/>
+      <c r="R27" s="26" t="n">
+        <v>75</v>
+      </c>
       <c r="S27" s="29" t="n">
         <v>0.75</v>
       </c>
       <c r="T27" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U27" s="24" t="inlineStr">
@@ -7835,11 +7952,11 @@
       <c r="X27" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="Y27" s="25" t="n"/>
+      <c r="Y27" s="38" t="n"/>
       <c r="Z27" s="26" t="n"/>
       <c r="AA27" s="28" t="n"/>
       <c r="AB27" s="28" t="n"/>
-      <c r="AC27" s="30" t="n">
+      <c r="AC27" s="40" t="n">
         <v>-0.75</v>
       </c>
       <c r="AD27" s="24" t="inlineStr">
@@ -7873,10 +7990,22 @@
       <c r="AX27" s="24" t="n"/>
       <c r="AY27" s="24" t="n"/>
       <c r="AZ27" s="24" t="n"/>
-      <c r="BA27" s="24" t="n"/>
+      <c r="BA27" s="24" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
       <c r="BB27" s="24" t="n"/>
-      <c r="BC27" s="24" t="n"/>
-      <c r="BD27" s="24" t="n"/>
+      <c r="BC27" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD27" s="24" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
       <c r="BE27" s="24" t="n"/>
       <c r="BF27" s="24" t="n"/>
       <c r="BG27" s="24" t="n"/>
@@ -7886,11 +8015,11 @@
         </is>
       </c>
       <c r="BI27" s="24" t="n"/>
-      <c r="BJ27" s="25" t="n"/>
+      <c r="BJ27" s="38" t="n"/>
       <c r="BK27" s="26" t="n">
         <v>120</v>
       </c>
-      <c r="BL27" s="27" t="n">
+      <c r="BL27" s="39" t="n">
         <v>2.2</v>
       </c>
       <c r="BM27" s="28" t="n">
@@ -7900,16 +8029,16 @@
         <v>0.452736</v>
       </c>
       <c r="BO27" s="28" t="n"/>
-      <c r="BP27" s="25" t="n"/>
-      <c r="BQ27" s="27" t="n"/>
+      <c r="BP27" s="38" t="n"/>
+      <c r="BQ27" s="39" t="n"/>
       <c r="BR27" s="28" t="n"/>
       <c r="BS27" s="28" t="n"/>
       <c r="BT27" s="28" t="n"/>
-      <c r="BU27" s="25" t="n"/>
+      <c r="BU27" s="38" t="n"/>
       <c r="BV27" s="29" t="n"/>
       <c r="BW27" s="24" t="n"/>
-      <c r="BX27" s="30" t="n"/>
-      <c r="BY27" s="27" t="n"/>
+      <c r="BX27" s="40" t="n"/>
+      <c r="BY27" s="39" t="n"/>
       <c r="BZ27" s="24" t="n"/>
       <c r="CA27" s="31" t="n"/>
     </row>
@@ -7959,7 +8088,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J28" s="25" t="n"/>
+      <c r="J28" s="38" t="n"/>
       <c r="K28" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -7968,7 +8097,7 @@
       <c r="L28" s="26" t="n">
         <v>100</v>
       </c>
-      <c r="M28" s="27" t="n">
+      <c r="M28" s="39" t="n">
         <v>2</v>
       </c>
       <c r="N28" s="28" t="n">
@@ -7983,13 +8112,15 @@
       <c r="Q28" s="28" t="n">
         <v>0.025388</v>
       </c>
-      <c r="R28" s="26" t="n"/>
+      <c r="R28" s="26" t="n">
+        <v>25</v>
+      </c>
       <c r="S28" s="29" t="n">
         <v>0.75</v>
       </c>
       <c r="T28" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U28" s="24" t="inlineStr">
@@ -8008,11 +8139,11 @@
       <c r="X28" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="Y28" s="25" t="n"/>
+      <c r="Y28" s="38" t="n"/>
       <c r="Z28" s="26" t="n"/>
       <c r="AA28" s="28" t="n"/>
       <c r="AB28" s="28" t="n"/>
-      <c r="AC28" s="30" t="n">
+      <c r="AC28" s="40" t="n">
         <v>-0.75</v>
       </c>
       <c r="AD28" s="24" t="inlineStr">
@@ -8046,10 +8177,22 @@
       <c r="AX28" s="24" t="n"/>
       <c r="AY28" s="24" t="n"/>
       <c r="AZ28" s="24" t="n"/>
-      <c r="BA28" s="24" t="n"/>
+      <c r="BA28" s="24" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
       <c r="BB28" s="24" t="n"/>
-      <c r="BC28" s="24" t="n"/>
-      <c r="BD28" s="24" t="n"/>
+      <c r="BC28" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD28" s="24" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
       <c r="BE28" s="24" t="n"/>
       <c r="BF28" s="24" t="n"/>
       <c r="BG28" s="24" t="n"/>
@@ -8059,11 +8202,11 @@
         </is>
       </c>
       <c r="BI28" s="24" t="n"/>
-      <c r="BJ28" s="25" t="n"/>
+      <c r="BJ28" s="38" t="n"/>
       <c r="BK28" s="26" t="n">
         <v>100</v>
       </c>
-      <c r="BL28" s="27" t="n">
+      <c r="BL28" s="39" t="n">
         <v>2</v>
       </c>
       <c r="BM28" s="28" t="n">
@@ -8073,16 +8216,16 @@
         <v>0.497512</v>
       </c>
       <c r="BO28" s="28" t="n"/>
-      <c r="BP28" s="25" t="n"/>
-      <c r="BQ28" s="27" t="n"/>
+      <c r="BP28" s="38" t="n"/>
+      <c r="BQ28" s="39" t="n"/>
       <c r="BR28" s="28" t="n"/>
       <c r="BS28" s="28" t="n"/>
       <c r="BT28" s="28" t="n"/>
-      <c r="BU28" s="25" t="n"/>
+      <c r="BU28" s="38" t="n"/>
       <c r="BV28" s="29" t="n"/>
       <c r="BW28" s="24" t="n"/>
-      <c r="BX28" s="30" t="n"/>
-      <c r="BY28" s="27" t="n"/>
+      <c r="BX28" s="40" t="n"/>
+      <c r="BY28" s="39" t="n"/>
       <c r="BZ28" s="24" t="n"/>
       <c r="CA28" s="31" t="n"/>
     </row>
@@ -8132,7 +8275,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J29" s="25" t="n"/>
+      <c r="J29" s="38" t="n"/>
       <c r="K29" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -8141,7 +8284,7 @@
       <c r="L29" s="26" t="n">
         <v>108</v>
       </c>
-      <c r="M29" s="27" t="n">
+      <c r="M29" s="39" t="n">
         <v>2.08</v>
       </c>
       <c r="N29" s="28" t="n">
@@ -8155,14 +8298,14 @@
         <v>0.085969</v>
       </c>
       <c r="R29" s="26" t="n">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="S29" s="29" t="n">
         <v>1.25</v>
       </c>
       <c r="T29" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U29" s="24" t="inlineStr">
@@ -8181,11 +8324,11 @@
       <c r="X29" s="26" t="n">
         <v>8</v>
       </c>
-      <c r="Y29" s="25" t="n"/>
+      <c r="Y29" s="38" t="n"/>
       <c r="Z29" s="26" t="n"/>
       <c r="AA29" s="28" t="n"/>
       <c r="AB29" s="28" t="n"/>
-      <c r="AC29" s="30" t="n">
+      <c r="AC29" s="40" t="n">
         <v>1.35</v>
       </c>
       <c r="AD29" s="24" t="inlineStr">
@@ -8279,7 +8422,7 @@
       </c>
       <c r="BA29" s="24" t="inlineStr">
         <is>
-          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BB29" s="24" t="inlineStr">
@@ -8289,29 +8432,29 @@
       </c>
       <c r="BC29" s="24" t="inlineStr">
         <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD29" s="24" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
+      <c r="BE29" s="24" t="inlineStr">
+        <is>
+          <t>94b28766e76410c6</t>
+        </is>
+      </c>
+      <c r="BF29" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG29" s="24" t="inlineStr">
+        <is>
           <t>mlb-elo-trend-lr-v3</t>
         </is>
       </c>
-      <c r="BD29" s="24" t="inlineStr">
-        <is>
-          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
-        </is>
-      </c>
-      <c r="BE29" s="24" t="inlineStr">
-        <is>
-          <t>94b28766e76410c6</t>
-        </is>
-      </c>
-      <c r="BF29" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG29" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v3</t>
-        </is>
-      </c>
       <c r="BH29" s="24" t="inlineStr">
         <is>
           <t>2026-07-19T13:22:02.614593Z</t>
@@ -8322,11 +8465,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ29" s="25" t="n"/>
+      <c r="BJ29" s="38" t="n"/>
       <c r="BK29" s="26" t="n">
         <v>108</v>
       </c>
-      <c r="BL29" s="27" t="n">
+      <c r="BL29" s="39" t="n">
         <v>2.08</v>
       </c>
       <c r="BM29" s="28" t="n">
@@ -8336,18 +8479,18 @@
         <v>0.477612</v>
       </c>
       <c r="BO29" s="28" t="n"/>
-      <c r="BP29" s="25" t="n"/>
-      <c r="BQ29" s="27" t="n"/>
+      <c r="BP29" s="38" t="n"/>
+      <c r="BQ29" s="39" t="n"/>
       <c r="BR29" s="28" t="n"/>
       <c r="BS29" s="28" t="n"/>
       <c r="BT29" s="28" t="n"/>
-      <c r="BU29" s="25" t="n"/>
+      <c r="BU29" s="38" t="n"/>
       <c r="BV29" s="29" t="n"/>
       <c r="BW29" s="24" t="n"/>
-      <c r="BX29" s="30" t="n">
+      <c r="BX29" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY29" s="27" t="n">
+      <c r="BY29" s="39" t="n">
         <v>1.08</v>
       </c>
       <c r="BZ29" s="24" t="inlineStr">
@@ -8407,7 +8550,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J30" s="25" t="n"/>
+      <c r="J30" s="38" t="n"/>
       <c r="K30" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -8416,7 +8559,7 @@
       <c r="L30" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="M30" s="27" t="n">
+      <c r="M30" s="39" t="n">
         <v>1.75188</v>
       </c>
       <c r="N30" s="28" t="n">
@@ -8430,14 +8573,14 @@
         <v>0.02961</v>
       </c>
       <c r="R30" s="26" t="n">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="S30" s="29" t="n">
         <v>1.5</v>
       </c>
       <c r="T30" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U30" s="24" t="inlineStr">
@@ -8456,11 +8599,11 @@
       <c r="X30" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="Y30" s="25" t="n"/>
+      <c r="Y30" s="38" t="n"/>
       <c r="Z30" s="26" t="n"/>
       <c r="AA30" s="28" t="n"/>
       <c r="AB30" s="28" t="n"/>
-      <c r="AC30" s="30" t="n">
+      <c r="AC30" s="40" t="n">
         <v>1.1278</v>
       </c>
       <c r="AD30" s="24" t="inlineStr">
@@ -8554,7 +8697,7 @@
       </c>
       <c r="BA30" s="24" t="inlineStr">
         <is>
-          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BB30" s="24" t="inlineStr">
@@ -8564,29 +8707,29 @@
       </c>
       <c r="BC30" s="24" t="inlineStr">
         <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD30" s="24" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
+      <c r="BE30" s="24" t="inlineStr">
+        <is>
+          <t>b8bf91edb90bdfcb</t>
+        </is>
+      </c>
+      <c r="BF30" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG30" s="24" t="inlineStr">
+        <is>
           <t>mlb-elo-trend-lr-v3</t>
         </is>
       </c>
-      <c r="BD30" s="24" t="inlineStr">
-        <is>
-          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
-        </is>
-      </c>
-      <c r="BE30" s="24" t="inlineStr">
-        <is>
-          <t>b8bf91edb90bdfcb</t>
-        </is>
-      </c>
-      <c r="BF30" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG30" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v3</t>
-        </is>
-      </c>
       <c r="BH30" s="24" t="inlineStr">
         <is>
           <t>2026-07-19T13:22:13.486376Z</t>
@@ -8597,11 +8740,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ30" s="25" t="n"/>
+      <c r="BJ30" s="38" t="n"/>
       <c r="BK30" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="BL30" s="27" t="n">
+      <c r="BL30" s="39" t="n">
         <v>1.75188</v>
       </c>
       <c r="BM30" s="28" t="n">
@@ -8611,18 +8754,18 @@
         <v>0.567164</v>
       </c>
       <c r="BO30" s="28" t="n"/>
-      <c r="BP30" s="25" t="n"/>
-      <c r="BQ30" s="27" t="n"/>
+      <c r="BP30" s="38" t="n"/>
+      <c r="BQ30" s="39" t="n"/>
       <c r="BR30" s="28" t="n"/>
       <c r="BS30" s="28" t="n"/>
       <c r="BT30" s="28" t="n"/>
-      <c r="BU30" s="25" t="n"/>
+      <c r="BU30" s="38" t="n"/>
       <c r="BV30" s="29" t="n"/>
       <c r="BW30" s="24" t="n"/>
-      <c r="BX30" s="30" t="n">
+      <c r="BX30" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY30" s="27" t="n">
+      <c r="BY30" s="39" t="n">
         <v>0.75188</v>
       </c>
       <c r="BZ30" s="24" t="inlineStr">
@@ -8682,7 +8825,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J31" s="25" t="n"/>
+      <c r="J31" s="38" t="n"/>
       <c r="K31" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -8691,7 +8834,7 @@
       <c r="L31" s="26" t="n">
         <v>130</v>
       </c>
-      <c r="M31" s="27" t="n">
+      <c r="M31" s="39" t="n">
         <v>2.3</v>
       </c>
       <c r="N31" s="28" t="n">
@@ -8712,7 +8855,7 @@
       </c>
       <c r="T31" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U31" s="24" t="inlineStr">
@@ -8731,11 +8874,11 @@
       <c r="X31" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y31" s="25" t="n"/>
+      <c r="Y31" s="38" t="n"/>
       <c r="Z31" s="26" t="n"/>
       <c r="AA31" s="28" t="n"/>
       <c r="AB31" s="28" t="n"/>
-      <c r="AC31" s="30" t="n">
+      <c r="AC31" s="40" t="n">
         <v>-1</v>
       </c>
       <c r="AD31" s="24" t="inlineStr">
@@ -8829,7 +8972,7 @@
       </c>
       <c r="BA31" s="24" t="inlineStr">
         <is>
-          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BB31" s="24" t="inlineStr">
@@ -8839,29 +8982,29 @@
       </c>
       <c r="BC31" s="24" t="inlineStr">
         <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD31" s="24" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
+      <c r="BE31" s="24" t="inlineStr">
+        <is>
+          <t>47154d07c5727d94</t>
+        </is>
+      </c>
+      <c r="BF31" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG31" s="24" t="inlineStr">
+        <is>
           <t>mlb-elo-trend-lr-v3</t>
         </is>
       </c>
-      <c r="BD31" s="24" t="inlineStr">
-        <is>
-          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
-        </is>
-      </c>
-      <c r="BE31" s="24" t="inlineStr">
-        <is>
-          <t>47154d07c5727d94</t>
-        </is>
-      </c>
-      <c r="BF31" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG31" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v3</t>
-        </is>
-      </c>
       <c r="BH31" s="24" t="inlineStr">
         <is>
           <t>2026-07-19T13:22:14.970065Z</t>
@@ -8872,11 +9015,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ31" s="25" t="n"/>
+      <c r="BJ31" s="38" t="n"/>
       <c r="BK31" s="26" t="n">
         <v>130</v>
       </c>
-      <c r="BL31" s="27" t="n">
+      <c r="BL31" s="39" t="n">
         <v>2.3</v>
       </c>
       <c r="BM31" s="28" t="n">
@@ -8886,18 +9029,18 @@
         <v>0.432836</v>
       </c>
       <c r="BO31" s="28" t="n"/>
-      <c r="BP31" s="25" t="n"/>
-      <c r="BQ31" s="27" t="n"/>
+      <c r="BP31" s="38" t="n"/>
+      <c r="BQ31" s="39" t="n"/>
       <c r="BR31" s="28" t="n"/>
       <c r="BS31" s="28" t="n"/>
       <c r="BT31" s="28" t="n"/>
-      <c r="BU31" s="25" t="n"/>
+      <c r="BU31" s="38" t="n"/>
       <c r="BV31" s="29" t="n"/>
       <c r="BW31" s="24" t="n"/>
-      <c r="BX31" s="30" t="n">
+      <c r="BX31" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY31" s="27" t="n">
+      <c r="BY31" s="39" t="n">
         <v>-1</v>
       </c>
       <c r="BZ31" s="24" t="inlineStr">
@@ -8914,22 +9057,22 @@
     <row r="32" ht="36" customHeight="1">
       <c r="A32" s="24" t="inlineStr">
         <is>
-          <t>279e8c5dd40743fe</t>
+          <t>3b298c42597d4a62</t>
         </is>
       </c>
       <c r="B32" s="24" t="inlineStr">
         <is>
-          <t>2026-07-19T17:18:24.670965Z</t>
+          <t>2026-07-20T15:22:23.198190Z</t>
         </is>
       </c>
       <c r="C32" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T19:00:00-0400</t>
+          <t>2026-07-20T18:40:00-0400</t>
         </is>
       </c>
       <c r="D32" s="24" t="inlineStr">
         <is>
-          <t>401816187</t>
+          <t>401816188</t>
         </is>
       </c>
       <c r="E32" s="24" t="inlineStr">
@@ -8939,12 +9082,12 @@
       </c>
       <c r="F32" s="24" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers</t>
+          <t>Minnesota Twins</t>
         </is>
       </c>
       <c r="G32" s="24" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies</t>
+          <t>Cleveland Guardians</t>
         </is>
       </c>
       <c r="H32" s="24" t="inlineStr">
@@ -8954,40 +9097,40 @@
       </c>
       <c r="I32" s="24" t="inlineStr">
         <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J32" s="25" t="n"/>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J32" s="38" t="n"/>
       <c r="K32" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
         </is>
       </c>
       <c r="L32" s="26" t="n">
-        <v>135</v>
-      </c>
-      <c r="M32" s="27" t="n">
-        <v>2.35</v>
+        <v>111</v>
+      </c>
+      <c r="M32" s="39" t="n">
+        <v>2.11</v>
       </c>
       <c r="N32" s="28" t="n">
-        <v>0.425532</v>
+        <v>0.473934</v>
       </c>
       <c r="O32" s="28" t="n">
-        <v>0.535498</v>
+        <v>0.5726869999999999</v>
       </c>
       <c r="P32" s="28" t="n"/>
       <c r="Q32" s="28" t="n">
-        <v>0.109966</v>
+        <v>0.09875299999999999</v>
       </c>
       <c r="R32" s="26" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="S32" s="29" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="T32" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U32" s="24" t="inlineStr">
@@ -8998,15 +9141,15 @@
       <c r="V32" s="24" t="n"/>
       <c r="W32" s="26" t="n"/>
       <c r="X32" s="26" t="n"/>
-      <c r="Y32" s="25" t="n"/>
+      <c r="Y32" s="38" t="n"/>
       <c r="Z32" s="26" t="n"/>
       <c r="AA32" s="28" t="n"/>
       <c r="AB32" s="28" t="n"/>
-      <c r="AC32" s="30" t="n"/>
+      <c r="AC32" s="40" t="n"/>
       <c r="AD32" s="24" t="n"/>
       <c r="AE32" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5150; executable ask 0.4250 (aec-mlb-lad-phi-2026-07-20).</t>
+          <t>Learned LR call at threshold 0.5500; executable ask 0.4750 (aec-mlb-min-cle-2026-07-20).</t>
         </is>
       </c>
       <c r="AF32" s="31" t="inlineStr">
@@ -9047,32 +9190,32 @@
       </c>
       <c r="AP32" s="24" t="inlineStr">
         <is>
-          <t>mlb-lad</t>
+          <t>mlb-min</t>
         </is>
       </c>
       <c r="AQ32" s="24" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers</t>
+          <t>Minnesota Twins</t>
         </is>
       </c>
       <c r="AR32" s="24" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers</t>
+          <t>Minnesota Twins</t>
         </is>
       </c>
       <c r="AS32" s="24" t="inlineStr">
         <is>
-          <t>mlb-phi</t>
+          <t>mlb-cle</t>
         </is>
       </c>
       <c r="AT32" s="24" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies</t>
+          <t>Cleveland Guardians</t>
         </is>
       </c>
       <c r="AU32" s="24" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies</t>
+          <t>Cleveland Guardians</t>
         </is>
       </c>
       <c r="AV32" s="24" t="n"/>
@@ -9090,7 +9233,7 @@
       </c>
       <c r="BA32" s="24" t="inlineStr">
         <is>
-          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BB32" s="24" t="inlineStr">
@@ -9100,17 +9243,17 @@
       </c>
       <c r="BC32" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="BD32" s="24" t="inlineStr">
         <is>
-          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BE32" s="24" t="inlineStr">
         <is>
-          <t>2e2c2111662001b9</t>
+          <t>2170ac399ced5417</t>
         </is>
       </c>
       <c r="BF32" s="24" t="inlineStr">
@@ -9120,12 +9263,12 @@
       </c>
       <c r="BG32" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="BH32" s="24" t="inlineStr">
         <is>
-          <t>2026-07-19T17:17:33.614115Z</t>
+          <t>2026-07-20T14:57:32.219947Z</t>
         </is>
       </c>
       <c r="BI32" s="24" t="inlineStr">
@@ -9133,52 +9276,52 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ32" s="25" t="n"/>
+      <c r="BJ32" s="38" t="n"/>
       <c r="BK32" s="26" t="n">
-        <v>135</v>
-      </c>
-      <c r="BL32" s="27" t="n">
-        <v>2.35</v>
+        <v>111</v>
+      </c>
+      <c r="BL32" s="39" t="n">
+        <v>2.11</v>
       </c>
       <c r="BM32" s="28" t="n">
-        <v>0.425532</v>
+        <v>0.473934</v>
       </c>
       <c r="BN32" s="28" t="n">
-        <v>0.422886</v>
+        <v>0.472637</v>
       </c>
       <c r="BO32" s="28" t="n"/>
-      <c r="BP32" s="25" t="n"/>
-      <c r="BQ32" s="27" t="n"/>
+      <c r="BP32" s="38" t="n"/>
+      <c r="BQ32" s="39" t="n"/>
       <c r="BR32" s="28" t="n"/>
       <c r="BS32" s="28" t="n"/>
       <c r="BT32" s="28" t="n"/>
-      <c r="BU32" s="25" t="n"/>
+      <c r="BU32" s="38" t="n"/>
       <c r="BV32" s="29" t="n"/>
       <c r="BW32" s="24" t="n"/>
-      <c r="BX32" s="30" t="n"/>
-      <c r="BY32" s="27" t="n"/>
+      <c r="BX32" s="40" t="n"/>
+      <c r="BY32" s="39" t="n"/>
       <c r="BZ32" s="24" t="n"/>
       <c r="CA32" s="31" t="n"/>
     </row>
     <row r="33" ht="36" customHeight="1">
       <c r="A33" s="24" t="inlineStr">
         <is>
-          <t>a1f560f16ca8495f</t>
+          <t>81ad16e9351d4806</t>
         </is>
       </c>
       <c r="B33" s="24" t="inlineStr">
         <is>
-          <t>2026-07-19T17:18:24.670965Z</t>
+          <t>2026-07-20T15:22:23.198190Z</t>
         </is>
       </c>
       <c r="C33" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T19:10:00-0400</t>
+          <t>2026-07-20T19:05:00-0400</t>
         </is>
       </c>
       <c r="D33" s="24" t="inlineStr">
         <is>
-          <t>401816186</t>
+          <t>401816189</t>
         </is>
       </c>
       <c r="E33" s="24" t="inlineStr">
@@ -9188,12 +9331,12 @@
       </c>
       <c r="F33" s="24" t="inlineStr">
         <is>
-          <t>Baltimore Orioles</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="G33" s="24" t="inlineStr">
         <is>
-          <t>Boston Red Sox</t>
+          <t>New York Yankees</t>
         </is>
       </c>
       <c r="H33" s="24" t="inlineStr">
@@ -9206,37 +9349,37 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J33" s="25" t="n"/>
+      <c r="J33" s="38" t="n"/>
       <c r="K33" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
         </is>
       </c>
       <c r="L33" s="26" t="n">
-        <v>-117</v>
-      </c>
-      <c r="M33" s="27" t="n">
-        <v>1.854701</v>
+        <v>-108</v>
+      </c>
+      <c r="M33" s="39" t="n">
+        <v>1.925926</v>
       </c>
       <c r="N33" s="28" t="n">
-        <v>0.539171</v>
+        <v>0.519231</v>
       </c>
       <c r="O33" s="28" t="n">
-        <v>0.56697</v>
+        <v>0.578558</v>
       </c>
       <c r="P33" s="28" t="n"/>
       <c r="Q33" s="28" t="n">
-        <v>0.027799</v>
+        <v>0.059327</v>
       </c>
       <c r="R33" s="26" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="S33" s="29" t="n">
         <v>1.25</v>
       </c>
       <c r="T33" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U33" s="24" t="inlineStr">
@@ -9247,15 +9390,15 @@
       <c r="V33" s="24" t="n"/>
       <c r="W33" s="26" t="n"/>
       <c r="X33" s="26" t="n"/>
-      <c r="Y33" s="25" t="n"/>
+      <c r="Y33" s="38" t="n"/>
       <c r="Z33" s="26" t="n"/>
       <c r="AA33" s="28" t="n"/>
       <c r="AB33" s="28" t="n"/>
-      <c r="AC33" s="30" t="n"/>
+      <c r="AC33" s="40" t="n"/>
       <c r="AD33" s="24" t="n"/>
       <c r="AE33" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5150; executable ask 0.5400 (aec-mlb-bal-bos-2026-07-20).</t>
+          <t>Learned LR call at threshold 0.5500; executable ask 0.5200 (aec-mlb-pit-nyy-2026-07-20).</t>
         </is>
       </c>
       <c r="AF33" s="31" t="inlineStr">
@@ -9296,32 +9439,32 @@
       </c>
       <c r="AP33" s="24" t="inlineStr">
         <is>
-          <t>mlb-bal</t>
+          <t>mlb-pit</t>
         </is>
       </c>
       <c r="AQ33" s="24" t="inlineStr">
         <is>
-          <t>Baltimore Orioles</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="AR33" s="24" t="inlineStr">
         <is>
-          <t>Baltimore Orioles</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="AS33" s="24" t="inlineStr">
         <is>
-          <t>mlb-bos</t>
+          <t>mlb-nyy</t>
         </is>
       </c>
       <c r="AT33" s="24" t="inlineStr">
         <is>
-          <t>Boston Red Sox</t>
+          <t>New York Yankees</t>
         </is>
       </c>
       <c r="AU33" s="24" t="inlineStr">
         <is>
-          <t>Boston Red Sox</t>
+          <t>New York Yankees</t>
         </is>
       </c>
       <c r="AV33" s="24" t="n"/>
@@ -9339,7 +9482,7 @@
       </c>
       <c r="BA33" s="24" t="inlineStr">
         <is>
-          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BB33" s="24" t="inlineStr">
@@ -9349,17 +9492,17 @@
       </c>
       <c r="BC33" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="BD33" s="24" t="inlineStr">
         <is>
-          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BE33" s="24" t="inlineStr">
         <is>
-          <t>a6a83b5ac90d7962</t>
+          <t>38ab7db5a3798f0c</t>
         </is>
       </c>
       <c r="BF33" s="24" t="inlineStr">
@@ -9369,12 +9512,12 @@
       </c>
       <c r="BG33" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="BH33" s="24" t="inlineStr">
         <is>
-          <t>2026-07-19T17:17:31.410943Z</t>
+          <t>2026-07-20T14:57:35.056972Z</t>
         </is>
       </c>
       <c r="BI33" s="24" t="inlineStr">
@@ -9382,52 +9525,52 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ33" s="25" t="n"/>
+      <c r="BJ33" s="38" t="n"/>
       <c r="BK33" s="26" t="n">
-        <v>-117</v>
-      </c>
-      <c r="BL33" s="27" t="n">
-        <v>1.854701</v>
+        <v>-108</v>
+      </c>
+      <c r="BL33" s="39" t="n">
+        <v>1.925926</v>
       </c>
       <c r="BM33" s="28" t="n">
-        <v>0.539171</v>
+        <v>0.519231</v>
       </c>
       <c r="BN33" s="28" t="n">
-        <v>0.537313</v>
+        <v>0.517413</v>
       </c>
       <c r="BO33" s="28" t="n"/>
-      <c r="BP33" s="25" t="n"/>
-      <c r="BQ33" s="27" t="n"/>
+      <c r="BP33" s="38" t="n"/>
+      <c r="BQ33" s="39" t="n"/>
       <c r="BR33" s="28" t="n"/>
       <c r="BS33" s="28" t="n"/>
       <c r="BT33" s="28" t="n"/>
-      <c r="BU33" s="25" t="n"/>
+      <c r="BU33" s="38" t="n"/>
       <c r="BV33" s="29" t="n"/>
       <c r="BW33" s="24" t="n"/>
-      <c r="BX33" s="30" t="n"/>
-      <c r="BY33" s="27" t="n"/>
+      <c r="BX33" s="40" t="n"/>
+      <c r="BY33" s="39" t="n"/>
       <c r="BZ33" s="24" t="n"/>
       <c r="CA33" s="31" t="n"/>
     </row>
     <row r="34" ht="36" customHeight="1">
       <c r="A34" s="24" t="inlineStr">
         <is>
-          <t>369b925b172f4b6a</t>
+          <t>d928b5795af74522</t>
         </is>
       </c>
       <c r="B34" s="24" t="inlineStr">
         <is>
-          <t>2026-07-19T17:18:24.670965Z</t>
+          <t>2026-07-20T15:22:23.198190Z</t>
         </is>
       </c>
       <c r="C34" s="24" t="inlineStr">
         <is>
-          <t>2026-07-21T01:40Z</t>
+          <t>2026-07-20T20:05:00-0400</t>
         </is>
       </c>
       <c r="D34" s="24" t="inlineStr">
         <is>
-          <t>401816199</t>
+          <t>401816193</t>
         </is>
       </c>
       <c r="E34" s="24" t="inlineStr">
@@ -9437,12 +9580,12 @@
       </c>
       <c r="F34" s="24" t="inlineStr">
         <is>
-          <t>Cincinnati Reds</t>
+          <t>Detroit Tigers</t>
         </is>
       </c>
       <c r="G34" s="24" t="inlineStr">
         <is>
-          <t>Seattle Mariners</t>
+          <t>Chicago Cubs</t>
         </is>
       </c>
       <c r="H34" s="24" t="inlineStr">
@@ -9455,37 +9598,37 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J34" s="25" t="n"/>
+      <c r="J34" s="38" t="n"/>
       <c r="K34" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
         </is>
       </c>
       <c r="L34" s="26" t="n">
-        <v>-125</v>
-      </c>
-      <c r="M34" s="27" t="n">
-        <v>1.8</v>
+        <v>-108</v>
+      </c>
+      <c r="M34" s="39" t="n">
+        <v>1.925926</v>
       </c>
       <c r="N34" s="28" t="n">
-        <v>0.555556</v>
+        <v>0.519231</v>
       </c>
       <c r="O34" s="28" t="n">
-        <v>0.597509</v>
+        <v>0.566967</v>
       </c>
       <c r="P34" s="28" t="n"/>
       <c r="Q34" s="28" t="n">
-        <v>0.041953</v>
+        <v>0.047736</v>
       </c>
       <c r="R34" s="26" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="S34" s="29" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="T34" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="U34" s="24" t="inlineStr">
@@ -9496,15 +9639,15 @@
       <c r="V34" s="24" t="n"/>
       <c r="W34" s="26" t="n"/>
       <c r="X34" s="26" t="n"/>
-      <c r="Y34" s="25" t="n"/>
+      <c r="Y34" s="38" t="n"/>
       <c r="Z34" s="26" t="n"/>
       <c r="AA34" s="28" t="n"/>
       <c r="AB34" s="28" t="n"/>
-      <c r="AC34" s="30" t="n"/>
+      <c r="AC34" s="40" t="n"/>
       <c r="AD34" s="24" t="n"/>
       <c r="AE34" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5150; executable ask 0.5550 (aec-mlb-cin-sea-2026-07-20).</t>
+          <t>Learned LR call at threshold 0.5500; executable ask 0.5200 (aec-mlb-det-chc-2026-07-20).</t>
         </is>
       </c>
       <c r="AF34" s="31" t="inlineStr">
@@ -9545,32 +9688,32 @@
       </c>
       <c r="AP34" s="24" t="inlineStr">
         <is>
-          <t>mlb-cin</t>
+          <t>mlb-det</t>
         </is>
       </c>
       <c r="AQ34" s="24" t="inlineStr">
         <is>
-          <t>Cincinnati Reds</t>
+          <t>Detroit Tigers</t>
         </is>
       </c>
       <c r="AR34" s="24" t="inlineStr">
         <is>
-          <t>Cincinnati Reds</t>
+          <t>Detroit Tigers</t>
         </is>
       </c>
       <c r="AS34" s="24" t="inlineStr">
         <is>
-          <t>mlb-sea</t>
+          <t>mlb-chc</t>
         </is>
       </c>
       <c r="AT34" s="24" t="inlineStr">
         <is>
-          <t>Seattle Mariners</t>
+          <t>Chicago Cubs</t>
         </is>
       </c>
       <c r="AU34" s="24" t="inlineStr">
         <is>
-          <t>Seattle Mariners</t>
+          <t>Chicago Cubs</t>
         </is>
       </c>
       <c r="AV34" s="24" t="n"/>
@@ -9588,7 +9731,7 @@
       </c>
       <c r="BA34" s="24" t="inlineStr">
         <is>
-          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BB34" s="24" t="inlineStr">
@@ -9598,17 +9741,17 @@
       </c>
       <c r="BC34" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="BD34" s="24" t="inlineStr">
         <is>
-          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
         </is>
       </c>
       <c r="BE34" s="24" t="inlineStr">
         <is>
-          <t>982d73638d70c45b</t>
+          <t>b84afb2c70e14d93</t>
         </is>
       </c>
       <c r="BF34" s="24" t="inlineStr">
@@ -9618,12 +9761,12 @@
       </c>
       <c r="BG34" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>mlb-elo-trend-lr-v4</t>
         </is>
       </c>
       <c r="BH34" s="24" t="inlineStr">
         <is>
-          <t>2026-07-19T17:17:46.849555Z</t>
+          <t>2026-07-20T14:57:46.871986Z</t>
         </is>
       </c>
       <c r="BI34" s="24" t="inlineStr">
@@ -9631,67 +9774,67 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ34" s="25" t="n"/>
+      <c r="BJ34" s="38" t="n"/>
       <c r="BK34" s="26" t="n">
-        <v>-125</v>
-      </c>
-      <c r="BL34" s="27" t="n">
-        <v>1.8</v>
+        <v>-108</v>
+      </c>
+      <c r="BL34" s="39" t="n">
+        <v>1.925926</v>
       </c>
       <c r="BM34" s="28" t="n">
-        <v>0.555556</v>
+        <v>0.519231</v>
       </c>
       <c r="BN34" s="28" t="n">
-        <v>0.552239</v>
+        <v>0.517413</v>
       </c>
       <c r="BO34" s="28" t="n"/>
-      <c r="BP34" s="25" t="n"/>
-      <c r="BQ34" s="27" t="n"/>
+      <c r="BP34" s="38" t="n"/>
+      <c r="BQ34" s="39" t="n"/>
       <c r="BR34" s="28" t="n"/>
       <c r="BS34" s="28" t="n"/>
       <c r="BT34" s="28" t="n"/>
-      <c r="BU34" s="25" t="n"/>
+      <c r="BU34" s="38" t="n"/>
       <c r="BV34" s="29" t="n"/>
       <c r="BW34" s="24" t="n"/>
-      <c r="BX34" s="30" t="n"/>
-      <c r="BY34" s="27" t="n"/>
+      <c r="BX34" s="40" t="n"/>
+      <c r="BY34" s="39" t="n"/>
       <c r="BZ34" s="24" t="n"/>
       <c r="CA34" s="31" t="n"/>
     </row>
     <row r="35" ht="36" customHeight="1">
       <c r="A35" s="24" t="inlineStr">
         <is>
-          <t>c7a1577522fb4d37</t>
+          <t>1b170fab0ebb46ee</t>
         </is>
       </c>
       <c r="B35" s="24" t="inlineStr">
         <is>
-          <t>2026-07-19T17:18:24.670965Z</t>
+          <t>2026-07-20T15:28:43.848060Z</t>
         </is>
       </c>
       <c r="C35" s="24" t="inlineStr">
         <is>
-          <t>2026-07-21T02:00Z</t>
+          <t>2026-07-20T20:00:00-0400</t>
         </is>
       </c>
       <c r="D35" s="24" t="inlineStr">
         <is>
-          <t>401816200</t>
+          <t>401892393</t>
         </is>
       </c>
       <c r="E35" s="24" t="inlineStr">
         <is>
-          <t>MLB</t>
+          <t>WNBA</t>
         </is>
       </c>
       <c r="F35" s="24" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals</t>
+          <t>New York Liberty</t>
         </is>
       </c>
       <c r="G35" s="24" t="inlineStr">
         <is>
-          <t>Los Angeles Angels</t>
+          <t>Dallas Wings</t>
         </is>
       </c>
       <c r="H35" s="24" t="inlineStr">
@@ -9701,40 +9844,40 @@
       </c>
       <c r="I35" s="24" t="inlineStr">
         <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J35" s="25" t="n"/>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J35" s="38" t="n"/>
       <c r="K35" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
         </is>
       </c>
       <c r="L35" s="26" t="n">
-        <v>-102</v>
-      </c>
-      <c r="M35" s="27" t="n">
-        <v>1.980392</v>
+        <v>156</v>
+      </c>
+      <c r="M35" s="39" t="n">
+        <v>2.56</v>
       </c>
       <c r="N35" s="28" t="n">
-        <v>0.50495</v>
+        <v>0.390625</v>
       </c>
       <c r="O35" s="28" t="n">
-        <v>0.541942</v>
+        <v>0.688998</v>
       </c>
       <c r="P35" s="28" t="n"/>
       <c r="Q35" s="28" t="n">
-        <v>0.036992</v>
+        <v>0.298373</v>
       </c>
       <c r="R35" s="26" t="n">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="S35" s="29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T35" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>wnba-elo-trend-lr-v3</t>
         </is>
       </c>
       <c r="U35" s="24" t="inlineStr">
@@ -9745,15 +9888,15 @@
       <c r="V35" s="24" t="n"/>
       <c r="W35" s="26" t="n"/>
       <c r="X35" s="26" t="n"/>
-      <c r="Y35" s="25" t="n"/>
+      <c r="Y35" s="38" t="n"/>
       <c r="Z35" s="26" t="n"/>
       <c r="AA35" s="28" t="n"/>
       <c r="AB35" s="28" t="n"/>
-      <c r="AC35" s="30" t="n"/>
+      <c r="AC35" s="40" t="n"/>
       <c r="AD35" s="24" t="n"/>
       <c r="AE35" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5150; executable ask 0.5050 (aec-mlb-stl-laa-2026-07-20).</t>
+          <t>Learned LR call at threshold 0.5051; executable ask 0.3900 (aec-wnba-ny-dal-2026-07-20).</t>
         </is>
       </c>
       <c r="AF35" s="31" t="inlineStr">
@@ -9789,37 +9932,37 @@
       </c>
       <c r="AO35" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>NO_CALL_LARGE_DISAGREEMENT_REVIEW</t>
         </is>
       </c>
       <c r="AP35" s="24" t="inlineStr">
         <is>
-          <t>mlb-stl</t>
+          <t>wnba-nyl</t>
         </is>
       </c>
       <c r="AQ35" s="24" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals</t>
+          <t>New York Liberty</t>
         </is>
       </c>
       <c r="AR35" s="24" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals</t>
+          <t>New York Liberty</t>
         </is>
       </c>
       <c r="AS35" s="24" t="inlineStr">
         <is>
-          <t>mlb-laa</t>
+          <t>wnba-dal</t>
         </is>
       </c>
       <c r="AT35" s="24" t="inlineStr">
         <is>
-          <t>Los Angeles Angels</t>
+          <t>Dallas Wings</t>
         </is>
       </c>
       <c r="AU35" s="24" t="inlineStr">
         <is>
-          <t>Los Angeles Angels</t>
+          <t>Dallas Wings</t>
         </is>
       </c>
       <c r="AV35" s="24" t="n"/>
@@ -9837,7 +9980,7 @@
       </c>
       <c r="BA35" s="24" t="inlineStr">
         <is>
-          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+          <t>43ee2f84f025c10f83f80a8c22d49c35c420734a8a730b5f272287225cceee4b</t>
         </is>
       </c>
       <c r="BB35" s="24" t="inlineStr">
@@ -9847,17 +9990,17 @@
       </c>
       <c r="BC35" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>wnba-elo-trend-lr-v3</t>
         </is>
       </c>
       <c r="BD35" s="24" t="inlineStr">
         <is>
-          <t>ebdb392c90fd9a9414a97c1b39024e1a4f2c894aee118b3b4598ecd7e5e96695</t>
+          <t>43ee2f84f025c10f83f80a8c22d49c35c420734a8a730b5f272287225cceee4b</t>
         </is>
       </c>
       <c r="BE35" s="24" t="inlineStr">
         <is>
-          <t>83613a19346b831e</t>
+          <t>c20bbb99f1fff741</t>
         </is>
       </c>
       <c r="BF35" s="24" t="inlineStr">
@@ -9867,12 +10010,12 @@
       </c>
       <c r="BG35" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v3</t>
+          <t>wnba-elo-trend-lr-v3</t>
         </is>
       </c>
       <c r="BH35" s="24" t="inlineStr">
         <is>
-          <t>2026-07-19T17:17:47.727344Z</t>
+          <t>2026-07-20T14:57:58.731031Z</t>
         </is>
       </c>
       <c r="BI35" s="24" t="inlineStr">
@@ -9880,1028 +10023,32 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ35" s="25" t="n"/>
+      <c r="BJ35" s="38" t="n"/>
       <c r="BK35" s="26" t="n">
-        <v>-102</v>
-      </c>
-      <c r="BL35" s="27" t="n">
-        <v>1.980392</v>
+        <v>156</v>
+      </c>
+      <c r="BL35" s="39" t="n">
+        <v>2.56</v>
       </c>
       <c r="BM35" s="28" t="n">
-        <v>0.50495</v>
+        <v>0.390625</v>
       </c>
       <c r="BN35" s="28" t="n">
-        <v>0.502488</v>
+        <v>0.386139</v>
       </c>
       <c r="BO35" s="28" t="n"/>
-      <c r="BP35" s="25" t="n"/>
-      <c r="BQ35" s="27" t="n"/>
+      <c r="BP35" s="38" t="n"/>
+      <c r="BQ35" s="39" t="n"/>
       <c r="BR35" s="28" t="n"/>
       <c r="BS35" s="28" t="n"/>
       <c r="BT35" s="28" t="n"/>
-      <c r="BU35" s="25" t="n"/>
+      <c r="BU35" s="38" t="n"/>
       <c r="BV35" s="29" t="n"/>
       <c r="BW35" s="24" t="n"/>
-      <c r="BX35" s="30" t="n"/>
-      <c r="BY35" s="27" t="n"/>
+      <c r="BX35" s="40" t="n"/>
+      <c r="BY35" s="39" t="n"/>
       <c r="BZ35" s="24" t="n"/>
       <c r="CA35" s="31" t="n"/>
-    </row>
-    <row r="36" ht="36" customHeight="1">
-      <c r="A36" s="24" t="inlineStr">
-        <is>
-          <t>5ddbae8d805944cb</t>
-        </is>
-      </c>
-      <c r="B36" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-19T17:18:29.371620Z</t>
-        </is>
-      </c>
-      <c r="C36" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-21T00:00Z</t>
-        </is>
-      </c>
-      <c r="D36" s="24" t="inlineStr">
-        <is>
-          <t>401892393</t>
-        </is>
-      </c>
-      <c r="E36" s="24" t="inlineStr">
-        <is>
-          <t>WNBA</t>
-        </is>
-      </c>
-      <c r="F36" s="24" t="inlineStr">
-        <is>
-          <t>New York Liberty</t>
-        </is>
-      </c>
-      <c r="G36" s="24" t="inlineStr">
-        <is>
-          <t>Dallas Wings</t>
-        </is>
-      </c>
-      <c r="H36" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I36" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J36" s="25" t="n"/>
-      <c r="K36" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L36" s="26" t="n">
-        <v>108</v>
-      </c>
-      <c r="M36" s="27" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="N36" s="28" t="n">
-        <v>0.480769</v>
-      </c>
-      <c r="O36" s="28" t="n">
-        <v>0.6787840000000001</v>
-      </c>
-      <c r="P36" s="28" t="n"/>
-      <c r="Q36" s="28" t="n">
-        <v>0.198015</v>
-      </c>
-      <c r="R36" s="26" t="n">
-        <v>100</v>
-      </c>
-      <c r="S36" s="29" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="T36" s="24" t="inlineStr">
-        <is>
-          <t>wnba-elo-trend-lr-v3</t>
-        </is>
-      </c>
-      <c r="U36" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V36" s="24" t="n"/>
-      <c r="W36" s="26" t="n"/>
-      <c r="X36" s="26" t="n"/>
-      <c r="Y36" s="25" t="n"/>
-      <c r="Z36" s="26" t="n"/>
-      <c r="AA36" s="28" t="n"/>
-      <c r="AB36" s="28" t="n"/>
-      <c r="AC36" s="30" t="n"/>
-      <c r="AD36" s="24" t="n"/>
-      <c r="AE36" s="31" t="inlineStr">
-        <is>
-          <t>Learned LR call at threshold 0.5000; executable ask 0.4800 (aec-wnba-ny-dal-2026-07-20).</t>
-        </is>
-      </c>
-      <c r="AF36" s="31" t="inlineStr">
-        <is>
-          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
-        </is>
-      </c>
-      <c r="AG36" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH36" s="24" t="n"/>
-      <c r="AI36" s="31" t="n"/>
-      <c r="AJ36" s="31" t="n"/>
-      <c r="AK36" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL36" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM36" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN36" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO36" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LARGE_DISAGREEMENT_REVIEW</t>
-        </is>
-      </c>
-      <c r="AP36" s="24" t="inlineStr">
-        <is>
-          <t>wnba-nyl</t>
-        </is>
-      </c>
-      <c r="AQ36" s="24" t="inlineStr">
-        <is>
-          <t>New York Liberty</t>
-        </is>
-      </c>
-      <c r="AR36" s="24" t="inlineStr">
-        <is>
-          <t>New York Liberty</t>
-        </is>
-      </c>
-      <c r="AS36" s="24" t="inlineStr">
-        <is>
-          <t>wnba-dal</t>
-        </is>
-      </c>
-      <c r="AT36" s="24" t="inlineStr">
-        <is>
-          <t>Dallas Wings</t>
-        </is>
-      </c>
-      <c r="AU36" s="24" t="inlineStr">
-        <is>
-          <t>Dallas Wings</t>
-        </is>
-      </c>
-      <c r="AV36" s="24" t="n"/>
-      <c r="AW36" s="24" t="n"/>
-      <c r="AX36" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY36" s="24" t="n"/>
-      <c r="AZ36" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA36" s="24" t="inlineStr">
-        <is>
-          <t>d339198b196cb3fcd02950ed5efbdd4cefbeb95b2cd63cd756e77f99dc483719</t>
-        </is>
-      </c>
-      <c r="BB36" s="24" t="inlineStr">
-        <is>
-          <t>learned_lr</t>
-        </is>
-      </c>
-      <c r="BC36" s="24" t="inlineStr">
-        <is>
-          <t>wnba-elo-trend-lr-v3</t>
-        </is>
-      </c>
-      <c r="BD36" s="24" t="inlineStr">
-        <is>
-          <t>d339198b196cb3fcd02950ed5efbdd4cefbeb95b2cd63cd756e77f99dc483719</t>
-        </is>
-      </c>
-      <c r="BE36" s="24" t="inlineStr">
-        <is>
-          <t>1c6f45e72b2d1f80</t>
-        </is>
-      </c>
-      <c r="BF36" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG36" s="24" t="inlineStr">
-        <is>
-          <t>wnba-elo-trend-lr-v3</t>
-        </is>
-      </c>
-      <c r="BH36" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-19T17:17:49.472621Z</t>
-        </is>
-      </c>
-      <c r="BI36" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ36" s="25" t="n"/>
-      <c r="BK36" s="26" t="n">
-        <v>108</v>
-      </c>
-      <c r="BL36" s="27" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="BM36" s="28" t="n">
-        <v>0.480769</v>
-      </c>
-      <c r="BN36" s="28" t="n">
-        <v>0.475248</v>
-      </c>
-      <c r="BO36" s="28" t="n"/>
-      <c r="BP36" s="25" t="n"/>
-      <c r="BQ36" s="27" t="n"/>
-      <c r="BR36" s="28" t="n"/>
-      <c r="BS36" s="28" t="n"/>
-      <c r="BT36" s="28" t="n"/>
-      <c r="BU36" s="25" t="n"/>
-      <c r="BV36" s="29" t="n"/>
-      <c r="BW36" s="24" t="n"/>
-      <c r="BX36" s="30" t="n"/>
-      <c r="BY36" s="27" t="n"/>
-      <c r="BZ36" s="24" t="n"/>
-      <c r="CA36" s="31" t="n"/>
-    </row>
-    <row r="37" ht="36" customHeight="1">
-      <c r="A37" s="24" t="inlineStr">
-        <is>
-          <t>ea9a359adce843bc</t>
-        </is>
-      </c>
-      <c r="B37" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-20T14:58:17.970946Z</t>
-        </is>
-      </c>
-      <c r="C37" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-20T18:40:00-0400</t>
-        </is>
-      </c>
-      <c r="D37" s="24" t="inlineStr">
-        <is>
-          <t>401816188</t>
-        </is>
-      </c>
-      <c r="E37" s="24" t="inlineStr">
-        <is>
-          <t>MLB</t>
-        </is>
-      </c>
-      <c r="F37" s="24" t="inlineStr">
-        <is>
-          <t>Minnesota Twins</t>
-        </is>
-      </c>
-      <c r="G37" s="24" t="inlineStr">
-        <is>
-          <t>Cleveland Guardians</t>
-        </is>
-      </c>
-      <c r="H37" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I37" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J37" s="25" t="n"/>
-      <c r="K37" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L37" s="26" t="n">
-        <v>111</v>
-      </c>
-      <c r="M37" s="27" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="N37" s="28" t="n">
-        <v>0.473934</v>
-      </c>
-      <c r="O37" s="28" t="n">
-        <v>0.5726869999999999</v>
-      </c>
-      <c r="P37" s="28" t="n"/>
-      <c r="Q37" s="28" t="n">
-        <v>0.09875299999999999</v>
-      </c>
-      <c r="R37" s="26" t="n">
-        <v>99</v>
-      </c>
-      <c r="S37" s="29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T37" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v4</t>
-        </is>
-      </c>
-      <c r="U37" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V37" s="24" t="n"/>
-      <c r="W37" s="26" t="n"/>
-      <c r="X37" s="26" t="n"/>
-      <c r="Y37" s="25" t="n"/>
-      <c r="Z37" s="26" t="n"/>
-      <c r="AA37" s="28" t="n"/>
-      <c r="AB37" s="28" t="n"/>
-      <c r="AC37" s="30" t="n"/>
-      <c r="AD37" s="24" t="n"/>
-      <c r="AE37" s="31" t="inlineStr">
-        <is>
-          <t>Learned LR call at threshold 0.5500; executable ask 0.4750 (aec-mlb-min-cle-2026-07-20).</t>
-        </is>
-      </c>
-      <c r="AF37" s="31" t="inlineStr">
-        <is>
-          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
-        </is>
-      </c>
-      <c r="AG37" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH37" s="24" t="n"/>
-      <c r="AI37" s="31" t="n"/>
-      <c r="AJ37" s="31" t="n"/>
-      <c r="AK37" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL37" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM37" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN37" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO37" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LARGE_DISAGREEMENT_REVIEW</t>
-        </is>
-      </c>
-      <c r="AP37" s="24" t="inlineStr">
-        <is>
-          <t>mlb-min</t>
-        </is>
-      </c>
-      <c r="AQ37" s="24" t="inlineStr">
-        <is>
-          <t>Minnesota Twins</t>
-        </is>
-      </c>
-      <c r="AR37" s="24" t="inlineStr">
-        <is>
-          <t>Minnesota Twins</t>
-        </is>
-      </c>
-      <c r="AS37" s="24" t="inlineStr">
-        <is>
-          <t>mlb-cle</t>
-        </is>
-      </c>
-      <c r="AT37" s="24" t="inlineStr">
-        <is>
-          <t>Cleveland Guardians</t>
-        </is>
-      </c>
-      <c r="AU37" s="24" t="inlineStr">
-        <is>
-          <t>Cleveland Guardians</t>
-        </is>
-      </c>
-      <c r="AV37" s="24" t="n"/>
-      <c r="AW37" s="24" t="n"/>
-      <c r="AX37" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY37" s="24" t="n"/>
-      <c r="AZ37" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA37" s="24" t="inlineStr">
-        <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
-        </is>
-      </c>
-      <c r="BB37" s="24" t="inlineStr">
-        <is>
-          <t>learned_lr</t>
-        </is>
-      </c>
-      <c r="BC37" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v4</t>
-        </is>
-      </c>
-      <c r="BD37" s="24" t="inlineStr">
-        <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
-        </is>
-      </c>
-      <c r="BE37" s="24" t="inlineStr">
-        <is>
-          <t>2170ac399ced5417</t>
-        </is>
-      </c>
-      <c r="BF37" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG37" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v4</t>
-        </is>
-      </c>
-      <c r="BH37" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-20T14:57:32.219947Z</t>
-        </is>
-      </c>
-      <c r="BI37" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ37" s="25" t="n"/>
-      <c r="BK37" s="26" t="n">
-        <v>111</v>
-      </c>
-      <c r="BL37" s="27" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="BM37" s="28" t="n">
-        <v>0.473934</v>
-      </c>
-      <c r="BN37" s="28" t="n">
-        <v>0.472637</v>
-      </c>
-      <c r="BO37" s="28" t="n"/>
-      <c r="BP37" s="25" t="n"/>
-      <c r="BQ37" s="27" t="n"/>
-      <c r="BR37" s="28" t="n"/>
-      <c r="BS37" s="28" t="n"/>
-      <c r="BT37" s="28" t="n"/>
-      <c r="BU37" s="25" t="n"/>
-      <c r="BV37" s="29" t="n"/>
-      <c r="BW37" s="24" t="n"/>
-      <c r="BX37" s="30" t="n"/>
-      <c r="BY37" s="27" t="n"/>
-      <c r="BZ37" s="24" t="n"/>
-      <c r="CA37" s="31" t="n"/>
-    </row>
-    <row r="38" ht="36" customHeight="1">
-      <c r="A38" s="24" t="inlineStr">
-        <is>
-          <t>9a7ddbfc3b7343bd</t>
-        </is>
-      </c>
-      <c r="B38" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-20T14:58:17.970946Z</t>
-        </is>
-      </c>
-      <c r="C38" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-20T19:05:00-0400</t>
-        </is>
-      </c>
-      <c r="D38" s="24" t="inlineStr">
-        <is>
-          <t>401816189</t>
-        </is>
-      </c>
-      <c r="E38" s="24" t="inlineStr">
-        <is>
-          <t>MLB</t>
-        </is>
-      </c>
-      <c r="F38" s="24" t="inlineStr">
-        <is>
-          <t>Pittsburgh Pirates</t>
-        </is>
-      </c>
-      <c r="G38" s="24" t="inlineStr">
-        <is>
-          <t>New York Yankees</t>
-        </is>
-      </c>
-      <c r="H38" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I38" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J38" s="25" t="n"/>
-      <c r="K38" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L38" s="26" t="n">
-        <v>-108</v>
-      </c>
-      <c r="M38" s="27" t="n">
-        <v>1.925926</v>
-      </c>
-      <c r="N38" s="28" t="n">
-        <v>0.519231</v>
-      </c>
-      <c r="O38" s="28" t="n">
-        <v>0.578558</v>
-      </c>
-      <c r="P38" s="28" t="n"/>
-      <c r="Q38" s="28" t="n">
-        <v>0.059327</v>
-      </c>
-      <c r="R38" s="26" t="n">
-        <v>50</v>
-      </c>
-      <c r="S38" s="29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T38" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v4</t>
-        </is>
-      </c>
-      <c r="U38" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V38" s="24" t="n"/>
-      <c r="W38" s="26" t="n"/>
-      <c r="X38" s="26" t="n"/>
-      <c r="Y38" s="25" t="n"/>
-      <c r="Z38" s="26" t="n"/>
-      <c r="AA38" s="28" t="n"/>
-      <c r="AB38" s="28" t="n"/>
-      <c r="AC38" s="30" t="n"/>
-      <c r="AD38" s="24" t="n"/>
-      <c r="AE38" s="31" t="inlineStr">
-        <is>
-          <t>Learned LR call at threshold 0.5500; executable ask 0.5200 (aec-mlb-pit-nyy-2026-07-20).</t>
-        </is>
-      </c>
-      <c r="AF38" s="31" t="inlineStr">
-        <is>
-          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
-        </is>
-      </c>
-      <c r="AG38" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH38" s="24" t="n"/>
-      <c r="AI38" s="31" t="n"/>
-      <c r="AJ38" s="31" t="n"/>
-      <c r="AK38" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL38" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM38" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN38" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO38" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LOW_EDGE</t>
-        </is>
-      </c>
-      <c r="AP38" s="24" t="inlineStr">
-        <is>
-          <t>mlb-pit</t>
-        </is>
-      </c>
-      <c r="AQ38" s="24" t="inlineStr">
-        <is>
-          <t>Pittsburgh Pirates</t>
-        </is>
-      </c>
-      <c r="AR38" s="24" t="inlineStr">
-        <is>
-          <t>Pittsburgh Pirates</t>
-        </is>
-      </c>
-      <c r="AS38" s="24" t="inlineStr">
-        <is>
-          <t>mlb-nyy</t>
-        </is>
-      </c>
-      <c r="AT38" s="24" t="inlineStr">
-        <is>
-          <t>New York Yankees</t>
-        </is>
-      </c>
-      <c r="AU38" s="24" t="inlineStr">
-        <is>
-          <t>New York Yankees</t>
-        </is>
-      </c>
-      <c r="AV38" s="24" t="n"/>
-      <c r="AW38" s="24" t="n"/>
-      <c r="AX38" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY38" s="24" t="n"/>
-      <c r="AZ38" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA38" s="24" t="inlineStr">
-        <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
-        </is>
-      </c>
-      <c r="BB38" s="24" t="inlineStr">
-        <is>
-          <t>learned_lr</t>
-        </is>
-      </c>
-      <c r="BC38" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v4</t>
-        </is>
-      </c>
-      <c r="BD38" s="24" t="inlineStr">
-        <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
-        </is>
-      </c>
-      <c r="BE38" s="24" t="inlineStr">
-        <is>
-          <t>38ab7db5a3798f0c</t>
-        </is>
-      </c>
-      <c r="BF38" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG38" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v4</t>
-        </is>
-      </c>
-      <c r="BH38" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-20T14:57:35.056972Z</t>
-        </is>
-      </c>
-      <c r="BI38" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ38" s="25" t="n"/>
-      <c r="BK38" s="26" t="n">
-        <v>-108</v>
-      </c>
-      <c r="BL38" s="27" t="n">
-        <v>1.925926</v>
-      </c>
-      <c r="BM38" s="28" t="n">
-        <v>0.519231</v>
-      </c>
-      <c r="BN38" s="28" t="n">
-        <v>0.517413</v>
-      </c>
-      <c r="BO38" s="28" t="n"/>
-      <c r="BP38" s="25" t="n"/>
-      <c r="BQ38" s="27" t="n"/>
-      <c r="BR38" s="28" t="n"/>
-      <c r="BS38" s="28" t="n"/>
-      <c r="BT38" s="28" t="n"/>
-      <c r="BU38" s="25" t="n"/>
-      <c r="BV38" s="29" t="n"/>
-      <c r="BW38" s="24" t="n"/>
-      <c r="BX38" s="30" t="n"/>
-      <c r="BY38" s="27" t="n"/>
-      <c r="BZ38" s="24" t="n"/>
-      <c r="CA38" s="31" t="n"/>
-    </row>
-    <row r="39" ht="36" customHeight="1">
-      <c r="A39" s="24" t="inlineStr">
-        <is>
-          <t>33b7223ce80841b3</t>
-        </is>
-      </c>
-      <c r="B39" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-20T14:58:17.970946Z</t>
-        </is>
-      </c>
-      <c r="C39" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-20T20:05:00-0400</t>
-        </is>
-      </c>
-      <c r="D39" s="24" t="inlineStr">
-        <is>
-          <t>401816193</t>
-        </is>
-      </c>
-      <c r="E39" s="24" t="inlineStr">
-        <is>
-          <t>MLB</t>
-        </is>
-      </c>
-      <c r="F39" s="24" t="inlineStr">
-        <is>
-          <t>Detroit Tigers</t>
-        </is>
-      </c>
-      <c r="G39" s="24" t="inlineStr">
-        <is>
-          <t>Chicago Cubs</t>
-        </is>
-      </c>
-      <c r="H39" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I39" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J39" s="25" t="n"/>
-      <c r="K39" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L39" s="26" t="n">
-        <v>-108</v>
-      </c>
-      <c r="M39" s="27" t="n">
-        <v>1.925926</v>
-      </c>
-      <c r="N39" s="28" t="n">
-        <v>0.519231</v>
-      </c>
-      <c r="O39" s="28" t="n">
-        <v>0.566967</v>
-      </c>
-      <c r="P39" s="28" t="n"/>
-      <c r="Q39" s="28" t="n">
-        <v>0.047736</v>
-      </c>
-      <c r="R39" s="26" t="n">
-        <v>44</v>
-      </c>
-      <c r="S39" s="29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T39" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v4</t>
-        </is>
-      </c>
-      <c r="U39" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V39" s="24" t="n"/>
-      <c r="W39" s="26" t="n"/>
-      <c r="X39" s="26" t="n"/>
-      <c r="Y39" s="25" t="n"/>
-      <c r="Z39" s="26" t="n"/>
-      <c r="AA39" s="28" t="n"/>
-      <c r="AB39" s="28" t="n"/>
-      <c r="AC39" s="30" t="n"/>
-      <c r="AD39" s="24" t="n"/>
-      <c r="AE39" s="31" t="inlineStr">
-        <is>
-          <t>Learned LR call at threshold 0.5500; executable ask 0.5200 (aec-mlb-det-chc-2026-07-20).</t>
-        </is>
-      </c>
-      <c r="AF39" s="31" t="inlineStr">
-        <is>
-          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
-        </is>
-      </c>
-      <c r="AG39" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH39" s="24" t="n"/>
-      <c r="AI39" s="31" t="n"/>
-      <c r="AJ39" s="31" t="n"/>
-      <c r="AK39" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL39" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM39" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN39" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO39" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LOW_EDGE</t>
-        </is>
-      </c>
-      <c r="AP39" s="24" t="inlineStr">
-        <is>
-          <t>mlb-det</t>
-        </is>
-      </c>
-      <c r="AQ39" s="24" t="inlineStr">
-        <is>
-          <t>Detroit Tigers</t>
-        </is>
-      </c>
-      <c r="AR39" s="24" t="inlineStr">
-        <is>
-          <t>Detroit Tigers</t>
-        </is>
-      </c>
-      <c r="AS39" s="24" t="inlineStr">
-        <is>
-          <t>mlb-chc</t>
-        </is>
-      </c>
-      <c r="AT39" s="24" t="inlineStr">
-        <is>
-          <t>Chicago Cubs</t>
-        </is>
-      </c>
-      <c r="AU39" s="24" t="inlineStr">
-        <is>
-          <t>Chicago Cubs</t>
-        </is>
-      </c>
-      <c r="AV39" s="24" t="n"/>
-      <c r="AW39" s="24" t="n"/>
-      <c r="AX39" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY39" s="24" t="n"/>
-      <c r="AZ39" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA39" s="24" t="inlineStr">
-        <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
-        </is>
-      </c>
-      <c r="BB39" s="24" t="inlineStr">
-        <is>
-          <t>learned_lr</t>
-        </is>
-      </c>
-      <c r="BC39" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v4</t>
-        </is>
-      </c>
-      <c r="BD39" s="24" t="inlineStr">
-        <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
-        </is>
-      </c>
-      <c r="BE39" s="24" t="inlineStr">
-        <is>
-          <t>b84afb2c70e14d93</t>
-        </is>
-      </c>
-      <c r="BF39" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG39" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v4</t>
-        </is>
-      </c>
-      <c r="BH39" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-20T14:57:46.871986Z</t>
-        </is>
-      </c>
-      <c r="BI39" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ39" s="25" t="n"/>
-      <c r="BK39" s="26" t="n">
-        <v>-108</v>
-      </c>
-      <c r="BL39" s="27" t="n">
-        <v>1.925926</v>
-      </c>
-      <c r="BM39" s="28" t="n">
-        <v>0.519231</v>
-      </c>
-      <c r="BN39" s="28" t="n">
-        <v>0.517413</v>
-      </c>
-      <c r="BO39" s="28" t="n"/>
-      <c r="BP39" s="25" t="n"/>
-      <c r="BQ39" s="27" t="n"/>
-      <c r="BR39" s="28" t="n"/>
-      <c r="BS39" s="28" t="n"/>
-      <c r="BT39" s="28" t="n"/>
-      <c r="BU39" s="25" t="n"/>
-      <c r="BV39" s="29" t="n"/>
-      <c r="BW39" s="24" t="n"/>
-      <c r="BX39" s="30" t="n"/>
-      <c r="BY39" s="27" t="n"/>
-      <c r="BZ39" s="24" t="n"/>
-      <c r="CA39" s="31" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/picks.xlsx
+++ b/data/picks.xlsx
@@ -21,10 +21,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="0.0%"/>
-    <numFmt numFmtId="165" formatCode="0.0000"/>
-    <numFmt numFmtId="166" formatCode="0.0###"/>
-    <numFmt numFmtId="167" formatCode="0.000000"/>
+    <numFmt numFmtId="164" formatCode="0.0###"/>
+    <numFmt numFmtId="165" formatCode="0.000000"/>
+    <numFmt numFmtId="166" formatCode="0.0000"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -136,7 +136,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -150,10 +150,10 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -169,10 +169,10 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -184,10 +184,10 @@
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -202,13 +202,13 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="10" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -217,38 +217,11 @@
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -327,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CA35" headerRowCount="1">
-  <autoFilter ref="A1:CA35"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CA43" headerRowCount="1">
+  <autoFilter ref="A1:CA43"/>
   <tableColumns count="79">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -765,23 +738,22 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$35)</f>
+        <f>COUNTA('Picks'!$A$2:$A$43)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$35,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$43,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$35,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$43,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$35,"settled",'Picks'!$V$2:$V$35,"win")+COUNTIFS('Picks'!$U$2:$U$35,"settled",'Picks'!$V$2:$V$35,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$43,"settled",'Picks'!$V$2:$V$43,"win")+COUNTIFS('Picks'!$U$2:$U$43,"settled",'Picks'!$V$2:$V$43,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
-    <row r="5"/>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
@@ -806,23 +778,22 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$35,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$43,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$35,"&gt;0",'Picks'!$V$2:$V$35,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$35,"&gt;0",'Picks'!$V$2:$V$35,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$43,"&gt;0",'Picks'!$V$2:$V$43,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$43,"&gt;0",'Picks'!$V$2:$V$43,"loss")</f>
         <v/>
       </c>
-      <c r="E7" s="32">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$35,"&gt;0",'Picks'!$V$2:$V$35,"win")/(COUNTIFS('Picks'!$BX$2:$BX$35,"&gt;0",'Picks'!$V$2:$V$35,"win")+COUNTIFS('Picks'!$BX$2:$BX$35,"&gt;0",'Picks'!$V$2:$V$35,"loss")),0)</f>
+      <c r="E7" s="7">
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$43,"&gt;0",'Picks'!$V$2:$V$43,"win")/(COUNTIFS('Picks'!$BX$2:$BX$43,"&gt;0",'Picks'!$V$2:$V$43,"win")+COUNTIFS('Picks'!$BX$2:$BX$43,"&gt;0",'Picks'!$V$2:$V$43,"loss")),0)</f>
         <v/>
       </c>
-      <c r="G7" s="32">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$35)/SUM('Picks'!$BX$2:$BX$35),0)</f>
+      <c r="G7" s="7">
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$43)/SUM('Picks'!$BX$2:$BX$43),0)</f>
         <v/>
       </c>
     </row>
-    <row r="8"/>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
@@ -846,24 +817,23 @@
       </c>
     </row>
     <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="33">
-        <f>SUM('Picks'!$BY$2:$BY$35)</f>
+      <c r="A10" s="8">
+        <f>SUM('Picks'!$BY$2:$BY$43)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$35,"&lt;&gt;",'Picks'!$AB$2:$AB$35),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$43,"&lt;&gt;",'Picks'!$AB$2:$AB$43),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$35,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$35,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$43,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$43,"settled")</f>
         <v/>
       </c>
-      <c r="G10" s="33">
-        <f>SUMIFS('Picks'!$AC$2:$AC$35,'Picks'!$AM$2:$AM$35,"QUALIFIED_SHADOW_CALL")</f>
+      <c r="G10" s="8">
+        <f>SUMIFS('Picks'!$AC$2:$AC$43,'Picks'!$AM$2:$AM$43,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
@@ -915,27 +885,27 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$35,$A14,'Picks'!$U$2:$U$35,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$43,$A14,'Picks'!$U$2:$U$43,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$35,$A14,'Picks'!$U$2:$U$35,"settled",'Picks'!$V$2:$V$35,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$43,$A14,'Picks'!$U$2:$U$43,"settled",'Picks'!$V$2:$V$43,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$35,$A14,'Picks'!$U$2:$U$35,"settled",'Picks'!$V$2:$V$35,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$43,$A14,'Picks'!$U$2:$U$43,"settled",'Picks'!$V$2:$V$43,"loss")</f>
         <v/>
       </c>
-      <c r="E14" s="34">
+      <c r="E14" s="14">
         <f>IFERROR(C14/(C14+D14),0)</f>
         <v/>
       </c>
-      <c r="F14" s="35">
-        <f>SUMIFS('Picks'!$BY$2:$BY$35,'Picks'!$H$2:$H$35,$A14)</f>
+      <c r="F14" s="15">
+        <f>SUMIFS('Picks'!$BY$2:$BY$43,'Picks'!$H$2:$H$43,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$35,'Picks'!$H$2:$H$35,$A14,'Picks'!$U$2:$U$35,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$43,'Picks'!$H$2:$H$43,$A14,'Picks'!$U$2:$U$43,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -946,27 +916,27 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$35,$A15,'Picks'!$U$2:$U$35,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$43,$A15,'Picks'!$U$2:$U$43,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$35,$A15,'Picks'!$U$2:$U$35,"settled",'Picks'!$V$2:$V$35,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$43,$A15,'Picks'!$U$2:$U$43,"settled",'Picks'!$V$2:$V$43,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$35,$A15,'Picks'!$U$2:$U$35,"settled",'Picks'!$V$2:$V$35,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$43,$A15,'Picks'!$U$2:$U$43,"settled",'Picks'!$V$2:$V$43,"loss")</f>
         <v/>
       </c>
-      <c r="E15" s="36">
+      <c r="E15" s="19">
         <f>IFERROR(C15/(C15+D15),0)</f>
         <v/>
       </c>
-      <c r="F15" s="37">
-        <f>SUMIFS('Picks'!$BY$2:$BY$35,'Picks'!$H$2:$H$35,$A15)</f>
+      <c r="F15" s="20">
+        <f>SUMIFS('Picks'!$BY$2:$BY$43,'Picks'!$H$2:$H$43,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$35,'Picks'!$H$2:$H$35,$A15,'Picks'!$U$2:$U$35,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$43,'Picks'!$H$2:$H$43,$A15,'Picks'!$U$2:$U$43,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -977,31 +947,30 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$35,$A16,'Picks'!$U$2:$U$35,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$43,$A16,'Picks'!$U$2:$U$43,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$35,$A16,'Picks'!$U$2:$U$35,"settled",'Picks'!$V$2:$V$35,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$43,$A16,'Picks'!$U$2:$U$43,"settled",'Picks'!$V$2:$V$43,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$35,$A16,'Picks'!$U$2:$U$35,"settled",'Picks'!$V$2:$V$35,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$43,$A16,'Picks'!$U$2:$U$43,"settled",'Picks'!$V$2:$V$43,"loss")</f>
         <v/>
       </c>
-      <c r="E16" s="34">
+      <c r="E16" s="14">
         <f>IFERROR(C16/(C16+D16),0)</f>
         <v/>
       </c>
-      <c r="F16" s="35">
-        <f>SUMIFS('Picks'!$BY$2:$BY$35,'Picks'!$H$2:$H$35,$A16)</f>
+      <c r="F16" s="15">
+        <f>SUMIFS('Picks'!$BY$2:$BY$43,'Picks'!$H$2:$H$43,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$35,'Picks'!$H$2:$H$35,$A16,'Picks'!$U$2:$U$35,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$43,'Picks'!$H$2:$H$43,$A16,'Picks'!$U$2:$U$43,"settled"),0)</f>
         <v/>
       </c>
     </row>
-    <row r="17"/>
     <row r="18">
       <c r="A18" s="22" t="inlineStr">
         <is>
@@ -1027,7 +996,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CA35"/>
+  <dimension ref="A1:CA43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1554,7 +1523,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J2" s="38" t="n"/>
+      <c r="J2" s="25" t="n"/>
       <c r="K2" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -1563,7 +1532,7 @@
       <c r="L2" s="26" t="n">
         <v>117</v>
       </c>
-      <c r="M2" s="39" t="n">
+      <c r="M2" s="27" t="n">
         <v>2.17</v>
       </c>
       <c r="N2" s="28" t="n">
@@ -1603,11 +1572,11 @@
       <c r="X2" s="26" t="n">
         <v>108</v>
       </c>
-      <c r="Y2" s="38" t="n"/>
+      <c r="Y2" s="25" t="n"/>
       <c r="Z2" s="26" t="n"/>
       <c r="AA2" s="28" t="n"/>
       <c r="AB2" s="28" t="n"/>
-      <c r="AC2" s="40" t="n">
+      <c r="AC2" s="30" t="n">
         <v>1.755</v>
       </c>
       <c r="AD2" s="24" t="inlineStr">
@@ -1744,11 +1713,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ2" s="38" t="n"/>
+      <c r="BJ2" s="25" t="n"/>
       <c r="BK2" s="26" t="n">
         <v>117</v>
       </c>
-      <c r="BL2" s="39" t="n">
+      <c r="BL2" s="27" t="n">
         <v>2.17</v>
       </c>
       <c r="BM2" s="28" t="n">
@@ -1758,18 +1727,18 @@
         <v>0.455446</v>
       </c>
       <c r="BO2" s="28" t="n"/>
-      <c r="BP2" s="38" t="n"/>
-      <c r="BQ2" s="39" t="n"/>
+      <c r="BP2" s="25" t="n"/>
+      <c r="BQ2" s="27" t="n"/>
       <c r="BR2" s="28" t="n"/>
       <c r="BS2" s="28" t="n"/>
       <c r="BT2" s="28" t="n"/>
-      <c r="BU2" s="38" t="n"/>
+      <c r="BU2" s="25" t="n"/>
       <c r="BV2" s="29" t="n"/>
       <c r="BW2" s="24" t="n"/>
-      <c r="BX2" s="40" t="n">
+      <c r="BX2" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY2" s="39" t="n">
+      <c r="BY2" s="27" t="n">
         <v>1.17</v>
       </c>
       <c r="BZ2" s="24" t="inlineStr">
@@ -1829,7 +1798,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J3" s="38" t="n"/>
+      <c r="J3" s="25" t="n"/>
       <c r="K3" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -1838,7 +1807,7 @@
       <c r="L3" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="M3" s="39" t="n">
+      <c r="M3" s="27" t="n">
         <v>1.75188</v>
       </c>
       <c r="N3" s="28" t="n">
@@ -1878,11 +1847,11 @@
       <c r="X3" s="26" t="n">
         <v>8</v>
       </c>
-      <c r="Y3" s="38" t="n"/>
+      <c r="Y3" s="25" t="n"/>
       <c r="Z3" s="26" t="n"/>
       <c r="AA3" s="28" t="n"/>
       <c r="AB3" s="28" t="n"/>
-      <c r="AC3" s="40" t="n">
+      <c r="AC3" s="30" t="n">
         <v>1.1278</v>
       </c>
       <c r="AD3" s="24" t="inlineStr">
@@ -2019,11 +1988,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ3" s="38" t="n"/>
+      <c r="BJ3" s="25" t="n"/>
       <c r="BK3" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="BL3" s="39" t="n">
+      <c r="BL3" s="27" t="n">
         <v>1.75188</v>
       </c>
       <c r="BM3" s="28" t="n">
@@ -2033,18 +2002,18 @@
         <v>0.567164</v>
       </c>
       <c r="BO3" s="28" t="n"/>
-      <c r="BP3" s="38" t="n"/>
-      <c r="BQ3" s="39" t="n"/>
+      <c r="BP3" s="25" t="n"/>
+      <c r="BQ3" s="27" t="n"/>
       <c r="BR3" s="28" t="n"/>
       <c r="BS3" s="28" t="n"/>
       <c r="BT3" s="28" t="n"/>
-      <c r="BU3" s="38" t="n"/>
+      <c r="BU3" s="25" t="n"/>
       <c r="BV3" s="29" t="n"/>
       <c r="BW3" s="24" t="n"/>
-      <c r="BX3" s="40" t="n">
+      <c r="BX3" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY3" s="39" t="n">
+      <c r="BY3" s="27" t="n">
         <v>0.75188</v>
       </c>
       <c r="BZ3" s="24" t="inlineStr">
@@ -2104,7 +2073,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J4" s="38" t="n"/>
+      <c r="J4" s="25" t="n"/>
       <c r="K4" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -2113,7 +2082,7 @@
       <c r="L4" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="M4" s="39" t="n">
+      <c r="M4" s="27" t="n">
         <v>1.980392</v>
       </c>
       <c r="N4" s="28" t="n">
@@ -2153,11 +2122,11 @@
       <c r="X4" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="Y4" s="38" t="n"/>
+      <c r="Y4" s="25" t="n"/>
       <c r="Z4" s="26" t="n"/>
       <c r="AA4" s="28" t="n"/>
       <c r="AB4" s="28" t="n"/>
-      <c r="AC4" s="40" t="n">
+      <c r="AC4" s="30" t="n">
         <v>-1</v>
       </c>
       <c r="AD4" s="24" t="inlineStr">
@@ -2294,11 +2263,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ4" s="38" t="n"/>
+      <c r="BJ4" s="25" t="n"/>
       <c r="BK4" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="BL4" s="39" t="n">
+      <c r="BL4" s="27" t="n">
         <v>1.980392</v>
       </c>
       <c r="BM4" s="28" t="n">
@@ -2308,18 +2277,18 @@
         <v>0.502488</v>
       </c>
       <c r="BO4" s="28" t="n"/>
-      <c r="BP4" s="38" t="n"/>
-      <c r="BQ4" s="39" t="n"/>
+      <c r="BP4" s="25" t="n"/>
+      <c r="BQ4" s="27" t="n"/>
       <c r="BR4" s="28" t="n"/>
       <c r="BS4" s="28" t="n"/>
       <c r="BT4" s="28" t="n"/>
-      <c r="BU4" s="38" t="n"/>
+      <c r="BU4" s="25" t="n"/>
       <c r="BV4" s="29" t="n"/>
       <c r="BW4" s="24" t="n"/>
-      <c r="BX4" s="40" t="n">
+      <c r="BX4" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY4" s="39" t="n">
+      <c r="BY4" s="27" t="n">
         <v>-1</v>
       </c>
       <c r="BZ4" s="24" t="inlineStr">
@@ -2379,7 +2348,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J5" s="38" t="n"/>
+      <c r="J5" s="25" t="n"/>
       <c r="K5" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -2388,7 +2357,7 @@
       <c r="L5" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="M5" s="39" t="n">
+      <c r="M5" s="27" t="n">
         <v>1.75188</v>
       </c>
       <c r="N5" s="28" t="n">
@@ -2428,11 +2397,11 @@
       <c r="X5" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="Y5" s="38" t="n"/>
+      <c r="Y5" s="25" t="n"/>
       <c r="Z5" s="26" t="n"/>
       <c r="AA5" s="28" t="n"/>
       <c r="AB5" s="28" t="n"/>
-      <c r="AC5" s="40" t="n">
+      <c r="AC5" s="30" t="n">
         <v>1.1278</v>
       </c>
       <c r="AD5" s="24" t="inlineStr">
@@ -2569,11 +2538,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ5" s="38" t="n"/>
+      <c r="BJ5" s="25" t="n"/>
       <c r="BK5" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="BL5" s="39" t="n">
+      <c r="BL5" s="27" t="n">
         <v>1.75188</v>
       </c>
       <c r="BM5" s="28" t="n">
@@ -2583,18 +2552,18 @@
         <v>0.567164</v>
       </c>
       <c r="BO5" s="28" t="n"/>
-      <c r="BP5" s="38" t="n"/>
-      <c r="BQ5" s="39" t="n"/>
+      <c r="BP5" s="25" t="n"/>
+      <c r="BQ5" s="27" t="n"/>
       <c r="BR5" s="28" t="n"/>
       <c r="BS5" s="28" t="n"/>
       <c r="BT5" s="28" t="n"/>
-      <c r="BU5" s="38" t="n"/>
+      <c r="BU5" s="25" t="n"/>
       <c r="BV5" s="29" t="n"/>
       <c r="BW5" s="24" t="n"/>
-      <c r="BX5" s="40" t="n">
+      <c r="BX5" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY5" s="39" t="n">
+      <c r="BY5" s="27" t="n">
         <v>0.75188</v>
       </c>
       <c r="BZ5" s="24" t="inlineStr">
@@ -2654,7 +2623,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J6" s="38" t="n"/>
+      <c r="J6" s="25" t="n"/>
       <c r="K6" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -2663,7 +2632,7 @@
       <c r="L6" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="M6" s="39" t="n">
+      <c r="M6" s="27" t="n">
         <v>1.961538</v>
       </c>
       <c r="N6" s="28" t="n">
@@ -2703,11 +2672,11 @@
       <c r="X6" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="Y6" s="38" t="n"/>
+      <c r="Y6" s="25" t="n"/>
       <c r="Z6" s="26" t="n"/>
       <c r="AA6" s="28" t="n"/>
       <c r="AB6" s="28" t="n"/>
-      <c r="AC6" s="40" t="n">
+      <c r="AC6" s="30" t="n">
         <v>1.2019</v>
       </c>
       <c r="AD6" s="24" t="inlineStr">
@@ -2844,11 +2813,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ6" s="38" t="n"/>
+      <c r="BJ6" s="25" t="n"/>
       <c r="BK6" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="BL6" s="39" t="n">
+      <c r="BL6" s="27" t="n">
         <v>1.961538</v>
       </c>
       <c r="BM6" s="28" t="n">
@@ -2858,18 +2827,18 @@
         <v>0.507463</v>
       </c>
       <c r="BO6" s="28" t="n"/>
-      <c r="BP6" s="38" t="n"/>
-      <c r="BQ6" s="39" t="n"/>
+      <c r="BP6" s="25" t="n"/>
+      <c r="BQ6" s="27" t="n"/>
       <c r="BR6" s="28" t="n"/>
       <c r="BS6" s="28" t="n"/>
       <c r="BT6" s="28" t="n"/>
-      <c r="BU6" s="38" t="n"/>
+      <c r="BU6" s="25" t="n"/>
       <c r="BV6" s="29" t="n"/>
       <c r="BW6" s="24" t="n"/>
-      <c r="BX6" s="40" t="n">
+      <c r="BX6" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY6" s="39" t="n">
+      <c r="BY6" s="27" t="n">
         <v>0.961538</v>
       </c>
       <c r="BZ6" s="24" t="inlineStr">
@@ -2929,7 +2898,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J7" s="38" t="n"/>
+      <c r="J7" s="25" t="n"/>
       <c r="K7" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -2938,7 +2907,7 @@
       <c r="L7" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="M7" s="39" t="n">
+      <c r="M7" s="27" t="n">
         <v>1.961538</v>
       </c>
       <c r="N7" s="28" t="n">
@@ -2978,11 +2947,11 @@
       <c r="X7" s="26" t="n">
         <v>10</v>
       </c>
-      <c r="Y7" s="38" t="n"/>
+      <c r="Y7" s="25" t="n"/>
       <c r="Z7" s="26" t="n"/>
       <c r="AA7" s="28" t="n"/>
       <c r="AB7" s="28" t="n"/>
-      <c r="AC7" s="40" t="n">
+      <c r="AC7" s="30" t="n">
         <v>-1.25</v>
       </c>
       <c r="AD7" s="24" t="inlineStr">
@@ -3119,11 +3088,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ7" s="38" t="n"/>
+      <c r="BJ7" s="25" t="n"/>
       <c r="BK7" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="BL7" s="39" t="n">
+      <c r="BL7" s="27" t="n">
         <v>1.961538</v>
       </c>
       <c r="BM7" s="28" t="n">
@@ -3133,18 +3102,18 @@
         <v>0.507463</v>
       </c>
       <c r="BO7" s="28" t="n"/>
-      <c r="BP7" s="38" t="n"/>
-      <c r="BQ7" s="39" t="n"/>
+      <c r="BP7" s="25" t="n"/>
+      <c r="BQ7" s="27" t="n"/>
       <c r="BR7" s="28" t="n"/>
       <c r="BS7" s="28" t="n"/>
       <c r="BT7" s="28" t="n"/>
-      <c r="BU7" s="38" t="n"/>
+      <c r="BU7" s="25" t="n"/>
       <c r="BV7" s="29" t="n"/>
       <c r="BW7" s="24" t="n"/>
-      <c r="BX7" s="40" t="n">
+      <c r="BX7" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY7" s="39" t="n">
+      <c r="BY7" s="27" t="n">
         <v>-1</v>
       </c>
       <c r="BZ7" s="24" t="inlineStr">
@@ -3204,7 +3173,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J8" s="38" t="n"/>
+      <c r="J8" s="25" t="n"/>
       <c r="K8" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -3213,7 +3182,7 @@
       <c r="L8" s="26" t="n">
         <v>-106</v>
       </c>
-      <c r="M8" s="39" t="n">
+      <c r="M8" s="27" t="n">
         <v>1.943396</v>
       </c>
       <c r="N8" s="28" t="n">
@@ -3253,11 +3222,11 @@
       <c r="X8" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="Y8" s="38" t="n"/>
+      <c r="Y8" s="25" t="n"/>
       <c r="Z8" s="26" t="n"/>
       <c r="AA8" s="28" t="n"/>
       <c r="AB8" s="28" t="n"/>
-      <c r="AC8" s="40" t="n">
+      <c r="AC8" s="30" t="n">
         <v>-1</v>
       </c>
       <c r="AD8" s="24" t="inlineStr">
@@ -3394,11 +3363,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ8" s="38" t="n"/>
+      <c r="BJ8" s="25" t="n"/>
       <c r="BK8" s="26" t="n">
         <v>-106</v>
       </c>
-      <c r="BL8" s="39" t="n">
+      <c r="BL8" s="27" t="n">
         <v>1.943396</v>
       </c>
       <c r="BM8" s="28" t="n">
@@ -3408,18 +3377,18 @@
         <v>0.5124379999999999</v>
       </c>
       <c r="BO8" s="28" t="n"/>
-      <c r="BP8" s="38" t="n"/>
-      <c r="BQ8" s="39" t="n"/>
+      <c r="BP8" s="25" t="n"/>
+      <c r="BQ8" s="27" t="n"/>
       <c r="BR8" s="28" t="n"/>
       <c r="BS8" s="28" t="n"/>
       <c r="BT8" s="28" t="n"/>
-      <c r="BU8" s="38" t="n"/>
+      <c r="BU8" s="25" t="n"/>
       <c r="BV8" s="29" t="n"/>
       <c r="BW8" s="24" t="n"/>
-      <c r="BX8" s="40" t="n">
+      <c r="BX8" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY8" s="39" t="n">
+      <c r="BY8" s="27" t="n">
         <v>-1</v>
       </c>
       <c r="BZ8" s="24" t="inlineStr">
@@ -3479,7 +3448,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J9" s="38" t="n"/>
+      <c r="J9" s="25" t="n"/>
       <c r="K9" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -3488,7 +3457,7 @@
       <c r="L9" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="M9" s="39" t="n">
+      <c r="M9" s="27" t="n">
         <v>1.980392</v>
       </c>
       <c r="N9" s="28" t="n">
@@ -3528,11 +3497,11 @@
       <c r="X9" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="Y9" s="38" t="n"/>
+      <c r="Y9" s="25" t="n"/>
       <c r="Z9" s="26" t="n"/>
       <c r="AA9" s="28" t="n"/>
       <c r="AB9" s="28" t="n"/>
-      <c r="AC9" s="40" t="n">
+      <c r="AC9" s="30" t="n">
         <v>0.9804</v>
       </c>
       <c r="AD9" s="24" t="inlineStr">
@@ -3669,11 +3638,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ9" s="38" t="n"/>
+      <c r="BJ9" s="25" t="n"/>
       <c r="BK9" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="BL9" s="39" t="n">
+      <c r="BL9" s="27" t="n">
         <v>1.980392</v>
       </c>
       <c r="BM9" s="28" t="n">
@@ -3683,18 +3652,18 @@
         <v>0.502488</v>
       </c>
       <c r="BO9" s="28" t="n"/>
-      <c r="BP9" s="38" t="n"/>
-      <c r="BQ9" s="39" t="n"/>
+      <c r="BP9" s="25" t="n"/>
+      <c r="BQ9" s="27" t="n"/>
       <c r="BR9" s="28" t="n"/>
       <c r="BS9" s="28" t="n"/>
       <c r="BT9" s="28" t="n"/>
-      <c r="BU9" s="38" t="n"/>
+      <c r="BU9" s="25" t="n"/>
       <c r="BV9" s="29" t="n"/>
       <c r="BW9" s="24" t="n"/>
-      <c r="BX9" s="40" t="n">
+      <c r="BX9" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY9" s="39" t="n">
+      <c r="BY9" s="27" t="n">
         <v>0.980392</v>
       </c>
       <c r="BZ9" s="24" t="inlineStr">
@@ -3754,7 +3723,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J10" s="38" t="n"/>
+      <c r="J10" s="25" t="n"/>
       <c r="K10" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -3763,7 +3732,7 @@
       <c r="L10" s="26" t="n">
         <v>-138</v>
       </c>
-      <c r="M10" s="39" t="n">
+      <c r="M10" s="27" t="n">
         <v>1.724638</v>
       </c>
       <c r="N10" s="28" t="n">
@@ -3803,11 +3772,11 @@
       <c r="X10" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="Y10" s="38" t="n"/>
+      <c r="Y10" s="25" t="n"/>
       <c r="Z10" s="26" t="n"/>
       <c r="AA10" s="28" t="n"/>
       <c r="AB10" s="28" t="n"/>
-      <c r="AC10" s="40" t="n">
+      <c r="AC10" s="30" t="n">
         <v>1.2681</v>
       </c>
       <c r="AD10" s="24" t="inlineStr">
@@ -3944,11 +3913,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ10" s="38" t="n"/>
+      <c r="BJ10" s="25" t="n"/>
       <c r="BK10" s="26" t="n">
         <v>-138</v>
       </c>
-      <c r="BL10" s="39" t="n">
+      <c r="BL10" s="27" t="n">
         <v>1.724638</v>
       </c>
       <c r="BM10" s="28" t="n">
@@ -3958,18 +3927,18 @@
         <v>0.577114</v>
       </c>
       <c r="BO10" s="28" t="n"/>
-      <c r="BP10" s="38" t="n"/>
-      <c r="BQ10" s="39" t="n"/>
+      <c r="BP10" s="25" t="n"/>
+      <c r="BQ10" s="27" t="n"/>
       <c r="BR10" s="28" t="n"/>
       <c r="BS10" s="28" t="n"/>
       <c r="BT10" s="28" t="n"/>
-      <c r="BU10" s="38" t="n"/>
+      <c r="BU10" s="25" t="n"/>
       <c r="BV10" s="29" t="n"/>
       <c r="BW10" s="24" t="n"/>
-      <c r="BX10" s="40" t="n">
+      <c r="BX10" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY10" s="39" t="n">
+      <c r="BY10" s="27" t="n">
         <v>0.724638</v>
       </c>
       <c r="BZ10" s="24" t="inlineStr">
@@ -4029,7 +3998,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J11" s="38" t="n"/>
+      <c r="J11" s="25" t="n"/>
       <c r="K11" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -4038,7 +4007,7 @@
       <c r="L11" s="26" t="n">
         <v>102</v>
       </c>
-      <c r="M11" s="39" t="n">
+      <c r="M11" s="27" t="n">
         <v>2.02</v>
       </c>
       <c r="N11" s="28" t="n">
@@ -4078,11 +4047,11 @@
       <c r="X11" s="26" t="n">
         <v>15</v>
       </c>
-      <c r="Y11" s="38" t="n"/>
+      <c r="Y11" s="25" t="n"/>
       <c r="Z11" s="26" t="n"/>
       <c r="AA11" s="28" t="n"/>
       <c r="AB11" s="28" t="n"/>
-      <c r="AC11" s="40" t="n">
+      <c r="AC11" s="30" t="n">
         <v>1.275</v>
       </c>
       <c r="AD11" s="24" t="inlineStr">
@@ -4219,11 +4188,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ11" s="38" t="n"/>
+      <c r="BJ11" s="25" t="n"/>
       <c r="BK11" s="26" t="n">
         <v>102</v>
       </c>
-      <c r="BL11" s="39" t="n">
+      <c r="BL11" s="27" t="n">
         <v>2.02</v>
       </c>
       <c r="BM11" s="28" t="n">
@@ -4233,18 +4202,18 @@
         <v>0.492537</v>
       </c>
       <c r="BO11" s="28" t="n"/>
-      <c r="BP11" s="38" t="n"/>
-      <c r="BQ11" s="39" t="n"/>
+      <c r="BP11" s="25" t="n"/>
+      <c r="BQ11" s="27" t="n"/>
       <c r="BR11" s="28" t="n"/>
       <c r="BS11" s="28" t="n"/>
       <c r="BT11" s="28" t="n"/>
-      <c r="BU11" s="38" t="n"/>
+      <c r="BU11" s="25" t="n"/>
       <c r="BV11" s="29" t="n"/>
       <c r="BW11" s="24" t="n"/>
-      <c r="BX11" s="40" t="n">
+      <c r="BX11" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY11" s="39" t="n">
+      <c r="BY11" s="27" t="n">
         <v>1.02</v>
       </c>
       <c r="BZ11" s="24" t="inlineStr">
@@ -4304,7 +4273,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J12" s="38" t="n"/>
+      <c r="J12" s="25" t="n"/>
       <c r="K12" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -4313,7 +4282,7 @@
       <c r="L12" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="M12" s="39" t="n">
+      <c r="M12" s="27" t="n">
         <v>1.980392</v>
       </c>
       <c r="N12" s="28" t="n">
@@ -4353,11 +4322,11 @@
       <c r="X12" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y12" s="38" t="n"/>
+      <c r="Y12" s="25" t="n"/>
       <c r="Z12" s="26" t="n"/>
       <c r="AA12" s="28" t="n"/>
       <c r="AB12" s="28" t="n"/>
-      <c r="AC12" s="40" t="n">
+      <c r="AC12" s="30" t="n">
         <v>-1</v>
       </c>
       <c r="AD12" s="24" t="inlineStr">
@@ -4494,11 +4463,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ12" s="38" t="n"/>
+      <c r="BJ12" s="25" t="n"/>
       <c r="BK12" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="BL12" s="39" t="n">
+      <c r="BL12" s="27" t="n">
         <v>1.980392</v>
       </c>
       <c r="BM12" s="28" t="n">
@@ -4508,18 +4477,18 @@
         <v>0.502488</v>
       </c>
       <c r="BO12" s="28" t="n"/>
-      <c r="BP12" s="38" t="n"/>
-      <c r="BQ12" s="39" t="n"/>
+      <c r="BP12" s="25" t="n"/>
+      <c r="BQ12" s="27" t="n"/>
       <c r="BR12" s="28" t="n"/>
       <c r="BS12" s="28" t="n"/>
       <c r="BT12" s="28" t="n"/>
-      <c r="BU12" s="38" t="n"/>
+      <c r="BU12" s="25" t="n"/>
       <c r="BV12" s="29" t="n"/>
       <c r="BW12" s="24" t="n"/>
-      <c r="BX12" s="40" t="n">
+      <c r="BX12" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY12" s="39" t="n">
+      <c r="BY12" s="27" t="n">
         <v>-1</v>
       </c>
       <c r="BZ12" s="24" t="inlineStr">
@@ -4579,7 +4548,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J13" s="38" t="n"/>
+      <c r="J13" s="25" t="n"/>
       <c r="K13" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -4588,7 +4557,7 @@
       <c r="L13" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="M13" s="39" t="n">
+      <c r="M13" s="27" t="n">
         <v>1.980392</v>
       </c>
       <c r="N13" s="28" t="n">
@@ -4628,11 +4597,11 @@
       <c r="X13" s="26" t="n">
         <v>7</v>
       </c>
-      <c r="Y13" s="38" t="n"/>
+      <c r="Y13" s="25" t="n"/>
       <c r="Z13" s="26" t="n"/>
       <c r="AA13" s="28" t="n"/>
       <c r="AB13" s="28" t="n"/>
-      <c r="AC13" s="40" t="n">
+      <c r="AC13" s="30" t="n">
         <v>1.2255</v>
       </c>
       <c r="AD13" s="24" t="inlineStr">
@@ -4769,11 +4738,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ13" s="38" t="n"/>
+      <c r="BJ13" s="25" t="n"/>
       <c r="BK13" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="BL13" s="39" t="n">
+      <c r="BL13" s="27" t="n">
         <v>1.980392</v>
       </c>
       <c r="BM13" s="28" t="n">
@@ -4783,18 +4752,18 @@
         <v>0.502488</v>
       </c>
       <c r="BO13" s="28" t="n"/>
-      <c r="BP13" s="38" t="n"/>
-      <c r="BQ13" s="39" t="n"/>
+      <c r="BP13" s="25" t="n"/>
+      <c r="BQ13" s="27" t="n"/>
       <c r="BR13" s="28" t="n"/>
       <c r="BS13" s="28" t="n"/>
       <c r="BT13" s="28" t="n"/>
-      <c r="BU13" s="38" t="n"/>
+      <c r="BU13" s="25" t="n"/>
       <c r="BV13" s="29" t="n"/>
       <c r="BW13" s="24" t="n"/>
-      <c r="BX13" s="40" t="n">
+      <c r="BX13" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY13" s="39" t="n">
+      <c r="BY13" s="27" t="n">
         <v>0.980392</v>
       </c>
       <c r="BZ13" s="24" t="inlineStr">
@@ -4854,7 +4823,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J14" s="38" t="n"/>
+      <c r="J14" s="25" t="n"/>
       <c r="K14" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -4863,7 +4832,7 @@
       <c r="L14" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="M14" s="39" t="n">
+      <c r="M14" s="27" t="n">
         <v>1.961538</v>
       </c>
       <c r="N14" s="28" t="n">
@@ -4903,11 +4872,11 @@
       <c r="X14" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="Y14" s="38" t="n"/>
+      <c r="Y14" s="25" t="n"/>
       <c r="Z14" s="26" t="n"/>
       <c r="AA14" s="28" t="n"/>
       <c r="AB14" s="28" t="n"/>
-      <c r="AC14" s="40" t="n">
+      <c r="AC14" s="30" t="n">
         <v>-0.75</v>
       </c>
       <c r="AD14" s="24" t="inlineStr">
@@ -5044,11 +5013,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ14" s="38" t="n"/>
+      <c r="BJ14" s="25" t="n"/>
       <c r="BK14" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="BL14" s="39" t="n">
+      <c r="BL14" s="27" t="n">
         <v>1.961538</v>
       </c>
       <c r="BM14" s="28" t="n">
@@ -5058,18 +5027,18 @@
         <v>0.507463</v>
       </c>
       <c r="BO14" s="28" t="n"/>
-      <c r="BP14" s="38" t="n"/>
-      <c r="BQ14" s="39" t="n"/>
+      <c r="BP14" s="25" t="n"/>
+      <c r="BQ14" s="27" t="n"/>
       <c r="BR14" s="28" t="n"/>
       <c r="BS14" s="28" t="n"/>
       <c r="BT14" s="28" t="n"/>
-      <c r="BU14" s="38" t="n"/>
+      <c r="BU14" s="25" t="n"/>
       <c r="BV14" s="29" t="n"/>
       <c r="BW14" s="24" t="n"/>
-      <c r="BX14" s="40" t="n">
+      <c r="BX14" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY14" s="39" t="n">
+      <c r="BY14" s="27" t="n">
         <v>-1</v>
       </c>
       <c r="BZ14" s="24" t="inlineStr">
@@ -5129,7 +5098,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J15" s="38" t="n"/>
+      <c r="J15" s="25" t="n"/>
       <c r="K15" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -5138,7 +5107,7 @@
       <c r="L15" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="M15" s="39" t="n">
+      <c r="M15" s="27" t="n">
         <v>1.961538</v>
       </c>
       <c r="N15" s="28" t="n">
@@ -5178,11 +5147,11 @@
       <c r="X15" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="Y15" s="38" t="n"/>
+      <c r="Y15" s="25" t="n"/>
       <c r="Z15" s="26" t="n"/>
       <c r="AA15" s="28" t="n"/>
       <c r="AB15" s="28" t="n"/>
-      <c r="AC15" s="40" t="n">
+      <c r="AC15" s="30" t="n">
         <v>-1</v>
       </c>
       <c r="AD15" s="24" t="inlineStr">
@@ -5319,11 +5288,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ15" s="38" t="n"/>
+      <c r="BJ15" s="25" t="n"/>
       <c r="BK15" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="BL15" s="39" t="n">
+      <c r="BL15" s="27" t="n">
         <v>1.961538</v>
       </c>
       <c r="BM15" s="28" t="n">
@@ -5333,18 +5302,18 @@
         <v>0.507463</v>
       </c>
       <c r="BO15" s="28" t="n"/>
-      <c r="BP15" s="38" t="n"/>
-      <c r="BQ15" s="39" t="n"/>
+      <c r="BP15" s="25" t="n"/>
+      <c r="BQ15" s="27" t="n"/>
       <c r="BR15" s="28" t="n"/>
       <c r="BS15" s="28" t="n"/>
       <c r="BT15" s="28" t="n"/>
-      <c r="BU15" s="38" t="n"/>
+      <c r="BU15" s="25" t="n"/>
       <c r="BV15" s="29" t="n"/>
       <c r="BW15" s="24" t="n"/>
-      <c r="BX15" s="40" t="n">
+      <c r="BX15" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY15" s="39" t="n">
+      <c r="BY15" s="27" t="n">
         <v>-1</v>
       </c>
       <c r="BZ15" s="24" t="inlineStr">
@@ -5404,7 +5373,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J16" s="38" t="n"/>
+      <c r="J16" s="25" t="n"/>
       <c r="K16" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -5413,7 +5382,7 @@
       <c r="L16" s="26" t="n">
         <v>-111</v>
       </c>
-      <c r="M16" s="39" t="n">
+      <c r="M16" s="27" t="n">
         <v>1.900901</v>
       </c>
       <c r="N16" s="28" t="n">
@@ -5453,11 +5422,11 @@
       <c r="X16" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="Y16" s="38" t="n"/>
+      <c r="Y16" s="25" t="n"/>
       <c r="Z16" s="26" t="n"/>
       <c r="AA16" s="28" t="n"/>
       <c r="AB16" s="28" t="n"/>
-      <c r="AC16" s="40" t="n">
+      <c r="AC16" s="30" t="n">
         <v>-1.5</v>
       </c>
       <c r="AD16" s="24" t="inlineStr">
@@ -5594,11 +5563,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ16" s="38" t="n"/>
+      <c r="BJ16" s="25" t="n"/>
       <c r="BK16" s="26" t="n">
         <v>-111</v>
       </c>
-      <c r="BL16" s="39" t="n">
+      <c r="BL16" s="27" t="n">
         <v>1.900901</v>
       </c>
       <c r="BM16" s="28" t="n">
@@ -5608,18 +5577,18 @@
         <v>0.522388</v>
       </c>
       <c r="BO16" s="28" t="n"/>
-      <c r="BP16" s="38" t="n"/>
-      <c r="BQ16" s="39" t="n"/>
+      <c r="BP16" s="25" t="n"/>
+      <c r="BQ16" s="27" t="n"/>
       <c r="BR16" s="28" t="n"/>
       <c r="BS16" s="28" t="n"/>
       <c r="BT16" s="28" t="n"/>
-      <c r="BU16" s="38" t="n"/>
+      <c r="BU16" s="25" t="n"/>
       <c r="BV16" s="29" t="n"/>
       <c r="BW16" s="24" t="n"/>
-      <c r="BX16" s="40" t="n">
+      <c r="BX16" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY16" s="39" t="n">
+      <c r="BY16" s="27" t="n">
         <v>-1</v>
       </c>
       <c r="BZ16" s="24" t="inlineStr">
@@ -5679,7 +5648,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J17" s="38" t="n"/>
+      <c r="J17" s="25" t="n"/>
       <c r="K17" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -5688,7 +5657,7 @@
       <c r="L17" s="26" t="n">
         <v>-108</v>
       </c>
-      <c r="M17" s="39" t="n">
+      <c r="M17" s="27" t="n">
         <v>1.925926</v>
       </c>
       <c r="N17" s="28" t="n">
@@ -5728,11 +5697,11 @@
       <c r="X17" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="Y17" s="38" t="n"/>
+      <c r="Y17" s="25" t="n"/>
       <c r="Z17" s="26" t="n"/>
       <c r="AA17" s="28" t="n"/>
       <c r="AB17" s="28" t="n"/>
-      <c r="AC17" s="40" t="n">
+      <c r="AC17" s="30" t="n">
         <v>0.9258999999999999</v>
       </c>
       <c r="AD17" s="24" t="inlineStr">
@@ -5869,11 +5838,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ17" s="38" t="n"/>
+      <c r="BJ17" s="25" t="n"/>
       <c r="BK17" s="26" t="n">
         <v>-108</v>
       </c>
-      <c r="BL17" s="39" t="n">
+      <c r="BL17" s="27" t="n">
         <v>1.925926</v>
       </c>
       <c r="BM17" s="28" t="n">
@@ -5883,18 +5852,18 @@
         <v>0.5148509999999999</v>
       </c>
       <c r="BO17" s="28" t="n"/>
-      <c r="BP17" s="38" t="n"/>
-      <c r="BQ17" s="39" t="n"/>
+      <c r="BP17" s="25" t="n"/>
+      <c r="BQ17" s="27" t="n"/>
       <c r="BR17" s="28" t="n"/>
       <c r="BS17" s="28" t="n"/>
       <c r="BT17" s="28" t="n"/>
-      <c r="BU17" s="38" t="n"/>
+      <c r="BU17" s="25" t="n"/>
       <c r="BV17" s="29" t="n"/>
       <c r="BW17" s="24" t="n"/>
-      <c r="BX17" s="40" t="n">
+      <c r="BX17" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY17" s="39" t="n">
+      <c r="BY17" s="27" t="n">
         <v>0.925926</v>
       </c>
       <c r="BZ17" s="24" t="inlineStr">
@@ -5954,7 +5923,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J18" s="38" t="n"/>
+      <c r="J18" s="25" t="n"/>
       <c r="K18" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -5963,7 +5932,7 @@
       <c r="L18" s="26" t="n">
         <v>111</v>
       </c>
-      <c r="M18" s="39" t="n">
+      <c r="M18" s="27" t="n">
         <v>2.11</v>
       </c>
       <c r="N18" s="28" t="n">
@@ -6003,11 +5972,11 @@
       <c r="X18" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="Y18" s="38" t="n"/>
+      <c r="Y18" s="25" t="n"/>
       <c r="Z18" s="26" t="n"/>
       <c r="AA18" s="28" t="n"/>
       <c r="AB18" s="28" t="n"/>
-      <c r="AC18" s="40" t="n">
+      <c r="AC18" s="30" t="n">
         <v>-1.25</v>
       </c>
       <c r="AD18" s="24" t="inlineStr">
@@ -6144,11 +6113,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ18" s="38" t="n"/>
+      <c r="BJ18" s="25" t="n"/>
       <c r="BK18" s="26" t="n">
         <v>111</v>
       </c>
-      <c r="BL18" s="39" t="n">
+      <c r="BL18" s="27" t="n">
         <v>2.11</v>
       </c>
       <c r="BM18" s="28" t="n">
@@ -6158,18 +6127,18 @@
         <v>0.472637</v>
       </c>
       <c r="BO18" s="28" t="n"/>
-      <c r="BP18" s="38" t="n"/>
-      <c r="BQ18" s="39" t="n"/>
+      <c r="BP18" s="25" t="n"/>
+      <c r="BQ18" s="27" t="n"/>
       <c r="BR18" s="28" t="n"/>
       <c r="BS18" s="28" t="n"/>
       <c r="BT18" s="28" t="n"/>
-      <c r="BU18" s="38" t="n"/>
+      <c r="BU18" s="25" t="n"/>
       <c r="BV18" s="29" t="n"/>
       <c r="BW18" s="24" t="n"/>
-      <c r="BX18" s="40" t="n">
+      <c r="BX18" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY18" s="39" t="n">
+      <c r="BY18" s="27" t="n">
         <v>-1</v>
       </c>
       <c r="BZ18" s="24" t="inlineStr">
@@ -6229,7 +6198,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J19" s="38" t="n"/>
+      <c r="J19" s="25" t="n"/>
       <c r="K19" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -6238,7 +6207,7 @@
       <c r="L19" s="26" t="n">
         <v>-125</v>
       </c>
-      <c r="M19" s="39" t="n">
+      <c r="M19" s="27" t="n">
         <v>1.8</v>
       </c>
       <c r="N19" s="28" t="n">
@@ -6278,11 +6247,11 @@
       <c r="X19" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="Y19" s="38" t="n"/>
+      <c r="Y19" s="25" t="n"/>
       <c r="Z19" s="26" t="n"/>
       <c r="AA19" s="28" t="n"/>
       <c r="AB19" s="28" t="n"/>
-      <c r="AC19" s="40" t="n">
+      <c r="AC19" s="30" t="n">
         <v>1.2</v>
       </c>
       <c r="AD19" s="24" t="inlineStr">
@@ -6419,11 +6388,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ19" s="38" t="n"/>
+      <c r="BJ19" s="25" t="n"/>
       <c r="BK19" s="26" t="n">
         <v>-125</v>
       </c>
-      <c r="BL19" s="39" t="n">
+      <c r="BL19" s="27" t="n">
         <v>1.8</v>
       </c>
       <c r="BM19" s="28" t="n">
@@ -6433,18 +6402,18 @@
         <v>0.552239</v>
       </c>
       <c r="BO19" s="28" t="n"/>
-      <c r="BP19" s="38" t="n"/>
-      <c r="BQ19" s="39" t="n"/>
+      <c r="BP19" s="25" t="n"/>
+      <c r="BQ19" s="27" t="n"/>
       <c r="BR19" s="28" t="n"/>
       <c r="BS19" s="28" t="n"/>
       <c r="BT19" s="28" t="n"/>
-      <c r="BU19" s="38" t="n"/>
+      <c r="BU19" s="25" t="n"/>
       <c r="BV19" s="29" t="n"/>
       <c r="BW19" s="24" t="n"/>
-      <c r="BX19" s="40" t="n">
+      <c r="BX19" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY19" s="39" t="n">
+      <c r="BY19" s="27" t="n">
         <v>0.8</v>
       </c>
       <c r="BZ19" s="24" t="inlineStr">
@@ -6504,7 +6473,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J20" s="38" t="n"/>
+      <c r="J20" s="25" t="n"/>
       <c r="K20" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -6513,7 +6482,7 @@
       <c r="L20" s="26" t="n">
         <v>106</v>
       </c>
-      <c r="M20" s="39" t="n">
+      <c r="M20" s="27" t="n">
         <v>2.06</v>
       </c>
       <c r="N20" s="28" t="n">
@@ -6553,11 +6522,11 @@
       <c r="X20" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y20" s="38" t="n"/>
+      <c r="Y20" s="25" t="n"/>
       <c r="Z20" s="26" t="n"/>
       <c r="AA20" s="28" t="n"/>
       <c r="AB20" s="28" t="n"/>
-      <c r="AC20" s="40" t="n">
+      <c r="AC20" s="30" t="n">
         <v>0.795</v>
       </c>
       <c r="AD20" s="24" t="inlineStr">
@@ -6694,11 +6663,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ20" s="38" t="n"/>
+      <c r="BJ20" s="25" t="n"/>
       <c r="BK20" s="26" t="n">
         <v>106</v>
       </c>
-      <c r="BL20" s="39" t="n">
+      <c r="BL20" s="27" t="n">
         <v>2.06</v>
       </c>
       <c r="BM20" s="28" t="n">
@@ -6708,18 +6677,18 @@
         <v>0.482587</v>
       </c>
       <c r="BO20" s="28" t="n"/>
-      <c r="BP20" s="38" t="n"/>
-      <c r="BQ20" s="39" t="n"/>
+      <c r="BP20" s="25" t="n"/>
+      <c r="BQ20" s="27" t="n"/>
       <c r="BR20" s="28" t="n"/>
       <c r="BS20" s="28" t="n"/>
       <c r="BT20" s="28" t="n"/>
-      <c r="BU20" s="38" t="n"/>
+      <c r="BU20" s="25" t="n"/>
       <c r="BV20" s="29" t="n"/>
       <c r="BW20" s="24" t="n"/>
-      <c r="BX20" s="40" t="n">
+      <c r="BX20" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY20" s="39" t="n">
+      <c r="BY20" s="27" t="n">
         <v>1.06</v>
       </c>
       <c r="BZ20" s="24" t="inlineStr">
@@ -6779,7 +6748,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J21" s="38" t="n"/>
+      <c r="J21" s="25" t="n"/>
       <c r="K21" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -6788,7 +6757,7 @@
       <c r="L21" s="26" t="n">
         <v>-106</v>
       </c>
-      <c r="M21" s="39" t="n">
+      <c r="M21" s="27" t="n">
         <v>1.943396</v>
       </c>
       <c r="N21" s="28" t="n">
@@ -6830,11 +6799,11 @@
       <c r="X21" s="26" t="n">
         <v>10</v>
       </c>
-      <c r="Y21" s="38" t="n"/>
+      <c r="Y21" s="25" t="n"/>
       <c r="Z21" s="26" t="n"/>
       <c r="AA21" s="28" t="n"/>
       <c r="AB21" s="28" t="n"/>
-      <c r="AC21" s="40" t="n">
+      <c r="AC21" s="30" t="n">
         <v>0.9434</v>
       </c>
       <c r="AD21" s="24" t="inlineStr">
@@ -6893,11 +6862,11 @@
         </is>
       </c>
       <c r="BI21" s="24" t="n"/>
-      <c r="BJ21" s="38" t="n"/>
+      <c r="BJ21" s="25" t="n"/>
       <c r="BK21" s="26" t="n">
         <v>-106</v>
       </c>
-      <c r="BL21" s="39" t="n">
+      <c r="BL21" s="27" t="n">
         <v>1.943396</v>
       </c>
       <c r="BM21" s="28" t="n">
@@ -6907,16 +6876,16 @@
         <v>0.5124379999999999</v>
       </c>
       <c r="BO21" s="28" t="n"/>
-      <c r="BP21" s="38" t="n"/>
-      <c r="BQ21" s="39" t="n"/>
+      <c r="BP21" s="25" t="n"/>
+      <c r="BQ21" s="27" t="n"/>
       <c r="BR21" s="28" t="n"/>
       <c r="BS21" s="28" t="n"/>
       <c r="BT21" s="28" t="n"/>
-      <c r="BU21" s="38" t="n"/>
+      <c r="BU21" s="25" t="n"/>
       <c r="BV21" s="29" t="n"/>
       <c r="BW21" s="24" t="n"/>
-      <c r="BX21" s="40" t="n"/>
-      <c r="BY21" s="39" t="n"/>
+      <c r="BX21" s="30" t="n"/>
+      <c r="BY21" s="27" t="n"/>
       <c r="BZ21" s="24" t="n"/>
       <c r="CA21" s="31" t="n"/>
     </row>
@@ -6966,7 +6935,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J22" s="38" t="n"/>
+      <c r="J22" s="25" t="n"/>
       <c r="K22" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -6975,7 +6944,7 @@
       <c r="L22" s="26" t="n">
         <v>-106</v>
       </c>
-      <c r="M22" s="39" t="n">
+      <c r="M22" s="27" t="n">
         <v>1.943396</v>
       </c>
       <c r="N22" s="28" t="n">
@@ -7017,11 +6986,11 @@
       <c r="X22" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="Y22" s="38" t="n"/>
+      <c r="Y22" s="25" t="n"/>
       <c r="Z22" s="26" t="n"/>
       <c r="AA22" s="28" t="n"/>
       <c r="AB22" s="28" t="n"/>
-      <c r="AC22" s="40" t="n">
+      <c r="AC22" s="30" t="n">
         <v>0.9434</v>
       </c>
       <c r="AD22" s="24" t="inlineStr">
@@ -7080,11 +7049,11 @@
         </is>
       </c>
       <c r="BI22" s="24" t="n"/>
-      <c r="BJ22" s="38" t="n"/>
+      <c r="BJ22" s="25" t="n"/>
       <c r="BK22" s="26" t="n">
         <v>-106</v>
       </c>
-      <c r="BL22" s="39" t="n">
+      <c r="BL22" s="27" t="n">
         <v>1.943396</v>
       </c>
       <c r="BM22" s="28" t="n">
@@ -7094,16 +7063,16 @@
         <v>0.5124379999999999</v>
       </c>
       <c r="BO22" s="28" t="n"/>
-      <c r="BP22" s="38" t="n"/>
-      <c r="BQ22" s="39" t="n"/>
+      <c r="BP22" s="25" t="n"/>
+      <c r="BQ22" s="27" t="n"/>
       <c r="BR22" s="28" t="n"/>
       <c r="BS22" s="28" t="n"/>
       <c r="BT22" s="28" t="n"/>
-      <c r="BU22" s="38" t="n"/>
+      <c r="BU22" s="25" t="n"/>
       <c r="BV22" s="29" t="n"/>
       <c r="BW22" s="24" t="n"/>
-      <c r="BX22" s="40" t="n"/>
-      <c r="BY22" s="39" t="n"/>
+      <c r="BX22" s="30" t="n"/>
+      <c r="BY22" s="27" t="n"/>
       <c r="BZ22" s="24" t="n"/>
       <c r="CA22" s="31" t="n"/>
     </row>
@@ -7153,7 +7122,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J23" s="38" t="n"/>
+      <c r="J23" s="25" t="n"/>
       <c r="K23" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -7162,7 +7131,7 @@
       <c r="L23" s="26" t="n">
         <v>-141</v>
       </c>
-      <c r="M23" s="39" t="n">
+      <c r="M23" s="27" t="n">
         <v>1.70922</v>
       </c>
       <c r="N23" s="28" t="n">
@@ -7204,11 +7173,11 @@
       <c r="X23" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y23" s="38" t="n"/>
+      <c r="Y23" s="25" t="n"/>
       <c r="Z23" s="26" t="n"/>
       <c r="AA23" s="28" t="n"/>
       <c r="AB23" s="28" t="n"/>
-      <c r="AC23" s="40" t="n">
+      <c r="AC23" s="30" t="n">
         <v>1.2411</v>
       </c>
       <c r="AD23" s="24" t="inlineStr">
@@ -7267,11 +7236,11 @@
         </is>
       </c>
       <c r="BI23" s="24" t="n"/>
-      <c r="BJ23" s="38" t="n"/>
+      <c r="BJ23" s="25" t="n"/>
       <c r="BK23" s="26" t="n">
         <v>-141</v>
       </c>
-      <c r="BL23" s="39" t="n">
+      <c r="BL23" s="27" t="n">
         <v>1.70922</v>
       </c>
       <c r="BM23" s="28" t="n">
@@ -7281,16 +7250,16 @@
         <v>0.58209</v>
       </c>
       <c r="BO23" s="28" t="n"/>
-      <c r="BP23" s="38" t="n"/>
-      <c r="BQ23" s="39" t="n"/>
+      <c r="BP23" s="25" t="n"/>
+      <c r="BQ23" s="27" t="n"/>
       <c r="BR23" s="28" t="n"/>
       <c r="BS23" s="28" t="n"/>
       <c r="BT23" s="28" t="n"/>
-      <c r="BU23" s="38" t="n"/>
+      <c r="BU23" s="25" t="n"/>
       <c r="BV23" s="29" t="n"/>
       <c r="BW23" s="24" t="n"/>
-      <c r="BX23" s="40" t="n"/>
-      <c r="BY23" s="39" t="n"/>
+      <c r="BX23" s="30" t="n"/>
+      <c r="BY23" s="27" t="n"/>
       <c r="BZ23" s="24" t="n"/>
       <c r="CA23" s="31" t="n"/>
     </row>
@@ -7340,7 +7309,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J24" s="38" t="n"/>
+      <c r="J24" s="25" t="n"/>
       <c r="K24" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -7349,7 +7318,7 @@
       <c r="L24" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="M24" s="39" t="n">
+      <c r="M24" s="27" t="n">
         <v>1.75188</v>
       </c>
       <c r="N24" s="28" t="n">
@@ -7391,11 +7360,11 @@
       <c r="X24" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y24" s="38" t="n"/>
+      <c r="Y24" s="25" t="n"/>
       <c r="Z24" s="26" t="n"/>
       <c r="AA24" s="28" t="n"/>
       <c r="AB24" s="28" t="n"/>
-      <c r="AC24" s="40" t="n">
+      <c r="AC24" s="30" t="n">
         <v>-1.5</v>
       </c>
       <c r="AD24" s="24" t="inlineStr">
@@ -7454,11 +7423,11 @@
         </is>
       </c>
       <c r="BI24" s="24" t="n"/>
-      <c r="BJ24" s="38" t="n"/>
+      <c r="BJ24" s="25" t="n"/>
       <c r="BK24" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="BL24" s="39" t="n">
+      <c r="BL24" s="27" t="n">
         <v>1.75188</v>
       </c>
       <c r="BM24" s="28" t="n">
@@ -7468,16 +7437,16 @@
         <v>0.567164</v>
       </c>
       <c r="BO24" s="28" t="n"/>
-      <c r="BP24" s="38" t="n"/>
-      <c r="BQ24" s="39" t="n"/>
+      <c r="BP24" s="25" t="n"/>
+      <c r="BQ24" s="27" t="n"/>
       <c r="BR24" s="28" t="n"/>
       <c r="BS24" s="28" t="n"/>
       <c r="BT24" s="28" t="n"/>
-      <c r="BU24" s="38" t="n"/>
+      <c r="BU24" s="25" t="n"/>
       <c r="BV24" s="29" t="n"/>
       <c r="BW24" s="24" t="n"/>
-      <c r="BX24" s="40" t="n"/>
-      <c r="BY24" s="39" t="n"/>
+      <c r="BX24" s="30" t="n"/>
+      <c r="BY24" s="27" t="n"/>
       <c r="BZ24" s="24" t="n"/>
       <c r="CA24" s="31" t="n"/>
     </row>
@@ -7527,7 +7496,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J25" s="38" t="n"/>
+      <c r="J25" s="25" t="n"/>
       <c r="K25" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -7536,7 +7505,7 @@
       <c r="L25" s="26" t="n">
         <v>104</v>
       </c>
-      <c r="M25" s="39" t="n">
+      <c r="M25" s="27" t="n">
         <v>2.04</v>
       </c>
       <c r="N25" s="28" t="n">
@@ -7578,11 +7547,11 @@
       <c r="X25" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y25" s="38" t="n"/>
+      <c r="Y25" s="25" t="n"/>
       <c r="Z25" s="26" t="n"/>
       <c r="AA25" s="28" t="n"/>
       <c r="AB25" s="28" t="n"/>
-      <c r="AC25" s="40" t="n">
+      <c r="AC25" s="30" t="n">
         <v>1.3</v>
       </c>
       <c r="AD25" s="24" t="inlineStr">
@@ -7641,11 +7610,11 @@
         </is>
       </c>
       <c r="BI25" s="24" t="n"/>
-      <c r="BJ25" s="38" t="n"/>
+      <c r="BJ25" s="25" t="n"/>
       <c r="BK25" s="26" t="n">
         <v>104</v>
       </c>
-      <c r="BL25" s="39" t="n">
+      <c r="BL25" s="27" t="n">
         <v>2.04</v>
       </c>
       <c r="BM25" s="28" t="n">
@@ -7655,16 +7624,16 @@
         <v>0.487562</v>
       </c>
       <c r="BO25" s="28" t="n"/>
-      <c r="BP25" s="38" t="n"/>
-      <c r="BQ25" s="39" t="n"/>
+      <c r="BP25" s="25" t="n"/>
+      <c r="BQ25" s="27" t="n"/>
       <c r="BR25" s="28" t="n"/>
       <c r="BS25" s="28" t="n"/>
       <c r="BT25" s="28" t="n"/>
-      <c r="BU25" s="38" t="n"/>
+      <c r="BU25" s="25" t="n"/>
       <c r="BV25" s="29" t="n"/>
       <c r="BW25" s="24" t="n"/>
-      <c r="BX25" s="40" t="n"/>
-      <c r="BY25" s="39" t="n"/>
+      <c r="BX25" s="30" t="n"/>
+      <c r="BY25" s="27" t="n"/>
       <c r="BZ25" s="24" t="n"/>
       <c r="CA25" s="31" t="n"/>
     </row>
@@ -7714,7 +7683,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J26" s="38" t="n"/>
+      <c r="J26" s="25" t="n"/>
       <c r="K26" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -7723,7 +7692,7 @@
       <c r="L26" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="M26" s="39" t="n">
+      <c r="M26" s="27" t="n">
         <v>1.961538</v>
       </c>
       <c r="N26" s="28" t="n">
@@ -7765,11 +7734,11 @@
       <c r="X26" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="Y26" s="38" t="n"/>
+      <c r="Y26" s="25" t="n"/>
       <c r="Z26" s="26" t="n"/>
       <c r="AA26" s="28" t="n"/>
       <c r="AB26" s="28" t="n"/>
-      <c r="AC26" s="40" t="n">
+      <c r="AC26" s="30" t="n">
         <v>0.9615</v>
       </c>
       <c r="AD26" s="24" t="inlineStr">
@@ -7828,11 +7797,11 @@
         </is>
       </c>
       <c r="BI26" s="24" t="n"/>
-      <c r="BJ26" s="38" t="n"/>
+      <c r="BJ26" s="25" t="n"/>
       <c r="BK26" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="BL26" s="39" t="n">
+      <c r="BL26" s="27" t="n">
         <v>1.961538</v>
       </c>
       <c r="BM26" s="28" t="n">
@@ -7842,16 +7811,16 @@
         <v>0.507463</v>
       </c>
       <c r="BO26" s="28" t="n"/>
-      <c r="BP26" s="38" t="n"/>
-      <c r="BQ26" s="39" t="n"/>
+      <c r="BP26" s="25" t="n"/>
+      <c r="BQ26" s="27" t="n"/>
       <c r="BR26" s="28" t="n"/>
       <c r="BS26" s="28" t="n"/>
       <c r="BT26" s="28" t="n"/>
-      <c r="BU26" s="38" t="n"/>
+      <c r="BU26" s="25" t="n"/>
       <c r="BV26" s="29" t="n"/>
       <c r="BW26" s="24" t="n"/>
-      <c r="BX26" s="40" t="n"/>
-      <c r="BY26" s="39" t="n"/>
+      <c r="BX26" s="30" t="n"/>
+      <c r="BY26" s="27" t="n"/>
       <c r="BZ26" s="24" t="n"/>
       <c r="CA26" s="31" t="n"/>
     </row>
@@ -7901,7 +7870,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J27" s="38" t="n"/>
+      <c r="J27" s="25" t="n"/>
       <c r="K27" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -7910,7 +7879,7 @@
       <c r="L27" s="26" t="n">
         <v>120</v>
       </c>
-      <c r="M27" s="39" t="n">
+      <c r="M27" s="27" t="n">
         <v>2.2</v>
       </c>
       <c r="N27" s="28" t="n">
@@ -7952,11 +7921,11 @@
       <c r="X27" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="Y27" s="38" t="n"/>
+      <c r="Y27" s="25" t="n"/>
       <c r="Z27" s="26" t="n"/>
       <c r="AA27" s="28" t="n"/>
       <c r="AB27" s="28" t="n"/>
-      <c r="AC27" s="40" t="n">
+      <c r="AC27" s="30" t="n">
         <v>-0.75</v>
       </c>
       <c r="AD27" s="24" t="inlineStr">
@@ -8015,11 +7984,11 @@
         </is>
       </c>
       <c r="BI27" s="24" t="n"/>
-      <c r="BJ27" s="38" t="n"/>
+      <c r="BJ27" s="25" t="n"/>
       <c r="BK27" s="26" t="n">
         <v>120</v>
       </c>
-      <c r="BL27" s="39" t="n">
+      <c r="BL27" s="27" t="n">
         <v>2.2</v>
       </c>
       <c r="BM27" s="28" t="n">
@@ -8029,16 +7998,16 @@
         <v>0.452736</v>
       </c>
       <c r="BO27" s="28" t="n"/>
-      <c r="BP27" s="38" t="n"/>
-      <c r="BQ27" s="39" t="n"/>
+      <c r="BP27" s="25" t="n"/>
+      <c r="BQ27" s="27" t="n"/>
       <c r="BR27" s="28" t="n"/>
       <c r="BS27" s="28" t="n"/>
       <c r="BT27" s="28" t="n"/>
-      <c r="BU27" s="38" t="n"/>
+      <c r="BU27" s="25" t="n"/>
       <c r="BV27" s="29" t="n"/>
       <c r="BW27" s="24" t="n"/>
-      <c r="BX27" s="40" t="n"/>
-      <c r="BY27" s="39" t="n"/>
+      <c r="BX27" s="30" t="n"/>
+      <c r="BY27" s="27" t="n"/>
       <c r="BZ27" s="24" t="n"/>
       <c r="CA27" s="31" t="n"/>
     </row>
@@ -8088,7 +8057,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J28" s="38" t="n"/>
+      <c r="J28" s="25" t="n"/>
       <c r="K28" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -8097,7 +8066,7 @@
       <c r="L28" s="26" t="n">
         <v>100</v>
       </c>
-      <c r="M28" s="39" t="n">
+      <c r="M28" s="27" t="n">
         <v>2</v>
       </c>
       <c r="N28" s="28" t="n">
@@ -8139,11 +8108,11 @@
       <c r="X28" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="Y28" s="38" t="n"/>
+      <c r="Y28" s="25" t="n"/>
       <c r="Z28" s="26" t="n"/>
       <c r="AA28" s="28" t="n"/>
       <c r="AB28" s="28" t="n"/>
-      <c r="AC28" s="40" t="n">
+      <c r="AC28" s="30" t="n">
         <v>-0.75</v>
       </c>
       <c r="AD28" s="24" t="inlineStr">
@@ -8202,11 +8171,11 @@
         </is>
       </c>
       <c r="BI28" s="24" t="n"/>
-      <c r="BJ28" s="38" t="n"/>
+      <c r="BJ28" s="25" t="n"/>
       <c r="BK28" s="26" t="n">
         <v>100</v>
       </c>
-      <c r="BL28" s="39" t="n">
+      <c r="BL28" s="27" t="n">
         <v>2</v>
       </c>
       <c r="BM28" s="28" t="n">
@@ -8216,16 +8185,16 @@
         <v>0.497512</v>
       </c>
       <c r="BO28" s="28" t="n"/>
-      <c r="BP28" s="38" t="n"/>
-      <c r="BQ28" s="39" t="n"/>
+      <c r="BP28" s="25" t="n"/>
+      <c r="BQ28" s="27" t="n"/>
       <c r="BR28" s="28" t="n"/>
       <c r="BS28" s="28" t="n"/>
       <c r="BT28" s="28" t="n"/>
-      <c r="BU28" s="38" t="n"/>
+      <c r="BU28" s="25" t="n"/>
       <c r="BV28" s="29" t="n"/>
       <c r="BW28" s="24" t="n"/>
-      <c r="BX28" s="40" t="n"/>
-      <c r="BY28" s="39" t="n"/>
+      <c r="BX28" s="30" t="n"/>
+      <c r="BY28" s="27" t="n"/>
       <c r="BZ28" s="24" t="n"/>
       <c r="CA28" s="31" t="n"/>
     </row>
@@ -8275,7 +8244,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J29" s="38" t="n"/>
+      <c r="J29" s="25" t="n"/>
       <c r="K29" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -8284,7 +8253,7 @@
       <c r="L29" s="26" t="n">
         <v>108</v>
       </c>
-      <c r="M29" s="39" t="n">
+      <c r="M29" s="27" t="n">
         <v>2.08</v>
       </c>
       <c r="N29" s="28" t="n">
@@ -8324,11 +8293,11 @@
       <c r="X29" s="26" t="n">
         <v>8</v>
       </c>
-      <c r="Y29" s="38" t="n"/>
+      <c r="Y29" s="25" t="n"/>
       <c r="Z29" s="26" t="n"/>
       <c r="AA29" s="28" t="n"/>
       <c r="AB29" s="28" t="n"/>
-      <c r="AC29" s="40" t="n">
+      <c r="AC29" s="30" t="n">
         <v>1.35</v>
       </c>
       <c r="AD29" s="24" t="inlineStr">
@@ -8465,11 +8434,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ29" s="38" t="n"/>
+      <c r="BJ29" s="25" t="n"/>
       <c r="BK29" s="26" t="n">
         <v>108</v>
       </c>
-      <c r="BL29" s="39" t="n">
+      <c r="BL29" s="27" t="n">
         <v>2.08</v>
       </c>
       <c r="BM29" s="28" t="n">
@@ -8479,18 +8448,18 @@
         <v>0.477612</v>
       </c>
       <c r="BO29" s="28" t="n"/>
-      <c r="BP29" s="38" t="n"/>
-      <c r="BQ29" s="39" t="n"/>
+      <c r="BP29" s="25" t="n"/>
+      <c r="BQ29" s="27" t="n"/>
       <c r="BR29" s="28" t="n"/>
       <c r="BS29" s="28" t="n"/>
       <c r="BT29" s="28" t="n"/>
-      <c r="BU29" s="38" t="n"/>
+      <c r="BU29" s="25" t="n"/>
       <c r="BV29" s="29" t="n"/>
       <c r="BW29" s="24" t="n"/>
-      <c r="BX29" s="40" t="n">
+      <c r="BX29" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY29" s="39" t="n">
+      <c r="BY29" s="27" t="n">
         <v>1.08</v>
       </c>
       <c r="BZ29" s="24" t="inlineStr">
@@ -8550,7 +8519,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J30" s="38" t="n"/>
+      <c r="J30" s="25" t="n"/>
       <c r="K30" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -8559,7 +8528,7 @@
       <c r="L30" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="M30" s="39" t="n">
+      <c r="M30" s="27" t="n">
         <v>1.75188</v>
       </c>
       <c r="N30" s="28" t="n">
@@ -8599,11 +8568,11 @@
       <c r="X30" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="Y30" s="38" t="n"/>
+      <c r="Y30" s="25" t="n"/>
       <c r="Z30" s="26" t="n"/>
       <c r="AA30" s="28" t="n"/>
       <c r="AB30" s="28" t="n"/>
-      <c r="AC30" s="40" t="n">
+      <c r="AC30" s="30" t="n">
         <v>1.1278</v>
       </c>
       <c r="AD30" s="24" t="inlineStr">
@@ -8740,11 +8709,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ30" s="38" t="n"/>
+      <c r="BJ30" s="25" t="n"/>
       <c r="BK30" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="BL30" s="39" t="n">
+      <c r="BL30" s="27" t="n">
         <v>1.75188</v>
       </c>
       <c r="BM30" s="28" t="n">
@@ -8754,18 +8723,18 @@
         <v>0.567164</v>
       </c>
       <c r="BO30" s="28" t="n"/>
-      <c r="BP30" s="38" t="n"/>
-      <c r="BQ30" s="39" t="n"/>
+      <c r="BP30" s="25" t="n"/>
+      <c r="BQ30" s="27" t="n"/>
       <c r="BR30" s="28" t="n"/>
       <c r="BS30" s="28" t="n"/>
       <c r="BT30" s="28" t="n"/>
-      <c r="BU30" s="38" t="n"/>
+      <c r="BU30" s="25" t="n"/>
       <c r="BV30" s="29" t="n"/>
       <c r="BW30" s="24" t="n"/>
-      <c r="BX30" s="40" t="n">
+      <c r="BX30" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY30" s="39" t="n">
+      <c r="BY30" s="27" t="n">
         <v>0.75188</v>
       </c>
       <c r="BZ30" s="24" t="inlineStr">
@@ -8825,7 +8794,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J31" s="38" t="n"/>
+      <c r="J31" s="25" t="n"/>
       <c r="K31" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -8834,7 +8803,7 @@
       <c r="L31" s="26" t="n">
         <v>130</v>
       </c>
-      <c r="M31" s="39" t="n">
+      <c r="M31" s="27" t="n">
         <v>2.3</v>
       </c>
       <c r="N31" s="28" t="n">
@@ -8874,11 +8843,11 @@
       <c r="X31" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y31" s="38" t="n"/>
+      <c r="Y31" s="25" t="n"/>
       <c r="Z31" s="26" t="n"/>
       <c r="AA31" s="28" t="n"/>
       <c r="AB31" s="28" t="n"/>
-      <c r="AC31" s="40" t="n">
+      <c r="AC31" s="30" t="n">
         <v>-1</v>
       </c>
       <c r="AD31" s="24" t="inlineStr">
@@ -9015,11 +8984,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ31" s="38" t="n"/>
+      <c r="BJ31" s="25" t="n"/>
       <c r="BK31" s="26" t="n">
         <v>130</v>
       </c>
-      <c r="BL31" s="39" t="n">
+      <c r="BL31" s="27" t="n">
         <v>2.3</v>
       </c>
       <c r="BM31" s="28" t="n">
@@ -9029,18 +8998,18 @@
         <v>0.432836</v>
       </c>
       <c r="BO31" s="28" t="n"/>
-      <c r="BP31" s="38" t="n"/>
-      <c r="BQ31" s="39" t="n"/>
+      <c r="BP31" s="25" t="n"/>
+      <c r="BQ31" s="27" t="n"/>
       <c r="BR31" s="28" t="n"/>
       <c r="BS31" s="28" t="n"/>
       <c r="BT31" s="28" t="n"/>
-      <c r="BU31" s="38" t="n"/>
+      <c r="BU31" s="25" t="n"/>
       <c r="BV31" s="29" t="n"/>
       <c r="BW31" s="24" t="n"/>
-      <c r="BX31" s="40" t="n">
+      <c r="BX31" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY31" s="39" t="n">
+      <c r="BY31" s="27" t="n">
         <v>-1</v>
       </c>
       <c r="BZ31" s="24" t="inlineStr">
@@ -9057,12 +9026,12 @@
     <row r="32" ht="36" customHeight="1">
       <c r="A32" s="24" t="inlineStr">
         <is>
-          <t>3b298c42597d4a62</t>
+          <t>ad621924660a4d49</t>
         </is>
       </c>
       <c r="B32" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T15:22:23.198190Z</t>
+          <t>2026-07-20T15:44:08.951770Z</t>
         </is>
       </c>
       <c r="C32" s="24" t="inlineStr">
@@ -9100,30 +9069,30 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J32" s="38" t="n"/>
+      <c r="J32" s="25" t="n"/>
       <c r="K32" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
         </is>
       </c>
       <c r="L32" s="26" t="n">
-        <v>111</v>
-      </c>
-      <c r="M32" s="39" t="n">
-        <v>2.11</v>
+        <v>113</v>
+      </c>
+      <c r="M32" s="27" t="n">
+        <v>2.13</v>
       </c>
       <c r="N32" s="28" t="n">
-        <v>0.473934</v>
+        <v>0.469484</v>
       </c>
       <c r="O32" s="28" t="n">
         <v>0.5726869999999999</v>
       </c>
       <c r="P32" s="28" t="n"/>
       <c r="Q32" s="28" t="n">
-        <v>0.09875299999999999</v>
+        <v>0.103203</v>
       </c>
       <c r="R32" s="26" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="S32" s="29" t="n">
         <v>1.25</v>
@@ -9141,15 +9110,15 @@
       <c r="V32" s="24" t="n"/>
       <c r="W32" s="26" t="n"/>
       <c r="X32" s="26" t="n"/>
-      <c r="Y32" s="38" t="n"/>
+      <c r="Y32" s="25" t="n"/>
       <c r="Z32" s="26" t="n"/>
       <c r="AA32" s="28" t="n"/>
       <c r="AB32" s="28" t="n"/>
-      <c r="AC32" s="40" t="n"/>
+      <c r="AC32" s="30" t="n"/>
       <c r="AD32" s="24" t="n"/>
       <c r="AE32" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5500; executable ask 0.4750 (aec-mlb-min-cle-2026-07-20).</t>
+          <t>Learned LR call at threshold 0.5500; executable ask 0.4700 (aec-mlb-min-cle-2026-07-20).</t>
         </is>
       </c>
       <c r="AF32" s="31" t="inlineStr">
@@ -9268,7 +9237,7 @@
       </c>
       <c r="BH32" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T14:57:32.219947Z</t>
+          <t>2026-07-20T15:40:37.473344Z</t>
         </is>
       </c>
       <c r="BI32" s="24" t="inlineStr">
@@ -9276,42 +9245,42 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ32" s="38" t="n"/>
+      <c r="BJ32" s="25" t="n"/>
       <c r="BK32" s="26" t="n">
-        <v>111</v>
-      </c>
-      <c r="BL32" s="39" t="n">
-        <v>2.11</v>
+        <v>113</v>
+      </c>
+      <c r="BL32" s="27" t="n">
+        <v>2.13</v>
       </c>
       <c r="BM32" s="28" t="n">
-        <v>0.473934</v>
+        <v>0.469484</v>
       </c>
       <c r="BN32" s="28" t="n">
-        <v>0.472637</v>
+        <v>0.467662</v>
       </c>
       <c r="BO32" s="28" t="n"/>
-      <c r="BP32" s="38" t="n"/>
-      <c r="BQ32" s="39" t="n"/>
+      <c r="BP32" s="25" t="n"/>
+      <c r="BQ32" s="27" t="n"/>
       <c r="BR32" s="28" t="n"/>
       <c r="BS32" s="28" t="n"/>
       <c r="BT32" s="28" t="n"/>
-      <c r="BU32" s="38" t="n"/>
+      <c r="BU32" s="25" t="n"/>
       <c r="BV32" s="29" t="n"/>
       <c r="BW32" s="24" t="n"/>
-      <c r="BX32" s="40" t="n"/>
-      <c r="BY32" s="39" t="n"/>
+      <c r="BX32" s="30" t="n"/>
+      <c r="BY32" s="27" t="n"/>
       <c r="BZ32" s="24" t="n"/>
       <c r="CA32" s="31" t="n"/>
     </row>
     <row r="33" ht="36" customHeight="1">
       <c r="A33" s="24" t="inlineStr">
         <is>
-          <t>81ad16e9351d4806</t>
+          <t>a72d0dab60924d62</t>
         </is>
       </c>
       <c r="B33" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T15:22:23.198190Z</t>
+          <t>2026-07-20T15:44:08.951770Z</t>
         </is>
       </c>
       <c r="C33" s="24" t="inlineStr">
@@ -9349,7 +9318,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J33" s="38" t="n"/>
+      <c r="J33" s="25" t="n"/>
       <c r="K33" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -9358,7 +9327,7 @@
       <c r="L33" s="26" t="n">
         <v>-108</v>
       </c>
-      <c r="M33" s="39" t="n">
+      <c r="M33" s="27" t="n">
         <v>1.925926</v>
       </c>
       <c r="N33" s="28" t="n">
@@ -9390,11 +9359,11 @@
       <c r="V33" s="24" t="n"/>
       <c r="W33" s="26" t="n"/>
       <c r="X33" s="26" t="n"/>
-      <c r="Y33" s="38" t="n"/>
+      <c r="Y33" s="25" t="n"/>
       <c r="Z33" s="26" t="n"/>
       <c r="AA33" s="28" t="n"/>
       <c r="AB33" s="28" t="n"/>
-      <c r="AC33" s="40" t="n"/>
+      <c r="AC33" s="30" t="n"/>
       <c r="AD33" s="24" t="n"/>
       <c r="AE33" s="31" t="inlineStr">
         <is>
@@ -9517,7 +9486,7 @@
       </c>
       <c r="BH33" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T14:57:35.056972Z</t>
+          <t>2026-07-20T15:40:38.983839Z</t>
         </is>
       </c>
       <c r="BI33" s="24" t="inlineStr">
@@ -9525,11 +9494,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ33" s="38" t="n"/>
+      <c r="BJ33" s="25" t="n"/>
       <c r="BK33" s="26" t="n">
         <v>-108</v>
       </c>
-      <c r="BL33" s="39" t="n">
+      <c r="BL33" s="27" t="n">
         <v>1.925926</v>
       </c>
       <c r="BM33" s="28" t="n">
@@ -9539,28 +9508,28 @@
         <v>0.517413</v>
       </c>
       <c r="BO33" s="28" t="n"/>
-      <c r="BP33" s="38" t="n"/>
-      <c r="BQ33" s="39" t="n"/>
+      <c r="BP33" s="25" t="n"/>
+      <c r="BQ33" s="27" t="n"/>
       <c r="BR33" s="28" t="n"/>
       <c r="BS33" s="28" t="n"/>
       <c r="BT33" s="28" t="n"/>
-      <c r="BU33" s="38" t="n"/>
+      <c r="BU33" s="25" t="n"/>
       <c r="BV33" s="29" t="n"/>
       <c r="BW33" s="24" t="n"/>
-      <c r="BX33" s="40" t="n"/>
-      <c r="BY33" s="39" t="n"/>
+      <c r="BX33" s="30" t="n"/>
+      <c r="BY33" s="27" t="n"/>
       <c r="BZ33" s="24" t="n"/>
       <c r="CA33" s="31" t="n"/>
     </row>
     <row r="34" ht="36" customHeight="1">
       <c r="A34" s="24" t="inlineStr">
         <is>
-          <t>d928b5795af74522</t>
+          <t>f96e5bd1ebcc4c62</t>
         </is>
       </c>
       <c r="B34" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T15:22:23.198190Z</t>
+          <t>2026-07-20T15:44:08.951770Z</t>
         </is>
       </c>
       <c r="C34" s="24" t="inlineStr">
@@ -9598,7 +9567,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J34" s="38" t="n"/>
+      <c r="J34" s="25" t="n"/>
       <c r="K34" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -9607,7 +9576,7 @@
       <c r="L34" s="26" t="n">
         <v>-108</v>
       </c>
-      <c r="M34" s="39" t="n">
+      <c r="M34" s="27" t="n">
         <v>1.925926</v>
       </c>
       <c r="N34" s="28" t="n">
@@ -9639,11 +9608,11 @@
       <c r="V34" s="24" t="n"/>
       <c r="W34" s="26" t="n"/>
       <c r="X34" s="26" t="n"/>
-      <c r="Y34" s="38" t="n"/>
+      <c r="Y34" s="25" t="n"/>
       <c r="Z34" s="26" t="n"/>
       <c r="AA34" s="28" t="n"/>
       <c r="AB34" s="28" t="n"/>
-      <c r="AC34" s="40" t="n"/>
+      <c r="AC34" s="30" t="n"/>
       <c r="AD34" s="24" t="n"/>
       <c r="AE34" s="31" t="inlineStr">
         <is>
@@ -9766,7 +9735,7 @@
       </c>
       <c r="BH34" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T14:57:46.871986Z</t>
+          <t>2026-07-20T15:40:51.564498Z</t>
         </is>
       </c>
       <c r="BI34" s="24" t="inlineStr">
@@ -9774,42 +9743,42 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ34" s="38" t="n"/>
+      <c r="BJ34" s="25" t="n"/>
       <c r="BK34" s="26" t="n">
         <v>-108</v>
       </c>
-      <c r="BL34" s="39" t="n">
+      <c r="BL34" s="27" t="n">
         <v>1.925926</v>
       </c>
       <c r="BM34" s="28" t="n">
         <v>0.519231</v>
       </c>
       <c r="BN34" s="28" t="n">
-        <v>0.517413</v>
+        <v>0.5148509999999999</v>
       </c>
       <c r="BO34" s="28" t="n"/>
-      <c r="BP34" s="38" t="n"/>
-      <c r="BQ34" s="39" t="n"/>
+      <c r="BP34" s="25" t="n"/>
+      <c r="BQ34" s="27" t="n"/>
       <c r="BR34" s="28" t="n"/>
       <c r="BS34" s="28" t="n"/>
       <c r="BT34" s="28" t="n"/>
-      <c r="BU34" s="38" t="n"/>
+      <c r="BU34" s="25" t="n"/>
       <c r="BV34" s="29" t="n"/>
       <c r="BW34" s="24" t="n"/>
-      <c r="BX34" s="40" t="n"/>
-      <c r="BY34" s="39" t="n"/>
+      <c r="BX34" s="30" t="n"/>
+      <c r="BY34" s="27" t="n"/>
       <c r="BZ34" s="24" t="n"/>
       <c r="CA34" s="31" t="n"/>
     </row>
     <row r="35" ht="36" customHeight="1">
       <c r="A35" s="24" t="inlineStr">
         <is>
-          <t>1b170fab0ebb46ee</t>
+          <t>147749d13cbd4451</t>
         </is>
       </c>
       <c r="B35" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T15:28:43.848060Z</t>
+          <t>2026-07-20T15:44:12.511288Z</t>
         </is>
       </c>
       <c r="C35" s="24" t="inlineStr">
@@ -9847,27 +9816,27 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J35" s="38" t="n"/>
+      <c r="J35" s="25" t="n"/>
       <c r="K35" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
         </is>
       </c>
       <c r="L35" s="26" t="n">
-        <v>156</v>
-      </c>
-      <c r="M35" s="39" t="n">
-        <v>2.56</v>
+        <v>150</v>
+      </c>
+      <c r="M35" s="27" t="n">
+        <v>2.5</v>
       </c>
       <c r="N35" s="28" t="n">
-        <v>0.390625</v>
+        <v>0.4</v>
       </c>
       <c r="O35" s="28" t="n">
         <v>0.688998</v>
       </c>
       <c r="P35" s="28" t="n"/>
       <c r="Q35" s="28" t="n">
-        <v>0.298373</v>
+        <v>0.288998</v>
       </c>
       <c r="R35" s="26" t="n">
         <v>100</v>
@@ -9888,15 +9857,15 @@
       <c r="V35" s="24" t="n"/>
       <c r="W35" s="26" t="n"/>
       <c r="X35" s="26" t="n"/>
-      <c r="Y35" s="38" t="n"/>
+      <c r="Y35" s="25" t="n"/>
       <c r="Z35" s="26" t="n"/>
       <c r="AA35" s="28" t="n"/>
       <c r="AB35" s="28" t="n"/>
-      <c r="AC35" s="40" t="n"/>
+      <c r="AC35" s="30" t="n"/>
       <c r="AD35" s="24" t="n"/>
       <c r="AE35" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5051; executable ask 0.3900 (aec-wnba-ny-dal-2026-07-20).</t>
+          <t>Learned LR call at threshold 0.5051; executable ask 0.4000 (aec-wnba-ny-dal-2026-07-20).</t>
         </is>
       </c>
       <c r="AF35" s="31" t="inlineStr">
@@ -10015,7 +9984,7 @@
       </c>
       <c r="BH35" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T14:57:58.731031Z</t>
+          <t>2026-07-20T15:41:03.863692Z</t>
         </is>
       </c>
       <c r="BI35" s="24" t="inlineStr">
@@ -10023,32 +9992,2008 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ35" s="38" t="n"/>
+      <c r="BJ35" s="25" t="n"/>
       <c r="BK35" s="26" t="n">
-        <v>156</v>
-      </c>
-      <c r="BL35" s="39" t="n">
-        <v>2.56</v>
+        <v>150</v>
+      </c>
+      <c r="BL35" s="27" t="n">
+        <v>2.5</v>
       </c>
       <c r="BM35" s="28" t="n">
-        <v>0.390625</v>
+        <v>0.4</v>
       </c>
       <c r="BN35" s="28" t="n">
-        <v>0.386139</v>
+        <v>0.39604</v>
       </c>
       <c r="BO35" s="28" t="n"/>
-      <c r="BP35" s="38" t="n"/>
-      <c r="BQ35" s="39" t="n"/>
+      <c r="BP35" s="25" t="n"/>
+      <c r="BQ35" s="27" t="n"/>
       <c r="BR35" s="28" t="n"/>
       <c r="BS35" s="28" t="n"/>
       <c r="BT35" s="28" t="n"/>
-      <c r="BU35" s="38" t="n"/>
+      <c r="BU35" s="25" t="n"/>
       <c r="BV35" s="29" t="n"/>
       <c r="BW35" s="24" t="n"/>
-      <c r="BX35" s="40" t="n"/>
-      <c r="BY35" s="39" t="n"/>
+      <c r="BX35" s="30" t="n"/>
+      <c r="BY35" s="27" t="n"/>
       <c r="BZ35" s="24" t="n"/>
       <c r="CA35" s="31" t="n"/>
+    </row>
+    <row r="36" ht="36" customHeight="1">
+      <c r="A36" s="24" t="inlineStr">
+        <is>
+          <t>8a8477c2b92442e1</t>
+        </is>
+      </c>
+      <c r="B36" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T16:18:24.995882Z</t>
+        </is>
+      </c>
+      <c r="C36" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="D36" s="24" t="inlineStr">
+        <is>
+          <t>54491</t>
+        </is>
+      </c>
+      <c r="E36" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F36" s="24" t="inlineStr">
+        <is>
+          <t>KaBuM! Ilha das Lendas</t>
+        </is>
+      </c>
+      <c r="G36" s="24" t="inlineStr">
+        <is>
+          <t>Vivo Keyd Stars Academy</t>
+        </is>
+      </c>
+      <c r="H36" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I36" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J36" s="25" t="n"/>
+      <c r="K36" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L36" s="26" t="n">
+        <v>144</v>
+      </c>
+      <c r="M36" s="27" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="N36" s="28" t="n">
+        <v>0.409836</v>
+      </c>
+      <c r="O36" s="28" t="n">
+        <v>0.555003</v>
+      </c>
+      <c r="P36" s="28" t="n"/>
+      <c r="Q36" s="28" t="n">
+        <v>0.145003</v>
+      </c>
+      <c r="R36" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S36" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T36" s="24" t="inlineStr">
+        <is>
+          <t>lol-neutral-series-elo-v1</t>
+        </is>
+      </c>
+      <c r="U36" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V36" s="24" t="n"/>
+      <c r="W36" s="26" t="n"/>
+      <c r="X36" s="26" t="n"/>
+      <c r="Y36" s="25" t="n"/>
+      <c r="Z36" s="26" t="n"/>
+      <c r="AA36" s="28" t="n"/>
+      <c r="AB36" s="28" t="n"/>
+      <c r="AC36" s="30" t="n"/>
+      <c r="AD36" s="24" t="n"/>
+      <c r="AE36" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4100 (aec-lol-vksa-kbm-2026-07-20).</t>
+        </is>
+      </c>
+      <c r="AF36" s="31" t="inlineStr">
+        <is>
+          <t>Research baseline; zero-unit shadow until qualified.</t>
+        </is>
+      </c>
+      <c r="AG36" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH36" s="24" t="n"/>
+      <c r="AI36" s="31" t="n"/>
+      <c r="AJ36" s="31" t="n"/>
+      <c r="AK36" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL36" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM36" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN36" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO36" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP36" s="24" t="inlineStr">
+        <is>
+          <t>KaBuM! Ilha das Lendas</t>
+        </is>
+      </c>
+      <c r="AQ36" s="24" t="inlineStr">
+        <is>
+          <t>KaBuM! Ilha das Lendas</t>
+        </is>
+      </c>
+      <c r="AR36" s="24" t="inlineStr">
+        <is>
+          <t>KaBuM! Ilha das Lendas</t>
+        </is>
+      </c>
+      <c r="AS36" s="24" t="inlineStr">
+        <is>
+          <t>Vivo Keyd Stars Academy</t>
+        </is>
+      </c>
+      <c r="AT36" s="24" t="inlineStr">
+        <is>
+          <t>Vivo Keyd Stars Academy</t>
+        </is>
+      </c>
+      <c r="AU36" s="24" t="inlineStr">
+        <is>
+          <t>Vivo Keyd Stars Academy</t>
+        </is>
+      </c>
+      <c r="AV36" s="24" t="n"/>
+      <c r="AW36" s="24" t="n"/>
+      <c r="AX36" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY36" s="24" t="n"/>
+      <c r="AZ36" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA36" s="24" t="inlineStr">
+        <is>
+          <t>1f56359bf30bb6d51629a345226e3008ebfe73210551f6db9f5ce09f656ffdd6</t>
+        </is>
+      </c>
+      <c r="BB36" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC36" s="24" t="inlineStr">
+        <is>
+          <t>lol-neutral-series-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD36" s="24" t="inlineStr">
+        <is>
+          <t>1f56359bf30bb6d51629a345226e3008ebfe73210551f6db9f5ce09f656ffdd6</t>
+        </is>
+      </c>
+      <c r="BE36" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF36" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG36" s="24" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="BH36" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T16:18:24.995882Z</t>
+        </is>
+      </c>
+      <c r="BI36" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ36" s="25" t="n"/>
+      <c r="BK36" s="26" t="n">
+        <v>144</v>
+      </c>
+      <c r="BL36" s="27" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BM36" s="28" t="n">
+        <v>0.409836</v>
+      </c>
+      <c r="BN36" s="28" t="n"/>
+      <c r="BO36" s="28" t="n"/>
+      <c r="BP36" s="25" t="n"/>
+      <c r="BQ36" s="27" t="n"/>
+      <c r="BR36" s="28" t="n"/>
+      <c r="BS36" s="28" t="n"/>
+      <c r="BT36" s="28" t="n"/>
+      <c r="BU36" s="25" t="n"/>
+      <c r="BV36" s="29" t="n"/>
+      <c r="BW36" s="24" t="n"/>
+      <c r="BX36" s="30" t="n"/>
+      <c r="BY36" s="27" t="n"/>
+      <c r="BZ36" s="24" t="n"/>
+      <c r="CA36" s="31" t="n"/>
+    </row>
+    <row r="37" ht="36" customHeight="1">
+      <c r="A37" s="24" t="inlineStr">
+        <is>
+          <t>dc63682b755a4fc5</t>
+        </is>
+      </c>
+      <c r="B37" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T16:18:25.123725Z</t>
+        </is>
+      </c>
+      <c r="C37" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="D37" s="24" t="inlineStr">
+        <is>
+          <t>54670</t>
+        </is>
+      </c>
+      <c r="E37" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F37" s="24" t="inlineStr">
+        <is>
+          <t>INTZ e-Sports</t>
+        </is>
+      </c>
+      <c r="G37" s="24" t="inlineStr">
+        <is>
+          <t>7REX</t>
+        </is>
+      </c>
+      <c r="H37" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I37" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J37" s="25" t="n"/>
+      <c r="K37" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L37" s="26" t="n">
+        <v>186</v>
+      </c>
+      <c r="M37" s="27" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="N37" s="28" t="n">
+        <v>0.34965</v>
+      </c>
+      <c r="O37" s="28" t="n">
+        <v>0.567918</v>
+      </c>
+      <c r="P37" s="28" t="n"/>
+      <c r="Q37" s="28" t="n">
+        <v>0.217918</v>
+      </c>
+      <c r="R37" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S37" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T37" s="24" t="inlineStr">
+        <is>
+          <t>lol-neutral-series-elo-v1</t>
+        </is>
+      </c>
+      <c r="U37" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V37" s="24" t="n"/>
+      <c r="W37" s="26" t="n"/>
+      <c r="X37" s="26" t="n"/>
+      <c r="Y37" s="25" t="n"/>
+      <c r="Z37" s="26" t="n"/>
+      <c r="AA37" s="28" t="n"/>
+      <c r="AB37" s="28" t="n"/>
+      <c r="AC37" s="30" t="n"/>
+      <c r="AD37" s="24" t="n"/>
+      <c r="AE37" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.3500 (aec-lol-itz-7rex-2026-07-20).</t>
+        </is>
+      </c>
+      <c r="AF37" s="31" t="inlineStr">
+        <is>
+          <t>Research baseline; zero-unit shadow until qualified.</t>
+        </is>
+      </c>
+      <c r="AG37" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH37" s="24" t="n"/>
+      <c r="AI37" s="31" t="n"/>
+      <c r="AJ37" s="31" t="n"/>
+      <c r="AK37" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL37" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM37" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN37" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO37" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP37" s="24" t="inlineStr">
+        <is>
+          <t>INTZ e-Sports</t>
+        </is>
+      </c>
+      <c r="AQ37" s="24" t="inlineStr">
+        <is>
+          <t>INTZ e-Sports</t>
+        </is>
+      </c>
+      <c r="AR37" s="24" t="inlineStr">
+        <is>
+          <t>INTZ e-Sports</t>
+        </is>
+      </c>
+      <c r="AS37" s="24" t="inlineStr">
+        <is>
+          <t>7REX</t>
+        </is>
+      </c>
+      <c r="AT37" s="24" t="inlineStr">
+        <is>
+          <t>7REX</t>
+        </is>
+      </c>
+      <c r="AU37" s="24" t="inlineStr">
+        <is>
+          <t>7REX</t>
+        </is>
+      </c>
+      <c r="AV37" s="24" t="n"/>
+      <c r="AW37" s="24" t="n"/>
+      <c r="AX37" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY37" s="24" t="n"/>
+      <c r="AZ37" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA37" s="24" t="inlineStr">
+        <is>
+          <t>1f56359bf30bb6d51629a345226e3008ebfe73210551f6db9f5ce09f656ffdd6</t>
+        </is>
+      </c>
+      <c r="BB37" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC37" s="24" t="inlineStr">
+        <is>
+          <t>lol-neutral-series-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD37" s="24" t="inlineStr">
+        <is>
+          <t>1f56359bf30bb6d51629a345226e3008ebfe73210551f6db9f5ce09f656ffdd6</t>
+        </is>
+      </c>
+      <c r="BE37" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF37" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG37" s="24" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="BH37" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T16:18:25.123725Z</t>
+        </is>
+      </c>
+      <c r="BI37" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ37" s="25" t="n"/>
+      <c r="BK37" s="26" t="n">
+        <v>186</v>
+      </c>
+      <c r="BL37" s="27" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="BM37" s="28" t="n">
+        <v>0.34965</v>
+      </c>
+      <c r="BN37" s="28" t="n"/>
+      <c r="BO37" s="28" t="n"/>
+      <c r="BP37" s="25" t="n"/>
+      <c r="BQ37" s="27" t="n"/>
+      <c r="BR37" s="28" t="n"/>
+      <c r="BS37" s="28" t="n"/>
+      <c r="BT37" s="28" t="n"/>
+      <c r="BU37" s="25" t="n"/>
+      <c r="BV37" s="29" t="n"/>
+      <c r="BW37" s="24" t="n"/>
+      <c r="BX37" s="30" t="n"/>
+      <c r="BY37" s="27" t="n"/>
+      <c r="BZ37" s="24" t="n"/>
+      <c r="CA37" s="31" t="n"/>
+    </row>
+    <row r="38" ht="36" customHeight="1">
+      <c r="A38" s="24" t="inlineStr">
+        <is>
+          <t>36b26e06b0c0460a</t>
+        </is>
+      </c>
+      <c r="B38" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T16:18:25.218065Z</t>
+        </is>
+      </c>
+      <c r="C38" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T22:00:00Z</t>
+        </is>
+      </c>
+      <c r="D38" s="24" t="inlineStr">
+        <is>
+          <t>54693</t>
+        </is>
+      </c>
+      <c r="E38" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F38" s="24" t="inlineStr">
+        <is>
+          <t>Ei Nerd Esports</t>
+        </is>
+      </c>
+      <c r="G38" s="24" t="inlineStr">
+        <is>
+          <t>RED Academy</t>
+        </is>
+      </c>
+      <c r="H38" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I38" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J38" s="25" t="n"/>
+      <c r="K38" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L38" s="26" t="n">
+        <v>300</v>
+      </c>
+      <c r="M38" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="N38" s="28" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="O38" s="28" t="n">
+        <v>0.674654</v>
+      </c>
+      <c r="P38" s="28" t="n"/>
+      <c r="Q38" s="28" t="n">
+        <v>0.424654</v>
+      </c>
+      <c r="R38" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S38" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T38" s="24" t="inlineStr">
+        <is>
+          <t>lol-neutral-series-elo-v1</t>
+        </is>
+      </c>
+      <c r="U38" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V38" s="24" t="n"/>
+      <c r="W38" s="26" t="n"/>
+      <c r="X38" s="26" t="n"/>
+      <c r="Y38" s="25" t="n"/>
+      <c r="Z38" s="26" t="n"/>
+      <c r="AA38" s="28" t="n"/>
+      <c r="AB38" s="28" t="n"/>
+      <c r="AC38" s="30" t="n"/>
+      <c r="AD38" s="24" t="n"/>
+      <c r="AE38" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.2500 (aec-lol-reda-nerd-2026-07-20).</t>
+        </is>
+      </c>
+      <c r="AF38" s="31" t="inlineStr">
+        <is>
+          <t>Research baseline; zero-unit shadow until qualified.</t>
+        </is>
+      </c>
+      <c r="AG38" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH38" s="24" t="n"/>
+      <c r="AI38" s="31" t="n"/>
+      <c r="AJ38" s="31" t="n"/>
+      <c r="AK38" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL38" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM38" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN38" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO38" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP38" s="24" t="inlineStr">
+        <is>
+          <t>Ei Nerd Esports</t>
+        </is>
+      </c>
+      <c r="AQ38" s="24" t="inlineStr">
+        <is>
+          <t>Ei Nerd Esports</t>
+        </is>
+      </c>
+      <c r="AR38" s="24" t="inlineStr">
+        <is>
+          <t>Ei Nerd Esports</t>
+        </is>
+      </c>
+      <c r="AS38" s="24" t="inlineStr">
+        <is>
+          <t>RED Academy</t>
+        </is>
+      </c>
+      <c r="AT38" s="24" t="inlineStr">
+        <is>
+          <t>RED Academy</t>
+        </is>
+      </c>
+      <c r="AU38" s="24" t="inlineStr">
+        <is>
+          <t>RED Academy</t>
+        </is>
+      </c>
+      <c r="AV38" s="24" t="n"/>
+      <c r="AW38" s="24" t="n"/>
+      <c r="AX38" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY38" s="24" t="n"/>
+      <c r="AZ38" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA38" s="24" t="inlineStr">
+        <is>
+          <t>1f56359bf30bb6d51629a345226e3008ebfe73210551f6db9f5ce09f656ffdd6</t>
+        </is>
+      </c>
+      <c r="BB38" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC38" s="24" t="inlineStr">
+        <is>
+          <t>lol-neutral-series-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD38" s="24" t="inlineStr">
+        <is>
+          <t>1f56359bf30bb6d51629a345226e3008ebfe73210551f6db9f5ce09f656ffdd6</t>
+        </is>
+      </c>
+      <c r="BE38" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF38" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG38" s="24" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="BH38" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T16:18:25.218065Z</t>
+        </is>
+      </c>
+      <c r="BI38" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ38" s="25" t="n"/>
+      <c r="BK38" s="26" t="n">
+        <v>300</v>
+      </c>
+      <c r="BL38" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="BM38" s="28" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="BN38" s="28" t="n"/>
+      <c r="BO38" s="28" t="n"/>
+      <c r="BP38" s="25" t="n"/>
+      <c r="BQ38" s="27" t="n"/>
+      <c r="BR38" s="28" t="n"/>
+      <c r="BS38" s="28" t="n"/>
+      <c r="BT38" s="28" t="n"/>
+      <c r="BU38" s="25" t="n"/>
+      <c r="BV38" s="29" t="n"/>
+      <c r="BW38" s="24" t="n"/>
+      <c r="BX38" s="30" t="n"/>
+      <c r="BY38" s="27" t="n"/>
+      <c r="BZ38" s="24" t="n"/>
+      <c r="CA38" s="31" t="n"/>
+    </row>
+    <row r="39" ht="36" customHeight="1">
+      <c r="A39" s="24" t="inlineStr">
+        <is>
+          <t>a72da5dc37704076</t>
+        </is>
+      </c>
+      <c r="B39" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T16:18:25.312075Z</t>
+        </is>
+      </c>
+      <c r="C39" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-21T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D39" s="24" t="inlineStr">
+        <is>
+          <t>54745</t>
+        </is>
+      </c>
+      <c r="E39" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F39" s="24" t="inlineStr">
+        <is>
+          <t>Estral Esports</t>
+        </is>
+      </c>
+      <c r="G39" s="24" t="inlineStr">
+        <is>
+          <t>paiN Gaming Academy</t>
+        </is>
+      </c>
+      <c r="H39" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I39" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J39" s="25" t="n"/>
+      <c r="K39" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L39" s="26" t="n">
+        <v>245</v>
+      </c>
+      <c r="M39" s="27" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N39" s="28" t="n">
+        <v>0.289855</v>
+      </c>
+      <c r="O39" s="28" t="n">
+        <v>0.586418</v>
+      </c>
+      <c r="P39" s="28" t="n"/>
+      <c r="Q39" s="28" t="n">
+        <v>0.296418</v>
+      </c>
+      <c r="R39" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S39" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T39" s="24" t="inlineStr">
+        <is>
+          <t>lol-neutral-series-elo-v1</t>
+        </is>
+      </c>
+      <c r="U39" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V39" s="24" t="n"/>
+      <c r="W39" s="26" t="n"/>
+      <c r="X39" s="26" t="n"/>
+      <c r="Y39" s="25" t="n"/>
+      <c r="Z39" s="26" t="n"/>
+      <c r="AA39" s="28" t="n"/>
+      <c r="AB39" s="28" t="n"/>
+      <c r="AC39" s="30" t="n"/>
+      <c r="AD39" s="24" t="n"/>
+      <c r="AE39" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.2900 (aec-lol-est-pnga-2026-07-21).</t>
+        </is>
+      </c>
+      <c r="AF39" s="31" t="inlineStr">
+        <is>
+          <t>Research baseline; zero-unit shadow until qualified.</t>
+        </is>
+      </c>
+      <c r="AG39" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH39" s="24" t="n"/>
+      <c r="AI39" s="31" t="n"/>
+      <c r="AJ39" s="31" t="n"/>
+      <c r="AK39" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL39" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM39" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN39" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO39" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP39" s="24" t="inlineStr">
+        <is>
+          <t>Estral Esports</t>
+        </is>
+      </c>
+      <c r="AQ39" s="24" t="inlineStr">
+        <is>
+          <t>Estral Esports</t>
+        </is>
+      </c>
+      <c r="AR39" s="24" t="inlineStr">
+        <is>
+          <t>Estral Esports</t>
+        </is>
+      </c>
+      <c r="AS39" s="24" t="inlineStr">
+        <is>
+          <t>paiN Gaming Academy</t>
+        </is>
+      </c>
+      <c r="AT39" s="24" t="inlineStr">
+        <is>
+          <t>paiN Gaming Academy</t>
+        </is>
+      </c>
+      <c r="AU39" s="24" t="inlineStr">
+        <is>
+          <t>paiN Gaming Academy</t>
+        </is>
+      </c>
+      <c r="AV39" s="24" t="n"/>
+      <c r="AW39" s="24" t="n"/>
+      <c r="AX39" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY39" s="24" t="n"/>
+      <c r="AZ39" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA39" s="24" t="inlineStr">
+        <is>
+          <t>1f56359bf30bb6d51629a345226e3008ebfe73210551f6db9f5ce09f656ffdd6</t>
+        </is>
+      </c>
+      <c r="BB39" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC39" s="24" t="inlineStr">
+        <is>
+          <t>lol-neutral-series-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD39" s="24" t="inlineStr">
+        <is>
+          <t>1f56359bf30bb6d51629a345226e3008ebfe73210551f6db9f5ce09f656ffdd6</t>
+        </is>
+      </c>
+      <c r="BE39" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF39" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG39" s="24" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="BH39" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T16:18:25.312075Z</t>
+        </is>
+      </c>
+      <c r="BI39" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ39" s="25" t="n"/>
+      <c r="BK39" s="26" t="n">
+        <v>245</v>
+      </c>
+      <c r="BL39" s="27" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BM39" s="28" t="n">
+        <v>0.289855</v>
+      </c>
+      <c r="BN39" s="28" t="n"/>
+      <c r="BO39" s="28" t="n"/>
+      <c r="BP39" s="25" t="n"/>
+      <c r="BQ39" s="27" t="n"/>
+      <c r="BR39" s="28" t="n"/>
+      <c r="BS39" s="28" t="n"/>
+      <c r="BT39" s="28" t="n"/>
+      <c r="BU39" s="25" t="n"/>
+      <c r="BV39" s="29" t="n"/>
+      <c r="BW39" s="24" t="n"/>
+      <c r="BX39" s="30" t="n"/>
+      <c r="BY39" s="27" t="n"/>
+      <c r="BZ39" s="24" t="n"/>
+      <c r="CA39" s="31" t="n"/>
+    </row>
+    <row r="40" ht="36" customHeight="1">
+      <c r="A40" s="24" t="inlineStr">
+        <is>
+          <t>66a67a653fb14bd2</t>
+        </is>
+      </c>
+      <c r="B40" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T16:26:22.811500Z</t>
+        </is>
+      </c>
+      <c r="C40" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="D40" s="24" t="inlineStr">
+        <is>
+          <t>56113</t>
+        </is>
+      </c>
+      <c r="E40" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F40" s="24" t="inlineStr">
+        <is>
+          <t>Inner Circle Academy</t>
+        </is>
+      </c>
+      <c r="G40" s="24" t="inlineStr">
+        <is>
+          <t>Endless Journey</t>
+        </is>
+      </c>
+      <c r="H40" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I40" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J40" s="25" t="n"/>
+      <c r="K40" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L40" s="26" t="n">
+        <v>-113</v>
+      </c>
+      <c r="M40" s="27" t="n">
+        <v>1.884956</v>
+      </c>
+      <c r="N40" s="28" t="n">
+        <v>0.530516</v>
+      </c>
+      <c r="O40" s="28" t="n">
+        <v>0.652434</v>
+      </c>
+      <c r="P40" s="28" t="n"/>
+      <c r="Q40" s="28" t="n">
+        <v>0.122434</v>
+      </c>
+      <c r="R40" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S40" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T40" s="24" t="inlineStr">
+        <is>
+          <t>cs2-neutral-series-elo-v1</t>
+        </is>
+      </c>
+      <c r="U40" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V40" s="24" t="n"/>
+      <c r="W40" s="26" t="n"/>
+      <c r="X40" s="26" t="n"/>
+      <c r="Y40" s="25" t="n"/>
+      <c r="Z40" s="26" t="n"/>
+      <c r="AA40" s="28" t="n"/>
+      <c r="AB40" s="28" t="n"/>
+      <c r="AC40" s="30" t="n"/>
+      <c r="AD40" s="24" t="n"/>
+      <c r="AE40" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5300 (aec-cs2-ica-ej-2026-07-20).</t>
+        </is>
+      </c>
+      <c r="AF40" s="31" t="inlineStr">
+        <is>
+          <t>Research baseline; zero-unit shadow until qualified.</t>
+        </is>
+      </c>
+      <c r="AG40" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH40" s="24" t="n"/>
+      <c r="AI40" s="31" t="n"/>
+      <c r="AJ40" s="31" t="n"/>
+      <c r="AK40" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL40" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM40" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN40" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO40" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP40" s="24" t="inlineStr">
+        <is>
+          <t>Inner Circle Academy</t>
+        </is>
+      </c>
+      <c r="AQ40" s="24" t="inlineStr">
+        <is>
+          <t>Inner Circle Academy</t>
+        </is>
+      </c>
+      <c r="AR40" s="24" t="inlineStr">
+        <is>
+          <t>Inner Circle Academy</t>
+        </is>
+      </c>
+      <c r="AS40" s="24" t="inlineStr">
+        <is>
+          <t>Endless Journey</t>
+        </is>
+      </c>
+      <c r="AT40" s="24" t="inlineStr">
+        <is>
+          <t>Endless Journey</t>
+        </is>
+      </c>
+      <c r="AU40" s="24" t="inlineStr">
+        <is>
+          <t>Endless Journey</t>
+        </is>
+      </c>
+      <c r="AV40" s="24" t="n"/>
+      <c r="AW40" s="24" t="n"/>
+      <c r="AX40" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY40" s="24" t="n"/>
+      <c r="AZ40" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA40" s="24" t="inlineStr">
+        <is>
+          <t>40df7f7b9128e86cfbc485914f5801a00963b62604711b733b60f782ba9e258b</t>
+        </is>
+      </c>
+      <c r="BB40" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC40" s="24" t="inlineStr">
+        <is>
+          <t>cs2-neutral-series-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD40" s="24" t="inlineStr">
+        <is>
+          <t>40df7f7b9128e86cfbc485914f5801a00963b62604711b733b60f782ba9e258b</t>
+        </is>
+      </c>
+      <c r="BE40" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF40" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG40" s="24" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="BH40" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T16:26:22.811500Z</t>
+        </is>
+      </c>
+      <c r="BI40" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ40" s="25" t="n"/>
+      <c r="BK40" s="26" t="n">
+        <v>-113</v>
+      </c>
+      <c r="BL40" s="27" t="n">
+        <v>1.884956</v>
+      </c>
+      <c r="BM40" s="28" t="n">
+        <v>0.530516</v>
+      </c>
+      <c r="BN40" s="28" t="n"/>
+      <c r="BO40" s="28" t="n"/>
+      <c r="BP40" s="25" t="n"/>
+      <c r="BQ40" s="27" t="n"/>
+      <c r="BR40" s="28" t="n"/>
+      <c r="BS40" s="28" t="n"/>
+      <c r="BT40" s="28" t="n"/>
+      <c r="BU40" s="25" t="n"/>
+      <c r="BV40" s="29" t="n"/>
+      <c r="BW40" s="24" t="n"/>
+      <c r="BX40" s="30" t="n"/>
+      <c r="BY40" s="27" t="n"/>
+      <c r="BZ40" s="24" t="n"/>
+      <c r="CA40" s="31" t="n"/>
+    </row>
+    <row r="41" ht="36" customHeight="1">
+      <c r="A41" s="24" t="inlineStr">
+        <is>
+          <t>a75a7af91f614c77</t>
+        </is>
+      </c>
+      <c r="B41" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T16:26:22.946543Z</t>
+        </is>
+      </c>
+      <c r="C41" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T19:00:00Z</t>
+        </is>
+      </c>
+      <c r="D41" s="24" t="inlineStr">
+        <is>
+          <t>56757</t>
+        </is>
+      </c>
+      <c r="E41" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F41" s="24" t="inlineStr">
+        <is>
+          <t>MAGICOS</t>
+        </is>
+      </c>
+      <c r="G41" s="24" t="inlineStr">
+        <is>
+          <t>Blitzkrieg</t>
+        </is>
+      </c>
+      <c r="H41" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I41" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J41" s="25" t="n"/>
+      <c r="K41" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L41" s="26" t="n">
+        <v>669</v>
+      </c>
+      <c r="M41" s="27" t="n">
+        <v>7.69</v>
+      </c>
+      <c r="N41" s="28" t="n">
+        <v>0.130039</v>
+      </c>
+      <c r="O41" s="28" t="n">
+        <v>0.598244</v>
+      </c>
+      <c r="P41" s="28" t="n"/>
+      <c r="Q41" s="28" t="n">
+        <v>0.468244</v>
+      </c>
+      <c r="R41" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S41" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T41" s="24" t="inlineStr">
+        <is>
+          <t>cs2-neutral-series-elo-v1</t>
+        </is>
+      </c>
+      <c r="U41" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V41" s="24" t="n"/>
+      <c r="W41" s="26" t="n"/>
+      <c r="X41" s="26" t="n"/>
+      <c r="Y41" s="25" t="n"/>
+      <c r="Z41" s="26" t="n"/>
+      <c r="AA41" s="28" t="n"/>
+      <c r="AB41" s="28" t="n"/>
+      <c r="AC41" s="30" t="n"/>
+      <c r="AD41" s="24" t="n"/>
+      <c r="AE41" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.1300 (aec-cs2-mag-bk-2026-07-20).</t>
+        </is>
+      </c>
+      <c r="AF41" s="31" t="inlineStr">
+        <is>
+          <t>Research baseline; zero-unit shadow until qualified.</t>
+        </is>
+      </c>
+      <c r="AG41" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH41" s="24" t="n"/>
+      <c r="AI41" s="31" t="n"/>
+      <c r="AJ41" s="31" t="n"/>
+      <c r="AK41" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL41" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM41" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN41" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO41" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP41" s="24" t="inlineStr">
+        <is>
+          <t>MAGICOS</t>
+        </is>
+      </c>
+      <c r="AQ41" s="24" t="inlineStr">
+        <is>
+          <t>MAGICOS</t>
+        </is>
+      </c>
+      <c r="AR41" s="24" t="inlineStr">
+        <is>
+          <t>MAGICOS</t>
+        </is>
+      </c>
+      <c r="AS41" s="24" t="inlineStr">
+        <is>
+          <t>Blitzkrieg</t>
+        </is>
+      </c>
+      <c r="AT41" s="24" t="inlineStr">
+        <is>
+          <t>Blitzkrieg</t>
+        </is>
+      </c>
+      <c r="AU41" s="24" t="inlineStr">
+        <is>
+          <t>Blitzkrieg</t>
+        </is>
+      </c>
+      <c r="AV41" s="24" t="n"/>
+      <c r="AW41" s="24" t="n"/>
+      <c r="AX41" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY41" s="24" t="n"/>
+      <c r="AZ41" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA41" s="24" t="inlineStr">
+        <is>
+          <t>40df7f7b9128e86cfbc485914f5801a00963b62604711b733b60f782ba9e258b</t>
+        </is>
+      </c>
+      <c r="BB41" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC41" s="24" t="inlineStr">
+        <is>
+          <t>cs2-neutral-series-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD41" s="24" t="inlineStr">
+        <is>
+          <t>40df7f7b9128e86cfbc485914f5801a00963b62604711b733b60f782ba9e258b</t>
+        </is>
+      </c>
+      <c r="BE41" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF41" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG41" s="24" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="BH41" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T16:26:22.946543Z</t>
+        </is>
+      </c>
+      <c r="BI41" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ41" s="25" t="n"/>
+      <c r="BK41" s="26" t="n">
+        <v>669</v>
+      </c>
+      <c r="BL41" s="27" t="n">
+        <v>7.69</v>
+      </c>
+      <c r="BM41" s="28" t="n">
+        <v>0.130039</v>
+      </c>
+      <c r="BN41" s="28" t="n"/>
+      <c r="BO41" s="28" t="n"/>
+      <c r="BP41" s="25" t="n"/>
+      <c r="BQ41" s="27" t="n"/>
+      <c r="BR41" s="28" t="n"/>
+      <c r="BS41" s="28" t="n"/>
+      <c r="BT41" s="28" t="n"/>
+      <c r="BU41" s="25" t="n"/>
+      <c r="BV41" s="29" t="n"/>
+      <c r="BW41" s="24" t="n"/>
+      <c r="BX41" s="30" t="n"/>
+      <c r="BY41" s="27" t="n"/>
+      <c r="BZ41" s="24" t="n"/>
+      <c r="CA41" s="31" t="n"/>
+    </row>
+    <row r="42" ht="36" customHeight="1">
+      <c r="A42" s="24" t="inlineStr">
+        <is>
+          <t>8a3b3559571c4133</t>
+        </is>
+      </c>
+      <c r="B42" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T16:26:23.050406Z</t>
+        </is>
+      </c>
+      <c r="C42" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T19:00:00Z</t>
+        </is>
+      </c>
+      <c r="D42" s="24" t="inlineStr">
+        <is>
+          <t>54667</t>
+        </is>
+      </c>
+      <c r="E42" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F42" s="24" t="inlineStr">
+        <is>
+          <t>paiN Academy</t>
+        </is>
+      </c>
+      <c r="G42" s="24" t="inlineStr">
+        <is>
+          <t>HATERS</t>
+        </is>
+      </c>
+      <c r="H42" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I42" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J42" s="25" t="n"/>
+      <c r="K42" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L42" s="26" t="n">
+        <v>335</v>
+      </c>
+      <c r="M42" s="27" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="N42" s="28" t="n">
+        <v>0.229885</v>
+      </c>
+      <c r="O42" s="28" t="n">
+        <v>0.558097</v>
+      </c>
+      <c r="P42" s="28" t="n"/>
+      <c r="Q42" s="28" t="n">
+        <v>0.328097</v>
+      </c>
+      <c r="R42" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S42" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T42" s="24" t="inlineStr">
+        <is>
+          <t>cs2-neutral-series-elo-v1</t>
+        </is>
+      </c>
+      <c r="U42" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V42" s="24" t="n"/>
+      <c r="W42" s="26" t="n"/>
+      <c r="X42" s="26" t="n"/>
+      <c r="Y42" s="25" t="n"/>
+      <c r="Z42" s="26" t="n"/>
+      <c r="AA42" s="28" t="n"/>
+      <c r="AB42" s="28" t="n"/>
+      <c r="AC42" s="30" t="n"/>
+      <c r="AD42" s="24" t="n"/>
+      <c r="AE42" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.2300 (aec-cs2-hat-paina-2026-07-20).</t>
+        </is>
+      </c>
+      <c r="AF42" s="31" t="inlineStr">
+        <is>
+          <t>Research baseline; zero-unit shadow until qualified.</t>
+        </is>
+      </c>
+      <c r="AG42" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH42" s="24" t="n"/>
+      <c r="AI42" s="31" t="n"/>
+      <c r="AJ42" s="31" t="n"/>
+      <c r="AK42" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL42" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM42" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN42" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO42" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP42" s="24" t="inlineStr">
+        <is>
+          <t>paiN Academy</t>
+        </is>
+      </c>
+      <c r="AQ42" s="24" t="inlineStr">
+        <is>
+          <t>paiN Academy</t>
+        </is>
+      </c>
+      <c r="AR42" s="24" t="inlineStr">
+        <is>
+          <t>paiN Academy</t>
+        </is>
+      </c>
+      <c r="AS42" s="24" t="inlineStr">
+        <is>
+          <t>HATERS</t>
+        </is>
+      </c>
+      <c r="AT42" s="24" t="inlineStr">
+        <is>
+          <t>HATERS</t>
+        </is>
+      </c>
+      <c r="AU42" s="24" t="inlineStr">
+        <is>
+          <t>HATERS</t>
+        </is>
+      </c>
+      <c r="AV42" s="24" t="n"/>
+      <c r="AW42" s="24" t="n"/>
+      <c r="AX42" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY42" s="24" t="n"/>
+      <c r="AZ42" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA42" s="24" t="inlineStr">
+        <is>
+          <t>40df7f7b9128e86cfbc485914f5801a00963b62604711b733b60f782ba9e258b</t>
+        </is>
+      </c>
+      <c r="BB42" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC42" s="24" t="inlineStr">
+        <is>
+          <t>cs2-neutral-series-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD42" s="24" t="inlineStr">
+        <is>
+          <t>40df7f7b9128e86cfbc485914f5801a00963b62604711b733b60f782ba9e258b</t>
+        </is>
+      </c>
+      <c r="BE42" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF42" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG42" s="24" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="BH42" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T16:26:23.050406Z</t>
+        </is>
+      </c>
+      <c r="BI42" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ42" s="25" t="n"/>
+      <c r="BK42" s="26" t="n">
+        <v>335</v>
+      </c>
+      <c r="BL42" s="27" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="BM42" s="28" t="n">
+        <v>0.229885</v>
+      </c>
+      <c r="BN42" s="28" t="n"/>
+      <c r="BO42" s="28" t="n"/>
+      <c r="BP42" s="25" t="n"/>
+      <c r="BQ42" s="27" t="n"/>
+      <c r="BR42" s="28" t="n"/>
+      <c r="BS42" s="28" t="n"/>
+      <c r="BT42" s="28" t="n"/>
+      <c r="BU42" s="25" t="n"/>
+      <c r="BV42" s="29" t="n"/>
+      <c r="BW42" s="24" t="n"/>
+      <c r="BX42" s="30" t="n"/>
+      <c r="BY42" s="27" t="n"/>
+      <c r="BZ42" s="24" t="n"/>
+      <c r="CA42" s="31" t="n"/>
+    </row>
+    <row r="43" ht="36" customHeight="1">
+      <c r="A43" s="24" t="inlineStr">
+        <is>
+          <t>5417c8a3e89a4c9f</t>
+        </is>
+      </c>
+      <c r="B43" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T16:26:23.154839Z</t>
+        </is>
+      </c>
+      <c r="C43" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="D43" s="24" t="inlineStr">
+        <is>
+          <t>54672</t>
+        </is>
+      </c>
+      <c r="E43" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F43" s="24" t="inlineStr">
+        <is>
+          <t>METANOIA WOLVES</t>
+        </is>
+      </c>
+      <c r="G43" s="24" t="inlineStr">
+        <is>
+          <t>RED Canids Academy</t>
+        </is>
+      </c>
+      <c r="H43" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I43" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J43" s="25" t="n"/>
+      <c r="K43" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L43" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="M43" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="N43" s="28" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="O43" s="28" t="n">
+        <v>0.885084</v>
+      </c>
+      <c r="P43" s="28" t="n"/>
+      <c r="Q43" s="28" t="n">
+        <v>0.295084</v>
+      </c>
+      <c r="R43" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S43" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T43" s="24" t="inlineStr">
+        <is>
+          <t>cs2-neutral-series-elo-v1</t>
+        </is>
+      </c>
+      <c r="U43" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V43" s="24" t="n"/>
+      <c r="W43" s="26" t="n"/>
+      <c r="X43" s="26" t="n"/>
+      <c r="Y43" s="25" t="n"/>
+      <c r="Z43" s="26" t="n"/>
+      <c r="AA43" s="28" t="n"/>
+      <c r="AB43" s="28" t="n"/>
+      <c r="AC43" s="30" t="n"/>
+      <c r="AD43" s="24" t="n"/>
+      <c r="AE43" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5900 (aec-cs2-reda-mw-2026-07-20).</t>
+        </is>
+      </c>
+      <c r="AF43" s="31" t="inlineStr">
+        <is>
+          <t>Research baseline; zero-unit shadow until qualified.</t>
+        </is>
+      </c>
+      <c r="AG43" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH43" s="24" t="n"/>
+      <c r="AI43" s="31" t="n"/>
+      <c r="AJ43" s="31" t="n"/>
+      <c r="AK43" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL43" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM43" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN43" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO43" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP43" s="24" t="inlineStr">
+        <is>
+          <t>METANOIA WOLVES</t>
+        </is>
+      </c>
+      <c r="AQ43" s="24" t="inlineStr">
+        <is>
+          <t>METANOIA WOLVES</t>
+        </is>
+      </c>
+      <c r="AR43" s="24" t="inlineStr">
+        <is>
+          <t>METANOIA WOLVES</t>
+        </is>
+      </c>
+      <c r="AS43" s="24" t="inlineStr">
+        <is>
+          <t>RED Canids Academy</t>
+        </is>
+      </c>
+      <c r="AT43" s="24" t="inlineStr">
+        <is>
+          <t>RED Canids Academy</t>
+        </is>
+      </c>
+      <c r="AU43" s="24" t="inlineStr">
+        <is>
+          <t>RED Canids Academy</t>
+        </is>
+      </c>
+      <c r="AV43" s="24" t="n"/>
+      <c r="AW43" s="24" t="n"/>
+      <c r="AX43" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY43" s="24" t="n"/>
+      <c r="AZ43" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA43" s="24" t="inlineStr">
+        <is>
+          <t>40df7f7b9128e86cfbc485914f5801a00963b62604711b733b60f782ba9e258b</t>
+        </is>
+      </c>
+      <c r="BB43" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC43" s="24" t="inlineStr">
+        <is>
+          <t>cs2-neutral-series-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD43" s="24" t="inlineStr">
+        <is>
+          <t>40df7f7b9128e86cfbc485914f5801a00963b62604711b733b60f782ba9e258b</t>
+        </is>
+      </c>
+      <c r="BE43" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF43" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG43" s="24" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="BH43" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-20T16:26:23.154839Z</t>
+        </is>
+      </c>
+      <c r="BI43" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ43" s="25" t="n"/>
+      <c r="BK43" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="BL43" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="BM43" s="28" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="BN43" s="28" t="n"/>
+      <c r="BO43" s="28" t="n"/>
+      <c r="BP43" s="25" t="n"/>
+      <c r="BQ43" s="27" t="n"/>
+      <c r="BR43" s="28" t="n"/>
+      <c r="BS43" s="28" t="n"/>
+      <c r="BT43" s="28" t="n"/>
+      <c r="BU43" s="25" t="n"/>
+      <c r="BV43" s="29" t="n"/>
+      <c r="BW43" s="24" t="n"/>
+      <c r="BX43" s="30" t="n"/>
+      <c r="BY43" s="27" t="n"/>
+      <c r="BZ43" s="24" t="n"/>
+      <c r="CA43" s="31" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/picks.xlsx
+++ b/data/picks.xlsx
@@ -21,10 +21,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="0.0###"/>
-    <numFmt numFmtId="165" formatCode="0.000000"/>
-    <numFmt numFmtId="166" formatCode="0.0000"/>
-    <numFmt numFmtId="167" formatCode="0.0%"/>
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
+    <numFmt numFmtId="166" formatCode="0.0###"/>
+    <numFmt numFmtId="167" formatCode="0.000000"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -136,7 +136,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -150,10 +150,10 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -169,10 +169,10 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -184,10 +184,10 @@
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -202,13 +202,13 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="10" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -217,11 +217,38 @@
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -300,8 +327,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CA43" headerRowCount="1">
-  <autoFilter ref="A1:CA43"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CA39" headerRowCount="1">
+  <autoFilter ref="A1:CA39"/>
   <tableColumns count="79">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -738,22 +765,23 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$43)</f>
+        <f>COUNTA('Picks'!$A$2:$A$39)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$43,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$39,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$43,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$39,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$43,"settled",'Picks'!$V$2:$V$43,"win")+COUNTIFS('Picks'!$U$2:$U$43,"settled",'Picks'!$V$2:$V$43,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$39,"settled",'Picks'!$V$2:$V$39,"win")+COUNTIFS('Picks'!$U$2:$U$39,"settled",'Picks'!$V$2:$V$39,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
+    <row r="5"/>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
@@ -778,22 +806,23 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$43,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$39,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$43,"&gt;0",'Picks'!$V$2:$V$43,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$43,"&gt;0",'Picks'!$V$2:$V$43,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$39,"&gt;0",'Picks'!$V$2:$V$39,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$39,"&gt;0",'Picks'!$V$2:$V$39,"loss")</f>
         <v/>
       </c>
-      <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$43,"&gt;0",'Picks'!$V$2:$V$43,"win")/(COUNTIFS('Picks'!$BX$2:$BX$43,"&gt;0",'Picks'!$V$2:$V$43,"win")+COUNTIFS('Picks'!$BX$2:$BX$43,"&gt;0",'Picks'!$V$2:$V$43,"loss")),0)</f>
+      <c r="E7" s="32">
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$39,"&gt;0",'Picks'!$V$2:$V$39,"win")/(COUNTIFS('Picks'!$BX$2:$BX$39,"&gt;0",'Picks'!$V$2:$V$39,"win")+COUNTIFS('Picks'!$BX$2:$BX$39,"&gt;0",'Picks'!$V$2:$V$39,"loss")),0)</f>
         <v/>
       </c>
-      <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$43)/SUM('Picks'!$BX$2:$BX$43),0)</f>
+      <c r="G7" s="32">
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$39)/SUM('Picks'!$BX$2:$BX$39),0)</f>
         <v/>
       </c>
     </row>
+    <row r="8"/>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
@@ -817,23 +846,24 @@
       </c>
     </row>
     <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$43)</f>
+      <c r="A10" s="33">
+        <f>SUM('Picks'!$BY$2:$BY$39)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$43,"&lt;&gt;",'Picks'!$AB$2:$AB$43),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$39,"&lt;&gt;",'Picks'!$AB$2:$AB$39),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$43,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$43,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$39,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$39,"settled")</f>
         <v/>
       </c>
-      <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$43,'Picks'!$AM$2:$AM$43,"QUALIFIED_SHADOW_CALL")</f>
+      <c r="G10" s="33">
+        <f>SUMIFS('Picks'!$AC$2:$AC$39,'Picks'!$AM$2:$AM$39,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
@@ -885,27 +915,27 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$43,$A14,'Picks'!$U$2:$U$43,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$39,$A14,'Picks'!$U$2:$U$39,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$43,$A14,'Picks'!$U$2:$U$43,"settled",'Picks'!$V$2:$V$43,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$39,$A14,'Picks'!$U$2:$U$39,"settled",'Picks'!$V$2:$V$39,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$43,$A14,'Picks'!$U$2:$U$43,"settled",'Picks'!$V$2:$V$43,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$39,$A14,'Picks'!$U$2:$U$39,"settled",'Picks'!$V$2:$V$39,"loss")</f>
         <v/>
       </c>
-      <c r="E14" s="14">
+      <c r="E14" s="34">
         <f>IFERROR(C14/(C14+D14),0)</f>
         <v/>
       </c>
-      <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$43,'Picks'!$H$2:$H$43,$A14)</f>
+      <c r="F14" s="35">
+        <f>SUMIFS('Picks'!$BY$2:$BY$39,'Picks'!$H$2:$H$39,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$43,'Picks'!$H$2:$H$43,$A14,'Picks'!$U$2:$U$43,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$39,'Picks'!$H$2:$H$39,$A14,'Picks'!$U$2:$U$39,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -916,27 +946,27 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$43,$A15,'Picks'!$U$2:$U$43,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$39,$A15,'Picks'!$U$2:$U$39,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$43,$A15,'Picks'!$U$2:$U$43,"settled",'Picks'!$V$2:$V$43,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$39,$A15,'Picks'!$U$2:$U$39,"settled",'Picks'!$V$2:$V$39,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$43,$A15,'Picks'!$U$2:$U$43,"settled",'Picks'!$V$2:$V$43,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$39,$A15,'Picks'!$U$2:$U$39,"settled",'Picks'!$V$2:$V$39,"loss")</f>
         <v/>
       </c>
-      <c r="E15" s="19">
+      <c r="E15" s="36">
         <f>IFERROR(C15/(C15+D15),0)</f>
         <v/>
       </c>
-      <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$43,'Picks'!$H$2:$H$43,$A15)</f>
+      <c r="F15" s="37">
+        <f>SUMIFS('Picks'!$BY$2:$BY$39,'Picks'!$H$2:$H$39,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$43,'Picks'!$H$2:$H$43,$A15,'Picks'!$U$2:$U$43,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$39,'Picks'!$H$2:$H$39,$A15,'Picks'!$U$2:$U$39,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -947,30 +977,31 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$43,$A16,'Picks'!$U$2:$U$43,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$39,$A16,'Picks'!$U$2:$U$39,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$43,$A16,'Picks'!$U$2:$U$43,"settled",'Picks'!$V$2:$V$43,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$39,$A16,'Picks'!$U$2:$U$39,"settled",'Picks'!$V$2:$V$39,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$43,$A16,'Picks'!$U$2:$U$43,"settled",'Picks'!$V$2:$V$43,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$39,$A16,'Picks'!$U$2:$U$39,"settled",'Picks'!$V$2:$V$39,"loss")</f>
         <v/>
       </c>
-      <c r="E16" s="14">
+      <c r="E16" s="34">
         <f>IFERROR(C16/(C16+D16),0)</f>
         <v/>
       </c>
-      <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$43,'Picks'!$H$2:$H$43,$A16)</f>
+      <c r="F16" s="35">
+        <f>SUMIFS('Picks'!$BY$2:$BY$39,'Picks'!$H$2:$H$39,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$43,'Picks'!$H$2:$H$43,$A16,'Picks'!$U$2:$U$43,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$39,'Picks'!$H$2:$H$39,$A16,'Picks'!$U$2:$U$39,"settled"),0)</f>
         <v/>
       </c>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="22" t="inlineStr">
         <is>
@@ -996,7 +1027,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CA43"/>
+  <dimension ref="A1:CA39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1523,7 +1554,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J2" s="25" t="n"/>
+      <c r="J2" s="38" t="n"/>
       <c r="K2" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -1532,7 +1563,7 @@
       <c r="L2" s="26" t="n">
         <v>117</v>
       </c>
-      <c r="M2" s="27" t="n">
+      <c r="M2" s="39" t="n">
         <v>2.17</v>
       </c>
       <c r="N2" s="28" t="n">
@@ -1572,11 +1603,11 @@
       <c r="X2" s="26" t="n">
         <v>108</v>
       </c>
-      <c r="Y2" s="25" t="n"/>
+      <c r="Y2" s="38" t="n"/>
       <c r="Z2" s="26" t="n"/>
       <c r="AA2" s="28" t="n"/>
       <c r="AB2" s="28" t="n"/>
-      <c r="AC2" s="30" t="n">
+      <c r="AC2" s="40" t="n">
         <v>1.755</v>
       </c>
       <c r="AD2" s="24" t="inlineStr">
@@ -1713,11 +1744,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ2" s="25" t="n"/>
+      <c r="BJ2" s="38" t="n"/>
       <c r="BK2" s="26" t="n">
         <v>117</v>
       </c>
-      <c r="BL2" s="27" t="n">
+      <c r="BL2" s="39" t="n">
         <v>2.17</v>
       </c>
       <c r="BM2" s="28" t="n">
@@ -1727,18 +1758,18 @@
         <v>0.455446</v>
       </c>
       <c r="BO2" s="28" t="n"/>
-      <c r="BP2" s="25" t="n"/>
-      <c r="BQ2" s="27" t="n"/>
+      <c r="BP2" s="38" t="n"/>
+      <c r="BQ2" s="39" t="n"/>
       <c r="BR2" s="28" t="n"/>
       <c r="BS2" s="28" t="n"/>
       <c r="BT2" s="28" t="n"/>
-      <c r="BU2" s="25" t="n"/>
+      <c r="BU2" s="38" t="n"/>
       <c r="BV2" s="29" t="n"/>
       <c r="BW2" s="24" t="n"/>
-      <c r="BX2" s="30" t="n">
+      <c r="BX2" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY2" s="27" t="n">
+      <c r="BY2" s="39" t="n">
         <v>1.17</v>
       </c>
       <c r="BZ2" s="24" t="inlineStr">
@@ -1798,7 +1829,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J3" s="25" t="n"/>
+      <c r="J3" s="38" t="n"/>
       <c r="K3" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -1807,7 +1838,7 @@
       <c r="L3" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="M3" s="27" t="n">
+      <c r="M3" s="39" t="n">
         <v>1.75188</v>
       </c>
       <c r="N3" s="28" t="n">
@@ -1847,11 +1878,11 @@
       <c r="X3" s="26" t="n">
         <v>8</v>
       </c>
-      <c r="Y3" s="25" t="n"/>
+      <c r="Y3" s="38" t="n"/>
       <c r="Z3" s="26" t="n"/>
       <c r="AA3" s="28" t="n"/>
       <c r="AB3" s="28" t="n"/>
-      <c r="AC3" s="30" t="n">
+      <c r="AC3" s="40" t="n">
         <v>1.1278</v>
       </c>
       <c r="AD3" s="24" t="inlineStr">
@@ -1988,11 +2019,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ3" s="25" t="n"/>
+      <c r="BJ3" s="38" t="n"/>
       <c r="BK3" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="BL3" s="27" t="n">
+      <c r="BL3" s="39" t="n">
         <v>1.75188</v>
       </c>
       <c r="BM3" s="28" t="n">
@@ -2002,18 +2033,18 @@
         <v>0.567164</v>
       </c>
       <c r="BO3" s="28" t="n"/>
-      <c r="BP3" s="25" t="n"/>
-      <c r="BQ3" s="27" t="n"/>
+      <c r="BP3" s="38" t="n"/>
+      <c r="BQ3" s="39" t="n"/>
       <c r="BR3" s="28" t="n"/>
       <c r="BS3" s="28" t="n"/>
       <c r="BT3" s="28" t="n"/>
-      <c r="BU3" s="25" t="n"/>
+      <c r="BU3" s="38" t="n"/>
       <c r="BV3" s="29" t="n"/>
       <c r="BW3" s="24" t="n"/>
-      <c r="BX3" s="30" t="n">
+      <c r="BX3" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY3" s="27" t="n">
+      <c r="BY3" s="39" t="n">
         <v>0.75188</v>
       </c>
       <c r="BZ3" s="24" t="inlineStr">
@@ -2073,7 +2104,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J4" s="25" t="n"/>
+      <c r="J4" s="38" t="n"/>
       <c r="K4" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -2082,7 +2113,7 @@
       <c r="L4" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="M4" s="27" t="n">
+      <c r="M4" s="39" t="n">
         <v>1.980392</v>
       </c>
       <c r="N4" s="28" t="n">
@@ -2122,11 +2153,11 @@
       <c r="X4" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="Y4" s="25" t="n"/>
+      <c r="Y4" s="38" t="n"/>
       <c r="Z4" s="26" t="n"/>
       <c r="AA4" s="28" t="n"/>
       <c r="AB4" s="28" t="n"/>
-      <c r="AC4" s="30" t="n">
+      <c r="AC4" s="40" t="n">
         <v>-1</v>
       </c>
       <c r="AD4" s="24" t="inlineStr">
@@ -2263,11 +2294,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ4" s="25" t="n"/>
+      <c r="BJ4" s="38" t="n"/>
       <c r="BK4" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="BL4" s="27" t="n">
+      <c r="BL4" s="39" t="n">
         <v>1.980392</v>
       </c>
       <c r="BM4" s="28" t="n">
@@ -2277,18 +2308,18 @@
         <v>0.502488</v>
       </c>
       <c r="BO4" s="28" t="n"/>
-      <c r="BP4" s="25" t="n"/>
-      <c r="BQ4" s="27" t="n"/>
+      <c r="BP4" s="38" t="n"/>
+      <c r="BQ4" s="39" t="n"/>
       <c r="BR4" s="28" t="n"/>
       <c r="BS4" s="28" t="n"/>
       <c r="BT4" s="28" t="n"/>
-      <c r="BU4" s="25" t="n"/>
+      <c r="BU4" s="38" t="n"/>
       <c r="BV4" s="29" t="n"/>
       <c r="BW4" s="24" t="n"/>
-      <c r="BX4" s="30" t="n">
+      <c r="BX4" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY4" s="27" t="n">
+      <c r="BY4" s="39" t="n">
         <v>-1</v>
       </c>
       <c r="BZ4" s="24" t="inlineStr">
@@ -2348,7 +2379,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J5" s="25" t="n"/>
+      <c r="J5" s="38" t="n"/>
       <c r="K5" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -2357,7 +2388,7 @@
       <c r="L5" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="M5" s="27" t="n">
+      <c r="M5" s="39" t="n">
         <v>1.75188</v>
       </c>
       <c r="N5" s="28" t="n">
@@ -2397,11 +2428,11 @@
       <c r="X5" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="Y5" s="25" t="n"/>
+      <c r="Y5" s="38" t="n"/>
       <c r="Z5" s="26" t="n"/>
       <c r="AA5" s="28" t="n"/>
       <c r="AB5" s="28" t="n"/>
-      <c r="AC5" s="30" t="n">
+      <c r="AC5" s="40" t="n">
         <v>1.1278</v>
       </c>
       <c r="AD5" s="24" t="inlineStr">
@@ -2538,11 +2569,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ5" s="25" t="n"/>
+      <c r="BJ5" s="38" t="n"/>
       <c r="BK5" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="BL5" s="27" t="n">
+      <c r="BL5" s="39" t="n">
         <v>1.75188</v>
       </c>
       <c r="BM5" s="28" t="n">
@@ -2552,18 +2583,18 @@
         <v>0.567164</v>
       </c>
       <c r="BO5" s="28" t="n"/>
-      <c r="BP5" s="25" t="n"/>
-      <c r="BQ5" s="27" t="n"/>
+      <c r="BP5" s="38" t="n"/>
+      <c r="BQ5" s="39" t="n"/>
       <c r="BR5" s="28" t="n"/>
       <c r="BS5" s="28" t="n"/>
       <c r="BT5" s="28" t="n"/>
-      <c r="BU5" s="25" t="n"/>
+      <c r="BU5" s="38" t="n"/>
       <c r="BV5" s="29" t="n"/>
       <c r="BW5" s="24" t="n"/>
-      <c r="BX5" s="30" t="n">
+      <c r="BX5" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY5" s="27" t="n">
+      <c r="BY5" s="39" t="n">
         <v>0.75188</v>
       </c>
       <c r="BZ5" s="24" t="inlineStr">
@@ -2623,7 +2654,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J6" s="25" t="n"/>
+      <c r="J6" s="38" t="n"/>
       <c r="K6" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -2632,7 +2663,7 @@
       <c r="L6" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="M6" s="27" t="n">
+      <c r="M6" s="39" t="n">
         <v>1.961538</v>
       </c>
       <c r="N6" s="28" t="n">
@@ -2672,11 +2703,11 @@
       <c r="X6" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="Y6" s="25" t="n"/>
+      <c r="Y6" s="38" t="n"/>
       <c r="Z6" s="26" t="n"/>
       <c r="AA6" s="28" t="n"/>
       <c r="AB6" s="28" t="n"/>
-      <c r="AC6" s="30" t="n">
+      <c r="AC6" s="40" t="n">
         <v>1.2019</v>
       </c>
       <c r="AD6" s="24" t="inlineStr">
@@ -2813,11 +2844,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ6" s="25" t="n"/>
+      <c r="BJ6" s="38" t="n"/>
       <c r="BK6" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="BL6" s="27" t="n">
+      <c r="BL6" s="39" t="n">
         <v>1.961538</v>
       </c>
       <c r="BM6" s="28" t="n">
@@ -2827,18 +2858,18 @@
         <v>0.507463</v>
       </c>
       <c r="BO6" s="28" t="n"/>
-      <c r="BP6" s="25" t="n"/>
-      <c r="BQ6" s="27" t="n"/>
+      <c r="BP6" s="38" t="n"/>
+      <c r="BQ6" s="39" t="n"/>
       <c r="BR6" s="28" t="n"/>
       <c r="BS6" s="28" t="n"/>
       <c r="BT6" s="28" t="n"/>
-      <c r="BU6" s="25" t="n"/>
+      <c r="BU6" s="38" t="n"/>
       <c r="BV6" s="29" t="n"/>
       <c r="BW6" s="24" t="n"/>
-      <c r="BX6" s="30" t="n">
+      <c r="BX6" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY6" s="27" t="n">
+      <c r="BY6" s="39" t="n">
         <v>0.961538</v>
       </c>
       <c r="BZ6" s="24" t="inlineStr">
@@ -2898,7 +2929,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J7" s="25" t="n"/>
+      <c r="J7" s="38" t="n"/>
       <c r="K7" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -2907,7 +2938,7 @@
       <c r="L7" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="M7" s="27" t="n">
+      <c r="M7" s="39" t="n">
         <v>1.961538</v>
       </c>
       <c r="N7" s="28" t="n">
@@ -2947,11 +2978,11 @@
       <c r="X7" s="26" t="n">
         <v>10</v>
       </c>
-      <c r="Y7" s="25" t="n"/>
+      <c r="Y7" s="38" t="n"/>
       <c r="Z7" s="26" t="n"/>
       <c r="AA7" s="28" t="n"/>
       <c r="AB7" s="28" t="n"/>
-      <c r="AC7" s="30" t="n">
+      <c r="AC7" s="40" t="n">
         <v>-1.25</v>
       </c>
       <c r="AD7" s="24" t="inlineStr">
@@ -3088,11 +3119,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ7" s="25" t="n"/>
+      <c r="BJ7" s="38" t="n"/>
       <c r="BK7" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="BL7" s="27" t="n">
+      <c r="BL7" s="39" t="n">
         <v>1.961538</v>
       </c>
       <c r="BM7" s="28" t="n">
@@ -3102,18 +3133,18 @@
         <v>0.507463</v>
       </c>
       <c r="BO7" s="28" t="n"/>
-      <c r="BP7" s="25" t="n"/>
-      <c r="BQ7" s="27" t="n"/>
+      <c r="BP7" s="38" t="n"/>
+      <c r="BQ7" s="39" t="n"/>
       <c r="BR7" s="28" t="n"/>
       <c r="BS7" s="28" t="n"/>
       <c r="BT7" s="28" t="n"/>
-      <c r="BU7" s="25" t="n"/>
+      <c r="BU7" s="38" t="n"/>
       <c r="BV7" s="29" t="n"/>
       <c r="BW7" s="24" t="n"/>
-      <c r="BX7" s="30" t="n">
+      <c r="BX7" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY7" s="27" t="n">
+      <c r="BY7" s="39" t="n">
         <v>-1</v>
       </c>
       <c r="BZ7" s="24" t="inlineStr">
@@ -3173,7 +3204,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J8" s="25" t="n"/>
+      <c r="J8" s="38" t="n"/>
       <c r="K8" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -3182,7 +3213,7 @@
       <c r="L8" s="26" t="n">
         <v>-106</v>
       </c>
-      <c r="M8" s="27" t="n">
+      <c r="M8" s="39" t="n">
         <v>1.943396</v>
       </c>
       <c r="N8" s="28" t="n">
@@ -3222,11 +3253,11 @@
       <c r="X8" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="Y8" s="25" t="n"/>
+      <c r="Y8" s="38" t="n"/>
       <c r="Z8" s="26" t="n"/>
       <c r="AA8" s="28" t="n"/>
       <c r="AB8" s="28" t="n"/>
-      <c r="AC8" s="30" t="n">
+      <c r="AC8" s="40" t="n">
         <v>-1</v>
       </c>
       <c r="AD8" s="24" t="inlineStr">
@@ -3363,11 +3394,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ8" s="25" t="n"/>
+      <c r="BJ8" s="38" t="n"/>
       <c r="BK8" s="26" t="n">
         <v>-106</v>
       </c>
-      <c r="BL8" s="27" t="n">
+      <c r="BL8" s="39" t="n">
         <v>1.943396</v>
       </c>
       <c r="BM8" s="28" t="n">
@@ -3377,18 +3408,18 @@
         <v>0.5124379999999999</v>
       </c>
       <c r="BO8" s="28" t="n"/>
-      <c r="BP8" s="25" t="n"/>
-      <c r="BQ8" s="27" t="n"/>
+      <c r="BP8" s="38" t="n"/>
+      <c r="BQ8" s="39" t="n"/>
       <c r="BR8" s="28" t="n"/>
       <c r="BS8" s="28" t="n"/>
       <c r="BT8" s="28" t="n"/>
-      <c r="BU8" s="25" t="n"/>
+      <c r="BU8" s="38" t="n"/>
       <c r="BV8" s="29" t="n"/>
       <c r="BW8" s="24" t="n"/>
-      <c r="BX8" s="30" t="n">
+      <c r="BX8" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY8" s="27" t="n">
+      <c r="BY8" s="39" t="n">
         <v>-1</v>
       </c>
       <c r="BZ8" s="24" t="inlineStr">
@@ -3448,7 +3479,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J9" s="25" t="n"/>
+      <c r="J9" s="38" t="n"/>
       <c r="K9" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -3457,7 +3488,7 @@
       <c r="L9" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="M9" s="27" t="n">
+      <c r="M9" s="39" t="n">
         <v>1.980392</v>
       </c>
       <c r="N9" s="28" t="n">
@@ -3497,11 +3528,11 @@
       <c r="X9" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="Y9" s="25" t="n"/>
+      <c r="Y9" s="38" t="n"/>
       <c r="Z9" s="26" t="n"/>
       <c r="AA9" s="28" t="n"/>
       <c r="AB9" s="28" t="n"/>
-      <c r="AC9" s="30" t="n">
+      <c r="AC9" s="40" t="n">
         <v>0.9804</v>
       </c>
       <c r="AD9" s="24" t="inlineStr">
@@ -3638,11 +3669,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ9" s="25" t="n"/>
+      <c r="BJ9" s="38" t="n"/>
       <c r="BK9" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="BL9" s="27" t="n">
+      <c r="BL9" s="39" t="n">
         <v>1.980392</v>
       </c>
       <c r="BM9" s="28" t="n">
@@ -3652,18 +3683,18 @@
         <v>0.502488</v>
       </c>
       <c r="BO9" s="28" t="n"/>
-      <c r="BP9" s="25" t="n"/>
-      <c r="BQ9" s="27" t="n"/>
+      <c r="BP9" s="38" t="n"/>
+      <c r="BQ9" s="39" t="n"/>
       <c r="BR9" s="28" t="n"/>
       <c r="BS9" s="28" t="n"/>
       <c r="BT9" s="28" t="n"/>
-      <c r="BU9" s="25" t="n"/>
+      <c r="BU9" s="38" t="n"/>
       <c r="BV9" s="29" t="n"/>
       <c r="BW9" s="24" t="n"/>
-      <c r="BX9" s="30" t="n">
+      <c r="BX9" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY9" s="27" t="n">
+      <c r="BY9" s="39" t="n">
         <v>0.980392</v>
       </c>
       <c r="BZ9" s="24" t="inlineStr">
@@ -3723,7 +3754,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J10" s="25" t="n"/>
+      <c r="J10" s="38" t="n"/>
       <c r="K10" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -3732,7 +3763,7 @@
       <c r="L10" s="26" t="n">
         <v>-138</v>
       </c>
-      <c r="M10" s="27" t="n">
+      <c r="M10" s="39" t="n">
         <v>1.724638</v>
       </c>
       <c r="N10" s="28" t="n">
@@ -3772,11 +3803,11 @@
       <c r="X10" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="Y10" s="25" t="n"/>
+      <c r="Y10" s="38" t="n"/>
       <c r="Z10" s="26" t="n"/>
       <c r="AA10" s="28" t="n"/>
       <c r="AB10" s="28" t="n"/>
-      <c r="AC10" s="30" t="n">
+      <c r="AC10" s="40" t="n">
         <v>1.2681</v>
       </c>
       <c r="AD10" s="24" t="inlineStr">
@@ -3913,11 +3944,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ10" s="25" t="n"/>
+      <c r="BJ10" s="38" t="n"/>
       <c r="BK10" s="26" t="n">
         <v>-138</v>
       </c>
-      <c r="BL10" s="27" t="n">
+      <c r="BL10" s="39" t="n">
         <v>1.724638</v>
       </c>
       <c r="BM10" s="28" t="n">
@@ -3927,18 +3958,18 @@
         <v>0.577114</v>
       </c>
       <c r="BO10" s="28" t="n"/>
-      <c r="BP10" s="25" t="n"/>
-      <c r="BQ10" s="27" t="n"/>
+      <c r="BP10" s="38" t="n"/>
+      <c r="BQ10" s="39" t="n"/>
       <c r="BR10" s="28" t="n"/>
       <c r="BS10" s="28" t="n"/>
       <c r="BT10" s="28" t="n"/>
-      <c r="BU10" s="25" t="n"/>
+      <c r="BU10" s="38" t="n"/>
       <c r="BV10" s="29" t="n"/>
       <c r="BW10" s="24" t="n"/>
-      <c r="BX10" s="30" t="n">
+      <c r="BX10" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY10" s="27" t="n">
+      <c r="BY10" s="39" t="n">
         <v>0.724638</v>
       </c>
       <c r="BZ10" s="24" t="inlineStr">
@@ -3998,7 +4029,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J11" s="25" t="n"/>
+      <c r="J11" s="38" t="n"/>
       <c r="K11" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -4007,7 +4038,7 @@
       <c r="L11" s="26" t="n">
         <v>102</v>
       </c>
-      <c r="M11" s="27" t="n">
+      <c r="M11" s="39" t="n">
         <v>2.02</v>
       </c>
       <c r="N11" s="28" t="n">
@@ -4047,11 +4078,11 @@
       <c r="X11" s="26" t="n">
         <v>15</v>
       </c>
-      <c r="Y11" s="25" t="n"/>
+      <c r="Y11" s="38" t="n"/>
       <c r="Z11" s="26" t="n"/>
       <c r="AA11" s="28" t="n"/>
       <c r="AB11" s="28" t="n"/>
-      <c r="AC11" s="30" t="n">
+      <c r="AC11" s="40" t="n">
         <v>1.275</v>
       </c>
       <c r="AD11" s="24" t="inlineStr">
@@ -4188,11 +4219,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ11" s="25" t="n"/>
+      <c r="BJ11" s="38" t="n"/>
       <c r="BK11" s="26" t="n">
         <v>102</v>
       </c>
-      <c r="BL11" s="27" t="n">
+      <c r="BL11" s="39" t="n">
         <v>2.02</v>
       </c>
       <c r="BM11" s="28" t="n">
@@ -4202,18 +4233,18 @@
         <v>0.492537</v>
       </c>
       <c r="BO11" s="28" t="n"/>
-      <c r="BP11" s="25" t="n"/>
-      <c r="BQ11" s="27" t="n"/>
+      <c r="BP11" s="38" t="n"/>
+      <c r="BQ11" s="39" t="n"/>
       <c r="BR11" s="28" t="n"/>
       <c r="BS11" s="28" t="n"/>
       <c r="BT11" s="28" t="n"/>
-      <c r="BU11" s="25" t="n"/>
+      <c r="BU11" s="38" t="n"/>
       <c r="BV11" s="29" t="n"/>
       <c r="BW11" s="24" t="n"/>
-      <c r="BX11" s="30" t="n">
+      <c r="BX11" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY11" s="27" t="n">
+      <c r="BY11" s="39" t="n">
         <v>1.02</v>
       </c>
       <c r="BZ11" s="24" t="inlineStr">
@@ -4273,7 +4304,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J12" s="25" t="n"/>
+      <c r="J12" s="38" t="n"/>
       <c r="K12" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -4282,7 +4313,7 @@
       <c r="L12" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="M12" s="27" t="n">
+      <c r="M12" s="39" t="n">
         <v>1.980392</v>
       </c>
       <c r="N12" s="28" t="n">
@@ -4322,11 +4353,11 @@
       <c r="X12" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y12" s="25" t="n"/>
+      <c r="Y12" s="38" t="n"/>
       <c r="Z12" s="26" t="n"/>
       <c r="AA12" s="28" t="n"/>
       <c r="AB12" s="28" t="n"/>
-      <c r="AC12" s="30" t="n">
+      <c r="AC12" s="40" t="n">
         <v>-1</v>
       </c>
       <c r="AD12" s="24" t="inlineStr">
@@ -4463,11 +4494,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ12" s="25" t="n"/>
+      <c r="BJ12" s="38" t="n"/>
       <c r="BK12" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="BL12" s="27" t="n">
+      <c r="BL12" s="39" t="n">
         <v>1.980392</v>
       </c>
       <c r="BM12" s="28" t="n">
@@ -4477,18 +4508,18 @@
         <v>0.502488</v>
       </c>
       <c r="BO12" s="28" t="n"/>
-      <c r="BP12" s="25" t="n"/>
-      <c r="BQ12" s="27" t="n"/>
+      <c r="BP12" s="38" t="n"/>
+      <c r="BQ12" s="39" t="n"/>
       <c r="BR12" s="28" t="n"/>
       <c r="BS12" s="28" t="n"/>
       <c r="BT12" s="28" t="n"/>
-      <c r="BU12" s="25" t="n"/>
+      <c r="BU12" s="38" t="n"/>
       <c r="BV12" s="29" t="n"/>
       <c r="BW12" s="24" t="n"/>
-      <c r="BX12" s="30" t="n">
+      <c r="BX12" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY12" s="27" t="n">
+      <c r="BY12" s="39" t="n">
         <v>-1</v>
       </c>
       <c r="BZ12" s="24" t="inlineStr">
@@ -4548,7 +4579,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J13" s="25" t="n"/>
+      <c r="J13" s="38" t="n"/>
       <c r="K13" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -4557,7 +4588,7 @@
       <c r="L13" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="M13" s="27" t="n">
+      <c r="M13" s="39" t="n">
         <v>1.980392</v>
       </c>
       <c r="N13" s="28" t="n">
@@ -4597,11 +4628,11 @@
       <c r="X13" s="26" t="n">
         <v>7</v>
       </c>
-      <c r="Y13" s="25" t="n"/>
+      <c r="Y13" s="38" t="n"/>
       <c r="Z13" s="26" t="n"/>
       <c r="AA13" s="28" t="n"/>
       <c r="AB13" s="28" t="n"/>
-      <c r="AC13" s="30" t="n">
+      <c r="AC13" s="40" t="n">
         <v>1.2255</v>
       </c>
       <c r="AD13" s="24" t="inlineStr">
@@ -4738,11 +4769,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ13" s="25" t="n"/>
+      <c r="BJ13" s="38" t="n"/>
       <c r="BK13" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="BL13" s="27" t="n">
+      <c r="BL13" s="39" t="n">
         <v>1.980392</v>
       </c>
       <c r="BM13" s="28" t="n">
@@ -4752,18 +4783,18 @@
         <v>0.502488</v>
       </c>
       <c r="BO13" s="28" t="n"/>
-      <c r="BP13" s="25" t="n"/>
-      <c r="BQ13" s="27" t="n"/>
+      <c r="BP13" s="38" t="n"/>
+      <c r="BQ13" s="39" t="n"/>
       <c r="BR13" s="28" t="n"/>
       <c r="BS13" s="28" t="n"/>
       <c r="BT13" s="28" t="n"/>
-      <c r="BU13" s="25" t="n"/>
+      <c r="BU13" s="38" t="n"/>
       <c r="BV13" s="29" t="n"/>
       <c r="BW13" s="24" t="n"/>
-      <c r="BX13" s="30" t="n">
+      <c r="BX13" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY13" s="27" t="n">
+      <c r="BY13" s="39" t="n">
         <v>0.980392</v>
       </c>
       <c r="BZ13" s="24" t="inlineStr">
@@ -4823,7 +4854,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J14" s="25" t="n"/>
+      <c r="J14" s="38" t="n"/>
       <c r="K14" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -4832,7 +4863,7 @@
       <c r="L14" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="M14" s="27" t="n">
+      <c r="M14" s="39" t="n">
         <v>1.961538</v>
       </c>
       <c r="N14" s="28" t="n">
@@ -4872,11 +4903,11 @@
       <c r="X14" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="Y14" s="25" t="n"/>
+      <c r="Y14" s="38" t="n"/>
       <c r="Z14" s="26" t="n"/>
       <c r="AA14" s="28" t="n"/>
       <c r="AB14" s="28" t="n"/>
-      <c r="AC14" s="30" t="n">
+      <c r="AC14" s="40" t="n">
         <v>-0.75</v>
       </c>
       <c r="AD14" s="24" t="inlineStr">
@@ -5013,11 +5044,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ14" s="25" t="n"/>
+      <c r="BJ14" s="38" t="n"/>
       <c r="BK14" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="BL14" s="27" t="n">
+      <c r="BL14" s="39" t="n">
         <v>1.961538</v>
       </c>
       <c r="BM14" s="28" t="n">
@@ -5027,18 +5058,18 @@
         <v>0.507463</v>
       </c>
       <c r="BO14" s="28" t="n"/>
-      <c r="BP14" s="25" t="n"/>
-      <c r="BQ14" s="27" t="n"/>
+      <c r="BP14" s="38" t="n"/>
+      <c r="BQ14" s="39" t="n"/>
       <c r="BR14" s="28" t="n"/>
       <c r="BS14" s="28" t="n"/>
       <c r="BT14" s="28" t="n"/>
-      <c r="BU14" s="25" t="n"/>
+      <c r="BU14" s="38" t="n"/>
       <c r="BV14" s="29" t="n"/>
       <c r="BW14" s="24" t="n"/>
-      <c r="BX14" s="30" t="n">
+      <c r="BX14" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY14" s="27" t="n">
+      <c r="BY14" s="39" t="n">
         <v>-1</v>
       </c>
       <c r="BZ14" s="24" t="inlineStr">
@@ -5098,7 +5129,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J15" s="25" t="n"/>
+      <c r="J15" s="38" t="n"/>
       <c r="K15" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -5107,7 +5138,7 @@
       <c r="L15" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="M15" s="27" t="n">
+      <c r="M15" s="39" t="n">
         <v>1.961538</v>
       </c>
       <c r="N15" s="28" t="n">
@@ -5147,11 +5178,11 @@
       <c r="X15" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="Y15" s="25" t="n"/>
+      <c r="Y15" s="38" t="n"/>
       <c r="Z15" s="26" t="n"/>
       <c r="AA15" s="28" t="n"/>
       <c r="AB15" s="28" t="n"/>
-      <c r="AC15" s="30" t="n">
+      <c r="AC15" s="40" t="n">
         <v>-1</v>
       </c>
       <c r="AD15" s="24" t="inlineStr">
@@ -5288,11 +5319,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ15" s="25" t="n"/>
+      <c r="BJ15" s="38" t="n"/>
       <c r="BK15" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="BL15" s="27" t="n">
+      <c r="BL15" s="39" t="n">
         <v>1.961538</v>
       </c>
       <c r="BM15" s="28" t="n">
@@ -5302,18 +5333,18 @@
         <v>0.507463</v>
       </c>
       <c r="BO15" s="28" t="n"/>
-      <c r="BP15" s="25" t="n"/>
-      <c r="BQ15" s="27" t="n"/>
+      <c r="BP15" s="38" t="n"/>
+      <c r="BQ15" s="39" t="n"/>
       <c r="BR15" s="28" t="n"/>
       <c r="BS15" s="28" t="n"/>
       <c r="BT15" s="28" t="n"/>
-      <c r="BU15" s="25" t="n"/>
+      <c r="BU15" s="38" t="n"/>
       <c r="BV15" s="29" t="n"/>
       <c r="BW15" s="24" t="n"/>
-      <c r="BX15" s="30" t="n">
+      <c r="BX15" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY15" s="27" t="n">
+      <c r="BY15" s="39" t="n">
         <v>-1</v>
       </c>
       <c r="BZ15" s="24" t="inlineStr">
@@ -5373,7 +5404,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J16" s="25" t="n"/>
+      <c r="J16" s="38" t="n"/>
       <c r="K16" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -5382,7 +5413,7 @@
       <c r="L16" s="26" t="n">
         <v>-111</v>
       </c>
-      <c r="M16" s="27" t="n">
+      <c r="M16" s="39" t="n">
         <v>1.900901</v>
       </c>
       <c r="N16" s="28" t="n">
@@ -5422,11 +5453,11 @@
       <c r="X16" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="Y16" s="25" t="n"/>
+      <c r="Y16" s="38" t="n"/>
       <c r="Z16" s="26" t="n"/>
       <c r="AA16" s="28" t="n"/>
       <c r="AB16" s="28" t="n"/>
-      <c r="AC16" s="30" t="n">
+      <c r="AC16" s="40" t="n">
         <v>-1.5</v>
       </c>
       <c r="AD16" s="24" t="inlineStr">
@@ -5563,11 +5594,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ16" s="25" t="n"/>
+      <c r="BJ16" s="38" t="n"/>
       <c r="BK16" s="26" t="n">
         <v>-111</v>
       </c>
-      <c r="BL16" s="27" t="n">
+      <c r="BL16" s="39" t="n">
         <v>1.900901</v>
       </c>
       <c r="BM16" s="28" t="n">
@@ -5577,18 +5608,18 @@
         <v>0.522388</v>
       </c>
       <c r="BO16" s="28" t="n"/>
-      <c r="BP16" s="25" t="n"/>
-      <c r="BQ16" s="27" t="n"/>
+      <c r="BP16" s="38" t="n"/>
+      <c r="BQ16" s="39" t="n"/>
       <c r="BR16" s="28" t="n"/>
       <c r="BS16" s="28" t="n"/>
       <c r="BT16" s="28" t="n"/>
-      <c r="BU16" s="25" t="n"/>
+      <c r="BU16" s="38" t="n"/>
       <c r="BV16" s="29" t="n"/>
       <c r="BW16" s="24" t="n"/>
-      <c r="BX16" s="30" t="n">
+      <c r="BX16" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY16" s="27" t="n">
+      <c r="BY16" s="39" t="n">
         <v>-1</v>
       </c>
       <c r="BZ16" s="24" t="inlineStr">
@@ -5648,7 +5679,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J17" s="25" t="n"/>
+      <c r="J17" s="38" t="n"/>
       <c r="K17" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -5657,7 +5688,7 @@
       <c r="L17" s="26" t="n">
         <v>-108</v>
       </c>
-      <c r="M17" s="27" t="n">
+      <c r="M17" s="39" t="n">
         <v>1.925926</v>
       </c>
       <c r="N17" s="28" t="n">
@@ -5697,11 +5728,11 @@
       <c r="X17" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="Y17" s="25" t="n"/>
+      <c r="Y17" s="38" t="n"/>
       <c r="Z17" s="26" t="n"/>
       <c r="AA17" s="28" t="n"/>
       <c r="AB17" s="28" t="n"/>
-      <c r="AC17" s="30" t="n">
+      <c r="AC17" s="40" t="n">
         <v>0.9258999999999999</v>
       </c>
       <c r="AD17" s="24" t="inlineStr">
@@ -5838,11 +5869,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ17" s="25" t="n"/>
+      <c r="BJ17" s="38" t="n"/>
       <c r="BK17" s="26" t="n">
         <v>-108</v>
       </c>
-      <c r="BL17" s="27" t="n">
+      <c r="BL17" s="39" t="n">
         <v>1.925926</v>
       </c>
       <c r="BM17" s="28" t="n">
@@ -5852,18 +5883,18 @@
         <v>0.5148509999999999</v>
       </c>
       <c r="BO17" s="28" t="n"/>
-      <c r="BP17" s="25" t="n"/>
-      <c r="BQ17" s="27" t="n"/>
+      <c r="BP17" s="38" t="n"/>
+      <c r="BQ17" s="39" t="n"/>
       <c r="BR17" s="28" t="n"/>
       <c r="BS17" s="28" t="n"/>
       <c r="BT17" s="28" t="n"/>
-      <c r="BU17" s="25" t="n"/>
+      <c r="BU17" s="38" t="n"/>
       <c r="BV17" s="29" t="n"/>
       <c r="BW17" s="24" t="n"/>
-      <c r="BX17" s="30" t="n">
+      <c r="BX17" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY17" s="27" t="n">
+      <c r="BY17" s="39" t="n">
         <v>0.925926</v>
       </c>
       <c r="BZ17" s="24" t="inlineStr">
@@ -5923,7 +5954,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J18" s="25" t="n"/>
+      <c r="J18" s="38" t="n"/>
       <c r="K18" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -5932,7 +5963,7 @@
       <c r="L18" s="26" t="n">
         <v>111</v>
       </c>
-      <c r="M18" s="27" t="n">
+      <c r="M18" s="39" t="n">
         <v>2.11</v>
       </c>
       <c r="N18" s="28" t="n">
@@ -5972,11 +6003,11 @@
       <c r="X18" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="Y18" s="25" t="n"/>
+      <c r="Y18" s="38" t="n"/>
       <c r="Z18" s="26" t="n"/>
       <c r="AA18" s="28" t="n"/>
       <c r="AB18" s="28" t="n"/>
-      <c r="AC18" s="30" t="n">
+      <c r="AC18" s="40" t="n">
         <v>-1.25</v>
       </c>
       <c r="AD18" s="24" t="inlineStr">
@@ -6113,11 +6144,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ18" s="25" t="n"/>
+      <c r="BJ18" s="38" t="n"/>
       <c r="BK18" s="26" t="n">
         <v>111</v>
       </c>
-      <c r="BL18" s="27" t="n">
+      <c r="BL18" s="39" t="n">
         <v>2.11</v>
       </c>
       <c r="BM18" s="28" t="n">
@@ -6127,18 +6158,18 @@
         <v>0.472637</v>
       </c>
       <c r="BO18" s="28" t="n"/>
-      <c r="BP18" s="25" t="n"/>
-      <c r="BQ18" s="27" t="n"/>
+      <c r="BP18" s="38" t="n"/>
+      <c r="BQ18" s="39" t="n"/>
       <c r="BR18" s="28" t="n"/>
       <c r="BS18" s="28" t="n"/>
       <c r="BT18" s="28" t="n"/>
-      <c r="BU18" s="25" t="n"/>
+      <c r="BU18" s="38" t="n"/>
       <c r="BV18" s="29" t="n"/>
       <c r="BW18" s="24" t="n"/>
-      <c r="BX18" s="30" t="n">
+      <c r="BX18" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY18" s="27" t="n">
+      <c r="BY18" s="39" t="n">
         <v>-1</v>
       </c>
       <c r="BZ18" s="24" t="inlineStr">
@@ -6198,7 +6229,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J19" s="25" t="n"/>
+      <c r="J19" s="38" t="n"/>
       <c r="K19" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -6207,7 +6238,7 @@
       <c r="L19" s="26" t="n">
         <v>-125</v>
       </c>
-      <c r="M19" s="27" t="n">
+      <c r="M19" s="39" t="n">
         <v>1.8</v>
       </c>
       <c r="N19" s="28" t="n">
@@ -6247,11 +6278,11 @@
       <c r="X19" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="Y19" s="25" t="n"/>
+      <c r="Y19" s="38" t="n"/>
       <c r="Z19" s="26" t="n"/>
       <c r="AA19" s="28" t="n"/>
       <c r="AB19" s="28" t="n"/>
-      <c r="AC19" s="30" t="n">
+      <c r="AC19" s="40" t="n">
         <v>1.2</v>
       </c>
       <c r="AD19" s="24" t="inlineStr">
@@ -6388,11 +6419,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ19" s="25" t="n"/>
+      <c r="BJ19" s="38" t="n"/>
       <c r="BK19" s="26" t="n">
         <v>-125</v>
       </c>
-      <c r="BL19" s="27" t="n">
+      <c r="BL19" s="39" t="n">
         <v>1.8</v>
       </c>
       <c r="BM19" s="28" t="n">
@@ -6402,18 +6433,18 @@
         <v>0.552239</v>
       </c>
       <c r="BO19" s="28" t="n"/>
-      <c r="BP19" s="25" t="n"/>
-      <c r="BQ19" s="27" t="n"/>
+      <c r="BP19" s="38" t="n"/>
+      <c r="BQ19" s="39" t="n"/>
       <c r="BR19" s="28" t="n"/>
       <c r="BS19" s="28" t="n"/>
       <c r="BT19" s="28" t="n"/>
-      <c r="BU19" s="25" t="n"/>
+      <c r="BU19" s="38" t="n"/>
       <c r="BV19" s="29" t="n"/>
       <c r="BW19" s="24" t="n"/>
-      <c r="BX19" s="30" t="n">
+      <c r="BX19" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY19" s="27" t="n">
+      <c r="BY19" s="39" t="n">
         <v>0.8</v>
       </c>
       <c r="BZ19" s="24" t="inlineStr">
@@ -6473,7 +6504,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J20" s="25" t="n"/>
+      <c r="J20" s="38" t="n"/>
       <c r="K20" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -6482,7 +6513,7 @@
       <c r="L20" s="26" t="n">
         <v>106</v>
       </c>
-      <c r="M20" s="27" t="n">
+      <c r="M20" s="39" t="n">
         <v>2.06</v>
       </c>
       <c r="N20" s="28" t="n">
@@ -6522,11 +6553,11 @@
       <c r="X20" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y20" s="25" t="n"/>
+      <c r="Y20" s="38" t="n"/>
       <c r="Z20" s="26" t="n"/>
       <c r="AA20" s="28" t="n"/>
       <c r="AB20" s="28" t="n"/>
-      <c r="AC20" s="30" t="n">
+      <c r="AC20" s="40" t="n">
         <v>0.795</v>
       </c>
       <c r="AD20" s="24" t="inlineStr">
@@ -6663,11 +6694,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ20" s="25" t="n"/>
+      <c r="BJ20" s="38" t="n"/>
       <c r="BK20" s="26" t="n">
         <v>106</v>
       </c>
-      <c r="BL20" s="27" t="n">
+      <c r="BL20" s="39" t="n">
         <v>2.06</v>
       </c>
       <c r="BM20" s="28" t="n">
@@ -6677,18 +6708,18 @@
         <v>0.482587</v>
       </c>
       <c r="BO20" s="28" t="n"/>
-      <c r="BP20" s="25" t="n"/>
-      <c r="BQ20" s="27" t="n"/>
+      <c r="BP20" s="38" t="n"/>
+      <c r="BQ20" s="39" t="n"/>
       <c r="BR20" s="28" t="n"/>
       <c r="BS20" s="28" t="n"/>
       <c r="BT20" s="28" t="n"/>
-      <c r="BU20" s="25" t="n"/>
+      <c r="BU20" s="38" t="n"/>
       <c r="BV20" s="29" t="n"/>
       <c r="BW20" s="24" t="n"/>
-      <c r="BX20" s="30" t="n">
+      <c r="BX20" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY20" s="27" t="n">
+      <c r="BY20" s="39" t="n">
         <v>1.06</v>
       </c>
       <c r="BZ20" s="24" t="inlineStr">
@@ -6748,7 +6779,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J21" s="25" t="n"/>
+      <c r="J21" s="38" t="n"/>
       <c r="K21" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -6757,7 +6788,7 @@
       <c r="L21" s="26" t="n">
         <v>-106</v>
       </c>
-      <c r="M21" s="27" t="n">
+      <c r="M21" s="39" t="n">
         <v>1.943396</v>
       </c>
       <c r="N21" s="28" t="n">
@@ -6799,11 +6830,11 @@
       <c r="X21" s="26" t="n">
         <v>10</v>
       </c>
-      <c r="Y21" s="25" t="n"/>
+      <c r="Y21" s="38" t="n"/>
       <c r="Z21" s="26" t="n"/>
       <c r="AA21" s="28" t="n"/>
       <c r="AB21" s="28" t="n"/>
-      <c r="AC21" s="30" t="n">
+      <c r="AC21" s="40" t="n">
         <v>0.9434</v>
       </c>
       <c r="AD21" s="24" t="inlineStr">
@@ -6862,11 +6893,11 @@
         </is>
       </c>
       <c r="BI21" s="24" t="n"/>
-      <c r="BJ21" s="25" t="n"/>
+      <c r="BJ21" s="38" t="n"/>
       <c r="BK21" s="26" t="n">
         <v>-106</v>
       </c>
-      <c r="BL21" s="27" t="n">
+      <c r="BL21" s="39" t="n">
         <v>1.943396</v>
       </c>
       <c r="BM21" s="28" t="n">
@@ -6876,16 +6907,16 @@
         <v>0.5124379999999999</v>
       </c>
       <c r="BO21" s="28" t="n"/>
-      <c r="BP21" s="25" t="n"/>
-      <c r="BQ21" s="27" t="n"/>
+      <c r="BP21" s="38" t="n"/>
+      <c r="BQ21" s="39" t="n"/>
       <c r="BR21" s="28" t="n"/>
       <c r="BS21" s="28" t="n"/>
       <c r="BT21" s="28" t="n"/>
-      <c r="BU21" s="25" t="n"/>
+      <c r="BU21" s="38" t="n"/>
       <c r="BV21" s="29" t="n"/>
       <c r="BW21" s="24" t="n"/>
-      <c r="BX21" s="30" t="n"/>
-      <c r="BY21" s="27" t="n"/>
+      <c r="BX21" s="40" t="n"/>
+      <c r="BY21" s="39" t="n"/>
       <c r="BZ21" s="24" t="n"/>
       <c r="CA21" s="31" t="n"/>
     </row>
@@ -6935,7 +6966,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J22" s="25" t="n"/>
+      <c r="J22" s="38" t="n"/>
       <c r="K22" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -6944,7 +6975,7 @@
       <c r="L22" s="26" t="n">
         <v>-106</v>
       </c>
-      <c r="M22" s="27" t="n">
+      <c r="M22" s="39" t="n">
         <v>1.943396</v>
       </c>
       <c r="N22" s="28" t="n">
@@ -6986,11 +7017,11 @@
       <c r="X22" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="Y22" s="25" t="n"/>
+      <c r="Y22" s="38" t="n"/>
       <c r="Z22" s="26" t="n"/>
       <c r="AA22" s="28" t="n"/>
       <c r="AB22" s="28" t="n"/>
-      <c r="AC22" s="30" t="n">
+      <c r="AC22" s="40" t="n">
         <v>0.9434</v>
       </c>
       <c r="AD22" s="24" t="inlineStr">
@@ -7049,11 +7080,11 @@
         </is>
       </c>
       <c r="BI22" s="24" t="n"/>
-      <c r="BJ22" s="25" t="n"/>
+      <c r="BJ22" s="38" t="n"/>
       <c r="BK22" s="26" t="n">
         <v>-106</v>
       </c>
-      <c r="BL22" s="27" t="n">
+      <c r="BL22" s="39" t="n">
         <v>1.943396</v>
       </c>
       <c r="BM22" s="28" t="n">
@@ -7063,16 +7094,16 @@
         <v>0.5124379999999999</v>
       </c>
       <c r="BO22" s="28" t="n"/>
-      <c r="BP22" s="25" t="n"/>
-      <c r="BQ22" s="27" t="n"/>
+      <c r="BP22" s="38" t="n"/>
+      <c r="BQ22" s="39" t="n"/>
       <c r="BR22" s="28" t="n"/>
       <c r="BS22" s="28" t="n"/>
       <c r="BT22" s="28" t="n"/>
-      <c r="BU22" s="25" t="n"/>
+      <c r="BU22" s="38" t="n"/>
       <c r="BV22" s="29" t="n"/>
       <c r="BW22" s="24" t="n"/>
-      <c r="BX22" s="30" t="n"/>
-      <c r="BY22" s="27" t="n"/>
+      <c r="BX22" s="40" t="n"/>
+      <c r="BY22" s="39" t="n"/>
       <c r="BZ22" s="24" t="n"/>
       <c r="CA22" s="31" t="n"/>
     </row>
@@ -7122,7 +7153,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J23" s="25" t="n"/>
+      <c r="J23" s="38" t="n"/>
       <c r="K23" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -7131,7 +7162,7 @@
       <c r="L23" s="26" t="n">
         <v>-141</v>
       </c>
-      <c r="M23" s="27" t="n">
+      <c r="M23" s="39" t="n">
         <v>1.70922</v>
       </c>
       <c r="N23" s="28" t="n">
@@ -7173,11 +7204,11 @@
       <c r="X23" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y23" s="25" t="n"/>
+      <c r="Y23" s="38" t="n"/>
       <c r="Z23" s="26" t="n"/>
       <c r="AA23" s="28" t="n"/>
       <c r="AB23" s="28" t="n"/>
-      <c r="AC23" s="30" t="n">
+      <c r="AC23" s="40" t="n">
         <v>1.2411</v>
       </c>
       <c r="AD23" s="24" t="inlineStr">
@@ -7236,11 +7267,11 @@
         </is>
       </c>
       <c r="BI23" s="24" t="n"/>
-      <c r="BJ23" s="25" t="n"/>
+      <c r="BJ23" s="38" t="n"/>
       <c r="BK23" s="26" t="n">
         <v>-141</v>
       </c>
-      <c r="BL23" s="27" t="n">
+      <c r="BL23" s="39" t="n">
         <v>1.70922</v>
       </c>
       <c r="BM23" s="28" t="n">
@@ -7250,16 +7281,16 @@
         <v>0.58209</v>
       </c>
       <c r="BO23" s="28" t="n"/>
-      <c r="BP23" s="25" t="n"/>
-      <c r="BQ23" s="27" t="n"/>
+      <c r="BP23" s="38" t="n"/>
+      <c r="BQ23" s="39" t="n"/>
       <c r="BR23" s="28" t="n"/>
       <c r="BS23" s="28" t="n"/>
       <c r="BT23" s="28" t="n"/>
-      <c r="BU23" s="25" t="n"/>
+      <c r="BU23" s="38" t="n"/>
       <c r="BV23" s="29" t="n"/>
       <c r="BW23" s="24" t="n"/>
-      <c r="BX23" s="30" t="n"/>
-      <c r="BY23" s="27" t="n"/>
+      <c r="BX23" s="40" t="n"/>
+      <c r="BY23" s="39" t="n"/>
       <c r="BZ23" s="24" t="n"/>
       <c r="CA23" s="31" t="n"/>
     </row>
@@ -7309,7 +7340,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J24" s="25" t="n"/>
+      <c r="J24" s="38" t="n"/>
       <c r="K24" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -7318,7 +7349,7 @@
       <c r="L24" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="M24" s="27" t="n">
+      <c r="M24" s="39" t="n">
         <v>1.75188</v>
       </c>
       <c r="N24" s="28" t="n">
@@ -7360,11 +7391,11 @@
       <c r="X24" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y24" s="25" t="n"/>
+      <c r="Y24" s="38" t="n"/>
       <c r="Z24" s="26" t="n"/>
       <c r="AA24" s="28" t="n"/>
       <c r="AB24" s="28" t="n"/>
-      <c r="AC24" s="30" t="n">
+      <c r="AC24" s="40" t="n">
         <v>-1.5</v>
       </c>
       <c r="AD24" s="24" t="inlineStr">
@@ -7423,11 +7454,11 @@
         </is>
       </c>
       <c r="BI24" s="24" t="n"/>
-      <c r="BJ24" s="25" t="n"/>
+      <c r="BJ24" s="38" t="n"/>
       <c r="BK24" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="BL24" s="27" t="n">
+      <c r="BL24" s="39" t="n">
         <v>1.75188</v>
       </c>
       <c r="BM24" s="28" t="n">
@@ -7437,16 +7468,16 @@
         <v>0.567164</v>
       </c>
       <c r="BO24" s="28" t="n"/>
-      <c r="BP24" s="25" t="n"/>
-      <c r="BQ24" s="27" t="n"/>
+      <c r="BP24" s="38" t="n"/>
+      <c r="BQ24" s="39" t="n"/>
       <c r="BR24" s="28" t="n"/>
       <c r="BS24" s="28" t="n"/>
       <c r="BT24" s="28" t="n"/>
-      <c r="BU24" s="25" t="n"/>
+      <c r="BU24" s="38" t="n"/>
       <c r="BV24" s="29" t="n"/>
       <c r="BW24" s="24" t="n"/>
-      <c r="BX24" s="30" t="n"/>
-      <c r="BY24" s="27" t="n"/>
+      <c r="BX24" s="40" t="n"/>
+      <c r="BY24" s="39" t="n"/>
       <c r="BZ24" s="24" t="n"/>
       <c r="CA24" s="31" t="n"/>
     </row>
@@ -7496,7 +7527,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J25" s="25" t="n"/>
+      <c r="J25" s="38" t="n"/>
       <c r="K25" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -7505,7 +7536,7 @@
       <c r="L25" s="26" t="n">
         <v>104</v>
       </c>
-      <c r="M25" s="27" t="n">
+      <c r="M25" s="39" t="n">
         <v>2.04</v>
       </c>
       <c r="N25" s="28" t="n">
@@ -7547,11 +7578,11 @@
       <c r="X25" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y25" s="25" t="n"/>
+      <c r="Y25" s="38" t="n"/>
       <c r="Z25" s="26" t="n"/>
       <c r="AA25" s="28" t="n"/>
       <c r="AB25" s="28" t="n"/>
-      <c r="AC25" s="30" t="n">
+      <c r="AC25" s="40" t="n">
         <v>1.3</v>
       </c>
       <c r="AD25" s="24" t="inlineStr">
@@ -7610,11 +7641,11 @@
         </is>
       </c>
       <c r="BI25" s="24" t="n"/>
-      <c r="BJ25" s="25" t="n"/>
+      <c r="BJ25" s="38" t="n"/>
       <c r="BK25" s="26" t="n">
         <v>104</v>
       </c>
-      <c r="BL25" s="27" t="n">
+      <c r="BL25" s="39" t="n">
         <v>2.04</v>
       </c>
       <c r="BM25" s="28" t="n">
@@ -7624,16 +7655,16 @@
         <v>0.487562</v>
       </c>
       <c r="BO25" s="28" t="n"/>
-      <c r="BP25" s="25" t="n"/>
-      <c r="BQ25" s="27" t="n"/>
+      <c r="BP25" s="38" t="n"/>
+      <c r="BQ25" s="39" t="n"/>
       <c r="BR25" s="28" t="n"/>
       <c r="BS25" s="28" t="n"/>
       <c r="BT25" s="28" t="n"/>
-      <c r="BU25" s="25" t="n"/>
+      <c r="BU25" s="38" t="n"/>
       <c r="BV25" s="29" t="n"/>
       <c r="BW25" s="24" t="n"/>
-      <c r="BX25" s="30" t="n"/>
-      <c r="BY25" s="27" t="n"/>
+      <c r="BX25" s="40" t="n"/>
+      <c r="BY25" s="39" t="n"/>
       <c r="BZ25" s="24" t="n"/>
       <c r="CA25" s="31" t="n"/>
     </row>
@@ -7683,7 +7714,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J26" s="25" t="n"/>
+      <c r="J26" s="38" t="n"/>
       <c r="K26" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -7692,7 +7723,7 @@
       <c r="L26" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="M26" s="27" t="n">
+      <c r="M26" s="39" t="n">
         <v>1.961538</v>
       </c>
       <c r="N26" s="28" t="n">
@@ -7734,11 +7765,11 @@
       <c r="X26" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="Y26" s="25" t="n"/>
+      <c r="Y26" s="38" t="n"/>
       <c r="Z26" s="26" t="n"/>
       <c r="AA26" s="28" t="n"/>
       <c r="AB26" s="28" t="n"/>
-      <c r="AC26" s="30" t="n">
+      <c r="AC26" s="40" t="n">
         <v>0.9615</v>
       </c>
       <c r="AD26" s="24" t="inlineStr">
@@ -7797,11 +7828,11 @@
         </is>
       </c>
       <c r="BI26" s="24" t="n"/>
-      <c r="BJ26" s="25" t="n"/>
+      <c r="BJ26" s="38" t="n"/>
       <c r="BK26" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="BL26" s="27" t="n">
+      <c r="BL26" s="39" t="n">
         <v>1.961538</v>
       </c>
       <c r="BM26" s="28" t="n">
@@ -7811,16 +7842,16 @@
         <v>0.507463</v>
       </c>
       <c r="BO26" s="28" t="n"/>
-      <c r="BP26" s="25" t="n"/>
-      <c r="BQ26" s="27" t="n"/>
+      <c r="BP26" s="38" t="n"/>
+      <c r="BQ26" s="39" t="n"/>
       <c r="BR26" s="28" t="n"/>
       <c r="BS26" s="28" t="n"/>
       <c r="BT26" s="28" t="n"/>
-      <c r="BU26" s="25" t="n"/>
+      <c r="BU26" s="38" t="n"/>
       <c r="BV26" s="29" t="n"/>
       <c r="BW26" s="24" t="n"/>
-      <c r="BX26" s="30" t="n"/>
-      <c r="BY26" s="27" t="n"/>
+      <c r="BX26" s="40" t="n"/>
+      <c r="BY26" s="39" t="n"/>
       <c r="BZ26" s="24" t="n"/>
       <c r="CA26" s="31" t="n"/>
     </row>
@@ -7870,7 +7901,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J27" s="25" t="n"/>
+      <c r="J27" s="38" t="n"/>
       <c r="K27" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -7879,7 +7910,7 @@
       <c r="L27" s="26" t="n">
         <v>120</v>
       </c>
-      <c r="M27" s="27" t="n">
+      <c r="M27" s="39" t="n">
         <v>2.2</v>
       </c>
       <c r="N27" s="28" t="n">
@@ -7921,11 +7952,11 @@
       <c r="X27" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="Y27" s="25" t="n"/>
+      <c r="Y27" s="38" t="n"/>
       <c r="Z27" s="26" t="n"/>
       <c r="AA27" s="28" t="n"/>
       <c r="AB27" s="28" t="n"/>
-      <c r="AC27" s="30" t="n">
+      <c r="AC27" s="40" t="n">
         <v>-0.75</v>
       </c>
       <c r="AD27" s="24" t="inlineStr">
@@ -7984,11 +8015,11 @@
         </is>
       </c>
       <c r="BI27" s="24" t="n"/>
-      <c r="BJ27" s="25" t="n"/>
+      <c r="BJ27" s="38" t="n"/>
       <c r="BK27" s="26" t="n">
         <v>120</v>
       </c>
-      <c r="BL27" s="27" t="n">
+      <c r="BL27" s="39" t="n">
         <v>2.2</v>
       </c>
       <c r="BM27" s="28" t="n">
@@ -7998,16 +8029,16 @@
         <v>0.452736</v>
       </c>
       <c r="BO27" s="28" t="n"/>
-      <c r="BP27" s="25" t="n"/>
-      <c r="BQ27" s="27" t="n"/>
+      <c r="BP27" s="38" t="n"/>
+      <c r="BQ27" s="39" t="n"/>
       <c r="BR27" s="28" t="n"/>
       <c r="BS27" s="28" t="n"/>
       <c r="BT27" s="28" t="n"/>
-      <c r="BU27" s="25" t="n"/>
+      <c r="BU27" s="38" t="n"/>
       <c r="BV27" s="29" t="n"/>
       <c r="BW27" s="24" t="n"/>
-      <c r="BX27" s="30" t="n"/>
-      <c r="BY27" s="27" t="n"/>
+      <c r="BX27" s="40" t="n"/>
+      <c r="BY27" s="39" t="n"/>
       <c r="BZ27" s="24" t="n"/>
       <c r="CA27" s="31" t="n"/>
     </row>
@@ -8057,7 +8088,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J28" s="25" t="n"/>
+      <c r="J28" s="38" t="n"/>
       <c r="K28" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -8066,7 +8097,7 @@
       <c r="L28" s="26" t="n">
         <v>100</v>
       </c>
-      <c r="M28" s="27" t="n">
+      <c r="M28" s="39" t="n">
         <v>2</v>
       </c>
       <c r="N28" s="28" t="n">
@@ -8108,11 +8139,11 @@
       <c r="X28" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="Y28" s="25" t="n"/>
+      <c r="Y28" s="38" t="n"/>
       <c r="Z28" s="26" t="n"/>
       <c r="AA28" s="28" t="n"/>
       <c r="AB28" s="28" t="n"/>
-      <c r="AC28" s="30" t="n">
+      <c r="AC28" s="40" t="n">
         <v>-0.75</v>
       </c>
       <c r="AD28" s="24" t="inlineStr">
@@ -8171,11 +8202,11 @@
         </is>
       </c>
       <c r="BI28" s="24" t="n"/>
-      <c r="BJ28" s="25" t="n"/>
+      <c r="BJ28" s="38" t="n"/>
       <c r="BK28" s="26" t="n">
         <v>100</v>
       </c>
-      <c r="BL28" s="27" t="n">
+      <c r="BL28" s="39" t="n">
         <v>2</v>
       </c>
       <c r="BM28" s="28" t="n">
@@ -8185,16 +8216,16 @@
         <v>0.497512</v>
       </c>
       <c r="BO28" s="28" t="n"/>
-      <c r="BP28" s="25" t="n"/>
-      <c r="BQ28" s="27" t="n"/>
+      <c r="BP28" s="38" t="n"/>
+      <c r="BQ28" s="39" t="n"/>
       <c r="BR28" s="28" t="n"/>
       <c r="BS28" s="28" t="n"/>
       <c r="BT28" s="28" t="n"/>
-      <c r="BU28" s="25" t="n"/>
+      <c r="BU28" s="38" t="n"/>
       <c r="BV28" s="29" t="n"/>
       <c r="BW28" s="24" t="n"/>
-      <c r="BX28" s="30" t="n"/>
-      <c r="BY28" s="27" t="n"/>
+      <c r="BX28" s="40" t="n"/>
+      <c r="BY28" s="39" t="n"/>
       <c r="BZ28" s="24" t="n"/>
       <c r="CA28" s="31" t="n"/>
     </row>
@@ -8244,7 +8275,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J29" s="25" t="n"/>
+      <c r="J29" s="38" t="n"/>
       <c r="K29" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -8253,7 +8284,7 @@
       <c r="L29" s="26" t="n">
         <v>108</v>
       </c>
-      <c r="M29" s="27" t="n">
+      <c r="M29" s="39" t="n">
         <v>2.08</v>
       </c>
       <c r="N29" s="28" t="n">
@@ -8293,11 +8324,11 @@
       <c r="X29" s="26" t="n">
         <v>8</v>
       </c>
-      <c r="Y29" s="25" t="n"/>
+      <c r="Y29" s="38" t="n"/>
       <c r="Z29" s="26" t="n"/>
       <c r="AA29" s="28" t="n"/>
       <c r="AB29" s="28" t="n"/>
-      <c r="AC29" s="30" t="n">
+      <c r="AC29" s="40" t="n">
         <v>1.35</v>
       </c>
       <c r="AD29" s="24" t="inlineStr">
@@ -8434,11 +8465,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ29" s="25" t="n"/>
+      <c r="BJ29" s="38" t="n"/>
       <c r="BK29" s="26" t="n">
         <v>108</v>
       </c>
-      <c r="BL29" s="27" t="n">
+      <c r="BL29" s="39" t="n">
         <v>2.08</v>
       </c>
       <c r="BM29" s="28" t="n">
@@ -8448,18 +8479,18 @@
         <v>0.477612</v>
       </c>
       <c r="BO29" s="28" t="n"/>
-      <c r="BP29" s="25" t="n"/>
-      <c r="BQ29" s="27" t="n"/>
+      <c r="BP29" s="38" t="n"/>
+      <c r="BQ29" s="39" t="n"/>
       <c r="BR29" s="28" t="n"/>
       <c r="BS29" s="28" t="n"/>
       <c r="BT29" s="28" t="n"/>
-      <c r="BU29" s="25" t="n"/>
+      <c r="BU29" s="38" t="n"/>
       <c r="BV29" s="29" t="n"/>
       <c r="BW29" s="24" t="n"/>
-      <c r="BX29" s="30" t="n">
+      <c r="BX29" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY29" s="27" t="n">
+      <c r="BY29" s="39" t="n">
         <v>1.08</v>
       </c>
       <c r="BZ29" s="24" t="inlineStr">
@@ -8519,7 +8550,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J30" s="25" t="n"/>
+      <c r="J30" s="38" t="n"/>
       <c r="K30" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -8528,7 +8559,7 @@
       <c r="L30" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="M30" s="27" t="n">
+      <c r="M30" s="39" t="n">
         <v>1.75188</v>
       </c>
       <c r="N30" s="28" t="n">
@@ -8568,11 +8599,11 @@
       <c r="X30" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="Y30" s="25" t="n"/>
+      <c r="Y30" s="38" t="n"/>
       <c r="Z30" s="26" t="n"/>
       <c r="AA30" s="28" t="n"/>
       <c r="AB30" s="28" t="n"/>
-      <c r="AC30" s="30" t="n">
+      <c r="AC30" s="40" t="n">
         <v>1.1278</v>
       </c>
       <c r="AD30" s="24" t="inlineStr">
@@ -8709,11 +8740,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ30" s="25" t="n"/>
+      <c r="BJ30" s="38" t="n"/>
       <c r="BK30" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="BL30" s="27" t="n">
+      <c r="BL30" s="39" t="n">
         <v>1.75188</v>
       </c>
       <c r="BM30" s="28" t="n">
@@ -8723,18 +8754,18 @@
         <v>0.567164</v>
       </c>
       <c r="BO30" s="28" t="n"/>
-      <c r="BP30" s="25" t="n"/>
-      <c r="BQ30" s="27" t="n"/>
+      <c r="BP30" s="38" t="n"/>
+      <c r="BQ30" s="39" t="n"/>
       <c r="BR30" s="28" t="n"/>
       <c r="BS30" s="28" t="n"/>
       <c r="BT30" s="28" t="n"/>
-      <c r="BU30" s="25" t="n"/>
+      <c r="BU30" s="38" t="n"/>
       <c r="BV30" s="29" t="n"/>
       <c r="BW30" s="24" t="n"/>
-      <c r="BX30" s="30" t="n">
+      <c r="BX30" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY30" s="27" t="n">
+      <c r="BY30" s="39" t="n">
         <v>0.75188</v>
       </c>
       <c r="BZ30" s="24" t="inlineStr">
@@ -8794,7 +8825,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J31" s="25" t="n"/>
+      <c r="J31" s="38" t="n"/>
       <c r="K31" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -8803,7 +8834,7 @@
       <c r="L31" s="26" t="n">
         <v>130</v>
       </c>
-      <c r="M31" s="27" t="n">
+      <c r="M31" s="39" t="n">
         <v>2.3</v>
       </c>
       <c r="N31" s="28" t="n">
@@ -8843,11 +8874,11 @@
       <c r="X31" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y31" s="25" t="n"/>
+      <c r="Y31" s="38" t="n"/>
       <c r="Z31" s="26" t="n"/>
       <c r="AA31" s="28" t="n"/>
       <c r="AB31" s="28" t="n"/>
-      <c r="AC31" s="30" t="n">
+      <c r="AC31" s="40" t="n">
         <v>-1</v>
       </c>
       <c r="AD31" s="24" t="inlineStr">
@@ -8984,11 +9015,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ31" s="25" t="n"/>
+      <c r="BJ31" s="38" t="n"/>
       <c r="BK31" s="26" t="n">
         <v>130</v>
       </c>
-      <c r="BL31" s="27" t="n">
+      <c r="BL31" s="39" t="n">
         <v>2.3</v>
       </c>
       <c r="BM31" s="28" t="n">
@@ -8998,18 +9029,18 @@
         <v>0.432836</v>
       </c>
       <c r="BO31" s="28" t="n"/>
-      <c r="BP31" s="25" t="n"/>
-      <c r="BQ31" s="27" t="n"/>
+      <c r="BP31" s="38" t="n"/>
+      <c r="BQ31" s="39" t="n"/>
       <c r="BR31" s="28" t="n"/>
       <c r="BS31" s="28" t="n"/>
       <c r="BT31" s="28" t="n"/>
-      <c r="BU31" s="25" t="n"/>
+      <c r="BU31" s="38" t="n"/>
       <c r="BV31" s="29" t="n"/>
       <c r="BW31" s="24" t="n"/>
-      <c r="BX31" s="30" t="n">
+      <c r="BX31" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY31" s="27" t="n">
+      <c r="BY31" s="39" t="n">
         <v>-1</v>
       </c>
       <c r="BZ31" s="24" t="inlineStr">
@@ -9069,7 +9100,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J32" s="25" t="n"/>
+      <c r="J32" s="38" t="n"/>
       <c r="K32" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -9078,7 +9109,7 @@
       <c r="L32" s="26" t="n">
         <v>113</v>
       </c>
-      <c r="M32" s="27" t="n">
+      <c r="M32" s="39" t="n">
         <v>2.13</v>
       </c>
       <c r="N32" s="28" t="n">
@@ -9110,11 +9141,11 @@
       <c r="V32" s="24" t="n"/>
       <c r="W32" s="26" t="n"/>
       <c r="X32" s="26" t="n"/>
-      <c r="Y32" s="25" t="n"/>
+      <c r="Y32" s="38" t="n"/>
       <c r="Z32" s="26" t="n"/>
       <c r="AA32" s="28" t="n"/>
       <c r="AB32" s="28" t="n"/>
-      <c r="AC32" s="30" t="n"/>
+      <c r="AC32" s="40" t="n"/>
       <c r="AD32" s="24" t="n"/>
       <c r="AE32" s="31" t="inlineStr">
         <is>
@@ -9245,11 +9276,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ32" s="25" t="n"/>
+      <c r="BJ32" s="38" t="n"/>
       <c r="BK32" s="26" t="n">
         <v>113</v>
       </c>
-      <c r="BL32" s="27" t="n">
+      <c r="BL32" s="39" t="n">
         <v>2.13</v>
       </c>
       <c r="BM32" s="28" t="n">
@@ -9259,16 +9290,16 @@
         <v>0.467662</v>
       </c>
       <c r="BO32" s="28" t="n"/>
-      <c r="BP32" s="25" t="n"/>
-      <c r="BQ32" s="27" t="n"/>
+      <c r="BP32" s="38" t="n"/>
+      <c r="BQ32" s="39" t="n"/>
       <c r="BR32" s="28" t="n"/>
       <c r="BS32" s="28" t="n"/>
       <c r="BT32" s="28" t="n"/>
-      <c r="BU32" s="25" t="n"/>
+      <c r="BU32" s="38" t="n"/>
       <c r="BV32" s="29" t="n"/>
       <c r="BW32" s="24" t="n"/>
-      <c r="BX32" s="30" t="n"/>
-      <c r="BY32" s="27" t="n"/>
+      <c r="BX32" s="40" t="n"/>
+      <c r="BY32" s="39" t="n"/>
       <c r="BZ32" s="24" t="n"/>
       <c r="CA32" s="31" t="n"/>
     </row>
@@ -9318,7 +9349,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J33" s="25" t="n"/>
+      <c r="J33" s="38" t="n"/>
       <c r="K33" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -9327,7 +9358,7 @@
       <c r="L33" s="26" t="n">
         <v>-108</v>
       </c>
-      <c r="M33" s="27" t="n">
+      <c r="M33" s="39" t="n">
         <v>1.925926</v>
       </c>
       <c r="N33" s="28" t="n">
@@ -9359,11 +9390,11 @@
       <c r="V33" s="24" t="n"/>
       <c r="W33" s="26" t="n"/>
       <c r="X33" s="26" t="n"/>
-      <c r="Y33" s="25" t="n"/>
+      <c r="Y33" s="38" t="n"/>
       <c r="Z33" s="26" t="n"/>
       <c r="AA33" s="28" t="n"/>
       <c r="AB33" s="28" t="n"/>
-      <c r="AC33" s="30" t="n"/>
+      <c r="AC33" s="40" t="n"/>
       <c r="AD33" s="24" t="n"/>
       <c r="AE33" s="31" t="inlineStr">
         <is>
@@ -9494,11 +9525,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ33" s="25" t="n"/>
+      <c r="BJ33" s="38" t="n"/>
       <c r="BK33" s="26" t="n">
         <v>-108</v>
       </c>
-      <c r="BL33" s="27" t="n">
+      <c r="BL33" s="39" t="n">
         <v>1.925926</v>
       </c>
       <c r="BM33" s="28" t="n">
@@ -9508,16 +9539,16 @@
         <v>0.517413</v>
       </c>
       <c r="BO33" s="28" t="n"/>
-      <c r="BP33" s="25" t="n"/>
-      <c r="BQ33" s="27" t="n"/>
+      <c r="BP33" s="38" t="n"/>
+      <c r="BQ33" s="39" t="n"/>
       <c r="BR33" s="28" t="n"/>
       <c r="BS33" s="28" t="n"/>
       <c r="BT33" s="28" t="n"/>
-      <c r="BU33" s="25" t="n"/>
+      <c r="BU33" s="38" t="n"/>
       <c r="BV33" s="29" t="n"/>
       <c r="BW33" s="24" t="n"/>
-      <c r="BX33" s="30" t="n"/>
-      <c r="BY33" s="27" t="n"/>
+      <c r="BX33" s="40" t="n"/>
+      <c r="BY33" s="39" t="n"/>
       <c r="BZ33" s="24" t="n"/>
       <c r="CA33" s="31" t="n"/>
     </row>
@@ -9567,7 +9598,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J34" s="25" t="n"/>
+      <c r="J34" s="38" t="n"/>
       <c r="K34" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -9576,7 +9607,7 @@
       <c r="L34" s="26" t="n">
         <v>-108</v>
       </c>
-      <c r="M34" s="27" t="n">
+      <c r="M34" s="39" t="n">
         <v>1.925926</v>
       </c>
       <c r="N34" s="28" t="n">
@@ -9608,11 +9639,11 @@
       <c r="V34" s="24" t="n"/>
       <c r="W34" s="26" t="n"/>
       <c r="X34" s="26" t="n"/>
-      <c r="Y34" s="25" t="n"/>
+      <c r="Y34" s="38" t="n"/>
       <c r="Z34" s="26" t="n"/>
       <c r="AA34" s="28" t="n"/>
       <c r="AB34" s="28" t="n"/>
-      <c r="AC34" s="30" t="n"/>
+      <c r="AC34" s="40" t="n"/>
       <c r="AD34" s="24" t="n"/>
       <c r="AE34" s="31" t="inlineStr">
         <is>
@@ -9743,11 +9774,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ34" s="25" t="n"/>
+      <c r="BJ34" s="38" t="n"/>
       <c r="BK34" s="26" t="n">
         <v>-108</v>
       </c>
-      <c r="BL34" s="27" t="n">
+      <c r="BL34" s="39" t="n">
         <v>1.925926</v>
       </c>
       <c r="BM34" s="28" t="n">
@@ -9757,16 +9788,16 @@
         <v>0.5148509999999999</v>
       </c>
       <c r="BO34" s="28" t="n"/>
-      <c r="BP34" s="25" t="n"/>
-      <c r="BQ34" s="27" t="n"/>
+      <c r="BP34" s="38" t="n"/>
+      <c r="BQ34" s="39" t="n"/>
       <c r="BR34" s="28" t="n"/>
       <c r="BS34" s="28" t="n"/>
       <c r="BT34" s="28" t="n"/>
-      <c r="BU34" s="25" t="n"/>
+      <c r="BU34" s="38" t="n"/>
       <c r="BV34" s="29" t="n"/>
       <c r="BW34" s="24" t="n"/>
-      <c r="BX34" s="30" t="n"/>
-      <c r="BY34" s="27" t="n"/>
+      <c r="BX34" s="40" t="n"/>
+      <c r="BY34" s="39" t="n"/>
       <c r="BZ34" s="24" t="n"/>
       <c r="CA34" s="31" t="n"/>
     </row>
@@ -9816,7 +9847,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J35" s="25" t="n"/>
+      <c r="J35" s="38" t="n"/>
       <c r="K35" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -9825,7 +9856,7 @@
       <c r="L35" s="26" t="n">
         <v>150</v>
       </c>
-      <c r="M35" s="27" t="n">
+      <c r="M35" s="39" t="n">
         <v>2.5</v>
       </c>
       <c r="N35" s="28" t="n">
@@ -9857,11 +9888,11 @@
       <c r="V35" s="24" t="n"/>
       <c r="W35" s="26" t="n"/>
       <c r="X35" s="26" t="n"/>
-      <c r="Y35" s="25" t="n"/>
+      <c r="Y35" s="38" t="n"/>
       <c r="Z35" s="26" t="n"/>
       <c r="AA35" s="28" t="n"/>
       <c r="AB35" s="28" t="n"/>
-      <c r="AC35" s="30" t="n"/>
+      <c r="AC35" s="40" t="n"/>
       <c r="AD35" s="24" t="n"/>
       <c r="AE35" s="31" t="inlineStr">
         <is>
@@ -9992,11 +10023,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ35" s="25" t="n"/>
+      <c r="BJ35" s="38" t="n"/>
       <c r="BK35" s="26" t="n">
         <v>150</v>
       </c>
-      <c r="BL35" s="27" t="n">
+      <c r="BL35" s="39" t="n">
         <v>2.5</v>
       </c>
       <c r="BM35" s="28" t="n">
@@ -10006,28 +10037,28 @@
         <v>0.39604</v>
       </c>
       <c r="BO35" s="28" t="n"/>
-      <c r="BP35" s="25" t="n"/>
-      <c r="BQ35" s="27" t="n"/>
+      <c r="BP35" s="38" t="n"/>
+      <c r="BQ35" s="39" t="n"/>
       <c r="BR35" s="28" t="n"/>
       <c r="BS35" s="28" t="n"/>
       <c r="BT35" s="28" t="n"/>
-      <c r="BU35" s="25" t="n"/>
+      <c r="BU35" s="38" t="n"/>
       <c r="BV35" s="29" t="n"/>
       <c r="BW35" s="24" t="n"/>
-      <c r="BX35" s="30" t="n"/>
-      <c r="BY35" s="27" t="n"/>
+      <c r="BX35" s="40" t="n"/>
+      <c r="BY35" s="39" t="n"/>
       <c r="BZ35" s="24" t="n"/>
       <c r="CA35" s="31" t="n"/>
     </row>
     <row r="36" ht="36" customHeight="1">
       <c r="A36" s="24" t="inlineStr">
         <is>
-          <t>8a8477c2b92442e1</t>
+          <t>2ca332931d5a4fdb</t>
         </is>
       </c>
       <c r="B36" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T16:18:24.995882Z</t>
+          <t>2026-07-20T16:32:37.034238Z</t>
         </is>
       </c>
       <c r="C36" s="24" t="inlineStr">
@@ -10065,7 +10096,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J36" s="25" t="n"/>
+      <c r="J36" s="38" t="n"/>
       <c r="K36" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -10074,24 +10105,24 @@
       <c r="L36" s="26" t="n">
         <v>144</v>
       </c>
-      <c r="M36" s="27" t="n">
+      <c r="M36" s="39" t="n">
         <v>2.44</v>
       </c>
       <c r="N36" s="28" t="n">
         <v>0.409836</v>
       </c>
       <c r="O36" s="28" t="n">
-        <v>0.555003</v>
+        <v>0.527501</v>
       </c>
       <c r="P36" s="28" t="n"/>
       <c r="Q36" s="28" t="n">
-        <v>0.145003</v>
+        <v>0.117501</v>
       </c>
       <c r="R36" s="26" t="n">
         <v>100</v>
       </c>
       <c r="S36" s="29" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="T36" s="24" t="inlineStr">
         <is>
@@ -10106,11 +10137,11 @@
       <c r="V36" s="24" t="n"/>
       <c r="W36" s="26" t="n"/>
       <c r="X36" s="26" t="n"/>
-      <c r="Y36" s="25" t="n"/>
+      <c r="Y36" s="38" t="n"/>
       <c r="Z36" s="26" t="n"/>
       <c r="AA36" s="28" t="n"/>
       <c r="AB36" s="28" t="n"/>
-      <c r="AC36" s="30" t="n"/>
+      <c r="AC36" s="40" t="n"/>
       <c r="AD36" s="24" t="n"/>
       <c r="AE36" s="31" t="inlineStr">
         <is>
@@ -10233,7 +10264,7 @@
       </c>
       <c r="BH36" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T16:18:24.995882Z</t>
+          <t>2026-07-20T16:32:37.034238Z</t>
         </is>
       </c>
       <c r="BI36" s="24" t="inlineStr">
@@ -10241,11 +10272,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ36" s="25" t="n"/>
+      <c r="BJ36" s="38" t="n"/>
       <c r="BK36" s="26" t="n">
         <v>144</v>
       </c>
-      <c r="BL36" s="27" t="n">
+      <c r="BL36" s="39" t="n">
         <v>2.44</v>
       </c>
       <c r="BM36" s="28" t="n">
@@ -10253,28 +10284,28 @@
       </c>
       <c r="BN36" s="28" t="n"/>
       <c r="BO36" s="28" t="n"/>
-      <c r="BP36" s="25" t="n"/>
-      <c r="BQ36" s="27" t="n"/>
+      <c r="BP36" s="38" t="n"/>
+      <c r="BQ36" s="39" t="n"/>
       <c r="BR36" s="28" t="n"/>
       <c r="BS36" s="28" t="n"/>
       <c r="BT36" s="28" t="n"/>
-      <c r="BU36" s="25" t="n"/>
+      <c r="BU36" s="38" t="n"/>
       <c r="BV36" s="29" t="n"/>
       <c r="BW36" s="24" t="n"/>
-      <c r="BX36" s="30" t="n"/>
-      <c r="BY36" s="27" t="n"/>
+      <c r="BX36" s="40" t="n"/>
+      <c r="BY36" s="39" t="n"/>
       <c r="BZ36" s="24" t="n"/>
       <c r="CA36" s="31" t="n"/>
     </row>
     <row r="37" ht="36" customHeight="1">
       <c r="A37" s="24" t="inlineStr">
         <is>
-          <t>dc63682b755a4fc5</t>
+          <t>19b13148b06b408d</t>
         </is>
       </c>
       <c r="B37" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T16:18:25.123725Z</t>
+          <t>2026-07-20T16:32:37.134076Z</t>
         </is>
       </c>
       <c r="C37" s="24" t="inlineStr">
@@ -10312,7 +10343,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J37" s="25" t="n"/>
+      <c r="J37" s="38" t="n"/>
       <c r="K37" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -10321,24 +10352,24 @@
       <c r="L37" s="26" t="n">
         <v>186</v>
       </c>
-      <c r="M37" s="27" t="n">
+      <c r="M37" s="39" t="n">
         <v>2.86</v>
       </c>
       <c r="N37" s="28" t="n">
         <v>0.34965</v>
       </c>
       <c r="O37" s="28" t="n">
-        <v>0.567918</v>
+        <v>0.533959</v>
       </c>
       <c r="P37" s="28" t="n"/>
       <c r="Q37" s="28" t="n">
-        <v>0.217918</v>
+        <v>0.183959</v>
       </c>
       <c r="R37" s="26" t="n">
         <v>100</v>
       </c>
       <c r="S37" s="29" t="n">
-        <v>1.25</v>
+        <v>0.75</v>
       </c>
       <c r="T37" s="24" t="inlineStr">
         <is>
@@ -10353,11 +10384,11 @@
       <c r="V37" s="24" t="n"/>
       <c r="W37" s="26" t="n"/>
       <c r="X37" s="26" t="n"/>
-      <c r="Y37" s="25" t="n"/>
+      <c r="Y37" s="38" t="n"/>
       <c r="Z37" s="26" t="n"/>
       <c r="AA37" s="28" t="n"/>
       <c r="AB37" s="28" t="n"/>
-      <c r="AC37" s="30" t="n"/>
+      <c r="AC37" s="40" t="n"/>
       <c r="AD37" s="24" t="n"/>
       <c r="AE37" s="31" t="inlineStr">
         <is>
@@ -10480,7 +10511,7 @@
       </c>
       <c r="BH37" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T16:18:25.123725Z</t>
+          <t>2026-07-20T16:32:37.134076Z</t>
         </is>
       </c>
       <c r="BI37" s="24" t="inlineStr">
@@ -10488,11 +10519,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ37" s="25" t="n"/>
+      <c r="BJ37" s="38" t="n"/>
       <c r="BK37" s="26" t="n">
         <v>186</v>
       </c>
-      <c r="BL37" s="27" t="n">
+      <c r="BL37" s="39" t="n">
         <v>2.86</v>
       </c>
       <c r="BM37" s="28" t="n">
@@ -10500,53 +10531,53 @@
       </c>
       <c r="BN37" s="28" t="n"/>
       <c r="BO37" s="28" t="n"/>
-      <c r="BP37" s="25" t="n"/>
-      <c r="BQ37" s="27" t="n"/>
+      <c r="BP37" s="38" t="n"/>
+      <c r="BQ37" s="39" t="n"/>
       <c r="BR37" s="28" t="n"/>
       <c r="BS37" s="28" t="n"/>
       <c r="BT37" s="28" t="n"/>
-      <c r="BU37" s="25" t="n"/>
+      <c r="BU37" s="38" t="n"/>
       <c r="BV37" s="29" t="n"/>
       <c r="BW37" s="24" t="n"/>
-      <c r="BX37" s="30" t="n"/>
-      <c r="BY37" s="27" t="n"/>
+      <c r="BX37" s="40" t="n"/>
+      <c r="BY37" s="39" t="n"/>
       <c r="BZ37" s="24" t="n"/>
       <c r="CA37" s="31" t="n"/>
     </row>
     <row r="38" ht="36" customHeight="1">
       <c r="A38" s="24" t="inlineStr">
         <is>
-          <t>36b26e06b0c0460a</t>
+          <t>3646f4334f58469d</t>
         </is>
       </c>
       <c r="B38" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T16:18:25.218065Z</t>
+          <t>2026-07-20T16:32:43.485216Z</t>
         </is>
       </c>
       <c r="C38" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T22:00:00Z</t>
+          <t>2026-07-20T17:00:00Z</t>
         </is>
       </c>
       <c r="D38" s="24" t="inlineStr">
         <is>
-          <t>54693</t>
+          <t>56113</t>
         </is>
       </c>
       <c r="E38" s="24" t="inlineStr">
         <is>
-          <t>LOL</t>
+          <t>CS2</t>
         </is>
       </c>
       <c r="F38" s="24" t="inlineStr">
         <is>
-          <t>Ei Nerd Esports</t>
+          <t>Inner Circle Academy</t>
         </is>
       </c>
       <c r="G38" s="24" t="inlineStr">
         <is>
-          <t>RED Academy</t>
+          <t>Endless Journey</t>
         </is>
       </c>
       <c r="H38" s="24" t="inlineStr">
@@ -10556,40 +10587,40 @@
       </c>
       <c r="I38" s="24" t="inlineStr">
         <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J38" s="25" t="n"/>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J38" s="38" t="n"/>
       <c r="K38" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
         </is>
       </c>
       <c r="L38" s="26" t="n">
-        <v>300</v>
-      </c>
-      <c r="M38" s="27" t="n">
-        <v>4</v>
+        <v>113</v>
+      </c>
+      <c r="M38" s="39" t="n">
+        <v>2.13</v>
       </c>
       <c r="N38" s="28" t="n">
-        <v>0.25</v>
+        <v>0.469484</v>
       </c>
       <c r="O38" s="28" t="n">
-        <v>0.674654</v>
+        <v>0.576217</v>
       </c>
       <c r="P38" s="28" t="n"/>
       <c r="Q38" s="28" t="n">
-        <v>0.424654</v>
+        <v>0.106217</v>
       </c>
       <c r="R38" s="26" t="n">
         <v>100</v>
       </c>
       <c r="S38" s="29" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="T38" s="24" t="inlineStr">
         <is>
-          <t>lol-neutral-series-elo-v1</t>
+          <t>cs2-neutral-series-elo-v1</t>
         </is>
       </c>
       <c r="U38" s="24" t="inlineStr">
@@ -10600,15 +10631,15 @@
       <c r="V38" s="24" t="n"/>
       <c r="W38" s="26" t="n"/>
       <c r="X38" s="26" t="n"/>
-      <c r="Y38" s="25" t="n"/>
+      <c r="Y38" s="38" t="n"/>
       <c r="Z38" s="26" t="n"/>
       <c r="AA38" s="28" t="n"/>
       <c r="AB38" s="28" t="n"/>
-      <c r="AC38" s="30" t="n"/>
+      <c r="AC38" s="40" t="n"/>
       <c r="AD38" s="24" t="n"/>
       <c r="AE38" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.2500 (aec-lol-reda-nerd-2026-07-20).</t>
+          <t>Neutral Elo baseline; executable ask 0.4700 (aec-cs2-ica-ej-2026-07-20).</t>
         </is>
       </c>
       <c r="AF38" s="31" t="inlineStr">
@@ -10649,32 +10680,32 @@
       </c>
       <c r="AP38" s="24" t="inlineStr">
         <is>
-          <t>Ei Nerd Esports</t>
+          <t>Inner Circle Academy</t>
         </is>
       </c>
       <c r="AQ38" s="24" t="inlineStr">
         <is>
-          <t>Ei Nerd Esports</t>
+          <t>Inner Circle Academy</t>
         </is>
       </c>
       <c r="AR38" s="24" t="inlineStr">
         <is>
-          <t>Ei Nerd Esports</t>
+          <t>Inner Circle Academy</t>
         </is>
       </c>
       <c r="AS38" s="24" t="inlineStr">
         <is>
-          <t>RED Academy</t>
+          <t>Endless Journey</t>
         </is>
       </c>
       <c r="AT38" s="24" t="inlineStr">
         <is>
-          <t>RED Academy</t>
+          <t>Endless Journey</t>
         </is>
       </c>
       <c r="AU38" s="24" t="inlineStr">
         <is>
-          <t>RED Academy</t>
+          <t>Endless Journey</t>
         </is>
       </c>
       <c r="AV38" s="24" t="n"/>
@@ -10692,7 +10723,7 @@
       </c>
       <c r="BA38" s="24" t="inlineStr">
         <is>
-          <t>1f56359bf30bb6d51629a345226e3008ebfe73210551f6db9f5ce09f656ffdd6</t>
+          <t>40df7f7b9128e86cfbc485914f5801a00963b62604711b733b60f782ba9e258b</t>
         </is>
       </c>
       <c r="BB38" s="24" t="inlineStr">
@@ -10702,12 +10733,12 @@
       </c>
       <c r="BC38" s="24" t="inlineStr">
         <is>
-          <t>lol-neutral-series-elo-v1</t>
+          <t>cs2-neutral-series-elo-v1</t>
         </is>
       </c>
       <c r="BD38" s="24" t="inlineStr">
         <is>
-          <t>1f56359bf30bb6d51629a345226e3008ebfe73210551f6db9f5ce09f656ffdd6</t>
+          <t>40df7f7b9128e86cfbc485914f5801a00963b62604711b733b60f782ba9e258b</t>
         </is>
       </c>
       <c r="BE38" s="24" t="inlineStr">
@@ -10727,7 +10758,7 @@
       </c>
       <c r="BH38" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T16:18:25.218065Z</t>
+          <t>2026-07-20T16:32:43.485216Z</t>
         </is>
       </c>
       <c r="BI38" s="24" t="inlineStr">
@@ -10735,65 +10766,65 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ38" s="25" t="n"/>
+      <c r="BJ38" s="38" t="n"/>
       <c r="BK38" s="26" t="n">
-        <v>300</v>
-      </c>
-      <c r="BL38" s="27" t="n">
-        <v>4</v>
+        <v>113</v>
+      </c>
+      <c r="BL38" s="39" t="n">
+        <v>2.13</v>
       </c>
       <c r="BM38" s="28" t="n">
-        <v>0.25</v>
+        <v>0.469484</v>
       </c>
       <c r="BN38" s="28" t="n"/>
       <c r="BO38" s="28" t="n"/>
-      <c r="BP38" s="25" t="n"/>
-      <c r="BQ38" s="27" t="n"/>
+      <c r="BP38" s="38" t="n"/>
+      <c r="BQ38" s="39" t="n"/>
       <c r="BR38" s="28" t="n"/>
       <c r="BS38" s="28" t="n"/>
       <c r="BT38" s="28" t="n"/>
-      <c r="BU38" s="25" t="n"/>
+      <c r="BU38" s="38" t="n"/>
       <c r="BV38" s="29" t="n"/>
       <c r="BW38" s="24" t="n"/>
-      <c r="BX38" s="30" t="n"/>
-      <c r="BY38" s="27" t="n"/>
+      <c r="BX38" s="40" t="n"/>
+      <c r="BY38" s="39" t="n"/>
       <c r="BZ38" s="24" t="n"/>
       <c r="CA38" s="31" t="n"/>
     </row>
     <row r="39" ht="36" customHeight="1">
       <c r="A39" s="24" t="inlineStr">
         <is>
-          <t>a72da5dc37704076</t>
+          <t>a2f62addc7be49e9</t>
         </is>
       </c>
       <c r="B39" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T16:18:25.312075Z</t>
+          <t>2026-07-20T16:32:43.612711Z</t>
         </is>
       </c>
       <c r="C39" s="24" t="inlineStr">
         <is>
-          <t>2026-07-21T00:00:00Z</t>
+          <t>2026-07-20T21:00:00Z</t>
         </is>
       </c>
       <c r="D39" s="24" t="inlineStr">
         <is>
-          <t>54745</t>
+          <t>54672</t>
         </is>
       </c>
       <c r="E39" s="24" t="inlineStr">
         <is>
-          <t>LOL</t>
+          <t>CS2</t>
         </is>
       </c>
       <c r="F39" s="24" t="inlineStr">
         <is>
-          <t>Estral Esports</t>
+          <t>METANOIA WOLVES</t>
         </is>
       </c>
       <c r="G39" s="24" t="inlineStr">
         <is>
-          <t>paiN Gaming Academy</t>
+          <t>RED Canids Academy</t>
         </is>
       </c>
       <c r="H39" s="24" t="inlineStr">
@@ -10803,40 +10834,40 @@
       </c>
       <c r="I39" s="24" t="inlineStr">
         <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J39" s="25" t="n"/>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J39" s="38" t="n"/>
       <c r="K39" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
         </is>
       </c>
       <c r="L39" s="26" t="n">
-        <v>245</v>
-      </c>
-      <c r="M39" s="27" t="n">
-        <v>3.45</v>
+        <v>-144</v>
+      </c>
+      <c r="M39" s="39" t="n">
+        <v>1.694444</v>
       </c>
       <c r="N39" s="28" t="n">
-        <v>0.289855</v>
+        <v>0.590164</v>
       </c>
       <c r="O39" s="28" t="n">
-        <v>0.586418</v>
+        <v>0.692542</v>
       </c>
       <c r="P39" s="28" t="n"/>
       <c r="Q39" s="28" t="n">
-        <v>0.296418</v>
+        <v>0.102542</v>
       </c>
       <c r="R39" s="26" t="n">
         <v>100</v>
       </c>
       <c r="S39" s="29" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="T39" s="24" t="inlineStr">
         <is>
-          <t>lol-neutral-series-elo-v1</t>
+          <t>cs2-neutral-series-elo-v1</t>
         </is>
       </c>
       <c r="U39" s="24" t="inlineStr">
@@ -10847,15 +10878,15 @@
       <c r="V39" s="24" t="n"/>
       <c r="W39" s="26" t="n"/>
       <c r="X39" s="26" t="n"/>
-      <c r="Y39" s="25" t="n"/>
+      <c r="Y39" s="38" t="n"/>
       <c r="Z39" s="26" t="n"/>
       <c r="AA39" s="28" t="n"/>
       <c r="AB39" s="28" t="n"/>
-      <c r="AC39" s="30" t="n"/>
+      <c r="AC39" s="40" t="n"/>
       <c r="AD39" s="24" t="n"/>
       <c r="AE39" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.2900 (aec-lol-est-pnga-2026-07-21).</t>
+          <t>Neutral Elo baseline; executable ask 0.5900 (aec-cs2-reda-mw-2026-07-20).</t>
         </is>
       </c>
       <c r="AF39" s="31" t="inlineStr">
@@ -10896,32 +10927,32 @@
       </c>
       <c r="AP39" s="24" t="inlineStr">
         <is>
-          <t>Estral Esports</t>
+          <t>METANOIA WOLVES</t>
         </is>
       </c>
       <c r="AQ39" s="24" t="inlineStr">
         <is>
-          <t>Estral Esports</t>
+          <t>METANOIA WOLVES</t>
         </is>
       </c>
       <c r="AR39" s="24" t="inlineStr">
         <is>
-          <t>Estral Esports</t>
+          <t>METANOIA WOLVES</t>
         </is>
       </c>
       <c r="AS39" s="24" t="inlineStr">
         <is>
-          <t>paiN Gaming Academy</t>
+          <t>RED Canids Academy</t>
         </is>
       </c>
       <c r="AT39" s="24" t="inlineStr">
         <is>
-          <t>paiN Gaming Academy</t>
+          <t>RED Canids Academy</t>
         </is>
       </c>
       <c r="AU39" s="24" t="inlineStr">
         <is>
-          <t>paiN Gaming Academy</t>
+          <t>RED Canids Academy</t>
         </is>
       </c>
       <c r="AV39" s="24" t="n"/>
@@ -10939,7 +10970,7 @@
       </c>
       <c r="BA39" s="24" t="inlineStr">
         <is>
-          <t>1f56359bf30bb6d51629a345226e3008ebfe73210551f6db9f5ce09f656ffdd6</t>
+          <t>40df7f7b9128e86cfbc485914f5801a00963b62604711b733b60f782ba9e258b</t>
         </is>
       </c>
       <c r="BB39" s="24" t="inlineStr">
@@ -10949,12 +10980,12 @@
       </c>
       <c r="BC39" s="24" t="inlineStr">
         <is>
-          <t>lol-neutral-series-elo-v1</t>
+          <t>cs2-neutral-series-elo-v1</t>
         </is>
       </c>
       <c r="BD39" s="24" t="inlineStr">
         <is>
-          <t>1f56359bf30bb6d51629a345226e3008ebfe73210551f6db9f5ce09f656ffdd6</t>
+          <t>40df7f7b9128e86cfbc485914f5801a00963b62604711b733b60f782ba9e258b</t>
         </is>
       </c>
       <c r="BE39" s="24" t="inlineStr">
@@ -10974,7 +11005,7 @@
       </c>
       <c r="BH39" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T16:18:25.312075Z</t>
+          <t>2026-07-20T16:32:43.612711Z</t>
         </is>
       </c>
       <c r="BI39" s="24" t="inlineStr">
@@ -10982,1018 +11013,30 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ39" s="25" t="n"/>
+      <c r="BJ39" s="38" t="n"/>
       <c r="BK39" s="26" t="n">
-        <v>245</v>
-      </c>
-      <c r="BL39" s="27" t="n">
-        <v>3.45</v>
+        <v>-144</v>
+      </c>
+      <c r="BL39" s="39" t="n">
+        <v>1.694444</v>
       </c>
       <c r="BM39" s="28" t="n">
-        <v>0.289855</v>
+        <v>0.590164</v>
       </c>
       <c r="BN39" s="28" t="n"/>
       <c r="BO39" s="28" t="n"/>
-      <c r="BP39" s="25" t="n"/>
-      <c r="BQ39" s="27" t="n"/>
+      <c r="BP39" s="38" t="n"/>
+      <c r="BQ39" s="39" t="n"/>
       <c r="BR39" s="28" t="n"/>
       <c r="BS39" s="28" t="n"/>
       <c r="BT39" s="28" t="n"/>
-      <c r="BU39" s="25" t="n"/>
+      <c r="BU39" s="38" t="n"/>
       <c r="BV39" s="29" t="n"/>
       <c r="BW39" s="24" t="n"/>
-      <c r="BX39" s="30" t="n"/>
-      <c r="BY39" s="27" t="n"/>
+      <c r="BX39" s="40" t="n"/>
+      <c r="BY39" s="39" t="n"/>
       <c r="BZ39" s="24" t="n"/>
       <c r="CA39" s="31" t="n"/>
-    </row>
-    <row r="40" ht="36" customHeight="1">
-      <c r="A40" s="24" t="inlineStr">
-        <is>
-          <t>66a67a653fb14bd2</t>
-        </is>
-      </c>
-      <c r="B40" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-20T16:26:22.811500Z</t>
-        </is>
-      </c>
-      <c r="C40" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-20T17:00:00Z</t>
-        </is>
-      </c>
-      <c r="D40" s="24" t="inlineStr">
-        <is>
-          <t>56113</t>
-        </is>
-      </c>
-      <c r="E40" s="24" t="inlineStr">
-        <is>
-          <t>CS2</t>
-        </is>
-      </c>
-      <c r="F40" s="24" t="inlineStr">
-        <is>
-          <t>Inner Circle Academy</t>
-        </is>
-      </c>
-      <c r="G40" s="24" t="inlineStr">
-        <is>
-          <t>Endless Journey</t>
-        </is>
-      </c>
-      <c r="H40" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I40" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J40" s="25" t="n"/>
-      <c r="K40" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L40" s="26" t="n">
-        <v>-113</v>
-      </c>
-      <c r="M40" s="27" t="n">
-        <v>1.884956</v>
-      </c>
-      <c r="N40" s="28" t="n">
-        <v>0.530516</v>
-      </c>
-      <c r="O40" s="28" t="n">
-        <v>0.652434</v>
-      </c>
-      <c r="P40" s="28" t="n"/>
-      <c r="Q40" s="28" t="n">
-        <v>0.122434</v>
-      </c>
-      <c r="R40" s="26" t="n">
-        <v>100</v>
-      </c>
-      <c r="S40" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="T40" s="24" t="inlineStr">
-        <is>
-          <t>cs2-neutral-series-elo-v1</t>
-        </is>
-      </c>
-      <c r="U40" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V40" s="24" t="n"/>
-      <c r="W40" s="26" t="n"/>
-      <c r="X40" s="26" t="n"/>
-      <c r="Y40" s="25" t="n"/>
-      <c r="Z40" s="26" t="n"/>
-      <c r="AA40" s="28" t="n"/>
-      <c r="AB40" s="28" t="n"/>
-      <c r="AC40" s="30" t="n"/>
-      <c r="AD40" s="24" t="n"/>
-      <c r="AE40" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.5300 (aec-cs2-ica-ej-2026-07-20).</t>
-        </is>
-      </c>
-      <c r="AF40" s="31" t="inlineStr">
-        <is>
-          <t>Research baseline; zero-unit shadow until qualified.</t>
-        </is>
-      </c>
-      <c r="AG40" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH40" s="24" t="n"/>
-      <c r="AI40" s="31" t="n"/>
-      <c r="AJ40" s="31" t="n"/>
-      <c r="AK40" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL40" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM40" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN40" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO40" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP40" s="24" t="inlineStr">
-        <is>
-          <t>Inner Circle Academy</t>
-        </is>
-      </c>
-      <c r="AQ40" s="24" t="inlineStr">
-        <is>
-          <t>Inner Circle Academy</t>
-        </is>
-      </c>
-      <c r="AR40" s="24" t="inlineStr">
-        <is>
-          <t>Inner Circle Academy</t>
-        </is>
-      </c>
-      <c r="AS40" s="24" t="inlineStr">
-        <is>
-          <t>Endless Journey</t>
-        </is>
-      </c>
-      <c r="AT40" s="24" t="inlineStr">
-        <is>
-          <t>Endless Journey</t>
-        </is>
-      </c>
-      <c r="AU40" s="24" t="inlineStr">
-        <is>
-          <t>Endless Journey</t>
-        </is>
-      </c>
-      <c r="AV40" s="24" t="n"/>
-      <c r="AW40" s="24" t="n"/>
-      <c r="AX40" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY40" s="24" t="n"/>
-      <c r="AZ40" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA40" s="24" t="inlineStr">
-        <is>
-          <t>40df7f7b9128e86cfbc485914f5801a00963b62604711b733b60f782ba9e258b</t>
-        </is>
-      </c>
-      <c r="BB40" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC40" s="24" t="inlineStr">
-        <is>
-          <t>cs2-neutral-series-elo-v1</t>
-        </is>
-      </c>
-      <c r="BD40" s="24" t="inlineStr">
-        <is>
-          <t>40df7f7b9128e86cfbc485914f5801a00963b62604711b733b60f782ba9e258b</t>
-        </is>
-      </c>
-      <c r="BE40" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF40" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG40" s="24" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="BH40" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-20T16:26:22.811500Z</t>
-        </is>
-      </c>
-      <c r="BI40" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ40" s="25" t="n"/>
-      <c r="BK40" s="26" t="n">
-        <v>-113</v>
-      </c>
-      <c r="BL40" s="27" t="n">
-        <v>1.884956</v>
-      </c>
-      <c r="BM40" s="28" t="n">
-        <v>0.530516</v>
-      </c>
-      <c r="BN40" s="28" t="n"/>
-      <c r="BO40" s="28" t="n"/>
-      <c r="BP40" s="25" t="n"/>
-      <c r="BQ40" s="27" t="n"/>
-      <c r="BR40" s="28" t="n"/>
-      <c r="BS40" s="28" t="n"/>
-      <c r="BT40" s="28" t="n"/>
-      <c r="BU40" s="25" t="n"/>
-      <c r="BV40" s="29" t="n"/>
-      <c r="BW40" s="24" t="n"/>
-      <c r="BX40" s="30" t="n"/>
-      <c r="BY40" s="27" t="n"/>
-      <c r="BZ40" s="24" t="n"/>
-      <c r="CA40" s="31" t="n"/>
-    </row>
-    <row r="41" ht="36" customHeight="1">
-      <c r="A41" s="24" t="inlineStr">
-        <is>
-          <t>a75a7af91f614c77</t>
-        </is>
-      </c>
-      <c r="B41" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-20T16:26:22.946543Z</t>
-        </is>
-      </c>
-      <c r="C41" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-20T19:00:00Z</t>
-        </is>
-      </c>
-      <c r="D41" s="24" t="inlineStr">
-        <is>
-          <t>56757</t>
-        </is>
-      </c>
-      <c r="E41" s="24" t="inlineStr">
-        <is>
-          <t>CS2</t>
-        </is>
-      </c>
-      <c r="F41" s="24" t="inlineStr">
-        <is>
-          <t>MAGICOS</t>
-        </is>
-      </c>
-      <c r="G41" s="24" t="inlineStr">
-        <is>
-          <t>Blitzkrieg</t>
-        </is>
-      </c>
-      <c r="H41" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I41" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J41" s="25" t="n"/>
-      <c r="K41" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L41" s="26" t="n">
-        <v>669</v>
-      </c>
-      <c r="M41" s="27" t="n">
-        <v>7.69</v>
-      </c>
-      <c r="N41" s="28" t="n">
-        <v>0.130039</v>
-      </c>
-      <c r="O41" s="28" t="n">
-        <v>0.598244</v>
-      </c>
-      <c r="P41" s="28" t="n"/>
-      <c r="Q41" s="28" t="n">
-        <v>0.468244</v>
-      </c>
-      <c r="R41" s="26" t="n">
-        <v>100</v>
-      </c>
-      <c r="S41" s="29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T41" s="24" t="inlineStr">
-        <is>
-          <t>cs2-neutral-series-elo-v1</t>
-        </is>
-      </c>
-      <c r="U41" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V41" s="24" t="n"/>
-      <c r="W41" s="26" t="n"/>
-      <c r="X41" s="26" t="n"/>
-      <c r="Y41" s="25" t="n"/>
-      <c r="Z41" s="26" t="n"/>
-      <c r="AA41" s="28" t="n"/>
-      <c r="AB41" s="28" t="n"/>
-      <c r="AC41" s="30" t="n"/>
-      <c r="AD41" s="24" t="n"/>
-      <c r="AE41" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.1300 (aec-cs2-mag-bk-2026-07-20).</t>
-        </is>
-      </c>
-      <c r="AF41" s="31" t="inlineStr">
-        <is>
-          <t>Research baseline; zero-unit shadow until qualified.</t>
-        </is>
-      </c>
-      <c r="AG41" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH41" s="24" t="n"/>
-      <c r="AI41" s="31" t="n"/>
-      <c r="AJ41" s="31" t="n"/>
-      <c r="AK41" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL41" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM41" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN41" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO41" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP41" s="24" t="inlineStr">
-        <is>
-          <t>MAGICOS</t>
-        </is>
-      </c>
-      <c r="AQ41" s="24" t="inlineStr">
-        <is>
-          <t>MAGICOS</t>
-        </is>
-      </c>
-      <c r="AR41" s="24" t="inlineStr">
-        <is>
-          <t>MAGICOS</t>
-        </is>
-      </c>
-      <c r="AS41" s="24" t="inlineStr">
-        <is>
-          <t>Blitzkrieg</t>
-        </is>
-      </c>
-      <c r="AT41" s="24" t="inlineStr">
-        <is>
-          <t>Blitzkrieg</t>
-        </is>
-      </c>
-      <c r="AU41" s="24" t="inlineStr">
-        <is>
-          <t>Blitzkrieg</t>
-        </is>
-      </c>
-      <c r="AV41" s="24" t="n"/>
-      <c r="AW41" s="24" t="n"/>
-      <c r="AX41" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY41" s="24" t="n"/>
-      <c r="AZ41" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA41" s="24" t="inlineStr">
-        <is>
-          <t>40df7f7b9128e86cfbc485914f5801a00963b62604711b733b60f782ba9e258b</t>
-        </is>
-      </c>
-      <c r="BB41" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC41" s="24" t="inlineStr">
-        <is>
-          <t>cs2-neutral-series-elo-v1</t>
-        </is>
-      </c>
-      <c r="BD41" s="24" t="inlineStr">
-        <is>
-          <t>40df7f7b9128e86cfbc485914f5801a00963b62604711b733b60f782ba9e258b</t>
-        </is>
-      </c>
-      <c r="BE41" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF41" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG41" s="24" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="BH41" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-20T16:26:22.946543Z</t>
-        </is>
-      </c>
-      <c r="BI41" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ41" s="25" t="n"/>
-      <c r="BK41" s="26" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL41" s="27" t="n">
-        <v>7.69</v>
-      </c>
-      <c r="BM41" s="28" t="n">
-        <v>0.130039</v>
-      </c>
-      <c r="BN41" s="28" t="n"/>
-      <c r="BO41" s="28" t="n"/>
-      <c r="BP41" s="25" t="n"/>
-      <c r="BQ41" s="27" t="n"/>
-      <c r="BR41" s="28" t="n"/>
-      <c r="BS41" s="28" t="n"/>
-      <c r="BT41" s="28" t="n"/>
-      <c r="BU41" s="25" t="n"/>
-      <c r="BV41" s="29" t="n"/>
-      <c r="BW41" s="24" t="n"/>
-      <c r="BX41" s="30" t="n"/>
-      <c r="BY41" s="27" t="n"/>
-      <c r="BZ41" s="24" t="n"/>
-      <c r="CA41" s="31" t="n"/>
-    </row>
-    <row r="42" ht="36" customHeight="1">
-      <c r="A42" s="24" t="inlineStr">
-        <is>
-          <t>8a3b3559571c4133</t>
-        </is>
-      </c>
-      <c r="B42" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-20T16:26:23.050406Z</t>
-        </is>
-      </c>
-      <c r="C42" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-20T19:00:00Z</t>
-        </is>
-      </c>
-      <c r="D42" s="24" t="inlineStr">
-        <is>
-          <t>54667</t>
-        </is>
-      </c>
-      <c r="E42" s="24" t="inlineStr">
-        <is>
-          <t>CS2</t>
-        </is>
-      </c>
-      <c r="F42" s="24" t="inlineStr">
-        <is>
-          <t>paiN Academy</t>
-        </is>
-      </c>
-      <c r="G42" s="24" t="inlineStr">
-        <is>
-          <t>HATERS</t>
-        </is>
-      </c>
-      <c r="H42" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I42" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J42" s="25" t="n"/>
-      <c r="K42" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L42" s="26" t="n">
-        <v>335</v>
-      </c>
-      <c r="M42" s="27" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="N42" s="28" t="n">
-        <v>0.229885</v>
-      </c>
-      <c r="O42" s="28" t="n">
-        <v>0.558097</v>
-      </c>
-      <c r="P42" s="28" t="n"/>
-      <c r="Q42" s="28" t="n">
-        <v>0.328097</v>
-      </c>
-      <c r="R42" s="26" t="n">
-        <v>100</v>
-      </c>
-      <c r="S42" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="T42" s="24" t="inlineStr">
-        <is>
-          <t>cs2-neutral-series-elo-v1</t>
-        </is>
-      </c>
-      <c r="U42" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V42" s="24" t="n"/>
-      <c r="W42" s="26" t="n"/>
-      <c r="X42" s="26" t="n"/>
-      <c r="Y42" s="25" t="n"/>
-      <c r="Z42" s="26" t="n"/>
-      <c r="AA42" s="28" t="n"/>
-      <c r="AB42" s="28" t="n"/>
-      <c r="AC42" s="30" t="n"/>
-      <c r="AD42" s="24" t="n"/>
-      <c r="AE42" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.2300 (aec-cs2-hat-paina-2026-07-20).</t>
-        </is>
-      </c>
-      <c r="AF42" s="31" t="inlineStr">
-        <is>
-          <t>Research baseline; zero-unit shadow until qualified.</t>
-        </is>
-      </c>
-      <c r="AG42" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH42" s="24" t="n"/>
-      <c r="AI42" s="31" t="n"/>
-      <c r="AJ42" s="31" t="n"/>
-      <c r="AK42" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL42" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM42" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN42" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO42" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP42" s="24" t="inlineStr">
-        <is>
-          <t>paiN Academy</t>
-        </is>
-      </c>
-      <c r="AQ42" s="24" t="inlineStr">
-        <is>
-          <t>paiN Academy</t>
-        </is>
-      </c>
-      <c r="AR42" s="24" t="inlineStr">
-        <is>
-          <t>paiN Academy</t>
-        </is>
-      </c>
-      <c r="AS42" s="24" t="inlineStr">
-        <is>
-          <t>HATERS</t>
-        </is>
-      </c>
-      <c r="AT42" s="24" t="inlineStr">
-        <is>
-          <t>HATERS</t>
-        </is>
-      </c>
-      <c r="AU42" s="24" t="inlineStr">
-        <is>
-          <t>HATERS</t>
-        </is>
-      </c>
-      <c r="AV42" s="24" t="n"/>
-      <c r="AW42" s="24" t="n"/>
-      <c r="AX42" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY42" s="24" t="n"/>
-      <c r="AZ42" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA42" s="24" t="inlineStr">
-        <is>
-          <t>40df7f7b9128e86cfbc485914f5801a00963b62604711b733b60f782ba9e258b</t>
-        </is>
-      </c>
-      <c r="BB42" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC42" s="24" t="inlineStr">
-        <is>
-          <t>cs2-neutral-series-elo-v1</t>
-        </is>
-      </c>
-      <c r="BD42" s="24" t="inlineStr">
-        <is>
-          <t>40df7f7b9128e86cfbc485914f5801a00963b62604711b733b60f782ba9e258b</t>
-        </is>
-      </c>
-      <c r="BE42" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF42" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG42" s="24" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="BH42" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-20T16:26:23.050406Z</t>
-        </is>
-      </c>
-      <c r="BI42" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ42" s="25" t="n"/>
-      <c r="BK42" s="26" t="n">
-        <v>335</v>
-      </c>
-      <c r="BL42" s="27" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="BM42" s="28" t="n">
-        <v>0.229885</v>
-      </c>
-      <c r="BN42" s="28" t="n"/>
-      <c r="BO42" s="28" t="n"/>
-      <c r="BP42" s="25" t="n"/>
-      <c r="BQ42" s="27" t="n"/>
-      <c r="BR42" s="28" t="n"/>
-      <c r="BS42" s="28" t="n"/>
-      <c r="BT42" s="28" t="n"/>
-      <c r="BU42" s="25" t="n"/>
-      <c r="BV42" s="29" t="n"/>
-      <c r="BW42" s="24" t="n"/>
-      <c r="BX42" s="30" t="n"/>
-      <c r="BY42" s="27" t="n"/>
-      <c r="BZ42" s="24" t="n"/>
-      <c r="CA42" s="31" t="n"/>
-    </row>
-    <row r="43" ht="36" customHeight="1">
-      <c r="A43" s="24" t="inlineStr">
-        <is>
-          <t>5417c8a3e89a4c9f</t>
-        </is>
-      </c>
-      <c r="B43" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-20T16:26:23.154839Z</t>
-        </is>
-      </c>
-      <c r="C43" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-20T21:00:00Z</t>
-        </is>
-      </c>
-      <c r="D43" s="24" t="inlineStr">
-        <is>
-          <t>54672</t>
-        </is>
-      </c>
-      <c r="E43" s="24" t="inlineStr">
-        <is>
-          <t>CS2</t>
-        </is>
-      </c>
-      <c r="F43" s="24" t="inlineStr">
-        <is>
-          <t>METANOIA WOLVES</t>
-        </is>
-      </c>
-      <c r="G43" s="24" t="inlineStr">
-        <is>
-          <t>RED Canids Academy</t>
-        </is>
-      </c>
-      <c r="H43" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I43" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J43" s="25" t="n"/>
-      <c r="K43" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L43" s="26" t="n">
-        <v>-144</v>
-      </c>
-      <c r="M43" s="27" t="n">
-        <v>1.694444</v>
-      </c>
-      <c r="N43" s="28" t="n">
-        <v>0.590164</v>
-      </c>
-      <c r="O43" s="28" t="n">
-        <v>0.885084</v>
-      </c>
-      <c r="P43" s="28" t="n"/>
-      <c r="Q43" s="28" t="n">
-        <v>0.295084</v>
-      </c>
-      <c r="R43" s="26" t="n">
-        <v>100</v>
-      </c>
-      <c r="S43" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="T43" s="24" t="inlineStr">
-        <is>
-          <t>cs2-neutral-series-elo-v1</t>
-        </is>
-      </c>
-      <c r="U43" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V43" s="24" t="n"/>
-      <c r="W43" s="26" t="n"/>
-      <c r="X43" s="26" t="n"/>
-      <c r="Y43" s="25" t="n"/>
-      <c r="Z43" s="26" t="n"/>
-      <c r="AA43" s="28" t="n"/>
-      <c r="AB43" s="28" t="n"/>
-      <c r="AC43" s="30" t="n"/>
-      <c r="AD43" s="24" t="n"/>
-      <c r="AE43" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.5900 (aec-cs2-reda-mw-2026-07-20).</t>
-        </is>
-      </c>
-      <c r="AF43" s="31" t="inlineStr">
-        <is>
-          <t>Research baseline; zero-unit shadow until qualified.</t>
-        </is>
-      </c>
-      <c r="AG43" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH43" s="24" t="n"/>
-      <c r="AI43" s="31" t="n"/>
-      <c r="AJ43" s="31" t="n"/>
-      <c r="AK43" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL43" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM43" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN43" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO43" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP43" s="24" t="inlineStr">
-        <is>
-          <t>METANOIA WOLVES</t>
-        </is>
-      </c>
-      <c r="AQ43" s="24" t="inlineStr">
-        <is>
-          <t>METANOIA WOLVES</t>
-        </is>
-      </c>
-      <c r="AR43" s="24" t="inlineStr">
-        <is>
-          <t>METANOIA WOLVES</t>
-        </is>
-      </c>
-      <c r="AS43" s="24" t="inlineStr">
-        <is>
-          <t>RED Canids Academy</t>
-        </is>
-      </c>
-      <c r="AT43" s="24" t="inlineStr">
-        <is>
-          <t>RED Canids Academy</t>
-        </is>
-      </c>
-      <c r="AU43" s="24" t="inlineStr">
-        <is>
-          <t>RED Canids Academy</t>
-        </is>
-      </c>
-      <c r="AV43" s="24" t="n"/>
-      <c r="AW43" s="24" t="n"/>
-      <c r="AX43" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY43" s="24" t="n"/>
-      <c r="AZ43" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA43" s="24" t="inlineStr">
-        <is>
-          <t>40df7f7b9128e86cfbc485914f5801a00963b62604711b733b60f782ba9e258b</t>
-        </is>
-      </c>
-      <c r="BB43" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC43" s="24" t="inlineStr">
-        <is>
-          <t>cs2-neutral-series-elo-v1</t>
-        </is>
-      </c>
-      <c r="BD43" s="24" t="inlineStr">
-        <is>
-          <t>40df7f7b9128e86cfbc485914f5801a00963b62604711b733b60f782ba9e258b</t>
-        </is>
-      </c>
-      <c r="BE43" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF43" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG43" s="24" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="BH43" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-20T16:26:23.154839Z</t>
-        </is>
-      </c>
-      <c r="BI43" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ43" s="25" t="n"/>
-      <c r="BK43" s="26" t="n">
-        <v>-144</v>
-      </c>
-      <c r="BL43" s="27" t="n">
-        <v>1.694444</v>
-      </c>
-      <c r="BM43" s="28" t="n">
-        <v>0.590164</v>
-      </c>
-      <c r="BN43" s="28" t="n"/>
-      <c r="BO43" s="28" t="n"/>
-      <c r="BP43" s="25" t="n"/>
-      <c r="BQ43" s="27" t="n"/>
-      <c r="BR43" s="28" t="n"/>
-      <c r="BS43" s="28" t="n"/>
-      <c r="BT43" s="28" t="n"/>
-      <c r="BU43" s="25" t="n"/>
-      <c r="BV43" s="29" t="n"/>
-      <c r="BW43" s="24" t="n"/>
-      <c r="BX43" s="30" t="n"/>
-      <c r="BY43" s="27" t="n"/>
-      <c r="BZ43" s="24" t="n"/>
-      <c r="CA43" s="31" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/picks.xlsx
+++ b/data/picks.xlsx
@@ -21,10 +21,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="0.0%"/>
-    <numFmt numFmtId="165" formatCode="0.0000"/>
-    <numFmt numFmtId="166" formatCode="0.0###"/>
-    <numFmt numFmtId="167" formatCode="0.000000"/>
+    <numFmt numFmtId="164" formatCode="0.0###"/>
+    <numFmt numFmtId="165" formatCode="0.000000"/>
+    <numFmt numFmtId="166" formatCode="0.0000"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -136,7 +136,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -150,10 +150,10 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -169,10 +169,10 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -184,10 +184,10 @@
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -202,13 +202,13 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="10" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -217,38 +217,11 @@
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -781,7 +754,6 @@
         <v/>
       </c>
     </row>
-    <row r="5"/>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
@@ -813,16 +785,15 @@
         <f>COUNTIFS('Picks'!$BX$2:$BX$39,"&gt;0",'Picks'!$V$2:$V$39,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$39,"&gt;0",'Picks'!$V$2:$V$39,"loss")</f>
         <v/>
       </c>
-      <c r="E7" s="32">
+      <c r="E7" s="7">
         <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$39,"&gt;0",'Picks'!$V$2:$V$39,"win")/(COUNTIFS('Picks'!$BX$2:$BX$39,"&gt;0",'Picks'!$V$2:$V$39,"win")+COUNTIFS('Picks'!$BX$2:$BX$39,"&gt;0",'Picks'!$V$2:$V$39,"loss")),0)</f>
         <v/>
       </c>
-      <c r="G7" s="32">
+      <c r="G7" s="7">
         <f>IFERROR(SUM('Picks'!$BY$2:$BY$39)/SUM('Picks'!$BX$2:$BX$39),0)</f>
         <v/>
       </c>
     </row>
-    <row r="8"/>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
@@ -846,7 +817,7 @@
       </c>
     </row>
     <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="33">
+      <c r="A10" s="8">
         <f>SUM('Picks'!$BY$2:$BY$39)</f>
         <v/>
       </c>
@@ -858,12 +829,11 @@
         <f>COUNTIFS('Picks'!$AM$2:$AM$39,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$39,"settled")</f>
         <v/>
       </c>
-      <c r="G10" s="33">
+      <c r="G10" s="8">
         <f>SUMIFS('Picks'!$AC$2:$AC$39,'Picks'!$AM$2:$AM$39,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
@@ -926,11 +896,11 @@
         <f>COUNTIFS('Picks'!$H$2:$H$39,$A14,'Picks'!$U$2:$U$39,"settled",'Picks'!$V$2:$V$39,"loss")</f>
         <v/>
       </c>
-      <c r="E14" s="34">
+      <c r="E14" s="14">
         <f>IFERROR(C14/(C14+D14),0)</f>
         <v/>
       </c>
-      <c r="F14" s="35">
+      <c r="F14" s="15">
         <f>SUMIFS('Picks'!$BY$2:$BY$39,'Picks'!$H$2:$H$39,$A14)</f>
         <v/>
       </c>
@@ -957,11 +927,11 @@
         <f>COUNTIFS('Picks'!$H$2:$H$39,$A15,'Picks'!$U$2:$U$39,"settled",'Picks'!$V$2:$V$39,"loss")</f>
         <v/>
       </c>
-      <c r="E15" s="36">
+      <c r="E15" s="19">
         <f>IFERROR(C15/(C15+D15),0)</f>
         <v/>
       </c>
-      <c r="F15" s="37">
+      <c r="F15" s="20">
         <f>SUMIFS('Picks'!$BY$2:$BY$39,'Picks'!$H$2:$H$39,$A15)</f>
         <v/>
       </c>
@@ -988,11 +958,11 @@
         <f>COUNTIFS('Picks'!$H$2:$H$39,$A16,'Picks'!$U$2:$U$39,"settled",'Picks'!$V$2:$V$39,"loss")</f>
         <v/>
       </c>
-      <c r="E16" s="34">
+      <c r="E16" s="14">
         <f>IFERROR(C16/(C16+D16),0)</f>
         <v/>
       </c>
-      <c r="F16" s="35">
+      <c r="F16" s="15">
         <f>SUMIFS('Picks'!$BY$2:$BY$39,'Picks'!$H$2:$H$39,$A16)</f>
         <v/>
       </c>
@@ -1001,7 +971,6 @@
         <v/>
       </c>
     </row>
-    <row r="17"/>
     <row r="18">
       <c r="A18" s="22" t="inlineStr">
         <is>
@@ -1554,7 +1523,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J2" s="38" t="n"/>
+      <c r="J2" s="25" t="n"/>
       <c r="K2" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -1563,7 +1532,7 @@
       <c r="L2" s="26" t="n">
         <v>117</v>
       </c>
-      <c r="M2" s="39" t="n">
+      <c r="M2" s="27" t="n">
         <v>2.17</v>
       </c>
       <c r="N2" s="28" t="n">
@@ -1603,11 +1572,11 @@
       <c r="X2" s="26" t="n">
         <v>108</v>
       </c>
-      <c r="Y2" s="38" t="n"/>
+      <c r="Y2" s="25" t="n"/>
       <c r="Z2" s="26" t="n"/>
       <c r="AA2" s="28" t="n"/>
       <c r="AB2" s="28" t="n"/>
-      <c r="AC2" s="40" t="n">
+      <c r="AC2" s="30" t="n">
         <v>1.755</v>
       </c>
       <c r="AD2" s="24" t="inlineStr">
@@ -1744,11 +1713,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ2" s="38" t="n"/>
+      <c r="BJ2" s="25" t="n"/>
       <c r="BK2" s="26" t="n">
         <v>117</v>
       </c>
-      <c r="BL2" s="39" t="n">
+      <c r="BL2" s="27" t="n">
         <v>2.17</v>
       </c>
       <c r="BM2" s="28" t="n">
@@ -1758,18 +1727,18 @@
         <v>0.455446</v>
       </c>
       <c r="BO2" s="28" t="n"/>
-      <c r="BP2" s="38" t="n"/>
-      <c r="BQ2" s="39" t="n"/>
+      <c r="BP2" s="25" t="n"/>
+      <c r="BQ2" s="27" t="n"/>
       <c r="BR2" s="28" t="n"/>
       <c r="BS2" s="28" t="n"/>
       <c r="BT2" s="28" t="n"/>
-      <c r="BU2" s="38" t="n"/>
+      <c r="BU2" s="25" t="n"/>
       <c r="BV2" s="29" t="n"/>
       <c r="BW2" s="24" t="n"/>
-      <c r="BX2" s="40" t="n">
+      <c r="BX2" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY2" s="39" t="n">
+      <c r="BY2" s="27" t="n">
         <v>1.17</v>
       </c>
       <c r="BZ2" s="24" t="inlineStr">
@@ -1829,7 +1798,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J3" s="38" t="n"/>
+      <c r="J3" s="25" t="n"/>
       <c r="K3" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -1838,7 +1807,7 @@
       <c r="L3" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="M3" s="39" t="n">
+      <c r="M3" s="27" t="n">
         <v>1.75188</v>
       </c>
       <c r="N3" s="28" t="n">
@@ -1878,11 +1847,11 @@
       <c r="X3" s="26" t="n">
         <v>8</v>
       </c>
-      <c r="Y3" s="38" t="n"/>
+      <c r="Y3" s="25" t="n"/>
       <c r="Z3" s="26" t="n"/>
       <c r="AA3" s="28" t="n"/>
       <c r="AB3" s="28" t="n"/>
-      <c r="AC3" s="40" t="n">
+      <c r="AC3" s="30" t="n">
         <v>1.1278</v>
       </c>
       <c r="AD3" s="24" t="inlineStr">
@@ -2019,11 +1988,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ3" s="38" t="n"/>
+      <c r="BJ3" s="25" t="n"/>
       <c r="BK3" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="BL3" s="39" t="n">
+      <c r="BL3" s="27" t="n">
         <v>1.75188</v>
       </c>
       <c r="BM3" s="28" t="n">
@@ -2033,18 +2002,18 @@
         <v>0.567164</v>
       </c>
       <c r="BO3" s="28" t="n"/>
-      <c r="BP3" s="38" t="n"/>
-      <c r="BQ3" s="39" t="n"/>
+      <c r="BP3" s="25" t="n"/>
+      <c r="BQ3" s="27" t="n"/>
       <c r="BR3" s="28" t="n"/>
       <c r="BS3" s="28" t="n"/>
       <c r="BT3" s="28" t="n"/>
-      <c r="BU3" s="38" t="n"/>
+      <c r="BU3" s="25" t="n"/>
       <c r="BV3" s="29" t="n"/>
       <c r="BW3" s="24" t="n"/>
-      <c r="BX3" s="40" t="n">
+      <c r="BX3" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY3" s="39" t="n">
+      <c r="BY3" s="27" t="n">
         <v>0.75188</v>
       </c>
       <c r="BZ3" s="24" t="inlineStr">
@@ -2104,7 +2073,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J4" s="38" t="n"/>
+      <c r="J4" s="25" t="n"/>
       <c r="K4" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -2113,7 +2082,7 @@
       <c r="L4" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="M4" s="39" t="n">
+      <c r="M4" s="27" t="n">
         <v>1.980392</v>
       </c>
       <c r="N4" s="28" t="n">
@@ -2153,11 +2122,11 @@
       <c r="X4" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="Y4" s="38" t="n"/>
+      <c r="Y4" s="25" t="n"/>
       <c r="Z4" s="26" t="n"/>
       <c r="AA4" s="28" t="n"/>
       <c r="AB4" s="28" t="n"/>
-      <c r="AC4" s="40" t="n">
+      <c r="AC4" s="30" t="n">
         <v>-1</v>
       </c>
       <c r="AD4" s="24" t="inlineStr">
@@ -2294,11 +2263,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ4" s="38" t="n"/>
+      <c r="BJ4" s="25" t="n"/>
       <c r="BK4" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="BL4" s="39" t="n">
+      <c r="BL4" s="27" t="n">
         <v>1.980392</v>
       </c>
       <c r="BM4" s="28" t="n">
@@ -2308,18 +2277,18 @@
         <v>0.502488</v>
       </c>
       <c r="BO4" s="28" t="n"/>
-      <c r="BP4" s="38" t="n"/>
-      <c r="BQ4" s="39" t="n"/>
+      <c r="BP4" s="25" t="n"/>
+      <c r="BQ4" s="27" t="n"/>
       <c r="BR4" s="28" t="n"/>
       <c r="BS4" s="28" t="n"/>
       <c r="BT4" s="28" t="n"/>
-      <c r="BU4" s="38" t="n"/>
+      <c r="BU4" s="25" t="n"/>
       <c r="BV4" s="29" t="n"/>
       <c r="BW4" s="24" t="n"/>
-      <c r="BX4" s="40" t="n">
+      <c r="BX4" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY4" s="39" t="n">
+      <c r="BY4" s="27" t="n">
         <v>-1</v>
       </c>
       <c r="BZ4" s="24" t="inlineStr">
@@ -2379,7 +2348,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J5" s="38" t="n"/>
+      <c r="J5" s="25" t="n"/>
       <c r="K5" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -2388,7 +2357,7 @@
       <c r="L5" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="M5" s="39" t="n">
+      <c r="M5" s="27" t="n">
         <v>1.75188</v>
       </c>
       <c r="N5" s="28" t="n">
@@ -2428,11 +2397,11 @@
       <c r="X5" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="Y5" s="38" t="n"/>
+      <c r="Y5" s="25" t="n"/>
       <c r="Z5" s="26" t="n"/>
       <c r="AA5" s="28" t="n"/>
       <c r="AB5" s="28" t="n"/>
-      <c r="AC5" s="40" t="n">
+      <c r="AC5" s="30" t="n">
         <v>1.1278</v>
       </c>
       <c r="AD5" s="24" t="inlineStr">
@@ -2569,11 +2538,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ5" s="38" t="n"/>
+      <c r="BJ5" s="25" t="n"/>
       <c r="BK5" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="BL5" s="39" t="n">
+      <c r="BL5" s="27" t="n">
         <v>1.75188</v>
       </c>
       <c r="BM5" s="28" t="n">
@@ -2583,18 +2552,18 @@
         <v>0.567164</v>
       </c>
       <c r="BO5" s="28" t="n"/>
-      <c r="BP5" s="38" t="n"/>
-      <c r="BQ5" s="39" t="n"/>
+      <c r="BP5" s="25" t="n"/>
+      <c r="BQ5" s="27" t="n"/>
       <c r="BR5" s="28" t="n"/>
       <c r="BS5" s="28" t="n"/>
       <c r="BT5" s="28" t="n"/>
-      <c r="BU5" s="38" t="n"/>
+      <c r="BU5" s="25" t="n"/>
       <c r="BV5" s="29" t="n"/>
       <c r="BW5" s="24" t="n"/>
-      <c r="BX5" s="40" t="n">
+      <c r="BX5" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY5" s="39" t="n">
+      <c r="BY5" s="27" t="n">
         <v>0.75188</v>
       </c>
       <c r="BZ5" s="24" t="inlineStr">
@@ -2654,7 +2623,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J6" s="38" t="n"/>
+      <c r="J6" s="25" t="n"/>
       <c r="K6" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -2663,7 +2632,7 @@
       <c r="L6" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="M6" s="39" t="n">
+      <c r="M6" s="27" t="n">
         <v>1.961538</v>
       </c>
       <c r="N6" s="28" t="n">
@@ -2703,11 +2672,11 @@
       <c r="X6" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="Y6" s="38" t="n"/>
+      <c r="Y6" s="25" t="n"/>
       <c r="Z6" s="26" t="n"/>
       <c r="AA6" s="28" t="n"/>
       <c r="AB6" s="28" t="n"/>
-      <c r="AC6" s="40" t="n">
+      <c r="AC6" s="30" t="n">
         <v>1.2019</v>
       </c>
       <c r="AD6" s="24" t="inlineStr">
@@ -2844,11 +2813,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ6" s="38" t="n"/>
+      <c r="BJ6" s="25" t="n"/>
       <c r="BK6" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="BL6" s="39" t="n">
+      <c r="BL6" s="27" t="n">
         <v>1.961538</v>
       </c>
       <c r="BM6" s="28" t="n">
@@ -2858,18 +2827,18 @@
         <v>0.507463</v>
       </c>
       <c r="BO6" s="28" t="n"/>
-      <c r="BP6" s="38" t="n"/>
-      <c r="BQ6" s="39" t="n"/>
+      <c r="BP6" s="25" t="n"/>
+      <c r="BQ6" s="27" t="n"/>
       <c r="BR6" s="28" t="n"/>
       <c r="BS6" s="28" t="n"/>
       <c r="BT6" s="28" t="n"/>
-      <c r="BU6" s="38" t="n"/>
+      <c r="BU6" s="25" t="n"/>
       <c r="BV6" s="29" t="n"/>
       <c r="BW6" s="24" t="n"/>
-      <c r="BX6" s="40" t="n">
+      <c r="BX6" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY6" s="39" t="n">
+      <c r="BY6" s="27" t="n">
         <v>0.961538</v>
       </c>
       <c r="BZ6" s="24" t="inlineStr">
@@ -2929,7 +2898,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J7" s="38" t="n"/>
+      <c r="J7" s="25" t="n"/>
       <c r="K7" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -2938,7 +2907,7 @@
       <c r="L7" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="M7" s="39" t="n">
+      <c r="M7" s="27" t="n">
         <v>1.961538</v>
       </c>
       <c r="N7" s="28" t="n">
@@ -2978,11 +2947,11 @@
       <c r="X7" s="26" t="n">
         <v>10</v>
       </c>
-      <c r="Y7" s="38" t="n"/>
+      <c r="Y7" s="25" t="n"/>
       <c r="Z7" s="26" t="n"/>
       <c r="AA7" s="28" t="n"/>
       <c r="AB7" s="28" t="n"/>
-      <c r="AC7" s="40" t="n">
+      <c r="AC7" s="30" t="n">
         <v>-1.25</v>
       </c>
       <c r="AD7" s="24" t="inlineStr">
@@ -3119,11 +3088,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ7" s="38" t="n"/>
+      <c r="BJ7" s="25" t="n"/>
       <c r="BK7" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="BL7" s="39" t="n">
+      <c r="BL7" s="27" t="n">
         <v>1.961538</v>
       </c>
       <c r="BM7" s="28" t="n">
@@ -3133,18 +3102,18 @@
         <v>0.507463</v>
       </c>
       <c r="BO7" s="28" t="n"/>
-      <c r="BP7" s="38" t="n"/>
-      <c r="BQ7" s="39" t="n"/>
+      <c r="BP7" s="25" t="n"/>
+      <c r="BQ7" s="27" t="n"/>
       <c r="BR7" s="28" t="n"/>
       <c r="BS7" s="28" t="n"/>
       <c r="BT7" s="28" t="n"/>
-      <c r="BU7" s="38" t="n"/>
+      <c r="BU7" s="25" t="n"/>
       <c r="BV7" s="29" t="n"/>
       <c r="BW7" s="24" t="n"/>
-      <c r="BX7" s="40" t="n">
+      <c r="BX7" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY7" s="39" t="n">
+      <c r="BY7" s="27" t="n">
         <v>-1</v>
       </c>
       <c r="BZ7" s="24" t="inlineStr">
@@ -3204,7 +3173,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J8" s="38" t="n"/>
+      <c r="J8" s="25" t="n"/>
       <c r="K8" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -3213,7 +3182,7 @@
       <c r="L8" s="26" t="n">
         <v>-106</v>
       </c>
-      <c r="M8" s="39" t="n">
+      <c r="M8" s="27" t="n">
         <v>1.943396</v>
       </c>
       <c r="N8" s="28" t="n">
@@ -3253,11 +3222,11 @@
       <c r="X8" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="Y8" s="38" t="n"/>
+      <c r="Y8" s="25" t="n"/>
       <c r="Z8" s="26" t="n"/>
       <c r="AA8" s="28" t="n"/>
       <c r="AB8" s="28" t="n"/>
-      <c r="AC8" s="40" t="n">
+      <c r="AC8" s="30" t="n">
         <v>-1</v>
       </c>
       <c r="AD8" s="24" t="inlineStr">
@@ -3394,11 +3363,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ8" s="38" t="n"/>
+      <c r="BJ8" s="25" t="n"/>
       <c r="BK8" s="26" t="n">
         <v>-106</v>
       </c>
-      <c r="BL8" s="39" t="n">
+      <c r="BL8" s="27" t="n">
         <v>1.943396</v>
       </c>
       <c r="BM8" s="28" t="n">
@@ -3408,18 +3377,18 @@
         <v>0.5124379999999999</v>
       </c>
       <c r="BO8" s="28" t="n"/>
-      <c r="BP8" s="38" t="n"/>
-      <c r="BQ8" s="39" t="n"/>
+      <c r="BP8" s="25" t="n"/>
+      <c r="BQ8" s="27" t="n"/>
       <c r="BR8" s="28" t="n"/>
       <c r="BS8" s="28" t="n"/>
       <c r="BT8" s="28" t="n"/>
-      <c r="BU8" s="38" t="n"/>
+      <c r="BU8" s="25" t="n"/>
       <c r="BV8" s="29" t="n"/>
       <c r="BW8" s="24" t="n"/>
-      <c r="BX8" s="40" t="n">
+      <c r="BX8" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY8" s="39" t="n">
+      <c r="BY8" s="27" t="n">
         <v>-1</v>
       </c>
       <c r="BZ8" s="24" t="inlineStr">
@@ -3479,7 +3448,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J9" s="38" t="n"/>
+      <c r="J9" s="25" t="n"/>
       <c r="K9" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -3488,7 +3457,7 @@
       <c r="L9" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="M9" s="39" t="n">
+      <c r="M9" s="27" t="n">
         <v>1.980392</v>
       </c>
       <c r="N9" s="28" t="n">
@@ -3528,11 +3497,11 @@
       <c r="X9" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="Y9" s="38" t="n"/>
+      <c r="Y9" s="25" t="n"/>
       <c r="Z9" s="26" t="n"/>
       <c r="AA9" s="28" t="n"/>
       <c r="AB9" s="28" t="n"/>
-      <c r="AC9" s="40" t="n">
+      <c r="AC9" s="30" t="n">
         <v>0.9804</v>
       </c>
       <c r="AD9" s="24" t="inlineStr">
@@ -3669,11 +3638,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ9" s="38" t="n"/>
+      <c r="BJ9" s="25" t="n"/>
       <c r="BK9" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="BL9" s="39" t="n">
+      <c r="BL9" s="27" t="n">
         <v>1.980392</v>
       </c>
       <c r="BM9" s="28" t="n">
@@ -3683,18 +3652,18 @@
         <v>0.502488</v>
       </c>
       <c r="BO9" s="28" t="n"/>
-      <c r="BP9" s="38" t="n"/>
-      <c r="BQ9" s="39" t="n"/>
+      <c r="BP9" s="25" t="n"/>
+      <c r="BQ9" s="27" t="n"/>
       <c r="BR9" s="28" t="n"/>
       <c r="BS9" s="28" t="n"/>
       <c r="BT9" s="28" t="n"/>
-      <c r="BU9" s="38" t="n"/>
+      <c r="BU9" s="25" t="n"/>
       <c r="BV9" s="29" t="n"/>
       <c r="BW9" s="24" t="n"/>
-      <c r="BX9" s="40" t="n">
+      <c r="BX9" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY9" s="39" t="n">
+      <c r="BY9" s="27" t="n">
         <v>0.980392</v>
       </c>
       <c r="BZ9" s="24" t="inlineStr">
@@ -3754,7 +3723,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J10" s="38" t="n"/>
+      <c r="J10" s="25" t="n"/>
       <c r="K10" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -3763,7 +3732,7 @@
       <c r="L10" s="26" t="n">
         <v>-138</v>
       </c>
-      <c r="M10" s="39" t="n">
+      <c r="M10" s="27" t="n">
         <v>1.724638</v>
       </c>
       <c r="N10" s="28" t="n">
@@ -3803,11 +3772,11 @@
       <c r="X10" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="Y10" s="38" t="n"/>
+      <c r="Y10" s="25" t="n"/>
       <c r="Z10" s="26" t="n"/>
       <c r="AA10" s="28" t="n"/>
       <c r="AB10" s="28" t="n"/>
-      <c r="AC10" s="40" t="n">
+      <c r="AC10" s="30" t="n">
         <v>1.2681</v>
       </c>
       <c r="AD10" s="24" t="inlineStr">
@@ -3944,11 +3913,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ10" s="38" t="n"/>
+      <c r="BJ10" s="25" t="n"/>
       <c r="BK10" s="26" t="n">
         <v>-138</v>
       </c>
-      <c r="BL10" s="39" t="n">
+      <c r="BL10" s="27" t="n">
         <v>1.724638</v>
       </c>
       <c r="BM10" s="28" t="n">
@@ -3958,18 +3927,18 @@
         <v>0.577114</v>
       </c>
       <c r="BO10" s="28" t="n"/>
-      <c r="BP10" s="38" t="n"/>
-      <c r="BQ10" s="39" t="n"/>
+      <c r="BP10" s="25" t="n"/>
+      <c r="BQ10" s="27" t="n"/>
       <c r="BR10" s="28" t="n"/>
       <c r="BS10" s="28" t="n"/>
       <c r="BT10" s="28" t="n"/>
-      <c r="BU10" s="38" t="n"/>
+      <c r="BU10" s="25" t="n"/>
       <c r="BV10" s="29" t="n"/>
       <c r="BW10" s="24" t="n"/>
-      <c r="BX10" s="40" t="n">
+      <c r="BX10" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY10" s="39" t="n">
+      <c r="BY10" s="27" t="n">
         <v>0.724638</v>
       </c>
       <c r="BZ10" s="24" t="inlineStr">
@@ -4029,7 +3998,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J11" s="38" t="n"/>
+      <c r="J11" s="25" t="n"/>
       <c r="K11" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -4038,7 +4007,7 @@
       <c r="L11" s="26" t="n">
         <v>102</v>
       </c>
-      <c r="M11" s="39" t="n">
+      <c r="M11" s="27" t="n">
         <v>2.02</v>
       </c>
       <c r="N11" s="28" t="n">
@@ -4078,11 +4047,11 @@
       <c r="X11" s="26" t="n">
         <v>15</v>
       </c>
-      <c r="Y11" s="38" t="n"/>
+      <c r="Y11" s="25" t="n"/>
       <c r="Z11" s="26" t="n"/>
       <c r="AA11" s="28" t="n"/>
       <c r="AB11" s="28" t="n"/>
-      <c r="AC11" s="40" t="n">
+      <c r="AC11" s="30" t="n">
         <v>1.275</v>
       </c>
       <c r="AD11" s="24" t="inlineStr">
@@ -4219,11 +4188,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ11" s="38" t="n"/>
+      <c r="BJ11" s="25" t="n"/>
       <c r="BK11" s="26" t="n">
         <v>102</v>
       </c>
-      <c r="BL11" s="39" t="n">
+      <c r="BL11" s="27" t="n">
         <v>2.02</v>
       </c>
       <c r="BM11" s="28" t="n">
@@ -4233,18 +4202,18 @@
         <v>0.492537</v>
       </c>
       <c r="BO11" s="28" t="n"/>
-      <c r="BP11" s="38" t="n"/>
-      <c r="BQ11" s="39" t="n"/>
+      <c r="BP11" s="25" t="n"/>
+      <c r="BQ11" s="27" t="n"/>
       <c r="BR11" s="28" t="n"/>
       <c r="BS11" s="28" t="n"/>
       <c r="BT11" s="28" t="n"/>
-      <c r="BU11" s="38" t="n"/>
+      <c r="BU11" s="25" t="n"/>
       <c r="BV11" s="29" t="n"/>
       <c r="BW11" s="24" t="n"/>
-      <c r="BX11" s="40" t="n">
+      <c r="BX11" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY11" s="39" t="n">
+      <c r="BY11" s="27" t="n">
         <v>1.02</v>
       </c>
       <c r="BZ11" s="24" t="inlineStr">
@@ -4304,7 +4273,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J12" s="38" t="n"/>
+      <c r="J12" s="25" t="n"/>
       <c r="K12" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -4313,7 +4282,7 @@
       <c r="L12" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="M12" s="39" t="n">
+      <c r="M12" s="27" t="n">
         <v>1.980392</v>
       </c>
       <c r="N12" s="28" t="n">
@@ -4353,11 +4322,11 @@
       <c r="X12" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y12" s="38" t="n"/>
+      <c r="Y12" s="25" t="n"/>
       <c r="Z12" s="26" t="n"/>
       <c r="AA12" s="28" t="n"/>
       <c r="AB12" s="28" t="n"/>
-      <c r="AC12" s="40" t="n">
+      <c r="AC12" s="30" t="n">
         <v>-1</v>
       </c>
       <c r="AD12" s="24" t="inlineStr">
@@ -4494,11 +4463,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ12" s="38" t="n"/>
+      <c r="BJ12" s="25" t="n"/>
       <c r="BK12" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="BL12" s="39" t="n">
+      <c r="BL12" s="27" t="n">
         <v>1.980392</v>
       </c>
       <c r="BM12" s="28" t="n">
@@ -4508,18 +4477,18 @@
         <v>0.502488</v>
       </c>
       <c r="BO12" s="28" t="n"/>
-      <c r="BP12" s="38" t="n"/>
-      <c r="BQ12" s="39" t="n"/>
+      <c r="BP12" s="25" t="n"/>
+      <c r="BQ12" s="27" t="n"/>
       <c r="BR12" s="28" t="n"/>
       <c r="BS12" s="28" t="n"/>
       <c r="BT12" s="28" t="n"/>
-      <c r="BU12" s="38" t="n"/>
+      <c r="BU12" s="25" t="n"/>
       <c r="BV12" s="29" t="n"/>
       <c r="BW12" s="24" t="n"/>
-      <c r="BX12" s="40" t="n">
+      <c r="BX12" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY12" s="39" t="n">
+      <c r="BY12" s="27" t="n">
         <v>-1</v>
       </c>
       <c r="BZ12" s="24" t="inlineStr">
@@ -4579,7 +4548,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J13" s="38" t="n"/>
+      <c r="J13" s="25" t="n"/>
       <c r="K13" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -4588,7 +4557,7 @@
       <c r="L13" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="M13" s="39" t="n">
+      <c r="M13" s="27" t="n">
         <v>1.980392</v>
       </c>
       <c r="N13" s="28" t="n">
@@ -4628,11 +4597,11 @@
       <c r="X13" s="26" t="n">
         <v>7</v>
       </c>
-      <c r="Y13" s="38" t="n"/>
+      <c r="Y13" s="25" t="n"/>
       <c r="Z13" s="26" t="n"/>
       <c r="AA13" s="28" t="n"/>
       <c r="AB13" s="28" t="n"/>
-      <c r="AC13" s="40" t="n">
+      <c r="AC13" s="30" t="n">
         <v>1.2255</v>
       </c>
       <c r="AD13" s="24" t="inlineStr">
@@ -4769,11 +4738,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ13" s="38" t="n"/>
+      <c r="BJ13" s="25" t="n"/>
       <c r="BK13" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="BL13" s="39" t="n">
+      <c r="BL13" s="27" t="n">
         <v>1.980392</v>
       </c>
       <c r="BM13" s="28" t="n">
@@ -4783,18 +4752,18 @@
         <v>0.502488</v>
       </c>
       <c r="BO13" s="28" t="n"/>
-      <c r="BP13" s="38" t="n"/>
-      <c r="BQ13" s="39" t="n"/>
+      <c r="BP13" s="25" t="n"/>
+      <c r="BQ13" s="27" t="n"/>
       <c r="BR13" s="28" t="n"/>
       <c r="BS13" s="28" t="n"/>
       <c r="BT13" s="28" t="n"/>
-      <c r="BU13" s="38" t="n"/>
+      <c r="BU13" s="25" t="n"/>
       <c r="BV13" s="29" t="n"/>
       <c r="BW13" s="24" t="n"/>
-      <c r="BX13" s="40" t="n">
+      <c r="BX13" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY13" s="39" t="n">
+      <c r="BY13" s="27" t="n">
         <v>0.980392</v>
       </c>
       <c r="BZ13" s="24" t="inlineStr">
@@ -4854,7 +4823,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J14" s="38" t="n"/>
+      <c r="J14" s="25" t="n"/>
       <c r="K14" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -4863,7 +4832,7 @@
       <c r="L14" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="M14" s="39" t="n">
+      <c r="M14" s="27" t="n">
         <v>1.961538</v>
       </c>
       <c r="N14" s="28" t="n">
@@ -4903,11 +4872,11 @@
       <c r="X14" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="Y14" s="38" t="n"/>
+      <c r="Y14" s="25" t="n"/>
       <c r="Z14" s="26" t="n"/>
       <c r="AA14" s="28" t="n"/>
       <c r="AB14" s="28" t="n"/>
-      <c r="AC14" s="40" t="n">
+      <c r="AC14" s="30" t="n">
         <v>-0.75</v>
       </c>
       <c r="AD14" s="24" t="inlineStr">
@@ -5044,11 +5013,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ14" s="38" t="n"/>
+      <c r="BJ14" s="25" t="n"/>
       <c r="BK14" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="BL14" s="39" t="n">
+      <c r="BL14" s="27" t="n">
         <v>1.961538</v>
       </c>
       <c r="BM14" s="28" t="n">
@@ -5058,18 +5027,18 @@
         <v>0.507463</v>
       </c>
       <c r="BO14" s="28" t="n"/>
-      <c r="BP14" s="38" t="n"/>
-      <c r="BQ14" s="39" t="n"/>
+      <c r="BP14" s="25" t="n"/>
+      <c r="BQ14" s="27" t="n"/>
       <c r="BR14" s="28" t="n"/>
       <c r="BS14" s="28" t="n"/>
       <c r="BT14" s="28" t="n"/>
-      <c r="BU14" s="38" t="n"/>
+      <c r="BU14" s="25" t="n"/>
       <c r="BV14" s="29" t="n"/>
       <c r="BW14" s="24" t="n"/>
-      <c r="BX14" s="40" t="n">
+      <c r="BX14" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY14" s="39" t="n">
+      <c r="BY14" s="27" t="n">
         <v>-1</v>
       </c>
       <c r="BZ14" s="24" t="inlineStr">
@@ -5129,7 +5098,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J15" s="38" t="n"/>
+      <c r="J15" s="25" t="n"/>
       <c r="K15" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -5138,7 +5107,7 @@
       <c r="L15" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="M15" s="39" t="n">
+      <c r="M15" s="27" t="n">
         <v>1.961538</v>
       </c>
       <c r="N15" s="28" t="n">
@@ -5178,11 +5147,11 @@
       <c r="X15" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="Y15" s="38" t="n"/>
+      <c r="Y15" s="25" t="n"/>
       <c r="Z15" s="26" t="n"/>
       <c r="AA15" s="28" t="n"/>
       <c r="AB15" s="28" t="n"/>
-      <c r="AC15" s="40" t="n">
+      <c r="AC15" s="30" t="n">
         <v>-1</v>
       </c>
       <c r="AD15" s="24" t="inlineStr">
@@ -5319,11 +5288,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ15" s="38" t="n"/>
+      <c r="BJ15" s="25" t="n"/>
       <c r="BK15" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="BL15" s="39" t="n">
+      <c r="BL15" s="27" t="n">
         <v>1.961538</v>
       </c>
       <c r="BM15" s="28" t="n">
@@ -5333,18 +5302,18 @@
         <v>0.507463</v>
       </c>
       <c r="BO15" s="28" t="n"/>
-      <c r="BP15" s="38" t="n"/>
-      <c r="BQ15" s="39" t="n"/>
+      <c r="BP15" s="25" t="n"/>
+      <c r="BQ15" s="27" t="n"/>
       <c r="BR15" s="28" t="n"/>
       <c r="BS15" s="28" t="n"/>
       <c r="BT15" s="28" t="n"/>
-      <c r="BU15" s="38" t="n"/>
+      <c r="BU15" s="25" t="n"/>
       <c r="BV15" s="29" t="n"/>
       <c r="BW15" s="24" t="n"/>
-      <c r="BX15" s="40" t="n">
+      <c r="BX15" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY15" s="39" t="n">
+      <c r="BY15" s="27" t="n">
         <v>-1</v>
       </c>
       <c r="BZ15" s="24" t="inlineStr">
@@ -5404,7 +5373,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J16" s="38" t="n"/>
+      <c r="J16" s="25" t="n"/>
       <c r="K16" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -5413,7 +5382,7 @@
       <c r="L16" s="26" t="n">
         <v>-111</v>
       </c>
-      <c r="M16" s="39" t="n">
+      <c r="M16" s="27" t="n">
         <v>1.900901</v>
       </c>
       <c r="N16" s="28" t="n">
@@ -5453,11 +5422,11 @@
       <c r="X16" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="Y16" s="38" t="n"/>
+      <c r="Y16" s="25" t="n"/>
       <c r="Z16" s="26" t="n"/>
       <c r="AA16" s="28" t="n"/>
       <c r="AB16" s="28" t="n"/>
-      <c r="AC16" s="40" t="n">
+      <c r="AC16" s="30" t="n">
         <v>-1.5</v>
       </c>
       <c r="AD16" s="24" t="inlineStr">
@@ -5594,11 +5563,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ16" s="38" t="n"/>
+      <c r="BJ16" s="25" t="n"/>
       <c r="BK16" s="26" t="n">
         <v>-111</v>
       </c>
-      <c r="BL16" s="39" t="n">
+      <c r="BL16" s="27" t="n">
         <v>1.900901</v>
       </c>
       <c r="BM16" s="28" t="n">
@@ -5608,18 +5577,18 @@
         <v>0.522388</v>
       </c>
       <c r="BO16" s="28" t="n"/>
-      <c r="BP16" s="38" t="n"/>
-      <c r="BQ16" s="39" t="n"/>
+      <c r="BP16" s="25" t="n"/>
+      <c r="BQ16" s="27" t="n"/>
       <c r="BR16" s="28" t="n"/>
       <c r="BS16" s="28" t="n"/>
       <c r="BT16" s="28" t="n"/>
-      <c r="BU16" s="38" t="n"/>
+      <c r="BU16" s="25" t="n"/>
       <c r="BV16" s="29" t="n"/>
       <c r="BW16" s="24" t="n"/>
-      <c r="BX16" s="40" t="n">
+      <c r="BX16" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY16" s="39" t="n">
+      <c r="BY16" s="27" t="n">
         <v>-1</v>
       </c>
       <c r="BZ16" s="24" t="inlineStr">
@@ -5679,7 +5648,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J17" s="38" t="n"/>
+      <c r="J17" s="25" t="n"/>
       <c r="K17" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -5688,7 +5657,7 @@
       <c r="L17" s="26" t="n">
         <v>-108</v>
       </c>
-      <c r="M17" s="39" t="n">
+      <c r="M17" s="27" t="n">
         <v>1.925926</v>
       </c>
       <c r="N17" s="28" t="n">
@@ -5728,11 +5697,11 @@
       <c r="X17" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="Y17" s="38" t="n"/>
+      <c r="Y17" s="25" t="n"/>
       <c r="Z17" s="26" t="n"/>
       <c r="AA17" s="28" t="n"/>
       <c r="AB17" s="28" t="n"/>
-      <c r="AC17" s="40" t="n">
+      <c r="AC17" s="30" t="n">
         <v>0.9258999999999999</v>
       </c>
       <c r="AD17" s="24" t="inlineStr">
@@ -5869,11 +5838,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ17" s="38" t="n"/>
+      <c r="BJ17" s="25" t="n"/>
       <c r="BK17" s="26" t="n">
         <v>-108</v>
       </c>
-      <c r="BL17" s="39" t="n">
+      <c r="BL17" s="27" t="n">
         <v>1.925926</v>
       </c>
       <c r="BM17" s="28" t="n">
@@ -5883,18 +5852,18 @@
         <v>0.5148509999999999</v>
       </c>
       <c r="BO17" s="28" t="n"/>
-      <c r="BP17" s="38" t="n"/>
-      <c r="BQ17" s="39" t="n"/>
+      <c r="BP17" s="25" t="n"/>
+      <c r="BQ17" s="27" t="n"/>
       <c r="BR17" s="28" t="n"/>
       <c r="BS17" s="28" t="n"/>
       <c r="BT17" s="28" t="n"/>
-      <c r="BU17" s="38" t="n"/>
+      <c r="BU17" s="25" t="n"/>
       <c r="BV17" s="29" t="n"/>
       <c r="BW17" s="24" t="n"/>
-      <c r="BX17" s="40" t="n">
+      <c r="BX17" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY17" s="39" t="n">
+      <c r="BY17" s="27" t="n">
         <v>0.925926</v>
       </c>
       <c r="BZ17" s="24" t="inlineStr">
@@ -5954,7 +5923,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J18" s="38" t="n"/>
+      <c r="J18" s="25" t="n"/>
       <c r="K18" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -5963,7 +5932,7 @@
       <c r="L18" s="26" t="n">
         <v>111</v>
       </c>
-      <c r="M18" s="39" t="n">
+      <c r="M18" s="27" t="n">
         <v>2.11</v>
       </c>
       <c r="N18" s="28" t="n">
@@ -6003,11 +5972,11 @@
       <c r="X18" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="Y18" s="38" t="n"/>
+      <c r="Y18" s="25" t="n"/>
       <c r="Z18" s="26" t="n"/>
       <c r="AA18" s="28" t="n"/>
       <c r="AB18" s="28" t="n"/>
-      <c r="AC18" s="40" t="n">
+      <c r="AC18" s="30" t="n">
         <v>-1.25</v>
       </c>
       <c r="AD18" s="24" t="inlineStr">
@@ -6144,11 +6113,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ18" s="38" t="n"/>
+      <c r="BJ18" s="25" t="n"/>
       <c r="BK18" s="26" t="n">
         <v>111</v>
       </c>
-      <c r="BL18" s="39" t="n">
+      <c r="BL18" s="27" t="n">
         <v>2.11</v>
       </c>
       <c r="BM18" s="28" t="n">
@@ -6158,18 +6127,18 @@
         <v>0.472637</v>
       </c>
       <c r="BO18" s="28" t="n"/>
-      <c r="BP18" s="38" t="n"/>
-      <c r="BQ18" s="39" t="n"/>
+      <c r="BP18" s="25" t="n"/>
+      <c r="BQ18" s="27" t="n"/>
       <c r="BR18" s="28" t="n"/>
       <c r="BS18" s="28" t="n"/>
       <c r="BT18" s="28" t="n"/>
-      <c r="BU18" s="38" t="n"/>
+      <c r="BU18" s="25" t="n"/>
       <c r="BV18" s="29" t="n"/>
       <c r="BW18" s="24" t="n"/>
-      <c r="BX18" s="40" t="n">
+      <c r="BX18" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY18" s="39" t="n">
+      <c r="BY18" s="27" t="n">
         <v>-1</v>
       </c>
       <c r="BZ18" s="24" t="inlineStr">
@@ -6229,7 +6198,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J19" s="38" t="n"/>
+      <c r="J19" s="25" t="n"/>
       <c r="K19" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -6238,7 +6207,7 @@
       <c r="L19" s="26" t="n">
         <v>-125</v>
       </c>
-      <c r="M19" s="39" t="n">
+      <c r="M19" s="27" t="n">
         <v>1.8</v>
       </c>
       <c r="N19" s="28" t="n">
@@ -6278,11 +6247,11 @@
       <c r="X19" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="Y19" s="38" t="n"/>
+      <c r="Y19" s="25" t="n"/>
       <c r="Z19" s="26" t="n"/>
       <c r="AA19" s="28" t="n"/>
       <c r="AB19" s="28" t="n"/>
-      <c r="AC19" s="40" t="n">
+      <c r="AC19" s="30" t="n">
         <v>1.2</v>
       </c>
       <c r="AD19" s="24" t="inlineStr">
@@ -6419,11 +6388,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ19" s="38" t="n"/>
+      <c r="BJ19" s="25" t="n"/>
       <c r="BK19" s="26" t="n">
         <v>-125</v>
       </c>
-      <c r="BL19" s="39" t="n">
+      <c r="BL19" s="27" t="n">
         <v>1.8</v>
       </c>
       <c r="BM19" s="28" t="n">
@@ -6433,18 +6402,18 @@
         <v>0.552239</v>
       </c>
       <c r="BO19" s="28" t="n"/>
-      <c r="BP19" s="38" t="n"/>
-      <c r="BQ19" s="39" t="n"/>
+      <c r="BP19" s="25" t="n"/>
+      <c r="BQ19" s="27" t="n"/>
       <c r="BR19" s="28" t="n"/>
       <c r="BS19" s="28" t="n"/>
       <c r="BT19" s="28" t="n"/>
-      <c r="BU19" s="38" t="n"/>
+      <c r="BU19" s="25" t="n"/>
       <c r="BV19" s="29" t="n"/>
       <c r="BW19" s="24" t="n"/>
-      <c r="BX19" s="40" t="n">
+      <c r="BX19" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY19" s="39" t="n">
+      <c r="BY19" s="27" t="n">
         <v>0.8</v>
       </c>
       <c r="BZ19" s="24" t="inlineStr">
@@ -6504,7 +6473,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J20" s="38" t="n"/>
+      <c r="J20" s="25" t="n"/>
       <c r="K20" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -6513,7 +6482,7 @@
       <c r="L20" s="26" t="n">
         <v>106</v>
       </c>
-      <c r="M20" s="39" t="n">
+      <c r="M20" s="27" t="n">
         <v>2.06</v>
       </c>
       <c r="N20" s="28" t="n">
@@ -6553,11 +6522,11 @@
       <c r="X20" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y20" s="38" t="n"/>
+      <c r="Y20" s="25" t="n"/>
       <c r="Z20" s="26" t="n"/>
       <c r="AA20" s="28" t="n"/>
       <c r="AB20" s="28" t="n"/>
-      <c r="AC20" s="40" t="n">
+      <c r="AC20" s="30" t="n">
         <v>0.795</v>
       </c>
       <c r="AD20" s="24" t="inlineStr">
@@ -6694,11 +6663,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ20" s="38" t="n"/>
+      <c r="BJ20" s="25" t="n"/>
       <c r="BK20" s="26" t="n">
         <v>106</v>
       </c>
-      <c r="BL20" s="39" t="n">
+      <c r="BL20" s="27" t="n">
         <v>2.06</v>
       </c>
       <c r="BM20" s="28" t="n">
@@ -6708,18 +6677,18 @@
         <v>0.482587</v>
       </c>
       <c r="BO20" s="28" t="n"/>
-      <c r="BP20" s="38" t="n"/>
-      <c r="BQ20" s="39" t="n"/>
+      <c r="BP20" s="25" t="n"/>
+      <c r="BQ20" s="27" t="n"/>
       <c r="BR20" s="28" t="n"/>
       <c r="BS20" s="28" t="n"/>
       <c r="BT20" s="28" t="n"/>
-      <c r="BU20" s="38" t="n"/>
+      <c r="BU20" s="25" t="n"/>
       <c r="BV20" s="29" t="n"/>
       <c r="BW20" s="24" t="n"/>
-      <c r="BX20" s="40" t="n">
+      <c r="BX20" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY20" s="39" t="n">
+      <c r="BY20" s="27" t="n">
         <v>1.06</v>
       </c>
       <c r="BZ20" s="24" t="inlineStr">
@@ -6779,7 +6748,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J21" s="38" t="n"/>
+      <c r="J21" s="25" t="n"/>
       <c r="K21" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -6788,7 +6757,7 @@
       <c r="L21" s="26" t="n">
         <v>-106</v>
       </c>
-      <c r="M21" s="39" t="n">
+      <c r="M21" s="27" t="n">
         <v>1.943396</v>
       </c>
       <c r="N21" s="28" t="n">
@@ -6830,11 +6799,11 @@
       <c r="X21" s="26" t="n">
         <v>10</v>
       </c>
-      <c r="Y21" s="38" t="n"/>
+      <c r="Y21" s="25" t="n"/>
       <c r="Z21" s="26" t="n"/>
       <c r="AA21" s="28" t="n"/>
       <c r="AB21" s="28" t="n"/>
-      <c r="AC21" s="40" t="n">
+      <c r="AC21" s="30" t="n">
         <v>0.9434</v>
       </c>
       <c r="AD21" s="24" t="inlineStr">
@@ -6893,11 +6862,11 @@
         </is>
       </c>
       <c r="BI21" s="24" t="n"/>
-      <c r="BJ21" s="38" t="n"/>
+      <c r="BJ21" s="25" t="n"/>
       <c r="BK21" s="26" t="n">
         <v>-106</v>
       </c>
-      <c r="BL21" s="39" t="n">
+      <c r="BL21" s="27" t="n">
         <v>1.943396</v>
       </c>
       <c r="BM21" s="28" t="n">
@@ -6907,16 +6876,16 @@
         <v>0.5124379999999999</v>
       </c>
       <c r="BO21" s="28" t="n"/>
-      <c r="BP21" s="38" t="n"/>
-      <c r="BQ21" s="39" t="n"/>
+      <c r="BP21" s="25" t="n"/>
+      <c r="BQ21" s="27" t="n"/>
       <c r="BR21" s="28" t="n"/>
       <c r="BS21" s="28" t="n"/>
       <c r="BT21" s="28" t="n"/>
-      <c r="BU21" s="38" t="n"/>
+      <c r="BU21" s="25" t="n"/>
       <c r="BV21" s="29" t="n"/>
       <c r="BW21" s="24" t="n"/>
-      <c r="BX21" s="40" t="n"/>
-      <c r="BY21" s="39" t="n"/>
+      <c r="BX21" s="30" t="n"/>
+      <c r="BY21" s="27" t="n"/>
       <c r="BZ21" s="24" t="n"/>
       <c r="CA21" s="31" t="n"/>
     </row>
@@ -6966,7 +6935,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J22" s="38" t="n"/>
+      <c r="J22" s="25" t="n"/>
       <c r="K22" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -6975,7 +6944,7 @@
       <c r="L22" s="26" t="n">
         <v>-106</v>
       </c>
-      <c r="M22" s="39" t="n">
+      <c r="M22" s="27" t="n">
         <v>1.943396</v>
       </c>
       <c r="N22" s="28" t="n">
@@ -7017,11 +6986,11 @@
       <c r="X22" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="Y22" s="38" t="n"/>
+      <c r="Y22" s="25" t="n"/>
       <c r="Z22" s="26" t="n"/>
       <c r="AA22" s="28" t="n"/>
       <c r="AB22" s="28" t="n"/>
-      <c r="AC22" s="40" t="n">
+      <c r="AC22" s="30" t="n">
         <v>0.9434</v>
       </c>
       <c r="AD22" s="24" t="inlineStr">
@@ -7080,11 +7049,11 @@
         </is>
       </c>
       <c r="BI22" s="24" t="n"/>
-      <c r="BJ22" s="38" t="n"/>
+      <c r="BJ22" s="25" t="n"/>
       <c r="BK22" s="26" t="n">
         <v>-106</v>
       </c>
-      <c r="BL22" s="39" t="n">
+      <c r="BL22" s="27" t="n">
         <v>1.943396</v>
       </c>
       <c r="BM22" s="28" t="n">
@@ -7094,16 +7063,16 @@
         <v>0.5124379999999999</v>
       </c>
       <c r="BO22" s="28" t="n"/>
-      <c r="BP22" s="38" t="n"/>
-      <c r="BQ22" s="39" t="n"/>
+      <c r="BP22" s="25" t="n"/>
+      <c r="BQ22" s="27" t="n"/>
       <c r="BR22" s="28" t="n"/>
       <c r="BS22" s="28" t="n"/>
       <c r="BT22" s="28" t="n"/>
-      <c r="BU22" s="38" t="n"/>
+      <c r="BU22" s="25" t="n"/>
       <c r="BV22" s="29" t="n"/>
       <c r="BW22" s="24" t="n"/>
-      <c r="BX22" s="40" t="n"/>
-      <c r="BY22" s="39" t="n"/>
+      <c r="BX22" s="30" t="n"/>
+      <c r="BY22" s="27" t="n"/>
       <c r="BZ22" s="24" t="n"/>
       <c r="CA22" s="31" t="n"/>
     </row>
@@ -7153,7 +7122,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J23" s="38" t="n"/>
+      <c r="J23" s="25" t="n"/>
       <c r="K23" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -7162,7 +7131,7 @@
       <c r="L23" s="26" t="n">
         <v>-141</v>
       </c>
-      <c r="M23" s="39" t="n">
+      <c r="M23" s="27" t="n">
         <v>1.70922</v>
       </c>
       <c r="N23" s="28" t="n">
@@ -7204,11 +7173,11 @@
       <c r="X23" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y23" s="38" t="n"/>
+      <c r="Y23" s="25" t="n"/>
       <c r="Z23" s="26" t="n"/>
       <c r="AA23" s="28" t="n"/>
       <c r="AB23" s="28" t="n"/>
-      <c r="AC23" s="40" t="n">
+      <c r="AC23" s="30" t="n">
         <v>1.2411</v>
       </c>
       <c r="AD23" s="24" t="inlineStr">
@@ -7267,11 +7236,11 @@
         </is>
       </c>
       <c r="BI23" s="24" t="n"/>
-      <c r="BJ23" s="38" t="n"/>
+      <c r="BJ23" s="25" t="n"/>
       <c r="BK23" s="26" t="n">
         <v>-141</v>
       </c>
-      <c r="BL23" s="39" t="n">
+      <c r="BL23" s="27" t="n">
         <v>1.70922</v>
       </c>
       <c r="BM23" s="28" t="n">
@@ -7281,16 +7250,16 @@
         <v>0.58209</v>
       </c>
       <c r="BO23" s="28" t="n"/>
-      <c r="BP23" s="38" t="n"/>
-      <c r="BQ23" s="39" t="n"/>
+      <c r="BP23" s="25" t="n"/>
+      <c r="BQ23" s="27" t="n"/>
       <c r="BR23" s="28" t="n"/>
       <c r="BS23" s="28" t="n"/>
       <c r="BT23" s="28" t="n"/>
-      <c r="BU23" s="38" t="n"/>
+      <c r="BU23" s="25" t="n"/>
       <c r="BV23" s="29" t="n"/>
       <c r="BW23" s="24" t="n"/>
-      <c r="BX23" s="40" t="n"/>
-      <c r="BY23" s="39" t="n"/>
+      <c r="BX23" s="30" t="n"/>
+      <c r="BY23" s="27" t="n"/>
       <c r="BZ23" s="24" t="n"/>
       <c r="CA23" s="31" t="n"/>
     </row>
@@ -7340,7 +7309,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J24" s="38" t="n"/>
+      <c r="J24" s="25" t="n"/>
       <c r="K24" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -7349,7 +7318,7 @@
       <c r="L24" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="M24" s="39" t="n">
+      <c r="M24" s="27" t="n">
         <v>1.75188</v>
       </c>
       <c r="N24" s="28" t="n">
@@ -7391,11 +7360,11 @@
       <c r="X24" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y24" s="38" t="n"/>
+      <c r="Y24" s="25" t="n"/>
       <c r="Z24" s="26" t="n"/>
       <c r="AA24" s="28" t="n"/>
       <c r="AB24" s="28" t="n"/>
-      <c r="AC24" s="40" t="n">
+      <c r="AC24" s="30" t="n">
         <v>-1.5</v>
       </c>
       <c r="AD24" s="24" t="inlineStr">
@@ -7454,11 +7423,11 @@
         </is>
       </c>
       <c r="BI24" s="24" t="n"/>
-      <c r="BJ24" s="38" t="n"/>
+      <c r="BJ24" s="25" t="n"/>
       <c r="BK24" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="BL24" s="39" t="n">
+      <c r="BL24" s="27" t="n">
         <v>1.75188</v>
       </c>
       <c r="BM24" s="28" t="n">
@@ -7468,16 +7437,16 @@
         <v>0.567164</v>
       </c>
       <c r="BO24" s="28" t="n"/>
-      <c r="BP24" s="38" t="n"/>
-      <c r="BQ24" s="39" t="n"/>
+      <c r="BP24" s="25" t="n"/>
+      <c r="BQ24" s="27" t="n"/>
       <c r="BR24" s="28" t="n"/>
       <c r="BS24" s="28" t="n"/>
       <c r="BT24" s="28" t="n"/>
-      <c r="BU24" s="38" t="n"/>
+      <c r="BU24" s="25" t="n"/>
       <c r="BV24" s="29" t="n"/>
       <c r="BW24" s="24" t="n"/>
-      <c r="BX24" s="40" t="n"/>
-      <c r="BY24" s="39" t="n"/>
+      <c r="BX24" s="30" t="n"/>
+      <c r="BY24" s="27" t="n"/>
       <c r="BZ24" s="24" t="n"/>
       <c r="CA24" s="31" t="n"/>
     </row>
@@ -7527,7 +7496,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J25" s="38" t="n"/>
+      <c r="J25" s="25" t="n"/>
       <c r="K25" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -7536,7 +7505,7 @@
       <c r="L25" s="26" t="n">
         <v>104</v>
       </c>
-      <c r="M25" s="39" t="n">
+      <c r="M25" s="27" t="n">
         <v>2.04</v>
       </c>
       <c r="N25" s="28" t="n">
@@ -7578,11 +7547,11 @@
       <c r="X25" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y25" s="38" t="n"/>
+      <c r="Y25" s="25" t="n"/>
       <c r="Z25" s="26" t="n"/>
       <c r="AA25" s="28" t="n"/>
       <c r="AB25" s="28" t="n"/>
-      <c r="AC25" s="40" t="n">
+      <c r="AC25" s="30" t="n">
         <v>1.3</v>
       </c>
       <c r="AD25" s="24" t="inlineStr">
@@ -7641,11 +7610,11 @@
         </is>
       </c>
       <c r="BI25" s="24" t="n"/>
-      <c r="BJ25" s="38" t="n"/>
+      <c r="BJ25" s="25" t="n"/>
       <c r="BK25" s="26" t="n">
         <v>104</v>
       </c>
-      <c r="BL25" s="39" t="n">
+      <c r="BL25" s="27" t="n">
         <v>2.04</v>
       </c>
       <c r="BM25" s="28" t="n">
@@ -7655,16 +7624,16 @@
         <v>0.487562</v>
       </c>
       <c r="BO25" s="28" t="n"/>
-      <c r="BP25" s="38" t="n"/>
-      <c r="BQ25" s="39" t="n"/>
+      <c r="BP25" s="25" t="n"/>
+      <c r="BQ25" s="27" t="n"/>
       <c r="BR25" s="28" t="n"/>
       <c r="BS25" s="28" t="n"/>
       <c r="BT25" s="28" t="n"/>
-      <c r="BU25" s="38" t="n"/>
+      <c r="BU25" s="25" t="n"/>
       <c r="BV25" s="29" t="n"/>
       <c r="BW25" s="24" t="n"/>
-      <c r="BX25" s="40" t="n"/>
-      <c r="BY25" s="39" t="n"/>
+      <c r="BX25" s="30" t="n"/>
+      <c r="BY25" s="27" t="n"/>
       <c r="BZ25" s="24" t="n"/>
       <c r="CA25" s="31" t="n"/>
     </row>
@@ -7714,7 +7683,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J26" s="38" t="n"/>
+      <c r="J26" s="25" t="n"/>
       <c r="K26" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -7723,7 +7692,7 @@
       <c r="L26" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="M26" s="39" t="n">
+      <c r="M26" s="27" t="n">
         <v>1.961538</v>
       </c>
       <c r="N26" s="28" t="n">
@@ -7765,11 +7734,11 @@
       <c r="X26" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="Y26" s="38" t="n"/>
+      <c r="Y26" s="25" t="n"/>
       <c r="Z26" s="26" t="n"/>
       <c r="AA26" s="28" t="n"/>
       <c r="AB26" s="28" t="n"/>
-      <c r="AC26" s="40" t="n">
+      <c r="AC26" s="30" t="n">
         <v>0.9615</v>
       </c>
       <c r="AD26" s="24" t="inlineStr">
@@ -7828,11 +7797,11 @@
         </is>
       </c>
       <c r="BI26" s="24" t="n"/>
-      <c r="BJ26" s="38" t="n"/>
+      <c r="BJ26" s="25" t="n"/>
       <c r="BK26" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="BL26" s="39" t="n">
+      <c r="BL26" s="27" t="n">
         <v>1.961538</v>
       </c>
       <c r="BM26" s="28" t="n">
@@ -7842,16 +7811,16 @@
         <v>0.507463</v>
       </c>
       <c r="BO26" s="28" t="n"/>
-      <c r="BP26" s="38" t="n"/>
-      <c r="BQ26" s="39" t="n"/>
+      <c r="BP26" s="25" t="n"/>
+      <c r="BQ26" s="27" t="n"/>
       <c r="BR26" s="28" t="n"/>
       <c r="BS26" s="28" t="n"/>
       <c r="BT26" s="28" t="n"/>
-      <c r="BU26" s="38" t="n"/>
+      <c r="BU26" s="25" t="n"/>
       <c r="BV26" s="29" t="n"/>
       <c r="BW26" s="24" t="n"/>
-      <c r="BX26" s="40" t="n"/>
-      <c r="BY26" s="39" t="n"/>
+      <c r="BX26" s="30" t="n"/>
+      <c r="BY26" s="27" t="n"/>
       <c r="BZ26" s="24" t="n"/>
       <c r="CA26" s="31" t="n"/>
     </row>
@@ -7901,7 +7870,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J27" s="38" t="n"/>
+      <c r="J27" s="25" t="n"/>
       <c r="K27" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -7910,7 +7879,7 @@
       <c r="L27" s="26" t="n">
         <v>120</v>
       </c>
-      <c r="M27" s="39" t="n">
+      <c r="M27" s="27" t="n">
         <v>2.2</v>
       </c>
       <c r="N27" s="28" t="n">
@@ -7952,11 +7921,11 @@
       <c r="X27" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="Y27" s="38" t="n"/>
+      <c r="Y27" s="25" t="n"/>
       <c r="Z27" s="26" t="n"/>
       <c r="AA27" s="28" t="n"/>
       <c r="AB27" s="28" t="n"/>
-      <c r="AC27" s="40" t="n">
+      <c r="AC27" s="30" t="n">
         <v>-0.75</v>
       </c>
       <c r="AD27" s="24" t="inlineStr">
@@ -8015,11 +7984,11 @@
         </is>
       </c>
       <c r="BI27" s="24" t="n"/>
-      <c r="BJ27" s="38" t="n"/>
+      <c r="BJ27" s="25" t="n"/>
       <c r="BK27" s="26" t="n">
         <v>120</v>
       </c>
-      <c r="BL27" s="39" t="n">
+      <c r="BL27" s="27" t="n">
         <v>2.2</v>
       </c>
       <c r="BM27" s="28" t="n">
@@ -8029,16 +7998,16 @@
         <v>0.452736</v>
       </c>
       <c r="BO27" s="28" t="n"/>
-      <c r="BP27" s="38" t="n"/>
-      <c r="BQ27" s="39" t="n"/>
+      <c r="BP27" s="25" t="n"/>
+      <c r="BQ27" s="27" t="n"/>
       <c r="BR27" s="28" t="n"/>
       <c r="BS27" s="28" t="n"/>
       <c r="BT27" s="28" t="n"/>
-      <c r="BU27" s="38" t="n"/>
+      <c r="BU27" s="25" t="n"/>
       <c r="BV27" s="29" t="n"/>
       <c r="BW27" s="24" t="n"/>
-      <c r="BX27" s="40" t="n"/>
-      <c r="BY27" s="39" t="n"/>
+      <c r="BX27" s="30" t="n"/>
+      <c r="BY27" s="27" t="n"/>
       <c r="BZ27" s="24" t="n"/>
       <c r="CA27" s="31" t="n"/>
     </row>
@@ -8088,7 +8057,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J28" s="38" t="n"/>
+      <c r="J28" s="25" t="n"/>
       <c r="K28" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -8097,7 +8066,7 @@
       <c r="L28" s="26" t="n">
         <v>100</v>
       </c>
-      <c r="M28" s="39" t="n">
+      <c r="M28" s="27" t="n">
         <v>2</v>
       </c>
       <c r="N28" s="28" t="n">
@@ -8139,11 +8108,11 @@
       <c r="X28" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="Y28" s="38" t="n"/>
+      <c r="Y28" s="25" t="n"/>
       <c r="Z28" s="26" t="n"/>
       <c r="AA28" s="28" t="n"/>
       <c r="AB28" s="28" t="n"/>
-      <c r="AC28" s="40" t="n">
+      <c r="AC28" s="30" t="n">
         <v>-0.75</v>
       </c>
       <c r="AD28" s="24" t="inlineStr">
@@ -8202,11 +8171,11 @@
         </is>
       </c>
       <c r="BI28" s="24" t="n"/>
-      <c r="BJ28" s="38" t="n"/>
+      <c r="BJ28" s="25" t="n"/>
       <c r="BK28" s="26" t="n">
         <v>100</v>
       </c>
-      <c r="BL28" s="39" t="n">
+      <c r="BL28" s="27" t="n">
         <v>2</v>
       </c>
       <c r="BM28" s="28" t="n">
@@ -8216,16 +8185,16 @@
         <v>0.497512</v>
       </c>
       <c r="BO28" s="28" t="n"/>
-      <c r="BP28" s="38" t="n"/>
-      <c r="BQ28" s="39" t="n"/>
+      <c r="BP28" s="25" t="n"/>
+      <c r="BQ28" s="27" t="n"/>
       <c r="BR28" s="28" t="n"/>
       <c r="BS28" s="28" t="n"/>
       <c r="BT28" s="28" t="n"/>
-      <c r="BU28" s="38" t="n"/>
+      <c r="BU28" s="25" t="n"/>
       <c r="BV28" s="29" t="n"/>
       <c r="BW28" s="24" t="n"/>
-      <c r="BX28" s="40" t="n"/>
-      <c r="BY28" s="39" t="n"/>
+      <c r="BX28" s="30" t="n"/>
+      <c r="BY28" s="27" t="n"/>
       <c r="BZ28" s="24" t="n"/>
       <c r="CA28" s="31" t="n"/>
     </row>
@@ -8275,7 +8244,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J29" s="38" t="n"/>
+      <c r="J29" s="25" t="n"/>
       <c r="K29" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -8284,7 +8253,7 @@
       <c r="L29" s="26" t="n">
         <v>108</v>
       </c>
-      <c r="M29" s="39" t="n">
+      <c r="M29" s="27" t="n">
         <v>2.08</v>
       </c>
       <c r="N29" s="28" t="n">
@@ -8324,11 +8293,11 @@
       <c r="X29" s="26" t="n">
         <v>8</v>
       </c>
-      <c r="Y29" s="38" t="n"/>
+      <c r="Y29" s="25" t="n"/>
       <c r="Z29" s="26" t="n"/>
       <c r="AA29" s="28" t="n"/>
       <c r="AB29" s="28" t="n"/>
-      <c r="AC29" s="40" t="n">
+      <c r="AC29" s="30" t="n">
         <v>1.35</v>
       </c>
       <c r="AD29" s="24" t="inlineStr">
@@ -8465,11 +8434,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ29" s="38" t="n"/>
+      <c r="BJ29" s="25" t="n"/>
       <c r="BK29" s="26" t="n">
         <v>108</v>
       </c>
-      <c r="BL29" s="39" t="n">
+      <c r="BL29" s="27" t="n">
         <v>2.08</v>
       </c>
       <c r="BM29" s="28" t="n">
@@ -8479,18 +8448,18 @@
         <v>0.477612</v>
       </c>
       <c r="BO29" s="28" t="n"/>
-      <c r="BP29" s="38" t="n"/>
-      <c r="BQ29" s="39" t="n"/>
+      <c r="BP29" s="25" t="n"/>
+      <c r="BQ29" s="27" t="n"/>
       <c r="BR29" s="28" t="n"/>
       <c r="BS29" s="28" t="n"/>
       <c r="BT29" s="28" t="n"/>
-      <c r="BU29" s="38" t="n"/>
+      <c r="BU29" s="25" t="n"/>
       <c r="BV29" s="29" t="n"/>
       <c r="BW29" s="24" t="n"/>
-      <c r="BX29" s="40" t="n">
+      <c r="BX29" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY29" s="39" t="n">
+      <c r="BY29" s="27" t="n">
         <v>1.08</v>
       </c>
       <c r="BZ29" s="24" t="inlineStr">
@@ -8550,7 +8519,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J30" s="38" t="n"/>
+      <c r="J30" s="25" t="n"/>
       <c r="K30" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -8559,7 +8528,7 @@
       <c r="L30" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="M30" s="39" t="n">
+      <c r="M30" s="27" t="n">
         <v>1.75188</v>
       </c>
       <c r="N30" s="28" t="n">
@@ -8599,11 +8568,11 @@
       <c r="X30" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="Y30" s="38" t="n"/>
+      <c r="Y30" s="25" t="n"/>
       <c r="Z30" s="26" t="n"/>
       <c r="AA30" s="28" t="n"/>
       <c r="AB30" s="28" t="n"/>
-      <c r="AC30" s="40" t="n">
+      <c r="AC30" s="30" t="n">
         <v>1.1278</v>
       </c>
       <c r="AD30" s="24" t="inlineStr">
@@ -8740,11 +8709,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ30" s="38" t="n"/>
+      <c r="BJ30" s="25" t="n"/>
       <c r="BK30" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="BL30" s="39" t="n">
+      <c r="BL30" s="27" t="n">
         <v>1.75188</v>
       </c>
       <c r="BM30" s="28" t="n">
@@ -8754,18 +8723,18 @@
         <v>0.567164</v>
       </c>
       <c r="BO30" s="28" t="n"/>
-      <c r="BP30" s="38" t="n"/>
-      <c r="BQ30" s="39" t="n"/>
+      <c r="BP30" s="25" t="n"/>
+      <c r="BQ30" s="27" t="n"/>
       <c r="BR30" s="28" t="n"/>
       <c r="BS30" s="28" t="n"/>
       <c r="BT30" s="28" t="n"/>
-      <c r="BU30" s="38" t="n"/>
+      <c r="BU30" s="25" t="n"/>
       <c r="BV30" s="29" t="n"/>
       <c r="BW30" s="24" t="n"/>
-      <c r="BX30" s="40" t="n">
+      <c r="BX30" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY30" s="39" t="n">
+      <c r="BY30" s="27" t="n">
         <v>0.75188</v>
       </c>
       <c r="BZ30" s="24" t="inlineStr">
@@ -8825,7 +8794,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J31" s="38" t="n"/>
+      <c r="J31" s="25" t="n"/>
       <c r="K31" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -8834,7 +8803,7 @@
       <c r="L31" s="26" t="n">
         <v>130</v>
       </c>
-      <c r="M31" s="39" t="n">
+      <c r="M31" s="27" t="n">
         <v>2.3</v>
       </c>
       <c r="N31" s="28" t="n">
@@ -8874,11 +8843,11 @@
       <c r="X31" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y31" s="38" t="n"/>
+      <c r="Y31" s="25" t="n"/>
       <c r="Z31" s="26" t="n"/>
       <c r="AA31" s="28" t="n"/>
       <c r="AB31" s="28" t="n"/>
-      <c r="AC31" s="40" t="n">
+      <c r="AC31" s="30" t="n">
         <v>-1</v>
       </c>
       <c r="AD31" s="24" t="inlineStr">
@@ -9015,11 +8984,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ31" s="38" t="n"/>
+      <c r="BJ31" s="25" t="n"/>
       <c r="BK31" s="26" t="n">
         <v>130</v>
       </c>
-      <c r="BL31" s="39" t="n">
+      <c r="BL31" s="27" t="n">
         <v>2.3</v>
       </c>
       <c r="BM31" s="28" t="n">
@@ -9029,18 +8998,18 @@
         <v>0.432836</v>
       </c>
       <c r="BO31" s="28" t="n"/>
-      <c r="BP31" s="38" t="n"/>
-      <c r="BQ31" s="39" t="n"/>
+      <c r="BP31" s="25" t="n"/>
+      <c r="BQ31" s="27" t="n"/>
       <c r="BR31" s="28" t="n"/>
       <c r="BS31" s="28" t="n"/>
       <c r="BT31" s="28" t="n"/>
-      <c r="BU31" s="38" t="n"/>
+      <c r="BU31" s="25" t="n"/>
       <c r="BV31" s="29" t="n"/>
       <c r="BW31" s="24" t="n"/>
-      <c r="BX31" s="40" t="n">
+      <c r="BX31" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="BY31" s="39" t="n">
+      <c r="BY31" s="27" t="n">
         <v>-1</v>
       </c>
       <c r="BZ31" s="24" t="inlineStr">
@@ -9100,7 +9069,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J32" s="38" t="n"/>
+      <c r="J32" s="25" t="n"/>
       <c r="K32" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -9109,7 +9078,7 @@
       <c r="L32" s="26" t="n">
         <v>113</v>
       </c>
-      <c r="M32" s="39" t="n">
+      <c r="M32" s="27" t="n">
         <v>2.13</v>
       </c>
       <c r="N32" s="28" t="n">
@@ -9141,11 +9110,11 @@
       <c r="V32" s="24" t="n"/>
       <c r="W32" s="26" t="n"/>
       <c r="X32" s="26" t="n"/>
-      <c r="Y32" s="38" t="n"/>
+      <c r="Y32" s="25" t="n"/>
       <c r="Z32" s="26" t="n"/>
       <c r="AA32" s="28" t="n"/>
       <c r="AB32" s="28" t="n"/>
-      <c r="AC32" s="40" t="n"/>
+      <c r="AC32" s="30" t="n"/>
       <c r="AD32" s="24" t="n"/>
       <c r="AE32" s="31" t="inlineStr">
         <is>
@@ -9276,11 +9245,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ32" s="38" t="n"/>
+      <c r="BJ32" s="25" t="n"/>
       <c r="BK32" s="26" t="n">
         <v>113</v>
       </c>
-      <c r="BL32" s="39" t="n">
+      <c r="BL32" s="27" t="n">
         <v>2.13</v>
       </c>
       <c r="BM32" s="28" t="n">
@@ -9290,16 +9259,16 @@
         <v>0.467662</v>
       </c>
       <c r="BO32" s="28" t="n"/>
-      <c r="BP32" s="38" t="n"/>
-      <c r="BQ32" s="39" t="n"/>
+      <c r="BP32" s="25" t="n"/>
+      <c r="BQ32" s="27" t="n"/>
       <c r="BR32" s="28" t="n"/>
       <c r="BS32" s="28" t="n"/>
       <c r="BT32" s="28" t="n"/>
-      <c r="BU32" s="38" t="n"/>
+      <c r="BU32" s="25" t="n"/>
       <c r="BV32" s="29" t="n"/>
       <c r="BW32" s="24" t="n"/>
-      <c r="BX32" s="40" t="n"/>
-      <c r="BY32" s="39" t="n"/>
+      <c r="BX32" s="30" t="n"/>
+      <c r="BY32" s="27" t="n"/>
       <c r="BZ32" s="24" t="n"/>
       <c r="CA32" s="31" t="n"/>
     </row>
@@ -9349,7 +9318,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J33" s="38" t="n"/>
+      <c r="J33" s="25" t="n"/>
       <c r="K33" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -9358,7 +9327,7 @@
       <c r="L33" s="26" t="n">
         <v>-108</v>
       </c>
-      <c r="M33" s="39" t="n">
+      <c r="M33" s="27" t="n">
         <v>1.925926</v>
       </c>
       <c r="N33" s="28" t="n">
@@ -9390,11 +9359,11 @@
       <c r="V33" s="24" t="n"/>
       <c r="W33" s="26" t="n"/>
       <c r="X33" s="26" t="n"/>
-      <c r="Y33" s="38" t="n"/>
+      <c r="Y33" s="25" t="n"/>
       <c r="Z33" s="26" t="n"/>
       <c r="AA33" s="28" t="n"/>
       <c r="AB33" s="28" t="n"/>
-      <c r="AC33" s="40" t="n"/>
+      <c r="AC33" s="30" t="n"/>
       <c r="AD33" s="24" t="n"/>
       <c r="AE33" s="31" t="inlineStr">
         <is>
@@ -9525,11 +9494,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ33" s="38" t="n"/>
+      <c r="BJ33" s="25" t="n"/>
       <c r="BK33" s="26" t="n">
         <v>-108</v>
       </c>
-      <c r="BL33" s="39" t="n">
+      <c r="BL33" s="27" t="n">
         <v>1.925926</v>
       </c>
       <c r="BM33" s="28" t="n">
@@ -9539,16 +9508,16 @@
         <v>0.517413</v>
       </c>
       <c r="BO33" s="28" t="n"/>
-      <c r="BP33" s="38" t="n"/>
-      <c r="BQ33" s="39" t="n"/>
+      <c r="BP33" s="25" t="n"/>
+      <c r="BQ33" s="27" t="n"/>
       <c r="BR33" s="28" t="n"/>
       <c r="BS33" s="28" t="n"/>
       <c r="BT33" s="28" t="n"/>
-      <c r="BU33" s="38" t="n"/>
+      <c r="BU33" s="25" t="n"/>
       <c r="BV33" s="29" t="n"/>
       <c r="BW33" s="24" t="n"/>
-      <c r="BX33" s="40" t="n"/>
-      <c r="BY33" s="39" t="n"/>
+      <c r="BX33" s="30" t="n"/>
+      <c r="BY33" s="27" t="n"/>
       <c r="BZ33" s="24" t="n"/>
       <c r="CA33" s="31" t="n"/>
     </row>
@@ -9598,7 +9567,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J34" s="38" t="n"/>
+      <c r="J34" s="25" t="n"/>
       <c r="K34" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -9607,7 +9576,7 @@
       <c r="L34" s="26" t="n">
         <v>-108</v>
       </c>
-      <c r="M34" s="39" t="n">
+      <c r="M34" s="27" t="n">
         <v>1.925926</v>
       </c>
       <c r="N34" s="28" t="n">
@@ -9639,11 +9608,11 @@
       <c r="V34" s="24" t="n"/>
       <c r="W34" s="26" t="n"/>
       <c r="X34" s="26" t="n"/>
-      <c r="Y34" s="38" t="n"/>
+      <c r="Y34" s="25" t="n"/>
       <c r="Z34" s="26" t="n"/>
       <c r="AA34" s="28" t="n"/>
       <c r="AB34" s="28" t="n"/>
-      <c r="AC34" s="40" t="n"/>
+      <c r="AC34" s="30" t="n"/>
       <c r="AD34" s="24" t="n"/>
       <c r="AE34" s="31" t="inlineStr">
         <is>
@@ -9774,11 +9743,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ34" s="38" t="n"/>
+      <c r="BJ34" s="25" t="n"/>
       <c r="BK34" s="26" t="n">
         <v>-108</v>
       </c>
-      <c r="BL34" s="39" t="n">
+      <c r="BL34" s="27" t="n">
         <v>1.925926</v>
       </c>
       <c r="BM34" s="28" t="n">
@@ -9788,16 +9757,16 @@
         <v>0.5148509999999999</v>
       </c>
       <c r="BO34" s="28" t="n"/>
-      <c r="BP34" s="38" t="n"/>
-      <c r="BQ34" s="39" t="n"/>
+      <c r="BP34" s="25" t="n"/>
+      <c r="BQ34" s="27" t="n"/>
       <c r="BR34" s="28" t="n"/>
       <c r="BS34" s="28" t="n"/>
       <c r="BT34" s="28" t="n"/>
-      <c r="BU34" s="38" t="n"/>
+      <c r="BU34" s="25" t="n"/>
       <c r="BV34" s="29" t="n"/>
       <c r="BW34" s="24" t="n"/>
-      <c r="BX34" s="40" t="n"/>
-      <c r="BY34" s="39" t="n"/>
+      <c r="BX34" s="30" t="n"/>
+      <c r="BY34" s="27" t="n"/>
       <c r="BZ34" s="24" t="n"/>
       <c r="CA34" s="31" t="n"/>
     </row>
@@ -9847,7 +9816,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J35" s="38" t="n"/>
+      <c r="J35" s="25" t="n"/>
       <c r="K35" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -9856,7 +9825,7 @@
       <c r="L35" s="26" t="n">
         <v>150</v>
       </c>
-      <c r="M35" s="39" t="n">
+      <c r="M35" s="27" t="n">
         <v>2.5</v>
       </c>
       <c r="N35" s="28" t="n">
@@ -9888,11 +9857,11 @@
       <c r="V35" s="24" t="n"/>
       <c r="W35" s="26" t="n"/>
       <c r="X35" s="26" t="n"/>
-      <c r="Y35" s="38" t="n"/>
+      <c r="Y35" s="25" t="n"/>
       <c r="Z35" s="26" t="n"/>
       <c r="AA35" s="28" t="n"/>
       <c r="AB35" s="28" t="n"/>
-      <c r="AC35" s="40" t="n"/>
+      <c r="AC35" s="30" t="n"/>
       <c r="AD35" s="24" t="n"/>
       <c r="AE35" s="31" t="inlineStr">
         <is>
@@ -10023,11 +9992,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ35" s="38" t="n"/>
+      <c r="BJ35" s="25" t="n"/>
       <c r="BK35" s="26" t="n">
         <v>150</v>
       </c>
-      <c r="BL35" s="39" t="n">
+      <c r="BL35" s="27" t="n">
         <v>2.5</v>
       </c>
       <c r="BM35" s="28" t="n">
@@ -10037,28 +10006,28 @@
         <v>0.39604</v>
       </c>
       <c r="BO35" s="28" t="n"/>
-      <c r="BP35" s="38" t="n"/>
-      <c r="BQ35" s="39" t="n"/>
+      <c r="BP35" s="25" t="n"/>
+      <c r="BQ35" s="27" t="n"/>
       <c r="BR35" s="28" t="n"/>
       <c r="BS35" s="28" t="n"/>
       <c r="BT35" s="28" t="n"/>
-      <c r="BU35" s="38" t="n"/>
+      <c r="BU35" s="25" t="n"/>
       <c r="BV35" s="29" t="n"/>
       <c r="BW35" s="24" t="n"/>
-      <c r="BX35" s="40" t="n"/>
-      <c r="BY35" s="39" t="n"/>
+      <c r="BX35" s="30" t="n"/>
+      <c r="BY35" s="27" t="n"/>
       <c r="BZ35" s="24" t="n"/>
       <c r="CA35" s="31" t="n"/>
     </row>
     <row r="36" ht="36" customHeight="1">
       <c r="A36" s="24" t="inlineStr">
         <is>
-          <t>2ca332931d5a4fdb</t>
+          <t>c799abfe71704ed8</t>
         </is>
       </c>
       <c r="B36" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T16:32:37.034238Z</t>
+          <t>2026-07-20T16:42:59.632078Z</t>
         </is>
       </c>
       <c r="C36" s="24" t="inlineStr">
@@ -10096,7 +10065,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J36" s="38" t="n"/>
+      <c r="J36" s="25" t="n"/>
       <c r="K36" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -10105,24 +10074,24 @@
       <c r="L36" s="26" t="n">
         <v>144</v>
       </c>
-      <c r="M36" s="39" t="n">
+      <c r="M36" s="27" t="n">
         <v>2.44</v>
       </c>
       <c r="N36" s="28" t="n">
         <v>0.409836</v>
       </c>
       <c r="O36" s="28" t="n">
-        <v>0.527501</v>
+        <v>0.597574</v>
       </c>
       <c r="P36" s="28" t="n"/>
       <c r="Q36" s="28" t="n">
-        <v>0.117501</v>
+        <v>0.187574</v>
       </c>
       <c r="R36" s="26" t="n">
         <v>100</v>
       </c>
       <c r="S36" s="29" t="n">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="T36" s="24" t="inlineStr">
         <is>
@@ -10137,11 +10106,11 @@
       <c r="V36" s="24" t="n"/>
       <c r="W36" s="26" t="n"/>
       <c r="X36" s="26" t="n"/>
-      <c r="Y36" s="38" t="n"/>
+      <c r="Y36" s="25" t="n"/>
       <c r="Z36" s="26" t="n"/>
       <c r="AA36" s="28" t="n"/>
       <c r="AB36" s="28" t="n"/>
-      <c r="AC36" s="40" t="n"/>
+      <c r="AC36" s="30" t="n"/>
       <c r="AD36" s="24" t="n"/>
       <c r="AE36" s="31" t="inlineStr">
         <is>
@@ -10229,7 +10198,7 @@
       </c>
       <c r="BA36" s="24" t="inlineStr">
         <is>
-          <t>1f56359bf30bb6d51629a345226e3008ebfe73210551f6db9f5ce09f656ffdd6</t>
+          <t>4657ea085a2e161ea0063f513a6bf98a7c01549b126f36526876e6d6a2152307</t>
         </is>
       </c>
       <c r="BB36" s="24" t="inlineStr">
@@ -10244,7 +10213,7 @@
       </c>
       <c r="BD36" s="24" t="inlineStr">
         <is>
-          <t>1f56359bf30bb6d51629a345226e3008ebfe73210551f6db9f5ce09f656ffdd6</t>
+          <t>4657ea085a2e161ea0063f513a6bf98a7c01549b126f36526876e6d6a2152307</t>
         </is>
       </c>
       <c r="BE36" s="24" t="inlineStr">
@@ -10264,7 +10233,7 @@
       </c>
       <c r="BH36" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T16:32:37.034238Z</t>
+          <t>2026-07-20T16:42:59.632078Z</t>
         </is>
       </c>
       <c r="BI36" s="24" t="inlineStr">
@@ -10272,11 +10241,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ36" s="38" t="n"/>
+      <c r="BJ36" s="25" t="n"/>
       <c r="BK36" s="26" t="n">
         <v>144</v>
       </c>
-      <c r="BL36" s="39" t="n">
+      <c r="BL36" s="27" t="n">
         <v>2.44</v>
       </c>
       <c r="BM36" s="28" t="n">
@@ -10284,28 +10253,28 @@
       </c>
       <c r="BN36" s="28" t="n"/>
       <c r="BO36" s="28" t="n"/>
-      <c r="BP36" s="38" t="n"/>
-      <c r="BQ36" s="39" t="n"/>
+      <c r="BP36" s="25" t="n"/>
+      <c r="BQ36" s="27" t="n"/>
       <c r="BR36" s="28" t="n"/>
       <c r="BS36" s="28" t="n"/>
       <c r="BT36" s="28" t="n"/>
-      <c r="BU36" s="38" t="n"/>
+      <c r="BU36" s="25" t="n"/>
       <c r="BV36" s="29" t="n"/>
       <c r="BW36" s="24" t="n"/>
-      <c r="BX36" s="40" t="n"/>
-      <c r="BY36" s="39" t="n"/>
+      <c r="BX36" s="30" t="n"/>
+      <c r="BY36" s="27" t="n"/>
       <c r="BZ36" s="24" t="n"/>
       <c r="CA36" s="31" t="n"/>
     </row>
     <row r="37" ht="36" customHeight="1">
       <c r="A37" s="24" t="inlineStr">
         <is>
-          <t>19b13148b06b408d</t>
+          <t>88e300838c684314</t>
         </is>
       </c>
       <c r="B37" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T16:32:37.134076Z</t>
+          <t>2026-07-20T16:42:59.757524Z</t>
         </is>
       </c>
       <c r="C37" s="24" t="inlineStr">
@@ -10340,10 +10309,10 @@
       </c>
       <c r="I37" s="24" t="inlineStr">
         <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J37" s="38" t="n"/>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J37" s="25" t="n"/>
       <c r="K37" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -10352,24 +10321,24 @@
       <c r="L37" s="26" t="n">
         <v>186</v>
       </c>
-      <c r="M37" s="39" t="n">
+      <c r="M37" s="27" t="n">
         <v>2.86</v>
       </c>
       <c r="N37" s="28" t="n">
         <v>0.34965</v>
       </c>
       <c r="O37" s="28" t="n">
-        <v>0.533959</v>
+        <v>0.597891</v>
       </c>
       <c r="P37" s="28" t="n"/>
       <c r="Q37" s="28" t="n">
-        <v>0.183959</v>
+        <v>0.247891</v>
       </c>
       <c r="R37" s="26" t="n">
         <v>100</v>
       </c>
       <c r="S37" s="29" t="n">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="T37" s="24" t="inlineStr">
         <is>
@@ -10384,11 +10353,11 @@
       <c r="V37" s="24" t="n"/>
       <c r="W37" s="26" t="n"/>
       <c r="X37" s="26" t="n"/>
-      <c r="Y37" s="38" t="n"/>
+      <c r="Y37" s="25" t="n"/>
       <c r="Z37" s="26" t="n"/>
       <c r="AA37" s="28" t="n"/>
       <c r="AB37" s="28" t="n"/>
-      <c r="AC37" s="40" t="n"/>
+      <c r="AC37" s="30" t="n"/>
       <c r="AD37" s="24" t="n"/>
       <c r="AE37" s="31" t="inlineStr">
         <is>
@@ -10476,7 +10445,7 @@
       </c>
       <c r="BA37" s="24" t="inlineStr">
         <is>
-          <t>1f56359bf30bb6d51629a345226e3008ebfe73210551f6db9f5ce09f656ffdd6</t>
+          <t>4657ea085a2e161ea0063f513a6bf98a7c01549b126f36526876e6d6a2152307</t>
         </is>
       </c>
       <c r="BB37" s="24" t="inlineStr">
@@ -10491,7 +10460,7 @@
       </c>
       <c r="BD37" s="24" t="inlineStr">
         <is>
-          <t>1f56359bf30bb6d51629a345226e3008ebfe73210551f6db9f5ce09f656ffdd6</t>
+          <t>4657ea085a2e161ea0063f513a6bf98a7c01549b126f36526876e6d6a2152307</t>
         </is>
       </c>
       <c r="BE37" s="24" t="inlineStr">
@@ -10511,7 +10480,7 @@
       </c>
       <c r="BH37" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T16:32:37.134076Z</t>
+          <t>2026-07-20T16:42:59.757524Z</t>
         </is>
       </c>
       <c r="BI37" s="24" t="inlineStr">
@@ -10519,11 +10488,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ37" s="38" t="n"/>
+      <c r="BJ37" s="25" t="n"/>
       <c r="BK37" s="26" t="n">
         <v>186</v>
       </c>
-      <c r="BL37" s="39" t="n">
+      <c r="BL37" s="27" t="n">
         <v>2.86</v>
       </c>
       <c r="BM37" s="28" t="n">
@@ -10531,28 +10500,28 @@
       </c>
       <c r="BN37" s="28" t="n"/>
       <c r="BO37" s="28" t="n"/>
-      <c r="BP37" s="38" t="n"/>
-      <c r="BQ37" s="39" t="n"/>
+      <c r="BP37" s="25" t="n"/>
+      <c r="BQ37" s="27" t="n"/>
       <c r="BR37" s="28" t="n"/>
       <c r="BS37" s="28" t="n"/>
       <c r="BT37" s="28" t="n"/>
-      <c r="BU37" s="38" t="n"/>
+      <c r="BU37" s="25" t="n"/>
       <c r="BV37" s="29" t="n"/>
       <c r="BW37" s="24" t="n"/>
-      <c r="BX37" s="40" t="n"/>
-      <c r="BY37" s="39" t="n"/>
+      <c r="BX37" s="30" t="n"/>
+      <c r="BY37" s="27" t="n"/>
       <c r="BZ37" s="24" t="n"/>
       <c r="CA37" s="31" t="n"/>
     </row>
     <row r="38" ht="36" customHeight="1">
       <c r="A38" s="24" t="inlineStr">
         <is>
-          <t>3646f4334f58469d</t>
+          <t>6fc69d654df04854</t>
         </is>
       </c>
       <c r="B38" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T16:32:43.485216Z</t>
+          <t>2026-07-20T16:43:06.018541Z</t>
         </is>
       </c>
       <c r="C38" s="24" t="inlineStr">
@@ -10587,36 +10556,36 @@
       </c>
       <c r="I38" s="24" t="inlineStr">
         <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J38" s="38" t="n"/>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J38" s="25" t="n"/>
       <c r="K38" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
         </is>
       </c>
       <c r="L38" s="26" t="n">
-        <v>113</v>
-      </c>
-      <c r="M38" s="39" t="n">
-        <v>2.13</v>
+        <v>223</v>
+      </c>
+      <c r="M38" s="27" t="n">
+        <v>3.23</v>
       </c>
       <c r="N38" s="28" t="n">
-        <v>0.469484</v>
+        <v>0.309598</v>
       </c>
       <c r="O38" s="28" t="n">
-        <v>0.576217</v>
+        <v>0.599201</v>
       </c>
       <c r="P38" s="28" t="n"/>
       <c r="Q38" s="28" t="n">
-        <v>0.106217</v>
+        <v>0.289201</v>
       </c>
       <c r="R38" s="26" t="n">
         <v>100</v>
       </c>
       <c r="S38" s="29" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="T38" s="24" t="inlineStr">
         <is>
@@ -10631,15 +10600,15 @@
       <c r="V38" s="24" t="n"/>
       <c r="W38" s="26" t="n"/>
       <c r="X38" s="26" t="n"/>
-      <c r="Y38" s="38" t="n"/>
+      <c r="Y38" s="25" t="n"/>
       <c r="Z38" s="26" t="n"/>
       <c r="AA38" s="28" t="n"/>
       <c r="AB38" s="28" t="n"/>
-      <c r="AC38" s="40" t="n"/>
+      <c r="AC38" s="30" t="n"/>
       <c r="AD38" s="24" t="n"/>
       <c r="AE38" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4700 (aec-cs2-ica-ej-2026-07-20).</t>
+          <t>Neutral Elo baseline; executable ask 0.3100 (aec-cs2-ica-ej-2026-07-20).</t>
         </is>
       </c>
       <c r="AF38" s="31" t="inlineStr">
@@ -10723,7 +10692,7 @@
       </c>
       <c r="BA38" s="24" t="inlineStr">
         <is>
-          <t>40df7f7b9128e86cfbc485914f5801a00963b62604711b733b60f782ba9e258b</t>
+          <t>8ec29f8dd1985b5dbc96c1339c99e2a2129c4afa4af6efce101e4f76d99dce85</t>
         </is>
       </c>
       <c r="BB38" s="24" t="inlineStr">
@@ -10738,7 +10707,7 @@
       </c>
       <c r="BD38" s="24" t="inlineStr">
         <is>
-          <t>40df7f7b9128e86cfbc485914f5801a00963b62604711b733b60f782ba9e258b</t>
+          <t>8ec29f8dd1985b5dbc96c1339c99e2a2129c4afa4af6efce101e4f76d99dce85</t>
         </is>
       </c>
       <c r="BE38" s="24" t="inlineStr">
@@ -10758,7 +10727,7 @@
       </c>
       <c r="BH38" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T16:32:43.485216Z</t>
+          <t>2026-07-20T16:43:06.018541Z</t>
         </is>
       </c>
       <c r="BI38" s="24" t="inlineStr">
@@ -10766,40 +10735,40 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ38" s="38" t="n"/>
+      <c r="BJ38" s="25" t="n"/>
       <c r="BK38" s="26" t="n">
-        <v>113</v>
-      </c>
-      <c r="BL38" s="39" t="n">
-        <v>2.13</v>
+        <v>223</v>
+      </c>
+      <c r="BL38" s="27" t="n">
+        <v>3.23</v>
       </c>
       <c r="BM38" s="28" t="n">
-        <v>0.469484</v>
+        <v>0.309598</v>
       </c>
       <c r="BN38" s="28" t="n"/>
       <c r="BO38" s="28" t="n"/>
-      <c r="BP38" s="38" t="n"/>
-      <c r="BQ38" s="39" t="n"/>
+      <c r="BP38" s="25" t="n"/>
+      <c r="BQ38" s="27" t="n"/>
       <c r="BR38" s="28" t="n"/>
       <c r="BS38" s="28" t="n"/>
       <c r="BT38" s="28" t="n"/>
-      <c r="BU38" s="38" t="n"/>
+      <c r="BU38" s="25" t="n"/>
       <c r="BV38" s="29" t="n"/>
       <c r="BW38" s="24" t="n"/>
-      <c r="BX38" s="40" t="n"/>
-      <c r="BY38" s="39" t="n"/>
+      <c r="BX38" s="30" t="n"/>
+      <c r="BY38" s="27" t="n"/>
       <c r="BZ38" s="24" t="n"/>
       <c r="CA38" s="31" t="n"/>
     </row>
     <row r="39" ht="36" customHeight="1">
       <c r="A39" s="24" t="inlineStr">
         <is>
-          <t>a2f62addc7be49e9</t>
+          <t>eab33644ea2b4fc1</t>
         </is>
       </c>
       <c r="B39" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T16:32:43.612711Z</t>
+          <t>2026-07-20T16:43:06.145847Z</t>
         </is>
       </c>
       <c r="C39" s="24" t="inlineStr">
@@ -10837,7 +10806,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J39" s="38" t="n"/>
+      <c r="J39" s="25" t="n"/>
       <c r="K39" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -10846,18 +10815,18 @@
       <c r="L39" s="26" t="n">
         <v>-144</v>
       </c>
-      <c r="M39" s="39" t="n">
+      <c r="M39" s="27" t="n">
         <v>1.694444</v>
       </c>
       <c r="N39" s="28" t="n">
         <v>0.590164</v>
       </c>
       <c r="O39" s="28" t="n">
-        <v>0.692542</v>
+        <v>0.719007</v>
       </c>
       <c r="P39" s="28" t="n"/>
       <c r="Q39" s="28" t="n">
-        <v>0.102542</v>
+        <v>0.129007</v>
       </c>
       <c r="R39" s="26" t="n">
         <v>100</v>
@@ -10878,11 +10847,11 @@
       <c r="V39" s="24" t="n"/>
       <c r="W39" s="26" t="n"/>
       <c r="X39" s="26" t="n"/>
-      <c r="Y39" s="38" t="n"/>
+      <c r="Y39" s="25" t="n"/>
       <c r="Z39" s="26" t="n"/>
       <c r="AA39" s="28" t="n"/>
       <c r="AB39" s="28" t="n"/>
-      <c r="AC39" s="40" t="n"/>
+      <c r="AC39" s="30" t="n"/>
       <c r="AD39" s="24" t="n"/>
       <c r="AE39" s="31" t="inlineStr">
         <is>
@@ -10970,7 +10939,7 @@
       </c>
       <c r="BA39" s="24" t="inlineStr">
         <is>
-          <t>40df7f7b9128e86cfbc485914f5801a00963b62604711b733b60f782ba9e258b</t>
+          <t>8ec29f8dd1985b5dbc96c1339c99e2a2129c4afa4af6efce101e4f76d99dce85</t>
         </is>
       </c>
       <c r="BB39" s="24" t="inlineStr">
@@ -10985,7 +10954,7 @@
       </c>
       <c r="BD39" s="24" t="inlineStr">
         <is>
-          <t>40df7f7b9128e86cfbc485914f5801a00963b62604711b733b60f782ba9e258b</t>
+          <t>8ec29f8dd1985b5dbc96c1339c99e2a2129c4afa4af6efce101e4f76d99dce85</t>
         </is>
       </c>
       <c r="BE39" s="24" t="inlineStr">
@@ -11005,7 +10974,7 @@
       </c>
       <c r="BH39" s="24" t="inlineStr">
         <is>
-          <t>2026-07-20T16:32:43.612711Z</t>
+          <t>2026-07-20T16:43:06.145847Z</t>
         </is>
       </c>
       <c r="BI39" s="24" t="inlineStr">
@@ -11013,11 +10982,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ39" s="38" t="n"/>
+      <c r="BJ39" s="25" t="n"/>
       <c r="BK39" s="26" t="n">
         <v>-144</v>
       </c>
-      <c r="BL39" s="39" t="n">
+      <c r="BL39" s="27" t="n">
         <v>1.694444</v>
       </c>
       <c r="BM39" s="28" t="n">
@@ -11025,16 +10994,16 @@
       </c>
       <c r="BN39" s="28" t="n"/>
       <c r="BO39" s="28" t="n"/>
-      <c r="BP39" s="38" t="n"/>
-      <c r="BQ39" s="39" t="n"/>
+      <c r="BP39" s="25" t="n"/>
+      <c r="BQ39" s="27" t="n"/>
       <c r="BR39" s="28" t="n"/>
       <c r="BS39" s="28" t="n"/>
       <c r="BT39" s="28" t="n"/>
-      <c r="BU39" s="38" t="n"/>
+      <c r="BU39" s="25" t="n"/>
       <c r="BV39" s="29" t="n"/>
       <c r="BW39" s="24" t="n"/>
-      <c r="BX39" s="40" t="n"/>
-      <c r="BY39" s="39" t="n"/>
+      <c r="BX39" s="30" t="n"/>
+      <c r="BY39" s="27" t="n"/>
       <c r="BZ39" s="24" t="n"/>
       <c r="CA39" s="31" t="n"/>
     </row>

--- a/data/picks.xlsx
+++ b/data/picks.xlsx
@@ -21,10 +21,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="0.0###"/>
-    <numFmt numFmtId="165" formatCode="0.000000"/>
-    <numFmt numFmtId="166" formatCode="0.0000"/>
-    <numFmt numFmtId="167" formatCode="0.0%"/>
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
+    <numFmt numFmtId="166" formatCode="0.0###"/>
+    <numFmt numFmtId="167" formatCode="0.000000"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -136,7 +136,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -150,10 +150,10 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -169,10 +169,10 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -184,10 +184,10 @@
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -202,13 +202,13 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="10" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -217,11 +217,38 @@
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -785,11 +812,11 @@
         <f>COUNTIFS('Picks'!$BX$2:$BX$39,"&gt;0",'Picks'!$V$2:$V$39,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$39,"&gt;0",'Picks'!$V$2:$V$39,"loss")</f>
         <v/>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="32">
         <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$39,"&gt;0",'Picks'!$V$2:$V$39,"win")/(COUNTIFS('Picks'!$BX$2:$BX$39,"&gt;0",'Picks'!$V$2:$V$39,"win")+COUNTIFS('Picks'!$BX$2:$BX$39,"&gt;0",'Picks'!$V$2:$V$39,"loss")),0)</f>
         <v/>
       </c>
-      <c r="G7" s="7">
+      <c r="G7" s="32">
         <f>IFERROR(SUM('Picks'!$BY$2:$BY$39)/SUM('Picks'!$BX$2:$BX$39),0)</f>
         <v/>
       </c>
@@ -817,7 +844,7 @@
       </c>
     </row>
     <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="8">
+      <c r="A10" s="33">
         <f>SUM('Picks'!$BY$2:$BY$39)</f>
         <v/>
       </c>
@@ -829,7 +856,7 @@
         <f>COUNTIFS('Picks'!$AM$2:$AM$39,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$39,"settled")</f>
         <v/>
       </c>
-      <c r="G10" s="8">
+      <c r="G10" s="33">
         <f>SUMIFS('Picks'!$AC$2:$AC$39,'Picks'!$AM$2:$AM$39,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
@@ -896,11 +923,11 @@
         <f>COUNTIFS('Picks'!$H$2:$H$39,$A14,'Picks'!$U$2:$U$39,"settled",'Picks'!$V$2:$V$39,"loss")</f>
         <v/>
       </c>
-      <c r="E14" s="14">
+      <c r="E14" s="34">
         <f>IFERROR(C14/(C14+D14),0)</f>
         <v/>
       </c>
-      <c r="F14" s="15">
+      <c r="F14" s="35">
         <f>SUMIFS('Picks'!$BY$2:$BY$39,'Picks'!$H$2:$H$39,$A14)</f>
         <v/>
       </c>
@@ -927,11 +954,11 @@
         <f>COUNTIFS('Picks'!$H$2:$H$39,$A15,'Picks'!$U$2:$U$39,"settled",'Picks'!$V$2:$V$39,"loss")</f>
         <v/>
       </c>
-      <c r="E15" s="19">
+      <c r="E15" s="36">
         <f>IFERROR(C15/(C15+D15),0)</f>
         <v/>
       </c>
-      <c r="F15" s="20">
+      <c r="F15" s="37">
         <f>SUMIFS('Picks'!$BY$2:$BY$39,'Picks'!$H$2:$H$39,$A15)</f>
         <v/>
       </c>
@@ -958,11 +985,11 @@
         <f>COUNTIFS('Picks'!$H$2:$H$39,$A16,'Picks'!$U$2:$U$39,"settled",'Picks'!$V$2:$V$39,"loss")</f>
         <v/>
       </c>
-      <c r="E16" s="14">
+      <c r="E16" s="34">
         <f>IFERROR(C16/(C16+D16),0)</f>
         <v/>
       </c>
-      <c r="F16" s="15">
+      <c r="F16" s="35">
         <f>SUMIFS('Picks'!$BY$2:$BY$39,'Picks'!$H$2:$H$39,$A16)</f>
         <v/>
       </c>
@@ -996,7 +1023,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CA39"/>
+  <dimension ref="A1:CA35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1523,7 +1550,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J2" s="25" t="n"/>
+      <c r="J2" s="38" t="n"/>
       <c r="K2" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -1532,7 +1559,7 @@
       <c r="L2" s="26" t="n">
         <v>117</v>
       </c>
-      <c r="M2" s="27" t="n">
+      <c r="M2" s="39" t="n">
         <v>2.17</v>
       </c>
       <c r="N2" s="28" t="n">
@@ -1572,11 +1599,11 @@
       <c r="X2" s="26" t="n">
         <v>108</v>
       </c>
-      <c r="Y2" s="25" t="n"/>
+      <c r="Y2" s="38" t="n"/>
       <c r="Z2" s="26" t="n"/>
       <c r="AA2" s="28" t="n"/>
       <c r="AB2" s="28" t="n"/>
-      <c r="AC2" s="30" t="n">
+      <c r="AC2" s="40" t="n">
         <v>1.755</v>
       </c>
       <c r="AD2" s="24" t="inlineStr">
@@ -1713,11 +1740,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ2" s="25" t="n"/>
+      <c r="BJ2" s="38" t="n"/>
       <c r="BK2" s="26" t="n">
         <v>117</v>
       </c>
-      <c r="BL2" s="27" t="n">
+      <c r="BL2" s="39" t="n">
         <v>2.17</v>
       </c>
       <c r="BM2" s="28" t="n">
@@ -1727,18 +1754,18 @@
         <v>0.455446</v>
       </c>
       <c r="BO2" s="28" t="n"/>
-      <c r="BP2" s="25" t="n"/>
-      <c r="BQ2" s="27" t="n"/>
+      <c r="BP2" s="38" t="n"/>
+      <c r="BQ2" s="39" t="n"/>
       <c r="BR2" s="28" t="n"/>
       <c r="BS2" s="28" t="n"/>
       <c r="BT2" s="28" t="n"/>
-      <c r="BU2" s="25" t="n"/>
+      <c r="BU2" s="38" t="n"/>
       <c r="BV2" s="29" t="n"/>
       <c r="BW2" s="24" t="n"/>
-      <c r="BX2" s="30" t="n">
+      <c r="BX2" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY2" s="27" t="n">
+      <c r="BY2" s="39" t="n">
         <v>1.17</v>
       </c>
       <c r="BZ2" s="24" t="inlineStr">
@@ -1798,7 +1825,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J3" s="25" t="n"/>
+      <c r="J3" s="38" t="n"/>
       <c r="K3" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -1807,7 +1834,7 @@
       <c r="L3" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="M3" s="27" t="n">
+      <c r="M3" s="39" t="n">
         <v>1.75188</v>
       </c>
       <c r="N3" s="28" t="n">
@@ -1847,11 +1874,11 @@
       <c r="X3" s="26" t="n">
         <v>8</v>
       </c>
-      <c r="Y3" s="25" t="n"/>
+      <c r="Y3" s="38" t="n"/>
       <c r="Z3" s="26" t="n"/>
       <c r="AA3" s="28" t="n"/>
       <c r="AB3" s="28" t="n"/>
-      <c r="AC3" s="30" t="n">
+      <c r="AC3" s="40" t="n">
         <v>1.1278</v>
       </c>
       <c r="AD3" s="24" t="inlineStr">
@@ -1988,11 +2015,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ3" s="25" t="n"/>
+      <c r="BJ3" s="38" t="n"/>
       <c r="BK3" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="BL3" s="27" t="n">
+      <c r="BL3" s="39" t="n">
         <v>1.75188</v>
       </c>
       <c r="BM3" s="28" t="n">
@@ -2002,18 +2029,18 @@
         <v>0.567164</v>
       </c>
       <c r="BO3" s="28" t="n"/>
-      <c r="BP3" s="25" t="n"/>
-      <c r="BQ3" s="27" t="n"/>
+      <c r="BP3" s="38" t="n"/>
+      <c r="BQ3" s="39" t="n"/>
       <c r="BR3" s="28" t="n"/>
       <c r="BS3" s="28" t="n"/>
       <c r="BT3" s="28" t="n"/>
-      <c r="BU3" s="25" t="n"/>
+      <c r="BU3" s="38" t="n"/>
       <c r="BV3" s="29" t="n"/>
       <c r="BW3" s="24" t="n"/>
-      <c r="BX3" s="30" t="n">
+      <c r="BX3" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY3" s="27" t="n">
+      <c r="BY3" s="39" t="n">
         <v>0.75188</v>
       </c>
       <c r="BZ3" s="24" t="inlineStr">
@@ -2073,7 +2100,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J4" s="25" t="n"/>
+      <c r="J4" s="38" t="n"/>
       <c r="K4" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -2082,7 +2109,7 @@
       <c r="L4" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="M4" s="27" t="n">
+      <c r="M4" s="39" t="n">
         <v>1.980392</v>
       </c>
       <c r="N4" s="28" t="n">
@@ -2122,11 +2149,11 @@
       <c r="X4" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="Y4" s="25" t="n"/>
+      <c r="Y4" s="38" t="n"/>
       <c r="Z4" s="26" t="n"/>
       <c r="AA4" s="28" t="n"/>
       <c r="AB4" s="28" t="n"/>
-      <c r="AC4" s="30" t="n">
+      <c r="AC4" s="40" t="n">
         <v>-1</v>
       </c>
       <c r="AD4" s="24" t="inlineStr">
@@ -2263,11 +2290,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ4" s="25" t="n"/>
+      <c r="BJ4" s="38" t="n"/>
       <c r="BK4" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="BL4" s="27" t="n">
+      <c r="BL4" s="39" t="n">
         <v>1.980392</v>
       </c>
       <c r="BM4" s="28" t="n">
@@ -2277,18 +2304,18 @@
         <v>0.502488</v>
       </c>
       <c r="BO4" s="28" t="n"/>
-      <c r="BP4" s="25" t="n"/>
-      <c r="BQ4" s="27" t="n"/>
+      <c r="BP4" s="38" t="n"/>
+      <c r="BQ4" s="39" t="n"/>
       <c r="BR4" s="28" t="n"/>
       <c r="BS4" s="28" t="n"/>
       <c r="BT4" s="28" t="n"/>
-      <c r="BU4" s="25" t="n"/>
+      <c r="BU4" s="38" t="n"/>
       <c r="BV4" s="29" t="n"/>
       <c r="BW4" s="24" t="n"/>
-      <c r="BX4" s="30" t="n">
+      <c r="BX4" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY4" s="27" t="n">
+      <c r="BY4" s="39" t="n">
         <v>-1</v>
       </c>
       <c r="BZ4" s="24" t="inlineStr">
@@ -2348,7 +2375,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J5" s="25" t="n"/>
+      <c r="J5" s="38" t="n"/>
       <c r="K5" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -2357,7 +2384,7 @@
       <c r="L5" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="M5" s="27" t="n">
+      <c r="M5" s="39" t="n">
         <v>1.75188</v>
       </c>
       <c r="N5" s="28" t="n">
@@ -2397,11 +2424,11 @@
       <c r="X5" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="Y5" s="25" t="n"/>
+      <c r="Y5" s="38" t="n"/>
       <c r="Z5" s="26" t="n"/>
       <c r="AA5" s="28" t="n"/>
       <c r="AB5" s="28" t="n"/>
-      <c r="AC5" s="30" t="n">
+      <c r="AC5" s="40" t="n">
         <v>1.1278</v>
       </c>
       <c r="AD5" s="24" t="inlineStr">
@@ -2538,11 +2565,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ5" s="25" t="n"/>
+      <c r="BJ5" s="38" t="n"/>
       <c r="BK5" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="BL5" s="27" t="n">
+      <c r="BL5" s="39" t="n">
         <v>1.75188</v>
       </c>
       <c r="BM5" s="28" t="n">
@@ -2552,18 +2579,18 @@
         <v>0.567164</v>
       </c>
       <c r="BO5" s="28" t="n"/>
-      <c r="BP5" s="25" t="n"/>
-      <c r="BQ5" s="27" t="n"/>
+      <c r="BP5" s="38" t="n"/>
+      <c r="BQ5" s="39" t="n"/>
       <c r="BR5" s="28" t="n"/>
       <c r="BS5" s="28" t="n"/>
       <c r="BT5" s="28" t="n"/>
-      <c r="BU5" s="25" t="n"/>
+      <c r="BU5" s="38" t="n"/>
       <c r="BV5" s="29" t="n"/>
       <c r="BW5" s="24" t="n"/>
-      <c r="BX5" s="30" t="n">
+      <c r="BX5" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY5" s="27" t="n">
+      <c r="BY5" s="39" t="n">
         <v>0.75188</v>
       </c>
       <c r="BZ5" s="24" t="inlineStr">
@@ -2623,7 +2650,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J6" s="25" t="n"/>
+      <c r="J6" s="38" t="n"/>
       <c r="K6" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -2632,7 +2659,7 @@
       <c r="L6" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="M6" s="27" t="n">
+      <c r="M6" s="39" t="n">
         <v>1.961538</v>
       </c>
       <c r="N6" s="28" t="n">
@@ -2672,11 +2699,11 @@
       <c r="X6" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="Y6" s="25" t="n"/>
+      <c r="Y6" s="38" t="n"/>
       <c r="Z6" s="26" t="n"/>
       <c r="AA6" s="28" t="n"/>
       <c r="AB6" s="28" t="n"/>
-      <c r="AC6" s="30" t="n">
+      <c r="AC6" s="40" t="n">
         <v>1.2019</v>
       </c>
       <c r="AD6" s="24" t="inlineStr">
@@ -2813,11 +2840,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ6" s="25" t="n"/>
+      <c r="BJ6" s="38" t="n"/>
       <c r="BK6" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="BL6" s="27" t="n">
+      <c r="BL6" s="39" t="n">
         <v>1.961538</v>
       </c>
       <c r="BM6" s="28" t="n">
@@ -2827,18 +2854,18 @@
         <v>0.507463</v>
       </c>
       <c r="BO6" s="28" t="n"/>
-      <c r="BP6" s="25" t="n"/>
-      <c r="BQ6" s="27" t="n"/>
+      <c r="BP6" s="38" t="n"/>
+      <c r="BQ6" s="39" t="n"/>
       <c r="BR6" s="28" t="n"/>
       <c r="BS6" s="28" t="n"/>
       <c r="BT6" s="28" t="n"/>
-      <c r="BU6" s="25" t="n"/>
+      <c r="BU6" s="38" t="n"/>
       <c r="BV6" s="29" t="n"/>
       <c r="BW6" s="24" t="n"/>
-      <c r="BX6" s="30" t="n">
+      <c r="BX6" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY6" s="27" t="n">
+      <c r="BY6" s="39" t="n">
         <v>0.961538</v>
       </c>
       <c r="BZ6" s="24" t="inlineStr">
@@ -2898,7 +2925,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J7" s="25" t="n"/>
+      <c r="J7" s="38" t="n"/>
       <c r="K7" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -2907,7 +2934,7 @@
       <c r="L7" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="M7" s="27" t="n">
+      <c r="M7" s="39" t="n">
         <v>1.961538</v>
       </c>
       <c r="N7" s="28" t="n">
@@ -2947,11 +2974,11 @@
       <c r="X7" s="26" t="n">
         <v>10</v>
       </c>
-      <c r="Y7" s="25" t="n"/>
+      <c r="Y7" s="38" t="n"/>
       <c r="Z7" s="26" t="n"/>
       <c r="AA7" s="28" t="n"/>
       <c r="AB7" s="28" t="n"/>
-      <c r="AC7" s="30" t="n">
+      <c r="AC7" s="40" t="n">
         <v>-1.25</v>
       </c>
       <c r="AD7" s="24" t="inlineStr">
@@ -3088,11 +3115,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ7" s="25" t="n"/>
+      <c r="BJ7" s="38" t="n"/>
       <c r="BK7" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="BL7" s="27" t="n">
+      <c r="BL7" s="39" t="n">
         <v>1.961538</v>
       </c>
       <c r="BM7" s="28" t="n">
@@ -3102,18 +3129,18 @@
         <v>0.507463</v>
       </c>
       <c r="BO7" s="28" t="n"/>
-      <c r="BP7" s="25" t="n"/>
-      <c r="BQ7" s="27" t="n"/>
+      <c r="BP7" s="38" t="n"/>
+      <c r="BQ7" s="39" t="n"/>
       <c r="BR7" s="28" t="n"/>
       <c r="BS7" s="28" t="n"/>
       <c r="BT7" s="28" t="n"/>
-      <c r="BU7" s="25" t="n"/>
+      <c r="BU7" s="38" t="n"/>
       <c r="BV7" s="29" t="n"/>
       <c r="BW7" s="24" t="n"/>
-      <c r="BX7" s="30" t="n">
+      <c r="BX7" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY7" s="27" t="n">
+      <c r="BY7" s="39" t="n">
         <v>-1</v>
       </c>
       <c r="BZ7" s="24" t="inlineStr">
@@ -3173,7 +3200,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J8" s="25" t="n"/>
+      <c r="J8" s="38" t="n"/>
       <c r="K8" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -3182,7 +3209,7 @@
       <c r="L8" s="26" t="n">
         <v>-106</v>
       </c>
-      <c r="M8" s="27" t="n">
+      <c r="M8" s="39" t="n">
         <v>1.943396</v>
       </c>
       <c r="N8" s="28" t="n">
@@ -3222,11 +3249,11 @@
       <c r="X8" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="Y8" s="25" t="n"/>
+      <c r="Y8" s="38" t="n"/>
       <c r="Z8" s="26" t="n"/>
       <c r="AA8" s="28" t="n"/>
       <c r="AB8" s="28" t="n"/>
-      <c r="AC8" s="30" t="n">
+      <c r="AC8" s="40" t="n">
         <v>-1</v>
       </c>
       <c r="AD8" s="24" t="inlineStr">
@@ -3363,11 +3390,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ8" s="25" t="n"/>
+      <c r="BJ8" s="38" t="n"/>
       <c r="BK8" s="26" t="n">
         <v>-106</v>
       </c>
-      <c r="BL8" s="27" t="n">
+      <c r="BL8" s="39" t="n">
         <v>1.943396</v>
       </c>
       <c r="BM8" s="28" t="n">
@@ -3377,18 +3404,18 @@
         <v>0.5124379999999999</v>
       </c>
       <c r="BO8" s="28" t="n"/>
-      <c r="BP8" s="25" t="n"/>
-      <c r="BQ8" s="27" t="n"/>
+      <c r="BP8" s="38" t="n"/>
+      <c r="BQ8" s="39" t="n"/>
       <c r="BR8" s="28" t="n"/>
       <c r="BS8" s="28" t="n"/>
       <c r="BT8" s="28" t="n"/>
-      <c r="BU8" s="25" t="n"/>
+      <c r="BU8" s="38" t="n"/>
       <c r="BV8" s="29" t="n"/>
       <c r="BW8" s="24" t="n"/>
-      <c r="BX8" s="30" t="n">
+      <c r="BX8" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY8" s="27" t="n">
+      <c r="BY8" s="39" t="n">
         <v>-1</v>
       </c>
       <c r="BZ8" s="24" t="inlineStr">
@@ -3448,7 +3475,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J9" s="25" t="n"/>
+      <c r="J9" s="38" t="n"/>
       <c r="K9" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -3457,7 +3484,7 @@
       <c r="L9" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="M9" s="27" t="n">
+      <c r="M9" s="39" t="n">
         <v>1.980392</v>
       </c>
       <c r="N9" s="28" t="n">
@@ -3497,11 +3524,11 @@
       <c r="X9" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="Y9" s="25" t="n"/>
+      <c r="Y9" s="38" t="n"/>
       <c r="Z9" s="26" t="n"/>
       <c r="AA9" s="28" t="n"/>
       <c r="AB9" s="28" t="n"/>
-      <c r="AC9" s="30" t="n">
+      <c r="AC9" s="40" t="n">
         <v>0.9804</v>
       </c>
       <c r="AD9" s="24" t="inlineStr">
@@ -3638,11 +3665,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ9" s="25" t="n"/>
+      <c r="BJ9" s="38" t="n"/>
       <c r="BK9" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="BL9" s="27" t="n">
+      <c r="BL9" s="39" t="n">
         <v>1.980392</v>
       </c>
       <c r="BM9" s="28" t="n">
@@ -3652,18 +3679,18 @@
         <v>0.502488</v>
       </c>
       <c r="BO9" s="28" t="n"/>
-      <c r="BP9" s="25" t="n"/>
-      <c r="BQ9" s="27" t="n"/>
+      <c r="BP9" s="38" t="n"/>
+      <c r="BQ9" s="39" t="n"/>
       <c r="BR9" s="28" t="n"/>
       <c r="BS9" s="28" t="n"/>
       <c r="BT9" s="28" t="n"/>
-      <c r="BU9" s="25" t="n"/>
+      <c r="BU9" s="38" t="n"/>
       <c r="BV9" s="29" t="n"/>
       <c r="BW9" s="24" t="n"/>
-      <c r="BX9" s="30" t="n">
+      <c r="BX9" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY9" s="27" t="n">
+      <c r="BY9" s="39" t="n">
         <v>0.980392</v>
       </c>
       <c r="BZ9" s="24" t="inlineStr">
@@ -3723,7 +3750,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J10" s="25" t="n"/>
+      <c r="J10" s="38" t="n"/>
       <c r="K10" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -3732,7 +3759,7 @@
       <c r="L10" s="26" t="n">
         <v>-138</v>
       </c>
-      <c r="M10" s="27" t="n">
+      <c r="M10" s="39" t="n">
         <v>1.724638</v>
       </c>
       <c r="N10" s="28" t="n">
@@ -3772,11 +3799,11 @@
       <c r="X10" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="Y10" s="25" t="n"/>
+      <c r="Y10" s="38" t="n"/>
       <c r="Z10" s="26" t="n"/>
       <c r="AA10" s="28" t="n"/>
       <c r="AB10" s="28" t="n"/>
-      <c r="AC10" s="30" t="n">
+      <c r="AC10" s="40" t="n">
         <v>1.2681</v>
       </c>
       <c r="AD10" s="24" t="inlineStr">
@@ -3913,11 +3940,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ10" s="25" t="n"/>
+      <c r="BJ10" s="38" t="n"/>
       <c r="BK10" s="26" t="n">
         <v>-138</v>
       </c>
-      <c r="BL10" s="27" t="n">
+      <c r="BL10" s="39" t="n">
         <v>1.724638</v>
       </c>
       <c r="BM10" s="28" t="n">
@@ -3927,18 +3954,18 @@
         <v>0.577114</v>
       </c>
       <c r="BO10" s="28" t="n"/>
-      <c r="BP10" s="25" t="n"/>
-      <c r="BQ10" s="27" t="n"/>
+      <c r="BP10" s="38" t="n"/>
+      <c r="BQ10" s="39" t="n"/>
       <c r="BR10" s="28" t="n"/>
       <c r="BS10" s="28" t="n"/>
       <c r="BT10" s="28" t="n"/>
-      <c r="BU10" s="25" t="n"/>
+      <c r="BU10" s="38" t="n"/>
       <c r="BV10" s="29" t="n"/>
       <c r="BW10" s="24" t="n"/>
-      <c r="BX10" s="30" t="n">
+      <c r="BX10" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY10" s="27" t="n">
+      <c r="BY10" s="39" t="n">
         <v>0.724638</v>
       </c>
       <c r="BZ10" s="24" t="inlineStr">
@@ -3998,7 +4025,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J11" s="25" t="n"/>
+      <c r="J11" s="38" t="n"/>
       <c r="K11" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -4007,7 +4034,7 @@
       <c r="L11" s="26" t="n">
         <v>102</v>
       </c>
-      <c r="M11" s="27" t="n">
+      <c r="M11" s="39" t="n">
         <v>2.02</v>
       </c>
       <c r="N11" s="28" t="n">
@@ -4047,11 +4074,11 @@
       <c r="X11" s="26" t="n">
         <v>15</v>
       </c>
-      <c r="Y11" s="25" t="n"/>
+      <c r="Y11" s="38" t="n"/>
       <c r="Z11" s="26" t="n"/>
       <c r="AA11" s="28" t="n"/>
       <c r="AB11" s="28" t="n"/>
-      <c r="AC11" s="30" t="n">
+      <c r="AC11" s="40" t="n">
         <v>1.275</v>
       </c>
       <c r="AD11" s="24" t="inlineStr">
@@ -4188,11 +4215,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ11" s="25" t="n"/>
+      <c r="BJ11" s="38" t="n"/>
       <c r="BK11" s="26" t="n">
         <v>102</v>
       </c>
-      <c r="BL11" s="27" t="n">
+      <c r="BL11" s="39" t="n">
         <v>2.02</v>
       </c>
       <c r="BM11" s="28" t="n">
@@ -4202,18 +4229,18 @@
         <v>0.492537</v>
       </c>
       <c r="BO11" s="28" t="n"/>
-      <c r="BP11" s="25" t="n"/>
-      <c r="BQ11" s="27" t="n"/>
+      <c r="BP11" s="38" t="n"/>
+      <c r="BQ11" s="39" t="n"/>
       <c r="BR11" s="28" t="n"/>
       <c r="BS11" s="28" t="n"/>
       <c r="BT11" s="28" t="n"/>
-      <c r="BU11" s="25" t="n"/>
+      <c r="BU11" s="38" t="n"/>
       <c r="BV11" s="29" t="n"/>
       <c r="BW11" s="24" t="n"/>
-      <c r="BX11" s="30" t="n">
+      <c r="BX11" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY11" s="27" t="n">
+      <c r="BY11" s="39" t="n">
         <v>1.02</v>
       </c>
       <c r="BZ11" s="24" t="inlineStr">
@@ -4273,7 +4300,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J12" s="25" t="n"/>
+      <c r="J12" s="38" t="n"/>
       <c r="K12" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -4282,7 +4309,7 @@
       <c r="L12" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="M12" s="27" t="n">
+      <c r="M12" s="39" t="n">
         <v>1.980392</v>
       </c>
       <c r="N12" s="28" t="n">
@@ -4322,11 +4349,11 @@
       <c r="X12" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y12" s="25" t="n"/>
+      <c r="Y12" s="38" t="n"/>
       <c r="Z12" s="26" t="n"/>
       <c r="AA12" s="28" t="n"/>
       <c r="AB12" s="28" t="n"/>
-      <c r="AC12" s="30" t="n">
+      <c r="AC12" s="40" t="n">
         <v>-1</v>
       </c>
       <c r="AD12" s="24" t="inlineStr">
@@ -4463,11 +4490,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ12" s="25" t="n"/>
+      <c r="BJ12" s="38" t="n"/>
       <c r="BK12" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="BL12" s="27" t="n">
+      <c r="BL12" s="39" t="n">
         <v>1.980392</v>
       </c>
       <c r="BM12" s="28" t="n">
@@ -4477,18 +4504,18 @@
         <v>0.502488</v>
       </c>
       <c r="BO12" s="28" t="n"/>
-      <c r="BP12" s="25" t="n"/>
-      <c r="BQ12" s="27" t="n"/>
+      <c r="BP12" s="38" t="n"/>
+      <c r="BQ12" s="39" t="n"/>
       <c r="BR12" s="28" t="n"/>
       <c r="BS12" s="28" t="n"/>
       <c r="BT12" s="28" t="n"/>
-      <c r="BU12" s="25" t="n"/>
+      <c r="BU12" s="38" t="n"/>
       <c r="BV12" s="29" t="n"/>
       <c r="BW12" s="24" t="n"/>
-      <c r="BX12" s="30" t="n">
+      <c r="BX12" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY12" s="27" t="n">
+      <c r="BY12" s="39" t="n">
         <v>-1</v>
       </c>
       <c r="BZ12" s="24" t="inlineStr">
@@ -4548,7 +4575,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J13" s="25" t="n"/>
+      <c r="J13" s="38" t="n"/>
       <c r="K13" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -4557,7 +4584,7 @@
       <c r="L13" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="M13" s="27" t="n">
+      <c r="M13" s="39" t="n">
         <v>1.980392</v>
       </c>
       <c r="N13" s="28" t="n">
@@ -4597,11 +4624,11 @@
       <c r="X13" s="26" t="n">
         <v>7</v>
       </c>
-      <c r="Y13" s="25" t="n"/>
+      <c r="Y13" s="38" t="n"/>
       <c r="Z13" s="26" t="n"/>
       <c r="AA13" s="28" t="n"/>
       <c r="AB13" s="28" t="n"/>
-      <c r="AC13" s="30" t="n">
+      <c r="AC13" s="40" t="n">
         <v>1.2255</v>
       </c>
       <c r="AD13" s="24" t="inlineStr">
@@ -4738,11 +4765,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ13" s="25" t="n"/>
+      <c r="BJ13" s="38" t="n"/>
       <c r="BK13" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="BL13" s="27" t="n">
+      <c r="BL13" s="39" t="n">
         <v>1.980392</v>
       </c>
       <c r="BM13" s="28" t="n">
@@ -4752,18 +4779,18 @@
         <v>0.502488</v>
       </c>
       <c r="BO13" s="28" t="n"/>
-      <c r="BP13" s="25" t="n"/>
-      <c r="BQ13" s="27" t="n"/>
+      <c r="BP13" s="38" t="n"/>
+      <c r="BQ13" s="39" t="n"/>
       <c r="BR13" s="28" t="n"/>
       <c r="BS13" s="28" t="n"/>
       <c r="BT13" s="28" t="n"/>
-      <c r="BU13" s="25" t="n"/>
+      <c r="BU13" s="38" t="n"/>
       <c r="BV13" s="29" t="n"/>
       <c r="BW13" s="24" t="n"/>
-      <c r="BX13" s="30" t="n">
+      <c r="BX13" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY13" s="27" t="n">
+      <c r="BY13" s="39" t="n">
         <v>0.980392</v>
       </c>
       <c r="BZ13" s="24" t="inlineStr">
@@ -4823,7 +4850,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J14" s="25" t="n"/>
+      <c r="J14" s="38" t="n"/>
       <c r="K14" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -4832,7 +4859,7 @@
       <c r="L14" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="M14" s="27" t="n">
+      <c r="M14" s="39" t="n">
         <v>1.961538</v>
       </c>
       <c r="N14" s="28" t="n">
@@ -4872,11 +4899,11 @@
       <c r="X14" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="Y14" s="25" t="n"/>
+      <c r="Y14" s="38" t="n"/>
       <c r="Z14" s="26" t="n"/>
       <c r="AA14" s="28" t="n"/>
       <c r="AB14" s="28" t="n"/>
-      <c r="AC14" s="30" t="n">
+      <c r="AC14" s="40" t="n">
         <v>-0.75</v>
       </c>
       <c r="AD14" s="24" t="inlineStr">
@@ -5013,11 +5040,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ14" s="25" t="n"/>
+      <c r="BJ14" s="38" t="n"/>
       <c r="BK14" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="BL14" s="27" t="n">
+      <c r="BL14" s="39" t="n">
         <v>1.961538</v>
       </c>
       <c r="BM14" s="28" t="n">
@@ -5027,18 +5054,18 @@
         <v>0.507463</v>
       </c>
       <c r="BO14" s="28" t="n"/>
-      <c r="BP14" s="25" t="n"/>
-      <c r="BQ14" s="27" t="n"/>
+      <c r="BP14" s="38" t="n"/>
+      <c r="BQ14" s="39" t="n"/>
       <c r="BR14" s="28" t="n"/>
       <c r="BS14" s="28" t="n"/>
       <c r="BT14" s="28" t="n"/>
-      <c r="BU14" s="25" t="n"/>
+      <c r="BU14" s="38" t="n"/>
       <c r="BV14" s="29" t="n"/>
       <c r="BW14" s="24" t="n"/>
-      <c r="BX14" s="30" t="n">
+      <c r="BX14" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY14" s="27" t="n">
+      <c r="BY14" s="39" t="n">
         <v>-1</v>
       </c>
       <c r="BZ14" s="24" t="inlineStr">
@@ -5098,7 +5125,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J15" s="25" t="n"/>
+      <c r="J15" s="38" t="n"/>
       <c r="K15" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -5107,7 +5134,7 @@
       <c r="L15" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="M15" s="27" t="n">
+      <c r="M15" s="39" t="n">
         <v>1.961538</v>
       </c>
       <c r="N15" s="28" t="n">
@@ -5147,11 +5174,11 @@
       <c r="X15" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="Y15" s="25" t="n"/>
+      <c r="Y15" s="38" t="n"/>
       <c r="Z15" s="26" t="n"/>
       <c r="AA15" s="28" t="n"/>
       <c r="AB15" s="28" t="n"/>
-      <c r="AC15" s="30" t="n">
+      <c r="AC15" s="40" t="n">
         <v>-1</v>
       </c>
       <c r="AD15" s="24" t="inlineStr">
@@ -5288,11 +5315,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ15" s="25" t="n"/>
+      <c r="BJ15" s="38" t="n"/>
       <c r="BK15" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="BL15" s="27" t="n">
+      <c r="BL15" s="39" t="n">
         <v>1.961538</v>
       </c>
       <c r="BM15" s="28" t="n">
@@ -5302,18 +5329,18 @@
         <v>0.507463</v>
       </c>
       <c r="BO15" s="28" t="n"/>
-      <c r="BP15" s="25" t="n"/>
-      <c r="BQ15" s="27" t="n"/>
+      <c r="BP15" s="38" t="n"/>
+      <c r="BQ15" s="39" t="n"/>
       <c r="BR15" s="28" t="n"/>
       <c r="BS15" s="28" t="n"/>
       <c r="BT15" s="28" t="n"/>
-      <c r="BU15" s="25" t="n"/>
+      <c r="BU15" s="38" t="n"/>
       <c r="BV15" s="29" t="n"/>
       <c r="BW15" s="24" t="n"/>
-      <c r="BX15" s="30" t="n">
+      <c r="BX15" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY15" s="27" t="n">
+      <c r="BY15" s="39" t="n">
         <v>-1</v>
       </c>
       <c r="BZ15" s="24" t="inlineStr">
@@ -5373,7 +5400,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J16" s="25" t="n"/>
+      <c r="J16" s="38" t="n"/>
       <c r="K16" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -5382,7 +5409,7 @@
       <c r="L16" s="26" t="n">
         <v>-111</v>
       </c>
-      <c r="M16" s="27" t="n">
+      <c r="M16" s="39" t="n">
         <v>1.900901</v>
       </c>
       <c r="N16" s="28" t="n">
@@ -5422,11 +5449,11 @@
       <c r="X16" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="Y16" s="25" t="n"/>
+      <c r="Y16" s="38" t="n"/>
       <c r="Z16" s="26" t="n"/>
       <c r="AA16" s="28" t="n"/>
       <c r="AB16" s="28" t="n"/>
-      <c r="AC16" s="30" t="n">
+      <c r="AC16" s="40" t="n">
         <v>-1.5</v>
       </c>
       <c r="AD16" s="24" t="inlineStr">
@@ -5563,11 +5590,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ16" s="25" t="n"/>
+      <c r="BJ16" s="38" t="n"/>
       <c r="BK16" s="26" t="n">
         <v>-111</v>
       </c>
-      <c r="BL16" s="27" t="n">
+      <c r="BL16" s="39" t="n">
         <v>1.900901</v>
       </c>
       <c r="BM16" s="28" t="n">
@@ -5577,18 +5604,18 @@
         <v>0.522388</v>
       </c>
       <c r="BO16" s="28" t="n"/>
-      <c r="BP16" s="25" t="n"/>
-      <c r="BQ16" s="27" t="n"/>
+      <c r="BP16" s="38" t="n"/>
+      <c r="BQ16" s="39" t="n"/>
       <c r="BR16" s="28" t="n"/>
       <c r="BS16" s="28" t="n"/>
       <c r="BT16" s="28" t="n"/>
-      <c r="BU16" s="25" t="n"/>
+      <c r="BU16" s="38" t="n"/>
       <c r="BV16" s="29" t="n"/>
       <c r="BW16" s="24" t="n"/>
-      <c r="BX16" s="30" t="n">
+      <c r="BX16" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY16" s="27" t="n">
+      <c r="BY16" s="39" t="n">
         <v>-1</v>
       </c>
       <c r="BZ16" s="24" t="inlineStr">
@@ -5648,7 +5675,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J17" s="25" t="n"/>
+      <c r="J17" s="38" t="n"/>
       <c r="K17" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -5657,7 +5684,7 @@
       <c r="L17" s="26" t="n">
         <v>-108</v>
       </c>
-      <c r="M17" s="27" t="n">
+      <c r="M17" s="39" t="n">
         <v>1.925926</v>
       </c>
       <c r="N17" s="28" t="n">
@@ -5697,11 +5724,11 @@
       <c r="X17" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="Y17" s="25" t="n"/>
+      <c r="Y17" s="38" t="n"/>
       <c r="Z17" s="26" t="n"/>
       <c r="AA17" s="28" t="n"/>
       <c r="AB17" s="28" t="n"/>
-      <c r="AC17" s="30" t="n">
+      <c r="AC17" s="40" t="n">
         <v>0.9258999999999999</v>
       </c>
       <c r="AD17" s="24" t="inlineStr">
@@ -5838,11 +5865,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ17" s="25" t="n"/>
+      <c r="BJ17" s="38" t="n"/>
       <c r="BK17" s="26" t="n">
         <v>-108</v>
       </c>
-      <c r="BL17" s="27" t="n">
+      <c r="BL17" s="39" t="n">
         <v>1.925926</v>
       </c>
       <c r="BM17" s="28" t="n">
@@ -5852,18 +5879,18 @@
         <v>0.5148509999999999</v>
       </c>
       <c r="BO17" s="28" t="n"/>
-      <c r="BP17" s="25" t="n"/>
-      <c r="BQ17" s="27" t="n"/>
+      <c r="BP17" s="38" t="n"/>
+      <c r="BQ17" s="39" t="n"/>
       <c r="BR17" s="28" t="n"/>
       <c r="BS17" s="28" t="n"/>
       <c r="BT17" s="28" t="n"/>
-      <c r="BU17" s="25" t="n"/>
+      <c r="BU17" s="38" t="n"/>
       <c r="BV17" s="29" t="n"/>
       <c r="BW17" s="24" t="n"/>
-      <c r="BX17" s="30" t="n">
+      <c r="BX17" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY17" s="27" t="n">
+      <c r="BY17" s="39" t="n">
         <v>0.925926</v>
       </c>
       <c r="BZ17" s="24" t="inlineStr">
@@ -5923,7 +5950,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J18" s="25" t="n"/>
+      <c r="J18" s="38" t="n"/>
       <c r="K18" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -5932,7 +5959,7 @@
       <c r="L18" s="26" t="n">
         <v>111</v>
       </c>
-      <c r="M18" s="27" t="n">
+      <c r="M18" s="39" t="n">
         <v>2.11</v>
       </c>
       <c r="N18" s="28" t="n">
@@ -5972,11 +5999,11 @@
       <c r="X18" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="Y18" s="25" t="n"/>
+      <c r="Y18" s="38" t="n"/>
       <c r="Z18" s="26" t="n"/>
       <c r="AA18" s="28" t="n"/>
       <c r="AB18" s="28" t="n"/>
-      <c r="AC18" s="30" t="n">
+      <c r="AC18" s="40" t="n">
         <v>-1.25</v>
       </c>
       <c r="AD18" s="24" t="inlineStr">
@@ -6113,11 +6140,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ18" s="25" t="n"/>
+      <c r="BJ18" s="38" t="n"/>
       <c r="BK18" s="26" t="n">
         <v>111</v>
       </c>
-      <c r="BL18" s="27" t="n">
+      <c r="BL18" s="39" t="n">
         <v>2.11</v>
       </c>
       <c r="BM18" s="28" t="n">
@@ -6127,18 +6154,18 @@
         <v>0.472637</v>
       </c>
       <c r="BO18" s="28" t="n"/>
-      <c r="BP18" s="25" t="n"/>
-      <c r="BQ18" s="27" t="n"/>
+      <c r="BP18" s="38" t="n"/>
+      <c r="BQ18" s="39" t="n"/>
       <c r="BR18" s="28" t="n"/>
       <c r="BS18" s="28" t="n"/>
       <c r="BT18" s="28" t="n"/>
-      <c r="BU18" s="25" t="n"/>
+      <c r="BU18" s="38" t="n"/>
       <c r="BV18" s="29" t="n"/>
       <c r="BW18" s="24" t="n"/>
-      <c r="BX18" s="30" t="n">
+      <c r="BX18" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY18" s="27" t="n">
+      <c r="BY18" s="39" t="n">
         <v>-1</v>
       </c>
       <c r="BZ18" s="24" t="inlineStr">
@@ -6198,7 +6225,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J19" s="25" t="n"/>
+      <c r="J19" s="38" t="n"/>
       <c r="K19" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -6207,7 +6234,7 @@
       <c r="L19" s="26" t="n">
         <v>-125</v>
       </c>
-      <c r="M19" s="27" t="n">
+      <c r="M19" s="39" t="n">
         <v>1.8</v>
       </c>
       <c r="N19" s="28" t="n">
@@ -6247,11 +6274,11 @@
       <c r="X19" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="Y19" s="25" t="n"/>
+      <c r="Y19" s="38" t="n"/>
       <c r="Z19" s="26" t="n"/>
       <c r="AA19" s="28" t="n"/>
       <c r="AB19" s="28" t="n"/>
-      <c r="AC19" s="30" t="n">
+      <c r="AC19" s="40" t="n">
         <v>1.2</v>
       </c>
       <c r="AD19" s="24" t="inlineStr">
@@ -6388,11 +6415,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ19" s="25" t="n"/>
+      <c r="BJ19" s="38" t="n"/>
       <c r="BK19" s="26" t="n">
         <v>-125</v>
       </c>
-      <c r="BL19" s="27" t="n">
+      <c r="BL19" s="39" t="n">
         <v>1.8</v>
       </c>
       <c r="BM19" s="28" t="n">
@@ -6402,18 +6429,18 @@
         <v>0.552239</v>
       </c>
       <c r="BO19" s="28" t="n"/>
-      <c r="BP19" s="25" t="n"/>
-      <c r="BQ19" s="27" t="n"/>
+      <c r="BP19" s="38" t="n"/>
+      <c r="BQ19" s="39" t="n"/>
       <c r="BR19" s="28" t="n"/>
       <c r="BS19" s="28" t="n"/>
       <c r="BT19" s="28" t="n"/>
-      <c r="BU19" s="25" t="n"/>
+      <c r="BU19" s="38" t="n"/>
       <c r="BV19" s="29" t="n"/>
       <c r="BW19" s="24" t="n"/>
-      <c r="BX19" s="30" t="n">
+      <c r="BX19" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY19" s="27" t="n">
+      <c r="BY19" s="39" t="n">
         <v>0.8</v>
       </c>
       <c r="BZ19" s="24" t="inlineStr">
@@ -6473,7 +6500,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J20" s="25" t="n"/>
+      <c r="J20" s="38" t="n"/>
       <c r="K20" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -6482,7 +6509,7 @@
       <c r="L20" s="26" t="n">
         <v>106</v>
       </c>
-      <c r="M20" s="27" t="n">
+      <c r="M20" s="39" t="n">
         <v>2.06</v>
       </c>
       <c r="N20" s="28" t="n">
@@ -6522,11 +6549,11 @@
       <c r="X20" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y20" s="25" t="n"/>
+      <c r="Y20" s="38" t="n"/>
       <c r="Z20" s="26" t="n"/>
       <c r="AA20" s="28" t="n"/>
       <c r="AB20" s="28" t="n"/>
-      <c r="AC20" s="30" t="n">
+      <c r="AC20" s="40" t="n">
         <v>0.795</v>
       </c>
       <c r="AD20" s="24" t="inlineStr">
@@ -6663,11 +6690,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ20" s="25" t="n"/>
+      <c r="BJ20" s="38" t="n"/>
       <c r="BK20" s="26" t="n">
         <v>106</v>
       </c>
-      <c r="BL20" s="27" t="n">
+      <c r="BL20" s="39" t="n">
         <v>2.06</v>
       </c>
       <c r="BM20" s="28" t="n">
@@ -6677,18 +6704,18 @@
         <v>0.482587</v>
       </c>
       <c r="BO20" s="28" t="n"/>
-      <c r="BP20" s="25" t="n"/>
-      <c r="BQ20" s="27" t="n"/>
+      <c r="BP20" s="38" t="n"/>
+      <c r="BQ20" s="39" t="n"/>
       <c r="BR20" s="28" t="n"/>
       <c r="BS20" s="28" t="n"/>
       <c r="BT20" s="28" t="n"/>
-      <c r="BU20" s="25" t="n"/>
+      <c r="BU20" s="38" t="n"/>
       <c r="BV20" s="29" t="n"/>
       <c r="BW20" s="24" t="n"/>
-      <c r="BX20" s="30" t="n">
+      <c r="BX20" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY20" s="27" t="n">
+      <c r="BY20" s="39" t="n">
         <v>1.06</v>
       </c>
       <c r="BZ20" s="24" t="inlineStr">
@@ -6748,7 +6775,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J21" s="25" t="n"/>
+      <c r="J21" s="38" t="n"/>
       <c r="K21" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -6757,7 +6784,7 @@
       <c r="L21" s="26" t="n">
         <v>-106</v>
       </c>
-      <c r="M21" s="27" t="n">
+      <c r="M21" s="39" t="n">
         <v>1.943396</v>
       </c>
       <c r="N21" s="28" t="n">
@@ -6799,11 +6826,11 @@
       <c r="X21" s="26" t="n">
         <v>10</v>
       </c>
-      <c r="Y21" s="25" t="n"/>
+      <c r="Y21" s="38" t="n"/>
       <c r="Z21" s="26" t="n"/>
       <c r="AA21" s="28" t="n"/>
       <c r="AB21" s="28" t="n"/>
-      <c r="AC21" s="30" t="n">
+      <c r="AC21" s="40" t="n">
         <v>0.9434</v>
       </c>
       <c r="AD21" s="24" t="inlineStr">
@@ -6862,11 +6889,11 @@
         </is>
       </c>
       <c r="BI21" s="24" t="n"/>
-      <c r="BJ21" s="25" t="n"/>
+      <c r="BJ21" s="38" t="n"/>
       <c r="BK21" s="26" t="n">
         <v>-106</v>
       </c>
-      <c r="BL21" s="27" t="n">
+      <c r="BL21" s="39" t="n">
         <v>1.943396</v>
       </c>
       <c r="BM21" s="28" t="n">
@@ -6876,16 +6903,16 @@
         <v>0.5124379999999999</v>
       </c>
       <c r="BO21" s="28" t="n"/>
-      <c r="BP21" s="25" t="n"/>
-      <c r="BQ21" s="27" t="n"/>
+      <c r="BP21" s="38" t="n"/>
+      <c r="BQ21" s="39" t="n"/>
       <c r="BR21" s="28" t="n"/>
       <c r="BS21" s="28" t="n"/>
       <c r="BT21" s="28" t="n"/>
-      <c r="BU21" s="25" t="n"/>
+      <c r="BU21" s="38" t="n"/>
       <c r="BV21" s="29" t="n"/>
       <c r="BW21" s="24" t="n"/>
-      <c r="BX21" s="30" t="n"/>
-      <c r="BY21" s="27" t="n"/>
+      <c r="BX21" s="40" t="n"/>
+      <c r="BY21" s="39" t="n"/>
       <c r="BZ21" s="24" t="n"/>
       <c r="CA21" s="31" t="n"/>
     </row>
@@ -6935,7 +6962,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J22" s="25" t="n"/>
+      <c r="J22" s="38" t="n"/>
       <c r="K22" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -6944,7 +6971,7 @@
       <c r="L22" s="26" t="n">
         <v>-106</v>
       </c>
-      <c r="M22" s="27" t="n">
+      <c r="M22" s="39" t="n">
         <v>1.943396</v>
       </c>
       <c r="N22" s="28" t="n">
@@ -6986,11 +7013,11 @@
       <c r="X22" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="Y22" s="25" t="n"/>
+      <c r="Y22" s="38" t="n"/>
       <c r="Z22" s="26" t="n"/>
       <c r="AA22" s="28" t="n"/>
       <c r="AB22" s="28" t="n"/>
-      <c r="AC22" s="30" t="n">
+      <c r="AC22" s="40" t="n">
         <v>0.9434</v>
       </c>
       <c r="AD22" s="24" t="inlineStr">
@@ -7049,11 +7076,11 @@
         </is>
       </c>
       <c r="BI22" s="24" t="n"/>
-      <c r="BJ22" s="25" t="n"/>
+      <c r="BJ22" s="38" t="n"/>
       <c r="BK22" s="26" t="n">
         <v>-106</v>
       </c>
-      <c r="BL22" s="27" t="n">
+      <c r="BL22" s="39" t="n">
         <v>1.943396</v>
       </c>
       <c r="BM22" s="28" t="n">
@@ -7063,16 +7090,16 @@
         <v>0.5124379999999999</v>
       </c>
       <c r="BO22" s="28" t="n"/>
-      <c r="BP22" s="25" t="n"/>
-      <c r="BQ22" s="27" t="n"/>
+      <c r="BP22" s="38" t="n"/>
+      <c r="BQ22" s="39" t="n"/>
       <c r="BR22" s="28" t="n"/>
       <c r="BS22" s="28" t="n"/>
       <c r="BT22" s="28" t="n"/>
-      <c r="BU22" s="25" t="n"/>
+      <c r="BU22" s="38" t="n"/>
       <c r="BV22" s="29" t="n"/>
       <c r="BW22" s="24" t="n"/>
-      <c r="BX22" s="30" t="n"/>
-      <c r="BY22" s="27" t="n"/>
+      <c r="BX22" s="40" t="n"/>
+      <c r="BY22" s="39" t="n"/>
       <c r="BZ22" s="24" t="n"/>
       <c r="CA22" s="31" t="n"/>
     </row>
@@ -7122,7 +7149,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J23" s="25" t="n"/>
+      <c r="J23" s="38" t="n"/>
       <c r="K23" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -7131,7 +7158,7 @@
       <c r="L23" s="26" t="n">
         <v>-141</v>
       </c>
-      <c r="M23" s="27" t="n">
+      <c r="M23" s="39" t="n">
         <v>1.70922</v>
       </c>
       <c r="N23" s="28" t="n">
@@ -7173,11 +7200,11 @@
       <c r="X23" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y23" s="25" t="n"/>
+      <c r="Y23" s="38" t="n"/>
       <c r="Z23" s="26" t="n"/>
       <c r="AA23" s="28" t="n"/>
       <c r="AB23" s="28" t="n"/>
-      <c r="AC23" s="30" t="n">
+      <c r="AC23" s="40" t="n">
         <v>1.2411</v>
       </c>
       <c r="AD23" s="24" t="inlineStr">
@@ -7236,11 +7263,11 @@
         </is>
       </c>
       <c r="BI23" s="24" t="n"/>
-      <c r="BJ23" s="25" t="n"/>
+      <c r="BJ23" s="38" t="n"/>
       <c r="BK23" s="26" t="n">
         <v>-141</v>
       </c>
-      <c r="BL23" s="27" t="n">
+      <c r="BL23" s="39" t="n">
         <v>1.70922</v>
       </c>
       <c r="BM23" s="28" t="n">
@@ -7250,16 +7277,16 @@
         <v>0.58209</v>
       </c>
       <c r="BO23" s="28" t="n"/>
-      <c r="BP23" s="25" t="n"/>
-      <c r="BQ23" s="27" t="n"/>
+      <c r="BP23" s="38" t="n"/>
+      <c r="BQ23" s="39" t="n"/>
       <c r="BR23" s="28" t="n"/>
       <c r="BS23" s="28" t="n"/>
       <c r="BT23" s="28" t="n"/>
-      <c r="BU23" s="25" t="n"/>
+      <c r="BU23" s="38" t="n"/>
       <c r="BV23" s="29" t="n"/>
       <c r="BW23" s="24" t="n"/>
-      <c r="BX23" s="30" t="n"/>
-      <c r="BY23" s="27" t="n"/>
+      <c r="BX23" s="40" t="n"/>
+      <c r="BY23" s="39" t="n"/>
       <c r="BZ23" s="24" t="n"/>
       <c r="CA23" s="31" t="n"/>
     </row>
@@ -7309,7 +7336,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J24" s="25" t="n"/>
+      <c r="J24" s="38" t="n"/>
       <c r="K24" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -7318,7 +7345,7 @@
       <c r="L24" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="M24" s="27" t="n">
+      <c r="M24" s="39" t="n">
         <v>1.75188</v>
       </c>
       <c r="N24" s="28" t="n">
@@ -7360,11 +7387,11 @@
       <c r="X24" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y24" s="25" t="n"/>
+      <c r="Y24" s="38" t="n"/>
       <c r="Z24" s="26" t="n"/>
       <c r="AA24" s="28" t="n"/>
       <c r="AB24" s="28" t="n"/>
-      <c r="AC24" s="30" t="n">
+      <c r="AC24" s="40" t="n">
         <v>-1.5</v>
       </c>
       <c r="AD24" s="24" t="inlineStr">
@@ -7423,11 +7450,11 @@
         </is>
       </c>
       <c r="BI24" s="24" t="n"/>
-      <c r="BJ24" s="25" t="n"/>
+      <c r="BJ24" s="38" t="n"/>
       <c r="BK24" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="BL24" s="27" t="n">
+      <c r="BL24" s="39" t="n">
         <v>1.75188</v>
       </c>
       <c r="BM24" s="28" t="n">
@@ -7437,16 +7464,16 @@
         <v>0.567164</v>
       </c>
       <c r="BO24" s="28" t="n"/>
-      <c r="BP24" s="25" t="n"/>
-      <c r="BQ24" s="27" t="n"/>
+      <c r="BP24" s="38" t="n"/>
+      <c r="BQ24" s="39" t="n"/>
       <c r="BR24" s="28" t="n"/>
       <c r="BS24" s="28" t="n"/>
       <c r="BT24" s="28" t="n"/>
-      <c r="BU24" s="25" t="n"/>
+      <c r="BU24" s="38" t="n"/>
       <c r="BV24" s="29" t="n"/>
       <c r="BW24" s="24" t="n"/>
-      <c r="BX24" s="30" t="n"/>
-      <c r="BY24" s="27" t="n"/>
+      <c r="BX24" s="40" t="n"/>
+      <c r="BY24" s="39" t="n"/>
       <c r="BZ24" s="24" t="n"/>
       <c r="CA24" s="31" t="n"/>
     </row>
@@ -7496,7 +7523,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J25" s="25" t="n"/>
+      <c r="J25" s="38" t="n"/>
       <c r="K25" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -7505,7 +7532,7 @@
       <c r="L25" s="26" t="n">
         <v>104</v>
       </c>
-      <c r="M25" s="27" t="n">
+      <c r="M25" s="39" t="n">
         <v>2.04</v>
       </c>
       <c r="N25" s="28" t="n">
@@ -7547,11 +7574,11 @@
       <c r="X25" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y25" s="25" t="n"/>
+      <c r="Y25" s="38" t="n"/>
       <c r="Z25" s="26" t="n"/>
       <c r="AA25" s="28" t="n"/>
       <c r="AB25" s="28" t="n"/>
-      <c r="AC25" s="30" t="n">
+      <c r="AC25" s="40" t="n">
         <v>1.3</v>
       </c>
       <c r="AD25" s="24" t="inlineStr">
@@ -7610,11 +7637,11 @@
         </is>
       </c>
       <c r="BI25" s="24" t="n"/>
-      <c r="BJ25" s="25" t="n"/>
+      <c r="BJ25" s="38" t="n"/>
       <c r="BK25" s="26" t="n">
         <v>104</v>
       </c>
-      <c r="BL25" s="27" t="n">
+      <c r="BL25" s="39" t="n">
         <v>2.04</v>
       </c>
       <c r="BM25" s="28" t="n">
@@ -7624,16 +7651,16 @@
         <v>0.487562</v>
       </c>
       <c r="BO25" s="28" t="n"/>
-      <c r="BP25" s="25" t="n"/>
-      <c r="BQ25" s="27" t="n"/>
+      <c r="BP25" s="38" t="n"/>
+      <c r="BQ25" s="39" t="n"/>
       <c r="BR25" s="28" t="n"/>
       <c r="BS25" s="28" t="n"/>
       <c r="BT25" s="28" t="n"/>
-      <c r="BU25" s="25" t="n"/>
+      <c r="BU25" s="38" t="n"/>
       <c r="BV25" s="29" t="n"/>
       <c r="BW25" s="24" t="n"/>
-      <c r="BX25" s="30" t="n"/>
-      <c r="BY25" s="27" t="n"/>
+      <c r="BX25" s="40" t="n"/>
+      <c r="BY25" s="39" t="n"/>
       <c r="BZ25" s="24" t="n"/>
       <c r="CA25" s="31" t="n"/>
     </row>
@@ -7683,7 +7710,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J26" s="25" t="n"/>
+      <c r="J26" s="38" t="n"/>
       <c r="K26" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -7692,7 +7719,7 @@
       <c r="L26" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="M26" s="27" t="n">
+      <c r="M26" s="39" t="n">
         <v>1.961538</v>
       </c>
       <c r="N26" s="28" t="n">
@@ -7734,11 +7761,11 @@
       <c r="X26" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="Y26" s="25" t="n"/>
+      <c r="Y26" s="38" t="n"/>
       <c r="Z26" s="26" t="n"/>
       <c r="AA26" s="28" t="n"/>
       <c r="AB26" s="28" t="n"/>
-      <c r="AC26" s="30" t="n">
+      <c r="AC26" s="40" t="n">
         <v>0.9615</v>
       </c>
       <c r="AD26" s="24" t="inlineStr">
@@ -7797,11 +7824,11 @@
         </is>
       </c>
       <c r="BI26" s="24" t="n"/>
-      <c r="BJ26" s="25" t="n"/>
+      <c r="BJ26" s="38" t="n"/>
       <c r="BK26" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="BL26" s="27" t="n">
+      <c r="BL26" s="39" t="n">
         <v>1.961538</v>
       </c>
       <c r="BM26" s="28" t="n">
@@ -7811,16 +7838,16 @@
         <v>0.507463</v>
       </c>
       <c r="BO26" s="28" t="n"/>
-      <c r="BP26" s="25" t="n"/>
-      <c r="BQ26" s="27" t="n"/>
+      <c r="BP26" s="38" t="n"/>
+      <c r="BQ26" s="39" t="n"/>
       <c r="BR26" s="28" t="n"/>
       <c r="BS26" s="28" t="n"/>
       <c r="BT26" s="28" t="n"/>
-      <c r="BU26" s="25" t="n"/>
+      <c r="BU26" s="38" t="n"/>
       <c r="BV26" s="29" t="n"/>
       <c r="BW26" s="24" t="n"/>
-      <c r="BX26" s="30" t="n"/>
-      <c r="BY26" s="27" t="n"/>
+      <c r="BX26" s="40" t="n"/>
+      <c r="BY26" s="39" t="n"/>
       <c r="BZ26" s="24" t="n"/>
       <c r="CA26" s="31" t="n"/>
     </row>
@@ -7870,7 +7897,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J27" s="25" t="n"/>
+      <c r="J27" s="38" t="n"/>
       <c r="K27" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -7879,7 +7906,7 @@
       <c r="L27" s="26" t="n">
         <v>120</v>
       </c>
-      <c r="M27" s="27" t="n">
+      <c r="M27" s="39" t="n">
         <v>2.2</v>
       </c>
       <c r="N27" s="28" t="n">
@@ -7921,11 +7948,11 @@
       <c r="X27" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="Y27" s="25" t="n"/>
+      <c r="Y27" s="38" t="n"/>
       <c r="Z27" s="26" t="n"/>
       <c r="AA27" s="28" t="n"/>
       <c r="AB27" s="28" t="n"/>
-      <c r="AC27" s="30" t="n">
+      <c r="AC27" s="40" t="n">
         <v>-0.75</v>
       </c>
       <c r="AD27" s="24" t="inlineStr">
@@ -7984,11 +8011,11 @@
         </is>
       </c>
       <c r="BI27" s="24" t="n"/>
-      <c r="BJ27" s="25" t="n"/>
+      <c r="BJ27" s="38" t="n"/>
       <c r="BK27" s="26" t="n">
         <v>120</v>
       </c>
-      <c r="BL27" s="27" t="n">
+      <c r="BL27" s="39" t="n">
         <v>2.2</v>
       </c>
       <c r="BM27" s="28" t="n">
@@ -7998,16 +8025,16 @@
         <v>0.452736</v>
       </c>
       <c r="BO27" s="28" t="n"/>
-      <c r="BP27" s="25" t="n"/>
-      <c r="BQ27" s="27" t="n"/>
+      <c r="BP27" s="38" t="n"/>
+      <c r="BQ27" s="39" t="n"/>
       <c r="BR27" s="28" t="n"/>
       <c r="BS27" s="28" t="n"/>
       <c r="BT27" s="28" t="n"/>
-      <c r="BU27" s="25" t="n"/>
+      <c r="BU27" s="38" t="n"/>
       <c r="BV27" s="29" t="n"/>
       <c r="BW27" s="24" t="n"/>
-      <c r="BX27" s="30" t="n"/>
-      <c r="BY27" s="27" t="n"/>
+      <c r="BX27" s="40" t="n"/>
+      <c r="BY27" s="39" t="n"/>
       <c r="BZ27" s="24" t="n"/>
       <c r="CA27" s="31" t="n"/>
     </row>
@@ -8057,7 +8084,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J28" s="25" t="n"/>
+      <c r="J28" s="38" t="n"/>
       <c r="K28" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -8066,7 +8093,7 @@
       <c r="L28" s="26" t="n">
         <v>100</v>
       </c>
-      <c r="M28" s="27" t="n">
+      <c r="M28" s="39" t="n">
         <v>2</v>
       </c>
       <c r="N28" s="28" t="n">
@@ -8108,11 +8135,11 @@
       <c r="X28" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="Y28" s="25" t="n"/>
+      <c r="Y28" s="38" t="n"/>
       <c r="Z28" s="26" t="n"/>
       <c r="AA28" s="28" t="n"/>
       <c r="AB28" s="28" t="n"/>
-      <c r="AC28" s="30" t="n">
+      <c r="AC28" s="40" t="n">
         <v>-0.75</v>
       </c>
       <c r="AD28" s="24" t="inlineStr">
@@ -8171,11 +8198,11 @@
         </is>
       </c>
       <c r="BI28" s="24" t="n"/>
-      <c r="BJ28" s="25" t="n"/>
+      <c r="BJ28" s="38" t="n"/>
       <c r="BK28" s="26" t="n">
         <v>100</v>
       </c>
-      <c r="BL28" s="27" t="n">
+      <c r="BL28" s="39" t="n">
         <v>2</v>
       </c>
       <c r="BM28" s="28" t="n">
@@ -8185,16 +8212,16 @@
         <v>0.497512</v>
       </c>
       <c r="BO28" s="28" t="n"/>
-      <c r="BP28" s="25" t="n"/>
-      <c r="BQ28" s="27" t="n"/>
+      <c r="BP28" s="38" t="n"/>
+      <c r="BQ28" s="39" t="n"/>
       <c r="BR28" s="28" t="n"/>
       <c r="BS28" s="28" t="n"/>
       <c r="BT28" s="28" t="n"/>
-      <c r="BU28" s="25" t="n"/>
+      <c r="BU28" s="38" t="n"/>
       <c r="BV28" s="29" t="n"/>
       <c r="BW28" s="24" t="n"/>
-      <c r="BX28" s="30" t="n"/>
-      <c r="BY28" s="27" t="n"/>
+      <c r="BX28" s="40" t="n"/>
+      <c r="BY28" s="39" t="n"/>
       <c r="BZ28" s="24" t="n"/>
       <c r="CA28" s="31" t="n"/>
     </row>
@@ -8244,7 +8271,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J29" s="25" t="n"/>
+      <c r="J29" s="38" t="n"/>
       <c r="K29" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -8253,7 +8280,7 @@
       <c r="L29" s="26" t="n">
         <v>108</v>
       </c>
-      <c r="M29" s="27" t="n">
+      <c r="M29" s="39" t="n">
         <v>2.08</v>
       </c>
       <c r="N29" s="28" t="n">
@@ -8293,11 +8320,11 @@
       <c r="X29" s="26" t="n">
         <v>8</v>
       </c>
-      <c r="Y29" s="25" t="n"/>
+      <c r="Y29" s="38" t="n"/>
       <c r="Z29" s="26" t="n"/>
       <c r="AA29" s="28" t="n"/>
       <c r="AB29" s="28" t="n"/>
-      <c r="AC29" s="30" t="n">
+      <c r="AC29" s="40" t="n">
         <v>1.35</v>
       </c>
       <c r="AD29" s="24" t="inlineStr">
@@ -8434,11 +8461,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ29" s="25" t="n"/>
+      <c r="BJ29" s="38" t="n"/>
       <c r="BK29" s="26" t="n">
         <v>108</v>
       </c>
-      <c r="BL29" s="27" t="n">
+      <c r="BL29" s="39" t="n">
         <v>2.08</v>
       </c>
       <c r="BM29" s="28" t="n">
@@ -8448,18 +8475,18 @@
         <v>0.477612</v>
       </c>
       <c r="BO29" s="28" t="n"/>
-      <c r="BP29" s="25" t="n"/>
-      <c r="BQ29" s="27" t="n"/>
+      <c r="BP29" s="38" t="n"/>
+      <c r="BQ29" s="39" t="n"/>
       <c r="BR29" s="28" t="n"/>
       <c r="BS29" s="28" t="n"/>
       <c r="BT29" s="28" t="n"/>
-      <c r="BU29" s="25" t="n"/>
+      <c r="BU29" s="38" t="n"/>
       <c r="BV29" s="29" t="n"/>
       <c r="BW29" s="24" t="n"/>
-      <c r="BX29" s="30" t="n">
+      <c r="BX29" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY29" s="27" t="n">
+      <c r="BY29" s="39" t="n">
         <v>1.08</v>
       </c>
       <c r="BZ29" s="24" t="inlineStr">
@@ -8519,7 +8546,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J30" s="25" t="n"/>
+      <c r="J30" s="38" t="n"/>
       <c r="K30" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -8528,7 +8555,7 @@
       <c r="L30" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="M30" s="27" t="n">
+      <c r="M30" s="39" t="n">
         <v>1.75188</v>
       </c>
       <c r="N30" s="28" t="n">
@@ -8568,11 +8595,11 @@
       <c r="X30" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="Y30" s="25" t="n"/>
+      <c r="Y30" s="38" t="n"/>
       <c r="Z30" s="26" t="n"/>
       <c r="AA30" s="28" t="n"/>
       <c r="AB30" s="28" t="n"/>
-      <c r="AC30" s="30" t="n">
+      <c r="AC30" s="40" t="n">
         <v>1.1278</v>
       </c>
       <c r="AD30" s="24" t="inlineStr">
@@ -8709,11 +8736,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ30" s="25" t="n"/>
+      <c r="BJ30" s="38" t="n"/>
       <c r="BK30" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="BL30" s="27" t="n">
+      <c r="BL30" s="39" t="n">
         <v>1.75188</v>
       </c>
       <c r="BM30" s="28" t="n">
@@ -8723,18 +8750,18 @@
         <v>0.567164</v>
       </c>
       <c r="BO30" s="28" t="n"/>
-      <c r="BP30" s="25" t="n"/>
-      <c r="BQ30" s="27" t="n"/>
+      <c r="BP30" s="38" t="n"/>
+      <c r="BQ30" s="39" t="n"/>
       <c r="BR30" s="28" t="n"/>
       <c r="BS30" s="28" t="n"/>
       <c r="BT30" s="28" t="n"/>
-      <c r="BU30" s="25" t="n"/>
+      <c r="BU30" s="38" t="n"/>
       <c r="BV30" s="29" t="n"/>
       <c r="BW30" s="24" t="n"/>
-      <c r="BX30" s="30" t="n">
+      <c r="BX30" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY30" s="27" t="n">
+      <c r="BY30" s="39" t="n">
         <v>0.75188</v>
       </c>
       <c r="BZ30" s="24" t="inlineStr">
@@ -8794,7 +8821,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J31" s="25" t="n"/>
+      <c r="J31" s="38" t="n"/>
       <c r="K31" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -8803,7 +8830,7 @@
       <c r="L31" s="26" t="n">
         <v>130</v>
       </c>
-      <c r="M31" s="27" t="n">
+      <c r="M31" s="39" t="n">
         <v>2.3</v>
       </c>
       <c r="N31" s="28" t="n">
@@ -8843,11 +8870,11 @@
       <c r="X31" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y31" s="25" t="n"/>
+      <c r="Y31" s="38" t="n"/>
       <c r="Z31" s="26" t="n"/>
       <c r="AA31" s="28" t="n"/>
       <c r="AB31" s="28" t="n"/>
-      <c r="AC31" s="30" t="n">
+      <c r="AC31" s="40" t="n">
         <v>-1</v>
       </c>
       <c r="AD31" s="24" t="inlineStr">
@@ -8984,11 +9011,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ31" s="25" t="n"/>
+      <c r="BJ31" s="38" t="n"/>
       <c r="BK31" s="26" t="n">
         <v>130</v>
       </c>
-      <c r="BL31" s="27" t="n">
+      <c r="BL31" s="39" t="n">
         <v>2.3</v>
       </c>
       <c r="BM31" s="28" t="n">
@@ -8998,18 +9025,18 @@
         <v>0.432836</v>
       </c>
       <c r="BO31" s="28" t="n"/>
-      <c r="BP31" s="25" t="n"/>
-      <c r="BQ31" s="27" t="n"/>
+      <c r="BP31" s="38" t="n"/>
+      <c r="BQ31" s="39" t="n"/>
       <c r="BR31" s="28" t="n"/>
       <c r="BS31" s="28" t="n"/>
       <c r="BT31" s="28" t="n"/>
-      <c r="BU31" s="25" t="n"/>
+      <c r="BU31" s="38" t="n"/>
       <c r="BV31" s="29" t="n"/>
       <c r="BW31" s="24" t="n"/>
-      <c r="BX31" s="30" t="n">
+      <c r="BX31" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY31" s="27" t="n">
+      <c r="BY31" s="39" t="n">
         <v>-1</v>
       </c>
       <c r="BZ31" s="24" t="inlineStr">
@@ -9069,7 +9096,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J32" s="25" t="n"/>
+      <c r="J32" s="38" t="n"/>
       <c r="K32" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -9078,7 +9105,7 @@
       <c r="L32" s="26" t="n">
         <v>113</v>
       </c>
-      <c r="M32" s="27" t="n">
+      <c r="M32" s="39" t="n">
         <v>2.13</v>
       </c>
       <c r="N32" s="28" t="n">
@@ -9110,11 +9137,11 @@
       <c r="V32" s="24" t="n"/>
       <c r="W32" s="26" t="n"/>
       <c r="X32" s="26" t="n"/>
-      <c r="Y32" s="25" t="n"/>
+      <c r="Y32" s="38" t="n"/>
       <c r="Z32" s="26" t="n"/>
       <c r="AA32" s="28" t="n"/>
       <c r="AB32" s="28" t="n"/>
-      <c r="AC32" s="30" t="n"/>
+      <c r="AC32" s="40" t="n"/>
       <c r="AD32" s="24" t="n"/>
       <c r="AE32" s="31" t="inlineStr">
         <is>
@@ -9245,11 +9272,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ32" s="25" t="n"/>
+      <c r="BJ32" s="38" t="n"/>
       <c r="BK32" s="26" t="n">
         <v>113</v>
       </c>
-      <c r="BL32" s="27" t="n">
+      <c r="BL32" s="39" t="n">
         <v>2.13</v>
       </c>
       <c r="BM32" s="28" t="n">
@@ -9259,16 +9286,16 @@
         <v>0.467662</v>
       </c>
       <c r="BO32" s="28" t="n"/>
-      <c r="BP32" s="25" t="n"/>
-      <c r="BQ32" s="27" t="n"/>
+      <c r="BP32" s="38" t="n"/>
+      <c r="BQ32" s="39" t="n"/>
       <c r="BR32" s="28" t="n"/>
       <c r="BS32" s="28" t="n"/>
       <c r="BT32" s="28" t="n"/>
-      <c r="BU32" s="25" t="n"/>
+      <c r="BU32" s="38" t="n"/>
       <c r="BV32" s="29" t="n"/>
       <c r="BW32" s="24" t="n"/>
-      <c r="BX32" s="30" t="n"/>
-      <c r="BY32" s="27" t="n"/>
+      <c r="BX32" s="40" t="n"/>
+      <c r="BY32" s="39" t="n"/>
       <c r="BZ32" s="24" t="n"/>
       <c r="CA32" s="31" t="n"/>
     </row>
@@ -9318,7 +9345,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J33" s="25" t="n"/>
+      <c r="J33" s="38" t="n"/>
       <c r="K33" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -9327,7 +9354,7 @@
       <c r="L33" s="26" t="n">
         <v>-108</v>
       </c>
-      <c r="M33" s="27" t="n">
+      <c r="M33" s="39" t="n">
         <v>1.925926</v>
       </c>
       <c r="N33" s="28" t="n">
@@ -9359,11 +9386,11 @@
       <c r="V33" s="24" t="n"/>
       <c r="W33" s="26" t="n"/>
       <c r="X33" s="26" t="n"/>
-      <c r="Y33" s="25" t="n"/>
+      <c r="Y33" s="38" t="n"/>
       <c r="Z33" s="26" t="n"/>
       <c r="AA33" s="28" t="n"/>
       <c r="AB33" s="28" t="n"/>
-      <c r="AC33" s="30" t="n"/>
+      <c r="AC33" s="40" t="n"/>
       <c r="AD33" s="24" t="n"/>
       <c r="AE33" s="31" t="inlineStr">
         <is>
@@ -9494,11 +9521,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ33" s="25" t="n"/>
+      <c r="BJ33" s="38" t="n"/>
       <c r="BK33" s="26" t="n">
         <v>-108</v>
       </c>
-      <c r="BL33" s="27" t="n">
+      <c r="BL33" s="39" t="n">
         <v>1.925926</v>
       </c>
       <c r="BM33" s="28" t="n">
@@ -9508,16 +9535,16 @@
         <v>0.517413</v>
       </c>
       <c r="BO33" s="28" t="n"/>
-      <c r="BP33" s="25" t="n"/>
-      <c r="BQ33" s="27" t="n"/>
+      <c r="BP33" s="38" t="n"/>
+      <c r="BQ33" s="39" t="n"/>
       <c r="BR33" s="28" t="n"/>
       <c r="BS33" s="28" t="n"/>
       <c r="BT33" s="28" t="n"/>
-      <c r="BU33" s="25" t="n"/>
+      <c r="BU33" s="38" t="n"/>
       <c r="BV33" s="29" t="n"/>
       <c r="BW33" s="24" t="n"/>
-      <c r="BX33" s="30" t="n"/>
-      <c r="BY33" s="27" t="n"/>
+      <c r="BX33" s="40" t="n"/>
+      <c r="BY33" s="39" t="n"/>
       <c r="BZ33" s="24" t="n"/>
       <c r="CA33" s="31" t="n"/>
     </row>
@@ -9567,7 +9594,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J34" s="25" t="n"/>
+      <c r="J34" s="38" t="n"/>
       <c r="K34" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -9576,7 +9603,7 @@
       <c r="L34" s="26" t="n">
         <v>-108</v>
       </c>
-      <c r="M34" s="27" t="n">
+      <c r="M34" s="39" t="n">
         <v>1.925926</v>
       </c>
       <c r="N34" s="28" t="n">
@@ -9608,11 +9635,11 @@
       <c r="V34" s="24" t="n"/>
       <c r="W34" s="26" t="n"/>
       <c r="X34" s="26" t="n"/>
-      <c r="Y34" s="25" t="n"/>
+      <c r="Y34" s="38" t="n"/>
       <c r="Z34" s="26" t="n"/>
       <c r="AA34" s="28" t="n"/>
       <c r="AB34" s="28" t="n"/>
-      <c r="AC34" s="30" t="n"/>
+      <c r="AC34" s="40" t="n"/>
       <c r="AD34" s="24" t="n"/>
       <c r="AE34" s="31" t="inlineStr">
         <is>
@@ -9743,11 +9770,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ34" s="25" t="n"/>
+      <c r="BJ34" s="38" t="n"/>
       <c r="BK34" s="26" t="n">
         <v>-108</v>
       </c>
-      <c r="BL34" s="27" t="n">
+      <c r="BL34" s="39" t="n">
         <v>1.925926</v>
       </c>
       <c r="BM34" s="28" t="n">
@@ -9757,16 +9784,16 @@
         <v>0.5148509999999999</v>
       </c>
       <c r="BO34" s="28" t="n"/>
-      <c r="BP34" s="25" t="n"/>
-      <c r="BQ34" s="27" t="n"/>
+      <c r="BP34" s="38" t="n"/>
+      <c r="BQ34" s="39" t="n"/>
       <c r="BR34" s="28" t="n"/>
       <c r="BS34" s="28" t="n"/>
       <c r="BT34" s="28" t="n"/>
-      <c r="BU34" s="25" t="n"/>
+      <c r="BU34" s="38" t="n"/>
       <c r="BV34" s="29" t="n"/>
       <c r="BW34" s="24" t="n"/>
-      <c r="BX34" s="30" t="n"/>
-      <c r="BY34" s="27" t="n"/>
+      <c r="BX34" s="40" t="n"/>
+      <c r="BY34" s="39" t="n"/>
       <c r="BZ34" s="24" t="n"/>
       <c r="CA34" s="31" t="n"/>
     </row>
@@ -9816,7 +9843,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J35" s="25" t="n"/>
+      <c r="J35" s="38" t="n"/>
       <c r="K35" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -9825,7 +9852,7 @@
       <c r="L35" s="26" t="n">
         <v>150</v>
       </c>
-      <c r="M35" s="27" t="n">
+      <c r="M35" s="39" t="n">
         <v>2.5</v>
       </c>
       <c r="N35" s="28" t="n">
@@ -9857,11 +9884,11 @@
       <c r="V35" s="24" t="n"/>
       <c r="W35" s="26" t="n"/>
       <c r="X35" s="26" t="n"/>
-      <c r="Y35" s="25" t="n"/>
+      <c r="Y35" s="38" t="n"/>
       <c r="Z35" s="26" t="n"/>
       <c r="AA35" s="28" t="n"/>
       <c r="AB35" s="28" t="n"/>
-      <c r="AC35" s="30" t="n"/>
+      <c r="AC35" s="40" t="n"/>
       <c r="AD35" s="24" t="n"/>
       <c r="AE35" s="31" t="inlineStr">
         <is>
@@ -9992,11 +10019,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ35" s="25" t="n"/>
+      <c r="BJ35" s="38" t="n"/>
       <c r="BK35" s="26" t="n">
         <v>150</v>
       </c>
-      <c r="BL35" s="27" t="n">
+      <c r="BL35" s="39" t="n">
         <v>2.5</v>
       </c>
       <c r="BM35" s="28" t="n">
@@ -10006,1007 +10033,23 @@
         <v>0.39604</v>
       </c>
       <c r="BO35" s="28" t="n"/>
-      <c r="BP35" s="25" t="n"/>
-      <c r="BQ35" s="27" t="n"/>
+      <c r="BP35" s="38" t="n"/>
+      <c r="BQ35" s="39" t="n"/>
       <c r="BR35" s="28" t="n"/>
       <c r="BS35" s="28" t="n"/>
       <c r="BT35" s="28" t="n"/>
-      <c r="BU35" s="25" t="n"/>
+      <c r="BU35" s="38" t="n"/>
       <c r="BV35" s="29" t="n"/>
       <c r="BW35" s="24" t="n"/>
-      <c r="BX35" s="30" t="n"/>
-      <c r="BY35" s="27" t="n"/>
+      <c r="BX35" s="40" t="n"/>
+      <c r="BY35" s="39" t="n"/>
       <c r="BZ35" s="24" t="n"/>
       <c r="CA35" s="31" t="n"/>
     </row>
-    <row r="36" ht="36" customHeight="1">
-      <c r="A36" s="24" t="inlineStr">
-        <is>
-          <t>c799abfe71704ed8</t>
-        </is>
-      </c>
-      <c r="B36" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-20T16:42:59.632078Z</t>
-        </is>
-      </c>
-      <c r="C36" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-20T20:00:00Z</t>
-        </is>
-      </c>
-      <c r="D36" s="24" t="inlineStr">
-        <is>
-          <t>54491</t>
-        </is>
-      </c>
-      <c r="E36" s="24" t="inlineStr">
-        <is>
-          <t>LOL</t>
-        </is>
-      </c>
-      <c r="F36" s="24" t="inlineStr">
-        <is>
-          <t>KaBuM! Ilha das Lendas</t>
-        </is>
-      </c>
-      <c r="G36" s="24" t="inlineStr">
-        <is>
-          <t>Vivo Keyd Stars Academy</t>
-        </is>
-      </c>
-      <c r="H36" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I36" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J36" s="25" t="n"/>
-      <c r="K36" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L36" s="26" t="n">
-        <v>144</v>
-      </c>
-      <c r="M36" s="27" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="N36" s="28" t="n">
-        <v>0.409836</v>
-      </c>
-      <c r="O36" s="28" t="n">
-        <v>0.597574</v>
-      </c>
-      <c r="P36" s="28" t="n"/>
-      <c r="Q36" s="28" t="n">
-        <v>0.187574</v>
-      </c>
-      <c r="R36" s="26" t="n">
-        <v>100</v>
-      </c>
-      <c r="S36" s="29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T36" s="24" t="inlineStr">
-        <is>
-          <t>lol-neutral-series-elo-v1</t>
-        </is>
-      </c>
-      <c r="U36" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V36" s="24" t="n"/>
-      <c r="W36" s="26" t="n"/>
-      <c r="X36" s="26" t="n"/>
-      <c r="Y36" s="25" t="n"/>
-      <c r="Z36" s="26" t="n"/>
-      <c r="AA36" s="28" t="n"/>
-      <c r="AB36" s="28" t="n"/>
-      <c r="AC36" s="30" t="n"/>
-      <c r="AD36" s="24" t="n"/>
-      <c r="AE36" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.4100 (aec-lol-vksa-kbm-2026-07-20).</t>
-        </is>
-      </c>
-      <c r="AF36" s="31" t="inlineStr">
-        <is>
-          <t>Research baseline; zero-unit shadow until qualified.</t>
-        </is>
-      </c>
-      <c r="AG36" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH36" s="24" t="n"/>
-      <c r="AI36" s="31" t="n"/>
-      <c r="AJ36" s="31" t="n"/>
-      <c r="AK36" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL36" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM36" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN36" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO36" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP36" s="24" t="inlineStr">
-        <is>
-          <t>KaBuM! Ilha das Lendas</t>
-        </is>
-      </c>
-      <c r="AQ36" s="24" t="inlineStr">
-        <is>
-          <t>KaBuM! Ilha das Lendas</t>
-        </is>
-      </c>
-      <c r="AR36" s="24" t="inlineStr">
-        <is>
-          <t>KaBuM! Ilha das Lendas</t>
-        </is>
-      </c>
-      <c r="AS36" s="24" t="inlineStr">
-        <is>
-          <t>Vivo Keyd Stars Academy</t>
-        </is>
-      </c>
-      <c r="AT36" s="24" t="inlineStr">
-        <is>
-          <t>Vivo Keyd Stars Academy</t>
-        </is>
-      </c>
-      <c r="AU36" s="24" t="inlineStr">
-        <is>
-          <t>Vivo Keyd Stars Academy</t>
-        </is>
-      </c>
-      <c r="AV36" s="24" t="n"/>
-      <c r="AW36" s="24" t="n"/>
-      <c r="AX36" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY36" s="24" t="n"/>
-      <c r="AZ36" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA36" s="24" t="inlineStr">
-        <is>
-          <t>4657ea085a2e161ea0063f513a6bf98a7c01549b126f36526876e6d6a2152307</t>
-        </is>
-      </c>
-      <c r="BB36" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC36" s="24" t="inlineStr">
-        <is>
-          <t>lol-neutral-series-elo-v1</t>
-        </is>
-      </c>
-      <c r="BD36" s="24" t="inlineStr">
-        <is>
-          <t>4657ea085a2e161ea0063f513a6bf98a7c01549b126f36526876e6d6a2152307</t>
-        </is>
-      </c>
-      <c r="BE36" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF36" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG36" s="24" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="BH36" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-20T16:42:59.632078Z</t>
-        </is>
-      </c>
-      <c r="BI36" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ36" s="25" t="n"/>
-      <c r="BK36" s="26" t="n">
-        <v>144</v>
-      </c>
-      <c r="BL36" s="27" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BM36" s="28" t="n">
-        <v>0.409836</v>
-      </c>
-      <c r="BN36" s="28" t="n"/>
-      <c r="BO36" s="28" t="n"/>
-      <c r="BP36" s="25" t="n"/>
-      <c r="BQ36" s="27" t="n"/>
-      <c r="BR36" s="28" t="n"/>
-      <c r="BS36" s="28" t="n"/>
-      <c r="BT36" s="28" t="n"/>
-      <c r="BU36" s="25" t="n"/>
-      <c r="BV36" s="29" t="n"/>
-      <c r="BW36" s="24" t="n"/>
-      <c r="BX36" s="30" t="n"/>
-      <c r="BY36" s="27" t="n"/>
-      <c r="BZ36" s="24" t="n"/>
-      <c r="CA36" s="31" t="n"/>
-    </row>
-    <row r="37" ht="36" customHeight="1">
-      <c r="A37" s="24" t="inlineStr">
-        <is>
-          <t>88e300838c684314</t>
-        </is>
-      </c>
-      <c r="B37" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-20T16:42:59.757524Z</t>
-        </is>
-      </c>
-      <c r="C37" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-20T21:00:00Z</t>
-        </is>
-      </c>
-      <c r="D37" s="24" t="inlineStr">
-        <is>
-          <t>54670</t>
-        </is>
-      </c>
-      <c r="E37" s="24" t="inlineStr">
-        <is>
-          <t>LOL</t>
-        </is>
-      </c>
-      <c r="F37" s="24" t="inlineStr">
-        <is>
-          <t>INTZ e-Sports</t>
-        </is>
-      </c>
-      <c r="G37" s="24" t="inlineStr">
-        <is>
-          <t>7REX</t>
-        </is>
-      </c>
-      <c r="H37" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I37" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J37" s="25" t="n"/>
-      <c r="K37" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L37" s="26" t="n">
-        <v>186</v>
-      </c>
-      <c r="M37" s="27" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="N37" s="28" t="n">
-        <v>0.34965</v>
-      </c>
-      <c r="O37" s="28" t="n">
-        <v>0.597891</v>
-      </c>
-      <c r="P37" s="28" t="n"/>
-      <c r="Q37" s="28" t="n">
-        <v>0.247891</v>
-      </c>
-      <c r="R37" s="26" t="n">
-        <v>100</v>
-      </c>
-      <c r="S37" s="29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T37" s="24" t="inlineStr">
-        <is>
-          <t>lol-neutral-series-elo-v1</t>
-        </is>
-      </c>
-      <c r="U37" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V37" s="24" t="n"/>
-      <c r="W37" s="26" t="n"/>
-      <c r="X37" s="26" t="n"/>
-      <c r="Y37" s="25" t="n"/>
-      <c r="Z37" s="26" t="n"/>
-      <c r="AA37" s="28" t="n"/>
-      <c r="AB37" s="28" t="n"/>
-      <c r="AC37" s="30" t="n"/>
-      <c r="AD37" s="24" t="n"/>
-      <c r="AE37" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.3500 (aec-lol-itz-7rex-2026-07-20).</t>
-        </is>
-      </c>
-      <c r="AF37" s="31" t="inlineStr">
-        <is>
-          <t>Research baseline; zero-unit shadow until qualified.</t>
-        </is>
-      </c>
-      <c r="AG37" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH37" s="24" t="n"/>
-      <c r="AI37" s="31" t="n"/>
-      <c r="AJ37" s="31" t="n"/>
-      <c r="AK37" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL37" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM37" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN37" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO37" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP37" s="24" t="inlineStr">
-        <is>
-          <t>INTZ e-Sports</t>
-        </is>
-      </c>
-      <c r="AQ37" s="24" t="inlineStr">
-        <is>
-          <t>INTZ e-Sports</t>
-        </is>
-      </c>
-      <c r="AR37" s="24" t="inlineStr">
-        <is>
-          <t>INTZ e-Sports</t>
-        </is>
-      </c>
-      <c r="AS37" s="24" t="inlineStr">
-        <is>
-          <t>7REX</t>
-        </is>
-      </c>
-      <c r="AT37" s="24" t="inlineStr">
-        <is>
-          <t>7REX</t>
-        </is>
-      </c>
-      <c r="AU37" s="24" t="inlineStr">
-        <is>
-          <t>7REX</t>
-        </is>
-      </c>
-      <c r="AV37" s="24" t="n"/>
-      <c r="AW37" s="24" t="n"/>
-      <c r="AX37" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY37" s="24" t="n"/>
-      <c r="AZ37" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA37" s="24" t="inlineStr">
-        <is>
-          <t>4657ea085a2e161ea0063f513a6bf98a7c01549b126f36526876e6d6a2152307</t>
-        </is>
-      </c>
-      <c r="BB37" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC37" s="24" t="inlineStr">
-        <is>
-          <t>lol-neutral-series-elo-v1</t>
-        </is>
-      </c>
-      <c r="BD37" s="24" t="inlineStr">
-        <is>
-          <t>4657ea085a2e161ea0063f513a6bf98a7c01549b126f36526876e6d6a2152307</t>
-        </is>
-      </c>
-      <c r="BE37" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF37" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG37" s="24" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="BH37" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-20T16:42:59.757524Z</t>
-        </is>
-      </c>
-      <c r="BI37" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ37" s="25" t="n"/>
-      <c r="BK37" s="26" t="n">
-        <v>186</v>
-      </c>
-      <c r="BL37" s="27" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="BM37" s="28" t="n">
-        <v>0.34965</v>
-      </c>
-      <c r="BN37" s="28" t="n"/>
-      <c r="BO37" s="28" t="n"/>
-      <c r="BP37" s="25" t="n"/>
-      <c r="BQ37" s="27" t="n"/>
-      <c r="BR37" s="28" t="n"/>
-      <c r="BS37" s="28" t="n"/>
-      <c r="BT37" s="28" t="n"/>
-      <c r="BU37" s="25" t="n"/>
-      <c r="BV37" s="29" t="n"/>
-      <c r="BW37" s="24" t="n"/>
-      <c r="BX37" s="30" t="n"/>
-      <c r="BY37" s="27" t="n"/>
-      <c r="BZ37" s="24" t="n"/>
-      <c r="CA37" s="31" t="n"/>
-    </row>
-    <row r="38" ht="36" customHeight="1">
-      <c r="A38" s="24" t="inlineStr">
-        <is>
-          <t>6fc69d654df04854</t>
-        </is>
-      </c>
-      <c r="B38" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-20T16:43:06.018541Z</t>
-        </is>
-      </c>
-      <c r="C38" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-20T17:00:00Z</t>
-        </is>
-      </c>
-      <c r="D38" s="24" t="inlineStr">
-        <is>
-          <t>56113</t>
-        </is>
-      </c>
-      <c r="E38" s="24" t="inlineStr">
-        <is>
-          <t>CS2</t>
-        </is>
-      </c>
-      <c r="F38" s="24" t="inlineStr">
-        <is>
-          <t>Inner Circle Academy</t>
-        </is>
-      </c>
-      <c r="G38" s="24" t="inlineStr">
-        <is>
-          <t>Endless Journey</t>
-        </is>
-      </c>
-      <c r="H38" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I38" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J38" s="25" t="n"/>
-      <c r="K38" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L38" s="26" t="n">
-        <v>223</v>
-      </c>
-      <c r="M38" s="27" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="N38" s="28" t="n">
-        <v>0.309598</v>
-      </c>
-      <c r="O38" s="28" t="n">
-        <v>0.599201</v>
-      </c>
-      <c r="P38" s="28" t="n"/>
-      <c r="Q38" s="28" t="n">
-        <v>0.289201</v>
-      </c>
-      <c r="R38" s="26" t="n">
-        <v>100</v>
-      </c>
-      <c r="S38" s="29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T38" s="24" t="inlineStr">
-        <is>
-          <t>cs2-neutral-series-elo-v1</t>
-        </is>
-      </c>
-      <c r="U38" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V38" s="24" t="n"/>
-      <c r="W38" s="26" t="n"/>
-      <c r="X38" s="26" t="n"/>
-      <c r="Y38" s="25" t="n"/>
-      <c r="Z38" s="26" t="n"/>
-      <c r="AA38" s="28" t="n"/>
-      <c r="AB38" s="28" t="n"/>
-      <c r="AC38" s="30" t="n"/>
-      <c r="AD38" s="24" t="n"/>
-      <c r="AE38" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.3100 (aec-cs2-ica-ej-2026-07-20).</t>
-        </is>
-      </c>
-      <c r="AF38" s="31" t="inlineStr">
-        <is>
-          <t>Research baseline; zero-unit shadow until qualified.</t>
-        </is>
-      </c>
-      <c r="AG38" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH38" s="24" t="n"/>
-      <c r="AI38" s="31" t="n"/>
-      <c r="AJ38" s="31" t="n"/>
-      <c r="AK38" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL38" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM38" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN38" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO38" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP38" s="24" t="inlineStr">
-        <is>
-          <t>Inner Circle Academy</t>
-        </is>
-      </c>
-      <c r="AQ38" s="24" t="inlineStr">
-        <is>
-          <t>Inner Circle Academy</t>
-        </is>
-      </c>
-      <c r="AR38" s="24" t="inlineStr">
-        <is>
-          <t>Inner Circle Academy</t>
-        </is>
-      </c>
-      <c r="AS38" s="24" t="inlineStr">
-        <is>
-          <t>Endless Journey</t>
-        </is>
-      </c>
-      <c r="AT38" s="24" t="inlineStr">
-        <is>
-          <t>Endless Journey</t>
-        </is>
-      </c>
-      <c r="AU38" s="24" t="inlineStr">
-        <is>
-          <t>Endless Journey</t>
-        </is>
-      </c>
-      <c r="AV38" s="24" t="n"/>
-      <c r="AW38" s="24" t="n"/>
-      <c r="AX38" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY38" s="24" t="n"/>
-      <c r="AZ38" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA38" s="24" t="inlineStr">
-        <is>
-          <t>8ec29f8dd1985b5dbc96c1339c99e2a2129c4afa4af6efce101e4f76d99dce85</t>
-        </is>
-      </c>
-      <c r="BB38" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC38" s="24" t="inlineStr">
-        <is>
-          <t>cs2-neutral-series-elo-v1</t>
-        </is>
-      </c>
-      <c r="BD38" s="24" t="inlineStr">
-        <is>
-          <t>8ec29f8dd1985b5dbc96c1339c99e2a2129c4afa4af6efce101e4f76d99dce85</t>
-        </is>
-      </c>
-      <c r="BE38" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF38" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG38" s="24" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="BH38" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-20T16:43:06.018541Z</t>
-        </is>
-      </c>
-      <c r="BI38" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ38" s="25" t="n"/>
-      <c r="BK38" s="26" t="n">
-        <v>223</v>
-      </c>
-      <c r="BL38" s="27" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="BM38" s="28" t="n">
-        <v>0.309598</v>
-      </c>
-      <c r="BN38" s="28" t="n"/>
-      <c r="BO38" s="28" t="n"/>
-      <c r="BP38" s="25" t="n"/>
-      <c r="BQ38" s="27" t="n"/>
-      <c r="BR38" s="28" t="n"/>
-      <c r="BS38" s="28" t="n"/>
-      <c r="BT38" s="28" t="n"/>
-      <c r="BU38" s="25" t="n"/>
-      <c r="BV38" s="29" t="n"/>
-      <c r="BW38" s="24" t="n"/>
-      <c r="BX38" s="30" t="n"/>
-      <c r="BY38" s="27" t="n"/>
-      <c r="BZ38" s="24" t="n"/>
-      <c r="CA38" s="31" t="n"/>
-    </row>
-    <row r="39" ht="36" customHeight="1">
-      <c r="A39" s="24" t="inlineStr">
-        <is>
-          <t>eab33644ea2b4fc1</t>
-        </is>
-      </c>
-      <c r="B39" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-20T16:43:06.145847Z</t>
-        </is>
-      </c>
-      <c r="C39" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-20T21:00:00Z</t>
-        </is>
-      </c>
-      <c r="D39" s="24" t="inlineStr">
-        <is>
-          <t>54672</t>
-        </is>
-      </c>
-      <c r="E39" s="24" t="inlineStr">
-        <is>
-          <t>CS2</t>
-        </is>
-      </c>
-      <c r="F39" s="24" t="inlineStr">
-        <is>
-          <t>METANOIA WOLVES</t>
-        </is>
-      </c>
-      <c r="G39" s="24" t="inlineStr">
-        <is>
-          <t>RED Canids Academy</t>
-        </is>
-      </c>
-      <c r="H39" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I39" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J39" s="25" t="n"/>
-      <c r="K39" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L39" s="26" t="n">
-        <v>-144</v>
-      </c>
-      <c r="M39" s="27" t="n">
-        <v>1.694444</v>
-      </c>
-      <c r="N39" s="28" t="n">
-        <v>0.590164</v>
-      </c>
-      <c r="O39" s="28" t="n">
-        <v>0.719007</v>
-      </c>
-      <c r="P39" s="28" t="n"/>
-      <c r="Q39" s="28" t="n">
-        <v>0.129007</v>
-      </c>
-      <c r="R39" s="26" t="n">
-        <v>100</v>
-      </c>
-      <c r="S39" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="T39" s="24" t="inlineStr">
-        <is>
-          <t>cs2-neutral-series-elo-v1</t>
-        </is>
-      </c>
-      <c r="U39" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V39" s="24" t="n"/>
-      <c r="W39" s="26" t="n"/>
-      <c r="X39" s="26" t="n"/>
-      <c r="Y39" s="25" t="n"/>
-      <c r="Z39" s="26" t="n"/>
-      <c r="AA39" s="28" t="n"/>
-      <c r="AB39" s="28" t="n"/>
-      <c r="AC39" s="30" t="n"/>
-      <c r="AD39" s="24" t="n"/>
-      <c r="AE39" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.5900 (aec-cs2-reda-mw-2026-07-20).</t>
-        </is>
-      </c>
-      <c r="AF39" s="31" t="inlineStr">
-        <is>
-          <t>Research baseline; zero-unit shadow until qualified.</t>
-        </is>
-      </c>
-      <c r="AG39" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH39" s="24" t="n"/>
-      <c r="AI39" s="31" t="n"/>
-      <c r="AJ39" s="31" t="n"/>
-      <c r="AK39" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL39" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM39" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN39" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO39" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP39" s="24" t="inlineStr">
-        <is>
-          <t>METANOIA WOLVES</t>
-        </is>
-      </c>
-      <c r="AQ39" s="24" t="inlineStr">
-        <is>
-          <t>METANOIA WOLVES</t>
-        </is>
-      </c>
-      <c r="AR39" s="24" t="inlineStr">
-        <is>
-          <t>METANOIA WOLVES</t>
-        </is>
-      </c>
-      <c r="AS39" s="24" t="inlineStr">
-        <is>
-          <t>RED Canids Academy</t>
-        </is>
-      </c>
-      <c r="AT39" s="24" t="inlineStr">
-        <is>
-          <t>RED Canids Academy</t>
-        </is>
-      </c>
-      <c r="AU39" s="24" t="inlineStr">
-        <is>
-          <t>RED Canids Academy</t>
-        </is>
-      </c>
-      <c r="AV39" s="24" t="n"/>
-      <c r="AW39" s="24" t="n"/>
-      <c r="AX39" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY39" s="24" t="n"/>
-      <c r="AZ39" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA39" s="24" t="inlineStr">
-        <is>
-          <t>8ec29f8dd1985b5dbc96c1339c99e2a2129c4afa4af6efce101e4f76d99dce85</t>
-        </is>
-      </c>
-      <c r="BB39" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC39" s="24" t="inlineStr">
-        <is>
-          <t>cs2-neutral-series-elo-v1</t>
-        </is>
-      </c>
-      <c r="BD39" s="24" t="inlineStr">
-        <is>
-          <t>8ec29f8dd1985b5dbc96c1339c99e2a2129c4afa4af6efce101e4f76d99dce85</t>
-        </is>
-      </c>
-      <c r="BE39" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF39" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG39" s="24" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="BH39" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-20T16:43:06.145847Z</t>
-        </is>
-      </c>
-      <c r="BI39" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ39" s="25" t="n"/>
-      <c r="BK39" s="26" t="n">
-        <v>-144</v>
-      </c>
-      <c r="BL39" s="27" t="n">
-        <v>1.694444</v>
-      </c>
-      <c r="BM39" s="28" t="n">
-        <v>0.590164</v>
-      </c>
-      <c r="BN39" s="28" t="n"/>
-      <c r="BO39" s="28" t="n"/>
-      <c r="BP39" s="25" t="n"/>
-      <c r="BQ39" s="27" t="n"/>
-      <c r="BR39" s="28" t="n"/>
-      <c r="BS39" s="28" t="n"/>
-      <c r="BT39" s="28" t="n"/>
-      <c r="BU39" s="25" t="n"/>
-      <c r="BV39" s="29" t="n"/>
-      <c r="BW39" s="24" t="n"/>
-      <c r="BX39" s="30" t="n"/>
-      <c r="BY39" s="27" t="n"/>
-      <c r="BZ39" s="24" t="n"/>
-      <c r="CA39" s="31" t="n"/>
-    </row>
+    <row r="36" ht="36" customHeight="1"/>
+    <row r="37" ht="36" customHeight="1"/>
+    <row r="38" ht="36" customHeight="1"/>
+    <row r="39" ht="36" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/picks.xlsx
+++ b/data/picks.xlsx
@@ -21,10 +21,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="0.0###"/>
-    <numFmt numFmtId="165" formatCode="0.000000"/>
-    <numFmt numFmtId="166" formatCode="0.0000"/>
-    <numFmt numFmtId="167" formatCode="0.0%"/>
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
+    <numFmt numFmtId="166" formatCode="0.0###"/>
+    <numFmt numFmtId="167" formatCode="0.000000"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -136,7 +136,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -150,10 +150,10 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -169,10 +169,10 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -184,10 +184,10 @@
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -202,13 +202,13 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="10" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -217,11 +217,38 @@
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -300,8 +327,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CA66" headerRowCount="1">
-  <autoFilter ref="A1:CA66"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CA71" headerRowCount="1">
+  <autoFilter ref="A1:CA71"/>
   <tableColumns count="79">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -738,22 +765,23 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$66)</f>
+        <f>COUNTA('Picks'!$A$2:$A$71)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$66,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$71,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$66,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$71,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$66,"settled",'Picks'!$V$2:$V$66,"win")+COUNTIFS('Picks'!$U$2:$U$66,"settled",'Picks'!$V$2:$V$66,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$71,"settled",'Picks'!$V$2:$V$71,"win")+COUNTIFS('Picks'!$U$2:$U$71,"settled",'Picks'!$V$2:$V$71,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
+    <row r="5"/>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
@@ -778,22 +806,23 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$66,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$71,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$66,"&gt;0",'Picks'!$V$2:$V$66,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$66,"&gt;0",'Picks'!$V$2:$V$66,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$71,"&gt;0",'Picks'!$V$2:$V$71,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$71,"&gt;0",'Picks'!$V$2:$V$71,"loss")</f>
         <v/>
       </c>
-      <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$66,"&gt;0",'Picks'!$V$2:$V$66,"win")/(COUNTIFS('Picks'!$BX$2:$BX$66,"&gt;0",'Picks'!$V$2:$V$66,"win")+COUNTIFS('Picks'!$BX$2:$BX$66,"&gt;0",'Picks'!$V$2:$V$66,"loss")),0)</f>
+      <c r="E7" s="32">
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$71,"&gt;0",'Picks'!$V$2:$V$71,"win")/(COUNTIFS('Picks'!$BX$2:$BX$71,"&gt;0",'Picks'!$V$2:$V$71,"win")+COUNTIFS('Picks'!$BX$2:$BX$71,"&gt;0",'Picks'!$V$2:$V$71,"loss")),0)</f>
         <v/>
       </c>
-      <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$66)/SUM('Picks'!$BX$2:$BX$66),0)</f>
+      <c r="G7" s="32">
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$71)/SUM('Picks'!$BX$2:$BX$71),0)</f>
         <v/>
       </c>
     </row>
+    <row r="8"/>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
@@ -817,23 +846,24 @@
       </c>
     </row>
     <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$66)</f>
+      <c r="A10" s="33">
+        <f>SUM('Picks'!$BY$2:$BY$71)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$66,"&lt;&gt;",'Picks'!$AB$2:$AB$66),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$71,"&lt;&gt;",'Picks'!$AB$2:$AB$71),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$66,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$66,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$71,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$71,"settled")</f>
         <v/>
       </c>
-      <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$66,'Picks'!$AM$2:$AM$66,"QUALIFIED_SHADOW_CALL")</f>
+      <c r="G10" s="33">
+        <f>SUMIFS('Picks'!$AC$2:$AC$71,'Picks'!$AM$2:$AM$71,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
@@ -885,27 +915,27 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$66,$A14,'Picks'!$U$2:$U$66,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$71,$A14,'Picks'!$U$2:$U$71,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$66,$A14,'Picks'!$U$2:$U$66,"settled",'Picks'!$V$2:$V$66,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$71,$A14,'Picks'!$U$2:$U$71,"settled",'Picks'!$V$2:$V$71,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$66,$A14,'Picks'!$U$2:$U$66,"settled",'Picks'!$V$2:$V$66,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$71,$A14,'Picks'!$U$2:$U$71,"settled",'Picks'!$V$2:$V$71,"loss")</f>
         <v/>
       </c>
-      <c r="E14" s="14">
+      <c r="E14" s="34">
         <f>IFERROR(C14/(C14+D14),0)</f>
         <v/>
       </c>
-      <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$66,'Picks'!$H$2:$H$66,$A14)</f>
+      <c r="F14" s="35">
+        <f>SUMIFS('Picks'!$BY$2:$BY$71,'Picks'!$H$2:$H$71,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$66,'Picks'!$H$2:$H$66,$A14,'Picks'!$U$2:$U$66,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$71,'Picks'!$H$2:$H$71,$A14,'Picks'!$U$2:$U$71,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -916,27 +946,27 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$66,$A15,'Picks'!$U$2:$U$66,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$71,$A15,'Picks'!$U$2:$U$71,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$66,$A15,'Picks'!$U$2:$U$66,"settled",'Picks'!$V$2:$V$66,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$71,$A15,'Picks'!$U$2:$U$71,"settled",'Picks'!$V$2:$V$71,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$66,$A15,'Picks'!$U$2:$U$66,"settled",'Picks'!$V$2:$V$66,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$71,$A15,'Picks'!$U$2:$U$71,"settled",'Picks'!$V$2:$V$71,"loss")</f>
         <v/>
       </c>
-      <c r="E15" s="19">
+      <c r="E15" s="36">
         <f>IFERROR(C15/(C15+D15),0)</f>
         <v/>
       </c>
-      <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$66,'Picks'!$H$2:$H$66,$A15)</f>
+      <c r="F15" s="37">
+        <f>SUMIFS('Picks'!$BY$2:$BY$71,'Picks'!$H$2:$H$71,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$66,'Picks'!$H$2:$H$66,$A15,'Picks'!$U$2:$U$66,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$71,'Picks'!$H$2:$H$71,$A15,'Picks'!$U$2:$U$71,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -947,30 +977,31 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$66,$A16,'Picks'!$U$2:$U$66,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$71,$A16,'Picks'!$U$2:$U$71,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$66,$A16,'Picks'!$U$2:$U$66,"settled",'Picks'!$V$2:$V$66,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$71,$A16,'Picks'!$U$2:$U$71,"settled",'Picks'!$V$2:$V$71,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$66,$A16,'Picks'!$U$2:$U$66,"settled",'Picks'!$V$2:$V$66,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$71,$A16,'Picks'!$U$2:$U$71,"settled",'Picks'!$V$2:$V$71,"loss")</f>
         <v/>
       </c>
-      <c r="E16" s="14">
+      <c r="E16" s="34">
         <f>IFERROR(C16/(C16+D16),0)</f>
         <v/>
       </c>
-      <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$66,'Picks'!$H$2:$H$66,$A16)</f>
+      <c r="F16" s="35">
+        <f>SUMIFS('Picks'!$BY$2:$BY$71,'Picks'!$H$2:$H$71,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$66,'Picks'!$H$2:$H$66,$A16,'Picks'!$U$2:$U$66,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$71,'Picks'!$H$2:$H$71,$A16,'Picks'!$U$2:$U$71,"settled"),0)</f>
         <v/>
       </c>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="22" t="inlineStr">
         <is>
@@ -996,7 +1027,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CA66"/>
+  <dimension ref="A1:CA71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1523,7 +1554,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J2" s="25" t="n"/>
+      <c r="J2" s="38" t="n"/>
       <c r="K2" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -1532,7 +1563,7 @@
       <c r="L2" s="26" t="n">
         <v>117</v>
       </c>
-      <c r="M2" s="27" t="n">
+      <c r="M2" s="39" t="n">
         <v>2.17</v>
       </c>
       <c r="N2" s="28" t="n">
@@ -1572,11 +1603,11 @@
       <c r="X2" s="26" t="n">
         <v>108</v>
       </c>
-      <c r="Y2" s="25" t="n"/>
+      <c r="Y2" s="38" t="n"/>
       <c r="Z2" s="26" t="n"/>
       <c r="AA2" s="28" t="n"/>
       <c r="AB2" s="28" t="n"/>
-      <c r="AC2" s="30" t="n">
+      <c r="AC2" s="40" t="n">
         <v>1.755</v>
       </c>
       <c r="AD2" s="24" t="inlineStr">
@@ -1713,11 +1744,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ2" s="25" t="n"/>
+      <c r="BJ2" s="38" t="n"/>
       <c r="BK2" s="26" t="n">
         <v>117</v>
       </c>
-      <c r="BL2" s="27" t="n">
+      <c r="BL2" s="39" t="n">
         <v>2.17</v>
       </c>
       <c r="BM2" s="28" t="n">
@@ -1727,18 +1758,18 @@
         <v>0.455446</v>
       </c>
       <c r="BO2" s="28" t="n"/>
-      <c r="BP2" s="25" t="n"/>
-      <c r="BQ2" s="27" t="n"/>
+      <c r="BP2" s="38" t="n"/>
+      <c r="BQ2" s="39" t="n"/>
       <c r="BR2" s="28" t="n"/>
       <c r="BS2" s="28" t="n"/>
       <c r="BT2" s="28" t="n"/>
-      <c r="BU2" s="25" t="n"/>
+      <c r="BU2" s="38" t="n"/>
       <c r="BV2" s="29" t="n"/>
       <c r="BW2" s="24" t="n"/>
-      <c r="BX2" s="30" t="n">
+      <c r="BX2" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY2" s="27" t="n">
+      <c r="BY2" s="39" t="n">
         <v>1.17</v>
       </c>
       <c r="BZ2" s="24" t="inlineStr">
@@ -1798,7 +1829,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J3" s="25" t="n"/>
+      <c r="J3" s="38" t="n"/>
       <c r="K3" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -1807,7 +1838,7 @@
       <c r="L3" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="M3" s="27" t="n">
+      <c r="M3" s="39" t="n">
         <v>1.75188</v>
       </c>
       <c r="N3" s="28" t="n">
@@ -1847,11 +1878,11 @@
       <c r="X3" s="26" t="n">
         <v>8</v>
       </c>
-      <c r="Y3" s="25" t="n"/>
+      <c r="Y3" s="38" t="n"/>
       <c r="Z3" s="26" t="n"/>
       <c r="AA3" s="28" t="n"/>
       <c r="AB3" s="28" t="n"/>
-      <c r="AC3" s="30" t="n">
+      <c r="AC3" s="40" t="n">
         <v>1.1278</v>
       </c>
       <c r="AD3" s="24" t="inlineStr">
@@ -1988,11 +2019,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ3" s="25" t="n"/>
+      <c r="BJ3" s="38" t="n"/>
       <c r="BK3" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="BL3" s="27" t="n">
+      <c r="BL3" s="39" t="n">
         <v>1.75188</v>
       </c>
       <c r="BM3" s="28" t="n">
@@ -2002,18 +2033,18 @@
         <v>0.567164</v>
       </c>
       <c r="BO3" s="28" t="n"/>
-      <c r="BP3" s="25" t="n"/>
-      <c r="BQ3" s="27" t="n"/>
+      <c r="BP3" s="38" t="n"/>
+      <c r="BQ3" s="39" t="n"/>
       <c r="BR3" s="28" t="n"/>
       <c r="BS3" s="28" t="n"/>
       <c r="BT3" s="28" t="n"/>
-      <c r="BU3" s="25" t="n"/>
+      <c r="BU3" s="38" t="n"/>
       <c r="BV3" s="29" t="n"/>
       <c r="BW3" s="24" t="n"/>
-      <c r="BX3" s="30" t="n">
+      <c r="BX3" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY3" s="27" t="n">
+      <c r="BY3" s="39" t="n">
         <v>0.75188</v>
       </c>
       <c r="BZ3" s="24" t="inlineStr">
@@ -2073,7 +2104,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J4" s="25" t="n"/>
+      <c r="J4" s="38" t="n"/>
       <c r="K4" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -2082,7 +2113,7 @@
       <c r="L4" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="M4" s="27" t="n">
+      <c r="M4" s="39" t="n">
         <v>1.980392</v>
       </c>
       <c r="N4" s="28" t="n">
@@ -2122,11 +2153,11 @@
       <c r="X4" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="Y4" s="25" t="n"/>
+      <c r="Y4" s="38" t="n"/>
       <c r="Z4" s="26" t="n"/>
       <c r="AA4" s="28" t="n"/>
       <c r="AB4" s="28" t="n"/>
-      <c r="AC4" s="30" t="n">
+      <c r="AC4" s="40" t="n">
         <v>-1</v>
       </c>
       <c r="AD4" s="24" t="inlineStr">
@@ -2263,11 +2294,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ4" s="25" t="n"/>
+      <c r="BJ4" s="38" t="n"/>
       <c r="BK4" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="BL4" s="27" t="n">
+      <c r="BL4" s="39" t="n">
         <v>1.980392</v>
       </c>
       <c r="BM4" s="28" t="n">
@@ -2277,18 +2308,18 @@
         <v>0.502488</v>
       </c>
       <c r="BO4" s="28" t="n"/>
-      <c r="BP4" s="25" t="n"/>
-      <c r="BQ4" s="27" t="n"/>
+      <c r="BP4" s="38" t="n"/>
+      <c r="BQ4" s="39" t="n"/>
       <c r="BR4" s="28" t="n"/>
       <c r="BS4" s="28" t="n"/>
       <c r="BT4" s="28" t="n"/>
-      <c r="BU4" s="25" t="n"/>
+      <c r="BU4" s="38" t="n"/>
       <c r="BV4" s="29" t="n"/>
       <c r="BW4" s="24" t="n"/>
-      <c r="BX4" s="30" t="n">
+      <c r="BX4" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY4" s="27" t="n">
+      <c r="BY4" s="39" t="n">
         <v>-1</v>
       </c>
       <c r="BZ4" s="24" t="inlineStr">
@@ -2348,7 +2379,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J5" s="25" t="n"/>
+      <c r="J5" s="38" t="n"/>
       <c r="K5" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -2357,7 +2388,7 @@
       <c r="L5" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="M5" s="27" t="n">
+      <c r="M5" s="39" t="n">
         <v>1.75188</v>
       </c>
       <c r="N5" s="28" t="n">
@@ -2397,11 +2428,11 @@
       <c r="X5" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="Y5" s="25" t="n"/>
+      <c r="Y5" s="38" t="n"/>
       <c r="Z5" s="26" t="n"/>
       <c r="AA5" s="28" t="n"/>
       <c r="AB5" s="28" t="n"/>
-      <c r="AC5" s="30" t="n">
+      <c r="AC5" s="40" t="n">
         <v>1.1278</v>
       </c>
       <c r="AD5" s="24" t="inlineStr">
@@ -2538,11 +2569,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ5" s="25" t="n"/>
+      <c r="BJ5" s="38" t="n"/>
       <c r="BK5" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="BL5" s="27" t="n">
+      <c r="BL5" s="39" t="n">
         <v>1.75188</v>
       </c>
       <c r="BM5" s="28" t="n">
@@ -2552,18 +2583,18 @@
         <v>0.567164</v>
       </c>
       <c r="BO5" s="28" t="n"/>
-      <c r="BP5" s="25" t="n"/>
-      <c r="BQ5" s="27" t="n"/>
+      <c r="BP5" s="38" t="n"/>
+      <c r="BQ5" s="39" t="n"/>
       <c r="BR5" s="28" t="n"/>
       <c r="BS5" s="28" t="n"/>
       <c r="BT5" s="28" t="n"/>
-      <c r="BU5" s="25" t="n"/>
+      <c r="BU5" s="38" t="n"/>
       <c r="BV5" s="29" t="n"/>
       <c r="BW5" s="24" t="n"/>
-      <c r="BX5" s="30" t="n">
+      <c r="BX5" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY5" s="27" t="n">
+      <c r="BY5" s="39" t="n">
         <v>0.75188</v>
       </c>
       <c r="BZ5" s="24" t="inlineStr">
@@ -2623,7 +2654,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J6" s="25" t="n"/>
+      <c r="J6" s="38" t="n"/>
       <c r="K6" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -2632,7 +2663,7 @@
       <c r="L6" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="M6" s="27" t="n">
+      <c r="M6" s="39" t="n">
         <v>1.961538</v>
       </c>
       <c r="N6" s="28" t="n">
@@ -2672,11 +2703,11 @@
       <c r="X6" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="Y6" s="25" t="n"/>
+      <c r="Y6" s="38" t="n"/>
       <c r="Z6" s="26" t="n"/>
       <c r="AA6" s="28" t="n"/>
       <c r="AB6" s="28" t="n"/>
-      <c r="AC6" s="30" t="n">
+      <c r="AC6" s="40" t="n">
         <v>1.2019</v>
       </c>
       <c r="AD6" s="24" t="inlineStr">
@@ -2813,11 +2844,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ6" s="25" t="n"/>
+      <c r="BJ6" s="38" t="n"/>
       <c r="BK6" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="BL6" s="27" t="n">
+      <c r="BL6" s="39" t="n">
         <v>1.961538</v>
       </c>
       <c r="BM6" s="28" t="n">
@@ -2827,18 +2858,18 @@
         <v>0.507463</v>
       </c>
       <c r="BO6" s="28" t="n"/>
-      <c r="BP6" s="25" t="n"/>
-      <c r="BQ6" s="27" t="n"/>
+      <c r="BP6" s="38" t="n"/>
+      <c r="BQ6" s="39" t="n"/>
       <c r="BR6" s="28" t="n"/>
       <c r="BS6" s="28" t="n"/>
       <c r="BT6" s="28" t="n"/>
-      <c r="BU6" s="25" t="n"/>
+      <c r="BU6" s="38" t="n"/>
       <c r="BV6" s="29" t="n"/>
       <c r="BW6" s="24" t="n"/>
-      <c r="BX6" s="30" t="n">
+      <c r="BX6" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY6" s="27" t="n">
+      <c r="BY6" s="39" t="n">
         <v>0.961538</v>
       </c>
       <c r="BZ6" s="24" t="inlineStr">
@@ -2898,7 +2929,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J7" s="25" t="n"/>
+      <c r="J7" s="38" t="n"/>
       <c r="K7" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -2907,7 +2938,7 @@
       <c r="L7" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="M7" s="27" t="n">
+      <c r="M7" s="39" t="n">
         <v>1.961538</v>
       </c>
       <c r="N7" s="28" t="n">
@@ -2947,11 +2978,11 @@
       <c r="X7" s="26" t="n">
         <v>10</v>
       </c>
-      <c r="Y7" s="25" t="n"/>
+      <c r="Y7" s="38" t="n"/>
       <c r="Z7" s="26" t="n"/>
       <c r="AA7" s="28" t="n"/>
       <c r="AB7" s="28" t="n"/>
-      <c r="AC7" s="30" t="n">
+      <c r="AC7" s="40" t="n">
         <v>-1.25</v>
       </c>
       <c r="AD7" s="24" t="inlineStr">
@@ -3088,11 +3119,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ7" s="25" t="n"/>
+      <c r="BJ7" s="38" t="n"/>
       <c r="BK7" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="BL7" s="27" t="n">
+      <c r="BL7" s="39" t="n">
         <v>1.961538</v>
       </c>
       <c r="BM7" s="28" t="n">
@@ -3102,18 +3133,18 @@
         <v>0.507463</v>
       </c>
       <c r="BO7" s="28" t="n"/>
-      <c r="BP7" s="25" t="n"/>
-      <c r="BQ7" s="27" t="n"/>
+      <c r="BP7" s="38" t="n"/>
+      <c r="BQ7" s="39" t="n"/>
       <c r="BR7" s="28" t="n"/>
       <c r="BS7" s="28" t="n"/>
       <c r="BT7" s="28" t="n"/>
-      <c r="BU7" s="25" t="n"/>
+      <c r="BU7" s="38" t="n"/>
       <c r="BV7" s="29" t="n"/>
       <c r="BW7" s="24" t="n"/>
-      <c r="BX7" s="30" t="n">
+      <c r="BX7" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY7" s="27" t="n">
+      <c r="BY7" s="39" t="n">
         <v>-1</v>
       </c>
       <c r="BZ7" s="24" t="inlineStr">
@@ -3173,7 +3204,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J8" s="25" t="n"/>
+      <c r="J8" s="38" t="n"/>
       <c r="K8" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -3182,7 +3213,7 @@
       <c r="L8" s="26" t="n">
         <v>-106</v>
       </c>
-      <c r="M8" s="27" t="n">
+      <c r="M8" s="39" t="n">
         <v>1.943396</v>
       </c>
       <c r="N8" s="28" t="n">
@@ -3222,11 +3253,11 @@
       <c r="X8" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="Y8" s="25" t="n"/>
+      <c r="Y8" s="38" t="n"/>
       <c r="Z8" s="26" t="n"/>
       <c r="AA8" s="28" t="n"/>
       <c r="AB8" s="28" t="n"/>
-      <c r="AC8" s="30" t="n">
+      <c r="AC8" s="40" t="n">
         <v>-1</v>
       </c>
       <c r="AD8" s="24" t="inlineStr">
@@ -3363,11 +3394,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ8" s="25" t="n"/>
+      <c r="BJ8" s="38" t="n"/>
       <c r="BK8" s="26" t="n">
         <v>-106</v>
       </c>
-      <c r="BL8" s="27" t="n">
+      <c r="BL8" s="39" t="n">
         <v>1.943396</v>
       </c>
       <c r="BM8" s="28" t="n">
@@ -3377,18 +3408,18 @@
         <v>0.5124379999999999</v>
       </c>
       <c r="BO8" s="28" t="n"/>
-      <c r="BP8" s="25" t="n"/>
-      <c r="BQ8" s="27" t="n"/>
+      <c r="BP8" s="38" t="n"/>
+      <c r="BQ8" s="39" t="n"/>
       <c r="BR8" s="28" t="n"/>
       <c r="BS8" s="28" t="n"/>
       <c r="BT8" s="28" t="n"/>
-      <c r="BU8" s="25" t="n"/>
+      <c r="BU8" s="38" t="n"/>
       <c r="BV8" s="29" t="n"/>
       <c r="BW8" s="24" t="n"/>
-      <c r="BX8" s="30" t="n">
+      <c r="BX8" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY8" s="27" t="n">
+      <c r="BY8" s="39" t="n">
         <v>-1</v>
       </c>
       <c r="BZ8" s="24" t="inlineStr">
@@ -3448,7 +3479,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J9" s="25" t="n"/>
+      <c r="J9" s="38" t="n"/>
       <c r="K9" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -3457,7 +3488,7 @@
       <c r="L9" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="M9" s="27" t="n">
+      <c r="M9" s="39" t="n">
         <v>1.980392</v>
       </c>
       <c r="N9" s="28" t="n">
@@ -3497,11 +3528,11 @@
       <c r="X9" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="Y9" s="25" t="n"/>
+      <c r="Y9" s="38" t="n"/>
       <c r="Z9" s="26" t="n"/>
       <c r="AA9" s="28" t="n"/>
       <c r="AB9" s="28" t="n"/>
-      <c r="AC9" s="30" t="n">
+      <c r="AC9" s="40" t="n">
         <v>0.9804</v>
       </c>
       <c r="AD9" s="24" t="inlineStr">
@@ -3638,11 +3669,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ9" s="25" t="n"/>
+      <c r="BJ9" s="38" t="n"/>
       <c r="BK9" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="BL9" s="27" t="n">
+      <c r="BL9" s="39" t="n">
         <v>1.980392</v>
       </c>
       <c r="BM9" s="28" t="n">
@@ -3652,18 +3683,18 @@
         <v>0.502488</v>
       </c>
       <c r="BO9" s="28" t="n"/>
-      <c r="BP9" s="25" t="n"/>
-      <c r="BQ9" s="27" t="n"/>
+      <c r="BP9" s="38" t="n"/>
+      <c r="BQ9" s="39" t="n"/>
       <c r="BR9" s="28" t="n"/>
       <c r="BS9" s="28" t="n"/>
       <c r="BT9" s="28" t="n"/>
-      <c r="BU9" s="25" t="n"/>
+      <c r="BU9" s="38" t="n"/>
       <c r="BV9" s="29" t="n"/>
       <c r="BW9" s="24" t="n"/>
-      <c r="BX9" s="30" t="n">
+      <c r="BX9" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY9" s="27" t="n">
+      <c r="BY9" s="39" t="n">
         <v>0.980392</v>
       </c>
       <c r="BZ9" s="24" t="inlineStr">
@@ -3723,7 +3754,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J10" s="25" t="n"/>
+      <c r="J10" s="38" t="n"/>
       <c r="K10" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -3732,7 +3763,7 @@
       <c r="L10" s="26" t="n">
         <v>-138</v>
       </c>
-      <c r="M10" s="27" t="n">
+      <c r="M10" s="39" t="n">
         <v>1.724638</v>
       </c>
       <c r="N10" s="28" t="n">
@@ -3772,11 +3803,11 @@
       <c r="X10" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="Y10" s="25" t="n"/>
+      <c r="Y10" s="38" t="n"/>
       <c r="Z10" s="26" t="n"/>
       <c r="AA10" s="28" t="n"/>
       <c r="AB10" s="28" t="n"/>
-      <c r="AC10" s="30" t="n">
+      <c r="AC10" s="40" t="n">
         <v>1.2681</v>
       </c>
       <c r="AD10" s="24" t="inlineStr">
@@ -3913,11 +3944,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ10" s="25" t="n"/>
+      <c r="BJ10" s="38" t="n"/>
       <c r="BK10" s="26" t="n">
         <v>-138</v>
       </c>
-      <c r="BL10" s="27" t="n">
+      <c r="BL10" s="39" t="n">
         <v>1.724638</v>
       </c>
       <c r="BM10" s="28" t="n">
@@ -3927,18 +3958,18 @@
         <v>0.577114</v>
       </c>
       <c r="BO10" s="28" t="n"/>
-      <c r="BP10" s="25" t="n"/>
-      <c r="BQ10" s="27" t="n"/>
+      <c r="BP10" s="38" t="n"/>
+      <c r="BQ10" s="39" t="n"/>
       <c r="BR10" s="28" t="n"/>
       <c r="BS10" s="28" t="n"/>
       <c r="BT10" s="28" t="n"/>
-      <c r="BU10" s="25" t="n"/>
+      <c r="BU10" s="38" t="n"/>
       <c r="BV10" s="29" t="n"/>
       <c r="BW10" s="24" t="n"/>
-      <c r="BX10" s="30" t="n">
+      <c r="BX10" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY10" s="27" t="n">
+      <c r="BY10" s="39" t="n">
         <v>0.724638</v>
       </c>
       <c r="BZ10" s="24" t="inlineStr">
@@ -3998,7 +4029,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J11" s="25" t="n"/>
+      <c r="J11" s="38" t="n"/>
       <c r="K11" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -4007,7 +4038,7 @@
       <c r="L11" s="26" t="n">
         <v>102</v>
       </c>
-      <c r="M11" s="27" t="n">
+      <c r="M11" s="39" t="n">
         <v>2.02</v>
       </c>
       <c r="N11" s="28" t="n">
@@ -4047,11 +4078,11 @@
       <c r="X11" s="26" t="n">
         <v>15</v>
       </c>
-      <c r="Y11" s="25" t="n"/>
+      <c r="Y11" s="38" t="n"/>
       <c r="Z11" s="26" t="n"/>
       <c r="AA11" s="28" t="n"/>
       <c r="AB11" s="28" t="n"/>
-      <c r="AC11" s="30" t="n">
+      <c r="AC11" s="40" t="n">
         <v>1.275</v>
       </c>
       <c r="AD11" s="24" t="inlineStr">
@@ -4188,11 +4219,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ11" s="25" t="n"/>
+      <c r="BJ11" s="38" t="n"/>
       <c r="BK11" s="26" t="n">
         <v>102</v>
       </c>
-      <c r="BL11" s="27" t="n">
+      <c r="BL11" s="39" t="n">
         <v>2.02</v>
       </c>
       <c r="BM11" s="28" t="n">
@@ -4202,18 +4233,18 @@
         <v>0.492537</v>
       </c>
       <c r="BO11" s="28" t="n"/>
-      <c r="BP11" s="25" t="n"/>
-      <c r="BQ11" s="27" t="n"/>
+      <c r="BP11" s="38" t="n"/>
+      <c r="BQ11" s="39" t="n"/>
       <c r="BR11" s="28" t="n"/>
       <c r="BS11" s="28" t="n"/>
       <c r="BT11" s="28" t="n"/>
-      <c r="BU11" s="25" t="n"/>
+      <c r="BU11" s="38" t="n"/>
       <c r="BV11" s="29" t="n"/>
       <c r="BW11" s="24" t="n"/>
-      <c r="BX11" s="30" t="n">
+      <c r="BX11" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY11" s="27" t="n">
+      <c r="BY11" s="39" t="n">
         <v>1.02</v>
       </c>
       <c r="BZ11" s="24" t="inlineStr">
@@ -4273,7 +4304,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J12" s="25" t="n"/>
+      <c r="J12" s="38" t="n"/>
       <c r="K12" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -4282,7 +4313,7 @@
       <c r="L12" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="M12" s="27" t="n">
+      <c r="M12" s="39" t="n">
         <v>1.980392</v>
       </c>
       <c r="N12" s="28" t="n">
@@ -4322,11 +4353,11 @@
       <c r="X12" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y12" s="25" t="n"/>
+      <c r="Y12" s="38" t="n"/>
       <c r="Z12" s="26" t="n"/>
       <c r="AA12" s="28" t="n"/>
       <c r="AB12" s="28" t="n"/>
-      <c r="AC12" s="30" t="n">
+      <c r="AC12" s="40" t="n">
         <v>-1</v>
       </c>
       <c r="AD12" s="24" t="inlineStr">
@@ -4463,11 +4494,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ12" s="25" t="n"/>
+      <c r="BJ12" s="38" t="n"/>
       <c r="BK12" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="BL12" s="27" t="n">
+      <c r="BL12" s="39" t="n">
         <v>1.980392</v>
       </c>
       <c r="BM12" s="28" t="n">
@@ -4477,18 +4508,18 @@
         <v>0.502488</v>
       </c>
       <c r="BO12" s="28" t="n"/>
-      <c r="BP12" s="25" t="n"/>
-      <c r="BQ12" s="27" t="n"/>
+      <c r="BP12" s="38" t="n"/>
+      <c r="BQ12" s="39" t="n"/>
       <c r="BR12" s="28" t="n"/>
       <c r="BS12" s="28" t="n"/>
       <c r="BT12" s="28" t="n"/>
-      <c r="BU12" s="25" t="n"/>
+      <c r="BU12" s="38" t="n"/>
       <c r="BV12" s="29" t="n"/>
       <c r="BW12" s="24" t="n"/>
-      <c r="BX12" s="30" t="n">
+      <c r="BX12" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY12" s="27" t="n">
+      <c r="BY12" s="39" t="n">
         <v>-1</v>
       </c>
       <c r="BZ12" s="24" t="inlineStr">
@@ -4548,7 +4579,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J13" s="25" t="n"/>
+      <c r="J13" s="38" t="n"/>
       <c r="K13" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -4557,7 +4588,7 @@
       <c r="L13" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="M13" s="27" t="n">
+      <c r="M13" s="39" t="n">
         <v>1.980392</v>
       </c>
       <c r="N13" s="28" t="n">
@@ -4597,11 +4628,11 @@
       <c r="X13" s="26" t="n">
         <v>7</v>
       </c>
-      <c r="Y13" s="25" t="n"/>
+      <c r="Y13" s="38" t="n"/>
       <c r="Z13" s="26" t="n"/>
       <c r="AA13" s="28" t="n"/>
       <c r="AB13" s="28" t="n"/>
-      <c r="AC13" s="30" t="n">
+      <c r="AC13" s="40" t="n">
         <v>1.2255</v>
       </c>
       <c r="AD13" s="24" t="inlineStr">
@@ -4738,11 +4769,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ13" s="25" t="n"/>
+      <c r="BJ13" s="38" t="n"/>
       <c r="BK13" s="26" t="n">
         <v>-102</v>
       </c>
-      <c r="BL13" s="27" t="n">
+      <c r="BL13" s="39" t="n">
         <v>1.980392</v>
       </c>
       <c r="BM13" s="28" t="n">
@@ -4752,18 +4783,18 @@
         <v>0.502488</v>
       </c>
       <c r="BO13" s="28" t="n"/>
-      <c r="BP13" s="25" t="n"/>
-      <c r="BQ13" s="27" t="n"/>
+      <c r="BP13" s="38" t="n"/>
+      <c r="BQ13" s="39" t="n"/>
       <c r="BR13" s="28" t="n"/>
       <c r="BS13" s="28" t="n"/>
       <c r="BT13" s="28" t="n"/>
-      <c r="BU13" s="25" t="n"/>
+      <c r="BU13" s="38" t="n"/>
       <c r="BV13" s="29" t="n"/>
       <c r="BW13" s="24" t="n"/>
-      <c r="BX13" s="30" t="n">
+      <c r="BX13" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY13" s="27" t="n">
+      <c r="BY13" s="39" t="n">
         <v>0.980392</v>
       </c>
       <c r="BZ13" s="24" t="inlineStr">
@@ -4823,7 +4854,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J14" s="25" t="n"/>
+      <c r="J14" s="38" t="n"/>
       <c r="K14" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -4832,7 +4863,7 @@
       <c r="L14" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="M14" s="27" t="n">
+      <c r="M14" s="39" t="n">
         <v>1.961538</v>
       </c>
       <c r="N14" s="28" t="n">
@@ -4872,11 +4903,11 @@
       <c r="X14" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="Y14" s="25" t="n"/>
+      <c r="Y14" s="38" t="n"/>
       <c r="Z14" s="26" t="n"/>
       <c r="AA14" s="28" t="n"/>
       <c r="AB14" s="28" t="n"/>
-      <c r="AC14" s="30" t="n">
+      <c r="AC14" s="40" t="n">
         <v>-0.75</v>
       </c>
       <c r="AD14" s="24" t="inlineStr">
@@ -5013,11 +5044,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ14" s="25" t="n"/>
+      <c r="BJ14" s="38" t="n"/>
       <c r="BK14" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="BL14" s="27" t="n">
+      <c r="BL14" s="39" t="n">
         <v>1.961538</v>
       </c>
       <c r="BM14" s="28" t="n">
@@ -5027,18 +5058,18 @@
         <v>0.507463</v>
       </c>
       <c r="BO14" s="28" t="n"/>
-      <c r="BP14" s="25" t="n"/>
-      <c r="BQ14" s="27" t="n"/>
+      <c r="BP14" s="38" t="n"/>
+      <c r="BQ14" s="39" t="n"/>
       <c r="BR14" s="28" t="n"/>
       <c r="BS14" s="28" t="n"/>
       <c r="BT14" s="28" t="n"/>
-      <c r="BU14" s="25" t="n"/>
+      <c r="BU14" s="38" t="n"/>
       <c r="BV14" s="29" t="n"/>
       <c r="BW14" s="24" t="n"/>
-      <c r="BX14" s="30" t="n">
+      <c r="BX14" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY14" s="27" t="n">
+      <c r="BY14" s="39" t="n">
         <v>-1</v>
       </c>
       <c r="BZ14" s="24" t="inlineStr">
@@ -5098,7 +5129,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J15" s="25" t="n"/>
+      <c r="J15" s="38" t="n"/>
       <c r="K15" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -5107,7 +5138,7 @@
       <c r="L15" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="M15" s="27" t="n">
+      <c r="M15" s="39" t="n">
         <v>1.961538</v>
       </c>
       <c r="N15" s="28" t="n">
@@ -5147,11 +5178,11 @@
       <c r="X15" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="Y15" s="25" t="n"/>
+      <c r="Y15" s="38" t="n"/>
       <c r="Z15" s="26" t="n"/>
       <c r="AA15" s="28" t="n"/>
       <c r="AB15" s="28" t="n"/>
-      <c r="AC15" s="30" t="n">
+      <c r="AC15" s="40" t="n">
         <v>-1</v>
       </c>
       <c r="AD15" s="24" t="inlineStr">
@@ -5288,11 +5319,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ15" s="25" t="n"/>
+      <c r="BJ15" s="38" t="n"/>
       <c r="BK15" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="BL15" s="27" t="n">
+      <c r="BL15" s="39" t="n">
         <v>1.961538</v>
       </c>
       <c r="BM15" s="28" t="n">
@@ -5302,18 +5333,18 @@
         <v>0.507463</v>
       </c>
       <c r="BO15" s="28" t="n"/>
-      <c r="BP15" s="25" t="n"/>
-      <c r="BQ15" s="27" t="n"/>
+      <c r="BP15" s="38" t="n"/>
+      <c r="BQ15" s="39" t="n"/>
       <c r="BR15" s="28" t="n"/>
       <c r="BS15" s="28" t="n"/>
       <c r="BT15" s="28" t="n"/>
-      <c r="BU15" s="25" t="n"/>
+      <c r="BU15" s="38" t="n"/>
       <c r="BV15" s="29" t="n"/>
       <c r="BW15" s="24" t="n"/>
-      <c r="BX15" s="30" t="n">
+      <c r="BX15" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY15" s="27" t="n">
+      <c r="BY15" s="39" t="n">
         <v>-1</v>
       </c>
       <c r="BZ15" s="24" t="inlineStr">
@@ -5373,7 +5404,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J16" s="25" t="n"/>
+      <c r="J16" s="38" t="n"/>
       <c r="K16" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -5382,7 +5413,7 @@
       <c r="L16" s="26" t="n">
         <v>-111</v>
       </c>
-      <c r="M16" s="27" t="n">
+      <c r="M16" s="39" t="n">
         <v>1.900901</v>
       </c>
       <c r="N16" s="28" t="n">
@@ -5422,11 +5453,11 @@
       <c r="X16" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="Y16" s="25" t="n"/>
+      <c r="Y16" s="38" t="n"/>
       <c r="Z16" s="26" t="n"/>
       <c r="AA16" s="28" t="n"/>
       <c r="AB16" s="28" t="n"/>
-      <c r="AC16" s="30" t="n">
+      <c r="AC16" s="40" t="n">
         <v>-1.5</v>
       </c>
       <c r="AD16" s="24" t="inlineStr">
@@ -5563,11 +5594,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ16" s="25" t="n"/>
+      <c r="BJ16" s="38" t="n"/>
       <c r="BK16" s="26" t="n">
         <v>-111</v>
       </c>
-      <c r="BL16" s="27" t="n">
+      <c r="BL16" s="39" t="n">
         <v>1.900901</v>
       </c>
       <c r="BM16" s="28" t="n">
@@ -5577,18 +5608,18 @@
         <v>0.522388</v>
       </c>
       <c r="BO16" s="28" t="n"/>
-      <c r="BP16" s="25" t="n"/>
-      <c r="BQ16" s="27" t="n"/>
+      <c r="BP16" s="38" t="n"/>
+      <c r="BQ16" s="39" t="n"/>
       <c r="BR16" s="28" t="n"/>
       <c r="BS16" s="28" t="n"/>
       <c r="BT16" s="28" t="n"/>
-      <c r="BU16" s="25" t="n"/>
+      <c r="BU16" s="38" t="n"/>
       <c r="BV16" s="29" t="n"/>
       <c r="BW16" s="24" t="n"/>
-      <c r="BX16" s="30" t="n">
+      <c r="BX16" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY16" s="27" t="n">
+      <c r="BY16" s="39" t="n">
         <v>-1</v>
       </c>
       <c r="BZ16" s="24" t="inlineStr">
@@ -5648,7 +5679,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J17" s="25" t="n"/>
+      <c r="J17" s="38" t="n"/>
       <c r="K17" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -5657,7 +5688,7 @@
       <c r="L17" s="26" t="n">
         <v>-108</v>
       </c>
-      <c r="M17" s="27" t="n">
+      <c r="M17" s="39" t="n">
         <v>1.925926</v>
       </c>
       <c r="N17" s="28" t="n">
@@ -5697,11 +5728,11 @@
       <c r="X17" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="Y17" s="25" t="n"/>
+      <c r="Y17" s="38" t="n"/>
       <c r="Z17" s="26" t="n"/>
       <c r="AA17" s="28" t="n"/>
       <c r="AB17" s="28" t="n"/>
-      <c r="AC17" s="30" t="n">
+      <c r="AC17" s="40" t="n">
         <v>0.9258999999999999</v>
       </c>
       <c r="AD17" s="24" t="inlineStr">
@@ -5838,11 +5869,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ17" s="25" t="n"/>
+      <c r="BJ17" s="38" t="n"/>
       <c r="BK17" s="26" t="n">
         <v>-108</v>
       </c>
-      <c r="BL17" s="27" t="n">
+      <c r="BL17" s="39" t="n">
         <v>1.925926</v>
       </c>
       <c r="BM17" s="28" t="n">
@@ -5852,18 +5883,18 @@
         <v>0.5148509999999999</v>
       </c>
       <c r="BO17" s="28" t="n"/>
-      <c r="BP17" s="25" t="n"/>
-      <c r="BQ17" s="27" t="n"/>
+      <c r="BP17" s="38" t="n"/>
+      <c r="BQ17" s="39" t="n"/>
       <c r="BR17" s="28" t="n"/>
       <c r="BS17" s="28" t="n"/>
       <c r="BT17" s="28" t="n"/>
-      <c r="BU17" s="25" t="n"/>
+      <c r="BU17" s="38" t="n"/>
       <c r="BV17" s="29" t="n"/>
       <c r="BW17" s="24" t="n"/>
-      <c r="BX17" s="30" t="n">
+      <c r="BX17" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY17" s="27" t="n">
+      <c r="BY17" s="39" t="n">
         <v>0.925926</v>
       </c>
       <c r="BZ17" s="24" t="inlineStr">
@@ -5923,7 +5954,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J18" s="25" t="n"/>
+      <c r="J18" s="38" t="n"/>
       <c r="K18" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -5932,7 +5963,7 @@
       <c r="L18" s="26" t="n">
         <v>111</v>
       </c>
-      <c r="M18" s="27" t="n">
+      <c r="M18" s="39" t="n">
         <v>2.11</v>
       </c>
       <c r="N18" s="28" t="n">
@@ -5972,11 +6003,11 @@
       <c r="X18" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="Y18" s="25" t="n"/>
+      <c r="Y18" s="38" t="n"/>
       <c r="Z18" s="26" t="n"/>
       <c r="AA18" s="28" t="n"/>
       <c r="AB18" s="28" t="n"/>
-      <c r="AC18" s="30" t="n">
+      <c r="AC18" s="40" t="n">
         <v>-1.25</v>
       </c>
       <c r="AD18" s="24" t="inlineStr">
@@ -6113,11 +6144,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ18" s="25" t="n"/>
+      <c r="BJ18" s="38" t="n"/>
       <c r="BK18" s="26" t="n">
         <v>111</v>
       </c>
-      <c r="BL18" s="27" t="n">
+      <c r="BL18" s="39" t="n">
         <v>2.11</v>
       </c>
       <c r="BM18" s="28" t="n">
@@ -6127,18 +6158,18 @@
         <v>0.472637</v>
       </c>
       <c r="BO18" s="28" t="n"/>
-      <c r="BP18" s="25" t="n"/>
-      <c r="BQ18" s="27" t="n"/>
+      <c r="BP18" s="38" t="n"/>
+      <c r="BQ18" s="39" t="n"/>
       <c r="BR18" s="28" t="n"/>
       <c r="BS18" s="28" t="n"/>
       <c r="BT18" s="28" t="n"/>
-      <c r="BU18" s="25" t="n"/>
+      <c r="BU18" s="38" t="n"/>
       <c r="BV18" s="29" t="n"/>
       <c r="BW18" s="24" t="n"/>
-      <c r="BX18" s="30" t="n">
+      <c r="BX18" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY18" s="27" t="n">
+      <c r="BY18" s="39" t="n">
         <v>-1</v>
       </c>
       <c r="BZ18" s="24" t="inlineStr">
@@ -6198,7 +6229,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J19" s="25" t="n"/>
+      <c r="J19" s="38" t="n"/>
       <c r="K19" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -6207,7 +6238,7 @@
       <c r="L19" s="26" t="n">
         <v>-125</v>
       </c>
-      <c r="M19" s="27" t="n">
+      <c r="M19" s="39" t="n">
         <v>1.8</v>
       </c>
       <c r="N19" s="28" t="n">
@@ -6247,11 +6278,11 @@
       <c r="X19" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="Y19" s="25" t="n"/>
+      <c r="Y19" s="38" t="n"/>
       <c r="Z19" s="26" t="n"/>
       <c r="AA19" s="28" t="n"/>
       <c r="AB19" s="28" t="n"/>
-      <c r="AC19" s="30" t="n">
+      <c r="AC19" s="40" t="n">
         <v>1.2</v>
       </c>
       <c r="AD19" s="24" t="inlineStr">
@@ -6388,11 +6419,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ19" s="25" t="n"/>
+      <c r="BJ19" s="38" t="n"/>
       <c r="BK19" s="26" t="n">
         <v>-125</v>
       </c>
-      <c r="BL19" s="27" t="n">
+      <c r="BL19" s="39" t="n">
         <v>1.8</v>
       </c>
       <c r="BM19" s="28" t="n">
@@ -6402,18 +6433,18 @@
         <v>0.552239</v>
       </c>
       <c r="BO19" s="28" t="n"/>
-      <c r="BP19" s="25" t="n"/>
-      <c r="BQ19" s="27" t="n"/>
+      <c r="BP19" s="38" t="n"/>
+      <c r="BQ19" s="39" t="n"/>
       <c r="BR19" s="28" t="n"/>
       <c r="BS19" s="28" t="n"/>
       <c r="BT19" s="28" t="n"/>
-      <c r="BU19" s="25" t="n"/>
+      <c r="BU19" s="38" t="n"/>
       <c r="BV19" s="29" t="n"/>
       <c r="BW19" s="24" t="n"/>
-      <c r="BX19" s="30" t="n">
+      <c r="BX19" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY19" s="27" t="n">
+      <c r="BY19" s="39" t="n">
         <v>0.8</v>
       </c>
       <c r="BZ19" s="24" t="inlineStr">
@@ -6473,7 +6504,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J20" s="25" t="n"/>
+      <c r="J20" s="38" t="n"/>
       <c r="K20" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -6482,7 +6513,7 @@
       <c r="L20" s="26" t="n">
         <v>106</v>
       </c>
-      <c r="M20" s="27" t="n">
+      <c r="M20" s="39" t="n">
         <v>2.06</v>
       </c>
       <c r="N20" s="28" t="n">
@@ -6522,11 +6553,11 @@
       <c r="X20" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y20" s="25" t="n"/>
+      <c r="Y20" s="38" t="n"/>
       <c r="Z20" s="26" t="n"/>
       <c r="AA20" s="28" t="n"/>
       <c r="AB20" s="28" t="n"/>
-      <c r="AC20" s="30" t="n">
+      <c r="AC20" s="40" t="n">
         <v>0.795</v>
       </c>
       <c r="AD20" s="24" t="inlineStr">
@@ -6663,11 +6694,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ20" s="25" t="n"/>
+      <c r="BJ20" s="38" t="n"/>
       <c r="BK20" s="26" t="n">
         <v>106</v>
       </c>
-      <c r="BL20" s="27" t="n">
+      <c r="BL20" s="39" t="n">
         <v>2.06</v>
       </c>
       <c r="BM20" s="28" t="n">
@@ -6677,18 +6708,18 @@
         <v>0.482587</v>
       </c>
       <c r="BO20" s="28" t="n"/>
-      <c r="BP20" s="25" t="n"/>
-      <c r="BQ20" s="27" t="n"/>
+      <c r="BP20" s="38" t="n"/>
+      <c r="BQ20" s="39" t="n"/>
       <c r="BR20" s="28" t="n"/>
       <c r="BS20" s="28" t="n"/>
       <c r="BT20" s="28" t="n"/>
-      <c r="BU20" s="25" t="n"/>
+      <c r="BU20" s="38" t="n"/>
       <c r="BV20" s="29" t="n"/>
       <c r="BW20" s="24" t="n"/>
-      <c r="BX20" s="30" t="n">
+      <c r="BX20" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY20" s="27" t="n">
+      <c r="BY20" s="39" t="n">
         <v>1.06</v>
       </c>
       <c r="BZ20" s="24" t="inlineStr">
@@ -6748,7 +6779,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J21" s="25" t="n"/>
+      <c r="J21" s="38" t="n"/>
       <c r="K21" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -6757,7 +6788,7 @@
       <c r="L21" s="26" t="n">
         <v>-106</v>
       </c>
-      <c r="M21" s="27" t="n">
+      <c r="M21" s="39" t="n">
         <v>1.943396</v>
       </c>
       <c r="N21" s="28" t="n">
@@ -6799,11 +6830,11 @@
       <c r="X21" s="26" t="n">
         <v>10</v>
       </c>
-      <c r="Y21" s="25" t="n"/>
+      <c r="Y21" s="38" t="n"/>
       <c r="Z21" s="26" t="n"/>
       <c r="AA21" s="28" t="n"/>
       <c r="AB21" s="28" t="n"/>
-      <c r="AC21" s="30" t="n">
+      <c r="AC21" s="40" t="n">
         <v>0.9434</v>
       </c>
       <c r="AD21" s="24" t="inlineStr">
@@ -6862,11 +6893,11 @@
         </is>
       </c>
       <c r="BI21" s="24" t="n"/>
-      <c r="BJ21" s="25" t="n"/>
+      <c r="BJ21" s="38" t="n"/>
       <c r="BK21" s="26" t="n">
         <v>-106</v>
       </c>
-      <c r="BL21" s="27" t="n">
+      <c r="BL21" s="39" t="n">
         <v>1.943396</v>
       </c>
       <c r="BM21" s="28" t="n">
@@ -6876,16 +6907,16 @@
         <v>0.5124379999999999</v>
       </c>
       <c r="BO21" s="28" t="n"/>
-      <c r="BP21" s="25" t="n"/>
-      <c r="BQ21" s="27" t="n"/>
+      <c r="BP21" s="38" t="n"/>
+      <c r="BQ21" s="39" t="n"/>
       <c r="BR21" s="28" t="n"/>
       <c r="BS21" s="28" t="n"/>
       <c r="BT21" s="28" t="n"/>
-      <c r="BU21" s="25" t="n"/>
+      <c r="BU21" s="38" t="n"/>
       <c r="BV21" s="29" t="n"/>
       <c r="BW21" s="24" t="n"/>
-      <c r="BX21" s="30" t="n"/>
-      <c r="BY21" s="27" t="n"/>
+      <c r="BX21" s="40" t="n"/>
+      <c r="BY21" s="39" t="n"/>
       <c r="BZ21" s="24" t="n"/>
       <c r="CA21" s="31" t="n"/>
     </row>
@@ -6935,7 +6966,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J22" s="25" t="n"/>
+      <c r="J22" s="38" t="n"/>
       <c r="K22" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -6944,7 +6975,7 @@
       <c r="L22" s="26" t="n">
         <v>-106</v>
       </c>
-      <c r="M22" s="27" t="n">
+      <c r="M22" s="39" t="n">
         <v>1.943396</v>
       </c>
       <c r="N22" s="28" t="n">
@@ -6986,11 +7017,11 @@
       <c r="X22" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="Y22" s="25" t="n"/>
+      <c r="Y22" s="38" t="n"/>
       <c r="Z22" s="26" t="n"/>
       <c r="AA22" s="28" t="n"/>
       <c r="AB22" s="28" t="n"/>
-      <c r="AC22" s="30" t="n">
+      <c r="AC22" s="40" t="n">
         <v>0.9434</v>
       </c>
       <c r="AD22" s="24" t="inlineStr">
@@ -7049,11 +7080,11 @@
         </is>
       </c>
       <c r="BI22" s="24" t="n"/>
-      <c r="BJ22" s="25" t="n"/>
+      <c r="BJ22" s="38" t="n"/>
       <c r="BK22" s="26" t="n">
         <v>-106</v>
       </c>
-      <c r="BL22" s="27" t="n">
+      <c r="BL22" s="39" t="n">
         <v>1.943396</v>
       </c>
       <c r="BM22" s="28" t="n">
@@ -7063,16 +7094,16 @@
         <v>0.5124379999999999</v>
       </c>
       <c r="BO22" s="28" t="n"/>
-      <c r="BP22" s="25" t="n"/>
-      <c r="BQ22" s="27" t="n"/>
+      <c r="BP22" s="38" t="n"/>
+      <c r="BQ22" s="39" t="n"/>
       <c r="BR22" s="28" t="n"/>
       <c r="BS22" s="28" t="n"/>
       <c r="BT22" s="28" t="n"/>
-      <c r="BU22" s="25" t="n"/>
+      <c r="BU22" s="38" t="n"/>
       <c r="BV22" s="29" t="n"/>
       <c r="BW22" s="24" t="n"/>
-      <c r="BX22" s="30" t="n"/>
-      <c r="BY22" s="27" t="n"/>
+      <c r="BX22" s="40" t="n"/>
+      <c r="BY22" s="39" t="n"/>
       <c r="BZ22" s="24" t="n"/>
       <c r="CA22" s="31" t="n"/>
     </row>
@@ -7122,7 +7153,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J23" s="25" t="n"/>
+      <c r="J23" s="38" t="n"/>
       <c r="K23" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -7131,7 +7162,7 @@
       <c r="L23" s="26" t="n">
         <v>-141</v>
       </c>
-      <c r="M23" s="27" t="n">
+      <c r="M23" s="39" t="n">
         <v>1.70922</v>
       </c>
       <c r="N23" s="28" t="n">
@@ -7173,11 +7204,11 @@
       <c r="X23" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y23" s="25" t="n"/>
+      <c r="Y23" s="38" t="n"/>
       <c r="Z23" s="26" t="n"/>
       <c r="AA23" s="28" t="n"/>
       <c r="AB23" s="28" t="n"/>
-      <c r="AC23" s="30" t="n">
+      <c r="AC23" s="40" t="n">
         <v>1.2411</v>
       </c>
       <c r="AD23" s="24" t="inlineStr">
@@ -7236,11 +7267,11 @@
         </is>
       </c>
       <c r="BI23" s="24" t="n"/>
-      <c r="BJ23" s="25" t="n"/>
+      <c r="BJ23" s="38" t="n"/>
       <c r="BK23" s="26" t="n">
         <v>-141</v>
       </c>
-      <c r="BL23" s="27" t="n">
+      <c r="BL23" s="39" t="n">
         <v>1.70922</v>
       </c>
       <c r="BM23" s="28" t="n">
@@ -7250,16 +7281,16 @@
         <v>0.58209</v>
       </c>
       <c r="BO23" s="28" t="n"/>
-      <c r="BP23" s="25" t="n"/>
-      <c r="BQ23" s="27" t="n"/>
+      <c r="BP23" s="38" t="n"/>
+      <c r="BQ23" s="39" t="n"/>
       <c r="BR23" s="28" t="n"/>
       <c r="BS23" s="28" t="n"/>
       <c r="BT23" s="28" t="n"/>
-      <c r="BU23" s="25" t="n"/>
+      <c r="BU23" s="38" t="n"/>
       <c r="BV23" s="29" t="n"/>
       <c r="BW23" s="24" t="n"/>
-      <c r="BX23" s="30" t="n"/>
-      <c r="BY23" s="27" t="n"/>
+      <c r="BX23" s="40" t="n"/>
+      <c r="BY23" s="39" t="n"/>
       <c r="BZ23" s="24" t="n"/>
       <c r="CA23" s="31" t="n"/>
     </row>
@@ -7309,7 +7340,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J24" s="25" t="n"/>
+      <c r="J24" s="38" t="n"/>
       <c r="K24" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -7318,7 +7349,7 @@
       <c r="L24" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="M24" s="27" t="n">
+      <c r="M24" s="39" t="n">
         <v>1.75188</v>
       </c>
       <c r="N24" s="28" t="n">
@@ -7360,11 +7391,11 @@
       <c r="X24" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y24" s="25" t="n"/>
+      <c r="Y24" s="38" t="n"/>
       <c r="Z24" s="26" t="n"/>
       <c r="AA24" s="28" t="n"/>
       <c r="AB24" s="28" t="n"/>
-      <c r="AC24" s="30" t="n">
+      <c r="AC24" s="40" t="n">
         <v>-1.5</v>
       </c>
       <c r="AD24" s="24" t="inlineStr">
@@ -7423,11 +7454,11 @@
         </is>
       </c>
       <c r="BI24" s="24" t="n"/>
-      <c r="BJ24" s="25" t="n"/>
+      <c r="BJ24" s="38" t="n"/>
       <c r="BK24" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="BL24" s="27" t="n">
+      <c r="BL24" s="39" t="n">
         <v>1.75188</v>
       </c>
       <c r="BM24" s="28" t="n">
@@ -7437,16 +7468,16 @@
         <v>0.567164</v>
       </c>
       <c r="BO24" s="28" t="n"/>
-      <c r="BP24" s="25" t="n"/>
-      <c r="BQ24" s="27" t="n"/>
+      <c r="BP24" s="38" t="n"/>
+      <c r="BQ24" s="39" t="n"/>
       <c r="BR24" s="28" t="n"/>
       <c r="BS24" s="28" t="n"/>
       <c r="BT24" s="28" t="n"/>
-      <c r="BU24" s="25" t="n"/>
+      <c r="BU24" s="38" t="n"/>
       <c r="BV24" s="29" t="n"/>
       <c r="BW24" s="24" t="n"/>
-      <c r="BX24" s="30" t="n"/>
-      <c r="BY24" s="27" t="n"/>
+      <c r="BX24" s="40" t="n"/>
+      <c r="BY24" s="39" t="n"/>
       <c r="BZ24" s="24" t="n"/>
       <c r="CA24" s="31" t="n"/>
     </row>
@@ -7496,7 +7527,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J25" s="25" t="n"/>
+      <c r="J25" s="38" t="n"/>
       <c r="K25" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -7505,7 +7536,7 @@
       <c r="L25" s="26" t="n">
         <v>104</v>
       </c>
-      <c r="M25" s="27" t="n">
+      <c r="M25" s="39" t="n">
         <v>2.04</v>
       </c>
       <c r="N25" s="28" t="n">
@@ -7547,11 +7578,11 @@
       <c r="X25" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y25" s="25" t="n"/>
+      <c r="Y25" s="38" t="n"/>
       <c r="Z25" s="26" t="n"/>
       <c r="AA25" s="28" t="n"/>
       <c r="AB25" s="28" t="n"/>
-      <c r="AC25" s="30" t="n">
+      <c r="AC25" s="40" t="n">
         <v>1.3</v>
       </c>
       <c r="AD25" s="24" t="inlineStr">
@@ -7610,11 +7641,11 @@
         </is>
       </c>
       <c r="BI25" s="24" t="n"/>
-      <c r="BJ25" s="25" t="n"/>
+      <c r="BJ25" s="38" t="n"/>
       <c r="BK25" s="26" t="n">
         <v>104</v>
       </c>
-      <c r="BL25" s="27" t="n">
+      <c r="BL25" s="39" t="n">
         <v>2.04</v>
       </c>
       <c r="BM25" s="28" t="n">
@@ -7624,16 +7655,16 @@
         <v>0.487562</v>
       </c>
       <c r="BO25" s="28" t="n"/>
-      <c r="BP25" s="25" t="n"/>
-      <c r="BQ25" s="27" t="n"/>
+      <c r="BP25" s="38" t="n"/>
+      <c r="BQ25" s="39" t="n"/>
       <c r="BR25" s="28" t="n"/>
       <c r="BS25" s="28" t="n"/>
       <c r="BT25" s="28" t="n"/>
-      <c r="BU25" s="25" t="n"/>
+      <c r="BU25" s="38" t="n"/>
       <c r="BV25" s="29" t="n"/>
       <c r="BW25" s="24" t="n"/>
-      <c r="BX25" s="30" t="n"/>
-      <c r="BY25" s="27" t="n"/>
+      <c r="BX25" s="40" t="n"/>
+      <c r="BY25" s="39" t="n"/>
       <c r="BZ25" s="24" t="n"/>
       <c r="CA25" s="31" t="n"/>
     </row>
@@ -7683,7 +7714,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J26" s="25" t="n"/>
+      <c r="J26" s="38" t="n"/>
       <c r="K26" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -7692,7 +7723,7 @@
       <c r="L26" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="M26" s="27" t="n">
+      <c r="M26" s="39" t="n">
         <v>1.961538</v>
       </c>
       <c r="N26" s="28" t="n">
@@ -7734,11 +7765,11 @@
       <c r="X26" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="Y26" s="25" t="n"/>
+      <c r="Y26" s="38" t="n"/>
       <c r="Z26" s="26" t="n"/>
       <c r="AA26" s="28" t="n"/>
       <c r="AB26" s="28" t="n"/>
-      <c r="AC26" s="30" t="n">
+      <c r="AC26" s="40" t="n">
         <v>0.9615</v>
       </c>
       <c r="AD26" s="24" t="inlineStr">
@@ -7797,11 +7828,11 @@
         </is>
       </c>
       <c r="BI26" s="24" t="n"/>
-      <c r="BJ26" s="25" t="n"/>
+      <c r="BJ26" s="38" t="n"/>
       <c r="BK26" s="26" t="n">
         <v>-104</v>
       </c>
-      <c r="BL26" s="27" t="n">
+      <c r="BL26" s="39" t="n">
         <v>1.961538</v>
       </c>
       <c r="BM26" s="28" t="n">
@@ -7811,16 +7842,16 @@
         <v>0.507463</v>
       </c>
       <c r="BO26" s="28" t="n"/>
-      <c r="BP26" s="25" t="n"/>
-      <c r="BQ26" s="27" t="n"/>
+      <c r="BP26" s="38" t="n"/>
+      <c r="BQ26" s="39" t="n"/>
       <c r="BR26" s="28" t="n"/>
       <c r="BS26" s="28" t="n"/>
       <c r="BT26" s="28" t="n"/>
-      <c r="BU26" s="25" t="n"/>
+      <c r="BU26" s="38" t="n"/>
       <c r="BV26" s="29" t="n"/>
       <c r="BW26" s="24" t="n"/>
-      <c r="BX26" s="30" t="n"/>
-      <c r="BY26" s="27" t="n"/>
+      <c r="BX26" s="40" t="n"/>
+      <c r="BY26" s="39" t="n"/>
       <c r="BZ26" s="24" t="n"/>
       <c r="CA26" s="31" t="n"/>
     </row>
@@ -7870,7 +7901,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J27" s="25" t="n"/>
+      <c r="J27" s="38" t="n"/>
       <c r="K27" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -7879,7 +7910,7 @@
       <c r="L27" s="26" t="n">
         <v>120</v>
       </c>
-      <c r="M27" s="27" t="n">
+      <c r="M27" s="39" t="n">
         <v>2.2</v>
       </c>
       <c r="N27" s="28" t="n">
@@ -7921,11 +7952,11 @@
       <c r="X27" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="Y27" s="25" t="n"/>
+      <c r="Y27" s="38" t="n"/>
       <c r="Z27" s="26" t="n"/>
       <c r="AA27" s="28" t="n"/>
       <c r="AB27" s="28" t="n"/>
-      <c r="AC27" s="30" t="n">
+      <c r="AC27" s="40" t="n">
         <v>-0.75</v>
       </c>
       <c r="AD27" s="24" t="inlineStr">
@@ -7984,11 +8015,11 @@
         </is>
       </c>
       <c r="BI27" s="24" t="n"/>
-      <c r="BJ27" s="25" t="n"/>
+      <c r="BJ27" s="38" t="n"/>
       <c r="BK27" s="26" t="n">
         <v>120</v>
       </c>
-      <c r="BL27" s="27" t="n">
+      <c r="BL27" s="39" t="n">
         <v>2.2</v>
       </c>
       <c r="BM27" s="28" t="n">
@@ -7998,16 +8029,16 @@
         <v>0.452736</v>
       </c>
       <c r="BO27" s="28" t="n"/>
-      <c r="BP27" s="25" t="n"/>
-      <c r="BQ27" s="27" t="n"/>
+      <c r="BP27" s="38" t="n"/>
+      <c r="BQ27" s="39" t="n"/>
       <c r="BR27" s="28" t="n"/>
       <c r="BS27" s="28" t="n"/>
       <c r="BT27" s="28" t="n"/>
-      <c r="BU27" s="25" t="n"/>
+      <c r="BU27" s="38" t="n"/>
       <c r="BV27" s="29" t="n"/>
       <c r="BW27" s="24" t="n"/>
-      <c r="BX27" s="30" t="n"/>
-      <c r="BY27" s="27" t="n"/>
+      <c r="BX27" s="40" t="n"/>
+      <c r="BY27" s="39" t="n"/>
       <c r="BZ27" s="24" t="n"/>
       <c r="CA27" s="31" t="n"/>
     </row>
@@ -8057,7 +8088,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J28" s="25" t="n"/>
+      <c r="J28" s="38" t="n"/>
       <c r="K28" s="24" t="inlineStr">
         <is>
           <t>polymarket</t>
@@ -8066,7 +8097,7 @@
       <c r="L28" s="26" t="n">
         <v>100</v>
       </c>
-      <c r="M28" s="27" t="n">
+      <c r="M28" s="39" t="n">
         <v>2</v>
       </c>
       <c r="N28" s="28" t="n">
@@ -8108,11 +8139,11 @@
       <c r="X28" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="Y28" s="25" t="n"/>
+      <c r="Y28" s="38" t="n"/>
       <c r="Z28" s="26" t="n"/>
       <c r="AA28" s="28" t="n"/>
       <c r="AB28" s="28" t="n"/>
-      <c r="AC28" s="30" t="n">
+      <c r="AC28" s="40" t="n">
         <v>-0.75</v>
       </c>
       <c r="AD28" s="24" t="inlineStr">
@@ -8171,11 +8202,11 @@
         </is>
       </c>
       <c r="BI28" s="24" t="n"/>
-      <c r="BJ28" s="25" t="n"/>
+      <c r="BJ28" s="38" t="n"/>
       <c r="BK28" s="26" t="n">
         <v>100</v>
       </c>
-      <c r="BL28" s="27" t="n">
+      <c r="BL28" s="39" t="n">
         <v>2</v>
       </c>
       <c r="BM28" s="28" t="n">
@@ -8185,16 +8216,16 @@
         <v>0.497512</v>
       </c>
       <c r="BO28" s="28" t="n"/>
-      <c r="BP28" s="25" t="n"/>
-      <c r="BQ28" s="27" t="n"/>
+      <c r="BP28" s="38" t="n"/>
+      <c r="BQ28" s="39" t="n"/>
       <c r="BR28" s="28" t="n"/>
       <c r="BS28" s="28" t="n"/>
       <c r="BT28" s="28" t="n"/>
-      <c r="BU28" s="25" t="n"/>
+      <c r="BU28" s="38" t="n"/>
       <c r="BV28" s="29" t="n"/>
       <c r="BW28" s="24" t="n"/>
-      <c r="BX28" s="30" t="n"/>
-      <c r="BY28" s="27" t="n"/>
+      <c r="BX28" s="40" t="n"/>
+      <c r="BY28" s="39" t="n"/>
       <c r="BZ28" s="24" t="n"/>
       <c r="CA28" s="31" t="n"/>
     </row>
@@ -8244,7 +8275,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J29" s="25" t="n"/>
+      <c r="J29" s="38" t="n"/>
       <c r="K29" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -8253,7 +8284,7 @@
       <c r="L29" s="26" t="n">
         <v>108</v>
       </c>
-      <c r="M29" s="27" t="n">
+      <c r="M29" s="39" t="n">
         <v>2.08</v>
       </c>
       <c r="N29" s="28" t="n">
@@ -8293,11 +8324,11 @@
       <c r="X29" s="26" t="n">
         <v>8</v>
       </c>
-      <c r="Y29" s="25" t="n"/>
+      <c r="Y29" s="38" t="n"/>
       <c r="Z29" s="26" t="n"/>
       <c r="AA29" s="28" t="n"/>
       <c r="AB29" s="28" t="n"/>
-      <c r="AC29" s="30" t="n">
+      <c r="AC29" s="40" t="n">
         <v>1.35</v>
       </c>
       <c r="AD29" s="24" t="inlineStr">
@@ -8434,11 +8465,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ29" s="25" t="n"/>
+      <c r="BJ29" s="38" t="n"/>
       <c r="BK29" s="26" t="n">
         <v>108</v>
       </c>
-      <c r="BL29" s="27" t="n">
+      <c r="BL29" s="39" t="n">
         <v>2.08</v>
       </c>
       <c r="BM29" s="28" t="n">
@@ -8448,18 +8479,18 @@
         <v>0.477612</v>
       </c>
       <c r="BO29" s="28" t="n"/>
-      <c r="BP29" s="25" t="n"/>
-      <c r="BQ29" s="27" t="n"/>
+      <c r="BP29" s="38" t="n"/>
+      <c r="BQ29" s="39" t="n"/>
       <c r="BR29" s="28" t="n"/>
       <c r="BS29" s="28" t="n"/>
       <c r="BT29" s="28" t="n"/>
-      <c r="BU29" s="25" t="n"/>
+      <c r="BU29" s="38" t="n"/>
       <c r="BV29" s="29" t="n"/>
       <c r="BW29" s="24" t="n"/>
-      <c r="BX29" s="30" t="n">
+      <c r="BX29" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY29" s="27" t="n">
+      <c r="BY29" s="39" t="n">
         <v>1.08</v>
       </c>
       <c r="BZ29" s="24" t="inlineStr">
@@ -8519,7 +8550,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J30" s="25" t="n"/>
+      <c r="J30" s="38" t="n"/>
       <c r="K30" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -8528,7 +8559,7 @@
       <c r="L30" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="M30" s="27" t="n">
+      <c r="M30" s="39" t="n">
         <v>1.75188</v>
       </c>
       <c r="N30" s="28" t="n">
@@ -8568,11 +8599,11 @@
       <c r="X30" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="Y30" s="25" t="n"/>
+      <c r="Y30" s="38" t="n"/>
       <c r="Z30" s="26" t="n"/>
       <c r="AA30" s="28" t="n"/>
       <c r="AB30" s="28" t="n"/>
-      <c r="AC30" s="30" t="n">
+      <c r="AC30" s="40" t="n">
         <v>1.1278</v>
       </c>
       <c r="AD30" s="24" t="inlineStr">
@@ -8709,11 +8740,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ30" s="25" t="n"/>
+      <c r="BJ30" s="38" t="n"/>
       <c r="BK30" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="BL30" s="27" t="n">
+      <c r="BL30" s="39" t="n">
         <v>1.75188</v>
       </c>
       <c r="BM30" s="28" t="n">
@@ -8723,18 +8754,18 @@
         <v>0.567164</v>
       </c>
       <c r="BO30" s="28" t="n"/>
-      <c r="BP30" s="25" t="n"/>
-      <c r="BQ30" s="27" t="n"/>
+      <c r="BP30" s="38" t="n"/>
+      <c r="BQ30" s="39" t="n"/>
       <c r="BR30" s="28" t="n"/>
       <c r="BS30" s="28" t="n"/>
       <c r="BT30" s="28" t="n"/>
-      <c r="BU30" s="25" t="n"/>
+      <c r="BU30" s="38" t="n"/>
       <c r="BV30" s="29" t="n"/>
       <c r="BW30" s="24" t="n"/>
-      <c r="BX30" s="30" t="n">
+      <c r="BX30" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY30" s="27" t="n">
+      <c r="BY30" s="39" t="n">
         <v>0.75188</v>
       </c>
       <c r="BZ30" s="24" t="inlineStr">
@@ -8794,7 +8825,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J31" s="25" t="n"/>
+      <c r="J31" s="38" t="n"/>
       <c r="K31" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -8803,7 +8834,7 @@
       <c r="L31" s="26" t="n">
         <v>130</v>
       </c>
-      <c r="M31" s="27" t="n">
+      <c r="M31" s="39" t="n">
         <v>2.3</v>
       </c>
       <c r="N31" s="28" t="n">
@@ -8843,11 +8874,11 @@
       <c r="X31" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y31" s="25" t="n"/>
+      <c r="Y31" s="38" t="n"/>
       <c r="Z31" s="26" t="n"/>
       <c r="AA31" s="28" t="n"/>
       <c r="AB31" s="28" t="n"/>
-      <c r="AC31" s="30" t="n">
+      <c r="AC31" s="40" t="n">
         <v>-1</v>
       </c>
       <c r="AD31" s="24" t="inlineStr">
@@ -8984,11 +9015,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ31" s="25" t="n"/>
+      <c r="BJ31" s="38" t="n"/>
       <c r="BK31" s="26" t="n">
         <v>130</v>
       </c>
-      <c r="BL31" s="27" t="n">
+      <c r="BL31" s="39" t="n">
         <v>2.3</v>
       </c>
       <c r="BM31" s="28" t="n">
@@ -8998,18 +9029,18 @@
         <v>0.432836</v>
       </c>
       <c r="BO31" s="28" t="n"/>
-      <c r="BP31" s="25" t="n"/>
-      <c r="BQ31" s="27" t="n"/>
+      <c r="BP31" s="38" t="n"/>
+      <c r="BQ31" s="39" t="n"/>
       <c r="BR31" s="28" t="n"/>
       <c r="BS31" s="28" t="n"/>
       <c r="BT31" s="28" t="n"/>
-      <c r="BU31" s="25" t="n"/>
+      <c r="BU31" s="38" t="n"/>
       <c r="BV31" s="29" t="n"/>
       <c r="BW31" s="24" t="n"/>
-      <c r="BX31" s="30" t="n">
+      <c r="BX31" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY31" s="27" t="n">
+      <c r="BY31" s="39" t="n">
         <v>-1</v>
       </c>
       <c r="BZ31" s="24" t="inlineStr">
@@ -9069,7 +9100,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J32" s="25" t="n"/>
+      <c r="J32" s="38" t="n"/>
       <c r="K32" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -9078,7 +9109,7 @@
       <c r="L32" s="26" t="n">
         <v>115</v>
       </c>
-      <c r="M32" s="27" t="n">
+      <c r="M32" s="39" t="n">
         <v>2.15</v>
       </c>
       <c r="N32" s="28" t="n">
@@ -9118,11 +9149,11 @@
       <c r="X32" s="26" t="n">
         <v>13</v>
       </c>
-      <c r="Y32" s="25" t="n"/>
+      <c r="Y32" s="38" t="n"/>
       <c r="Z32" s="26" t="n"/>
       <c r="AA32" s="28" t="n"/>
       <c r="AB32" s="28" t="n"/>
-      <c r="AC32" s="30" t="n">
+      <c r="AC32" s="40" t="n">
         <v>1.4375</v>
       </c>
       <c r="AD32" s="24" t="inlineStr">
@@ -9259,11 +9290,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ32" s="25" t="n"/>
+      <c r="BJ32" s="38" t="n"/>
       <c r="BK32" s="26" t="n">
         <v>115</v>
       </c>
-      <c r="BL32" s="27" t="n">
+      <c r="BL32" s="39" t="n">
         <v>2.15</v>
       </c>
       <c r="BM32" s="28" t="n">
@@ -9273,18 +9304,18 @@
         <v>0.462687</v>
       </c>
       <c r="BO32" s="28" t="n"/>
-      <c r="BP32" s="25" t="n"/>
-      <c r="BQ32" s="27" t="n"/>
+      <c r="BP32" s="38" t="n"/>
+      <c r="BQ32" s="39" t="n"/>
       <c r="BR32" s="28" t="n"/>
       <c r="BS32" s="28" t="n"/>
       <c r="BT32" s="28" t="n"/>
-      <c r="BU32" s="25" t="n"/>
+      <c r="BU32" s="38" t="n"/>
       <c r="BV32" s="29" t="n"/>
       <c r="BW32" s="24" t="n"/>
-      <c r="BX32" s="30" t="n">
+      <c r="BX32" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY32" s="27" t="n">
+      <c r="BY32" s="39" t="n">
         <v>1.15</v>
       </c>
       <c r="BZ32" s="24" t="inlineStr">
@@ -9344,7 +9375,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J33" s="25" t="n"/>
+      <c r="J33" s="38" t="n"/>
       <c r="K33" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -9353,7 +9384,7 @@
       <c r="L33" s="26" t="n">
         <v>-108</v>
       </c>
-      <c r="M33" s="27" t="n">
+      <c r="M33" s="39" t="n">
         <v>1.925926</v>
       </c>
       <c r="N33" s="28" t="n">
@@ -9393,11 +9424,11 @@
       <c r="X33" s="26" t="n">
         <v>8</v>
       </c>
-      <c r="Y33" s="25" t="n"/>
+      <c r="Y33" s="38" t="n"/>
       <c r="Z33" s="26" t="n"/>
       <c r="AA33" s="28" t="n"/>
       <c r="AB33" s="28" t="n"/>
-      <c r="AC33" s="30" t="n">
+      <c r="AC33" s="40" t="n">
         <v>1.1574</v>
       </c>
       <c r="AD33" s="24" t="inlineStr">
@@ -9534,11 +9565,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ33" s="25" t="n"/>
+      <c r="BJ33" s="38" t="n"/>
       <c r="BK33" s="26" t="n">
         <v>-108</v>
       </c>
-      <c r="BL33" s="27" t="n">
+      <c r="BL33" s="39" t="n">
         <v>1.925926</v>
       </c>
       <c r="BM33" s="28" t="n">
@@ -9548,18 +9579,18 @@
         <v>0.517413</v>
       </c>
       <c r="BO33" s="28" t="n"/>
-      <c r="BP33" s="25" t="n"/>
-      <c r="BQ33" s="27" t="n"/>
+      <c r="BP33" s="38" t="n"/>
+      <c r="BQ33" s="39" t="n"/>
       <c r="BR33" s="28" t="n"/>
       <c r="BS33" s="28" t="n"/>
       <c r="BT33" s="28" t="n"/>
-      <c r="BU33" s="25" t="n"/>
+      <c r="BU33" s="38" t="n"/>
       <c r="BV33" s="29" t="n"/>
       <c r="BW33" s="24" t="n"/>
-      <c r="BX33" s="30" t="n">
+      <c r="BX33" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY33" s="27" t="n">
+      <c r="BY33" s="39" t="n">
         <v>0.925926</v>
       </c>
       <c r="BZ33" s="24" t="inlineStr">
@@ -9619,7 +9650,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J34" s="25" t="n"/>
+      <c r="J34" s="38" t="n"/>
       <c r="K34" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -9628,7 +9659,7 @@
       <c r="L34" s="26" t="n">
         <v>-106</v>
       </c>
-      <c r="M34" s="27" t="n">
+      <c r="M34" s="39" t="n">
         <v>1.943396</v>
       </c>
       <c r="N34" s="28" t="n">
@@ -9654,18 +9685,32 @@
       </c>
       <c r="U34" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V34" s="24" t="n"/>
-      <c r="W34" s="26" t="n"/>
-      <c r="X34" s="26" t="n"/>
-      <c r="Y34" s="25" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V34" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W34" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="X34" s="26" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y34" s="38" t="n"/>
       <c r="Z34" s="26" t="n"/>
       <c r="AA34" s="28" t="n"/>
       <c r="AB34" s="28" t="n"/>
-      <c r="AC34" s="30" t="n"/>
-      <c r="AD34" s="24" t="n"/>
+      <c r="AC34" s="40" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="AD34" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-21T04:41:10.971771Z</t>
+        </is>
+      </c>
       <c r="AE34" s="31" t="inlineStr">
         <is>
           <t>Learned LR call at threshold 0.5500; executable ask 0.5150 (aec-mlb-det-chc-2026-07-20).</t>
@@ -9678,7 +9723,7 @@
       </c>
       <c r="AG34" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH34" s="24" t="n"/>
@@ -9795,11 +9840,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ34" s="25" t="n"/>
+      <c r="BJ34" s="38" t="n"/>
       <c r="BK34" s="26" t="n">
         <v>-106</v>
       </c>
-      <c r="BL34" s="27" t="n">
+      <c r="BL34" s="39" t="n">
         <v>1.943396</v>
       </c>
       <c r="BM34" s="28" t="n">
@@ -9809,16 +9854,16 @@
         <v>0.5124379999999999</v>
       </c>
       <c r="BO34" s="28" t="n"/>
-      <c r="BP34" s="25" t="n"/>
-      <c r="BQ34" s="27" t="n"/>
+      <c r="BP34" s="38" t="n"/>
+      <c r="BQ34" s="39" t="n"/>
       <c r="BR34" s="28" t="n"/>
       <c r="BS34" s="28" t="n"/>
       <c r="BT34" s="28" t="n"/>
-      <c r="BU34" s="25" t="n"/>
+      <c r="BU34" s="38" t="n"/>
       <c r="BV34" s="29" t="n"/>
       <c r="BW34" s="24" t="n"/>
-      <c r="BX34" s="30" t="n"/>
-      <c r="BY34" s="27" t="n"/>
+      <c r="BX34" s="40" t="n"/>
+      <c r="BY34" s="39" t="n"/>
       <c r="BZ34" s="24" t="n"/>
       <c r="CA34" s="31" t="n"/>
     </row>
@@ -9868,7 +9913,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J35" s="25" t="n"/>
+      <c r="J35" s="38" t="n"/>
       <c r="K35" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -9877,7 +9922,7 @@
       <c r="L35" s="26" t="n">
         <v>150</v>
       </c>
-      <c r="M35" s="27" t="n">
+      <c r="M35" s="39" t="n">
         <v>2.5</v>
       </c>
       <c r="N35" s="28" t="n">
@@ -9917,11 +9962,11 @@
       <c r="X35" s="26" t="n">
         <v>98</v>
       </c>
-      <c r="Y35" s="25" t="n"/>
+      <c r="Y35" s="38" t="n"/>
       <c r="Z35" s="26" t="n"/>
       <c r="AA35" s="28" t="n"/>
       <c r="AB35" s="28" t="n"/>
-      <c r="AC35" s="30" t="n">
+      <c r="AC35" s="40" t="n">
         <v>-2</v>
       </c>
       <c r="AD35" s="24" t="inlineStr">
@@ -10058,11 +10103,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ35" s="25" t="n"/>
+      <c r="BJ35" s="38" t="n"/>
       <c r="BK35" s="26" t="n">
         <v>150</v>
       </c>
-      <c r="BL35" s="27" t="n">
+      <c r="BL35" s="39" t="n">
         <v>2.5</v>
       </c>
       <c r="BM35" s="28" t="n">
@@ -10072,18 +10117,18 @@
         <v>0.39604</v>
       </c>
       <c r="BO35" s="28" t="n"/>
-      <c r="BP35" s="25" t="n"/>
-      <c r="BQ35" s="27" t="n"/>
+      <c r="BP35" s="38" t="n"/>
+      <c r="BQ35" s="39" t="n"/>
       <c r="BR35" s="28" t="n"/>
       <c r="BS35" s="28" t="n"/>
       <c r="BT35" s="28" t="n"/>
-      <c r="BU35" s="25" t="n"/>
+      <c r="BU35" s="38" t="n"/>
       <c r="BV35" s="29" t="n"/>
       <c r="BW35" s="24" t="n"/>
-      <c r="BX35" s="30" t="n">
+      <c r="BX35" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY35" s="27" t="n">
+      <c r="BY35" s="39" t="n">
         <v>-1</v>
       </c>
       <c r="BZ35" s="24" t="inlineStr">
@@ -10143,7 +10188,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J36" s="25" t="n"/>
+      <c r="J36" s="38" t="n"/>
       <c r="K36" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -10152,7 +10197,7 @@
       <c r="L36" s="26" t="n">
         <v>-120</v>
       </c>
-      <c r="M36" s="27" t="n">
+      <c r="M36" s="39" t="n">
         <v>1.833333</v>
       </c>
       <c r="N36" s="28" t="n">
@@ -10184,11 +10229,11 @@
       <c r="V36" s="24" t="n"/>
       <c r="W36" s="26" t="n"/>
       <c r="X36" s="26" t="n"/>
-      <c r="Y36" s="25" t="n"/>
+      <c r="Y36" s="38" t="n"/>
       <c r="Z36" s="26" t="n"/>
       <c r="AA36" s="28" t="n"/>
       <c r="AB36" s="28" t="n"/>
-      <c r="AC36" s="30" t="n"/>
+      <c r="AC36" s="40" t="n"/>
       <c r="AD36" s="24" t="n"/>
       <c r="AE36" s="31" t="inlineStr">
         <is>
@@ -10319,11 +10364,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ36" s="25" t="n"/>
+      <c r="BJ36" s="38" t="n"/>
       <c r="BK36" s="26" t="n">
         <v>-120</v>
       </c>
-      <c r="BL36" s="27" t="n">
+      <c r="BL36" s="39" t="n">
         <v>1.833333</v>
       </c>
       <c r="BM36" s="28" t="n">
@@ -10333,16 +10378,16 @@
         <v>0.542289</v>
       </c>
       <c r="BO36" s="28" t="n"/>
-      <c r="BP36" s="25" t="n"/>
-      <c r="BQ36" s="27" t="n"/>
+      <c r="BP36" s="38" t="n"/>
+      <c r="BQ36" s="39" t="n"/>
       <c r="BR36" s="28" t="n"/>
       <c r="BS36" s="28" t="n"/>
       <c r="BT36" s="28" t="n"/>
-      <c r="BU36" s="25" t="n"/>
+      <c r="BU36" s="38" t="n"/>
       <c r="BV36" s="29" t="n"/>
       <c r="BW36" s="24" t="n"/>
-      <c r="BX36" s="30" t="n"/>
-      <c r="BY36" s="27" t="n"/>
+      <c r="BX36" s="40" t="n"/>
+      <c r="BY36" s="39" t="n"/>
       <c r="BZ36" s="24" t="n"/>
       <c r="CA36" s="31" t="n"/>
     </row>
@@ -10392,7 +10437,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J37" s="25" t="n"/>
+      <c r="J37" s="38" t="n"/>
       <c r="K37" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -10401,7 +10446,7 @@
       <c r="L37" s="26" t="n">
         <v>-122</v>
       </c>
-      <c r="M37" s="27" t="n">
+      <c r="M37" s="39" t="n">
         <v>1.819672</v>
       </c>
       <c r="N37" s="28" t="n">
@@ -10433,11 +10478,11 @@
       <c r="V37" s="24" t="n"/>
       <c r="W37" s="26" t="n"/>
       <c r="X37" s="26" t="n"/>
-      <c r="Y37" s="25" t="n"/>
+      <c r="Y37" s="38" t="n"/>
       <c r="Z37" s="26" t="n"/>
       <c r="AA37" s="28" t="n"/>
       <c r="AB37" s="28" t="n"/>
-      <c r="AC37" s="30" t="n"/>
+      <c r="AC37" s="40" t="n"/>
       <c r="AD37" s="24" t="n"/>
       <c r="AE37" s="31" t="inlineStr">
         <is>
@@ -10568,11 +10613,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ37" s="25" t="n"/>
+      <c r="BJ37" s="38" t="n"/>
       <c r="BK37" s="26" t="n">
         <v>-122</v>
       </c>
-      <c r="BL37" s="27" t="n">
+      <c r="BL37" s="39" t="n">
         <v>1.819672</v>
       </c>
       <c r="BM37" s="28" t="n">
@@ -10582,16 +10627,16 @@
         <v>0.547264</v>
       </c>
       <c r="BO37" s="28" t="n"/>
-      <c r="BP37" s="25" t="n"/>
-      <c r="BQ37" s="27" t="n"/>
+      <c r="BP37" s="38" t="n"/>
+      <c r="BQ37" s="39" t="n"/>
       <c r="BR37" s="28" t="n"/>
       <c r="BS37" s="28" t="n"/>
       <c r="BT37" s="28" t="n"/>
-      <c r="BU37" s="25" t="n"/>
+      <c r="BU37" s="38" t="n"/>
       <c r="BV37" s="29" t="n"/>
       <c r="BW37" s="24" t="n"/>
-      <c r="BX37" s="30" t="n"/>
-      <c r="BY37" s="27" t="n"/>
+      <c r="BX37" s="40" t="n"/>
+      <c r="BY37" s="39" t="n"/>
       <c r="BZ37" s="24" t="n"/>
       <c r="CA37" s="31" t="n"/>
     </row>
@@ -10641,7 +10686,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J38" s="25" t="n"/>
+      <c r="J38" s="38" t="n"/>
       <c r="K38" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -10650,7 +10695,7 @@
       <c r="L38" s="26" t="n">
         <v>-147</v>
       </c>
-      <c r="M38" s="27" t="n">
+      <c r="M38" s="39" t="n">
         <v>1.680272</v>
       </c>
       <c r="N38" s="28" t="n">
@@ -10682,11 +10727,11 @@
       <c r="V38" s="24" t="n"/>
       <c r="W38" s="26" t="n"/>
       <c r="X38" s="26" t="n"/>
-      <c r="Y38" s="25" t="n"/>
+      <c r="Y38" s="38" t="n"/>
       <c r="Z38" s="26" t="n"/>
       <c r="AA38" s="28" t="n"/>
       <c r="AB38" s="28" t="n"/>
-      <c r="AC38" s="30" t="n"/>
+      <c r="AC38" s="40" t="n"/>
       <c r="AD38" s="24" t="n"/>
       <c r="AE38" s="31" t="inlineStr">
         <is>
@@ -10817,11 +10862,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ38" s="25" t="n"/>
+      <c r="BJ38" s="38" t="n"/>
       <c r="BK38" s="26" t="n">
         <v>-147</v>
       </c>
-      <c r="BL38" s="27" t="n">
+      <c r="BL38" s="39" t="n">
         <v>1.680272</v>
       </c>
       <c r="BM38" s="28" t="n">
@@ -10831,16 +10876,16 @@
         <v>0.59204</v>
       </c>
       <c r="BO38" s="28" t="n"/>
-      <c r="BP38" s="25" t="n"/>
-      <c r="BQ38" s="27" t="n"/>
+      <c r="BP38" s="38" t="n"/>
+      <c r="BQ38" s="39" t="n"/>
       <c r="BR38" s="28" t="n"/>
       <c r="BS38" s="28" t="n"/>
       <c r="BT38" s="28" t="n"/>
-      <c r="BU38" s="25" t="n"/>
+      <c r="BU38" s="38" t="n"/>
       <c r="BV38" s="29" t="n"/>
       <c r="BW38" s="24" t="n"/>
-      <c r="BX38" s="30" t="n"/>
-      <c r="BY38" s="27" t="n"/>
+      <c r="BX38" s="40" t="n"/>
+      <c r="BY38" s="39" t="n"/>
       <c r="BZ38" s="24" t="n"/>
       <c r="CA38" s="31" t="n"/>
     </row>
@@ -10890,7 +10935,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J39" s="25" t="n"/>
+      <c r="J39" s="38" t="n"/>
       <c r="K39" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -10899,7 +10944,7 @@
       <c r="L39" s="26" t="n">
         <v>-113</v>
       </c>
-      <c r="M39" s="27" t="n">
+      <c r="M39" s="39" t="n">
         <v>1.884956</v>
       </c>
       <c r="N39" s="28" t="n">
@@ -10931,11 +10976,11 @@
       <c r="V39" s="24" t="n"/>
       <c r="W39" s="26" t="n"/>
       <c r="X39" s="26" t="n"/>
-      <c r="Y39" s="25" t="n"/>
+      <c r="Y39" s="38" t="n"/>
       <c r="Z39" s="26" t="n"/>
       <c r="AA39" s="28" t="n"/>
       <c r="AB39" s="28" t="n"/>
-      <c r="AC39" s="30" t="n"/>
+      <c r="AC39" s="40" t="n"/>
       <c r="AD39" s="24" t="n"/>
       <c r="AE39" s="31" t="inlineStr">
         <is>
@@ -11066,11 +11111,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ39" s="25" t="n"/>
+      <c r="BJ39" s="38" t="n"/>
       <c r="BK39" s="26" t="n">
         <v>-113</v>
       </c>
-      <c r="BL39" s="27" t="n">
+      <c r="BL39" s="39" t="n">
         <v>1.884956</v>
       </c>
       <c r="BM39" s="28" t="n">
@@ -11080,16 +11125,16 @@
         <v>0.527363</v>
       </c>
       <c r="BO39" s="28" t="n"/>
-      <c r="BP39" s="25" t="n"/>
-      <c r="BQ39" s="27" t="n"/>
+      <c r="BP39" s="38" t="n"/>
+      <c r="BQ39" s="39" t="n"/>
       <c r="BR39" s="28" t="n"/>
       <c r="BS39" s="28" t="n"/>
       <c r="BT39" s="28" t="n"/>
-      <c r="BU39" s="25" t="n"/>
+      <c r="BU39" s="38" t="n"/>
       <c r="BV39" s="29" t="n"/>
       <c r="BW39" s="24" t="n"/>
-      <c r="BX39" s="30" t="n"/>
-      <c r="BY39" s="27" t="n"/>
+      <c r="BX39" s="40" t="n"/>
+      <c r="BY39" s="39" t="n"/>
       <c r="BZ39" s="24" t="n"/>
       <c r="CA39" s="31" t="n"/>
     </row>
@@ -11139,7 +11184,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J40" s="25" t="n"/>
+      <c r="J40" s="38" t="n"/>
       <c r="K40" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -11148,7 +11193,7 @@
       <c r="L40" s="26" t="n">
         <v>104</v>
       </c>
-      <c r="M40" s="27" t="n">
+      <c r="M40" s="39" t="n">
         <v>2.04</v>
       </c>
       <c r="N40" s="28" t="n">
@@ -11180,11 +11225,11 @@
       <c r="V40" s="24" t="n"/>
       <c r="W40" s="26" t="n"/>
       <c r="X40" s="26" t="n"/>
-      <c r="Y40" s="25" t="n"/>
+      <c r="Y40" s="38" t="n"/>
       <c r="Z40" s="26" t="n"/>
       <c r="AA40" s="28" t="n"/>
       <c r="AB40" s="28" t="n"/>
-      <c r="AC40" s="30" t="n"/>
+      <c r="AC40" s="40" t="n"/>
       <c r="AD40" s="24" t="n"/>
       <c r="AE40" s="31" t="inlineStr">
         <is>
@@ -11315,11 +11360,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ40" s="25" t="n"/>
+      <c r="BJ40" s="38" t="n"/>
       <c r="BK40" s="26" t="n">
         <v>104</v>
       </c>
-      <c r="BL40" s="27" t="n">
+      <c r="BL40" s="39" t="n">
         <v>2.04</v>
       </c>
       <c r="BM40" s="28" t="n">
@@ -11329,16 +11374,16 @@
         <v>0.487562</v>
       </c>
       <c r="BO40" s="28" t="n"/>
-      <c r="BP40" s="25" t="n"/>
-      <c r="BQ40" s="27" t="n"/>
+      <c r="BP40" s="38" t="n"/>
+      <c r="BQ40" s="39" t="n"/>
       <c r="BR40" s="28" t="n"/>
       <c r="BS40" s="28" t="n"/>
       <c r="BT40" s="28" t="n"/>
-      <c r="BU40" s="25" t="n"/>
+      <c r="BU40" s="38" t="n"/>
       <c r="BV40" s="29" t="n"/>
       <c r="BW40" s="24" t="n"/>
-      <c r="BX40" s="30" t="n"/>
-      <c r="BY40" s="27" t="n"/>
+      <c r="BX40" s="40" t="n"/>
+      <c r="BY40" s="39" t="n"/>
       <c r="BZ40" s="24" t="n"/>
       <c r="CA40" s="31" t="n"/>
     </row>
@@ -11388,7 +11433,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J41" s="25" t="n"/>
+      <c r="J41" s="38" t="n"/>
       <c r="K41" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -11397,7 +11442,7 @@
       <c r="L41" s="26" t="n">
         <v>-113</v>
       </c>
-      <c r="M41" s="27" t="n">
+      <c r="M41" s="39" t="n">
         <v>1.884956</v>
       </c>
       <c r="N41" s="28" t="n">
@@ -11429,11 +11474,11 @@
       <c r="V41" s="24" t="n"/>
       <c r="W41" s="26" t="n"/>
       <c r="X41" s="26" t="n"/>
-      <c r="Y41" s="25" t="n"/>
+      <c r="Y41" s="38" t="n"/>
       <c r="Z41" s="26" t="n"/>
       <c r="AA41" s="28" t="n"/>
       <c r="AB41" s="28" t="n"/>
-      <c r="AC41" s="30" t="n"/>
+      <c r="AC41" s="40" t="n"/>
       <c r="AD41" s="24" t="n"/>
       <c r="AE41" s="31" t="inlineStr">
         <is>
@@ -11564,11 +11609,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ41" s="25" t="n"/>
+      <c r="BJ41" s="38" t="n"/>
       <c r="BK41" s="26" t="n">
         <v>-113</v>
       </c>
-      <c r="BL41" s="27" t="n">
+      <c r="BL41" s="39" t="n">
         <v>1.884956</v>
       </c>
       <c r="BM41" s="28" t="n">
@@ -11578,16 +11623,16 @@
         <v>0.527363</v>
       </c>
       <c r="BO41" s="28" t="n"/>
-      <c r="BP41" s="25" t="n"/>
-      <c r="BQ41" s="27" t="n"/>
+      <c r="BP41" s="38" t="n"/>
+      <c r="BQ41" s="39" t="n"/>
       <c r="BR41" s="28" t="n"/>
       <c r="BS41" s="28" t="n"/>
       <c r="BT41" s="28" t="n"/>
-      <c r="BU41" s="25" t="n"/>
+      <c r="BU41" s="38" t="n"/>
       <c r="BV41" s="29" t="n"/>
       <c r="BW41" s="24" t="n"/>
-      <c r="BX41" s="30" t="n"/>
-      <c r="BY41" s="27" t="n"/>
+      <c r="BX41" s="40" t="n"/>
+      <c r="BY41" s="39" t="n"/>
       <c r="BZ41" s="24" t="n"/>
       <c r="CA41" s="31" t="n"/>
     </row>
@@ -11637,7 +11682,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J42" s="25" t="n"/>
+      <c r="J42" s="38" t="n"/>
       <c r="K42" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -11646,7 +11691,7 @@
       <c r="L42" s="26" t="n">
         <v>203</v>
       </c>
-      <c r="M42" s="27" t="n">
+      <c r="M42" s="39" t="n">
         <v>3.03</v>
       </c>
       <c r="N42" s="28" t="n">
@@ -11678,11 +11723,11 @@
       <c r="V42" s="24" t="n"/>
       <c r="W42" s="26" t="n"/>
       <c r="X42" s="26" t="n"/>
-      <c r="Y42" s="25" t="n"/>
+      <c r="Y42" s="38" t="n"/>
       <c r="Z42" s="26" t="n"/>
       <c r="AA42" s="28" t="n"/>
       <c r="AB42" s="28" t="n"/>
-      <c r="AC42" s="30" t="n"/>
+      <c r="AC42" s="40" t="n"/>
       <c r="AD42" s="24" t="n"/>
       <c r="AE42" s="31" t="inlineStr">
         <is>
@@ -11813,11 +11858,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ42" s="25" t="n"/>
+      <c r="BJ42" s="38" t="n"/>
       <c r="BK42" s="26" t="n">
         <v>203</v>
       </c>
-      <c r="BL42" s="27" t="n">
+      <c r="BL42" s="39" t="n">
         <v>3.03</v>
       </c>
       <c r="BM42" s="28" t="n">
@@ -11825,16 +11870,16 @@
       </c>
       <c r="BN42" s="28" t="n"/>
       <c r="BO42" s="28" t="n"/>
-      <c r="BP42" s="25" t="n"/>
-      <c r="BQ42" s="27" t="n"/>
+      <c r="BP42" s="38" t="n"/>
+      <c r="BQ42" s="39" t="n"/>
       <c r="BR42" s="28" t="n"/>
       <c r="BS42" s="28" t="n"/>
       <c r="BT42" s="28" t="n"/>
-      <c r="BU42" s="25" t="n"/>
+      <c r="BU42" s="38" t="n"/>
       <c r="BV42" s="29" t="n"/>
       <c r="BW42" s="24" t="n"/>
-      <c r="BX42" s="30" t="n"/>
-      <c r="BY42" s="27" t="n"/>
+      <c r="BX42" s="40" t="n"/>
+      <c r="BY42" s="39" t="n"/>
       <c r="BZ42" s="24" t="n"/>
       <c r="CA42" s="31" t="n"/>
     </row>
@@ -11884,7 +11929,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J43" s="25" t="n"/>
+      <c r="J43" s="38" t="n"/>
       <c r="K43" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -11893,7 +11938,7 @@
       <c r="L43" s="26" t="n">
         <v>100</v>
       </c>
-      <c r="M43" s="27" t="n">
+      <c r="M43" s="39" t="n">
         <v>2</v>
       </c>
       <c r="N43" s="28" t="n">
@@ -11925,11 +11970,11 @@
       <c r="V43" s="24" t="n"/>
       <c r="W43" s="26" t="n"/>
       <c r="X43" s="26" t="n"/>
-      <c r="Y43" s="25" t="n"/>
+      <c r="Y43" s="38" t="n"/>
       <c r="Z43" s="26" t="n"/>
       <c r="AA43" s="28" t="n"/>
       <c r="AB43" s="28" t="n"/>
-      <c r="AC43" s="30" t="n"/>
+      <c r="AC43" s="40" t="n"/>
       <c r="AD43" s="24" t="n"/>
       <c r="AE43" s="31" t="inlineStr">
         <is>
@@ -12060,11 +12105,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ43" s="25" t="n"/>
+      <c r="BJ43" s="38" t="n"/>
       <c r="BK43" s="26" t="n">
         <v>100</v>
       </c>
-      <c r="BL43" s="27" t="n">
+      <c r="BL43" s="39" t="n">
         <v>2</v>
       </c>
       <c r="BM43" s="28" t="n">
@@ -12072,16 +12117,16 @@
       </c>
       <c r="BN43" s="28" t="n"/>
       <c r="BO43" s="28" t="n"/>
-      <c r="BP43" s="25" t="n"/>
-      <c r="BQ43" s="27" t="n"/>
+      <c r="BP43" s="38" t="n"/>
+      <c r="BQ43" s="39" t="n"/>
       <c r="BR43" s="28" t="n"/>
       <c r="BS43" s="28" t="n"/>
       <c r="BT43" s="28" t="n"/>
-      <c r="BU43" s="25" t="n"/>
+      <c r="BU43" s="38" t="n"/>
       <c r="BV43" s="29" t="n"/>
       <c r="BW43" s="24" t="n"/>
-      <c r="BX43" s="30" t="n"/>
-      <c r="BY43" s="27" t="n"/>
+      <c r="BX43" s="40" t="n"/>
+      <c r="BY43" s="39" t="n"/>
       <c r="BZ43" s="24" t="n"/>
       <c r="CA43" s="31" t="n"/>
     </row>
@@ -12131,7 +12176,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J44" s="25" t="n"/>
+      <c r="J44" s="38" t="n"/>
       <c r="K44" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -12140,7 +12185,7 @@
       <c r="L44" s="26" t="n">
         <v>-186</v>
       </c>
-      <c r="M44" s="27" t="n">
+      <c r="M44" s="39" t="n">
         <v>1.537634</v>
       </c>
       <c r="N44" s="28" t="n">
@@ -12172,11 +12217,11 @@
       <c r="V44" s="24" t="n"/>
       <c r="W44" s="26" t="n"/>
       <c r="X44" s="26" t="n"/>
-      <c r="Y44" s="25" t="n"/>
+      <c r="Y44" s="38" t="n"/>
       <c r="Z44" s="26" t="n"/>
       <c r="AA44" s="28" t="n"/>
       <c r="AB44" s="28" t="n"/>
-      <c r="AC44" s="30" t="n"/>
+      <c r="AC44" s="40" t="n"/>
       <c r="AD44" s="24" t="n"/>
       <c r="AE44" s="31" t="inlineStr">
         <is>
@@ -12307,11 +12352,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ44" s="25" t="n"/>
+      <c r="BJ44" s="38" t="n"/>
       <c r="BK44" s="26" t="n">
         <v>-186</v>
       </c>
-      <c r="BL44" s="27" t="n">
+      <c r="BL44" s="39" t="n">
         <v>1.537634</v>
       </c>
       <c r="BM44" s="28" t="n">
@@ -12319,16 +12364,16 @@
       </c>
       <c r="BN44" s="28" t="n"/>
       <c r="BO44" s="28" t="n"/>
-      <c r="BP44" s="25" t="n"/>
-      <c r="BQ44" s="27" t="n"/>
+      <c r="BP44" s="38" t="n"/>
+      <c r="BQ44" s="39" t="n"/>
       <c r="BR44" s="28" t="n"/>
       <c r="BS44" s="28" t="n"/>
       <c r="BT44" s="28" t="n"/>
-      <c r="BU44" s="25" t="n"/>
+      <c r="BU44" s="38" t="n"/>
       <c r="BV44" s="29" t="n"/>
       <c r="BW44" s="24" t="n"/>
-      <c r="BX44" s="30" t="n"/>
-      <c r="BY44" s="27" t="n"/>
+      <c r="BX44" s="40" t="n"/>
+      <c r="BY44" s="39" t="n"/>
       <c r="BZ44" s="24" t="n"/>
       <c r="CA44" s="31" t="n"/>
     </row>
@@ -12378,7 +12423,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J45" s="25" t="n"/>
+      <c r="J45" s="38" t="n"/>
       <c r="K45" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -12387,7 +12432,7 @@
       <c r="L45" s="26" t="n">
         <v>117</v>
       </c>
-      <c r="M45" s="27" t="n">
+      <c r="M45" s="39" t="n">
         <v>2.17</v>
       </c>
       <c r="N45" s="28" t="n">
@@ -12419,11 +12464,11 @@
       <c r="V45" s="24" t="n"/>
       <c r="W45" s="26" t="n"/>
       <c r="X45" s="26" t="n"/>
-      <c r="Y45" s="25" t="n"/>
+      <c r="Y45" s="38" t="n"/>
       <c r="Z45" s="26" t="n"/>
       <c r="AA45" s="28" t="n"/>
       <c r="AB45" s="28" t="n"/>
-      <c r="AC45" s="30" t="n"/>
+      <c r="AC45" s="40" t="n"/>
       <c r="AD45" s="24" t="n"/>
       <c r="AE45" s="31" t="inlineStr">
         <is>
@@ -12554,11 +12599,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ45" s="25" t="n"/>
+      <c r="BJ45" s="38" t="n"/>
       <c r="BK45" s="26" t="n">
         <v>117</v>
       </c>
-      <c r="BL45" s="27" t="n">
+      <c r="BL45" s="39" t="n">
         <v>2.17</v>
       </c>
       <c r="BM45" s="28" t="n">
@@ -12566,16 +12611,16 @@
       </c>
       <c r="BN45" s="28" t="n"/>
       <c r="BO45" s="28" t="n"/>
-      <c r="BP45" s="25" t="n"/>
-      <c r="BQ45" s="27" t="n"/>
+      <c r="BP45" s="38" t="n"/>
+      <c r="BQ45" s="39" t="n"/>
       <c r="BR45" s="28" t="n"/>
       <c r="BS45" s="28" t="n"/>
       <c r="BT45" s="28" t="n"/>
-      <c r="BU45" s="25" t="n"/>
+      <c r="BU45" s="38" t="n"/>
       <c r="BV45" s="29" t="n"/>
       <c r="BW45" s="24" t="n"/>
-      <c r="BX45" s="30" t="n"/>
-      <c r="BY45" s="27" t="n"/>
+      <c r="BX45" s="40" t="n"/>
+      <c r="BY45" s="39" t="n"/>
       <c r="BZ45" s="24" t="n"/>
       <c r="CA45" s="31" t="n"/>
     </row>
@@ -12625,7 +12670,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J46" s="25" t="n"/>
+      <c r="J46" s="38" t="n"/>
       <c r="K46" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -12634,7 +12679,7 @@
       <c r="L46" s="26" t="n">
         <v>122</v>
       </c>
-      <c r="M46" s="27" t="n">
+      <c r="M46" s="39" t="n">
         <v>2.22</v>
       </c>
       <c r="N46" s="28" t="n">
@@ -12666,11 +12711,11 @@
       <c r="V46" s="24" t="n"/>
       <c r="W46" s="26" t="n"/>
       <c r="X46" s="26" t="n"/>
-      <c r="Y46" s="25" t="n"/>
+      <c r="Y46" s="38" t="n"/>
       <c r="Z46" s="26" t="n"/>
       <c r="AA46" s="28" t="n"/>
       <c r="AB46" s="28" t="n"/>
-      <c r="AC46" s="30" t="n"/>
+      <c r="AC46" s="40" t="n"/>
       <c r="AD46" s="24" t="n"/>
       <c r="AE46" s="31" t="inlineStr">
         <is>
@@ -12801,11 +12846,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ46" s="25" t="n"/>
+      <c r="BJ46" s="38" t="n"/>
       <c r="BK46" s="26" t="n">
         <v>122</v>
       </c>
-      <c r="BL46" s="27" t="n">
+      <c r="BL46" s="39" t="n">
         <v>2.22</v>
       </c>
       <c r="BM46" s="28" t="n">
@@ -12813,16 +12858,16 @@
       </c>
       <c r="BN46" s="28" t="n"/>
       <c r="BO46" s="28" t="n"/>
-      <c r="BP46" s="25" t="n"/>
-      <c r="BQ46" s="27" t="n"/>
+      <c r="BP46" s="38" t="n"/>
+      <c r="BQ46" s="39" t="n"/>
       <c r="BR46" s="28" t="n"/>
       <c r="BS46" s="28" t="n"/>
       <c r="BT46" s="28" t="n"/>
-      <c r="BU46" s="25" t="n"/>
+      <c r="BU46" s="38" t="n"/>
       <c r="BV46" s="29" t="n"/>
       <c r="BW46" s="24" t="n"/>
-      <c r="BX46" s="30" t="n"/>
-      <c r="BY46" s="27" t="n"/>
+      <c r="BX46" s="40" t="n"/>
+      <c r="BY46" s="39" t="n"/>
       <c r="BZ46" s="24" t="n"/>
       <c r="CA46" s="31" t="n"/>
     </row>
@@ -12872,7 +12917,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J47" s="25" t="n"/>
+      <c r="J47" s="38" t="n"/>
       <c r="K47" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -12881,7 +12926,7 @@
       <c r="L47" s="26" t="n">
         <v>100</v>
       </c>
-      <c r="M47" s="27" t="n">
+      <c r="M47" s="39" t="n">
         <v>2</v>
       </c>
       <c r="N47" s="28" t="n">
@@ -12913,11 +12958,11 @@
       <c r="V47" s="24" t="n"/>
       <c r="W47" s="26" t="n"/>
       <c r="X47" s="26" t="n"/>
-      <c r="Y47" s="25" t="n"/>
+      <c r="Y47" s="38" t="n"/>
       <c r="Z47" s="26" t="n"/>
       <c r="AA47" s="28" t="n"/>
       <c r="AB47" s="28" t="n"/>
-      <c r="AC47" s="30" t="n"/>
+      <c r="AC47" s="40" t="n"/>
       <c r="AD47" s="24" t="n"/>
       <c r="AE47" s="31" t="inlineStr">
         <is>
@@ -13048,11 +13093,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ47" s="25" t="n"/>
+      <c r="BJ47" s="38" t="n"/>
       <c r="BK47" s="26" t="n">
         <v>100</v>
       </c>
-      <c r="BL47" s="27" t="n">
+      <c r="BL47" s="39" t="n">
         <v>2</v>
       </c>
       <c r="BM47" s="28" t="n">
@@ -13060,16 +13105,16 @@
       </c>
       <c r="BN47" s="28" t="n"/>
       <c r="BO47" s="28" t="n"/>
-      <c r="BP47" s="25" t="n"/>
-      <c r="BQ47" s="27" t="n"/>
+      <c r="BP47" s="38" t="n"/>
+      <c r="BQ47" s="39" t="n"/>
       <c r="BR47" s="28" t="n"/>
       <c r="BS47" s="28" t="n"/>
       <c r="BT47" s="28" t="n"/>
-      <c r="BU47" s="25" t="n"/>
+      <c r="BU47" s="38" t="n"/>
       <c r="BV47" s="29" t="n"/>
       <c r="BW47" s="24" t="n"/>
-      <c r="BX47" s="30" t="n"/>
-      <c r="BY47" s="27" t="n"/>
+      <c r="BX47" s="40" t="n"/>
+      <c r="BY47" s="39" t="n"/>
       <c r="BZ47" s="24" t="n"/>
       <c r="CA47" s="31" t="n"/>
     </row>
@@ -13119,7 +13164,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J48" s="25" t="n"/>
+      <c r="J48" s="38" t="n"/>
       <c r="K48" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -13128,7 +13173,7 @@
       <c r="L48" s="26" t="n">
         <v>108</v>
       </c>
-      <c r="M48" s="27" t="n">
+      <c r="M48" s="39" t="n">
         <v>2.08</v>
       </c>
       <c r="N48" s="28" t="n">
@@ -13160,11 +13205,11 @@
       <c r="V48" s="24" t="n"/>
       <c r="W48" s="26" t="n"/>
       <c r="X48" s="26" t="n"/>
-      <c r="Y48" s="25" t="n"/>
+      <c r="Y48" s="38" t="n"/>
       <c r="Z48" s="26" t="n"/>
       <c r="AA48" s="28" t="n"/>
       <c r="AB48" s="28" t="n"/>
-      <c r="AC48" s="30" t="n"/>
+      <c r="AC48" s="40" t="n"/>
       <c r="AD48" s="24" t="n"/>
       <c r="AE48" s="31" t="inlineStr">
         <is>
@@ -13295,11 +13340,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ48" s="25" t="n"/>
+      <c r="BJ48" s="38" t="n"/>
       <c r="BK48" s="26" t="n">
         <v>108</v>
       </c>
-      <c r="BL48" s="27" t="n">
+      <c r="BL48" s="39" t="n">
         <v>2.08</v>
       </c>
       <c r="BM48" s="28" t="n">
@@ -13307,16 +13352,16 @@
       </c>
       <c r="BN48" s="28" t="n"/>
       <c r="BO48" s="28" t="n"/>
-      <c r="BP48" s="25" t="n"/>
-      <c r="BQ48" s="27" t="n"/>
+      <c r="BP48" s="38" t="n"/>
+      <c r="BQ48" s="39" t="n"/>
       <c r="BR48" s="28" t="n"/>
       <c r="BS48" s="28" t="n"/>
       <c r="BT48" s="28" t="n"/>
-      <c r="BU48" s="25" t="n"/>
+      <c r="BU48" s="38" t="n"/>
       <c r="BV48" s="29" t="n"/>
       <c r="BW48" s="24" t="n"/>
-      <c r="BX48" s="30" t="n"/>
-      <c r="BY48" s="27" t="n"/>
+      <c r="BX48" s="40" t="n"/>
+      <c r="BY48" s="39" t="n"/>
       <c r="BZ48" s="24" t="n"/>
       <c r="CA48" s="31" t="n"/>
     </row>
@@ -13366,7 +13411,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J49" s="25" t="n"/>
+      <c r="J49" s="38" t="n"/>
       <c r="K49" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -13375,7 +13420,7 @@
       <c r="L49" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="M49" s="27" t="n">
+      <c r="M49" s="39" t="n">
         <v>1.75188</v>
       </c>
       <c r="N49" s="28" t="n">
@@ -13407,11 +13452,11 @@
       <c r="V49" s="24" t="n"/>
       <c r="W49" s="26" t="n"/>
       <c r="X49" s="26" t="n"/>
-      <c r="Y49" s="25" t="n"/>
+      <c r="Y49" s="38" t="n"/>
       <c r="Z49" s="26" t="n"/>
       <c r="AA49" s="28" t="n"/>
       <c r="AB49" s="28" t="n"/>
-      <c r="AC49" s="30" t="n"/>
+      <c r="AC49" s="40" t="n"/>
       <c r="AD49" s="24" t="n"/>
       <c r="AE49" s="31" t="inlineStr">
         <is>
@@ -13542,11 +13587,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ49" s="25" t="n"/>
+      <c r="BJ49" s="38" t="n"/>
       <c r="BK49" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="BL49" s="27" t="n">
+      <c r="BL49" s="39" t="n">
         <v>1.75188</v>
       </c>
       <c r="BM49" s="28" t="n">
@@ -13554,16 +13599,16 @@
       </c>
       <c r="BN49" s="28" t="n"/>
       <c r="BO49" s="28" t="n"/>
-      <c r="BP49" s="25" t="n"/>
-      <c r="BQ49" s="27" t="n"/>
+      <c r="BP49" s="38" t="n"/>
+      <c r="BQ49" s="39" t="n"/>
       <c r="BR49" s="28" t="n"/>
       <c r="BS49" s="28" t="n"/>
       <c r="BT49" s="28" t="n"/>
-      <c r="BU49" s="25" t="n"/>
+      <c r="BU49" s="38" t="n"/>
       <c r="BV49" s="29" t="n"/>
       <c r="BW49" s="24" t="n"/>
-      <c r="BX49" s="30" t="n"/>
-      <c r="BY49" s="27" t="n"/>
+      <c r="BX49" s="40" t="n"/>
+      <c r="BY49" s="39" t="n"/>
       <c r="BZ49" s="24" t="n"/>
       <c r="CA49" s="31" t="n"/>
     </row>
@@ -13613,7 +13658,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J50" s="25" t="n"/>
+      <c r="J50" s="38" t="n"/>
       <c r="K50" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -13622,7 +13667,7 @@
       <c r="L50" s="26" t="n">
         <v>-113</v>
       </c>
-      <c r="M50" s="27" t="n">
+      <c r="M50" s="39" t="n">
         <v>1.884956</v>
       </c>
       <c r="N50" s="28" t="n">
@@ -13654,11 +13699,11 @@
       <c r="V50" s="24" t="n"/>
       <c r="W50" s="26" t="n"/>
       <c r="X50" s="26" t="n"/>
-      <c r="Y50" s="25" t="n"/>
+      <c r="Y50" s="38" t="n"/>
       <c r="Z50" s="26" t="n"/>
       <c r="AA50" s="28" t="n"/>
       <c r="AB50" s="28" t="n"/>
-      <c r="AC50" s="30" t="n"/>
+      <c r="AC50" s="40" t="n"/>
       <c r="AD50" s="24" t="n"/>
       <c r="AE50" s="31" t="inlineStr">
         <is>
@@ -13789,11 +13834,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ50" s="25" t="n"/>
+      <c r="BJ50" s="38" t="n"/>
       <c r="BK50" s="26" t="n">
         <v>-113</v>
       </c>
-      <c r="BL50" s="27" t="n">
+      <c r="BL50" s="39" t="n">
         <v>1.884956</v>
       </c>
       <c r="BM50" s="28" t="n">
@@ -13801,16 +13846,16 @@
       </c>
       <c r="BN50" s="28" t="n"/>
       <c r="BO50" s="28" t="n"/>
-      <c r="BP50" s="25" t="n"/>
-      <c r="BQ50" s="27" t="n"/>
+      <c r="BP50" s="38" t="n"/>
+      <c r="BQ50" s="39" t="n"/>
       <c r="BR50" s="28" t="n"/>
       <c r="BS50" s="28" t="n"/>
       <c r="BT50" s="28" t="n"/>
-      <c r="BU50" s="25" t="n"/>
+      <c r="BU50" s="38" t="n"/>
       <c r="BV50" s="29" t="n"/>
       <c r="BW50" s="24" t="n"/>
-      <c r="BX50" s="30" t="n"/>
-      <c r="BY50" s="27" t="n"/>
+      <c r="BX50" s="40" t="n"/>
+      <c r="BY50" s="39" t="n"/>
       <c r="BZ50" s="24" t="n"/>
       <c r="CA50" s="31" t="n"/>
     </row>
@@ -13860,7 +13905,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J51" s="25" t="n"/>
+      <c r="J51" s="38" t="n"/>
       <c r="K51" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -13869,7 +13914,7 @@
       <c r="L51" s="26" t="n">
         <v>-144</v>
       </c>
-      <c r="M51" s="27" t="n">
+      <c r="M51" s="39" t="n">
         <v>1.694444</v>
       </c>
       <c r="N51" s="28" t="n">
@@ -13901,11 +13946,11 @@
       <c r="V51" s="24" t="n"/>
       <c r="W51" s="26" t="n"/>
       <c r="X51" s="26" t="n"/>
-      <c r="Y51" s="25" t="n"/>
+      <c r="Y51" s="38" t="n"/>
       <c r="Z51" s="26" t="n"/>
       <c r="AA51" s="28" t="n"/>
       <c r="AB51" s="28" t="n"/>
-      <c r="AC51" s="30" t="n"/>
+      <c r="AC51" s="40" t="n"/>
       <c r="AD51" s="24" t="n"/>
       <c r="AE51" s="31" t="inlineStr">
         <is>
@@ -14036,11 +14081,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ51" s="25" t="n"/>
+      <c r="BJ51" s="38" t="n"/>
       <c r="BK51" s="26" t="n">
         <v>-144</v>
       </c>
-      <c r="BL51" s="27" t="n">
+      <c r="BL51" s="39" t="n">
         <v>1.694444</v>
       </c>
       <c r="BM51" s="28" t="n">
@@ -14048,16 +14093,16 @@
       </c>
       <c r="BN51" s="28" t="n"/>
       <c r="BO51" s="28" t="n"/>
-      <c r="BP51" s="25" t="n"/>
-      <c r="BQ51" s="27" t="n"/>
+      <c r="BP51" s="38" t="n"/>
+      <c r="BQ51" s="39" t="n"/>
       <c r="BR51" s="28" t="n"/>
       <c r="BS51" s="28" t="n"/>
       <c r="BT51" s="28" t="n"/>
-      <c r="BU51" s="25" t="n"/>
+      <c r="BU51" s="38" t="n"/>
       <c r="BV51" s="29" t="n"/>
       <c r="BW51" s="24" t="n"/>
-      <c r="BX51" s="30" t="n"/>
-      <c r="BY51" s="27" t="n"/>
+      <c r="BX51" s="40" t="n"/>
+      <c r="BY51" s="39" t="n"/>
       <c r="BZ51" s="24" t="n"/>
       <c r="CA51" s="31" t="n"/>
     </row>
@@ -14107,7 +14152,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J52" s="25" t="n"/>
+      <c r="J52" s="38" t="n"/>
       <c r="K52" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -14116,7 +14161,7 @@
       <c r="L52" s="26" t="n">
         <v>-144</v>
       </c>
-      <c r="M52" s="27" t="n">
+      <c r="M52" s="39" t="n">
         <v>1.694444</v>
       </c>
       <c r="N52" s="28" t="n">
@@ -14148,11 +14193,11 @@
       <c r="V52" s="24" t="n"/>
       <c r="W52" s="26" t="n"/>
       <c r="X52" s="26" t="n"/>
-      <c r="Y52" s="25" t="n"/>
+      <c r="Y52" s="38" t="n"/>
       <c r="Z52" s="26" t="n"/>
       <c r="AA52" s="28" t="n"/>
       <c r="AB52" s="28" t="n"/>
-      <c r="AC52" s="30" t="n"/>
+      <c r="AC52" s="40" t="n"/>
       <c r="AD52" s="24" t="n"/>
       <c r="AE52" s="31" t="inlineStr">
         <is>
@@ -14283,11 +14328,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ52" s="25" t="n"/>
+      <c r="BJ52" s="38" t="n"/>
       <c r="BK52" s="26" t="n">
         <v>-144</v>
       </c>
-      <c r="BL52" s="27" t="n">
+      <c r="BL52" s="39" t="n">
         <v>1.694444</v>
       </c>
       <c r="BM52" s="28" t="n">
@@ -14295,16 +14340,16 @@
       </c>
       <c r="BN52" s="28" t="n"/>
       <c r="BO52" s="28" t="n"/>
-      <c r="BP52" s="25" t="n"/>
-      <c r="BQ52" s="27" t="n"/>
+      <c r="BP52" s="38" t="n"/>
+      <c r="BQ52" s="39" t="n"/>
       <c r="BR52" s="28" t="n"/>
       <c r="BS52" s="28" t="n"/>
       <c r="BT52" s="28" t="n"/>
-      <c r="BU52" s="25" t="n"/>
+      <c r="BU52" s="38" t="n"/>
       <c r="BV52" s="29" t="n"/>
       <c r="BW52" s="24" t="n"/>
-      <c r="BX52" s="30" t="n"/>
-      <c r="BY52" s="27" t="n"/>
+      <c r="BX52" s="40" t="n"/>
+      <c r="BY52" s="39" t="n"/>
       <c r="BZ52" s="24" t="n"/>
       <c r="CA52" s="31" t="n"/>
     </row>
@@ -14354,7 +14399,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J53" s="25" t="n"/>
+      <c r="J53" s="38" t="n"/>
       <c r="K53" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -14363,7 +14408,7 @@
       <c r="L53" s="26" t="n">
         <v>113</v>
       </c>
-      <c r="M53" s="27" t="n">
+      <c r="M53" s="39" t="n">
         <v>2.13</v>
       </c>
       <c r="N53" s="28" t="n">
@@ -14395,11 +14440,11 @@
       <c r="V53" s="24" t="n"/>
       <c r="W53" s="26" t="n"/>
       <c r="X53" s="26" t="n"/>
-      <c r="Y53" s="25" t="n"/>
+      <c r="Y53" s="38" t="n"/>
       <c r="Z53" s="26" t="n"/>
       <c r="AA53" s="28" t="n"/>
       <c r="AB53" s="28" t="n"/>
-      <c r="AC53" s="30" t="n"/>
+      <c r="AC53" s="40" t="n"/>
       <c r="AD53" s="24" t="n"/>
       <c r="AE53" s="31" t="inlineStr">
         <is>
@@ -14530,11 +14575,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ53" s="25" t="n"/>
+      <c r="BJ53" s="38" t="n"/>
       <c r="BK53" s="26" t="n">
         <v>113</v>
       </c>
-      <c r="BL53" s="27" t="n">
+      <c r="BL53" s="39" t="n">
         <v>2.13</v>
       </c>
       <c r="BM53" s="28" t="n">
@@ -14542,16 +14587,16 @@
       </c>
       <c r="BN53" s="28" t="n"/>
       <c r="BO53" s="28" t="n"/>
-      <c r="BP53" s="25" t="n"/>
-      <c r="BQ53" s="27" t="n"/>
+      <c r="BP53" s="38" t="n"/>
+      <c r="BQ53" s="39" t="n"/>
       <c r="BR53" s="28" t="n"/>
       <c r="BS53" s="28" t="n"/>
       <c r="BT53" s="28" t="n"/>
-      <c r="BU53" s="25" t="n"/>
+      <c r="BU53" s="38" t="n"/>
       <c r="BV53" s="29" t="n"/>
       <c r="BW53" s="24" t="n"/>
-      <c r="BX53" s="30" t="n"/>
-      <c r="BY53" s="27" t="n"/>
+      <c r="BX53" s="40" t="n"/>
+      <c r="BY53" s="39" t="n"/>
       <c r="BZ53" s="24" t="n"/>
       <c r="CA53" s="31" t="n"/>
     </row>
@@ -14601,7 +14646,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J54" s="25" t="n"/>
+      <c r="J54" s="38" t="n"/>
       <c r="K54" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -14610,7 +14655,7 @@
       <c r="L54" s="26" t="n">
         <v>-194</v>
       </c>
-      <c r="M54" s="27" t="n">
+      <c r="M54" s="39" t="n">
         <v>1.515464</v>
       </c>
       <c r="N54" s="28" t="n">
@@ -14642,11 +14687,11 @@
       <c r="V54" s="24" t="n"/>
       <c r="W54" s="26" t="n"/>
       <c r="X54" s="26" t="n"/>
-      <c r="Y54" s="25" t="n"/>
+      <c r="Y54" s="38" t="n"/>
       <c r="Z54" s="26" t="n"/>
       <c r="AA54" s="28" t="n"/>
       <c r="AB54" s="28" t="n"/>
-      <c r="AC54" s="30" t="n"/>
+      <c r="AC54" s="40" t="n"/>
       <c r="AD54" s="24" t="n"/>
       <c r="AE54" s="31" t="inlineStr">
         <is>
@@ -14777,11 +14822,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ54" s="25" t="n"/>
+      <c r="BJ54" s="38" t="n"/>
       <c r="BK54" s="26" t="n">
         <v>-194</v>
       </c>
-      <c r="BL54" s="27" t="n">
+      <c r="BL54" s="39" t="n">
         <v>1.515464</v>
       </c>
       <c r="BM54" s="28" t="n">
@@ -14789,16 +14834,16 @@
       </c>
       <c r="BN54" s="28" t="n"/>
       <c r="BO54" s="28" t="n"/>
-      <c r="BP54" s="25" t="n"/>
-      <c r="BQ54" s="27" t="n"/>
+      <c r="BP54" s="38" t="n"/>
+      <c r="BQ54" s="39" t="n"/>
       <c r="BR54" s="28" t="n"/>
       <c r="BS54" s="28" t="n"/>
       <c r="BT54" s="28" t="n"/>
-      <c r="BU54" s="25" t="n"/>
+      <c r="BU54" s="38" t="n"/>
       <c r="BV54" s="29" t="n"/>
       <c r="BW54" s="24" t="n"/>
-      <c r="BX54" s="30" t="n"/>
-      <c r="BY54" s="27" t="n"/>
+      <c r="BX54" s="40" t="n"/>
+      <c r="BY54" s="39" t="n"/>
       <c r="BZ54" s="24" t="n"/>
       <c r="CA54" s="31" t="n"/>
     </row>
@@ -14848,7 +14893,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J55" s="25" t="n"/>
+      <c r="J55" s="38" t="n"/>
       <c r="K55" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -14857,7 +14902,7 @@
       <c r="L55" s="26" t="n">
         <v>-203</v>
       </c>
-      <c r="M55" s="27" t="n">
+      <c r="M55" s="39" t="n">
         <v>1.492611</v>
       </c>
       <c r="N55" s="28" t="n">
@@ -14889,11 +14934,11 @@
       <c r="V55" s="24" t="n"/>
       <c r="W55" s="26" t="n"/>
       <c r="X55" s="26" t="n"/>
-      <c r="Y55" s="25" t="n"/>
+      <c r="Y55" s="38" t="n"/>
       <c r="Z55" s="26" t="n"/>
       <c r="AA55" s="28" t="n"/>
       <c r="AB55" s="28" t="n"/>
-      <c r="AC55" s="30" t="n"/>
+      <c r="AC55" s="40" t="n"/>
       <c r="AD55" s="24" t="n"/>
       <c r="AE55" s="31" t="inlineStr">
         <is>
@@ -15024,11 +15069,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ55" s="25" t="n"/>
+      <c r="BJ55" s="38" t="n"/>
       <c r="BK55" s="26" t="n">
         <v>-203</v>
       </c>
-      <c r="BL55" s="27" t="n">
+      <c r="BL55" s="39" t="n">
         <v>1.492611</v>
       </c>
       <c r="BM55" s="28" t="n">
@@ -15036,16 +15081,16 @@
       </c>
       <c r="BN55" s="28" t="n"/>
       <c r="BO55" s="28" t="n"/>
-      <c r="BP55" s="25" t="n"/>
-      <c r="BQ55" s="27" t="n"/>
+      <c r="BP55" s="38" t="n"/>
+      <c r="BQ55" s="39" t="n"/>
       <c r="BR55" s="28" t="n"/>
       <c r="BS55" s="28" t="n"/>
       <c r="BT55" s="28" t="n"/>
-      <c r="BU55" s="25" t="n"/>
+      <c r="BU55" s="38" t="n"/>
       <c r="BV55" s="29" t="n"/>
       <c r="BW55" s="24" t="n"/>
-      <c r="BX55" s="30" t="n"/>
-      <c r="BY55" s="27" t="n"/>
+      <c r="BX55" s="40" t="n"/>
+      <c r="BY55" s="39" t="n"/>
       <c r="BZ55" s="24" t="n"/>
       <c r="CA55" s="31" t="n"/>
     </row>
@@ -15095,7 +15140,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J56" s="25" t="n"/>
+      <c r="J56" s="38" t="n"/>
       <c r="K56" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -15104,7 +15149,7 @@
       <c r="L56" s="26" t="n">
         <v>163</v>
       </c>
-      <c r="M56" s="27" t="n">
+      <c r="M56" s="39" t="n">
         <v>2.63</v>
       </c>
       <c r="N56" s="28" t="n">
@@ -15136,11 +15181,11 @@
       <c r="V56" s="24" t="n"/>
       <c r="W56" s="26" t="n"/>
       <c r="X56" s="26" t="n"/>
-      <c r="Y56" s="25" t="n"/>
+      <c r="Y56" s="38" t="n"/>
       <c r="Z56" s="26" t="n"/>
       <c r="AA56" s="28" t="n"/>
       <c r="AB56" s="28" t="n"/>
-      <c r="AC56" s="30" t="n"/>
+      <c r="AC56" s="40" t="n"/>
       <c r="AD56" s="24" t="n"/>
       <c r="AE56" s="31" t="inlineStr">
         <is>
@@ -15271,11 +15316,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ56" s="25" t="n"/>
+      <c r="BJ56" s="38" t="n"/>
       <c r="BK56" s="26" t="n">
         <v>163</v>
       </c>
-      <c r="BL56" s="27" t="n">
+      <c r="BL56" s="39" t="n">
         <v>2.63</v>
       </c>
       <c r="BM56" s="28" t="n">
@@ -15283,16 +15328,16 @@
       </c>
       <c r="BN56" s="28" t="n"/>
       <c r="BO56" s="28" t="n"/>
-      <c r="BP56" s="25" t="n"/>
-      <c r="BQ56" s="27" t="n"/>
+      <c r="BP56" s="38" t="n"/>
+      <c r="BQ56" s="39" t="n"/>
       <c r="BR56" s="28" t="n"/>
       <c r="BS56" s="28" t="n"/>
       <c r="BT56" s="28" t="n"/>
-      <c r="BU56" s="25" t="n"/>
+      <c r="BU56" s="38" t="n"/>
       <c r="BV56" s="29" t="n"/>
       <c r="BW56" s="24" t="n"/>
-      <c r="BX56" s="30" t="n"/>
-      <c r="BY56" s="27" t="n"/>
+      <c r="BX56" s="40" t="n"/>
+      <c r="BY56" s="39" t="n"/>
       <c r="BZ56" s="24" t="n"/>
       <c r="CA56" s="31" t="n"/>
     </row>
@@ -15342,7 +15387,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J57" s="25" t="n"/>
+      <c r="J57" s="38" t="n"/>
       <c r="K57" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -15351,7 +15396,7 @@
       <c r="L57" s="26" t="n">
         <v>-213</v>
       </c>
-      <c r="M57" s="27" t="n">
+      <c r="M57" s="39" t="n">
         <v>1.469484</v>
       </c>
       <c r="N57" s="28" t="n">
@@ -15383,11 +15428,11 @@
       <c r="V57" s="24" t="n"/>
       <c r="W57" s="26" t="n"/>
       <c r="X57" s="26" t="n"/>
-      <c r="Y57" s="25" t="n"/>
+      <c r="Y57" s="38" t="n"/>
       <c r="Z57" s="26" t="n"/>
       <c r="AA57" s="28" t="n"/>
       <c r="AB57" s="28" t="n"/>
-      <c r="AC57" s="30" t="n"/>
+      <c r="AC57" s="40" t="n"/>
       <c r="AD57" s="24" t="n"/>
       <c r="AE57" s="31" t="inlineStr">
         <is>
@@ -15518,11 +15563,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ57" s="25" t="n"/>
+      <c r="BJ57" s="38" t="n"/>
       <c r="BK57" s="26" t="n">
         <v>-213</v>
       </c>
-      <c r="BL57" s="27" t="n">
+      <c r="BL57" s="39" t="n">
         <v>1.469484</v>
       </c>
       <c r="BM57" s="28" t="n">
@@ -15530,16 +15575,16 @@
       </c>
       <c r="BN57" s="28" t="n"/>
       <c r="BO57" s="28" t="n"/>
-      <c r="BP57" s="25" t="n"/>
-      <c r="BQ57" s="27" t="n"/>
+      <c r="BP57" s="38" t="n"/>
+      <c r="BQ57" s="39" t="n"/>
       <c r="BR57" s="28" t="n"/>
       <c r="BS57" s="28" t="n"/>
       <c r="BT57" s="28" t="n"/>
-      <c r="BU57" s="25" t="n"/>
+      <c r="BU57" s="38" t="n"/>
       <c r="BV57" s="29" t="n"/>
       <c r="BW57" s="24" t="n"/>
-      <c r="BX57" s="30" t="n"/>
-      <c r="BY57" s="27" t="n"/>
+      <c r="BX57" s="40" t="n"/>
+      <c r="BY57" s="39" t="n"/>
       <c r="BZ57" s="24" t="n"/>
       <c r="CA57" s="31" t="n"/>
     </row>
@@ -15589,7 +15634,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J58" s="25" t="n"/>
+      <c r="J58" s="38" t="n"/>
       <c r="K58" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -15598,7 +15643,7 @@
       <c r="L58" s="26" t="n">
         <v>156</v>
       </c>
-      <c r="M58" s="27" t="n">
+      <c r="M58" s="39" t="n">
         <v>2.56</v>
       </c>
       <c r="N58" s="28" t="n">
@@ -15630,11 +15675,11 @@
       <c r="V58" s="24" t="n"/>
       <c r="W58" s="26" t="n"/>
       <c r="X58" s="26" t="n"/>
-      <c r="Y58" s="25" t="n"/>
+      <c r="Y58" s="38" t="n"/>
       <c r="Z58" s="26" t="n"/>
       <c r="AA58" s="28" t="n"/>
       <c r="AB58" s="28" t="n"/>
-      <c r="AC58" s="30" t="n"/>
+      <c r="AC58" s="40" t="n"/>
       <c r="AD58" s="24" t="n"/>
       <c r="AE58" s="31" t="inlineStr">
         <is>
@@ -15765,11 +15810,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ58" s="25" t="n"/>
+      <c r="BJ58" s="38" t="n"/>
       <c r="BK58" s="26" t="n">
         <v>156</v>
       </c>
-      <c r="BL58" s="27" t="n">
+      <c r="BL58" s="39" t="n">
         <v>2.56</v>
       </c>
       <c r="BM58" s="28" t="n">
@@ -15777,16 +15822,16 @@
       </c>
       <c r="BN58" s="28" t="n"/>
       <c r="BO58" s="28" t="n"/>
-      <c r="BP58" s="25" t="n"/>
-      <c r="BQ58" s="27" t="n"/>
+      <c r="BP58" s="38" t="n"/>
+      <c r="BQ58" s="39" t="n"/>
       <c r="BR58" s="28" t="n"/>
       <c r="BS58" s="28" t="n"/>
       <c r="BT58" s="28" t="n"/>
-      <c r="BU58" s="25" t="n"/>
+      <c r="BU58" s="38" t="n"/>
       <c r="BV58" s="29" t="n"/>
       <c r="BW58" s="24" t="n"/>
-      <c r="BX58" s="30" t="n"/>
-      <c r="BY58" s="27" t="n"/>
+      <c r="BX58" s="40" t="n"/>
+      <c r="BY58" s="39" t="n"/>
       <c r="BZ58" s="24" t="n"/>
       <c r="CA58" s="31" t="n"/>
     </row>
@@ -15836,7 +15881,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J59" s="25" t="n"/>
+      <c r="J59" s="38" t="n"/>
       <c r="K59" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -15845,7 +15890,7 @@
       <c r="L59" s="26" t="n">
         <v>113</v>
       </c>
-      <c r="M59" s="27" t="n">
+      <c r="M59" s="39" t="n">
         <v>2.13</v>
       </c>
       <c r="N59" s="28" t="n">
@@ -15877,11 +15922,11 @@
       <c r="V59" s="24" t="n"/>
       <c r="W59" s="26" t="n"/>
       <c r="X59" s="26" t="n"/>
-      <c r="Y59" s="25" t="n"/>
+      <c r="Y59" s="38" t="n"/>
       <c r="Z59" s="26" t="n"/>
       <c r="AA59" s="28" t="n"/>
       <c r="AB59" s="28" t="n"/>
-      <c r="AC59" s="30" t="n"/>
+      <c r="AC59" s="40" t="n"/>
       <c r="AD59" s="24" t="n"/>
       <c r="AE59" s="31" t="inlineStr">
         <is>
@@ -16012,11 +16057,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ59" s="25" t="n"/>
+      <c r="BJ59" s="38" t="n"/>
       <c r="BK59" s="26" t="n">
         <v>113</v>
       </c>
-      <c r="BL59" s="27" t="n">
+      <c r="BL59" s="39" t="n">
         <v>2.13</v>
       </c>
       <c r="BM59" s="28" t="n">
@@ -16024,16 +16069,16 @@
       </c>
       <c r="BN59" s="28" t="n"/>
       <c r="BO59" s="28" t="n"/>
-      <c r="BP59" s="25" t="n"/>
-      <c r="BQ59" s="27" t="n"/>
+      <c r="BP59" s="38" t="n"/>
+      <c r="BQ59" s="39" t="n"/>
       <c r="BR59" s="28" t="n"/>
       <c r="BS59" s="28" t="n"/>
       <c r="BT59" s="28" t="n"/>
-      <c r="BU59" s="25" t="n"/>
+      <c r="BU59" s="38" t="n"/>
       <c r="BV59" s="29" t="n"/>
       <c r="BW59" s="24" t="n"/>
-      <c r="BX59" s="30" t="n"/>
-      <c r="BY59" s="27" t="n"/>
+      <c r="BX59" s="40" t="n"/>
+      <c r="BY59" s="39" t="n"/>
       <c r="BZ59" s="24" t="n"/>
       <c r="CA59" s="31" t="n"/>
     </row>
@@ -16083,7 +16128,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J60" s="25" t="n"/>
+      <c r="J60" s="38" t="n"/>
       <c r="K60" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -16092,7 +16137,7 @@
       <c r="L60" s="26" t="n">
         <v>108</v>
       </c>
-      <c r="M60" s="27" t="n">
+      <c r="M60" s="39" t="n">
         <v>2.08</v>
       </c>
       <c r="N60" s="28" t="n">
@@ -16124,11 +16169,11 @@
       <c r="V60" s="24" t="n"/>
       <c r="W60" s="26" t="n"/>
       <c r="X60" s="26" t="n"/>
-      <c r="Y60" s="25" t="n"/>
+      <c r="Y60" s="38" t="n"/>
       <c r="Z60" s="26" t="n"/>
       <c r="AA60" s="28" t="n"/>
       <c r="AB60" s="28" t="n"/>
-      <c r="AC60" s="30" t="n"/>
+      <c r="AC60" s="40" t="n"/>
       <c r="AD60" s="24" t="n"/>
       <c r="AE60" s="31" t="inlineStr">
         <is>
@@ -16259,11 +16304,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ60" s="25" t="n"/>
+      <c r="BJ60" s="38" t="n"/>
       <c r="BK60" s="26" t="n">
         <v>108</v>
       </c>
-      <c r="BL60" s="27" t="n">
+      <c r="BL60" s="39" t="n">
         <v>2.08</v>
       </c>
       <c r="BM60" s="28" t="n">
@@ -16271,16 +16316,16 @@
       </c>
       <c r="BN60" s="28" t="n"/>
       <c r="BO60" s="28" t="n"/>
-      <c r="BP60" s="25" t="n"/>
-      <c r="BQ60" s="27" t="n"/>
+      <c r="BP60" s="38" t="n"/>
+      <c r="BQ60" s="39" t="n"/>
       <c r="BR60" s="28" t="n"/>
       <c r="BS60" s="28" t="n"/>
       <c r="BT60" s="28" t="n"/>
-      <c r="BU60" s="25" t="n"/>
+      <c r="BU60" s="38" t="n"/>
       <c r="BV60" s="29" t="n"/>
       <c r="BW60" s="24" t="n"/>
-      <c r="BX60" s="30" t="n"/>
-      <c r="BY60" s="27" t="n"/>
+      <c r="BX60" s="40" t="n"/>
+      <c r="BY60" s="39" t="n"/>
       <c r="BZ60" s="24" t="n"/>
       <c r="CA60" s="31" t="n"/>
     </row>
@@ -16330,7 +16375,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J61" s="25" t="n"/>
+      <c r="J61" s="38" t="n"/>
       <c r="K61" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -16339,7 +16384,7 @@
       <c r="L61" s="26" t="n">
         <v>156</v>
       </c>
-      <c r="M61" s="27" t="n">
+      <c r="M61" s="39" t="n">
         <v>2.56</v>
       </c>
       <c r="N61" s="28" t="n">
@@ -16371,11 +16416,11 @@
       <c r="V61" s="24" t="n"/>
       <c r="W61" s="26" t="n"/>
       <c r="X61" s="26" t="n"/>
-      <c r="Y61" s="25" t="n"/>
+      <c r="Y61" s="38" t="n"/>
       <c r="Z61" s="26" t="n"/>
       <c r="AA61" s="28" t="n"/>
       <c r="AB61" s="28" t="n"/>
-      <c r="AC61" s="30" t="n"/>
+      <c r="AC61" s="40" t="n"/>
       <c r="AD61" s="24" t="n"/>
       <c r="AE61" s="31" t="inlineStr">
         <is>
@@ -16506,11 +16551,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ61" s="25" t="n"/>
+      <c r="BJ61" s="38" t="n"/>
       <c r="BK61" s="26" t="n">
         <v>156</v>
       </c>
-      <c r="BL61" s="27" t="n">
+      <c r="BL61" s="39" t="n">
         <v>2.56</v>
       </c>
       <c r="BM61" s="28" t="n">
@@ -16518,16 +16563,16 @@
       </c>
       <c r="BN61" s="28" t="n"/>
       <c r="BO61" s="28" t="n"/>
-      <c r="BP61" s="25" t="n"/>
-      <c r="BQ61" s="27" t="n"/>
+      <c r="BP61" s="38" t="n"/>
+      <c r="BQ61" s="39" t="n"/>
       <c r="BR61" s="28" t="n"/>
       <c r="BS61" s="28" t="n"/>
       <c r="BT61" s="28" t="n"/>
-      <c r="BU61" s="25" t="n"/>
+      <c r="BU61" s="38" t="n"/>
       <c r="BV61" s="29" t="n"/>
       <c r="BW61" s="24" t="n"/>
-      <c r="BX61" s="30" t="n"/>
-      <c r="BY61" s="27" t="n"/>
+      <c r="BX61" s="40" t="n"/>
+      <c r="BY61" s="39" t="n"/>
       <c r="BZ61" s="24" t="n"/>
       <c r="CA61" s="31" t="n"/>
     </row>
@@ -16577,7 +16622,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J62" s="25" t="n"/>
+      <c r="J62" s="38" t="n"/>
       <c r="K62" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -16586,7 +16631,7 @@
       <c r="L62" s="26" t="n">
         <v>117</v>
       </c>
-      <c r="M62" s="27" t="n">
+      <c r="M62" s="39" t="n">
         <v>2.17</v>
       </c>
       <c r="N62" s="28" t="n">
@@ -16618,11 +16663,11 @@
       <c r="V62" s="24" t="n"/>
       <c r="W62" s="26" t="n"/>
       <c r="X62" s="26" t="n"/>
-      <c r="Y62" s="25" t="n"/>
+      <c r="Y62" s="38" t="n"/>
       <c r="Z62" s="26" t="n"/>
       <c r="AA62" s="28" t="n"/>
       <c r="AB62" s="28" t="n"/>
-      <c r="AC62" s="30" t="n"/>
+      <c r="AC62" s="40" t="n"/>
       <c r="AD62" s="24" t="n"/>
       <c r="AE62" s="31" t="inlineStr">
         <is>
@@ -16753,11 +16798,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ62" s="25" t="n"/>
+      <c r="BJ62" s="38" t="n"/>
       <c r="BK62" s="26" t="n">
         <v>117</v>
       </c>
-      <c r="BL62" s="27" t="n">
+      <c r="BL62" s="39" t="n">
         <v>2.17</v>
       </c>
       <c r="BM62" s="28" t="n">
@@ -16765,16 +16810,16 @@
       </c>
       <c r="BN62" s="28" t="n"/>
       <c r="BO62" s="28" t="n"/>
-      <c r="BP62" s="25" t="n"/>
-      <c r="BQ62" s="27" t="n"/>
+      <c r="BP62" s="38" t="n"/>
+      <c r="BQ62" s="39" t="n"/>
       <c r="BR62" s="28" t="n"/>
       <c r="BS62" s="28" t="n"/>
       <c r="BT62" s="28" t="n"/>
-      <c r="BU62" s="25" t="n"/>
+      <c r="BU62" s="38" t="n"/>
       <c r="BV62" s="29" t="n"/>
       <c r="BW62" s="24" t="n"/>
-      <c r="BX62" s="30" t="n"/>
-      <c r="BY62" s="27" t="n"/>
+      <c r="BX62" s="40" t="n"/>
+      <c r="BY62" s="39" t="n"/>
       <c r="BZ62" s="24" t="n"/>
       <c r="CA62" s="31" t="n"/>
     </row>
@@ -16824,7 +16869,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J63" s="25" t="n"/>
+      <c r="J63" s="38" t="n"/>
       <c r="K63" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -16833,7 +16878,7 @@
       <c r="L63" s="26" t="n">
         <v>-117</v>
       </c>
-      <c r="M63" s="27" t="n">
+      <c r="M63" s="39" t="n">
         <v>1.854701</v>
       </c>
       <c r="N63" s="28" t="n">
@@ -16865,11 +16910,11 @@
       <c r="V63" s="24" t="n"/>
       <c r="W63" s="26" t="n"/>
       <c r="X63" s="26" t="n"/>
-      <c r="Y63" s="25" t="n"/>
+      <c r="Y63" s="38" t="n"/>
       <c r="Z63" s="26" t="n"/>
       <c r="AA63" s="28" t="n"/>
       <c r="AB63" s="28" t="n"/>
-      <c r="AC63" s="30" t="n"/>
+      <c r="AC63" s="40" t="n"/>
       <c r="AD63" s="24" t="n"/>
       <c r="AE63" s="31" t="inlineStr">
         <is>
@@ -17000,11 +17045,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ63" s="25" t="n"/>
+      <c r="BJ63" s="38" t="n"/>
       <c r="BK63" s="26" t="n">
         <v>-117</v>
       </c>
-      <c r="BL63" s="27" t="n">
+      <c r="BL63" s="39" t="n">
         <v>1.854701</v>
       </c>
       <c r="BM63" s="28" t="n">
@@ -17012,16 +17057,16 @@
       </c>
       <c r="BN63" s="28" t="n"/>
       <c r="BO63" s="28" t="n"/>
-      <c r="BP63" s="25" t="n"/>
-      <c r="BQ63" s="27" t="n"/>
+      <c r="BP63" s="38" t="n"/>
+      <c r="BQ63" s="39" t="n"/>
       <c r="BR63" s="28" t="n"/>
       <c r="BS63" s="28" t="n"/>
       <c r="BT63" s="28" t="n"/>
-      <c r="BU63" s="25" t="n"/>
+      <c r="BU63" s="38" t="n"/>
       <c r="BV63" s="29" t="n"/>
       <c r="BW63" s="24" t="n"/>
-      <c r="BX63" s="30" t="n"/>
-      <c r="BY63" s="27" t="n"/>
+      <c r="BX63" s="40" t="n"/>
+      <c r="BY63" s="39" t="n"/>
       <c r="BZ63" s="24" t="n"/>
       <c r="CA63" s="31" t="n"/>
     </row>
@@ -17071,7 +17116,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J64" s="25" t="n"/>
+      <c r="J64" s="38" t="n"/>
       <c r="K64" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -17080,7 +17125,7 @@
       <c r="L64" s="26" t="n">
         <v>-178</v>
       </c>
-      <c r="M64" s="27" t="n">
+      <c r="M64" s="39" t="n">
         <v>1.561798</v>
       </c>
       <c r="N64" s="28" t="n">
@@ -17112,11 +17157,11 @@
       <c r="V64" s="24" t="n"/>
       <c r="W64" s="26" t="n"/>
       <c r="X64" s="26" t="n"/>
-      <c r="Y64" s="25" t="n"/>
+      <c r="Y64" s="38" t="n"/>
       <c r="Z64" s="26" t="n"/>
       <c r="AA64" s="28" t="n"/>
       <c r="AB64" s="28" t="n"/>
-      <c r="AC64" s="30" t="n"/>
+      <c r="AC64" s="40" t="n"/>
       <c r="AD64" s="24" t="n"/>
       <c r="AE64" s="31" t="inlineStr">
         <is>
@@ -17247,11 +17292,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ64" s="25" t="n"/>
+      <c r="BJ64" s="38" t="n"/>
       <c r="BK64" s="26" t="n">
         <v>-178</v>
       </c>
-      <c r="BL64" s="27" t="n">
+      <c r="BL64" s="39" t="n">
         <v>1.561798</v>
       </c>
       <c r="BM64" s="28" t="n">
@@ -17259,16 +17304,16 @@
       </c>
       <c r="BN64" s="28" t="n"/>
       <c r="BO64" s="28" t="n"/>
-      <c r="BP64" s="25" t="n"/>
-      <c r="BQ64" s="27" t="n"/>
+      <c r="BP64" s="38" t="n"/>
+      <c r="BQ64" s="39" t="n"/>
       <c r="BR64" s="28" t="n"/>
       <c r="BS64" s="28" t="n"/>
       <c r="BT64" s="28" t="n"/>
-      <c r="BU64" s="25" t="n"/>
+      <c r="BU64" s="38" t="n"/>
       <c r="BV64" s="29" t="n"/>
       <c r="BW64" s="24" t="n"/>
-      <c r="BX64" s="30" t="n"/>
-      <c r="BY64" s="27" t="n"/>
+      <c r="BX64" s="40" t="n"/>
+      <c r="BY64" s="39" t="n"/>
       <c r="BZ64" s="24" t="n"/>
       <c r="CA64" s="31" t="n"/>
     </row>
@@ -17318,7 +17363,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J65" s="25" t="n"/>
+      <c r="J65" s="38" t="n"/>
       <c r="K65" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -17327,7 +17372,7 @@
       <c r="L65" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="M65" s="27" t="n">
+      <c r="M65" s="39" t="n">
         <v>1.75188</v>
       </c>
       <c r="N65" s="28" t="n">
@@ -17359,11 +17404,11 @@
       <c r="V65" s="24" t="n"/>
       <c r="W65" s="26" t="n"/>
       <c r="X65" s="26" t="n"/>
-      <c r="Y65" s="25" t="n"/>
+      <c r="Y65" s="38" t="n"/>
       <c r="Z65" s="26" t="n"/>
       <c r="AA65" s="28" t="n"/>
       <c r="AB65" s="28" t="n"/>
-      <c r="AC65" s="30" t="n"/>
+      <c r="AC65" s="40" t="n"/>
       <c r="AD65" s="24" t="n"/>
       <c r="AE65" s="31" t="inlineStr">
         <is>
@@ -17494,11 +17539,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ65" s="25" t="n"/>
+      <c r="BJ65" s="38" t="n"/>
       <c r="BK65" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="BL65" s="27" t="n">
+      <c r="BL65" s="39" t="n">
         <v>1.75188</v>
       </c>
       <c r="BM65" s="28" t="n">
@@ -17506,16 +17551,16 @@
       </c>
       <c r="BN65" s="28" t="n"/>
       <c r="BO65" s="28" t="n"/>
-      <c r="BP65" s="25" t="n"/>
-      <c r="BQ65" s="27" t="n"/>
+      <c r="BP65" s="38" t="n"/>
+      <c r="BQ65" s="39" t="n"/>
       <c r="BR65" s="28" t="n"/>
       <c r="BS65" s="28" t="n"/>
       <c r="BT65" s="28" t="n"/>
-      <c r="BU65" s="25" t="n"/>
+      <c r="BU65" s="38" t="n"/>
       <c r="BV65" s="29" t="n"/>
       <c r="BW65" s="24" t="n"/>
-      <c r="BX65" s="30" t="n"/>
-      <c r="BY65" s="27" t="n"/>
+      <c r="BX65" s="40" t="n"/>
+      <c r="BY65" s="39" t="n"/>
       <c r="BZ65" s="24" t="n"/>
       <c r="CA65" s="31" t="n"/>
     </row>
@@ -17565,7 +17610,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J66" s="25" t="n"/>
+      <c r="J66" s="38" t="n"/>
       <c r="K66" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -17574,7 +17619,7 @@
       <c r="L66" s="26" t="n">
         <v>138</v>
       </c>
-      <c r="M66" s="27" t="n">
+      <c r="M66" s="39" t="n">
         <v>2.38</v>
       </c>
       <c r="N66" s="28" t="n">
@@ -17606,11 +17651,11 @@
       <c r="V66" s="24" t="n"/>
       <c r="W66" s="26" t="n"/>
       <c r="X66" s="26" t="n"/>
-      <c r="Y66" s="25" t="n"/>
+      <c r="Y66" s="38" t="n"/>
       <c r="Z66" s="26" t="n"/>
       <c r="AA66" s="28" t="n"/>
       <c r="AB66" s="28" t="n"/>
-      <c r="AC66" s="30" t="n"/>
+      <c r="AC66" s="40" t="n"/>
       <c r="AD66" s="24" t="n"/>
       <c r="AE66" s="31" t="inlineStr">
         <is>
@@ -17741,11 +17786,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ66" s="25" t="n"/>
+      <c r="BJ66" s="38" t="n"/>
       <c r="BK66" s="26" t="n">
         <v>138</v>
       </c>
-      <c r="BL66" s="27" t="n">
+      <c r="BL66" s="39" t="n">
         <v>2.38</v>
       </c>
       <c r="BM66" s="28" t="n">
@@ -17753,18 +17798,1255 @@
       </c>
       <c r="BN66" s="28" t="n"/>
       <c r="BO66" s="28" t="n"/>
-      <c r="BP66" s="25" t="n"/>
-      <c r="BQ66" s="27" t="n"/>
+      <c r="BP66" s="38" t="n"/>
+      <c r="BQ66" s="39" t="n"/>
       <c r="BR66" s="28" t="n"/>
       <c r="BS66" s="28" t="n"/>
       <c r="BT66" s="28" t="n"/>
-      <c r="BU66" s="25" t="n"/>
+      <c r="BU66" s="38" t="n"/>
       <c r="BV66" s="29" t="n"/>
       <c r="BW66" s="24" t="n"/>
-      <c r="BX66" s="30" t="n"/>
-      <c r="BY66" s="27" t="n"/>
+      <c r="BX66" s="40" t="n"/>
+      <c r="BY66" s="39" t="n"/>
       <c r="BZ66" s="24" t="n"/>
       <c r="CA66" s="31" t="n"/>
+    </row>
+    <row r="67" ht="36" customHeight="1">
+      <c r="A67" s="24" t="inlineStr">
+        <is>
+          <t>e05499360e0946b9</t>
+        </is>
+      </c>
+      <c r="B67" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-21T03:37:13.798671Z</t>
+        </is>
+      </c>
+      <c r="C67" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-21T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="D67" s="24" t="inlineStr">
+        <is>
+          <t>56865</t>
+        </is>
+      </c>
+      <c r="E67" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F67" s="24" t="inlineStr">
+        <is>
+          <t>Julie&amp;cie</t>
+        </is>
+      </c>
+      <c r="G67" s="24" t="inlineStr">
+        <is>
+          <t>Honvéd</t>
+        </is>
+      </c>
+      <c r="H67" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I67" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J67" s="38" t="n"/>
+      <c r="K67" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L67" s="26" t="n">
+        <v>-194</v>
+      </c>
+      <c r="M67" s="39" t="n">
+        <v>1.515464</v>
+      </c>
+      <c r="N67" s="28" t="n">
+        <v>0.659864</v>
+      </c>
+      <c r="O67" s="28" t="n">
+        <v>0.705785</v>
+      </c>
+      <c r="P67" s="28" t="n"/>
+      <c r="Q67" s="28" t="n">
+        <v>0.045785</v>
+      </c>
+      <c r="R67" s="26" t="n">
+        <v>45</v>
+      </c>
+      <c r="S67" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T67" s="24" t="inlineStr">
+        <is>
+          <t>cs2-neutral-series-elo-v1</t>
+        </is>
+      </c>
+      <c r="U67" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V67" s="24" t="n"/>
+      <c r="W67" s="26" t="n"/>
+      <c r="X67" s="26" t="n"/>
+      <c r="Y67" s="38" t="n"/>
+      <c r="Z67" s="26" t="n"/>
+      <c r="AA67" s="28" t="n"/>
+      <c r="AB67" s="28" t="n"/>
+      <c r="AC67" s="40" t="n"/>
+      <c r="AD67" s="24" t="n"/>
+      <c r="AE67" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6600 (aec-cs2-hon-jul-2026-07-21).</t>
+        </is>
+      </c>
+      <c r="AF67" s="31" t="inlineStr">
+        <is>
+          <t>Research baseline; zero-unit shadow until qualified.</t>
+        </is>
+      </c>
+      <c r="AG67" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH67" s="24" t="n"/>
+      <c r="AI67" s="31" t="n"/>
+      <c r="AJ67" s="31" t="n"/>
+      <c r="AK67" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL67" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM67" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN67" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO67" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP67" s="24" t="inlineStr">
+        <is>
+          <t>Julie&amp;cie</t>
+        </is>
+      </c>
+      <c r="AQ67" s="24" t="inlineStr">
+        <is>
+          <t>Julie&amp;cie</t>
+        </is>
+      </c>
+      <c r="AR67" s="24" t="inlineStr">
+        <is>
+          <t>Julie&amp;cie</t>
+        </is>
+      </c>
+      <c r="AS67" s="24" t="inlineStr">
+        <is>
+          <t>Honvéd</t>
+        </is>
+      </c>
+      <c r="AT67" s="24" t="inlineStr">
+        <is>
+          <t>Honvéd</t>
+        </is>
+      </c>
+      <c r="AU67" s="24" t="inlineStr">
+        <is>
+          <t>Honvéd</t>
+        </is>
+      </c>
+      <c r="AV67" s="24" t="n"/>
+      <c r="AW67" s="24" t="n"/>
+      <c r="AX67" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY67" s="24" t="n"/>
+      <c r="AZ67" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA67" s="24" t="inlineStr">
+        <is>
+          <t>9dbde86ab8062ac73a51c94b0ad431573ac8b755ccd742d86794849a749958c7</t>
+        </is>
+      </c>
+      <c r="BB67" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC67" s="24" t="inlineStr">
+        <is>
+          <t>cs2-neutral-series-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD67" s="24" t="inlineStr">
+        <is>
+          <t>9dbde86ab8062ac73a51c94b0ad431573ac8b755ccd742d86794849a749958c7</t>
+        </is>
+      </c>
+      <c r="BE67" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF67" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG67" s="24" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="BH67" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-21T03:37:13.798671Z</t>
+        </is>
+      </c>
+      <c r="BI67" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ67" s="38" t="n"/>
+      <c r="BK67" s="26" t="n">
+        <v>-194</v>
+      </c>
+      <c r="BL67" s="39" t="n">
+        <v>1.515464</v>
+      </c>
+      <c r="BM67" s="28" t="n">
+        <v>0.659864</v>
+      </c>
+      <c r="BN67" s="28" t="n"/>
+      <c r="BO67" s="28" t="n"/>
+      <c r="BP67" s="38" t="n"/>
+      <c r="BQ67" s="39" t="n"/>
+      <c r="BR67" s="28" t="n"/>
+      <c r="BS67" s="28" t="n"/>
+      <c r="BT67" s="28" t="n"/>
+      <c r="BU67" s="38" t="n"/>
+      <c r="BV67" s="29" t="n"/>
+      <c r="BW67" s="24" t="n"/>
+      <c r="BX67" s="40" t="n"/>
+      <c r="BY67" s="39" t="n"/>
+      <c r="BZ67" s="24" t="n"/>
+      <c r="CA67" s="31" t="n"/>
+    </row>
+    <row r="68" ht="36" customHeight="1">
+      <c r="A68" s="24" t="inlineStr">
+        <is>
+          <t>d8b509d231b749ff</t>
+        </is>
+      </c>
+      <c r="B68" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-21T04:39:43.652985Z</t>
+        </is>
+      </c>
+      <c r="C68" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-21T21:40:00-0400</t>
+        </is>
+      </c>
+      <c r="D68" s="24" t="inlineStr">
+        <is>
+          <t>401816213</t>
+        </is>
+      </c>
+      <c r="E68" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F68" s="24" t="inlineStr">
+        <is>
+          <t>Athletics</t>
+        </is>
+      </c>
+      <c r="G68" s="24" t="inlineStr">
+        <is>
+          <t>Arizona Diamondbacks</t>
+        </is>
+      </c>
+      <c r="H68" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I68" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J68" s="38" t="n"/>
+      <c r="K68" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L68" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="M68" s="39" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="N68" s="28" t="n">
+        <v>0.5594710000000001</v>
+      </c>
+      <c r="O68" s="28" t="n">
+        <v>0.58189</v>
+      </c>
+      <c r="P68" s="28" t="n"/>
+      <c r="Q68" s="28" t="n">
+        <v>0.022419</v>
+      </c>
+      <c r="R68" s="26" t="n">
+        <v>31</v>
+      </c>
+      <c r="S68" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T68" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="U68" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V68" s="24" t="n"/>
+      <c r="W68" s="26" t="n"/>
+      <c r="X68" s="26" t="n"/>
+      <c r="Y68" s="38" t="n"/>
+      <c r="Z68" s="26" t="n"/>
+      <c r="AA68" s="28" t="n"/>
+      <c r="AB68" s="28" t="n"/>
+      <c r="AC68" s="40" t="n"/>
+      <c r="AD68" s="24" t="n"/>
+      <c r="AE68" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5500; executable ask 0.5600 (aec-mlb-ath-az-2026-07-21).</t>
+        </is>
+      </c>
+      <c r="AF68" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; promotion gate not yet open; zero-unit research until review.</t>
+        </is>
+      </c>
+      <c r="AG68" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH68" s="24" t="n"/>
+      <c r="AI68" s="31" t="n"/>
+      <c r="AJ68" s="31" t="n"/>
+      <c r="AK68" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL68" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM68" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN68" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO68" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP68" s="24" t="inlineStr">
+        <is>
+          <t>mlb-ath</t>
+        </is>
+      </c>
+      <c r="AQ68" s="24" t="inlineStr">
+        <is>
+          <t>Athletics</t>
+        </is>
+      </c>
+      <c r="AR68" s="24" t="inlineStr">
+        <is>
+          <t>Athletics</t>
+        </is>
+      </c>
+      <c r="AS68" s="24" t="inlineStr">
+        <is>
+          <t>mlb-ari</t>
+        </is>
+      </c>
+      <c r="AT68" s="24" t="inlineStr">
+        <is>
+          <t>Arizona Diamondbacks</t>
+        </is>
+      </c>
+      <c r="AU68" s="24" t="inlineStr">
+        <is>
+          <t>Arizona Diamondbacks</t>
+        </is>
+      </c>
+      <c r="AV68" s="24" t="n"/>
+      <c r="AW68" s="24" t="n"/>
+      <c r="AX68" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY68" s="24" t="n"/>
+      <c r="AZ68" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA68" s="24" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
+      <c r="BB68" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC68" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD68" s="24" t="inlineStr">
+        <is>
+          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+        </is>
+      </c>
+      <c r="BE68" s="24" t="inlineStr">
+        <is>
+          <t>9892b2a76fbe9db3</t>
+        </is>
+      </c>
+      <c r="BF68" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG68" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BH68" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-21T04:39:17.517164Z</t>
+        </is>
+      </c>
+      <c r="BI68" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ68" s="38" t="n"/>
+      <c r="BK68" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="BL68" s="39" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="BM68" s="28" t="n">
+        <v>0.5594710000000001</v>
+      </c>
+      <c r="BN68" s="28" t="n">
+        <v>0.557214</v>
+      </c>
+      <c r="BO68" s="28" t="n"/>
+      <c r="BP68" s="38" t="n"/>
+      <c r="BQ68" s="39" t="n"/>
+      <c r="BR68" s="28" t="n"/>
+      <c r="BS68" s="28" t="n"/>
+      <c r="BT68" s="28" t="n"/>
+      <c r="BU68" s="38" t="n"/>
+      <c r="BV68" s="29" t="n"/>
+      <c r="BW68" s="24" t="n"/>
+      <c r="BX68" s="40" t="n"/>
+      <c r="BY68" s="39" t="n"/>
+      <c r="BZ68" s="24" t="n"/>
+      <c r="CA68" s="31" t="n"/>
+    </row>
+    <row r="69" ht="36" customHeight="1">
+      <c r="A69" s="24" t="inlineStr">
+        <is>
+          <t>91bedfe6718a4a34</t>
+        </is>
+      </c>
+      <c r="B69" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-21T04:40:39.530059Z</t>
+        </is>
+      </c>
+      <c r="C69" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-22T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="D69" s="24" t="inlineStr">
+        <is>
+          <t>55996</t>
+        </is>
+      </c>
+      <c r="E69" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F69" s="24" t="inlineStr">
+        <is>
+          <t>Team WE</t>
+        </is>
+      </c>
+      <c r="G69" s="24" t="inlineStr">
+        <is>
+          <t>Top Esports</t>
+        </is>
+      </c>
+      <c r="H69" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I69" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J69" s="38" t="n"/>
+      <c r="K69" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L69" s="26" t="n">
+        <v>-203</v>
+      </c>
+      <c r="M69" s="39" t="n">
+        <v>1.492611</v>
+      </c>
+      <c r="N69" s="28" t="n">
+        <v>0.669967</v>
+      </c>
+      <c r="O69" s="28" t="n">
+        <v>0.748396</v>
+      </c>
+      <c r="P69" s="28" t="n"/>
+      <c r="Q69" s="28" t="n">
+        <v>0.07839599999999999</v>
+      </c>
+      <c r="R69" s="26" t="n">
+        <v>78</v>
+      </c>
+      <c r="S69" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T69" s="24" t="inlineStr">
+        <is>
+          <t>lol-neutral-series-elo-v1</t>
+        </is>
+      </c>
+      <c r="U69" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V69" s="24" t="n"/>
+      <c r="W69" s="26" t="n"/>
+      <c r="X69" s="26" t="n"/>
+      <c r="Y69" s="38" t="n"/>
+      <c r="Z69" s="26" t="n"/>
+      <c r="AA69" s="28" t="n"/>
+      <c r="AB69" s="28" t="n"/>
+      <c r="AC69" s="40" t="n"/>
+      <c r="AD69" s="24" t="n"/>
+      <c r="AE69" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6700 (aec-lol-tes-we-2026-07-22).</t>
+        </is>
+      </c>
+      <c r="AF69" s="31" t="inlineStr">
+        <is>
+          <t>Research baseline; zero-unit shadow until qualified.</t>
+        </is>
+      </c>
+      <c r="AG69" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH69" s="24" t="n"/>
+      <c r="AI69" s="31" t="n"/>
+      <c r="AJ69" s="31" t="n"/>
+      <c r="AK69" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL69" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM69" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN69" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO69" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP69" s="24" t="inlineStr">
+        <is>
+          <t>Team WE</t>
+        </is>
+      </c>
+      <c r="AQ69" s="24" t="inlineStr">
+        <is>
+          <t>Team WE</t>
+        </is>
+      </c>
+      <c r="AR69" s="24" t="inlineStr">
+        <is>
+          <t>Team WE</t>
+        </is>
+      </c>
+      <c r="AS69" s="24" t="inlineStr">
+        <is>
+          <t>Top Esports</t>
+        </is>
+      </c>
+      <c r="AT69" s="24" t="inlineStr">
+        <is>
+          <t>Top Esports</t>
+        </is>
+      </c>
+      <c r="AU69" s="24" t="inlineStr">
+        <is>
+          <t>Top Esports</t>
+        </is>
+      </c>
+      <c r="AV69" s="24" t="n"/>
+      <c r="AW69" s="24" t="n"/>
+      <c r="AX69" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY69" s="24" t="n"/>
+      <c r="AZ69" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA69" s="24" t="inlineStr">
+        <is>
+          <t>82612f1b27d5065af8d70fd6669509ff00dc1c7e3a91bb423192bf3b0a9736ce</t>
+        </is>
+      </c>
+      <c r="BB69" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC69" s="24" t="inlineStr">
+        <is>
+          <t>lol-neutral-series-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD69" s="24" t="inlineStr">
+        <is>
+          <t>82612f1b27d5065af8d70fd6669509ff00dc1c7e3a91bb423192bf3b0a9736ce</t>
+        </is>
+      </c>
+      <c r="BE69" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF69" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG69" s="24" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="BH69" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-21T04:40:39.530059Z</t>
+        </is>
+      </c>
+      <c r="BI69" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ69" s="38" t="n"/>
+      <c r="BK69" s="26" t="n">
+        <v>-203</v>
+      </c>
+      <c r="BL69" s="39" t="n">
+        <v>1.492611</v>
+      </c>
+      <c r="BM69" s="28" t="n">
+        <v>0.669967</v>
+      </c>
+      <c r="BN69" s="28" t="n"/>
+      <c r="BO69" s="28" t="n"/>
+      <c r="BP69" s="38" t="n"/>
+      <c r="BQ69" s="39" t="n"/>
+      <c r="BR69" s="28" t="n"/>
+      <c r="BS69" s="28" t="n"/>
+      <c r="BT69" s="28" t="n"/>
+      <c r="BU69" s="38" t="n"/>
+      <c r="BV69" s="29" t="n"/>
+      <c r="BW69" s="24" t="n"/>
+      <c r="BX69" s="40" t="n"/>
+      <c r="BY69" s="39" t="n"/>
+      <c r="BZ69" s="24" t="n"/>
+      <c r="CA69" s="31" t="n"/>
+    </row>
+    <row r="70" ht="36" customHeight="1">
+      <c r="A70" s="24" t="inlineStr">
+        <is>
+          <t>6bfc970ce3e64df9</t>
+        </is>
+      </c>
+      <c r="B70" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-21T04:40:39.852711Z</t>
+        </is>
+      </c>
+      <c r="C70" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-22T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="D70" s="24" t="inlineStr">
+        <is>
+          <t>56056</t>
+        </is>
+      </c>
+      <c r="E70" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F70" s="24" t="inlineStr">
+        <is>
+          <t>FALKE Esports</t>
+        </is>
+      </c>
+      <c r="G70" s="24" t="inlineStr">
+        <is>
+          <t>UB Alma Mater</t>
+        </is>
+      </c>
+      <c r="H70" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I70" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J70" s="38" t="n"/>
+      <c r="K70" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L70" s="26" t="n">
+        <v>203</v>
+      </c>
+      <c r="M70" s="39" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="N70" s="28" t="n">
+        <v>0.330033</v>
+      </c>
+      <c r="O70" s="28" t="n">
+        <v>0.64693</v>
+      </c>
+      <c r="P70" s="28" t="n"/>
+      <c r="Q70" s="28" t="n">
+        <v>0.31693</v>
+      </c>
+      <c r="R70" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S70" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T70" s="24" t="inlineStr">
+        <is>
+          <t>lol-neutral-series-elo-v1</t>
+        </is>
+      </c>
+      <c r="U70" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V70" s="24" t="n"/>
+      <c r="W70" s="26" t="n"/>
+      <c r="X70" s="26" t="n"/>
+      <c r="Y70" s="38" t="n"/>
+      <c r="Z70" s="26" t="n"/>
+      <c r="AA70" s="28" t="n"/>
+      <c r="AB70" s="28" t="n"/>
+      <c r="AC70" s="40" t="n"/>
+      <c r="AD70" s="24" t="n"/>
+      <c r="AE70" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.3300 (aec-lol-ub-flk-2026-07-22).</t>
+        </is>
+      </c>
+      <c r="AF70" s="31" t="inlineStr">
+        <is>
+          <t>Research baseline; zero-unit shadow until qualified.</t>
+        </is>
+      </c>
+      <c r="AG70" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH70" s="24" t="n"/>
+      <c r="AI70" s="31" t="n"/>
+      <c r="AJ70" s="31" t="n"/>
+      <c r="AK70" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL70" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM70" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN70" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO70" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP70" s="24" t="inlineStr">
+        <is>
+          <t>FALKE Esports</t>
+        </is>
+      </c>
+      <c r="AQ70" s="24" t="inlineStr">
+        <is>
+          <t>FALKE Esports</t>
+        </is>
+      </c>
+      <c r="AR70" s="24" t="inlineStr">
+        <is>
+          <t>FALKE Esports</t>
+        </is>
+      </c>
+      <c r="AS70" s="24" t="inlineStr">
+        <is>
+          <t>UB Alma Mater</t>
+        </is>
+      </c>
+      <c r="AT70" s="24" t="inlineStr">
+        <is>
+          <t>UB Alma Mater</t>
+        </is>
+      </c>
+      <c r="AU70" s="24" t="inlineStr">
+        <is>
+          <t>UB Alma Mater</t>
+        </is>
+      </c>
+      <c r="AV70" s="24" t="n"/>
+      <c r="AW70" s="24" t="n"/>
+      <c r="AX70" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY70" s="24" t="n"/>
+      <c r="AZ70" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA70" s="24" t="inlineStr">
+        <is>
+          <t>82612f1b27d5065af8d70fd6669509ff00dc1c7e3a91bb423192bf3b0a9736ce</t>
+        </is>
+      </c>
+      <c r="BB70" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC70" s="24" t="inlineStr">
+        <is>
+          <t>lol-neutral-series-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD70" s="24" t="inlineStr">
+        <is>
+          <t>82612f1b27d5065af8d70fd6669509ff00dc1c7e3a91bb423192bf3b0a9736ce</t>
+        </is>
+      </c>
+      <c r="BE70" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF70" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG70" s="24" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="BH70" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-21T04:40:39.852711Z</t>
+        </is>
+      </c>
+      <c r="BI70" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ70" s="38" t="n"/>
+      <c r="BK70" s="26" t="n">
+        <v>203</v>
+      </c>
+      <c r="BL70" s="39" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="BM70" s="28" t="n">
+        <v>0.330033</v>
+      </c>
+      <c r="BN70" s="28" t="n"/>
+      <c r="BO70" s="28" t="n"/>
+      <c r="BP70" s="38" t="n"/>
+      <c r="BQ70" s="39" t="n"/>
+      <c r="BR70" s="28" t="n"/>
+      <c r="BS70" s="28" t="n"/>
+      <c r="BT70" s="28" t="n"/>
+      <c r="BU70" s="38" t="n"/>
+      <c r="BV70" s="29" t="n"/>
+      <c r="BW70" s="24" t="n"/>
+      <c r="BX70" s="40" t="n"/>
+      <c r="BY70" s="39" t="n"/>
+      <c r="BZ70" s="24" t="n"/>
+      <c r="CA70" s="31" t="n"/>
+    </row>
+    <row r="71" ht="36" customHeight="1">
+      <c r="A71" s="24" t="inlineStr">
+        <is>
+          <t>9b7656db50b347b6</t>
+        </is>
+      </c>
+      <c r="B71" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-21T04:40:40.178590Z</t>
+        </is>
+      </c>
+      <c r="C71" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-22T17:30:00Z</t>
+        </is>
+      </c>
+      <c r="D71" s="24" t="inlineStr">
+        <is>
+          <t>56127</t>
+        </is>
+      </c>
+      <c r="E71" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F71" s="24" t="inlineStr">
+        <is>
+          <t>UCAM Esports Club</t>
+        </is>
+      </c>
+      <c r="G71" s="24" t="inlineStr">
+        <is>
+          <t>Barça eSports</t>
+        </is>
+      </c>
+      <c r="H71" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I71" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J71" s="38" t="n"/>
+      <c r="K71" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L71" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="M71" s="39" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="N71" s="28" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="O71" s="28" t="n">
+        <v>0.6951349999999999</v>
+      </c>
+      <c r="P71" s="28" t="n"/>
+      <c r="Q71" s="28" t="n">
+        <v>0.105135</v>
+      </c>
+      <c r="R71" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S71" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T71" s="24" t="inlineStr">
+        <is>
+          <t>lol-neutral-series-elo-v1</t>
+        </is>
+      </c>
+      <c r="U71" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V71" s="24" t="n"/>
+      <c r="W71" s="26" t="n"/>
+      <c r="X71" s="26" t="n"/>
+      <c r="Y71" s="38" t="n"/>
+      <c r="Z71" s="26" t="n"/>
+      <c r="AA71" s="28" t="n"/>
+      <c r="AB71" s="28" t="n"/>
+      <c r="AC71" s="40" t="n"/>
+      <c r="AD71" s="24" t="n"/>
+      <c r="AE71" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5900 (aec-lol-bar-ucam-2026-07-22).</t>
+        </is>
+      </c>
+      <c r="AF71" s="31" t="inlineStr">
+        <is>
+          <t>Research baseline; zero-unit shadow until qualified.</t>
+        </is>
+      </c>
+      <c r="AG71" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH71" s="24" t="n"/>
+      <c r="AI71" s="31" t="n"/>
+      <c r="AJ71" s="31" t="n"/>
+      <c r="AK71" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL71" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM71" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN71" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO71" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP71" s="24" t="inlineStr">
+        <is>
+          <t>UCAM Esports Club</t>
+        </is>
+      </c>
+      <c r="AQ71" s="24" t="inlineStr">
+        <is>
+          <t>UCAM Esports Club</t>
+        </is>
+      </c>
+      <c r="AR71" s="24" t="inlineStr">
+        <is>
+          <t>UCAM Esports Club</t>
+        </is>
+      </c>
+      <c r="AS71" s="24" t="inlineStr">
+        <is>
+          <t>Barça eSports</t>
+        </is>
+      </c>
+      <c r="AT71" s="24" t="inlineStr">
+        <is>
+          <t>Barça eSports</t>
+        </is>
+      </c>
+      <c r="AU71" s="24" t="inlineStr">
+        <is>
+          <t>Barça eSports</t>
+        </is>
+      </c>
+      <c r="AV71" s="24" t="n"/>
+      <c r="AW71" s="24" t="n"/>
+      <c r="AX71" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY71" s="24" t="n"/>
+      <c r="AZ71" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA71" s="24" t="inlineStr">
+        <is>
+          <t>82612f1b27d5065af8d70fd6669509ff00dc1c7e3a91bb423192bf3b0a9736ce</t>
+        </is>
+      </c>
+      <c r="BB71" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC71" s="24" t="inlineStr">
+        <is>
+          <t>lol-neutral-series-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD71" s="24" t="inlineStr">
+        <is>
+          <t>82612f1b27d5065af8d70fd6669509ff00dc1c7e3a91bb423192bf3b0a9736ce</t>
+        </is>
+      </c>
+      <c r="BE71" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF71" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG71" s="24" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="BH71" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-21T04:40:40.178590Z</t>
+        </is>
+      </c>
+      <c r="BI71" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ71" s="38" t="n"/>
+      <c r="BK71" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="BL71" s="39" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="BM71" s="28" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="BN71" s="28" t="n"/>
+      <c r="BO71" s="28" t="n"/>
+      <c r="BP71" s="38" t="n"/>
+      <c r="BQ71" s="39" t="n"/>
+      <c r="BR71" s="28" t="n"/>
+      <c r="BS71" s="28" t="n"/>
+      <c r="BT71" s="28" t="n"/>
+      <c r="BU71" s="38" t="n"/>
+      <c r="BV71" s="29" t="n"/>
+      <c r="BW71" s="24" t="n"/>
+      <c r="BX71" s="40" t="n"/>
+      <c r="BY71" s="39" t="n"/>
+      <c r="BZ71" s="24" t="n"/>
+      <c r="CA71" s="31" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/picks.xlsx
+++ b/data/picks.xlsx
@@ -327,8 +327,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CA71" headerRowCount="1">
-  <autoFilter ref="A1:CA71"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CA75" headerRowCount="1">
+  <autoFilter ref="A1:CA75"/>
   <tableColumns count="79">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -765,19 +765,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$71)</f>
+        <f>COUNTA('Picks'!$A$2:$A$75)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$71,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$75,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$71,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$75,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$71,"settled",'Picks'!$V$2:$V$71,"win")+COUNTIFS('Picks'!$U$2:$U$71,"settled",'Picks'!$V$2:$V$71,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$75,"settled",'Picks'!$V$2:$V$75,"win")+COUNTIFS('Picks'!$U$2:$U$75,"settled",'Picks'!$V$2:$V$75,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -806,19 +806,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$71,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$75,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$71,"&gt;0",'Picks'!$V$2:$V$71,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$71,"&gt;0",'Picks'!$V$2:$V$71,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$75,"&gt;0",'Picks'!$V$2:$V$75,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$75,"&gt;0",'Picks'!$V$2:$V$75,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="32">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$71,"&gt;0",'Picks'!$V$2:$V$71,"win")/(COUNTIFS('Picks'!$BX$2:$BX$71,"&gt;0",'Picks'!$V$2:$V$71,"win")+COUNTIFS('Picks'!$BX$2:$BX$71,"&gt;0",'Picks'!$V$2:$V$71,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$75,"&gt;0",'Picks'!$V$2:$V$75,"win")/(COUNTIFS('Picks'!$BX$2:$BX$75,"&gt;0",'Picks'!$V$2:$V$75,"win")+COUNTIFS('Picks'!$BX$2:$BX$75,"&gt;0",'Picks'!$V$2:$V$75,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="32">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$71)/SUM('Picks'!$BX$2:$BX$71),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$75)/SUM('Picks'!$BX$2:$BX$75),0)</f>
         <v/>
       </c>
     </row>
@@ -847,19 +847,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="33">
-        <f>SUM('Picks'!$BY$2:$BY$71)</f>
+        <f>SUM('Picks'!$BY$2:$BY$75)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$71,"&lt;&gt;",'Picks'!$AB$2:$AB$71),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$75,"&lt;&gt;",'Picks'!$AB$2:$AB$75),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$71,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$71,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$75,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$75,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="33">
-        <f>SUMIFS('Picks'!$AC$2:$AC$71,'Picks'!$AM$2:$AM$71,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$75,'Picks'!$AM$2:$AM$75,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -915,15 +915,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$71,$A14,'Picks'!$U$2:$U$71,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$75,$A14,'Picks'!$U$2:$U$75,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$71,$A14,'Picks'!$U$2:$U$71,"settled",'Picks'!$V$2:$V$71,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$75,$A14,'Picks'!$U$2:$U$75,"settled",'Picks'!$V$2:$V$75,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$71,$A14,'Picks'!$U$2:$U$71,"settled",'Picks'!$V$2:$V$71,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$75,$A14,'Picks'!$U$2:$U$75,"settled",'Picks'!$V$2:$V$75,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="34">
@@ -931,11 +931,11 @@
         <v/>
       </c>
       <c r="F14" s="35">
-        <f>SUMIFS('Picks'!$BY$2:$BY$71,'Picks'!$H$2:$H$71,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$75,'Picks'!$H$2:$H$75,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$71,'Picks'!$H$2:$H$71,$A14,'Picks'!$U$2:$U$71,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$75,'Picks'!$H$2:$H$75,$A14,'Picks'!$U$2:$U$75,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -946,15 +946,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$71,$A15,'Picks'!$U$2:$U$71,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$75,$A15,'Picks'!$U$2:$U$75,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$71,$A15,'Picks'!$U$2:$U$71,"settled",'Picks'!$V$2:$V$71,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$75,$A15,'Picks'!$U$2:$U$75,"settled",'Picks'!$V$2:$V$75,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$71,$A15,'Picks'!$U$2:$U$71,"settled",'Picks'!$V$2:$V$71,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$75,$A15,'Picks'!$U$2:$U$75,"settled",'Picks'!$V$2:$V$75,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="36">
@@ -962,11 +962,11 @@
         <v/>
       </c>
       <c r="F15" s="37">
-        <f>SUMIFS('Picks'!$BY$2:$BY$71,'Picks'!$H$2:$H$71,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$75,'Picks'!$H$2:$H$75,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$71,'Picks'!$H$2:$H$71,$A15,'Picks'!$U$2:$U$71,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$75,'Picks'!$H$2:$H$75,$A15,'Picks'!$U$2:$U$75,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -977,15 +977,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$71,$A16,'Picks'!$U$2:$U$71,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$75,$A16,'Picks'!$U$2:$U$75,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$71,$A16,'Picks'!$U$2:$U$71,"settled",'Picks'!$V$2:$V$71,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$75,$A16,'Picks'!$U$2:$U$75,"settled",'Picks'!$V$2:$V$75,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$71,$A16,'Picks'!$U$2:$U$71,"settled",'Picks'!$V$2:$V$71,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$75,$A16,'Picks'!$U$2:$U$75,"settled",'Picks'!$V$2:$V$75,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="34">
@@ -993,11 +993,11 @@
         <v/>
       </c>
       <c r="F16" s="35">
-        <f>SUMIFS('Picks'!$BY$2:$BY$71,'Picks'!$H$2:$H$71,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$75,'Picks'!$H$2:$H$75,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$71,'Picks'!$H$2:$H$71,$A16,'Picks'!$U$2:$U$71,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$75,'Picks'!$H$2:$H$75,$A16,'Picks'!$U$2:$U$75,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CA71"/>
+  <dimension ref="A1:CA75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -19048,6 +19048,994 @@
       <c r="BZ71" s="24" t="n"/>
       <c r="CA71" s="31" t="n"/>
     </row>
+    <row r="72" ht="36" customHeight="1">
+      <c r="A72" s="24" t="inlineStr">
+        <is>
+          <t>c8e1a4ddb2b147b4</t>
+        </is>
+      </c>
+      <c r="B72" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-21T05:21:42.337431Z</t>
+        </is>
+      </c>
+      <c r="C72" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-21T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="D72" s="24" t="inlineStr">
+        <is>
+          <t>58068</t>
+        </is>
+      </c>
+      <c r="E72" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F72" s="24" t="inlineStr">
+        <is>
+          <t>Strael-Bora</t>
+        </is>
+      </c>
+      <c r="G72" s="24" t="inlineStr">
+        <is>
+          <t>Bushido Wildcats</t>
+        </is>
+      </c>
+      <c r="H72" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I72" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J72" s="38" t="n"/>
+      <c r="K72" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L72" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="M72" s="39" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="N72" s="28" t="n">
+        <v>0.690402</v>
+      </c>
+      <c r="O72" s="28" t="n">
+        <v>0.710718</v>
+      </c>
+      <c r="P72" s="28" t="n"/>
+      <c r="Q72" s="28" t="n">
+        <v>0.020718</v>
+      </c>
+      <c r="R72" s="26" t="n">
+        <v>20</v>
+      </c>
+      <c r="S72" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T72" s="24" t="inlineStr">
+        <is>
+          <t>cs2-neutral-series-elo-v1</t>
+        </is>
+      </c>
+      <c r="U72" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V72" s="24" t="n"/>
+      <c r="W72" s="26" t="n"/>
+      <c r="X72" s="26" t="n"/>
+      <c r="Y72" s="38" t="n"/>
+      <c r="Z72" s="26" t="n"/>
+      <c r="AA72" s="28" t="n"/>
+      <c r="AB72" s="28" t="n"/>
+      <c r="AC72" s="40" t="n"/>
+      <c r="AD72" s="24" t="n"/>
+      <c r="AE72" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6900 (aec-cs2-bw-sb-2026-07-21).</t>
+        </is>
+      </c>
+      <c r="AF72" s="31" t="inlineStr">
+        <is>
+          <t>Research baseline; zero-unit shadow until qualified.</t>
+        </is>
+      </c>
+      <c r="AG72" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH72" s="24" t="n"/>
+      <c r="AI72" s="31" t="n"/>
+      <c r="AJ72" s="31" t="n"/>
+      <c r="AK72" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL72" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM72" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN72" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO72" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP72" s="24" t="inlineStr">
+        <is>
+          <t>Strael-Bora</t>
+        </is>
+      </c>
+      <c r="AQ72" s="24" t="inlineStr">
+        <is>
+          <t>Strael-Bora</t>
+        </is>
+      </c>
+      <c r="AR72" s="24" t="inlineStr">
+        <is>
+          <t>Strael-Bora</t>
+        </is>
+      </c>
+      <c r="AS72" s="24" t="inlineStr">
+        <is>
+          <t>Bushido Wildcats</t>
+        </is>
+      </c>
+      <c r="AT72" s="24" t="inlineStr">
+        <is>
+          <t>Bushido Wildcats</t>
+        </is>
+      </c>
+      <c r="AU72" s="24" t="inlineStr">
+        <is>
+          <t>Bushido Wildcats</t>
+        </is>
+      </c>
+      <c r="AV72" s="24" t="n"/>
+      <c r="AW72" s="24" t="n"/>
+      <c r="AX72" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY72" s="24" t="n"/>
+      <c r="AZ72" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA72" s="24" t="inlineStr">
+        <is>
+          <t>9dbde86ab8062ac73a51c94b0ad431573ac8b755ccd742d86794849a749958c7</t>
+        </is>
+      </c>
+      <c r="BB72" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC72" s="24" t="inlineStr">
+        <is>
+          <t>cs2-neutral-series-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD72" s="24" t="inlineStr">
+        <is>
+          <t>9dbde86ab8062ac73a51c94b0ad431573ac8b755ccd742d86794849a749958c7</t>
+        </is>
+      </c>
+      <c r="BE72" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF72" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG72" s="24" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="BH72" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-21T05:21:42.337431Z</t>
+        </is>
+      </c>
+      <c r="BI72" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ72" s="38" t="n"/>
+      <c r="BK72" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="BL72" s="39" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="BM72" s="28" t="n">
+        <v>0.690402</v>
+      </c>
+      <c r="BN72" s="28" t="n"/>
+      <c r="BO72" s="28" t="n"/>
+      <c r="BP72" s="38" t="n"/>
+      <c r="BQ72" s="39" t="n"/>
+      <c r="BR72" s="28" t="n"/>
+      <c r="BS72" s="28" t="n"/>
+      <c r="BT72" s="28" t="n"/>
+      <c r="BU72" s="38" t="n"/>
+      <c r="BV72" s="29" t="n"/>
+      <c r="BW72" s="24" t="n"/>
+      <c r="BX72" s="40" t="n"/>
+      <c r="BY72" s="39" t="n"/>
+      <c r="BZ72" s="24" t="n"/>
+      <c r="CA72" s="31" t="n"/>
+    </row>
+    <row r="73" ht="36" customHeight="1">
+      <c r="A73" s="24" t="inlineStr">
+        <is>
+          <t>29fb46cae668405f</t>
+        </is>
+      </c>
+      <c r="B73" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-21T08:13:56.528127Z</t>
+        </is>
+      </c>
+      <c r="C73" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-21T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="D73" s="24" t="inlineStr">
+        <is>
+          <t>57524</t>
+        </is>
+      </c>
+      <c r="E73" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F73" s="24" t="inlineStr">
+        <is>
+          <t>Entropy</t>
+        </is>
+      </c>
+      <c r="G73" s="24" t="inlineStr">
+        <is>
+          <t>Esport Academy Copenhagen</t>
+        </is>
+      </c>
+      <c r="H73" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I73" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J73" s="38" t="n"/>
+      <c r="K73" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L73" s="26" t="n">
+        <v>-108</v>
+      </c>
+      <c r="M73" s="39" t="n">
+        <v>1.925926</v>
+      </c>
+      <c r="N73" s="28" t="n">
+        <v>0.519231</v>
+      </c>
+      <c r="O73" s="28" t="n">
+        <v>0.602113</v>
+      </c>
+      <c r="P73" s="28" t="n"/>
+      <c r="Q73" s="28" t="n">
+        <v>0.08211300000000001</v>
+      </c>
+      <c r="R73" s="26" t="n">
+        <v>82</v>
+      </c>
+      <c r="S73" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T73" s="24" t="inlineStr">
+        <is>
+          <t>cs2-neutral-series-elo-v1</t>
+        </is>
+      </c>
+      <c r="U73" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V73" s="24" t="n"/>
+      <c r="W73" s="26" t="n"/>
+      <c r="X73" s="26" t="n"/>
+      <c r="Y73" s="38" t="n"/>
+      <c r="Z73" s="26" t="n"/>
+      <c r="AA73" s="28" t="n"/>
+      <c r="AB73" s="28" t="n"/>
+      <c r="AC73" s="40" t="n"/>
+      <c r="AD73" s="24" t="n"/>
+      <c r="AE73" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5200 (aec-cs2-eac-ent-2026-07-21).</t>
+        </is>
+      </c>
+      <c r="AF73" s="31" t="inlineStr">
+        <is>
+          <t>Research baseline; zero-unit shadow until qualified.</t>
+        </is>
+      </c>
+      <c r="AG73" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH73" s="24" t="n"/>
+      <c r="AI73" s="31" t="n"/>
+      <c r="AJ73" s="31" t="n"/>
+      <c r="AK73" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL73" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM73" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN73" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO73" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP73" s="24" t="inlineStr">
+        <is>
+          <t>Entropy</t>
+        </is>
+      </c>
+      <c r="AQ73" s="24" t="inlineStr">
+        <is>
+          <t>Entropy</t>
+        </is>
+      </c>
+      <c r="AR73" s="24" t="inlineStr">
+        <is>
+          <t>Entropy</t>
+        </is>
+      </c>
+      <c r="AS73" s="24" t="inlineStr">
+        <is>
+          <t>Esport Academy Copenhagen</t>
+        </is>
+      </c>
+      <c r="AT73" s="24" t="inlineStr">
+        <is>
+          <t>Esport Academy Copenhagen</t>
+        </is>
+      </c>
+      <c r="AU73" s="24" t="inlineStr">
+        <is>
+          <t>Esport Academy Copenhagen</t>
+        </is>
+      </c>
+      <c r="AV73" s="24" t="n"/>
+      <c r="AW73" s="24" t="n"/>
+      <c r="AX73" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY73" s="24" t="n"/>
+      <c r="AZ73" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA73" s="24" t="inlineStr">
+        <is>
+          <t>9dbde86ab8062ac73a51c94b0ad431573ac8b755ccd742d86794849a749958c7</t>
+        </is>
+      </c>
+      <c r="BB73" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC73" s="24" t="inlineStr">
+        <is>
+          <t>cs2-neutral-series-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD73" s="24" t="inlineStr">
+        <is>
+          <t>9dbde86ab8062ac73a51c94b0ad431573ac8b755ccd742d86794849a749958c7</t>
+        </is>
+      </c>
+      <c r="BE73" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF73" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG73" s="24" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="BH73" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-21T08:13:56.528127Z</t>
+        </is>
+      </c>
+      <c r="BI73" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ73" s="38" t="n"/>
+      <c r="BK73" s="26" t="n">
+        <v>-108</v>
+      </c>
+      <c r="BL73" s="39" t="n">
+        <v>1.925926</v>
+      </c>
+      <c r="BM73" s="28" t="n">
+        <v>0.519231</v>
+      </c>
+      <c r="BN73" s="28" t="n"/>
+      <c r="BO73" s="28" t="n"/>
+      <c r="BP73" s="38" t="n"/>
+      <c r="BQ73" s="39" t="n"/>
+      <c r="BR73" s="28" t="n"/>
+      <c r="BS73" s="28" t="n"/>
+      <c r="BT73" s="28" t="n"/>
+      <c r="BU73" s="38" t="n"/>
+      <c r="BV73" s="29" t="n"/>
+      <c r="BW73" s="24" t="n"/>
+      <c r="BX73" s="40" t="n"/>
+      <c r="BY73" s="39" t="n"/>
+      <c r="BZ73" s="24" t="n"/>
+      <c r="CA73" s="31" t="n"/>
+    </row>
+    <row r="74" ht="36" customHeight="1">
+      <c r="A74" s="24" t="inlineStr">
+        <is>
+          <t>42c5e25bbaa741b6</t>
+        </is>
+      </c>
+      <c r="B74" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-21T08:13:57.068809Z</t>
+        </is>
+      </c>
+      <c r="C74" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-21T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="D74" s="24" t="inlineStr">
+        <is>
+          <t>56032</t>
+        </is>
+      </c>
+      <c r="E74" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F74" s="24" t="inlineStr">
+        <is>
+          <t>FOKUS</t>
+        </is>
+      </c>
+      <c r="G74" s="24" t="inlineStr">
+        <is>
+          <t>Astralis</t>
+        </is>
+      </c>
+      <c r="H74" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I74" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J74" s="38" t="n"/>
+      <c r="K74" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L74" s="26" t="n">
+        <v>-233</v>
+      </c>
+      <c r="M74" s="39" t="n">
+        <v>1.429185</v>
+      </c>
+      <c r="N74" s="28" t="n">
+        <v>0.6997</v>
+      </c>
+      <c r="O74" s="28" t="n">
+        <v>0.725656</v>
+      </c>
+      <c r="P74" s="28" t="n"/>
+      <c r="Q74" s="28" t="n">
+        <v>0.025656</v>
+      </c>
+      <c r="R74" s="26" t="n">
+        <v>25</v>
+      </c>
+      <c r="S74" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T74" s="24" t="inlineStr">
+        <is>
+          <t>cs2-neutral-series-elo-v1</t>
+        </is>
+      </c>
+      <c r="U74" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V74" s="24" t="n"/>
+      <c r="W74" s="26" t="n"/>
+      <c r="X74" s="26" t="n"/>
+      <c r="Y74" s="38" t="n"/>
+      <c r="Z74" s="26" t="n"/>
+      <c r="AA74" s="28" t="n"/>
+      <c r="AB74" s="28" t="n"/>
+      <c r="AC74" s="40" t="n"/>
+      <c r="AD74" s="24" t="n"/>
+      <c r="AE74" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.7000 (aec-cs2-ast-fokus-2026-07-21).</t>
+        </is>
+      </c>
+      <c r="AF74" s="31" t="inlineStr">
+        <is>
+          <t>Research baseline; zero-unit shadow until qualified.</t>
+        </is>
+      </c>
+      <c r="AG74" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH74" s="24" t="n"/>
+      <c r="AI74" s="31" t="n"/>
+      <c r="AJ74" s="31" t="n"/>
+      <c r="AK74" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL74" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM74" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN74" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO74" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP74" s="24" t="inlineStr">
+        <is>
+          <t>FOKUS</t>
+        </is>
+      </c>
+      <c r="AQ74" s="24" t="inlineStr">
+        <is>
+          <t>FOKUS</t>
+        </is>
+      </c>
+      <c r="AR74" s="24" t="inlineStr">
+        <is>
+          <t>FOKUS</t>
+        </is>
+      </c>
+      <c r="AS74" s="24" t="inlineStr">
+        <is>
+          <t>Astralis</t>
+        </is>
+      </c>
+      <c r="AT74" s="24" t="inlineStr">
+        <is>
+          <t>Astralis</t>
+        </is>
+      </c>
+      <c r="AU74" s="24" t="inlineStr">
+        <is>
+          <t>Astralis</t>
+        </is>
+      </c>
+      <c r="AV74" s="24" t="n"/>
+      <c r="AW74" s="24" t="n"/>
+      <c r="AX74" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY74" s="24" t="n"/>
+      <c r="AZ74" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA74" s="24" t="inlineStr">
+        <is>
+          <t>9dbde86ab8062ac73a51c94b0ad431573ac8b755ccd742d86794849a749958c7</t>
+        </is>
+      </c>
+      <c r="BB74" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC74" s="24" t="inlineStr">
+        <is>
+          <t>cs2-neutral-series-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD74" s="24" t="inlineStr">
+        <is>
+          <t>9dbde86ab8062ac73a51c94b0ad431573ac8b755ccd742d86794849a749958c7</t>
+        </is>
+      </c>
+      <c r="BE74" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF74" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG74" s="24" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="BH74" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-21T08:13:57.068809Z</t>
+        </is>
+      </c>
+      <c r="BI74" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ74" s="38" t="n"/>
+      <c r="BK74" s="26" t="n">
+        <v>-233</v>
+      </c>
+      <c r="BL74" s="39" t="n">
+        <v>1.429185</v>
+      </c>
+      <c r="BM74" s="28" t="n">
+        <v>0.6997</v>
+      </c>
+      <c r="BN74" s="28" t="n"/>
+      <c r="BO74" s="28" t="n"/>
+      <c r="BP74" s="38" t="n"/>
+      <c r="BQ74" s="39" t="n"/>
+      <c r="BR74" s="28" t="n"/>
+      <c r="BS74" s="28" t="n"/>
+      <c r="BT74" s="28" t="n"/>
+      <c r="BU74" s="38" t="n"/>
+      <c r="BV74" s="29" t="n"/>
+      <c r="BW74" s="24" t="n"/>
+      <c r="BX74" s="40" t="n"/>
+      <c r="BY74" s="39" t="n"/>
+      <c r="BZ74" s="24" t="n"/>
+      <c r="CA74" s="31" t="n"/>
+    </row>
+    <row r="75" ht="36" customHeight="1">
+      <c r="A75" s="24" t="inlineStr">
+        <is>
+          <t>e4f64939c21b430a</t>
+        </is>
+      </c>
+      <c r="B75" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-21T08:13:57.416034Z</t>
+        </is>
+      </c>
+      <c r="C75" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-21T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="D75" s="24" t="inlineStr">
+        <is>
+          <t>57988</t>
+        </is>
+      </c>
+      <c r="E75" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F75" s="24" t="inlineStr">
+        <is>
+          <t>Just Players</t>
+        </is>
+      </c>
+      <c r="G75" s="24" t="inlineStr">
+        <is>
+          <t>ex-RUSTEC</t>
+        </is>
+      </c>
+      <c r="H75" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I75" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J75" s="38" t="n"/>
+      <c r="K75" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L75" s="26" t="n">
+        <v>-117</v>
+      </c>
+      <c r="M75" s="39" t="n">
+        <v>1.854701</v>
+      </c>
+      <c r="N75" s="28" t="n">
+        <v>0.539171</v>
+      </c>
+      <c r="O75" s="28" t="n">
+        <v>0.6339399999999999</v>
+      </c>
+      <c r="P75" s="28" t="n"/>
+      <c r="Q75" s="28" t="n">
+        <v>0.09394</v>
+      </c>
+      <c r="R75" s="26" t="n">
+        <v>93</v>
+      </c>
+      <c r="S75" s="29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T75" s="24" t="inlineStr">
+        <is>
+          <t>cs2-neutral-series-elo-v1</t>
+        </is>
+      </c>
+      <c r="U75" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V75" s="24" t="n"/>
+      <c r="W75" s="26" t="n"/>
+      <c r="X75" s="26" t="n"/>
+      <c r="Y75" s="38" t="n"/>
+      <c r="Z75" s="26" t="n"/>
+      <c r="AA75" s="28" t="n"/>
+      <c r="AB75" s="28" t="n"/>
+      <c r="AC75" s="40" t="n"/>
+      <c r="AD75" s="24" t="n"/>
+      <c r="AE75" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5400 (aec-cs2-erx-jpu-2026-07-21).</t>
+        </is>
+      </c>
+      <c r="AF75" s="31" t="inlineStr">
+        <is>
+          <t>Research baseline; zero-unit shadow until qualified.</t>
+        </is>
+      </c>
+      <c r="AG75" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH75" s="24" t="n"/>
+      <c r="AI75" s="31" t="n"/>
+      <c r="AJ75" s="31" t="n"/>
+      <c r="AK75" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL75" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM75" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN75" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO75" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP75" s="24" t="inlineStr">
+        <is>
+          <t>Just Players</t>
+        </is>
+      </c>
+      <c r="AQ75" s="24" t="inlineStr">
+        <is>
+          <t>Just Players</t>
+        </is>
+      </c>
+      <c r="AR75" s="24" t="inlineStr">
+        <is>
+          <t>Just Players</t>
+        </is>
+      </c>
+      <c r="AS75" s="24" t="inlineStr">
+        <is>
+          <t>ex-RUSTEC</t>
+        </is>
+      </c>
+      <c r="AT75" s="24" t="inlineStr">
+        <is>
+          <t>ex-RUSTEC</t>
+        </is>
+      </c>
+      <c r="AU75" s="24" t="inlineStr">
+        <is>
+          <t>ex-RUSTEC</t>
+        </is>
+      </c>
+      <c r="AV75" s="24" t="n"/>
+      <c r="AW75" s="24" t="n"/>
+      <c r="AX75" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY75" s="24" t="n"/>
+      <c r="AZ75" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA75" s="24" t="inlineStr">
+        <is>
+          <t>9dbde86ab8062ac73a51c94b0ad431573ac8b755ccd742d86794849a749958c7</t>
+        </is>
+      </c>
+      <c r="BB75" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC75" s="24" t="inlineStr">
+        <is>
+          <t>cs2-neutral-series-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD75" s="24" t="inlineStr">
+        <is>
+          <t>9dbde86ab8062ac73a51c94b0ad431573ac8b755ccd742d86794849a749958c7</t>
+        </is>
+      </c>
+      <c r="BE75" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF75" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG75" s="24" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="BH75" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-21T08:13:57.416034Z</t>
+        </is>
+      </c>
+      <c r="BI75" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ75" s="38" t="n"/>
+      <c r="BK75" s="26" t="n">
+        <v>-117</v>
+      </c>
+      <c r="BL75" s="39" t="n">
+        <v>1.854701</v>
+      </c>
+      <c r="BM75" s="28" t="n">
+        <v>0.539171</v>
+      </c>
+      <c r="BN75" s="28" t="n"/>
+      <c r="BO75" s="28" t="n"/>
+      <c r="BP75" s="38" t="n"/>
+      <c r="BQ75" s="39" t="n"/>
+      <c r="BR75" s="28" t="n"/>
+      <c r="BS75" s="28" t="n"/>
+      <c r="BT75" s="28" t="n"/>
+      <c r="BU75" s="38" t="n"/>
+      <c r="BV75" s="29" t="n"/>
+      <c r="BW75" s="24" t="n"/>
+      <c r="BX75" s="40" t="n"/>
+      <c r="BY75" s="39" t="n"/>
+      <c r="BZ75" s="24" t="n"/>
+      <c r="CA75" s="31" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/picks.xlsx
+++ b/data/picks.xlsx
@@ -1374,7 +1374,7 @@
       <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL2" t="n">
@@ -1650,7 +1650,7 @@
       <c r="AJ3" t="inlineStr"/>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL3" t="n">
@@ -1926,7 +1926,7 @@
       <c r="AJ4" t="inlineStr"/>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL4" t="n">
@@ -2202,7 +2202,7 @@
       <c r="AJ5" t="inlineStr"/>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL5" t="n">
@@ -2478,7 +2478,7 @@
       <c r="AJ6" t="inlineStr"/>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL6" t="n">
@@ -2754,7 +2754,7 @@
       <c r="AJ7" t="inlineStr"/>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL7" t="n">
@@ -3030,7 +3030,7 @@
       <c r="AJ8" t="inlineStr"/>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL8" t="n">
@@ -3306,7 +3306,7 @@
       <c r="AJ9" t="inlineStr"/>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL9" t="n">
@@ -3582,7 +3582,7 @@
       <c r="AJ10" t="inlineStr"/>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL10" t="n">
@@ -3858,7 +3858,7 @@
       <c r="AJ11" t="inlineStr"/>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL11" t="n">
@@ -4134,7 +4134,7 @@
       <c r="AJ12" t="inlineStr"/>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL12" t="n">
@@ -4410,7 +4410,7 @@
       <c r="AJ13" t="inlineStr"/>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL13" t="n">
@@ -4686,7 +4686,7 @@
       <c r="AJ14" t="inlineStr"/>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL14" t="n">
@@ -4962,7 +4962,7 @@
       <c r="AJ15" t="inlineStr"/>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL15" t="n">
@@ -5238,7 +5238,7 @@
       <c r="AJ16" t="inlineStr"/>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL16" t="n">
@@ -5514,7 +5514,7 @@
       <c r="AJ17" t="inlineStr"/>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL17" t="n">
@@ -5790,7 +5790,7 @@
       <c r="AJ18" t="inlineStr"/>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL18" t="n">
@@ -6066,7 +6066,7 @@
       <c r="AJ19" t="inlineStr"/>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL19" t="n">
@@ -6342,7 +6342,7 @@
       <c r="AJ20" t="inlineStr"/>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL20" t="n">
@@ -6610,7 +6610,11 @@
       <c r="AH21" t="inlineStr"/>
       <c r="AI21" t="inlineStr"/>
       <c r="AJ21" t="inlineStr"/>
-      <c r="AK21" t="inlineStr"/>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
       <c r="AL21" t="n">
         <v>3</v>
       </c>
@@ -6844,7 +6848,11 @@
       <c r="AH22" t="inlineStr"/>
       <c r="AI22" t="inlineStr"/>
       <c r="AJ22" t="inlineStr"/>
-      <c r="AK22" t="inlineStr"/>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
       <c r="AL22" t="n">
         <v>3</v>
       </c>
@@ -7078,7 +7086,11 @@
       <c r="AH23" t="inlineStr"/>
       <c r="AI23" t="inlineStr"/>
       <c r="AJ23" t="inlineStr"/>
-      <c r="AK23" t="inlineStr"/>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
       <c r="AL23" t="n">
         <v>3</v>
       </c>
@@ -7312,7 +7324,11 @@
       <c r="AH24" t="inlineStr"/>
       <c r="AI24" t="inlineStr"/>
       <c r="AJ24" t="inlineStr"/>
-      <c r="AK24" t="inlineStr"/>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
       <c r="AL24" t="n">
         <v>3</v>
       </c>
@@ -7546,7 +7562,11 @@
       <c r="AH25" t="inlineStr"/>
       <c r="AI25" t="inlineStr"/>
       <c r="AJ25" t="inlineStr"/>
-      <c r="AK25" t="inlineStr"/>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
       <c r="AL25" t="n">
         <v>3</v>
       </c>
@@ -7780,7 +7800,11 @@
       <c r="AH26" t="inlineStr"/>
       <c r="AI26" t="inlineStr"/>
       <c r="AJ26" t="inlineStr"/>
-      <c r="AK26" t="inlineStr"/>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
       <c r="AL26" t="n">
         <v>3</v>
       </c>
@@ -8014,7 +8038,11 @@
       <c r="AH27" t="inlineStr"/>
       <c r="AI27" t="inlineStr"/>
       <c r="AJ27" t="inlineStr"/>
-      <c r="AK27" t="inlineStr"/>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
       <c r="AL27" t="n">
         <v>3</v>
       </c>
@@ -8248,7 +8276,11 @@
       <c r="AH28" t="inlineStr"/>
       <c r="AI28" t="inlineStr"/>
       <c r="AJ28" t="inlineStr"/>
-      <c r="AK28" t="inlineStr"/>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
       <c r="AL28" t="n">
         <v>3</v>
       </c>
@@ -8490,7 +8522,7 @@
       <c r="AJ29" t="inlineStr"/>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL29" t="n">
@@ -8766,7 +8798,7 @@
       <c r="AJ30" t="inlineStr"/>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL30" t="n">
@@ -9042,7 +9074,7 @@
       <c r="AJ31" t="inlineStr"/>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL31" t="n">
@@ -9318,7 +9350,7 @@
       <c r="AJ32" t="inlineStr"/>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL32" t="n">
@@ -9594,7 +9626,7 @@
       <c r="AJ33" t="inlineStr"/>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL33" t="n">
@@ -9870,7 +9902,7 @@
       <c r="AJ34" t="inlineStr"/>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL34" t="n">
@@ -10134,7 +10166,7 @@
       <c r="AJ35" t="inlineStr"/>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL35" t="n">
@@ -13998,7 +14030,7 @@
       <c r="AJ50" t="inlineStr"/>
       <c r="AK50" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL50" t="n">
@@ -14246,7 +14278,7 @@
       <c r="AJ51" t="inlineStr"/>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL51" t="n">
@@ -14494,7 +14526,7 @@
       <c r="AJ52" t="inlineStr"/>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL52" t="n">
@@ -14742,7 +14774,7 @@
       <c r="AJ53" t="inlineStr"/>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL53" t="n">
@@ -14990,7 +15022,7 @@
       <c r="AJ54" t="inlineStr"/>
       <c r="AK54" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL54" t="n">
@@ -15238,7 +15270,7 @@
       <c r="AJ55" t="inlineStr"/>
       <c r="AK55" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL55" t="n">
@@ -15486,7 +15518,7 @@
       <c r="AJ56" t="inlineStr"/>
       <c r="AK56" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL56" t="n">
@@ -15734,7 +15766,7 @@
       <c r="AJ57" t="inlineStr"/>
       <c r="AK57" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL57" t="n">

--- a/data/picks.xlsx
+++ b/data/picks.xlsx
@@ -1313,7 +1313,7 @@
       </c>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="n">
-        <v>0.119772</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>100</v>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>dota2-neutral-series-elo-v2</t>
+          <t>dota2-tiered-elo-v3</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -1360,7 +1360,7 @@
       <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>NO_CALL_UNKNOWN_TEAM</t>
         </is>
       </c>
       <c r="AL2" t="n">
@@ -1557,11 +1557,11 @@
         <v>0.4</v>
       </c>
       <c r="O3" t="n">
-        <v>0.625394</v>
+        <v>0.5</v>
       </c>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="n">
-        <v>0.225394</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>100</v>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>dota2-neutral-series-elo-v2</t>
+          <t>dota2-tiered-elo-v3</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -1608,7 +1608,7 @@
       <c r="AJ3" t="inlineStr"/>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>NO_CALL_UNKNOWN_TEAM</t>
         </is>
       </c>
       <c r="AL3" t="n">
@@ -1805,11 +1805,11 @@
         <v>0.420168</v>
       </c>
       <c r="O4" t="n">
-        <v>0.583304</v>
+        <v>0.5</v>
       </c>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="n">
-        <v>0.163136</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>100</v>
@@ -1819,7 +1819,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>dota2-neutral-series-elo-v2</t>
+          <t>dota2-tiered-elo-v3</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -1856,7 +1856,7 @@
       <c r="AJ4" t="inlineStr"/>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>NO_CALL_UNKNOWN_TEAM</t>
         </is>
       </c>
       <c r="AL4" t="n">
@@ -2053,11 +2053,11 @@
         <v>0.420168</v>
       </c>
       <c r="O5" t="n">
-        <v>0.589489</v>
+        <v>0.589971</v>
       </c>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="n">
-        <v>0.169321</v>
+        <v>0.169803</v>
       </c>
       <c r="R5" t="n">
         <v>100</v>
@@ -2067,7 +2067,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>lol-neutral-series-elo-v2</t>
+          <t>lol-tiered-elo-v3</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -2104,7 +2104,7 @@
       <c r="AJ5" t="inlineStr"/>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AL5" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>daa3fc90ca4593e2a301d3702bff6f84e813dc20ca7f7c0733d1637d80aeadf8</t>
+          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
@@ -2301,11 +2301,11 @@
         <v>0.539171</v>
       </c>
       <c r="O6" t="n">
-        <v>0.625647</v>
+        <v>0.700126</v>
       </c>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="n">
-        <v>0.086476</v>
+        <v>0.160955</v>
       </c>
       <c r="R6" t="n">
         <v>63</v>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>lol-neutral-series-elo-v2</t>
+          <t>lol-tiered-elo-v3</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -2418,7 +2418,7 @@
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>daa3fc90ca4593e2a301d3702bff6f84e813dc20ca7f7c0733d1637d80aeadf8</t>
+          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
@@ -2549,11 +2549,11 @@
         <v>0.6</v>
       </c>
       <c r="O7" t="n">
-        <v>0.689025</v>
+        <v>0.662969</v>
       </c>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="n">
-        <v>0.08902500000000001</v>
+        <v>0.062969</v>
       </c>
       <c r="R7" t="n">
         <v>65</v>
@@ -2563,7 +2563,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>lol-neutral-series-elo-v2</t>
+          <t>lol-tiered-elo-v3</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -2600,7 +2600,7 @@
       <c r="AJ7" t="inlineStr"/>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AL7" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>daa3fc90ca4593e2a301d3702bff6f84e813dc20ca7f7c0733d1637d80aeadf8</t>
+          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
@@ -2797,11 +2797,11 @@
         <v>0.619772</v>
       </c>
       <c r="O8" t="n">
-        <v>0.651459</v>
+        <v>0.769629</v>
       </c>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="n">
-        <v>0.031687</v>
+        <v>0.149857</v>
       </c>
       <c r="R8" t="n">
         <v>36</v>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>lol-neutral-series-elo-v2</t>
+          <t>lol-tiered-elo-v3</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>daa3fc90ca4593e2a301d3702bff6f84e813dc20ca7f7c0733d1637d80aeadf8</t>
+          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
@@ -3045,11 +3045,11 @@
         <v>0.309598</v>
       </c>
       <c r="O9" t="n">
-        <v>0.549502</v>
+        <v>0.600415</v>
       </c>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="n">
-        <v>0.239904</v>
+        <v>0.290817</v>
       </c>
       <c r="R9" t="n">
         <v>100</v>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>lol-neutral-series-elo-v2</t>
+          <t>lol-tiered-elo-v3</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -3096,7 +3096,7 @@
       <c r="AJ9" t="inlineStr"/>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AL9" t="n">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>daa3fc90ca4593e2a301d3702bff6f84e813dc20ca7f7c0733d1637d80aeadf8</t>
+          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
@@ -3817,11 +3817,11 @@
         <v>0.669967</v>
       </c>
       <c r="O12" t="n">
-        <v>0.748396</v>
+        <v>0.7733100000000001</v>
       </c>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="n">
-        <v>0.07839599999999999</v>
+        <v>0.103343</v>
       </c>
       <c r="R12" t="n">
         <v>78</v>
@@ -3831,7 +3831,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>lol-neutral-series-elo-v1</t>
+          <t>lol-tiered-elo-v3</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>82612f1b27d5065af8d70fd6669509ff00dc1c7e3a91bb423192bf3b0a9736ce</t>
+          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
@@ -4065,11 +4065,11 @@
         <v>0.320513</v>
       </c>
       <c r="O13" t="n">
-        <v>0.59232</v>
+        <v>0.563621</v>
       </c>
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="n">
-        <v>0.27232</v>
+        <v>0.243108</v>
       </c>
       <c r="R13" t="n">
         <v>100</v>
@@ -4079,7 +4079,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>lol-neutral-series-elo-v1</t>
+          <t>lol-tiered-elo-v3</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -4130,7 +4130,7 @@
       <c r="AJ13" t="inlineStr"/>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AL13" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>82612f1b27d5065af8d70fd6669509ff00dc1c7e3a91bb423192bf3b0a9736ce</t>
+          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
@@ -4327,11 +4327,11 @@
         <v>0.669967</v>
       </c>
       <c r="O14" t="n">
-        <v>0.731785</v>
+        <v>0.753541</v>
       </c>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="n">
-        <v>0.061785</v>
+        <v>0.083574</v>
       </c>
       <c r="R14" t="n">
         <v>61</v>
@@ -4341,7 +4341,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>lol-neutral-series-elo-v1</t>
+          <t>lol-tiered-elo-v3</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -4458,7 +4458,7 @@
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>82612f1b27d5065af8d70fd6669509ff00dc1c7e3a91bb423192bf3b0a9736ce</t>
+          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
@@ -4589,11 +4589,11 @@
         <v>0.659864</v>
       </c>
       <c r="O15" t="n">
-        <v>0.748054</v>
+        <v>0.8542149999999999</v>
       </c>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="n">
-        <v>0.08805399999999999</v>
+        <v>0.194351</v>
       </c>
       <c r="R15" t="n">
         <v>88</v>
@@ -4603,7 +4603,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>lol-neutral-series-elo-v1</t>
+          <t>lol-tiered-elo-v3</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>82612f1b27d5065af8d70fd6669509ff00dc1c7e3a91bb423192bf3b0a9736ce</t>
+          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
@@ -4851,11 +4851,11 @@
         <v>0.469484</v>
       </c>
       <c r="O16" t="n">
-        <v>0.503502</v>
+        <v>0.5</v>
       </c>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="n">
-        <v>0.033502</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>33</v>
@@ -4865,7 +4865,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>lol-neutral-series-elo-v1</t>
+          <t>lol-tiered-elo-v3</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -4916,7 +4916,7 @@
       <c r="AJ16" t="inlineStr"/>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>NO_CALL_UNKNOWN_TEAM</t>
         </is>
       </c>
       <c r="AL16" t="n">
@@ -5113,11 +5113,11 @@
         <v>0.590164</v>
       </c>
       <c r="O17" t="n">
-        <v>0.650242</v>
+        <v>0.615103</v>
       </c>
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="n">
-        <v>0.060242</v>
+        <v>0.024939</v>
       </c>
       <c r="R17" t="n">
         <v>60</v>
@@ -5127,7 +5127,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>lol-neutral-series-elo-v1</t>
+          <t>lol-tiered-elo-v3</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -5178,7 +5178,7 @@
       <c r="AJ17" t="inlineStr"/>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AL17" t="n">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>82612f1b27d5065af8d70fd6669509ff00dc1c7e3a91bb423192bf3b0a9736ce</t>
+          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
@@ -5375,11 +5375,11 @@
         <v>0.340136</v>
       </c>
       <c r="O18" t="n">
-        <v>0.75</v>
+        <v>0.958215</v>
       </c>
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="n">
-        <v>0.41</v>
+        <v>0.618079</v>
       </c>
       <c r="R18" t="n">
         <v>100</v>
@@ -5389,7 +5389,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>lol-neutral-series-elo-v1</t>
+          <t>lol-tiered-elo-v3</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -5506,7 +5506,7 @@
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>82612f1b27d5065af8d70fd6669509ff00dc1c7e3a91bb423192bf3b0a9736ce</t>
+          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
@@ -5637,11 +5637,11 @@
         <v>0.409836</v>
       </c>
       <c r="O19" t="n">
-        <v>0.7499980000000001</v>
+        <v>0.933732</v>
       </c>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="n">
-        <v>0.339998</v>
+        <v>0.523896</v>
       </c>
       <c r="R19" t="n">
         <v>100</v>
@@ -5651,7 +5651,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>lol-neutral-series-elo-v1</t>
+          <t>lol-tiered-elo-v3</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -5768,7 +5768,7 @@
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>82612f1b27d5065af8d70fd6669509ff00dc1c7e3a91bb423192bf3b0a9736ce</t>
+          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">

--- a/data/picks.xlsx
+++ b/data/picks.xlsx
@@ -842,7 +842,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB102"/>
+  <dimension ref="A1:CB123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27461,6 +27461,5354 @@
       <c r="CA102" t="inlineStr"/>
       <c r="CB102" t="inlineStr"/>
     </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>10bb7e438b824bad</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>2026-07-21T08:30:10.932567Z</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>2026-07-22T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>55211</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>7REX</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Vivo Keyd Stars Academy</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L103" t="n">
+        <v>-233</v>
+      </c>
+      <c r="M103" t="n">
+        <v>1.429185</v>
+      </c>
+      <c r="N103" t="n">
+        <v>0.6997</v>
+      </c>
+      <c r="O103" t="n">
+        <v>0.6887720000000001</v>
+      </c>
+      <c r="P103" t="inlineStr"/>
+      <c r="Q103" t="n">
+        <v>-0.010928</v>
+      </c>
+      <c r="R103" t="n">
+        <v>4</v>
+      </c>
+      <c r="S103" t="n">
+        <v>2</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W103" t="n">
+        <v>0</v>
+      </c>
+      <c r="X103" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y103" t="inlineStr"/>
+      <c r="Z103" t="inlineStr"/>
+      <c r="AA103" t="inlineStr"/>
+      <c r="AB103" t="inlineStr"/>
+      <c r="AC103" t="n">
+        <v>0.8584000000000001</v>
+      </c>
+      <c r="AD103" t="inlineStr">
+        <is>
+          <t>2026-07-22T00:57:09.040256Z</t>
+        </is>
+      </c>
+      <c r="AE103" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.7000 (aec-lol-vksa-7rex-2026-07-22).</t>
+        </is>
+      </c>
+      <c r="AF103" t="inlineStr">
+        <is>
+          <t>Research baseline; zero-unit shadow until qualified.</t>
+        </is>
+      </c>
+      <c r="AG103" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH103" t="inlineStr"/>
+      <c r="AI103" t="inlineStr"/>
+      <c r="AJ103" t="inlineStr"/>
+      <c r="AK103" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL103" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM103" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN103" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO103" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP103" t="inlineStr">
+        <is>
+          <t>7REX</t>
+        </is>
+      </c>
+      <c r="AQ103" t="inlineStr">
+        <is>
+          <t>7REX</t>
+        </is>
+      </c>
+      <c r="AR103" t="inlineStr">
+        <is>
+          <t>7REX</t>
+        </is>
+      </c>
+      <c r="AS103" t="inlineStr">
+        <is>
+          <t>Vivo Keyd Stars Academy</t>
+        </is>
+      </c>
+      <c r="AT103" t="inlineStr">
+        <is>
+          <t>Vivo Keyd Stars Academy</t>
+        </is>
+      </c>
+      <c r="AU103" t="inlineStr">
+        <is>
+          <t>Vivo Keyd Stars Academy</t>
+        </is>
+      </c>
+      <c r="AV103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr"/>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA103" t="inlineStr">
+        <is>
+          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
+        </is>
+      </c>
+      <c r="BB103" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC103" t="inlineStr">
+        <is>
+          <t>lol-neutral-series-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD103" t="inlineStr">
+        <is>
+          <t>82612f1b27d5065af8d70fd6669509ff00dc1c7e3a91bb423192bf3b0a9736ce</t>
+        </is>
+      </c>
+      <c r="BE103" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF103" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG103" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="BH103" t="inlineStr">
+        <is>
+          <t>2026-07-21T08:30:10.932567Z</t>
+        </is>
+      </c>
+      <c r="BI103" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ103" t="inlineStr"/>
+      <c r="BK103" t="n">
+        <v>-233</v>
+      </c>
+      <c r="BL103" t="n">
+        <v>1.429185</v>
+      </c>
+      <c r="BM103" t="n">
+        <v>0.6997</v>
+      </c>
+      <c r="BN103" t="inlineStr"/>
+      <c r="BO103" t="inlineStr"/>
+      <c r="BP103" t="inlineStr"/>
+      <c r="BQ103" t="inlineStr"/>
+      <c r="BR103" t="inlineStr"/>
+      <c r="BS103" t="inlineStr"/>
+      <c r="BT103" t="inlineStr"/>
+      <c r="BU103" t="inlineStr"/>
+      <c r="BV103" t="inlineStr"/>
+      <c r="BW103" t="inlineStr"/>
+      <c r="BX103" t="inlineStr"/>
+      <c r="BY103" t="inlineStr"/>
+      <c r="BZ103" t="inlineStr"/>
+      <c r="CA103" t="inlineStr"/>
+      <c r="CB103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>23354aa9fad94658</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>2026-07-21T08:30:10.496331Z</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>2026-07-21T23:00:00Z</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>55208</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Ei Nerd Esports</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Team Solid</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L104" t="n">
+        <v>-194</v>
+      </c>
+      <c r="M104" t="n">
+        <v>1.515464</v>
+      </c>
+      <c r="N104" t="n">
+        <v>0.659864</v>
+      </c>
+      <c r="O104" t="n">
+        <v>0.5767600000000001</v>
+      </c>
+      <c r="P104" t="inlineStr"/>
+      <c r="Q104" t="n">
+        <v>-0.083104</v>
+      </c>
+      <c r="R104" t="n">
+        <v>0</v>
+      </c>
+      <c r="S104" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W104" t="n">
+        <v>1</v>
+      </c>
+      <c r="X104" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y104" t="inlineStr"/>
+      <c r="Z104" t="inlineStr"/>
+      <c r="AA104" t="inlineStr"/>
+      <c r="AB104" t="inlineStr"/>
+      <c r="AC104" t="n">
+        <v>0.7732</v>
+      </c>
+      <c r="AD104" t="inlineStr">
+        <is>
+          <t>2026-07-22T00:36:34.578720Z</t>
+        </is>
+      </c>
+      <c r="AE104" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6600 (aec-lol-tse-nerd-2026-07-21).</t>
+        </is>
+      </c>
+      <c r="AF104" t="inlineStr">
+        <is>
+          <t>Research baseline; zero-unit shadow until qualified.</t>
+        </is>
+      </c>
+      <c r="AG104" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH104" t="inlineStr"/>
+      <c r="AI104" t="inlineStr"/>
+      <c r="AJ104" t="inlineStr"/>
+      <c r="AK104" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL104" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM104" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN104" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO104" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP104" t="inlineStr">
+        <is>
+          <t>Ei Nerd Esports</t>
+        </is>
+      </c>
+      <c r="AQ104" t="inlineStr">
+        <is>
+          <t>Ei Nerd Esports</t>
+        </is>
+      </c>
+      <c r="AR104" t="inlineStr">
+        <is>
+          <t>Ei Nerd Esports</t>
+        </is>
+      </c>
+      <c r="AS104" t="inlineStr">
+        <is>
+          <t>Team Solid</t>
+        </is>
+      </c>
+      <c r="AT104" t="inlineStr">
+        <is>
+          <t>Team Solid</t>
+        </is>
+      </c>
+      <c r="AU104" t="inlineStr">
+        <is>
+          <t>Team Solid</t>
+        </is>
+      </c>
+      <c r="AV104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr"/>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA104" t="inlineStr">
+        <is>
+          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
+        </is>
+      </c>
+      <c r="BB104" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC104" t="inlineStr">
+        <is>
+          <t>lol-neutral-series-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD104" t="inlineStr">
+        <is>
+          <t>82612f1b27d5065af8d70fd6669509ff00dc1c7e3a91bb423192bf3b0a9736ce</t>
+        </is>
+      </c>
+      <c r="BE104" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF104" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG104" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="BH104" t="inlineStr">
+        <is>
+          <t>2026-07-21T08:30:10.496331Z</t>
+        </is>
+      </c>
+      <c r="BI104" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ104" t="inlineStr"/>
+      <c r="BK104" t="n">
+        <v>-194</v>
+      </c>
+      <c r="BL104" t="n">
+        <v>1.515464</v>
+      </c>
+      <c r="BM104" t="n">
+        <v>0.659864</v>
+      </c>
+      <c r="BN104" t="inlineStr"/>
+      <c r="BO104" t="inlineStr"/>
+      <c r="BP104" t="inlineStr"/>
+      <c r="BQ104" t="inlineStr"/>
+      <c r="BR104" t="inlineStr"/>
+      <c r="BS104" t="inlineStr"/>
+      <c r="BT104" t="inlineStr"/>
+      <c r="BU104" t="inlineStr"/>
+      <c r="BV104" t="inlineStr"/>
+      <c r="BW104" t="inlineStr"/>
+      <c r="BX104" t="inlineStr"/>
+      <c r="BY104" t="inlineStr"/>
+      <c r="BZ104" t="inlineStr"/>
+      <c r="CA104" t="inlineStr"/>
+      <c r="CB104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>171bce26e273463d</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>2026-07-21T08:30:10.070369Z</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>2026-07-21T22:00:00Z</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>55206</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Estral Esports</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>KaBuM! Ilha das Lendas</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L105" t="n">
+        <v>212</v>
+      </c>
+      <c r="M105" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="N105" t="n">
+        <v>0.320513</v>
+      </c>
+      <c r="O105" t="n">
+        <v>0.563621</v>
+      </c>
+      <c r="P105" t="inlineStr"/>
+      <c r="Q105" t="n">
+        <v>0.243108</v>
+      </c>
+      <c r="R105" t="n">
+        <v>100</v>
+      </c>
+      <c r="S105" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W105" t="n">
+        <v>1</v>
+      </c>
+      <c r="X105" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y105" t="inlineStr"/>
+      <c r="Z105" t="inlineStr"/>
+      <c r="AA105" t="inlineStr"/>
+      <c r="AB105" t="inlineStr"/>
+      <c r="AC105" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AD105" t="inlineStr">
+        <is>
+          <t>2026-07-22T00:36:24.235556Z</t>
+        </is>
+      </c>
+      <c r="AE105" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.3200 (aec-lol-kbm-est-2026-07-21).</t>
+        </is>
+      </c>
+      <c r="AF105" t="inlineStr">
+        <is>
+          <t>Research baseline; zero-unit shadow until qualified.</t>
+        </is>
+      </c>
+      <c r="AG105" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH105" t="inlineStr"/>
+      <c r="AI105" t="inlineStr"/>
+      <c r="AJ105" t="inlineStr"/>
+      <c r="AK105" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL105" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM105" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN105" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO105" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP105" t="inlineStr">
+        <is>
+          <t>Estral Esports</t>
+        </is>
+      </c>
+      <c r="AQ105" t="inlineStr">
+        <is>
+          <t>Estral Esports</t>
+        </is>
+      </c>
+      <c r="AR105" t="inlineStr">
+        <is>
+          <t>Estral Esports</t>
+        </is>
+      </c>
+      <c r="AS105" t="inlineStr">
+        <is>
+          <t>KaBuM! Ilha das Lendas</t>
+        </is>
+      </c>
+      <c r="AT105" t="inlineStr">
+        <is>
+          <t>KaBuM! Ilha das Lendas</t>
+        </is>
+      </c>
+      <c r="AU105" t="inlineStr">
+        <is>
+          <t>KaBuM! Ilha das Lendas</t>
+        </is>
+      </c>
+      <c r="AV105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr"/>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA105" t="inlineStr">
+        <is>
+          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
+        </is>
+      </c>
+      <c r="BB105" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC105" t="inlineStr">
+        <is>
+          <t>lol-neutral-series-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD105" t="inlineStr">
+        <is>
+          <t>82612f1b27d5065af8d70fd6669509ff00dc1c7e3a91bb423192bf3b0a9736ce</t>
+        </is>
+      </c>
+      <c r="BE105" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF105" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG105" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="BH105" t="inlineStr">
+        <is>
+          <t>2026-07-21T08:30:10.070369Z</t>
+        </is>
+      </c>
+      <c r="BI105" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ105" t="inlineStr"/>
+      <c r="BK105" t="n">
+        <v>212</v>
+      </c>
+      <c r="BL105" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="BM105" t="n">
+        <v>0.320513</v>
+      </c>
+      <c r="BN105" t="inlineStr"/>
+      <c r="BO105" t="inlineStr"/>
+      <c r="BP105" t="inlineStr"/>
+      <c r="BQ105" t="inlineStr"/>
+      <c r="BR105" t="inlineStr"/>
+      <c r="BS105" t="inlineStr"/>
+      <c r="BT105" t="inlineStr"/>
+      <c r="BU105" t="inlineStr"/>
+      <c r="BV105" t="inlineStr"/>
+      <c r="BW105" t="inlineStr"/>
+      <c r="BX105" t="inlineStr"/>
+      <c r="BY105" t="inlineStr"/>
+      <c r="BZ105" t="inlineStr"/>
+      <c r="CA105" t="inlineStr"/>
+      <c r="CB105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>e61dd2ea3da24872</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>2026-07-21T08:30:09.587217Z</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>2026-07-21T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>55205</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>RMD Gaming</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>paiN Gaming Academy</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L106" t="n">
+        <v>-203</v>
+      </c>
+      <c r="M106" t="n">
+        <v>1.492611</v>
+      </c>
+      <c r="N106" t="n">
+        <v>0.669967</v>
+      </c>
+      <c r="O106" t="n">
+        <v>0.753541</v>
+      </c>
+      <c r="P106" t="inlineStr"/>
+      <c r="Q106" t="n">
+        <v>0.083574</v>
+      </c>
+      <c r="R106" t="n">
+        <v>61</v>
+      </c>
+      <c r="S106" t="n">
+        <v>2</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W106" t="n">
+        <v>0</v>
+      </c>
+      <c r="X106" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y106" t="inlineStr"/>
+      <c r="Z106" t="inlineStr"/>
+      <c r="AA106" t="inlineStr"/>
+      <c r="AB106" t="inlineStr"/>
+      <c r="AC106" t="n">
+        <v>0.9852</v>
+      </c>
+      <c r="AD106" t="inlineStr">
+        <is>
+          <t>2026-07-22T00:57:07.221385Z</t>
+        </is>
+      </c>
+      <c r="AE106" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6700 (aec-lol-pnga-rmd-2026-07-21).</t>
+        </is>
+      </c>
+      <c r="AF106" t="inlineStr">
+        <is>
+          <t>Research baseline; zero-unit shadow until qualified.</t>
+        </is>
+      </c>
+      <c r="AG106" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH106" t="inlineStr"/>
+      <c r="AI106" t="inlineStr"/>
+      <c r="AJ106" t="inlineStr"/>
+      <c r="AK106" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL106" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM106" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN106" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO106" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP106" t="inlineStr">
+        <is>
+          <t>RMD Gaming</t>
+        </is>
+      </c>
+      <c r="AQ106" t="inlineStr">
+        <is>
+          <t>RMD Gaming</t>
+        </is>
+      </c>
+      <c r="AR106" t="inlineStr">
+        <is>
+          <t>RMD Gaming</t>
+        </is>
+      </c>
+      <c r="AS106" t="inlineStr">
+        <is>
+          <t>paiN Gaming Academy</t>
+        </is>
+      </c>
+      <c r="AT106" t="inlineStr">
+        <is>
+          <t>paiN Gaming Academy</t>
+        </is>
+      </c>
+      <c r="AU106" t="inlineStr">
+        <is>
+          <t>paiN Gaming Academy</t>
+        </is>
+      </c>
+      <c r="AV106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr"/>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA106" t="inlineStr">
+        <is>
+          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
+        </is>
+      </c>
+      <c r="BB106" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC106" t="inlineStr">
+        <is>
+          <t>lol-neutral-series-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD106" t="inlineStr">
+        <is>
+          <t>82612f1b27d5065af8d70fd6669509ff00dc1c7e3a91bb423192bf3b0a9736ce</t>
+        </is>
+      </c>
+      <c r="BE106" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF106" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG106" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="BH106" t="inlineStr">
+        <is>
+          <t>2026-07-21T08:30:09.587217Z</t>
+        </is>
+      </c>
+      <c r="BI106" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ106" t="inlineStr"/>
+      <c r="BK106" t="n">
+        <v>-203</v>
+      </c>
+      <c r="BL106" t="n">
+        <v>1.492611</v>
+      </c>
+      <c r="BM106" t="n">
+        <v>0.669967</v>
+      </c>
+      <c r="BN106" t="inlineStr"/>
+      <c r="BO106" t="inlineStr"/>
+      <c r="BP106" t="inlineStr"/>
+      <c r="BQ106" t="inlineStr"/>
+      <c r="BR106" t="inlineStr"/>
+      <c r="BS106" t="inlineStr"/>
+      <c r="BT106" t="inlineStr"/>
+      <c r="BU106" t="inlineStr"/>
+      <c r="BV106" t="inlineStr"/>
+      <c r="BW106" t="inlineStr"/>
+      <c r="BX106" t="inlineStr"/>
+      <c r="BY106" t="inlineStr"/>
+      <c r="BZ106" t="inlineStr"/>
+      <c r="CA106" t="inlineStr"/>
+      <c r="CB106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>89ced1ad6ac349bb</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>2026-07-21T08:30:09.169381Z</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>2026-07-21T19:00:00Z</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>56856</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Joblife</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Galions</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L107" t="n">
+        <v>-194</v>
+      </c>
+      <c r="M107" t="n">
+        <v>1.515464</v>
+      </c>
+      <c r="N107" t="n">
+        <v>0.659864</v>
+      </c>
+      <c r="O107" t="n">
+        <v>0.8542149999999999</v>
+      </c>
+      <c r="P107" t="inlineStr"/>
+      <c r="Q107" t="n">
+        <v>0.194351</v>
+      </c>
+      <c r="R107" t="n">
+        <v>88</v>
+      </c>
+      <c r="S107" t="n">
+        <v>2</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W107" t="n">
+        <v>0</v>
+      </c>
+      <c r="X107" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y107" t="inlineStr"/>
+      <c r="Z107" t="inlineStr"/>
+      <c r="AA107" t="inlineStr"/>
+      <c r="AB107" t="inlineStr"/>
+      <c r="AC107" t="n">
+        <v>1.0309</v>
+      </c>
+      <c r="AD107" t="inlineStr">
+        <is>
+          <t>2026-07-22T00:36:02.950999Z</t>
+        </is>
+      </c>
+      <c r="AE107" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6600 (aec-lol-gal-jl-2026-07-21).</t>
+        </is>
+      </c>
+      <c r="AF107" t="inlineStr">
+        <is>
+          <t>Research baseline; zero-unit shadow until qualified.</t>
+        </is>
+      </c>
+      <c r="AG107" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH107" t="inlineStr"/>
+      <c r="AI107" t="inlineStr"/>
+      <c r="AJ107" t="inlineStr"/>
+      <c r="AK107" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL107" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM107" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN107" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO107" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP107" t="inlineStr">
+        <is>
+          <t>Joblife</t>
+        </is>
+      </c>
+      <c r="AQ107" t="inlineStr">
+        <is>
+          <t>Joblife</t>
+        </is>
+      </c>
+      <c r="AR107" t="inlineStr">
+        <is>
+          <t>Joblife</t>
+        </is>
+      </c>
+      <c r="AS107" t="inlineStr">
+        <is>
+          <t>Galions</t>
+        </is>
+      </c>
+      <c r="AT107" t="inlineStr">
+        <is>
+          <t>Galions</t>
+        </is>
+      </c>
+      <c r="AU107" t="inlineStr">
+        <is>
+          <t>Galions</t>
+        </is>
+      </c>
+      <c r="AV107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr"/>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA107" t="inlineStr">
+        <is>
+          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
+        </is>
+      </c>
+      <c r="BB107" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC107" t="inlineStr">
+        <is>
+          <t>lol-neutral-series-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD107" t="inlineStr">
+        <is>
+          <t>82612f1b27d5065af8d70fd6669509ff00dc1c7e3a91bb423192bf3b0a9736ce</t>
+        </is>
+      </c>
+      <c r="BE107" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF107" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG107" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="BH107" t="inlineStr">
+        <is>
+          <t>2026-07-21T08:30:09.169381Z</t>
+        </is>
+      </c>
+      <c r="BI107" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ107" t="inlineStr"/>
+      <c r="BK107" t="n">
+        <v>-194</v>
+      </c>
+      <c r="BL107" t="n">
+        <v>1.515464</v>
+      </c>
+      <c r="BM107" t="n">
+        <v>0.659864</v>
+      </c>
+      <c r="BN107" t="inlineStr"/>
+      <c r="BO107" t="inlineStr"/>
+      <c r="BP107" t="inlineStr"/>
+      <c r="BQ107" t="inlineStr"/>
+      <c r="BR107" t="inlineStr"/>
+      <c r="BS107" t="inlineStr"/>
+      <c r="BT107" t="inlineStr"/>
+      <c r="BU107" t="inlineStr"/>
+      <c r="BV107" t="inlineStr"/>
+      <c r="BW107" t="inlineStr"/>
+      <c r="BX107" t="inlineStr"/>
+      <c r="BY107" t="inlineStr"/>
+      <c r="BZ107" t="inlineStr"/>
+      <c r="CA107" t="inlineStr"/>
+      <c r="CB107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>5985b78f606946dd</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>2026-07-21T08:30:08.750906Z</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>2026-07-21T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>57016</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Baam Esports</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Pyramid IV Esports</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L108" t="n">
+        <v>113</v>
+      </c>
+      <c r="M108" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="N108" t="n">
+        <v>0.469484</v>
+      </c>
+      <c r="O108" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P108" t="inlineStr"/>
+      <c r="Q108" t="n">
+        <v>0</v>
+      </c>
+      <c r="R108" t="n">
+        <v>33</v>
+      </c>
+      <c r="S108" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W108" t="n">
+        <v>1</v>
+      </c>
+      <c r="X108" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y108" t="inlineStr"/>
+      <c r="Z108" t="inlineStr"/>
+      <c r="AA108" t="inlineStr"/>
+      <c r="AB108" t="inlineStr"/>
+      <c r="AC108" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AD108" t="inlineStr">
+        <is>
+          <t>2026-07-22T00:35:59.617906Z</t>
+        </is>
+      </c>
+      <c r="AE108" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4700 (aec-lol-piv-bam-2026-07-21).</t>
+        </is>
+      </c>
+      <c r="AF108" t="inlineStr">
+        <is>
+          <t>Research baseline; zero-unit shadow until qualified.</t>
+        </is>
+      </c>
+      <c r="AG108" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH108" t="inlineStr"/>
+      <c r="AI108" t="inlineStr"/>
+      <c r="AJ108" t="inlineStr"/>
+      <c r="AK108" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL108" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM108" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN108" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO108" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP108" t="inlineStr">
+        <is>
+          <t>Baam Esports</t>
+        </is>
+      </c>
+      <c r="AQ108" t="inlineStr">
+        <is>
+          <t>Baam Esports</t>
+        </is>
+      </c>
+      <c r="AR108" t="inlineStr">
+        <is>
+          <t>Baam Esports</t>
+        </is>
+      </c>
+      <c r="AS108" t="inlineStr">
+        <is>
+          <t>Pyramid IV Esports</t>
+        </is>
+      </c>
+      <c r="AT108" t="inlineStr">
+        <is>
+          <t>Pyramid IV Esports</t>
+        </is>
+      </c>
+      <c r="AU108" t="inlineStr">
+        <is>
+          <t>Pyramid IV Esports</t>
+        </is>
+      </c>
+      <c r="AV108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr"/>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA108" t="inlineStr">
+        <is>
+          <t>82612f1b27d5065af8d70fd6669509ff00dc1c7e3a91bb423192bf3b0a9736ce</t>
+        </is>
+      </c>
+      <c r="BB108" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC108" t="inlineStr">
+        <is>
+          <t>lol-neutral-series-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD108" t="inlineStr">
+        <is>
+          <t>82612f1b27d5065af8d70fd6669509ff00dc1c7e3a91bb423192bf3b0a9736ce</t>
+        </is>
+      </c>
+      <c r="BE108" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF108" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG108" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="BH108" t="inlineStr">
+        <is>
+          <t>2026-07-21T08:30:08.750906Z</t>
+        </is>
+      </c>
+      <c r="BI108" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ108" t="inlineStr"/>
+      <c r="BK108" t="n">
+        <v>113</v>
+      </c>
+      <c r="BL108" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="BM108" t="n">
+        <v>0.469484</v>
+      </c>
+      <c r="BN108" t="inlineStr"/>
+      <c r="BO108" t="inlineStr"/>
+      <c r="BP108" t="inlineStr"/>
+      <c r="BQ108" t="inlineStr"/>
+      <c r="BR108" t="inlineStr"/>
+      <c r="BS108" t="inlineStr"/>
+      <c r="BT108" t="inlineStr"/>
+      <c r="BU108" t="inlineStr"/>
+      <c r="BV108" t="inlineStr"/>
+      <c r="BW108" t="inlineStr"/>
+      <c r="BX108" t="inlineStr"/>
+      <c r="BY108" t="inlineStr"/>
+      <c r="BZ108" t="inlineStr"/>
+      <c r="CA108" t="inlineStr"/>
+      <c r="CB108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>cb4fb35e52d449cd</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>2026-07-21T08:30:08.334204Z</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>2026-07-21T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>55198</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Once Upon A Team</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>mCon esports</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L109" t="n">
+        <v>-186</v>
+      </c>
+      <c r="M109" t="n">
+        <v>1.537634</v>
+      </c>
+      <c r="N109" t="n">
+        <v>0.65035</v>
+      </c>
+      <c r="O109" t="n">
+        <v>0.616388</v>
+      </c>
+      <c r="P109" t="inlineStr"/>
+      <c r="Q109" t="n">
+        <v>-0.033962</v>
+      </c>
+      <c r="R109" t="n">
+        <v>0</v>
+      </c>
+      <c r="S109" t="n">
+        <v>2</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W109" t="n">
+        <v>0</v>
+      </c>
+      <c r="X109" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y109" t="inlineStr"/>
+      <c r="Z109" t="inlineStr"/>
+      <c r="AA109" t="inlineStr"/>
+      <c r="AB109" t="inlineStr"/>
+      <c r="AC109" t="n">
+        <v>1.0753</v>
+      </c>
+      <c r="AD109" t="inlineStr">
+        <is>
+          <t>2026-07-22T00:35:53.796726Z</t>
+        </is>
+      </c>
+      <c r="AE109" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6500 (aec-lol-mcn-ouat-2026-07-21).</t>
+        </is>
+      </c>
+      <c r="AF109" t="inlineStr">
+        <is>
+          <t>Research baseline; zero-unit shadow until qualified.</t>
+        </is>
+      </c>
+      <c r="AG109" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH109" t="inlineStr"/>
+      <c r="AI109" t="inlineStr"/>
+      <c r="AJ109" t="inlineStr"/>
+      <c r="AK109" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL109" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM109" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN109" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO109" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP109" t="inlineStr">
+        <is>
+          <t>Once Upon A Team</t>
+        </is>
+      </c>
+      <c r="AQ109" t="inlineStr">
+        <is>
+          <t>Once Upon A Team</t>
+        </is>
+      </c>
+      <c r="AR109" t="inlineStr">
+        <is>
+          <t>Once Upon A Team</t>
+        </is>
+      </c>
+      <c r="AS109" t="inlineStr">
+        <is>
+          <t>mCon esports</t>
+        </is>
+      </c>
+      <c r="AT109" t="inlineStr">
+        <is>
+          <t>mCon esports</t>
+        </is>
+      </c>
+      <c r="AU109" t="inlineStr">
+        <is>
+          <t>mCon esports</t>
+        </is>
+      </c>
+      <c r="AV109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr"/>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA109" t="inlineStr">
+        <is>
+          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
+        </is>
+      </c>
+      <c r="BB109" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC109" t="inlineStr">
+        <is>
+          <t>lol-neutral-series-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD109" t="inlineStr">
+        <is>
+          <t>82612f1b27d5065af8d70fd6669509ff00dc1c7e3a91bb423192bf3b0a9736ce</t>
+        </is>
+      </c>
+      <c r="BE109" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF109" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG109" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="BH109" t="inlineStr">
+        <is>
+          <t>2026-07-21T08:30:08.334204Z</t>
+        </is>
+      </c>
+      <c r="BI109" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ109" t="inlineStr"/>
+      <c r="BK109" t="n">
+        <v>-186</v>
+      </c>
+      <c r="BL109" t="n">
+        <v>1.537634</v>
+      </c>
+      <c r="BM109" t="n">
+        <v>0.65035</v>
+      </c>
+      <c r="BN109" t="inlineStr"/>
+      <c r="BO109" t="inlineStr"/>
+      <c r="BP109" t="inlineStr"/>
+      <c r="BQ109" t="inlineStr"/>
+      <c r="BR109" t="inlineStr"/>
+      <c r="BS109" t="inlineStr"/>
+      <c r="BT109" t="inlineStr"/>
+      <c r="BU109" t="inlineStr"/>
+      <c r="BV109" t="inlineStr"/>
+      <c r="BW109" t="inlineStr"/>
+      <c r="BX109" t="inlineStr"/>
+      <c r="BY109" t="inlineStr"/>
+      <c r="BZ109" t="inlineStr"/>
+      <c r="CA109" t="inlineStr"/>
+      <c r="CB109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>8cb5922c7860424f</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>2026-07-21T08:30:07.926214Z</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>2026-07-21T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>56853</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Ici Japon Corp. Esport</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>TLN Pirates</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L110" t="n">
+        <v>-144</v>
+      </c>
+      <c r="M110" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="N110" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="O110" t="n">
+        <v>0.615103</v>
+      </c>
+      <c r="P110" t="inlineStr"/>
+      <c r="Q110" t="n">
+        <v>0.024939</v>
+      </c>
+      <c r="R110" t="n">
+        <v>60</v>
+      </c>
+      <c r="S110" t="n">
+        <v>2</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W110" t="n">
+        <v>1</v>
+      </c>
+      <c r="X110" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y110" t="inlineStr"/>
+      <c r="Z110" t="inlineStr"/>
+      <c r="AA110" t="inlineStr"/>
+      <c r="AB110" t="inlineStr"/>
+      <c r="AC110" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AD110" t="inlineStr">
+        <is>
+          <t>2026-07-22T00:57:04.641649Z</t>
+        </is>
+      </c>
+      <c r="AE110" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5900 (aec-lol-tlnp-ijc-2026-07-21).</t>
+        </is>
+      </c>
+      <c r="AF110" t="inlineStr">
+        <is>
+          <t>Research baseline; zero-unit shadow until qualified.</t>
+        </is>
+      </c>
+      <c r="AG110" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH110" t="inlineStr"/>
+      <c r="AI110" t="inlineStr"/>
+      <c r="AJ110" t="inlineStr"/>
+      <c r="AK110" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL110" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM110" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN110" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO110" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP110" t="inlineStr">
+        <is>
+          <t>Ici Japon Corp. Esport</t>
+        </is>
+      </c>
+      <c r="AQ110" t="inlineStr">
+        <is>
+          <t>Ici Japon Corp. Esport</t>
+        </is>
+      </c>
+      <c r="AR110" t="inlineStr">
+        <is>
+          <t>Ici Japon Corp. Esport</t>
+        </is>
+      </c>
+      <c r="AS110" t="inlineStr">
+        <is>
+          <t>TLN Pirates</t>
+        </is>
+      </c>
+      <c r="AT110" t="inlineStr">
+        <is>
+          <t>TLN Pirates</t>
+        </is>
+      </c>
+      <c r="AU110" t="inlineStr">
+        <is>
+          <t>TLN Pirates</t>
+        </is>
+      </c>
+      <c r="AV110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr"/>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA110" t="inlineStr">
+        <is>
+          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
+        </is>
+      </c>
+      <c r="BB110" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC110" t="inlineStr">
+        <is>
+          <t>lol-neutral-series-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD110" t="inlineStr">
+        <is>
+          <t>82612f1b27d5065af8d70fd6669509ff00dc1c7e3a91bb423192bf3b0a9736ce</t>
+        </is>
+      </c>
+      <c r="BE110" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF110" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG110" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="BH110" t="inlineStr">
+        <is>
+          <t>2026-07-21T08:30:07.926214Z</t>
+        </is>
+      </c>
+      <c r="BI110" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ110" t="inlineStr"/>
+      <c r="BK110" t="n">
+        <v>-144</v>
+      </c>
+      <c r="BL110" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="BM110" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="BN110" t="inlineStr"/>
+      <c r="BO110" t="inlineStr"/>
+      <c r="BP110" t="inlineStr"/>
+      <c r="BQ110" t="inlineStr"/>
+      <c r="BR110" t="inlineStr"/>
+      <c r="BS110" t="inlineStr"/>
+      <c r="BT110" t="inlineStr"/>
+      <c r="BU110" t="inlineStr"/>
+      <c r="BV110" t="inlineStr"/>
+      <c r="BW110" t="inlineStr"/>
+      <c r="BX110" t="inlineStr"/>
+      <c r="BY110" t="inlineStr"/>
+      <c r="BZ110" t="inlineStr"/>
+      <c r="CA110" t="inlineStr"/>
+      <c r="CB110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>ae3d2668608949f1</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>2026-07-21T08:30:07.516232Z</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>2026-07-21T11:30:00Z</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>54961</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>DN SOOPers</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Hanwha Life Esports</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L111" t="n">
+        <v>194</v>
+      </c>
+      <c r="M111" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="N111" t="n">
+        <v>0.340136</v>
+      </c>
+      <c r="O111" t="n">
+        <v>0.958215</v>
+      </c>
+      <c r="P111" t="inlineStr"/>
+      <c r="Q111" t="n">
+        <v>0.618079</v>
+      </c>
+      <c r="R111" t="n">
+        <v>100</v>
+      </c>
+      <c r="S111" t="n">
+        <v>2</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W111" t="n">
+        <v>1</v>
+      </c>
+      <c r="X111" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y111" t="inlineStr"/>
+      <c r="Z111" t="inlineStr"/>
+      <c r="AA111" t="inlineStr"/>
+      <c r="AB111" t="inlineStr"/>
+      <c r="AC111" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AD111" t="inlineStr">
+        <is>
+          <t>2026-07-21T16:22:59.458123Z</t>
+        </is>
+      </c>
+      <c r="AE111" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.3400 (aec-lol-hle-dns-2026-07-21).</t>
+        </is>
+      </c>
+      <c r="AF111" t="inlineStr">
+        <is>
+          <t>Research baseline; zero-unit shadow until qualified.</t>
+        </is>
+      </c>
+      <c r="AG111" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH111" t="inlineStr"/>
+      <c r="AI111" t="inlineStr"/>
+      <c r="AJ111" t="inlineStr"/>
+      <c r="AK111" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL111" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM111" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN111" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO111" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP111" t="inlineStr">
+        <is>
+          <t>DN SOOPers</t>
+        </is>
+      </c>
+      <c r="AQ111" t="inlineStr">
+        <is>
+          <t>DN SOOPers</t>
+        </is>
+      </c>
+      <c r="AR111" t="inlineStr">
+        <is>
+          <t>DN SOOPers</t>
+        </is>
+      </c>
+      <c r="AS111" t="inlineStr">
+        <is>
+          <t>Hanwha Life Esports</t>
+        </is>
+      </c>
+      <c r="AT111" t="inlineStr">
+        <is>
+          <t>Hanwha Life Esports</t>
+        </is>
+      </c>
+      <c r="AU111" t="inlineStr">
+        <is>
+          <t>Hanwha Life Esports</t>
+        </is>
+      </c>
+      <c r="AV111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr"/>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA111" t="inlineStr">
+        <is>
+          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
+        </is>
+      </c>
+      <c r="BB111" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC111" t="inlineStr">
+        <is>
+          <t>lol-neutral-series-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD111" t="inlineStr">
+        <is>
+          <t>82612f1b27d5065af8d70fd6669509ff00dc1c7e3a91bb423192bf3b0a9736ce</t>
+        </is>
+      </c>
+      <c r="BE111" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF111" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG111" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="BH111" t="inlineStr">
+        <is>
+          <t>2026-07-21T08:30:07.516232Z</t>
+        </is>
+      </c>
+      <c r="BI111" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ111" t="inlineStr"/>
+      <c r="BK111" t="n">
+        <v>194</v>
+      </c>
+      <c r="BL111" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="BM111" t="n">
+        <v>0.340136</v>
+      </c>
+      <c r="BN111" t="inlineStr"/>
+      <c r="BO111" t="inlineStr"/>
+      <c r="BP111" t="inlineStr"/>
+      <c r="BQ111" t="inlineStr"/>
+      <c r="BR111" t="inlineStr"/>
+      <c r="BS111" t="inlineStr"/>
+      <c r="BT111" t="inlineStr"/>
+      <c r="BU111" t="inlineStr"/>
+      <c r="BV111" t="inlineStr"/>
+      <c r="BW111" t="inlineStr"/>
+      <c r="BX111" t="inlineStr"/>
+      <c r="BY111" t="inlineStr"/>
+      <c r="BZ111" t="inlineStr"/>
+      <c r="CA111" t="inlineStr"/>
+      <c r="CB111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>a5e22a03019c4082</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>2026-07-21T08:30:07.112719Z</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>2026-07-21T10:45:00Z</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>54950</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Kiwoom DRX</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L112" t="n">
+        <v>144</v>
+      </c>
+      <c r="M112" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="N112" t="n">
+        <v>0.409836</v>
+      </c>
+      <c r="O112" t="n">
+        <v>0.933732</v>
+      </c>
+      <c r="P112" t="inlineStr"/>
+      <c r="Q112" t="n">
+        <v>0.523896</v>
+      </c>
+      <c r="R112" t="n">
+        <v>100</v>
+      </c>
+      <c r="S112" t="n">
+        <v>2</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W112" t="n">
+        <v>0</v>
+      </c>
+      <c r="X112" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y112" t="inlineStr"/>
+      <c r="Z112" t="inlineStr"/>
+      <c r="AA112" t="inlineStr"/>
+      <c r="AB112" t="inlineStr"/>
+      <c r="AC112" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AD112" t="inlineStr">
+        <is>
+          <t>2026-07-21T16:22:57.422620Z</t>
+        </is>
+      </c>
+      <c r="AE112" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4100 (aec-lol-t1-krx-2026-07-21).</t>
+        </is>
+      </c>
+      <c r="AF112" t="inlineStr">
+        <is>
+          <t>Research baseline; zero-unit shadow until qualified.</t>
+        </is>
+      </c>
+      <c r="AG112" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH112" t="inlineStr"/>
+      <c r="AI112" t="inlineStr"/>
+      <c r="AJ112" t="inlineStr"/>
+      <c r="AK112" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL112" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM112" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN112" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO112" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP112" t="inlineStr">
+        <is>
+          <t>Kiwoom DRX</t>
+        </is>
+      </c>
+      <c r="AQ112" t="inlineStr">
+        <is>
+          <t>Kiwoom DRX</t>
+        </is>
+      </c>
+      <c r="AR112" t="inlineStr">
+        <is>
+          <t>Kiwoom DRX</t>
+        </is>
+      </c>
+      <c r="AS112" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="AT112" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="AU112" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="AV112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr"/>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA112" t="inlineStr">
+        <is>
+          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
+        </is>
+      </c>
+      <c r="BB112" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC112" t="inlineStr">
+        <is>
+          <t>lol-neutral-series-elo-v1</t>
+        </is>
+      </c>
+      <c r="BD112" t="inlineStr">
+        <is>
+          <t>82612f1b27d5065af8d70fd6669509ff00dc1c7e3a91bb423192bf3b0a9736ce</t>
+        </is>
+      </c>
+      <c r="BE112" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF112" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG112" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="BH112" t="inlineStr">
+        <is>
+          <t>2026-07-21T08:30:07.112719Z</t>
+        </is>
+      </c>
+      <c r="BI112" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ112" t="inlineStr"/>
+      <c r="BK112" t="n">
+        <v>144</v>
+      </c>
+      <c r="BL112" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BM112" t="n">
+        <v>0.409836</v>
+      </c>
+      <c r="BN112" t="inlineStr"/>
+      <c r="BO112" t="inlineStr"/>
+      <c r="BP112" t="inlineStr"/>
+      <c r="BQ112" t="inlineStr"/>
+      <c r="BR112" t="inlineStr"/>
+      <c r="BS112" t="inlineStr"/>
+      <c r="BT112" t="inlineStr"/>
+      <c r="BU112" t="inlineStr"/>
+      <c r="BV112" t="inlineStr"/>
+      <c r="BW112" t="inlineStr"/>
+      <c r="BX112" t="inlineStr"/>
+      <c r="BY112" t="inlineStr"/>
+      <c r="BZ112" t="inlineStr"/>
+      <c r="CA112" t="inlineStr"/>
+      <c r="CB112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>d487a54363744159</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>2026-07-22T05:19:52.182978Z</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>2026-07-22T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>55954</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>EDward Gaming</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>LGD Gaming</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L113" t="n">
+        <v>-122</v>
+      </c>
+      <c r="M113" t="n">
+        <v>1.819672</v>
+      </c>
+      <c r="N113" t="n">
+        <v>0.54955</v>
+      </c>
+      <c r="O113" t="n">
+        <v>0.528201</v>
+      </c>
+      <c r="P113" t="inlineStr"/>
+      <c r="Q113" t="n">
+        <v>-0.021349</v>
+      </c>
+      <c r="R113" t="n">
+        <v>9</v>
+      </c>
+      <c r="S113" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr"/>
+      <c r="W113" t="inlineStr"/>
+      <c r="X113" t="inlineStr"/>
+      <c r="Y113" t="inlineStr"/>
+      <c r="Z113" t="inlineStr"/>
+      <c r="AA113" t="inlineStr"/>
+      <c r="AB113" t="inlineStr"/>
+      <c r="AC113" t="inlineStr"/>
+      <c r="AD113" t="inlineStr"/>
+      <c r="AE113" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5500 (market_slug=aec-lol-lgd-edg-2026-07-22).</t>
+        </is>
+      </c>
+      <c r="AF113" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG113" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH113" t="inlineStr"/>
+      <c r="AI113" t="inlineStr"/>
+      <c r="AJ113" t="inlineStr"/>
+      <c r="AK113" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL113" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM113" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN113" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO113" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP113" t="inlineStr">
+        <is>
+          <t>EDward Gaming</t>
+        </is>
+      </c>
+      <c r="AQ113" t="inlineStr">
+        <is>
+          <t>EDward Gaming</t>
+        </is>
+      </c>
+      <c r="AR113" t="inlineStr">
+        <is>
+          <t>EDward Gaming</t>
+        </is>
+      </c>
+      <c r="AS113" t="inlineStr">
+        <is>
+          <t>LGD Gaming</t>
+        </is>
+      </c>
+      <c r="AT113" t="inlineStr">
+        <is>
+          <t>LGD Gaming</t>
+        </is>
+      </c>
+      <c r="AU113" t="inlineStr">
+        <is>
+          <t>LGD Gaming</t>
+        </is>
+      </c>
+      <c r="AV113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr"/>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA113" t="inlineStr">
+        <is>
+          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
+        </is>
+      </c>
+      <c r="BB113" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC113" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="BD113" t="inlineStr">
+        <is>
+          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
+        </is>
+      </c>
+      <c r="BE113" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF113" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG113" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="BH113" t="inlineStr">
+        <is>
+          <t>2026-07-22T05:17:02.737464Z</t>
+        </is>
+      </c>
+      <c r="BI113" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ113" t="inlineStr"/>
+      <c r="BK113" t="n">
+        <v>-122</v>
+      </c>
+      <c r="BL113" t="n">
+        <v>1.819672</v>
+      </c>
+      <c r="BM113" t="n">
+        <v>0.54955</v>
+      </c>
+      <c r="BN113" t="inlineStr"/>
+      <c r="BO113" t="inlineStr"/>
+      <c r="BP113" t="inlineStr"/>
+      <c r="BQ113" t="inlineStr"/>
+      <c r="BR113" t="inlineStr"/>
+      <c r="BS113" t="inlineStr"/>
+      <c r="BT113" t="inlineStr"/>
+      <c r="BU113" t="inlineStr"/>
+      <c r="BV113" t="inlineStr"/>
+      <c r="BW113" t="inlineStr"/>
+      <c r="BX113" t="inlineStr"/>
+      <c r="BY113" t="inlineStr"/>
+      <c r="BZ113" t="inlineStr"/>
+      <c r="CA113" t="inlineStr"/>
+      <c r="CB113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>53088914289f4187</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>2026-07-22T05:19:52.182978Z</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>2026-07-22T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>55996</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Team WE</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Top Esports</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L114" t="n">
+        <v>-223</v>
+      </c>
+      <c r="M114" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="N114" t="n">
+        <v>0.690402</v>
+      </c>
+      <c r="O114" t="n">
+        <v>0.636655</v>
+      </c>
+      <c r="P114" t="inlineStr"/>
+      <c r="Q114" t="n">
+        <v>-0.053747</v>
+      </c>
+      <c r="R114" t="n">
+        <v>0</v>
+      </c>
+      <c r="S114" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr"/>
+      <c r="W114" t="inlineStr"/>
+      <c r="X114" t="inlineStr"/>
+      <c r="Y114" t="inlineStr"/>
+      <c r="Z114" t="inlineStr"/>
+      <c r="AA114" t="inlineStr"/>
+      <c r="AB114" t="inlineStr"/>
+      <c r="AC114" t="inlineStr"/>
+      <c r="AD114" t="inlineStr"/>
+      <c r="AE114" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-lol-tes-we-2026-07-22).</t>
+        </is>
+      </c>
+      <c r="AF114" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG114" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH114" t="inlineStr"/>
+      <c r="AI114" t="inlineStr"/>
+      <c r="AJ114" t="inlineStr"/>
+      <c r="AK114" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL114" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM114" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN114" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO114" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP114" t="inlineStr">
+        <is>
+          <t>Team WE</t>
+        </is>
+      </c>
+      <c r="AQ114" t="inlineStr">
+        <is>
+          <t>Team WE</t>
+        </is>
+      </c>
+      <c r="AR114" t="inlineStr">
+        <is>
+          <t>Team WE</t>
+        </is>
+      </c>
+      <c r="AS114" t="inlineStr">
+        <is>
+          <t>Top Esports</t>
+        </is>
+      </c>
+      <c r="AT114" t="inlineStr">
+        <is>
+          <t>Top Esports</t>
+        </is>
+      </c>
+      <c r="AU114" t="inlineStr">
+        <is>
+          <t>Top Esports</t>
+        </is>
+      </c>
+      <c r="AV114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr"/>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA114" t="inlineStr">
+        <is>
+          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
+        </is>
+      </c>
+      <c r="BB114" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC114" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="BD114" t="inlineStr">
+        <is>
+          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
+        </is>
+      </c>
+      <c r="BE114" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF114" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG114" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="BH114" t="inlineStr">
+        <is>
+          <t>2026-07-22T05:17:03.510789Z</t>
+        </is>
+      </c>
+      <c r="BI114" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ114" t="inlineStr"/>
+      <c r="BK114" t="n">
+        <v>-223</v>
+      </c>
+      <c r="BL114" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="BM114" t="n">
+        <v>0.690402</v>
+      </c>
+      <c r="BN114" t="inlineStr"/>
+      <c r="BO114" t="inlineStr"/>
+      <c r="BP114" t="inlineStr"/>
+      <c r="BQ114" t="inlineStr"/>
+      <c r="BR114" t="inlineStr"/>
+      <c r="BS114" t="inlineStr"/>
+      <c r="BT114" t="inlineStr"/>
+      <c r="BU114" t="inlineStr"/>
+      <c r="BV114" t="inlineStr"/>
+      <c r="BW114" t="inlineStr"/>
+      <c r="BX114" t="inlineStr"/>
+      <c r="BY114" t="inlineStr"/>
+      <c r="BZ114" t="inlineStr"/>
+      <c r="CA114" t="inlineStr"/>
+      <c r="CB114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>71faf50807664dea</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>2026-07-22T05:19:52.182978Z</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>2026-07-22T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>56126</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>GMBLERS ESPORTS</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>HMBLE</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L115" t="n">
+        <v>-233</v>
+      </c>
+      <c r="M115" t="n">
+        <v>1.429185</v>
+      </c>
+      <c r="N115" t="n">
+        <v>0.6997</v>
+      </c>
+      <c r="O115" t="n">
+        <v>0.575556</v>
+      </c>
+      <c r="P115" t="inlineStr"/>
+      <c r="Q115" t="n">
+        <v>-0.124144</v>
+      </c>
+      <c r="R115" t="n">
+        <v>0</v>
+      </c>
+      <c r="S115" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr"/>
+      <c r="W115" t="inlineStr"/>
+      <c r="X115" t="inlineStr"/>
+      <c r="Y115" t="inlineStr"/>
+      <c r="Z115" t="inlineStr"/>
+      <c r="AA115" t="inlineStr"/>
+      <c r="AB115" t="inlineStr"/>
+      <c r="AC115" t="inlineStr"/>
+      <c r="AD115" t="inlineStr"/>
+      <c r="AE115" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.7000 (market_slug=aec-lol-hmble-gmb-2026-07-22).</t>
+        </is>
+      </c>
+      <c r="AF115" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG115" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH115" t="inlineStr"/>
+      <c r="AI115" t="inlineStr"/>
+      <c r="AJ115" t="inlineStr"/>
+      <c r="AK115" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL115" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM115" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN115" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO115" t="inlineStr">
+        <is>
+          <t>NO_CALL_LARGE_DISAGREEMENT_REVIEW</t>
+        </is>
+      </c>
+      <c r="AP115" t="inlineStr">
+        <is>
+          <t>GMBLERS ESPORTS</t>
+        </is>
+      </c>
+      <c r="AQ115" t="inlineStr">
+        <is>
+          <t>GMBLERS ESPORTS</t>
+        </is>
+      </c>
+      <c r="AR115" t="inlineStr">
+        <is>
+          <t>GMBLERS ESPORTS</t>
+        </is>
+      </c>
+      <c r="AS115" t="inlineStr">
+        <is>
+          <t>HMBLE</t>
+        </is>
+      </c>
+      <c r="AT115" t="inlineStr">
+        <is>
+          <t>HMBLE</t>
+        </is>
+      </c>
+      <c r="AU115" t="inlineStr">
+        <is>
+          <t>HMBLE</t>
+        </is>
+      </c>
+      <c r="AV115" t="inlineStr"/>
+      <c r="AW115" t="inlineStr"/>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA115" t="inlineStr">
+        <is>
+          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
+        </is>
+      </c>
+      <c r="BB115" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC115" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="BD115" t="inlineStr">
+        <is>
+          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
+        </is>
+      </c>
+      <c r="BE115" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF115" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG115" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="BH115" t="inlineStr">
+        <is>
+          <t>2026-07-22T05:17:10.295865Z</t>
+        </is>
+      </c>
+      <c r="BI115" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ115" t="inlineStr"/>
+      <c r="BK115" t="n">
+        <v>-233</v>
+      </c>
+      <c r="BL115" t="n">
+        <v>1.429185</v>
+      </c>
+      <c r="BM115" t="n">
+        <v>0.6997</v>
+      </c>
+      <c r="BN115" t="inlineStr"/>
+      <c r="BO115" t="inlineStr"/>
+      <c r="BP115" t="inlineStr"/>
+      <c r="BQ115" t="inlineStr"/>
+      <c r="BR115" t="inlineStr"/>
+      <c r="BS115" t="inlineStr"/>
+      <c r="BT115" t="inlineStr"/>
+      <c r="BU115" t="inlineStr"/>
+      <c r="BV115" t="inlineStr"/>
+      <c r="BW115" t="inlineStr"/>
+      <c r="BX115" t="inlineStr"/>
+      <c r="BY115" t="inlineStr"/>
+      <c r="BZ115" t="inlineStr"/>
+      <c r="CA115" t="inlineStr"/>
+      <c r="CB115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>f003875538a34221</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>2026-07-22T05:19:52.182978Z</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>2026-07-22T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>58172</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Unicorns Of Love Sexy Edition</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Kaufland Hangry Knights</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L116" t="n">
+        <v>-163</v>
+      </c>
+      <c r="M116" t="n">
+        <v>1.613497</v>
+      </c>
+      <c r="N116" t="n">
+        <v>0.619772</v>
+      </c>
+      <c r="O116" t="n">
+        <v>0.634815</v>
+      </c>
+      <c r="P116" t="inlineStr"/>
+      <c r="Q116" t="n">
+        <v>0.015043</v>
+      </c>
+      <c r="R116" t="n">
+        <v>28</v>
+      </c>
+      <c r="S116" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr"/>
+      <c r="W116" t="inlineStr"/>
+      <c r="X116" t="inlineStr"/>
+      <c r="Y116" t="inlineStr"/>
+      <c r="Z116" t="inlineStr"/>
+      <c r="AA116" t="inlineStr"/>
+      <c r="AB116" t="inlineStr"/>
+      <c r="AC116" t="inlineStr"/>
+      <c r="AD116" t="inlineStr"/>
+      <c r="AE116" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-lol-khk-use-2026-07-22).</t>
+        </is>
+      </c>
+      <c r="AF116" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG116" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH116" t="inlineStr"/>
+      <c r="AI116" t="inlineStr"/>
+      <c r="AJ116" t="inlineStr"/>
+      <c r="AK116" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL116" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM116" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN116" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO116" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP116" t="inlineStr">
+        <is>
+          <t>Unicorns Of Love Sexy Edition</t>
+        </is>
+      </c>
+      <c r="AQ116" t="inlineStr">
+        <is>
+          <t>Unicorns Of Love Sexy Edition</t>
+        </is>
+      </c>
+      <c r="AR116" t="inlineStr">
+        <is>
+          <t>Unicorns Of Love Sexy Edition</t>
+        </is>
+      </c>
+      <c r="AS116" t="inlineStr">
+        <is>
+          <t>Kaufland Hangry Knights</t>
+        </is>
+      </c>
+      <c r="AT116" t="inlineStr">
+        <is>
+          <t>Kaufland Hangry Knights</t>
+        </is>
+      </c>
+      <c r="AU116" t="inlineStr">
+        <is>
+          <t>Kaufland Hangry Knights</t>
+        </is>
+      </c>
+      <c r="AV116" t="inlineStr"/>
+      <c r="AW116" t="inlineStr"/>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA116" t="inlineStr">
+        <is>
+          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
+        </is>
+      </c>
+      <c r="BB116" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC116" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="BD116" t="inlineStr">
+        <is>
+          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
+        </is>
+      </c>
+      <c r="BE116" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF116" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG116" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="BH116" t="inlineStr">
+        <is>
+          <t>2026-07-22T05:17:11.065754Z</t>
+        </is>
+      </c>
+      <c r="BI116" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ116" t="inlineStr"/>
+      <c r="BK116" t="n">
+        <v>-163</v>
+      </c>
+      <c r="BL116" t="n">
+        <v>1.613497</v>
+      </c>
+      <c r="BM116" t="n">
+        <v>0.619772</v>
+      </c>
+      <c r="BN116" t="inlineStr"/>
+      <c r="BO116" t="inlineStr"/>
+      <c r="BP116" t="inlineStr"/>
+      <c r="BQ116" t="inlineStr"/>
+      <c r="BR116" t="inlineStr"/>
+      <c r="BS116" t="inlineStr"/>
+      <c r="BT116" t="inlineStr"/>
+      <c r="BU116" t="inlineStr"/>
+      <c r="BV116" t="inlineStr"/>
+      <c r="BW116" t="inlineStr"/>
+      <c r="BX116" t="inlineStr"/>
+      <c r="BY116" t="inlineStr"/>
+      <c r="BZ116" t="inlineStr"/>
+      <c r="CA116" t="inlineStr"/>
+      <c r="CB116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>b3933a7255314a9c</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>2026-07-22T05:19:52.182978Z</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>2026-07-22T17:30:00Z</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>56127</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>UCAM Esports Club</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Barça eSports</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L117" t="n">
+        <v>-150</v>
+      </c>
+      <c r="M117" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.581485</v>
+      </c>
+      <c r="P117" t="inlineStr"/>
+      <c r="Q117" t="n">
+        <v>-0.018515</v>
+      </c>
+      <c r="R117" t="n">
+        <v>11</v>
+      </c>
+      <c r="S117" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr"/>
+      <c r="W117" t="inlineStr"/>
+      <c r="X117" t="inlineStr"/>
+      <c r="Y117" t="inlineStr"/>
+      <c r="Z117" t="inlineStr"/>
+      <c r="AA117" t="inlineStr"/>
+      <c r="AB117" t="inlineStr"/>
+      <c r="AC117" t="inlineStr"/>
+      <c r="AD117" t="inlineStr"/>
+      <c r="AE117" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6000 (market_slug=aec-lol-bar-ucam-2026-07-22).</t>
+        </is>
+      </c>
+      <c r="AF117" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG117" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH117" t="inlineStr"/>
+      <c r="AI117" t="inlineStr"/>
+      <c r="AJ117" t="inlineStr"/>
+      <c r="AK117" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL117" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM117" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN117" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO117" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP117" t="inlineStr">
+        <is>
+          <t>UCAM Esports Club</t>
+        </is>
+      </c>
+      <c r="AQ117" t="inlineStr">
+        <is>
+          <t>UCAM Esports Club</t>
+        </is>
+      </c>
+      <c r="AR117" t="inlineStr">
+        <is>
+          <t>UCAM Esports Club</t>
+        </is>
+      </c>
+      <c r="AS117" t="inlineStr">
+        <is>
+          <t>Barça eSports</t>
+        </is>
+      </c>
+      <c r="AT117" t="inlineStr">
+        <is>
+          <t>Barça eSports</t>
+        </is>
+      </c>
+      <c r="AU117" t="inlineStr">
+        <is>
+          <t>Barça eSports</t>
+        </is>
+      </c>
+      <c r="AV117" t="inlineStr"/>
+      <c r="AW117" t="inlineStr"/>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA117" t="inlineStr">
+        <is>
+          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
+        </is>
+      </c>
+      <c r="BB117" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC117" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="BD117" t="inlineStr">
+        <is>
+          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
+        </is>
+      </c>
+      <c r="BE117" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF117" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG117" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="BH117" t="inlineStr">
+        <is>
+          <t>2026-07-22T05:17:11.800383Z</t>
+        </is>
+      </c>
+      <c r="BI117" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ117" t="inlineStr"/>
+      <c r="BK117" t="n">
+        <v>-150</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BN117" t="inlineStr"/>
+      <c r="BO117" t="inlineStr"/>
+      <c r="BP117" t="inlineStr"/>
+      <c r="BQ117" t="inlineStr"/>
+      <c r="BR117" t="inlineStr"/>
+      <c r="BS117" t="inlineStr"/>
+      <c r="BT117" t="inlineStr"/>
+      <c r="BU117" t="inlineStr"/>
+      <c r="BV117" t="inlineStr"/>
+      <c r="BW117" t="inlineStr"/>
+      <c r="BX117" t="inlineStr"/>
+      <c r="BY117" t="inlineStr"/>
+      <c r="BZ117" t="inlineStr"/>
+      <c r="CA117" t="inlineStr"/>
+      <c r="CB117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>69fb3791da444f92</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>2026-07-22T05:19:52.182978Z</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>2026-07-22T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>56129</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>EKO Esports</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>TITANS</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L118" t="n">
+        <v>133</v>
+      </c>
+      <c r="M118" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.429185</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.514184</v>
+      </c>
+      <c r="P118" t="inlineStr"/>
+      <c r="Q118" t="n">
+        <v>0.08499900000000001</v>
+      </c>
+      <c r="R118" t="n">
+        <v>62</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr"/>
+      <c r="W118" t="inlineStr"/>
+      <c r="X118" t="inlineStr"/>
+      <c r="Y118" t="inlineStr"/>
+      <c r="Z118" t="inlineStr"/>
+      <c r="AA118" t="inlineStr"/>
+      <c r="AB118" t="inlineStr"/>
+      <c r="AC118" t="inlineStr"/>
+      <c r="AD118" t="inlineStr"/>
+      <c r="AE118" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4300 (market_slug=aec-lol-tts-eko-2026-07-22).</t>
+        </is>
+      </c>
+      <c r="AF118" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG118" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH118" t="inlineStr"/>
+      <c r="AI118" t="inlineStr"/>
+      <c r="AJ118" t="inlineStr"/>
+      <c r="AK118" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL118" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM118" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN118" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO118" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP118" t="inlineStr">
+        <is>
+          <t>EKO Esports</t>
+        </is>
+      </c>
+      <c r="AQ118" t="inlineStr">
+        <is>
+          <t>EKO Esports</t>
+        </is>
+      </c>
+      <c r="AR118" t="inlineStr">
+        <is>
+          <t>EKO Esports</t>
+        </is>
+      </c>
+      <c r="AS118" t="inlineStr">
+        <is>
+          <t>TITANS</t>
+        </is>
+      </c>
+      <c r="AT118" t="inlineStr">
+        <is>
+          <t>TITANS</t>
+        </is>
+      </c>
+      <c r="AU118" t="inlineStr">
+        <is>
+          <t>TITANS</t>
+        </is>
+      </c>
+      <c r="AV118" t="inlineStr"/>
+      <c r="AW118" t="inlineStr"/>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA118" t="inlineStr">
+        <is>
+          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
+        </is>
+      </c>
+      <c r="BB118" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC118" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="BD118" t="inlineStr">
+        <is>
+          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
+        </is>
+      </c>
+      <c r="BE118" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF118" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG118" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="BH118" t="inlineStr">
+        <is>
+          <t>2026-07-22T05:17:13.396220Z</t>
+        </is>
+      </c>
+      <c r="BI118" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ118" t="inlineStr"/>
+      <c r="BK118" t="n">
+        <v>133</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.429185</v>
+      </c>
+      <c r="BN118" t="inlineStr"/>
+      <c r="BO118" t="inlineStr"/>
+      <c r="BP118" t="inlineStr"/>
+      <c r="BQ118" t="inlineStr"/>
+      <c r="BR118" t="inlineStr"/>
+      <c r="BS118" t="inlineStr"/>
+      <c r="BT118" t="inlineStr"/>
+      <c r="BU118" t="inlineStr"/>
+      <c r="BV118" t="inlineStr"/>
+      <c r="BW118" t="inlineStr"/>
+      <c r="BX118" t="inlineStr"/>
+      <c r="BY118" t="inlineStr"/>
+      <c r="BZ118" t="inlineStr"/>
+      <c r="CA118" t="inlineStr"/>
+      <c r="CB118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>acbde024ef4d41db</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>2026-07-22T05:19:52.182978Z</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>2026-07-22T19:00:00Z</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>56130</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Aeterna Esports</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>P11 Esports</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L119" t="n">
+        <v>-163</v>
+      </c>
+      <c r="M119" t="n">
+        <v>1.613497</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.619772</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.518543</v>
+      </c>
+      <c r="P119" t="inlineStr"/>
+      <c r="Q119" t="n">
+        <v>-0.101229</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr"/>
+      <c r="W119" t="inlineStr"/>
+      <c r="X119" t="inlineStr"/>
+      <c r="Y119" t="inlineStr"/>
+      <c r="Z119" t="inlineStr"/>
+      <c r="AA119" t="inlineStr"/>
+      <c r="AB119" t="inlineStr"/>
+      <c r="AC119" t="inlineStr"/>
+      <c r="AD119" t="inlineStr"/>
+      <c r="AE119" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-lol-p11-aee-2026-07-22).</t>
+        </is>
+      </c>
+      <c r="AF119" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG119" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH119" t="inlineStr"/>
+      <c r="AI119" t="inlineStr"/>
+      <c r="AJ119" t="inlineStr"/>
+      <c r="AK119" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL119" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM119" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN119" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO119" t="inlineStr">
+        <is>
+          <t>NO_CALL_LARGE_DISAGREEMENT_REVIEW</t>
+        </is>
+      </c>
+      <c r="AP119" t="inlineStr">
+        <is>
+          <t>Aeterna Esports</t>
+        </is>
+      </c>
+      <c r="AQ119" t="inlineStr">
+        <is>
+          <t>Aeterna Esports</t>
+        </is>
+      </c>
+      <c r="AR119" t="inlineStr">
+        <is>
+          <t>Aeterna Esports</t>
+        </is>
+      </c>
+      <c r="AS119" t="inlineStr">
+        <is>
+          <t>P11 Esports</t>
+        </is>
+      </c>
+      <c r="AT119" t="inlineStr">
+        <is>
+          <t>P11 Esports</t>
+        </is>
+      </c>
+      <c r="AU119" t="inlineStr">
+        <is>
+          <t>P11 Esports</t>
+        </is>
+      </c>
+      <c r="AV119" t="inlineStr"/>
+      <c r="AW119" t="inlineStr"/>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA119" t="inlineStr">
+        <is>
+          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
+        </is>
+      </c>
+      <c r="BB119" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC119" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="BD119" t="inlineStr">
+        <is>
+          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
+        </is>
+      </c>
+      <c r="BE119" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF119" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG119" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="BH119" t="inlineStr">
+        <is>
+          <t>2026-07-22T05:17:18.687465Z</t>
+        </is>
+      </c>
+      <c r="BI119" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ119" t="inlineStr"/>
+      <c r="BK119" t="n">
+        <v>-163</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>1.613497</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.619772</v>
+      </c>
+      <c r="BN119" t="inlineStr"/>
+      <c r="BO119" t="inlineStr"/>
+      <c r="BP119" t="inlineStr"/>
+      <c r="BQ119" t="inlineStr"/>
+      <c r="BR119" t="inlineStr"/>
+      <c r="BS119" t="inlineStr"/>
+      <c r="BT119" t="inlineStr"/>
+      <c r="BU119" t="inlineStr"/>
+      <c r="BV119" t="inlineStr"/>
+      <c r="BW119" t="inlineStr"/>
+      <c r="BX119" t="inlineStr"/>
+      <c r="BY119" t="inlineStr"/>
+      <c r="BZ119" t="inlineStr"/>
+      <c r="CA119" t="inlineStr"/>
+      <c r="CB119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>af7e142ab3744a4a</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>2026-07-22T05:19:52.182978Z</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>2026-07-22T20:00:00Z</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>56132</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>INTZ e-Sports</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>KaBuM! Ilha das Lendas</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L120" t="n">
+        <v>-104</v>
+      </c>
+      <c r="M120" t="n">
+        <v>1.961538</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.509804</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.600063</v>
+      </c>
+      <c r="P120" t="inlineStr"/>
+      <c r="Q120" t="n">
+        <v>0.09025900000000001</v>
+      </c>
+      <c r="R120" t="n">
+        <v>65</v>
+      </c>
+      <c r="S120" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr"/>
+      <c r="W120" t="inlineStr"/>
+      <c r="X120" t="inlineStr"/>
+      <c r="Y120" t="inlineStr"/>
+      <c r="Z120" t="inlineStr"/>
+      <c r="AA120" t="inlineStr"/>
+      <c r="AB120" t="inlineStr"/>
+      <c r="AC120" t="inlineStr"/>
+      <c r="AD120" t="inlineStr"/>
+      <c r="AE120" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5100 (market_slug=aec-lol-kbm-itz-2026-07-22).</t>
+        </is>
+      </c>
+      <c r="AF120" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG120" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH120" t="inlineStr"/>
+      <c r="AI120" t="inlineStr"/>
+      <c r="AJ120" t="inlineStr"/>
+      <c r="AK120" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL120" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM120" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN120" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO120" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP120" t="inlineStr">
+        <is>
+          <t>INTZ e-Sports</t>
+        </is>
+      </c>
+      <c r="AQ120" t="inlineStr">
+        <is>
+          <t>INTZ e-Sports</t>
+        </is>
+      </c>
+      <c r="AR120" t="inlineStr">
+        <is>
+          <t>INTZ e-Sports</t>
+        </is>
+      </c>
+      <c r="AS120" t="inlineStr">
+        <is>
+          <t>KaBuM! Ilha das Lendas</t>
+        </is>
+      </c>
+      <c r="AT120" t="inlineStr">
+        <is>
+          <t>KaBuM! Ilha das Lendas</t>
+        </is>
+      </c>
+      <c r="AU120" t="inlineStr">
+        <is>
+          <t>KaBuM! Ilha das Lendas</t>
+        </is>
+      </c>
+      <c r="AV120" t="inlineStr"/>
+      <c r="AW120" t="inlineStr"/>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA120" t="inlineStr">
+        <is>
+          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
+        </is>
+      </c>
+      <c r="BB120" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC120" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="BD120" t="inlineStr">
+        <is>
+          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
+        </is>
+      </c>
+      <c r="BE120" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF120" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG120" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="BH120" t="inlineStr">
+        <is>
+          <t>2026-07-22T05:17:20.981406Z</t>
+        </is>
+      </c>
+      <c r="BI120" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ120" t="inlineStr"/>
+      <c r="BK120" t="n">
+        <v>-104</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>1.961538</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.509804</v>
+      </c>
+      <c r="BN120" t="inlineStr"/>
+      <c r="BO120" t="inlineStr"/>
+      <c r="BP120" t="inlineStr"/>
+      <c r="BQ120" t="inlineStr"/>
+      <c r="BR120" t="inlineStr"/>
+      <c r="BS120" t="inlineStr"/>
+      <c r="BT120" t="inlineStr"/>
+      <c r="BU120" t="inlineStr"/>
+      <c r="BV120" t="inlineStr"/>
+      <c r="BW120" t="inlineStr"/>
+      <c r="BX120" t="inlineStr"/>
+      <c r="BY120" t="inlineStr"/>
+      <c r="BZ120" t="inlineStr"/>
+      <c r="CA120" t="inlineStr"/>
+      <c r="CB120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>cb95d785b47c4574</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>2026-07-22T05:19:52.182978Z</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>2026-07-22T23:00:00Z</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>56138</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>7REX</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Ei Nerd Esports</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L121" t="n">
+        <v>138</v>
+      </c>
+      <c r="M121" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.420168</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.5449850000000001</v>
+      </c>
+      <c r="P121" t="inlineStr"/>
+      <c r="Q121" t="n">
+        <v>0.124817</v>
+      </c>
+      <c r="R121" t="n">
+        <v>100</v>
+      </c>
+      <c r="S121" t="n">
+        <v>1</v>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr"/>
+      <c r="W121" t="inlineStr"/>
+      <c r="X121" t="inlineStr"/>
+      <c r="Y121" t="inlineStr"/>
+      <c r="Z121" t="inlineStr"/>
+      <c r="AA121" t="inlineStr"/>
+      <c r="AB121" t="inlineStr"/>
+      <c r="AC121" t="inlineStr"/>
+      <c r="AD121" t="inlineStr"/>
+      <c r="AE121" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4200 (market_slug=aec-lol-nerd-7rex-2026-07-22).</t>
+        </is>
+      </c>
+      <c r="AF121" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG121" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH121" t="inlineStr"/>
+      <c r="AI121" t="inlineStr"/>
+      <c r="AJ121" t="inlineStr"/>
+      <c r="AK121" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL121" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM121" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN121" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO121" t="inlineStr">
+        <is>
+          <t>NO_CALL_LARGE_DISAGREEMENT_REVIEW</t>
+        </is>
+      </c>
+      <c r="AP121" t="inlineStr">
+        <is>
+          <t>7REX</t>
+        </is>
+      </c>
+      <c r="AQ121" t="inlineStr">
+        <is>
+          <t>7REX</t>
+        </is>
+      </c>
+      <c r="AR121" t="inlineStr">
+        <is>
+          <t>7REX</t>
+        </is>
+      </c>
+      <c r="AS121" t="inlineStr">
+        <is>
+          <t>Ei Nerd Esports</t>
+        </is>
+      </c>
+      <c r="AT121" t="inlineStr">
+        <is>
+          <t>Ei Nerd Esports</t>
+        </is>
+      </c>
+      <c r="AU121" t="inlineStr">
+        <is>
+          <t>Ei Nerd Esports</t>
+        </is>
+      </c>
+      <c r="AV121" t="inlineStr"/>
+      <c r="AW121" t="inlineStr"/>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA121" t="inlineStr">
+        <is>
+          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
+        </is>
+      </c>
+      <c r="BB121" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC121" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="BD121" t="inlineStr">
+        <is>
+          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
+        </is>
+      </c>
+      <c r="BE121" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF121" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG121" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="BH121" t="inlineStr">
+        <is>
+          <t>2026-07-22T05:17:24.819172Z</t>
+        </is>
+      </c>
+      <c r="BI121" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ121" t="inlineStr"/>
+      <c r="BK121" t="n">
+        <v>138</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.420168</v>
+      </c>
+      <c r="BN121" t="inlineStr"/>
+      <c r="BO121" t="inlineStr"/>
+      <c r="BP121" t="inlineStr"/>
+      <c r="BQ121" t="inlineStr"/>
+      <c r="BR121" t="inlineStr"/>
+      <c r="BS121" t="inlineStr"/>
+      <c r="BT121" t="inlineStr"/>
+      <c r="BU121" t="inlineStr"/>
+      <c r="BV121" t="inlineStr"/>
+      <c r="BW121" t="inlineStr"/>
+      <c r="BX121" t="inlineStr"/>
+      <c r="BY121" t="inlineStr"/>
+      <c r="BZ121" t="inlineStr"/>
+      <c r="CA121" t="inlineStr"/>
+      <c r="CB121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>8af698b4ee2c496c</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>2026-07-22T05:19:52.182978Z</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>2026-07-23T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>56810</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Anyone's Legend</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>JD Gaming</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L122" t="n">
+        <v>-138</v>
+      </c>
+      <c r="M122" t="n">
+        <v>1.724638</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.579832</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.529047</v>
+      </c>
+      <c r="P122" t="inlineStr"/>
+      <c r="Q122" t="n">
+        <v>-0.050785</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr"/>
+      <c r="W122" t="inlineStr"/>
+      <c r="X122" t="inlineStr"/>
+      <c r="Y122" t="inlineStr"/>
+      <c r="Z122" t="inlineStr"/>
+      <c r="AA122" t="inlineStr"/>
+      <c r="AB122" t="inlineStr"/>
+      <c r="AC122" t="inlineStr"/>
+      <c r="AD122" t="inlineStr"/>
+      <c r="AE122" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-lol-jdg-al-2026-07-23).</t>
+        </is>
+      </c>
+      <c r="AF122" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG122" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH122" t="inlineStr"/>
+      <c r="AI122" t="inlineStr"/>
+      <c r="AJ122" t="inlineStr"/>
+      <c r="AK122" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL122" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM122" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN122" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO122" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP122" t="inlineStr">
+        <is>
+          <t>Anyone's Legend</t>
+        </is>
+      </c>
+      <c r="AQ122" t="inlineStr">
+        <is>
+          <t>Anyone's Legend</t>
+        </is>
+      </c>
+      <c r="AR122" t="inlineStr">
+        <is>
+          <t>Anyone's Legend</t>
+        </is>
+      </c>
+      <c r="AS122" t="inlineStr">
+        <is>
+          <t>JD Gaming</t>
+        </is>
+      </c>
+      <c r="AT122" t="inlineStr">
+        <is>
+          <t>JD Gaming</t>
+        </is>
+      </c>
+      <c r="AU122" t="inlineStr">
+        <is>
+          <t>JD Gaming</t>
+        </is>
+      </c>
+      <c r="AV122" t="inlineStr"/>
+      <c r="AW122" t="inlineStr"/>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA122" t="inlineStr">
+        <is>
+          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
+        </is>
+      </c>
+      <c r="BB122" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC122" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="BD122" t="inlineStr">
+        <is>
+          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
+        </is>
+      </c>
+      <c r="BE122" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF122" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG122" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="BH122" t="inlineStr">
+        <is>
+          <t>2026-07-22T05:17:27.088741Z</t>
+        </is>
+      </c>
+      <c r="BI122" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ122" t="inlineStr"/>
+      <c r="BK122" t="n">
+        <v>-138</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>1.724638</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>0.579832</v>
+      </c>
+      <c r="BN122" t="inlineStr"/>
+      <c r="BO122" t="inlineStr"/>
+      <c r="BP122" t="inlineStr"/>
+      <c r="BQ122" t="inlineStr"/>
+      <c r="BR122" t="inlineStr"/>
+      <c r="BS122" t="inlineStr"/>
+      <c r="BT122" t="inlineStr"/>
+      <c r="BU122" t="inlineStr"/>
+      <c r="BV122" t="inlineStr"/>
+      <c r="BW122" t="inlineStr"/>
+      <c r="BX122" t="inlineStr"/>
+      <c r="BY122" t="inlineStr"/>
+      <c r="BZ122" t="inlineStr"/>
+      <c r="CA122" t="inlineStr"/>
+      <c r="CB122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2fc0c6b918364ae8</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>2026-07-22T05:19:52.182978Z</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>2026-07-23T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>57088</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Dynasty</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Myth Esports</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L123" t="n">
+        <v>138</v>
+      </c>
+      <c r="M123" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.420168</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.501096</v>
+      </c>
+      <c r="P123" t="inlineStr"/>
+      <c r="Q123" t="n">
+        <v>0.080928</v>
+      </c>
+      <c r="R123" t="n">
+        <v>60</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr"/>
+      <c r="W123" t="inlineStr"/>
+      <c r="X123" t="inlineStr"/>
+      <c r="Y123" t="inlineStr"/>
+      <c r="Z123" t="inlineStr"/>
+      <c r="AA123" t="inlineStr"/>
+      <c r="AB123" t="inlineStr"/>
+      <c r="AC123" t="inlineStr"/>
+      <c r="AD123" t="inlineStr"/>
+      <c r="AE123" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4200 (market_slug=aec-lol-myth-dyn-2026-07-23).</t>
+        </is>
+      </c>
+      <c r="AF123" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG123" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH123" t="inlineStr"/>
+      <c r="AI123" t="inlineStr"/>
+      <c r="AJ123" t="inlineStr"/>
+      <c r="AK123" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL123" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM123" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN123" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO123" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP123" t="inlineStr">
+        <is>
+          <t>Dynasty</t>
+        </is>
+      </c>
+      <c r="AQ123" t="inlineStr">
+        <is>
+          <t>Dynasty</t>
+        </is>
+      </c>
+      <c r="AR123" t="inlineStr">
+        <is>
+          <t>Dynasty</t>
+        </is>
+      </c>
+      <c r="AS123" t="inlineStr">
+        <is>
+          <t>Myth Esports</t>
+        </is>
+      </c>
+      <c r="AT123" t="inlineStr">
+        <is>
+          <t>Myth Esports</t>
+        </is>
+      </c>
+      <c r="AU123" t="inlineStr">
+        <is>
+          <t>Myth Esports</t>
+        </is>
+      </c>
+      <c r="AV123" t="inlineStr"/>
+      <c r="AW123" t="inlineStr"/>
+      <c r="AX123" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA123" t="inlineStr">
+        <is>
+          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
+        </is>
+      </c>
+      <c r="BB123" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC123" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="BD123" t="inlineStr">
+        <is>
+          <t>e0cd9cffa8d11f894fd13b69be474bf2e4371b29db5e62888aec7b8f44f78946</t>
+        </is>
+      </c>
+      <c r="BE123" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF123" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG123" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v3</t>
+        </is>
+      </c>
+      <c r="BH123" t="inlineStr">
+        <is>
+          <t>2026-07-22T05:17:33.061872Z</t>
+        </is>
+      </c>
+      <c r="BI123" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ123" t="inlineStr"/>
+      <c r="BK123" t="n">
+        <v>138</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.420168</v>
+      </c>
+      <c r="BN123" t="inlineStr"/>
+      <c r="BO123" t="inlineStr"/>
+      <c r="BP123" t="inlineStr"/>
+      <c r="BQ123" t="inlineStr"/>
+      <c r="BR123" t="inlineStr"/>
+      <c r="BS123" t="inlineStr"/>
+      <c r="BT123" t="inlineStr"/>
+      <c r="BU123" t="inlineStr"/>
+      <c r="BV123" t="inlineStr"/>
+      <c r="BW123" t="inlineStr"/>
+      <c r="BX123" t="inlineStr"/>
+      <c r="BY123" t="inlineStr"/>
+      <c r="BZ123" t="inlineStr"/>
+      <c r="CA123" t="inlineStr"/>
+      <c r="CB123" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/picks.xlsx
+++ b/data/picks.xlsx
@@ -4032,7 +4032,7 @@
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
@@ -4296,7 +4296,7 @@
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>43ee2f84f025c10f83f80a8c22d49c35c420734a8a730b5f272287225cceee4b</t>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
@@ -5100,7 +5100,7 @@
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
@@ -5376,7 +5376,7 @@
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
@@ -5652,7 +5652,7 @@
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
@@ -5928,7 +5928,7 @@
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
@@ -6204,7 +6204,7 @@
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
@@ -6458,7 +6458,7 @@
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
@@ -7172,7 +7172,7 @@
       </c>
       <c r="BA24" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB24" t="inlineStr">
@@ -7410,7 +7410,7 @@
       </c>
       <c r="BA25" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB25" t="inlineStr">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="BA26" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB26" t="inlineStr">
@@ -7886,7 +7886,7 @@
       </c>
       <c r="BA27" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB27" t="inlineStr">
@@ -8124,7 +8124,7 @@
       </c>
       <c r="BA28" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB28" t="inlineStr">
@@ -8384,7 +8384,7 @@
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
@@ -8660,7 +8660,7 @@
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB30" t="inlineStr">
@@ -8936,7 +8936,7 @@
       </c>
       <c r="BA31" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB31" t="inlineStr">
@@ -9212,7 +9212,7 @@
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
@@ -9488,7 +9488,7 @@
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
@@ -9764,7 +9764,7 @@
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
@@ -10040,7 +10040,7 @@
       </c>
       <c r="BA35" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB35" t="inlineStr">
@@ -10316,7 +10316,7 @@
       </c>
       <c r="BA36" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB36" t="inlineStr">
@@ -10592,7 +10592,7 @@
       </c>
       <c r="BA37" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB37" t="inlineStr">
@@ -10868,7 +10868,7 @@
       </c>
       <c r="BA38" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB38" t="inlineStr">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="BA39" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB39" t="inlineStr">
@@ -11420,7 +11420,7 @@
       </c>
       <c r="BA40" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB40" t="inlineStr">
@@ -11696,7 +11696,7 @@
       </c>
       <c r="BA41" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB41" t="inlineStr">
@@ -11972,7 +11972,7 @@
       </c>
       <c r="BA42" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB42" t="inlineStr">
@@ -12248,7 +12248,7 @@
       </c>
       <c r="BA43" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB43" t="inlineStr">
@@ -12524,7 +12524,7 @@
       </c>
       <c r="BA44" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB44" t="inlineStr">
@@ -12800,7 +12800,7 @@
       </c>
       <c r="BA45" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB45" t="inlineStr">
@@ -13076,7 +13076,7 @@
       </c>
       <c r="BA46" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB46" t="inlineStr">
@@ -13352,7 +13352,7 @@
       </c>
       <c r="BA47" t="inlineStr">
         <is>
-          <t>6b38a269117f4c6c1ae1e324273c2f9b9d11b2c15d99242f39aa89882d15db32</t>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
         </is>
       </c>
       <c r="BB47" t="inlineStr">
@@ -14622,7 +14622,7 @@
       </c>
       <c r="BA52" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB52" t="inlineStr">
@@ -14886,7 +14886,7 @@
       </c>
       <c r="BA53" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB53" t="inlineStr">
@@ -15150,7 +15150,7 @@
       </c>
       <c r="BA54" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB54" t="inlineStr">
@@ -15414,7 +15414,7 @@
       </c>
       <c r="BA55" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB55" t="inlineStr">
@@ -15678,7 +15678,7 @@
       </c>
       <c r="BA56" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB56" t="inlineStr">
@@ -15942,7 +15942,7 @@
       </c>
       <c r="BA57" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB57" t="inlineStr">
@@ -16206,7 +16206,7 @@
       </c>
       <c r="BA58" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB58" t="inlineStr">
@@ -16470,7 +16470,7 @@
       </c>
       <c r="BA59" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB59" t="inlineStr">
@@ -16734,7 +16734,7 @@
       </c>
       <c r="BA60" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB60" t="inlineStr">
@@ -16998,7 +16998,7 @@
       </c>
       <c r="BA61" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB61" t="inlineStr">
@@ -17262,7 +17262,7 @@
       </c>
       <c r="BA62" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB62" t="inlineStr">
@@ -17526,7 +17526,7 @@
       </c>
       <c r="BA63" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB63" t="inlineStr">
@@ -17790,7 +17790,7 @@
       </c>
       <c r="BA64" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB64" t="inlineStr">
@@ -18054,7 +18054,7 @@
       </c>
       <c r="BA65" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB65" t="inlineStr">
@@ -18318,7 +18318,7 @@
       </c>
       <c r="BA66" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB66" t="inlineStr">
@@ -18582,7 +18582,7 @@
       </c>
       <c r="BA67" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB67" t="inlineStr">
@@ -18846,7 +18846,7 @@
       </c>
       <c r="BA68" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB68" t="inlineStr">
@@ -19110,7 +19110,7 @@
       </c>
       <c r="BA69" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB69" t="inlineStr">
@@ -19374,7 +19374,7 @@
       </c>
       <c r="BA70" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB70" t="inlineStr">
@@ -19638,7 +19638,7 @@
       </c>
       <c r="BA71" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB71" t="inlineStr">
@@ -19902,7 +19902,7 @@
       </c>
       <c r="BA72" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB72" t="inlineStr">
@@ -20166,7 +20166,7 @@
       </c>
       <c r="BA73" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB73" t="inlineStr">
@@ -20430,7 +20430,7 @@
       </c>
       <c r="BA74" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB74" t="inlineStr">
@@ -20694,7 +20694,7 @@
       </c>
       <c r="BA75" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB75" t="inlineStr">
@@ -20958,7 +20958,7 @@
       </c>
       <c r="BA76" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB76" t="inlineStr">
@@ -21222,7 +21222,7 @@
       </c>
       <c r="BA77" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB77" t="inlineStr">
@@ -21486,7 +21486,7 @@
       </c>
       <c r="BA78" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB78" t="inlineStr">
@@ -21750,7 +21750,7 @@
       </c>
       <c r="BA79" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB79" t="inlineStr">
@@ -21992,7 +21992,7 @@
       </c>
       <c r="BA80" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB80" t="inlineStr">
@@ -22230,7 +22230,7 @@
       </c>
       <c r="BA81" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB81" t="inlineStr">
@@ -22468,7 +22468,7 @@
       </c>
       <c r="BA82" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB82" t="inlineStr">
@@ -22706,7 +22706,7 @@
       </c>
       <c r="BA83" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB83" t="inlineStr">
@@ -22944,7 +22944,7 @@
       </c>
       <c r="BA84" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB84" t="inlineStr">
@@ -23182,7 +23182,7 @@
       </c>
       <c r="BA85" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB85" t="inlineStr">
@@ -23420,7 +23420,7 @@
       </c>
       <c r="BA86" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB86" t="inlineStr">
@@ -23658,7 +23658,7 @@
       </c>
       <c r="BA87" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB87" t="inlineStr">
@@ -23896,7 +23896,7 @@
       </c>
       <c r="BA88" t="inlineStr">
         <is>
-          <t>5224fb6ffbc9ddf8fa517627b830ac851192da94d241963d556945393a42bb9d</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB88" t="inlineStr">

--- a/data/picks.xlsx
+++ b/data/picks.xlsx
@@ -4032,7 +4032,7 @@
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
@@ -4296,7 +4296,7 @@
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
@@ -5100,7 +5100,7 @@
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
@@ -5376,7 +5376,7 @@
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
@@ -5652,7 +5652,7 @@
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
@@ -5928,7 +5928,7 @@
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
@@ -6204,7 +6204,7 @@
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
@@ -6458,7 +6458,7 @@
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
@@ -7172,7 +7172,7 @@
       </c>
       <c r="BA24" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB24" t="inlineStr">
@@ -7410,7 +7410,7 @@
       </c>
       <c r="BA25" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB25" t="inlineStr">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="BA26" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB26" t="inlineStr">
@@ -7886,7 +7886,7 @@
       </c>
       <c r="BA27" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB27" t="inlineStr">
@@ -8124,7 +8124,7 @@
       </c>
       <c r="BA28" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB28" t="inlineStr">
@@ -8384,7 +8384,7 @@
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
@@ -8660,7 +8660,7 @@
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB30" t="inlineStr">
@@ -8936,7 +8936,7 @@
       </c>
       <c r="BA31" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB31" t="inlineStr">
@@ -9212,7 +9212,7 @@
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
@@ -9488,7 +9488,7 @@
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
@@ -9764,7 +9764,7 @@
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
@@ -10040,7 +10040,7 @@
       </c>
       <c r="BA35" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB35" t="inlineStr">
@@ -10316,7 +10316,7 @@
       </c>
       <c r="BA36" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB36" t="inlineStr">
@@ -10592,7 +10592,7 @@
       </c>
       <c r="BA37" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB37" t="inlineStr">
@@ -10868,7 +10868,7 @@
       </c>
       <c r="BA38" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB38" t="inlineStr">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="BA39" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB39" t="inlineStr">
@@ -11420,7 +11420,7 @@
       </c>
       <c r="BA40" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB40" t="inlineStr">
@@ -11696,7 +11696,7 @@
       </c>
       <c r="BA41" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB41" t="inlineStr">
@@ -11972,7 +11972,7 @@
       </c>
       <c r="BA42" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB42" t="inlineStr">
@@ -12248,7 +12248,7 @@
       </c>
       <c r="BA43" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB43" t="inlineStr">
@@ -12524,7 +12524,7 @@
       </c>
       <c r="BA44" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB44" t="inlineStr">
@@ -12800,7 +12800,7 @@
       </c>
       <c r="BA45" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB45" t="inlineStr">
@@ -13076,7 +13076,7 @@
       </c>
       <c r="BA46" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB46" t="inlineStr">
@@ -13614,7 +13614,7 @@
       </c>
       <c r="BA48" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB48" t="inlineStr">
@@ -14622,7 +14622,7 @@
       </c>
       <c r="BA52" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB52" t="inlineStr">
@@ -14886,7 +14886,7 @@
       </c>
       <c r="BA53" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB53" t="inlineStr">
@@ -15150,7 +15150,7 @@
       </c>
       <c r="BA54" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB54" t="inlineStr">
@@ -15414,7 +15414,7 @@
       </c>
       <c r="BA55" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB55" t="inlineStr">
@@ -15678,7 +15678,7 @@
       </c>
       <c r="BA56" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB56" t="inlineStr">
@@ -15942,7 +15942,7 @@
       </c>
       <c r="BA57" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB57" t="inlineStr">
@@ -16206,7 +16206,7 @@
       </c>
       <c r="BA58" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB58" t="inlineStr">
@@ -16470,7 +16470,7 @@
       </c>
       <c r="BA59" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB59" t="inlineStr">
@@ -16734,7 +16734,7 @@
       </c>
       <c r="BA60" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB60" t="inlineStr">
@@ -16998,7 +16998,7 @@
       </c>
       <c r="BA61" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB61" t="inlineStr">
@@ -17262,7 +17262,7 @@
       </c>
       <c r="BA62" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB62" t="inlineStr">
@@ -17526,7 +17526,7 @@
       </c>
       <c r="BA63" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB63" t="inlineStr">
@@ -17790,7 +17790,7 @@
       </c>
       <c r="BA64" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB64" t="inlineStr">
@@ -18054,7 +18054,7 @@
       </c>
       <c r="BA65" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB65" t="inlineStr">
@@ -18318,7 +18318,7 @@
       </c>
       <c r="BA66" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB66" t="inlineStr">
@@ -18582,7 +18582,7 @@
       </c>
       <c r="BA67" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB67" t="inlineStr">
@@ -18846,7 +18846,7 @@
       </c>
       <c r="BA68" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB68" t="inlineStr">
@@ -19110,7 +19110,7 @@
       </c>
       <c r="BA69" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB69" t="inlineStr">
@@ -19374,7 +19374,7 @@
       </c>
       <c r="BA70" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB70" t="inlineStr">
@@ -19638,7 +19638,7 @@
       </c>
       <c r="BA71" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB71" t="inlineStr">
@@ -19902,7 +19902,7 @@
       </c>
       <c r="BA72" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB72" t="inlineStr">
@@ -20166,7 +20166,7 @@
       </c>
       <c r="BA73" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB73" t="inlineStr">
@@ -20430,7 +20430,7 @@
       </c>
       <c r="BA74" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB74" t="inlineStr">
@@ -20694,7 +20694,7 @@
       </c>
       <c r="BA75" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB75" t="inlineStr">
@@ -20958,7 +20958,7 @@
       </c>
       <c r="BA76" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB76" t="inlineStr">
@@ -21222,7 +21222,7 @@
       </c>
       <c r="BA77" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB77" t="inlineStr">
@@ -21486,7 +21486,7 @@
       </c>
       <c r="BA78" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB78" t="inlineStr">
@@ -21750,7 +21750,7 @@
       </c>
       <c r="BA79" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB79" t="inlineStr">
@@ -21992,7 +21992,7 @@
       </c>
       <c r="BA80" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB80" t="inlineStr">
@@ -22230,7 +22230,7 @@
       </c>
       <c r="BA81" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB81" t="inlineStr">
@@ -22468,7 +22468,7 @@
       </c>
       <c r="BA82" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB82" t="inlineStr">
@@ -22706,7 +22706,7 @@
       </c>
       <c r="BA83" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB83" t="inlineStr">
@@ -22944,7 +22944,7 @@
       </c>
       <c r="BA84" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB84" t="inlineStr">
@@ -23182,7 +23182,7 @@
       </c>
       <c r="BA85" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB85" t="inlineStr">
@@ -23420,7 +23420,7 @@
       </c>
       <c r="BA86" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB86" t="inlineStr">
@@ -23658,7 +23658,7 @@
       </c>
       <c r="BA87" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB87" t="inlineStr">
@@ -23896,7 +23896,7 @@
       </c>
       <c r="BA88" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB88" t="inlineStr">
@@ -24142,7 +24142,7 @@
       </c>
       <c r="BA89" t="inlineStr">
         <is>
-          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
+          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
         </is>
       </c>
       <c r="BB89" t="inlineStr">

--- a/data/picks.xlsx
+++ b/data/picks.xlsx
@@ -4032,7 +4032,7 @@
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
@@ -4296,7 +4296,7 @@
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
@@ -5100,7 +5100,7 @@
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
@@ -5376,7 +5376,7 @@
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
@@ -5652,7 +5652,7 @@
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
@@ -5928,7 +5928,7 @@
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
@@ -6204,7 +6204,7 @@
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
@@ -6458,7 +6458,7 @@
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
@@ -7172,7 +7172,7 @@
       </c>
       <c r="BA24" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB24" t="inlineStr">
@@ -7410,7 +7410,7 @@
       </c>
       <c r="BA25" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB25" t="inlineStr">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="BA26" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB26" t="inlineStr">
@@ -7886,7 +7886,7 @@
       </c>
       <c r="BA27" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB27" t="inlineStr">
@@ -8124,7 +8124,7 @@
       </c>
       <c r="BA28" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB28" t="inlineStr">
@@ -8384,7 +8384,7 @@
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
@@ -8660,7 +8660,7 @@
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB30" t="inlineStr">
@@ -8936,7 +8936,7 @@
       </c>
       <c r="BA31" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB31" t="inlineStr">
@@ -9212,7 +9212,7 @@
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
@@ -9488,7 +9488,7 @@
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
@@ -9764,7 +9764,7 @@
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
@@ -10040,7 +10040,7 @@
       </c>
       <c r="BA35" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB35" t="inlineStr">
@@ -10316,7 +10316,7 @@
       </c>
       <c r="BA36" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB36" t="inlineStr">
@@ -10592,7 +10592,7 @@
       </c>
       <c r="BA37" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB37" t="inlineStr">
@@ -10868,7 +10868,7 @@
       </c>
       <c r="BA38" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB38" t="inlineStr">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="BA39" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB39" t="inlineStr">
@@ -11420,7 +11420,7 @@
       </c>
       <c r="BA40" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB40" t="inlineStr">
@@ -11696,7 +11696,7 @@
       </c>
       <c r="BA41" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB41" t="inlineStr">
@@ -11972,7 +11972,7 @@
       </c>
       <c r="BA42" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB42" t="inlineStr">
@@ -12248,7 +12248,7 @@
       </c>
       <c r="BA43" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB43" t="inlineStr">
@@ -12524,7 +12524,7 @@
       </c>
       <c r="BA44" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB44" t="inlineStr">
@@ -12800,7 +12800,7 @@
       </c>
       <c r="BA45" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB45" t="inlineStr">
@@ -13076,7 +13076,7 @@
       </c>
       <c r="BA46" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB46" t="inlineStr">
@@ -13614,7 +13614,7 @@
       </c>
       <c r="BA48" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB48" t="inlineStr">
@@ -14622,7 +14622,7 @@
       </c>
       <c r="BA52" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB52" t="inlineStr">
@@ -14886,7 +14886,7 @@
       </c>
       <c r="BA53" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB53" t="inlineStr">
@@ -15150,7 +15150,7 @@
       </c>
       <c r="BA54" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB54" t="inlineStr">
@@ -15414,7 +15414,7 @@
       </c>
       <c r="BA55" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB55" t="inlineStr">
@@ -15678,7 +15678,7 @@
       </c>
       <c r="BA56" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB56" t="inlineStr">
@@ -15942,7 +15942,7 @@
       </c>
       <c r="BA57" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB57" t="inlineStr">
@@ -16206,7 +16206,7 @@
       </c>
       <c r="BA58" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB58" t="inlineStr">
@@ -16470,7 +16470,7 @@
       </c>
       <c r="BA59" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB59" t="inlineStr">
@@ -16734,7 +16734,7 @@
       </c>
       <c r="BA60" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB60" t="inlineStr">
@@ -16998,7 +16998,7 @@
       </c>
       <c r="BA61" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB61" t="inlineStr">
@@ -17262,7 +17262,7 @@
       </c>
       <c r="BA62" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB62" t="inlineStr">
@@ -17526,7 +17526,7 @@
       </c>
       <c r="BA63" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB63" t="inlineStr">
@@ -17790,7 +17790,7 @@
       </c>
       <c r="BA64" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB64" t="inlineStr">
@@ -18054,7 +18054,7 @@
       </c>
       <c r="BA65" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB65" t="inlineStr">
@@ -18318,7 +18318,7 @@
       </c>
       <c r="BA66" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB66" t="inlineStr">
@@ -18582,7 +18582,7 @@
       </c>
       <c r="BA67" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB67" t="inlineStr">
@@ -18846,7 +18846,7 @@
       </c>
       <c r="BA68" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB68" t="inlineStr">
@@ -19110,7 +19110,7 @@
       </c>
       <c r="BA69" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB69" t="inlineStr">
@@ -19374,7 +19374,7 @@
       </c>
       <c r="BA70" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB70" t="inlineStr">
@@ -19638,7 +19638,7 @@
       </c>
       <c r="BA71" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB71" t="inlineStr">
@@ -19902,7 +19902,7 @@
       </c>
       <c r="BA72" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB72" t="inlineStr">
@@ -20166,7 +20166,7 @@
       </c>
       <c r="BA73" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB73" t="inlineStr">
@@ -20430,7 +20430,7 @@
       </c>
       <c r="BA74" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB74" t="inlineStr">
@@ -20694,7 +20694,7 @@
       </c>
       <c r="BA75" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB75" t="inlineStr">
@@ -20958,7 +20958,7 @@
       </c>
       <c r="BA76" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB76" t="inlineStr">
@@ -21222,7 +21222,7 @@
       </c>
       <c r="BA77" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB77" t="inlineStr">
@@ -21486,7 +21486,7 @@
       </c>
       <c r="BA78" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB78" t="inlineStr">
@@ -21750,7 +21750,7 @@
       </c>
       <c r="BA79" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB79" t="inlineStr">
@@ -21992,7 +21992,7 @@
       </c>
       <c r="BA80" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB80" t="inlineStr">
@@ -22230,7 +22230,7 @@
       </c>
       <c r="BA81" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB81" t="inlineStr">
@@ -22468,7 +22468,7 @@
       </c>
       <c r="BA82" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB82" t="inlineStr">
@@ -22706,7 +22706,7 @@
       </c>
       <c r="BA83" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB83" t="inlineStr">
@@ -22944,7 +22944,7 @@
       </c>
       <c r="BA84" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB84" t="inlineStr">
@@ -23182,7 +23182,7 @@
       </c>
       <c r="BA85" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB85" t="inlineStr">
@@ -23420,7 +23420,7 @@
       </c>
       <c r="BA86" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB86" t="inlineStr">
@@ -23658,7 +23658,7 @@
       </c>
       <c r="BA87" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB87" t="inlineStr">
@@ -23896,7 +23896,7 @@
       </c>
       <c r="BA88" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB88" t="inlineStr">
@@ -24142,7 +24142,7 @@
       </c>
       <c r="BA89" t="inlineStr">
         <is>
-          <t>5d940eaff171d6bcc6970411acaeebec40a73a586a0d518e876dd01b0efb985e</t>
+          <t>bb6331f9ae39a7346e90a5f33f6b4e07168a5805b49be25c6e6134d413c081de</t>
         </is>
       </c>
       <c r="BB89" t="inlineStr">

--- a/data/picks.xlsx
+++ b/data/picks.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CM66" headerRowCount="1">
-  <autoFilter ref="A1:CM66"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CM40" headerRowCount="1">
+  <autoFilter ref="A1:CM40"/>
   <tableColumns count="91">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -750,19 +750,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$66)</f>
+        <f>COUNTA('Picks'!$A$2:$A$40)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$66,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$40,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$66,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$40,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$66,"settled",'Picks'!$V$2:$V$66,"win")+COUNTIFS('Picks'!$U$2:$U$66,"settled",'Picks'!$V$2:$V$66,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$40,"settled",'Picks'!$V$2:$V$40,"win")+COUNTIFS('Picks'!$U$2:$U$40,"settled",'Picks'!$V$2:$V$40,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -790,19 +790,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$66,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$40,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$66,"&gt;0",'Picks'!$V$2:$V$66,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$66,"&gt;0",'Picks'!$V$2:$V$66,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$40,"&gt;0",'Picks'!$V$2:$V$40,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$40,"&gt;0",'Picks'!$V$2:$V$40,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$66,"&gt;0",'Picks'!$V$2:$V$66,"win")/(COUNTIFS('Picks'!$BX$2:$BX$66,"&gt;0",'Picks'!$V$2:$V$66,"win")+COUNTIFS('Picks'!$BX$2:$BX$66,"&gt;0",'Picks'!$V$2:$V$66,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$40,"&gt;0",'Picks'!$V$2:$V$40,"win")/(COUNTIFS('Picks'!$BX$2:$BX$40,"&gt;0",'Picks'!$V$2:$V$40,"win")+COUNTIFS('Picks'!$BX$2:$BX$40,"&gt;0",'Picks'!$V$2:$V$40,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$66)/SUM('Picks'!$BX$2:$BX$66),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$40)/SUM('Picks'!$BX$2:$BX$40),0)</f>
         <v/>
       </c>
     </row>
@@ -830,19 +830,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$66)</f>
+        <f>SUM('Picks'!$BY$2:$BY$40)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$66,"&lt;&gt;",'Picks'!$AB$2:$AB$66),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$40,"&lt;&gt;",'Picks'!$AB$2:$AB$40),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$66,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$66,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$40,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$40,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$66,'Picks'!$AM$2:$AM$66,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$40,'Picks'!$AM$2:$AM$40,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -897,15 +897,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$66,$A14,'Picks'!$U$2:$U$66,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$40,$A14,'Picks'!$U$2:$U$40,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$66,$A14,'Picks'!$U$2:$U$66,"settled",'Picks'!$V$2:$V$66,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$40,$A14,'Picks'!$U$2:$U$40,"settled",'Picks'!$V$2:$V$40,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$66,$A14,'Picks'!$U$2:$U$66,"settled",'Picks'!$V$2:$V$66,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$40,$A14,'Picks'!$U$2:$U$40,"settled",'Picks'!$V$2:$V$40,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -913,11 +913,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$66,'Picks'!$H$2:$H$66,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$40,'Picks'!$H$2:$H$40,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$66,'Picks'!$H$2:$H$66,$A14,'Picks'!$U$2:$U$66,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$40,'Picks'!$H$2:$H$40,$A14,'Picks'!$U$2:$U$40,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -928,15 +928,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$66,$A15,'Picks'!$U$2:$U$66,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$40,$A15,'Picks'!$U$2:$U$40,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$66,$A15,'Picks'!$U$2:$U$66,"settled",'Picks'!$V$2:$V$66,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$40,$A15,'Picks'!$U$2:$U$40,"settled",'Picks'!$V$2:$V$40,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$66,$A15,'Picks'!$U$2:$U$66,"settled",'Picks'!$V$2:$V$66,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$40,$A15,'Picks'!$U$2:$U$40,"settled",'Picks'!$V$2:$V$40,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -944,11 +944,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$66,'Picks'!$H$2:$H$66,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$40,'Picks'!$H$2:$H$40,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$66,'Picks'!$H$2:$H$66,$A15,'Picks'!$U$2:$U$66,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$40,'Picks'!$H$2:$H$40,$A15,'Picks'!$U$2:$U$40,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -959,15 +959,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$66,$A16,'Picks'!$U$2:$U$66,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$40,$A16,'Picks'!$U$2:$U$40,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$66,$A16,'Picks'!$U$2:$U$66,"settled",'Picks'!$V$2:$V$66,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$40,$A16,'Picks'!$U$2:$U$40,"settled",'Picks'!$V$2:$V$40,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$66,$A16,'Picks'!$U$2:$U$66,"settled",'Picks'!$V$2:$V$66,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$40,$A16,'Picks'!$U$2:$U$40,"settled",'Picks'!$V$2:$V$40,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -975,11 +975,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$66,'Picks'!$H$2:$H$66,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$40,'Picks'!$H$2:$H$40,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$66,'Picks'!$H$2:$H$66,$A16,'Picks'!$U$2:$U$66,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$40,'Picks'!$H$2:$H$40,$A16,'Picks'!$U$2:$U$40,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CM66"/>
+  <dimension ref="A1:CM40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4753,7 +4753,7 @@
       </c>
       <c r="V14" s="24" t="inlineStr">
         <is>
-          <t>win</t>
+          <t>push</t>
         </is>
       </c>
       <c r="W14" s="26" t="n">
@@ -4771,7 +4771,7 @@
       </c>
       <c r="AB14" s="28" t="n"/>
       <c r="AC14" s="30" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AD14" s="24" t="inlineStr">
         <is>
@@ -4780,7 +4780,11 @@
       </c>
       <c r="AE14" s="31" t="n"/>
       <c r="AF14" s="31" t="n"/>
-      <c r="AG14" s="24" t="n"/>
+      <c r="AG14" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
       <c r="AH14" s="24" t="n"/>
       <c r="AI14" s="31" t="n"/>
       <c r="AJ14" s="31" t="n"/>
@@ -4886,7 +4890,11 @@
       <c r="BV14" s="29" t="n">
         <v>1.04</v>
       </c>
-      <c r="BW14" s="24" t="n"/>
+      <c r="BW14" s="24" t="inlineStr">
+        <is>
+          <t>postponed</t>
+        </is>
+      </c>
       <c r="BX14" s="30" t="n"/>
       <c r="BY14" s="27" t="n"/>
       <c r="BZ14" s="24" t="n"/>
@@ -11536,6740 +11544,6 @@
       <c r="CL40" s="24" t="n"/>
       <c r="CM40" s="24" t="n"/>
     </row>
-    <row r="41" ht="36" customHeight="1">
-      <c r="A41" s="24" t="inlineStr">
-        <is>
-          <t>44151cf5c911413f</t>
-        </is>
-      </c>
-      <c r="B41" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-23T07:19:40.966816Z</t>
-        </is>
-      </c>
-      <c r="C41" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-23T09:00:00Z</t>
-        </is>
-      </c>
-      <c r="D41" s="24" t="inlineStr">
-        <is>
-          <t>56810</t>
-        </is>
-      </c>
-      <c r="E41" s="24" t="inlineStr">
-        <is>
-          <t>LOL</t>
-        </is>
-      </c>
-      <c r="F41" s="24" t="inlineStr">
-        <is>
-          <t>Anyone's Legend</t>
-        </is>
-      </c>
-      <c r="G41" s="24" t="inlineStr">
-        <is>
-          <t>JD Gaming</t>
-        </is>
-      </c>
-      <c r="H41" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I41" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J41" s="25" t="n"/>
-      <c r="K41" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L41" s="26" t="n">
-        <v>104</v>
-      </c>
-      <c r="M41" s="27" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="N41" s="28" t="n">
-        <v>0.490196</v>
-      </c>
-      <c r="O41" s="28" t="n">
-        <v>0.529047</v>
-      </c>
-      <c r="P41" s="28" t="n"/>
-      <c r="Q41" s="28" t="n">
-        <v>0.038851</v>
-      </c>
-      <c r="R41" s="26" t="n">
-        <v>39</v>
-      </c>
-      <c r="S41" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T41" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="U41" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V41" s="24" t="n"/>
-      <c r="W41" s="26" t="n"/>
-      <c r="X41" s="26" t="n"/>
-      <c r="Y41" s="25" t="n"/>
-      <c r="Z41" s="26" t="n"/>
-      <c r="AA41" s="28" t="n"/>
-      <c r="AB41" s="28" t="n"/>
-      <c r="AC41" s="30" t="n"/>
-      <c r="AD41" s="24" t="n"/>
-      <c r="AE41" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.4900 (market_slug=aec-lol-jdg-al-2026-07-23).</t>
-        </is>
-      </c>
-      <c r="AF41" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG41" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH41" s="24" t="n"/>
-      <c r="AI41" s="31" t="n"/>
-      <c r="AJ41" s="31" t="n"/>
-      <c r="AK41" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL41" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM41" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN41" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO41" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LOW_EDGE</t>
-        </is>
-      </c>
-      <c r="AP41" s="24" t="inlineStr">
-        <is>
-          <t>Anyone's Legend</t>
-        </is>
-      </c>
-      <c r="AQ41" s="24" t="inlineStr">
-        <is>
-          <t>Anyone's Legend</t>
-        </is>
-      </c>
-      <c r="AR41" s="24" t="inlineStr">
-        <is>
-          <t>Anyone's Legend</t>
-        </is>
-      </c>
-      <c r="AS41" s="24" t="inlineStr">
-        <is>
-          <t>JD Gaming</t>
-        </is>
-      </c>
-      <c r="AT41" s="24" t="inlineStr">
-        <is>
-          <t>JD Gaming</t>
-        </is>
-      </c>
-      <c r="AU41" s="24" t="inlineStr">
-        <is>
-          <t>JD Gaming</t>
-        </is>
-      </c>
-      <c r="AV41" s="24" t="n"/>
-      <c r="AW41" s="24" t="n"/>
-      <c r="AX41" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY41" s="24" t="n"/>
-      <c r="AZ41" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA41" s="24" t="inlineStr">
-        <is>
-          <t>dbc38ecdb090b63690db810d40eb29d0a69435c83dfbf24eb00d22aa42c177ae</t>
-        </is>
-      </c>
-      <c r="BB41" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC41" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="BD41" s="24" t="inlineStr">
-        <is>
-          <t>dbc38ecdb090b63690db810d40eb29d0a69435c83dfbf24eb00d22aa42c177ae</t>
-        </is>
-      </c>
-      <c r="BE41" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF41" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG41" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="BH41" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-23T07:19:09.188062Z</t>
-        </is>
-      </c>
-      <c r="BI41" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ41" s="25" t="n"/>
-      <c r="BK41" s="26" t="n">
-        <v>104</v>
-      </c>
-      <c r="BL41" s="27" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="BM41" s="28" t="n">
-        <v>0.490196</v>
-      </c>
-      <c r="BN41" s="28" t="n"/>
-      <c r="BO41" s="28" t="n"/>
-      <c r="BP41" s="25" t="n"/>
-      <c r="BQ41" s="27" t="n"/>
-      <c r="BR41" s="28" t="n"/>
-      <c r="BS41" s="28" t="n"/>
-      <c r="BT41" s="28" t="n"/>
-      <c r="BU41" s="25" t="n"/>
-      <c r="BV41" s="29" t="n"/>
-      <c r="BW41" s="24" t="n"/>
-      <c r="BX41" s="30" t="n"/>
-      <c r="BY41" s="27" t="n"/>
-      <c r="BZ41" s="24" t="n"/>
-      <c r="CA41" s="31" t="n"/>
-      <c r="CB41" s="24" t="n"/>
-      <c r="CC41" s="24" t="n"/>
-      <c r="CD41" s="24" t="n"/>
-      <c r="CE41" s="24" t="n"/>
-      <c r="CF41" s="24" t="n"/>
-      <c r="CG41" s="24" t="n"/>
-      <c r="CH41" s="24" t="n"/>
-      <c r="CI41" s="24" t="n"/>
-      <c r="CJ41" s="24" t="n"/>
-      <c r="CK41" s="24" t="n"/>
-      <c r="CL41" s="24" t="n"/>
-      <c r="CM41" s="24" t="n"/>
-    </row>
-    <row r="42" ht="36" customHeight="1">
-      <c r="A42" s="24" t="inlineStr">
-        <is>
-          <t>d6b9048395ba4f70</t>
-        </is>
-      </c>
-      <c r="B42" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-23T07:19:40.966816Z</t>
-        </is>
-      </c>
-      <c r="C42" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-23T16:00:00Z</t>
-        </is>
-      </c>
-      <c r="D42" s="24" t="inlineStr">
-        <is>
-          <t>57023</t>
-        </is>
-      </c>
-      <c r="E42" s="24" t="inlineStr">
-        <is>
-          <t>LOL</t>
-        </is>
-      </c>
-      <c r="F42" s="24" t="inlineStr">
-        <is>
-          <t>Esprit Shōnen</t>
-        </is>
-      </c>
-      <c r="G42" s="24" t="inlineStr">
-        <is>
-          <t>Skillcamp Esport</t>
-        </is>
-      </c>
-      <c r="H42" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I42" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J42" s="25" t="n"/>
-      <c r="K42" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L42" s="26" t="n">
-        <v>144</v>
-      </c>
-      <c r="M42" s="27" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="N42" s="28" t="n">
-        <v>0.409836</v>
-      </c>
-      <c r="O42" s="28" t="n">
-        <v>0.598228</v>
-      </c>
-      <c r="P42" s="28" t="n"/>
-      <c r="Q42" s="28" t="n">
-        <v>0.188392</v>
-      </c>
-      <c r="R42" s="26" t="n">
-        <v>100</v>
-      </c>
-      <c r="S42" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T42" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="U42" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V42" s="24" t="n"/>
-      <c r="W42" s="26" t="n"/>
-      <c r="X42" s="26" t="n"/>
-      <c r="Y42" s="25" t="n"/>
-      <c r="Z42" s="26" t="n"/>
-      <c r="AA42" s="28" t="n"/>
-      <c r="AB42" s="28" t="n"/>
-      <c r="AC42" s="30" t="n"/>
-      <c r="AD42" s="24" t="n"/>
-      <c r="AE42" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.4100 (market_slug=aec-lol-sc-ess-2026-07-23).</t>
-        </is>
-      </c>
-      <c r="AF42" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG42" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH42" s="24" t="n"/>
-      <c r="AI42" s="31" t="n"/>
-      <c r="AJ42" s="31" t="n"/>
-      <c r="AK42" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL42" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM42" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN42" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO42" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LARGE_DISAGREEMENT_REVIEW</t>
-        </is>
-      </c>
-      <c r="AP42" s="24" t="inlineStr">
-        <is>
-          <t>Esprit Shōnen</t>
-        </is>
-      </c>
-      <c r="AQ42" s="24" t="inlineStr">
-        <is>
-          <t>Esprit Shōnen</t>
-        </is>
-      </c>
-      <c r="AR42" s="24" t="inlineStr">
-        <is>
-          <t>Esprit Shōnen</t>
-        </is>
-      </c>
-      <c r="AS42" s="24" t="inlineStr">
-        <is>
-          <t>Skillcamp Esport</t>
-        </is>
-      </c>
-      <c r="AT42" s="24" t="inlineStr">
-        <is>
-          <t>Skillcamp Esport</t>
-        </is>
-      </c>
-      <c r="AU42" s="24" t="inlineStr">
-        <is>
-          <t>Skillcamp Esport</t>
-        </is>
-      </c>
-      <c r="AV42" s="24" t="n"/>
-      <c r="AW42" s="24" t="n"/>
-      <c r="AX42" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY42" s="24" t="n"/>
-      <c r="AZ42" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA42" s="24" t="inlineStr">
-        <is>
-          <t>dbc38ecdb090b63690db810d40eb29d0a69435c83dfbf24eb00d22aa42c177ae</t>
-        </is>
-      </c>
-      <c r="BB42" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC42" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="BD42" s="24" t="inlineStr">
-        <is>
-          <t>dbc38ecdb090b63690db810d40eb29d0a69435c83dfbf24eb00d22aa42c177ae</t>
-        </is>
-      </c>
-      <c r="BE42" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF42" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG42" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="BH42" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-23T07:19:11.879111Z</t>
-        </is>
-      </c>
-      <c r="BI42" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ42" s="25" t="n"/>
-      <c r="BK42" s="26" t="n">
-        <v>144</v>
-      </c>
-      <c r="BL42" s="27" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BM42" s="28" t="n">
-        <v>0.409836</v>
-      </c>
-      <c r="BN42" s="28" t="n"/>
-      <c r="BO42" s="28" t="n"/>
-      <c r="BP42" s="25" t="n"/>
-      <c r="BQ42" s="27" t="n"/>
-      <c r="BR42" s="28" t="n"/>
-      <c r="BS42" s="28" t="n"/>
-      <c r="BT42" s="28" t="n"/>
-      <c r="BU42" s="25" t="n"/>
-      <c r="BV42" s="29" t="n"/>
-      <c r="BW42" s="24" t="n"/>
-      <c r="BX42" s="30" t="n"/>
-      <c r="BY42" s="27" t="n"/>
-      <c r="BZ42" s="24" t="n"/>
-      <c r="CA42" s="31" t="n"/>
-      <c r="CB42" s="24" t="n"/>
-      <c r="CC42" s="24" t="n"/>
-      <c r="CD42" s="24" t="n"/>
-      <c r="CE42" s="24" t="n"/>
-      <c r="CF42" s="24" t="n"/>
-      <c r="CG42" s="24" t="n"/>
-      <c r="CH42" s="24" t="n"/>
-      <c r="CI42" s="24" t="n"/>
-      <c r="CJ42" s="24" t="n"/>
-      <c r="CK42" s="24" t="n"/>
-      <c r="CL42" s="24" t="n"/>
-      <c r="CM42" s="24" t="n"/>
-    </row>
-    <row r="43" ht="36" customHeight="1">
-      <c r="A43" s="24" t="inlineStr">
-        <is>
-          <t>1d45f066aa5e4ee0</t>
-        </is>
-      </c>
-      <c r="B43" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-23T07:19:40.966816Z</t>
-        </is>
-      </c>
-      <c r="C43" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-23T17:00:00Z</t>
-        </is>
-      </c>
-      <c r="D43" s="24" t="inlineStr">
-        <is>
-          <t>57086</t>
-        </is>
-      </c>
-      <c r="E43" s="24" t="inlineStr">
-        <is>
-          <t>LOL</t>
-        </is>
-      </c>
-      <c r="F43" s="24" t="inlineStr">
-        <is>
-          <t>Ici Japon Corp. Esport</t>
-        </is>
-      </c>
-      <c r="G43" s="24" t="inlineStr">
-        <is>
-          <t>Joblife</t>
-        </is>
-      </c>
-      <c r="H43" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I43" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J43" s="25" t="n"/>
-      <c r="K43" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L43" s="26" t="n">
-        <v>186</v>
-      </c>
-      <c r="M43" s="27" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="N43" s="28" t="n">
-        <v>0.34965</v>
-      </c>
-      <c r="O43" s="28" t="n">
-        <v>0.549847</v>
-      </c>
-      <c r="P43" s="28" t="n"/>
-      <c r="Q43" s="28" t="n">
-        <v>0.200197</v>
-      </c>
-      <c r="R43" s="26" t="n">
-        <v>100</v>
-      </c>
-      <c r="S43" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T43" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="U43" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V43" s="24" t="n"/>
-      <c r="W43" s="26" t="n"/>
-      <c r="X43" s="26" t="n"/>
-      <c r="Y43" s="25" t="n"/>
-      <c r="Z43" s="26" t="n"/>
-      <c r="AA43" s="28" t="n"/>
-      <c r="AB43" s="28" t="n"/>
-      <c r="AC43" s="30" t="n"/>
-      <c r="AD43" s="24" t="n"/>
-      <c r="AE43" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.3500 (market_slug=aec-lol-jl-ijc-2026-07-23).</t>
-        </is>
-      </c>
-      <c r="AF43" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG43" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH43" s="24" t="n"/>
-      <c r="AI43" s="31" t="n"/>
-      <c r="AJ43" s="31" t="n"/>
-      <c r="AK43" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL43" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM43" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN43" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO43" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LARGE_DISAGREEMENT_REVIEW</t>
-        </is>
-      </c>
-      <c r="AP43" s="24" t="inlineStr">
-        <is>
-          <t>Ici Japon Corp. Esport</t>
-        </is>
-      </c>
-      <c r="AQ43" s="24" t="inlineStr">
-        <is>
-          <t>Ici Japon Corp. Esport</t>
-        </is>
-      </c>
-      <c r="AR43" s="24" t="inlineStr">
-        <is>
-          <t>Ici Japon Corp. Esport</t>
-        </is>
-      </c>
-      <c r="AS43" s="24" t="inlineStr">
-        <is>
-          <t>Joblife</t>
-        </is>
-      </c>
-      <c r="AT43" s="24" t="inlineStr">
-        <is>
-          <t>Joblife</t>
-        </is>
-      </c>
-      <c r="AU43" s="24" t="inlineStr">
-        <is>
-          <t>Joblife</t>
-        </is>
-      </c>
-      <c r="AV43" s="24" t="n"/>
-      <c r="AW43" s="24" t="n"/>
-      <c r="AX43" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY43" s="24" t="n"/>
-      <c r="AZ43" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA43" s="24" t="inlineStr">
-        <is>
-          <t>dbc38ecdb090b63690db810d40eb29d0a69435c83dfbf24eb00d22aa42c177ae</t>
-        </is>
-      </c>
-      <c r="BB43" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC43" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="BD43" s="24" t="inlineStr">
-        <is>
-          <t>dbc38ecdb090b63690db810d40eb29d0a69435c83dfbf24eb00d22aa42c177ae</t>
-        </is>
-      </c>
-      <c r="BE43" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF43" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG43" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="BH43" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-23T07:19:15.348357Z</t>
-        </is>
-      </c>
-      <c r="BI43" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ43" s="25" t="n"/>
-      <c r="BK43" s="26" t="n">
-        <v>186</v>
-      </c>
-      <c r="BL43" s="27" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="BM43" s="28" t="n">
-        <v>0.34965</v>
-      </c>
-      <c r="BN43" s="28" t="n"/>
-      <c r="BO43" s="28" t="n"/>
-      <c r="BP43" s="25" t="n"/>
-      <c r="BQ43" s="27" t="n"/>
-      <c r="BR43" s="28" t="n"/>
-      <c r="BS43" s="28" t="n"/>
-      <c r="BT43" s="28" t="n"/>
-      <c r="BU43" s="25" t="n"/>
-      <c r="BV43" s="29" t="n"/>
-      <c r="BW43" s="24" t="n"/>
-      <c r="BX43" s="30" t="n"/>
-      <c r="BY43" s="27" t="n"/>
-      <c r="BZ43" s="24" t="n"/>
-      <c r="CA43" s="31" t="n"/>
-      <c r="CB43" s="24" t="n"/>
-      <c r="CC43" s="24" t="n"/>
-      <c r="CD43" s="24" t="n"/>
-      <c r="CE43" s="24" t="n"/>
-      <c r="CF43" s="24" t="n"/>
-      <c r="CG43" s="24" t="n"/>
-      <c r="CH43" s="24" t="n"/>
-      <c r="CI43" s="24" t="n"/>
-      <c r="CJ43" s="24" t="n"/>
-      <c r="CK43" s="24" t="n"/>
-      <c r="CL43" s="24" t="n"/>
-      <c r="CM43" s="24" t="n"/>
-    </row>
-    <row r="44" ht="36" customHeight="1">
-      <c r="A44" s="24" t="inlineStr">
-        <is>
-          <t>9775e1763adf4911</t>
-        </is>
-      </c>
-      <c r="B44" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-23T07:19:40.966816Z</t>
-        </is>
-      </c>
-      <c r="C44" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-23T17:00:00Z</t>
-        </is>
-      </c>
-      <c r="D44" s="24" t="inlineStr">
-        <is>
-          <t>57088</t>
-        </is>
-      </c>
-      <c r="E44" s="24" t="inlineStr">
-        <is>
-          <t>LOL</t>
-        </is>
-      </c>
-      <c r="F44" s="24" t="inlineStr">
-        <is>
-          <t>Dynasty</t>
-        </is>
-      </c>
-      <c r="G44" s="24" t="inlineStr">
-        <is>
-          <t>Myth Esports</t>
-        </is>
-      </c>
-      <c r="H44" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I44" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J44" s="25" t="n"/>
-      <c r="K44" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L44" s="26" t="n">
-        <v>203</v>
-      </c>
-      <c r="M44" s="27" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="N44" s="28" t="n">
-        <v>0.330033</v>
-      </c>
-      <c r="O44" s="28" t="n">
-        <v>0.501096</v>
-      </c>
-      <c r="P44" s="28" t="n"/>
-      <c r="Q44" s="28" t="n">
-        <v>0.171063</v>
-      </c>
-      <c r="R44" s="26" t="n">
-        <v>100</v>
-      </c>
-      <c r="S44" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T44" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="U44" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V44" s="24" t="n"/>
-      <c r="W44" s="26" t="n"/>
-      <c r="X44" s="26" t="n"/>
-      <c r="Y44" s="25" t="n"/>
-      <c r="Z44" s="26" t="n"/>
-      <c r="AA44" s="28" t="n"/>
-      <c r="AB44" s="28" t="n"/>
-      <c r="AC44" s="30" t="n"/>
-      <c r="AD44" s="24" t="n"/>
-      <c r="AE44" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.3300 (market_slug=aec-lol-myth-dyn-2026-07-23).</t>
-        </is>
-      </c>
-      <c r="AF44" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG44" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH44" s="24" t="n"/>
-      <c r="AI44" s="31" t="n"/>
-      <c r="AJ44" s="31" t="n"/>
-      <c r="AK44" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL44" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM44" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN44" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO44" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LARGE_DISAGREEMENT_REVIEW</t>
-        </is>
-      </c>
-      <c r="AP44" s="24" t="inlineStr">
-        <is>
-          <t>Dynasty</t>
-        </is>
-      </c>
-      <c r="AQ44" s="24" t="inlineStr">
-        <is>
-          <t>Dynasty</t>
-        </is>
-      </c>
-      <c r="AR44" s="24" t="inlineStr">
-        <is>
-          <t>Dynasty</t>
-        </is>
-      </c>
-      <c r="AS44" s="24" t="inlineStr">
-        <is>
-          <t>Myth Esports</t>
-        </is>
-      </c>
-      <c r="AT44" s="24" t="inlineStr">
-        <is>
-          <t>Myth Esports</t>
-        </is>
-      </c>
-      <c r="AU44" s="24" t="inlineStr">
-        <is>
-          <t>Myth Esports</t>
-        </is>
-      </c>
-      <c r="AV44" s="24" t="n"/>
-      <c r="AW44" s="24" t="n"/>
-      <c r="AX44" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY44" s="24" t="n"/>
-      <c r="AZ44" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA44" s="24" t="inlineStr">
-        <is>
-          <t>dbc38ecdb090b63690db810d40eb29d0a69435c83dfbf24eb00d22aa42c177ae</t>
-        </is>
-      </c>
-      <c r="BB44" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC44" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="BD44" s="24" t="inlineStr">
-        <is>
-          <t>dbc38ecdb090b63690db810d40eb29d0a69435c83dfbf24eb00d22aa42c177ae</t>
-        </is>
-      </c>
-      <c r="BE44" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF44" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG44" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="BH44" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-23T07:19:17.018506Z</t>
-        </is>
-      </c>
-      <c r="BI44" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ44" s="25" t="n"/>
-      <c r="BK44" s="26" t="n">
-        <v>203</v>
-      </c>
-      <c r="BL44" s="27" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="BM44" s="28" t="n">
-        <v>0.330033</v>
-      </c>
-      <c r="BN44" s="28" t="n"/>
-      <c r="BO44" s="28" t="n"/>
-      <c r="BP44" s="25" t="n"/>
-      <c r="BQ44" s="27" t="n"/>
-      <c r="BR44" s="28" t="n"/>
-      <c r="BS44" s="28" t="n"/>
-      <c r="BT44" s="28" t="n"/>
-      <c r="BU44" s="25" t="n"/>
-      <c r="BV44" s="29" t="n"/>
-      <c r="BW44" s="24" t="n"/>
-      <c r="BX44" s="30" t="n"/>
-      <c r="BY44" s="27" t="n"/>
-      <c r="BZ44" s="24" t="n"/>
-      <c r="CA44" s="31" t="n"/>
-      <c r="CB44" s="24" t="n"/>
-      <c r="CC44" s="24" t="n"/>
-      <c r="CD44" s="24" t="n"/>
-      <c r="CE44" s="24" t="n"/>
-      <c r="CF44" s="24" t="n"/>
-      <c r="CG44" s="24" t="n"/>
-      <c r="CH44" s="24" t="n"/>
-      <c r="CI44" s="24" t="n"/>
-      <c r="CJ44" s="24" t="n"/>
-      <c r="CK44" s="24" t="n"/>
-      <c r="CL44" s="24" t="n"/>
-      <c r="CM44" s="24" t="n"/>
-    </row>
-    <row r="45" ht="36" customHeight="1">
-      <c r="A45" s="24" t="inlineStr">
-        <is>
-          <t>4abf5cf067fa41ac</t>
-        </is>
-      </c>
-      <c r="B45" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-23T07:20:39.530092Z</t>
-        </is>
-      </c>
-      <c r="C45" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-23T08:00:00Z</t>
-        </is>
-      </c>
-      <c r="D45" s="24" t="inlineStr">
-        <is>
-          <t>59672</t>
-        </is>
-      </c>
-      <c r="E45" s="24" t="inlineStr">
-        <is>
-          <t>CS2</t>
-        </is>
-      </c>
-      <c r="F45" s="24" t="inlineStr">
-        <is>
-          <t>Entropy</t>
-        </is>
-      </c>
-      <c r="G45" s="24" t="inlineStr">
-        <is>
-          <t>Rune Eaters</t>
-        </is>
-      </c>
-      <c r="H45" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I45" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J45" s="25" t="n"/>
-      <c r="K45" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L45" s="26" t="n">
-        <v>117</v>
-      </c>
-      <c r="M45" s="27" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="N45" s="28" t="n">
-        <v>0.460829</v>
-      </c>
-      <c r="O45" s="28" t="n">
-        <v>0.517948</v>
-      </c>
-      <c r="P45" s="28" t="n"/>
-      <c r="Q45" s="28" t="n">
-        <v>0.057119</v>
-      </c>
-      <c r="R45" s="26" t="n">
-        <v>49</v>
-      </c>
-      <c r="S45" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T45" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="U45" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V45" s="24" t="n"/>
-      <c r="W45" s="26" t="n"/>
-      <c r="X45" s="26" t="n"/>
-      <c r="Y45" s="25" t="n"/>
-      <c r="Z45" s="26" t="n"/>
-      <c r="AA45" s="28" t="n"/>
-      <c r="AB45" s="28" t="n"/>
-      <c r="AC45" s="30" t="n"/>
-      <c r="AD45" s="24" t="n"/>
-      <c r="AE45" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.4600 (market_slug=aec-cs2-re-ent-2026-07-23).</t>
-        </is>
-      </c>
-      <c r="AF45" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG45" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH45" s="24" t="n"/>
-      <c r="AI45" s="31" t="n"/>
-      <c r="AJ45" s="31" t="n"/>
-      <c r="AK45" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL45" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM45" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN45" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO45" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LOW_EDGE</t>
-        </is>
-      </c>
-      <c r="AP45" s="24" t="inlineStr">
-        <is>
-          <t>Entropy</t>
-        </is>
-      </c>
-      <c r="AQ45" s="24" t="inlineStr">
-        <is>
-          <t>Entropy</t>
-        </is>
-      </c>
-      <c r="AR45" s="24" t="inlineStr">
-        <is>
-          <t>Entropy</t>
-        </is>
-      </c>
-      <c r="AS45" s="24" t="inlineStr">
-        <is>
-          <t>Rune Eaters</t>
-        </is>
-      </c>
-      <c r="AT45" s="24" t="inlineStr">
-        <is>
-          <t>Rune Eaters</t>
-        </is>
-      </c>
-      <c r="AU45" s="24" t="inlineStr">
-        <is>
-          <t>Rune Eaters</t>
-        </is>
-      </c>
-      <c r="AV45" s="24" t="n"/>
-      <c r="AW45" s="24" t="n"/>
-      <c r="AX45" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY45" s="24" t="n"/>
-      <c r="AZ45" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA45" s="24" t="inlineStr">
-        <is>
-          <t>48424b79d75fc1173c9c465d95feb6fc041a2ccfbc64455058b3f74905ce28d5</t>
-        </is>
-      </c>
-      <c r="BB45" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC45" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="BD45" s="24" t="inlineStr">
-        <is>
-          <t>48424b79d75fc1173c9c465d95feb6fc041a2ccfbc64455058b3f74905ce28d5</t>
-        </is>
-      </c>
-      <c r="BE45" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF45" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG45" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="BH45" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-23T07:19:53.300087Z</t>
-        </is>
-      </c>
-      <c r="BI45" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ45" s="25" t="n"/>
-      <c r="BK45" s="26" t="n">
-        <v>117</v>
-      </c>
-      <c r="BL45" s="27" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="BM45" s="28" t="n">
-        <v>0.460829</v>
-      </c>
-      <c r="BN45" s="28" t="n"/>
-      <c r="BO45" s="28" t="n"/>
-      <c r="BP45" s="25" t="n"/>
-      <c r="BQ45" s="27" t="n"/>
-      <c r="BR45" s="28" t="n"/>
-      <c r="BS45" s="28" t="n"/>
-      <c r="BT45" s="28" t="n"/>
-      <c r="BU45" s="25" t="n"/>
-      <c r="BV45" s="29" t="n"/>
-      <c r="BW45" s="24" t="n"/>
-      <c r="BX45" s="30" t="n"/>
-      <c r="BY45" s="27" t="n"/>
-      <c r="BZ45" s="24" t="n"/>
-      <c r="CA45" s="31" t="n"/>
-      <c r="CB45" s="24" t="n"/>
-      <c r="CC45" s="24" t="n"/>
-      <c r="CD45" s="24" t="n"/>
-      <c r="CE45" s="24" t="n"/>
-      <c r="CF45" s="24" t="n"/>
-      <c r="CG45" s="24" t="n"/>
-      <c r="CH45" s="24" t="n"/>
-      <c r="CI45" s="24" t="n"/>
-      <c r="CJ45" s="24" t="n"/>
-      <c r="CK45" s="24" t="n"/>
-      <c r="CL45" s="24" t="n"/>
-      <c r="CM45" s="24" t="n"/>
-    </row>
-    <row r="46" ht="36" customHeight="1">
-      <c r="A46" s="24" t="inlineStr">
-        <is>
-          <t>c06a28256d0a4a72</t>
-        </is>
-      </c>
-      <c r="B46" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-23T07:20:39.530092Z</t>
-        </is>
-      </c>
-      <c r="C46" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-23T11:00:00Z</t>
-        </is>
-      </c>
-      <c r="D46" s="24" t="inlineStr">
-        <is>
-          <t>56870</t>
-        </is>
-      </c>
-      <c r="E46" s="24" t="inlineStr">
-        <is>
-          <t>CS2</t>
-        </is>
-      </c>
-      <c r="F46" s="24" t="inlineStr">
-        <is>
-          <t>Benched gods</t>
-        </is>
-      </c>
-      <c r="G46" s="24" t="inlineStr">
-        <is>
-          <t>NEW VISION</t>
-        </is>
-      </c>
-      <c r="H46" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I46" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J46" s="25" t="n"/>
-      <c r="K46" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L46" s="26" t="n">
-        <v>-122</v>
-      </c>
-      <c r="M46" s="27" t="n">
-        <v>1.819672</v>
-      </c>
-      <c r="N46" s="28" t="n">
-        <v>0.54955</v>
-      </c>
-      <c r="O46" s="28" t="n">
-        <v>0.682691</v>
-      </c>
-      <c r="P46" s="28" t="n"/>
-      <c r="Q46" s="28" t="n">
-        <v>0.133141</v>
-      </c>
-      <c r="R46" s="26" t="n">
-        <v>100</v>
-      </c>
-      <c r="S46" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T46" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="U46" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V46" s="24" t="n"/>
-      <c r="W46" s="26" t="n"/>
-      <c r="X46" s="26" t="n"/>
-      <c r="Y46" s="25" t="n"/>
-      <c r="Z46" s="26" t="n"/>
-      <c r="AA46" s="28" t="n"/>
-      <c r="AB46" s="28" t="n"/>
-      <c r="AC46" s="30" t="n"/>
-      <c r="AD46" s="24" t="n"/>
-      <c r="AE46" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.5500 (market_slug=aec-cs2-nve-bge-2026-07-23).</t>
-        </is>
-      </c>
-      <c r="AF46" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG46" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH46" s="24" t="n"/>
-      <c r="AI46" s="31" t="n"/>
-      <c r="AJ46" s="31" t="n"/>
-      <c r="AK46" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL46" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM46" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN46" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO46" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LARGE_DISAGREEMENT_REVIEW</t>
-        </is>
-      </c>
-      <c r="AP46" s="24" t="inlineStr">
-        <is>
-          <t>Benched gods</t>
-        </is>
-      </c>
-      <c r="AQ46" s="24" t="inlineStr">
-        <is>
-          <t>Benched gods</t>
-        </is>
-      </c>
-      <c r="AR46" s="24" t="inlineStr">
-        <is>
-          <t>Benched gods</t>
-        </is>
-      </c>
-      <c r="AS46" s="24" t="inlineStr">
-        <is>
-          <t>NEW VISION</t>
-        </is>
-      </c>
-      <c r="AT46" s="24" t="inlineStr">
-        <is>
-          <t>NEW VISION</t>
-        </is>
-      </c>
-      <c r="AU46" s="24" t="inlineStr">
-        <is>
-          <t>NEW VISION</t>
-        </is>
-      </c>
-      <c r="AV46" s="24" t="n"/>
-      <c r="AW46" s="24" t="n"/>
-      <c r="AX46" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY46" s="24" t="n"/>
-      <c r="AZ46" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA46" s="24" t="inlineStr">
-        <is>
-          <t>48424b79d75fc1173c9c465d95feb6fc041a2ccfbc64455058b3f74905ce28d5</t>
-        </is>
-      </c>
-      <c r="BB46" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC46" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="BD46" s="24" t="inlineStr">
-        <is>
-          <t>48424b79d75fc1173c9c465d95feb6fc041a2ccfbc64455058b3f74905ce28d5</t>
-        </is>
-      </c>
-      <c r="BE46" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF46" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG46" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="BH46" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-23T07:19:56.117565Z</t>
-        </is>
-      </c>
-      <c r="BI46" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ46" s="25" t="n"/>
-      <c r="BK46" s="26" t="n">
-        <v>-122</v>
-      </c>
-      <c r="BL46" s="27" t="n">
-        <v>1.819672</v>
-      </c>
-      <c r="BM46" s="28" t="n">
-        <v>0.54955</v>
-      </c>
-      <c r="BN46" s="28" t="n"/>
-      <c r="BO46" s="28" t="n"/>
-      <c r="BP46" s="25" t="n"/>
-      <c r="BQ46" s="27" t="n"/>
-      <c r="BR46" s="28" t="n"/>
-      <c r="BS46" s="28" t="n"/>
-      <c r="BT46" s="28" t="n"/>
-      <c r="BU46" s="25" t="n"/>
-      <c r="BV46" s="29" t="n"/>
-      <c r="BW46" s="24" t="n"/>
-      <c r="BX46" s="30" t="n"/>
-      <c r="BY46" s="27" t="n"/>
-      <c r="BZ46" s="24" t="n"/>
-      <c r="CA46" s="31" t="n"/>
-      <c r="CB46" s="24" t="n"/>
-      <c r="CC46" s="24" t="n"/>
-      <c r="CD46" s="24" t="n"/>
-      <c r="CE46" s="24" t="n"/>
-      <c r="CF46" s="24" t="n"/>
-      <c r="CG46" s="24" t="n"/>
-      <c r="CH46" s="24" t="n"/>
-      <c r="CI46" s="24" t="n"/>
-      <c r="CJ46" s="24" t="n"/>
-      <c r="CK46" s="24" t="n"/>
-      <c r="CL46" s="24" t="n"/>
-      <c r="CM46" s="24" t="n"/>
-    </row>
-    <row r="47" ht="36" customHeight="1">
-      <c r="A47" s="24" t="inlineStr">
-        <is>
-          <t>48b186b9b9b44f05</t>
-        </is>
-      </c>
-      <c r="B47" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-23T07:20:39.530092Z</t>
-        </is>
-      </c>
-      <c r="C47" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-23T11:00:00Z</t>
-        </is>
-      </c>
-      <c r="D47" s="24" t="inlineStr">
-        <is>
-          <t>59036</t>
-        </is>
-      </c>
-      <c r="E47" s="24" t="inlineStr">
-        <is>
-          <t>CS2</t>
-        </is>
-      </c>
-      <c r="F47" s="24" t="inlineStr">
-        <is>
-          <t>ex-RUSTEC</t>
-        </is>
-      </c>
-      <c r="G47" s="24" t="inlineStr">
-        <is>
-          <t>Lavked</t>
-        </is>
-      </c>
-      <c r="H47" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I47" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J47" s="25" t="n"/>
-      <c r="K47" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L47" s="26" t="n">
-        <v>113</v>
-      </c>
-      <c r="M47" s="27" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="N47" s="28" t="n">
-        <v>0.469484</v>
-      </c>
-      <c r="O47" s="28" t="n">
-        <v>0.692685</v>
-      </c>
-      <c r="P47" s="28" t="n"/>
-      <c r="Q47" s="28" t="n">
-        <v>0.223201</v>
-      </c>
-      <c r="R47" s="26" t="n">
-        <v>100</v>
-      </c>
-      <c r="S47" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T47" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="U47" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V47" s="24" t="n"/>
-      <c r="W47" s="26" t="n"/>
-      <c r="X47" s="26" t="n"/>
-      <c r="Y47" s="25" t="n"/>
-      <c r="Z47" s="26" t="n"/>
-      <c r="AA47" s="28" t="n"/>
-      <c r="AB47" s="28" t="n"/>
-      <c r="AC47" s="30" t="n"/>
-      <c r="AD47" s="24" t="n"/>
-      <c r="AE47" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.4700 (market_slug=aec-cs2-lav-erx-2026-07-23).</t>
-        </is>
-      </c>
-      <c r="AF47" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG47" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH47" s="24" t="n"/>
-      <c r="AI47" s="31" t="n"/>
-      <c r="AJ47" s="31" t="n"/>
-      <c r="AK47" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL47" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM47" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN47" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO47" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LARGE_DISAGREEMENT_REVIEW</t>
-        </is>
-      </c>
-      <c r="AP47" s="24" t="inlineStr">
-        <is>
-          <t>ex-RUSTEC</t>
-        </is>
-      </c>
-      <c r="AQ47" s="24" t="inlineStr">
-        <is>
-          <t>ex-RUSTEC</t>
-        </is>
-      </c>
-      <c r="AR47" s="24" t="inlineStr">
-        <is>
-          <t>ex-RUSTEC</t>
-        </is>
-      </c>
-      <c r="AS47" s="24" t="inlineStr">
-        <is>
-          <t>Lavked</t>
-        </is>
-      </c>
-      <c r="AT47" s="24" t="inlineStr">
-        <is>
-          <t>Lavked</t>
-        </is>
-      </c>
-      <c r="AU47" s="24" t="inlineStr">
-        <is>
-          <t>Lavked</t>
-        </is>
-      </c>
-      <c r="AV47" s="24" t="n"/>
-      <c r="AW47" s="24" t="n"/>
-      <c r="AX47" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY47" s="24" t="n"/>
-      <c r="AZ47" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA47" s="24" t="inlineStr">
-        <is>
-          <t>48424b79d75fc1173c9c465d95feb6fc041a2ccfbc64455058b3f74905ce28d5</t>
-        </is>
-      </c>
-      <c r="BB47" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC47" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="BD47" s="24" t="inlineStr">
-        <is>
-          <t>48424b79d75fc1173c9c465d95feb6fc041a2ccfbc64455058b3f74905ce28d5</t>
-        </is>
-      </c>
-      <c r="BE47" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF47" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG47" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="BH47" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-23T07:19:56.934670Z</t>
-        </is>
-      </c>
-      <c r="BI47" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ47" s="25" t="n"/>
-      <c r="BK47" s="26" t="n">
-        <v>113</v>
-      </c>
-      <c r="BL47" s="27" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="BM47" s="28" t="n">
-        <v>0.469484</v>
-      </c>
-      <c r="BN47" s="28" t="n"/>
-      <c r="BO47" s="28" t="n"/>
-      <c r="BP47" s="25" t="n"/>
-      <c r="BQ47" s="27" t="n"/>
-      <c r="BR47" s="28" t="n"/>
-      <c r="BS47" s="28" t="n"/>
-      <c r="BT47" s="28" t="n"/>
-      <c r="BU47" s="25" t="n"/>
-      <c r="BV47" s="29" t="n"/>
-      <c r="BW47" s="24" t="n"/>
-      <c r="BX47" s="30" t="n"/>
-      <c r="BY47" s="27" t="n"/>
-      <c r="BZ47" s="24" t="n"/>
-      <c r="CA47" s="31" t="n"/>
-      <c r="CB47" s="24" t="n"/>
-      <c r="CC47" s="24" t="n"/>
-      <c r="CD47" s="24" t="n"/>
-      <c r="CE47" s="24" t="n"/>
-      <c r="CF47" s="24" t="n"/>
-      <c r="CG47" s="24" t="n"/>
-      <c r="CH47" s="24" t="n"/>
-      <c r="CI47" s="24" t="n"/>
-      <c r="CJ47" s="24" t="n"/>
-      <c r="CK47" s="24" t="n"/>
-      <c r="CL47" s="24" t="n"/>
-      <c r="CM47" s="24" t="n"/>
-    </row>
-    <row r="48" ht="36" customHeight="1">
-      <c r="A48" s="24" t="inlineStr">
-        <is>
-          <t>450565bf55b1476b</t>
-        </is>
-      </c>
-      <c r="B48" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-23T07:20:39.530092Z</t>
-        </is>
-      </c>
-      <c r="C48" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-23T13:00:00Z</t>
-        </is>
-      </c>
-      <c r="D48" s="24" t="inlineStr">
-        <is>
-          <t>59442</t>
-        </is>
-      </c>
-      <c r="E48" s="24" t="inlineStr">
-        <is>
-          <t>CS2</t>
-        </is>
-      </c>
-      <c r="F48" s="24" t="inlineStr">
-        <is>
-          <t>Nuclear TigeRES</t>
-        </is>
-      </c>
-      <c r="G48" s="24" t="inlineStr">
-        <is>
-          <t>100 Thieves</t>
-        </is>
-      </c>
-      <c r="H48" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I48" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J48" s="25" t="n"/>
-      <c r="K48" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L48" s="26" t="n">
-        <v>150</v>
-      </c>
-      <c r="M48" s="27" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N48" s="28" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="O48" s="28" t="n">
-        <v>0.5681389999999999</v>
-      </c>
-      <c r="P48" s="28" t="n"/>
-      <c r="Q48" s="28" t="n">
-        <v>0.168139</v>
-      </c>
-      <c r="R48" s="26" t="n">
-        <v>100</v>
-      </c>
-      <c r="S48" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T48" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="U48" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V48" s="24" t="n"/>
-      <c r="W48" s="26" t="n"/>
-      <c r="X48" s="26" t="n"/>
-      <c r="Y48" s="25" t="n"/>
-      <c r="Z48" s="26" t="n"/>
-      <c r="AA48" s="28" t="n"/>
-      <c r="AB48" s="28" t="n"/>
-      <c r="AC48" s="30" t="n"/>
-      <c r="AD48" s="24" t="n"/>
-      <c r="AE48" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.4000 (market_slug=aec-cs2-100t-ntr-2026-07-23).</t>
-        </is>
-      </c>
-      <c r="AF48" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG48" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH48" s="24" t="n"/>
-      <c r="AI48" s="31" t="n"/>
-      <c r="AJ48" s="31" t="n"/>
-      <c r="AK48" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL48" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM48" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN48" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO48" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LARGE_DISAGREEMENT_REVIEW</t>
-        </is>
-      </c>
-      <c r="AP48" s="24" t="inlineStr">
-        <is>
-          <t>Nuclear TigeRES</t>
-        </is>
-      </c>
-      <c r="AQ48" s="24" t="inlineStr">
-        <is>
-          <t>Nuclear TigeRES</t>
-        </is>
-      </c>
-      <c r="AR48" s="24" t="inlineStr">
-        <is>
-          <t>Nuclear TigeRES</t>
-        </is>
-      </c>
-      <c r="AS48" s="24" t="inlineStr">
-        <is>
-          <t>100 Thieves</t>
-        </is>
-      </c>
-      <c r="AT48" s="24" t="inlineStr">
-        <is>
-          <t>100 Thieves</t>
-        </is>
-      </c>
-      <c r="AU48" s="24" t="inlineStr">
-        <is>
-          <t>100 Thieves</t>
-        </is>
-      </c>
-      <c r="AV48" s="24" t="n"/>
-      <c r="AW48" s="24" t="n"/>
-      <c r="AX48" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY48" s="24" t="n"/>
-      <c r="AZ48" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA48" s="24" t="inlineStr">
-        <is>
-          <t>48424b79d75fc1173c9c465d95feb6fc041a2ccfbc64455058b3f74905ce28d5</t>
-        </is>
-      </c>
-      <c r="BB48" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC48" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="BD48" s="24" t="inlineStr">
-        <is>
-          <t>48424b79d75fc1173c9c465d95feb6fc041a2ccfbc64455058b3f74905ce28d5</t>
-        </is>
-      </c>
-      <c r="BE48" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF48" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG48" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="BH48" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-23T07:20:01.184225Z</t>
-        </is>
-      </c>
-      <c r="BI48" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ48" s="25" t="n"/>
-      <c r="BK48" s="26" t="n">
-        <v>150</v>
-      </c>
-      <c r="BL48" s="27" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BM48" s="28" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="BN48" s="28" t="n"/>
-      <c r="BO48" s="28" t="n"/>
-      <c r="BP48" s="25" t="n"/>
-      <c r="BQ48" s="27" t="n"/>
-      <c r="BR48" s="28" t="n"/>
-      <c r="BS48" s="28" t="n"/>
-      <c r="BT48" s="28" t="n"/>
-      <c r="BU48" s="25" t="n"/>
-      <c r="BV48" s="29" t="n"/>
-      <c r="BW48" s="24" t="n"/>
-      <c r="BX48" s="30" t="n"/>
-      <c r="BY48" s="27" t="n"/>
-      <c r="BZ48" s="24" t="n"/>
-      <c r="CA48" s="31" t="n"/>
-      <c r="CB48" s="24" t="n"/>
-      <c r="CC48" s="24" t="n"/>
-      <c r="CD48" s="24" t="n"/>
-      <c r="CE48" s="24" t="n"/>
-      <c r="CF48" s="24" t="n"/>
-      <c r="CG48" s="24" t="n"/>
-      <c r="CH48" s="24" t="n"/>
-      <c r="CI48" s="24" t="n"/>
-      <c r="CJ48" s="24" t="n"/>
-      <c r="CK48" s="24" t="n"/>
-      <c r="CL48" s="24" t="n"/>
-      <c r="CM48" s="24" t="n"/>
-    </row>
-    <row r="49" ht="36" customHeight="1">
-      <c r="A49" s="24" t="inlineStr">
-        <is>
-          <t>61731992c1874734</t>
-        </is>
-      </c>
-      <c r="B49" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-23T07:20:39.530092Z</t>
-        </is>
-      </c>
-      <c r="C49" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-23T14:00:00Z</t>
-        </is>
-      </c>
-      <c r="D49" s="24" t="inlineStr">
-        <is>
-          <t>59038</t>
-        </is>
-      </c>
-      <c r="E49" s="24" t="inlineStr">
-        <is>
-          <t>CS2</t>
-        </is>
-      </c>
-      <c r="F49" s="24" t="inlineStr">
-        <is>
-          <t>SPARTA</t>
-        </is>
-      </c>
-      <c r="G49" s="24" t="inlineStr">
-        <is>
-          <t>BET-M 33</t>
-        </is>
-      </c>
-      <c r="H49" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I49" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J49" s="25" t="n"/>
-      <c r="K49" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L49" s="26" t="n">
-        <v>108</v>
-      </c>
-      <c r="M49" s="27" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="N49" s="28" t="n">
-        <v>0.480769</v>
-      </c>
-      <c r="O49" s="28" t="n">
-        <v>0.524292</v>
-      </c>
-      <c r="P49" s="28" t="n"/>
-      <c r="Q49" s="28" t="n">
-        <v>0.043523</v>
-      </c>
-      <c r="R49" s="26" t="n">
-        <v>42</v>
-      </c>
-      <c r="S49" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T49" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="U49" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V49" s="24" t="n"/>
-      <c r="W49" s="26" t="n"/>
-      <c r="X49" s="26" t="n"/>
-      <c r="Y49" s="25" t="n"/>
-      <c r="Z49" s="26" t="n"/>
-      <c r="AA49" s="28" t="n"/>
-      <c r="AB49" s="28" t="n"/>
-      <c r="AC49" s="30" t="n"/>
-      <c r="AD49" s="24" t="n"/>
-      <c r="AE49" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.4800 (market_slug=aec-cs2-33-sparta-2026-07-23).</t>
-        </is>
-      </c>
-      <c r="AF49" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG49" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH49" s="24" t="n"/>
-      <c r="AI49" s="31" t="n"/>
-      <c r="AJ49" s="31" t="n"/>
-      <c r="AK49" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL49" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM49" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN49" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO49" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LOW_EDGE</t>
-        </is>
-      </c>
-      <c r="AP49" s="24" t="inlineStr">
-        <is>
-          <t>SPARTA</t>
-        </is>
-      </c>
-      <c r="AQ49" s="24" t="inlineStr">
-        <is>
-          <t>SPARTA</t>
-        </is>
-      </c>
-      <c r="AR49" s="24" t="inlineStr">
-        <is>
-          <t>SPARTA</t>
-        </is>
-      </c>
-      <c r="AS49" s="24" t="inlineStr">
-        <is>
-          <t>BET-M 33</t>
-        </is>
-      </c>
-      <c r="AT49" s="24" t="inlineStr">
-        <is>
-          <t>BET-M 33</t>
-        </is>
-      </c>
-      <c r="AU49" s="24" t="inlineStr">
-        <is>
-          <t>BET-M 33</t>
-        </is>
-      </c>
-      <c r="AV49" s="24" t="n"/>
-      <c r="AW49" s="24" t="n"/>
-      <c r="AX49" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY49" s="24" t="n"/>
-      <c r="AZ49" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA49" s="24" t="inlineStr">
-        <is>
-          <t>48424b79d75fc1173c9c465d95feb6fc041a2ccfbc64455058b3f74905ce28d5</t>
-        </is>
-      </c>
-      <c r="BB49" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC49" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="BD49" s="24" t="inlineStr">
-        <is>
-          <t>48424b79d75fc1173c9c465d95feb6fc041a2ccfbc64455058b3f74905ce28d5</t>
-        </is>
-      </c>
-      <c r="BE49" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF49" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG49" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="BH49" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-23T07:20:05.735307Z</t>
-        </is>
-      </c>
-      <c r="BI49" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ49" s="25" t="n"/>
-      <c r="BK49" s="26" t="n">
-        <v>108</v>
-      </c>
-      <c r="BL49" s="27" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="BM49" s="28" t="n">
-        <v>0.480769</v>
-      </c>
-      <c r="BN49" s="28" t="n"/>
-      <c r="BO49" s="28" t="n"/>
-      <c r="BP49" s="25" t="n"/>
-      <c r="BQ49" s="27" t="n"/>
-      <c r="BR49" s="28" t="n"/>
-      <c r="BS49" s="28" t="n"/>
-      <c r="BT49" s="28" t="n"/>
-      <c r="BU49" s="25" t="n"/>
-      <c r="BV49" s="29" t="n"/>
-      <c r="BW49" s="24" t="n"/>
-      <c r="BX49" s="30" t="n"/>
-      <c r="BY49" s="27" t="n"/>
-      <c r="BZ49" s="24" t="n"/>
-      <c r="CA49" s="31" t="n"/>
-      <c r="CB49" s="24" t="n"/>
-      <c r="CC49" s="24" t="n"/>
-      <c r="CD49" s="24" t="n"/>
-      <c r="CE49" s="24" t="n"/>
-      <c r="CF49" s="24" t="n"/>
-      <c r="CG49" s="24" t="n"/>
-      <c r="CH49" s="24" t="n"/>
-      <c r="CI49" s="24" t="n"/>
-      <c r="CJ49" s="24" t="n"/>
-      <c r="CK49" s="24" t="n"/>
-      <c r="CL49" s="24" t="n"/>
-      <c r="CM49" s="24" t="n"/>
-    </row>
-    <row r="50" ht="36" customHeight="1">
-      <c r="A50" s="24" t="inlineStr">
-        <is>
-          <t>4b1175c03baa474d</t>
-        </is>
-      </c>
-      <c r="B50" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-23T07:20:39.530092Z</t>
-        </is>
-      </c>
-      <c r="C50" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-23T14:00:00Z</t>
-        </is>
-      </c>
-      <c r="D50" s="24" t="inlineStr">
-        <is>
-          <t>56895</t>
-        </is>
-      </c>
-      <c r="E50" s="24" t="inlineStr">
-        <is>
-          <t>CS2</t>
-        </is>
-      </c>
-      <c r="F50" s="24" t="inlineStr">
-        <is>
-          <t>Privateer Gaming</t>
-        </is>
-      </c>
-      <c r="G50" s="24" t="inlineStr">
-        <is>
-          <t>megoshort</t>
-        </is>
-      </c>
-      <c r="H50" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I50" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J50" s="25" t="n"/>
-      <c r="K50" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L50" s="26" t="n">
-        <v>127</v>
-      </c>
-      <c r="M50" s="27" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="N50" s="28" t="n">
-        <v>0.440529</v>
-      </c>
-      <c r="O50" s="28" t="n">
-        <v>0.586941</v>
-      </c>
-      <c r="P50" s="28" t="n"/>
-      <c r="Q50" s="28" t="n">
-        <v>0.146412</v>
-      </c>
-      <c r="R50" s="26" t="n">
-        <v>100</v>
-      </c>
-      <c r="S50" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T50" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="U50" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V50" s="24" t="n"/>
-      <c r="W50" s="26" t="n"/>
-      <c r="X50" s="26" t="n"/>
-      <c r="Y50" s="25" t="n"/>
-      <c r="Z50" s="26" t="n"/>
-      <c r="AA50" s="28" t="n"/>
-      <c r="AB50" s="28" t="n"/>
-      <c r="AC50" s="30" t="n"/>
-      <c r="AD50" s="24" t="n"/>
-      <c r="AE50" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.4400 (market_slug=aec-cs2-mego-pg-2026-07-23).</t>
-        </is>
-      </c>
-      <c r="AF50" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG50" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH50" s="24" t="n"/>
-      <c r="AI50" s="31" t="n"/>
-      <c r="AJ50" s="31" t="n"/>
-      <c r="AK50" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL50" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM50" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN50" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO50" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LARGE_DISAGREEMENT_REVIEW</t>
-        </is>
-      </c>
-      <c r="AP50" s="24" t="inlineStr">
-        <is>
-          <t>Privateer Gaming</t>
-        </is>
-      </c>
-      <c r="AQ50" s="24" t="inlineStr">
-        <is>
-          <t>Privateer Gaming</t>
-        </is>
-      </c>
-      <c r="AR50" s="24" t="inlineStr">
-        <is>
-          <t>Privateer Gaming</t>
-        </is>
-      </c>
-      <c r="AS50" s="24" t="inlineStr">
-        <is>
-          <t>megoshort</t>
-        </is>
-      </c>
-      <c r="AT50" s="24" t="inlineStr">
-        <is>
-          <t>megoshort</t>
-        </is>
-      </c>
-      <c r="AU50" s="24" t="inlineStr">
-        <is>
-          <t>megoshort</t>
-        </is>
-      </c>
-      <c r="AV50" s="24" t="n"/>
-      <c r="AW50" s="24" t="n"/>
-      <c r="AX50" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY50" s="24" t="n"/>
-      <c r="AZ50" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA50" s="24" t="inlineStr">
-        <is>
-          <t>48424b79d75fc1173c9c465d95feb6fc041a2ccfbc64455058b3f74905ce28d5</t>
-        </is>
-      </c>
-      <c r="BB50" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC50" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="BD50" s="24" t="inlineStr">
-        <is>
-          <t>48424b79d75fc1173c9c465d95feb6fc041a2ccfbc64455058b3f74905ce28d5</t>
-        </is>
-      </c>
-      <c r="BE50" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF50" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG50" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="BH50" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-23T07:20:06.778014Z</t>
-        </is>
-      </c>
-      <c r="BI50" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ50" s="25" t="n"/>
-      <c r="BK50" s="26" t="n">
-        <v>127</v>
-      </c>
-      <c r="BL50" s="27" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="BM50" s="28" t="n">
-        <v>0.440529</v>
-      </c>
-      <c r="BN50" s="28" t="n"/>
-      <c r="BO50" s="28" t="n"/>
-      <c r="BP50" s="25" t="n"/>
-      <c r="BQ50" s="27" t="n"/>
-      <c r="BR50" s="28" t="n"/>
-      <c r="BS50" s="28" t="n"/>
-      <c r="BT50" s="28" t="n"/>
-      <c r="BU50" s="25" t="n"/>
-      <c r="BV50" s="29" t="n"/>
-      <c r="BW50" s="24" t="n"/>
-      <c r="BX50" s="30" t="n"/>
-      <c r="BY50" s="27" t="n"/>
-      <c r="BZ50" s="24" t="n"/>
-      <c r="CA50" s="31" t="n"/>
-      <c r="CB50" s="24" t="n"/>
-      <c r="CC50" s="24" t="n"/>
-      <c r="CD50" s="24" t="n"/>
-      <c r="CE50" s="24" t="n"/>
-      <c r="CF50" s="24" t="n"/>
-      <c r="CG50" s="24" t="n"/>
-      <c r="CH50" s="24" t="n"/>
-      <c r="CI50" s="24" t="n"/>
-      <c r="CJ50" s="24" t="n"/>
-      <c r="CK50" s="24" t="n"/>
-      <c r="CL50" s="24" t="n"/>
-      <c r="CM50" s="24" t="n"/>
-    </row>
-    <row r="51" ht="36" customHeight="1">
-      <c r="A51" s="24" t="inlineStr">
-        <is>
-          <t>7e331e3092b54f39</t>
-        </is>
-      </c>
-      <c r="B51" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-23T07:20:39.530092Z</t>
-        </is>
-      </c>
-      <c r="C51" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-23T15:00:00Z</t>
-        </is>
-      </c>
-      <c r="D51" s="24" t="inlineStr">
-        <is>
-          <t>56958</t>
-        </is>
-      </c>
-      <c r="E51" s="24" t="inlineStr">
-        <is>
-          <t>CS2</t>
-        </is>
-      </c>
-      <c r="F51" s="24" t="inlineStr">
-        <is>
-          <t>paiN</t>
-        </is>
-      </c>
-      <c r="G51" s="24" t="inlineStr">
-        <is>
-          <t>Gentle Mates</t>
-        </is>
-      </c>
-      <c r="H51" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I51" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J51" s="25" t="n"/>
-      <c r="K51" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L51" s="26" t="n">
-        <v>133</v>
-      </c>
-      <c r="M51" s="27" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="N51" s="28" t="n">
-        <v>0.429185</v>
-      </c>
-      <c r="O51" s="28" t="n">
-        <v>0.524605</v>
-      </c>
-      <c r="P51" s="28" t="n"/>
-      <c r="Q51" s="28" t="n">
-        <v>0.09542</v>
-      </c>
-      <c r="R51" s="26" t="n">
-        <v>68</v>
-      </c>
-      <c r="S51" s="29" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="T51" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="U51" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V51" s="24" t="n"/>
-      <c r="W51" s="26" t="n"/>
-      <c r="X51" s="26" t="n"/>
-      <c r="Y51" s="25" t="n"/>
-      <c r="Z51" s="26" t="n"/>
-      <c r="AA51" s="28" t="n"/>
-      <c r="AB51" s="28" t="n"/>
-      <c r="AC51" s="30" t="n"/>
-      <c r="AD51" s="24" t="n"/>
-      <c r="AE51" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.4300 (market_slug=aec-cs2-m8-pain-2026-07-23).</t>
-        </is>
-      </c>
-      <c r="AF51" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG51" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH51" s="24" t="n"/>
-      <c r="AI51" s="31" t="n"/>
-      <c r="AJ51" s="31" t="n"/>
-      <c r="AK51" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL51" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM51" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN51" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO51" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP51" s="24" t="inlineStr">
-        <is>
-          <t>paiN</t>
-        </is>
-      </c>
-      <c r="AQ51" s="24" t="inlineStr">
-        <is>
-          <t>paiN</t>
-        </is>
-      </c>
-      <c r="AR51" s="24" t="inlineStr">
-        <is>
-          <t>paiN</t>
-        </is>
-      </c>
-      <c r="AS51" s="24" t="inlineStr">
-        <is>
-          <t>Gentle Mates</t>
-        </is>
-      </c>
-      <c r="AT51" s="24" t="inlineStr">
-        <is>
-          <t>Gentle Mates</t>
-        </is>
-      </c>
-      <c r="AU51" s="24" t="inlineStr">
-        <is>
-          <t>Gentle Mates</t>
-        </is>
-      </c>
-      <c r="AV51" s="24" t="n"/>
-      <c r="AW51" s="24" t="n"/>
-      <c r="AX51" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY51" s="24" t="n"/>
-      <c r="AZ51" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA51" s="24" t="inlineStr">
-        <is>
-          <t>48424b79d75fc1173c9c465d95feb6fc041a2ccfbc64455058b3f74905ce28d5</t>
-        </is>
-      </c>
-      <c r="BB51" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC51" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="BD51" s="24" t="inlineStr">
-        <is>
-          <t>48424b79d75fc1173c9c465d95feb6fc041a2ccfbc64455058b3f74905ce28d5</t>
-        </is>
-      </c>
-      <c r="BE51" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF51" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG51" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="BH51" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-23T07:20:08.563260Z</t>
-        </is>
-      </c>
-      <c r="BI51" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ51" s="25" t="n"/>
-      <c r="BK51" s="26" t="n">
-        <v>133</v>
-      </c>
-      <c r="BL51" s="27" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="BM51" s="28" t="n">
-        <v>0.429185</v>
-      </c>
-      <c r="BN51" s="28" t="n"/>
-      <c r="BO51" s="28" t="n"/>
-      <c r="BP51" s="25" t="n"/>
-      <c r="BQ51" s="27" t="n"/>
-      <c r="BR51" s="28" t="n"/>
-      <c r="BS51" s="28" t="n"/>
-      <c r="BT51" s="28" t="n"/>
-      <c r="BU51" s="25" t="n"/>
-      <c r="BV51" s="29" t="n"/>
-      <c r="BW51" s="24" t="n"/>
-      <c r="BX51" s="30" t="n"/>
-      <c r="BY51" s="27" t="n"/>
-      <c r="BZ51" s="24" t="n"/>
-      <c r="CA51" s="31" t="n"/>
-      <c r="CB51" s="24" t="n"/>
-      <c r="CC51" s="24" t="n"/>
-      <c r="CD51" s="24" t="n"/>
-      <c r="CE51" s="24" t="n"/>
-      <c r="CF51" s="24" t="n"/>
-      <c r="CG51" s="24" t="n"/>
-      <c r="CH51" s="24" t="n"/>
-      <c r="CI51" s="24" t="n"/>
-      <c r="CJ51" s="24" t="n"/>
-      <c r="CK51" s="24" t="n"/>
-      <c r="CL51" s="24" t="n"/>
-      <c r="CM51" s="24" t="n"/>
-    </row>
-    <row r="52" ht="36" customHeight="1">
-      <c r="A52" s="24" t="inlineStr">
-        <is>
-          <t>785b91cd35224c25</t>
-        </is>
-      </c>
-      <c r="B52" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-23T07:20:39.530092Z</t>
-        </is>
-      </c>
-      <c r="C52" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-23T17:00:00Z</t>
-        </is>
-      </c>
-      <c r="D52" s="24" t="inlineStr">
-        <is>
-          <t>59678</t>
-        </is>
-      </c>
-      <c r="E52" s="24" t="inlineStr">
-        <is>
-          <t>CS2</t>
-        </is>
-      </c>
-      <c r="F52" s="24" t="inlineStr">
-        <is>
-          <t>Benched gods</t>
-        </is>
-      </c>
-      <c r="G52" s="24" t="inlineStr">
-        <is>
-          <t>CYBERSHOKE Prospects</t>
-        </is>
-      </c>
-      <c r="H52" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I52" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J52" s="25" t="n"/>
-      <c r="K52" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L52" s="26" t="n">
-        <v>-144</v>
-      </c>
-      <c r="M52" s="27" t="n">
-        <v>1.694444</v>
-      </c>
-      <c r="N52" s="28" t="n">
-        <v>0.590164</v>
-      </c>
-      <c r="O52" s="28" t="n">
-        <v>0.63774</v>
-      </c>
-      <c r="P52" s="28" t="n"/>
-      <c r="Q52" s="28" t="n">
-        <v>0.047576</v>
-      </c>
-      <c r="R52" s="26" t="n">
-        <v>44</v>
-      </c>
-      <c r="S52" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T52" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="U52" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V52" s="24" t="n"/>
-      <c r="W52" s="26" t="n"/>
-      <c r="X52" s="26" t="n"/>
-      <c r="Y52" s="25" t="n"/>
-      <c r="Z52" s="26" t="n"/>
-      <c r="AA52" s="28" t="n"/>
-      <c r="AB52" s="28" t="n"/>
-      <c r="AC52" s="30" t="n"/>
-      <c r="AD52" s="24" t="n"/>
-      <c r="AE52" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-cs2-cshp-bge-2026-07-23).</t>
-        </is>
-      </c>
-      <c r="AF52" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG52" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH52" s="24" t="n"/>
-      <c r="AI52" s="31" t="n"/>
-      <c r="AJ52" s="31" t="n"/>
-      <c r="AK52" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL52" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM52" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN52" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO52" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LOW_EDGE</t>
-        </is>
-      </c>
-      <c r="AP52" s="24" t="inlineStr">
-        <is>
-          <t>Benched gods</t>
-        </is>
-      </c>
-      <c r="AQ52" s="24" t="inlineStr">
-        <is>
-          <t>Benched gods</t>
-        </is>
-      </c>
-      <c r="AR52" s="24" t="inlineStr">
-        <is>
-          <t>Benched gods</t>
-        </is>
-      </c>
-      <c r="AS52" s="24" t="inlineStr">
-        <is>
-          <t>CYBERSHOKE Prospects</t>
-        </is>
-      </c>
-      <c r="AT52" s="24" t="inlineStr">
-        <is>
-          <t>CYBERSHOKE Prospects</t>
-        </is>
-      </c>
-      <c r="AU52" s="24" t="inlineStr">
-        <is>
-          <t>CYBERSHOKE Prospects</t>
-        </is>
-      </c>
-      <c r="AV52" s="24" t="n"/>
-      <c r="AW52" s="24" t="n"/>
-      <c r="AX52" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY52" s="24" t="n"/>
-      <c r="AZ52" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA52" s="24" t="inlineStr">
-        <is>
-          <t>48424b79d75fc1173c9c465d95feb6fc041a2ccfbc64455058b3f74905ce28d5</t>
-        </is>
-      </c>
-      <c r="BB52" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC52" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="BD52" s="24" t="inlineStr">
-        <is>
-          <t>48424b79d75fc1173c9c465d95feb6fc041a2ccfbc64455058b3f74905ce28d5</t>
-        </is>
-      </c>
-      <c r="BE52" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF52" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG52" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="BH52" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-23T07:20:13.459542Z</t>
-        </is>
-      </c>
-      <c r="BI52" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ52" s="25" t="n"/>
-      <c r="BK52" s="26" t="n">
-        <v>-144</v>
-      </c>
-      <c r="BL52" s="27" t="n">
-        <v>1.694444</v>
-      </c>
-      <c r="BM52" s="28" t="n">
-        <v>0.590164</v>
-      </c>
-      <c r="BN52" s="28" t="n"/>
-      <c r="BO52" s="28" t="n"/>
-      <c r="BP52" s="25" t="n"/>
-      <c r="BQ52" s="27" t="n"/>
-      <c r="BR52" s="28" t="n"/>
-      <c r="BS52" s="28" t="n"/>
-      <c r="BT52" s="28" t="n"/>
-      <c r="BU52" s="25" t="n"/>
-      <c r="BV52" s="29" t="n"/>
-      <c r="BW52" s="24" t="n"/>
-      <c r="BX52" s="30" t="n"/>
-      <c r="BY52" s="27" t="n"/>
-      <c r="BZ52" s="24" t="n"/>
-      <c r="CA52" s="31" t="n"/>
-      <c r="CB52" s="24" t="n"/>
-      <c r="CC52" s="24" t="n"/>
-      <c r="CD52" s="24" t="n"/>
-      <c r="CE52" s="24" t="n"/>
-      <c r="CF52" s="24" t="n"/>
-      <c r="CG52" s="24" t="n"/>
-      <c r="CH52" s="24" t="n"/>
-      <c r="CI52" s="24" t="n"/>
-      <c r="CJ52" s="24" t="n"/>
-      <c r="CK52" s="24" t="n"/>
-      <c r="CL52" s="24" t="n"/>
-      <c r="CM52" s="24" t="n"/>
-    </row>
-    <row r="53" ht="36" customHeight="1">
-      <c r="A53" s="24" t="inlineStr">
-        <is>
-          <t>7af09bb274ab4660</t>
-        </is>
-      </c>
-      <c r="B53" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-23T07:20:39.530092Z</t>
-        </is>
-      </c>
-      <c r="C53" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-23T17:00:00Z</t>
-        </is>
-      </c>
-      <c r="D53" s="24" t="inlineStr">
-        <is>
-          <t>59039</t>
-        </is>
-      </c>
-      <c r="E53" s="24" t="inlineStr">
-        <is>
-          <t>CS2</t>
-        </is>
-      </c>
-      <c r="F53" s="24" t="inlineStr">
-        <is>
-          <t>Just Players</t>
-        </is>
-      </c>
-      <c r="G53" s="24" t="inlineStr">
-        <is>
-          <t>Butterfly</t>
-        </is>
-      </c>
-      <c r="H53" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I53" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J53" s="25" t="n"/>
-      <c r="K53" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L53" s="26" t="n">
-        <v>-144</v>
-      </c>
-      <c r="M53" s="27" t="n">
-        <v>1.694444</v>
-      </c>
-      <c r="N53" s="28" t="n">
-        <v>0.590164</v>
-      </c>
-      <c r="O53" s="28" t="n">
-        <v>0.685765</v>
-      </c>
-      <c r="P53" s="28" t="n"/>
-      <c r="Q53" s="28" t="n">
-        <v>0.09560100000000001</v>
-      </c>
-      <c r="R53" s="26" t="n">
-        <v>68</v>
-      </c>
-      <c r="S53" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="T53" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="U53" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V53" s="24" t="n"/>
-      <c r="W53" s="26" t="n"/>
-      <c r="X53" s="26" t="n"/>
-      <c r="Y53" s="25" t="n"/>
-      <c r="Z53" s="26" t="n"/>
-      <c r="AA53" s="28" t="n"/>
-      <c r="AB53" s="28" t="n"/>
-      <c r="AC53" s="30" t="n"/>
-      <c r="AD53" s="24" t="n"/>
-      <c r="AE53" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-cs2-btf-jpu-2026-07-23).</t>
-        </is>
-      </c>
-      <c r="AF53" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG53" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH53" s="24" t="n"/>
-      <c r="AI53" s="31" t="n"/>
-      <c r="AJ53" s="31" t="n"/>
-      <c r="AK53" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL53" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM53" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN53" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO53" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP53" s="24" t="inlineStr">
-        <is>
-          <t>Just Players</t>
-        </is>
-      </c>
-      <c r="AQ53" s="24" t="inlineStr">
-        <is>
-          <t>Just Players</t>
-        </is>
-      </c>
-      <c r="AR53" s="24" t="inlineStr">
-        <is>
-          <t>Just Players</t>
-        </is>
-      </c>
-      <c r="AS53" s="24" t="inlineStr">
-        <is>
-          <t>Butterfly</t>
-        </is>
-      </c>
-      <c r="AT53" s="24" t="inlineStr">
-        <is>
-          <t>Butterfly</t>
-        </is>
-      </c>
-      <c r="AU53" s="24" t="inlineStr">
-        <is>
-          <t>Butterfly</t>
-        </is>
-      </c>
-      <c r="AV53" s="24" t="n"/>
-      <c r="AW53" s="24" t="n"/>
-      <c r="AX53" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY53" s="24" t="n"/>
-      <c r="AZ53" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA53" s="24" t="inlineStr">
-        <is>
-          <t>48424b79d75fc1173c9c465d95feb6fc041a2ccfbc64455058b3f74905ce28d5</t>
-        </is>
-      </c>
-      <c r="BB53" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC53" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="BD53" s="24" t="inlineStr">
-        <is>
-          <t>48424b79d75fc1173c9c465d95feb6fc041a2ccfbc64455058b3f74905ce28d5</t>
-        </is>
-      </c>
-      <c r="BE53" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF53" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG53" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="BH53" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-23T07:20:15.985178Z</t>
-        </is>
-      </c>
-      <c r="BI53" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ53" s="25" t="n"/>
-      <c r="BK53" s="26" t="n">
-        <v>-144</v>
-      </c>
-      <c r="BL53" s="27" t="n">
-        <v>1.694444</v>
-      </c>
-      <c r="BM53" s="28" t="n">
-        <v>0.590164</v>
-      </c>
-      <c r="BN53" s="28" t="n"/>
-      <c r="BO53" s="28" t="n"/>
-      <c r="BP53" s="25" t="n"/>
-      <c r="BQ53" s="27" t="n"/>
-      <c r="BR53" s="28" t="n"/>
-      <c r="BS53" s="28" t="n"/>
-      <c r="BT53" s="28" t="n"/>
-      <c r="BU53" s="25" t="n"/>
-      <c r="BV53" s="29" t="n"/>
-      <c r="BW53" s="24" t="n"/>
-      <c r="BX53" s="30" t="n"/>
-      <c r="BY53" s="27" t="n"/>
-      <c r="BZ53" s="24" t="n"/>
-      <c r="CA53" s="31" t="n"/>
-      <c r="CB53" s="24" t="n"/>
-      <c r="CC53" s="24" t="n"/>
-      <c r="CD53" s="24" t="n"/>
-      <c r="CE53" s="24" t="n"/>
-      <c r="CF53" s="24" t="n"/>
-      <c r="CG53" s="24" t="n"/>
-      <c r="CH53" s="24" t="n"/>
-      <c r="CI53" s="24" t="n"/>
-      <c r="CJ53" s="24" t="n"/>
-      <c r="CK53" s="24" t="n"/>
-      <c r="CL53" s="24" t="n"/>
-      <c r="CM53" s="24" t="n"/>
-    </row>
-    <row r="54" ht="36" customHeight="1">
-      <c r="A54" s="24" t="inlineStr">
-        <is>
-          <t>59cf95be24aa4f71</t>
-        </is>
-      </c>
-      <c r="B54" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-23T07:20:39.530092Z</t>
-        </is>
-      </c>
-      <c r="C54" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-23T22:00:00Z</t>
-        </is>
-      </c>
-      <c r="D54" s="24" t="inlineStr">
-        <is>
-          <t>59964</t>
-        </is>
-      </c>
-      <c r="E54" s="24" t="inlineStr">
-        <is>
-          <t>CS2</t>
-        </is>
-      </c>
-      <c r="F54" s="24" t="inlineStr">
-        <is>
-          <t>Patins da Ferrari</t>
-        </is>
-      </c>
-      <c r="G54" s="24" t="inlineStr">
-        <is>
-          <t>Isurus</t>
-        </is>
-      </c>
-      <c r="H54" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I54" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J54" s="25" t="n"/>
-      <c r="K54" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L54" s="26" t="n">
-        <v>133</v>
-      </c>
-      <c r="M54" s="27" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="N54" s="28" t="n">
-        <v>0.429185</v>
-      </c>
-      <c r="O54" s="28" t="n">
-        <v>0.502768</v>
-      </c>
-      <c r="P54" s="28" t="n"/>
-      <c r="Q54" s="28" t="n">
-        <v>0.073583</v>
-      </c>
-      <c r="R54" s="26" t="n">
-        <v>57</v>
-      </c>
-      <c r="S54" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T54" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="U54" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V54" s="24" t="n"/>
-      <c r="W54" s="26" t="n"/>
-      <c r="X54" s="26" t="n"/>
-      <c r="Y54" s="25" t="n"/>
-      <c r="Z54" s="26" t="n"/>
-      <c r="AA54" s="28" t="n"/>
-      <c r="AB54" s="28" t="n"/>
-      <c r="AC54" s="30" t="n"/>
-      <c r="AD54" s="24" t="n"/>
-      <c r="AE54" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.4300 (market_slug=aec-cs2-isg-pdaf-2026-07-23).</t>
-        </is>
-      </c>
-      <c r="AF54" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG54" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH54" s="24" t="n"/>
-      <c r="AI54" s="31" t="n"/>
-      <c r="AJ54" s="31" t="n"/>
-      <c r="AK54" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL54" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM54" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN54" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO54" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_EXPOSURE_LIMIT</t>
-        </is>
-      </c>
-      <c r="AP54" s="24" t="inlineStr">
-        <is>
-          <t>Patins da Ferrari</t>
-        </is>
-      </c>
-      <c r="AQ54" s="24" t="inlineStr">
-        <is>
-          <t>Patins da Ferrari</t>
-        </is>
-      </c>
-      <c r="AR54" s="24" t="inlineStr">
-        <is>
-          <t>Patins da Ferrari</t>
-        </is>
-      </c>
-      <c r="AS54" s="24" t="inlineStr">
-        <is>
-          <t>Isurus</t>
-        </is>
-      </c>
-      <c r="AT54" s="24" t="inlineStr">
-        <is>
-          <t>Isurus</t>
-        </is>
-      </c>
-      <c r="AU54" s="24" t="inlineStr">
-        <is>
-          <t>Isurus</t>
-        </is>
-      </c>
-      <c r="AV54" s="24" t="n"/>
-      <c r="AW54" s="24" t="n"/>
-      <c r="AX54" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY54" s="24" t="n"/>
-      <c r="AZ54" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA54" s="24" t="inlineStr">
-        <is>
-          <t>48424b79d75fc1173c9c465d95feb6fc041a2ccfbc64455058b3f74905ce28d5</t>
-        </is>
-      </c>
-      <c r="BB54" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC54" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="BD54" s="24" t="inlineStr">
-        <is>
-          <t>48424b79d75fc1173c9c465d95feb6fc041a2ccfbc64455058b3f74905ce28d5</t>
-        </is>
-      </c>
-      <c r="BE54" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF54" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG54" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="BH54" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-23T07:20:26.998884Z</t>
-        </is>
-      </c>
-      <c r="BI54" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ54" s="25" t="n"/>
-      <c r="BK54" s="26" t="n">
-        <v>133</v>
-      </c>
-      <c r="BL54" s="27" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="BM54" s="28" t="n">
-        <v>0.429185</v>
-      </c>
-      <c r="BN54" s="28" t="n"/>
-      <c r="BO54" s="28" t="n"/>
-      <c r="BP54" s="25" t="n"/>
-      <c r="BQ54" s="27" t="n"/>
-      <c r="BR54" s="28" t="n"/>
-      <c r="BS54" s="28" t="n"/>
-      <c r="BT54" s="28" t="n"/>
-      <c r="BU54" s="25" t="n"/>
-      <c r="BV54" s="29" t="n"/>
-      <c r="BW54" s="24" t="n"/>
-      <c r="BX54" s="30" t="n"/>
-      <c r="BY54" s="27" t="n"/>
-      <c r="BZ54" s="24" t="n"/>
-      <c r="CA54" s="31" t="n"/>
-      <c r="CB54" s="24" t="n"/>
-      <c r="CC54" s="24" t="n"/>
-      <c r="CD54" s="24" t="n"/>
-      <c r="CE54" s="24" t="n"/>
-      <c r="CF54" s="24" t="n"/>
-      <c r="CG54" s="24" t="n"/>
-      <c r="CH54" s="24" t="n"/>
-      <c r="CI54" s="24" t="n"/>
-      <c r="CJ54" s="24" t="n"/>
-      <c r="CK54" s="24" t="n"/>
-      <c r="CL54" s="24" t="n"/>
-      <c r="CM54" s="24" t="n"/>
-    </row>
-    <row r="55" ht="36" customHeight="1">
-      <c r="A55" s="24" t="inlineStr">
-        <is>
-          <t>81a328b8d84a4505</t>
-        </is>
-      </c>
-      <c r="B55" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-23T07:20:39.530092Z</t>
-        </is>
-      </c>
-      <c r="C55" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-24T08:00:00Z</t>
-        </is>
-      </c>
-      <c r="D55" s="24" t="inlineStr">
-        <is>
-          <t>59681</t>
-        </is>
-      </c>
-      <c r="E55" s="24" t="inlineStr">
-        <is>
-          <t>CS2</t>
-        </is>
-      </c>
-      <c r="F55" s="24" t="inlineStr">
-        <is>
-          <t>ex-RUSTEC</t>
-        </is>
-      </c>
-      <c r="G55" s="24" t="inlineStr">
-        <is>
-          <t>INOX Division</t>
-        </is>
-      </c>
-      <c r="H55" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I55" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J55" s="25" t="n"/>
-      <c r="K55" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L55" s="26" t="n">
-        <v>-178</v>
-      </c>
-      <c r="M55" s="27" t="n">
-        <v>1.561798</v>
-      </c>
-      <c r="N55" s="28" t="n">
-        <v>0.640288</v>
-      </c>
-      <c r="O55" s="28" t="n">
-        <v>0.677314</v>
-      </c>
-      <c r="P55" s="28" t="n"/>
-      <c r="Q55" s="28" t="n">
-        <v>0.037026</v>
-      </c>
-      <c r="R55" s="26" t="n">
-        <v>39</v>
-      </c>
-      <c r="S55" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T55" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="U55" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V55" s="24" t="n"/>
-      <c r="W55" s="26" t="n"/>
-      <c r="X55" s="26" t="n"/>
-      <c r="Y55" s="25" t="n"/>
-      <c r="Z55" s="26" t="n"/>
-      <c r="AA55" s="28" t="n"/>
-      <c r="AB55" s="28" t="n"/>
-      <c r="AC55" s="30" t="n"/>
-      <c r="AD55" s="24" t="n"/>
-      <c r="AE55" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-cs2-inox-erx-2026-07-24).</t>
-        </is>
-      </c>
-      <c r="AF55" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG55" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH55" s="24" t="n"/>
-      <c r="AI55" s="31" t="n"/>
-      <c r="AJ55" s="31" t="n"/>
-      <c r="AK55" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL55" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM55" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN55" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO55" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LOW_EDGE</t>
-        </is>
-      </c>
-      <c r="AP55" s="24" t="inlineStr">
-        <is>
-          <t>ex-RUSTEC</t>
-        </is>
-      </c>
-      <c r="AQ55" s="24" t="inlineStr">
-        <is>
-          <t>ex-RUSTEC</t>
-        </is>
-      </c>
-      <c r="AR55" s="24" t="inlineStr">
-        <is>
-          <t>ex-RUSTEC</t>
-        </is>
-      </c>
-      <c r="AS55" s="24" t="inlineStr">
-        <is>
-          <t>INOX Division</t>
-        </is>
-      </c>
-      <c r="AT55" s="24" t="inlineStr">
-        <is>
-          <t>INOX Division</t>
-        </is>
-      </c>
-      <c r="AU55" s="24" t="inlineStr">
-        <is>
-          <t>INOX Division</t>
-        </is>
-      </c>
-      <c r="AV55" s="24" t="n"/>
-      <c r="AW55" s="24" t="n"/>
-      <c r="AX55" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY55" s="24" t="n"/>
-      <c r="AZ55" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA55" s="24" t="inlineStr">
-        <is>
-          <t>48424b79d75fc1173c9c465d95feb6fc041a2ccfbc64455058b3f74905ce28d5</t>
-        </is>
-      </c>
-      <c r="BB55" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC55" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="BD55" s="24" t="inlineStr">
-        <is>
-          <t>48424b79d75fc1173c9c465d95feb6fc041a2ccfbc64455058b3f74905ce28d5</t>
-        </is>
-      </c>
-      <c r="BE55" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF55" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG55" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="BH55" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-23T07:20:27.867010Z</t>
-        </is>
-      </c>
-      <c r="BI55" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ55" s="25" t="n"/>
-      <c r="BK55" s="26" t="n">
-        <v>-178</v>
-      </c>
-      <c r="BL55" s="27" t="n">
-        <v>1.561798</v>
-      </c>
-      <c r="BM55" s="28" t="n">
-        <v>0.640288</v>
-      </c>
-      <c r="BN55" s="28" t="n"/>
-      <c r="BO55" s="28" t="n"/>
-      <c r="BP55" s="25" t="n"/>
-      <c r="BQ55" s="27" t="n"/>
-      <c r="BR55" s="28" t="n"/>
-      <c r="BS55" s="28" t="n"/>
-      <c r="BT55" s="28" t="n"/>
-      <c r="BU55" s="25" t="n"/>
-      <c r="BV55" s="29" t="n"/>
-      <c r="BW55" s="24" t="n"/>
-      <c r="BX55" s="30" t="n"/>
-      <c r="BY55" s="27" t="n"/>
-      <c r="BZ55" s="24" t="n"/>
-      <c r="CA55" s="31" t="n"/>
-      <c r="CB55" s="24" t="n"/>
-      <c r="CC55" s="24" t="n"/>
-      <c r="CD55" s="24" t="n"/>
-      <c r="CE55" s="24" t="n"/>
-      <c r="CF55" s="24" t="n"/>
-      <c r="CG55" s="24" t="n"/>
-      <c r="CH55" s="24" t="n"/>
-      <c r="CI55" s="24" t="n"/>
-      <c r="CJ55" s="24" t="n"/>
-      <c r="CK55" s="24" t="n"/>
-      <c r="CL55" s="24" t="n"/>
-      <c r="CM55" s="24" t="n"/>
-    </row>
-    <row r="56" ht="36" customHeight="1">
-      <c r="A56" s="24" t="inlineStr">
-        <is>
-          <t>a232e14d96984007</t>
-        </is>
-      </c>
-      <c r="B56" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-23T07:20:39.530092Z</t>
-        </is>
-      </c>
-      <c r="C56" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-24T08:00:00Z</t>
-        </is>
-      </c>
-      <c r="D56" s="24" t="inlineStr">
-        <is>
-          <t>59323</t>
-        </is>
-      </c>
-      <c r="E56" s="24" t="inlineStr">
-        <is>
-          <t>CS2</t>
-        </is>
-      </c>
-      <c r="F56" s="24" t="inlineStr">
-        <is>
-          <t>Eternal Fire</t>
-        </is>
-      </c>
-      <c r="G56" s="24" t="inlineStr">
-        <is>
-          <t>1WIN</t>
-        </is>
-      </c>
-      <c r="H56" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I56" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J56" s="25" t="n"/>
-      <c r="K56" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L56" s="26" t="n">
-        <v>117</v>
-      </c>
-      <c r="M56" s="27" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="N56" s="28" t="n">
-        <v>0.460829</v>
-      </c>
-      <c r="O56" s="28" t="n">
-        <v>0.5965279999999999</v>
-      </c>
-      <c r="P56" s="28" t="n"/>
-      <c r="Q56" s="28" t="n">
-        <v>0.135699</v>
-      </c>
-      <c r="R56" s="26" t="n">
-        <v>100</v>
-      </c>
-      <c r="S56" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T56" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="U56" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V56" s="24" t="n"/>
-      <c r="W56" s="26" t="n"/>
-      <c r="X56" s="26" t="n"/>
-      <c r="Y56" s="25" t="n"/>
-      <c r="Z56" s="26" t="n"/>
-      <c r="AA56" s="28" t="n"/>
-      <c r="AB56" s="28" t="n"/>
-      <c r="AC56" s="30" t="n"/>
-      <c r="AD56" s="24" t="n"/>
-      <c r="AE56" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.4600 (market_slug=aec-cs2-1win-ef-2026-07-24).</t>
-        </is>
-      </c>
-      <c r="AF56" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG56" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH56" s="24" t="n"/>
-      <c r="AI56" s="31" t="n"/>
-      <c r="AJ56" s="31" t="n"/>
-      <c r="AK56" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL56" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM56" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN56" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO56" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LARGE_DISAGREEMENT_REVIEW</t>
-        </is>
-      </c>
-      <c r="AP56" s="24" t="inlineStr">
-        <is>
-          <t>Eternal Fire</t>
-        </is>
-      </c>
-      <c r="AQ56" s="24" t="inlineStr">
-        <is>
-          <t>Eternal Fire</t>
-        </is>
-      </c>
-      <c r="AR56" s="24" t="inlineStr">
-        <is>
-          <t>Eternal Fire</t>
-        </is>
-      </c>
-      <c r="AS56" s="24" t="inlineStr">
-        <is>
-          <t>1WIN</t>
-        </is>
-      </c>
-      <c r="AT56" s="24" t="inlineStr">
-        <is>
-          <t>1WIN</t>
-        </is>
-      </c>
-      <c r="AU56" s="24" t="inlineStr">
-        <is>
-          <t>1WIN</t>
-        </is>
-      </c>
-      <c r="AV56" s="24" t="n"/>
-      <c r="AW56" s="24" t="n"/>
-      <c r="AX56" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY56" s="24" t="n"/>
-      <c r="AZ56" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA56" s="24" t="inlineStr">
-        <is>
-          <t>48424b79d75fc1173c9c465d95feb6fc041a2ccfbc64455058b3f74905ce28d5</t>
-        </is>
-      </c>
-      <c r="BB56" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC56" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="BD56" s="24" t="inlineStr">
-        <is>
-          <t>48424b79d75fc1173c9c465d95feb6fc041a2ccfbc64455058b3f74905ce28d5</t>
-        </is>
-      </c>
-      <c r="BE56" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF56" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG56" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="BH56" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-23T07:20:28.828828Z</t>
-        </is>
-      </c>
-      <c r="BI56" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ56" s="25" t="n"/>
-      <c r="BK56" s="26" t="n">
-        <v>117</v>
-      </c>
-      <c r="BL56" s="27" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="BM56" s="28" t="n">
-        <v>0.460829</v>
-      </c>
-      <c r="BN56" s="28" t="n"/>
-      <c r="BO56" s="28" t="n"/>
-      <c r="BP56" s="25" t="n"/>
-      <c r="BQ56" s="27" t="n"/>
-      <c r="BR56" s="28" t="n"/>
-      <c r="BS56" s="28" t="n"/>
-      <c r="BT56" s="28" t="n"/>
-      <c r="BU56" s="25" t="n"/>
-      <c r="BV56" s="29" t="n"/>
-      <c r="BW56" s="24" t="n"/>
-      <c r="BX56" s="30" t="n"/>
-      <c r="BY56" s="27" t="n"/>
-      <c r="BZ56" s="24" t="n"/>
-      <c r="CA56" s="31" t="n"/>
-      <c r="CB56" s="24" t="n"/>
-      <c r="CC56" s="24" t="n"/>
-      <c r="CD56" s="24" t="n"/>
-      <c r="CE56" s="24" t="n"/>
-      <c r="CF56" s="24" t="n"/>
-      <c r="CG56" s="24" t="n"/>
-      <c r="CH56" s="24" t="n"/>
-      <c r="CI56" s="24" t="n"/>
-      <c r="CJ56" s="24" t="n"/>
-      <c r="CK56" s="24" t="n"/>
-      <c r="CL56" s="24" t="n"/>
-      <c r="CM56" s="24" t="n"/>
-    </row>
-    <row r="57" ht="36" customHeight="1">
-      <c r="A57" s="24" t="inlineStr">
-        <is>
-          <t>d90d48e1a8cc4623</t>
-        </is>
-      </c>
-      <c r="B57" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-23T07:20:39.530092Z</t>
-        </is>
-      </c>
-      <c r="C57" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-24T10:00:00Z</t>
-        </is>
-      </c>
-      <c r="D57" s="24" t="inlineStr">
-        <is>
-          <t>58248</t>
-        </is>
-      </c>
-      <c r="E57" s="24" t="inlineStr">
-        <is>
-          <t>CS2</t>
-        </is>
-      </c>
-      <c r="F57" s="24" t="inlineStr">
-        <is>
-          <t>3DMAX</t>
-        </is>
-      </c>
-      <c r="G57" s="24" t="inlineStr">
-        <is>
-          <t>magic</t>
-        </is>
-      </c>
-      <c r="H57" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I57" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J57" s="25" t="n"/>
-      <c r="K57" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L57" s="26" t="n">
-        <v>-138</v>
-      </c>
-      <c r="M57" s="27" t="n">
-        <v>1.724638</v>
-      </c>
-      <c r="N57" s="28" t="n">
-        <v>0.579832</v>
-      </c>
-      <c r="O57" s="28" t="n">
-        <v>0.624985</v>
-      </c>
-      <c r="P57" s="28" t="n"/>
-      <c r="Q57" s="28" t="n">
-        <v>0.045153</v>
-      </c>
-      <c r="R57" s="26" t="n">
-        <v>43</v>
-      </c>
-      <c r="S57" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T57" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="U57" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V57" s="24" t="n"/>
-      <c r="W57" s="26" t="n"/>
-      <c r="X57" s="26" t="n"/>
-      <c r="Y57" s="25" t="n"/>
-      <c r="Z57" s="26" t="n"/>
-      <c r="AA57" s="28" t="n"/>
-      <c r="AB57" s="28" t="n"/>
-      <c r="AC57" s="30" t="n"/>
-      <c r="AD57" s="24" t="n"/>
-      <c r="AE57" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-cs2-mgc-3dmax-2026-07-24).</t>
-        </is>
-      </c>
-      <c r="AF57" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG57" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH57" s="24" t="n"/>
-      <c r="AI57" s="31" t="n"/>
-      <c r="AJ57" s="31" t="n"/>
-      <c r="AK57" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL57" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM57" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN57" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO57" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LOW_EDGE</t>
-        </is>
-      </c>
-      <c r="AP57" s="24" t="inlineStr">
-        <is>
-          <t>3DMAX</t>
-        </is>
-      </c>
-      <c r="AQ57" s="24" t="inlineStr">
-        <is>
-          <t>3DMAX</t>
-        </is>
-      </c>
-      <c r="AR57" s="24" t="inlineStr">
-        <is>
-          <t>3DMAX</t>
-        </is>
-      </c>
-      <c r="AS57" s="24" t="inlineStr">
-        <is>
-          <t>magic</t>
-        </is>
-      </c>
-      <c r="AT57" s="24" t="inlineStr">
-        <is>
-          <t>magic</t>
-        </is>
-      </c>
-      <c r="AU57" s="24" t="inlineStr">
-        <is>
-          <t>magic</t>
-        </is>
-      </c>
-      <c r="AV57" s="24" t="n"/>
-      <c r="AW57" s="24" t="n"/>
-      <c r="AX57" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY57" s="24" t="n"/>
-      <c r="AZ57" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA57" s="24" t="inlineStr">
-        <is>
-          <t>48424b79d75fc1173c9c465d95feb6fc041a2ccfbc64455058b3f74905ce28d5</t>
-        </is>
-      </c>
-      <c r="BB57" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC57" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="BD57" s="24" t="inlineStr">
-        <is>
-          <t>48424b79d75fc1173c9c465d95feb6fc041a2ccfbc64455058b3f74905ce28d5</t>
-        </is>
-      </c>
-      <c r="BE57" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF57" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG57" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="BH57" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-23T07:20:31.167816Z</t>
-        </is>
-      </c>
-      <c r="BI57" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ57" s="25" t="n"/>
-      <c r="BK57" s="26" t="n">
-        <v>-138</v>
-      </c>
-      <c r="BL57" s="27" t="n">
-        <v>1.724638</v>
-      </c>
-      <c r="BM57" s="28" t="n">
-        <v>0.579832</v>
-      </c>
-      <c r="BN57" s="28" t="n"/>
-      <c r="BO57" s="28" t="n"/>
-      <c r="BP57" s="25" t="n"/>
-      <c r="BQ57" s="27" t="n"/>
-      <c r="BR57" s="28" t="n"/>
-      <c r="BS57" s="28" t="n"/>
-      <c r="BT57" s="28" t="n"/>
-      <c r="BU57" s="25" t="n"/>
-      <c r="BV57" s="29" t="n"/>
-      <c r="BW57" s="24" t="n"/>
-      <c r="BX57" s="30" t="n"/>
-      <c r="BY57" s="27" t="n"/>
-      <c r="BZ57" s="24" t="n"/>
-      <c r="CA57" s="31" t="n"/>
-      <c r="CB57" s="24" t="n"/>
-      <c r="CC57" s="24" t="n"/>
-      <c r="CD57" s="24" t="n"/>
-      <c r="CE57" s="24" t="n"/>
-      <c r="CF57" s="24" t="n"/>
-      <c r="CG57" s="24" t="n"/>
-      <c r="CH57" s="24" t="n"/>
-      <c r="CI57" s="24" t="n"/>
-      <c r="CJ57" s="24" t="n"/>
-      <c r="CK57" s="24" t="n"/>
-      <c r="CL57" s="24" t="n"/>
-      <c r="CM57" s="24" t="n"/>
-    </row>
-    <row r="58" ht="36" customHeight="1">
-      <c r="A58" s="24" t="inlineStr">
-        <is>
-          <t>3b498ded64774a56</t>
-        </is>
-      </c>
-      <c r="B58" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-23T07:20:39.530092Z</t>
-        </is>
-      </c>
-      <c r="C58" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-24T12:30:00Z</t>
-        </is>
-      </c>
-      <c r="D58" s="24" t="inlineStr">
-        <is>
-          <t>58309</t>
-        </is>
-      </c>
-      <c r="E58" s="24" t="inlineStr">
-        <is>
-          <t>CS2</t>
-        </is>
-      </c>
-      <c r="F58" s="24" t="inlineStr">
-        <is>
-          <t>TheMongolz</t>
-        </is>
-      </c>
-      <c r="G58" s="24" t="inlineStr">
-        <is>
-          <t>Heroic</t>
-        </is>
-      </c>
-      <c r="H58" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I58" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J58" s="25" t="n"/>
-      <c r="K58" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L58" s="26" t="n">
-        <v>144</v>
-      </c>
-      <c r="M58" s="27" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="N58" s="28" t="n">
-        <v>0.409836</v>
-      </c>
-      <c r="O58" s="28" t="n">
-        <v>0.633024</v>
-      </c>
-      <c r="P58" s="28" t="n"/>
-      <c r="Q58" s="28" t="n">
-        <v>0.223188</v>
-      </c>
-      <c r="R58" s="26" t="n">
-        <v>100</v>
-      </c>
-      <c r="S58" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T58" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="U58" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V58" s="24" t="n"/>
-      <c r="W58" s="26" t="n"/>
-      <c r="X58" s="26" t="n"/>
-      <c r="Y58" s="25" t="n"/>
-      <c r="Z58" s="26" t="n"/>
-      <c r="AA58" s="28" t="n"/>
-      <c r="AB58" s="28" t="n"/>
-      <c r="AC58" s="30" t="n"/>
-      <c r="AD58" s="24" t="n"/>
-      <c r="AE58" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.4100 (market_slug=aec-cs2-hero-mglz-2026-07-24).</t>
-        </is>
-      </c>
-      <c r="AF58" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG58" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH58" s="24" t="n"/>
-      <c r="AI58" s="31" t="n"/>
-      <c r="AJ58" s="31" t="n"/>
-      <c r="AK58" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL58" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM58" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN58" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO58" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LARGE_DISAGREEMENT_REVIEW</t>
-        </is>
-      </c>
-      <c r="AP58" s="24" t="inlineStr">
-        <is>
-          <t>TheMongolz</t>
-        </is>
-      </c>
-      <c r="AQ58" s="24" t="inlineStr">
-        <is>
-          <t>TheMongolz</t>
-        </is>
-      </c>
-      <c r="AR58" s="24" t="inlineStr">
-        <is>
-          <t>TheMongolz</t>
-        </is>
-      </c>
-      <c r="AS58" s="24" t="inlineStr">
-        <is>
-          <t>Heroic</t>
-        </is>
-      </c>
-      <c r="AT58" s="24" t="inlineStr">
-        <is>
-          <t>Heroic</t>
-        </is>
-      </c>
-      <c r="AU58" s="24" t="inlineStr">
-        <is>
-          <t>Heroic</t>
-        </is>
-      </c>
-      <c r="AV58" s="24" t="n"/>
-      <c r="AW58" s="24" t="n"/>
-      <c r="AX58" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY58" s="24" t="n"/>
-      <c r="AZ58" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA58" s="24" t="inlineStr">
-        <is>
-          <t>48424b79d75fc1173c9c465d95feb6fc041a2ccfbc64455058b3f74905ce28d5</t>
-        </is>
-      </c>
-      <c r="BB58" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC58" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="BD58" s="24" t="inlineStr">
-        <is>
-          <t>48424b79d75fc1173c9c465d95feb6fc041a2ccfbc64455058b3f74905ce28d5</t>
-        </is>
-      </c>
-      <c r="BE58" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF58" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG58" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="BH58" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-23T07:20:34.856171Z</t>
-        </is>
-      </c>
-      <c r="BI58" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ58" s="25" t="n"/>
-      <c r="BK58" s="26" t="n">
-        <v>144</v>
-      </c>
-      <c r="BL58" s="27" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BM58" s="28" t="n">
-        <v>0.409836</v>
-      </c>
-      <c r="BN58" s="28" t="n"/>
-      <c r="BO58" s="28" t="n"/>
-      <c r="BP58" s="25" t="n"/>
-      <c r="BQ58" s="27" t="n"/>
-      <c r="BR58" s="28" t="n"/>
-      <c r="BS58" s="28" t="n"/>
-      <c r="BT58" s="28" t="n"/>
-      <c r="BU58" s="25" t="n"/>
-      <c r="BV58" s="29" t="n"/>
-      <c r="BW58" s="24" t="n"/>
-      <c r="BX58" s="30" t="n"/>
-      <c r="BY58" s="27" t="n"/>
-      <c r="BZ58" s="24" t="n"/>
-      <c r="CA58" s="31" t="n"/>
-      <c r="CB58" s="24" t="n"/>
-      <c r="CC58" s="24" t="n"/>
-      <c r="CD58" s="24" t="n"/>
-      <c r="CE58" s="24" t="n"/>
-      <c r="CF58" s="24" t="n"/>
-      <c r="CG58" s="24" t="n"/>
-      <c r="CH58" s="24" t="n"/>
-      <c r="CI58" s="24" t="n"/>
-      <c r="CJ58" s="24" t="n"/>
-      <c r="CK58" s="24" t="n"/>
-      <c r="CL58" s="24" t="n"/>
-      <c r="CM58" s="24" t="n"/>
-    </row>
-    <row r="59" ht="36" customHeight="1">
-      <c r="A59" s="24" t="inlineStr">
-        <is>
-          <t>a2ecee09f466426a</t>
-        </is>
-      </c>
-      <c r="B59" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-23T07:21:10.371129Z</t>
-        </is>
-      </c>
-      <c r="C59" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-23T13:00:00Z</t>
-        </is>
-      </c>
-      <c r="D59" s="24" t="inlineStr">
-        <is>
-          <t>56888</t>
-        </is>
-      </c>
-      <c r="E59" s="24" t="inlineStr">
-        <is>
-          <t>DOTA2</t>
-        </is>
-      </c>
-      <c r="F59" s="24" t="inlineStr">
-        <is>
-          <t>Inner Circle x Insanity</t>
-        </is>
-      </c>
-      <c r="G59" s="24" t="inlineStr">
-        <is>
-          <t>Team Jenz</t>
-        </is>
-      </c>
-      <c r="H59" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I59" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J59" s="25" t="n"/>
-      <c r="K59" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L59" s="26" t="n">
-        <v>212</v>
-      </c>
-      <c r="M59" s="27" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="N59" s="28" t="n">
-        <v>0.320513</v>
-      </c>
-      <c r="O59" s="28" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="P59" s="28" t="n"/>
-      <c r="Q59" s="28" t="n">
-        <v>0.179487</v>
-      </c>
-      <c r="R59" s="26" t="n">
-        <v>100</v>
-      </c>
-      <c r="S59" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T59" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="U59" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V59" s="24" t="n"/>
-      <c r="W59" s="26" t="n"/>
-      <c r="X59" s="26" t="n"/>
-      <c r="Y59" s="25" t="n"/>
-      <c r="Z59" s="26" t="n"/>
-      <c r="AA59" s="28" t="n"/>
-      <c r="AB59" s="28" t="n"/>
-      <c r="AC59" s="30" t="n"/>
-      <c r="AD59" s="24" t="n"/>
-      <c r="AE59" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.3200 (market_slug=aec-dota2-tje-icxi-2026-07-23).</t>
-        </is>
-      </c>
-      <c r="AF59" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG59" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH59" s="24" t="n"/>
-      <c r="AI59" s="31" t="n"/>
-      <c r="AJ59" s="31" t="n"/>
-      <c r="AK59" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL59" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM59" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN59" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO59" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LARGE_DISAGREEMENT_REVIEW</t>
-        </is>
-      </c>
-      <c r="AP59" s="24" t="inlineStr">
-        <is>
-          <t>Inner Circle x Insanity</t>
-        </is>
-      </c>
-      <c r="AQ59" s="24" t="inlineStr">
-        <is>
-          <t>Inner Circle x Insanity</t>
-        </is>
-      </c>
-      <c r="AR59" s="24" t="inlineStr">
-        <is>
-          <t>Inner Circle x Insanity</t>
-        </is>
-      </c>
-      <c r="AS59" s="24" t="inlineStr">
-        <is>
-          <t>Team Jenz</t>
-        </is>
-      </c>
-      <c r="AT59" s="24" t="inlineStr">
-        <is>
-          <t>Team Jenz</t>
-        </is>
-      </c>
-      <c r="AU59" s="24" t="inlineStr">
-        <is>
-          <t>Team Jenz</t>
-        </is>
-      </c>
-      <c r="AV59" s="24" t="n"/>
-      <c r="AW59" s="24" t="n"/>
-      <c r="AX59" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY59" s="24" t="n"/>
-      <c r="AZ59" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA59" s="24" t="inlineStr">
-        <is>
-          <t>a799fd6b531f6a50433d392237bace95036714f80bb3516384271ef275ed7763</t>
-        </is>
-      </c>
-      <c r="BB59" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC59" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="BD59" s="24" t="inlineStr">
-        <is>
-          <t>a799fd6b531f6a50433d392237bace95036714f80bb3516384271ef275ed7763</t>
-        </is>
-      </c>
-      <c r="BE59" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF59" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG59" s="24" t="inlineStr">
-        <is>
-          <t>dota2-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="BH59" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-23T07:21:04.162632Z</t>
-        </is>
-      </c>
-      <c r="BI59" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ59" s="25" t="n"/>
-      <c r="BK59" s="26" t="n">
-        <v>212</v>
-      </c>
-      <c r="BL59" s="27" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="BM59" s="28" t="n">
-        <v>0.320513</v>
-      </c>
-      <c r="BN59" s="28" t="n"/>
-      <c r="BO59" s="28" t="n"/>
-      <c r="BP59" s="25" t="n"/>
-      <c r="BQ59" s="27" t="n"/>
-      <c r="BR59" s="28" t="n"/>
-      <c r="BS59" s="28" t="n"/>
-      <c r="BT59" s="28" t="n"/>
-      <c r="BU59" s="25" t="n"/>
-      <c r="BV59" s="29" t="n"/>
-      <c r="BW59" s="24" t="n"/>
-      <c r="BX59" s="30" t="n"/>
-      <c r="BY59" s="27" t="n"/>
-      <c r="BZ59" s="24" t="n"/>
-      <c r="CA59" s="31" t="n"/>
-      <c r="CB59" s="24" t="n"/>
-      <c r="CC59" s="24" t="n"/>
-      <c r="CD59" s="24" t="n"/>
-      <c r="CE59" s="24" t="n"/>
-      <c r="CF59" s="24" t="n"/>
-      <c r="CG59" s="24" t="n"/>
-      <c r="CH59" s="24" t="n"/>
-      <c r="CI59" s="24" t="n"/>
-      <c r="CJ59" s="24" t="n"/>
-      <c r="CK59" s="24" t="n"/>
-      <c r="CL59" s="24" t="n"/>
-      <c r="CM59" s="24" t="n"/>
-    </row>
-    <row r="60" ht="36" customHeight="1">
-      <c r="A60" s="24" t="inlineStr">
-        <is>
-          <t>4a643321b24f4278</t>
-        </is>
-      </c>
-      <c r="B60" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-23T07:21:34.143456Z</t>
-        </is>
-      </c>
-      <c r="C60" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-23T08:00:00Z</t>
-        </is>
-      </c>
-      <c r="D60" s="24" t="inlineStr">
-        <is>
-          <t>56787</t>
-        </is>
-      </c>
-      <c r="E60" s="24" t="inlineStr">
-        <is>
-          <t>VALORANT</t>
-        </is>
-      </c>
-      <c r="F60" s="24" t="inlineStr">
-        <is>
-          <t>FULL SENSE</t>
-        </is>
-      </c>
-      <c r="G60" s="24" t="inlineStr">
-        <is>
-          <t>Global Esports</t>
-        </is>
-      </c>
-      <c r="H60" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I60" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J60" s="25" t="n"/>
-      <c r="K60" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L60" s="26" t="n">
-        <v>117</v>
-      </c>
-      <c r="M60" s="27" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="N60" s="28" t="n">
-        <v>0.460829</v>
-      </c>
-      <c r="O60" s="28" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="P60" s="28" t="n"/>
-      <c r="Q60" s="28" t="n">
-        <v>0.039171</v>
-      </c>
-      <c r="R60" s="26" t="n">
-        <v>40</v>
-      </c>
-      <c r="S60" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T60" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="U60" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V60" s="24" t="n"/>
-      <c r="W60" s="26" t="n"/>
-      <c r="X60" s="26" t="n"/>
-      <c r="Y60" s="25" t="n"/>
-      <c r="Z60" s="26" t="n"/>
-      <c r="AA60" s="28" t="n"/>
-      <c r="AB60" s="28" t="n"/>
-      <c r="AC60" s="30" t="n"/>
-      <c r="AD60" s="24" t="n"/>
-      <c r="AE60" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.4600 (market_slug=aec-valorant-ge-fs-2026-07-23).</t>
-        </is>
-      </c>
-      <c r="AF60" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG60" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH60" s="24" t="n"/>
-      <c r="AI60" s="31" t="n"/>
-      <c r="AJ60" s="31" t="n"/>
-      <c r="AK60" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL60" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM60" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN60" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO60" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LOW_EDGE</t>
-        </is>
-      </c>
-      <c r="AP60" s="24" t="inlineStr">
-        <is>
-          <t>FULL SENSE</t>
-        </is>
-      </c>
-      <c r="AQ60" s="24" t="inlineStr">
-        <is>
-          <t>FULL SENSE</t>
-        </is>
-      </c>
-      <c r="AR60" s="24" t="inlineStr">
-        <is>
-          <t>FULL SENSE</t>
-        </is>
-      </c>
-      <c r="AS60" s="24" t="inlineStr">
-        <is>
-          <t>Global Esports</t>
-        </is>
-      </c>
-      <c r="AT60" s="24" t="inlineStr">
-        <is>
-          <t>Global Esports</t>
-        </is>
-      </c>
-      <c r="AU60" s="24" t="inlineStr">
-        <is>
-          <t>Global Esports</t>
-        </is>
-      </c>
-      <c r="AV60" s="24" t="n"/>
-      <c r="AW60" s="24" t="n"/>
-      <c r="AX60" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY60" s="24" t="n"/>
-      <c r="AZ60" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA60" s="24" t="inlineStr">
-        <is>
-          <t>df5a226c64918a54c70b8af3e0cd4abb6c4f42b67acb5547da319458502b0ed4</t>
-        </is>
-      </c>
-      <c r="BB60" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC60" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="BD60" s="24" t="inlineStr">
-        <is>
-          <t>df5a226c64918a54c70b8af3e0cd4abb6c4f42b67acb5547da319458502b0ed4</t>
-        </is>
-      </c>
-      <c r="BE60" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF60" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG60" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="BH60" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-23T07:21:16.291113Z</t>
-        </is>
-      </c>
-      <c r="BI60" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ60" s="25" t="n"/>
-      <c r="BK60" s="26" t="n">
-        <v>117</v>
-      </c>
-      <c r="BL60" s="27" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="BM60" s="28" t="n">
-        <v>0.460829</v>
-      </c>
-      <c r="BN60" s="28" t="n"/>
-      <c r="BO60" s="28" t="n"/>
-      <c r="BP60" s="25" t="n"/>
-      <c r="BQ60" s="27" t="n"/>
-      <c r="BR60" s="28" t="n"/>
-      <c r="BS60" s="28" t="n"/>
-      <c r="BT60" s="28" t="n"/>
-      <c r="BU60" s="25" t="n"/>
-      <c r="BV60" s="29" t="n"/>
-      <c r="BW60" s="24" t="n"/>
-      <c r="BX60" s="30" t="n"/>
-      <c r="BY60" s="27" t="n"/>
-      <c r="BZ60" s="24" t="n"/>
-      <c r="CA60" s="31" t="n"/>
-      <c r="CB60" s="24" t="n"/>
-      <c r="CC60" s="24" t="n"/>
-      <c r="CD60" s="24" t="n"/>
-      <c r="CE60" s="24" t="n"/>
-      <c r="CF60" s="24" t="n"/>
-      <c r="CG60" s="24" t="n"/>
-      <c r="CH60" s="24" t="n"/>
-      <c r="CI60" s="24" t="n"/>
-      <c r="CJ60" s="24" t="n"/>
-      <c r="CK60" s="24" t="n"/>
-      <c r="CL60" s="24" t="n"/>
-      <c r="CM60" s="24" t="n"/>
-    </row>
-    <row r="61" ht="36" customHeight="1">
-      <c r="A61" s="24" t="inlineStr">
-        <is>
-          <t>e0b7f3e51a944d45</t>
-        </is>
-      </c>
-      <c r="B61" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-23T07:21:34.143456Z</t>
-        </is>
-      </c>
-      <c r="C61" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-23T15:00:00Z</t>
-        </is>
-      </c>
-      <c r="D61" s="24" t="inlineStr">
-        <is>
-          <t>56966</t>
-        </is>
-      </c>
-      <c r="E61" s="24" t="inlineStr">
-        <is>
-          <t>VALORANT</t>
-        </is>
-      </c>
-      <c r="F61" s="24" t="inlineStr">
-        <is>
-          <t>Team Heretics</t>
-        </is>
-      </c>
-      <c r="G61" s="24" t="inlineStr">
-        <is>
-          <t>Eternal Fire</t>
-        </is>
-      </c>
-      <c r="H61" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I61" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J61" s="25" t="n"/>
-      <c r="K61" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L61" s="26" t="n">
-        <v>144</v>
-      </c>
-      <c r="M61" s="27" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="N61" s="28" t="n">
-        <v>0.409836</v>
-      </c>
-      <c r="O61" s="28" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="P61" s="28" t="n"/>
-      <c r="Q61" s="28" t="n">
-        <v>0.09016399999999999</v>
-      </c>
-      <c r="R61" s="26" t="n">
-        <v>65</v>
-      </c>
-      <c r="S61" s="29" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="T61" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="U61" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V61" s="24" t="n"/>
-      <c r="W61" s="26" t="n"/>
-      <c r="X61" s="26" t="n"/>
-      <c r="Y61" s="25" t="n"/>
-      <c r="Z61" s="26" t="n"/>
-      <c r="AA61" s="28" t="n"/>
-      <c r="AB61" s="28" t="n"/>
-      <c r="AC61" s="30" t="n"/>
-      <c r="AD61" s="24" t="n"/>
-      <c r="AE61" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.4100 (market_slug=aec-valorant-ef-th-2026-07-23).</t>
-        </is>
-      </c>
-      <c r="AF61" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG61" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH61" s="24" t="n"/>
-      <c r="AI61" s="31" t="n"/>
-      <c r="AJ61" s="31" t="n"/>
-      <c r="AK61" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL61" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM61" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN61" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO61" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP61" s="24" t="inlineStr">
-        <is>
-          <t>Team Heretics</t>
-        </is>
-      </c>
-      <c r="AQ61" s="24" t="inlineStr">
-        <is>
-          <t>Team Heretics</t>
-        </is>
-      </c>
-      <c r="AR61" s="24" t="inlineStr">
-        <is>
-          <t>Team Heretics</t>
-        </is>
-      </c>
-      <c r="AS61" s="24" t="inlineStr">
-        <is>
-          <t>Eternal Fire</t>
-        </is>
-      </c>
-      <c r="AT61" s="24" t="inlineStr">
-        <is>
-          <t>Eternal Fire</t>
-        </is>
-      </c>
-      <c r="AU61" s="24" t="inlineStr">
-        <is>
-          <t>Eternal Fire</t>
-        </is>
-      </c>
-      <c r="AV61" s="24" t="n"/>
-      <c r="AW61" s="24" t="n"/>
-      <c r="AX61" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY61" s="24" t="n"/>
-      <c r="AZ61" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA61" s="24" t="inlineStr">
-        <is>
-          <t>df5a226c64918a54c70b8af3e0cd4abb6c4f42b67acb5547da319458502b0ed4</t>
-        </is>
-      </c>
-      <c r="BB61" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC61" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="BD61" s="24" t="inlineStr">
-        <is>
-          <t>df5a226c64918a54c70b8af3e0cd4abb6c4f42b67acb5547da319458502b0ed4</t>
-        </is>
-      </c>
-      <c r="BE61" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF61" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG61" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="BH61" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-23T07:21:21.528202Z</t>
-        </is>
-      </c>
-      <c r="BI61" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ61" s="25" t="n"/>
-      <c r="BK61" s="26" t="n">
-        <v>144</v>
-      </c>
-      <c r="BL61" s="27" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BM61" s="28" t="n">
-        <v>0.409836</v>
-      </c>
-      <c r="BN61" s="28" t="n"/>
-      <c r="BO61" s="28" t="n"/>
-      <c r="BP61" s="25" t="n"/>
-      <c r="BQ61" s="27" t="n"/>
-      <c r="BR61" s="28" t="n"/>
-      <c r="BS61" s="28" t="n"/>
-      <c r="BT61" s="28" t="n"/>
-      <c r="BU61" s="25" t="n"/>
-      <c r="BV61" s="29" t="n"/>
-      <c r="BW61" s="24" t="n"/>
-      <c r="BX61" s="30" t="n"/>
-      <c r="BY61" s="27" t="n"/>
-      <c r="BZ61" s="24" t="n"/>
-      <c r="CA61" s="31" t="n"/>
-      <c r="CB61" s="24" t="n"/>
-      <c r="CC61" s="24" t="n"/>
-      <c r="CD61" s="24" t="n"/>
-      <c r="CE61" s="24" t="n"/>
-      <c r="CF61" s="24" t="n"/>
-      <c r="CG61" s="24" t="n"/>
-      <c r="CH61" s="24" t="n"/>
-      <c r="CI61" s="24" t="n"/>
-      <c r="CJ61" s="24" t="n"/>
-      <c r="CK61" s="24" t="n"/>
-      <c r="CL61" s="24" t="n"/>
-      <c r="CM61" s="24" t="n"/>
-    </row>
-    <row r="62" ht="36" customHeight="1">
-      <c r="A62" s="24" t="inlineStr">
-        <is>
-          <t>2a13950c7f3c4575</t>
-        </is>
-      </c>
-      <c r="B62" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-23T07:21:34.143456Z</t>
-        </is>
-      </c>
-      <c r="C62" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-23T18:00:00Z</t>
-        </is>
-      </c>
-      <c r="D62" s="24" t="inlineStr">
-        <is>
-          <t>57151</t>
-        </is>
-      </c>
-      <c r="E62" s="24" t="inlineStr">
-        <is>
-          <t>VALORANT</t>
-        </is>
-      </c>
-      <c r="F62" s="24" t="inlineStr">
-        <is>
-          <t>Twisted Minds Orchid</t>
-        </is>
-      </c>
-      <c r="G62" s="24" t="inlineStr">
-        <is>
-          <t>GIANTX GC</t>
-        </is>
-      </c>
-      <c r="H62" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I62" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J62" s="25" t="n"/>
-      <c r="K62" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L62" s="26" t="n">
-        <v>144</v>
-      </c>
-      <c r="M62" s="27" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="N62" s="28" t="n">
-        <v>0.409836</v>
-      </c>
-      <c r="O62" s="28" t="n">
-        <v>0.5043260000000001</v>
-      </c>
-      <c r="P62" s="28" t="n"/>
-      <c r="Q62" s="28" t="n">
-        <v>0.09449</v>
-      </c>
-      <c r="R62" s="26" t="n">
-        <v>67</v>
-      </c>
-      <c r="S62" s="29" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="T62" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="U62" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V62" s="24" t="n"/>
-      <c r="W62" s="26" t="n"/>
-      <c r="X62" s="26" t="n"/>
-      <c r="Y62" s="25" t="n"/>
-      <c r="Z62" s="26" t="n"/>
-      <c r="AA62" s="28" t="n"/>
-      <c r="AB62" s="28" t="n"/>
-      <c r="AC62" s="30" t="n"/>
-      <c r="AD62" s="24" t="n"/>
-      <c r="AE62" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.4100 (market_slug=aec-valorant-gxgc-tmo-2026-07-23).</t>
-        </is>
-      </c>
-      <c r="AF62" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG62" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH62" s="24" t="n"/>
-      <c r="AI62" s="31" t="n"/>
-      <c r="AJ62" s="31" t="n"/>
-      <c r="AK62" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL62" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM62" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN62" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO62" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP62" s="24" t="inlineStr">
-        <is>
-          <t>Twisted Minds Orchid</t>
-        </is>
-      </c>
-      <c r="AQ62" s="24" t="inlineStr">
-        <is>
-          <t>Twisted Minds Orchid</t>
-        </is>
-      </c>
-      <c r="AR62" s="24" t="inlineStr">
-        <is>
-          <t>Twisted Minds Orchid</t>
-        </is>
-      </c>
-      <c r="AS62" s="24" t="inlineStr">
-        <is>
-          <t>GIANTX GC</t>
-        </is>
-      </c>
-      <c r="AT62" s="24" t="inlineStr">
-        <is>
-          <t>GIANTX GC</t>
-        </is>
-      </c>
-      <c r="AU62" s="24" t="inlineStr">
-        <is>
-          <t>GIANTX GC</t>
-        </is>
-      </c>
-      <c r="AV62" s="24" t="n"/>
-      <c r="AW62" s="24" t="n"/>
-      <c r="AX62" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY62" s="24" t="n"/>
-      <c r="AZ62" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA62" s="24" t="inlineStr">
-        <is>
-          <t>df5a226c64918a54c70b8af3e0cd4abb6c4f42b67acb5547da319458502b0ed4</t>
-        </is>
-      </c>
-      <c r="BB62" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC62" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="BD62" s="24" t="inlineStr">
-        <is>
-          <t>df5a226c64918a54c70b8af3e0cd4abb6c4f42b67acb5547da319458502b0ed4</t>
-        </is>
-      </c>
-      <c r="BE62" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF62" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG62" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="BH62" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-23T07:21:22.385691Z</t>
-        </is>
-      </c>
-      <c r="BI62" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ62" s="25" t="n"/>
-      <c r="BK62" s="26" t="n">
-        <v>144</v>
-      </c>
-      <c r="BL62" s="27" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BM62" s="28" t="n">
-        <v>0.409836</v>
-      </c>
-      <c r="BN62" s="28" t="n"/>
-      <c r="BO62" s="28" t="n"/>
-      <c r="BP62" s="25" t="n"/>
-      <c r="BQ62" s="27" t="n"/>
-      <c r="BR62" s="28" t="n"/>
-      <c r="BS62" s="28" t="n"/>
-      <c r="BT62" s="28" t="n"/>
-      <c r="BU62" s="25" t="n"/>
-      <c r="BV62" s="29" t="n"/>
-      <c r="BW62" s="24" t="n"/>
-      <c r="BX62" s="30" t="n"/>
-      <c r="BY62" s="27" t="n"/>
-      <c r="BZ62" s="24" t="n"/>
-      <c r="CA62" s="31" t="n"/>
-      <c r="CB62" s="24" t="n"/>
-      <c r="CC62" s="24" t="n"/>
-      <c r="CD62" s="24" t="n"/>
-      <c r="CE62" s="24" t="n"/>
-      <c r="CF62" s="24" t="n"/>
-      <c r="CG62" s="24" t="n"/>
-      <c r="CH62" s="24" t="n"/>
-      <c r="CI62" s="24" t="n"/>
-      <c r="CJ62" s="24" t="n"/>
-      <c r="CK62" s="24" t="n"/>
-      <c r="CL62" s="24" t="n"/>
-      <c r="CM62" s="24" t="n"/>
-    </row>
-    <row r="63" ht="36" customHeight="1">
-      <c r="A63" s="24" t="inlineStr">
-        <is>
-          <t>5d0f3f7a2dcb4750</t>
-        </is>
-      </c>
-      <c r="B63" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-23T07:21:34.143456Z</t>
-        </is>
-      </c>
-      <c r="C63" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-23T18:00:00Z</t>
-        </is>
-      </c>
-      <c r="D63" s="24" t="inlineStr">
-        <is>
-          <t>57153</t>
-        </is>
-      </c>
-      <c r="E63" s="24" t="inlineStr">
-        <is>
-          <t>VALORANT</t>
-        </is>
-      </c>
-      <c r="F63" s="24" t="inlineStr">
-        <is>
-          <t>Natus Vincere</t>
-        </is>
-      </c>
-      <c r="G63" s="24" t="inlineStr">
-        <is>
-          <t>Gentle Mates</t>
-        </is>
-      </c>
-      <c r="H63" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I63" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J63" s="25" t="n"/>
-      <c r="K63" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L63" s="26" t="n">
-        <v>-113</v>
-      </c>
-      <c r="M63" s="27" t="n">
-        <v>1.884956</v>
-      </c>
-      <c r="N63" s="28" t="n">
-        <v>0.530516</v>
-      </c>
-      <c r="O63" s="28" t="n">
-        <v>0.681625</v>
-      </c>
-      <c r="P63" s="28" t="n"/>
-      <c r="Q63" s="28" t="n">
-        <v>0.151109</v>
-      </c>
-      <c r="R63" s="26" t="n">
-        <v>100</v>
-      </c>
-      <c r="S63" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T63" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v3</t>
-        </is>
-      </c>
-      <c r="U63" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V63" s="24" t="n"/>
-      <c r="W63" s="26" t="n"/>
-      <c r="X63" s="26" t="n"/>
-      <c r="Y63" s="25" t="n"/>
-      <c r="Z63" s="26" t="n"/>
-      <c r="AA63" s="28" t="n"/>
-      <c r="AB63" s="28" t="n"/>
-      <c r="AC63" s="30" t="n"/>
-      <c r="AD63" s="24" t